--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>America’s Cup – Five teams to contest the Louis Vuitton 38th America’s Cup in Naples - Sailweb</t>
+          <t>alfani Calvin Klein Performance Women's Logo Half-Zip Cozy Fleece Sweatshirt Women's Fashion Shoes &amp; Accessories Hot Sale | Clothing - Backseat Mafia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:35:25 GMT</t>
+          <t>Mon, 22 Dec 2025 18:37:59 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNdVJNS1BCNngxRkpmcjFNdUpmajN1RW0wcGtOcE9SRjBPVjYwa1hUUlU1UTR0RXFTV0dzcU1hQm53ckxmY2xOd2N4Q1Q5d25vaWxJd2gxWURqMEpiYndGTmxnQ1RhWldaLTltdjFHMVlYVy02NXlJNU9FYnhWTUxKTm1Md0MtSG9oa291di04Y2d0VDhVNFRvdTlLRWtZVFVJZHVUYUswY1pDWlRvZnpINlBuV3V4b0lha2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9Uc0JlYUVzdVhpX1pVSE1fX2VmMWJ0c2lad2x4aFJtRWp1cDIwaGhITFpxV2h5Q1lFTTFSQnBJc2VWM09qM0pEY0tVOHBPTWc2NVE?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46013.48292824074</v>
+        <v>46013.77637731482</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>When stores become destinations: Louis Vuitton’s Beijing vision - Jing Daily</t>
+          <t>Why Ralph Lauren Paint Colors Have "Enduring Appeal" - Livingetc</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:54:36 GMT</t>
+          <t>Tue, 23 Dec 2025 06:30:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPWE14VWdvM055cmd5ZEJ4cVM4Y1RIZXdpdmZ4T0N6NEcxdE1iTGFnN2RMVnN0SlBfaGIyVmdhVEF6QXZFWUVkVnVOYl9SMWtsZmJOczhCU0VJbTZnVDI0VUtXUUt2a2J1d2lDS0VKdDUzMkRRWUpTTTM3WjhjcXF6dWhxUEQyUkJid1Jma0RuLW80eEow?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9nUndZeWZlZnJNbGYxcWlVMjh1NDFqeGtjUk9OTERBTjVsTTBUQVJOLUJxZG5BdjVTVno2N3pMOWR1aExJMHE5QXRsN2o1MjdDcllBaTFsbWZrUnpQeXBHT2lvVG5TbzV5U0E?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46013.45458333333</v>
+        <v>46014.27083333334</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Valentino Returns to Rome for Their Fall/Winter 2027 Show - L'Officiel Singapore</t>
+          <t>Elizabeth Hurley reveals her Ralph Lauren sweater is older than lookalike son Damian, 23, as she slips back into the stylish look for a festive snap - Daily Mail</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:56:41 GMT</t>
+          <t>Tue, 23 Dec 2025 00:40:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT0NYZEV0WENWaGJZeHdjMTV0NEhFUF93MTF0Nl9zY3pjYWNGOWsxS0l4eDZWaC00UHZPdkJUMUVGalhfcE01TTRURHRhT2VLQTg4U0REcU0taUxFTzFZMXctblhab0pRbkxRZnc3SUtLY01zSHl0cjJWMmFuY2dSTmlROW5HTzUySVYweTN3aHBrX2VOOHRfdjNpNllENDIxRjE2RXYyX1RYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQY2cyZ1hlQzRsRzJWWHloTHVtUGZkTElkWkNPZ1locXhQcWIxR3BhODAtRmNNZC1MT296V2xRbjAzWUs3OVRqN1B6c1pfc2ltMnVrUG1PbEFYcE93TkNaeHF3YWFlVnl5RHZCRVZKekpMb1gyMGdaa0E2U1ZRbzV2OWxXU0pjS01fRE10UkhiSDJJNExBN09iS21nMG9mUjEtTDFGTmlCaHNuaTJzZEJmM0pWOGPSAboBQVVfeXFMT2JRaV9QTGtZaVIxSG5ISEFjQS1jOW5DalFVVG4zQXlZMWZQMU1mN3RtZEtmVDFfWmwtcHRaXy1RM1ZQemI4ZVl3VkZEeWVxVEJxNGJfdmVYMDVwU3ZOcElDVERhbzRxYnVsTi0wMEhGY3E5UEh1MjJndTM5UE0wQzVvTkdpSGpVQlI3VXpGQVBWQ3Z2RFRMcUVCUVZMSmNzZGxQVlFZMFJ3d2hqYndfZHkwZGRIeE9GUGtn?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46013.37269675926</v>
+        <v>46014.02777777778</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dior Fine Jewelry Editorial - Savoir Flair</t>
+          <t>Jisoo, Anya Taylor-Joy and Willow Smith to Front Dior Addict Scents - WWD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:33:35 GMT</t>
+          <t>Mon, 22 Dec 2025 13:01:44 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMEsxMzJIWndoSWlmOFFzaFZCTm1aWEdLd21TWThQZlJuZVZ3aG9DZU9WOWN4VFZYWFFOX3hYSnl2WEJTdjFYZFpVd0MwY1pVUk4zS3ZucWd4b2lBNnU0XzNuVkJ6c1pnXzd3QVJDSjB0c1NZdFVuc0doLVU1bXhwcmZUMVNTejlfcDVIN1pOcFhzeEJiVkNvRm92NkYyeTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQT1dkRmtLSnlLcjd1RjZlQ0dsaWQ0NGVNdFZ5ZVA3RnU4dldOY1U5TGRhT0ZQUWZrajBTSGpxdHNHMTB1YmtTeDd5d2NVN3ZLbExqb1ZxZTBIZE9uRFl2YkxrM182WUtWbVlIYW43XzVjNFBMNHRDX1diVmNWak9fYUFXaExlWWpZZjJwVEc3MEdkTVBTY3Zic3R0WE9reEthMXV1d2czODFpVkFEUEl6c0FCank2T0lUWmhFUDFwckJQZw?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46013.52332175926</v>
+        <v>46013.54287037037</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sound the Alarm—Armani Beauty Tweaked the Iconic Luminous Silk Foundation - Marie Claire</t>
+          <t>LVMH opens Seoul flagship dubbed Louis Vuitton’s Visionary Journeys - Inside Retail Asia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 02:19:41 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNN0lwR2c1WWdxREx4YVk3VUZDTEV1aUZ6X2UyMUpUZjVDZ2JGRzBjMW1EblhCOW5UaGVtbUVkc1hweWNEc253OFg2VnlNampWSlBCVlVHRzYwQzh1ZFNZWjZ0WHRZRVN6TkI5dUlHVjdMaWRXSV9PTWx0V1hzZjBiYll1Yk5OMXl0NDh4bnZsNjFMbUdaaDE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQd0dwVVZmUk1zZThlQ19yR2hEY0VibXc1RHZtTWZoblNlMERSa2JlOVFxYmNyaWhmeHR0NTZfU1RLMXlaanpaOGI2ZmRzaUcwUmtVYUx1MmYxdGRqbndVZ3FhV0Q3ZnZaS2J6ZzU3cEpQZGVRQjJBSG9iUndXNkVBV0xuTm9iYlV5T3VEbHdsYjdoTHJFU0hsbDRiN09lZVpkc0pYMTRBdw?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46013.45833333334</v>
+        <v>46014.09700231482</v>
       </c>
     </row>
     <row r="7">
@@ -647,24 +647,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Art and Architecture in Flux: Fondation Cartier’s New Home - Prestige Hong Kong</t>
+          <t>Not Fair Isle, Not Argyle - This Is The Knitwear Trend We're Actually Wearing This Winter - Grazia Daily UK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 01:19:00 GMT</t>
+          <t>Mon, 22 Dec 2025 14:26:52 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOWVRrU0FYbVhYbnJFTDVLZU9vV1AxS25PZTRIREZ6WWJnc09XQWVsQWktdXFiVnFYM2RDWXMxZFQ4b2czX0hrZ3QyMVdqdUgzMGxFNjRpNzk2T0c5UmZGa3NEX0k0VlFxRWgyZEtITFR1ekU4a2R0ZXJKczJ4MnYxYVpGc3VFQ2dpNDRpa3RvZWVjOURhSFZlVUJvLWJJZFN4cHllVUpyMEU3bFVSbVlIaFE4dnVrczYtd2tPOEpR0gHDAUFVX3lxTE9KcUw0R3ZSams5MWZHZ1VSMDVJTVVaRkI5Nl9sZkN3akNhRnFJWUt6RFVuRzZTSlRVMmJOT3ZHcFlZZTZsd1BBVEc3ZktwMUxfd3Y5dmhyY3BKTWtmZXFJVXZ5MkZZS3lsUmhobW53T01qZE5DcGxsZDNjNl9ILUFwRHdEQngzSTlmTUMxa1dlTklBa19PbHV5d1JUcDZ1QmdMdUZERndGTlFud2FvYllLbUhXNy1CQTEya2NmMUlfR000QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPVWowWFBITTQ3RDdOUnVGaHphaHU4SHZwQjlXLWIzV0xTR2xxLWp6UGdwSFZjV0dqZ001R0xkRGJGclN4TmRiOVc4MUp5V3BMWF90VlpkVUNjWUdtM3YyaHB2VDNYNmVfcFRDcEdJeXF6Ny1Qc3RLU1RyTFRVa21VRmhBSS1SMkZJX3B6ZA?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46013.05486111111</v>
+        <v>46013.60199074074</v>
       </c>
     </row>
     <row r="8">
@@ -680,24 +680,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The 2026 Kings' Cake by Louis Vuitton designed by Maxime Frédéric: hazelnuts elevated through the iconic Monogram - Sortir à Paris</t>
+          <t>America’s Cup – Five teams to contest the Louis Vuitton 38th America’s Cup in Naples - Sailweb</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:35:36 GMT</t>
+          <t>Mon, 22 Dec 2025 11:35:25 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQdTNZLUFJNHR1MEtLb2RhbmI2WGVRalgyajVGZjc1am9ZeXB2U04ySUkwWnphaXAwaDVnU2UtWTdVLW1TdGVJUXA5dHFQaHZfZGN0aGR0UFNWaWhaT0tMSVV2YlV4U1Q0ZDVMZnRCTUtFZmV6QVFXdnR5My0zaFlWa191SS1hMGpsY05GNnVrZHdwRm93OHVJeGxKaEVvakt3N0tmYlN6WWRaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNdVJNS1BCNngxRkpmcjFNdUpmajN1RW0wcGtOcE9SRjBPVjYwa1hUUlU1UTR0RXFTV0dzcU1hQm53ckxmY2xOd2N4Q1Q5d25vaWxJd2gxWURqMEpiYndGTmxnQ1RhWldaLTltdjFHMVlYVy02NXlJNU9FYnhWTUxKTm1Md0MtSG9oa291di04Y2d0VDhVNFRvdTlLRWtZVFVJZHVUYUswY1pDWlRvZnpINlBuV3V4b0lha2c?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46013.52472222222</v>
+        <v>46013.48292824074</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Who is Coty's new interim CEO? - Reuters</t>
+          <t>Festive home games must-win for Gillingham, says the skipper - Kent Online</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:22:07 GMT</t>
+          <t>Tue, 23 Dec 2025 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9FRjVuOTYxamM2bUFfOUFYcmktZGM1RmlyU2hTSkEyd1RZTWZ5N2NCU05FWDNucFdLV1VFMEpFb3NhMFoza29rdFdXeHhoc1lObDNrbnN6Q212ZUpOVUxPd2FDTC1hWkwyS2JTMGRmVUdRN1pTTkpUaTZ3eF9JQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPMWd2dlNqQm5sdno2TU1laWpOb2dCTjRmQVlhNWRUYUxISEdUcDlzelQzeUdFV0NNUnNCNTBoLU5lVHl2dXY1dTZNeE03RWk2cG5TbTZiS3pWbmlnUWk3Tm96bmtsRGhrbzR4Rm1hRFg2am5EYVcyc09rbmd0TFYxVm5aVkp6TVEtcWIwZlJZc1JIX3R6SVNZVzBQeEJWakY5dE03dU1MM2lqSkhJcGc?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46013.47369212963</v>
+        <v>46014.20833333334</v>
       </c>
     </row>
     <row r="10">
@@ -746,24 +746,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Two Spirit Airlines staff face charges over theft of passenger’s $500 Louis Vuitton bag - The Independent</t>
+          <t>No. 10: MotoGP Great Valentino Rossi Adds Four-Wheeled Win at IMS - Indianapolis Motor Speedway</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:30:00 GMT</t>
+          <t>Mon, 22 Dec 2025 21:50:59 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPdVQ2Qk81LUlzSWRZNW51azhxSjNNTW5tZlBxOFg0N1lXVlZ5UmUzSGlGcDdwMXZfOEhDMUFpYmdGZ1V6clFuaVhkdXIyWDhXWjFhWFhOTS1WQnQ5Nmh0Ry1qTVJ5WlJmX3ZKSF9rSW1TOVJ4SjNsalhZdEhQb3h4MlVyek80dzFvS0NocXpEQXhuY01JaVkyNExlYWVpMU1nZ1hLNTVqUHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOR0c3QU4zUjdITnJwaE96Wnh6Z0NneEVLUG4xc0E1VlBOTmt2QmhyTFluaXZKWExBTFFZb1lvQXFTQmVpNkIzRm5tWkNQYWV0QkNqenlkQ0k5eE9sT2JNNGFleGVvSXE2UmdScjRVcmJFNHlLanJKeWhKUEtnWkRMZUdTd29XYlBRUUJEb3EzdzY5UGRITzZsTkI2YXdTZw?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46012.6875</v>
+        <v>46013.9104050926</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Think It's Too Late to Buy Ralph Lauren Stock? Here's the 1 Reason Why There's Still Time. - The Motley Fool</t>
+          <t>Style File: Orm Kornnaphat - Vogue Hong Kong</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 04:47:00 GMT</t>
+          <t>Tue, 23 Dec 2025 03:57:33 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObEk4SmIyTVRLN1hNT3dBVXVISXBwT3NpQlJIUUoxU1JWaHRYZnBYaHVJMHUzYUlvbWhtSEZfUjZ3eU9RLWxBczRHYTJ3SkFlRFo4S19DMFNRRFpOVTRXUXZLQzZnZXgwamxPWnZTcVNSWE5zT3V0b18tR1E4NXhaQzlEcVg5dzQ4UE9KZ0lJZG9sdmxqMWRJSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1za0dLSE0xVVZ0UWxHMG9RekliTmNSbnZXMktzX0FTQ0FwMmlOZmlPOTFIWGMycVhCc3NIblhBc2NiVFNSYUZLM3YtSzdzb3Z3QWRBcGFaYVFuaThnQ1hJOVU3bE9iazJQWnZ3OEF0S2plMmRHeUd3V19GRQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46013.19930555556</v>
+        <v>46014.16496527778</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A tale of two Ralphs — Lauren and the supermarket — shows the reality of a K-shaped economy - MSN</t>
+          <t>Customs Seizes Hundreds of Fake Rolex, Cartier Watches - nationaljeweler.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:33:13 GMT</t>
+          <t>Mon, 22 Dec 2025 15:45:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxNb1BZM3pVakd0MzEwamtITEl5UGhmMUZhV2VWRElWeUhDMUFrSUxON0xfR3FrMmZvTzMxVFpYMHJwbExVaFdTOVNGSmNNRDNRSVZhejZZS1hkalU0X2h6eklnYl90NXdDR3RWTFFnOWtqbEdZWmRrS3JwVzFwRmhsNU9OOGFYT28zOHJ5XzNBUXlkQkZWNHlRLWhoMENCNnVvSXpodGxDRzFGdmJsLXNzNmxPeGRvTm03SjJFM0thbkNfRnl1UEpFNG1kZThXcF9oNU5ncms3ZjE1QnV6OGpkU1dVNFRwUmY1N2dpR29Vci1pQTVTZWIyTmdtcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPa2JTaTZVWkJpbl96MkFIY2FWWTBoTGpTZC1jTkRGa0N1S1BQZUR6Tm5GU3g0UlU2TExMa1hidHViS1lkcHV5RW9mWUJxSzZaLTcwMFRFYnF3SmdqazFjSmhuQTRVVjl3UUVXZ00tVWxRN2hfNnZXbFlfbnF0OGUyeTRMcU5KbkZQb3E0RE9VWnhXM3I1dFFBM3Nwa2c?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46013.48140046297</v>
+        <v>46013.65625</v>
       </c>
     </row>
     <row r="13">
@@ -845,24 +845,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonathan Anderson gives Dior’s everyday wardrobe a bold new twist for Pre-Fall 2026 - Times of India</t>
+          <t>Sound the Alarm—Armani Beauty Tweaked the Iconic Luminous Silk Foundation - Marie Claire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:00:00 GMT</t>
+          <t>Mon, 22 Dec 2025 11:00:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxQbHE2ck00cFdsVEM3MmxJLVBMSW9ldzJKSElHMlA0RWVkVks2elRxdjZVLWljM1poWUI4c2t5Y3h5RzJ0Nm1KcHlMZXcwRlViRXdsR0hWTHowM01Ta3Fld2ZUbmV0Mk9IbzhtT2M4RGNqZzBzY2VtcHZud1NXcHJYRnQ0SG52VnNTcUtoSDJITS1mRUE4dEVsQkxqeUQyeFAtV29tX2hqZ3dIc0tLcUZMRkZXSFlwWTdUeUVhWWp3TklQa2RmTWdzRTZuSFg2T3h0d29fdGF6UmNCTzVhNUxQRVIzbTMxYVF6b1RidEt1dGFJNWhCQmR6SlZBWVZwN3NERWlF0gGIAkFVX3lxTFBNS1BtV1NHM1VCT1NXbjVuNjlyRkhjd0hGRFdyMEowQzBzek1PRWtTbVNjaVZXcnR3d2o2S2NoSHlwNmo2RE4wUkVIMFRBUWhnZmZmSXZCRjdhcUx6MUNDMkpIVENWSFktLWRIWUdsTElKelk3MVROckI5dW15clVmektFS2tqQjkxWmdHRzR2c3pUYmRpVUFRV0llYmwzNkJMRkZ4U09Wd0lPYVZNeks5MTRCelp5QXFQY0M3T2I4dkFDWm44NGtqUUc1djdXUUZMd1JyeWY4WHNyS3plaW9SUmlqckppX0tWc2hJcnZ3ZnZvQVRxZnNXRXpySFQwNEtBNTQ0UXhfUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNN0lwR2c1WWdxREx4YVk3VUZDTEV1aUZ6X2UyMUpUZjVDZ2JGRzBjMW1EblhCOW5UaGVtbUVkc1hweWNEc253OFg2VnlNampWSlBCVlVHRzYwQzh1ZFNZWjZ0WHRZRVN6TkI5dUlHVjdMaWRXSV9PTWx0V1hzZjBiYll1Yk5OMXl0NDh4bnZsNjFMbUdaaDE0?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46013.5</v>
+        <v>46013.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -878,24 +878,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Louis Vuitton’s ship to nowhere marks the new age of luxury - MSN</t>
+          <t>A-List Beauty Ambassador Campaigns - Trend Hunter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 14:45:23 GMT</t>
+          <t>Tue, 23 Dec 2025 04:47:47 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE84WU9xQlZMOGJBSUFkX1Vod1d2VDJHckFkc0pkcFZNNUdidXN3OERod0xLcXBreUpIRERLQXRrVzgwcl9wbXBLVzJXYlJPWk15ZnlTVlRtNnJqME15RWxaN0tqcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE01QlFNZFZTaXR3VjFIaXF5WGlfRjF5R0xjVjd3bmlzX19pUFIyLWdtWHl5azdTRnV6T0czMGZESU5ROF8yd3poamNLRmpCTkswcVRpbzhHOUxPSHJRaWw4WkNGb2d4ZGNBc19vSHNGd9IBdEFVX3lxTFBmRVpIZG1RN0tCWHpYdm1lRVZDNnBaZDk0WmR2TTBNOWJHTEFHcWQ1MDJzOTgtaDdtaGt3dkxvRklSVjExNWNNb1QzSlZmc1dtTkIyeUw5Y3dqUXBvdTRMamFmWDJfblVNUVN1STQ1dHF1UlVU?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46012.61484953704</v>
+        <v>46014.19984953704</v>
       </c>
     </row>
     <row r="15">
@@ -911,24 +911,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Woman Finds Rs 1.4 Lakh Louis Vuitton Bag While Picking Garbage In Affluent Neighbourhood - NDTV</t>
+          <t>Ralph Lauren Was Always Cool. Now Gen Z Knows Why. - The Wall Street Journal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 04:19:07 GMT</t>
+          <t>Mon, 22 Dec 2025 22:31:13 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVFo1N2QwcGJkb0Z2eVFxakgzTXdBaTZ4cVlBVVJNQllDNDQtS0Q0RmswakN0WUVTaGJiTG5BNG43OE5PRmItMUdjSnMxeWtYcGJDNnhiYmJYb1pmZnJKT01JUU1qRFE3WXQ5NGxaQ0RMQVpoT0NKaGxOSUZPbkJFTGc5d3UyaXdlRTRKcG9ncXUtYzgyaHhOYVlUY0IwTWpGd05aZWhoZjBjMkNlcUtJZzl30gG6AUFVX3lxTFBUYUZvTjhzZFdtb2liUTg4aFU3azdrXzFRSl9vSW9vSWJfY2UtZG43M3Rhc3J6YnU4LTBrMGFrM3poWEdVVEZIZFl3Yi1VSVBEMk9pTHVDemJyQUp6Z01JdTVfTUJrWmFzZVRtSVd3ZDVMOWJBVHdhNHNmQ1BBTzNHZXNyejZrWnVaTkhjWGNRWUVyZGx6TGo5YTJrSy1Uc0NNaXlUTFVDWlVxai1pYmpnTElXMS1jZkxXZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingNBVV95cUxOZGNncG1GaGxEc2ZFVGo5R2Z6VXp6aVJpcERzaF8xUFlpcGJmbGExWWE2ekhfZUtYSC12d0txVkx3WGlvTXpzYzBTdnJtUjN5WC11SkdCMkQwS1FfUUZzWkpFOFdBd2JLQzZhblVFaEdGQnYzWE5CZVZlX1hXWC16ek9CZ2F6QWtLTUlBT1owbWx5b0lOX21SX0lJSlNLMmdyYnA0U3BKWVJST3dlajRWak5tLWdYdnJNNkNpZ013Vi1SZ3puSzlNSXBRTEZHclh4a09GMW0ySHp6ODhhcWRVQVBZYkhLZl9tdkhjS0N5cTR1TzU3bE5OUG92cW9OYUJTVk9vb0I0QjVJclpDVUh6YnFfaWpmNDJIT0hlVnI0QjJNUmRoRlNtREhNS1VQbGpGUmlJelBXOUlHNTMxYmRJM0FDelcxVHU1TjBKWkE5eEVPZkNPekJwUk5Tc0J3bm0waG1vUEc3OTkwcENBRzdlcFZZemVMN21IRlh3Ym1JUFNjbGZHczNYSU9VdFZoLWk1TEh3MWFTbkhCZXR0alE?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46013.17994212963</v>
+        <v>46013.93834490741</v>
       </c>
     </row>
     <row r="16">
@@ -944,387 +944,387 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zoë Kravitz and Harry Styles Get Cozy on a Walk With Alessandro Michele - harpersbazaar.com</t>
+          <t>Forget a Ralph Lauren Christmas—I Want a Roberto Cavalli Christmas - Vogue</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 22:21:00 GMT</t>
+          <t>Mon, 22 Dec 2025 16:36:29 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQU1NhTDd3aGZjeGdQdGxHd3Jjekh3X214Y1RpeGJNSm9zM0JqV0VoTG5iVTVCRG9MS05xNUVpaWNOYmVYZF9UTUxaYXptUTk5d0UwZFlEZWNJZ1F6WFB3WDV0M1h3QXZFRGhNMjlDQ1ZZWUdNTllaVE9mUWZ3SVZOeTdwRWk0aFJuT1BfWmx3bDIzb2FvTVVUemh0V000MnFuRDZxZ01xekE3VW93eGUzWk5NdXQwVGYyRHJN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQbWlpRUhLUXFRRTc4d0dDTkt2MGIxeVAyZlhhbVd0Z0lMSGtzYXNPclJ1QS1kN1pnaUszS1NESnpOcmhYNzJHem5wM2M0alBFeWRBLUZXY3RYelF6SXlQZGRDcUhhYTdGdWx1Q1NCejdGZ0VxU2ZNRTBPZEZTRGNGUDlkMWtsZ1k5Yjl6OHg4c0FPbm16ZksyMmM0aTE?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46012.93125</v>
+        <v>46013.69200231481</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B&amp;M European Value Retail (OTCMKTS:BMRRY) Trading Down 4.5% – Time to Sell? - Defense World</t>
+          <t>Calvin Klein owner sees higher inventory costs due to tariffs - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:00:26 GMT</t>
+          <t>Mon, 22 Dec 2025 15:04:47 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQYlhGX0pYMmh4Mkk0MWNIaEpZX3hwajdlNHl0M3dPTExsTE5DU3hzZmJQLUpPemkyRlNuWFVxUnNET0NzQWtfdzdGajlibWpLcFRsZ1dCWjBTWHgyTGJESi0wVl84cHVCNkI1ck82bnRRWmNzM19hWmdjX2V0S1ZObUstYVp6RnhXS0xYSDRFTWNVdHNCa1o5amZkWXoxVE05SEoyMVZKdzhlRmt4cjVISFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbC12THg4RnhMUDlHdTZrTnA4dm9OU1RRQUMwcm9YNnFQbG1zTWctT01WOXJlU1hPTjFUT19SQ0ZqeGpDRGlEdXduWjRwQWVJbGFKa2J2UW04ejVyeHdWamZyVEl5ZVhZSWVRRmNCSElhSHdkSl9Oa3F3eXpISXR6UUVJeUk0ZmdXeGFkSFNCSGVEWnJ6bkpQQllGOFB2bktHa2hqWDFn?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46013.45863425926</v>
+        <v>46013.62832175926</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Evri sack delivery driver as parcels go missing in Wiltshire - Gazette and Herald</t>
+          <t>Elle Fanning Wore Ralph Lauren To The Neon Holiday Party - Red Carpet Fashion Awards</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:13:37 GMT</t>
+          <t>Mon, 22 Dec 2025 16:10:14 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPLXhaRUphQnFkaWFWU25UQ19kc1ZXMExDX2VUS1lJeURBZU1vdmpGX3ZTODAybWw4SWk0SWllZGZjMC1DVl9jZUNrU3BOYVFZZnNEN3VDbEl5VEJUODhGV0hqQUdFcEx2SmZSRGZHbGh0bm9HQlJ5Umt2UGY5SmRTWlpTRU1QTXZTNHZwUWF0S1RqbWxUakpOWl9VOFB6VG1uSmRZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQdXJKYzZmeUt2MTk4bm4xZHFZbTBHOC0xSHF5Ym5KUU5rdHhQREtwVzUxbHJudk9iVF9rbWM5NGtRN29lS25xaEZMdE1QRFNkX1dpUnZhZFVFeno0M0xVZHNneXB6M3llVjJ1dmFvN0hOMHdWbE1rSzc3RFUtZU9lYmYxVzhycmFMN3dNLU1mTmRXMHJpUkFtamZYQUlIM2YxTVQ0QnR6MU9DTGQt?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46013.38445601852</v>
+        <v>46013.67377314815</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Royal Mail Christmas delivery delays update - full list of postcodes released - Yahoo News UK</t>
+          <t>Valentino Returns to Rome for Their Fall/Winter 2027 Show - L'Officiel Singapore</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:27:27 GMT</t>
+          <t>Mon, 22 Dec 2025 08:56:41 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQemU1X2o1UWtrRm5RMWNpUHR0YzIxcXFoWWJtbTVHcHM2UVR6cXRVclRrc0ZtVThPZEhBQ3J4TWREMVRtTmFDV3pValVkZjFIUExCSHFKbFFnanZ4SHp4UW9lQWhqUElpY1BCX0FGYUktTmJiS01jcGFFTVFzU1prOWhNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT0NYZEV0WENWaGJZeHdjMTV0NEhFUF93MTF0Nl9zY3pjYWNGOWsxS0l4eDZWaC00UHZPdkJUMUVGalhfcE01TTRURHRhT2VLQTg4U0REcU0taUxFTzFZMXctblhab0pRbkxRZnc3SUtLY01zSHl0cjJWMmFuY2dSTmlROW5HTzUySVYweTN3aHBrX2VOOHRfdjNpNllENDIxRjE2RXYyX1RYZw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46013.5190625</v>
+        <v>46013.37269675926</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Worker caught stealing parcels from DPD delivery company depot in Yorkshire - Telegraph and Argus</t>
+          <t>Dior Fine Jewelry Editorial - Savoir Flair</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:58:14 GMT</t>
+          <t>Mon, 22 Dec 2025 12:33:35 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPT2xZS1Fla1pkd1lsSEdJMWNvdlVrT2JBNWthQ2NWdnFlUDRsQ0hFNVBYREZyc0dhMW0wbFhqWnVxM2sxUTR3MGdLb2JZaVh2cGI0MV9VeHRLbFdSMlJMS0x1VHpWS01zWFZNbnFRMWdoR0xxeHNSOEpTTmFocGREQ0FFT1QyNTlQMHlERUphLWxhSW9wRVM0Y2tUVEJ5aVBnbllsLVJ6T0J0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMEsxMzJIWndoSWlmOFFzaFZCTm1aWEdLd21TWThQZlJuZVZ3aG9DZU9WOWN4VFZYWFFOX3hYSnl2WEJTdjFYZFpVd0MwY1pVUk4zS3ZucWd4b2lBNnU0XzNuVkJ6c1pnXzd3QVJDSjB0c1NZdFVuc0doLVU1bXhwcmZUMVNTejlfcDVIN1pOcFhzeEJiVkNvRm92NkYyeTQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46013.49877314815</v>
+        <v>46013.52332175926</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amazon reduces large 800g M&amp;M chocolate bag to £10 with Christmas delivery - The Mirror</t>
+          <t>Fashion Week Fall/Winter 2026-2027: The official runway calendar - Numéro Magazine</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:28:00 GMT</t>
+          <t>Mon, 22 Dec 2025 14:31:23 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOcWFKUUxtRUNYd1I2aUZFb3o0a2w1cWctVHI5NkZqOU1uVWRUVWp1OEtNYU5HTkkzaGRycXRCR1NmWGhuOWtqUmd6NEh4ZEh4OGI4YlFjYmcxclV5TnNsVlM2ZkhacXJLamVJY2xySEVHQmY4TDZkQjYzU2JjRG55NWZud3RlaVlCVExn0gGQAUFVX3lxTFBRcWstalpQSllMMnU5dGpsd1V5OEFOZHZJeVV4ZDFJTExhcXZRSW9ncjNyamNKc0J6VGF6bDE5eW1ZYTcyMkZHVW12S1FUY3phNVc4MVJCbWt3NGtlRksxLUI3ekpja2IzaGlxZ2JLQkIxeFFLc3ZnTWQ2amI0aHlBYW5hTjNNRW1iYkFwU0VhTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWVZJNUsybDFYZUlsU2x4eV84MWs2cFF6X05tcUxpN2RQd3hRbm0zTkVKbU9CUHkwQnpKejVWSGlFOGwxR0NZcG1aeHE3aWdqUHlHR1c1Wm54cWNxQS1rS3BxaUZ5U0FYTHlROGlUakVTYlVJTHNFVnlMM0J3ZTBvano3cWtMVWx6UEJVRXJTRnJBYjJ0dTBPckpxazVOLU8zcGo4QmpVblI?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46013.43611111111</v>
+        <v>46013.60512731481</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Linlithgow MSP visits Royal Mail Delivery Office to thank posties for their hard work - Daily Record</t>
+          <t>Gerhard Richter at Fondation Louis Vuitton - Arquitectura Viva</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:58:00 GMT</t>
+          <t>Mon, 22 Dec 2025 12:09:22 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPU3UxTG9relFJaFN5RTFLUllxYWhsUkJYVE5LanB5US1aVXBLWDllaHFVV0NlUGlZZWRXeTFZV2pacTJlOHYwbUFRb0RJWHpwSklVQjVnU1JrY3Z3RDFoMkpxQ3RUZEJGWDM3UE1qczZsM2E3V0pJYXpjT0dQbV84ZWhNTDVHOThiNjFWbUdvUmLSAZYBQVVfeXFMTzQtRmMwNzI5YUQwODRFanJBMTNQbmdHeFBxOWtrR3VNbVM1a2h6R1YyU1JnNm9qdTVvcU41THRVOUtUMzdEaDBSU1NieGNBXzNtclZVUGl2LUlYa2oyT2VyNmZIQmdWQ0tKTDVEZkluRzd4RVNpZWZESDJVdVMwRDl3WnlTbGd4SVYtNWRPMllMRXk4eGZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd2ZKQXV3d0tUNFFaUUZMWUp0RnVVM1dhWEY2aEJISmQ1Zl9MQ0JIU0VwUnZsWVpfc1c5Q2xndUt0eE5zUGw0MHF3UEVMNjZNc3VqZ1JYWXdkZE43TUoxSDZ2Q2wwRDE5OE1ocUN4SVlkUkxaZkFSN1JZWHVrVFdBVjNXX2NORk1aeW0w?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46013.37361111111</v>
+        <v>46013.50650462963</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Last minute shopper? Amazon Australia announces delivery cut-off date so your gifts arrive in time for Christmas - Daily Mail</t>
+          <t>The Best Designer Bags and Trends Worth Investing In For 2026, According to Experts - Marie Claire UK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:18:36 GMT</t>
+          <t>Mon, 22 Dec 2025 10:42:59 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNSGNfcFF2TzZNR3pSb3B4Ulk4cHlfdE1yUkNsRnp1S3pNQjdpWHJ0TWtDczBqT0haUnpOZkVGdGgxSGpIREhkN2ozdEVCRzl5dFZyS0xfMXlzNS1FWC1PS00ybXlUM0Iwc2xMLWZtdGllc090R2JKN1JOZnE0TTJ0NkZUR3ZLd2JMcG0wUk9GaEcxaFRKV1lrYklxbU9yVVF2U3JsTElRZDFXR3gyVWVfUXJGaWNnaTdkcEljakFTMGtUSnhIRGhnWEdYdEtJNks5ckY2Vk5XNDlmRjhEbzR6WnpEV2bSAeoBQVVfeXFMTkQyaXphWjlzR3NIXzhxRVRia1ZnTzVsdENaSndGMG1OWTNJRkNDbnkyR3VJOWgxRE5sU2tucVVRdExRQlltUmhXRkNsMDM5SVpNaEFSSll5eGlibHZSbndQcWVsbzVpUU1wb3ZYWEwzOUNiZS1sdFVOT19US2Y1bG1mcjlBeENZNExHYnFoaEhhZ1JwbGduQWJTUzRtaVd3djk1MGd5YzZPSjdtYUIzandPZVZZaU0yN3F1SHROQ3RtYTQ4aXdKNDRTZm1yX2Nnbk9JLU01VFByV3VlMWNKcndzRXlFLVd1dWpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFA3eFVKLXhoa1NaekhQZUpvVzBvS0x3YUUxbUVKRG1sX1FUQ3hwVzNYc3dzNE1lTC0wZFM4RU0xeWN3TzhOWVJ2Y0hWTTFfUWRyTWczRU9NdEtEM2ptUnhHaFV4ckIzRG4zWndQTWZfMnNId1QtUDlDWnhPWmQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46013.22125</v>
+        <v>46013.4465162037</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hisense 55-inch 4K TV cut by £250 with free delivery before Christmas available - Daily Record</t>
+          <t>The 2026 Kings' Cake by Louis Vuitton designed by Maxime Frédéric: hazelnuts elevated through the iconic Monogram - Sortir à Paris</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:20:00 GMT</t>
+          <t>Mon, 22 Dec 2025 12:35:36 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPRzVoRFNvUDR4SVo1aDhELUdJV2p3LU9kY3pVTUdNN0ZzYldMcUV2SkhCSy1mc3lJQnF5bmdwUVpob3dqYWZnbUJNV1QyZDNLb056RXZrUWs5bmxRU1JuT3NXSGRhQ0d4WkN2cUtTeVFlQ0dIS0R1dk5YQ3o5WHM0NEtn0gGHAUFVX3lxTFBaVHhSS3ZVMkhVMldDSDBRV3dmaXB4ZGhxaF9taVdRU2k4MGpfcW1hUVMyN1pURkpLV2Vhc1pOUm9hc29KeGJIMndER2hnYWJfRmU2MTNaYTFucnZXdnBBNGFhSGstUFc2NjlHUlVuWGlvdlRaMlBWajlkaDVNLW1uVW0yYWZJMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQdTNZLUFJNHR1MEtLb2RhbmI2WGVRalgyajVGZjc1am9ZeXB2U04ySUkwWnphaXAwaDVnU2UtWTdVLW1TdGVJUXA5dHFQaHZfZGN0aGR0UFNWaWhaT0tMSVV2YlV4U1Q0ZDVMZnRCTUtFZmV6QVFXdnR5My0zaFlWa191SS1hMGpsY05GNnVrZHdwRm93OHVJeGxKaEVvakt3N0tmYlN6WWRaQQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46012.72222222222</v>
+        <v>46013.52472222222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Amazon delivery center in Weatherford to bring faster delivery for rural communities - KOCO</t>
+          <t>Dior’s New Addict Perfumes Have a Seriously Starry Line-Up - BusinessToday Malaysia</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 04:10:00 GMT</t>
+          <t>Tue, 23 Dec 2025 03:23:18 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQX2RvenNVaFNoeldraGdsWlpaaDBNeWRobnFydUtWbDBGX0EzV3pOME9VYXFSUXJDTF8zM2QzNE1KTjBxVXQ3U1RkREJyUHgyYkZtR1JmcG94X2JRSDZxNlVHQWtfcl9Bd21pai1NRDFuS1p1N1Z0XzhHZkNNeGZUcUhTZlVTQ29K?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNRkd3cHFWWFJhek1VQmVyZVV6REhjYlViWDk2dENqOEdBcEItVVRrczVtRC1XTUtSYms1VEJGeUJnWi1QZ3J6QWtlRFJJTUpJajZMR0plcl9WdUVWZW1OdU1OU3dzZ1hYV0JKZG5ZSzA0MFp6MHFjOGtaYzlBcHJFVTk4ZW5ZWTd0WlptRGJHb2t0eGx6N0Z3X3RtdzZlMnhIaERzRw?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46013.17361111111</v>
+        <v>46014.14118055555</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Watch UPS Driver beat the heat by joining Slip 'N Slide party! - AOL.com</t>
+          <t>How Product Roadmap Could Affect Suvidha Infraestate Corporation Limiteds Future Value - Retail Trading Trends &amp; Budget Friendly Trading Ideas - earlytimes.in</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:06:04 GMT</t>
+          <t>Tue, 23 Dec 2025 02:02:02 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1wOERmeVdPWVdMNWVETWx2YTNObjBveklMdk9ocldUWFBkQl9wdzZoZ2dVVDg1TTlDRk1JNW5pSzNFNFFvQ0tJRjdzeGtMMFFPaTJlOEZLYWZsZGdNQmp6UGl3NC1wTE4zbE5OTU5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPMGpuOFNDcVpiREkwYkk2ZEZMcVZBTXNOa293aGZHeGdCdGJnenhlZUV1dzNZZWF6QWZmLWl0U2tCeGpOMUZyTGlmLWR6UVVyaFBnWUJjZHgxMVZLcmJIdmQxUVhMb2hIY3dnWURDRUhuSTA4UnRNMmU4SThOUmxjTnpKV0MxN0tGOUdqakpOY3BrTkREM3hDVU1MN2dzNW5oOWZzNXBWQlFjQ1BrS1ZXREtGVGsxNTZtNXc?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46013.37921296297</v>
+        <v>46014.08474537037</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>“Customers value low prices, vast selection, and high levels of convenience over delivery speed.” On #YoungTurksReloaded, Udit Madan, Senior VP of Amazon Worldwide Operations, shares the future of delivery: “Customers will still want millions of products - LinkedIn</t>
+          <t>B&amp;M European Value Retail (OTCMKTS:BMRRY) Trading Down 4.5% – Time to Sell? - Defense World</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 14:27:47 GMT</t>
+          <t>Mon, 22 Dec 2025 11:00:26 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOZl9DZkFzamI5cENyYmhLWHJWZWNKQWxyUWdUOWhmdVBYWkxFNFc5aEhqX1h2VUVlNkdYQlFJb0FiMThFY3lNVFpIRnVBTkNtd3NScXYzeTVkbVNuR1prbnFlYlBWWDcxODg1ZzJYUEgxYjRlUXBKbkdIdGNWbFNQRHdZS2ZXTVVjOHExaDY0TlFSbVdHU0R6LXowZmxjUEVQU2V1S2hMNDBEZ3JELXRj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQYlhGX0pYMmh4Mkk0MWNIaEpZX3hwajdlNHl0M3dPTExsTE5DU3hzZmJQLUpPemkyRlNuWFVxUnNET0NzQWtfdzdGajlibWpLcFRsZ1dCWjBTWHgyTGJESi0wVl84cHVCNkI1ck82bnRRWmNzM19hWmdjX2V0S1ZObUstYVp6RnhXS0xYSDRFTWNVdHNCa1o5amZkWXoxVE05SEoyMVZKdzhlRmt4cjVISFdn?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46012.60262731482</v>
+        <v>46013.45863425926</v>
       </c>
     </row>
     <row r="28">
@@ -1340,24 +1340,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Amazon Tests Delivery in 30 Minutes or Less With Amazon Now - AOL.com</t>
+          <t>Everything you need to know about Amazon's last delivery dates for Christmas - GB News</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:05:38 GMT</t>
+          <t>Tue, 23 Dec 2025 00:11:05 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOa0VveUhnVnlmNlprMVNCcXRVV29rNjItM1BBdXFqaHo0QkxQWnFQWlZObW9sajhiNDZWb2J6eDJJZFlYTDdydHd3cE1BUFg1UXVlZlJNVldoS2lhTm5ZYjRENXdXWU1SNjB1T3JieW5oWERXdWVqOWNHQ0JLaU5xdS1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBTSGM4dDlSVGRGd09CYjlwQXNBSmpPRUpteVdxQm1USDdmbV9yRFpjdlY5NEpTc1BZV3BGSTZGZVp1M2VhS0J6ajRyZHRWd3FkQTljRVRHNWJldV9kaXprWWlhaVpnbVprcXQyZA?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46012.71224537037</v>
+        <v>46014.00769675926</v>
       </c>
     </row>
     <row r="29">
@@ -1373,4842 +1373,5898 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Amazon Apologizes After Delivery Driver Drops Off Package, Allegedly Steals Homeowner's Cat - westernjournal.com</t>
+          <t>Woman pleads with Amazon after botched Evri delivery - Oxford Mail</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 13:05:49 GMT</t>
+          <t>Tue, 23 Dec 2025 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOUFZKUmY2YVNVUnZXdkNaazA0U3E3QllMNUN6UmVzejFndXpvVWpoYXlvbTF3NDl1N19kUWJvTF9JaVduRGlIdFhyRHhJQkFnNWl3bU1DX01pVjk4XzJ4VVNYOWl6a09IbkpTV3ZwTEZXYlF6aVJRdzRPZXZUQV9vM2VHNlp4OU9XRHJ5YVc0SVVwbEstUWV2eWhJTHViQ3MxcFJWa2dyU3RBYThKMDc5NGQ1Q2xFUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUTQwWTVJMExwZG1WRVFKdzBBS3UwaVA2YWpFYzR1SGVEeXZ5bVFQRTBLQ0lPaW9CTjVBdy1FOHo1YkJYdG93blBKeUdIblhUX09HaENCSS1Yd0daLXRpUGMwREtMdEsyRlBNcUdJSmxfc2haaHdhMU14Qlc1STVEY1NDa25UMjd6bHJBVVdlYTJFNEk?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46012.54570601852</v>
+        <v>46014.20833333334</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium English language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Retail crime")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Week in Pictures: From shooting in Australia to protest in Brussels - Al Jazeera</t>
+          <t>DHL Supply Chain Appointed by Siemens Mobility in New Multi-year Contract - DHL - United Kingdom - DHL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 13:37:34 GMT</t>
+          <t>Mon, 22 Dec 2025 23:53:33 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxON2t1Ql8xcGpDV29KZnc2MEtDcVJrdjcwbzBLbEhhbmlHeDgzUGkyczBhR1B2aDhWbmJrSmFoVURFeXdhTC0tU0lWQ3p3WFVlbUVfdmlET1hGdjBnTEliUXZRYS01cXNKMnFQWTVXdDNOZkptMHJUN1AyMktLb0ZYZW1jdHo0OUFfRG9PblNhMU9UeHlJR29hOG1rQjhacElTQWN6ODU1X0phem1CZDRWcNIBtgFBVV95cUxQU3RKMnhLWFowVWp2ZmZVZ1Nlb3hLb3BlZG5GNzBkRzBNWDJKS2h1YWFWR2hWcXduUEozT1Z5MC1RM2dCTFJSVVJ0RHNEblhTQTY5NktjWEladmVfNjdkdEQyQmNJdy1NX3dIY3Q5VjF0TjRKZnlTbE5Ra1FzNGVLOUtDcFljaWRPMUtTNmFYbVhiT2dLTHJUSVUxRkk4M1gxVnI0Y2RTSWZLaHBZTm45NTV4Rl9UQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOeDhqeENxc0tRSGtBckJnSlhKa2NzUElZUEFTa2FZaks3cHdWQlZwVHB5S3FxZ3AxcFk3TS1GOEkwdVo5UG1hVVMtallzNlUyNDJFLVREajdxRUxQcGtUWXJDSllwWUV2c0E0eVcyX2FtUE5kbE95NUpGY1RRN294UHlnMmw0bi1ydkpiY3Z1Q1piWXBFel9DN1FoMjVZZWVhekNNMVF4MFRuUDg?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46012.56775462963</v>
+        <v>46013.99552083333</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rising drug-related violence in Belgium raises concerns over public safety - belganewsagency.eu</t>
+          <t>We sent five Christmas packages across Britain: Royal Mail, Parcelforce, Evri and DPD - only one arrived on time and unbroken, so can you guess which? - Daily Mail</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 06:00:00 GMT</t>
+          <t>Mon, 22 Dec 2025 16:53:40 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNUzBXcG5Dc0EzSHNjUWw5ZWRVd1R4ZHFUd0dfYWRyd21PYm4yVXl4eDd6OUJNdzVlOGIzRVpUanNpY2MwX0h5dTRBYk9DZU5lb3ZHLW1CR1hFelVNUlF2UzQ4MWxVRzA4aHl0MlVyeTRxeE5kZjRxY054QTJKTWNzUTFaQVk2czRkTlVUQnFHZWgxVlhjd2ZPdkEyUzNUZ3UzVUxiSFZuc3A?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPSWJERnJaTUNQVk1GanVJbDJCeW5LSk1ESGN3SGt3WnJ0OWhiUC1TSS1MWWtBZXdZYnZTT3RXbEltWnJBWGRwTnRyUlBFYVg4a2FTR09YeFUyLUIxbU5JVkFKTVlJRGktWkp5YkxYRFhfaEUzZHhwdmEyLVJzTksybkh0SzNiWHlqaUQ3Wlh1Z1NhVU53X2tCcHNQWmd6a2PSAaQBQVVfeXFMT2xBdEVGcElEdk1JampRLWNBTnl5di02dXFZaVRFeWI1SlIzc0xPYzJPeWZKWlJ4Sks5UDZmZVJ6dTYxdlRMSEhKTmxpeWQxcmdHbUpkbkllRUIyVWtqM1Q0RkdQQTd2LXNrVjRTM3BpNEszTFN4YzNyOTY5NjlPcElBLUM1SFVlTlJ1cXZDUTJ6OEptbUk2WGlNZ05nR0RQNXlfZjU?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46013.25</v>
+        <v>46013.70393518519</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TUI fly launches direct Düsseldorf and Brussels flights to Sweden’s Sälenfjällen ski region - Aviation24.be</t>
+          <t>Delivery driver arrested after suspected Southampton parcel theft - BBC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 20:23:47 GMT</t>
+          <t>Mon, 22 Dec 2025 14:26:33 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPakp2QUl2SWljaWhWbS1ZNkNmMFNOYmNRY2t1aDRaVmY2VFZ1amxrOEY1NzRMZ1JfRnNrOG52Nkp3Z1NnazZmNEViUUdvN0VMZWhIdTdVNHpDT1NFQ3VlSzEwd2Z5OEh3OTZTSldueXBpWGM1VVFtd29wSm5QQmpqMmJ3M0ZpYUFJVms3UmFKSnVheU9CenJBSV90SmJkZ1lhLVVqaC1zbElURk9ybktpUFdGd1NUWXI1UzNzT2UwQXRwbmZIMWhYU19EUXlsc3JYNUZMdDBWTHlJS3lPUFhOQk02dkQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE4wcEpCVGkzZFRJdzJ2YldaaXB3cU9kLUNtdUpOaWNObmRxclFJeTVueExTdjVOWlFjQkpycXZfN2RiZVRmVm9pQ0JqOWpJSzVXQklxNUNkZ0wwYi100gFiQVVfeXFMTzVoTGg0a0FYMW9GQm1hQnRTNG92QVFDVzN6VEhKSVlyUF9CSEk0THNPaEU3NGdrelJER0luYVdobVk3cWJpYlpQSnkwYWhfSGgtMmZyY1FjY3NSZHB6OFUtN0E?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46012.84984953704</v>
+        <v>46013.60177083333</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Man dies falling into canals with bike in Flanders - The Brussels Times</t>
+          <t>Evri sack delivery driver as parcels go missing in Wiltshire - The Wiltshire Gazette and Herald</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:59:45 GMT</t>
+          <t>Mon, 22 Dec 2025 09:13:37 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOcGFoUEdsdXNNRVN6YkJ0MzQxcG1rSklwazhHVTg5T1RKaWRIRlJxV2hzaklsTUdNb21iVlNKai1WamtiU2hjSmktQWR3enhtdEVjMXFpS2xhQzA2WVotVkF2VzJwQVRsRHpOaWU3Tm9OMkNqVVg0S1hXdTgwT0I5TjU5alRRMi0xd1RZU1U4RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPLXhaRUphQnFkaWFWU25UQ19kc1ZXMExDX2VUS1lJeURBZU1vdmpGX3ZTODAybWw4SWk0SWllZGZjMC1DVl9jZUNrU3BOYVFZZnNEN3VDbEl5VEJUODhGV0hqQUdFcEx2SmZSRGZHbGh0bm9HQlJ5Umt2UGY5SmRTWlpTRU1QTXZTNHZwUWF0S1RqbWxUakpOWl9VOFB6VG1uSmRZ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46012.70815972222</v>
+        <v>46013.38445601852</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Food aid network fears closures after federal government cuts - The Brussels Times</t>
+          <t>Evri employee arrested after more than 120 parcels stolen - Daily Echo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:57:46 GMT</t>
+          <t>Mon, 22 Dec 2025 14:35:56 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNcWYxdmFXRGtjUElWeHkzOFg0SDEwZ3B6ZnVoQlJka2JWNm4wc0wzcW9BelpuTnBhUkF3c2JGU2pvTUlnWkdnY01DTDZ5WkpISjRNRmFsekdsWjNsUXRvUFRqQ2xwSE8zNVNnazZ3TzBUVTg4a2xtQk9BeWFaS09MbmhNRXFwakF0SHJDTjdSVXd3NHBHUUd3aGRNT29XUTNmSzVkSkViUDdjTFo5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYmdfRUh1elJBMzNBYUxDU3pkS180cWFfbDB5LWcwYzdiaWgwN2lfRWl1SlZyZnctbXZkUnFKTFNheDAtQnM2U1ZIbEFQX2dHWHBudjJjMnp5SzV1WWtQMmxmTGpBMFJ5Q1FwVWxfLUtCd3VrY2ZwZkhXNF9nMHhfWWdUT0x4UjNDdTVQSXRrVE9LZEVJR1FSOGx3?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46012.7067824074</v>
+        <v>46013.60828703704</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Erasmus is back: The London-Brussels agreement - lnginnorthernbc.ca</t>
+          <t>Amazon Now Delivery Push Could Boost Its 2026 Outlook - MarketBeat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:18:15 GMT</t>
+          <t>Mon, 22 Dec 2025 14:17:33 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPYWVlVlluaGNVbnRBSV9JSlAzZ0JHd29EOFU1RXJDc09JYlQxNFZFUXNFSC1vakMtcnBQQl9pSHNvZk43X0ZwcG5oQUk2UkJnZ04xb0NvaHVBMUdKREJ5OTZkNWk5S1BKWEw0VnNwdHBiMlFqdTZqVmdXZFMyMW1vb1c1eG5hUDFIeVpxOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObkFPR18wTlQtOUp6SFFrRWlUMHpqVGJEUDhmVXZ1Q1N0RV81WUIzTkZ3QV9XNFlPWVR1UWdGNHdicTA3VWx2Y2xBTVMtUmRKeFo3SDRhRU10cER6dW1ZN0p5VTdLNURkQWE3eldnbGxhdGEzNlJNeWxJdS1DVkpwWlFKc091VS16OGlpeDhlVVNEWW1GdVE?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46013.42934027778</v>
+        <v>46013.59552083333</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hinrunde Wrapped: Looking back on Bayern Munich’s first half - Bavarian Football Works</t>
+          <t>Christmas ‘ruined’ for nine-year-old after delivery driver puts present in rubbish bin which is then collected - Advertiser and Times</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:20:27 GMT</t>
+          <t>Mon, 22 Dec 2025 10:42:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOazJXb3ZtQ01lOHpqZTRWbFJlZHEwNGJ2ZHZBYXZKWU1DTjNsUWhrRFdiOEU5Mkd5ek1TVVM3NFVIQlFyQ0x5anMwMFZnaE9ROHVCQ0ZaRnFJTVNpT0pQTFQ2OXIwX2pzMGxnYk1WQUY2TDBOZEp5YjF5OUdZZXg1UVpWTFVwbEZYMV96TTVqclYxbEtudHJiOEtqQXZ1eUZweE9QR1VPZVRwUGgtc1RqdDA0TzFKaWpuc19UOHlidjhxVDJVbzdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPZ3JJWEVSR3MyeUhMU0V3eGxzalR3Qk5EN3pjdzZGaUhlUkpYQ0tDZC12OWdpWllDemVZSU9jT2FwUjJ3eDRMT1FPUGx4dE9GZWxjSUpVdnBrakZXRURQa2oyV21EQkFVbWt3MVZyY2phdkM3VWdaZTVJUERVLUJVLWYxRUtiY3ROM0dTRTFMYVlUYmJNeFhMNFI1SEtpdWpTR204TmdUZVdLRjlZckE?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46013.51420138889</v>
+        <v>46013.44583333333</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>‘Munich’ at 20: Daniel Craig says he was ‘terrified’ to work with Steven Spielberg on the 2005 Best Picture nominee - Gold Derby</t>
+          <t>Amazon to pay $1.5 billion to millions of customers over 'deceptive' Prime sign-ups - Mashable</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 18:00:00 GMT</t>
+          <t>Mon, 22 Dec 2025 23:00:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNTnh1ZmFsRzlKaEczakkzUmxqMXI5TUNtRzlYbVlka0MzVGxyRmRqLWQ5TzNzQW5nTmdjdGNpVDVad0NVamNFeHV3dUU4UmRvVkRzbTRDdjVsYnhoX29GS2t4czRpQmlBcGxDSUpqdGJBRjhlenhLd2VVQ2gtY3RXUlpGLXpBQTViYkd0YXcwZkxUOTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9DNlJadzRjcEdRSWVuSFk2aFNnMXBmZzgxV2RyaUMzREdFUDdndThmNXhoVHRmbW5JanZFQnNnd1NSbUNrOXMtYWo3TmtFSVE1VkFxNUtNM3lObmV3cWNv?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46012.75</v>
+        <v>46013.95833333334</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inter Globe Finance Limited Chart Enters High Volatility Zone - Bollywood Helpline</t>
+          <t>Linlithgow MSP visits Royal Mail Delivery Office to thank posties for their hard work - Daily Record</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 04:04:54 GMT</t>
+          <t>Mon, 22 Dec 2025 08:58:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZV9lM2FBaU5UMUJPT1BXeFpIYWFmWVlYaWhxVnYyTmRSelNLZ0l4c2VWdmtMTjZXd0lXcXU4SzYyVGY0N0k1U0ZmNVFzeUt4dmFUSVRwSXotbWtNQUN0SU9SVHVWY2pOZEN5amktdC01Z085TlpjaDhLNGhHNUFtckg0YnB4a3c2VnpGZUwycWstM3FJZ3BxWG9OeTFlS0dMdHhMSDlRYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPU3UxTG9relFJaFN5RTFLUllxYWhsUkJYVE5LanB5US1aVXBLWDllaHFVV0NlUGlZZWRXeTFZV2pacTJlOHYwbUFRb0RJWHpwSklVQjVnU1JrY3Z3RDFoMkpxQ3RUZEJGWDM3UE1qczZsM2E3V0pJYXpjT0dQbV84ZWhNTDVHOThiNjFWbUdvUmLSAZYBQVVfeXFMTzQtRmMwNzI5YUQwODRFanJBMTNQbmdHeFBxOWtrR3VNbVM1a2h6R1YyU1JnNm9qdTVvcU41THRVOUtUMzdEaDBSU1NieGNBXzNtclZVUGl2LUlYa2oyT2VyNmZIQmdWQ0tKTDVEZkluRzd4RVNpZWZESDJVdVMwRDl3WnlTbGd4SVYtNWRPMllMRXk4eGZ3?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46013.17006944444</v>
+        <v>46013.37361111111</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Captain Kane helps undermanned Bayern go nine clear in Bundesliga - NST Online</t>
+          <t>Amazon selling 'huge' 800g M&amp;M bag for £10 with final Christmas delivery - Bristol Live</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 00:25:21 GMT</t>
+          <t>Mon, 22 Dec 2025 11:48:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPZXlZSHdmdnhkc2cwb1dnSDFWZzk2SDVQWjk4aEJydkJtUkhFVklpTnpkLWwzSXFuUkN2YlZOSDRDN01yYTdOYi0zZzB4S3F1eVlhMW1kaW9aUFhhVVBrbkFlMncxaVZfdVoxXzJqa05naFZqWTNUM1lDWkJPMUtEdzNhSm9XWjNPY1JsbGtpR3pabzNmNHgzZGlSZExlV1pKdThuRGNqZkx3SER3UlJfNW53WlRPaUdCQ0c3QVJR0gG-AUFVX3lxTE9leVlId2Z2eGRzZzBvV2dIMVZnOTZINVBaOThoQnJ2Qm1SSEVWSWlOemQtbDNJcW5SQ3ZiVk5INEM3TXJhN05iLTNnMHhLcXV5WWExbWRpb1pQWGFVUGtuQWUydzFpVl91WjFfMmprTmdoVmpZM1QzWUNaQk8xS0R3M2FKb1daM09jUmxsa2lHelpvM2Y0eDNkaVJkTGVXWkp1OG5EY2pmTHdIRHdSUl81bndaVE9pR0JDRzdBUlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNeXlRalJyUmkyYV9PT1pJX3lhczVlMG13cmUwZlg2OGFXVUxBYk5nYW9NX2ZCbmVHWEhXUFFJVS1iZmtMRzFoRkE2ME9nQjQwSzVzN01hM0NoMkpIVm1iakxaS296MmZiSTIyeHA4RVBRZV9fZGZsVHp2TDdySFdmSXJFVmxFcHhxY0VVRg?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46013.01760416666</v>
+        <v>46013.49166666667</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Intraday Charts Show Spike in Arvind SmartSpaces Limited Activity - Market Entry Points &amp; Best Stocks For Explosive Growth - Bollywood Helpline</t>
+          <t>Amazon trains delivery drivers for winter weather safety - WFSB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 23:35:41 GMT</t>
+          <t>Mon, 22 Dec 2025 22:17:01 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQUUNLeWk4VkpZRmlNVVgtZ1F1a211QzBBekZtUF9IME5icDF5amhaM1gxbTBaTWs5VzNCUEUydmN1Sl9GMmlleFF6QVg2MnZIb3pvZGdQNXdmNjhmcU9OaV9DRU5vdU9PTkdSckU5aW03Sjd3TUxtZnpoVnllNWxtY21Qa05xZ2xSTXZTUDBvYmFtZDByc05JWHNvVTFGYU1ydVJfcEk2bWpjNENEcWpVWHBULVo4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQTXU0UVNLMHNuTWpnVUV5X09XSWM0SWxrVENlN0w0NmlGbzROOUNDR1hWdWZ6a2RhY1ZMUm9fOFYzSGEwZGtFNHQxQnY0RFJTNEM0cW1hQ28zZTdkNkpDX3hTd0V0UnI1M2xpRzFITUNiRy1VaDk2VlVJTzJ4c293UnExX0xVTXFiTGZjRVNkaDI0U28yVHc?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46012.98311342593</v>
+        <v>46013.9284837963</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Postecoglou sticking around 'a little longer' as Spurs show fight in Frankfurt - NST Online</t>
+          <t>‘Then You Get Termination’: Amazon Delivery Van Hijacked, Crashed - MotorBiscuit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 13:39:11 GMT</t>
+          <t>Mon, 22 Dec 2025 18:00:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE43MFMyWkY5cDdZZUY0SFpTRTBtZktyZFBWWFFQWXhYSFRKZHQ5WER2OEJZcmpnNFRlOHZyWFpqQ1NZUmxLZGRTdEMzb1Q3RXVwZGV3QklsbWliUy1EdS1tZHBjLTdNUzk4cjRPSlVISmNSMjdVTGR3aFo3UGxkNTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1tcTc0aXVKUng1Vi1lR1RySmd1S2stRWEwSHR6M3hBQW1CUUdERXowTXZSQ0dhd1ZoWWpoNm9Id1lnMl9ZWlJPem5yeVVsSEN3NE9yeG9HZnRGWHVvTUt5VjNDU0xNUlBM?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46012.56887731481</v>
+        <v>46013.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minutowa rekonstrukcja zamachu w Lockerbie - liganews.net</t>
+          <t>Amazon Stock (AMZN) Today: OpenAI Talks, AWS AI Spending, and Ultra‑Fast Delivery Set the 2026 Debate - ts2.tech</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 02:52:35 GMT</t>
+          <t>Mon, 22 Dec 2025 16:27:50 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE0wWnhXdWEyQjJzVm1QR1FMVC1pOWVlYndtTTl1ajZvY3lwRHZjNHQwY1Zid0VtbXBDazA5aGhJVmI3TlVKeHRqOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQcS1jSkpMVlpqM09aSFNFYmdBSkUzajI5a0tlZFdCWVdNXzRiZUZXVVRXaXp3S0Q1QkNiZXo3QlE5R0NINmx0YjNYWmJ1Ni1uYWg0a1QzUDRzazNrZEJaZXBFOUk3OTluME9yU2czb3dKc2FFYl9xUG9IRmVmSTJFTEpZWkZGd1ItX0VmWDhUMnI5VFRUUDB1U0JrZjRzU3ZpWXU4NE9OVFVqQWE2andEM1NDY0JDSi13?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46013.11984953703</v>
+        <v>46013.68599537037</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, German language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bombe" OR "explosion" OR "unbeaufsichtigtes Paket"  OR "verdächtiges Paket" OR "Sprengstoffe" OR "Bombendrohung" OR "Schießen" OR "Stechen")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FAA says SpaceX Starship explosion put passenger jets at “extreme safety risk” - Aviation24.be</t>
+          <t>What's open, closed on Christmas Eve, Christmas? Stock market, mail? - The News-Press</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:29:23 GMT</t>
+          <t>Mon, 22 Dec 2025 14:01:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPSnlaZlFnU2VMbFM1ZHo2OE9wdjktZUpIclVMYlpqd0V0Zjl6ZHF0bEpwYm9HeUxBWFZJQ3B3Y1hGY0hrTnJOa24tYjE5TkgyTVVFeE1wZFZ6VTZHVUQyVlZ5YVIwRTJfSmZTcnE2YUNkLVdMdkF4YW1fdFlHLXAwbUxXeEpQbWxuc2VOUGpjUTM5cTA4Vk1GeVlYZTVPVmE5R0VFVGNkRXk5UFJ2YlgtZVQ3dG02Y25LUWNKOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOWUF5dWxDeHhvSWZOaG9BdU1SekFad3NPLUg0Rld5M1RFVVhQRFZiamFudWVxRFV4c1FNUW1waVdEVVNkU3pfZHpJcUx2UWM0R2puN2lBNHVNUkhIdG93MkwzUEhldTlUM2Zqb2pQZnN0REFqc0ZYV29kajk5QTBPdzh5MVpGOTA5WklIX04zVHd3d3pkUDI1OE9oUFk2eXFGU2lzdnZNbnBlQWNjaXc4aUFybFJPbUc1VmVGVDR5YjZaUDdIcFdjWHFTS0NOUDVQWEE?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46012.68707175926</v>
+        <v>46013.58402777778</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>This year’s divestment campaign highlights - Friends of the Earth Scotland</t>
+          <t>Adidas sale is live from $12 at Amazon — final hours for holiday delivery - Tom's Guide</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:44:41 GMT</t>
+          <t>Mon, 22 Dec 2025 13:10:13 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE90cVJ2eGxrLTgwdDZzS0tVaGU1T1R2N0p2dlF4dGVMa0FXZWdDeFoyLUNCd2xHMnliY2JaLUJTcVN1d3hfbGJNUHh2OUl3ckd4bE94Mzg4T2o1SlFoUXNUMnVWRE51bmtGYVVtcXV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNWjdsWnhnZnRiNkhTVUhySHo5eHZpTFhISm9LdDRGNG9fazhKT05MWFR0cEdkQ2I1MDF1bUdzQmduVURVNmt3Nk1IR0RIUVh0M2xXOHkyY081OFc5REYwTXgtY3VzNWRlcURDVG5LYnNqQmhsb0RiVjZ4NXpzSC1kTXZUNDFncVpORHlJTjJoZTNtMllMRVVjelltbWFVMkJ5bGVscFl6TWVFaWNuMjNkdFBWZWZVaVE?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46013.53103009259</v>
+        <v>46013.54876157407</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Extinction Rebellion activists target Whitehall in dramatic warning over missed global climate targets - Morning Star | The People’s Daily</t>
+          <t>Video Amazon delivery driver arrested in fatal road rage incident - ABC News</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 19:43:17 GMT</t>
+          <t>Mon, 22 Dec 2025 17:37:34 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOdHlGcXFjZERLV3JuOFJXOGw3SG5ud0Q1eHB0djNLWXVHVXpDZnE2SFJDenVXMjFvd1hrQ3hUMXhPUHRpWnZnWmp0UnZHQXl5RmxOY19VX2Q4N09pcnRvZzNNa2tHTE1lOGR5aUwwUzhQYUpBV3dzTm11ekNJa1AzSWxRdXRpVnozdzJlUzVFSW5BdERvdWhjRVJLcFBNcm01Y2h4X1VYeU9EQVRGQzBRX0IwVWlibG42OUxsUmZFVTZ5VmRCSlRRSDNjbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNakJNTV9qaFJTXy04S2hkY2NocU1MdnpuR2FIcWZrcFhVQm54UFNRLVFnNExfYjBxblM3YlVGZ1oxY1lJR2l4YjRzbDNCTTdKUDh1Qlljb1lzYm9CS1FTQzFqNzUyZndGZDVPSDJIVjd1RkZSelBjNU1rYTF2ci1tZERTdHRyY1FZQnU1MV9oalRob3BYaVhaa295U2VQakE?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46012.82172453704</v>
+        <v>46013.7344212963</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lily Allen hosts star-studded Christmas party at Stringfellows as she cosies up to Jonah Freud - London Evening Standard</t>
+          <t>Amazon customers complain about packages stuck for weeks in Armstrong County: "It's there to die" - CBS News</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:30:02 GMT</t>
+          <t>Mon, 22 Dec 2025 18:07:06 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQdldpRWlVdHdRdFhzcGdXS0NJNDUtTnlCZ29ncHlsWFVCMUxZZ0J4MEhYQ3lEd1JTSm5OaEJmby1rRGdkX0N1NzNReGotbV9aVVRxT2hsQlk1VS1DTmpmTzJPNTh3YnBRc0cxNE1DQmIxclRScHNJWTFtN0NHaU5iMGpRYWpiV1VBNGRySjhzNlEtM0pvbHhhZ1hNM3VQZF8yY3RQbG1oVmNJeHplNWJlSExoajBabUU4UEs3eXBIT0hHRGtZeWxmbjR2dXJyeEticW5zR01DUFhKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPZ2xzeUplZEVXUDBlbnFhTlROaWF0UU84cE92eFhQZTFWME9YakhORlRGVk1vdjJRb3JWYmFZdlBqMGNzSHVtZFYxdTBMel9EcFl2VGt5bjZTYUxLTnJTYk10aXdiSzZveHNiMUJQNlhzQ1JhQXk4VjAtWFhrcUtCUldlMGFudw?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46013.39585648148</v>
+        <v>46013.75493055556</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Far right uses baking contests and video games to lure recruits - The Times</t>
+          <t>Amazon Mexico Hires 8,000 Seasonal Workers for 2025 Peak - Mexico Business News</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 21:22:07 GMT</t>
+          <t>Mon, 22 Dec 2025 19:43:10 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwNBVV95cUxQMHJlWTBkLUFtem9lNURvZDhoYlVBZ240bHFMRXR5UGY5OXluUkJuZWp2aGRpdVVZZ19tb1VOckpJSUlqQWRiUWJZZXJQdjFTbGlqelh5LWpsWFRTUzZ0Z2JyZlJJNk8xNDZQVlN1SmlRRkVON2FVUDdaeW45R2tETkw4Q0ZUdHVVUTlnNWVZdDlPRkpWWXRtdUptVzFGcHVMSEFrU0YyYkxJQ1lHVzNDdFlScFFQdTl6YVRodXVGRmFEM0pjbkZUNEFvVmxPdW82MHlOTDBLTWQxR29lOWs2T3dsVVIwMmN1bnp3cmJFNjBodnZEV3ljREVOTUppbXVuc3R2ME5aMW1QOURvT3k1NFdnaVBWTzFFNzhfZUV6ZzJJM3VlLW0tQVlSQWdFT0wyQlZpTzV0V2NzWFd6V1BNaEZxUlIyNFYyUDJySFdzQm1pc2dSWjhfQjRmUHZDNUlkaG1na2lEa1puamswNXFpSnl5b25yeVo4NHl5VkhZa0U5QktQMGF5WXZhUHVlUXZBUUlOc182NHUxLWl0SXllTkpJWEIzdUNuWDZrQXZ2Nk1nRkZsUkRoTWhNdjJqSTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOTzRrOW01MFcxZXMxdm1uc2RYejJ2dVRNZHhXZnVxR1QyM2cxdWpNTTdmM1FoZVk3bVhsNlJjbzdSLTNMNS1Ibi10YWs3SHYtUHFFejNXQjlhaGc0dEFobHl3TnJCTnRfOXBENEo0cGdacG01MTY1bk1ZRF9vdGs4LTJEbmxJdGVXcjZHbDFaWG0wMkpTaG5SUEl3?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46012.8903587963</v>
+        <v>46013.82164351852</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Climate Change Sparks Global Action Amid Extreme Events - Evrim Ağacı</t>
+          <t>FedEx questioned for hiring hundreds of H-1B workers while firing US staff after $2.24 billion federal co - Times of India</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 14:11:05 GMT</t>
+          <t>Mon, 22 Dec 2025 20:35:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNMmg1bE03OTlmQjk5V2tBdlFaU09qRHBUSkdTRlVTRzZya1FGUzdXalFCRk5PM1hMLUFXTUtnek93MktfWlZ4UTgyMEhfZHZSeG9kMDZ5Z1I4RU1tWkhUT2I1aW4tU1ViV2I2cHVZMnpSQ1NVeHdLVDZDcnpUd1Z1WldXY0pNS2UyRTZ0bWlwdWt3aTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwJBVV95cUxQVDQtZlowV0paSWJtMUwzci1vRnNDY0xUSUxveEo5Rjg5QkdJMEJURFAtMHEyNmdKZmpKVVpacmNFczB1cUJzOFV0RE9jM0QwUjlTR1FfREwyUnFMcWV1RzRyd1p1dmtUcVN5S2sxUllVUFNDT3ZpdG1HRktmYkJHbDdfeUU5SE93NVczYXZEdFBNUUs5N2NNcFNMM3RMcWNNcHJHRmdKWkRfSThVZkpEVnVKNVNhMW54VDNXM3lEdDNlTkNiYWZLSlJkaXNhbGhHRFRsRnVSNHBzTVg3N25fTjdVRDhSVldBbXlULXVjYi1mcDI4UDRNcDBSb29zUG4xelNHR3c1NFk4Rk50SlpQN3FxMUtNcE5FVUZZeHR0V0EwVmZlVlg3MDJnbEtZUzVHbENwNzBGVm5RWFNjZzdSM29UUdIByAJBVV95cUxQLUE4X2poVUxCeWZPcW5BQUlMR0p0SlB0dFBMS3EwZjJCUDBtTTBmOTdkbmRyX0g4b3AxNFEzTDFHRS1KYmRFNDlONmEwY1lUWlh6Rl9CYnQybVhvZlZGZWdCVTlWWkRvQS1lRkM3a0lSR280Rnc1WUdadzh4QTFwNWk0OEVwWkdDcXl6RnA4OUpOaThQSnAxV1dJNjR3andUOWxwWG1JN3VyU2xFaEx5dkx5VjRiRm1lZzc3aUMtajN4dzFyTjd6SkF4MzJDcE11cWo0dTJ2UUVHQU9vSmp2TmdsNGlleDI4U3RudEdyV0FZMi1HakZlZzliOVBOYVRrUGNoVFJuTjZVS2JsblBuWmNsdWl6QVZhQXNXZnMxLTdoQWRHVDE4RmJkeHFVSFc2M3d6N05qcnRIV2xPdDYwSDFxb2ZWOEdM?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46012.59103009259</v>
+        <v>46013.85763888889</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dozens charged across Waikato amid retail crime crackdown - Waikato Times</t>
+          <t>Amazon delivery at dawn leads to gunfire, Coweta man charged - The Newnan Times-Herald</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 00:44:15 GMT</t>
+          <t>Mon, 22 Dec 2025 17:56:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPWFpwZ3FuYmt3MWJyWk5UblhJaWZvdjg2MWhWM3BZZmJuQjItM0pDY2VYTjV1YmcyTTdFWi1aYU5BamQxTkZxU21BQmRMNnN4TVdoZHVuUDVUYXo3U0R5QlV3UnprcHZNNFRkbDk0SjVCTExsb25IQ1RvQVNiQmdOSDdyTFVsZEZWQnFUbDY5NEd2dlIza255bUhBRjBDTk1wbkZhYk0xbkpPZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNdzUzcnFPcFpjdWN3SGdXTUtRMXptcUdjQ2hDM2k0OVRoNElPdzBtdlo3dGhEaHFzajluQ3A3QnRzTkRFSW9rRzlkekhGUWdmUDVvODdCcUhreV9wbzNLdEpxcnFqOTF1S1gzb19Za0NQUTFiRXJMcEg5TXc1czE5RGhoTFB2Y1lGeTV5RFh4VnFfRVBYQzluQy1vOXd4X2JXRFJXMXZ3ZkhJZU9SdTE1UF9NZWJJb0pRZjQ4d01Cc294VWQ5Y2tfenA3Tkt1aDNTUEplb0dtbURFdlU?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46013.03072916667</v>
+        <v>46013.74722222222</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prolific North East thief 'on naughty list' when trying to get housing at Christmas - Chronicle Live</t>
+          <t>Gift ideas for your dog walker, delivery driver, nail tech and more - Good Morning America</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 15:12:00 GMT</t>
+          <t>Mon, 22 Dec 2025 10:45:00 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNTzJ0YTRzOVo1WXBJaXo0Q21kdThkcnVlTmlVM2Q1WHJ2aG1NcXROQXdyRld0c3FYMGlPZFBDZ25UWHc2VldYTXJmYTk5WHNnQkhQdnd4M05JQ3hNSDBxQ19BcnlfM1dhZEg0NnRoajZETm4xRkFlTGtjUC1za2lwMUF2QnlCMXpHT3NhWDZSLWJja1dh0gGaAUFVX3lxTE15eHQ0dzRJa1hrZXRwNGg4RG9Mc3JpT0RjN0t1eVZBWDZidlpFN2ZMcmRJQ1pMdWRrXzNvQ1RYOGFGS2puZlMtYThTa0hXWTAtTERwTTNBUWRYNGFIR1RnUGt4WThENW5iQzJXbjBjamVlU2FVRkFqMjJEY2ZEdDd0SDZBZEZkY19hVEo1VWgySFpBYVlrVkVDSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPczYwRHRmU2stcEVuYVBnSHFlbHhjOUJUbDBELVVYTnJZX2xrX053Y2FQNzd0TWN5NEM0RE00RElNeHZMX051eTV4SFFCUEdONVdFY0hrdlJVMExDcEFYQlo1bjhpZnJScTFqYVdRc1NPdEprNXQ4M1MtUlJWaXl0Qk0yaTdGZkFFMG14ZkRfV3ByMThzbkFVYXA5QUgtdzZXN3hzcVJR0gGrAUFVX3lxTFBGRDFzS0Z5MkwzeUhUMGdNcG12Si1zcnhLdUFvSGs1S21lamhWTFByQWN1MFVDM3NGWEozX1d1ckxLQXJYcVNfYmhCSzUtNlYwV2FkT1F3bDNzYkV4TEJEQ2FaX3FBTFBHZERndVhFSDhGekVYd0RNY0kwcjhiUVhSSGQ4QkRCekpIZE9SVW4yRUxGeERIMU1nOUI4Szg1M1RfbzVMdTQ3UjZHNA?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46012.63333333333</v>
+        <v>46013.44791666666</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Trio charged with organized retail crime after $4,700+ in thefts from Chattanooga Boot Barn - Local 3 News</t>
+          <t>Unmissable offer: PlayStation Portal for 199 euros on Amazon with immediate delivery - Mix Vale</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:44:00 GMT</t>
+          <t>Mon, 22 Dec 2025 19:03:08 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQczNBMGpvX3RzV3RhUU0zaFFTd1M3TlQtdC1ndndTd0t2SmVWLUtNRUFwdkg0Vzdyb1BRWFJGejBjaENoLW9VaXRLQVpCTXEwcTB0N3dRdlIwcHctV0lDaDl0bk5aTmQ0RFdlVzBfTmp4TmZLRzVkdEh2NGVuclJqNnU2ekZsREFSZTdsTS1yU3pfSmprakNHdndrZFZNM0hIREtRdDFwMW94MzNLZV9tNDhvNTc4QmozdVdyNUlJOTBTcWZZZWdUY2MzZm0yTGREb2Q3dU43R0JzbURqVjNQd2kxbEZpb3JNTk1rQzFJSnVib2NUWGN2a1BDWE5JNzA3a3ZpbERsMFc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNcUl0cGhVZmFDdVItbUZWQjNnRF95Zm9WNXlwWFRUVGZyb0NpZ3JVVjdTeHFSeDhDVjg5bjg1Um9RZHNjdW11STlGNUdza3NSUGR2NU41R1VsNi10cFFpZnRFS0FGYjFIS1E2aDVqZXRVVHc3SjMyM0hmWG42RHdaUVppLXZlSG5xYVNMMndmRWZDdDBKRVhwSThERklvRmVxZmdNZkRnUnNlSmRvaDFLMDBNb214Q0IzV3Jxa0FtWVZqOHpHcGVUa9IByAFBVV95cUxNcUl0cGhVZmFDdVItbUZWQjNnRF95Zm9WNXlwWFRUVGZyb0NpZ3JVVjdTeHFSeDhDVjg5bjg1Um9RZHNjdW11STlGNUdza3NSUGR2NU41R1VsNi10cFFpZnRFS0FGYjFIS1E2aDVqZXRVVHc3SjMyM0hmWG42RHdaUVppLXZlSG5xYVNMMndmRWZDdDBKRVhwSThERklvRmVxZmdNZkRnUnNlSmRvaDFLMDBNb214Q0IzV3Jxa0FtWVZqOHpHcGVUaw?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46012.73888888889</v>
+        <v>46013.79384259259</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4 arrested in organized retail crime operation at SouthPark Mall - WCCB Charlotte</t>
+          <t>Amazon launches Western Pa. same-day delivery facility - Mon Valley Independent</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 18:37:07 GMT</t>
+          <t>Mon, 22 Dec 2025 08:09:22 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQT0NuQWVSeGZ6eVdGTXFpMlJ2aVN2V1lTT0QxcGMxNzU3NzZLMXhiWnlvVjJKLTVoczhPTGZ6SFFRR3lZSWVxcExtWmpYaXloQlpIZldnUms4NnJmSW5ITW53dmdBTHdBVjBYb1dLcWNTeWV0dVlxYWZubXVxbHRNWUZLQ296NzU0YlYyLWcwcG0xWldDaldVWms0NlctZFZ2YnJhNXNidVR1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUVRpTlJwcEpLYTlPZzIyNC1OcjJtQnZkY1d0YWg3Zjd3UTFRQzBNSUZLRHFJVlh6VFVubnVwTFVoRmhEb21lR2tCVlVtdTFnYzFLWlhsZzFkX2pQdWRpS3R2MzNNaDNIZnFITjBwN19nd2VPTUZSVUVZRGRzcWFRbFNaREs0QVhrWURQY0gxQndzQTBxVGM3UmEzaDhSS2xfYjhXVw?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46012.77577546296</v>
+        <v>46013.33983796297</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Belgium French language</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New CCTV images released in Carpenders Park shoplifting crackdown - Harrow Online</t>
+          <t>SpaceX test flight explosion endangered 450 passengers on commercial flights, FAA files show - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:22:54 GMT</t>
+          <t>Tue, 23 Dec 2025 06:18:13 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQam1NS3IwVGpWSjZRajg4LThELVRyS0gtNU1MRXRuN291Y0VyN0NERlBLb2ZHOS1jcHEySzBKVlBBUllHUjJEbEszTlZ4dm9qVHRucmx2WDJaUDNlU3BUUVhCeUtWRGUybG1TRndFUzd4ZzhyNFlRaVFXN3Fqcy1PVElmZGVNbjFtYWZtbFVCNXp5VlNkZnRCVDdOWkRLR2MwMURpRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNdjUtWGtLTEE5bFY2dU95NkdBbDAyaU9zcUhyUzV3SDJ5UEFQRk01NzNBMnZtcjJPZ19SVVZUaThkVnRfaGI0czZjaTVEYllORDBIMDR5Zlo4WmFmWV9ra1gxWkFlbllfSU42dTlQaEw1V3JuSWluYmZNemllbWg0enAwN1M0a1JqZWVFa18yWEhFOVJRYnRPTmFVSElCSmtxaGgyS0I2T2ZIeGVqY19pRkR2UkloS3pPLTE4?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46013.51590277778</v>
+        <v>46014.26265046297</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Police Charge Suspects in Goulburn Retail Theft Bust - Mirage News</t>
+          <t>Hinrunde Wrapped: Looking back on Bayern Munich’s first half - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:00:00 GMT</t>
+          <t>Mon, 22 Dec 2025 12:20:27 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPNWR4di13MWE5YWEyNzlNRUdKeldiTzFvdzNYVklDTEVwaWVBelBLTHFlU1UwVWtZU3NTM0ZoRkpYYm9CVS1HcmZVeDhfZ3dZQ19YVklKcXl1Q3pncUNabXlwQWdhTDhEOWdnVUd3YVZQa3hoQVB1SmVFRkxtVFB5dWRPTXl0TmZtamtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOazJXb3ZtQ01lOHpqZTRWbFJlZHEwNGJ2ZHZBYXZKWU1DTjNsUWhrRFdiOEU5Mkd5ek1TVVM3NFVIQlFyQ0x5anMwMFZnaE9ROHVCQ0ZaRnFJTVNpT0pQTFQ2OXIwX2pzMGxnYk1WQUY2TDBOZEp5YjF5OUdZZXg1UVpWTFVwbEZYMV96TTVqclYxbEtudHJiOEtqQXZ1eUZweE9QR1VPZVRwUGgtc1RqdDA0TzFKaWpuc19UOHlidjhxVDJVbzdV?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46013.20833333334</v>
+        <v>46013.51420138889</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sacramento County Sheriff Reports Second Day of Organized Retail Theft Operation Ended with 8 Arrests (Video) - Sierra Sun Times</t>
+          <t>Singer-songwriter Chris Rea, known for 'Driving Home for Christmas,' dies at 74 - ABC13 Houston</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 15:39:44 GMT</t>
+          <t>Mon, 22 Dec 2025 16:48:48 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNLS1xcy1SOUcxNS1tZk5KQ0R2NWIyODU3T2MySEhGSVRlalZIQnBkTHdnMGVCOWVpTHNGby14UThrS2Jmam1MWlhQaU9sQzd2c2NIc1dKRlF6c3BZTjNlNzBkem1IS1hxcm5FMEF5YVNMR0RDRGJSU2FKdGcxRUlBRmEwWFlHbnp6aDItOC15bHYwaW9GX0VCZVcyMDExd3ZtdGRYcjVZR0xZWmdjc0VhZEhGQ3JhaFBLTWVDdGZBcVRPZlVRN0NCdVJSeWdCdjBoYmNhem1sLTZwWmYwaTlhRTc4ZjBiejFUSVM4NXVVUVJLdEFOSWQwMlNRd0pXZ2tlVExqMC1iajNJUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNRWZPTDVQT3pQR1J0MTA1aFBaaFhXdHRzMWhrNnEwWVFDRUdCOUFXSGZsdjNzVHNiWE93WHpyVVZxTGVFZXZ1bHFnSjl0b241dlVzVW5XSkNaQ0w2d2w3bC1QLS1wcHgyOEctc0RYYzVzQTJwU2YwaHBOTVhuYWZYNS1GRDFKdnFmRlh4QTlxQnE5U05vdEZZSEpNMExHQdIBowFBVV95cUxONHEwd3N1dFJsblRfelRNTmg0QnhaTkFxeXNrdkE5M1NrRkxjQmQ0RlhXS3pVbElfdWdiMTZXTFNmV3N2Ym5zR0tQcWE1eU9Vd2E4RmhqZHUzY21NTVJZNUw4ZEtVZkRIaXd4U3NoOE1MaEYzcE45NnQwVGFzVzNaMk9QV3BKLWpVcUlBRDU3Q0R4QjlVWk1uSVFSc0dMa04wNDA4?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46012.6525925926</v>
+        <v>46013.70055555556</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lancs man jailed for shoplifting offences just days after arrest - Lancashire Telegraph</t>
+          <t>FC Bayern against Hapoel Tel Aviv: All you need to know - FC Bayern</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 14:00:00 GMT</t>
+          <t>Mon, 22 Dec 2025 13:40:00 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeTBXa2hlanh3a1p6cDFpaHdpcDZidU5DVWVOWmVnV2ZQQjY2Rnd2Y3hwZWVtamROS2g0RkZZQmJIUXdIYUdObGQycVVDemVwX0phY1dYdG4tNmlKWmdHZjk4LUpFZS1QaHUyaU9RQVNWR2pRdUV2M2hpczJpNkR5YXRqQ0JoSVJxZGdrYklMcVg5dWh0YTNfeGN6VlBWdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNNi04c0RXbzk1dGJqWlpHVi05RU9ISUJveUpHV1NFMU9IUU51ZzNoQk5qQ1k0UzV4THRJQnd2cHlxM0QweEdFYUQ2UV8zb2x0LUpwa1drRF8yZ2UwNk1CS2Q0UUhIbnU4T0Z3Y3ZmNWx5WjIyMVd2dWhoVGJSbjdlczlNMTBBSkRLTjhqQlUzRW4?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46012.58333333334</v>
+        <v>46013.56944444445</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russian general killed in bomb attack in a suspected Ukraine intelligence services operation - France 24</t>
+          <t>Goodman Group, Canada's CPPIB strike US$9.3bil deal for Europe data centres - NST Online</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:36:55 GMT</t>
+          <t>Tue, 23 Dec 2025 01:05:45 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQUjAyR2pfNmdjZEJaUUF2MGRkNVF2bWZpTWNSNDUtXzFFOTE1VzZScTdNWjJRb0RqZkdmR3YyY2x6c0owQkVOV3g0ZVBialBiZG9FOTJkNnBSRWJDWVRmMzZZT0lvYjlLX3JKanJONkdxdzhNcUhSZVcxMl9nUVcta0ZLaXBwYmVJR3B2RFkySW9XTHlIUWNDb0tyZTFvMUFMaHFaYUpCQTh0Zk5JR3pjVHJYeG1WRFhNcDRuMlBZZ1ZDQXhNZi1zMXlmRHY2Y0g4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPQzFZQnpnYWFYUHVsU3hfM0RfaXZFeDBjcDdTMXg5T0ZoWjN2MFA4TFVXYnctUnEzdWxPdFFNZWdoNG9TbnJKa29hTThObnlDMjV3SDhmUTFKT19SUXdGZ051SFFlMHk2M3FlTzVVdGQ5V0xBTDkwUmNBa3p2WlRRU2dUR2JkWmRoZml2aTdaYnBwZUE1WmJ0a2hqRXZ4a2h5M3FUSU8xejNQdngyWXFUdjBqTXRHUVZRUWFV0gG7AUFVX3lxTE9DMVlCemdhYVhQdWxTeF8zRF9pdkV4MGNwN1MxeDlPRmhaM3YwUDhMVVdidy1ScTN1bE90UU1lZ2g0b1Nuckprb2FNOE5ueUMyNXdIOGZRMUpPX1JRd0ZnTnVIUWUweTYzcWVPNVV0ZDlXTEFMOTBSY0FrenZaVFFTZ1RHYmRaZGhmaXZpN1picHBlQTVaYnRraGpFdnhraHkzcVRJTzF6M1B2eDJZcVR2MGpNdEdRVlFRYVU?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46013.44230324074</v>
+        <v>46014.04565972222</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Evansville police: Fatal shooting of teen came during botched robbery - Courier &amp; Press</t>
+          <t>ECB to Celebrate Bulgarias Eurozone Entry with Special Light Display - irishsun.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:06:00 GMT</t>
+          <t>Mon, 22 Dec 2025 08:23:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOaHBTU1NqUWx3eVBndENkRVRJMkt5M1Fsdl9TR25RcDJvSXhsS3RxeTFxNE1acFJUUV9JQ1pRRTMweHEwQUN1MGwyamxlSnpGc1NuUFZmZ1lFM1JCYkxQOHBhMGZDV2VUWTFoSFFmd0hTYU9qby0yWjdLZUs2SW1iSUV3MEFnNkpVaURBV09aYVhHWDlpQ1huTy1nNzdVWXFVNm5OcGNiSTg3VUF5VmNVTThMMzlUQ3RvYmtiaWQtYjlGSzA5LUlKN09zSnNhYTZ0WGJGSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPY1ZBSnZYN2lYRnFMWnNwRHZ4a3ZMejU5cW5waDFEa3dqN1d1MFIyQXFKc25pLWNIdDQ2MURPOGtpUkZFU2pkMVlLU0gxNjZ1MmZQemtkRFBvQmVhNW1fNmhuVjluLWtpQl9zbG5RaVpWVmRPSkZMOEoxTHhKUFZ2Q21DbXpCWlIxM3JHMWo4UlhMZTd2eEc0Ml9kbmdPLUpjenFGN3p4MUtSbWJV?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46013.42083333333</v>
+        <v>46013.34930555556</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Real Madrid watching wing-back previously linked to Liverpool - DaveOCKOP</t>
+          <t>Bayern focus on Stuttgart but Leverkusen Champions League tie looms large - NST Online</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 20:04:21 GMT</t>
+          <t>Mon, 22 Dec 2025 16:18:00 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPNEpwNkdYcHBHQ3h1eWZHbjJwSU5TcWRoN3FGaXMtZENOM09DUWRRbmQ1Q1ZoQUh3S05INUNXdTljdklqdlZBZkdQTy1YNURfTmg4RklXSGlUZVhrbmNpM215Umd4YzRvR2J3LVJqVkdGZ3cwYkVyZUhOQWJpajNRajd3THFBNzRaQkRqcW05WEN5MjdJRFZkRmlKQWFDVjZaSEZHaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4zLWQ0S1Vya1JFSThOeHE4YnMtRVY2VVRWRjBmam5wT1JxNDE4Q2dTZWpPcU5ZX0pRMjZfV3dTdnN1azUxNk04M25wRWRXZy1YT1J3cmhEQV9kXy0xcDIzWnAwZ2FIUmF1Z3dZc3BkSWc1S0F5TmZvQkRmRHAxaVk?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46012.83635416667</v>
+        <v>46013.67916666667</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unbeaten Gael boys rally to top Madrid in Hardwood Classic - messengernews.net</t>
+          <t>Lamine Yamal Launches His YouTube Channel with a Special Nod to Luis Díaz - Soy Fútbol</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 06:29:26 GMT</t>
+          <t>Mon, 22 Dec 2025 20:26:26 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZWNWazVGX3hpeGYtd3l5b0tIUUxRdW5OQmgyb1JnNkR2QjNpUnBadWQyVUV4RzZnV1hUeFQxWm9mU2ZLV1VTbV9SVU1wenpyLW96T1dLb2E4U1RDWW5oeExvUnFyVUhFcGUxYzVvYl9zbEJfSnpocl92SXQyZkktQ2xpTnByTUd3NGJuRnlCMHNCNGFZTEFtRExTWXhWNUdacGIyM3pWejV4WjlDcjB6d3AtT1lSeDR0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQM09QTHlBZEJTczFjQ0NJelZHNnhUSHcxV05YdzJldzBaSUpTVVBrUUM3dE1ha1RaeUl3Y2dzbHcxSHhPQjIyRGh2Q0JUczJrRDh3TnFKLTU4UUVfaGpjNXBJRzlhdTZ1VTUtaDdWc0Y0bmIwT3g4ZmtOY0J3c29JQW5KWTA5ZmlJNndzWmpxMTd2SFZzaEU2b1lmOU42VHV5d3BYeEpOdVVlUVVES1lvWldTcE1JNkE2WndNTVlRMHJhOG5iRFNIcw?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46013.27043981481</v>
+        <v>46013.85168981482</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>La Liga: Why Atletico Madrid players were forced to train barefoot - MSN</t>
+          <t>Secret Kangol Memo to ‘Do Nothing’ About Cruel Angora Sales Accidentally Sent to PETA - PETA UK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 00:30:55 GMT</t>
+          <t>Mon, 22 Dec 2025 10:09:09 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgNBVV95cUxQc25hd2Z2d2h3Z0VrTFpzNktyWWxJckwwdURMaEd1U3ZDS0VvVlpXMThDcnZUSVlIMko4YUxYWTFiS2p5TVdQNl93YzNKRmdYNFRtZFU0SUowNkNFUFpWSThOTjE3QVQ5bnNzUDAxbjQ3ODhsa0lEQzN3N3BGYjdhTVprYmZPN3VYS3Y1TzdLWnpac1pONlFYUUpBRW5WdW5tQUpLRmZtMjdoTmtHbEx0T1pnRFV1YVllMlpvWUhmdjVUMnNydEFzMlItb3doS0h5TkpfWVQ2YUZCeVNiTVVpQ0lZX20xTk0xaURKM1M5M1J5U2FodkxMQU9reXpIVGI5ZjA1MlpnLUNXQlNDSE5oMnNpamR4d1J5M1BzYzdwdTd0bGdZRWtlYjV3YmdWVlpiUGd6dXhKVkRtc2pOVURQMGZ2bDlFVWxuWEpFb0VhdmwzeGVTTVRuNzV2aXRBd2NYcHpVNkxMNzNjQ2s2bnJ1czhXSnBNMFFaTW9vRDU2SGF6akhLNVZtTVlpem54dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQQTYxYjNLY28tQm5FdnZkbEFGUWxGRDFQN2pkRXdaX0kwakR2Y250UlBvTFU4OFBFY3dRU2drTmQ3WEtqTVJwcHVsTXI1ZUxwZDJ6QUVVTnhNNHRUMDB2RmtuOS1majRua25vMnBsRmFVVTZsVkxpQnVMbGEyOTFMbHk5N3hTTU9xZnpyMjg4cWJ2VmFpdVBQTXo1bnZfTEdlMWRfY2hhSnNKaWV3YnBMRzVKVklSM3hNRjJSekt6a0ZJVmFxajFv?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46013.02146990741</v>
+        <v>46013.42302083333</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lamine Yamal hits new milestone as Barcelona beat Villarreal in La Liga - footballtoday.com</t>
+          <t>Do corona-contaminated mink carcasses end up in biodiesel? - Wild beim Wild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:25:24 GMT</t>
+          <t>Mon, 22 Dec 2025 16:02:46 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPbjhpY0ZCZ3FGZ3hITnV5aG5TaTUxZjdDVFB4aGJLa01wbUpMYUJqNll6OEZZcU13RGlES0FLZEQ4eXJfV0p6TkdneWxkMGFMTktJVmw4RGpwZXJmMFRTQmJzeWdnQmdOcUZDRUVnWUZ6cVlvcGNib28zZ3dCRElvNTVfT3lzN0p3THpvM081d1hlRTE2dUtXNGgzVUNxZm5rUVRYQVN4QnoxZTdLTXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQby1UZUJsVExubl9uZ1JqMERNV2xOQ2RPMURqdnlTODYtNDMtOG1MRG1CYTZXN21mTFFVSEtVR0Y5dHZoWHhKMWROUXZ2djM3dk9OTkxhSjQtSGY0VnVHSWRHTDFqYXdBZ1FqSFgxWTVEb1JGM3Q0V1VPNlZrWm9qNGIycFNJR0llX0FsVVJVMTc?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46012.72597222222</v>
+        <v>46013.66858796297</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atletico go third with comfortable win at Girona - The Guardian Nigeria News</t>
+          <t>Faux Real: These ‘Fur’ Coats Won’t Get You on PETA’s Naughty List - WWD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 18:08:00 GMT</t>
+          <t>Mon, 22 Dec 2025 17:24:59 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPOGVSUXIxVEo3di1JbjFPTDh0RkN5Mnl2MmVPdURzQUFiZjBZZ1J3R1I2R0J6UDZtVEpTN1g2UmNYVXZRNTZ0UmlzNE5YQXk5XzhfZUxTM0UxWjl0OG8zZzU0ZkN1RDVyYURlU1htNVBGdFpXS1RScFhZSUlqeG1zZDNZb1lUTjdzUmZqaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNUmJqbnFpbTRreDZVTHdfRm1qVl96S19HUGhiS1Bnc0VIOXdsdTRSS0pIU1YycUwxbF9fRmxyTzBnNGV6ZVk0dGUxNmo2ZWowOGtBelg2TmtMVjY1dlhIX2daYjNBRV9ud3E1NXgwM2dUM293Q2pBbDdkTWhRWVBidXhfb0VzN0hIVVE?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46012.75555555556</v>
+        <v>46013.72568287037</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sivasspor dethrone Başakşehir in Super Lig - Yeni Safak English</t>
+          <t>This year’s divestment campaign highlights - Friends of the Earth Scotland</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 03:07:31 GMT</t>
+          <t>Mon, 22 Dec 2025 12:44:41 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNV1NrVDNiU01SbVBWRENENEIxaUljR0pLc1lFUHJwampBUGNPVGtjWUlRaGdIVGRvYUp5SXFyeThSZTJtZlhUa2txV0ZSb2NVQjNFRHRqdU5tNEdMQmFVZmhJSld4NEpEWkJ2MkxGRWNvZXk0UmVZX0k5aUZIV1I1V19zQnJnNW8yNEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE90cVJ2eGxrLTgwdDZzS0tVaGU1T1R2N0p2dlF4dGVMa0FXZWdDeFoyLUNCd2xHMnliY2JaLUJTcVN1d3hfbGJNUHh2OUl3ckd4bE94Mzg4T2o1SlFoUXNUMnVWRE51bmtGYVVtcXV3?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46013.13021990741</v>
+        <v>46013.53103009259</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The NBA lands in Europe: a farce or a historic opportunity? - Diari ARA</t>
+          <t>Greta Thunberg banned from Venice after dying Grand Canal green in COP30 protest - AOL.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 06:00:57 GMT</t>
+          <t>Mon, 22 Dec 2025 14:28:03 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPWTk3cFRBd3Y0RjlZblhXMEhqNVRMYjRXbmNES2VKVi1qX0F2X1Z6X3ZIUlA1bnkzRGJnNVAzV1lRcm1jWTJ2UV9CNnNpVUhFdUdLNHVWMjZReE10WWxiT3lEam1SYVhRSjQ3eGRUekxjWkFaN1ZmdjhGNWttbUlrXzhSM1Bya014QjJuS1NOT2NmREdZdi02UlVXMXLSAaIBQVVfeXFMTlFuQTFYTTRMZXgzXzl6OW1vQW1xU0xYTjZPTEU0TFpwdFYtMlhONXlnWnFKcGprNk9BV2JsZzFCWkRpNGNHNGFpaUJ5LTd2TGlvbTFENDhtVGhqWV9ndmZQLWZ5WFdJNmNMdlJHbnY4ZkllekVCOHdJVE9qM2xwM0I5QXRGUkZfUG95WnVKdzJoS0ZIeUpHZ01zMUU4SmZ5YUVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNZkwtcDRLSmt4SmhmWFo2RXp5ZG1lWktjVVRHeG1wOVFMUm5nS0VxV0JxZ3VxUTVjampJOFBqaFB5RXFLSWU0Xy1QRzFmVDlhR3ZxWlpOVFVNYWs0ZXp3aE1rX2N3YmRHdHh6YlpXWDdZX1ctVFpUTVltZ1NRemJoZHFFb3Y?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46013.25065972222</v>
+        <v>46013.6028125</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chelsea bomb drops as Man Utd make fatal Semenyo mistake: FootballTransfers recap - MSN</t>
+          <t>CCTV pictures of two men released following shop theft in Belper - derbyshire.police.uk</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 13:21:30 GMT</t>
+          <t>Mon, 22 Dec 2025 14:11:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOYUxlclFTb2c2Q2JocFZuMmV0d3dTUXN6VnRjUFNxbW92M19BTGRRQ0FSclRvb0RSM0ZnbXdLT25teXRlS0ZZOWRRandrd3VOcldKTnVkQUVmRGJteWtqdzNkZ2M2N0t6YjRtYzhvWVIxRFVhQm1iVXpaTmtid3RHaE9tUTc5UUl2VUVIUjB3NEtaMHlKcjcyS0FrYWtXcUphdUJ5c0xPVmVCNTFsY1dYTTRZRjZ2N0tVZXo4dmxYQlZ4NmtpYkM4ZUx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOeFRLMWNROU40U3p2RzVFa1NTSWpvR0lTLXZYalg3R3IyLTc0bmpoaE1pNzY1dTdGQlNrUjktb3ZzajFIWHNJYzhoNnlVMmt0eVJwUWtPejVNTzJCZkdsMjl5bHJWbEpzNE9yNkQwcXREZ0dpUnVGSmVQN3NFcHNxWmRZU2RQY21ERTQxTkd5LVdOLWVJbzRSRVVyWTZYWlNfbGRpcV8zczlVZ25TUjVzQ2l6cUxGYXpNSVh1ZGJHYldtcGhRb0g1TDdtZFdfdzh1b3BKWVBXNUtwSm5IMnViNw?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46012.55659722222</v>
+        <v>46013.59097222222</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador international Mario Pineida killed in gun attack - MSN</t>
+          <t>15 people arrested following retail winter action in Norwich - Norfolk Constabulary</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 15:52:43 GMT</t>
+          <t>Mon, 22 Dec 2025 15:06:00 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNSWFKcDJzRUZCTHlCS1U3ckJpMjBwZUpmSTRRVW84eXllTG5uR0gwUHlIZTY5SHlHTFNLNnJGMnl5X2dpM1lsZk52M2l2YV92MF9FY25GeXR6WlhPYmNrbVdjRUdlMURzTnpxdG80enV4UEZSTHZFQmZSOTlvd0NZWVdqRFNiS0lYUXF2eHJyNHlDZzMzdFgxZFlYRlMwOU1ra1lWdFV2bE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOaFdOWDJUanQ3VFgyc1JHYm5ReXVJZzFMekdiMS1zZEdXOXExOTlNbVFlbWh4ZllwSFJxcVlEVnpJMFhvZTh3RGtSOGVzVmh1SjBUR2E4RnRnWXdGMUVTa0p5aUlONENCTFpHRUJuQTNVRElyZUFWMHJUY2pnQ1dLT3hncG9MVHBWejN4MXNkMTZDdDMxS0hMQnFld3ZVcmxaS0tJN2ZVMU5tOGtacy1ycnljWlRCRVZmUGJXLTRaS29vUTBZYTlj?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46012.6616087963</v>
+        <v>46013.62916666667</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Barca's Denmark defender Christensen suffers cruciate ligament tear - NST Online</t>
+          <t>Police patrol around town in bid to target retail crime this Christmas - malverngazette.co.uk</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 14:09:24 GMT</t>
+          <t>Mon, 22 Dec 2025 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNM284WWRFU2xLdGVEZEtDRE9Oc2dwQl8yUnVDQXIxTmdHR3JuUzI0ckRReTlZVGxmYWJRd25manZNOXV0TnNNV1NCbUxXRmNZT19sbTQycFRYMGdKUVlvRUQwSzJhRmRvZldTM1BHTXRHMjM2bXlhTjZPNkVpZEVJcERaQXJOY3JJQXdXdDU5NjFWbmtad0VtTXJ2NVZDUUVRbXkwbUhhN2tnNm5oWkZzS0pxUFNKX1YtU25sVXlSUWJnM0nSAcMBQVVfeXFMTTNvOFlkRVNsS3RlRGRLQ0RPTnNncEJfMlJ1Q0FyMU5nR0dyblMyNHJEUXk5WVRsZmFiUXduZmp2TTl1dE5zTVdTQm1MV0ZjWU9fbG00MnBUWDBnSlFZb0VEMEsyYUZkb2ZXUzNQR010RzIzNm15YU42TzZFaWRFSXBEWkFyTmNySUF3V3Q1OTYxVm5rWndFbU1ydjVWQ1FFUW15MG1IYTdrZzZuaFpGc0tKcVBTSl9WLVNubFV5UlFiZzNJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQVDBOVm5iRTZiYVY2Z3NJUjNUYklycmhUX04tNExsSm1vTnNkNVIyY1dtNkRkYnd2eUUxZzRMUFJWUERiVXFTSkxqWFRza1dvOXIwTWtCWHFzZEdEZ05aQ2dCS2ZpcENuQUxjQ3JlNEJsNHpVZjJyQm04aXJsUHEzTW5sYUdTZU5LdHI4NlRMWFBiUzkyOTFMWGI4SFd5TWxf?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46012.58986111111</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>🚨Liverpool, Man United and Real Madrid among top clubs chasing Leicester City star - the Daily Briefing | Substack</t>
+          <t>Two shoplifters jailed as police crack down on retail crime - Blackpool Gazette</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 18:27:23 GMT</t>
+          <t>Mon, 22 Dec 2025 13:07:00 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPdERBQmdzdXVQazFKMHBoQXlmX21XTVFJZXdKRjdRWmRQOHRzS3BNQkEzQXNieU5lUkhVUE5RMmNXRVl2d2JJR3RzMlIyVGhIdHI3czZ2U0V2VV9WZVRwUm1IeEZWa1NhTnM5LVdXeWdQbWFueEdMOXBLY3k1cmt6djRtWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPQXFHYmFKM1FLYVJoMVNZalRRbTd4d1BXYnlCS2NORTR1ejBWOEVROV9RWFRHRzAwd2xpUDJxdGtTa3hJdm5pWUFlamdwSGFQWndtZkY5SzlBeXlfWVowclhSTE8zNlpIcWl4UG96OGpYbTNINVBzRDBlWUlQZEwwRl9EYVd1LV9CdkFjODhrRWVkeTZXRWQyRXZvQjlTYzlwTFFrQVJKcGxhcldzeVJmQlp5dWNCRlYyb0xjTVNnTW9CXzRKUmJz?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46012.7690162037</v>
+        <v>46013.54652777778</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Barça 90-80 Joventut Badalona: Great game, great win - FC Barcelona Website</t>
+          <t>Offaly TD Makes Call For Retail Crime Reporting Systems - Midlands 103</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 20:25:50 GMT</t>
+          <t>Mon, 22 Dec 2025 14:33:48 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQUlo1NzFQczNLNTdMS0dPbERmNmQtRVJUUkNkRFNQN1lPalcyYVp2cFA5VDNBMU5ldWFtOXdCRW1UQURIWW1scDV0MmF5NVRpVHJETmFZcVNVY3lCLXEzZlRER0xDWXRDcmtDaWJCSm9DaF9HUi10M0hOajJJT3hMZnBYLTNQNmI1bGxJTmxiRVVja08wcXZVYjN3ZEh5RHZ6MEhTNFdpang0WUl0M1VKdmF1b1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQRnN5Ui1ZVWMyNGF5LU96N3dEejJBdlM2LWM2SlBKeGlVdDc2RXBlc2U5eHZqaVNRZk5PcWE0ZGp0UFFPNl8xSUVuckVNMXI4NlJFeVl3Vnp3dm5pU3k0dTNyNDRyV1NZb3o0anU1cFN2clN5WURfRUdGUE9KQmpkcmZMeFhHX1ZfdHh3ME5PWmlCUGhIdDhxMF9RQUpEa2ZNc2JlRHNB?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46012.85127314815</v>
+        <v>46013.60680555556</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vinicius Junior under fire as Real Madrid prepare controversial move - footballtransfers.com</t>
+          <t>BBB warns of online shopping risks as Chattanooga retail thefts exposed - Local 3 News</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:27:00 GMT</t>
+          <t>Mon, 22 Dec 2025 20:14:34 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPNmNTT1FJSzh5VVQ1aVNyNzUtRDNvR2hVLWZrSGNDSWFQUl9rTmcxeHdxcUxPb0xnQTJVVTlJSmlwUDlwOUdUaDlQNGxkcWZIYjhsR2R1NzFvX1ZRalAwZG0wODF3cTFJbkhuVnI2VjhKdlN3cmViZ1VrRUhrQ2F3eGpzcVJuZklEaEI3VVJjTVJweXp0MXlRb2pIaUhWdnktd21QX0tycVIyWEl2UWp4Y0Q2TEdQRUZPUW9XSF94cjY4cVhLM1pTVVdTa0FFTG50WUU4NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUVTSWZESUg4U2loblhMVWlIaHdONEpJMjhwWE8xZjJkNVF6WGdKVEpXSnhCVjc5d3Q2bjJzcW9HRlFfU1BzUXNFWldMYmV2OXJrZmVHSGtNc3FCTnJHQkkzZ1RRN0FvWi1oeHB4Y0tQZ2NrUFdKQUhUTk9iTUFkRjIzZVJVVmYwZmRpZF83X3RJcDlsLUxEejNrMTZOcnZ3OEctVzVlbTRxZUxmWGFPdlo3SjFXQ3lUZ1U0WV9LelZ4bjExTlFDRkNDZzdDMDlaRkhaSHpoQmFNV0lyczdBZjlMbzRfU2JEZTZtOGJzYlc?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46013.43541666667</v>
+        <v>46013.84344907408</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fabrizio Romano Transfer News: Isak INJURY update, Semenyo BATTLE, Rogers January DEAL? - footballtransfers.com</t>
+          <t>Ohio AG Yost and KPD announces indictments in organized retail crime, TCSU investiagtions - WKEF</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 06:47:00 GMT</t>
+          <t>Mon, 22 Dec 2025 20:26:14 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNUHpIRS1HMGEtUTNRSXBkU09WVHcybGVQRm1iZEJ2SmkwbmhVcFpRVC1YR1piS24wTDN0bVo5T1g0bDUxU1BwM2JoQVh6ZDlXX3VkYzE0eTRndms2OEFWdjJqVE1OVmlBMVBzRF9FUl92Q1VmWGU1UmF0a1JGWm1WT2lLdi1qdnh6dURtOXpYS3A1TWp3RHZsa3haTVZmU3Nib1pzVHFnUGNkQkV3Q3lKcjR4ZDljOWozUVZ1WkQ3STI5c2dCYWVTT2dOYlF3N2ZIUDc3RXRIRU9tYUpobzFwMUQ1Q0ptVTJYLTF4cVlkRnQ5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQbzZXZ3pza1lsY0poa2FLcG1FUVJvSTNpWW1kUXJDVmU2R2tNVVpkcTFLNVcxQmg3eHRrMlVCVXhiWGFGcHdraHBsc2pZRURzcWUyVmRiU19yT3FRcFlvLUlVb21UQjUxeVpfRTJNMkZ0cjZkMFh4YllvdnBMdTl4azVmbjRZUnVWMzlJUnZSUHo4ckFlWkdqSUx5WWdpOW15RTh4RWl3Mm0tQ2taWmlUNEJpdW40OTl5RnMyX0FaNmtBdw?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46013.28263888889</v>
+        <v>46013.85155092592</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Coach Confident Mohamed Salah Will Rise to the Occasion at AFCON Despite Liverpool Crisis - Republic World</t>
+          <t>San Francisco Police Nab 104 Suspects in Clampdown on Organized Retail Crime in SoMa District - Hoodline</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 14:23:05 GMT</t>
+          <t>Tue, 23 Dec 2025 00:28:13 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMU41Zk01UERqZzdEdno4NWhIdERQRXVNdXpRNU9QejBBWlhWNGRDcDBTZ1IyV2E1cG5HWlVuSkNmU2NCck9VWWU4Zkh5UHg0OWlDUU1WQkFiYko2VXhyRVZEckNXb0ZhNHl0QlV4eHlScXlBclpVNkZfTmlYUFVUMVRaRkEtUFI4d1ItUTNISFlnN19rOE8zWUlaQ1dWRE5aQm9VV05MMTZ5UjBTMUdzZlVMc1ZqQTVvTXJDbTdvZzRyQzhndUJYS3A5YTlxbEx0dUw2X2YtbHbSAd4BQVVfeXFMTTJ5cnBhWUdxTW9pQmoxeUFKSjdMVU8xaWg1U294OWVfaGE2X1V2NXNndndnNFFVS1RSTFRPU0RBNjVrdi1UMXpMY3J4TDdtdmVaQ2xNb1BvWjRMUGtrLUhBeE41akh6ZzlIZ1B5S085ejY2dW1GLWxYeWx4dWlEbUUwOHhNblQwcHItb3dFd0d5bF9ULTJaeEhBd3YzWVBjQ3dlMnFoQS1xMko3YWZUMWE5d2V4ZERUamJRa1RzNmcyMENXZjFfbHJzLU9yeXlKS2x6M1NFV2d0cWZicVhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUEJZbW1WcXVSeWJReVdvcWpia1MtbmRQYWxzalV3ME1TRXc5QXVFNEhxR0hnY0FYT1JUNnVkOW5BbzdUMlo0b2FiZDVRMUp1d0xJOWFuT3R5WUJMQ1gzUXZ5NVA5bzVvdnVzRzZ5NzNzeWJlUWF6UWxYXzVrSEZMUFplYm51a0p3RmZjMnY1Z1lsaTJDTzc0OVpzdlNRaWstYjhLTjZIMVo3ZDEwNWM1VUtOdjZRZTJ5bmlycldBNVI?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46012.59936342593</v>
+        <v>46014.0195949074</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Barça: Xavi Pascual's team, touched by angels and with a perpetual smile - Diari ARA</t>
+          <t>Greater Manchester Police make 671 arrests during ‘Festive Friday’ weekend - Greater Manchester Police</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 13:21:56 GMT</t>
+          <t>Mon, 22 Dec 2025 16:38:00 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFB1UkJIZjRxYXZLOTZNalFZdHA5TFVrcFlxNTcyZC01bzhOUkd4dnczRlluYXFIVkpzWTFZendQT1VZZkcybjR5Sk1hUnVtLUJjY0lVTXpValdWcTF4bkJ4R29oUjlIUjJnZllRMTQzc3RWb3NVbVhrdlVtSzROZjTSAYQBQVVfeXFMTkFoT3lkbVVndFNEQWVtRWk2MzdENlcydUZtenFoYUhJeGtjc0ZGVmw1ZGxFVTNXa1BxVVFyMVJ0cmFJeGFScHlkWVpMT2ttYUZTWkNiS1Vud05mOWhjelRxRlBJTEc4V0g5cGUwTXE1NjRBWld3dVN4ajI3UkZpUnN6dk9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPclpHLWcxRUYzZVlkR2FyYnlKZm9zNktFMUJCNElveTNDTFpPb09oX1ladl9KN2hZMkE2eVBxdmpBSUxrRmVMOTdnNzIxekw0UWI1dnZGWWdQbzZvckJ1NHFZZV95YTFJVkpaMU9pTXQ4VW15MzlmaTJZQ1JXYTdlajBBTGNuc3dVbkNhaEU5d3ZEVWZMc1diTlQ1dmNsQjV5U1FjUExDd0ZHZWQzRmtfWTlsc18tSnBacm9YZkxHOXRtTUtfM1lNM19rV2VsbkJEazhaQU10TEQ1UzU3VTR2Mw?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46012.55689814815</v>
+        <v>46013.69305555556</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eli Ndiaye’s rookie NBA season has come to an early end - Mundo Deportivo</t>
+          <t>Serial thief stole almost £1,700 of cosmetics from Sunderland Boots branch - Sunderland Echo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:20:00 GMT</t>
+          <t>Mon, 22 Dec 2025 15:18:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPa2taN1I5LS1UOHAwNGt4allCLTFSbFVZaEtQZkgxeVVsbG8zOTB1QlJDa3FyUTd3bkZKZFNBeFVObXpVX1JiNXAzdUNXMU9iV0lScXRxWW9zRGNXbTY1SlE5aEtBRkZtVkx1OC1EQUpHaFhyN01yejRKSFYzOWVhdUt6ZXBEZThtZ3dGU3NtWGxOMU1jLUJpdlVXd28zdmNBcnN2alJBcnZXdkFaTktZRFlPNNIBwAFBVV95cUxQU3M2SkY2MWg2cWNvZnJGblkwOGN5ZC11U2JNR1YyenR3dDFqNFJnQVdYcVJLZTlodDFGa2g0RGduanAxdFcxUGp2MmVZWWlha21RQktsT2M0dW9xQmJYWkZyZTR6QkdMZEMtRFJTOWNPZlZtYmhQUHRac053UExEUEQ4aGtFbUp5bUJXNVhpU3NFaVRLcTZhSEowNlZIeE51UThVbi1BUTBLbGNtdjNoblQwV0VseGFqblpmM3VscGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPOTNzLURzei0zQXhOaEtpVlJuWVA0TVEwRXZCdURjVmEyN29PUUk3ZXlraG1NVGZiaWNzSXZJYXkyZmR6TFdqOUpla1R0U2ZlTmw5R0Z1MWwydlZxWklyZmhYcUk2Z0VOUFBySE03cjVjVFF6S1ByTWhwLW4tcmxSMG4xYzNUVU1aTUZqLTQ4akxzOW5tUzZqODhjOWRITGlSZ0NVZDE0OVpEa2ZRWkJxWGlMd25UT2ZSUG1JYWtiT0tqZw?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46013.51388888889</v>
+        <v>46013.6375</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Better than Barcelona where hotels cost $230 and Tarragona keeps Roman ruins empty for $110 - Journée Mondiale</t>
+          <t>Congress Weighs Sunsetting Section 230, Putting eBay, Amazon, Etsy &amp; More In Potential Liability Crosshairs - Value Added Resource</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:26:36 GMT</t>
+          <t>Mon, 22 Dec 2025 19:08:43 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQakVINDFRMld2VmJRSmdfNXpqVmpfZTdjSlo1T2ljanFZZmZtR1pqWUxEMHVQNVY4b2FnUlJERWpmMUlkYVMwZF83a0ZaNkFaRWxxU1otdEhEMk1YMEtXX1JjZkJyMHF6YmJIekQwRUZGTnpqcVpPSnBnZjl3OHJRWUMxOXJvd0FCWmZIaHJkbkZCbTBNU3FSc2hMZFdHSGRYNjE2N1ZfTkJDZlM1QVZxdzBzLVJhUldfM0xqZHpseThJSzRo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1ZQWJHcmNHSHkwaEYtVFVaTktpR29hUTN1WFdVeU5vYUlsV3JoR3ZuRmYyd2o0dU0tT3R1WVlndFJ2RC1ZVnVITEZpMk91WklOVGZ1YVBsT2VhRWxjSk1HWkJ4ZDdiNkt6Ylpka1FLZUE4TmF5aHI1NUJDMDJhbDQ?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46013.35180555555</v>
+        <v>46013.79771990741</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bombshell! Florentino will sign the new 'Toni Kroos' in 2026: better and cheaper than Zubimendi - madrid-barcelona.com</t>
+          <t>AGs Unite to Keep Gift Cards Safe - Lelezard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 19:00:00 GMT</t>
+          <t>Mon, 22 Dec 2025 22:21:35 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOOEQtaFROQ1RZZ1VaR0Y1QkhfYUZrWWhWakExZFN4YXJUbDZ5VHBHWExsRUlsWjRTcWFjVk9rUWprRjRaQmJUVWpSVU0zNV9id3BaRkJtcmFSTmd5X0R4WlNOa041Zmh6TkM4MkVJMzVZamtKWENQaHhmc2o2UHRtWUF1Q1FvNGFWTUpUUjRtSExZR1pPQ281bVZOQVhVdHFOT2ZyR1ZuSGJBUm4yZF9yS1NBbjVaejRfM1BQbVRpTF8zMzB3Z2FDRFo2MzNudw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5EQWNGODRyQ0NuQ2dVUjBuY0lxOHRWSllIVEZxNFdrRlJocTQtSHZ4X2U2bW5jVE0zb3Z1eDktZzZGalRaQ0VsT1V0elpXQ0FzSmpqaHNaUGI1Zw?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46012.79166666666</v>
+        <v>46013.93165509259</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kylian Mbappe Ties Cristiano Ronaldo’s Historic 59-Goal Year at Real Madrid - Zoom Bangla News</t>
+          <t>Heartless thieves hit ‘easy target’ op-shops as retail theft soars - Herald Sun</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:22:56 GMT</t>
+          <t>Tue, 23 Dec 2025 03:47:32 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNdFVMN2g3YVphZDl4Sk9ZeHAwQXhRZmtmeE1hUEtXOFlyb2JaTi1uYmVCSDJTNFpKX0ROeWYtLV9kaDR4VE55WU9kbHhTX002RnhkTHNuNmowdlNOeFJpLU4wdVRiakV2a2NUT3JZWnNUUlJKU0VZTElaVWJGQXRqeFBzNGI5ajJWU3NINDR3SXY2TFZYSjNIZWYwelc5R0dMMkpIaTFlWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQZ3ZaOU9peTNFQVAya3Nid0JfbWw1UnNWQ1VFQ2tkb1RRVjBWeHZ5dDgzcmR3cDU3ZC14VU9vdVVvaHJXTmV5N2JNdGhpeGx2S0dyZE9jU0VEU3VMNVlTd1JQVGEzeDFzQXNWRXZfVGtsZmRRRW5sMEpJal92OVRvQlNMRGNKNHJKUTNWRkNhWUttNHJ5Nlp6ZWdEcWpJejZhQ3huSzIzaUtkb2NNNWhIME9jOVBVbV9fbV9odk12YURhSFdfR282LWtrUEVjdVFCVlV6dFlQc1F0WnZOMXFGQmJmd3RFXzlJSE9teWhlRDVrbmVTc01HeFBtaktJZ0pDYVZzUkJiVVhXd9IBigJBVV95cUxQZ3ZaOU9peTNFQVAya3Nid0JfbWw1UnNWQ1VFQ2tkb1RRVjBWeHZ5dDgzcmR3cDU3ZC14VU9vdVVvaHJXTmV5N2JNdGhpeGx2S0dyZE9jU0VEU3VMNVlTd1JQVGEzeDFzQXNWRXZfVGtsZmRRRW5sMEpJal92OVRvQlNMRGNKNHJKUTNWRkNhWUttNHJ5Nlp6ZWdEcWpJejZhQ3huSzIzaUtkb2NNNWhIME9jOVBVbV9fbV9odk12YURhSFdfR282LWtrUEVjdVFCVlV6dFlQc1F0WnZOMXFGQmJmd3RFXzlJSE9teWhlRDVrbmVTc01HeFBtaktJZ0pDYVZzUkJiVVhXdw?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>46012.72425925926</v>
+        <v>46014.15800925926</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rugby club wins award and receives nearly £2,000 to support community work - Oxford Mail</t>
+          <t>Burbank PD News Release: Burbank Police Participated in Statewide Organized Retail Theft Operation - City of Burbank (.gov)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:00:00 GMT</t>
+          <t>Mon, 22 Dec 2025 18:50:27 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOc01aWHhOTEUxZUxPVmwtcU9YN1AwY1ExVlgzSFZTbGp3eWhOdGxUZGRHbmNUd1ZwSzRHaHV2ZF8tTDhHbDB5bWRvNFBUREtyNzRqNnF1cDE0MFpBaXdsdVliZ2tjbG1KeFo1dVhKUDE3SUVKVTZuWkd1NHVkNF9tQjJCU2ptdU1hamQxYkZpTkhqeFlJWHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPVFQ2NXo2S0RRS19HcjlxQktVR1RwRnRnckxuYnNXWWoyajk1aWltRWZPR29fcVdqZElXblNOdklLQW5yQWhaYU9oZHhNMFNTbl81cmIzQzlPc2xCeU9fOXNfUElxZXE2Ry04WnN4SW9IMWRwOElvMWR3cHdIVlZVRkhFSnFxbzBpNy1LRU5qOG43c3lueXNIUnZTQUxxYW1EQkxKRHhadm0tTzBNWlktUmRDTDF6R0UxMTRrWTdkWTByUk1VRjhoSmh6OFV6WTFReDlMY1VDQ2dMRkdjRF9iQUdISmU?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>46013.20833333334</v>
+        <v>46013.78503472222</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Actor Simon Delaney set to launch his own food brand - businessplus.ie</t>
+          <t>Investigators recover 12 tons of stolen coffee from Melrose Park, Illinois warehouse - CBS News</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:58:56 GMT</t>
+          <t>Mon, 22 Dec 2025 19:02:00 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5heWVRYmZhLUNXUFNyOF9ZV3Qzd1NQaFBZRURZZFZIUG9hVkxTOThpcUF0Wi15ZGhtZE52RE9DTkExZWx3ZEhmR1VRcWVoNGM0cWI2SHhTemZpeFd5ZnMzQXBvTFNrSmk1UGN2aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQb09jMklUaHBVQmlsUERGb2xhRWdDMzAwQVRuVVp0dVJ1Y2RYVGJhYVNsT1dxLXdqX3RuOWxzUC1jV2ExLXlQMS1JWm5QQmFBdG1KQnNlUVFEZFNiOGExY1U4S0h6MklVYkdEcXc3Q1FHdExDQlMzdUJFcmJrSG9zNl84NjZxdDlTeXNLcTczUFBrS3NZdDE3NG1FejFMOFlIcWZJNVZGalo?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46013.33259259259</v>
+        <v>46013.79305555556</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pictured: Man, 55, killed in London shooting - The Telegraph</t>
+          <t>C.C. Citizens Police Academy Alumni Association responds to officer investigation - KRIS 6 News Corpus Christi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:13:00 GMT</t>
+          <t>Mon, 22 Dec 2025 18:40:54 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPVExIa2t5MUtSamwxa2VtYkt6eGpaYndzeDluMjJfeF84cjA0Nnlxb0V0bkZ4aUI0WWpfV1ctNjNCd0twTy1vNVU4em9Rb1BuODZmdjM1NTY4dTg0dUFfTjNSd19NOUlRNE5IUUhFNHpTSUx6b1cxakU3N3otWGJ0c3pmS0dqRVJLTjU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPZFpLbFZFRld0eDZ2Qy1ScWlOTkJ5bGt5aGo2OWhKbE5Md2xoMlk3dDV5eDh4ZGo5UFFSbndNUDRicW9zRWdGR1ptU3FfU0t3NTQzdk4yQnpuZEFXVHk4OW1SYlg4Nkd3VVhUTFBKSUhkOXMzdTVnbzU1UkhHbE1QYmR1QlpNOTZTNFIwQ01PYm1DRC1HcDVzUUMxbmFPZDVNY3dITFJpQzBIUTN0SC13WmpWNzdxa0hMYkllSzBnQnZodGc3YmpqWUJnX1FHcDh1UlN2Q19GRnEtRVR5MGtnS2o1RnJFQ1hLaEw0?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46012.67569444444</v>
+        <v>46013.77840277777</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>London Shooting And Maida Vale Stabbing Leave Two Dead - Lawyer Monthly</t>
+          <t>Police Say Gang Of Thieves Stealing And Reselling Boots, Other Items - Chattanoogan.com Breaking News</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:36:31 GMT</t>
+          <t>Mon, 22 Dec 2025 17:56:22 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPbHZ2ZENFQ3R0ZFhpanUzUGVKbmsybFlRdk9fWEdqNzM2ejN5LWl6dS1ZVVdNd2R1LUlhb1ZGWEctT2VFTXVsUTIwZW5lMl9rT2VTZkpocTgzaWlwbXctWkhFdjNKTXdvMmFVTV9SczBMeFNKWUl2ZVIxbDNPUzI1TTEwRW56YXFtVHllRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPbk0wbzBKN1JTYzdkVWhzNFdJMWFUdzJXTUJ4VHd5V0VVcnVoNWJRRWNSTGZNQTZLbUdKMkZxLWFUU2dPTlVpLUxVQkcxSndFVE4yWXpMaEpwa2NrYzNuTHFyZkhzczk2cG9MZGRRREgwMGFlVEcyTHF1LWRnbmFwWDZoUVpjYno3VzBmWlptaHU?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46013.44202546297</v>
+        <v>46013.74747685185</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Explosion W Celebrates Retirement at London International - Everything Horse Magazine</t>
+          <t>Man stabbed to death in Fitzroy, second killing in less than 24 hours - Herald Sun</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:16:43 GMT</t>
+          <t>Mon, 22 Dec 2025 20:33:10 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcEtwSlU2ZlNrb0ZyX2NJbllMNUZkb1Zscndvd3ZGeVhpM3IzWm1uWUNGLVpoRGhaQ1IzaGNNUWxfa2J5WHI1dExrTlM2T3RSRHluU2piOEU4OHpOTk1uMURVZjZSV1Z1NzJQaHI0d1BxMVVkWmRMckREaWF0MzVmOUFYOWFEcDE0YjRMam50VU9ic21TWURpVjdmWDM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPNU9hMGU0TWI4MnZzMUxzNy1lRjJqMzk0SW1SaTFxTXAwRXJHd0FIMVEzRW5TTkZ2YUpZUkY4Y0Fhd1Y0TGwwRDA2VmNBcWxiUDM2aFcxT09QSzBxaHhWUWhKN210QXEtSFlBUTZrcXlNR2lScXB2UmxqSTdQVDVQbmE5WXZuNHc2X3FDemtxWUZHczdUbjVUak5KM3o5clFDSktXWTZGY2FIUWhueHptYlNabWR2R01FR3hHcTNwX0lxOC1KQVgyOUpWektLSTlCeWgzZERGUm9MaXpFMW52ZmdaeHlpN3V0Ni1pd3F1ZkRyUTl6aGdGWDJUc3BfNWFsdW1nM1p4bF8tUURq0gGMAkFVX3lxTE81T2EwZTRNYjgydnMxTHM3LWVGMmozOTRJbVJpMXFNcDBFckd3QUgxUTNFblNORnZhSllSRjhjQWF3VjRMbDBEMDZWY0FxbGJQMzZoVzFPT1BLMHFoeFZRaEo3bXRBcS1IWUFRNmtxeU1HaVJxcHZSbGpJN1BUNVBuYTlZdm40dzZfcUN6a3FZRkdzN1RuNVRqTkozejlyUUNKS1dZNkZjYUhRaG54em1iU1ptZHZHTUVHeEdxM3BfSXE4LUpBWDI5SlZ6S0tJOUJ5aDNkREZSb0xpekUxbnZmZ1p4eWk3dXQ2LWl3cXVmRHJROXpoZ0ZYMlRzcF81YWx1bWczWnhsXy1RRGo?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>46013.46994212963</v>
+        <v>46013.85636574074</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>‘Words aren’t enough to thank him’: ‘Magical’ Olympic champion who changed lives and touched hearts bows out in London to standing ovation - Horse &amp; Hound</t>
+          <t>Real Madrid Eye Loan for Uzbekistan Defender Khusanov - Caspian Post</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 21:22:39 GMT</t>
+          <t>Mon, 22 Dec 2025 17:40:00 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQNG1XVDFQUTVRZkJtNEE3eTNTUER2elU0T2tfY0JpU3BocmFXZEJmRGljb292bWgtdDNYNFFNZkZHYUd0TktFaGlrd0ctem1zajMxS3RvTmpHbFo3WFRicE5MZzB5YXJKMUVrYUstbzNCUDhoR3ZsdVI3XzFxRFBIRllKMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOa3otZ1ROZS1ZZk42Q1p0Skh3OW1PT3EtNTJfVnlxUUdVRmc1eVA2MnY2OHB1ZWFyM1laXzVKaXF1VWlRaEtDamlON0FSdE9ZSWItMmlmV0RvcjZOQU5Dbk1vT1NuN3h1RXhTeGhQMThyUG9Ualp2V1U5bzZyT3pCM2hDZHlmaHVGdzVN?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46012.89072916667</v>
+        <v>46013.73611111111</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gun crime 'not out of control' says police chief who oversees South Yorkshire Police - thestar.co.uk</t>
+          <t>Explosion W Retired in Emotional Farewell at London International Horse Show - The Chronicle of the Horse</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:40:00 GMT</t>
+          <t>Mon, 22 Dec 2025 14:07:45 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPLXJCcFprYmxtbzk4a0dwaWdJcmJLVG9LdVFsZ0UwcEdUSUMzODFvaUVUbVVIamZwSENZOXJLanV1U3hXZ3c0ekYtOEJGS3Y1aXozbEdXVlZ1QWlpQmZOVEpyeHEyRVJCYU5PMkxHaWJFbHdKVV9oalN2QThkTkJxRkJwRjFpZ0ZvSk9RNEl1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPMTNrZ095MDhuNHhVWjM4ckZyR2NRVlV2WjVpSk52VXdvRFp3blpXczVBTTBkYjV6VTVLSFBwRjFQXzBVTTBFLVQ0Mjdxc1N1QVJtVnJsRnBNRlBReHlkeTdTV0thX0JxSmwwXzV0cFdCRmJkMEZQUjVjdC02aXFPUHV1QW5pNU1iUUF3QXpHTTI1ZFNKUGt0Y0hLZnE1cWpXdEIyZmx1WFFfaXp6eE5ucWtkMXQ?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46013.23611111111</v>
+        <v>46013.58871527778</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Australian PM apologizes to Jewish community over Bondi Beach shooting - news.cgtn.com</t>
+          <t>Xinhua Photo Daily | Dec. 23, 2025 - Xinhua</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:30:31 GMT</t>
+          <t>Tue, 23 Dec 2025 07:22:15 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQOGxUYlZhbGM5ZVh2dDhGZk9NeTNCcm5mcmRzc0Y5OTZjd1ZCVGZleGc0LWpocFpMWW5OQlE1U21WYk4tbS1aRzNfYkRYVE1SclA2UlZxNzVOSWhDcXRMNFgxcXlSMDl3MUlaVkRfd3NCZ1pIM2lZcDZlM195bU92M0dxNVdNSFRGMFY4TXZuejk2SHdFQ0M4dk1pVmRZdXduLVUtcUdROTVCMkxscklvT0VRUWcxMmN5SWw5VlJNSmZ3TjhidWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1ycW40aG5iSDktNjE4c2xiWkJjbVkwbndDSFZhX0RrNXMwSjBUTkd1V193OVR4aUFVbDc2MFpiRTJfWlAwdXpGaGxjOTJtZVJuMzQwdnNZY2hSTVNaX1poQ3F6bmNHaWtidXlZUGRud2pFbEgxZ3U3a0l5Z2g?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46013.39619212963</v>
+        <v>46014.30711805556</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Preacher stabbed at Speakers’ Corner: 'Attacker was trying to kill me' - AOL.com</t>
+          <t>Car bomb in Moscow kills Russia's Lieutenant General Fanil Sarvarov - France 24</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 04:24:10 GMT</t>
+          <t>Mon, 22 Dec 2025 15:18:16 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQXzRQRzQ3M2RBOUN1THd6MHh2OUlfOEJhZ0x2VHdDdFJFTDV3cjYwb3N0RVFaeGV4SDJmU3ZjaFlpTjVDRTUyU2h5c1VhTnNrLVd1TW91YWZlbWlfb1V2WE0yX1Y4X0Z1MXNWR1A5RkRaMVNjZTN0YXktUVQ3U0QyMWdXTzB2dmZINTRpaWlhaFExQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNQ2hTdEludk1UWWpiUFNTY250NFhEanlmd3ZKaUNUNFMyMkd3UHhLQ0JxMmtQUTg1MS1lSUkwZW05d1Z3ZHB3SjN4d2JEVWJnQWZWVEVjZFZkR1VKYk9sWk85cExIdUE1dFByNW1aa0ZRMEk0cTN5RzJZcVBwbnFFVFBpSjRadDBDYkktWHh2RjhaRHdoOEh0MkhObVdscXZ5WmI0aVZzMWJUeEJzR0hF?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46013.18344907407</v>
+        <v>46013.63768518518</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Identifying teen shooting suspect comes with pros and cons, lawyer says - London Free Press</t>
+          <t>Woman shot dead by car of armed men while attending funeral of star footballer who had also been gunned down - The Sun</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 19:16:33 GMT</t>
+          <t>Mon, 22 Dec 2025 22:55:00 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNX1l1MkJfaXBfd1dGd2tkdlE2bk1sWGcxUUpPV2FRMWM4NVV5cVp2ZXJKdVhTc290bF9JSU9lVFVfbE5WbFRGcm9XQlBrSzZ3TXVaU2tnLVpPQXhGek56WkdKNmNZNTRpazdMYWEyaW8wWFdsR3pCcExyLUFkU3NpY2hlZkZYVUw4aXRrakpBbE1yVk91T21ZdnJTLUE0MWlrdGJzNGl3NkZRdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPNWxabS1OZFZoRVdtZ09SemNNZERtcHNVdm9iM19ZWW9ONUxqZEpUbEVmT0ctUzFvWUw3YjNUdlpRbUJtRjRZdmFRSUZZOVVFcGJaclRZeE1wUzd2dEcySVA5TmFKbzA5LW0tU0k1WGVUZ3Q2eTFVWW9PbGZwNkhucDFvX1ExQQ?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>46012.80315972222</v>
+        <v>46013.95486111111</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oxford police investigating shooting of 19-year-old man | News - Greatest Hits Radio (Oxfordshire) - hellorayo.co.uk</t>
+          <t>Evansville police: Fatal shooting of teen came during botched robbery - Courier &amp; Press</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:44:12 GMT</t>
+          <t>Mon, 22 Dec 2025 10:06:00 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPU21xMENXLWFSOHlBcDZvTUV4Q0ZlRFdnWVBrQXJrVll3Q3BfSUlGc05TVzZoMkFTUUhrZEdYRGlhRUVTelB5cmk4dlEtSGZWb0htXy1BNGNsOFhoNjBOeExaR3FTTjY0RGhodW5fNE1WWXY4Uzg1X2UwMDcwc0hqa1FqYkhGMWZRVWJwYjk1bmdZQWtFeXF5YzlQenA1RktGY25mVy1VUnJESjRGYmplbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOaHBTU1NqUWx3eVBndENkRVRJMkt5M1Fsdl9TR25RcDJvSXhsS3RxeTFxNE1acFJUUV9JQ1pRRTMweHEwQUN1MGwyamxlSnpGc1NuUFZmZ1lFM1JCYkxQOHBhMGZDV2VUWTFoSFFmd0hTYU9qby0yWjdLZUs2SW1iSUV3MEFnNkpVaURBV09aYVhHWDlpQ1huTy1nNzdVWXFVNm5OcGNiSTg3VUF5VmNVTThMMzlUQ3RvYmtiaWQtYjlGSzA5LUlKN09zSnNhYTZ0WGJGSQ?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46012.69736111111</v>
+        <v>46013.42083333333</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New interactive map shows the London areas hit hardest by crime - see how yours compares - My London</t>
+          <t>Man shot dead in Castelldefels street - Diari ARA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 06:35:36 GMT</t>
+          <t>Mon, 22 Dec 2025 17:12:40 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORG12a2NhSUZ3MXBrLWRocElWNzB3WjRINHVISkFBRmdicHlGNVpFSHAyanV2Sm1Uc2RJOGZ1QWNfcTFXbDdCRjRhRUtFTktROWZtSzlZaXNQV1JmY3hFTmJwY3l2LTNrTHFGRlZPd21WZlFEU1VrNXB0Z0RsRXBTejBsdUZSLUk2d0JBRXhIM1VYZGdP0gGUAUFVX3lxTE5EbXZrY2FJRncxcGstZGhwSVY3MHdaNEg0dUhKQUFGZ2JweUY1WkVIcDJqdXZKbVRzZEk4ZnVBY19xMVdsN0JGNGFFS0VOS1E5Zm1LOVlpc1BXUmZjeEVOYnBjeXYtM2tMcUZGVk93bVZmUURTVWs1cHRnRGxFcFN6MGx1RlItSTZ3QkFFeEgzVVhkZ08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQNHNaWEpWSHlpdFZ3eVNzcjktX0JPQWRINS1pOVVkNTlzTnc5ZEVKVlgzLUl0MDhjMjFsMDFXdDBLTzhDZ2tIRXJHX3NhM2FSaVJRYTd6aGZLRGZjNTJiZ181bS1YU3c2WFlUb2JaUnV4SllqaGZqX2JlaDUwVi1YM19UQ0ZTd9IBiwFBVV95cUxPZ0hyMmxmcXhiOXVUS1dzM0tyTHh5R2g5Wnpxam12c2FPR2tCSmJZY0dnX051OENjcFBjNkhPSngxREVaLXFBQVlIWGNyV2NHVVN4Wk1UOWdLekFMT2R4Q3RTUjc0MnhsOFMwaXJ0RF9MS095TUxrZ09XS1VTVWZROXltcFZnSEczMzFz?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>46013.27472222222</v>
+        <v>46013.71712962963</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>North London's 'real life Santa' making £1,500 doing people's Christmas admin - My London</t>
+          <t>Barcelona star REFUSES to leave in January - FootballTransfers.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:16:49 GMT</t>
+          <t>Mon, 22 Dec 2025 12:14:00 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNMWtVUmc0VV9yVU9JeTVoZ01WTm9NQ3g5TktPVE5wTFFSbVJ6ZEJubDNublpmTEQwaWt3b0VvNURnNWJsZlkzVWtNUTJsdkpkWE52Ul9zYWtEdFZEalhRQkZYWXN4RjQyVFkxY05uQUh1LWxhaUEzekMwTXRmcklTc0NWY054WkpiYW5mQ3VLR2vSAZYBQVVfeXFMTmR5bkNoVGp4S0dCb29rb25EdHp1bDE3eVJjV2xqSlpyaS1YdHVQUUpSNEVNeWhSM2l6VjR6cnR6eDg5S2kwRC1kQUQtQnFZRWY5Mm5CZ3JTRnFxeDVYbTV6YlpsOGRhbjI1VjJFRGszMWlWZTh6Wk1zVm1FZm9mMnEyeWRmamRfcTk1UlEzV0RSdmV1Ukl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQ19pMEo2b3Ftdm9NOGtNcjdlRUt6aF9qNjB1Q0ZZanViYUNKcnRtUUZGbU16TDFKaVdTalJkdTNrSXY4VG51akZScnk1ZXc2c0YtLUhyTW00blJFRlRya2RMclVlVl9OYmdfSWhiZDBsMEw4WjdrcjladGZLTU00YjYyU0dxUjYyakpSOG1hRkJ5ZFVHcWItZjJnRjVGaVlrQzZHMTRUSHVRQ244dGNja0tBdmJLNXpueXF5cFZUaEJvRkdLbVdZZGVR?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46013.42834490741</v>
+        <v>46013.50972222222</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hounslow Council Leader 'had no idea' one of his councillors employed illegal worker in her home - My London</t>
+          <t>La Liga: Four things we learned in Spain's matchday 17 - lokmattimes.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:03:48 GMT</t>
+          <t>Mon, 22 Dec 2025 17:25:41 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQdTlKQ3EybXo1X0hqeW9PQjVNYjFxQzlCcC1ad2ltTk9vVEFuZE13YkM4YTFMczhIa2hlb0hRUkU4Sm5SRVJkak9DT1RwT1pIZVRSZFA1TzJyN1ZFV0JEcnhnTUdobk13MllBVzNTWHJTZ0lQTE5fM0hoR0hNWTR2N3JnTmpwV2F1QUxEYk1EbkjSAZYBQVVfeXFMTWdnOU10eFc1VWwybHI3WUJzX3AzVXZwUFUwZVBxT252b1FtaWRubmlSWjZkVW1JVHFzVlV2cVhWZzAybVI5b1AwYzJwLXpCVTJrdUJYTWVVcUpIUl9ybERZRmFBVUJQY0k0QjBMYl9OM2dmaUQyUTc4czBObExPVjBBZ09XNFRKZFBrT2lKaDRjbURpZ3Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPMVBCUWV0NjJBb0V2d3FJTUdSMmFlci1iQnZwa1JtWFhNQXByV1ZXMDV6X2lfOHdJNzRiMjVlY0lYOEVEYmJTdTYxd1d6Q3F1M0Ywd1o1ZDM0WG9NYXBpb2RtN3FIa3EzYXRESDNDUmw5YWJXRmtaVVFUamlwWHZkY3ViTjRxRzI1d20xSFVKSzFuSmRHdHpDUHVn0gGfAUFVX3lxTE9uLVZhV0Z3NUNZVmEwMkRKUDNsMG85eXRiS2F3TTBxVVMwSkVYdGNyYnZybUY3cUFYNWRvd1I2SEZkTHNyeFVrTGdTajVEWmRwaDFreGVyMk9ZaF9kdmFXVUlmWmhiVVdXQlV3MkJFUG9yVlgzSUNGRklzYnRvYWF3N2FCSkpXSVNiRGUteXJhb1pKM3ZJZTBzQXh5ZmZfQQ?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46013.37763888889</v>
+        <v>46013.72616898148</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Elderly ram who thinks he's a dog becomes unlikely family pet - My London</t>
+          <t>Spain's traditional Christmas lottery draw starts in Madrid - Bangkok Post</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:46:15 GMT</t>
+          <t>Tue, 23 Dec 2025 04:04:30 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPZHpScXdUNUlBMndSTXBqQVRfc3h6VzBLbUhDNk9hZ3RETFl4UUVHUnloTGZpNjdBT0pDNVRvNGNiQmxoemxkR2NrTW91RTEwR3hEQWVmSXZQSm95MDQxanNrVHRGTW80TTNOS0FoRlY4TEk0TjdaeXd6YV82OVU3OTIwZi1iZUk0TTJPONIBjAFBVV95cUxPZHpScXdUNUlBMndSTXBqQVRfc3h6VzBLbUhDNk9hZ3RETFl4UUVHUnloTGZpNjdBT0pDNVRvNGNiQmxoemxkR2NrTW91RTEwR3hEQWVmSXZQSm95MDQxanNrVHRGTW80TTNOS0FoRlY4TEk0TjdaeXd6YV82OVU3OTIwZi1iZUk0TTJPOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNVmVqYy1rYUZ3aXVNMU1jWjZLMjAyc01vMlFGRnAxb3V0X1hPZmhUMG5TQ0VsQWJIR0lVZ2lDdkhOZUZjZjUzMVNXZGZETWQ3UlB3WEpiSEswYjFFcmdabnV0aDRpU0dwUHZpcWhIWnUwNFFKQkVQRTJ6ZUpnZy1KcmwtdHJzUGNKSDU4SHZhVnhOcGdScnI5NldvcWFPM3lUdHZjQ3hLM0JmQQ?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>46012.69878472222</v>
+        <v>46014.16979166667</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mother of girl injured in Parnell Square stabbings says daughter may one day tell 'own story' - BreakingNews.ie</t>
+          <t>White Duo Lead Rookie Race After Historic Draft - 조선일보</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:26:57 GMT</t>
+          <t>Mon, 22 Dec 2025 21:25:03 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQay1BblBoa2RoZ0xfeEtCZTRiLVZQSmlwT1FGM1VhekhGUllOX2NCd2pHMFRUM2dpQ2FManMtSnZxcENBdll1OHVSU21BX2l5cDZSMFlDaTNTZzhWSzR5b2hXS2VRUHM0ckZ3VHlvU3ozblRTMHJGaGcxMUZsdkVNbDJ4SVF5dE04bVhvc3dMZDd1RVFuTWtPT0V2d2pvak9XUkdiX2hhMENpalBGeWlpakZ3dUh1U2VtNGJUR3N6MnZyY0pWRmlTUzlsOUJZbnFUUWNLNkhpYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPU2taS1BQS3Z3LWJMREZGVjlxMXlmWmhtZURidlBTUXN1cGVjRXVfSDZDc0xzMEVocGJCM0s3OFJETWg5SklEWUdaZi0zc2t5LXBJV0lvc3lMR2xsXzd6bzMtNkxCNURKT3E5Q28wdVRVdnZTb2t3WExvMXN1VFAzS0E4MHFQdw?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>46013.47704861111</v>
+        <v>46013.89239583333</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>'I found a tracker in my car - I was horrified to discover who put it there' - My London</t>
+          <t>Florentino’s reach vs. the NBA’s claws: an MVP could be snatched away - Mundo Deportivo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:31:33 GMT</t>
+          <t>Mon, 22 Dec 2025 12:25:00 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPWjJiVnJpb1REcDgtM2wyU1VmaHBfbFdyLVZ5elBlS2l4RGF1N1lCX2E2SS1xNHhwVzd4QkE5aGs3Tmxya0llSjZRU25NUy1oLWZJYkxlVXd0N0E5R0xzd2ZLU0tvWXdWUTkwTEpnZ3JTbGlUMXhJbmtPZ3BuTWUyaHBuZVF0LWxMQXRsdFR1MnrSAZABQVVfeXFMT1oyYlZyaW9URHA4LTNsMlNVZmhwX2xXci1WeXpQZUtpeERhdTdZQl9hNkktcTR4cFc3eEJBOWhrN05scmtJZUo2UVNuTVMtaC1mSWJMZVV3dDdBOUdMc3dmS1NLb1l3VlE5MExKZ2dyU2xpVDF4SW5rT2dwbk1lMmhwbmVRdC1sTEF0bHRUdTJ6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQampjYXJkdG1naFF3ZzIwSzdJcnFmal80NDhoX2FrWUtXbjhfcHF1dklKbFhUcHZFaktnNllMTjk3VEFXcWMwVzBBXzEzeVg0UUgyMGhabnQ3NlhqR3FqVWJLZ2FUc2g1SERaQ1FZaEg3VEczWXlWb2VPanlOdVFPdGZJZm1Kd2NlX0l6VHc3SEhDVW96d0dKN3EwQmFpeDhQSDhrZUN6M0h2dHc4QlJ5dnRoaGFQa0wzUE5EcHpkbXJLLTTSAdABQVVfeXFMUDB6c3hwek4tTk1iMUZIWDBwUG15cE9rY1V4emh2SEZpSS1tZHhCeGF6eG5VVjFxWkpWaE5qOF92WEpKWFFaNTdTLWs2M0g3TVVzN25yMFY0eGxNVlMwTUFfR2dGSHczRWhTWUI0ZFZ2T2twbEJvV0ZDVEg4OWhManJ1YThmWm9DVUFJRERBY1pRNjRxSUMwVHljMmtPMVhSZFNkWFdwV0NnRGRtczViOU1hZWxuNnNXSVpTcjZDN291b2s3cXBDZHMtSGFiVUE4Xw?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>46012.68857638889</v>
+        <v>46013.51736111111</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>One year later: Laurel County fatal police shooting investigation continues - FOX 56 News</t>
+          <t>Barcelona enjoy resurgence under Hansi Flick — all thanks to ONE player - Tribuna.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 23:06:30 GMT</t>
+          <t>Mon, 22 Dec 2025 11:21:00 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOelNPbndEQk5ia1dteXlYQmh3OWxDcFJjRU5vbncxakplb19lODFCOXJHRjhPTVZ3cmpZa0FwbWtpRkpFUk9vTUxvbmJBcmY2a3B5SFZuRGpKdkItRGpvR0FzcmRwODVPUTlWbkNWNEN6dTdoNUpWaEVVOUF5bXp4cENvYmgycDRqd0ZyYm9Mc28tTjhtekZCM1c0VUdfVlo5cmszYWtRa2RqQ2FLY2drRdIBtgFBVV95cUxPZWRibXZ2TGVlRDJLb3Q0Qkk2U2s4LW04R0wwVDRNVW0xN1V4d2lFNHlhSm94dmZQaElHS0VSeXZYQkFwUWNCa3hMTzZ2Z0dqRmE2TzY0a081UlRvTlcweFNsc2pEaVZwdFR4bnNUc0Fwa1kyWGNjZHFTaWNLM2NxXzlhSlpQV2pCZFNMNU1MWFFmWWExcEJaNV95WHJFcjlVTGJIN0xaNER4Q04xU2E2Y3IyekR0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2hpZXUtUFkyTEQxNUV3V0w3SjZieURjNXpWZHJlXzYyRy1SZndIbXIxUVBLSHBDWDhMc1BiTDkyNHhHcFlwd0d4ZmNyYzE0cDM0ek5UWktTWnl5RVdDUDNzanBUSUJjVGU2c2pTUF81cnJOeExSd0x3YW0wZDJtNDVuVk9NbFh4bjF4a040Tm82NWhici1sR2dR0gGaAUFVX3lxTE5HaGlldS1QWTJMRDE1RXdXTDdKNmJ5RGM1elZkcmVfNjJHLVJmd0htcjFRUEtIcENYOExzUGJMOTI0eEdwWXB3R3hmY3JjMTRwMzR6TlRaS1NaeXlFV0NQM3NqcFRJQmNUZTZzalNQXzVyck54TFJ3THdhbTBkMm00NW5WT01sWHhuMXhrTjRObzY1aGJyLWxHZ1E?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>46012.96284722222</v>
+        <v>46013.47291666667</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>North London shop's plea after filthy pans and dirty clothes fly-tipped outside shop - My London</t>
+          <t>Thousands of runners dressed as Santa take part in a race in Barcelona - France 24</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:04:43 GMT</t>
+          <t>Mon, 22 Dec 2025 09:37:11 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNM1BsRy1tMmRWYnM3RF9rRktKZnVvZ0hhbU5naEFFTUNOZ1JxclRIMjFfc2ZuandaV1QtbGZsSkVDWGJkMHlQRWZVNFlodFlHOWw0VVE2UTU5bHk4VjV1bFAzYkZmcTVEbDlVVWFMUVNXSGlvSkRyY1BORWhaWWtENFppb2Vfa1p2RUFaaG54SGZaeWPSAZgBQVVfeXFMTko2VVJTdXRPc3ZHLVljYkUxOVh2ZE5NMU9QQ0E2RGNIeHpUMHpfZTFHTzZCUVYxUGhROXhQcjZuM0dNSXM4RmpYTFlTNUhvc1R1R2pXcl9tci1zd0NZRlZUNk9LNEpVRUUyaXhhUkQyVnFQVmkzYW5HOExUdEtFaXBGeHdjZlVVZXJ0RTZiTkZxYVA1Q2JNWDc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxONjlnc3hkNkc0Z0lPcVN4bkpOZXdvMzZvNUxaMHFPU2VISmpRY0lfWFlsamYzWXNMcm40MHY4VWRBOVAyY2h3Q1lhbEVabnJnVGxJWF94UDZNdTJwOVZ2TjF6YmlFcS0wVkVwSnpWMHNZOHFYejROWDFLWkdvLXAtVmZKY1pieU1MYV9jbUsxZERQMFd5QUNJdzdSZklmY1FzZVJDNlRnWnRkdlNRNUo3S2JoTQ?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>46013.41994212963</v>
+        <v>46013.40082175926</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Two British nationals arrested on suspicion of murder in train stabbing incident, UK police explains - MSN</t>
+          <t>Raphinha and Yamal fire Barca four points clear at the top - NST Online</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:19:53 GMT</t>
+          <t>Mon, 22 Dec 2025 22:00:21 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxPcUV5d2dERTc3SUowQjFodjJuNVBDNGJNd1hOWlJOZEZfY0pZSHI4dlJwVk5qUnNNb1pQSF9ZenhoaTZraTd6MDJ4ZlFWRXZPeHkwNUNQa1RZa2lOTjBYRjlJT0tYWjRqaXBZY05kRUFfVzBNQU1MZzZSaGlSRlBKdjQzY25tcDVjaXJfREVBSnowS05seE1yZVc3VGxZQ3RFWi1QSjBZaEdkOFN5Qm02dUREWkxDdlVEYmZCempMRHlCcWFVOTJoMVVURXZNeldPWWljVlVXeXA3V2xHb3VITXU5VjBkMkY3V2F1TEg0R3V0TV9ZUDRfaTdrSjhUMkxZQkVkeDdGRUdkY0hCWXZjLXc4Qld3NnBBMlowbHJxVmI2SGY0YXR6S3czZUE1cDExOEN1WmdCQUpoX25BRFYxSFgwNmtYVWlheFJrZWNPVzE3R0hHSl9kSFRDcEJTSW9rMERpbnBKS3A4VGdUemVMSzRMWFBCclB1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDljdTBRM3lHbXdRX29zcnhSVnkyQkdLanlpMDVDQUU4NmZCdjhFX0p5bFB4MjJjT0N4Q25Mb0Z4UUFycEswcE5iXzFpeTJ2NnozZElUUGFqaTZOTlNpUkgxdkVKdmkwd1Z0Y1VUVDNLMzdMTV84QWdyQzJfREo1Wk9lbUt3N1I1VUJPN2VtRHlaWG1TYVlwd1Z5NnlWUXBIcExtRFRwY2FfaG1QUzJB?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>46013.2221412037</v>
+        <v>46013.91690972223</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nine killed and at least 10 wounded in South African pub shooting - Surrey Comet</t>
+          <t>Inspired by Iniesta and eyes on Brazil - Morocco's El Aynaoui stays true to his passion - NST Online</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 15:57:00 GMT</t>
+          <t>Tue, 23 Dec 2025 00:26:50 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPNnRsX1pPZ0M2QWNkd3VCMi1TSjlFdWczWjk2ejZXM200S1lVSElsaW9iVjIwWmplcnA3eDdQOGtNTWhfc2xDUzN4Z2NSaEQtOFFuWk5IaDU3SWMwT01sV3VCOUNyVEd4NDJDYTlvTlpCMWRmMjd0aG85eUhROTlWU0NFTTIyVmZUY253Z3lPeVNFN3JtczNsWkwzTWJCYzdRTERHNEVjZlJWUlNGbEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkFDaUhsOXFKazJPS3hQcnJscF9jakdLbnJtcnNGVGNUZ3pCT2tURXU4QUxLcUItOEs1ZlRxQS1zdzZOdzhRVW1xOGY0ckdmVDJURW12eTZ3TnRrbDVyaGRXWmVOUjRoZzFnVl9Db3I3am9RejVHSlhzR1ctbTB1Sk5qLUlVeEYwR3BLT1RZZ0cyN2NkZFZkMUpRTm5QWXlOcUFneS1OV0piMUVxa2JmT2RobUoxdk0yRWNBcWQza3BCRHFB0gHEAUFVX3lxTFBSQUNpSGw5cUprMk9LeFBycmxwX2NqR0tucm1yc0ZUY1RnekJPa1RFdThBTEtxQi04SzVmVHFBLXN3Nk53OFFVbXE4ZjRyR2ZUMlRFbXZ5NndOdGtsNXJoZFdaZU5SNGhnMWdWX0Nvcjdqb1F6NUdKWHNHVy1tMHVKTmotSVV4RjBHcEtPVFlnRzI3Y2RkVmQxSlFOblBZeU5xQWd5LU5XSmIxRXFrYmZPZGhtSjF2TTJFY0FxZDNrcEJEcUE?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>46012.66458333333</v>
+        <v>46014.01863425926</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>The Royal Family's huge mansion so expensive to maintain Queen Elizabeth's cousins couldn't afford it - My London</t>
+          <t>Neymar undergoes surgery for meniscus injury - NST Online</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 13:16:52 GMT</t>
+          <t>Mon, 22 Dec 2025 23:46:49 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQM3p1N2ZmRXRSd050ckNId1hiOHFFUDFaX0ZXUXdhZTFLSV9PVEhGOEJaMHFuNFlBOFN0cEY1a2x5dmVuU3F4N1lITGZPRDVEZmpfSEt0Y3dtaTZsMjFjaDlUcnhIV1lXT3VmOUFDODZMeTJfRzBHNFhDcmZKRThfdWVEVXZucXdsYm94dXRIcjFhck9sN2s0empn0gGaAUFVX3lxTFAzenU3ZmZFdFJ3TnRyQ0h3WGI4cUVQMVpfRldRd2FlMUtJX09USEY4QlowcW40WUE4U3RwRjVrbHl2ZW5TcXg3WUhMZk9ENURmal9IS3Rjd21pNmwyMWNoOVRyeEhXWVdPdWY5QUM4Nkx5Ml9HMEc0WENyZkpFOF91ZURVdm5xd2xib3h1dEhyMWFyT2w3azR6amc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOMFNmekRHMjRGRkh5N3RSdDNFQWFnb1BxTVBjcnJQSFBNS1BpT1h3ME9lWjBMd2xZS3VMZFJGTm41WnU4c2VUMi1mSE5FRF9meVRLRDhwMU1TOEk0VnZmcm9DeTl4TFRyeXVIb3hHR1BlQ0FRanhQSUlDelJYZ3BCZHNiZjdXblY2WkZkVWNyRDlOa2VDUkk4cldzRWU3d0Rt0gGgAUFVX3lxTE4wU2Z6REcyNEZGSHk3dFJ0M0VBYWdvUHFNUGNyclBIUE1LUGlPWHcwT2VaMEx3bFlLdUxkUkZObjVadThzZVQyLWZITkVEX2Z5VEtEOHAxTVM4STRWdmZyb0N5OXhMVHJ5dUhveEdHUGVDQVFqeFBJSUN6UlhncEJkc2JmN1duVjZaRmRVY3JEOU5rZUNSSThyV3NFZTd3RG0?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>46012.55337962963</v>
+        <v>46013.99084490741</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Granard Clay Shooting Club raises impressive €4,550 for Friends of St Luke's Cancer Care - Longford Leader</t>
+          <t>Police are investigating whether a Podgorica resident was killed in Barcelona. - vijesti.me</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:08:42 GMT</t>
+          <t>Mon, 22 Dec 2025 19:43:20 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQMWhSTGFuX0oxeXBvOHlFVHROWGhCUDhEUXV1OUlRWUVUU2pVZ28zX0NxcUtzUEhxX19UTm9RMjhCNm9aZXhacnVmTlJWLWVBcDhxY2xPV3FsU096Y1pOa2ZfYVlhU2tDTUN6SzF2TEtJQU9icDhhNEZpYjlEQ1Nvd3VRQTlZNUtBSXItcEV6b3lmMmZXQ25fNG16ZnpxOG9lZHAydHA0Ny1fSWdxR1pxaXpFNVR5bjZPNGRBWjB6ZHZZSmRkbE1MNjFKb3NKemJwZkJxVUIwZVoxMklLSGJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNd2ttcm84VmFRYTB1VFl5RzlaTFlkTzlycHdhMG1iMnU3U1EtdDljTHVwRUozMHZ3WXc3cTdNb0M0d08yaUN5YmhPMGQwZnlFRFpDUllWeXpPZzlnVnVwR1dqRTIzYUh4Skpfeklfd2lWWk9OcDZaV2NNVUUxUERnVnB6ajJFRUxBOGs5NUdMSkY0d2Fsc2sxbng3NmdCcEZ3X3ljQ19aTGFYa3Q3dG5j0gGvAUFVX3lxTE13a21ybzhWYVFhMHVUWXlHOVpMWWRPOXJwd2EwbWIydTdTUS10OWNMdXBFSjMwdndZdzdxN01vQzR3TzJpQ3liaE8wZDBmeUVEWkNSWVZ5ek9nOWdWdXBHV2pFMjNhSHhKSl96SV93aVZaT05wNlpXY01VRTFQRGdWcHpqMkVFTEE4azk1R0xKRjR3YWxzazFueDc2Z0JwRndfeWNDX1pMYVhrdDd0bmM?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>1</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>46013.339375</v>
+        <v>46013.82175925926</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Man critically injured after shooting in Toronto’s Kensington Market neighbourhood - CP24</t>
+          <t>Real Madrid make €150m Vinicius Jr sale decision - FootballTransfers.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:16:52 GMT</t>
+          <t>Mon, 22 Dec 2025 16:06:00 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQdXVyZ3lHM29VVGRFVFlfUDhhMlNmdG5fM2lDT2x2Yy1yMllzU2NuZFdOcW5Yek9zSkFwcVlzak1zY3B5OTRMYkhIa2VzTEl2SzlvaTU3blR1U3AwMVFUNTBqQTFIRFpyRGlWZVRVOE96MUR6QTdtaGdDQWlfNnMxS1o0NlJuVWlOS0hUS003QWtBX3Eyd2JQQjNLZmozYWlBd0xLRFdBZmF2ajFjbVFZM3I3R1Y1OTEzd3RTd0xEYTRyRGloa3VN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPSnRvVUFDR3dSXzV0dmhmYUcxVXU0ZDl6R0M3NHpwVDlKWmFXcG5pQTJyR1BCWEdCRGNjRDBJcnc4TF9idU02eERRLTVEaWU4a0dtNzR1WUN5MmNhaW90Z0tBNGJfMFlHc3BpRmk2bkVMTzFORE1Va295Mk5Oekl4ZXNEYlg4VkctNUt6RjFLRk95bFRENjg2dEoyb05BcGRkb3hYWkV4ZVRoM3BsWUVWLXpCVGVEbE9lbjUwdDdHaThWYkJYbU1qTzlYNkdzdWIySmIxVTczT0dzMkpQaXpj?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>46013.47004629629</v>
+        <v>46013.67083333333</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Police offer huge reward as they hunt for the killer of a “mistaken identity” shooting - Daily Express</t>
+          <t>Lewis Hamilton admits he loves “eating all of that” - F1 world champ explains his typical festive feast - GPblog</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:55:00 GMT</t>
+          <t>Mon, 22 Dec 2025 19:29:00 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPVTNzbjRxb2pJSnlrQkIxRW5GRXRxbnVtVE5UZlRGclBPRlg5dFpMQjh5bGVPNktnQlBBWFlRY1VwR1BqQ0NrQzlSamtTR0VTZ3ZETmhzTTMxM0FOY1l1NWlGQnFnbi1zY1Q2TWdiaE5ZSDNvSExPOVB4LWhSRDJVV9IBhgFBVV95cUxPNGpuR1kxczlfb25HRVZVZS1ET0ZIeF95MDlHYU9YdHlIM1RUSDlDcm9GMlRjVlo5Vmowb0kxX01ER0RBa0VpU19YYWg1a1NfRUk5RTJHYmVfZ05xYUNRbG5ZV1RKOGFVLTBpdjFnQlk5VHRHMmczT3hCUm8zV01BdkRNb1p4UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNeXFXbmpEZG02eGxvOGFiUEMxQm9HMlhxVFI2WUZweWdNNXlRaVNfR3VzX3E3RWtZMWQ0dnRDTU5fcHM3WTl4X3k3aV9sUUtHTWVOWFF6U2l1bXFDWVA5XzQzajktS19ZbzhheEtDdVctM3RlSndWbFhDbHhXQ3QzdExfMzNzY0V0QVl0TFlVNTZGTGRFbUJvSUNaZ1hPOUE?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>46012.74652777778</v>
+        <v>46013.81180555555</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>The 197 new M&amp;S stores opening in London - full list - Daily Express</t>
+          <t>Eli Ndiaye’s rookie NBA season has come to an early end - Mundo Deportivo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 20:07:00 GMT</t>
+          <t>Mon, 22 Dec 2025 12:20:00 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE8zdmk5TGRJaVhlX0dvcFNMSjZocjljMXdLSm16TEl3Q1c1cGNacHYtaUxTdUxqWElqZFRsUElCQks2NnZfYlF0T0hiTXU4Zzl5b3A3RmJjdWx6OGlGcWFFelJsZEhOOU0zY2ZzWEFVaTBnMjR2ZGJyNjR30gF_QVVfeXFMTWVYOHp3Qkp5TERWSndvaHhkR1F6a0tMSXg0YkJXQTA1TlRocXZTb1dnU1hvVDZ1Q0FEQjFYdWQzNEhVNVpEZkNLSDNNSW5TQ056Q3NFWlRIUEQyajNqdm50d3piYnRmRUFldDIyLVNEbnZwalc3TG9DbHo3RDFGVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPa2taN1I5LS1UOHAwNGt4allCLTFSbFVZaEtQZkgxeVVsbG8zOTB1QlJDa3FyUTd3bkZKZFNBeFVObXpVX1JiNXAzdUNXMU9iV0lScXRxWW9zRGNXbTY1SlE5aEtBRkZtVkx1OC1EQUpHaFhyN01yejRKSFYzOWVhdUt6ZXBEZThtZ3dGU3NtWGxOMU1jLUJpdlVXd28zdmNBcnN2alJBcnZXdkFaTktZRFlPNNIBwAFBVV95cUxQU3M2SkY2MWg2cWNvZnJGblkwOGN5ZC11U2JNR1YyenR3dDFqNFJnQVdYcVJLZTlodDFGa2g0RGduanAxdFcxUGp2MmVZWWlha21RQktsT2M0dW9xQmJYWkZyZTR6QkdMZEMtRFJTOWNPZlZtYmhQUHRac053UExEUEQ4aGtFbUp5bUJXNVhpU3NFaVRLcTZhSEowNlZIeE51UThVbi1BUTBLbGNtdjNoblQwV0VseGFqblpmM3VscGU?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>46012.83819444444</v>
+        <v>46013.51388888889</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UK snow maps show 600-mile 'Beast from the East' hitting 24 counties - full list - Daily Express</t>
+          <t>Sar Auto Products Limited (538992) Quarterly Results Are Out - Volatility Adjusted Trading &amp; Explosive Profit Growth - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 15:57:00 GMT</t>
+          <t>Mon, 22 Dec 2025 14:40:07 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPZGRSdjVBWjJRUUpBTUYwSlNTUU1sZVdLeGh6RmtJV0lEV085VzRGY0VnTFltVHhkczIzS1JpUGtFSndLdldYWTh2TTNET3JDdThtR1JoV0JYUnhsVGgxUGVLWmNweXZ1WXBUd3ZtSWdIcXpvdzRycWlObTFXWUNEVmFuYVM0RG1XTkpqSGJCUV9uZ9IBlwFBVV95cUxPTnc4X29vYl9sTVNLTlZhV0NBdlhqSGlrc1M1NU5GTV9od1FlMktpNGxERnNxaWFpVlFOcU05Q2VhRWNTWThwNWJ1RXVtRmpXZVpLZEstTlNJeTNkNkxfcFd1ZTYzQTV6X3hyYWpQWlJ5bjlFTUZ3X0haZlZoYWxia1JTaGdmenBwYk5LNmlkS3I1T0dhdFpv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNUXJ3S015VGdBMTBWOVcxU2hNNW9LbkRtTkkxOU9Kd0pqYmttSTd5X0RKV3ZHSjBBODFYa2hEV01UT25wV0pUYk1jYllsZjRvSHdjQkRqQTFPNW44cEJSWmg2NzdTZnNtRmJ2NkY2TnJnMGZkTFg4SFE2T2VYMHdEcWUwd2ozOTF3eHFiLWJFTW5Hbk9Ycm1vVTB0TQ?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>46012.66458333333</v>
+        <v>46013.61119212963</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ethan Hallows convicted of Kevin Pokuta's murder in Sheffield - BBC</t>
+          <t>Better than Barcelona where hotels cost $230 and Tarragona keeps Roman ruins empty for $110 - Journée Mondiale</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:40:01 GMT</t>
+          <t>Mon, 22 Dec 2025 08:26:36 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNbFBSNFNRdnpDV0hHVE9mTjI4cF81VTg4bWlOX1hhLUtrZjFTOGhHTFpjRkZ3OFEtaFpDb25YSE9rbGpKREVFeW8xUWo1QlZRQjlUQkdBd0xXVEZPZEZ0TmF0YkJhdWgzekx5V2ZXMXFpbEtkOW01cVdXYk9SejRCcVhR0gFfQVVfeXFMTk0wcWhKZ2VMRS1ZOFNqNm5MNHR3dFhiQ3I2ZlNSOFBQRVBJbjBOT05YdGo4X3V5cTQ0cWRnNnBQVm43ZXluN1BYVUQ0UVAxbFJGRy0wbkFYTVdmM1Npa2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQakVINDFRMld2VmJRSmdfNXpqVmpfZTdjSlo1T2ljanFZZmZtR1pqWUxEMHVQNVY4b2FnUlJERWpmMUlkYVMwZF83a0ZaNkFaRWxxU1otdEhEMk1YMEtXX1JjZkJyMHF6YmJIekQwRUZGTnpqcVpPSnBnZjl3OHJRWUMxOXJvd0FCWmZIaHJkbkZCbTBNU3FSc2hMZFdHSGRYNjE2N1ZfTkJDZlM1QVZxdzBzLVJhUldfM0xqZHpseThJSzRo?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>46013.52778935185</v>
+        <v>46013.35180555555</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>‘Dan taught me to live for every moment’: French Bondi shooting victim, 27, honoured at Sydney memorial - The Guardian</t>
+          <t>The development regarding Asensio that is causing concern among Fenerbahçe fans. - Haberler</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:42:00 GMT</t>
+          <t>Mon, 22 Dec 2025 20:40:21 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPM0xqeGZySXFETjRGRnNmUXRzVC1yUndabnMzN0hvQmpxNy1kNmZLcVR4LXB0bkUzSFd2SlUzc3dlMkJHZDhlbHpYS28tZ1hTX25zUVFCQWZoVUJxU2NqeWthS09JcU1ObEh3S0VBcXViV2FlbmMyVG81YUhYMlVBbV9DZnhMcFR6SkdZWGMwV2cyT1V6Y1Q1d3ktSE5IMW1VSWVxU2NZQVctMldmaWljVmV0Z1IwR0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQS1RhLTNtM1MtbXMzajgxR2hNNlc3ai0xTm0xOEVDTUtIbnNBQ255LV9EVFFiVXZxLW4wUVRhZmVsYk9EQjlROG5xTVcxLXVNMnVVMzlscHdXdFpndDZYT0dIWjEtc2dhb3RobVZQa05wU0FTUG1OQmxTWDk2YzlpMHRxMmYtQlM2?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>46013.32083333333</v>
+        <v>46013.86135416666</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, Spanish   language</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Home Alone's Kate McCallister journey voted UK's top Christmas film moment - Lincolnshire Live</t>
+          <t>El peor balance económico de Sánchez: los datos que desmontan su moto - Libertad Digital</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:49:17 GMT</t>
+          <t>Mon, 22 Dec 2025 14:00:11 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNRHdFN3pJaWpkQldudmxMREQwTDY5VWlQdWFvNG9MQ3h4c2VHN3BOTDFPOFNpUmZnQ0xhNXkxclR2ZjhuYzhxYTk0UTcwMXlVbkpEUE9HZmtwWU1nY1RiTjVCRlB5NmpUQVJmT2ZvNFQwLXZTWTA3dzRMY3QtVFVFX3BTdWp0cmVpcTl4MUhtRUFFNEgxdEJlRFo1Tk56LUhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUEkzZndoZ1ZnU3pwREpEUERlSEVabWJ4cnZYZ0Q2WW5iTjZrR1hYeUF1Q09jaVNNdFMxVElPay1FM2J5TG44R0xMY0cweE9MT19oM19FNUU2LVp0eV9fc1NmZ0pUOFNodFlEU2ZvNk1lZXVJTm53R3hULU9XQXh5OFd3UDlIZUhsVFNpU2hzUjFiNFVraVpPZFFJV0JRXzdpTEZVeEFLWHoyeGxBZDZvSGpCQmFxSTRXaHBNblprWFZ1R2I0UGg3V0pEeHZldw?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
         <v>1</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>46013.40922453703</v>
+        <v>46013.58346064815</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Village Search Bicester and Kildare</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Love, Fashion &amp; New Cities: The Filming Locations Of ‘Emily In Paris’ Season 5 - Travel and Leisure Asia</t>
+          <t>Designer shopping outlet's demolition of sports ground shown from above - Oxford Mail</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 02:04:47 GMT</t>
+          <t>Mon, 22 Dec 2025 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQdTNCWi1UTkN2cGI4dVVBVVhkcmZuM3R2U1NwaWtqRWhDQVZzR2dCRkJVWkc4a2h0Q3FWRG43bTk0ZnhoSHE5NHQyRWN1OEloSmtwbUMtZzRGYkJLOFh2T1Z4U212ZzVPTzhBMEZ4UW15OVNwX0M5cmhaeE9qNGxLNFRZNGhOMkxES1h3THR1VXBvdjNaR1ZFSGEzc3NUU3hiMEE4Tm40aERGR1VWRXZuSDRZY0NrRE1aUllEUWpOQlVtWWgzSkJyemVHVURCd9IB0wFBVV95cUxOTEo0cTVjcm5VWmdsSjhkRFlfNmpLR0RldXZyNjRUSUZkMmdTN205dGE4LUJfM1I5RUhRdGVlWVJkY0lwOGpsMHpPN0JHS3Y3cXdGakxVeWlVanRRdmU0Z1c5YkhENDZVUDhsSXZYUWJtNjFkQVlRVGZmeF9sZl9XQWFBNmRyVEZtT1pTR3VLYVFNblUyYV9sRkI0REE0WlMyQkh2X0NSQXA2VEk4ZFE5QmpCc0pERk9QRFBabDM4bE9kRC02ekhEQlBuM0lvbDFBSXFJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPaUsydVVMc2V3RXh0SjJ3anNicG1RRmVYZWE0SHlmOG5xcTVTeHhzZE1RV25kYjBELU5rM2xMR3BldnZ5VVc4X3gzU19KWXJHbUFkTGtnQ2VoT2lkOFEwQkZuMmhFYkFNRUstLXpucUpHT0tkRjRwQ3RwS1FHTGdXa0xVM1FmZEctdjFGOEJZWQ?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>46013.08665509259</v>
+        <v>46013.66666666666</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Village Search Bicester and Kildare</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>“Parallel Tales” by Asghar Farhadi on its way to the 2026 Cannes Film Festival - WANA News Agency</t>
+          <t>Actor Simon Delaney set to launch his own food brand - businessplus.ie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:54:15 GMT</t>
+          <t>Mon, 22 Dec 2025 07:58:56 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNOGd2V3dBbHNlSVk5djVLNlJoU29YLTF3MmpjVFZWR3BIcE55bEdYOE9HWkRILVlrVThvVmZxNmJtQmNEMTBWNFJpdF9JLWdFMVA4Y0tTekNydTZzWVNXUGdESjMza1g3cFRyUWlXZUVEZXZSc01leXAwcGttdnQ5ODE1V29YaGd4NDdGTHA1Ym1OODMyVmRDNlRqWUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5heWVRYmZhLUNXUFNyOF9ZV3Qzd1NQaFBZRURZZFZIUG9hVkxTOThpcUF0Wi15ZGhtZE52RE9DTkExZWx3ZEhmR1VRcWVoNGM0cWI2SHhTemZpeFd5ZnMzQXBvTFNrSmk1UGN2aA?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>46013.41267361111</v>
+        <v>46013.33259259259</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>They’re Finally Letting Nancy Meyers Make Movies Again - Vulture</t>
+          <t>Man jailed for at least 26 years for fatal stabbing in Tottenham - BBC</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 18:45:33 GMT</t>
+          <t>Mon, 22 Dec 2025 18:32:56 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1mbW9hYmJVbTI0RHA5OVlVdEZjNzBHanY5N1dDajVyV2RIZEl4NnhYZGYtdTBkckVzZWNuam9VVmpYN1pZbGctcjJENDQ1RXF1Sk5iQjVTdldyTGRiS1h2Y0lDQ2pqM1pCbVhGYVRwc3Z3c3pRVFRtNEo2T3dFUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1SZmFtRFZuVDZFcVA0TkNlMzQ3Zm80bEIwVUhvY2p3bXBjd2Q4X0V2TlcyM3BEX0psN2VtaGZpLU4xa0ZoUXAxZlhUNVBibTItbHhuY2dvc09nOW1y0gFiQVVfeXFMTXI5Yk9kMVJRUVdDVTVvZDVfbjBwODNSbmVSUXpuRVRmc3lpMnowYlU4S25ocTVtN2RFYmFxLVRKUFlpTEpNTk9kNXdiU3NZbWJZUm1Tc2ZUNWE3Q0NuUjFKbWc?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>46012.78163194445</v>
+        <v>46013.77287037037</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fendi Brings The World Of Emily In Paris To Life With A Special Capsule Collection - FZINE Singapore</t>
+          <t>Bermondsey double shooting recap as man and woman attacked near Old Kent Road - My London</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:27:39 GMT</t>
+          <t>Mon, 22 Dec 2025 17:37:30 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxONE9RMFdKT1l5Y3JkX3dHQmJ3QTV0WUlnUmh6THN1Nk5yZE1Xa2IzMnRoUTBIVjdjZnJHV18xV0FVZTBYY2R2SU5jTktCdy02ZUVnVzdndER2M0xXbVJXd3Z5UzF0Szl1dW5lMkRCMk5QbEpRVmpEcjgydlF6MDBNZDBSNkVlRnYteFF6bHQwbDE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNHdCMFFQV3Y2dmdia29TQWYtTjZPakNYSWFVRGZ6TllSR09zaEVieFJlUGlBZVBFc3E3M0w2WDNtOU5PSVFxNHBIdHRwcFNqenFRbmRMM2Z1RWVzdDJVWnFzZUliUzVsc0U5Z0dXTnk0SjU1bDBlNmVaX0ZJU054Y0hKbjFQTVhTZWpyckdZRlpzeG82ZF9RUtIBngFBVV95cUxNM2xMM3NNZm02R090cV9jcUlZelYtdXp1WXJVamxnNXZ2T1lxejY5R1lNTUpaVUlDRU9KbzFhV3VSTVVpS04xT3lQMjBTVElfNjBNcDhwNUhELXlOdk44c01GQ2Fna3RCeTlubHdXMGVKcHNwRjhtVHVlTGYteEhqWV9mbU1GaG04YTluVmREOWlOVzMwR2hLM1hYQzN5QQ?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>46013.43586805555</v>
+        <v>46013.734375</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Deporting American democracy - The Korea Times</t>
+          <t>December 22: Oxford Shooting Probe and Hit-and-Run Sentencing Put Security and Insurance Risks in FO - Meyka</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 03:30:00 GMT</t>
+          <t>Tue, 23 Dec 2025 04:36:06 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNM3ROU2pjeHlfRjRsY19rZC1uYU40NklzeGd3Uk8tRmZUVkZTN1ZGRHUwUGtMakZQdkJvVktid1JKWjlYV0JyOFVVR3U2TnktalJ4Rlpsd3JBTm0tWW5Ha0xqZ2t1WS1ERVA3bnZsbFRiaURTdFBuQmhJVjhpbzhRNlJrMC3SAYQBQVVfeXFMTTN0TlNqY3h5X0Y0bGNfa2QtbmFONDZJc3hnd1JPLUZmVFZGUzdWRkR1MFBrTGpGUHZCb1ZLYndSSlo5WFdCcjhVVUd1Nk55LWpSeEZabHdyQU5tLVluR2tMamdrdVktREVQN252bGxUYmlEU3RQbkJoSVY4aW84UTZSazAt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQSlBLZEZkbk1uc1BDd2hQOHJ6YUktUGM3ZHNfZ1ZNRXAzbl9jWmFaOGRZcGJaWm80alYzUkpiVVZKNlphNTFoQUJuWDJmMEFDcldTdVg3TWM3RFl3NkttWDQyOG5kZ2E4dUZObUEwN1V3SzhlLXBjOFlkTG9lOEhaV3hRalBmdXlDOVNfUlpJTHZ4OUdMVzF3OE9yUzFxNFhmMEdUQ2FEZWlVREhVNHl2UWg4UWxQRE9pdmZZLW5pNmVGU190cmp3?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>46013.14583333334</v>
+        <v>46014.19173611111</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Gamecocks Host South Carolina State Monday at 4 p.m. - University of South Carolina Athletics</t>
+          <t>Man and woman taken to hospital after shooting in south east London - News Shopper</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 18:55:55 GMT</t>
+          <t>Mon, 22 Dec 2025 13:26:57 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPMU1hOXk0UEVqamFDdXhEZTBxSWhaZDFJUktlalRBTnVMUUN6V3l1Y1RXUml5aXJpVzY1WFFUa0h5eXh0UE90SkJZRXd6dE5IemowUFpuRXQ5Z1pmSXVUbXU0Vi1MOGhteTg1TElGaXg3emlRRzVPanR2SlZGZTQ1bkduYlpfYlhpenpjLXFRMzBhUzBBZUQwYXFoUDU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOSUhRV25VN1FrQnpqZ0daOGdlbE9qOVdYZTJSYU55STBFRV9OZGV6WmFBMVdWc2l4RHk4cFdBUmlPSzFHVmdwWmNnUjZINGR6YjNqZFc0QXJja1ZDbHp5WTZDLUxMekNWSldTa3M2M3NTNUN3SFF5b21WekF6QVJrLTgyWDFnRlZoNWJPeVJLdXVwN08yenJyVjhuUQ?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>46012.78883101852</v>
+        <v>46013.56038194444</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bondi Beach shooting suspect conducted firearms training with his father, Australian police say - WHEC.com</t>
+          <t>London-Hyderabad British Airways Flight Gets Bomb Threat, Lands Safely - Kashmir Observer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:18:03 GMT</t>
+          <t>Tue, 23 Dec 2025 06:35:59 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPX2cybUdsUmVkTVNoYk4wcHFsY1dialpXeTBILXpaWXBkeGZRd3QzSnQ5YVFRbi10bnU2Vl9PekdkWVhzSVQ3SDVjWFNkZ0J1VnFPc0JRQURfTDRNM2lQTU9Qcmh5bEpQc2tJMWVGQ25OSmZ1RzNwMHMzQVQyTHkyV0ZXMEkxOGtkU2VlZ3N3WkFhU3BYWHB0Y0FiNnpnT0x3M3dQa3dScEZNWXY5enE0dmdvVEE4ZjI0OVZCbFVudUJFdGN4ZDh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOdEVPLTJ2b0E2bFZVa2czNkJFVklUSHZYM01kRXBiNElHaG5tX21uUGdncFRVNFF3TTVrT19LYnExUmxfZi0xUy0tYkducExURnZIdWRNTTFNS21SVExNM1RxOHNoakRieGVLRWtQNHNpeksyMmdLNko5V1REZ1ZUNDZrblBTX051RFRUUHJ1cy1zdDdBdUE2Ykk4Vi1YV0NfdU5uV2dLZ0w3WW9PMmc?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>46013.30420138889</v>
+        <v>46014.27498842592</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lily Collins says she "cried" filming hilarious Emily in Paris season 5 scene - The Express Tribune</t>
+          <t>London Shooting And Maida Vale Stabbing Leave Two Dead - Lawyer Monthly</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 15:22:30 GMT</t>
+          <t>Mon, 22 Dec 2025 10:36:31 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNY3JHRWRvbHgtWXprZ2dtVWd5YVJLNDRJR2JBY0FuTWZ2VFd5YVpSUi1MczYxdHlBVkVwZmplR1l0NEJfVks5VzZ2Y3lKamFCdTMzY0xLSVV3RTRLSzlqSkZGclp1TV9ZTldhbXN1QWJXbXY4NTRtdUdHUkMyUklHaUcyLWd0dFYwaVp5dTVDUVZWMzBmMGdaaGh5OUdqazlSc0l1cDhOdGZJWXY5NXZSTEdR0gG6AUFVX3lxTE1kazZkdkp6a2EyaVZaYkZoUzA5c09ka0NfQjEwdG1MMFpTYWpveDl2WkRFcUdzTEpQTkxOX3lGX21oRlhlYmhuY1NZSS1ZYldLX2dBVzdHR1BoeWtyUWs3RDVlVXgtcHdCaTd4MF9adk5LekV4cUFRb3ExR1RzVjlzZkZXSDhmcEQxVHZlaWhjbmJfeUNnRDU1OUpJaG1UTERDRFlDVDRUZVpEemRpRXo1eWxuRFR0QjNIdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPbHZ2ZENFQ3R0ZFhpanUzUGVKbmsybFlRdk9fWEdqNzM2ejN5LWl6dS1ZVVdNd2R1LUlhb1ZGWEctT2VFTXVsUTIwZW5lMl9rT2VTZkpocTgzaWlwbXctWkhFdjNKTXdvMmFVTV9SczBMeFNKWUl2ZVIxbDNPUzI1TTEwRW56YXFtVHllRw?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>46012.640625</v>
+        <v>46013.44202546297</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Carolina looks to shore up offense vs. S.C. State - Field Level Media</t>
+          <t>Man in serious condition after targeted shooting in Kensington Market: Toronto police - CBC</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 02:13:22 GMT</t>
+          <t>Mon, 22 Dec 2025 18:12:55 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOMXgwRndvMzZqM2g3YXVWek1tUU9sa2Q2YTNtcjhaM1BQOV9KY0NteVczQkFZV082Vy1TQVFXV0EwdkhnNEJGX2tPVjMtNVZvS1ByblRzWGxsWWNCTW1QN05mQWhieHYyZ2d1Mm5RQ25BSUFMeE44TExsVEE2X1dnVXEtanR4bW03VXJsaFRvc0JSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNWUpEQzk3RmdOaUZzWE45Zk80MlA5cWo5di1oTjltMFFZX3pCMTRJOEFwM2xNRU9MMW9oVUFQVklrNHZJVnhjR00tamV1X0h4RDl5YnpFVTRvZEcxejBlRDZzTGR0SGYyUExnM0lmWXlqLUxrdGFqd0x1T0l1am9lNzlUNVFVVmZoNjl5aUVmd3dNZmZsSlZ3R2pzVUlvak9fck5oZWRZWlE5d0Y1Y2ViSW1VNjViZndjMmFlWHhIRHFTTGZtaXllVnZGbGtvdw?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>46013.09261574074</v>
+        <v>46013.75896990741</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Marseille cruise in French Cup as Monaco, Lyon advance to last 32 - NST Online</t>
+          <t>Two arrests made after man 'shot' in Oxford - Oxford Mail</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 04:42:44 GMT</t>
+          <t>Mon, 22 Dec 2025 14:18:47 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZjlDQ2VqX2UwMnd5RTVZMFhXTDNoTW51T2RMYlA3dFBpR2k4bTJOaXNmNzREUmkzQk12X1EtSENpQ3pnSTE0YjJnTFBsQnlWSUx3THR0T0wwV1F5NURCQm90TlJyazlLdE1VTFVNTnB4U3lFSEFyQ0kzYjlVNVRTUTMxeHU5cFdnTW1VSG9rUE1nX01ka0ZYTDYxdGpCMTZ3Z2lZZzNUcUFCR2F6S2NwLWN1TUHSAbQBQVVfeXFMTmY5Q0Nlal9lMDJ3eUU1WTBYV0wzaE1udU9kTGJQN3RQaUdpOG0yTmlzZjc0RFJpM0JNdl9RLUhDaUN6Z0kxNGIyZ0xQbEJ5VklMd0x0dE9MMFdReTVEQkJvdE5Scms5S3RNVUxVTU5weFN5RUhBckNJM2I5VTVUU1EzMXh1OXBXZ01tVUhva1BNZ19NZGtGWEw2MXRqQjE2d2dpWWczVHFBQkdhektjcC1jdU1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOMWRtV2tFR3hHbXFVcDJrV0poNTYzVVNKV0NPaHNuMTFrRnFxZnpSU0xPOVFlY1ZqemJZaDNhcnlSaGpRYW1SaGdBbnlvVGtYdVp6T0l6QTdXQ0hHZWpFQzg3WlU5Z3JVdlBLQWlIMGsyb1JjZHpjVzlObldxZEVyZFNrN3lKQXNPOG5DS3JwZ2g?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>46013.19634259259</v>
+        <v>46013.59637731482</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>American WWII bomb found buried in Hong Kong, thousands evacuated - AOL.com</t>
+          <t>New 'Banksy' art appears by central London skyscraper - My London</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:36:42 GMT</t>
+          <t>Mon, 22 Dec 2025 13:30:00 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQdmtJOXppSzlCZnpOZDE3UFgxaGVwQm5KR2tDOWFLN2xlcXBKcEFhdXRiQUIxXzRGa0R6LVJPUm5TRTV3blNrNFpiYUIyMzdnRElpN242cmpmQVVvd3VSNEZVWW1wb2luNzNXZzEyb2xiWF8ycFhzX3dKU2t4LWtzaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxObV9nNTJnOW1lTFFjeEFtcWVoYWZ1QmNGVmhiYnRlOFAtQThja2dwUGhjTGFRUVUxd0RlSV85UlpwSTAzbGU5bjdrcWdqeG1wRnMzWlcxTDJhS0g0c2YtLURKeHhwVG1lZEpJRlR6YlRVUHhURndCckVLdC1qMVJHV0c4M1g3NVlKUGQ1bkJDTWZWWGUwUXln0gGcAUFVX3lxTE5NUWxtRmU3YTk5S3V2dXdzclZmUkRlZVZ5NVlOWXdMNmJsY21WOWpoWFFXbm1aRVNyeXRWUGFJa3dpMlVKZ2NFZjhjMWVLMU1Od1dJOFktc1ZtZjk3cjVsYXdOYzFHcFE3OEE4ankwZVpPTENzZDRRVzhOVW9xS1B4c3ZTYXJWNUZhVlgtUXZaeU11S3J5LTRfclVlVA?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>46013.35881944445</v>
+        <v>46013.5625</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Outdated Images Misleadingly Linked to Recent Mass Shooting in South Africa - موقع مسبار</t>
+          <t>Man, 28, in hospital after being stabbed multiple times - Harrow Times</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 15:19:40 GMT</t>
+          <t>Mon, 22 Dec 2025 08:04:17 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNbzRPLVVUY0dvdHJDMWNYNzBhT3RfdDJZVWdueFh1anBUcUozck55RUFNLTVtemZwZkRTZGVRSURMa1F3cm5DNGFjTC1NeWc2VU5DN2pwaFVXNVBaQks2ZjZhWUNPclVkbTdoOXlDRUNIV0JpMGs4dnRGWXMtVlc0WmhvSjlaczR4aThGbnpsSzJOandWTTJVV2VZcXlzMHFvSUR6eXNZb1c2ZTJfX1ZtUFdXVFJQSk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPYlpqSjdsMXpqbnJNdFRuZXdVVDFLZFRlX1lGa2otR0pKS0ZXT2g1RThidV9OaGk1NlZxMkRIYk05NGRQMTMxQ3Nmb1ZqdHRmTWVCbEZob3NNUzlKTVRLeUl1c1ZDSmh2N1FBTlJ2MUhWNnJVRThXd0pUSXVWU0YyNXNpVmg1LWxnQXJLTkN0S3pLTWozRW9oQQ?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>46012.63865740741</v>
+        <v>46013.33630787037</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Élysée Palace silver steward arrested for stealing thousands of euros' worth of silverware - WPXI</t>
+          <t>North London shop's plea after filthy pans and dirty clothes fly-tipped outside shop - My London</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:19:08 GMT</t>
+          <t>Mon, 22 Dec 2025 10:04:43 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQc0k2NHp0UF9yZkR0c1lGLTBPUlU3a3NaV29QM1R4Z2tIREFJdkZyaEZGcUd4enFhc0NuNFJxa1RjQzNaaVVlckhvalRLdFA0cUZwenNLQ2ZDbmNRZjNwdkdMR0NHVm5Xd1IzZmlfSXR6OEQ3MWY5S3lYNE9OdS15RlZjeWzSAZgBQVVfeXFMTV95SE5SREp3R1MzcmlJenl3aDhNM21JMXJFOU5sN3NuZHRiRUxKVExLVGVveGdIclJjbUhwMlV1bFI5ZGUyeUdkRjVZWWpxVEg0ZWhibVdSQVIwcjRWSFR6WlBlTzk0V2s4Q043Wm5sWjlBbWVQaWVnbkMyd3NTWEF1OTBrV1JNNEtILXJZeTRUMkpnU0RtRXU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNM1BsRy1tMmRWYnM3RF9rRktKZnVvZ0hhbU5naEFFTUNOZ1JxclRIMjFfc2ZuandaV1QtbGZsSkVDWGJkMHlQRWZVNFlodFlHOWw0VVE2UTU5bHk4VjV1bFAzYkZmcTVEbDlVVWFMUVNXSGlvSkRyY1BORWhaWWtENFppb2Vfa1p2RUFaaG54SGZaeWPSAZgBQVVfeXFMTko2VVJTdXRPc3ZHLVljYkUxOVh2ZE5NMU9QQ0E2RGNIeHpUMHpfZTFHTzZCUVYxUGhROXhQcjZuM0dNSXM4RmpYTFlTNUhvc1R1R2pXcl9tci1zd0NZRlZUNk9LNEpVRUUyaXhhUkQyVnFQVmkzYW5HOExUdEtFaXBGeHdjZlVVZXJ0RTZiTkZxYVA1Q2JNWDc?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>46012.72162037037</v>
+        <v>46013.41994212963</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Quote of the day by Benjamin Franklin: 'Diligence is the mother of good luck' - The Economic Times</t>
+          <t>Sheffield shooting police probe as homes peppered with bullets - Arrest made - Yorkshire Live</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 02:37:00 GMT</t>
+          <t>Mon, 22 Dec 2025 17:02:00 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQTXRhT1Y5ODFNSTE4Z1lMdER6VjZ5N2doalY3Rmk4SzZBOGRzNEdfMUhxSmRaSnFYY19lSW9makkzSnhNblF1dVpRS3luaHAzcDk1SXpIblRZMVI3OTN2QUd6RC1DWmF1NVZscjlWazRRRlh1VW4tSGZBRktVU19ESDdtTlcwLVBac1YzNGZSWVBwWXVxSHpKRktwbEFCZHVFa254SUJoYnRQQi04R3J5NTZoQnNCMGZubkpqclJXbW5xV19FY0hDcXJDMEF0QlIzWFBOYmY0NNIB1wFBVV95cUxQTXRhT1Y5ODFNSTE4Z1lMdER6VjZ5N2doalY3Rmk4SzZBOGRzNEdfMUhxSmRaSnFYY19lSW9makkzSnhNblF1dVpRS3luaHAzcDk1SXpIblRZMVI3OTN2QUd6RC1DWmF1NVZscjlWazRRRlh1VW4tSGZBRktVU19ESDdtTlcwLVBac1YzNGZSWVBwWXVxSHpKRktwbEFCZHVFa254SUJoYnRQQi04R3J5NTZoQnNCMGZubkpqclJXbW5xV19FY0hDcXJDMEF0QlIzWFBOYmY0NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPS1FJSVBpdG9ZMS1GdXpSYVV0RDZ6clljU28waFNZNVFjSy14RlMzT0E3cGo0VGdxazF6MUdGbGxocjctWFBNQ1dEZGZPSWdQc3dsNDVjSGR1Yk96bVhwX29yN0RaMHBkdVNOT3BfWkhZaGRwYWFxVjNSNVU0dHdVQy1sZm1RM2JfSjd3c0ZJWW9WN3BBUmowS9IBngFBVV95cUxQd3MyTTRLako1Z3BMejdtUE1pZ1hoSXNIa0FLRTh5V183eS1rZHd1eERJUzB0UFY5aEM5Sk1NWndmc2JBX2h2S3UtdV9yclF3ZGx5bTdnellyRHZuSDN5ZzllMHc4cmRiSUVrQXBhTlRhVmJ5S1ZzVVYxeURzOWp6aEVPRjV4dERUVDA4NEFaU1lRQjZDcHRiQTFNZVI0dw?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>46013.10902777778</v>
+        <v>46013.70972222222</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sathish joins hands with Telugu actor Aadi Saikumar for his next - Cinema Express</t>
+          <t>TGI Fridays on brink of administration with 49 diners at risk - My London</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:46:50 GMT</t>
+          <t>Mon, 22 Dec 2025 16:57:26 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQdjYwSUNGcWE5ZXNfV2FVZmhyRE15dUxsZW1wcWpuRFlETDR4VXEybXg5emJsYlh6TllNSzVUd2NHRDFRdkFpSm5sRGwtR2xwcVJzeHhXR21mZzdtQ2lCaGhMaHdxQ0ZLdmxtdzRFdXg3TEJpSFNpMWI3aHdiTHN5OEhIWkl3cGZQanZrMkJvVmhlZUlnb29LM3RFUHNET2ZGOF9RcVRYLWtBQ3BkelRkdXJIbVRuLW5aOVo4NEkzUWNneUduMlHSAcYBQVVfeXFMUHY2MElDRnFhOWVzX1dhVWZockRNeXVMbGVtcHFqbkRZREw0eFVxMm14OXpibGJYek5ZTUs1VHdjR0QxUXZBaUpubERsLUdscHFSc3h4V0dtZmc3bUNpQmhoTGh3cUNGS3ZsbXc0RXV4N0xCaUhTaTFiN2h3YkxzeThISFpJd3BmUGp2azJCb1ZoZWVJZ29vSzN0RVBzRE9mRjhfUXFUWC1rQUNwZHpUZHVySG1Ubi1uWjlaODRJM1FjZ3lHbjJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQdFpFS180V1JHY3hYS1J1NkpYOWhqS3lCTVowU01CZHppUWVWbVhEQjd2RnVDUVhLUDNZUGM4Z3VFUmhTSW45Y2NzOFcwQW1ya1JHQ0JVVFoyRnhhNWphaEk3ZFh5Z3AwWmx1bFpCZDRFaVdWVG9tdjJPV3dvelpNNHI3RUF0bU9rbkplOEpybUFtMTkxbEJPQtIBmAFBVV95cUxQdFpFS180V1JHY3hYS1J1NkpYOWhqS3lCTVowU01CZHppUWVWbVhEQjd2RnVDUVhLUDNZUGM4Z3VFUmhTSW45Y2NzOFcwQW1ya1JHQ0JVVFoyRnhhNWphaEk3ZFh5Z3AwWmx1bFpCZDRFaVdWVG9tdjJPV3dvelpNNHI3RUF0bU9rbkplOEpybUFtMTkxbEJPQg?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46013.24085648148</v>
+        <v>46013.70655092593</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New UK theme park to be as big as Disneyland Paris - Daily Express</t>
+          <t>3 tower blocks planned near Tube station - developer's previous block saw window fall out - My London</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 22:22:00 GMT</t>
+          <t>Mon, 22 Dec 2025 11:15:00 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBWNlRubG03YUVhdGx3Z2N6Rm1lTDhhdTZ1UHJxVlhXejB1dGxieEZZbFA4QnFuZ0JQSWJBSzBjSTlyRkFVVmo1b3F1UG15YWxlMWt3MTlLTS1XRFFCeGg0SlBXazg0Z0RtRjRSdEFZQdIBdEFVX3lxTE1yUkItdkZWRHBKY2pYbko4ZW53Ri1wenItSHhTNzBvNlJXMFVVcUhtTy1Ed2JfZGVIVzR1TjhweUVzaERIUkNBQnlHX0Y2RXpwQnNZbFVxazZkNmlpSFVfR2ItS2pIMkFmSkVmYmpaV01VT085?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPbXlkMGpia0ZxTWNPRFZlNWtsZXByY2tKSDNDTEtwMDRXTjBHaXZoVWxqLTBhRUdVYXFEcUNnSTlKYXdwMEdEWTRiYjVHSkU5YUd2TjhkcThpZ3RySG5zMWxTc2kzbml6RFQ1MG5BRVBrQWJBYmNkS3B4NjFhUmFPS0tYcDlkdkhhdUNBR1ZR0gGTAUFVX3lxTE9ZY3p0bjVhR2xuQnB6Slo5cXB0Z3lSODV2QnNNSGl5aldQejFfZDI3SVJPcmJKX1V5SzNYbExfZ3ZSQ04tTkZaTnVsSjBTa2VXOE43aFFUR2xoWnV3TXFkNEJuc1ZtSnRncURIUlNjcERaM3NETU05Uk96V2ZVVGpCT2QxZGxoNDJUVElmcnpwWGFxQQ?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>46012.93194444444</v>
+        <v>46013.46875</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Succession’s Kieran Culkin’s Next Movie Is a Reunion 30 Years in the Making - ComingSoon.net</t>
+          <t>Explosion in a laboratory in the Rhone region, at least four injured - French media - news.cgtn.com</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:07:59 GMT</t>
+          <t>Mon, 22 Dec 2025 14:21:17 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOWldkX012V3F3V3VmcUhmbEhGeHlpaERkcG94UHVack85UzZQUEt3cWpxQWM3N3NHWnZTNlN4QTdacDJCVS1JTzBJVlBWd2pBdzJaUzJlQi1pQlVPYVhLd0lqVXdVYnMzc3ZPV1VRV1JjN01yWmRGU056V1ZCNGFvbzlBWU0xMTJ5bG8xWllMLUZLZmtLbTZ1bzNSVlBEZVRoaERScWYxeXdtSjQzTHdET2hHQnQ3MHB4N3FxNWhpU0jSAcABQVVfeXFMTlpXZF9Ndldxd1d1ZnFIZmxIRnh5aWhEZHBveFB1WnJPOVM2UFBLd3FqcUFjNzdzR1p2UzZTeEE3WnAyQlUtSU8wSVZQVndqQXcyWlMyZUItaUJVT2FYS3dJalV3VWJzM3N2T1dVUVdSYzdNclpkRlNOeldWQjRhb285QVlNMTEyeWxvMVpZTC1GS2ZrS202dW8zUlZQRGVUaGhEUnFmMXl3bUo0M0x3RE9oR0J0NzBweDdxcTVoaVNI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBUUmNkN1JGYmdPNWJOMjBYWjk4djA4Q0RTS3gtMEpiU2xzbGhYa1lRWnVEdDViNlIwU3ZrZ210YUJFVVI3WlRfQkdrSTV2c0FvT3pNeFJKY3BqVE4xNF9YVWZvU3dvdWw0T3dCSHZn?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>46013.29721064815</v>
+        <v>46013.59811342593</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Beyond Paradise cast: Who stars in the Christmas special? - Daily Express</t>
+          <t>Transport for London - My London</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 18:30:00 GMT</t>
+          <t>Mon, 22 Dec 2025 10:17:51 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPbklGUExVTEVEMENsUmgtS3hUQ0FRc2x0aVdQUjg3dFJ6Nnd0WVdjNngxZ0N2eGZxcjNUc0VXZnpiaWROY2VzNmxQMFhzMlptamdhVWt4N1lnNW1LUUxNY1ZsdVhFbGVyYWducnpZemdCRzNaR0E4M19jUWdWQk01ZDlVSEktZTFFdzR5ZFk3TTJZdjlsMS1MbEdLanlrdXpu0gGmAUFVX3lxTFA3X25tOWdUek85dnZDQTBPVUZXNlJUVmR5dVc5TUN3TzZlcjI3Z1BIS2NxMzB3NWRONWV2VkNDTmhpX1BlNEhxVWRYb3hkcEhCSTI3RnhjSFhIbU1vckgxMEhyTXNFWXhXUmxwcE5ZekFwMUFnOVZMNGN4MnhRSjYzTjBKOEhFa01FZ292a2N2X1hoTzZKQ1lRUktPRHFiMUFZUlcydHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1hdFhJUDBZNktZQ1hmWmVpell3Z1hJRElPWWdwQTZCVWVUaXZ1dnJadVFtcWFWb1ZBeklBdVFTbWNWNmdNM2tHZHZzbXRzeVlfdEt1QjNRS3hHU3AyRkhsNXI5VjdXc0k?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>46012.77083333334</v>
+        <v>46013.4290625</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tube Investments of India Limited Shows Support at Fibonacci Level - Earnings Call Summaries &amp; Free Explosive Trading Growth - Bollywood Helpline</t>
+          <t>Australian PM apologizes to Jewish community over Bondi Beach shooting - news.cgtn.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:20:16 GMT</t>
+          <t>Mon, 22 Dec 2025 09:30:31 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbjk1U0JMNS1HRWpsRzV1NVN1OFBrcmMxMExjdENJcVU0ZkZkUWF0VnMteGVNd2E5UjI2WWNtYUZJYUdvR1VaOHhhNExYZ1RTWmoxaG1VZE1nQ3VaelVabDA0NUQwZXN2N3FyRUJaZ01pb0VQQkw1NFZvd1RMWGJUOG5rejk1ZDIyaXFleEJEaEs4eTZDaWphd3hHNTRvWE1wV3BJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQOGxUYlZhbGM5ZVh2dDhGZk9NeTNCcm5mcmRzc0Y5OTZjd1ZCVGZleGc0LWpocFpMWW5OQlE1U21WYk4tbS1aRzNfYkRYVE1SclA2UlZxNzVOSWhDcXRMNFgxcXlSMDl3MUlaVkRfd3NCZ1pIM2lZcDZlM195bU92M0dxNVdNSFRGMFY4TXZuejk2SHdFQ0M4dk1pVmRZdXduLVUtcUdROTVCMkxscklvT0VRUWcxMmN5SWw5VlJNSmZ3TjhidWc?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>46013.4724074074</v>
+        <v>46013.39619212963</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Watch for Bullish Crossover in Infosys Limited - Utilities Sector Analysis &amp; Free Explosive Return Secrets - Bollywood Helpline</t>
+          <t>Lambeth bin collection dates for Christmas and New Year plus how to get real tree collected - My London</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:50:10 GMT</t>
+          <t>Mon, 22 Dec 2025 11:34:10 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPR1Y1Ti1kckM2ZlRxTXhZSWczRF9MLUJTSDEwa2hKdjlfOFg0dldPUmI3ZVkxdUZrMExISDFiVGdEczJlNVg3YUt6akpyQm43dS15eEVGN0lzcFYyRzcxdzQ5WFZSRUl6Y055ZG9yMzNXRFhEaXBXeXo1YlFtVXFmNUJ1cG1ZcnFh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOTU0wTjVucVQ2b2lveWpIN0s4QkxnQ1lTU0ZjaUk0OFFaZUtyWjRUcTVUa2RNVDZveE04dzAyYXYtRzBGSFY2akpQbW1MSlBOOFg5Y2t6eExBWFdiTFJZSkRqenpLZGZYbmxXeExJNWNLRDhKMnUxaldsREdFS3NYZXk5VW9iVVBQRkJ6YWxKRExGMUxJVmNJWHd3eEfSAaIBQVVfeXFMUHZ5cHM4eGRlWHEtcU56eDlxYkl1NUZpWHdadUpORTg3em5hOVBxT0hRcWVtNWNDWXJ2T0Y2WnF1YktZTGM2bnYyS01LU1oyU2FBQXNwaEt0S1BnbndvX3l2OTdUYmNvMEw2XzZZbkpHcWZNZ2FIbWQwOGRyUzJaMFZWSHlta2FZUDhjSUVjel9OcTZyZmFpdEZEYVFiNUx1V2dB?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>46013.24317129629</v>
+        <v>46013.48206018518</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Gujarat Winding Systems Limited (541627) Expands into New Market - Sector-Based Investing &amp; Stay Invested. Stay Smart. - Bollywood Helpline</t>
+          <t>Police Seek Teen Shooting Suspect In Chatham - CKXS FM</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 02:40:47 GMT</t>
+          <t>Mon, 22 Dec 2025 09:33:34 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOdmNnUHgyYkVQMFR4dFRPc0RISkR5Q3JYSzJldVlSeGFqSWJJSEJ1RFBUbzBZNHZueG9ObUVOSlJ4ZFhWd3FSRDNycUd6ajJnOFJmMUZiM2NTSmpLSmlVNWMwTll0Vm1jOUdnTjZqXy1XT05KUTUwMDVMbTFJZjRiODRpOTl6V2V1SlY3S2Mta0FMMGxodFdoQzlXT2dqdlAtS25GVzJmaVd0Sml1ckRrS2NXdUY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9VeVU1VzByRm15Z1JLb2V1STVvT0lFUzgwSTFVSUVNVi16eG9wSEk1bUlfNGtBd0hXVTh3UkRScEtWX2ZLRHBTWTdZMjVQRUduVnlJQmZaNS1ReDN2d3pjejQ0STFNQngzVExKSko0VWtPd9IBd0FVX3lxTFBLd3VfN012NjFkS0tjaGRKc2NJb2txMllQV3p5TFhkTHdQRjNCLVhpWF9RSUxsSEVPbmpJaEZSWUhZVlZPLUpCMGQ2Z29sUmtSUFh6NUJVaUtSd2xNRHJiVU9qbkVsb0RKS3ZFYXFNbkNHOWI2LV9r?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>46013.11165509259</v>
+        <v>46013.39831018518</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Short Term Trend Reversal in Gothi Plascon (India) Limited Possible - Small Cap Stock Opportunities &amp; Smarter Trades Backed by Machine Learning - Bollywood Helpline</t>
+          <t>Parnell Square stabbing survivor, 7, continues recovery - Gript</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 15:50:08 GMT</t>
+          <t>Mon, 22 Dec 2025 14:07:52 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUUZwVG1BSUZYWEpDcnFTWU5Vc0RmSGM0dkFMcjVVOVN3RDZjS2lIRFFMVXUtNDJwY3Bna0tRaThhQTF1S1BEWDV6RnVyQl9qak5FWUU0ZU5pdlBkUlVrTEF4aC1YNVZ1eVRwV3VyNWUtbW5TWWowX2UyaldlSFhHUk82U2w4b3VPcnF4cGw2aUVkUnZERXN5Vk5GX0I0WlVranY2bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5JOWRlMG1ULTZVRUdsWWhIaWpKZ1d4VXQwdWc1YVNCZlZOUG9mcXktRVh6ZTBZYVgtV2k2ck5BT0pmUTV0NWxpcWJkNkxTYTIwSXBGNUEydlpfQlRSbzB1d3NiMlNDdGxPNVJKUGNrdGI5cDA2cXJWRUlHbw?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>46012.65981481481</v>
+        <v>46013.5887962963</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Shubhankar Sharma and the Anatomy of a Two-Eagle Day: Signs of Revival on the DP World Tour - IndiaSportsHub</t>
+          <t>Mother of girl injured in Parnell Square stabbings says daughter may one day tell 'own story' - BreakingNews.ie</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:01:31 GMT</t>
+          <t>Mon, 22 Dec 2025 11:26:57 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNcU1PNEcyM2ZjNUxxS2RQMkNTckloY0E3WkNSWmlmYWVwRDNKT1A3ZUtXUWZWX093Yk41ajFsUS05a2hUWmVDekRTVUJoajktbmxORUI0dkJQN1FDd1FuaGFxRDFtdUdVRlo5NlFCYWhqZlVUTHQxc1NFWE9lZnhObHNJaGI0OTIzNldIQ1EwYlI1T1lLcVdqbzF6elpNeERSSUk0Y0FPOEttY1hUNEZ0bkNmV3BOZTJtS3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQay1BblBoa2RoZ0xfeEtCZTRiLVZQSmlwT1FGM1VhekhGUllOX2NCd2pHMFRUM2dpQ2FManMtSnZxcENBdll1OHVSU21BX2l5cDZSMFlDaTNTZzhWSzR5b2hXS2VRUHM0ckZ3VHlvU3ozblRTMHJGaGcxMUZsdkVNbDJ4SVF5dE04bVhvc3dMZDd1RVFuTWtPT0V2d2pvak9XUkdiX2hhMENpalBGeWlpakZ3dUh1U2VtNGJUR3N6MnZyY0pWRmlTUzlsOUJZbnFUUWNLNkhpYw?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>46013.2927199074</v>
+        <v>46013.47704861111</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Furies Season 2 Confirmed: French Action ThrillerDominates Netflix’s Global Charts - TechnoSports Media Group</t>
+          <t>Where Was Goodbye June Filmed? All Shooting Locations - Moviedelic</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:05:42 GMT</t>
+          <t>Tue, 23 Dec 2025 04:49:17 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1FUXJqYVNNVXZ3dXZMU3c4R2hrc2FjRTNLX1Y1SFhLMlAtbDB3WndveVJHY2kyaHJmdktnZExROVczeUg4YWpJUVF3dWNiSE9CV2tvN3U0Yy1oSVRRSGE3RlVSMk13MHhhN05KWWVMLXVaWU9nT0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9zM1pMOVBVX2JTQThUYk1iOW1tT1ZkMkNUQVVLbTZMQm0yZGJyYVRlX25IdkdhbXF2VVBhVUw1Vm1wUnNJeUplaFdWMWxtU2M5MVVacXhxZjZqTG0xSmc?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>46013.295625</v>
+        <v>46014.20089120371</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Iowa State basketball's Milan Momcilovic reveals his shooting mantra - The Des Moines Register</t>
+          <t>Ethan Hallows convicted of Kevin Pokuta's murder in Sheffield - BBC</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 01:58:08 GMT</t>
+          <t>Mon, 22 Dec 2025 12:40:01 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOczhZYXhzSC1zSmV1MHJnMG53b0VaRUJvenVjZ21CLXM4S1ZTZE0zZ3pnTVgyb203RTVkM1FZVmRBMkNSNFlGY1BhSWlKMXRZNkF1Q3Ywc2FEalpfYURQc2d1Y2RjZnJDejVSa3p2bkI3N2dKV3lnajhQVUJraWphVk9oM1ZXcEtmVng2Zi16aV9WLVFrZHRNMGNpQi15S2cwRHducDlLemRLSkczY2xWbXpETE96RmhLaUN0ODFrbHktV3QwN1NGc0JKLU50bjU5ZDR4eUMtZlhDOWpReHd0WWFRNmhtMzluRkFwS3ZWaTRUXzhyeTJrV3pTSE8zMUtDZWpHRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBoeUlwMEVrb2E2eFR3bDNnRkJJOTI1UG96Mno1Z3pUWkZ4SXk5NUhjTUdwYjdLVC1mZHhzSjJDdXpLaURXMEFuZURkS3hEMHoyRmRYSW01WU4wWjJ20gFiQVVfeXFMTURsZWRid1B4Z2lVNjB5NVRwQ0JZZVE3U0tVRzJDbTY3Qm1wUVRrYW5qOGlpN3kxWnJ0dVQtM0I1RW1PM2xuMHBWdlF0TlU2bi1WYm5vUVRHbVhRcXdRT3RWWVE?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>46013.08203703703</v>
+        <v>46013.52778935185</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Milan’s the man - Times Republican</t>
+          <t>‘Dan taught me to live for every moment’: French Bondi shooting victim, 27, honoured at Sydney memorial - The Guardian</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 06:11:15 GMT</t>
+          <t>Mon, 22 Dec 2025 07:42:00 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNTXhMeUVKZ2QtNE1kMkY2QVBUZEZ4SjBYaU1hVUFjSWVScFlaSFNVWTB5RWdSUnJoTXh2bjY2MGF4VjdzWU5JSXZnLVl3enNKenFkd1ZkeEpyVGlDd05IUHFoeDRDbDBiUlBiTU1tSzlXYnVHbU9mU0NUblV4UXZybA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPM0xqeGZySXFETjRGRnNmUXRzVC1yUndabnMzN0hvQmpxNy1kNmZLcVR4LXB0bkUzSFd2SlUzc3dlMkJHZDhlbHpYS28tZ1hTX25zUVFCQWZoVUJxU2NqeWthS09JcU1ObEh3S0VBcXViV2FlbmMyVG81YUhYMlVBbV9DZnhMcFR6SkdZWGMwV2cyT1V6Y1Q1d3ktSE5IMW1VSWVxU2NZQVctMldmaWljVmV0Z1IwR0U?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>46013.2578125</v>
+        <v>46013.32083333333</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pro-Palestine protesters smash Milan train station entrance and hurl rocks at police in Gaza fury - AOL.com</t>
+          <t>"Emily in Paris" Inspired Cocktails - FOX 5 DC</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 06:42:32 GMT</t>
+          <t>Mon, 22 Dec 2025 16:06:00 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNTXEyaVJOeWduRnJybjVkQ1NQMjgtWHZ6MzF0R1Z1MlNvZ2dLMHdoYnJtS1lMamR3SG5XeGRxSURGQ1ZwTTZyZUFrM2pWYl9xc1IwcWdKQTMzTnRKTEdLZjZyRkVTMUxFa0lMbHljWjZGZnpHeTczbU5PUjd6cGs2ejVYN3NUY00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE5LSi1BVmtSM05rc05wWmNIeEZSQ1NPZjI0Q0lKQzZyakxiM25qS0MzeXNYVXQwc0w1UkptbmdHZ0IxVHRIQl9UeVpfc2FXcE1YLTVXbTc4c1k3cW5rY1HSAWNBVV95cUxQcGdTNG1mRUdCc2VLVTFHcDI4ZzJtb0NYaGhmZFFoMjF4Nmx0V2lGQU9yMy1mLVEzVk96YmxMV1diTXp5SnFXU1cxdUo4cGFRWVFEbFRwMFRRck5fQzZ2cjJReGM?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>46013.27953703704</v>
+        <v>46013.67083333333</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Basketball Recap: Milan Comes Up Short - MaxPreps.com</t>
+          <t>Shooting “Parallel Tales” directed by Asghar Farhadi has concluded in Paris - آسیانیوز ایران</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:51:07 GMT</t>
+          <t>Mon, 22 Dec 2025 20:21:08 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNUJzNU9JTE9kdm5rTTVFaW9UcGZUVTVNYU4zY0M4MWZLVThVUXUyZnVxVEhZMzQ4a1FqNGdOM3lDZk40QmRiV0pZUUh5Z0dsMWxaQ0dfdmJwWUIxak9heERiQWJWZHVVRWdBYzA0VE0xMEJ2NFZ6b28xZ0lDRjF4d3BpdC1YZ1FjSTF6NUFDMFljS1ZMVUlndTB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1ib1Y3dTJWelpUakRMbVM2cEoyeExkUS1rblRvTmVzRUI1elQxSkNqOEFIeWVIN2tqb1RIbHhncGFKV2w4THBBNVlTZl9kZV9xeEFGeWN1eGI4blEtQzRxUjhZbDRNNUE4WFZzMzg1YkdKR3NDTk53QWVySnA2QQ?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
         <v>1</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>46013.32716435185</v>
+        <v>46013.84800925926</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Long Beach State proves no match for No. 4 Iowa State - Press Telegram</t>
+          <t>Balanced effort guides Gamecocks past South Carolina State, 95-70 - WYFF News 4</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 04:50:40 GMT</t>
+          <t>Tue, 23 Dec 2025 05:02:00 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPVEZQTUZOYko3QmZFSUdoUVYzMU9nOHo0RVNvQmsxVTBaMFFaZmdCNC16T1Z4T2xfVUZKMGdrbzVnMEhBNHlBbFJIWWE0WWhDQkp1SU50RDk5WWF5M0VDeVhxLUc3YmMyakNuWnBHRGpZNjAtLXRidHFFbUNTbUVYYTh1c254VXJOdC1CbFVwam4xaE1LVllKYzNDYkpnSzDSAZ8BQVVfeXFMT1RGUE1GTmJKN0JmRUlHaFFWMzFPZzh6NEVTb0JrMVUwWjBRWmZnQjQtek9WeE9sX1VGSjBna281ZzBIQTR5QWxSSFlhNFloQ0JKdUlOdEQ5OVlheTNFQ3lYcS1HN2JjMmpDblpwR0RqWTYwLS10YnRxRW1DU21FWGE4dXNueFVyTnQtQmxVcGpuMWhNS1ZZSmMzQ2JKZ0sw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbkpQamxvU1dUSjBGVXg3N0pmR2gxZ2xWQTFSU0FuekNXQl9UanUyeDNNd05RTHl1M0xPMElLR0Rid0JGNjgxc1ZnYTc3Ym5yZ2d5RUZ0TEtTMGZrNXNyNmpHZ2VTbzBCcklWTW5FYXVBa1ZzYjRIRHE0NUJHNmtHMGc1RmZESjJJN2E2MUg1MWhNYVhNNzlMSEpwNHgwVVZlV1E?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>46013.20185185185</v>
+        <v>46014.20972222222</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Troubled Fiorentina thump Udinese to get first Serie A win of season - NST Online</t>
+          <t>Terror on board Air France jet as plane plummets 30,000ft - Daily Mail</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 00:42:18 GMT</t>
+          <t>Mon, 22 Dec 2025 12:08:03 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxObmFvVDZqMEUwS05wQVYxN1g1a1JTQ21BZ3RfdDU1M2xIVU1jZ1hBbnFSd1hYc2JFeV9EN1JRZEhhWXpoSFBkMW9fY1dOb0V3RDhLOEltS1M1allSelgzRkNNcjZxUXpsSXNqZkZ3b0o2cy1KYS1DTm4yeVlnTmU2Z2VBSFRxMEc3NHc1NzgtMTVVTXNkaFNmTDhuOE0tWW5pWE9KZ1BYQm54U1g0OUMyem0xUGxLRWRvYzZJ0gG7AUFVX3lxTE5uYW9UNmowRTBLTnBBVjE3WDVrUlNDbUFndF90NTUzbEhVTWNnWEFucVJ3WFhzYkV5X0Q3UlFkSGFZemhIUGQxb19jV05vRXdEOEs4SW1LUzVqWVJ6WDNGQ01yNnFRemxJc2pmRndvSjZzLUphLUNObjJ5WWdOZTZnZUFIVHEwRzc0dzU3OC0xNVVNc2RoU2ZMOG44TS1ZbmlYT0pnUFhCbnhTWDQ5QzJ6bTFQbEtFZG9jNkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPZ056VFBTcklVYWhpNG5NdnI0OGR0STNRUXRvSkxQcTY3Y3hhdHlOdFQ4UHRFYV92OTV6STc3M0N6WEFaVXYtbFowbW1FbV83YWZheXFtS0huMGZuOG4zTThtU3o1cW5YbW85cUNid1JVbXNqSFVqZUNBWWJadWhwdUZUa2ZqWldkM1FnaF9Mb2dfaEJ1TFJkQnVXaFVIZ29rSGVEU3BnOFBHZTQyNVdST0ZQc1ZUeEN3c2M1NFdLMGlMSXRaYS04UWw5RnRjVU9QM1VHeWZJNF9kTXlWQzRMSDZUU0R0VWJUM2FRYm1FWWxJcWt4a1BSR2xlVmlvdm9GUFUyTWdBTmhUMllJTDhTVVRkamVQX0cyTjBEZ3M1QQ?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>46013.029375</v>
+        <v>46013.50559027777</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Gennings Dunker credits George Barnett's belief in Iowa O-line journey - The Des Moines Register</t>
+          <t>"Sky Zone Takeover" social media trend sparks police response at Tulsa trampoline park - fox23.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:06:40 GMT</t>
+          <t>Tue, 23 Dec 2025 02:58:00 GMT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQLVpXckRpcUlHTGU0QmctN1JHcmluYVplUUFoRHdfOHd2cWJjSjR4RHR1eng4QUxhdDNiaUJreG1pb1pvN1BhejREWTNFRllIWUNwaFNJenZ5d1E1MlNrVXVBNEhQcWt2MXFseVZFT3BJaTVEdGFZbFpPUEtKZW9hRkhMbF96NUJmbWNPR3pCMXQ5a1BTUzcxWXhSNU9pVUJDM1owTUxLeWQwdmN6N2JySlhZTmozXzBRekhxUXpMaG9GSHNVU0NrdGFBNzNVenJkck4xMTRwMFg4cDNkVXBHYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQSF92aTV0cE93Y1lVU0NNSnRoa01GLXo0dHdjOE5lZGJtMkc4LUk1S3R4QjdDUHhObGZwTWxFc1VIalRIa2QzdGR6TmpOTEN5WnUyUUNyZ1cyb1g4ZW5aRFNacnltbkdpeDlBXzRCazJhMXNmcHN0NVRQblFDWGFqaWs5NE9HXy1BUnAzQnJ3M0g1RHZEeXFDczlZem5oZzhCVWhDRkRta0w2UWVPMFY5bmQ5NWRScnRhZFVpRzg3R0VUei1SX2ZYWTlPekpPRU9yZnBwVkZlSk10VERJU2NxdEZIa21IVUtmQ0NMcVZYQVZpbFU?oc=5</t>
         </is>
       </c>
       <c r="F139" t="n">
         <v>1</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>46013.50462962963</v>
+        <v>46014.12361111111</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Iowan Brittni Donaldson is a trailblazer in the NBA and WNBA - The Des Moines Register</t>
+          <t>South Carolina QB LaNorris Sellers stays put, vows stronger return for 2026 season - WACH</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:49:14 GMT</t>
+          <t>Mon, 22 Dec 2025 22:43:41 GMT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNbEJ5d3E4ZUxua3J1cWdpRnZkX3lqLU12S3UyUjFqa3JnZUZ3QXFhVnNwT3ZXVDZlM0wxc1FsODh6RUN1cXpwRkxyeUZQcUljTVViY0F6UVE4U3ktMzdLSUlpTTN0Z3IwbGxsa2tHaUFTMW02ai1SZDdHeTdudTAzV09yb05qam45ZUEzanJJWFJXMXR1Zk0tVTlkTnM4Q1VRU0Q4bGtVTS1BbTNHU3hv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPN0RxdlEtOHVLQjFBUVp3Q1dzVTJ4UlJTY1FlODExYXhHdlg3WEdFVFZaTnZsUFk0M2tQWWI2MFRoNGNscmFnRnMzWTVmR1AydHJMakdENWxlYU9Ubl9LMk4wclktYW9JakV5NXQ5Tk9wVkI0UnZseGJQMHZDY3kzYWpSY1hhODBpWHFfTjlhVnd3OElxaVhFMEVsS2ZPREdSTWZUdGpHN3lDOXo2Q0tvbEJ5ZTFsQ3hSX3ZV?oc=5</t>
         </is>
       </c>
       <c r="F140" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>46013.49252314815</v>
+        <v>46013.94700231482</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Logan Jones: Adversity helped shape Iowa's offensive line in 2025 - The Des Moines Register</t>
+          <t>SAI Governing Body approves infrastructure upgrade at centres across India - Sportstar</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:06:40 GMT</t>
+          <t>Mon, 22 Dec 2025 15:26:06 GMT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNWUZSbDROOG1RRTc1dV9iUnVtZHF6eFR2eVdaekIxTmdkZm1vSDVFNGFCa2Q5NUxYMEtzd0paMktoVDdqZGEyWFpiWW5kSkVUMGFDOWx1YTd6cVRNQjBaelJtMUptRUxyOUdVMjJuR3d2THoySmZiS2xKQ0YybjFyY0puUzhzZ29BaTlhQnpwdTQ5LTN2STd1aHFTM0dNNGpxT2FSb1pWMkpTVWt0ak1hQzAyMkVMYXh1eURzbXB0d3BhZHpuc1JwWDVIUzRBLTJZTkdZdUNtZldsbERSUUZpWDRDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQMXNtMUgzTW1JNm5xc0NLWjVEVVAyRnNFaWsyVWZQck1zM3poODR2c1RuTFY3OEpoTF9GZ2pTQjhvaUZxay1hR3FTb1kwbXI3OFJaQnJ4T3BjaTVpZEZXd29Iek4zWHdOY1RUS29CWUhFYm5ic0NCdUszMVp3TXNOd1VvVG1aV2NMOExGcUdua294TWF4VnkxVktjUXpyUk1ibURFZTV5WEZ5VFJFbFRDbHNIUTZ2M1BrRExoMW9kcWxlRWNxbG5EOHZ4R3A0M2JXWWh2YThR0gHWAUFVX3lxTFAxc20xSDNNbUk2bnFzQ0taNURVUDJGc0VpazJVZlByTXMzemg4NHZzVG5MVjc4SmhMX0ZnalNCOG9pRnFrLWFHcVNvWTBtcjc4UlpCcnhPcGNpNWlkRld3b0h6TjNYd05jVFRLb0JZSEVibmJzQ0J1SzMxWndNc053VW9UbVpXY0w4TEZxR25rb3hNYXhWeTFWS2NRenJSTWJtREVlNXlYRnlUUkVsVENsc0hRNnYzUGtETGgxb2RxbGVFY3FsbkQ4dnhHcDQzYldZaHZhOFE?oc=5</t>
         </is>
       </c>
       <c r="F141" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>46013.50462962963</v>
+        <v>46013.643125</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Premier League return for Christian Pulisic? Transfer update on USMNT star after talk of interest from Man Utd in AC Milan contract rebel - MSN</t>
+          <t>SAI Governing Body Approves New Hockey Turf For Bengaluru; Electronic Targets For Karni Singh Shooting Ranges - Ommcom News</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 14:16:26 GMT</t>
+          <t>Mon, 22 Dec 2025 16:04:25 GMT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQbXlHQWhUYlpEZ29DV3o2bkZPaGNHVUpRVVFvb09wUmpHaTA5dmtQRFR4R09BNE9XZUctNlk4a0hLUzh3TzE0a3NCeDRMUmtDaW42VFA0Qm1mb0l5cVFfUW5BbzlxV1NmdFJ6MDdmcm0zXzVJY25DcTM3Sk5zTEo0NlBrZ2E2SURWcWxtVE5zZi14dWZYNGFBN0JucG81R0tHSHF1ckdmV1JSbTF3NjAyM1pITWlCOFNOMXhhNWtaajFEWGpqZGNSVFBnd3FnZFM0NEc1elRJQTlLWHpYNVRLd1hlaDVBX1JUNjU1MUg4Y2xhZFdJcXdBTDMyckxVNTNDZHQ4WWVXbW9BRHJjVEhPQVRSYVpYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPQkJPUVEtQ2Vyd1lFcEQ5ZldVUkk4ZUN3M0RDR3RDZnhIZFY3d0N3MFRRZU5Ea05mQm1LenluVG9HZE5iVlU4RUhtY2xMUTNkZUdjRHFtY1NHUTVZdm9NT3VOZXpLazB1RThYZEstNXNnVlBvMWdrQUZpYzJ1VUJITHhac2Y5TFkxS1NwRG9rTjhzeURQcXZ3bGhpWW9sSC0zRFFpanZhWEY5S1Q3YWkwd2V2bTZ3TFFIQ3RYckgyX2xmTTZOZE9RS0lmSFlFcm1iM01YZndtTUdKMFk?oc=5</t>
         </is>
       </c>
       <c r="F142" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>46012.59474537037</v>
+        <v>46013.6697337963</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Holiday Plot To Bomb CA | Change Coming To California Pizza Kitchen | Flying Cars For Sale: CA Business News - Patch</t>
+          <t>Judge sentences defendant for 2023 fatal shooting of man family says was gentle-natured - WKBN.com</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 03:03:00 GMT</t>
+          <t>Mon, 22 Dec 2025 10:41:02 GMT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQME9pUWhDNWEyVnR6ODY0akdUbTA3UlJOaWtJUU1tMXFYYlhudWNjOVY4YjVnYTZsOEdKQmk4ay1mS3dxU3RKSHVfak43VmQ2RXRWdDBPVWVFal9ORjBicWJSV2o1VWI5LXVWNF9oM0NJWXpuZUtsZzR6TVdDNXk1REhsMEVrb2tIeG1NZ3pyVXE2dzZJWnJrZTJCVDkxMWlra3hyZWduNVlvRmJIdlFBSG9rZ3p0dkkxU1HSAecBQVVfeXFMTkZJbE92OVVEZ1BxLTRhYlNnckFCQVFJNF9fWUpyRmpTMU44a3p6Z00yUkV5a1A4UU1SNWx1d2VLRGZ6SVNabXUtLW1Gc1JKU3kxUkNJa2ZlYm9hOGhaNkllaXJTN29ZVWNlX1N3LUlzbG94RTNDb29ZQjh0SVNXSXh1SDJVbmo2UmlBangwa0wxOEVBX2wwNm53QWoyZDRjVFdtZ2R1Q1dmN2NPUXF2aGc4NkJraWMza2x5ak1wU3M0LXpRZDJKTUExdmt6SV9JQ0hUQUJGUW1wekw4dGRNUzZ1aEhjN1Rn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOUWVjWXlYdTYwcXRzdmdubm02NzIwdVVqUTFoTHEyTkRvUWhLSi0zdXNRNGhvTVN5WXdjRGNZXzloRXlmQ1VydUhmWFh2TkJFTE9mMjZlbkFDSzUtN0F0ZDZtdjZXRG5hYmVnR1dtZjA5OUR5OGtuQzFxdU93WVgwWmxVbF9mQl92R25TTWpKNkxEX2hfR0VKeUdKRlJ5RVlMWnR4LXhZeTltSEVOY2lyU3hJQktsUzBTd0ZoTW5reFN1cU5EWFR6ZmItOE52bUVSQVVnZGluVkJhSnhjR3fSAd4BQVVfeXFMTlFlY1l5WHU2MHF0c3Znbm5tNjcyMHVValExaExxMk5Eb1FoS0otM3VzUTRob01TeVl3Y0RjWV85aEV5ZkNVcnVIZlhYdk5CRUxPZjI2ZW5BQ0s1LTdBdGQ2bXY2V0RuYWJlZ0dXbWYwOTlEeThrbkMxcXVPd1lYMFpsVWxfZkJfdkduU01qSjZMRF9oX0dFSnlHSkZSeUVZTFp0eC14WXk5bUhFTmNpclN4SUJLbFMwU3dGaE1ua3hTdXFORFhUemZiLThOdm1FUkFVZ2RpblZCYUp4Y0d3?oc=5</t>
         </is>
       </c>
       <c r="F143" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>46013.12708333333</v>
+        <v>46013.44516203704</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Cuban Nationals Arrested in Italy for Theft - CubaHeadlines</t>
+          <t>Filming locations of Emily in Paris season 5 - Prestige Hong Kong</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:04:57 GMT</t>
+          <t>Mon, 22 Dec 2025 09:11:15 GMT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBfaDJjRlhZRUVRTHc3TmJGb0pGTlBlRTB6ZWgyd016SENIWW4xcXhUeDVRcE40dHBMVlVPNnU1YzVTeGJzRHVTNC1LbUxnUjNUcmJ2SlBkUGk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNREdIOUxWVDNxbXFCOG9CTHhlR3R5VElJSUdSUVdVeVgyOE9DWVdRc2xoVkQ2QWxMRnFZMWM0WlZrTU1yOWItSVZXS09mRE1PWDlQUEVzbG1HdmtOMFNZNXNIOHdkNUZpMEZOM0pyNGpiZHFicE14SGFjOGduQ0poc2VtQ0k4X09tMXZRX3JHU1BqdkNNWVhZaEhZemc1LTJERmE0RGZianMxVlhRc0kxbG5nQ3VhdDd1VFFTdDdPT3hZQQ?oc=5</t>
         </is>
       </c>
       <c r="F144" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>46013.29510416667</v>
+        <v>46013.3828125</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Europe Looks Frail When It Needs to Be Strong - Bloomberg.com</t>
+          <t>“Emily in Paris”' William Abadie Reveals the Extreme Sport He's Competing in This Winter: 'I Think I'm Still 20' (Exclusive) - Yahoo News Singapore</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:02:35 GMT</t>
+          <t>Mon, 22 Dec 2025 20:36:30 GMT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWUpEWEU2OVBzQTZoWmpBVlhXdlQyNjRXNWVoX2xwSDJCQnBxWDZqc1VWdTUtNWFzd0pvV2xUOGdpS0lST2Q3NGNOX1RXVi05blFhaUZLeVNBTERwaE14M0YtS21BUDcybDJ2S1o4OXBSdUNnNEVOUEtXQTVLV2s0cWZKODFmZmt2bzU0QlZfLVdHX1FXWnVUV25jZ2hHdUw1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNU1dieW5ENFcyd1Q0YzBjZGF4dXNQdVZhbExvNm9WbDBsWThGUmM5bTBKaXo0SkwtMmdHWVIyci1NYVF3bnRmSzRIek9abkdjaTRBbDZJaGlXMzl3emk0cjNKLTFjZDg5UUNCc0I5MjhhWmc1ZEI3MzVBU2NDSlFxUQ?oc=5</t>
         </is>
       </c>
       <c r="F145" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>46013.46012731481</v>
+        <v>46013.85868055555</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Over €16,000 in fines issued for fly tipping in Brussels - The Brussels Times</t>
+          <t>Arts Vanity: Gen Z TV Shows to Add to Your Golden Age Favs - The Harvard Crimson</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:16:09 GMT</t>
+          <t>Tue, 23 Dec 2025 03:35:02 GMT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRTlxTWxSTno4ODUwUEctOG5Za0ZvVUVRT3NuOW53b2VtTzVhb0J4ZnpDUnl2Tl9IOWdLVmpIOVB1VUI5ZUt5TVNSWl81NjZuMnFDcV9CX1dGbXZxNWdORGcya2dDczE3SnZ2OXVURGMteTZlNkh5a3N0M0JQS2diU2NDMC1WbG1RQml2ODBnMUljZHdpWEduNWh4cU5CemZXYzdOZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQVGlGNS02MGY2ZXlGYVZDbnljTExha1EzYjNYWmhYTXBwWnNTUlNCbDFjdjJWTkxuTTRKRXFfY3EzeTR4ckNSOHV5V2l5TTBsak9pcklqb3dwS3hrQTh0Q09mWDk3aUIzX2Jkc3ozdm1mMjIzSnpfQmlPQVNjMDlCdTBDU0ZucXN4NU1jZkV3?oc=5</t>
         </is>
       </c>
       <c r="F146" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>46013.46954861111</v>
+        <v>46014.1493287037</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Exclusive: Former MEP Kaili doubles down on 'Belgiangate' - Euronews.com</t>
+          <t>The Boys: Season 5, the final chapter, finally unveils itself - Sortir à Paris</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:00:44 GMT</t>
+          <t>Mon, 22 Dec 2025 20:58:07 GMT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQclAyU3JmazBZVWhlRmo4bmctaWdoRTVvWkYtMzFGNnJaakE4OV9jWU05QTBWOEwzZFV4SjVoUTFVZlNSNUFfNzhwbXh2bjl4YVItdWtjc290dFFySXlpNkhYQ3Iyemp0WVhpWEU0RVBlWUt2MzhSZ0UxMjNITmdPdm9DcG5WSE84dUo2ZngzRmViUnBNOHd4c2dWSjdfUncxX2p6ZGZ6MS00NkUzX3pTZ2xKb05xbVpxM3BiN2JhWDRxb2tMYk5uTE9pUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVkl0MHl6cWtZX0pLa3ZnclhNcExJMUh2SjlqZHpPQjZMelRSSEhKNkJRZkJmT0Y4eURobk1QOXZ0V0dpRWhmbFNINkVCWGFGSXQ5TU4ydlVKT2h6Z2w4QlhwTzZzZU5UYnRRZjk2SkZnOVhaS2ZjUVl1UWhCekFWWHRpMVV1RUZFQjIxdGFpQllqcVlIT2xFSVpCZUNOM3p5U0pLVQ?oc=5</t>
         </is>
       </c>
       <c r="F147" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>46013.33384259259</v>
+        <v>46013.87369212963</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Eddie Punch: Why the Brussels Mercosur protest is more than just ‘business as usual’ - The Irish Independent</t>
+          <t>Gamecock Women's Basketball secures French recruit, to join team after holiday break - WCIV</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:24:59 GMT</t>
+          <t>Tue, 23 Dec 2025 03:12:17 GMT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQcDFhM0xuTmhMRnBuTDZtREIyOGxseS00NXhFVzgxVVJsR3FNVENkWXRORjR1Um9vWERhQ1dmV05kQmZFLW9JcUVuSTQtY0dsMWpVM1JUUEdLTE5fSWhZUTFncjlZbFJIQ2tkaHN5NlZvaDNiMFZMdUxLOXJWd2VLSFRYUmdUMnc1MFlQU0NHckNfTG9QRklsZENzRXhFUEZNbG5iaERfNEJYUlhDaGpOaERqVmFTd2Z4b1pBTzR6SEZtWElHdF9Va1ZWUVMzd2dmRy03dUFmZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQVDV5Q1d2ZXUzLTZxOHBFYVp0eW9rUjAtMXhuNGVnVFlYRjlOZ1Y5RXBlbEMzNVg0cGkwWjBwblhkeFpGVWpzX2V2bUJDclNjYXQ2c3pCZjZFTnVmLTA1ODIybUNEaExMVC1NUm9nRHlvREE2bGRwYkRmZGZ2M0tqNDNzYVBEQWVxV0pOWDhMMVhaSVBpSy1qMjF1T2l0WHFYZ1BzSW4xdDFGQVBPSUZQN0dlRWNZZ2hEV3k0VzJvTTF6S1BzTTQxM2JIM3BOZXYwQVJWb1FBdGxWSG5fUFY0Z3RlN294NXoteGpTNGpYemxwSTZ3UnpDeUVDM1U0YlNuSFgySE1CZUVRZU9kN09uVkJfVmgydw?oc=5</t>
         </is>
       </c>
       <c r="F148" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>46013.3090162037</v>
+        <v>46014.13353009259</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Swiss court to hear Indonesian islanders’ climate case against cement giant Holcim - RFI</t>
+          <t>Bondi Beach shooting suspect conducted firearms training with his father, Australian police say - ABC7 New York</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:18:27 GMT</t>
+          <t>Mon, 22 Dec 2025 14:30:48 GMT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQlJXRHRjelhSUTVEeDF0MnBodVpoLVJGa1ZQbjZMUm9iTl9jell1TmtpQ1RNYUxSQ3VuTC11TFZ0VnNic2E2MHFYMUFQUVIyN0JWeWdpazYwdzAyU3JocmhjNEUwd0lwbGZRMVR4M2FMOVNEYUdzakpUeENGM2xoY1ZzaFNBRnJpc1FISWxpWEg0dmNiY1JyWUpaTEtJZEFJLVl6cGZBMV9IUGZDeERGeVp3TUc5OENYWnVfNFhlZzBNbmw1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPSXh3UlZlY1h6c2NydGhmb19EYmtONFFMZUlzM042NFZwaHZMN29FaHVzdHZZQWpYdjlRakx1aGJLTTc4U1FpVEsyMWZHaDVlMVJFOHFVcktwNkg1S2FCNk1UeUNhSHo4WjBTZk9GNFFDSml4MUxzR1JuZ3lWZ2NqeEZ1aVlJUmtaeWpSOHRrSFV1YlB5T21ERDdxYU9COVc5bGVKSTF5Z3Y4ZF9CeG8wRkFxQlMzQmt1QmRJ0gHAAUFVX3lxTFB2R3NPTlVQVmRTcnNIbFk3RFYzaGxnMHRMbU9fTnFpUm8xSk1VRUxXSF9HbDRXdndVT3NZTHBTWURuNXIwMWJ6ZzRmM3lLQ0dSY1VlV1JWNjBQSkphSWpMOTJHQlp2SURHSXBCZThkbW03cEljUktUZXBmS2tyZGtUUTMxNzJZZXBqUjV0dVdkbkpXbmNEX19nTWstU0xJTFFFdXMyNE5xSlJqZ0I3Y2JoNHFrcjdUMFdTcTJlaEdseQ?oc=5</t>
         </is>
       </c>
       <c r="F149" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>46013.47114583333</v>
+        <v>46013.60472222222</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>E-scooters to be banned in Brussels on New Year's Eve - The Brussels Times</t>
+          <t>Cyberattack disrupts France's postal service and banking during Christmas rush - ClickOnDetroit | WDIV Local 4</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:48:47 GMT</t>
+          <t>Mon, 22 Dec 2025 13:18:24 GMT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOUmRBdzdGOG9CY3lfdzFySjdxZFprb3BDSERZY0c3c3MwVUh3S2lDWVNoc3lhRDc4WnJxbzBGZnQ2TUk0WnY5SGoxS05fck5ac3UyMkhPZ0ppQU5LODNPb0x3a3RHN1pSalJGT1dRMWxXbkpJV29HMEZQVjNYeGlNS2JCVUczZkpPNTU1ZnplaXRVVEZJWTI5M3JWVTRQTVR5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNYlRkSHBCMzNDRWRKV0NCa0RXdHdZSXlhMTNCcUxaeGxGVnRKWWhnMVFJWkRZS0pJbktxMGlZZVRqZFBNSDJ2WFlOM1ZLZlBBbGJFc25XNGFuUEhkbW5oSExiQldXVlQ2dlBWOUN3d0lxWDkwNnR2bEpnNjd3X1RMNC1YX2FHZHQxZ1JTUUdZU3o4dkJTbEY1eGgtRk1PLXJXRkJFTmd2Qk9YN3otemsyNERhNFN2TTBvOHl4U0VvSWRNWVk?oc=5</t>
         </is>
       </c>
       <c r="F150" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>46013.45054398148</v>
+        <v>46013.55444444445</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Labour will unleash a blizzard of lies to drag us back under the heel of Brussels. It's time for Brexiteers to wake up, says STEPHEN GLOVER - Daily Mail</t>
+          <t>American WWII bomb found buried in Hong Kong, thousands evacuated - AOL.com</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 00:03:00 GMT</t>
+          <t>Mon, 22 Dec 2025 08:36:42 GMT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxORUZLNDJHM1YzVDJZNXprSjBNdDFicWxrY0tMVFpZTGwyVDktQkRDV1kzeGdFS0VPbjhDODdIVERfUTN3Z0o2bnZqX2d6NGh6S2JHTnlLNWxFTWs2YkJEVjUyWlVNaG1BRG82XzMyZnZFWjdLWmxOeVRWUEM1aXlZelFKLXBkMExzbTFlRFo1N0RfNWlfbUlqYXFrZlBjNjdHM0JZYzBsZUluck1vOWVzUDBPdjFudThvOEVrRUd1NjhyZ3h5OHVNeU5VdDFOUjEzTlJ6dW5VWnBGaDZVLVHSAeMBQVVfeXFMUFRUbnM5YVlUOVNVSTg4empNdlhWdE4yREhhTDREcngydEQwMmhWcnBDWXotYUhJcUFXUTU5VTlOb0RSSEItZWxPY0h5b2JScFVVYS1GNXdueW1fbnExWjd4dEotOVZ4YUZ3UGRVam5PRHFudGtTOWEzajlwRWdmamd4UnAwZHhvcnlMMXBuUWpSOUNmRXR6ZEhFVHphV0p1UWtxVHVBVUhpam5RQ09NNmUtSWxmVURxcjFUNm9YbjV1LTBqTkF0Mm1TMTh5dHNMZTNpeG0ybXpoOGdZR3pvbzcxQWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQdmtJOXppSzlCZnpOZDE3UFgxaGVwQm5KR2tDOWFLN2xlcXBKcEFhdXRiQUIxXzRGa0R6LVJPUm5TRTV3blNrNFpiYUIyMzdnRElpN242cmpmQVVvd3VSNEZVWW1wb2luNzNXZzEyb2xiWF8ycFhzX3dKU2t4LWtzaw?oc=5</t>
         </is>
       </c>
       <c r="F151" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>46013.00208333333</v>
+        <v>46013.35881944445</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Thousands of Farmers Protest Against EU Policy in Brussels - الإذاعة الجزائرية |</t>
+          <t>CCU to host SC Republican gubernatorial debate - WCIV</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 19:24:09 GMT</t>
+          <t>Mon, 22 Dec 2025 22:19:47 GMT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9ncGJIcDR1WldVejVFQVJnWFNCb0g3d3VlSDZUSjBqbkpRRzNwZ0pXc09odFdIR0JpdnB4ZlAxR1BsNHNEbE1ELXY5bmozX2Rsd0dOdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxONW9Sb3dBRVFxS0N3NGR5Smp4WGNaVEgwZGE3WlowMkxpcnpqMTNSeGxGcm9DRmY1Mi1ELWpTQWZad2xnUkdsSGRRU3RMQVJnSjRpWS1wMVFTbEVDdzFnckNLZ2FvaE9uc280ck1EeDdmMW1pQTV6Y0pHWFN2ZUpkN3RKcWl6anQ3cEdISDNVUzRJVVZXeDR3aXNIOEtUTmpYby0tQUZTTm1WcmFCTE10MkNHckxBOGxnYk5zQXNkNXotMUg0ZnA3Y3BkNll6WDRBbjI1RWVjTFZnQV83MXh6QlhKck1GazZk?oc=5</t>
         </is>
       </c>
       <c r="F152" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>46012.8084375</v>
+        <v>46013.93040509259</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>First lady Melania Trump's documentary movie trailer is out - ԱՐՑԱԽ ԼՐԱՏՎԱԿԱՆ</t>
+          <t>Suspect charged in shooting death on June 13 | Here's what we know - WXII</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:22:33 GMT</t>
+          <t>Mon, 22 Dec 2025 22:17:00 GMT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTFBra1cxLTZacXdIY0tocjFmQ0ZYclJHZUt3dFpLZ0k1V0R2SUpRMmhUMzl4eTYyR0VUUXlqTUM5UDNlbFA5QzhqczBGWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9zb29lM3BjeDFRMkU0d0FYNHVqTmc1cVVsOWJsZ3ZablVhYVdrcHh4YmoxZjc0VlB3eEJRT3VUT2t3OVRIWUFLczVOUjBkUVdYZFJIVEtzb2NTS1M4MFY3VXY0a1B2aWtVc25aYURFTmNvWlo4NkE?oc=5</t>
         </is>
       </c>
       <c r="F153" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>46013.39065972222</v>
+        <v>46013.92847222222</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>One person critically injured in Brussels apartment fire - The Brussels Times</t>
+          <t>Everything Lamont Paris said after South Carolina's win over SC State - On3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:16:09 GMT</t>
+          <t>Tue, 23 Dec 2025 05:04:39 GMT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNY3l6RExDRHZ1MV9Wa21YbVpWRzN3aW80SFNmMFVCd0tYWmpVQ2sxODZxLUZUZnRNelNjY0FhVHUxMkpRWkNLaUh5WHpuWEdmdGNhSWxReGEtSUdubmpMUl80UVVhTzhmWDluRXJhZEVBazFaNExnVGJGZnRqRzQ3M0wzdzZUU1ZGVF91dWEzZV9WNWxsc0c2UDQ4V1Jjc1k4N2s1eExn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQa3NfVzdJQXZieGlmV0ZwWmVjcUNRVV9wVk9kUmlCNFB6ZVh1NXpENFY2dmtINVlnRzRXOUVlNjhGYmwyWGdlbWttbEFFcGVZdnNRS2RseHEzY3FQSkVXamlpN0dTTExSVnhJc3NZR3FXVW1FcWpxLXhxZFFYVC1Ca1RJamZONzZLamEzTHA2VlQ3SEdZUDg3MXY3UkVfVEsxb0RDcnpXV0U2VmljX1Q2Q2xPUVo4eVhKcjlPVV9STDZlc2s?oc=5</t>
         </is>
       </c>
       <c r="F154" t="n">
         <v>1</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>46013.46954861111</v>
+        <v>46014.2115625</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>‘I hope France speaks out’ son of jailed Hong Kong media icon tells RFI - RFI</t>
+          <t>South Carolina MBB heads into holidays with home win over SC State. What we learned - The State</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 19:29:20 GMT</t>
+          <t>Mon, 22 Dec 2025 23:02:00 GMT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPLUg0T1NGX0ZZdVBvN3JJMGVhb0N1STBVcHNVQ1l0TVowUW55LWx2bGcxMThlLXUwZE1UTFdOdExWa2tfdDJxbUwxUzlJSnFGbXJTTEJMOTJHTlRIOHRNZEI3UHFpdVBYUWg3ajVVVTJ2V1VXcFFEamFhb2J5cnZlNnlnNjJkbWhFX05WR1FydHRycXhrSjNTZjhmVTBsQjRZN1A1ZDB2NWhSeVdUQmFWcXNVZ2pTalZqd2dCQm1FZzY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQamttWGVCSmlFVnBvQUNhRFdrdVh2REZHaWNuQjlFc3JOcnpsVVdrR1NESllzOGdwVkV6dF95d2Vjem9vU3M0aVoyNDZkUkRTRFlRajBVLUNnV2hZRXBNWlBESUVMMjVSZDRyS0hURHUzZmtSLTdCRG41Zm1wQnYwQUpELTZhZk5KRWNjQTg0dmhtWGhXVHdxT0dkMUdxUW1HUldHdWlCUXYyRWZhQzZZ0gGvAUFVX3lxTE5xMmNTYUE3MlZpbWExdzZ3Vm82Z0VlZndrOExGNDdVa3NNNXQyajBJeHR5ZjktZXU1b3otYVZlS2g4SHJlaWM3S0dNNllyZWJvYzBRelZJVlBjSHpWckJKbDVZWlB6Vm9JMEc2Y0RiMlVuOVllWThMTk5qazBBQ1ZLNXRIdG9JbXRrQWg5Z2l3Ry1CQ1FLdWtpTExNWVJCQXBLMmpnb1BXc0ZndEFMMTA?oc=5</t>
         </is>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>46012.81203703704</v>
+        <v>46013.95972222222</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Inmate attacks Haren prison guards - The Brussels Times</t>
+          <t>Algeria to criminalize French colonial rule - irishsun.com</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 16:57:44 GMT</t>
+          <t>Mon, 22 Dec 2025 08:20:00 GMT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNcnRqQk5EMVNiM0lOdWhIQ2dQWTE0RUhvMGtTQ1JYM3VTTDNvV3NROHRiOFE4ZVZrbHZGYmJLcEhqaGtfUGN0LUJPb1p6c2R4TUdlenpnMW1Pc2JySHh3V044LXlmNDNIaFVDWVBtR3hxRlhvWFFrQzJkaXV1MzljS3RLVXhBZ3RK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNWm03eWQxWGhQZUdjOFRYV0U5d1pNaHkyWlljZVBrT2dwRno2aTFVMDNRRFU5UFRROER3M0dSZWxoMlhFZ3pUVzMtQWJWanlxdXF4N3JHeHhYYkhLZWRDbVFFZWdMVHVDTEtNckx3Uk5EajZjN0JQNnFpdVZ1Ylg3LWp5R25VeFR3OGFz?oc=5</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>46012.70675925926</v>
+        <v>46013.34722222222</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Swedish 12-year-old boy is arrested on charges of contract murder - ԱՐՑԱԽ ԼՐԱՏՎԱԿԱՆ</t>
+          <t>'60 Minutes' in Turmoil: Sharyn Alfonsi Blasts Bari Weiss Over Axed Segment - TV Insider</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 20:48:45 GMT</t>
+          <t>Mon, 22 Dec 2025 13:06:24 GMT</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTFBucFg5QlhQdEVSeVgxa3Q1RGZDeGVtb3A0Rk9aS1JMVlZ2Tm5HVVhuSmNJOGtxU21TUkpsMWhEU2lJVlQzSEVHQ1Mycw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOWGhvVG5oSzZoNWZ4VjhTNUJjVWJ2NE81WUhabWxfaWRGaS1UTS1JekZjQ29Rb0owOXVid09DZG40S2dpazNNdmNzYU5JWDhkYnQxT0VCU0pZRy1oSzZLaU01aVRackZSdkFOMUo0blVZeGJ1cWd1NkZCSnUyRm0wWFJPalhjUFV2V0xFTmd1Z3I?oc=5</t>
         </is>
       </c>
       <c r="F157" t="n">
         <v>1</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>46012.8671875</v>
+        <v>46013.54611111111</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>EU to probe Czech aid for two nuclear units - France 24</t>
+          <t>Lin Zhipeng (aka No.223) on nudity, Paris and forbidden love - Dazed</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:33:13 GMT</t>
+          <t>Mon, 22 Dec 2025 09:02:00 GMT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdk01dEJDNlg2RzNoQUw4cFo4dXZaZ0VleU1OY1VadTlhNVpUNENzWEhMbVpDZ3RpbFB5dVpvbEZtM2pwLXRfczBENVRZOFc5UjZtR19BTnV3NG5Lak9lMzNQVzFTRmRIMFRfMlFCcUR4TkpOWXRCRFFMOHAyX0N0LUhucUZKRUdITXhJeU1rODZkbTE5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOZUFIR1hYbmg0b0tPUzhOaUlmMnNnY24wRDZybnBiRnNxQXZKTTV1MTYxX2lYcXA4Q19kY2VrQ1RNU3ZGakxhZkNJM21zcG5mYlkxSjlRcGVoUkJXcjJBMkJuREpkQ09VZkNoZ2I2RnhiOTdiUktqT0ZZak5JNjN3ZHVScFJENmU0UEQycUh4TEVkT1hkOGpGbnp6QmJobDJuM1FtaTNwcEx5VnRZZ0lZck9EbXA4U3dFbjFfWFJjMWJIRGtEaW1ucw?oc=5</t>
         </is>
       </c>
       <c r="F158" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>46013.52306712963</v>
+        <v>46013.37638888889</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>EU Warns Georgia Risks Losing Visa-Free Travel Access - Caspian Post</t>
+          <t>Can Tirupati Forge Limited (TIRUPATIFL) Maintain Its Valuation - Equity Performance Review &amp; Double Digit Returns - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:00:00 GMT</t>
+          <t>Mon, 22 Dec 2025 17:30:28 GMT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOVkpVd0NXOWdfU19sWl9tTjUxNzl6alFaQmM0NUJxa05fQjF5NlV2eThMcDlCVHlINU0wLWl1WW1OWmFibV9JbEpkcy1wV0Y5WXBNQWNTUHJfbl9idEJfZW5IQmJWajJFOU9qX2ZKa3I1Y1NWTF8wTXMzN080RXdsYzBrTFpDZXl2TXdNbkl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPektWNzExdzdNczZOMF9qSk51bVNQNkdBLWt2VHhueTRlcVVvRXl4SEtWMmhqUm1CRFhWMkRWNGQxSWQwOXh0ZXl6SFpOU3RWWnIySm51aDQxLWRwcjZpRGlIY05IU2Q1MkZ0QWY0OUo0Q3FtUEdRZUpHWW1mYlFMSHotMHBfZlRmUVBELTQ4X09pSGY1RmZiaXU0c3VGSnZwV2ZwQW9MT0Q?oc=5</t>
         </is>
       </c>
       <c r="F159" t="n">
         <v>1</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>46013.29166666666</v>
+        <v>46013.72949074074</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Kosovo To Hold Snap Elections As Relations With Brussels Reach New Low - Eurasia Review</t>
+          <t>Napoli Wins the Italian Super Cup Against Bologna - ysscores.com</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 01:28:13 GMT</t>
+          <t>Mon, 22 Dec 2025 21:47:40 GMT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQbHVxNzBuY0xveHpkWEJuSVIwSDFXRmlmc0pKczh5akllR1Q5VlhBRTJuNTdGazNTQXRIWE5KSTBsVE5vQ2xhSWFmTGJnWVlQT2I5VWE5TmpLYVVDRTEtQlNEdWV3dkNtRzNNQ1NJUThjN0ZmaUllOVJ3TEtXNnZsaDNIV084UTN2VzhfcHAxMWZyRGdyVXpxcWRtRUVfQzVxUHd1bmp1NHhSOXNOdDU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPcjJ2YmZDallGV2hiSlZnZGFPcmxuQnRNSjlQd3dETXg0Qm9GLVpHTWFGMmlZeDd5ZGVZRzhtaXNURnBNQ01NbDNKXzM4aTctTExTLVpOUVVvcWhXaGROV2Vra0RBNmxSNER6c3pINjZSb0FsajZuSHR5eERWQlB1ekdncjYxX1BiUXJHY3lRamhMUHRHdnc?oc=5</t>
         </is>
       </c>
       <c r="F160" t="n">
         <v>1</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>46013.06126157408</v>
+        <v>46013.90810185186</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>The Bondi Beach massacre proved Islamic terror never went away in Australia. Here's how young men are being recruited in YOUR suburb - Daily Mail</t>
+          <t>'I am not weak' says Slot, but Salah could return - AOL.com</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:58:15 GMT</t>
+          <t>Mon, 22 Dec 2025 22:22:40 GMT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMGJfaktMc1paaWZnTXlpaFdLWnB4SWJRbEg5REcwci1hd0Zvb3U0SVBNTG9zRkgtRmVXQU10d0F0MTBKeHNfRmxNTEhfZktGVF9oYlNKck9zbUtzQjdkakE5Wi02MXRlTzZKNzh3RmJJZjh1OTJ5c2dObGoyd3FyWUxubnVNemJQUFNQeFhLZFFKQmhfY3BRemE2NmJYeTV2elhGVnRidFNURy1NRmNpbXIxZnBsUEEtdHp0NWF1S0zSAcYBQVVfeXFMTVluUWtqV2QxMHFCZkUzaWN2T281enpGN1h1U3FKZjNQdG56N1N4YUVZZlM4OTBkS3VYY2gxWDQyWDYzRHdLOENwc2hKWHNmN0dJYU52RTRBY0lFMlplNTZ4Tm43SUhQUDBNT09MRFlKUEU5TGtZd1k3U1VrRWY2ZzlyMEtpQWtJR0diNkY1LVBnU0d6VUhWbXpNc2x5LUlDM3hEZjdFRjByLVBfN3VaTGxUVXN0QWllVmoxNnFabldUYmZyd1RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFAxZC1UVnFsQ2tOSVdVNlRmaW5XTHU1X3RXeTh2VTdUT01WWGxLVk9QeW1JTnluQTV3cjY1Q0JXeFVHNnBGcUlFeTVMa3Y0cWpHY3ZpeFRjZHJLWmduVTdoNjJfX19fU3BJUkdmaE5qbGJDYjQ?oc=5</t>
         </is>
       </c>
       <c r="F161" t="n">
         <v>1</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>46013.37378472222</v>
+        <v>46013.93240740741</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>US says talks with Russia, Ukraine in Miami ‘constructive, productive’ - Al Jazeera</t>
+          <t>Milan Momcilovic's not eating jellybeans for each 3-pointer, he's saying the word and watching 'em fall - 247Sports</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:03:45 GMT</t>
+          <t>Mon, 22 Dec 2025 10:31:22 GMT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOeGlNbFFnY3VUNkpxczRSM25MU055X1ZleWlwNktPT1lLWnljVG45N0hoMk9UN3BjOW5kZVl0Z05wNFozc2dxWlVLdEk2Z3VaZ3E2aTlVUG1lQjZRS1d6Sk91NFRCbDRJekhNTDBadndaR2dTQVhkdDRXcWt5Wl9TSFNCV1BvTEdZa2FNdGtlT3p4d1lCQlZHVWJPZFBMbmdvZlo4YXVB0gGrAUFVX3lxTFBJWXFvX3N6ZEt1Ny1vMTVHMERPLXpqLU5YdDhIeE5zaG1IMF8xZTlZZVFwTHJoNXBiREh0R0ZNN2NUZmF1WWhWYUZyNWpHYzlZbU5XTHZ5VlMyajV2ZzZzaHZBLVBJWWFaa3FVN2sxVUNVRHNxQ2RUNDNMOV8yRUlxZzJ2UWhaNEllWmNOMVZNOHVMRzF4R2JFcElQQUNOcXZHbThyTDdjS1FmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPOThYU3RGWE5uajdTVVRxVGcwNTROVHpMc0pQM3NwMnFVdTJCamNHX2FIMUpjZXBXQjZ0TTZRVXFHZ29vUVBOYVl1dlAzRzgzX0cxbFRVSHJteFFvOHlLMXotemxteXcyS2lqVE16QUNQbGc5eXBLb2FWU2E3b2Qwa2xrZmhJRVJrM0tYazBKS2NVUFN6YjJoalpLOTdJMFo0eWUtaGNCcXNiX21SMnZpQ2wxbXNRNHMtQ0Z6ODlsVkQ0eVA5aHBXcVJn?oc=5</t>
         </is>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>46013.2109375</v>
+        <v>46013.43844907408</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>The EU warns of measures against Turkey - Balkanweb.com</t>
+          <t>Iowa State basketball takeaways, Momcilovic scoring, Buchanan progress - The Des Moines Register</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 00:53:29 GMT</t>
+          <t>Mon, 22 Dec 2025 12:04:00 GMT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE03OVp4UHlRZkNTaDQzc3laZE1maTByR1BqR2dYMmZyaDdKQ2RQazkxeE5HZjlPVFJfNEVqa2lJVHd4RFNfV2N1NmZLNTVlLVN0aEJQcnFHZnVKVkE5LThkam1WQUtJd1FKQW9VOTZvb2ZKQXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOZkw1ZkVsUHl5cFdQX2JURW9GZWtSeEp3QVV6c2JZX3BFSk5FSkpHT2ZmYVBzQ05GOGhxVFRfQlphWGhsUjhQSVlkbTN6THFFR21tcWk5aktpZVRtdlBaSVNnbnhobm5YRldVOVF4MHVfNG1VV0FzejZHQmJ0V2dGSDhzVVpQd1ZHQXRkbjlweWhNa29kS1VvVXFrU004R1RwY1FMaTltQi1XOE1kSk1JUWNndDZ3bnQ5TEJjaGw4alR3U3RKU0VCV3FFRy1lS1JRWFNaMDFUbkV6RFlaOWxNZzEzU3VHdW9lUEdHSlhIZ21OR1F4empRWHZqcElSa3FmSXdIdFRROE1EcFlNU3BzWnlTZw?oc=5</t>
         </is>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>46013.03714120371</v>
+        <v>46013.50277777778</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Trump set to expand immigration crackdown in 2026 amid outcry - ԱՐՑԱԽ ԼՐԱՏՎԱԿԱՆ</t>
+          <t>Italy’s 4 flag bearers for Milan Cortina Winter Olympics honored in handover ceremony - KFOR.com</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 20:18:23 GMT</t>
+          <t>Mon, 22 Dec 2025 16:58:41 GMT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE1GWGIzVEl4SGwwaG9wSVN4VnBNZER4clZjbS02X0tNdFR4TE9ZamIwZHY4aWxjOUlIdVREaG8xNVUxbnpvQ0M0MzVSOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPUmJCNTNSRDItcHdiS1h3anhWTEpWS3llNURVTUs4VV9uNUJiNnlMUUZvNDVNMHlVbXN3RWJMLWxycXR2OEl0cGdaUm5sMmNTWUdJd3BNZXBWWDR1X2JsSlZVcEs3czZQbmN1ckhUNklIbW5OelRZRHFpZzJ5RmhxR1BjU2dBWEZKS3prbFZwa1VvaDRTQmF2S0pWMFJIOC1LVm14RFU3aE12bmlvM29EdGxiaC1FZWFabV81TFN2aEhsQdIBxwFBVV95cUxOLUVDaUFjOGd3Uk5wQW4xVVBVdnJDbGFhZ24zMjN4bVZoTWRvQXppUXpGNFNPcnJ5aHNodmFYTU9fcWNGUFhWbWtFdkpfaE9xWDRuMkpaTkxjR0V0WVBTZzdlczM4Ukw0dnBYVjc2aW52UEdHejc2VWVSUl80SVg4aUhVY0FQaksxOFhzLWYxbHgwMHdrMU53cWIzTzhVTjFicDY2dndXS3VMRmR3elVuaUZZRHk3eDJFNGZYcEJBYkxjVXVFWWtn?oc=5</t>
         </is>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>46012.84609953704</v>
+        <v>46013.70741898148</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Competition in Italy fines Apple almost 100 million for abuse of dominant position - lnginnorthernbc.ca</t>
+          <t>Basketball Recap: Milan Comes Up Short - MaxPreps.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:08:10 GMT</t>
+          <t>Mon, 22 Dec 2025 07:51:07 GMT</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZUpaVTlsYWg0a3JYdFZiN092bmlaWUhQeDFEd01RUjdja3BKeTExNGlPeElWTWlIQnItTzlJVG1iSG5MUGJjaXNhenVMb19zcm91bkFkUmJtOGczZ0dDZGxoN2k3c2YtM0RZMlVUNXpqUG41R1Y5V2VKMTh3eEw5UTVhTnJMUXZFSF9yMWZaLXNreF9MdC1xU1V0eUtCa1cwbU9xd3RqN2xSYTNicXM4bmIweUVVWjVyNHJjZ2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNUJzNU9JTE9kdm5rTTVFaW9UcGZUVTVNYU4zY0M4MWZLVThVUXUyZnVxVEhZMzQ4a1FqNGdOM3lDZk40QmRiV0pZUUh5Z0dsMWxaQ0dfdmJwWUIxak9heERiQWJWZHVVRWdBYzA0VE0xMEJ2NFZ6b28xZ0lDRjF4d3BpdC1YZ1FjSTF6NUFDMFljS1ZMVUlndTB3?oc=5</t>
         </is>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>46013.46400462963</v>
+        <v>46013.32716435185</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>The Japanese H3 rocket failed to launch a satellite into Earth orbit - lnginnorthernbc.ca</t>
+          <t>Gennings Dunker credits George Barnett's belief in Iowa O-line journey - The Des Moines Register</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:03:12 GMT</t>
+          <t>Mon, 22 Dec 2025 12:06:40 GMT</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPVXVsX2E0NTZab0dwd0R2cXpGV1Jxam1nMjctaDM5d2Ntd2JwcVQzYlJmNlFkd2dMQVI0YVdPdE1aaEJLc3ZZdXF1a3NWbkpiTjhoRzNRRzNkekR3bmUwUnJQSkZ2RDk3aEFLaUV2RFh4cWV6SDk3dTM2NDVJd09xWV9ReFNsY1RhSlVDalpWSHowcVY4Uzh1WjllZGVjN2xRaHhRVFQ2emRxZGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQLVpXckRpcUlHTGU0QmctN1JHcmluYVplUUFoRHdfOHd2cWJjSjR4RHR1eng4QUxhdDNiaUJreG1pb1pvN1BhejREWTNFRllIWUNwaFNJenZ5d1E1MlNrVXVBNEhQcWt2MXFseVZFT3BJaTVEdGFZbFpPUEtKZW9hRkhMbF96NUJmbWNPR3pCMXQ5a1BTUzcxWXhSNU9pVUJDM1owTUxLeWQwdmN6N2JySlhZTmozXzBRekhxUXpMaG9GSHNVU0NrdGFBNzNVenJkck4xMTRwMFg4cDNkVXBHYg?oc=5</t>
         </is>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>46013.41888888889</v>
+        <v>46013.50462962963</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Local Town Searches Wertheim German Terms</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Germany mourns knife attack victims as Afghan suspect investigated - MSN</t>
+          <t>Jackie Chan carries the Milan Cortina Olympic torch through the ruins of Pompeii - KFOR.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 05:48:47 GMT</t>
+          <t>Mon, 22 Dec 2025 17:28:07 GMT</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwJBVV95cUxORWx0SGRoeTdyY1pLbnRSWm9jR0kzanRtbWZhcjZhZlVrdGtfaEtoUEtlYTdnQ2RlQ1FhdWFOWjhpX1A3UTMzZEFVaGdmM1NLN3M5WFRnTDdtc3c4MmJBSmhaeVNwMlZVWmUxTXhNdXUtWmxIYnBmc1N1dTNZcDFVdi1tMzBPbGtqZUVFYldzanFqamhOV3lPQXZTSklLVTRvS1RuXzlvaGRfa3BCRERodnVSMHZuZGMtdWd5Y0pCSElOWHdEdFVJUzUyN05td1hyUnVHZ0lPUnJJX1pYcmdCSnFJdGllZm5nMFJRSVVSNE9UOTBROTNrNGJBRGZoUElWZXFtQ2I1SUNaSzJxblItOTB3bEpGNm1IWTJPZ2w5MFlJNURveFhialdqLXFyQVFXYzR6UjhYOUo2Z2xjTGctMmZDMV82bjdBRHlfbmg0MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOMWxGQmsxRG9ra2xsQjFORThDQmI0Z2JXNEQ3NVFxUnNHdFJjSHBOZWZUX3doOVp2X1ZkYl92eFM1eFF0SWhHSnlkZFJhZnhTTzRiUk5vWUxTSHBJVVpTb21QWkxxYmdmelNkTlczLXItM3liVUR0SS1OWGNydXdjaTJLSjhDSGtVVF9XR0RsclkxSThpUEY4dFBMd3F2LXMxLVl0WGVYSWlxZHhvUjdiUHFGSmdRTHlyYW9yYnJpRzYtLXNDWDIyQ0FGemtDck1sSkxV0gHYAUFVX3lxTE9DTEhTbGRWbnVsd0VrNGpJS1ZwQU9QLTFTRUx3U184cEtNQVJxbVZQTWpldDdkWWdlN1VoZVZPd3ZiSEtFRDBOVWZjaDE3TzV5ZGdoU0x2Z0JMNG5hNWw3Q3QyOVdmb2RmaHNuZm9BTVlRZTNQVEstU1RkcU94YnZPYkF6QmlMN1pKNl9ObjU4TUNwX1pZN1hoQ0RrLTdJTi1FUTE2TGtzajU4YmVNb3BVeXp2MWppdW83aWhmNUVPMWpYcGp2M3NYTEhXLXE3aVUwMmNvRkkxMw?oc=5</t>
         </is>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>46013.24221064815</v>
+        <v>46013.72785879629</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Village search Wertheim,</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR Wertheim) AND (incident OR protest OR police OR security OR evacuation OR closure)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Curt Cignetti Led Indiana to Impossible Success and Closure for Bob Knight - Sports Illustrated</t>
+          <t>Iowan Brittni Donaldson is a trailblazer in the NBA and WNBA - The Des Moines Register</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:00:04 GMT</t>
+          <t>Mon, 22 Dec 2025 11:49:14 GMT</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNbkEtQmFzRndxTTFnUHVJcUdFN1BBc2VOd1UwRUk4UVhRNkwxSEt4RWpyRUFzRW9UUDVramJfZWszay1FMkd1UThpQi00MzNnZWNzZFhzbzNCUlNjY284WDhfWjVxMUxEQVA4UVZHWlJtTlZBSDV0X1JnT2psQ1lpYnFmdGRXS1pXRjloTHdqWG9yQ2NxOU9CQmNwbE91Ul8zcDZ1OThSd21ydklkZlh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNbEJ5d3E4ZUxua3J1cWdpRnZkX3lqLU12S3UyUjFqa3JnZUZ3QXFhVnNwT3ZXVDZlM0wxc1FsODh6RUN1cXpwRkxyeUZQcUljTVViY0F6UVE4U3ktMzdLSUlpTTN0Z3IwbGxsa2tHaUFTMW02ai1SZDdHeTdudTAzV09yb05qam45ZUEzanJJWFJXMXR1Zk0tVTlkTnM4Q1VRU0Q4bGtVTS1BbTNHU3hv?oc=5</t>
         </is>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>46013.5000462963</v>
+        <v>46013.49252314815</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Man dies after incident on Dartmoor by River Dart - Cornwall Live</t>
+          <t>Logan Jones: Adversity helped shape Iowa's offensive line in 2025 - The Des Moines Register</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:13:58 GMT</t>
+          <t>Mon, 22 Dec 2025 12:06:40 GMT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQTTJuYlJzLUtyYUJ3WVM3N0l0dmkwMFFpamdTNGw1OXA2alpka285c3hLTTc3cFZORFpVY00tbGY1bGRHZlZjT3NXMDJKRWlQVnlWTWlGNXhZY09BME1BZWRabUxRUkljWFBPajVlZmk5alVDdVJYaU1QSzQ0ZzJpcE41R29WZ0NNdGZNakt5SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNWUZSbDROOG1RRTc1dV9iUnVtZHF6eFR2eVdaekIxTmdkZm1vSDVFNGFCa2Q5NUxYMEtzd0paMktoVDdqZGEyWFpiWW5kSkVUMGFDOWx1YTd6cVRNQjBaelJtMUptRUxyOUdVMjJuR3d2THoySmZiS2xKQ0YybjFyY0puUzhzZ29BaTlhQnpwdTQ5LTN2STd1aHFTM0dNNGpxT2FSb1pWMkpTVWt0ak1hQzAyMkVMYXh1eURzbXB0d3BhZHpuc1JwWDVIUzRBLTJZTkdZdUNtZldsbERSUUZpWDRDUQ?oc=5</t>
         </is>
       </c>
       <c r="F169" t="n">
         <v>1</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>46013.46803240741</v>
+        <v>46013.50462962963</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Car park at Castletown demesne reopens following standoff - RTE.ie</t>
+          <t>Italian Championship game in Australia is canceled – 12/22/2025 – Sport - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:48:30 GMT</t>
+          <t>Mon, 22 Dec 2025 17:32:33 GMT</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOeU5aRElCMWZ3NnVoaU9oeE1YRjRrOUZYYUdvaUlDeFhqcGFCVi1MNTRPcXl0SmhQcWdiRDhXdjZaVlMyZGhxaWZlbFhmaDg1R2l3WHgzM05jam04YlIxSTE0VmJtZ21CZHNqWVZXSEkyOS1Wa0ZmcHhrYW1XUGlOWHRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPMnRQODdabnM1ZTFWYUJpTzdmeGhlNC1uM000Q1JBNXg3NXVHdldLTlMwQ1RwekZjZmllTU9LM3hIYjRYN3pjdHJJMGo2UlV5eW5pLTBkckxRUjl4cVVRb3JJUXZqbXk3Tk04V0NoNEJZNU5YdFFyM1FkanBQWl9EX1l2aHFiTjEyV0RsaHJxcVU3bWF1TjlPaXVNUG5CbU9LZjFGRzZVZ01hdw?oc=5</t>
         </is>
       </c>
       <c r="F170" t="n">
         <v>1</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>46013.36701388889</v>
+        <v>46013.7309375</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Woman arrested on suspicion of murder in Irish toddler death probe - Leinster Leader</t>
+          <t>Belgium’s police forces under pressure as staff shortages and public distrust deepen - belganewsagency.eu</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:40:26 GMT</t>
+          <t>Tue, 23 Dec 2025 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQVFFUNHB6X1I4V2xoUlBIem93STRLdlZpRUJaamh4N1RsVktKQlJhRVl4QkNWbGhJT0FDTkIxNVBmZ05PRVhCOG43NDYxcWpSWHczNWd1RGJUYlJBSkVIZVJNVV81OGNYQjdaamRPS1ItV05GZ20tVXlwbzIteUNFZVFUdU9FekNJSm1GNjhTZ2ZBRjV1MXBOUDJqNkVzTFp2SmFjcV9Fb0tvZk9xVHN3N2tSS0w0cXRpdldlNlJCWU5OSVlaV2lJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR24ycThyWHFHdFA2M1FOUDV1NFg5ZkJxcVZ5WVhuRG9Zc3R1OUxLbUdSTjVOSXhSUWxmWkN2MmxfQnB4VGRocnZuS2ltdVBUUjJhR19OcFltUVh0NnFTLVFsWlpfYThFbnlPM3IwU25uQlpsX0xCRTQ4NGFnRVU3b1hzVE1QcmQxOUw0TnQtbVhfb3FPcmoyXzdVcDQ0LTVqTEx5aTQtM2lXWHBuVW4xZDdBTU0?oc=5</t>
         </is>
       </c>
       <c r="F171" t="n">
         <v>1</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>46013.5280787037</v>
+        <v>46014.25</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Police to increase patrols after second incident of shots being fired in Belfast - kildare-nationalist.ie</t>
+          <t>EU slams China over 'unjustified' tariffs on European dairy imports - RFI</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 13:16:57 GMT</t>
+          <t>Tue, 23 Dec 2025 06:24:54 GMT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOM2FJa204M3F2aEJ6UzNlWkNVNGlhMTlULUQ4ZXZ2NzgxY1BZcm10NWpac3ZtZEhXUS1MSlFQR3JVcGpVQ3hOTzlBMXVGOHRmMG9TYnJJNmU3UnNyeHlkWmZReDJpWDdubjJQdVpiX3V0UmUwd3Y2MllZZmZJaVkzRExHbnRZdkw3WlZWQXNIb3VpbVk0cFl0Z0VlTm5adzh5Qm9FUG9qSk9ERG9pWjhZa25jZjM1ODRVOXp6UXFtMDNiV08wcUNHRThMVFZScEQ4UVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPV3ptNG54M2ppQXRsTG5DbkJXMmJJT1RvVnVwTUoxNEtWZHRfTWNwR0Z1em0wbUpmWnpBNDdKMHJVcWlxLXBQdk1ZMTV4MEJQSmVXNjZQanpMVlNGWUcyQXAwQ1Faci1sanRub2J3b2VIZk9jT0luTnAxdVl6c1Zud25HN21YU19wc0NBVkxqd1ZEWkpWNWtOQnh2U2otTVN5akJURTdlMXYyQ2VBcGM0?oc=5</t>
         </is>
       </c>
       <c r="F172" t="n">
         <v>1</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>46012.5534375</v>
+        <v>46014.26729166666</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bellmore Woman Arrested for Allegedly Using Stolen Debit, Credit Cards - Long Island Life &amp; Politics</t>
+          <t>Europe Looks Frail When It Needs to Be Strong - Bloomberg.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:05:29 GMT</t>
+          <t>Tue, 23 Dec 2025 06:34:34 GMT</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNQktNbDI5eXpBQ2NkVFdmVFUzQXJVeFR6NzhkVlJMMFZLVU1KTXFFa3daY3hyU0RDYTdadkhyTXV3Q0tKTThHeGJYeElTU0l1c1BwUGpvT2VfNTBIUDI1YUZkaTBhWk43bVdKR2pqUE93U193S2NHQmlrNm1mdlRISzZ2OVJPem5xdGhvMGpkY3JUWTR2NEM3bGlJNEhVT1Uxa0JRcUFjUkNXdVFJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWUpEWEU2OVBzQTZoWmpBVlhXdlQyNjRXNWVoX2xwSDJCQnBxWDZqc1VWdTUtNWFzd0pvV2xUOGdpS0lST2Q3NGNOX1RXVi05blFhaUZLeVNBTERwaE14M0YtS21BUDcybDJ2S1o4OXBSdUNnNEVOUEtXQTVLV2s0cWZKODFmZmt2bzU0QlZfLVdHX1FXWnVUV25jZ2hHdUw1?oc=5</t>
         </is>
       </c>
       <c r="F173" t="n">
         <v>1</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>46012.7121412037</v>
+        <v>46014.27400462963</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Man in 90s dies following Co Down road crash - kildare-nationalist.ie</t>
+          <t>Spectacular Christmas light show in 800-year-old cathedral in Brussels - France 24</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 13:31:03 GMT</t>
+          <t>Mon, 22 Dec 2025 16:34:12 GMT</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbGF1b1haM2NjQWNnUkFBa2s3S0NRWGJQbHBPdG1uUlRpREtGWlV2RXNPd0hneS1MVDAzVDc0X1RXX0hFNW1XOUFOYmFiaFd1NlVqQThHVG5qS2NOLTNveE5JZDR3MHA1VFBWbUJHNGh1enFTeTRQTkViQVJxTWR3MER6bDJDQldUbmhpUFZWTzJIdW05R0dwZ0VJcTJIUTBHSVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNNXN0Tk1ZRENNZTMyQzc4ZFlLRmpiTk4weThLSnlaNVZFNWFyNHhBelE0YVV0OThfaEdDeHVkUXlvMU01R0pzcnZrbWpwdGNwZHoxZDhYSzhJeTdrTHUxZk1JTnFMVXF0Um9yeXpwZHJ5eW1EZlY5eHh0eFVSczgxX2R4cnJnVE5DemVoWEZCc2hGYXNRS2hiVXVKUzJnejVfUU55S04yaDE1UGRXcFlfUGhEYw?oc=5</t>
         </is>
       </c>
       <c r="F174" t="n">
         <v>1</v>
       </c>
       <c r="G174" s="2" t="n">
-        <v>46012.56322916667</v>
+        <v>46013.69041666666</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Local Town Searches Ingolstadt German Terms</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (protest OR strike OR boycott OR police OR evacuation OR bomb OR "bomb threat" OR explosion OR stabbing OR shooting OR "suspicious package" OR "unattended package")</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Woman stabbed to death on the street in Germany’s Ingolstadt - MSN</t>
+          <t>Belgian Christmas markets disrupted by anti-Israel protests - The Jerusalem Post</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Sun, 21 Dec 2025 17:01:08 GMT</t>
+          <t>Mon, 22 Dec 2025 21:24:06 GMT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgJBVV95cUxQTEZnOTlkUW5XQmtoME9WX1BjVlF0SzIwV3M4bE9ET3ByWUhONWJjMV9XdFE5WTNyMFcyNWdKTWdSYmFPNkhSZTMxUmRkM0pRb0lpUm51cUdZWlNqcV9meFk1NWFMTDhlR1owRWdWLUxKSXdPeVlyYVhPckxQbklsSzh3RUFsV2hIUmFHb3h1aVNfLS11WkZBYkpkUzlCcllWY1MzMlA5V0xUcWpxd054M1NnRW1UOEVpWDNKWUxMV3pJbUdLY3ZpU085cnk0OVVFYjhlX3hnMW0yY3Nwd3lua1VCcWNsd0hjVW9kRE12dXA0U2tBZWxuUjdlei03T2RCcVRpUUpxa0JXdEg3dmQ5MTZmX28tdmJhWnJfUnpLaUgyVmhGaThRb19yLUdaZ0poYnFCT0ctcjBIOXRjZ18xTTBwYzVjdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1JQ1BtSVZ5dHdKelJqVlc1LU4xNjZlNkFMcHBGMDc3MXRNck5NVTlmbnlpa3pERVkyckRxNWtzdzlTOXF1T0RxM05EWUQ5dFRpYUV3TENCZEJNTzg0b1Bab0pGbElqdDBDN2c?oc=5</t>
         </is>
       </c>
       <c r="F175" t="n">
         <v>1</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>46012.70912037037</v>
+        <v>46013.89173611111</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>A Huge Protest Shakes Europe’s Conscience Over Sudan - The Times of Israel</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 13:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPMGZYMFVHVE1YNkRXMWl1UVQ2ZmFYOEtnTkZxd1FfU0hSbUJGeWpRM05kY0FRd1E3NXR1SjJacFJVZDFQVlBaSTZBZ2MtdGxTdGJyaW1SZThSRW9hcHFCZXZwMzVXSWFudkt5WkNBYS1mWk02SE8xNmNCQm9xSjlFQ0dYTW10QkZ6MEFiRw?oc=5</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>46013.55972222222</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Exclusive: Former MEP Kaili doubles down on 'Belgiangate' - Euronews.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 08:00:44 GMT</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQclAyU3JmazBZVWhlRmo4bmctaWdoRTVvWkYtMzFGNnJaakE4OV9jWU05QTBWOEwzZFV4SjVoUTFVZlNSNUFfNzhwbXh2bjl4YVItdWtjc290dFFySXlpNkhYQ3Iyemp0WVhpWEU0RVBlWUt2MzhSZ0UxMjNITmdPdm9DcG5WSE84dUo2ZngzRmViUnBNOHd4c2dWSjdfUncxX2p6ZGZ6MS00NkUzX3pTZ2xKb05xbVpxM3BiN2JhWDRxb2tMYk5uTE9pUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>46013.33384259259</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Eva Kaili renews attack on Belgian investigators as fresh Brussels fraud probe grips EU - EU Today</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 21:54:41 GMT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE95MmNjV2ZMci00MG1hQ0dORG9vMDRqZ1ZCRGJ1MngzSUFQR0tzLVkwQ0VvVmFlODU5cVNLSXktVnhJM2pqR250eDRWX0xfMVh6R3RvUnNRSmZfU19PYnAwUjM2bmtnRHo4TkpVM2lKRVU1Y2oyMi1vag?oc=5</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>46013.91297453704</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Over €16,000 in fines issued for fly tipping in Brussels - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 11:16:09 GMT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRTlxTWxSTno4ODUwUEctOG5Za0ZvVUVRT3NuOW53b2VtTzVhb0J4ZnpDUnl2Tl9IOWdLVmpIOVB1VUI5ZUt5TVNSWl81NjZuMnFDcV9CX1dGbXZxNWdORGcya2dDczE3SnZ2OXVURGMteTZlNkh5a3N0M0JQS2diU2NDMC1WbG1RQml2ODBnMUljZHdpWEduNWh4cU5CemZXYzdOZg?oc=5</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>46013.46954861111</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Westmeath IFA chair joins farming protest in Brussels - Westmeath Independent</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 16:25:47 GMT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPYkhyUFhOY0hLWDlEbUQ1TXg3X2hWWEtobE1qLVdaWlB2ZndxdjVhVU4teXhaejFXM0RVeWxXSFhURzZRWEc5bGRkVTg3Wl8zUkpfSzdjVjY3VThDdVFlQVRyeUdhTmJfUjg0NndPZG9PaGFqNGp3eVhSMU4tcWh2MzU0V3pYWFNNR29UX3ppUkNveFBKbDVZTF9XNEZSdkk4aHdJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>46013.68457175926</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>E-scooters to be banned in Brussels on New Year's Eve - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 10:48:47 GMT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOUmRBdzdGOG9CY3lfdzFySjdxZFprb3BDSERZY0c3c3MwVUh3S2lDWVNoc3lhRDc4WnJxbzBGZnQ2TUk0WnY5SGoxS05fck5ac3UyMkhPZ0ppQU5LODNPb0x3a3RHN1pSalJGT1dRMWxXbkpJV29HMEZQVjNYeGlNS2JCVUczZkpPNTU1ZnplaXRVVEZJWTI5M3JWVTRQTVR5?oc=5</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>46013.45054398148</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>US tariffs hit German car industry, threatening EU’s export-driven economy - RFI</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 13:28:55 GMT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQSnh2ZU5VQU9lWTduNGlDM214UEVWYzJnZGRZNXhUSEZweU9VWkQ4OTdmQ1NHeHVsUHpBbUtHSlZCV0NENTNZUm1PemMyMWRLQ0RORm44bmxENHNGQ3R0MnZHdG1uRVN3TWpuZE9JcUtKTEE0NUVab3hGX0w1MjFHMml6UzdTOC14SWhESXVtOUx1andpVWMyMGhZdDZGOUlYakNRTEFSSlRZbmJoem9ReFAwOVBJRXFfd1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>46013.56174768518</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Belgian cannabis dealer linked to Dutch criminal network - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 13:41:58 GMT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNR090Y3VqWlRnS2lNMGVvcExZbm85YzVZRl96MEFMSGNlMFRDb1lKRlV2cDN3X2xteHFEY2ZBWjVNS2ZvVFYwRjgyMi1ubGdZdThfbEs0TzJOUHhORExndlZxMDk1UXZTNURuLXptODZ6bmtLUk1uZ1hfUHpPbU5oNTlzNmhESHdNVC1NWjBlMmF3YXZmNlB3VGNVMU1YaUNJX0tqUEhR?oc=5</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>46013.57081018519</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Swiss court to hear Indonesian islanders’ climate case against cement giant Holcim - RFI</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 11:18:27 GMT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQlJXRHRjelhSUTVEeDF0MnBodVpoLVJGa1ZQbjZMUm9iTl9jell1TmtpQ1RNYUxSQ3VuTC11TFZ0VnNic2E2MHFYMUFQUVIyN0JWeWdpazYwdzAyU3JocmhjNEUwd0lwbGZRMVR4M2FMOVNEYUdzakpUeENGM2xoY1ZzaFNBRnJpc1FISWxpWEg0dmNiY1JyWUpaTEtJZEFJLVl6cGZBMV9IUGZDeERGeVp3TUc5OENYWnVfNFhlZzBNbmw1?oc=5</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>46013.47114583333</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>One person critically injured in Brussels apartment fire - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 11:16:09 GMT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTkFxOG5kZVhldDFnakZMYnFldHp0Z0psS0ZJeVdJLVRSNVdjZ3RMd2RGdXBMMnl4aWFQNk43VzgyZHI5ZmgxLUtPdW83RnA3eHZIbS1xQWszRkJWVm1YV2NZdXVSVHBkYWM2S19EcVRhMzdSSE90UElPSmx6M3FDcHNJOTFPNFJpS3k1SURjcmZ6VlpvSGdKd0l3?oc=5</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>46013.46954861111</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>RTÉ tenders €1m contract to boost Brussels office - Gript</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 15:47:22 GMT</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE4xUWZUckgzSW5WVmY5Wk5STjVaU2diV0xXdXRzWnNaUWk2OE83TjAwUWh0MUtscVVJVnhBTDhWVEx5TVMxMDA0b1hiMEx5ZktaVlpWdG1rUWt5Wm82Z2lIMWNNU1lWdWstS1NYZjByYU92XzcweXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>46013.65789351852</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>EU Commissioner pulls out of Brazil visit - Shannonside.ie</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 17:23:13 GMT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQZmhRTVo2WjlmbHlVeVJBaDhvY01ZVjhfWUJIVlpDQmg4QUstUGlZY1FzcmVXUXFSRGhoZGZvd1dIS2dlcFpBa3JKUlJnXzhRaVdwYVFpZV85dHF0cUFzRjlRZldZYmM2Q09jZWRub1dKeDk3OGdmNDVJRVBCbmMxZzV4NHdGNVk?oc=5</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>46013.72445601852</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>The EU-Mercosur Deal Is an Opportunity Europe Can’t Afford to Miss - World Politics Review</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 13:58:15 GMT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5yZ29faXd5SjVYVV83MWNUYktXX0ZWN0puWEZIenpVVGZ5eldya01QSERRMlg4VlFKRUV4eG5kNmlzYkJFTzhKdTg4VnM5UHA2Q3NCbnlkSXJoSFZwU1BZRm8wRmFpTHJQY2lMZXhJdWsxTG1h?oc=5</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>46013.58211805556</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>New app maps drink-driving checkpoints in Flanders, highlighting legal grey area - belganewsagency.eu</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 13:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNZzc2UktrbUozbHlvdGNVQmJPU3plTE5NY19FYTEyMHV3MjY4S0k3Q2E0Z2JHQTZ3aFU1WTFHSzVlMkczNS1yRERqVHBYaHV5aW82NzEtSnB2UlJzb3ExNW04cnAwV1RCa3JfTS1kM0RMLUhfY2dIY2d1NmJxMTEzMEM1NTZFdTB5Y3l5dzVROXEyYzZkQ2FDcnAtYk83dUhNWnkzejZfek1aSEpCYi1V?oc=5</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>46013.55486111111</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Rejoining the Customs Union would mean a Brexit forever war. Why would the EU let us? - Yahoo News UK</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 12:20:43 GMT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPR3h2bGNwVEt0N1h5SnN6bVcxLVY5Uy1nbmhWbHU4ZThhUGk3d2p1UWptdFZQM1VjczVFSmVJR0Z1czUyanV0ZDFTbjVpM1Nfd19jaGhHa3FrdkM0NzVxWU5EdXFaZXVmWkZicldlTWFlS19KSFZvMmhiVjQ1emZnSkhR?oc=5</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>46013.51438657408</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Brazil's Lula Hopes EU-Mercosur Trade Deal Will Be Signed In January - Food Manufacturing</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 16:10:26 GMT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZnRQeFl5N2l3TnA2NTdUTGhaMFU5VklEQzdRWnpHZC15SHZqb1JkMkVEM0YwS2gtQUlwcEdpQjRIOUFndnVVNFhCMngtc09TSGQzWXJEdVY5UFhTSGEwakZXNGY2SEFSSVQ5cTl4VTBCOGwzT2dteFVfdi1OQnhHMjN0QlBLUWNtdXd2RGoycS1maEdnaERQdlYxSGFVMjJ4S09IZFR4bnBBVlhlOV9BT2dOTmI0Nk9zWk9vWjRBbnU1c19GLVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>46013.67391203704</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>EU to probe Czech aid for two nuclear units - France 24</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 12:33:13 GMT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdk01dEJDNlg2RzNoQUw4cFo4dXZaZ0VleU1OY1VadTlhNVpUNENzWEhMbVpDZ3RpbFB5dVpvbEZtM2pwLXRfczBENVRZOFc5UjZtR19BTnV3NG5Lak9lMzNQVzFTRmRIMFRfMlFCcUR4TkpOWXRCRFFMOHAyX0N0LUhucUZKRUdITXhJeU1rODZkbTE5?oc=5</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>46013.52306712963</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Cloudy Future for Bourbon Has Jim Beam Closing Kentucky Distillery for a Year - Food Manufacturing</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 21:21:32 GMT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQZEdmN25jWmNiVU92ZXR4YTVyRVVqdzdSekJHNXRrQ25iSW1uTndJU2ljVFNUUVlfWENRQVh6N3lfQlZRWXJXS2NkWGJOelBzQzNLbHNueDBVMkdja3FPa3B2aXBCaHJYNTA0V05hVHdreDM2ZHhpcnBMN1VURzhjRi1tbWUzUTBubFk4MDMwampoMFNWN0hZaG1iRWoxdlRSWkpqMi1Pa0pMeWJoXzd2UWQtNTNEd0x2Y2I1RkJzVDFlWnpoT0VleHlacHlHamhldWtvYg?oc=5</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>46013.88995370371</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>India, New Zealand Finalize a Free Trade Agreement, Eyeing Growth as Global Uncertainties Persist - Food Manufacturing</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 16:20:28 GMT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQdVlpMHJsTWJwTFkxcHRqUVhJS2Jvb0g3cC1POFRTTXdXYjJKQXJBckxQTnNkT3o4TTU3S0ViOEM5OEZlbFZGVHR4UG1fVV9TX2tUYlppVHRQaDdBcjB1Wlg0WnpOOWIxTi1jckNseG54WXM4cGE1T01FOW95ZVkwazJLNWdsUDRBZ19oeFhJYUhmSnlEMHNMMnh1TDdQQ1h1ZV9VX1lPalJfb1I2X1RPdTZraGFTek5uNC05TlVCLXZVRFJ1SXZ2WnZfVnFMdUluOWZuRHdaOGNYaWc1SUNhWkMzUHBCN2ZPdFhJMQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>46013.68087962963</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Pay scandal scars fade as IFA posts strong surplus - The Irish Independent</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 05:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVjVQekJDNlllb01kdFE1UXl2bXphc3FZR3FhSTdlM3R2V01PdHZCV3N5TjFldUhJZWxQOHctVS1Ra290WWVtWEVUSXZrV2J6LV9KelJmM05IelZDYTE5UDR2T25oMWoyV3BXWVlWQjl3R1dER01kRWlPdkpfRHpCTWt6ZTdVZjNqTmlEZk9yYmRTQ2VyN0pURnZTdmZUMVEwbTRjbU5iTnJJZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>46014.22916666666</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>My mum charges me £100 for Christmas dinner - and I'm happy to pay every penny - Devon Live</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 15:52:18 GMT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUmRXZ1NKaDRvUm5GaVJSakJyME9vV0lnSnJvZ0Q4ampieGcya19ZekxYMlhHbkFReXU1NE5qUmM3cTJRTlVNYnk0V0xWbVozM09DcEYtbEkxX1o1WUpvdkxTdno2WXlzUmUwR1UxcjdTeUlHaWU1Mk1LVFR5cXlTUllQOGk3MmNpRmdfUzBrTdIBjwFBVV95cUxNUmRXZ1NKaDRvUm5GaVJSakJyME9vV0lnSnJvZ0Q4ampieGcya19ZekxYMlhHbkFReXU1NE5qUmM3cTJRTlVNYnk0V0xWbVozM09DcEYtbEkxX1o1WUpvdkxTdno2WXlzUmUwR1UxcjdTeUlHaWU1Mk1LVFR5cXlTUllQOGk3MmNpRmdfUzBrTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>46013.66131944444</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Horizon police arrest 22-year-old for hit-and-run, DWI, and using false ID - KDBC</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 19:00:41 GMT</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNLVNpSVM0TGlGdVh5MlQtejdndzdRNlFocWZnYTB4enpacUlOUFRIX09KWHhsaXlyb0JzZVdOdG9DQUlmMjRXbUtySVAxQmtCT3NEbUdZTVJiVVdhLXRIZ0lYTVZuYnBWc3NNUGxrTmhSeE9ob2NZa01VODF6RWVMbUdscHNiOUsyWHR4Ym5XaGlWU0RaanpTRkF1Z0VPTzduUTNGTTJNNENvQ2VVeWozT2VQTHlrVm9rMUtueGhvTkh1QUl5bDB3TDloaG5JY2dYMElBbmdwMGRxa2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>46013.7921412037</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Swiss Mansion Where Ronald Reagan Held Cold War Peace Talks Heads to Auction - ԱՐՑԱԽ ԼՐԱՏՎԱԿԱՆ</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 19:41:16 GMT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTFBKaDR1eEJKbzkxWHRzMTJudWJ3ZTN3OUlhbDJudlBlOG4xZWh3MHJoVWlKUHo4Z1ZtQVNQSHE4QTMxTXRKQlhoS1hNTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>46013.82032407408</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>What happened overnight? Police blotter report for Monday, December 22 - Newzjunky</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 15:30:04 GMT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQN2hsaHo5SjVnNjI1MEkwYlVLUU5Bd3RlZnZzTm1ITEx1dGYtaVRPSjRCcmFCbWhjNXdDZ1JSckRONW42UHI4UXhZbDQ4UlhacVphc0FKY242ODJJd2dialkzZ2oxVmt1NldvYzVvc3VpamhUeWhLN28wYnZiOVpBbjFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>46013.64587962963</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Drug-related violence rises in Belgium, increasing public safety concerns: Report - usmuslims.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 09:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQOVVqVk9vMFlCZ3ZyQm5PblcxREZ1MXJUSW5EQS1rSEt0Y09tRHhyMXlTazZiVGxUeHpaX3FqUmVDXzJ4eXQ5QjhqMkZQUy1NbnVCUndmTzFiNWZyZ1lHY09QTUppZE1aWEpFT3ZpODhFRnBBOURFa08wdVZWV2ZKRWV0ZUhvUGFTb1ZyTk5zcWlORktTa0R0YlAtWENmUllORHhUWWN6ZXFXZGdMUzVxYVNlWFBZanlN0gHIAUFVX3lxTFBCZ09PaUx6T2ZHQ18wT2pUN1d4YndsdkdEOW1PVTdONmR2VlFJZjk5Y214cWF6TUhsQVBpemlaTmZXckxWX1VVazhndEc5eWk0ZHZYNV9pcll1dXpRR3RnclFLZDRBZ3A0cU05VXoyUVBzWDY2NzkxaTNfekQ0aUtpenIwZDdsQWN6dnZLTEVoeFlMNEI3STJockxSalR3OFowQXFlMVQwNGNrRXZwc1BueGFXYXVCQU9jUlVLSTdjd2tUdkNpQVBJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>46013.40694444445</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Erasmus is back: The London-Brussels agreement - lnginnorthernbc.ca</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 10:18:15 GMT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPYWVlVlluaGNVbnRBSV9JSlAzZ0JHd29EOFU1RXJDc09JYlQxNFZFUXNFSC1vakMtcnBQQl9pSHNvZk43X0ZwcG5oQUk2UkJnZ04xb0NvaHVBMUdKREJ5OTZkNWk5S1BKWEw0VnNwdHBiMlFqdTZqVmdXZFMyMW1vb1c1eG5hUDFIeVpxOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>46013.42934027778</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Village search Wertheim,</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>("Wertheim Village" OR Wertheim) AND (incident OR protest OR police OR security OR evacuation OR closure)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Curt Cignetti Led Indiana to Impossible Success and Closure for Bob Knight - Sports Illustrated</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 12:00:05 GMT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNbkEtQmFzRndxTTFnUHVJcUdFN1BBc2VOd1UwRUk4UVhRNkwxSEt4RWpyRUFzRW9UUDVramJfZWszay1FMkd1UThpQi00MzNnZWNzZFhzbzNCUlNjY284WDhfWjVxMUxEQVA4UVZHWlJtTlZBSDV0X1JnT2psQ1lpYnFmdGRXS1pXRjloTHdqWG9yQ2NxOU9CQmNwbE91Ul8zcDZ1OThSd21ydklkZlh3?oc=5</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>46013.50005787037</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Man dies after incident on Dartmoor by River Dart - Devon Live</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 03:05:45 GMT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNQ0NSei1heWU0M0JFVER6NDRhT1FhNzRlRHlMWEdTQjkyWk15M3hiQVJwell1T1F0LVM2LW1LOUZFS0VUd1ZaYkhhcGNLSnZ1WkMwbGN0YmEwNktxUUlFellEZHZGTzZvZVVaRlZ5WVNuTkEtQWhZdXVCd2hGaDhpQWEtMDZldFE1S1dj0gGQAUFVX3lxTE1CalJmMEhwN09sQzBRa1NkMmxzcHRvTjV6NjhNZ3B0bmhGRC0yLU5TZEFCRjBtRzJnMU1GaVVTNnZVRjVqYXdvSjBjc1NjQUhvRzdJdERwWGFNcEVoTGhmbGFBNS1nTWRsOExWckQ0c0RlanlmWTZ3djBJc3hMSHNZUEVoU3JxNHBCanY1cmFPdA?oc=5</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>46014.12899305556</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Car park at Castletown demesne reopens following standoff - RTE.ie</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 08:48:30 GMT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOeU5aRElCMWZ3NnVoaU9oeE1YRjRrOUZYYUdvaUlDeFhqcGFCVi1MNTRPcXl0SmhQcWdiRDhXdjZaVlMyZGhxaWZlbFhmaDg1R2l3WHgzM05jam04YlIxSTE0VmJtZ21CZHNqWVZXSEkyOS1Wa0ZmcHhrYW1XUGlOWHRB?oc=5</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>46013.36701388889</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>€239,040 Funding for Kildare playground recreational space upgrade - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 14:40:04 GMT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQaXJiUGNrU0JHTllMVS1aek0xOWVwd011SS16SlNfNndjSWw0WWtkOEZoQ3l6WUNOUE10MlJyWEZRZWtFNHlEY3RSbGg4OUhGRVZQLUs5Z2laeTRPZ2hWaUFONHl2bFdwRWR2T0VpZjJVTXdCRkxZTGROT2NqSzdQQTFfNzVFWVJfOUkzY29ubmxsMWVyd1MyVmlKYTg3WmpTcW14MWdLVzNOem1VcjJtWVNmUVUtNm95Z2tMQXY3X2M1QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>46013.61115740741</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Woman arrested on suspicion of murder in Irish toddler death probe - Kildare Now</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 12:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOS2hiUTRncTY1RXppdE9nYVo5eVI1Q25EN0FQMHc4cGM0WjZnNnBjbHNaNFlOQXVMNXduX1lrRHR1RnVZWUxBNmRjZ0VuTzBzS2RjT1UzQUVXY3V3ajg4VGNsY3ctRVg4Q090VFZsbFdDRnBrTVVBcGhMNW9JaEJBUERscV80OW43MjNhTllLdEZIMi1TWEdrY3hqZmxyNURreWFrTlFOQzFCWkF3ZmlhV0lrbDAwYThPdnlPZTFfcVUyXzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>46013.52430555555</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Overturned vehicle on Highway 21 NB, left lane blocked - WTOC</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 12:48:01 GMT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOa1dHRWdJUGxibkUyV1U5S2pKSEZKUGlTbU5MbU1JNzAzZklINl93LTlBUEV1dmQtZDBkOERleXJnVHYtaFJnVVRNQTJYX3lPNW5iYTQ1dXdWX0gtRDVCQm9BTDVWaVJnYjJNUFJ4MExOMWF0SVhzYzNkeFM5NGxvVjNqdDNDQ0lDUmNLRXRyQncySlNNSVZvWGo5cnlLSFB2NEVGSdIBpAFBVV95cUxOa1dHRWdJUGxibkUyV1U5S2pKSEZKUGlTbU5MbU1JNzAzZklINl93LTlBUEV1dmQtZDBkOERleXJnVHYtaFJnVVRNQTJYX3lPNW5iYTQ1dXdWX0gtRDVCQm9BTDVWaVJnYjJNUFJ4MExOMWF0SVhzYzNkeFM5NGxvVjNqdDNDQ0lDUmNLRXRyQncySlNNSVZvWGo5cnlLSFB2NEVGSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>46013.53334490741</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alfani Calvin Klein Performance Women's Logo Half-Zip Cozy Fleece Sweatshirt Women's Fashion Shoes &amp; Accessories Hot Sale | Clothing - Backseat Mafia</t>
+          <t>Dolce &amp; Gabbana Fall 1996 Ready-to-Wear Collection - Vogue</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 18:37:59 GMT</t>
+          <t>Tue, 23 Dec 2025 11:08:55 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9Uc0JlYUVzdVhpX1pVSE1fX2VmMWJ0c2lad2x4aFJtRWp1cDIwaGhITFpxV2h5Q1lFTTFSQnBJc2VWM09qM0pEY0tVOHBPTWc2NVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1mMWQ4MW9IOTAtajc5SlBKRGQ1NXZWbHptenk3Q1g1QV9CQkdLanJaM25qQmVmaUdrM0ZxZWhaeHl1cS1UaGVaOTJsaDNDTW5GWEJwUUhiWlN0TTFJX1ljQVpKa2xlSDlDZ2Z3bjQ0QXpKX1Jwbk0xYXhyLWxzdw?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46013.77637731482</v>
+        <v>46014.46452546296</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Why Ralph Lauren Paint Colors Have "Enduring Appeal" - Livingetc</t>
+          <t>Dior presents House of Dior Beijing, reaffirming r... - LVMH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 06:30:00 GMT</t>
+          <t>Tue, 23 Dec 2025 16:34:22 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9nUndZeWZlZnJNbGYxcWlVMjh1NDFqeGtjUk9OTERBTjVsTTBUQVJOLUJxZG5BdjVTVno2N3pMOWR1aExJMHE5QXRsN2o1MjdDcllBaTFsbWZrUnpQeXBHT2lvVG5TbzV5U0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQdXhRbzJEWGJGNGE4MEk1VkNuRmdZSU9yR05wV2VweTlnX1B2VlhYZlAtTVlEamlZOElMbGxpNzRBU3FVcnU3TTl4ODJPYk1QTVhNQzdsaGstZnphYXU3SXhhN0pqRU9nNk1odXB0VnR1clhxdXI5Wl9LazE5SWxUQnlTdGRTYTVKcFI0cDNDQVNYY1lvenk5Ulpkck5Hcjd4cTFPYWdaMm5QM2Nl?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46014.27083333334</v>
+        <v>46014.69053240741</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Elizabeth Hurley reveals her Ralph Lauren sweater is older than lookalike son Damian, 23, as she slips back into the stylish look for a festive snap - Daily Mail</t>
+          <t>The focus of the Gucci Christmas 2025 edit is joyous celebration - Prestige Hong Kong</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 00:40:00 GMT</t>
+          <t>Wed, 24 Dec 2025 02:20:20 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQY2cyZ1hlQzRsRzJWWHloTHVtUGZkTElkWkNPZ1locXhQcWIxR3BhODAtRmNNZC1MT296V2xRbjAzWUs3OVRqN1B6c1pfc2ltMnVrUG1PbEFYcE93TkNaeHF3YWFlVnl5RHZCRVZKekpMb1gyMGdaa0E2U1ZRbzV2OWxXU0pjS01fRE10UkhiSDJJNExBN09iS21nMG9mUjEtTDFGTmlCaHNuaTJzZEJmM0pWOGPSAboBQVVfeXFMT2JRaV9QTGtZaVIxSG5ISEFjQS1jOW5DalFVVG4zQXlZMWZQMU1mN3RtZEtmVDFfWmwtcHRaXy1RM1ZQemI4ZVl3VkZEeWVxVEJxNGJfdmVYMDVwU3ZOcElDVERhbzRxYnVsTi0wMEhGY3E5UEh1MjJndTM5UE0wQzVvTkdpSGpVQlI3VXpGQVBWQ3Z2RFRMcUVCUVZMSmNzZGxQVlFZMFJ3d2hqYndfZHkwZGRIeE9GUGtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOUUMzaUJ0Y2t6YWZ0ajR2ZVpBRFd5UkhnLWtlMUZXQUllc296XzVwUXFDZEVZVi1tOHp4ekF0SXcySmNRUnFoWHB4bWdSMjlHSzBuZUpKQjBud0E0b0tlcHpCWG12RmVaRFowRFN0cmhNOEFseDAzNWlQR1Fkc2FPaS03V3g0WXRaN2VHR3ZTdWZHcWtwUnJnbFJHVTJFa2tJWEs1MUNONmtPREJ1NmlQdkFtdHNkQjE5UHFfQjUyRHpEVm5HUHfSAcsBQVVfeXFMTnVhSkpHWG5IS3VrQlhRVDNBMnEwMENqb05kZ1BSVkNxa1A5TjltVnprcEdmNlVvVlZ5dzBhSzItU2p4WUJaYV9wS0JKZ2lrQWpjNUg4QVRZaW9EN21mUWZpOXdGVE16a1JxQjJHU3E4azFCTk95c3Rtb1VUMERSNzQ0ZDRBckJoUG8yYmNLY1VrZWtkaE1OdEo1M1I3ODQ3b3VFTXMwWEJmSDJFSHp1WDlhQTR6Uko4TDR2R1VXR2l1SXBhRVQ0NUppSXM?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46014.02777777778</v>
+        <v>46015.0974537037</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jisoo, Anya Taylor-Joy and Willow Smith to Front Dior Addict Scents - WWD</t>
+          <t>Dolce &amp; Gabbana Lands in Peru - Retail &amp; Leisure International</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:01:44 GMT</t>
+          <t>Tue, 23 Dec 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQT1dkRmtLSnlLcjd1RjZlQ0dsaWQ0NGVNdFZ5ZVA3RnU4dldOY1U5TGRhT0ZQUWZrajBTSGpxdHNHMTB1YmtTeDd5d2NVN3ZLbExqb1ZxZTBIZE9uRFl2YkxrM182WUtWbVlIYW43XzVjNFBMNHRDX1diVmNWak9fYUFXaExlWWpZZjJwVEc3MEdkTVBTY3Zic3R0WE9reEthMXV1d2czODFpVkFEUEl6c0FCank2T0lUWmhFUDFwckJQZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9abGRJRVBPN0h0UUl0YTgzRjV1QUhZMlJXUWNJTlpkQ3pNOTM4UE5udlp0VFFWUmpnQXc2djJQRF9rVjhFNDRVQ3lHdjB2a3g0d1hmMTVwbmFIOWEzVFJNbQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46013.54287037037</v>
+        <v>46014.33333333334</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LVMH opens Seoul flagship dubbed Louis Vuitton’s Visionary Journeys - Inside Retail Asia</t>
+          <t>Gucci’s Horsebit 1955 Bag Is the Ultimate Cool-Girl Investment for 2026 - Harper's BAZAAR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 02:19:41 GMT</t>
+          <t>Tue, 23 Dec 2025 15:57:44 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQd0dwVVZmUk1zZThlQ19yR2hEY0VibXc1RHZtTWZoblNlMERSa2JlOVFxYmNyaWhmeHR0NTZfU1RLMXlaanpaOGI2ZmRzaUcwUmtVYUx1MmYxdGRqbndVZ3FhV0Q3ZnZaS2J6ZzU3cEpQZGVRQjJBSG9iUndXNkVBV0xuTm9iYlV5T3VEbHdsYjdoTHJFU0hsbDRiN09lZVpkc0pYMTRBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQOXFPY1ZtekI3STkxN1R3WThmelV0bC0ybEVlLTFMeFdFcE5pWWZweENvMURPZnlaTjVMRXdUMlY0MTBTVTVsZFVyWl9QbFFINVBhMDcxY3F4Y2pSeHhkTlpKbHRVbEZwLXRkZkZnVlBtRml5VkRNWGRYNTdFMVFNR0tjcE1xUQ?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46014.09700231482</v>
+        <v>46014.66509259259</v>
       </c>
     </row>
     <row r="7">
@@ -647,24 +647,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Not Fair Isle, Not Argyle - This Is The Knitwear Trend We're Actually Wearing This Winter - Grazia Daily UK</t>
+          <t>Jisoo, Anya Taylor-Joy and Willow Smith are the Faces of New Dior Addict Fragrances - L'Officiel Singapore</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:26:52 GMT</t>
+          <t>Tue, 23 Dec 2025 08:36:42 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPVWowWFBITTQ3RDdOUnVGaHphaHU4SHZwQjlXLWIzV0xTR2xxLWp6UGdwSFZjV0dqZ001R0xkRGJGclN4TmRiOVc4MUp5V3BMWF90VlpkVUNjWUdtM3YyaHB2VDNYNmVfcFRDcEdJeXF6Ny1Qc3RLU1RyTFRVa21VRmhBSS1SMkZJX3B6ZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQZlp3NG1lZ3ZKSW9MNHgxZnMyd0RDd3ZuYVRQRDBnUDZEMFFGYmJNbUdidmcwUEJzb0tza3Zna0NocklpalFWUERnOGpUVW9lY2VvNDZzLXdhbXpyUnhFbE9WcU5UZ3lvZEYtNkw0dXZXOEFqVXh6RlBQWDFSQjg1Y0J5V29ESkpvdHczNnJHemE0cS1Qc1lvYW5mMm14R0pMa1hpWXpiajVMdGJfSXNCR2dFSUdfVG4tRGFiUzAxX1MycHNyWVE?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46013.60199074074</v>
+        <v>46014.35881944445</v>
       </c>
     </row>
     <row r="8">
@@ -680,24 +680,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>America’s Cup – Five teams to contest the Louis Vuitton 38th America’s Cup in Naples - Sailweb</t>
+          <t>Louis Vuitton’s ship to nowhere marks the new age of luxury - MSN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:35:25 GMT</t>
+          <t>Tue, 23 Dec 2025 23:01:48 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNdVJNS1BCNngxRkpmcjFNdUpmajN1RW0wcGtOcE9SRjBPVjYwa1hUUlU1UTR0RXFTV0dzcU1hQm53ckxmY2xOd2N4Q1Q5d25vaWxJd2gxWURqMEpiYndGTmxnQ1RhWldaLTltdjFHMVlYVy02NXlJNU9FYnhWTUxKTm1Md0MtSG9oa291di04Y2d0VDhVNFRvdTlLRWtZVFVJZHVUYUswY1pDWlRvZnpINlBuV3V4b0lha2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOc3ZpdU5OdXVlRWNBRm01Nnlwa2tqckhBVkhoejhLYXRIUEJ5M19LUmlSb0VRMXowZU9RRFY0WlFrNkxLdy1BbG5FYmlQekZpTHFWRklwcmFlNDVGRGM5RDA4UkNpb2xTNEVlZmZOb2FQb2pQWlJ5YnU5M2VzNk9hYjh5UDhkMklGOEhtOTc1NzNlVGtLNUZ6ckRQWDI2SE9UOHlNbzdjaGRFYS1EOTZVSmVzMA?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46013.48292824074</v>
+        <v>46014.95958333334</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Festive home games must-win for Gillingham, says the skipper - Kent Online</t>
+          <t>Dubai Basketball-EA7 Emporio Armani Milan | Round 18 Highlights | 2025-26 EuroLeague - Euroleague Basketball</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 05:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 20:03:47 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPMWd2dlNqQm5sdno2TU1laWpOb2dCTjRmQVlhNWRUYUxISEdUcDlzelQzeUdFV0NNUnNCNTBoLU5lVHl2dXY1dTZNeE03RWk2cG5TbTZiS3pWbmlnUWk3Tm96bmtsRGhrbzR4Rm1hRFg2am5EYVcyc09rbmd0TFYxVm5aVkp6TVEtcWIwZlJZc1JIX3R6SVNZVzBQeEJWakY5dE03dU1MM2lqSkhJcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOTlhVbnJnck9JUjlkZ21GT25Dd1cxWHNaUkFPaVVIeG51SmtyNDBpQ3p2V0s1ZTlYaTlmLU9zTW9Qa0FWSnI4TFdzZm9VSzN1blRhb2FrUkhFNE11SS11bUEyZWlZeWhQQTFHRkZ3c0tMai1nOUdZNFE5NF9BYm9rc3NEUjVyVGJEQkd3UENHckNYNmxYNGl6TGR0QmlBQkhJMzB6RXdKR2lPQTg0VnltR2JzQ25pdmgySVFGemRBazNIdGllYVBNejBZOGtFalpoS0pR?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46014.20833333334</v>
+        <v>46014.83596064815</v>
       </c>
     </row>
     <row r="10">
@@ -746,24 +746,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No. 10: MotoGP Great Valentino Rossi Adds Four-Wheeled Win at IMS - Indianapolis Motor Speedway</t>
+          <t>Man stunned by shocking final gift in $1,000 Dior advent calendar - LADbible</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 21:50:59 GMT</t>
+          <t>Tue, 23 Dec 2025 12:25:51 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOR0c3QU4zUjdITnJwaE96Wnh6Z0NneEVLUG4xc0E1VlBOTmt2QmhyTFluaXZKWExBTFFZb1lvQXFTQmVpNkIzRm5tWkNQYWV0QkNqenlkQ0k5eE9sT2JNNGFleGVvSXE2UmdScjRVcmJFNHlLanJKeWhKUEtnWkRMZUdTd29XYlBRUUJEb3EzdzY5UGRITzZsTkI2YXdTZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQeTNEdkF5a19BWDBILWVUa1d2SnhuMWpnYzFnSHp3RERwRC1EbUtpZElnNmNaSWJHNVgzTFhsZzI5QnNWWklwbDRxRmxhZWxsRUIxeVRNRGg1aWRnRzV5OG0xX0ZHVlBZdHZySWJxc3ZMazNfMXVnNlNJdnctUmZwRkF6THpxaUpGOXNkYnJTdEtEWEpTcXhJMmV3SjlYc1FOVm9TWTdSVE41SjdUSExxbFBQVC0?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46013.9104050926</v>
+        <v>46014.51795138889</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Style File: Orm Kornnaphat - Vogue Hong Kong</t>
+          <t>Cartier-Bresson’s Rare Book “The Europeans” Has Been Reissued After 70 Years - Fstoppers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 03:57:33 GMT</t>
+          <t>Tue, 23 Dec 2025 19:22:40 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1za0dLSE0xVVZ0UWxHMG9RekliTmNSbnZXMktzX0FTQ0FwMmlOZmlPOTFIWGMycVhCc3NIblhBc2NiVFNSYUZLM3YtSzdzb3Z3QWRBcGFaYVFuaThnQ1hJOVU3bE9iazJQWnZ3OEF0S2plMmRHeUd3V19GRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVEdteU5xWjdLdEI4V2pLUTl0MlN6WFptc0VtOTZRQm14a2JpUUxNOXNTN0t4THI5dXFPNVBhVWVwNHozNGZxY2JpRHl3UHViZUN6M094UzYwRHl2YW5seWx3SHZZbUVMdGZxNXI3dWRrOTd5X2VyYXQ5YkRmLWJVN3pmVVY3T2dUUGJQZlQxdGV2dGM3NUV3U3RDcGRZV2tV?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46014.16496527778</v>
+        <v>46014.80740740741</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Customs Seizes Hundreds of Fake Rolex, Cartier Watches - nationaljeweler.com</t>
+          <t>How Do You Capture 170 Years of Louis Vuitton in a Single Book? Start With the Carry-On Bag - Cultured Mag</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:45:00 GMT</t>
+          <t>Tue, 23 Dec 2025 13:24:28 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPa2JTaTZVWkJpbl96MkFIY2FWWTBoTGpTZC1jTkRGa0N1S1BQZUR6Tm5GU3g0UlU2TExMa1hidHViS1lkcHV5RW9mWUJxSzZaLTcwMFRFYnF3SmdqazFjSmhuQTRVVjl3UUVXZ00tVWxRN2hfNnZXbFlfbnF0OGUyeTRMcU5KbkZQb3E0RE9VWnhXM3I1dFFBM3Nwa2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNc09CMFpuaUMtNlFLR3N3TDUzNzVURTBYWGxWWmUxc05FbWdET0NQN1Z2MG00WXNESkRkejhFbXlwWHYzVk5tbDZGT1dobm1DOUR1UlRPNGI0WDhDUF9HeFQ5YW9MU3JZUnF6VWhsNW1IX2FucjN6S1BvQzEwR3dxUXM5NTV0UEdMWkE?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46013.65625</v>
+        <v>46014.5586574074</v>
       </c>
     </row>
     <row r="13">
@@ -845,24 +845,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sound the Alarm—Armani Beauty Tweaked the Iconic Luminous Silk Foundation - Marie Claire</t>
+          <t>F1 star reveals brilliant advice given to him by racing legend Valentino Rossi - gpfans.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 09:57:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNN0lwR2c1WWdxREx4YVk3VUZDTEV1aUZ6X2UyMUpUZjVDZ2JGRzBjMW1EblhCOW5UaGVtbUVkc1hweWNEc253OFg2VnlNampWSlBCVlVHRzYwQzh1ZFNZWjZ0WHRZRVN6TkI5dUlHVjdMaWRXSV9PTWx0V1hzZjBiYll1Yk5OMXl0NDh4bnZsNjFMbUdaaDE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQVHdYbXZ3bmJVV3lMWlRaMFI5Nlh6b2ZSdXlSS2FoVkU5aXZNNDE0OVcxZVN1R1Z0VW0wZVhTVndQa0oxajBmZEhVTW5hYnVnVnppZ3RUUWZua1NETlZHVThkek0tUHBQdUVJOFNfNEVUS0NhZTBRVVAxTFIyWjk3V3RLUVdQZHZRTGpJRlFvTVZSclctUkJvRGZMUEJIY0Vxb1E?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46013.45833333334</v>
+        <v>46014.41458333333</v>
       </c>
     </row>
     <row r="14">
@@ -878,24 +878,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A-List Beauty Ambassador Campaigns - Trend Hunter</t>
+          <t>Drug dealer with taste for Louis Vitton and Gucci caught red handed by police - Wales Online</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 04:47:47 GMT</t>
+          <t>Tue, 23 Dec 2025 14:07:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE01QlFNZFZTaXR3VjFIaXF5WGlfRjF5R0xjVjd3bmlzX19pUFIyLWdtWHl5azdTRnV6T0czMGZESU5ROF8yd3poamNLRmpCTkswcVRpbzhHOUxPSHJRaWw4WkNGb2d4ZGNBc19vSHNGd9IBdEFVX3lxTFBmRVpIZG1RN0tCWHpYdm1lRVZDNnBaZDk0WmR2TTBNOWJHTEFHcWQ1MDJzOTgtaDdtaGt3dkxvRklSVjExNWNNb1QzSlZmc1dtTkIyeUw5Y3dqUXBvdTRMamFmWDJfblVNUVN1STQ1dHF1UlVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNWFpKWl9aRjR2YTRXSGNWcDhuUjZIdTZTZTB6cmsxUWM4VGdlYWo3c3VHV2FmMk9VZi1GbWVVbEhobF9weThPaVdCcFdyQ2VFVlAwWUtyUnNzVWdLMHNPWWNMRlZUTGFQTmpuNVBTNTVWRDVrM3hJa3NFRUFUb0F0VS14RlZmV1JHbkNfMHBn0gGTAUFVX3lxTE5CTWNkS2FJOXdkNmJESjVxWUxNTlpxLVFfY09PeGRtZ3kzMktheG1ubDBVN3lmbUVlb2UzQzlOYnduTkxyRWJNMUlmNXBRdTU0aTY5ckNCRGJmVUVKaTU4TjhZZTdUVzFHVm5HT1JKeGl5djhNX2JKSEQ2ZndFN280NWU1TGtab0VXSFdsdEhXYXJOdw?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46014.19984953704</v>
+        <v>46014.58819444444</v>
       </c>
     </row>
     <row r="15">
@@ -911,24 +911,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ralph Lauren Was Always Cool. Now Gen Z Knows Why. - The Wall Street Journal</t>
+          <t>Tommy And Dee Hilfiger Share Their Christmas Traditions - The Gloss Magazine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:31:13 GMT</t>
+          <t>Wed, 24 Dec 2025 07:04:24 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingNBVV95cUxOZGNncG1GaGxEc2ZFVGo5R2Z6VXp6aVJpcERzaF8xUFlpcGJmbGExWWE2ekhfZUtYSC12d0txVkx3WGlvTXpzYzBTdnJtUjN5WC11SkdCMkQwS1FfUUZzWkpFOFdBd2JLQzZhblVFaEdGQnYzWE5CZVZlX1hXWC16ek9CZ2F6QWtLTUlBT1owbWx5b0lOX21SX0lJSlNLMmdyYnA0U3BKWVJST3dlajRWak5tLWdYdnJNNkNpZ013Vi1SZ3puSzlNSXBRTEZHclh4a09GMW0ySHp6ODhhcWRVQVBZYkhLZl9tdkhjS0N5cTR1TzU3bE5OUG92cW9OYUJTVk9vb0I0QjVJclpDVUh6YnFfaWpmNDJIT0hlVnI0QjJNUmRoRlNtREhNS1VQbGpGUmlJelBXOUlHNTMxYmRJM0FDelcxVHU1TjBKWkE5eEVPZkNPekJwUk5Tc0J3bm0waG1vUEc3OTkwcENBRzdlcFZZemVMN21IRlh3Ym1JUFNjbGZHczNYSU9VdFZoLWk1TEh3MWFTbkhCZXR0alE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOM2trenF5N3Z3ZG1PQXBiTzNNdjY1UVhIZ25haFV6Q1FyLTBCdGRiU1FnZGFBRU1RNVRoR18yQnItUjVSOXJMUkhyME1iakdMSk0tNjR0TDkyamtoWnZLLW1oTWdwWGhteU43bFZIeVRQUVVhUTlENXNBeDZ5VUdSWm1B?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46013.93834490741</v>
+        <v>46015.29472222222</v>
       </c>
     </row>
     <row r="16">
@@ -944,24 +944,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Forget a Ralph Lauren Christmas—I Want a Roberto Cavalli Christmas - Vogue</t>
+          <t>The End of Flexing: Why Gen Z Is Walking Away From Gucci and Louis Vuitton - International Business Times UK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:36:29 GMT</t>
+          <t>Tue, 23 Dec 2025 09:45:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQbWlpRUhLUXFRRTc4d0dDTkt2MGIxeVAyZlhhbVd0Z0lMSGtzYXNPclJ1QS1kN1pnaUszS1NESnpOcmhYNzJHem5wM2M0alBFeWRBLUZXY3RYelF6SXlQZGRDcUhhYTdGdWx1Q1NCejdGZ0VxU2ZNRTBPZEZTRGNGUDlkMWtsZ1k5Yjl6OHg4c0FPbm16ZksyMmM0aTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOT0Z2QmotYmJSTDI4TVVnT2Vod2RIVDlsekxnbWwwd3JBSmh2a2U5SjNlWFlicFZOT3MtQzJaT2p2SzBQdjNGcXFsNlUxazJkeGkzYVVGRHFpcVZYRWpnTHJPekdPNnNRTHQ5RTA1eEdBcGJRY0lnWnBQdUxBQmJRUXN6ZlQzRHRqczVyWVZMV3NpZw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46013.69200231481</v>
+        <v>46014.40625</v>
       </c>
     </row>
     <row r="17">
@@ -977,24 +977,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Calvin Klein owner sees higher inventory costs due to tariffs - Supply Chain Dive</t>
+          <t>An intimate reading of Dior and Alaïa through cut, structure, and restraint - Harper's Bazaar India</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:04:47 GMT</t>
+          <t>Tue, 23 Dec 2025 12:46:04 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPbC12THg4RnhMUDlHdTZrTnA4dm9OU1RRQUMwcm9YNnFQbG1zTWctT01WOXJlU1hPTjFUT19SQ0ZqeGpDRGlEdXduWjRwQWVJbGFKa2J2UW04ejVyeHdWamZyVEl5ZVhZSWVRRmNCSElhSHdkSl9Oa3F3eXpISXR6UUVJeUk0ZmdXeGFkSFNCSGVEWnJ6bkpQQllGOFB2bktHa2hqWDFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPS0pfNU9Sblp6bUZON3BrcXdYTHhEaUhQcXg4WlRpckxUTmN6R2NFTzBuSDRzX050OVZsaTRwWVl1d1habVBuUm45UW44cGExN1FnSXc0LVFEOEY3a0Z5TG5UTWc4a3J3OGNXOU1MRzJGQVAtQ3pqQk9kQXkwWGJpSk0ySVE0eXNNaGFVRzBOUmRUdlRydFA2ZWdmVTJ6WjNUVkpzb2ZFNjAyWVRvTGdnOThwNHlZM1FmQXBGdUtsVjdheWotZkZWYzFnNlJDYnhP0gHWAUFVX3lxTE1PQkxUd0JxYkdMNGJzYnpSMW90aTQxdXFBNE9kYUp1SWJLTks0bUZqM2EtbC03RDVsb0lzSW1ZNHlzanA1VlU1ckkyNFNuOFBzVDRCVlg5RVdERkZ6VWtfXzlBUWFqZjJxTldnS0pnV2VGci1QSUJVaUdNQVR5T2U4ZXBXWVdaOGxKYU1sQ1BtbnVYSWhHdU11ZFBKUnBWX0tHQV81Y2tEblFwOGZEZzVrQUdVUF90VGMzQkt1Ny1JWEprY2NTd1h1b095bE5kUHEwUzk1REE?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46013.62832175926</v>
+        <v>46014.53199074074</v>
       </c>
     </row>
     <row r="18">
@@ -1010,24 +1010,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Elle Fanning Wore Ralph Lauren To The Neon Holiday Party - Red Carpet Fashion Awards</t>
+          <t>Jung Kook and Calvin Klein find their rhythm in a high-octane ode to ‘90s grit - senatus.net</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:10:14 GMT</t>
+          <t>Tue, 23 Dec 2025 08:30:26 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQdXJKYzZmeUt2MTk4bm4xZHFZbTBHOC0xSHF5Ym5KUU5rdHhQREtwVzUxbHJudk9iVF9rbWM5NGtRN29lS25xaEZMdE1QRFNkX1dpUnZhZFVFeno0M0xVZHNneXB6M3llVjJ1dmFvN0hOMHdWbE1rSzc3RFUtZU9lYmYxVzhycmFMN3dNLU1mTmRXMHJpUkFtamZYQUlIM2YxTVQ0QnR6MU9DTGQt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOdi1RdWFORldwSHRTTzVpRkdhQ0J0WjcyRGh4UFRaYkpsdWExSTlBdV8tMDlMZkV0aDltZGthWlA0bnlnbDBXdE1kXy1NRmZhODUtcFgzWFhBbmtvYm16QmFCdEdmMGpaOEwxTTZ1c0J4bjQ0UUx2czJsZkxDdDE0ak1rVFZxOG91ZVlmVFpYdVhhY1JHbG15c0pSbFNNbTA?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46013.67377314815</v>
+        <v>46014.3544675926</v>
       </c>
     </row>
     <row r="19">
@@ -1043,24 +1043,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Valentino Returns to Rome for Their Fall/Winter 2027 Show - L'Officiel Singapore</t>
+          <t>In Review 2025: This year's biggest C-suite appointments - TheIndustry.fashion</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:56:41 GMT</t>
+          <t>Tue, 23 Dec 2025 08:32:26 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT0NYZEV0WENWaGJZeHdjMTV0NEhFUF93MTF0Nl9zY3pjYWNGOWsxS0l4eDZWaC00UHZPdkJUMUVGalhfcE01TTRURHRhT2VLQTg4U0REcU0taUxFTzFZMXctblhab0pRbkxRZnc3SUtLY01zSHl0cjJWMmFuY2dSTmlROW5HTzUySVYweTN3aHBrX2VOOHRfdjNpNllENDIxRjE2RXYyX1RYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOal9DNmFlaGxpanVXTDdZRWlpV1lkLUFNaGNJbm5DN3g4bGJHT3g1TXJ1b2xLMlBPcDczeGpIa1FHczZxbEVYd2lVZ3ZWTmVDM2VOVGdJMHlYajU2RjRRWEFBRFUzdHVmQjZGdEZydlEtR2trQkFZNWcyYjV3Zlk3TDdQWEhUWVhHOGVaaDhHLUM?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46013.37269675926</v>
+        <v>46014.35585648148</v>
       </c>
     </row>
     <row r="20">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dior Fine Jewelry Editorial - Savoir Flair</t>
+          <t>Elizabeth Hurley, 60, Slays in Vintage Ralph Lauren Sweater From Over 23 Years Ago: 'Still in Style!' - Parade</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:33:35 GMT</t>
+          <t>Tue, 23 Dec 2025 16:42:26 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPMEsxMzJIWndoSWlmOFFzaFZCTm1aWEdLd21TWThQZlJuZVZ3aG9DZU9WOWN4VFZYWFFOX3hYSnl2WEJTdjFYZFpVd0MwY1pVUk4zS3ZucWd4b2lBNnU0XzNuVkJ6c1pnXzd3QVJDSjB0c1NZdFVuc0doLVU1bXhwcmZUMVNTejlfcDVIN1pOcFhzeEJiVkNvRm92NkYyeTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNMEVyTEVnM3ZRMlRKdWlNVkV6NVJROWd1aUZMX1BRQ0FIVzhKY0liTlc1dWl1U3BiYWFqa2VxSEpsN2hTWTdGeG9FaGlTMzFtY1duNEFtRVMtY09oSlFhTTFxeE9oOVpEU1ZUS2lqMWdiSUpMRnlfZFkzZmZlQ013eWVmWkhzencxeVQzTnZtVmwxbEpCT1JuTTlBbVVDLU53NUhtVnVxSQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46013.52332175926</v>
+        <v>46014.69613425926</v>
       </c>
     </row>
     <row r="21">
@@ -1109,24 +1109,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fashion Week Fall/Winter 2026-2027: The official runway calendar - Numéro Magazine</t>
+          <t>Green shoots sprout in fashion landscape - China Daily - Global Edition</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:31:23 GMT</t>
+          <t>Wed, 24 Dec 2025 02:12:56 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWVZJNUsybDFYZUlsU2x4eV84MWs2cFF6X05tcUxpN2RQd3hRbm0zTkVKbU9CUHkwQnpKejVWSGlFOGwxR0NZcG1aeHE3aWdqUHlHR1c1Wm54cWNxQS1rS3BxaUZ5U0FYTHlROGlUakVTYlVJTHNFVnlMM0J3ZTBvano3cWtMVWx6UEJVRXJTRnJBYjJ0dTBPckpxazVOLU8zcGo4QmpVblI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNbzFTLWkyc250WTYzaUFYYzZfbjhCRkU4cUdaR3BFS3JTTzAtNVRNQThlTFpCNHo5aGtoT2ppZjlJaHVWRzJJQkhKYkN3dThkazJZTmt2ZDdOempXSzV3UUJpcU1LeGd6Z1VHd1ZTNkhnY01Yalc2Y2JBZWo5bnR5RTZ3?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46013.60512731481</v>
+        <v>46015.09231481481</v>
       </c>
     </row>
     <row r="22">
@@ -1142,24 +1142,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gerhard Richter at Fondation Louis Vuitton - Arquitectura Viva</t>
+          <t>Large-Scale DooH Illuminates Cities for Christmas 2025 - invidis.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:09:22 GMT</t>
+          <t>Tue, 23 Dec 2025 10:50:34 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd2ZKQXV3d0tUNFFaUUZMWUp0RnVVM1dhWEY2aEJISmQ1Zl9MQ0JIU0VwUnZsWVpfc1c5Q2xndUt0eE5zUGw0MHF3UEVMNjZNc3VqZ1JYWXdkZE43TUoxSDZ2Q2wwRDE5OE1ocUN4SVlkUkxaZkFSN1JZWHVrVFdBVjNXX2NORk1aeW0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOVTA1N0kyMG5PSFVKTDJqbWlSeXNLZC1KT0FBb1BacjBCemFFSFVEeDhqdk12VFZTV3lUVTcyeW0wODF6ekJNVm1sYjFjTUZweXV6MmlDSHZVYzM3eURYcndKTzZSY3pOd3N6eG5oclJNOV81emEwNzd2SWFyYTFKUVRkLWdvN3RMT2c?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46013.50650462963</v>
+        <v>46014.45178240741</v>
       </c>
     </row>
     <row r="23">
@@ -1175,24 +1175,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The Best Designer Bags and Trends Worth Investing In For 2026, According to Experts - Marie Claire UK</t>
+          <t>Mariah Carey Shows Love for Gucci With Stiletto Boots in Aspen - WWD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:42:59 GMT</t>
+          <t>Tue, 23 Dec 2025 16:22:25 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFA3eFVKLXhoa1NaekhQZUpvVzBvS0x3YUUxbUVKRG1sX1FUQ3hwVzNYc3dzNE1lTC0wZFM4RU0xeWN3TzhOWVJ2Y0hWTTFfUWRyTWczRU9NdEtEM2ptUnhHaFV4ckIzRG4zWndQTWZfMnNId1QtUDlDWnhPWmQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPTDlTWnNXMHE0U2lVNnB6QlppSmpObG1mVjM3TVU1ZDBkZ1VuNU02dEtGempaX1FiWm51QURhTkZlV3hVSDczMmdzSnJDS2RjSnpoY0RIazhsYkxqZmM5Q0lGT2k0WkJQR05kTmZPWEhxRU92ekloTVIybjdkZXdfR2d2XzlJN1RweGhmQQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46013.4465162037</v>
+        <v>46014.68223379629</v>
       </c>
     </row>
     <row r="24">
@@ -1208,24 +1208,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The 2026 Kings' Cake by Louis Vuitton designed by Maxime Frédéric: hazelnuts elevated through the iconic Monogram - Sortir à Paris</t>
+          <t>London still looks rich – but its wealth is slowly leaving - Arabian Gulf Business Insight | AGBI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:35:36 GMT</t>
+          <t>Tue, 23 Dec 2025 12:40:49 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQdTNZLUFJNHR1MEtLb2RhbmI2WGVRalgyajVGZjc1am9ZeXB2U04ySUkwWnphaXAwaDVnU2UtWTdVLW1TdGVJUXA5dHFQaHZfZGN0aGR0UFNWaWhaT0tMSVV2YlV4U1Q0ZDVMZnRCTUtFZmV6QVFXdnR5My0zaFlWa191SS1hMGpsY05GNnVrZHdwRm93OHVJeGxKaEVvakt3N0tmYlN6WWRaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNaEtYSG01Qk1KaVFqTlp5anlTTkpabjNuZDdyWHZ6SGZrZnhLUG8yZEhZZloxaTdjMG5BTk42STZkOG52YUxiNXRMR1RYWEZCeTd4eWphUnhxczRTYU9ETTJBeVczeXlHRkZZVEsyOUJpcklFRUdSUGg1V3hsX3BHY3RTZF9lc2FCMERIOFNHcWVha1lxblVwc0pQbV9qZkhaOGlWaQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46013.52472222222</v>
+        <v>46014.5283449074</v>
       </c>
     </row>
     <row r="25">
@@ -1241,24 +1241,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dior’s New Addict Perfumes Have a Seriously Starry Line-Up - BusinessToday Malaysia</t>
+          <t>Louis Vuitton in Seoul: A Multi-Sensory Journey Through Culture and Craft - Luxebook India</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 03:23:18 GMT</t>
+          <t>Wed, 24 Dec 2025 05:49:50 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNRkd3cHFWWFJhek1VQmVyZVV6REhjYlViWDk2dENqOEdBcEItVVRrczVtRC1XTUtSYms1VEJGeUJnWi1QZ3J6QWtlRFJJTUpJajZMR0plcl9WdUVWZW1OdU1OU3dzZ1hYV0JKZG5ZSzA0MFp6MHFjOGtaYzlBcHJFVTk4ZW5ZWTd0WlptRGJHb2t0eGx6N0Z3X3RtdzZlMnhIaERzRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOVVc5WEZqc0JRSjJ1WVVnNEN3aUVWVWJSbVBWdlRqMjh0dnowaUFTYnlJN3RlQ3dvaFlkVWFUTjJDeEM1b3BwUndSX09iRHpnZ3pTdVZib1hDRmwzeHN4TGY1dkxKaGVVVjV0QVZmYkdxWExac1IzNG8zSThGd2djVXQ5ay1qTGtzQ0RhdUdqVHBfVGpmaVVXVw?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46014.14118055555</v>
+        <v>46015.24293981482</v>
       </c>
     </row>
     <row r="26">
@@ -1274,24 +1274,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How Product Roadmap Could Affect Suvidha Infraestate Corporation Limiteds Future Value - Retail Trading Trends &amp; Budget Friendly Trading Ideas - earlytimes.in</t>
+          <t>Elevate Your Winter Holidays With The Bicester Collection’s Festive Magic - Travel and Leisure Asia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 02:02:02 GMT</t>
+          <t>Tue, 23 Dec 2025 07:33:50 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPMGpuOFNDcVpiREkwYkk2ZEZMcVZBTXNOa293aGZHeGdCdGJnenhlZUV1dzNZZWF6QWZmLWl0U2tCeGpOMUZyTGlmLWR6UVVyaFBnWUJjZHgxMVZLcmJIdmQxUVhMb2hIY3dnWURDRUhuSTA4UnRNMmU4SThOUmxjTnpKV0MxN0tGOUdqakpOY3BrTkREM3hDVU1MN2dzNW5oOWZzNXBWQlFjQ1BrS1ZXREtGVGsxNTZtNXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbUpJcXpvTl9MMFphQmpzY0N4SDdiS09fZUdNMm50ME1VWmxOZzFtdHF2c0l0UXlhSE1PQUhpcG9BOGZsSkZUdEJ2a1FVajRsRmkwdmp5NWZWbzdwMEYtUlRUUWN1NVVvbjRPMWJXWWlXTDhEN3B6WlV4aEQ0eEFhdE92SzkxNWJOLU9qMGtQRkt3MWxOYkt0Vm1WTUpiU3pmeFN5ZFBtZ1dDdWdScWhMY1pfWnhXbi1oZWg2WEJFTUcxbVNY0gHKAUFVX3lxTE1OLTNwZHkwdk5vX2JKaEM5WWpMOWlvR0ZrRUg5eXhfZ2hRdTdQX1loZ0VGZU4xNDJYWjdtNU9WVWw3QkhMdU40cmx3U2tWY2owUnlLby1uNW5QMjByUEszb0pxZ2dFV3JDVnVVcWVIZmN4aDlSX3pjYkl5VVFlZjBWYTNZdEpWcEE3WE9TT2lFTXNnTWtXZW5BTDFnOXlNMUdQTndZSzduX2ZUamxvN2lib0dFM1VXbVo4Y0FJeWdPR0ZxZ1hnUjN6TGc?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46014.08474537037</v>
+        <v>46014.31516203703</v>
       </c>
     </row>
     <row r="27">
@@ -1307,123 +1307,123 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B&amp;M European Value Retail (OTCMKTS:BMRRY) Trading Down 4.5% – Time to Sell? - Defense World</t>
+          <t>REG - B&amp;M European - Timing of Q3 FY26 Trading Statement - TradingView — Track All Markets</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:00:26 GMT</t>
+          <t>Tue, 23 Dec 2025 14:00:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQYlhGX0pYMmh4Mkk0MWNIaEpZX3hwajdlNHl0M3dPTExsTE5DU3hzZmJQLUpPemkyRlNuWFVxUnNET0NzQWtfdzdGajlibWpLcFRsZ1dCWjBTWHgyTGJESi0wVl84cHVCNkI1ck82bnRRWmNzM19hWmdjX2V0S1ZObUstYVp6RnhXS0xYSDRFTWNVdHNCa1o5amZkWXoxVE05SEoyMVZKdzhlRmt4cjVISFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPTWtJU0x0alhjRkNKTklVZV9tR1N3VDhVMTVJOEJDWVB0Z2pleUxiVUZKaDBMSmxGNmV3Nzk0d2pSd3phTDRjQy04eUVsRFc3ZV9pZVVZOWNBdFA3M280SzNIS3Rad3lxeWVtRzhjU21iTnppd1ZvT2ZhWUFPcWtXRDVhM2xhU0VEZFRwSTVMWHZCQkxZSDMxNjJ1N0JYV3ZuOGQwRVdpSGpVYWRYQ1cwVWhrbTg2RDFEb0g4aUl5bUI1SVZQNGlR?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46013.45863425926</v>
+        <v>46014.58333333334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Everything you need to know about Amazon's last delivery dates for Christmas - GB News</t>
+          <t>What Analyst Ratings Reveal About IKIO Lighting Limiteds Future Value - Retail Investor Activity &amp; Free Dynamic Profit Opportunities - earlytimes.in</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 00:11:05 GMT</t>
+          <t>Tue, 23 Dec 2025 15:40:10 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBTSGM4dDlSVGRGd09CYjlwQXNBSmpPRUpteVdxQm1USDdmbV9yRFpjdlY5NEpTc1BZV3BGSTZGZVp1M2VhS0J6ajRyZHRWd3FkQTljRVRHNWJldV9kaXprWWlhaVpnbVprcXQyZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRV93dzdUWThaeld5ZHc4Q1NVSGdMSE05OUJ3N2J4dzJOVHJ1dWh6SHY1Z0Fld19tTVpIVldrcUlJSzZNQTZPRkxWVlZTR2lQcGZuSUNFdHJENlh6RXM0Y1RQWHd3RkJLU2JvOU83eTF3VG45V2Z3VTU4NUNRMFJ0NTJoYlZSVzQtUFhRT2dCN1c5UU5GRVgtWXlvSDR0U3JiNk9Z?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46014.00769675926</v>
+        <v>46014.65289351852</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Woman pleads with Amazon after botched Evri delivery - Oxford Mail</t>
+          <t>New Strong Sell Stocks for Dec. 23 - Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 05:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 09:54:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUTQwWTVJMExwZG1WRVFKdzBBS3UwaVA2YWpFYzR1SGVEeXZ5bVFQRTBLQ0lPaW9CTjVBdy1FOHo1YkJYdG93blBKeUdIblhUX09HaENCSS1Yd0daLXRpUGMwREtMdEsyRlBNcUdJSmxfc2haaHdhMU14Qlc1STVEY1NDa25UMjd6bHJBVVdlYTJFNEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9ZeDdkX2RmUFBDVWRvSFVkOEFnS2tmMmY4anFVVWVjTlFreGdZc2JhY0dxWWRjZW14RW9RN0JMbmlTZWJiX3IxX0lFU0VqbHp1NlJhWlpTRFhEb2l4MnF4d0d3dVJNaUc5WkNPTnNXSHRTUjRhMmdYSi1zNDJ5aFk?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46014.20833333334</v>
+        <v>46014.4125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DHL Supply Chain Appointed by Siemens Mobility in New Multi-year Contract - DHL - United Kingdom - DHL</t>
+          <t>B&amp;M European Value Retail (LON:BME) Shares Pass Below Fifty Day Moving Average – Time to Sell? - Defense World</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 23:53:33 GMT</t>
+          <t>Tue, 23 Dec 2025 10:07:13 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOeDhqeENxc0tRSGtBckJnSlhKa2NzUElZUEFTa2FZaks3cHdWQlZwVHB5S3FxZ3AxcFk3TS1GOEkwdVo5UG1hVVMtallzNlUyNDJFLVREajdxRUxQcGtUWXJDSllwWUV2c0E0eVcyX2FtUE5kbE95NUpGY1RRN294UHlnMmw0bi1ydkpiY3Z1Q1piWXBFel9DN1FoMjVZZWVhekNNMVF4MFRuUDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOT1FWNUt4SDNvN2J1ZEV6Y2d1cm1BOHREMElhbkI4VG53V2Y5dWtHOEhIYzJSbjM1eTlTZ0F0aEFEeGdScEtfWVNYbmdsb3ZqVVJ3OXZiQ0dUc2pyR2RxRnp6cERDVjlpVGFZMURlanZRXy1qTzl4NjNzdGlIQjhDU083TVNEeEx6aDZhVUYtbUtNLTRidHY5QWVRLWRvdjF1SVVBbzByQnhrQkR5SG9ZYlZXS3RoT29zWDFyS2RpVmhCSFl3UUNWMVVsb3A?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46013.99552083333</v>
+        <v>46014.42167824074</v>
       </c>
     </row>
     <row r="31">
@@ -1439,24 +1439,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>We sent five Christmas packages across Britain: Royal Mail, Parcelforce, Evri and DPD - only one arrived on time and unbroken, so can you guess which? - Daily Mail</t>
+          <t>IDS.L Stock Today, December 23: Royal Mail Hit by UK Delivery Delays - Meyka</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:53:40 GMT</t>
+          <t>Wed, 24 Dec 2025 00:08:32 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPSWJERnJaTUNQVk1GanVJbDJCeW5LSk1ESGN3SGt3WnJ0OWhiUC1TSS1MWWtBZXdZYnZTT3RXbEltWnJBWGRwTnRyUlBFYVg4a2FTR09YeFUyLUIxbU5JVkFKTVlJRGktWkp5YkxYRFhfaEUzZHhwdmEyLVJzTksybkh0SzNiWHlqaUQ3Wlh1Z1NhVU53X2tCcHNQWmd6a2PSAaQBQVVfeXFMT2xBdEVGcElEdk1JampRLWNBTnl5di02dXFZaVRFeWI1SlIzc0xPYzJPeWZKWlJ4Sks5UDZmZVJ6dTYxdlRMSEhKTmxpeWQxcmdHbUpkbkllRUIyVWtqM1Q0RkdQQTd2LXNrVjRTM3BpNEszTFN4YzNyOTY5NjlPcElBLUM1SFVlTlJ1cXZDUTJ6OEptbUk2WGlNZ05nR0RQNXlfZjU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNc2drSjNSVTJLZWxzdDZVX09mdjFhT0xlOVhBcHhENW40NkxaeHZ1NmpvSnN4NEdDbTh3U1N1Zm5pQzVSVFRJeDJXeU10d05zVVlNTEk3V1VqeVNNQnFJMmFZay0xb2xyRHZlT3kwOG9fdTJsdFdQQ3hQaDFXbGoxb0pGRFlEeUx5c1NhVktSbjdkamRldWp4a2dR?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46013.70393518519</v>
+        <v>46015.00592592593</v>
       </c>
     </row>
     <row r="32">
@@ -1472,24 +1472,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Delivery driver arrested after suspected Southampton parcel theft - BBC</t>
+          <t>Siemens Mobility awards DHL Supply Chain multi-year UK rail logistics contract - Global Railway Review</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:26:33 GMT</t>
+          <t>Tue, 23 Dec 2025 11:37:04 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE4wcEpCVGkzZFRJdzJ2YldaaXB3cU9kLUNtdUpOaWNObmRxclFJeTVueExTdjVOWlFjQkpycXZfN2RiZVRmVm9pQ0JqOWpJSzVXQklxNUNkZ0wwYi100gFiQVVfeXFMTzVoTGg0a0FYMW9GQm1hQnRTNG92QVFDVzN6VEhKSVlyUF9CSEk0THNPaEU3NGdrelJER0luYVdobVk3cWJpYlpQSnkwYWhfSGgtMmZyY1FjY3NSZHB6OFUtN0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOa0J0R0xaVzNydm1oWl9KTno4blhMT25BWlgzY250Uk45Z2hiMTJtNUhudmRNTk5fcUVqUXlFLUJ5dHZCSFR0b2FDcnpNOWVLLXd3T01DQURKVnBGeU5qYmJadDFCS00xcHJfRFJ2d284QnFodk9MU2FXTlhQMVA2VWdhM3E2MVo4TlBRYWNIVWtHRlVEYjhGS2c5QnlBZjFvUUhZZTI5OEJycTJIR3FJZjUyZHNxenhJNWJTRlN0bk5DdXhSR0E?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46013.60177083333</v>
+        <v>46014.48407407408</v>
       </c>
     </row>
     <row r="33">
@@ -1505,24 +1505,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Evri sack delivery driver as parcels go missing in Wiltshire - The Wiltshire Gazette and Herald</t>
+          <t>Evri driver arrested after 120 parcels stolen before Christmas - The Telegraph</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:13:37 GMT</t>
+          <t>Tue, 23 Dec 2025 08:55:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPLXhaRUphQnFkaWFWU25UQ19kc1ZXMExDX2VUS1lJeURBZU1vdmpGX3ZTODAybWw4SWk0SWllZGZjMC1DVl9jZUNrU3BOYVFZZnNEN3VDbEl5VEJUODhGV0hqQUdFcEx2SmZSRGZHbGh0bm9HQlJ5Umt2UGY5SmRTWlpTRU1QTXZTNHZwUWF0S1RqbWxUakpOWl9VOFB6VG1uSmRZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQemZBM096bEZZc1dzczRtdmJ3SHhKUFN6dl8tN2hIMmdxazFJMWZpMjVocGRrdDVkbjNEUlNYdzJCbEY0Mm1KWXM2bXA1ZXZDbnNjR1JnaWVIWnFmSHZkWWN6RGRfZVRmLTlKbnpjdGlRSXZLMzFCN3gtUWxpMld4czNVVGp4WkM3bmJ1UzFOVzBzM1UtVndyajFmU1ItQS1HRE5z?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46013.38445601852</v>
+        <v>46014.37152777778</v>
       </c>
     </row>
     <row r="34">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Evri employee arrested after more than 120 parcels stolen - Daily Echo</t>
+          <t>Newport man’s anger after £800 gold bracelet goes missing during delivery - South Wales Argus</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:35:56 GMT</t>
+          <t>Tue, 23 Dec 2025 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYmdfRUh1elJBMzNBYUxDU3pkS180cWFfbDB5LWcwYzdiaWgwN2lfRWl1SlZyZnctbXZkUnFKTFNheDAtQnM2U1ZIbEFQX2dHWHBudjJjMnp5SzV1WWtQMmxmTGpBMFJ5Q1FwVWxfLUtCd3VrY2ZwZkhXNF9nMHhfWWdUT0x4UjNDdTVQSXRrVE9LZEVJR1FSOGx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOckxPOGFHM1pMQ1hWaHVKVGdxeG5yZzF4cWhBTUxLNEFQa0IyOC1nNUxBTENyTXlQTjBxemVkeW1WR2NHVTBYaXhEVUU4eTk4Q0tyUFM3MTZOTzEySHBzOE5FVFRJVGg1cmdaSGRhb25iYjJTcVlHejJJSzAxWXkyeWZYTDJFR09UZHd4QWJHdzJYUWpWM0lYR0FZTGlzZjhqZ0E?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46013.60828703704</v>
+        <v>46014.66666666666</v>
       </c>
     </row>
     <row r="35">
@@ -1571,24 +1571,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Amazon Now Delivery Push Could Boost Its 2026 Outlook - MarketBeat</t>
+          <t>Missed the Christmas delivery window? These 9 gift cards will save you at the last minute - TechRadar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:17:33 GMT</t>
+          <t>Tue, 23 Dec 2025 16:05:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObkFPR18wTlQtOUp6SFFrRWlUMHpqVGJEUDhmVXZ1Q1N0RV81WUIzTkZ3QV9XNFlPWVR1UWdGNHdicTA3VWx2Y2xBTVMtUmRKeFo3SDRhRU10cER6dW1ZN0p5VTdLNURkQWE3eldnbGxhdGEzNlJNeWxJdS1DVkpwWlFKc091VS16OGlpeDhlVVNEWW1GdVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOVnNHLTRIVi1FOUNsNXpJMWFjZV82OUU2M0NUU0pZeWswZnhVSVFDcnBVVG5md1otdlFaQl9UeXpIZU1CWEY0eF9ZM3FvbUNad25yRU9NZGFlQjJWWmlSZVdCbXJKX1R4R01IZ0VfN0cwX3l1S1dZM0g0MXFSMXVXNHQ2U1dOYy1NQVZCaGpONFV3R2xBWnBkb2RoZ01aaHh0cGhWVktyM1NjTm8tWlNHUzRqblFjSzg1WlVCd0JaOE1mTXIzNUdkaDgxSmhWS1BQQU9paFhWMXRXanRIY29sN1VOcmRIcmtm?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46013.59552083333</v>
+        <v>46014.67013888889</v>
       </c>
     </row>
     <row r="36">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Christmas ‘ruined’ for nine-year-old after delivery driver puts present in rubbish bin which is then collected - Advertiser and Times</t>
+          <t>Fast shipping has environmental impact as delivery becomes more polluting - PBS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:42:00 GMT</t>
+          <t>Tue, 23 Dec 2025 18:29:32 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPZ3JJWEVSR3MyeUhMU0V3eGxzalR3Qk5EN3pjdzZGaUhlUkpYQ0tDZC12OWdpWllDemVZSU9jT2FwUjJ3eDRMT1FPUGx4dE9GZWxjSUpVdnBrakZXRURQa2oyV21EQkFVbWt3MVZyY2phdkM3VWdaZTVJUERVLUJVLWYxRUtiY3ROM0dTRTFMYVlUYmJNeFhMNFI1SEtpdWpTR204TmdUZVdLRjlZckE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOVEs3b2k1X011RzJnN1lCSjRtT212ZGoteFFxbTgyeUFMeUpJQ2JZaVNpMi0wSHNCX3pYVnFfN2NIc3VOa09NQmdxWGpCTG92bTNndnZLdnFDSVBqZl9IY2UwTDlEN3U4Q19PRGhPYWNsY3dEUzFVT2F4YzdwOHRuUnlQTHNXbXB4YVZLQmZUZnpGS3RnMTBmYmg1Q3F6VnJoQlNnUmRwaVNGZEI2akE?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46013.44583333333</v>
+        <v>46014.77050925926</v>
       </c>
     </row>
     <row r="37">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 23:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 20:58:14 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46013.95833333334</v>
+        <v>46014.87377314815</v>
       </c>
     </row>
     <row r="38">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Linlithgow MSP visits Royal Mail Delivery Office to thank posties for their hard work - Daily Record</t>
+          <t>Adidas sale is live from $12 at Amazon — final hours for holiday delivery - Tom's Guide</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:58:00 GMT</t>
+          <t>Tue, 23 Dec 2025 20:01:59 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPU3UxTG9relFJaFN5RTFLUllxYWhsUkJYVE5LanB5US1aVXBLWDllaHFVV0NlUGlZZWRXeTFZV2pacTJlOHYwbUFRb0RJWHpwSklVQjVnU1JrY3Z3RDFoMkpxQ3RUZEJGWDM3UE1qczZsM2E3V0pJYXpjT0dQbV84ZWhNTDVHOThiNjFWbUdvUmLSAZYBQVVfeXFMTzQtRmMwNzI5YUQwODRFanJBMTNQbmdHeFBxOWtrR3VNbVM1a2h6R1YyU1JnNm9qdTVvcU41THRVOUtUMzdEaDBSU1NieGNBXzNtclZVUGl2LUlYa2oyT2VyNmZIQmdWQ0tKTDVEZkluRzd4RVNpZWZESDJVdVMwRDl3WnlTbGd4SVYtNWRPMllMRXk4eGZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNWjdsWnhnZnRiNkhTVUhySHo5eHZpTFhISm9LdDRGNG9fazhKT05MWFR0cEdkQ2I1MDF1bUdzQmduVURVNmt3Nk1IR0RIUVh0M2xXOHkyY081OFc5REYwTXgtY3VzNWRlcURDVG5LYnNqQmhsb0RiVjZ4NXpzSC1kTXZUNDFncVpORHlJTjJoZTNtMllMRVVjelltbWFVMkJ5bGVscFl6TWVFaWNuMjNkdFBWZWZVaVE?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46013.37361111111</v>
+        <v>46014.83471064815</v>
       </c>
     </row>
     <row r="39">
@@ -1703,24 +1703,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Amazon selling 'huge' 800g M&amp;M bag for £10 with final Christmas delivery - Bristol Live</t>
+          <t>Man fired shotgun at Amazon delivery driver who mistakenly pulled into his driveway with her teenage son in the car: Police - Law and Crime News</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:48:00 GMT</t>
+          <t>Tue, 23 Dec 2025 18:45:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNeXlRalJyUmkyYV9PT1pJX3lhczVlMG13cmUwZlg2OGFXVUxBYk5nYW9NX2ZCbmVHWEhXUFFJVS1iZmtMRzFoRkE2ME9nQjQwSzVzN01hM0NoMkpIVm1iakxaS296MmZiSTIyeHA4RVBRZV9fZGZsVHp2TDdySFdmSXJFVmxFcHhxY0VVRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNTGdXQUp4dVhjSWdoTEVXQ3JTSDRrelBiSmRfZmQ1WU9uN3J0UUp6SWdsZkdLa0w4MUxuRGJHQWFDcU1zUXFJSXdmeFM5Y2RoVXlPdHNpbjRXQmQzS1M5U1Jwcjc2eWVXSHdISFZ0cHR6X0VBeHh6dFcyTXktUWJ4Rlk4MTAxWUtGZDU4bUtZdlg4VjJxaDVCNFZXS0l5UWVSSnpJeFVSTWNORndya2x4cW9CX0hZTWZ3UFRvR2pFeEJKTTRSN2pyU05vSUtYamhocnlCWG5iTlJYazVBNmQ2Z191ZWtwcnRW0gHuAUFVX3lxTE8wNWF2Mzh6dGVaQlJ3dFpYMl9KVkl1MTJSZWpRaE9HNHFOTWlrVHNSQTdPY2dhYVRfdWNDU25SczRiYmw0SVRsVkotdW1FelpKa1JYb04tWnQ3Y3o0VjlPRWNsdmk1M3RFOTNZcnZJY0dtWGQwX2pzWjljTjR2bk03emdkX1lPa3ZvVXdEdFBhV1NVVWtrbTdXYkVUUzZFcXJyVGxIaVFZdWpOb2FDc0NHWVdMcnZNLXVnOHo3TVJtMG4tS0F1cnl4Tk9zTjJnRVpUeEt0N2g5eVlYdjBJRzR4UVhwVnNyYXdwQ196Q3c?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46013.49166666667</v>
+        <v>46014.78125</v>
       </c>
     </row>
     <row r="40">
@@ -1736,24 +1736,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Amazon trains delivery drivers for winter weather safety - WFSB</t>
+          <t>Shop the Amazon Last-Minute Gift Deals with Same-Day Delivery - findarticles.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:17:01 GMT</t>
+          <t>Tue, 23 Dec 2025 18:22:48 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQTXU0UVNLMHNuTWpnVUV5X09XSWM0SWxrVENlN0w0NmlGbzROOUNDR1hWdWZ6a2RhY1ZMUm9fOFYzSGEwZGtFNHQxQnY0RFJTNEM0cW1hQ28zZTdkNkpDX3hTd0V0UnI1M2xpRzFITUNiRy1VaDk2VlVJTzJ4c293UnExX0xVTXFiTGZjRVNkaDI0U28yVHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPWl95X2RoZXlrbTVPMHhmY1NFbk5OVk01clpKdkx2R0U2V0lUNlZNbmVwS3VZYmdyQkF6S0N6TE91MURnS1NWdmlScjkzdG1rOHVJb2hHUnVmMjgxb2ZxcUlidGRHX09CX0VBNEdtbzlwVWE0QXREZDg0d3ZKeEZ0NEg5Zldiai1XUC1HS1BpOW9wdmc5a1HSAZ4BQVVfeXFMUFZSamJOLVdBdHlVNE94OWp4RFpTMTVSalJvSU11MGpMQjUwRHQ3Unh2ckctR1BmV3Q4c2RreE5PdjlvazVFeXF4cjVuLUFreFloejBPdm1kcEMwQjBSUWM5Y2RDYzhCNXhGQ1Q4ZjUwLURYR3ZaVXVwbnQ4b0tIek9QS3ptYW5YMW9mYzR6eGloQTdUQ3hTRDMwMzgtSXc?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46013.9284837963</v>
+        <v>46014.76583333333</v>
       </c>
     </row>
     <row r="41">
@@ -1769,24 +1769,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>‘Then You Get Termination’: Amazon Delivery Van Hijacked, Crashed - MotorBiscuit</t>
+          <t>‘If You Have A Package And You Know It’s On The Way…’: Ohio Amazon Driver Calls Out Homeowners For This Common Customer Behavior - BroBible</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 18:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 23:46:20 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1tcTc0aXVKUng1Vi1lR1RySmd1S2stRWEwSHR6M3hBQW1CUUdERXowTXZSQ0dhd1ZoWWpoNm9Id1lnMl9ZWlJPem5yeVVsSEN3NE9yeG9HZnRGWHVvTUt5VjNDU0xNUlBM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOWDBPUkptcGhHdEZvQWVIYWhCQTlCajVuMU01aElqemI3ZzVWM3IyMS1ZNjcyUU1zOU95MGZ2MC1pcl9ucXhmUURTYlB3eUdMV1V3MmppeEtHWV9feUZ0aEFWeWN3QW04WDJNdWZGQVlUZk5XQ0pLNFBvQllsVDhxZTJ6TDlPUzI0OXIteA?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46013.75</v>
+        <v>46014.99050925926</v>
       </c>
     </row>
     <row r="42">
@@ -1802,24 +1802,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Amazon Stock (AMZN) Today: OpenAI Talks, AWS AI Spending, and Ultra‑Fast Delivery Set the 2026 Debate - ts2.tech</t>
+          <t>From Amazon Route to Altar Call: Pastor “Brad” Catches Consequences After Spitting on a Black Delivery Driver - The Daily Scrum News</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:27:50 GMT</t>
+          <t>Wed, 24 Dec 2025 00:22:55 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQcS1jSkpMVlpqM09aSFNFYmdBSkUzajI5a0tlZFdCWVdNXzRiZUZXVVRXaXp3S0Q1QkNiZXo3QlE5R0NINmx0YjNYWmJ1Ni1uYWg0a1QzUDRzazNrZEJaZXBFOUk3OTluME9yU2czb3dKc2FFYl9xUG9IRmVmSTJFTEpZWkZGd1ItX0VmWDhUMnI5VFRUUDB1U0JrZjRzU3ZpWXU4NE9OVFVqQWE2andEM1NDY0JDSi13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdEJPZEtkNjBBbDNGUlViSm4tcXFISjVyeTNFcERGYWxRSi1CbEpWQXNQNFNoU2xqVmZJNWtrbGZnQWY3UkdDeDlZTEZSX3RrVHNVUVZ4a1pSRDJKRzJiRndiU1dmeHdoV2ExM1ByTDBiaEVWVWQ3Tl92SXlLVmFYb3NHTWRKXzVYc1lONG5BT2lDOG0xRi1nTEVHeWR5UlI1UFZhVU9xckV2d1BPZENHa3NqTGRNb0pJZUU1WGxuUlJnNVU3cFF3Wi04dlBNaEViOTdQdWdqOUQ?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46013.68599537037</v>
+        <v>46015.01591435185</v>
       </c>
     </row>
     <row r="43">
@@ -1835,24 +1835,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>What's open, closed on Christmas Eve, Christmas? Stock market, mail? - The News-Press</t>
+          <t>Amazon Delivery Station coming to Perry and Weatherford - KFOR.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:01:00 GMT</t>
+          <t>Tue, 23 Dec 2025 23:17:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOWUF5dWxDeHhvSWZOaG9BdU1SekFad3NPLUg0Rld5M1RFVVhQRFZiamFudWVxRFV4c1FNUW1waVdEVVNkU3pfZHpJcUx2UWM0R2puN2lBNHVNUkhIdG93MkwzUEhldTlUM2Zqb2pQZnN0REFqc0ZYV29kajk5QTBPdzh5MVpGOTA5WklIX04zVHd3d3pkUDI1OE9oUFk2eXFGU2lzdnZNbnBlQWNjaXc4aUFybFJPbUc1VmVGVDR5YjZaUDdIcFdjWHFTS0NOUDVQWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOR2RiU2JMcWNmQVR6clB6S0NqSElVWExIcG8yQUUwRXdTU0NFa1R1b0lDd0dCVEdseG1YU0JDV3RFcGJoNlhQLXpHQS1LRzVWOHlLQjVOT2lSaF91enNoUTBYbloyRHdZaFNNNy0tblZxMXlSVEdBS0VLMEN3NkVfQWJzWHF3RXliZHNlZtIBkgFBVV95cUxPek85ZS14cEJmTWt6TzNzZVh5SHIzb0haQkl0cTg1ZXFfaXVUWnJPaVdfS1FkcVc5Rk1GNnhKOXZMUHRndWRHQzJxUThBcXhBWWl3YnZOT3JPa2pGRHd0QldJdHZ4S3FCYzhZMGl1WlBia05jMWlhWDFqalRfeHNLZU5Mankwb1hvRWEwUmpMdFN4QQ?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46013.58402777778</v>
+        <v>46014.97013888889</v>
       </c>
     </row>
     <row r="44">
@@ -1868,24 +1868,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Adidas sale is live from $12 at Amazon — final hours for holiday delivery - Tom's Guide</t>
+          <t>Grammy winner Ricky Kej says delivery agents refused to carry TV to second floor; Amazon apologises - The Indian Express</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:10:13 GMT</t>
+          <t>Wed, 24 Dec 2025 06:39:55 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNWjdsWnhnZnRiNkhTVUhySHo5eHZpTFhISm9LdDRGNG9fazhKT05MWFR0cEdkQ2I1MDF1bUdzQmduVURVNmt3Nk1IR0RIUVh0M2xXOHkyY081OFc5REYwTXgtY3VzNWRlcURDVG5LYnNqQmhsb0RiVjZ4NXpzSC1kTXZUNDFncVpORHlJTjJoZTNtMllMRVVjelltbWFVMkJ5bGVscFl6TWVFaWNuMjNkdFBWZWZVaVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQS0NNMFpkU1hWWmFtX2RObWswRnRJZVZPSGlaaFpPcTFHQ1JDNXNsNnNWZzRqeEJTYWVBRG4yUm5RazJhbGQyYzRoNW5NQVhPUkdERkJObEhUNWlqdE53ZGZoMjQzejBDcS1Gc3JMZlA3Sy1Rd1VmNFY4RV9ISEM2QnVqQXFKWU9jVnRST05WVGFraGdJZ1E3cHpiMUphRTJHY3dfZkZRS2h5eEs3S1JCWjRiUEJaVlFLUTRWdFVrRzNoZmZBN1JiOXVpdVpYSFNiQUhIN0FGM0czSm9kQ2pyNm1rRlpFeFhKVzlZeE9vUWZYOFowTGMyY3JRQ09WZ9IBhAJBVV95cUxOU3pBY1dVOEtZNHNsMXMtYkVRM3gzV0dyR3NfNjI0S2dvWUxUNG5OZVJuZWlGYTdhUGpiUWszWlhERGpsZWdxcTZuVEc0emFEd0ZKUElVcVl5YmFveE4xRnZkRUpkS29mNE9LTU5yclBDRnUxaFZDOU1jN2otZEVkWnBFaDU0UjVmWTVpZl9PbkZheU9USXpjcXliWjZ4cWFrOUxMTDl3ejhoTTNMSVIycUFndndqbzZZd2dlMHdOWXprUVlWUlhaM3FGcTdSV1BxUlQ0YTNmVFBfanRydnVZcXoyRVVDMDNZU2pPTmh1ejFCWGNuZVFJUFlzdGdBWG5rZVk4Nw?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46013.54876157407</v>
+        <v>46015.2777199074</v>
       </c>
     </row>
     <row r="45">
@@ -1901,24 +1901,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Video Amazon delivery driver arrested in fatal road rage incident - ABC News</t>
+          <t>Amazon trains delivery drivers for winter weather safety - WFSB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:37:34 GMT</t>
+          <t>Tue, 23 Dec 2025 12:52:22 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNakJNTV9qaFJTXy04S2hkY2NocU1MdnpuR2FIcWZrcFhVQm54UFNRLVFnNExfYjBxblM3YlVGZ1oxY1lJR2l4YjRzbDNCTTdKUDh1Qlljb1lzYm9CS1FTQzFqNzUyZndGZDVPSDJIVjd1RkZSelBjNU1rYTF2ci1tZERTdHRyY1FZQnU1MV9oalRob3BYaVhaa295U2VQakE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQTXU0UVNLMHNuTWpnVUV5X09XSWM0SWxrVENlN0w0NmlGbzROOUNDR1hWdWZ6a2RhY1ZMUm9fOFYzSGEwZGtFNHQxQnY0RFJTNEM0cW1hQ28zZTdkNkpDX3hTd0V0UnI1M2xpRzFITUNiRy1VaDk2VlVJTzJ4c293UnExX0xVTXFiTGZjRVNkaDI0U28yVHc?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46013.7344212963</v>
+        <v>46014.53636574074</v>
       </c>
     </row>
     <row r="46">
@@ -1934,24 +1934,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Amazon customers complain about packages stuck for weeks in Armstrong County: "It's there to die" - CBS News</t>
+          <t>You Can Now Tip Your Amazon Delivery Driver for Christmas – at No Extra Cost - People.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 18:07:06 GMT</t>
+          <t>Tue, 23 Dec 2025 11:00:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPZ2xzeUplZEVXUDBlbnFhTlROaWF0UU84cE92eFhQZTFWME9YakhORlRGVk1vdjJRb3JWYmFZdlBqMGNzSHVtZFYxdTBMel9EcFl2VGt5bjZTYUxLTnJTYk10aXdiSzZveHNiMUJQNlhzQ1JhQXk4VjAtWFhrcUtCUldlMGFudw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNLUxIRFVJdE9qS0tpUUJrczdFeGtibUhJaHc4aDBKNlFGNWpSTkxVNHNITnozVURJZ2s3QkJnVEhmZTZERE9SZ2s0aTA2VWc5akJiZnJwQ0kxdkdnYVoxWkhpQ0dFVDhIdkpwN1RHWk92cTRfc1BKWVVlelM1TUxTTHJvSGdJQ25pMGc?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46013.75493055556</v>
+        <v>46014.45833333334</v>
       </c>
     </row>
     <row r="47">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Amazon Mexico Hires 8,000 Seasonal Workers for 2025 Peak - Mexico Business News</t>
+          <t>Samsung Galaxy Buds 3 FE (2025) Crash to All-Time Low on Amazon With This-Week Delivery, While AirPods Pro 3 Ship in 2026 - Kotaku</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 19:43:10 GMT</t>
+          <t>Tue, 23 Dec 2025 12:05:37 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOTzRrOW01MFcxZXMxdm1uc2RYejJ2dVRNZHhXZnVxR1QyM2cxdWpNTTdmM1FoZVk3bVhsNlJjbzdSLTNMNS1Ibi10YWs3SHYtUHFFejNXQjlhaGc0dEFobHl3TnJCTnRfOXBENEo0cGdacG01MTY1bk1ZRF9vdGs4LTJEbmxJdGVXcjZHbDFaWG0wMkpTaG5SUEl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxQSWNaUnUzZWg0d2JseGpTTG5pbEY1RW41Y2luSXRkUnoxWWJOUDF1ZDcxb09ROGV2X0huVXVsc2xtbm1pVFo4dklnQ2piRC0zSlJBR2l0QWNJbHNzZVFUWnhiM3EyWnFsUllwNXdlX0hqSU1wRnlEb0tnQXJ2bVpSZGZRZS1EdkdpY2FuOFA4aG4zQnpfTmpLQ0Z1ZlhvVzRNVWNRNlo5R3hMUWdhMnJKVkxfVjA1V08zM2hkOTZyVWVwYklBRE5YLTlZU00zWm9nRk91eW1fQ0QzemFNdzFNTVBhNW1aZw?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46013.82164351852</v>
+        <v>46014.50390046297</v>
       </c>
     </row>
     <row r="48">
@@ -2000,24 +2000,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FedEx questioned for hiring hundreds of H-1B workers while firing US staff after $2.24 billion federal co - Times of India</t>
+          <t>Options are narrowing to ship packages for Dec. 24 delivery - Spectrum News</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:35:00 GMT</t>
+          <t>Tue, 23 Dec 2025 15:42:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwJBVV95cUxQVDQtZlowV0paSWJtMUwzci1vRnNDY0xUSUxveEo5Rjg5QkdJMEJURFAtMHEyNmdKZmpKVVpacmNFczB1cUJzOFV0RE9jM0QwUjlTR1FfREwyUnFMcWV1RzRyd1p1dmtUcVN5S2sxUllVUFNDT3ZpdG1HRktmYkJHbDdfeUU5SE93NVczYXZEdFBNUUs5N2NNcFNMM3RMcWNNcHJHRmdKWkRfSThVZkpEVnVKNVNhMW54VDNXM3lEdDNlTkNiYWZLSlJkaXNhbGhHRFRsRnVSNHBzTVg3N25fTjdVRDhSVldBbXlULXVjYi1mcDI4UDRNcDBSb29zUG4xelNHR3c1NFk4Rk50SlpQN3FxMUtNcE5FVUZZeHR0V0EwVmZlVlg3MDJnbEtZUzVHbENwNzBGVm5RWFNjZzdSM29UUdIByAJBVV95cUxQLUE4X2poVUxCeWZPcW5BQUlMR0p0SlB0dFBMS3EwZjJCUDBtTTBmOTdkbmRyX0g4b3AxNFEzTDFHRS1KYmRFNDlONmEwY1lUWlh6Rl9CYnQybVhvZlZGZWdCVTlWWkRvQS1lRkM3a0lSR280Rnc1WUdadzh4QTFwNWk0OEVwWkdDcXl6RnA4OUpOaThQSnAxV1dJNjR3andUOWxwWG1JN3VyU2xFaEx5dkx5VjRiRm1lZzc3aUMtajN4dzFyTjd6SkF4MzJDcE11cWo0dTJ2UUVHQU9vSmp2TmdsNGlleDI4U3RudEdyV0FZMi1HakZlZzliOVBOYVRrUGNoVFJuTjZVS2JsblBuWmNsdWl6QVZhQXNXZnMxLTdoQWRHVDE4RmJkeHFVSFc2M3d6N05qcnRIV2xPdDYwSDFxb2ZWOEdM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNY0R4TU1wcktReWo0dkpUNU1VM0RuT3FNVEFsejI0ZFdqUkI2YW5LUUxhb0RLbFIxUHB0cERQcXlMQ1FPeENpbnUyOW1ONU9GSGxjeVZkS3p3aHQ1Qm1kMHNjbDg1SEpBSGZJalZsR0N5cmZHOFNuenNOWFlCZk96NWo4c2tpeG1uM3lhWm84cWxXY05lSWVoSmhGYnZnX0VmaGczOQ?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46013.85763888889</v>
+        <v>46014.65416666667</v>
       </c>
     </row>
     <row r="49">
@@ -2033,24 +2033,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Amazon delivery at dawn leads to gunfire, Coweta man charged - The Newnan Times-Herald</t>
+          <t>Amazon-backed delivery robot startup RIVR puts its tech to the test in Pittsburgh - Technical.ly</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:56:00 GMT</t>
+          <t>Tue, 23 Dec 2025 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNdzUzcnFPcFpjdWN3SGdXTUtRMXptcUdjQ2hDM2k0OVRoNElPdzBtdlo3dGhEaHFzajluQ3A3QnRzTkRFSW9rRzlkekhGUWdmUDVvODdCcUhreV9wbzNLdEpxcnFqOTF1S1gzb19Za0NQUTFiRXJMcEg5TXc1czE5RGhoTFB2Y1lGeTV5RFh4VnFfRVBYQzluQy1vOXd4X2JXRFJXMXZ3ZkhJZU9SdTE1UF9NZWJJb0pRZjQ4d01Cc294VWQ5Y2tfenA3Tkt1aDNTUEplb0dtbURFdlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxONFBuTVZ5RXZfejVyc09KQm91LU5UVndjbi1vWF9NLUVyYk94SFpRV190RnpTanpHdE9FdWp5d0Q1X3h0bGpab2R4dmZTWml2bC1kRDNsdEJ4YWF4RmxHWU5tYXZjdnVYR29tQUxFMUhtQktSSmE4bDg3LVlfcVJCaThkR09UanJpZnNUdw?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46013.74722222222</v>
+        <v>46014.625</v>
       </c>
     </row>
     <row r="50">
@@ -2066,24 +2066,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gift ideas for your dog walker, delivery driver, nail tech and more - Good Morning America</t>
+          <t>Amazon reveals mega Christmas promotion with discounts and guaranteed delivery superior to Black Friday - Mix Vale</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:45:00 GMT</t>
+          <t>Wed, 24 Dec 2025 02:13:58 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPczYwRHRmU2stcEVuYVBnSHFlbHhjOUJUbDBELVVYTnJZX2xrX053Y2FQNzd0TWN5NEM0RE00RElNeHZMX051eTV4SFFCUEdONVdFY0hrdlJVMExDcEFYQlo1bjhpZnJScTFqYVdRc1NPdEprNXQ4M1MtUlJWaXl0Qk0yaTdGZkFFMG14ZkRfV3ByMThzbkFVYXA5QUgtdzZXN3hzcVJR0gGrAUFVX3lxTFBGRDFzS0Z5MkwzeUhUMGdNcG12Si1zcnhLdUFvSGs1S21lamhWTFByQWN1MFVDM3NGWEozX1d1ckxLQXJYcVNfYmhCSzUtNlYwV2FkT1F3bDNzYkV4TEJEQ2FaX3FBTFBHZERndVhFSDhGekVYd0RNY0kwcjhiUVhSSGQ4QkRCekpIZE9SVW4yRUxGeERIMU1nOUI4Szg1M1RfbzVMdTQ3UjZHNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPNW9oNDg4eDRRczNxV3BBZkRZQ05Wckg3R19hNHNNSENNeGlaRWVMd2l3X0d4aUFSUjk3OUFPSXBpVVpnWjhwbWctZjVwYjFvTWZCX3hlb2NMaTVDbFlUbnc0MWNQVFJtY1B1RUl1ZkZteVplSmN6UWstd2FxQUluMHhWTHNxVFAzYVpRMlpIQkktbVhTVmRVX0F2YWFJWUltQTkwSS15X1dORDFQNTNKLS1OQUlfaDI2SEZkMnRFYm9rd0d6dUFKQ3o0TzBxVHlKYlhWdGZGQ0YtN1g2b0HSAd4BQVVfeXFMTzVvaDQ4OHg0UXMzcVdwQWZEWUNOVnJIN0dfYTRzTUhDTXhpWkVlTHdpd19HeGlBUlI5NzlBT0lwaVVaZ1o4cG1nLWY1cGIxb01mQl94ZW9jTGk1Q2xZVG53NDFjUFRSbWNQdUVJdWZGbXlaZUpjelFrLXdhcUFJbjB4VkxzcVRQM2FaUTJaSEJJLW1YU1ZkVV9BdmFhSVlJbUE5MEkteV9XTkQxUDUzSi0tTkFJX2gyNkhGZDJ0RWJva3dHenVBSkN6NE8wcVR5SmJYVnRmRkNGLTdYNm9B?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46013.44791666666</v>
+        <v>46015.09303240741</v>
       </c>
     </row>
     <row r="51">
@@ -2099,24 +2099,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unmissable offer: PlayStation Portal for 199 euros on Amazon with immediate delivery - Mix Vale</t>
+          <t>AMAZON TO OPEN DELIVERY FACILITY IN WESTERN PA - WCCS AM1160 &amp; 101.1FM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 19:03:08 GMT</t>
+          <t>Wed, 24 Dec 2025 00:50:03 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNcUl0cGhVZmFDdVItbUZWQjNnRF95Zm9WNXlwWFRUVGZyb0NpZ3JVVjdTeHFSeDhDVjg5bjg1Um9RZHNjdW11STlGNUdza3NSUGR2NU41R1VsNi10cFFpZnRFS0FGYjFIS1E2aDVqZXRVVHc3SjMyM0hmWG42RHdaUVppLXZlSG5xYVNMMndmRWZDdDBKRVhwSThERklvRmVxZmdNZkRnUnNlSmRvaDFLMDBNb214Q0IzV3Jxa0FtWVZqOHpHcGVUa9IByAFBVV95cUxNcUl0cGhVZmFDdVItbUZWQjNnRF95Zm9WNXlwWFRUVGZyb0NpZ3JVVjdTeHFSeDhDVjg5bjg1Um9RZHNjdW11STlGNUdza3NSUGR2NU41R1VsNi10cFFpZnRFS0FGYjFIS1E2aDVqZXRVVHc3SjMyM0hmWG42RHdaUVppLXZlSG5xYVNMMndmRWZDdDBKRVhwSThERklvRmVxZmdNZkRnUnNlSmRvaDFLMDBNb214Q0IzV3Jxa0FtWVZqOHpHcGVUaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNZkhlY3BEZk00QWlpSnVWTXMzSE5rNjVxU1RSWTFMYXFmTVBxSWh6azhPcHRkV3gtLWw1RVppc0tiOU1CclYzRXR1Y2lsd09xTE5pMGxubEQxX1R0NGNGOHZRWjFzN1ZWN1BEMUZkOENEbjJVYlQwTTZCUE1HNW11YWF0cjYwc2NocnVSag?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46013.79384259259</v>
+        <v>46015.03475694444</v>
       </c>
     </row>
     <row r="52">
@@ -2132,57 +2132,57 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Amazon launches Western Pa. same-day delivery facility - Mon Valley Independent</t>
+          <t>New York AG sues UPS over alleged wage and hour violations - New England Biz Law Update</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:09:22 GMT</t>
+          <t>Tue, 23 Dec 2025 18:40:08 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOUVRpTlJwcEpLYTlPZzIyNC1OcjJtQnZkY1d0YWg3Zjd3UTFRQzBNSUZLRHFJVlh6VFVubnVwTFVoRmhEb21lR2tCVlVtdTFnYzFLWlhsZzFkX2pQdWRpS3R2MzNNaDNIZnFITjBwN19nd2VPTUZSVUVZRGRzcWFRbFNaREs0QVhrWURQY0gxQndzQTBxVGM3UmEzaDhSS2xfYjhXVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPN2hZVjhkcWlrdVk0SDIwc1Ixb0pMcXk5Tmx4Rk9PcktDM3NuMEVheU5XbXJFbjNZd0diY3VqOHpobzcwM1FrWFp6dkkyVUJMaXVUaE9WaFRzMF9oUmZPMVAySzR2UENFTlZfN0pwQnV3VTBScUlkbzFJakVDeXZmTHNNNnVsYUlrMjVBRGFiLWtzZFVlX1Q0TzNuTjNuQlpQR0t1RU9HX1c?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46013.33983796297</v>
+        <v>46014.77787037037</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SpaceX test flight explosion endangered 450 passengers on commercial flights, FAA files show - Travel Tomorrow</t>
+          <t>Oregon Cattle Rancher Accuses Amazon Data Center of Poisoning Local Water Supply - westernjournal.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 06:18:13 GMT</t>
+          <t>Tue, 23 Dec 2025 12:01:32 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNdjUtWGtLTEE5bFY2dU95NkdBbDAyaU9zcUhyUzV3SDJ5UEFQRk01NzNBMnZtcjJPZ19SVVZUaThkVnRfaGI0czZjaTVEYllORDBIMDR5Zlo4WmFmWV9ra1gxWkFlbllfSU42dTlQaEw1V3JuSWluYmZNemllbWg0enAwN1M0a1JqZWVFa18yWEhFOVJRYnRPTmFVSElCSmtxaGgyS0I2T2ZIeGVqY19pRkR2UkloS3pPLTE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQZzV5aUd1eXJheXpJXzhUOXN4SHQ1SkRhU0xPNUxPajF5YWp4eVdmekpDQUxKd24zc0FmdEtGM01VYlF1SEFpYkZLNmFfSlp0ajRXaDA2anp1RHp4Zm5LSG5RZW5Kc1Z2UjBrbkNKQkQ3T3p2MzZjdWRVWWxJMkV5YzM3UzlxNG5WWHpXaUZ5YThuVWxDaGNxT1BMem43YV9YSFpSaC1jbElYaWtvZ1E?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46014.26265046297</v>
+        <v>46014.50106481482</v>
       </c>
     </row>
     <row r="54">
@@ -2198,24 +2198,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hinrunde Wrapped: Looking back on Bayern Munich’s first half - Bavarian Football Works</t>
+          <t>Watch: Bayern Munich striker Nicolas Jackson nabs brace in Senegal’s AFCON win over Botswana - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:20:27 GMT</t>
+          <t>Wed, 24 Dec 2025 00:30:00 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOazJXb3ZtQ01lOHpqZTRWbFJlZHEwNGJ2ZHZBYXZKWU1DTjNsUWhrRFdiOEU5Mkd5ek1TVVM3NFVIQlFyQ0x5anMwMFZnaE9ROHVCQ0ZaRnFJTVNpT0pQTFQ2OXIwX2pzMGxnYk1WQUY2TDBOZEp5YjF5OUdZZXg1UVpWTFVwbEZYMV96TTVqclYxbEtudHJiOEtqQXZ1eUZweE9QR1VPZVRwUGgtc1RqdDA0TzFKaWpuc19UOHlidjhxVDJVbzdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOVFpYNVdvUjN3NVUxaUpEQXVMNjFYZTY4UXcxaks5TjM2MkowZ01ZenRZS1M0eVFmSVByYUk0azFfdXlEbHlJbkJxb29UVE9FT2l6Qnc0WFVtU0l1cHdONUJLRHN1cDljNlNlckcxZ0pRY1pEUFpkUDdPdl92Ujdfb1dURGpLNXJnY09mU0JxY3BkZGhiQUJ0SnZGTkVBTVZwcmFrR3l3Vk5yZ09FeHViMjE3Q0Rka1I2NDBxX1UwZG5KbUtzeVFhYWJ2Y1NHaVRtSU9zWVNnQQ?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46013.51420138889</v>
+        <v>46015.02083333334</v>
       </c>
     </row>
     <row r="55">
@@ -2231,24 +2231,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Singer-songwriter Chris Rea, known for 'Driving Home for Christmas,' dies at 74 - ABC13 Houston</t>
+          <t>Transfer Bomb-Schüll: Bayern Munich Frauen player set for Manchester United WFC swap - Yahoo Sports</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:48:48 GMT</t>
+          <t>Tue, 23 Dec 2025 18:30:00 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNRWZPTDVQT3pQR1J0MTA1aFBaaFhXdHRzMWhrNnEwWVFDRUdCOUFXSGZsdjNzVHNiWE93WHpyVVZxTGVFZXZ1bHFnSjl0b241dlVzVW5XSkNaQ0w2d2w3bC1QLS1wcHgyOEctc0RYYzVzQTJwU2YwaHBOTVhuYWZYNS1GRDFKdnFmRlh4QTlxQnE5U05vdEZZSEpNMExHQdIBowFBVV95cUxONHEwd3N1dFJsblRfelRNTmg0QnhaTkFxeXNrdkE5M1NrRkxjQmQ0RlhXS3pVbElfdWdiMTZXTFNmV3N2Ym5zR0tQcWE1eU9Vd2E4RmhqZHUzY21NTVJZNUw4ZEtVZkRIaXd4U3NoOE1MaEYzcE45NnQwVGFzVzNaMk9QV3BKLWpVcUlBRDU3Q0R4QjlVWk1uSVFSc0dMa04wNDA4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNNjR1ZzAxV09ZRzRpQ2JLNUlfekFtajNocEhKWmppUC1nTkRNaUhDU3dKYjdWaXBDMTJLbXZyYWRySktjMzBnSjRIaTAxb0xiZklVNXdPSDZBSDIzdnB6akNQSmpVc3JhSTZ4QXB0dGJlam1Dek9wR2pwNUpJTXRyLW1R?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46013.70055555556</v>
+        <v>46014.77083333334</v>
       </c>
     </row>
     <row r="56">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FC Bayern against Hapoel Tel Aviv: All you need to know - FC Bayern</t>
+          <t>December 22: Cologne Hells Angels Shooting Spurs Police Manhunt — Security and Insurance Risk Watch - Meyka</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:40:00 GMT</t>
+          <t>Tue, 23 Dec 2025 11:12:14 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNNi04c0RXbzk1dGJqWlpHVi05RU9ISUJveUpHV1NFMU9IUU51ZzNoQk5qQ1k0UzV4THRJQnd2cHlxM0QweEdFYUQ2UV8zb2x0LUpwa1drRF8yZ2UwNk1CS2Q0UUhIbnU4T0Z3Y3ZmNWx5WjIyMVd2dWhoVGJSbjdlczlNMTBBSkRLTjhqQlUzRW4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxObVZrWWxZWXBTWXk1UjBrZjZLRjF3Z1RHQjdkWjBBbmpkMG9yaWlQWXV1TlU1d1ZuWHdSQU1qaTVyVy05Q0IyMUl2MGV0MG0xMnRoU0Z1N3hPUUsyMEludnhham1wOTVMZmxKclZjenkzVTRLdDZvT0g0MTlGWkJ5QmZ1VFRPNzVzZk5ybEhQMHJ4dEluLTl3VzQyZUstcmhRVS1TQ2NXOXMzcXVLVHRDUF9Tcm5WLU40Q1BsXzdjMFE3VDA?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46013.56944444445</v>
+        <v>46014.46682870371</v>
       </c>
     </row>
     <row r="57">
@@ -2297,24 +2297,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Goodman Group, Canada's CPPIB strike US$9.3bil deal for Europe data centres - NST Online</t>
+          <t>The Return of Total War and the New Munich: Russia’s WWII Tactics and Western Appeasement - UkraineWorld</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 01:05:45 GMT</t>
+          <t>Tue, 23 Dec 2025 08:27:49 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPQzFZQnpnYWFYUHVsU3hfM0RfaXZFeDBjcDdTMXg5T0ZoWjN2MFA4TFVXYnctUnEzdWxPdFFNZWdoNG9TbnJKa29hTThObnlDMjV3SDhmUTFKT19SUXdGZ051SFFlMHk2M3FlTzVVdGQ5V0xBTDkwUmNBa3p2WlRRU2dUR2JkWmRoZml2aTdaYnBwZUE1WmJ0a2hqRXZ4a2h5M3FUSU8xejNQdngyWXFUdjBqTXRHUVZRUWFV0gG7AUFVX3lxTE9DMVlCemdhYVhQdWxTeF8zRF9pdkV4MGNwN1MxeDlPRmhaM3YwUDhMVVdidy1ScTN1bE90UU1lZ2g0b1Nuckprb2FNOE5ueUMyNXdIOGZRMUpPX1JRd0ZnTnVIUWUweTYzcWVPNVV0ZDlXTEFMOTBSY0FrenZaVFFTZ1RHYmRaZGhmaXZpN1picHBlQTVaYnRraGpFdnhraHkzcVRJTzF6M1B2eDJZcVR2MGpNdEdRVlFRYVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9ibTRmSU43V3hGeVd6T0Y3NUExYjhpVHpzbC1XaUJDOU00bzRCaGVocGFFM1E3UTQ3QWpWUVozU1R4MlJsSXgxcFk3b2JkZmJDMEtkdWpObjZ5VWxyYUNZeDlHLVQzaFBDTHZv?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46014.04565972222</v>
+        <v>46014.35265046296</v>
       </c>
     </row>
     <row r="58">
@@ -2330,24 +2330,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ECB to Celebrate Bulgarias Eurozone Entry with Special Light Display - irishsun.com</t>
+          <t>Ukrainian Detained in Germany for Alleged Railway Sabotage Linked to Russia - Букви</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:23:00 GMT</t>
+          <t>Tue, 23 Dec 2025 20:19:21 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPY1ZBSnZYN2lYRnFMWnNwRHZ4a3ZMejU5cW5waDFEa3dqN1d1MFIyQXFKc25pLWNIdDQ2MURPOGtpUkZFU2pkMVlLU0gxNjZ1MmZQemtkRFBvQmVhNW1fNmhuVjluLWtpQl9zbG5RaVpWVmRPSkZMOEoxTHhKUFZ2Q21DbXpCWlIxM3JHMWo4UlhMZTd2eEc0Ml9kbmdPLUpjenFGN3p4MUtSbWJV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQQWp4WjdjOHcxOVlHcXpQZTR5LXZVb2pWcl80YmIzU285dWg0bjM3QkpRUDZnTW1VV0o3QlJHTmNJT3BOX18xUHpLU1ZoWHlvT1ZoVFRUYmdCOWZZVjVSNGhVNGhzcWNZMGprcUxWb1pVREtfeXM5ZWI3T0VadHlZZ3RHUGl5ZTF5WjlwaU13MjRzTWx3emFUejlSQXlXYWdaTFduYzZnLXBFSEJn0gGsAUFVX3lxTFBBanhaN2M4dzE5WUdxelBlNHktdlVvalZyXzRiYjNTbzl1aDRuMzdCSlFQNmdNbVVXSjdCUkdOY0lPcE5fXzFQektTVmhYeW9PVmhUVFRiZ0I5ZllWNVI0aFU0aHNxY1kwamtxTFZvWlVES195czllYjdPRVp0eVlndEdQaXllMXlaOXBpTXcyNHNNbHd6YVR6OVJBeVdhZ1pMV25jNmctcEVIQmc?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46013.34930555556</v>
+        <v>46014.84677083333</v>
       </c>
     </row>
     <row r="59">
@@ -2363,24 +2363,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bayern focus on Stuttgart but Leverkusen Champions League tie looms large - NST Online</t>
+          <t>Trading Bots Trigger Alerts on Equitas Holdings Limited Activity - Stock Price Targets &amp; Free Explosive Portfolio Gains - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:18:00 GMT</t>
+          <t>Wed, 24 Dec 2025 04:35:08 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE4zLWQ0S1Vya1JFSThOeHE4YnMtRVY2VVRWRjBmam5wT1JxNDE4Q2dTZWpPcU5ZX0pRMjZfV3dTdnN1azUxNk04M25wRWRXZy1YT1J3cmhEQV9kXy0xcDIzWnAwZ2FIUmF1Z3dZc3BkSWc1S0F5TmZvQkRmRHAxaVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPb2NGMjN4UmdJMDJXQkVuZUw3bEk3MjFyWFJma0JEbkpfMFVNaENCOTg0bl9kSE1zUWxkQVBjV2J3UGVJZVkyVmZpRGVSdGZmX2N6dWZsMmRZeHNXYktjQ0FpUW9kSnVuNGdwVjl0MWx5YWQ5bGFJd3VFQTI2TzdBUzdMaWhnOHFoQ3lnUEhycDVJZmYtUnN0MnczRXQwNTZp?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46013.67916666667</v>
+        <v>46015.19106481481</v>
       </c>
     </row>
     <row r="60">
@@ -2396,387 +2396,387 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lamine Yamal Launches His YouTube Channel with a Special Nod to Luis Díaz - Soy Fútbol</t>
+          <t>David Ornstein drops €120m Man Utd bomb - FootballTransfers.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:26:26 GMT</t>
+          <t>Tue, 23 Dec 2025 08:27:00 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQM09QTHlBZEJTczFjQ0NJelZHNnhUSHcxV05YdzJldzBaSUpTVVBrUUM3dE1ha1RaeUl3Y2dzbHcxSHhPQjIyRGh2Q0JUczJrRDh3TnFKLTU4UUVfaGpjNXBJRzlhdTZ1VTUtaDdWc0Y0bmIwT3g4ZmtOY0J3c29JQW5KWTA5ZmlJNndzWmpxMTd2SFZzaEU2b1lmOU42VHV5d3BYeEpOdVVlUVVES1lvWldTcE1JNkE2WndNTVlRMHJhOG5iRFNIcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOUDR6UmVOSVBMV20zX09ZaEd4VlZWZVk4SUtRT3ZLUHVtV05oaWVDN1YycVE1TnlfR1Y2WmYxclYyVDNKaEgxYklJMXRXaTV4Y2xYcDZnYkhpM2U4Y2JER25BcUJ2b1JkMWFwSUs3TzVUbTdZbElsdUUtUUIxY3ZqM2NwUS1DenpDTGJwOTZLSE5fY2tITW9Sd1VBVnNCeVJMWDR6ZEZpQ2hGRnNKejRjdjJlaTV5eko3VmdvN2s3UHJka083UmQ1dk9sRjdYc3ZGU3ZvODFHUnJLaTB0WWM4Zmg4QkpHNk91SkJN?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46013.85168981482</v>
+        <v>46014.35208333333</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PETA Twitter search</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Secret Kangol Memo to ‘Do Nothing’ About Cruel Angora Sales Accidentally Sent to PETA - PETA UK</t>
+          <t>Hinrunde Wrapped: Looking back on Bayern Munich’s first half - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:09:09 GMT</t>
+          <t>Tue, 23 Dec 2025 12:30:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQQTYxYjNLY28tQm5FdnZkbEFGUWxGRDFQN2pkRXdaX0kwakR2Y250UlBvTFU4OFBFY3dRU2drTmQ3WEtqTVJwcHVsTXI1ZUxwZDJ6QUVVTnhNNHRUMDB2RmtuOS1majRua25vMnBsRmFVVTZsVkxpQnVMbGEyOTFMbHk5N3hTTU9xZnpyMjg4cWJ2VmFpdVBQTXo1bnZfTEdlMWRfY2hhSnNKaWV3YnBMRzVKVklSM3hNRjJSekt6a0ZJVmFxajFv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOazJXb3ZtQ01lOHpqZTRWbFJlZHEwNGJ2ZHZBYXZKWU1DTjNsUWhrRFdiOEU5Mkd5ek1TVVM3NFVIQlFyQ0x5anMwMFZnaE9ROHVCQ0ZaRnFJTVNpT0pQTFQ2OXIwX2pzMGxnYk1WQUY2TDBOZEp5YjF5OUdZZXg1UVpWTFVwbEZYMV96TTVqclYxbEtudHJiOEtqQXZ1eUZweE9QR1VPZVRwUGgtc1RqdDA0TzFKaWpuc19UOHlidjhxVDJVbzdV?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46013.42302083333</v>
+        <v>46014.52083333334</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PETA Twitter search</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Do corona-contaminated mink carcasses end up in biodiesel? - Wild beim Wild</t>
+          <t>Banaras Beads Limited Price Holds Above Key Fib Level - Weekly Market Snapshot &amp; Accelerated Financial Growth - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:02:46 GMT</t>
+          <t>Wed, 24 Dec 2025 04:30:18 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQby1UZUJsVExubl9uZ1JqMERNV2xOQ2RPMURqdnlTODYtNDMtOG1MRG1CYTZXN21mTFFVSEtVR0Y5dHZoWHhKMWROUXZ2djM3dk9OTkxhSjQtSGY0VnVHSWRHTDFqYXdBZ1FqSFgxWTVEb1JGM3Q0V1VPNlZrWm9qNGIycFNJR0llX0FsVVJVMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQQVNtN0ZNaF9qYWVTcnZMZmJFNjM3RUFYRXFwLUZ0b3pMa2NuRGV3cERzLWpUUVo1cnJuQnIyWjFyRFRQN1A3MXFXU0ZMczVuZi1KUDBWRTVkYWI0bzduUDZtY25MdHpwUHpTNmk0UXNPNmlSRW9SeG1lbEpPWHJTckVJWkpEVGdNdDVqaGtlSFBPeUZGcF92aDROOEFmVTJiZXh3QWxB?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46013.66858796297</v>
+        <v>46015.18770833333</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PETA Twitter search</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faux Real: These ‘Fur’ Coats Won’t Get You on PETA’s Naughty List - WWD</t>
+          <t>Punjab Communications Limited Price Targets Raised After Rebound - Global Trade Effects &amp; Exceptional Capital Trading - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:24:59 GMT</t>
+          <t>Tue, 23 Dec 2025 18:09:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNUmJqbnFpbTRreDZVTHdfRm1qVl96S19HUGhiS1Bnc0VIOXdsdTRSS0pIU1YycUwxbF9fRmxyTzBnNGV6ZVk0dGUxNmo2ZWowOGtBelg2TmtMVjY1dlhIX2daYjNBRV9ud3E1NXgwM2dUM293Q2pBbDdkTWhRWVBidXhfb0VzN0hIVVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPdW54a3UwNlYyck9VaC1xb0V0YkxxU2o1TkhHSFBmcVNDUHlKZjFMdXlmVzRRdHhGUXNJcGFRWF9ScEV1dzVMLTdnM0RabUpRa3ItbFRGN3R5bkVKd3ZNaGdYaFh0VWpEcXZtSjl6LWJhV3VNYUtnMnh2RGpocUJiUTVXQlo5ODIxZjJRSlFoQnJXR0gyUmhlYjFIY0tPTHRh?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46013.72568287037</v>
+        <v>46014.75625</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>This year’s divestment campaign highlights - Friends of the Earth Scotland</t>
+          <t>Top six quickest players to reach 100 Bundesliga goal contributions; Kane, Aubameyang &amp; more - Khel Now</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:44:41 GMT</t>
+          <t>Tue, 23 Dec 2025 13:33:25 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE90cVJ2eGxrLTgwdDZzS0tVaGU1T1R2N0p2dlF4dGVMa0FXZWdDeFoyLUNCd2xHMnliY2JaLUJTcVN1d3hfbGJNUHh2OUl3ckd4bE94Mzg4T2o1SlFoUXNUMnVWRE51bmtGYVVtcXV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOdnVWbllTdEJaSlYzXzZLNURrSVRrQWlVMFFJTkt3UDRJaE40NXdHNzlzWElHLWNHMHNqUF82QTg4VUotWFg1czBzNkdrTUtPNC1jMnVZWDNNNFpPLUtiWW5pRWE0ZWwtVHJBSkhRcmFZUVBzQWZrMHdTLVEtamszcVNycExsR2prdkN6a1BWYTE2aDcxb29yQ1JjLVZEemsxMTF3?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46013.53103009259</v>
+        <v>46014.56487268519</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Greta Thunberg banned from Venice after dying Grand Canal green in COP30 protest - AOL.com</t>
+          <t>ChatGPT Wrapped: OpenAI’s Year-End Review Highlights Explosive Growth, New Features, and Rising Challenges - Azat TV</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:28:03 GMT</t>
+          <t>Tue, 23 Dec 2025 07:30:33 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNZkwtcDRLSmt4SmhmWFo2RXp5ZG1lWktjVVRHeG1wOVFMUm5nS0VxV0JxZ3VxUTVjampJOFBqaFB5RXFLSWU0Xy1QRzFmVDlhR3ZxWlpOVFVNYWs0ZXp3aE1rX2N3YmRHdHh6YlpXWDdZX1ctVFpUTVltZ1NRemJoZHFFb3Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5heWVkZmY0OERUakdTZFNWQ2VHUzF5U0VfMFgtZ3B4UWEwVkItODZreExadmNEYVJEY0RWaFJyZ1hsbTdMUlVRcHAwU0tOS1c2QTdmLUwxWVR4YVI3WUc0UkhxSXgtelZjUURxMno2Tlk?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46013.6028125</v>
+        <v>46014.31288194445</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Germany, German language</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bombe" OR "explosion" OR "unbeaufsichtigtes Paket"  OR "verdächtiges Paket" OR "Sprengstoffe" OR "Bombendrohung" OR "Schießen" OR "Stechen")</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CCTV pictures of two men released following shop theft in Belper - derbyshire.police.uk</t>
+          <t>Today in History - December 24: The girl who fell 3km from a plane explosion and survived - 9News.com.au</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:11:00 GMT</t>
+          <t>Tue, 23 Dec 2025 18:40:37 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOeFRLMWNROU40U3p2RzVFa1NTSWpvR0lTLXZYalg3R3IyLTc0bmpoaE1pNzY1dTdGQlNrUjktb3ZzajFIWHNJYzhoNnlVMmt0eVJwUWtPejVNTzJCZkdsMjl5bHJWbEpzNE9yNkQwcXREZ0dpUnVGSmVQN3NFcHNxWmRZU2RQY21ERTQxTkd5LVdOLWVJbzRSRVVyWTZYWlNfbGRpcV8zczlVZ25TUjVzQ2l6cUxGYXpNSVh1ZGJHYldtcGhRb0g1TDdtZFdfdzh1b3BKWVBXNUtwSm5IMnViNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswJBVV95cUxQdjFOTXhjWUxqN0U0SGxUcDRod2pZaV9kR0xDdFFfVFlPRWF4RU0yeWk2QWVyeHNWUmtvMWNQR01yZ2d4dGdvODdXbFRhT283RFNHRnpWc1JWLUE1ZTRwbGxDQW84MHNDOUVIUGM3Z0hnTlpxdmVvTHRuU2oyZ1FRV25IbFhiSkQ5SEFTdXBWVUlVWWZ5MmxXc3dsRDItX0tCOUJBYVBsR3JZbmM3OE5LUlJnWGRPc29fdE93VUJGZVhRMXpPeGNjbk9YZmRNNGZKdkxueHpFWXdOd2M2U1Q0UXhZYmJ1d3FvdE94VFF3Vzl5UmtyeUFyVkEzZTJPcE1lM3B3UXk3MjFxbDdPeWtUdllpR1VMNHdkb1JuOEJ1RWZEWHVOQl8yeFMtdDhnaXZjWWVN0gF4QVVfeXFMT0VlSFRjdGFSMm1rWG42Ml8yZmFwS2ZEc1lkejBWYWJseUc5MGJjV2ZPWkVTYnNZcHZWb3VabmFjMjhMQkZiUG1VbE10TlBDbUlWNFJKbjRVMkRzUHV5a0t2Zmd0T3h1dmJxeVdSb1BZb3RfdUVTWDdC?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46013.59097222222</v>
+        <v>46014.77820601852</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>15 people arrested following retail winter action in Norwich - Norfolk Constabulary</t>
+          <t>How a Photographer From a Tiny Town Gets Big-Time Assignments - PetaPixel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:06:00 GMT</t>
+          <t>Tue, 23 Dec 2025 16:43:02 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOaFdOWDJUanQ3VFgyc1JHYm5ReXVJZzFMekdiMS1zZEdXOXExOTlNbVFlbWh4ZllwSFJxcVlEVnpJMFhvZTh3RGtSOGVzVmh1SjBUR2E4RnRnWXdGMUVTa0p5aUlONENCTFpHRUJuQTNVRElyZUFWMHJUY2pnQ1dLT3hncG9MVHBWejN4MXNkMTZDdDMxS0hMQnFld3ZVcmxaS0tJN2ZVMU5tOGtacy1ycnljWlRCRVZmUGJXLTRaS29vUTBZYTlj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNaVJFVWwwZzZ1THRXNTNEYmxGZE15WU9MMXFKZ3B1Ry12UE9JZzJYLXpnVWx0YWZmNkJNVV9Kc3FpcTlBdlBvLVBZUUFsVkozdTBseHFDM3FET0tKb1E3UldlQlMta3RSSFVQMFdYR25yNTY1YlRPUmJFLUU2Y3RxQzFobjZLd2lLU0V6OFlwS3FxVDJuNXE3SkxWRQ?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46013.62916666667</v>
+        <v>46014.69655092592</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Police patrol around town in bid to target retail crime this Christmas - malverngazette.co.uk</t>
+          <t>Woman killed on country road named as Green Party stalwart who ran to be Greater Manchester MP - Manchester Evening News</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 16:53:00 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQVDBOVm5iRTZiYVY2Z3NJUjNUYklycmhUX04tNExsSm1vTnNkNVIyY1dtNkRkYnd2eUUxZzRMUFJWUERiVXFTSkxqWFRza1dvOXIwTWtCWHFzZEdEZ05aQ2dCS2ZpcENuQUxjQ3JlNEJsNHpVZjJyQm04aXJsUHEzTW5sYUdTZU5LdHI4NlRMWFBiUzkyOTFMWGI4SFd5TWxf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQZDNrZzdqVHZWcjRPOEtwUkVzcWpHQWhybHV1cFJtUWtWaGd3M19GWW9ZZWdBUjM1VzhXWFctZ0F4WDE3d3AyY1JxMFNMTmlEdkFocUFCVjdraU5YRzhpTlhFNk00bW9WZUtpeU9RT0EwNHl5YTVDY25pLWtYZTlCYlFZdVd4WmxZNXlxSWszNXBUaG5LMzJYS0NrcV9WbUctb2FZZWZiX3pnOWJ6N1lJZVBHS1k1V2FaVDdEQdIBvAFBVV95cUxQZDNrZzdqVHZWcjRPOEtwUkVzcWpHQWhybHV1cFJtUWtWaGd3M19GWW9ZZWdBUjM1VzhXWFctZ0F4WDE3d3AyY1JxMFNMTmlEdkFocUFCVjdraU5YRzhpTlhFNk00bW9WZUtpeU9RT0EwNHl5YTVDY25pLWtYZTlCYlFZdVd4WmxZNXlxSWszNXBUaG5LMzJYS0NrcV9WbUctb2FZZWZiX3pnOWJ6N1lJZVBHS1k1V2FaVDdEQQ?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46013.66666666666</v>
+        <v>46014.70347222222</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Two shoplifters jailed as police crack down on retail crime - Blackpool Gazette</t>
+          <t>British Embassy in The Hague vandalized over UK's role in Gaza; Suspect arrested - NL Times</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:07:00 GMT</t>
+          <t>Tue, 23 Dec 2025 20:10:00 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPQXFHYmFKM1FLYVJoMVNZalRRbTd4d1BXYnlCS2NORTR1ejBWOEVROV9RWFRHRzAwd2xpUDJxdGtTa3hJdm5pWUFlamdwSGFQWndtZkY5SzlBeXlfWVowclhSTE8zNlpIcWl4UG96OGpYbTNINVBzRDBlWUlQZEwwRl9EYVd1LV9CdkFjODhrRWVkeTZXRWQyRXZvQjlTYzlwTFFrQVJKcGxhcldzeVJmQlp5dWNCRlYyb0xjTVNnTW9CXzRKUmJz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNM1pGdk94bEJYMlU3M0FNUnRGM2dKalZ3ak42Q09oclFUVnIwZ3NvUVlnbU1WbnFoS1RJTk5zcHlIQXVhVWZiYWNsRU0zNHRnMW5GSEZ6X1dCLU9FbmFFdzJPNm1Dc1dqUGNIeXdOaWdCMVA0UFZqQjN2bUZmQlJiRlZ6SUJIaC1KR3U4MWplRTFEcGxwTkk3VQ?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46013.54652777778</v>
+        <v>46014.84027777778</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Offaly TD Makes Call For Retail Crime Reporting Systems - Midlands 103</t>
+          <t>Woke warrior Greta Thunberg arrested at London pro-Palestine protest - The Sun</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:33:48 GMT</t>
+          <t>Tue, 23 Dec 2025 11:24:00 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQRnN5Ui1ZVWMyNGF5LU96N3dEejJBdlM2LWM2SlBKeGlVdDc2RXBlc2U5eHZqaVNRZk5PcWE0ZGp0UFFPNl8xSUVuckVNMXI4NlJFeVl3Vnp3dm5pU3k0dTNyNDRyV1NZb3o0anU1cFN2clN5WURfRUdGUE9KQmpkcmZMeFhHX1ZfdHh3ME5PWmlCUGhIdDhxMF9RQUpEa2ZNc2JlRHNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNZ3Q0X0Y4YVFlTWVnTVQ1M19CRUNQai1RZFpBa0JOcWd0YlU4LWUxWTRBZDJWeUhWVnVnNm9PZWlUOFJzaDFPM19COWJMYjhiM3gxMnNLX2Z2UmlpRUViU2h5aVdCeGcxS3BTZE1yQWRQUVYtOXdiZEdGTG1VZ0xScDZacks?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46013.60680555556</v>
+        <v>46014.475</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BBB warns of online shopping risks as Chattanooga retail thefts exposed - Local 3 News</t>
+          <t>Green Party’s Vicki Attenborough Killed in Tragic Bolton Crash - UK News in Pictures</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:14:34 GMT</t>
+          <t>Tue, 23 Dec 2025 18:36:00 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUVTSWZESUg4U2loblhMVWlIaHdONEpJMjhwWE8xZjJkNVF6WGdKVEpXSnhCVjc5d3Q2bjJzcW9HRlFfU1BzUXNFWldMYmV2OXJrZmVHSGtNc3FCTnJHQkkzZ1RRN0FvWi1oeHB4Y0tQZ2NrUFdKQUhUTk9iTUFkRjIzZVJVVmYwZmRpZF83X3RJcDlsLUxEejNrMTZOcnZ3OEctVzVlbTRxZUxmWGFPdlo3SjFXQ3lUZ1U0WV9LelZ4bjExTlFDRkNDZzdDMDlaRkhaSHpoQmFNV0lyczdBZjlMbzRfU2JEZTZtOGJzYlc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPZG1YdjYzQVJMME8yZU9aY0hacUJPc0dla2p4RHZEUS1zc0Zpd2VuU2dwekotUFMzZUtjQVEtbEc4dGh3Z1M5M2M5Tk5CQVNjWWhaMk5JS3ZUODJ1bEhlWlkyNm5lM1JQeTFQT2M1RzVYeXF0Z0hJYm5iaHJVdVEwRXg4Vmh1bXp0cGg1Q21HUHpPNTJ6VlNaRzNDTXVMNjJO?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46013.84344907408</v>
+        <v>46014.775</v>
       </c>
     </row>
     <row r="72">
@@ -2792,24 +2792,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ohio AG Yost and KPD announces indictments in organized retail crime, TCSU investiagtions - WKEF</t>
+          <t>Christmas in jail after multiple shop theft and CBO breaches - Lincolnshire Police</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:26:14 GMT</t>
+          <t>Tue, 23 Dec 2025 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQbzZXZ3pza1lsY0poa2FLcG1FUVJvSTNpWW1kUXJDVmU2R2tNVVpkcTFLNVcxQmg3eHRrMlVCVXhiWGFGcHdraHBsc2pZRURzcWUyVmRiU19yT3FRcFlvLUlVb21UQjUxeVpfRTJNMkZ0cjZkMFh4YllvdnBMdTl4azVmbjRZUnVWMzlJUnZSUHo4ckFlWkdqSUx5WWdpOW15RTh4RWl3Mm0tQ2taWmlUNEJpdW40OTl5RnMyX0FaNmtBdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOenIybFFfSWZNYXVPaWxDR3BNbnFaTU5qYlZiTG5IelIyZEpnNVpHWU1lV252akpjaXFQM0dpcmN4UWJuMVhNYnpaQ29FMVMwMXRrMnYzU2swbVhaRDVieUZZdnliUkppTXpwRTlPNHhXQ0NLVXJSLTlOeGhEZHNPdTJYb0pkQlFSc1lITlg4Mm56dk8zamxfTHlRM1U1M3J4aUxZSWdweXl5WmxPUDQ1WHpRLUV0WGttdnBsZkNqcw?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46013.85155092592</v>
+        <v>46014.5</v>
       </c>
     </row>
     <row r="73">
@@ -2825,24 +2825,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco Police Nab 104 Suspects in Clampdown on Organized Retail Crime in SoMa District - Hoodline</t>
+          <t>Jail for prolific Dudley shop thief - West Midlands Police</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 00:28:13 GMT</t>
+          <t>Tue, 23 Dec 2025 19:05:00 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUEJZbW1WcXVSeWJReVdvcWpia1MtbmRQYWxzalV3ME1TRXc5QXVFNEhxR0hnY0FYT1JUNnVkOW5BbzdUMlo0b2FiZDVRMUp1d0xJOWFuT3R5WUJMQ1gzUXZ5NVA5bzVvdnVzRzZ5NzNzeWJlUWF6UWxYXzVrSEZMUFplYm51a0p3RmZjMnY1Z1lsaTJDTzc0OVpzdlNRaWstYjhLTjZIMVo3ZDEwNWM1VUtOdjZRZTJ5bmlycldBNVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPSER3SndyY2tXb21raDRmY1BBRkFfOEljN0VzOFB2M1l4cHh5OHgzZGRDYlNFRUY0cGZOYmp3cWxtamJhNDh5bm1XMFg3UFgzc0tmWWlrWU8zTmJvREtNWVFNTUs0UERQaXhoUDNDZ2tYX214YzA5TzNCMkJCalh3QXotUzZ1Nlh4blI4a1NOY1lQV3hBUmZSRExJSEdOMDVwckFHbmdmWXRaelR0QmY2UmctcWk?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46014.0195949074</v>
+        <v>46014.79513888889</v>
       </c>
     </row>
     <row r="74">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Greater Manchester Police make 671 arrests during ‘Festive Friday’ weekend - Greater Manchester Police</t>
+          <t>Teenager charged with attempted murder amid spate of retail crime in Glasgow - STV News</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:38:00 GMT</t>
+          <t>Tue, 23 Dec 2025 20:18:50 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPclpHLWcxRUYzZVlkR2FyYnlKZm9zNktFMUJCNElveTNDTFpPb09oX1ladl9KN2hZMkE2eVBxdmpBSUxrRmVMOTdnNzIxekw0UWI1dnZGWWdQbzZvckJ1NHFZZV95YTFJVkpaMU9pTXQ4VW15MzlmaTJZQ1JXYTdlajBBTGNuc3dVbkNhaEU5d3ZEVWZMc1diTlQ1dmNsQjV5U1FjUExDd0ZHZWQzRmtfWTlsc18tSnBacm9YZkxHOXRtTUtfM1lNM19rV2VsbkJEazhaQU10TEQ1UzU3VTR2Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPNGR6S2dMR0wyMXVVLVN0MWV0eWlxT1phZ3dDd3pZa3FQZkJLNXFpODZxNkZnNlZHZHY3cWNqYV9mcmhOaHBpY2FpZ0NyNGxnOXh0ZXVfTFBYc2cyTUt2ekZXakN6cHFhakRDQjZWSWZILWhpdnV1WC1oODhhV2tCd1dXOFdOUGtNT3R2MGo2bDRvR3RYTzE5dGdFVXYzRWRHUFdqR092UXR5djhSRWc?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46013.69305555556</v>
+        <v>46014.84641203703</v>
       </c>
     </row>
     <row r="75">
@@ -2891,24 +2891,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serial thief stole almost £1,700 of cosmetics from Sunderland Boots branch - Sunderland Echo</t>
+          <t>Police step up patrols to keep people safe in Oldham town centre - Oldham Times</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:18:00 GMT</t>
+          <t>Wed, 24 Dec 2025 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPOTNzLURzei0zQXhOaEtpVlJuWVA0TVEwRXZCdURjVmEyN29PUUk3ZXlraG1NVGZiaWNzSXZJYXkyZmR6TFdqOUpla1R0U2ZlTmw5R0Z1MWwydlZxWklyZmhYcUk2Z0VOUFBySE03cjVjVFF6S1ByTWhwLW4tcmxSMG4xYzNUVU1aTUZqLTQ4akxzOW5tUzZqODhjOWRITGlSZ0NVZDE0OVpEa2ZRWkJxWGlMd25UT2ZSUG1JYWtiT0tqZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONDhYMURhaWlvUm56R3dBUXlmRGtJcTVISmtweFYySVR3SGJIYkg5dXgwbUlpRkVSdkpwWkFDaDlEUG5KZU83bUszQ0VNQUpvRVk1TV9vVXROd2ZXX0UwdmZ1MFhJY09VWXJ0ZC1HRV9VaGlrQW9EbGc1b1FVLVhpdlJIRWxFOTU0czVVYWNxaGZUY2tNbHR3R29aYktIQQ?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46013.6375</v>
+        <v>46015.20833333334</v>
       </c>
     </row>
     <row r="76">
@@ -2924,24 +2924,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Congress Weighs Sunsetting Section 230, Putting eBay, Amazon, Etsy &amp; More In Potential Liability Crosshairs - Value Added Resource</t>
+          <t>Two men charged in Birmingham after police stop retail crime operation - Birmingham Live</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 19:08:43 GMT</t>
+          <t>Tue, 23 Dec 2025 11:52:00 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1ZQWJHcmNHSHkwaEYtVFVaTktpR29hUTN1WFdVeU5vYUlsV3JoR3ZuRmYyd2o0dU0tT3R1WVlndFJ2RC1ZVnVITEZpMk91WklOVGZ1YVBsT2VhRWxjSk1HWkJ4ZDdiNkt6Ylpka1FLZUE4TmF5aHI1NUJDMDJhbDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNdFJoWlVWTXJrdlpyeXFnTVloLVhhWDZhakZMQUJQU3NRazdKT09zMHNfMTROLTNOSGVVcUtpeTFuRWhuNWtzVnUyYUpQMEdGS2lCRXZVTHM2emZSWEdoa3FZY3M2TGRzaDVlWVdHN3NGN2tqNXM1WkltU2xoOUJyWEZFdkFVOUlIV2ZuVGkwWGJZZGVVQW54b9IBngFBVV95cUxOM3dTazduVHNLeWRWZE8tYmFVS3B2emd0OVZNcG1PZmlBM3IxZU5mYTBWajRFdDFRUlp5QklpNURxUTJiRnBnUWxtaTRfWUNOVmQwczhJWl9PMGtNWDlnTmNSd3lTdTNrYkg4MjlMRklRSHlkQlM5SlVrV29yQlZ2V2NRRXhLaTZmSFdEZUZudlo2QkJoaHlocFFVVlBIQQ?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46013.79771990741</v>
+        <v>46014.49444444444</v>
       </c>
     </row>
     <row r="77">
@@ -2957,24 +2957,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AGs Unite to Keep Gift Cards Safe - Lelezard</t>
+          <t>CCTV appeal after Ripon shop theft - Your Harrogate</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:21:35 GMT</t>
+          <t>Tue, 23 Dec 2025 10:08:00 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5EQWNGODRyQ0NuQ2dVUjBuY0lxOHRWSllIVEZxNFdrRlJocTQtSHZ4X2U2bW5jVE0zb3Z1eDktZzZGalRaQ0VsT1V0elpXQ0FzSmpqaHNaUGI1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQNWJCVURNdEZmazMyVEl5eUo4RS1XLVlrVVB0RXd0dTZnNXFucDBLTEIza3NhVl9OZHJNNlVOSW1DMm93XzV2T0ZSMHlTU1l6QnV5bGE4bHhGTGwwU0IyMnp5OHh2bXJYczlxTFU2bFJOVkJqd1hQUlBkd1p5M0NxdkI5QjZIcldrbE1FUmM2UzVyQQ?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46013.93165509259</v>
+        <v>46014.42222222222</v>
       </c>
     </row>
     <row r="78">
@@ -2990,24 +2990,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Heartless thieves hit ‘easy target’ op-shops as retail theft soars - Herald Sun</t>
+          <t>Bid to boost police and shop owner relations - PressReader</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 03:47:32 GMT</t>
+          <t>Tue, 23 Dec 2025 17:52:16 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQZ3ZaOU9peTNFQVAya3Nid0JfbWw1UnNWQ1VFQ2tkb1RRVjBWeHZ5dDgzcmR3cDU3ZC14VU9vdVVvaHJXTmV5N2JNdGhpeGx2S0dyZE9jU0VEU3VMNVlTd1JQVGEzeDFzQXNWRXZfVGtsZmRRRW5sMEpJal92OVRvQlNMRGNKNHJKUTNWRkNhWUttNHJ5Nlp6ZWdEcWpJejZhQ3huSzIzaUtkb2NNNWhIME9jOVBVbV9fbV9odk12YURhSFdfR282LWtrUEVjdVFCVlV6dFlQc1F0WnZOMXFGQmJmd3RFXzlJSE9teWhlRDVrbmVTc01HeFBtaktJZ0pDYVZzUkJiVVhXd9IBigJBVV95cUxQZ3ZaOU9peTNFQVAya3Nid0JfbWw1UnNWQ1VFQ2tkb1RRVjBWeHZ5dDgzcmR3cDU3ZC14VU9vdVVvaHJXTmV5N2JNdGhpeGx2S0dyZE9jU0VEU3VMNVlTd1JQVGEzeDFzQXNWRXZfVGtsZmRRRW5sMEpJal92OVRvQlNMRGNKNHJKUTNWRkNhWUttNHJ5Nlp6ZWdEcWpJejZhQ3huSzIzaUtkb2NNNWhIME9jOVBVbV9fbV9odk12YURhSFdfR282LWtrUEVjdVFCVlV6dFlQc1F0WnZOMXFGQmJmd3RFXzlJSE9teWhlRDVrbmVTc01HeFBtaktJZ0pDYVZzUkJiVVhXdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBjMzh2VjVpWUpRa0FPc1dNZ2g3bUtJaXBPbnpaNG14Tl9YUUxxR0QzY3RfWmZFTTNJSDhvWXEzWHdLYV9iOGg3TTFDWThsSG5VZ19oVDhVMHBfZ3hEUXZHTGQwRU54YUJVRzJRMk9WQkZKWmVBZS1wUg?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>46014.15800925926</v>
+        <v>46014.74462962963</v>
       </c>
     </row>
     <row r="79">
@@ -3023,24 +3023,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Burbank PD News Release: Burbank Police Participated in Statewide Organized Retail Theft Operation - City of Burbank (.gov)</t>
+          <t>Man to appear in court after £900 shoplifting arrest in Garstang - Lancashire Evening Post</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 18:50:27 GMT</t>
+          <t>Tue, 23 Dec 2025 18:33:00 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPVFQ2NXo2S0RRS19HcjlxQktVR1RwRnRnckxuYnNXWWoyajk1aWltRWZPR29fcVdqZElXblNOdklLQW5yQWhaYU9oZHhNMFNTbl81cmIzQzlPc2xCeU9fOXNfUElxZXE2Ry04WnN4SW9IMWRwOElvMWR3cHdIVlZVRkhFSnFxbzBpNy1LRU5qOG43c3lueXNIUnZTQUxxYW1EQkxKRHhadm0tTzBNWlktUmRDTDF6R0UxMTRrWTdkWTByUk1VRjhoSmh6OFV6WTFReDlMY1VDQ2dMRkdjRF9iQUdISmU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQTnZDd3daQ0tTZElad0U5REc1SGV3V2pNQUhmbFFEVzlpdHltaTY5VlBIRHUzYXJ5RFFoYTFjWm9OaWVHRTVvSEtVdW8xaWp1d3NLckFoSjZYenMzR0R1MjJ0ellPRXFVNDNtUkxWb1hWQXNUNS1VSlE1YzZEZjN4QmFyT2c5U1BqNEVxalg2ZzlvczU1T1ZqZUg0SWZLeEh2dEE?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>46013.78503472222</v>
+        <v>46014.77291666667</v>
       </c>
     </row>
     <row r="80">
@@ -3056,24 +3056,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Investigators recover 12 tons of stolen coffee from Melrose Park, Illinois warehouse - CBS News</t>
+          <t>Police launch festive season operation to tackle crime and antisocial behaviour - Nation.Cymru</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 19:02:00 GMT</t>
+          <t>Tue, 23 Dec 2025 15:04:30 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQb09jMklUaHBVQmlsUERGb2xhRWdDMzAwQVRuVVp0dVJ1Y2RYVGJhYVNsT1dxLXdqX3RuOWxzUC1jV2ExLXlQMS1JWm5QQmFBdG1KQnNlUVFEZFNiOGExY1U4S0h6MklVYkdEcXc3Q1FHdExDQlMzdUJFcmJrSG9zNl84NjZxdDlTeXNLcTczUFBrS3NZdDE3NG1FejFMOFlIcWZJNVZGalo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNdzdLWEx0bjE5c09OVzQ0OXhaZ1lxYTNlb1g5dGpzVXo4dGZRdUo1WFZEZXVVdzhLblJ2c01hQUJqMHdiVzYydXYweEk1VXZzcmFUbTA1LWplSlFUejU3bF9VdVRibFBiZDZYdjVncHJPdE1NTk5fVlNZRXcwVGJrVmZEWTVnRzNnUGtyb2t2SDZQUy1JREtqdmxncVJtQ1d3MFlUajgtMkI3UQ?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46013.79305555556</v>
+        <v>46014.628125</v>
       </c>
     </row>
     <row r="81">
@@ -3089,24 +3089,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C.C. Citizens Police Academy Alumni Association responds to officer investigation - KRIS 6 News Corpus Christi</t>
+          <t>Multiple people jailed amid crackdown on high street crime - The Wiltshire Gazette and Herald</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 18:40:54 GMT</t>
+          <t>Tue, 23 Dec 2025 10:37:27 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPZFpLbFZFRld0eDZ2Qy1ScWlOTkJ5bGt5aGo2OWhKbE5Md2xoMlk3dDV5eDh4ZGo5UFFSbndNUDRicW9zRWdGR1ptU3FfU0t3NTQzdk4yQnpuZEFXVHk4OW1SYlg4Nkd3VVhUTFBKSUhkOXMzdTVnbzU1UkhHbE1QYmR1QlpNOTZTNFIwQ01PYm1DRC1HcDVzUUMxbmFPZDVNY3dITFJpQzBIUTN0SC13WmpWNzdxa0hMYkllSzBnQnZodGc3YmpqWUJnX1FHcDh1UlN2Q19GRnEtRVR5MGtnS2o1RnJFQ1hLaEw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPTTFlUVUyMzJKc3RPM0RkMVIweFNkTGQxWkNORG4ydTNxQ25JbGx2M3ZCV19jYS1LN21keXlqR0tPb0hCTUFfX1JVRS1RYktEUVFVc3BoRGVEaGk2MjV1THNBZUgyZEhUOXlkVUxDc3BocUR2b2dWbkhtSTk1SFRmbkhCY3QyVExvcGZhZ1NIMkw3bHdmSDFFMnhQZV9vVnpEeWc?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46013.77840277777</v>
+        <v>46014.44267361111</v>
       </c>
     </row>
     <row r="82">
@@ -3122,24 +3122,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Police Say Gang Of Thieves Stealing And Reselling Boots, Other Items - Chattanoogan.com Breaking News</t>
+          <t>Prolific Doncaster shoplifter jailed and £800,000 of drugs seized in targeted warrants - Doncaster Free Press</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:56:22 GMT</t>
+          <t>Tue, 23 Dec 2025 10:25:00 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPbk0wbzBKN1JTYzdkVWhzNFdJMWFUdzJXTUJ4VHd5V0VVcnVoNWJRRWNSTGZNQTZLbUdKMkZxLWFUU2dPTlVpLUxVQkcxSndFVE4yWXpMaEpwa2NrYzNuTHFyZkhzczk2cG9MZGRRREgwMGFlVEcyTHF1LWRnbmFwWDZoUVpjYno3VzBmWlptaHU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObXhsMmlMYXNrWHJ6OFk5S3FpeG5iZ0xBcm1FWlRCcDNjTGpNRndtc0dDVEIwZ2U5UWR0YUNKNTFVb1YybFFwNkx1VmpGZXRxOVpPSERFMEdfUHU3ME1kVzgzekhJSlY3QzlmaWRzRDByUlppWjlXbVVZZ21LYTdaajdmQk1XNEdxSUZkV01CZ21LMWFsYzZOY2JjcXlRWWRvbWdSNjk4cjVjRFd2eHRWdDlhUXJrdkNtd0poeDdLR2tPNmVXa0hqaXRyZFZiWFIxS3hXcm9jc3lOQQ?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46013.74747685185</v>
+        <v>46014.43402777778</v>
       </c>
     </row>
     <row r="83">
@@ -3155,90 +3155,90 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Man stabbed to death in Fitzroy, second killing in less than 24 hours - Herald Sun</t>
+          <t>Record number of officers back on streets according to Sussex PCC - hellorayo.co.uk</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:33:10 GMT</t>
+          <t>Tue, 23 Dec 2025 13:04:56 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPNU9hMGU0TWI4MnZzMUxzNy1lRjJqMzk0SW1SaTFxTXAwRXJHd0FIMVEzRW5TTkZ2YUpZUkY4Y0Fhd1Y0TGwwRDA2VmNBcWxiUDM2aFcxT09QSzBxaHhWUWhKN210QXEtSFlBUTZrcXlNR2lScXB2UmxqSTdQVDVQbmE5WXZuNHc2X3FDemtxWUZHczdUbjVUak5KM3o5clFDSktXWTZGY2FIUWhueHptYlNabWR2R01FR3hHcTNwX0lxOC1KQVgyOUpWektLSTlCeWgzZERGUm9MaXpFMW52ZmdaeHlpN3V0Ni1pd3F1ZkRyUTl6aGdGWDJUc3BfNWFsdW1nM1p4bF8tUURq0gGMAkFVX3lxTE81T2EwZTRNYjgydnMxTHM3LWVGMmozOTRJbVJpMXFNcDBFckd3QUgxUTNFblNORnZhSllSRjhjQWF3VjRMbDBEMDZWY0FxbGJQMzZoVzFPT1BLMHFoeFZRaEo3bXRBcS1IWUFRNmtxeU1HaVJxcHZSbGpJN1BUNVBuYTlZdm40dzZfcUN6a3FZRkdzN1RuNVRqTkozejlyUUNKS1dZNkZjYUhRaG54em1iU1ptZHZHTUVHeEdxM3BfSXE4LUpBWDI5SlZ6S0tJOUJ5aDNkREZSb0xpekUxbnZmZ1p4eWk3dXQ2LWl3cXVmRHJROXpoZ0ZYMlRzcF81YWx1bWczWnhsXy1RRGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQWldBNFFBZjhDQmd6Q09waC0tU0dOWXl6TlBBQjF0eFR4OWRfUktMSUROVk5QUUQ1QmdqVXB4OUw2WmpoVnFCYmRYeGlYQVB2ZVI3OE1jYjYxUVlSY2gyaHBZb25lZlRzb0ktYUw0YWw4R0Rxc2hPeGxZYTVjeExwMno0VmRLUmdlLXpiRQ?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>46013.85636574074</v>
+        <v>46014.54509259259</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Real Madrid Eye Loan for Uzbekistan Defender Khusanov - Caspian Post</t>
+          <t>Multiple suspects arrested in CHP operation targeting Northern California organized retail theft ring - CBS News</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:40:00 GMT</t>
+          <t>Tue, 23 Dec 2025 23:28:44 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOa3otZ1ROZS1ZZk42Q1p0Skh3OW1PT3EtNTJfVnlxUUdVRmc1eVA2MnY2OHB1ZWFyM1laXzVKaXF1VWlRaEtDamlON0FSdE9ZSWItMmlmV0RvcjZOQU5Dbk1vT1NuN3h1RXhTeGhQMThyUG9Ualp2V1U5bzZyT3pCM2hDZHlmaHVGdzVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOZlA0OEhpVXZ0cGRZWHZWVGNzeWdnS1lJNVZfR3VJM1c0UTFJeWpueHNHRWxzdHhTZ1lKMzlybng2MjEyWk5FTENzSC1Ca3FxVm5jcW03WThPUWIzT3hEVmpSTmRyMUNDdHVYR2wyQWE1VmZzS0lLSm9CbFFGTExPTFVaa29VQlpuc2Y4S3dsTFBreEdlODdXRUdhaV9kNGJoeDRybTRiNEw4MjNNc3d6dDZtT0NUa1hCUXhJQ19QYTB6T1Bma0ZzWDVaVUNCbHRuUjNjVGpR?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46013.73611111111</v>
+        <v>46014.97828703704</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Explosion W Retired in Emotional Farewell at London International Horse Show - The Chronicle of the Horse</t>
+          <t>Retail Crime Task Force Arrests 17 - crimevoice.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:07:45 GMT</t>
+          <t>Tue, 23 Dec 2025 18:02:20 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPMTNrZ095MDhuNHhVWjM4ckZyR2NRVlV2WjVpSk52VXdvRFp3blpXczVBTTBkYjV6VTVLSFBwRjFQXzBVTTBFLVQ0Mjdxc1N1QVJtVnJsRnBNRlBReHlkeTdTV0thX0JxSmwwXzV0cFdCRmJkMEZQUjVjdC02aXFPUHV1QW5pNU1iUUF3QXpHTTI1ZFNKUGt0Y0hLZnE1cWpXdEIyZmx1WFFfaXp6eE5ucWtkMXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1Cel9aOFV6Ni1LMWJfRUNzTk83cGczcW9kOV9TbFhjYVZUcmZmZG9zZlFSMTM4eTM1SzAyZnE0WlZNM2tVbS14ekRhdXNIcWx2WFUta2V6SS1yS3BHU0ktUVdQT2xFVVNid2dheGo2YlJPTmVHYjlDTXhtSHRsUQ?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46013.58871527778</v>
+        <v>46014.75162037037</v>
       </c>
     </row>
     <row r="86">
@@ -3254,24 +3254,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Xinhua Photo Daily | Dec. 23, 2025 - Xinhua</t>
+          <t>Saudi Pro League star Karim Benzema goes wild over Endrick’s 2026 FIFA World Cup-driven loan move to Lyon f... - World Soccer Talk</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 07:22:15 GMT</t>
+          <t>Tue, 23 Dec 2025 21:34:18 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1ycW40aG5iSDktNjE4c2xiWkJjbVkwbndDSFZhX0RrNXMwSjBUTkd1V193OVR4aUFVbDc2MFpiRTJfWlAwdXpGaGxjOTJtZVJuMzQwdnNZY2hSTVNaX1poQ3F6bmNHaWtidXlZUGRud2pFbEgxZ3U3a0l5Z2g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQMUZZTFAtUlZBZE9uSTBSMDg3U2FuWUktbGhlSGowaGljSUhUUmxQclFZSHRIQU90blEwbFRkemRKaThjcFZxWmJjS29MV3NuZDNxdWdyUGVoM0dNOEcxRGlvdHF5NktZWW1CZERfcEdxTTZFT2hPV19yeXRJNnNRclhzSUcta2JJMGpRY09XV2pGWUtBSnh0aXlHMmE2TUV3WWNmNG5BZE1VaVJVaXlnREY2cDlHa1Y5V2FQcVpjOHU3TGlNYmJFU3pvT2dfQk1aRVRIWTd4OWN0VlhyTGRoUTJrYmZfVGZMaFFkeUY4M2N6UkJqaTF6LWVCTmZQZndRREpDRUtZc1Jxd9IBjwJBVV95cUxPQWc4TmFkWlRrMklzQXA5X2JsaVY2dmFlWDFfNFZ1VnB2Q1d1N0xpU2Utc0xWWlJkNHgyXzI0ODEwYU13eGV4YnZ4UzB0NlFjWGJnSjlBVjZTdnIyaGw0eGNRTUZfRjdnVzFqRE0tSW81RDN4QUlnVTFHYWFPOUQ2X1lXUXR0ZWVqTEdzbndUdmxVYVE4STdVbTZxY3lCdG9PRm1FN1MydnViUWFqNnpub1RGRmVaSENwMm1tRmJPSmZpYjZNcnpUQ2lDRmVMbWFmSGR3SzhWUU9waWFHTjgtUlN5d1NLajIwRXVQbU9pbzJ1RVZTN2otMk5pSVNodkFKUWFkb3RZWjBJdW9kelJN?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46014.30711805556</v>
+        <v>46014.89881944445</v>
       </c>
     </row>
     <row r="87">
@@ -3287,24 +3287,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Car bomb in Moscow kills Russia's Lieutenant General Fanil Sarvarov - France 24</t>
+          <t>Khusanov at Real Madrid and Liverpool: When is the transfer "bomb"? - Zamin.uz</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:18:16 GMT</t>
+          <t>Wed, 24 Dec 2025 03:28:00 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNQ2hTdEludk1UWWpiUFNTY250NFhEanlmd3ZKaUNUNFMyMkd3UHhLQ0JxMmtQUTg1MS1lSUkwZW05d1Z3ZHB3SjN4d2JEVWJnQWZWVEVjZFZkR1VKYk9sWk85cExIdUE1dFByNW1aa0ZRMEk0cTN5RzJZcVBwbnFFVFBpSjRadDBDYkktWHh2RjhaRHdoOEh0MkhObVdscXZ5WmI0aVZzMWJUeEJzR0hF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUVFhSGMtMjZubmszcFZTcUdQYlhjeHFGWEdENEE0bXJoallPQldoTlgxTG5IMDA4VzBybDBOa29QVmIyNUdsc2RlV29TT2hjZHNTMS1vSkpvclFzWExfb21KdFM1d1R4OUlBeE5nU1l5UGUtTTg5SWFtMi0xckZ2YlNHaEtSOVREaXRHeWNpUmhKQ0V0YWMzaEhfX19LbUdlcHFR?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46013.63768518518</v>
+        <v>46015.14444444444</v>
       </c>
     </row>
     <row r="88">
@@ -3320,24 +3320,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Woman shot dead by car of armed men while attending funeral of star footballer who had also been gunned down - The Sun</t>
+          <t>Films to get to know Barcelona and Catalonia better - Catalan News</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:55:00 GMT</t>
+          <t>Tue, 23 Dec 2025 12:34:25 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPNWxabS1OZFZoRVdtZ09SemNNZERtcHNVdm9iM19ZWW9ONUxqZEpUbEVmT0ctUzFvWUw3YjNUdlpRbUJtRjRZdmFRSUZZOVVFcGJaclRZeE1wUzd2dEcySVA5TmFKbzA5LW0tU0k1WGVUZ3Q2eTFVWW9PbGZwNkhucDFvX1ExQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVGtaYjJzSGFpckszOWJmX0JpWnljRFAxcEZIQ0RpRFk4eF9Vd0pZcDNWQlNETktzbjh0em5YWkV1Zm9KOGJpd3hJM3lKYk1XMkVGdEV4Y3paeTEyb1ZtVGVYZVd5a1d4OG5Ddkd3MXdrX0lIMU14eTNvNDliaFd6NjlydHBXRmVuOUZMakpkTi1jdGZtMVNZbHRwRlZMUGtqNmdZaDhR?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>46013.95486111111</v>
+        <v>46014.52390046296</v>
       </c>
     </row>
     <row r="89">
@@ -3353,24 +3353,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Evansville police: Fatal shooting of teen came during botched robbery - Courier &amp; Press</t>
+          <t>Rashford Quietly Departs Manchester United for Barcelona - 조선일보</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:06:00 GMT</t>
+          <t>Wed, 24 Dec 2025 03:50:49 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOaHBTU1NqUWx3eVBndENkRVRJMkt5M1Fsdl9TR25RcDJvSXhsS3RxeTFxNE1acFJUUV9JQ1pRRTMweHEwQUN1MGwyamxlSnpGc1NuUFZmZ1lFM1JCYkxQOHBhMGZDV2VUWTFoSFFmd0hTYU9qby0yWjdLZUs2SW1iSUV3MEFnNkpVaURBV09aYVhHWDlpQ1huTy1nNzdVWXFVNm5OcGNiSTg3VUF5VmNVTThMMzlUQ3RvYmtiaWQtYjlGSzA5LUlKN09zSnNhYTZ0WGJGSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQWkwtZndhVUdUZVBmX3pUaElVZzUyajdxZWVYVWRGMjBWeFpEcTJ3c3NZbnFiYXJRenN6MHVWdTJOZ2ppSFZmY2NaT2MyaHFCVTBKS253ZXRZNWl0MjRDVExxMzloQXE1MXJabTVSUnF6ZVlEY0p2b3dMaWVwVFJtTGN2UFRwZw?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46013.42083333333</v>
+        <v>46015.16028935185</v>
       </c>
     </row>
     <row r="90">
@@ -3386,24 +3386,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Man shot dead in Castelldefels street - Diari ARA</t>
+          <t>Real Madrid reward youth team prodigy with second renewal in one year – report - Yahoo Sports Canada</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:12:40 GMT</t>
+          <t>Tue, 23 Dec 2025 12:52:45 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQNHNaWEpWSHlpdFZ3eVNzcjktX0JPQWRINS1pOVVkNTlzTnc5ZEVKVlgzLUl0MDhjMjFsMDFXdDBLTzhDZ2tIRXJHX3NhM2FSaVJRYTd6aGZLRGZjNTJiZ181bS1YU3c2WFlUb2JaUnV4SllqaGZqX2JlaDUwVi1YM19UQ0ZTd9IBiwFBVV95cUxPZ0hyMmxmcXhiOXVUS1dzM0tyTHh5R2g5Wnpxam12c2FPR2tCSmJZY0dnX051OENjcFBjNkhPSngxREVaLXFBQVlIWGNyV2NHVVN4Wk1UOWdLekFMT2R4Q3RTUjc0MnhsOFMwaXJ0RF9MS095TUxrZ09XS1VTVWZROXltcFZnSEczMzFz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPcTRZdmtWaEtCRWZuT0JNTGdRczhSNjdRUXFCbHdqdmRTN2Q1SlNuX2IxemxyUVBReUNzOHU3Q2tsdzdrekpUbWQ5eHdhYmg1b2pSOFMtTHJmQ3k4SmppZTZGM3pxUVRMSnJNOVJvdmdYZjkzanVzUzhRZzctTV9pWXZEOA?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>46013.71712962963</v>
+        <v>46014.53663194444</v>
       </c>
     </row>
     <row r="91">
@@ -3419,24 +3419,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Barcelona star REFUSES to leave in January - FootballTransfers.com</t>
+          <t>Red Bull respond to explosive Helmut Marko claims - racingnews365.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:14:00 GMT</t>
+          <t>Tue, 23 Dec 2025 11:00:00 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQ19pMEo2b3Ftdm9NOGtNcjdlRUt6aF9qNjB1Q0ZZanViYUNKcnRtUUZGbU16TDFKaVdTalJkdTNrSXY4VG51akZScnk1ZXc2c0YtLUhyTW00blJFRlRya2RMclVlVl9OYmdfSWhiZDBsMEw4WjdrcjladGZLTU00YjYyU0dxUjYyakpSOG1hRkJ5ZFVHcWItZjJnRjVGaVlrQzZHMTRUSHVRQ244dGNja0tBdmJLNXpueXF5cFZUaEJvRkdLbVdZZGVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNQmEtc2xRZTc4UURhZWVNUmFtU1k2SW5pVFVJSHp6bkNHTnE3dU8yMWN0MDltOGdqMjZIeU9wZ3YwT1kzVXJCQkZDNGEwME13T1VYeGFLZDVtdTlfMFZGS2Nzc0phV21hT3hhOVZnWWNSdDZZVTU1dlB0RVJqeEVvbw?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46013.50972222222</v>
+        <v>46014.45833333334</v>
       </c>
     </row>
     <row r="92">
@@ -3452,24 +3452,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>La Liga: Four things we learned in Spain's matchday 17 - lokmattimes.com</t>
+          <t>United Interactive Limited Hits Price Floor — Bounce Incoming - Momentum Trading Signals &amp; Achieve Explosive Results - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:25:41 GMT</t>
+          <t>Wed, 24 Dec 2025 01:22:11 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPMVBCUWV0NjJBb0V2d3FJTUdSMmFlci1iQnZwa1JtWFhNQXByV1ZXMDV6X2lfOHdJNzRiMjVlY0lYOEVEYmJTdTYxd1d6Q3F1M0Ywd1o1ZDM0WG9NYXBpb2RtN3FIa3EzYXRESDNDUmw5YWJXRmtaVVFUamlwWHZkY3ViTjRxRzI1d20xSFVKSzFuSmRHdHpDUHVn0gGfAUFVX3lxTE9uLVZhV0Z3NUNZVmEwMkRKUDNsMG85eXRiS2F3TTBxVVMwSkVYdGNyYnZybUY3cUFYNWRvd1I2SEZkTHNyeFVrTGdTajVEWmRwaDFreGVyMk9ZaF9kdmFXVUlmWmhiVVdXQlV3MkJFUG9yVlgzSUNGRklzYnRvYWF3N2FCSkpXSVNiRGUteXJhb1pKM3ZJZTBzQXh5ZmZfQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNOFI2NFp3VXpDeFFqUVJNV0oteU5PQ21Xc3lYak15SEdSZkNHUXdhZUt2ZGRzNTRVbFhRQUVJNVhPUGw3MWNQZHgwQ2JTUy02RmRVWGN1b2pPQzFCd0liM1l3XzJVUmtTTFd2MnEwdVpsN0w5VTZoU25pUGx2eHFScDdZNDlTOTNKTExaNUN0dTB6UDRRaDZJdTNVcWV0SlRFRzUtX0ktbw?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46013.72616898148</v>
+        <v>46015.05707175926</v>
       </c>
     </row>
     <row r="93">
@@ -3485,24 +3485,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain's traditional Christmas lottery draw starts in Madrid - Bangkok Post</t>
+          <t>More goals, a dance partner and a bomb squad – an A to Z of ‘All I want for Christmas’ - The Irish Independent</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 04:04:30 GMT</t>
+          <t>Tue, 23 Dec 2025 19:30:00 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNVmVqYy1rYUZ3aXVNMU1jWjZLMjAyc01vMlFGRnAxb3V0X1hPZmhUMG5TQ0VsQWJIR0lVZ2lDdkhOZUZjZjUzMVNXZGZETWQ3UlB3WEpiSEswYjFFcmdabnV0aDRpU0dwUHZpcWhIWnUwNFFKQkVQRTJ6ZUpnZy1KcmwtdHJzUGNKSDU4SHZhVnhOcGdScnI5NldvcWFPM3lUdHZjQ3hLM0JmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTlFfMEphV2xKZnNyR1MzVUJocGJUSnUtYWNVaV8yWHI0YS02NnZVLUFfQ0pqMXYzSTVLNXFLM1pWd0h5TzZpZ2l2ck1kQWFWZGk2eVhWaXlwYmJfX3VrM3ExakJ4b0RJeGt2TmNsRW55andvNEVMUVpSeVFmVFR6WHNuZjFoOUR2V3I1NUdjdm5NTGZCajJfQmt2akxYaHU5YzhFbWYyVXhESE9pU0kzZXQ1WVYyTGFnMjV2eE5ROGp5V3l5UzFXQm53?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>46014.16979166667</v>
+        <v>46014.8125</v>
       </c>
     </row>
     <row r="94">
@@ -3518,24 +3518,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>White Duo Lead Rookie Race After Historic Draft - 조선일보</t>
+          <t>Arsenal officially appoint scouting guru: His first deal could be explosive - FootballTransfers.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 21:25:03 GMT</t>
+          <t>Tue, 23 Dec 2025 16:30:00 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPU2taS1BQS3Z3LWJMREZGVjlxMXlmWmhtZURidlBTUXN1cGVjRXVfSDZDc0xzMEVocGJCM0s3OFJETWg5SklEWUdaZi0zc2t5LXBJV0lvc3lMR2xsXzd6bzMtNkxCNURKT3E5Q28wdVRVdnZTb2t3WExvMXN1VFAzS0E4MHFQdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxNTm9oWTBBaC1RZmxrYVRldmtPUGRaMHNyaVkyUzdzOUJYX0U5TjNxZEZqSlJhM3BnVTU2MUEzbGx4a1RFUzJkUXZ4UVhZTmEtZk5RWkUtMXUxUF9sWlpjNmZITks0dUo4YzFDclJzbk9aTk1TWkxmUWo0cXBVLUwzS1kxRGRyTlFCV2VJeE1fVDhVVmE5c0VHOGpWdFhuSERmZTBnMVZCVkxldlJmeWFyZ1FBYkVlZ2NKSzFsQ3E2M055QnRwVWRPVjVqakVVa3cyeUgxcmg0cW1LdVdMclVOUkJfWWpyT3Npb0dHbVlyOGUxVkFweTBia0d3UHY?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>46013.89239583333</v>
+        <v>46014.6875</v>
       </c>
     </row>
     <row r="95">
@@ -3551,24 +3551,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Florentino’s reach vs. the NBA’s claws: an MVP could be snatched away - Mundo Deportivo</t>
+          <t>‘Contaminated sausage sandwich’ blamed for swine fever outbreak in Spain - AOL.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:25:00 GMT</t>
+          <t>Tue, 23 Dec 2025 20:37:07 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQampjYXJkdG1naFF3ZzIwSzdJcnFmal80NDhoX2FrWUtXbjhfcHF1dklKbFhUcHZFaktnNllMTjk3VEFXcWMwVzBBXzEzeVg0UUgyMGhabnQ3NlhqR3FqVWJLZ2FUc2g1SERaQ1FZaEg3VEczWXlWb2VPanlOdVFPdGZJZm1Kd2NlX0l6VHc3SEhDVW96d0dKN3EwQmFpeDhQSDhrZUN6M0h2dHc4QlJ5dnRoaGFQa0wzUE5EcHpkbXJLLTTSAdABQVVfeXFMUDB6c3hwek4tTk1iMUZIWDBwUG15cE9rY1V4emh2SEZpSS1tZHhCeGF6eG5VVjFxWkpWaE5qOF92WEpKWFFaNTdTLWs2M0g3TVVzN25yMFY0eGxNVlMwTUFfR2dGSHczRWhTWUI0ZFZ2T2twbEJvV0ZDVEg4OWhManJ1YThmWm9DVUFJRERBY1pRNjRxSUMwVHljMmtPMVhSZFNkWFdwV0NnRGRtczViOU1hZWxuNnNXSVpTcjZDN291b2s3cXBDZHMtSGFiVUE4Xw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOTi00MXZpVzR2TGpUX3dQblJMWmdKcmVweEhmcnJBZUlaLXRnMWtITDFESWJYbnlfb1NXc1FHSzQzV3V0TndZRFpLVmpnazlyWFRaZGRiaEJ6S25zSG1XQmFOY0hpZEprOEhiZC0yLTlBM2FsYzZFNEdtaHMwVFAtdkdZQnhlWnBKaFE?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>46013.51736111111</v>
+        <v>46014.8591087963</v>
       </c>
     </row>
     <row r="96">
@@ -3584,24 +3584,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Barcelona enjoy resurgence under Hansi Flick — all thanks to ONE player - Tribuna.com</t>
+          <t>Ruben Neves linked with Real Madrid: "I'm afraid he will leave for free" - MARCA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:21:00 GMT</t>
+          <t>Tue, 23 Dec 2025 18:45:28 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2hpZXUtUFkyTEQxNUV3V0w3SjZieURjNXpWZHJlXzYyRy1SZndIbXIxUVBLSHBDWDhMc1BiTDkyNHhHcFlwd0d4ZmNyYzE0cDM0ek5UWktTWnl5RVdDUDNzanBUSUJjVGU2c2pTUF81cnJOeExSd0x3YW0wZDJtNDVuVk9NbFh4bjF4a040Tm82NWhici1sR2dR0gGaAUFVX3lxTE5HaGlldS1QWTJMRDE1RXdXTDdKNmJ5RGM1elZkcmVfNjJHLVJmd0htcjFRUEtIcENYOExzUGJMOTI0eEdwWXB3R3hmY3JjMTRwMzR6TlRaS1NaeXlFV0NQM3NqcFRJQmNUZTZzalNQXzVyck54TFJ3THdhbTBkMm00NW5WT01sWHhuMXhrTjRObzY1aGJyLWxHZ1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQaGFqTnh6NVV2WkdULVd6X1A2ZGxKUk9GdTAwNjQzQ3RhR1p5X1ZMUHFDSTEtcnpBMjJKczRpRWJ6OFhBOFlFRXQwampKaER5U1ZhcjhNVzFJRjQ4VVcwT3JxaE5sbmJvXzZ3RkRWWXB1V2pZQWxkSWJOSDkyZVRJSjRKZEdPeWxtSDNweU1MMGZtU0s2S1HSAZYBQVVfeXFMUGhhak54ejVVdlpHVC1Xel9QNmRsSlJPRnUwMDY0M0N0YUdaeV9WTFBxQ0kxLXJ6QTIySnM0aUViejhYQThZRUV0MGpqSmhEeVNWYXI4TVcxSUY0OFVXME9ycWhObG5ib182d0ZEVllwdVdqWUFsZEliTkg5MmVUSUo0SmRHT3lsbUgzcHlNTDBmbVNLNktR?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>46013.47291666667</v>
+        <v>46014.78157407408</v>
       </c>
     </row>
     <row r="97">
@@ -3617,24 +3617,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Thousands of runners dressed as Santa take part in a race in Barcelona - France 24</t>
+          <t>Real Madrid gear up for the game against Monaco - realmadrid.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:37:11 GMT</t>
+          <t>Tue, 23 Dec 2025 08:48:00 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxONjlnc3hkNkc0Z0lPcVN4bkpOZXdvMzZvNUxaMHFPU2VISmpRY0lfWFlsamYzWXNMcm40MHY4VWRBOVAyY2h3Q1lhbEVabnJnVGxJWF94UDZNdTJwOVZ2TjF6YmlFcS0wVkVwSnpWMHNZOHFYejROWDFLWkdvLXAtVmZKY1pieU1MYV9jbUsxZERQMFd5QUNJdzdSZklmY1FzZVJDNlRnWnRkdlNRNUo3S2JoTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOQzlLQUh1aWgtdlk2YXFQQ0hEUUZBZ2pFdFRlczlhZm5hbC0yLTNaRGVIcHNYNUdwRTh0eEc5VXkxSWhxRTJMX3JFcVhIdi1OLTFoX1ZHbEM4OXZHZjdwN0QzWF9fa0QwM0JaZzhYNWg1VnlTWFVEamZsb0NrS0E0N2o0NmVJckdGZUxoak9fYURELUNkTlJQNHM0aTBiV1RHQlIzM21KQ0c2UQ?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>46013.40082175926</v>
+        <v>46014.36666666667</v>
       </c>
     </row>
     <row r="98">
@@ -3650,24 +3650,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Raphinha and Yamal fire Barca four points clear at the top - NST Online</t>
+          <t>Police Investigate Bomb Terror Email 10 Schools in Depok - VOI.id</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:00:21 GMT</t>
+          <t>Wed, 24 Dec 2025 02:17:43 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDljdTBRM3lHbXdRX29zcnhSVnkyQkdLanlpMDVDQUU4NmZCdjhFX0p5bFB4MjJjT0N4Q25Mb0Z4UUFycEswcE5iXzFpeTJ2NnozZElUUGFqaTZOTlNpUkgxdkVKdmkwd1Z0Y1VUVDNLMzdMTV84QWdyQzJfREo1Wk9lbUt3N1I1VUJPN2VtRHlaWG1TYVlwd1Z5NnlWUXBIcExtRFRwY2FfaG1QUzJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiQkFVX3lxTE1XbnVBYjBZY1lGb2hkY2xOR2NIa2ZIaDBDeWhqTEpUTFo2aDVELVp0eFRQZ1k2ODBtZC1vUHBkMXZjUdIBQkFVX3lxTE1XbnVBYjBZY1lGb2hkY2xOR2NIa2ZIaDBDeWhqTEpUTFo2aDVELVp0eFRQZ1k2ODBtZC1vUHBkMXZjUQ?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>46013.91690972223</v>
+        <v>46015.09563657407</v>
       </c>
     </row>
     <row r="99">
@@ -3683,24 +3683,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Inspired by Iniesta and eyes on Brazil - Morocco's El Aynaoui stays true to his passion - NST Online</t>
+          <t>Real Madrid's FIRST 2026 signing confirmed - FootballTransfers.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 00:26:50 GMT</t>
+          <t>Tue, 23 Dec 2025 10:31:00 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQUkFDaUhsOXFKazJPS3hQcnJscF9jakdLbnJtcnNGVGNUZ3pCT2tURXU4QUxLcUItOEs1ZlRxQS1zdzZOdzhRVW1xOGY0ckdmVDJURW12eTZ3TnRrbDVyaGRXWmVOUjRoZzFnVl9Db3I3am9RejVHSlhzR1ctbTB1Sk5qLUlVeEYwR3BLT1RZZ0cyN2NkZFZkMUpRTm5QWXlOcUFneS1OV0piMUVxa2JmT2RobUoxdk0yRWNBcWQza3BCRHFB0gHEAUFVX3lxTFBSQUNpSGw5cUprMk9LeFBycmxwX2NqR0tucm1yc0ZUY1RnekJPa1RFdThBTEtxQi04SzVmVHFBLXN3Nk53OFFVbXE4ZjRyR2ZUMlRFbXZ5NndOdGtsNXJoZFdaZU5SNGhnMWdWX0Nvcjdqb1F6NUdKWHNHVy1tMHVKTmotSVV4RjBHcEtPVFlnRzI3Y2RkVmQxSlFOblBZeU5xQWd5LU5XSmIxRXFrYmZPZGhtSjF2TTJFY0FxZDNrcEJEcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPVE5nRkwzUk5qQnN2dUljTXpWOGpOVHRQSFFNUVUwNjNOSE9ReWNHbHZ5Z2RlYTVjdTl2NVdHVGE5Z3NlYVhFaV9DTXRHclpqMk9feVFfdllTWnNaZDV0RDkzSFlEaVZPTjRnZnZPYkhnRkFHaU9wYUxzelhNSVFMVlBIWFNjZFVaaWUtdVJNRVFGZEtHSFlEemN6VVpnZ2lBNlNjTDFtY2FHRi1ZSVN0V05iTWFTZjEtTmkyMHhteHQzeXUydWpKRVF3?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>46014.01863425926</v>
+        <v>46014.43819444445</v>
       </c>
     </row>
     <row r="100">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Neymar undergoes surgery for meniscus injury - NST Online</t>
+          <t>Gilgeous-Alexander makes history against Aldama with 100 straight 20-point games - Mundo Deportivo</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 23:46:49 GMT</t>
+          <t>Tue, 23 Dec 2025 12:24:06 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOMFNmekRHMjRGRkh5N3RSdDNFQWFnb1BxTVBjcnJQSFBNS1BpT1h3ME9lWjBMd2xZS3VMZFJGTm41WnU4c2VUMi1mSE5FRF9meVRLRDhwMU1TOEk0VnZmcm9DeTl4TFRyeXVIb3hHR1BlQ0FRanhQSUlDelJYZ3BCZHNiZjdXblY2WkZkVWNyRDlOa2VDUkk4cldzRWU3d0Rt0gGgAUFVX3lxTE4wU2Z6REcyNEZGSHk3dFJ0M0VBYWdvUHFNUGNyclBIUE1LUGlPWHcwT2VaMEx3bFlLdUxkUkZObjVadThzZVQyLWZITkVEX2Z5VEtEOHAxTVM4STRWdmZyb0N5OXhMVHJ5dUhveEdHUGVDQVFqeFBJSUN6UlhncEJkc2JmN1duVjZaRmRVY3JEOU5rZUNSSThyV3NFZTd3RG0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQZzNQUGE5ZWV0bWQzZGkwc29STGg0cl8zV2dSMnNVZFVjVHFtakp2NFVWT2dmdDlUUVZwclozc1I4NVZOYncxSkxuVTNVd0kyTEdnYk9rZE02RFhNRk1zWjBMLXZqZ0NKM0VvWl83MnU3RVc0QkFSSkxjMXQ4M0FvY3k2a3hvd1pGU0xjUmpaNHdiLTRSRlQ2SkFmUXFndmVhRTVFLTAyRjMxd1k0cVNabjhHSk5lYUhsNkNpQWRJTHBGQ0JfLWtldEw1VFBjVU5MYU40bEF4RTRmd2FVTzJhMTBn0gHiAUFVX3lxTFBnM1BQYTllZXRtZDNkaTBzb1JMaDRyXzNXZ1Iyc1VkVWNUcW1qSnY0VVZPZ2Z0OVRRVnByWjNzUjg1Vk5idzFKTG5VM1V3STJMR2diT2tkTTZEWE1GTXNaMEwtdmpnQ0ozRW9aXzcydTdFVzRCQVJKTGMxdDgzQW9jeTZreG93WkZTTGNSalo0d2ItNFJGVDZKQWZRcWd2ZWFFNUUtMDJGMzF3WTRxU1puOEdKTmVhSGw2Q2lBZElMcEZDQl8ta2V0TDVUUGNVTkxhTjRsQXhFNGZ3YVVPMmExMGc?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>46013.99084490741</v>
+        <v>46014.51673611111</v>
       </c>
     </row>
     <row r="101">
@@ -3749,24 +3749,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Police are investigating whether a Podgorica resident was killed in Barcelona. - vijesti.me</t>
+          <t>SKIL Infrastructure Limited (SKIL) Stock Experiences Sudden Dip - Price-to-Book Ratio Updates &amp; Explosive Profit Growth - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 19:43:20 GMT</t>
+          <t>Wed, 24 Dec 2025 02:55:50 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNd2ttcm84VmFRYTB1VFl5RzlaTFlkTzlycHdhMG1iMnU3U1EtdDljTHVwRUozMHZ3WXc3cTdNb0M0d08yaUN5YmhPMGQwZnlFRFpDUllWeXpPZzlnVnVwR1dqRTIzYUh4Skpfeklfd2lWWk9OcDZaV2NNVUUxUERnVnB6ajJFRUxBOGs5NUdMSkY0d2Fsc2sxbng3NmdCcEZ3X3ljQ19aTGFYa3Q3dG5j0gGvAUFVX3lxTE13a21ybzhWYVFhMHVUWXlHOVpMWWRPOXJwd2EwbWIydTdTUS10OWNMdXBFSjMwdndZdzdxN01vQzR3TzJpQ3liaE8wZDBmeUVEWkNSWVZ5ek9nOWdWdXBHV2pFMjNhSHhKSl96SV93aVZaT05wNlpXY01VRTFQRGdWcHpqMkVFTEE4azk1R0xKRjR3YWxzazFueDc2Z0JwRndfeWNDX1pMYVhrdDd0bmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQS0o5TGRsSXI2VGtVbm1ibVVvMXRqYWJIX3QzVU9ta2VmVFdLRXI5WmswZzhfUnh3dm9LYWVWZm9LRHl2OHR4Rk5IUW8tcHVFS2pHbl9Xb2luNUgyeXlCV0VkV0N4NzZrVk1hVDFzZW50WWFnUHZQSi0xQjV2UkNOOWhVa1EzaWZNRmV6dGVDMXlONDdxX2FEc3BUQXBjV3lVaHA3eTVxbmN2UQ?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>1</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>46013.82175925926</v>
+        <v>46015.12210648148</v>
       </c>
     </row>
     <row r="102">
@@ -3782,24 +3782,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Real Madrid make €150m Vinicius Jr sale decision - FootballTransfers.com</t>
+          <t>Shobhit Learnings and Long Term Portfolio - RSI Overbought/Oversold &amp; Budget Friendly Capital Growth - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:06:00 GMT</t>
+          <t>Tue, 23 Dec 2025 21:40:51 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPSnRvVUFDR3dSXzV0dmhmYUcxVXU0ZDl6R0M3NHpwVDlKWmFXcG5pQTJyR1BCWEdCRGNjRDBJcnc4TF9idU02eERRLTVEaWU4a0dtNzR1WUN5MmNhaW90Z0tBNGJfMFlHc3BpRmk2bkVMTzFORE1Va295Mk5Oekl4ZXNEYlg4VkctNUt6RjFLRk95bFRENjg2dEoyb05BcGRkb3hYWkV4ZVRoM3BsWUVWLXpCVGVEbE9lbjUwdDdHaThWYkJYbU1qTzlYNkdzdWIySmIxVTczT0dzMkpQaXpj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQ0ZoTnp4N1FoY3hZcFV3WmxwcGZ3bUxWNWNxR3g1aEhVamJkOHZudHFvcTlmanhvVndYTzZEaWpkOGZZYUZ2UERHZkFRVnlyc0E3T213WDR2VDNPaC1rOVVvVW5hRkVJQWw0bjlPSkhIVjRGZmtsVlhzY2JMSWpMbnRIZHVGZ0stcV9Haw?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>46013.67083333333</v>
+        <v>46014.90336805556</v>
       </c>
     </row>
     <row r="103">
@@ -3815,24 +3815,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lewis Hamilton admits he loves “eating all of that” - F1 world champ explains his typical festive feast - GPblog</t>
+          <t>Japan's Minamino ruptures ACL, World Cup campaign in doubt - NST Online</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 19:29:00 GMT</t>
+          <t>Tue, 23 Dec 2025 13:53:40 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNeXFXbmpEZG02eGxvOGFiUEMxQm9HMlhxVFI2WUZweWdNNXlRaVNfR3VzX3E3RWtZMWQ0dnRDTU5fcHM3WTl4X3k3aV9sUUtHTWVOWFF6U2l1bXFDWVA5XzQzajktS19ZbzhheEtDdVctM3RlSndWbFhDbHhXQ3QzdExfMzNzY0V0QVl0TFlVNTZGTGRFbUJvSUNaZ1hPOUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNRXFJc0l2MVlvSGVjZXlqLTRveGpkUkVYTlp0WG93SXF3MU9vMmI0ZnA3a09iRjZ6YTFpSDJXNS1LcnQ3bGFJNHVCRHMwQ1pfNGo3WmY5akRQRlo3R2YyNmZkQlJfTTk2Y2lfZHU3UWx3MlRJTmRPN2c3QXJ3ZmdVcFUwRmczZ2I5NTgyaVZ4cXNHMFpNaU9CS3NsVTNlejFxSVlsQlJtZFIwWDI0aVczX3Z30gGyAUFVX3lxTE1FcUlzSXYxWW9IZWNleWotNG94amRSRVhOWnRYb3dJcXcxT28yYjRmcDdrT2JGNnphMWlIMlc1LUtydDdsYUk0dUJEczBDWl80ajdaZjlqRFBGWjdHZjI2ZmRCUl9NOTZjaV9kdTdRbHcyVElOZE83ZzdBcndmZ1VwVTBGZzNnYjk1ODJpVnhxc0cwWk1pT0JLc2xVM2V6MXFJWWxCUm1kUjBYMjRpVzNfdnc?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>46013.81180555555</v>
+        <v>46014.57893518519</v>
       </c>
     </row>
     <row r="104">
@@ -3848,156 +3848,156 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Eli Ndiaye’s rookie NBA season has come to an early end - Mundo Deportivo</t>
+          <t>Bombshell! PSG offers him a blank check to leave Real Madrid, it is Luis Enrique's request - madrid-barcelona.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:20:00 GMT</t>
+          <t>Tue, 23 Dec 2025 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPa2taN1I5LS1UOHAwNGt4allCLTFSbFVZaEtQZkgxeVVsbG8zOTB1QlJDa3FyUTd3bkZKZFNBeFVObXpVX1JiNXAzdUNXMU9iV0lScXRxWW9zRGNXbTY1SlE5aEtBRkZtVkx1OC1EQUpHaFhyN01yejRKSFYzOWVhdUt6ZXBEZThtZ3dGU3NtWGxOMU1jLUJpdlVXd28zdmNBcnN2alJBcnZXdkFaTktZRFlPNNIBwAFBVV95cUxQU3M2SkY2MWg2cWNvZnJGblkwOGN5ZC11U2JNR1YyenR3dDFqNFJnQVdYcVJLZTlodDFGa2g0RGduanAxdFcxUGp2MmVZWWlha21RQktsT2M0dW9xQmJYWkZyZTR6QkdMZEMtRFJTOWNPZlZtYmhQUHRac053UExEUEQ4aGtFbUp5bUJXNVhpU3NFaVRLcTZhSEowNlZIeE51UThVbi1BUTBLbGNtdjNoblQwV0VseGFqblpmM3VscGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNYnlBNzdQQ3laTUJsbURPblYtQU1RX0xieFdZNzVYX1F1ckFnNnZDRjh0cGREc1dqZk9ycU5FMjlWTzY0WHQ5cHdfZVJJdmRNRkRqTlZoVTlVMHFwU3dXLUdlNmd2aVI3TEpDWlRRMFZFdEthWEJSZEw0SDdLcXlDS2gyQ3pTalMzbkRGY214ZHVIREdUUUxkYTBqYUwtMi1nN0JFOFN4Y1F6bW1XQzFld0FwNnQ2d0pvMjI4Y3RB?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>46013.51388888889</v>
+        <v>46014.375</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Spain, Spanish   language</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sar Auto Products Limited (538992) Quarterly Results Are Out - Volatility Adjusted Trading &amp; Explosive Profit Growth - Bollywood Helpline</t>
+          <t>A getaway to the bucolic festival four hours from Barcelona: Pirineos Sur line-up and tickets preview - Barcelona Secreta</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:40:07 GMT</t>
+          <t>Tue, 23 Dec 2025 15:11:14 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNUXJ3S015VGdBMTBWOVcxU2hNNW9LbkRtTkkxOU9Kd0pqYmttSTd5X0RKV3ZHSjBBODFYa2hEV01UT25wV0pUYk1jYllsZjRvSHdjQkRqQTFPNW44cEJSWmg2NzdTZnNtRmJ2NkY2TnJnMGZkTFg4SFE2T2VYMHdEcWUwd2ozOTF3eHFiLWJFTW5Hbk9Ycm1vVTB0TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBxM3lCeFBRMzJ0QTlfV0dvYmRxR2NUZkdVbnNOR1ROQnpvaXIwMm4yMEoyRlhCVWlDQjNfMGFTbFAzNk9wLUdlWm8yX08zZHNkN1ptcHVvS1BCdVkzcHB3bjNEOUlDbENMLWNMSTFkc0d0bmhFcTlkY3FlN0NFSFE?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>46013.61119212963</v>
+        <v>46014.63280092592</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Spain, Spanish   language</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Better than Barcelona where hotels cost $230 and Tarragona keeps Roman ruins empty for $110 - Journée Mondiale</t>
+          <t>La epidemia de gripe desborda las urgencias de algunos hospitales de Madrid - El Mundo</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:26:36 GMT</t>
+          <t>Tue, 23 Dec 2025 08:45:10 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQakVINDFRMld2VmJRSmdfNXpqVmpfZTdjSlo1T2ljanFZZmZtR1pqWUxEMHVQNVY4b2FnUlJERWpmMUlkYVMwZF83a0ZaNkFaRWxxU1otdEhEMk1YMEtXX1JjZkJyMHF6YmJIekQwRUZGTnpqcVpPSnBnZjl3OHJRWUMxOXJvd0FCWmZIaHJkbkZCbTBNU3FSc2hMZFdHSGRYNjE2N1ZfTkJDZlM1QVZxdzBzLVJhUldfM0xqZHpseThJSzRo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5NRWttOC1ZbkpyTXVaN3NGNURsbS13Z2JOTnN5QW9HZGFRSThjRTNDeEVoVEZya21Bd21LOEFWWjl0b2ZjSWpUWHZjM3lRR1JqZGx3UWRCU1RNTy1JX0FzcHhSajBqTDc4d1BvNVpYdmFNN18wZHliQzlR0gF6QVVfeXFMTlZnelJuOVpHY2Nsdk1BZ3VIY05nOWh3a014ZkZiNlFoSmNMZi1wT1pTTjRZeGVTTzBrWDN6b3RNWHllb1FYOTE2NU1PZDJLM0lzX0xSNXhGR2NldC02RGtsbDVSajZ0bExCTldwcm90RVJfYXZVQnVOMGc?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>46013.35180555555</v>
+        <v>46014.36469907407</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Spain, Spanish   language</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>The development regarding Asensio that is causing concern among Fenerbahçe fans. - Haberler</t>
+          <t>Detienen a dos hombres que se atrincheraron en un chalet de Elche tras matar a golpes a dos alemanes - Libertad Digital</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:40:21 GMT</t>
+          <t>Tue, 23 Dec 2025 12:14:47 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQS1RhLTNtM1MtbXMzajgxR2hNNlc3ai0xTm0xOEVDTUtIbnNBQ255LV9EVFFiVXZxLW4wUVRhZmVsYk9EQjlROG5xTVcxLXVNMnVVMzlscHdXdFpndDZYT0dIWjEtc2dhb3RobVZQa05wU0FTUG1OQmxTWDk2YzlpMHRxMmYtQlM2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPT1NiM0RxYzVJZWRjOEpXZld6WUlLMDBGY3F0enJuVk9uS2lSS09qQ3c2aTZ4RnB1SGxSM3dZVG8ta216alRQWk91QWc3bzBLdlJEQXllaGVXU19PTXNxdVlkbG5pbW9xeVROYVZrVVFLUVJGeU5zbV9uY1NFcDY1WFNnRUthenlCNHJrdnc0eXJFNXFWMzFheHpjNnNrUGhaOW5HWkwxTWhtUEg4dFpXcnNUWVhtWnp0RjZFUllkd3lneHVSSkZOMnJ2cXQ2bmNMQjBEUE1lckltcFdKRTc00gHqAUFVX3lxTFAybXlNWmhXNkN3bkZxdWpFZUZ5aklZMDVodEZtQTlOVzlyRFBfZVNWT1g4SVJvcGk3eTBZUGpGeVIxQVBGOHpBRlB6MXA0YlY5ZWZVMWN4VzdlY0dDY3FzZmNtQ2dJNnhJNUhPYmZJVXJFRjBRTEZZS0trbDJibWNlWEdraDNnOG9ZRXhzVkwtTnJoRjdKWjNleFJmcXJ4NjNnQks4ckk3b3NBb0YwdFRlaDZKbXNtck84UUdYX3dHdmhLbUVYTWh0WWVjOWhHSnR6b2RqY2tiZTY5dTdjdHQyWUZOOHNBQnRRdw?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>46013.86135416666</v>
+        <v>46014.5102662037</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, Spanish   language</t>
+          <t>Village Search Bicester and Kildare</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>El peor balance económico de Sánchez: los datos que desmontan su moto - Libertad Digital</t>
+          <t>From Westgate to Bicester Village: Shopping centre Christmas opening hours - Witney Gazette</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:00:11 GMT</t>
+          <t>Tue, 23 Dec 2025 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUEkzZndoZ1ZnU3pwREpEUERlSEVabWJ4cnZYZ0Q2WW5iTjZrR1hYeUF1Q09jaVNNdFMxVElPay1FM2J5TG44R0xMY0cweE9MT19oM19FNUU2LVp0eV9fc1NmZ0pUOFNodFlEU2ZvNk1lZXVJTm53R3hULU9XQXh5OFd3UDlIZUhsVFNpU2hzUjFiNFVraVpPZFFJV0JRXzdpTEZVeEFLWHoyeGxBZDZvSGpCQmFxSTRXaHBNblprWFZ1R2I0UGg3V0pEeHZldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONjQxY0tLSkI5VWxGRVlFMC1mYW85OWZaZHEwdmVhQnVrdXNEUm50Nm5FSTZIcWgzRUN2ekVFbTI0ajcwRkpvV19xVlZrNUpzTUgwbzJBTmJPLUc4MDJrbnFzRFp0VTdDTzRfVEFTT3hMZjFDNUVvRkJST2ZHNmxRQ3g4UldtT2ZwRE5ZQjNJckpYb0E3SDZBYW90M2RqaU05dFE?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
         <v>1</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>46013.58346064815</v>
+        <v>46014.66666666666</v>
       </c>
     </row>
     <row r="109">
@@ -4013,24 +4013,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Designer shopping outlet's demolition of sports ground shown from above - Oxford Mail</t>
+          <t>New apartments could be coming to Kildare village - kildare-nationalist.ie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 19:00:37 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPaUsydVVMc2V3RXh0SjJ3anNicG1RRmVYZWE0SHlmOG5xcTVTeHhzZE1RV25kYjBELU5rM2xMR3BldnZ5VVc4X3gzU19KWXJHbUFkTGtnQ2VoT2lkOFEwQkZuMmhFYkFNRUstLXpucUpHT0tkRjRwQ3RwS1FHTGdXa0xVM1FmZEctdjFGOEJZWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRVY5NjJ1VENkT2dfSlBLM0tSUlk5WEVrNTMwcDAwd2dKZ0JnWG5TY2stM1dxSGxydVRmZFltQXVnaXVTTEpiaHBmVi1oYjR6SWE1UDlfQXh5eDBRaGhHTEhCOUJTSndiU2hpZzNYVTJOZUlPX0gzRFV2VWN6MHExTzJZY2k3M1RYSWp5SnBrbDcwZ2ZSbFIzbHlXUE5fYjVVZHdoQ01qWmU?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>46013.66666666666</v>
+        <v>46014.79209490741</v>
       </c>
     </row>
     <row r="110">
@@ -4046,24 +4046,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Actor Simon Delaney set to launch his own food brand - businessplus.ie</t>
+          <t>Who’s opening stores in 2025? - Drapers</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:58:56 GMT</t>
+          <t>Tue, 23 Dec 2025 20:00:40 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5heWVRYmZhLUNXUFNyOF9ZV3Qzd1NQaFBZRURZZFZIUG9hVkxTOThpcUF0Wi15ZGhtZE52RE9DTkExZWx3ZEhmR1VRcWVoNGM0cWI2SHhTemZpeFd5ZnMzQXBvTFNrSmk1UGN2aA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5mM3dOTHlwenpXbDZHSUljX01zS3pKQm5TOVA3aTh5SU5YWi1FekpPLXRUODd2aHk1dzZzNERadGVxS19hbjFrc0J2RHBfYnhWLV9LRkJ5SG9paGl3NlN6c09FeXVhcHF1OTA1M283TQ?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>46013.33259259259</v>
+        <v>46014.8337962963</v>
       </c>
     </row>
     <row r="111">
@@ -4079,24 +4079,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Man jailed for at least 26 years for fatal stabbing in Tottenham - BBC</t>
+          <t>Colliers Wood Tube stabbing: Knife fight breaks out on Tube platform in front of horrified passengers - London Evening Standard</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 18:32:56 GMT</t>
+          <t>Tue, 23 Dec 2025 21:38:06 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1SZmFtRFZuVDZFcVA0TkNlMzQ3Zm80bEIwVUhvY2p3bXBjd2Q4X0V2TlcyM3BEX0psN2VtaGZpLU4xa0ZoUXAxZlhUNVBibTItbHhuY2dvc09nOW1y0gFiQVVfeXFMTXI5Yk9kMVJRUVdDVTVvZDVfbjBwODNSbmVSUXpuRVRmc3lpMnowYlU4S25ocTVtN2RFYmFxLVRKUFlpTEpNTk9kNXdiU3NZbWJZUm1Tc2ZUNWE3Q0NuUjFKbWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPQ1NoTXVwV056cXBDZXRmT1BOWG1GVElPYzd6allIeFBrd2dkSEl6S3gwLV9FNXhlM3VMb2NzQVlRdUpaME1YNTRzSmVCWHFEb0FURmlvVGZ3WWlSMVl0eTVBWFhMTGFoVDNnV3VaYmk5R19DWGYzTDdTcU1RbDRiS2JFLWxVWmlTV0RGUGU5aUNlTEJvTkdXVFRUM0NBRGY2?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>46013.77287037037</v>
+        <v>46014.90145833333</v>
       </c>
     </row>
     <row r="112">
@@ -4112,24 +4112,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bermondsey double shooting recap as man and woman attacked near Old Kent Road - My London</t>
+          <t>Teenager taken to hospital after broad daylight stabbing in west London - Yahoo News UK</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:37:30 GMT</t>
+          <t>Tue, 23 Dec 2025 17:33:01 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNHdCMFFQV3Y2dmdia29TQWYtTjZPakNYSWFVRGZ6TllSR09zaEVieFJlUGlBZVBFc3E3M0w2WDNtOU5PSVFxNHBIdHRwcFNqenFRbmRMM2Z1RWVzdDJVWnFzZUliUzVsc0U5Z0dXTnk0SjU1bDBlNmVaX0ZJU054Y0hKbjFQTVhTZWpyckdZRlpzeG82ZF9RUtIBngFBVV95cUxNM2xMM3NNZm02R090cV9jcUlZelYtdXp1WXJVamxnNXZ2T1lxejY5R1lNTUpaVUlDRU9KbzFhV3VSTVVpS04xT3lQMjBTVElfNjBNcDhwNUhELXlOdk44c01GQ2Fna3RCeTlubHdXMGVKcHNwRjhtVHVlTGYteEhqWV9mbU1GaG04YTluVmREOWlOVzMwR2hLM1hYQzN5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOeGVHTkxzLS1fbW9aaGJfZjhyMzRwZE9UR0dWeGg4LXV4dnhFT091elE0dHYxV2ticTN4Nk5VeVpCenJzLUE2bzNkYXlfRjVwT3cyTEhBNU9ZellwdVhuRjluWTRjX0VrY2xQZE5rZ01EWFdFWkpkYXRVblRQQlFMNEU0NnpCUQ?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>46013.734375</v>
+        <v>46014.73126157407</v>
       </c>
     </row>
     <row r="113">
@@ -4145,24 +4145,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>December 22: Oxford Shooting Probe and Hit-and-Run Sentencing Put Security and Insurance Risks in FO - Meyka</t>
+          <t>Bomb disposal units descend on village as locals evacuated - Oxford Mail</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 04:36:06 GMT</t>
+          <t>Tue, 23 Dec 2025 15:17:45 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQSlBLZEZkbk1uc1BDd2hQOHJ6YUktUGM3ZHNfZ1ZNRXAzbl9jWmFaOGRZcGJaWm80alYzUkpiVVZKNlphNTFoQUJuWDJmMEFDcldTdVg3TWM3RFl3NkttWDQyOG5kZ2E4dUZObUEwN1V3SzhlLXBjOFlkTG9lOEhaV3hRalBmdXlDOVNfUlpJTHZ4OUdMVzF3OE9yUzFxNFhmMEdUQ2FEZWlVREhVNHl2UWg4UWxQRE9pdmZZLW5pNmVGU190cmp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxORS1XOTdGb0hXa283SGk5N0JFS1ludlROQWZHSHQzMEF2YktSeEx0eVJqOW94bWFDM3lVTnlHVUNkRnFuSDRzU3B0QkJlUTE1TlNtYVd6dW9KM2YxTzNIUVgzOE1vcEpsQ2l0UU1WbmwyQzEzenZSQ3JVWVBwcE1NcTRiUGNvaGltT3pOYUd5SWg5cXA2dTBWUUxaMTExSkwxTWIwVTg5Zw?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>46014.19173611111</v>
+        <v>46014.63732638889</v>
       </c>
     </row>
     <row r="114">
@@ -4178,24 +4178,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Man and woman taken to hospital after shooting in south east London - News Shopper</t>
+          <t>Man charged in Joan's Place gunfire previously charged in shooting: Records - London Free Press</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:26:57 GMT</t>
+          <t>Tue, 23 Dec 2025 21:37:54 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOSUhRV25VN1FrQnpqZ0daOGdlbE9qOVdYZTJSYU55STBFRV9OZGV6WmFBMVdWc2l4RHk4cFdBUmlPSzFHVmdwWmNnUjZINGR6YjNqZFc0QXJja1ZDbHp5WTZDLUxMekNWSldTa3M2M3NTNUN3SFF5b21WekF6QVJrLTgyWDFnRlZoNWJPeVJLdXVwN08yenJyVjhuUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNM2kwRWd6YzNNR0tHajhHNVRiNzR2SkZ1azVJcnZ0ZVg4SlNLZzJrNHlPT3NDSU1WQ2RLeWlTMHR3T0hiYzA2Q0VzWFQ4MjBBOGxWZ0hnVC0xbE4yLWNfME1CeGlBTHJQdUpQeTBOTFVsejI1X1FHeWpJNFpDSnJWVUxJYXV0a1hZU2RKaU1UNHFDR3g5czhpUEM3OEQyVzd4TGdFZl9pOFR3RXZyRFE?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>46013.56038194444</v>
+        <v>46014.90131944444</v>
       </c>
     </row>
     <row r="115">
@@ -4211,24 +4211,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>London-Hyderabad British Airways Flight Gets Bomb Threat, Lands Safely - Kashmir Observer</t>
+          <t>Worker to face charges for shooting at suspected thief in shopping center parking lot, Oxford police say - CBS 17</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 06:35:59 GMT</t>
+          <t>Wed, 24 Dec 2025 03:26:12 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOdEVPLTJ2b0E2bFZVa2czNkJFVklUSHZYM01kRXBiNElHaG5tX21uUGdncFRVNFF3TTVrT19LYnExUmxfZi0xUy0tYkducExURnZIdWRNTTFNS21SVExNM1RxOHNoakRieGVLRWtQNHNpeksyMmdLNko5V1REZ1ZUNDZrblBTX051RFRUUHJ1cy1zdDdBdUE2Ykk4Vi1YV0NfdU5uV2dLZ0w3WW9PMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPdGxmV29QMjhsTS15TXE0bmNtMFFRWW0ydmtMRm02akJuSWZKWEh5MGhEcEtWZDYwdWRSUjAxQ1VSNWpoLUplR29HNmxLSlBGTDRmcVVhdmRnZTlac0xCYjlqbWVOazZ2Q2FnYUIzelVrZ2lOUkxUVnpQV1BabFIzam5nTUJWZkF1SkNUUEtfSEduSjZTallUQUlzcEREZVhVbTlWcklLSVJ6Z2Q3elNOR0hEZWNmbjU3cW02RHpTakVWWGdVOXFNQjRKdG94OVdqUThLZXVNcmQwUdIB3wFBVV95cUxQTGo0YjZ6Zk45WkVuZVBGZGowWkwzLTN0VVp0ZG1WMTBOOVZJMGRqR0I2UlhvX21FWm91ZHJwMThvcDlfNW8ybUVZOTU5cFdqZDhDamlmdWV0UFFZa242SVZCb2g1Q0xTb1RUUHVmRDY3R1ZIa2xEQjFiUEZFRG9wTkIyLU5VaTZFX0xsSl8zczZQalU3d0JodzNCNnVDTmFmTS1kNXprQ0ZUQks2dldpZDNUdExwSldtU0VuLVFscllxTV8tTnVzV1Y4eV82cGNKamJaNzhtdzd4T3NyV0pZ?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>46014.27498842592</v>
+        <v>46015.14319444444</v>
       </c>
     </row>
     <row r="116">
@@ -4244,24 +4244,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>London Shooting And Maida Vale Stabbing Leave Two Dead - Lawyer Monthly</t>
+          <t>London-Hyd flight gets bomb threat, turns out hoax - Times of India</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:36:31 GMT</t>
+          <t>Tue, 23 Dec 2025 21:34:00 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPbHZ2ZENFQ3R0ZFhpanUzUGVKbmsybFlRdk9fWEdqNzM2ejN5LWl6dS1ZVVdNd2R1LUlhb1ZGWEctT2VFTXVsUTIwZW5lMl9rT2VTZkpocTgzaWlwbXctWkhFdjNKTXdvMmFVTV9SczBMeFNKWUl2ZVIxbDNPUzI1TTEwRW56YXFtVHllRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQU2RIZVljekhETXlGd2JFWVItM0RVeXVkRk9JdkYydzA4Y1NoUUV2WlBTc0Nyb29QVlUyVHRCaG96TUd4RWk5WGNXMG9IVXVGc2o2cmRLZjRieER6RHhzV0NoMzRET2d1U3dGSmVMVkVPNEZIeVdCd3pyeE51NURLeDlydHNTb1ZBcFRMWmRkbDRxSFVjNnVLX2pDT0VMN1I1OFA3WUFPZ3ViZUtmeEozU1VmUVNFWUpxOGZnamFZWTU1UFNa0gHKAUFVX3lxTE1HWmhtbXlHQmFENXhjVENWMDdFVmdPVHVoT2pVUjViMlJOZ2ZjUmJMRjZ0bHNZWFNtWWg0ZG9JaERKcVlNUGdjWWJBX0o3bkloNlBUZ2hOZ3N4d19vMlNhRUp0c2pmanJWYkt6Z1NUZlVPWTV2LUc0UVhXSVFBM1VBaHRLTnE5TlIzRWl0WXZvNXZBRUwzME9JVGpfUEVLaDYyVEtnN0ZrdkVVT3lfbk15QTNrMllrbC1XcTlKYjFaaFd2M3RGbTAtbXc?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>46013.44202546297</v>
+        <v>46014.89861111111</v>
       </c>
     </row>
     <row r="117">
@@ -4277,24 +4277,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Man in serious condition after targeted shooting in Kensington Market: Toronto police - CBC</t>
+          <t>Man on the run after shooting his girlfriend in Oxford Circle, Philadelphia police say - 6abc Philadelphia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 18:12:55 GMT</t>
+          <t>Tue, 23 Dec 2025 15:21:19 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNWUpEQzk3RmdOaUZzWE45Zk80MlA5cWo5di1oTjltMFFZX3pCMTRJOEFwM2xNRU9MMW9oVUFQVklrNHZJVnhjR00tamV1X0h4RDl5YnpFVTRvZEcxejBlRDZzTGR0SGYyUExnM0lmWXlqLUxrdGFqd0x1T0l1am9lNzlUNVFVVmZoNjl5aUVmd3dNZmZsSlZ3R2pzVUlvak9fck5oZWRZWlE5d0Y1Y2ViSW1VNjViZndjMmFlWHhIRHFTTGZtaXllVnZGbGtvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPZV9SYUdTYS02TUdqcW1SZUUyQnhObFFrYUR1amR1bXBYNVllUU93NzFSNnZmZDhiTDhZQ09sc0cySkVPQmpUdGtnS3BwNDlIaXpqZU9DYzFJN3FFWm9LeGc0M01PZWtjSHpwLUxUNGhZZmxteU14YjdNNTdLTUVLOXhWS2lWOENZX0JkNWY4bWs0dEoxeFIxa3FxR2xoQdIBowFBVV95cUxPdEJYSC1oeVhtYWc3d094cmRBNEU0Y0htbGQyX2laSlpjSEthOGlDTFl6cU1zclJmd21oNjN1MnRwYWFacUJKaVFZalhFQWN3M2RsMmdpRzVGZ0FSbWFhVVRkUVhiZVRvS2xIcDNPUWVTQUVZMmtJRmM4NjcyQmdpaXBaMTZEWHN5c0RoSTlXWGtqNDN6WThZYVF0akhXV2ZLdmV3?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>46013.75896990741</v>
+        <v>46014.63980324074</v>
       </c>
     </row>
     <row r="118">
@@ -4310,24 +4310,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Two arrests made after man 'shot' in Oxford - Oxford Mail</t>
+          <t>London man charged after raid on cannabis shop where man was shot - London Free Press</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:18:47 GMT</t>
+          <t>Tue, 23 Dec 2025 19:06:58 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOMWRtV2tFR3hHbXFVcDJrV0poNTYzVVNKV0NPaHNuMTFrRnFxZnpSU0xPOVFlY1ZqemJZaDNhcnlSaGpRYW1SaGdBbnlvVGtYdVp6T0l6QTdXQ0hHZWpFQzg3WlU5Z3JVdlBLQWlIMGsyb1JjZHpjVzlObldxZEVyZFNrN3lKQXNPOG5DS3JwZ2g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPREl3bXJzRlZEYm9qd1VsZTRJb0VISnN1aGYtSk5Pai1pQTA2ajF2TzBIY3dtcUVPMFpfV2Q3UnF3WGEtODVxRHkydndJM3Z2VUdBVXZwcHYwSHBiZDdqUndqaGdVTU1YcTItNjcxU3R6UGEwWWJ4T2gzLUw1ZjJ6WmhtUXd5TmVkVUNKYkxZZHpZbmE5My0zbFVhRldTSG9Iclpn?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>46013.59637731482</v>
+        <v>46014.79650462963</v>
       </c>
     </row>
     <row r="119">
@@ -4343,24 +4343,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New 'Banksy' art appears by central London skyscraper - My London</t>
+          <t>Dublin Man Facing Weapons Charges - The National Tribune</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:30:00 GMT</t>
+          <t>Wed, 24 Dec 2025 00:51:42 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxObV9nNTJnOW1lTFFjeEFtcWVoYWZ1QmNGVmhiYnRlOFAtQThja2dwUGhjTGFRUVUxd0RlSV85UlpwSTAzbGU5bjdrcWdqeG1wRnMzWlcxTDJhS0g0c2YtLURKeHhwVG1lZEpJRlR6YlRVUHhURndCckVLdC1qMVJHV0c4M1g3NVlKUGQ1bkJDTWZWWGUwUXln0gGcAUFVX3lxTE5NUWxtRmU3YTk5S3V2dXdzclZmUkRlZVZ5NVlOWXdMNmJsY21WOWpoWFFXbm1aRVNyeXRWUGFJa3dpMlVKZ2NFZjhjMWVLMU1Od1dJOFktc1ZtZjk3cjVsYXdOYzFHcFE3OEE4ankwZVpPTENzZDRRVzhOVW9xS1B4c3ZTYXJWNUZhVlgtUXZaeU11S3J5LTRfclVlVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9rWjFDVWxuZVdQTUhBMHhrSGlRbUpmQk1UZHp5ZVFaMHJuQm1xcloxMTNmSjh5Rm80bl9NTVZldEx3dXgtTXJxYy1fV0s3X1NDWnhVdm1zWjByYVh6R20wQlp3dzE4RGhVSHZLSWVyWm5CeVlHT0Z1Xw?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>46013.5625</v>
+        <v>46015.03590277778</v>
       </c>
     </row>
     <row r="120">
@@ -4376,24 +4376,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Man, 28, in hospital after being stabbed multiple times - Harrow Times</t>
+          <t>Shots fired in north Dublin as gardaí launch investigation - Dublin Live</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:04:17 GMT</t>
+          <t>Tue, 23 Dec 2025 10:22:07 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPYlpqSjdsMXpqbnJNdFRuZXdVVDFLZFRlX1lGa2otR0pKS0ZXT2g1RThidV9OaGk1NlZxMkRIYk05NGRQMTMxQ3Nmb1ZqdHRmTWVCbEZob3NNUzlKTVRLeUl1c1ZDSmh2N1FBTlJ2MUhWNnJVRThXd0pUSXVWU0YyNXNpVmg1LWxnQXJLTkN0S3pLTWozRW9oQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOV1gzakpKendRSHRrb2NhMnpDTzR0NWRZSWZTckNORXBXbE80SmtNVkV6eGZhYU56VERxaUt5ZndjTmxLenFQbFRNQzUwOXgyRzhGbENJZXJRS2JMbTYwa01TZ2JNUjdIMTRHalFrWEtZTndsd1IzWm53XzNaQzdqY2ZaQkhObTV4MTlJ0gGQAUFVX3lxTFBVOUxodTVoRkJUQVBqVW5hTnltcHA1bkhwcXlWMG5zVVlWaTdXMTI2cGVka3VGMEYzM1ByN0FkSUc0ZkQ4RUpHS3ZUUUpjdVJXcS1aSkVXUjdwWGxENk0wMnFHbnZ4UUxUQUNJVTdoaVVabmRWNFZWOF9Ub2ttMG1OS2NteHFQUWNsSVdhcktWOQ?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>46013.33630787037</v>
+        <v>46014.43202546296</v>
       </c>
     </row>
     <row r="121">
@@ -4409,24 +4409,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>North London shop's plea after filthy pans and dirty clothes fly-tipped outside shop - My London</t>
+          <t>London train lines closed after person hit by train - Hackney Gazette</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:04:43 GMT</t>
+          <t>Tue, 23 Dec 2025 08:44:32 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNM1BsRy1tMmRWYnM3RF9rRktKZnVvZ0hhbU5naEFFTUNOZ1JxclRIMjFfc2ZuandaV1QtbGZsSkVDWGJkMHlQRWZVNFlodFlHOWw0VVE2UTU5bHk4VjV1bFAzYkZmcTVEbDlVVWFMUVNXSGlvSkRyY1BORWhaWWtENFppb2Vfa1p2RUFaaG54SGZaeWPSAZgBQVVfeXFMTko2VVJTdXRPc3ZHLVljYkUxOVh2ZE5NMU9QQ0E2RGNIeHpUMHpfZTFHTzZCUVYxUGhROXhQcjZuM0dNSXM4RmpYTFlTNUhvc1R1R2pXcl9tci1zd0NZRlZUNk9LNEpVRUUyaXhhUkQyVnFQVmkzYW5HOExUdEtFaXBGeHdjZlVVZXJ0RTZiTkZxYVA1Q2JNWDc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPc0kzWmt5djNZR3YwMTFweEo0RzJWc1Y2a3lFUHUtUzVDU1c5dWJXTDNJZzJMc095S1NQT2owR3JaeWMta1Z5QjFZLXVubEt3eWlDYmtvMjRYV3hVWHc5MjM0RUVrbGc3VHAxbWlJYjJjLXNjZ1FyVmE5eEtvX2JnODUtM1k2X1dFX2p6Q2FQRlhkalUxODJUN3FTQXZMVEhSN2s2Mg?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>46013.41994212963</v>
+        <v>46014.36425925926</v>
       </c>
     </row>
     <row r="122">
@@ -4442,24 +4442,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sheffield shooting police probe as homes peppered with bullets - Arrest made - Yorkshire Live</t>
+          <t>Woman dies after being taken to hospital from house fire in Peckham - News Shopper</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:02:00 GMT</t>
+          <t>Tue, 23 Dec 2025 15:21:04 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPS1FJSVBpdG9ZMS1GdXpSYVV0RDZ6clljU28waFNZNVFjSy14RlMzT0E3cGo0VGdxazF6MUdGbGxocjctWFBNQ1dEZGZPSWdQc3dsNDVjSGR1Yk96bVhwX29yN0RaMHBkdVNOT3BfWkhZaGRwYWFxVjNSNVU0dHdVQy1sZm1RM2JfSjd3c0ZJWW9WN3BBUmowS9IBngFBVV95cUxQd3MyTTRLako1Z3BMejdtUE1pZ1hoSXNIa0FLRTh5V183eS1rZHd1eERJUzB0UFY5aEM5Sk1NWndmc2JBX2h2S3UtdV9yclF3ZGx5bTdnellyRHZuSDN5ZzllMHc4cmRiSUVrQXBhTlRhVmJ5S1ZzVVYxeURzOWp6aEVPRjV4dERUVDA4NEFaU1lRQjZDcHRiQTFNZVI0dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQTUZoTUI4N0VEczlPaXlnVWdiN3A5UFIybFNDenFJa0VHdXAyOEl3dEdEbkhIZ2JjT09LNmNKUm5LdGNSNzVETHNDbEQ0cnJvN2c5ZDg2WHk1Rk9oc3d5VUUzTGh1LUhRR0MtS2ZzZGEycDd6WDhnOVFTRnZwWXF4cXQ3TWc5N2pUbTNYNUt3?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>46013.70972222222</v>
+        <v>46014.63962962963</v>
       </c>
     </row>
     <row r="123">
@@ -4475,24 +4475,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TGI Fridays on brink of administration with 49 diners at risk - My London</t>
+          <t>Weapons, detonators allegedly found in Adelaide's north - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:57:26 GMT</t>
+          <t>Wed, 24 Dec 2025 03:05:17 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQdFpFS180V1JHY3hYS1J1NkpYOWhqS3lCTVowU01CZHppUWVWbVhEQjd2RnVDUVhLUDNZUGM4Z3VFUmhTSW45Y2NzOFcwQW1ya1JHQ0JVVFoyRnhhNWphaEk3ZFh5Z3AwWmx1bFpCZDRFaVdWVG9tdjJPV3dvelpNNHI3RUF0bU9rbkplOEpybUFtMTkxbEJPQtIBmAFBVV95cUxQdFpFS180V1JHY3hYS1J1NkpYOWhqS3lCTVowU01CZHppUWVWbVhEQjd2RnVDUVhLUDNZUGM4Z3VFUmhTSW45Y2NzOFcwQW1ya1JHQ0JVVFoyRnhhNWphaEk3ZFh5Z3AwWmx1bFpCZDRFaVdWVG9tdjJPV3dvelpNNHI3RUF0bU9rbkplOEpybUFtMTkxbEJPQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOaVBfYVZ5OFg1S2ZxYkxnZTRDS19qS2taODJzeXlENlN4Rl9yZzg2RnRmYkNtM292NzFQMW10dzJQZDd2SkY4OVN6NFpybXc3WWVLQmliZmNQMktoR2M5dE9QVGxkNjl5QlJiN0I2MXBpemM0OEFIbUpKSnZydmlCYjJqUWJ2anNiTWluTGJBZFotNmQ0QkhTckp1eXVicHF6bXh0cE9n?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46013.70655092593</v>
+        <v>46015.12866898148</v>
       </c>
     </row>
     <row r="124">
@@ -4508,24 +4508,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>3 tower blocks planned near Tube station - developer's previous block saw window fall out - My London</t>
+          <t>Andrew surrenders shotgun licence after Met Police visit Windsor home - My London</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:15:00 GMT</t>
+          <t>Tue, 23 Dec 2025 11:09:08 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPbXlkMGpia0ZxTWNPRFZlNWtsZXByY2tKSDNDTEtwMDRXTjBHaXZoVWxqLTBhRUdVYXFEcUNnSTlKYXdwMEdEWTRiYjVHSkU5YUd2TjhkcThpZ3RySG5zMWxTc2kzbml6RFQ1MG5BRVBrQWJBYmNkS3B4NjFhUmFPS0tYcDlkdkhhdUNBR1ZR0gGTAUFVX3lxTE9ZY3p0bjVhR2xuQnB6Slo5cXB0Z3lSODV2QnNNSGl5aldQejFfZDI3SVJPcmJKX1V5SzNYbExfZ3ZSQ04tTkZaTnVsSjBTa2VXOE43aFFUR2xoWnV3TXFkNEJuc1ZtSnRncURIUlNjcERaM3NETU05Uk96V2ZVVGpCT2QxZGxoNDJUVElmcnpwWGFxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNQ2VLei1oWGVBMGtESXhYdzlrS0tyZ3dCckw5N2NLVkpvR3dra3RlZzA3aWtXZHdaOHJNVmY5a0RtSXVySXEzczFrMWxLX2ZmVGlSNTRIVDJoaFo1RFYweWtTMFBEb0lhcnRMY2tKUFQwUFJLYkFTakRtalJkUFYyRWxjalYyT3c2eFNRY1EybFgtUm5oeUEzYtIBngFBVV95cUxNRThyZ2MxcU5HYjM0Smdwd1BYUVpNaFFWVUZVbWpGMU95VDF2Y0ppR0hiOEhOWGlNU2wwRFQwZWtGVjB3VEtoXzI2TWFZQTlpNTkwOWNmbEpTaU9ncjNMcnFLTm5BYUN5S1FrU0g1eUhKTi1NLUVPX05oOVhxSW9OUnd5blZXbDdWV2lNVEhvYzAtblpEdnZGNEU1OWpwQQ?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>46013.46875</v>
+        <v>46014.46467592593</v>
       </c>
     </row>
     <row r="125">
@@ -4541,24 +4541,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Explosion in a laboratory in the Rhone region, at least four injured - French media - news.cgtn.com</t>
+          <t>Community marks one year since Doug Harless killed by London police - WKYT</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:21:17 GMT</t>
+          <t>Tue, 23 Dec 2025 21:36:30 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBUUmNkN1JGYmdPNWJOMjBYWjk4djA4Q0RTS3gtMEpiU2xzbGhYa1lRWnVEdDViNlIwU3ZrZ210YUJFVVI3WlRfQkdrSTV2c0FvT3pNeFJKY3BqVE4xNF9YVWZvU3dvdWw0T3dCSHZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQZnBJcThfeGRubTk1aTUzeWFXYmh5WE00VHpJZ2RXMi1odWVUM1dydFJWd0ltekZlbDdvREpONWtiWE5uMnZ1bGFEdzl6SXg3UjRvT2hwc1JicXl6OXhXY0pRajZtN1hvRkZiaEVLUEtBclE1OFlmRVpvS0RUSmFuMjFOa3d0Y3A3a05aQUFjcGJ1d0FDZmpLbm4tdDF2QmlQcTJpZ2hyX29xUQ?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>46013.59811342593</v>
+        <v>46014.90034722222</v>
       </c>
     </row>
     <row r="126">
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Transport for London - My London</t>
+          <t>Bondi Memorial: Australia holds mass vigil for 15 victims of deadly shooting - news.cgtn.com</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:17:51 GMT</t>
+          <t>Tue, 23 Dec 2025 11:01:46 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1hdFhJUDBZNktZQ1hmWmVpell3Z1hJRElPWWdwQTZCVWVUaXZ1dnJadVFtcWFWb1ZBeklBdVFTbWNWNmdNM2tHZHZzbXRzeVlfdEt1QjNRS3hHU3AyRkhsNXI5VjdXc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE96bjcxYTF1bmxOcDZqZlV6NmhfcTUxa2NGdzdWdG5La0FCLUhhY0FHVGg1dmVvbzNiQl9mZWh0N2E4dzdHUlhKVnA0Mi1VVWQ1cHN4SGFzQ3dNRTlnR0ptX1o2RUU0cUNtU3g1YjdOZjA5aFc1a0Z1Qw?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>46013.4290625</v>
+        <v>46014.45956018518</v>
       </c>
     </row>
     <row r="127">
@@ -4607,24 +4607,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Australian PM apologizes to Jewish community over Bondi Beach shooting - news.cgtn.com</t>
+          <t>Jailhouse call leads to conviction in Olney double shooting, Philadelphia DA says - 6abc Philadelphia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:30:31 GMT</t>
+          <t>Tue, 23 Dec 2025 22:20:29 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQOGxUYlZhbGM5ZVh2dDhGZk9NeTNCcm5mcmRzc0Y5OTZjd1ZCVGZleGc0LWpocFpMWW5OQlE1U21WYk4tbS1aRzNfYkRYVE1SclA2UlZxNzVOSWhDcXRMNFgxcXlSMDl3MUlaVkRfd3NCZ1pIM2lZcDZlM195bU92M0dxNVdNSFRGMFY4TXZuejk2SHdFQ0M4dk1pVmRZdXduLVUtcUdROTVCMkxscklvT0VRUWcxMmN5SWw5VlJNSmZ3TjhidWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNN1lRd1BQQi1QMGh5bHh1R1l5eWMwUnNUNFdzZkVnZWFfZnlISWNwNTJUVEdyRTdGdWY4Zk1NWjZNMTY3UWlZTzVaTGptY0x3ekpCZE14WDZIM21HMVV0MFhWdENGcEhrMktxSVRLQVE5XzNOSjhwOW9GVHg5OHVfR3lBeU1FSzFxYUU2ZzlncklpZkRnRTV5QmNkU0UzSlBfVUdrLWVVdl9RZ9IBrwFBVV95cUxOS3hFenhfZnlqWmY1OHI4VFg2UlhsVTFoQ1FBNUUwT2dVLWtuQ3dLUXBMTHJwRmZLRUFsSWdPR2dKQlIyTktzNEVFVHN6bUlzNjg4YnpyVWVlU25vRTlydXRkZjFqcENFYWxNQnhUOWNpV0FQSGtuNWdUeWZvRDVWTkxIbW9jX2xLUVVoUkRDYXVrYmFXU01odk82XzZFUmxPamd0c2Q4YjNaUGVkbFJz?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>46013.39619212963</v>
+        <v>46014.9308912037</v>
       </c>
     </row>
     <row r="128">
@@ -4640,24 +4640,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lambeth bin collection dates for Christmas and New Year plus how to get real tree collected - My London</t>
+          <t>Wednesday’s briefing: Nightmare for Lacroix while Slot and Frank clash - Herts Advertiser</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:34:10 GMT</t>
+          <t>Wed, 24 Dec 2025 04:36:44 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOTU0wTjVucVQ2b2lveWpIN0s4QkxnQ1lTU0ZjaUk0OFFaZUtyWjRUcTVUa2RNVDZveE04dzAyYXYtRzBGSFY2akpQbW1MSlBOOFg5Y2t6eExBWFdiTFJZSkRqenpLZGZYbmxXeExJNWNLRDhKMnUxaldsREdFS3NYZXk5VW9iVVBQRkJ6YWxKRExGMUxJVmNJWHd3eEfSAaIBQVVfeXFMUHZ5cHM4eGRlWHEtcU56eDlxYkl1NUZpWHdadUpORTg3em5hOVBxT0hRcWVtNWNDWXJ2T0Y2WnF1YktZTGM2bnYyS01LU1oyU2FBQXNwaEt0S1BnbndvX3l2OTdUYmNvMEw2XzZZbkpHcWZNZ2FIbWQwOGRyUzJaMFZWSHlta2FZUDhjSUVjel9OcTZyZmFpdEZEYVFiNUx1V2dB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQcElBUWFYelRaTG5fanZZRFFkQzR6Qjc5UlJwT0VKY2dyaUpneTRzQTAxMG5Ic1NiZDIxN2dZNmFFODBNUTVRZWZFWHVsczFSMUZvdDlSbmRpR0ZTUzBieWNlMjE3d1lDZlZDMG1rSWtCeVpudmpLSUZSOUhkREo5dFhZYmpqZEMwdnk4NFNNWjRFZWlGNUk1ZVBuM01PT18xcGRtclAyeGI?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>46013.48206018518</v>
+        <v>46015.19217592593</v>
       </c>
     </row>
     <row r="129">
@@ -4673,24 +4673,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Police Seek Teen Shooting Suspect In Chatham - CKXS FM</t>
+          <t>Daniel Craig filming in London, first photos from "Bond 25" - Balkanweb.com</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:33:34 GMT</t>
+          <t>Tue, 23 Dec 2025 10:38:52 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9VeVU1VzByRm15Z1JLb2V1STVvT0lFUzgwSTFVSUVNVi16eG9wSEk1bUlfNGtBd0hXVTh3UkRScEtWX2ZLRHBTWTdZMjVQRUduVnlJQmZaNS1ReDN2d3pjejQ0STFNQngzVExKSko0VWtPd9IBd0FVX3lxTFBLd3VfN012NjFkS0tjaGRKc2NJb2txMllQV3p5TFhkTHdQRjNCLVhpWF9RSUxsSEVPbmpJaEZSWUhZVlZPLUpCMGQ2Z29sUmtSUFh6NUJVaUtSd2xNRHJiVU9qbkVsb0RKS3ZFYXFNbkNHOWI2LV9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZC13N3RGWkFleENoZlJvWk1mYU80MWduX3BUaTl6SEltMXlFTVIwR2swWDlEeUo5bm5qeDN4WW81N0N1aUdURm1LS05lbG1KYTVZWGhWSmYzaXJncHg4Vk5vRVM1cUJ6QS01SmFKcGZKUkRiUExfT21TelAta2lUQmZ2RHM5V1dkcDBfamd1V2I?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>46013.39831018518</v>
+        <v>46014.44365740741</v>
       </c>
     </row>
     <row r="130">
@@ -4706,24 +4706,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Parnell Square stabbing survivor, 7, continues recovery - Gript</t>
+          <t>One year later: Laurel County fatal police shooting investigation continues - Z93 Country</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:07:52 GMT</t>
+          <t>Tue, 23 Dec 2025 18:13:40 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5JOWRlMG1ULTZVRUdsWWhIaWpKZ1d4VXQwdWc1YVNCZlZOUG9mcXktRVh6ZTBZYVgtV2k2ck5BT0pmUTV0NWxpcWJkNkxTYTIwSXBGNUEydlpfQlRSbzB1d3NiMlNDdGxPNVJKUGNrdGI5cDA2cXJWRUlHbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE05em4xWmdHbDdGWHhOVUFjaHpSRHF5dUlGUjZGR1BMVld3eks0eERvbER5ZFAxZFI2VW5kb0E2Mmhrelhpd3pwZERzZzhqZTVONWJWeWxWSmZuOGtkWUdWNw?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>46013.5887962963</v>
+        <v>46014.75949074074</v>
       </c>
     </row>
     <row r="131">
@@ -4739,24 +4739,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Mother of girl injured in Parnell Square stabbings says daughter may one day tell 'own story' - BreakingNews.ie</t>
+          <t>Guns and gold win in 2025, but other ‘safety’ trades bomb - The Globe and Mail</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:26:57 GMT</t>
+          <t>Tue, 23 Dec 2025 10:21:58 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQay1BblBoa2RoZ0xfeEtCZTRiLVZQSmlwT1FGM1VhekhGUllOX2NCd2pHMFRUM2dpQ2FManMtSnZxcENBdll1OHVSU21BX2l5cDZSMFlDaTNTZzhWSzR5b2hXS2VRUHM0ckZ3VHlvU3ozblRTMHJGaGcxMUZsdkVNbDJ4SVF5dE04bVhvc3dMZDd1RVFuTWtPT0V2d2pvak9XUkdiX2hhMENpalBGeWlpakZ3dUh1U2VtNGJUR3N6MnZyY0pWRmlTUzlsOUJZbnFUUWNLNkhpYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxORTJTU2hiTER1OTR4VTQyNVhpZ0FCVm45ODBnMFRpTzE3Vi00WjBZQ0p6ZlRvUDMxLXdrVFBKNjhBdFdHbXQtN1A3YkpMQXU3bDVCRklVT1Etd2hvX2xpcVhucXZqd3B2b2x6Z1BKbTdhUzZ5RGxmckhmUGpFT1JjMjFhRHVKMURmUl91Q3c1TmFueEhubUV2R0dQdXh6NWpnTEdvc29BY2c?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>46013.47704861111</v>
+        <v>46014.43192129629</v>
       </c>
     </row>
     <row r="132">
@@ -4772,189 +4772,189 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Where Was Goodbye June Filmed? All Shooting Locations - Moviedelic</t>
+          <t>Michigan schools lose court battle over controversial waiver for safety funding - MLive.com</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 04:49:17 GMT</t>
+          <t>Tue, 23 Dec 2025 22:26:00 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9zM1pMOVBVX2JTQThUYk1iOW1tT1ZkMkNUQVVLbTZMQm0yZGJyYVRlX25IdkdhbXF2VVBhVUw1Vm1wUnNJeUplaFdWMWxtU2M5MVVacXhxZjZqTG0xSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOdWNqbzNYeVZCYW9CcFE1cndLMW9QSHBsRXk5b1FQY0drMy1KZXgxOE8tcjRQSTVBbVJuZDRPelZBamVfVmdCUFNVby1SYU9UTkVYc05jaHhfQXZaUncxNVQyLUdrZ3drQkcwcllOdnJ4aGlyQTNsb3lvQ2VyWFRKYS1uOHpxRXZ4WUpZNTlGMXdxU1FUVTR5Qmx0YXQ3THNrZXo1SHUxaGpCalFpNURYeE1rNmdrTU9wRUJQZkZMQzNkZw?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>46014.20089120371</v>
+        <v>46014.93472222222</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ethan Hallows convicted of Kevin Pokuta's murder in Sheffield - BBC</t>
+          <t>Trooper and suspect killed in a shooting at a Delaware DMV - Castanet</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:40:01 GMT</t>
+          <t>Tue, 23 Dec 2025 20:59:00 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBoeUlwMEVrb2E2eFR3bDNnRkJJOTI1UG96Mno1Z3pUWkZ4SXk5NUhjTUdwYjdLVC1mZHhzSjJDdXpLaURXMEFuZURkS3hEMHoyRmRYSW01WU4wWjJ20gFiQVVfeXFMTURsZWRid1B4Z2lVNjB5NVRwQ0JZZVE3U0tVRzJDbTY3Qm1wUVRrYW5qOGlpN3kxWnJ0dVQtM0I1RW1PM2xuMHBWdlF0TlU2bi1WYm5vUVRHbVhRcXdRT3RWWVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE95MGoxSkY2OWkwR0pKSXFhaE5DVFRYUkphRnJ2YXdyeWQzajczaUVoWFd5TWpXZkxWdVVVc2kwM2Z0clVBdEdQT05JVW4yYUtxQ2poUjc3QUliekV0ZFlIenl3X0FUblhZ?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>46013.52778935185</v>
+        <v>46014.87430555555</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>‘Dan taught me to live for every moment’: French Bondi shooting victim, 27, honoured at Sydney memorial - The Guardian</t>
+          <t>Suspicious Google searches in 'Israel' spark fears of new attacks - Roya News</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:42:00 GMT</t>
+          <t>Tue, 23 Dec 2025 14:29:10 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPM0xqeGZySXFETjRGRnNmUXRzVC1yUndabnMzN0hvQmpxNy1kNmZLcVR4LXB0bkUzSFd2SlUzc3dlMkJHZDhlbHpYS28tZ1hTX25zUVFCQWZoVUJxU2NqeWthS09JcU1ObEh3S0VBcXViV2FlbmMyVG81YUhYMlVBbV9DZnhMcFR6SkdZWGMwV2cyT1V6Y1Q1d3ktSE5IMW1VSWVxU2NZQVctMldmaWljVmV0Z1IwR0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE5GR2IxVEluZGtvZnFYcWtCZ1pfOGtlTGJ4Z2N5VURFNC1pb1ByU1JMU0dpZ0hrRVNqakt3MUVVeENWSzBmWWlvaw?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>46013.32083333333</v>
+        <v>46014.60358796296</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>"Emily in Paris" Inspired Cocktails - FOX 5 DC</t>
+          <t>Manhunt launched for 55-year-old as police issue appeal weeks after his prison release - Daily Express</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:06:00 GMT</t>
+          <t>Tue, 23 Dec 2025 20:46:00 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE5LSi1BVmtSM05rc05wWmNIeEZSQ1NPZjI0Q0lKQzZyakxiM25qS0MzeXNYVXQwc0w1UkptbmdHZ0IxVHRIQl9UeVpfc2FXcE1YLTVXbTc4c1k3cW5rY1HSAWNBVV95cUxQcGdTNG1mRUdCc2VLVTFHcDI4ZzJtb0NYaGhmZFFoMjF4Nmx0V2lGQU9yMy1mLVEzVk96YmxMV1diTXp5SnFXU1cxdUo4cGFRWVFEbFRwMFRRck5fQzZ2cjJReGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1vZXI3bmU0YUZvTHplRjJ0bENoMmJ4eGE5X2p4dlR0cjgzY1dYSzloYXljbG1oQjRRMjV5WVpQb08xbFUxNGdtVUpIUFJaR0V6SkVoa3c1Ti1DOGoyMTd4M3VnZ0NqS0NtcEpmOWNDbExWZlNITW8yclVBMWlhQTDSAYQBQVVfeXFMT3ZPOEY1TkE5RkJrVVZ0UW5KclVXXzE2MTl4NTJrY0hMSU5MbFlWMGt1NnFTZ2daUENHdkVxVTh3U2dKUFU2UktjalQyRW94REdDRlAzcW8wT3djZGdXTEpBUGtXdFppUE9TV245bDEwcWQ4T3lUQU0tTUtSYnFxLTVYS2RD?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>46013.67083333333</v>
+        <v>46014.86527777778</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Shooting “Parallel Tales” directed by Asghar Farhadi has concluded in Paris - آسیانیوز ایران</t>
+          <t>Non-crime hate incidents to be scrapped after outrage over controversial arrests - Daily Express</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:21:08 GMT</t>
+          <t>Tue, 23 Dec 2025 07:53:00 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1ib1Y3dTJWelpUakRMbVM2cEoyeExkUS1rblRvTmVzRUI1elQxSkNqOEFIeWVIN2tqb1RIbHhncGFKV2w4THBBNVlTZl9kZV9xeEFGeWN1eGI4blEtQzRxUjhZbDRNNUE4WFZzMzg1YkdKR3NDTk53QWVySnA2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQNFNfejNwdU1uZGlySmFLWlB0QzhGS21kZlM0VV8yU3ZSNl9ZSnFvX0g5bE1MSFR4ell5VG5GbmIwMEIxSnZQQldxbzdCN2I2T252dTRYWWFPYjFGQ0ZjeUZPLW9hU1lUQXFGbVJpMEtGRkViOUI2ZURSODMzMVBJOW40Zkd5Q205akVwSlQ3enZFbTdVbm1ETG9kSTRlSXJ6MVFaLVVHN2VpZ1V4VjdCc0FvWDdTNE81Vlg2N3JmS0TSAcYBQVVfeXFMUFhEOV9jT1l1ellfZkJOaGpGN29KZ1VJYlpaMFFSU1oxWFV3dkZPck5fTHg1SUwwcGxSWWZlSEV3cDVDUmtxamY5bFJPZVp6VW1CQ2pxVlF5LUVCMHItSnJWb0p5dXcwYkpHREhtVXRDdUlBZlVQQ0hXemxPU2toYldmZFZzcUMyWUNyRzNVbGV2MmRHaGxnYWNfRkV6b3NlSE5ERlNTdDJQdkRneEdBQk1CTGItbzgyQ3VNUDhraC0zcldwd1RB?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
         <v>1</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>46013.84800925926</v>
+        <v>46014.32847222222</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Balanced effort guides Gamecocks past South Carolina State, 95-70 - WYFF News 4</t>
+          <t>Croatian school killer gets maximum 50-year prison term - newswav.com</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 05:02:00 GMT</t>
+          <t>Tue, 23 Dec 2025 14:54:02 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbkpQamxvU1dUSjBGVXg3N0pmR2gxZ2xWQTFSU0FuekNXQl9UanUyeDNNd05RTHl1M0xPMElLR0Rid0JGNjgxc1ZnYTc3Ym5yZ2d5RUZ0TEtTMGZrNXNyNmpHZ2VTbzBCcklWTW5FYXVBa1ZzYjRIRHE0NUJHNmtHMGc1RmZESjJJN2E2MUg1MWhNYVhNNzlMSEpwNHgwVVZlV1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNMEhldlF0QjNSWDdnWmdhNzZ4cV9ObEloa0hHMVc5aU94czFJb041cDNQQjBDc2RpbXRnTmFwYUZTclVYc0V4bVBKX1V3cktYRTdyZk9USTRzb2NRbkpHck9rTU05cXpDZHY2ZFM4T2ZSSEdzQV9FS2ctWDRKb05oTS1CcHJsVUhJeEp3d0x2cnFIRFhEV2o3VDg5eU0?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>46014.20972222222</v>
+        <v>46014.62085648148</v>
       </c>
     </row>
     <row r="138">
@@ -4970,24 +4970,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Terror on board Air France jet as plane plummets 30,000ft - Daily Mail</t>
+          <t>How “Emily in Paris” season 5 pays tribute to assistant director who died during filming - MSN</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:08:03 GMT</t>
+          <t>Tue, 23 Dec 2025 20:14:34 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPZ056VFBTcklVYWhpNG5NdnI0OGR0STNRUXRvSkxQcTY3Y3hhdHlOdFQ4UHRFYV92OTV6STc3M0N6WEFaVXYtbFowbW1FbV83YWZheXFtS0huMGZuOG4zTThtU3o1cW5YbW85cUNid1JVbXNqSFVqZUNBWWJadWhwdUZUa2ZqWldkM1FnaF9Mb2dfaEJ1TFJkQnVXaFVIZ29rSGVEU3BnOFBHZTQyNVdST0ZQc1ZUeEN3c2M1NFdLMGlMSXRaYS04UWw5RnRjVU9QM1VHeWZJNF9kTXlWQzRMSDZUU0R0VWJUM2FRYm1FWWxJcWt4a1BSR2xlVmlvdm9GUFUyTWdBTmhUMllJTDhTVVRkamVQX0cyTjBEZ3M1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQMWtybmxuQmJkclp2djNwWGh2QVlGS0xfOTY0dHpyNkZlRlZxWWVFNDkwaXlGMlJHTHFNSjJRdGxuLVZfbF9nR1h5Q0U2MzhXRW4zRlZIYUVUaE9waFd3Rjh0ZDZEVWNfMTZfNzlpdFI3NmNkVkhaZGZUb01BdXlyT1FqN3o4N3Juby1KTmVHREFMQjZwYWRZdHlac0xNNDBLQTVMV2pkb0VvbXRPRkJoYXE4Q0lSVnlmWVFJd0RZS0FWSERDREVnRGthZkQ?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>46013.50559027777</v>
+        <v>46014.84344907408</v>
       </c>
     </row>
     <row r="139">
@@ -5003,24 +5003,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>"Sky Zone Takeover" social media trend sparks police response at Tulsa trampoline park - fox23.com</t>
+          <t>Reality TV Casting Booms As Maya Jama Shines In Paris - Evrim Ağacı</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 02:58:00 GMT</t>
+          <t>Tue, 23 Dec 2025 21:30:45 GMT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQSF92aTV0cE93Y1lVU0NNSnRoa01GLXo0dHdjOE5lZGJtMkc4LUk1S3R4QjdDUHhObGZwTWxFc1VIalRIa2QzdGR6TmpOTEN5WnUyUUNyZ1cyb1g4ZW5aRFNacnltbkdpeDlBXzRCazJhMXNmcHN0NVRQblFDWGFqaWs5NE9HXy1BUnAzQnJ3M0g1RHZEeXFDczlZem5oZzhCVWhDRkRta0w2UWVPMFY5bmQ5NWRScnRhZFVpRzg3R0VUei1SX2ZYWTlPekpPRU9yZnBwVkZlSk10VERJU2NxdEZIa21IVUtmQ0NMcVZYQVZpbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOX0hEUTlkdWkzQVh3bjBvbjVzM0EtQ0Vfd2pYdzlUYlJhRG1IdXFfaUl1ZW5Da2M0UDFEemN4Vk92RGp3TGN5TjVsY0RpT0JDU1p1WTJhX1EtWU5FdEZkYjJKY21iZk04cTRLNmw2ZkRXZzV0cUlETy1rVml3Z1VxU01jbEhZR1BpdGw0ZkV6Zmc?oc=5</t>
         </is>
       </c>
       <c r="F139" t="n">
         <v>1</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>46014.12361111111</v>
+        <v>46014.89635416667</v>
       </c>
     </row>
     <row r="140">
@@ -5036,24 +5036,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>South Carolina QB LaNorris Sellers stays put, vows stronger return for 2026 season - WACH</t>
+          <t>District Attorney Larry Krasner Announces First Degree Murder Conviction and Sentencing of Sabir Bunch for Double Homicide Shooting - phillyda.org</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:43:41 GMT</t>
+          <t>Wed, 24 Dec 2025 01:14:21 GMT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPN0RxdlEtOHVLQjFBUVp3Q1dzVTJ4UlJTY1FlODExYXhHdlg3WEdFVFZaTnZsUFk0M2tQWWI2MFRoNGNscmFnRnMzWTVmR1AydHJMakdENWxlYU9Ubl9LMk4wclktYW9JakV5NXQ5Tk9wVkI0UnZseGJQMHZDY3kzYWpSY1hhODBpWHFfTjlhVnd3OElxaVhFMEVsS2ZPREdSTWZUdGpHN3lDOXo2Q0tvbEJ5ZTFsQ3hSX3ZV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNYWJpRHBfclA1Ym1tMlVwcmdUakJGeXROSFoyRGNRRlN6NnJwUFRqdmxXT0RKcGdFMXRRc09LRHJCbzJWYnFmZmZtdjhfR2d0SG5XYllaTkJJNE85Z25FU0EtbnNtcC0wWmktV2xJMFRZcVFPRWpvYUlaWEg2UjR3eFE1ZWtKUzg5d3puWXpBZnlaRFhaUVN5RUt4NTdRRDVQenVYNTJSeHpHNVN3SG9GaXN5YVdfZlRObG83SG9fbGdmWGtEdkdnb05kTkV6SlRiMnpjN05BUzVEU0VETDNESDlQUGk5LUpLN2FtQmtMUQ?oc=5</t>
         </is>
       </c>
       <c r="F140" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>46013.94700231482</v>
+        <v>46015.05163194444</v>
       </c>
     </row>
     <row r="141">
@@ -5069,24 +5069,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SAI Governing Body approves infrastructure upgrade at centres across India - Sportstar</t>
+          <t>Two men found guilty of UK plot to kill hundreds of Jews as IS fears grow - Reuters</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:26:06 GMT</t>
+          <t>Tue, 23 Dec 2025 20:27:11 GMT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQMXNtMUgzTW1JNm5xc0NLWjVEVVAyRnNFaWsyVWZQck1zM3poODR2c1RuTFY3OEpoTF9GZ2pTQjhvaUZxay1hR3FTb1kwbXI3OFJaQnJ4T3BjaTVpZEZXd29Iek4zWHdOY1RUS29CWUhFYm5ic0NCdUszMVp3TXNOd1VvVG1aV2NMOExGcUdua294TWF4VnkxVktjUXpyUk1ibURFZTV5WEZ5VFJFbFRDbHNIUTZ2M1BrRExoMW9kcWxlRWNxbG5EOHZ4R3A0M2JXWWh2YThR0gHWAUFVX3lxTFAxc20xSDNNbUk2bnFzQ0taNURVUDJGc0VpazJVZlByTXMzemg4NHZzVG5MVjc4SmhMX0ZnalNCOG9pRnFrLWFHcVNvWTBtcjc4UlpCcnhPcGNpNWlkRld3b0h6TjNYd05jVFRLb0JZSEVibmJzQ0J1SzMxWndNc053VW9UbVpXY0w4TEZxR25rb3hNYXhWeTFWS2NRenJSTWJtREVlNXlYRnlUUkVsVENsc0hRNnYzUGtETGgxb2RxbGVFY3FsbkQ4dnhHcDQzYldZaHZhOFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPZUpLOU4wQk5HbUhXalgtU3lldzFRQ0c0dmg3bVEzMGtjVlNPankzVXB3UDAzeXNXRVJKbERUOGhzWnVQcGVoTlpBM2gxRzJzNlNTRU9RX0RlYnBJZ2dvMk9OX3hpV2ZUdElsbWdMb2ptNnlvQkNUcjh2WE9GWWFwQ1gxOVpGNG0zSS1xcHhydTRmZGVKeFN1UjBpRl9VRm1QM1NBNDBEeXA2REdZRVlzMzh2dDJQQlA4OGc5ckNadw?oc=5</t>
         </is>
       </c>
       <c r="F141" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>46013.643125</v>
+        <v>46014.85221064815</v>
       </c>
     </row>
     <row r="142">
@@ -5102,24 +5102,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SAI Governing Body Approves New Hockey Turf For Bengaluru; Electronic Targets For Karni Singh Shooting Ranges - Ommcom News</t>
+          <t>This Is How They Advertise Absolute Batman In Paris, France - Bleeding Cool News</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:04:25 GMT</t>
+          <t>Tue, 23 Dec 2025 19:57:05 GMT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPQkJPUVEtQ2Vyd1lFcEQ5ZldVUkk4ZUN3M0RDR3RDZnhIZFY3d0N3MFRRZU5Ea05mQm1LenluVG9HZE5iVlU4RUhtY2xMUTNkZUdjRHFtY1NHUTVZdm9NT3VOZXpLazB1RThYZEstNXNnVlBvMWdrQUZpYzJ1VUJITHhac2Y5TFkxS1NwRG9rTjhzeURQcXZ3bGhpWW9sSC0zRFFpanZhWEY5S1Q3YWkwd2V2bTZ3TFFIQ3RYckgyX2xmTTZOZE9RS0lmSFlFcm1iM01YZndtTUdKMFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPOGdNRnNLbDJYVEN2UUkzRWZRVzNYQnotWGpJaXh0dFp0Sllmc1pnOVVGWmhvR25ZMnNUVThyYldoT2t1UFpMNktadnFjd0pvWTh1dnhibkdHZS1Tb3NxX2FzUWs2ekZSSEcwM3BTSHczUjRjYms3MTBDY3VBcFc2WDVlVEMzbldSalE3cXFlRTI4OXFJQ1E?oc=5</t>
         </is>
       </c>
       <c r="F142" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>46013.6697337963</v>
+        <v>46014.83130787037</v>
       </c>
     </row>
     <row r="143">
@@ -5135,24 +5135,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Judge sentences defendant for 2023 fatal shooting of man family says was gentle-natured - WKBN.com</t>
+          <t>Four in critical condition after blast destroys house near Paris - PHOTO - Caliber.Az</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:41:02 GMT</t>
+          <t>Tue, 23 Dec 2025 15:50:31 GMT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOUWVjWXlYdTYwcXRzdmdubm02NzIwdVVqUTFoTHEyTkRvUWhLSi0zdXNRNGhvTVN5WXdjRGNZXzloRXlmQ1VydUhmWFh2TkJFTE9mMjZlbkFDSzUtN0F0ZDZtdjZXRG5hYmVnR1dtZjA5OUR5OGtuQzFxdU93WVgwWmxVbF9mQl92R25TTWpKNkxEX2hfR0VKeUdKRlJ5RVlMWnR4LXhZeTltSEVOY2lyU3hJQktsUzBTd0ZoTW5reFN1cU5EWFR6ZmItOE52bUVSQVVnZGluVkJhSnhjR3fSAd4BQVVfeXFMTlFlY1l5WHU2MHF0c3Znbm5tNjcyMHVValExaExxMk5Eb1FoS0otM3VzUTRob01TeVl3Y0RjWV85aEV5ZkNVcnVIZlhYdk5CRUxPZjI2ZW5BQ0s1LTdBdGQ2bXY2V0RuYWJlZ0dXbWYwOTlEeThrbkMxcXVPd1lYMFpsVWxfZkJfdkduU01qSjZMRF9oX0dFSnlHSkZSeUVZTFp0eC14WXk5bUhFTmNpclN4SUJLbFMwU3dGaE1ua3hTdXFORFhUemZiLThOdm1FUkFVZ2RpblZCYUp4Y0d3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQNDB3R09WUEMwNkN1WHZNZ2FIRDBCeUdyWlhSTElYQ09QcWFZWHBzbWdXQWxHbUlRMmZFbmhpVXpBVC1UMzRHYXdCOVpDT2Y5X05rc1BDUFlFWWJQbklBWG53R3dHWm1WMXRGUHFiSEZqZ2p1V29kbi1HODZxNjZRRGVhUTcxaUVtXzRUV1ROUTRaWk5BRkE?oc=5</t>
         </is>
       </c>
       <c r="F143" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>46013.44516203704</v>
+        <v>46014.66008101852</v>
       </c>
     </row>
     <row r="144">
@@ -5168,24 +5168,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Filming locations of Emily in Paris season 5 - Prestige Hong Kong</t>
+          <t>Three children and adult seriously injured in explosion near Paris - Yahoo</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:11:15 GMT</t>
+          <t>Tue, 23 Dec 2025 12:55:16 GMT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNREdIOUxWVDNxbXFCOG9CTHhlR3R5VElJSUdSUVdVeVgyOE9DWVdRc2xoVkQ2QWxMRnFZMWM0WlZrTU1yOWItSVZXS09mRE1PWDlQUEVzbG1HdmtOMFNZNXNIOHdkNUZpMEZOM0pyNGpiZHFicE14SGFjOGduQ0poc2VtQ0k4X09tMXZRX3JHU1BqdkNNWVhZaEhZemc1LTJERmE0RGZianMxVlhRc0kxbG5nQ3VhdDd1VFFTdDdPT3hZQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQNkx2Z0dKUWJuNmpuZnhPOTdlUEI0RUJQa2VKUzlMSEZQZ0FFN1FwNzR5cU52UGY3NkoyejRRU2VGdG9LNk5sUFJxSV9EVW92Q3hXRmN3NndNMXI5SFlnMEdjRUxJcEw4YU85dGtKNXlrYUVpdlJtQ19HMjNaZ2x2cy1IY1hJZnU0b0E0X0dlTVJwTWM?oc=5</t>
         </is>
       </c>
       <c r="F144" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>46013.3828125</v>
+        <v>46014.53837962963</v>
       </c>
     </row>
     <row r="145">
@@ -5201,24 +5201,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>“Emily in Paris”' William Abadie Reveals the Extreme Sport He's Competing in This Winter: 'I Think I'm Still 20' (Exclusive) - Yahoo News Singapore</t>
+          <t>‘Emily in Paris’ Star Ashley Park’s 5 Favorite Places in Rome - The New York Times</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:36:30 GMT</t>
+          <t>Tue, 23 Dec 2025 10:02:55 GMT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNU1dieW5ENFcyd1Q0YzBjZGF4dXNQdVZhbExvNm9WbDBsWThGUmM5bTBKaXo0SkwtMmdHWVIyci1NYVF3bnRmSzRIek9abkdjaTRBbDZJaGlXMzl3emk0cjNKLTFjZDg5UUNCc0I5MjhhWmc1ZEI3MzVBU2NDSlFxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOZ3pwaXg0cnlweGE0dXNLZEU2bGlzY0FWR0ZkWE9oVGZkOV93OXJlazN1R1pzWHk2b29WaFhKQXB3bTVncnZnYlVVbzcxa1VVcEtPVW9kOURxTHFpNktPOUVvZ0lSSGxFWVRNWmx2bTlnZ1NycHdMR0cwTU5uVEkzb05GUF8?oc=5</t>
         </is>
       </c>
       <c r="F145" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>46013.85868055555</v>
+        <v>46014.41869212963</v>
       </c>
     </row>
     <row r="146">
@@ -5234,24 +5234,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Arts Vanity: Gen Z TV Shows to Add to Your Golden Age Favs - The Harvard Crimson</t>
+          <t>Just before Hanukkah attack, Jewish mayor of Bondi Beach region had been praised for fighting antisemitism - Jewish Telegraphic Agency</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 03:35:02 GMT</t>
+          <t>Tue, 23 Dec 2025 17:50:24 GMT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQVGlGNS02MGY2ZXlGYVZDbnljTExha1EzYjNYWmhYTXBwWnNTUlNCbDFjdjJWTkxuTTRKRXFfY3EzeTR4ckNSOHV5V2l5TTBsak9pcklqb3dwS3hrQTh0Q09mWDk3aUIzX2Jkc3ozdm1mMjIzSnpfQmlPQVNjMDlCdTBDU0ZucXN4NU1jZkV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNM19mVlE0aVNDQ2g0U2dLWXF1WFYzdTR3YTh6ZmJvazkwcEY2bnFPV2t3YTQ1V05kNVZPaW16TDBQNWtXVG9OejZhZlppanA3dk5tY2QxWlVKX1M0NTNlQVdFMWh5Tk0zeVpsSnpUbW4wZzVkalhXZzdVQWxOQzUtWFJGZjA2OF93TlFnZXdGbksxcU0xZEFyYWUxdi1RZ3I3Q2lfbHZ1T19rdHFRVVM2RlhTWnUxMmFBaUp2VnR1Q1BIbUR3S2RVS1RaUHplLWQ3OUUxU3BnRzNaOWM?oc=5</t>
         </is>
       </c>
       <c r="F146" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>46014.1493287037</v>
+        <v>46014.74333333333</v>
       </c>
     </row>
     <row r="147">
@@ -5267,24 +5267,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>The Boys: Season 5, the final chapter, finally unveils itself - Sortir à Paris</t>
+          <t>Public safety concerns lead to cancellation of major New Year’s Eve events: What to know - AOL.com</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 20:58:07 GMT</t>
+          <t>Wed, 24 Dec 2025 03:14:28 GMT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVkl0MHl6cWtZX0pLa3ZnclhNcExJMUh2SjlqZHpPQjZMelRSSEhKNkJRZkJmT0Y4eURobk1QOXZ0V0dpRWhmbFNINkVCWGFGSXQ5TU4ydlVKT2h6Z2w4QlhwTzZzZU5UYnRRZjk2SkZnOVhaS2ZjUVl1UWhCekFWWHRpMVV1RUZFQjIxdGFpQllqcVlIT2xFSVpCZUNOM3p5U0pLVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNVnM1Y2VrN1BubkVqakxlRHpGdUJNeXllS1dxMG96UGdsdFgxcE5lMVlnNWZ3SzBUVEZDNW4ydS1Ka2dYNVpuczRPSE5yRGNDVWJueWZGVENiejdzTzFPbFAzOXJ1eUZoRDE0OWMzM3lGSXVERDVZOVFkalM1c0U5dk15RWJzd2hqRkNpQw?oc=5</t>
         </is>
       </c>
       <c r="F147" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>46013.87369212963</v>
+        <v>46015.13504629629</v>
       </c>
     </row>
     <row r="148">
@@ -5300,24 +5300,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Gamecock Women's Basketball secures French recruit, to join team after holiday break - WCIV</t>
+          <t>Terror on board Air France jet as plane plummets 30,000ft - Daily Mail</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 03:12:17 GMT</t>
+          <t>Tue, 23 Dec 2025 15:57:30 GMT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxQVDV5Q1d2ZXUzLTZxOHBFYVp0eW9rUjAtMXhuNGVnVFlYRjlOZ1Y5RXBlbEMzNVg0cGkwWjBwblhkeFpGVWpzX2V2bUJDclNjYXQ2c3pCZjZFTnVmLTA1ODIybUNEaExMVC1NUm9nRHlvREE2bGRwYkRmZGZ2M0tqNDNzYVBEQWVxV0pOWDhMMVhaSVBpSy1qMjF1T2l0WHFYZ1BzSW4xdDFGQVBPSUZQN0dlRWNZZ2hEV3k0VzJvTTF6S1BzTTQxM2JIM3BOZXYwQVJWb1FBdGxWSG5fUFY0Z3RlN294NXoteGpTNGpYemxwSTZ3UnpDeUVDM1U0YlNuSFgySE1CZUVRZU9kN09uVkJfVmgydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV95cUxPZ056VFBTcklVYWhpNG5NdnI0OGR0STNRUXRvSkxQcTY3Y3hhdHlOdFQ4UHRFYV92OTV6STc3M0N6WEFaVXYtbFowbW1FbV83YWZheXFtS0huMGZuOG4zTThtU3o1cW5YbW85cUNid1JVbXNqSFVqZUNBWWJadWhwdUZUa2ZqWldkM1FnaF9Mb2dfaEJ1TFJkQnVXaFVIZ29rSGVEU3BnOFBHZTQyNVdST0ZQc1ZUeEN3c2M1NFdLMGlMSXRaYS04UWw5RnRjVU9QM1VHeWZJNF9kTXlWQzRMSDZUU0R0VWJUM2FRYm1FWWxJcWt4a1BSR2xlVmlvdm9GUFUyTWdBTmhUMllJTDhTVVRkamVQX0cyTjBEZ3M1QQ?oc=5</t>
         </is>
       </c>
       <c r="F148" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>46014.13353009259</v>
+        <v>46014.66493055555</v>
       </c>
     </row>
     <row r="149">
@@ -5333,24 +5333,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bondi Beach shooting suspect conducted firearms training with his father, Australian police say - ABC7 New York</t>
+          <t>Louvre tightens security after $102M jewel heist, installs bars on infamous window - Boston Herald</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:30:48 GMT</t>
+          <t>Tue, 23 Dec 2025 15:54:42 GMT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPSXh3UlZlY1h6c2NydGhmb19EYmtONFFMZUlzM042NFZwaHZMN29FaHVzdHZZQWpYdjlRakx1aGJLTTc4U1FpVEsyMWZHaDVlMVJFOHFVcktwNkg1S2FCNk1UeUNhSHo4WjBTZk9GNFFDSml4MUxzR1JuZ3lWZ2NqeEZ1aVlJUmtaeWpSOHRrSFV1YlB5T21ERDdxYU9COVc5bGVKSTF5Z3Y4ZF9CeG8wRkFxQlMzQmt1QmRJ0gHAAUFVX3lxTFB2R3NPTlVQVmRTcnNIbFk3RFYzaGxnMHRMbU9fTnFpUm8xSk1VRUxXSF9HbDRXdndVT3NZTHBTWURuNXIwMWJ6ZzRmM3lLQ0dSY1VlV1JWNjBQSkphSWpMOTJHQlp2SURHSXBCZThkbW03cEljUktUZXBmS2tyZGtUUTMxNzJZZXBqUjV0dVdkbkpXbmNEX19nTWstU0xJTFFFdXMyNE5xSlJqZ0I3Y2JoNHFrcjdUMFdTcTJlaEdseQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPNGFNMW5oY1JpLUMxWHNVR1lvTy1iTmRyMlF4b29Scl81aTRheHZIVmtCeERBb09HY2xiYWNvNVNqcFJjYnRRamJiY18xaDVEaEtqcTF5ZERQVjlDUlQ5d2ZjRTZVcFhIV3hTZE5yX0dtd3hqSWRCSnZpZzVWdDE0RkxB0gGCAUFVX3lxTE80YU0xbmhjUmktQzFYc1VHWW9PLWJOZHIyUXhvb1JyXzVpNGF4dkhWa0J4REFvT0djbGJhY281U2pwUmNidFFqYmJjXzFoNURoS2pxMXlkRFBWOUNSVDl3ZmNFNlVwWEhXeFNkTnJfR213eGpJZEJKdmlnNVZ0MTRGTEE?oc=5</t>
         </is>
       </c>
       <c r="F149" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>46013.60472222222</v>
+        <v>46014.66298611111</v>
       </c>
     </row>
     <row r="150">
@@ -5366,24 +5366,24 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cyberattack disrupts France's postal service and banking during Christmas rush - ClickOnDetroit | WDIV Local 4</t>
+          <t>🚨🇬🇧 RESTAURANT OWNER SOLD EVERYTHING TO BUY AK-47S FOR "DEADLIEST UK TERROR ATTACK IN HISTORY" Walid Saadaoui hero-worshipped the Paris attacks mastermind. He wanted his own 130-body-count moment. So the 38-year-old Tuni - x.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:18:24 GMT</t>
+          <t>Tue, 23 Dec 2025 13:35:18 GMT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNYlRkSHBCMzNDRWRKV0NCa0RXdHdZSXlhMTNCcUxaeGxGVnRKWWhnMVFJWkRZS0pJbktxMGlZZVRqZFBNSDJ2WFlOM1ZLZlBBbGJFc25XNGFuUEhkbW5oSExiQldXVlQ2dlBWOUN3d0lxWDkwNnR2bEpnNjd3X1RMNC1YX2FHZHQxZ1JTUUdZU3o4dkJTbEY1eGgtRk1PLXJXRkJFTmd2Qk9YN3otemsyNERhNFN2TTBvOHl4U0VvSWRNWVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9CVTU4ZzZEVDE4ZE02VkJwVG5wUG1Jdngxc3lLelZWMzRnNmxkc1JGRGtEaE4wRHdWLVZJb0swa2dNdHFtVUdmTG4zaW0tT284NEtkdEJvMkl6RXplLVdQdEdn?oc=5</t>
         </is>
       </c>
       <c r="F150" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>46013.55444444445</v>
+        <v>46014.56618055556</v>
       </c>
     </row>
     <row r="151">
@@ -5399,24 +5399,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>American WWII bomb found buried in Hong Kong, thousands evacuated - AOL.com</t>
+          <t>Dylan Stewart announces his return to South Carolina - WACH</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:36:42 GMT</t>
+          <t>Tue, 23 Dec 2025 23:14:40 GMT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQdmtJOXppSzlCZnpOZDE3UFgxaGVwQm5KR2tDOWFLN2xlcXBKcEFhdXRiQUIxXzRGa0R6LVJPUm5TRTV3blNrNFpiYUIyMzdnRElpN242cmpmQVVvd3VSNEZVWW1wb2luNzNXZzEyb2xiWF8ycFhzX3dKU2t4LWtzaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQLTBOY2RTcGM3S2R3eTRjWkxtbWNQS1VlVmtZQkF4SXYtY1NQZDI4eHMxVlFITV9GSTlSdjFINVNkMmdCdmw5eGo5YUF5UTlCdXp3amdnRC1RZFNhbVhtcXFlRGFFYjZNNF91RWpaamNFMjJSbFF1bUpMWUJLZUF1V3prZW5NaWtXTW9CdEdUZkdSenJp?oc=5</t>
         </is>
       </c>
       <c r="F151" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>46013.35881944445</v>
+        <v>46014.96851851852</v>
       </c>
     </row>
     <row r="152">
@@ -5432,24 +5432,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CCU to host SC Republican gubernatorial debate - WCIV</t>
+          <t>Harsha Engineers International Limited Recovery Linked to Earnings Surprise - Volume Weighted Average Price &amp; Explosive Profit Potential - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:19:47 GMT</t>
+          <t>Tue, 23 Dec 2025 08:36:55 GMT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxONW9Sb3dBRVFxS0N3NGR5Smp4WGNaVEgwZGE3WlowMkxpcnpqMTNSeGxGcm9DRmY1Mi1ELWpTQWZad2xnUkdsSGRRU3RMQVJnSjRpWS1wMVFTbEVDdzFnckNLZ2FvaE9uc280ck1EeDdmMW1pQTV6Y0pHWFN2ZUpkN3RKcWl6anQ3cEdISDNVUzRJVVZXeDR3aXNIOEtUTmpYby0tQUZTTm1WcmFCTE10MkNHckxBOGxnYk5zQXNkNXotMUg0ZnA3Y3BkNll6WDRBbjI1RWVjTFZnQV83MXh6QlhKck1GazZk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOQTVIZm9KbHJIMnh1UlE5QlpFeFFsVEJfX0ExY2tEdXZhanFjSjNkLS1LU1d5U3FHTEo4dTJpTjZJMXRUa1JSN3Q4R3pmZDZUd2J2TFNEVlJBUENYMkFEclJyT3g0SmVlNDhQeEFUOW43dkE1bXBacVkwajJQaDZ5OVZGOTBYWVFYX0dQYmFmcGg2Sk4zUjlMbmFiV0xuMy1HVVZVaDlqNUlDRkRkcldiLQ?oc=5</t>
         </is>
       </c>
       <c r="F152" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>46013.93040509259</v>
+        <v>46014.35896990741</v>
       </c>
     </row>
     <row r="153">
@@ -5465,24 +5465,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Suspect charged in shooting death on June 13 | Here's what we know - WXII</t>
+          <t>Omari Moore slices through the lane for the explosive jam! Motorola Magic Moment - Euroleague Basketball</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:17:00 GMT</t>
+          <t>Tue, 23 Dec 2025 21:09:56 GMT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9zb29lM3BjeDFRMkU0d0FYNHVqTmc1cVVsOWJsZ3ZablVhYVdrcHh4YmoxZjc0VlB3eEJRT3VUT2t3OVRIWUFLczVOUjBkUVdYZFJIVEtzb2NTS1M4MFY3VXY0a1B2aWtVc25aYURFTmNvWlo4NkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOcVYxSTNpanFZX216eWs5TnRrZ093OUlDUGoyVW9tRlpnLUc0OFNfQWIzd1E4MnIzODFlWlBSb2E1dmVmWk03ZUZwVTNJalBuSGtEaGowNk4wS3ROejZUWVpMcm13MGNyQ3ZIcEdEZjNrY3k2QWxuanRXSTBPeGZuSy1tNm1Qdkt1eXJWQkR1a1Y5TmFXazJ4ZGNxb1ZyWXJXZGlsd05uVzJqY1JyR25meXZWOVY3Z01DbHY2d3hPWlc2NmRrd2xUb09ETnBKeVBYS0E?oc=5</t>
         </is>
       </c>
       <c r="F153" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>46013.92847222222</v>
+        <v>46014.88189814815</v>
       </c>
     </row>
     <row r="154">
@@ -5498,24 +5498,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Everything Lamont Paris said after South Carolina's win over SC State - On3</t>
+          <t>The Pluribus Season 1 Finale Answers Some Questions—and Raises One Big One - elle.com</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 05:04:39 GMT</t>
+          <t>Wed, 24 Dec 2025 03:01:07 GMT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQa3NfVzdJQXZieGlmV0ZwWmVjcUNRVV9wVk9kUmlCNFB6ZVh1NXpENFY2dmtINVlnRzRXOUVlNjhGYmwyWGdlbWttbEFFcGVZdnNRS2RseHEzY3FQSkVXamlpN0dTTExSVnhJc3NZR3FXVW1FcWpxLXhxZFFYVC1Ca1RJamZONzZLamEzTHA2VlQ3SEdZUDg3MXY3UkVfVEsxb0RDcnpXV0U2VmljX1Q2Q2xPUVo4eVhKcjlPVV9STDZlc2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPbFhrZHhEV1NTNGRXWUhQdFMydGVjcVJiYnBRbjU0WFNQT2RpSGtKdV84V2Vxam93eVc1eVRmb0o3S1RrZVdUbEZoR19aVk9XR0prR3hHTGZ2UXVQVHdRY1pVT2hGVmxIQjFmeGZJcVRJNzhBVHVXcFJHQnV1NTJneEpROG1oRHBLUzR2U0pKa2hVeW9xbmc?oc=5</t>
         </is>
       </c>
       <c r="F154" t="n">
         <v>1</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>46014.2115625</v>
+        <v>46015.12577546296</v>
       </c>
     </row>
     <row r="155">
@@ -5531,24 +5531,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>South Carolina MBB heads into holidays with home win over SC State. What we learned - The State</t>
+          <t>Margaret Thatcher 'ignored French assassination threat despite high risk and warnings' - Daily Mail</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 23:02:00 GMT</t>
+          <t>Wed, 24 Dec 2025 00:53:00 GMT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQamttWGVCSmlFVnBvQUNhRFdrdVh2REZHaWNuQjlFc3JOcnpsVVdrR1NESllzOGdwVkV6dF95d2Vjem9vU3M0aVoyNDZkUkRTRFlRajBVLUNnV2hZRXBNWlBESUVMMjVSZDRyS0hURHUzZmtSLTdCRG41Zm1wQnYwQUpELTZhZk5KRWNjQTg0dmhtWGhXVHdxT0dkMUdxUW1HUldHdWlCUXYyRWZhQzZZ0gGvAUFVX3lxTE5xMmNTYUE3MlZpbWExdzZ3Vm82Z0VlZndrOExGNDdVa3NNNXQyajBJeHR5ZjktZXU1b3otYVZlS2g4SHJlaWM3S0dNNllyZWJvYzBRelZJVlBjSHpWckJKbDVZWlB6Vm9JMEc2Y0RiMlVuOVllWThMTk5qazBBQ1ZLNXRIdG9JbXRrQWg5Z2l3Ry1CQ1FLdWtpTExNWVJCQXBLMmpnb1BXc0ZndEFMMTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOR0FCSl9IN3d6Rk9kSndnREFvczNLUTZoVkU4bEIzSjZ4X1dlT1Rsck93N05rY3ZQN2xpVjJDVmlIMDhvaWtUOTFXc0ZtODVuTVItWTZRekNXUVByc2lfTmltNHFwNk5rRDlaMDJDczlITmtGZm1QUmZtSW1nd1l0OURUTkNUZWdkRmtoVTNiZW1OOVdSNVhaZWNQdUg4NmNJSTl2RUZOSkRydUFPVnhvdDRzVklqLUxQNl96NGlMN2theS1fYnfSAcsBQVVfeXFMTlhwMHpsNjhmaFhYSmRoSzdYNnkyZ1dSR0VoMjAxZTNPMWdYNTRLa1VHZ1RtVUNvZXhsb3VCZzRldjlkVHFfTERQTy0wUUROLUhGd1ZZdlVMS0E4aDRfTUMxZlN4eVhtOE9MWDN0MlpVU1RPTXh2Sk1XQWZ1MU1IZGowWWVwamNxQkRKaWxIbjFXS3I3aVRXQzJaVWtTejRfYWluQWZvVHJSaHdLNmlabDlxbXVocWpfNjRHWnBQRUJIaTRMOGNSbTFRMXc?oc=5</t>
         </is>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>46013.95972222222</v>
+        <v>46015.03680555556</v>
       </c>
     </row>
     <row r="156">
@@ -5564,24 +5564,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Algeria to criminalize French colonial rule - irishsun.com</t>
+          <t>Four charged in alleged New Year’s Eve California bombing plot - The Desert Sun</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:20:00 GMT</t>
+          <t>Tue, 23 Dec 2025 22:50:00 GMT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNWm03eWQxWGhQZUdjOFRYV0U5d1pNaHkyWlljZVBrT2dwRno2aTFVMDNRRFU5UFRROER3M0dSZWxoMlhFZ3pUVzMtQWJWanlxdXF4N3JHeHhYYkhLZWRDbVFFZWdMVHVDTEtNckx3Uk5EajZjN0JQNnFpdVZ1Ylg3LWp5R25VeFR3OGFz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQWllRTVEzYWdkdHhvWVcyTGpoZFNLM3NKQWhfSHZNZDI3N09FLXpHVl82U0JFcHFtUVhETks5bzdfSHp0a0oxN1F4VmxKbzJkUGdaMUNKRk1DTld3OUNyYzJqN1E1Q2UyZDItNzBUUGNlRzB4ZF9sOEZ4RnJSczkwVlhKTFVHQjdhd0gyNnFGVzk1YWZScTlrdGQ2WlFiRVd4emhmN2JONnZZUkVVVWJFSUlBa2FnWW5haFVESUtlUEU2ZDlUU0JMcUt5TkFOdw?oc=5</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>46013.34722222222</v>
+        <v>46014.95138888889</v>
       </c>
     </row>
     <row r="157">
@@ -5597,24 +5597,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>'60 Minutes' in Turmoil: Sharyn Alfonsi Blasts Bari Weiss Over Axed Segment - TV Insider</t>
+          <t>South African Pub Shooting Leaves 9 Dead, 10 Injured - The North Africa Post</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:06:24 GMT</t>
+          <t>Tue, 23 Dec 2025 13:09:45 GMT</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOWGhvVG5oSzZoNWZ4VjhTNUJjVWJ2NE81WUhabWxfaWRGaS1UTS1JekZjQ29Rb0owOXVid09DZG40S2dpazNNdmNzYU5JWDhkYnQxT0VCU0pZRy1oSzZLaU01aVRackZSdkFOMUo0blVZeGJ1cWd1NkZCSnUyRm0wWFJPalhjUFV2V0xFTmd1Z3I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNUlhRZkhUVEhDUGNObmNtbTVKN3liM014Zk1rNER4cGVGcC0yc2ZNNU90Tk8tb042QkQ5X1I2Ym9LRzNmazZheFM0RU1ZdlNGbEdjNWZfVDNPV0tUMnktYWVwRlhwODRuV19lNnVYZFlYWG5STXhDQ21RYk1qME5yR3lvR28wOFkwcXQ5VDVHOUJnLUhE?oc=5</t>
         </is>
       </c>
       <c r="F157" t="n">
         <v>1</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>46013.54611111111</v>
+        <v>46014.5484375</v>
       </c>
     </row>
     <row r="158">
@@ -5630,981 +5630,981 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Lin Zhipeng (aka No.223) on nudity, Paris and forbidden love - Dazed</t>
+          <t>Arts Vanity: Gen Z TV Shows to Add to Your Golden Age Favs - The Harvard Crimson</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:02:00 GMT</t>
+          <t>Tue, 23 Dec 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOZUFIR1hYbmg0b0tPUzhOaUlmMnNnY24wRDZybnBiRnNxQXZKTTV1MTYxX2lYcXA4Q19kY2VrQ1RNU3ZGakxhZkNJM21zcG5mYlkxSjlRcGVoUkJXcjJBMkJuREpkQ09VZkNoZ2I2RnhiOTdiUktqT0ZZak5JNjN3ZHVScFJENmU0UEQycUh4TEVkT1hkOGpGbnp6QmJobDJuM1FtaTNwcEx5VnRZZ0lZck9EbXA4U3dFbjFfWFJjMWJIRGtEaW1ucw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQVGlGNS02MGY2ZXlGYVZDbnljTExha1EzYjNYWmhYTXBwWnNTUlNCbDFjdjJWTkxuTTRKRXFfY3EzeTR4ckNSOHV5V2l5TTBsak9pcklqb3dwS3hrQTh0Q09mWDk3aUIzX2Jkc3ozdm1mMjIzSnpfQmlPQVNjMDlCdTBDU0ZucXN4NU1jZkV3?oc=5</t>
         </is>
       </c>
       <c r="F158" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>46013.37638888889</v>
+        <v>46014.33333333334</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Can Tirupati Forge Limited (TIRUPATIFL) Maintain Its Valuation - Equity Performance Review &amp; Double Digit Returns - Bollywood Helpline</t>
+          <t>‘Black In Paris’ —This Is the Exhibit Shedding Light On How Our Legends Lived Abroad - EBONY Magazine</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:30:28 GMT</t>
+          <t>Tue, 23 Dec 2025 16:51:05 GMT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPektWNzExdzdNczZOMF9qSk51bVNQNkdBLWt2VHhueTRlcVVvRXl4SEtWMmhqUm1CRFhWMkRWNGQxSWQwOXh0ZXl6SFpOU3RWWnIySm51aDQxLWRwcjZpRGlIY05IU2Q1MkZ0QWY0OUo0Q3FtUEdRZUpHWW1mYlFMSHotMHBfZlRmUVBELTQ4X09pSGY1RmZiaXU0c3VGSnZwV2ZwQW9MT0Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNaTNkNGxhOVBpeHFjRF9jdGlQWXg1SHRFazQ0QjRrRmh4a1A0aE1JWjNLMlZOeUx3NGF5UmtGa254X0tQY2tOSmppdWZ0TzNKSnBBZ3NIVC1tZnk0Z3lMa2hRZTJMTmhONkFlQTlESmFvTVdRZ3otUGxfdksxeDgzU21PNA?oc=5</t>
         </is>
       </c>
       <c r="F159" t="n">
         <v>1</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>46013.72949074074</v>
+        <v>46014.70214120371</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Napoli Wins the Italian Super Cup Against Bologna - ysscores.com</t>
+          <t>Twilight Chapter 1, a fantasy romance, scheduled to debut on Prime Video in 2026 - Sortir à Paris</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 21:47:40 GMT</t>
+          <t>Tue, 23 Dec 2025 12:33:42 GMT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPcjJ2YmZDallGV2hiSlZnZGFPcmxuQnRNSjlQd3dETXg0Qm9GLVpHTWFGMmlZeDd5ZGVZRzhtaXNURnBNQ01NbDNKXzM4aTctTExTLVpOUVVvcWhXaGROV2Vra0RBNmxSNER6c3pINjZSb0FsajZuSHR5eERWQlB1ekdncjYxX1BiUXJHY3lRamhMUHRHdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQSmVuM2JpZExzUkhQTnFRVHZEQkxNMzZWU2xPSkJwdGpJSjhSckpyWThzZlVUbEduMXctUWg1ZDk0SldXQ1NoV1NJdXVzNEgtbVB6YUFGU0hZMzRXbFBFMkZGZ3ZoV01VRzhEeUtNR1RkSWoydGtQa1VaZnVzYzdUajhFTFRkTHZVcG1vRkxqMFItZVhjS3k5c25JV01tbVVwOGMwRDRkME9EbTBlMkhWX0F3YmNJbU0?oc=5</t>
         </is>
       </c>
       <c r="F160" t="n">
         <v>1</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>46013.90810185186</v>
+        <v>46014.52340277778</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>'I am not weak' says Slot, but Salah could return - AOL.com</t>
+          <t>SC launches Roblox investigation; parents urged to monitor kids' online activity - WCIV</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 22:22:40 GMT</t>
+          <t>Tue, 23 Dec 2025 10:54:56 GMT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFAxZC1UVnFsQ2tOSVdVNlRmaW5XTHU1X3RXeTh2VTdUT01WWGxLVk9QeW1JTnluQTV3cjY1Q0JXeFVHNnBGcUlFeTVMa3Y0cWpHY3ZpeFRjZHJLWmduVTdoNjJfX19fU3BJUkdmaE5qbGJDYjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQTVp2blUxMjU5Rkh0Yml0Ymhvd1dJWHR6TmIzbklNQTR3bnBicGFtclRNS1dSU19qcEZZY05YYnduUV96VXpaMksyNjdqbE1DS1I2NXpXc1RvWW5tTXhlN25ETDNnMENreUppUkZHcmtFMGk3S01WS09PZ0MwcllLSThVQWJycmh2eUh2dHFWQ0hheXhCQ0pEcHljdmUtRXVOdlE?oc=5</t>
         </is>
       </c>
       <c r="F161" t="n">
         <v>1</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>46013.93240740741</v>
+        <v>46014.45481481482</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Milan Momcilovic's not eating jellybeans for each 3-pointer, he's saying the word and watching 'em fall - 247Sports</t>
+          <t>TPD reports woman in critical condition after being shot in head, suspect taken into custody - fox23.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:31:22 GMT</t>
+          <t>Tue, 23 Dec 2025 20:52:00 GMT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPOThYU3RGWE5uajdTVVRxVGcwNTROVHpMc0pQM3NwMnFVdTJCamNHX2FIMUpjZXBXQjZ0TTZRVXFHZ29vUVBOYVl1dlAzRzgzX0cxbFRVSHJteFFvOHlLMXotemxteXcyS2lqVE16QUNQbGc5eXBLb2FWU2E3b2Qwa2xrZmhJRVJrM0tYazBKS2NVUFN6YjJoalpLOTdJMFo0eWUtaGNCcXNiX21SMnZpQ2wxbXNRNHMtQ0Z6ODlsVkQ0eVA5aHBXcVJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQTUFrS19IU3Nxbmk5Z2hWdFZvN1FIYTNMQkZFV0RncDItZ19qT1VNaVZyTTZuSkN4WlYtOWlCSWwxT2VNZE82dVg0RW1SZmhEand1UTd6YkZWZFdGVTg3ZmxnUTZ5THExTG9ET0xFVXBhTzdvSWI2WDMwZkxlVG1IczFjbHN2NTJCZHJSd2FEUk1fN0NObjlOa3JxOElPOWtlNnIxYjhmbXY4UE5DOTlrZGVRSG0xd09YczZmeTdJMHFzTG5WMzR2VzYxb1BkUWJMNld0QnB3ckE5N2s3bHZQWlZ4Qlhzejh1SkxjQ3djU0NtMnBVNy1sTy1HVDY?oc=5</t>
         </is>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>46013.43844907408</v>
+        <v>46014.86944444444</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Iowa State basketball takeaways, Momcilovic scoring, Buchanan progress - The Des Moines Register</t>
+          <t>As demand for year-end home parties increases, the Christmas cake market is heating up rapidly. Pre - 매일경제</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:04:00 GMT</t>
+          <t>Wed, 24 Dec 2025 05:51:00 GMT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxOZkw1ZkVsUHl5cFdQX2JURW9GZWtSeEp3QVV6c2JZX3BFSk5FSkpHT2ZmYVBzQ05GOGhxVFRfQlphWGhsUjhQSVlkbTN6THFFR21tcWk5aktpZVRtdlBaSVNnbnhobm5YRldVOVF4MHVfNG1VV0FzejZHQmJ0V2dGSDhzVVpQd1ZHQXRkbjlweWhNa29kS1VvVXFrU004R1RwY1FMaTltQi1XOE1kSk1JUWNndDZ3bnQ5TEJjaGw4alR3U3RKU0VCV3FFRy1lS1JRWFNaMDFUbkV6RFlaOWxNZzEzU3VHdW9lUEdHSlhIZ21OR1F4empRWHZqcElSa3FmSXdIdFRROE1EcFlNU3BzWnlTZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1KVTd4aV9kVlpkbEFzaUsxWjVjUWx6enFtdXlITWhEN3VQRkNENklPREZ4bW9yV2dVaExITGFnMHV3UXY2S0lVZkdSdkZENFpsNWc?oc=5</t>
         </is>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>46013.50277777778</v>
+        <v>46015.24375</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Italy’s 4 flag bearers for Milan Cortina Winter Olympics honored in handover ceremony - KFOR.com</t>
+          <t>Recovery Signals Appearing in 20 Microns Limited Charts - Dividend Stability Analysis &amp; Free Explosive Earning Power - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:58:41 GMT</t>
+          <t>Tue, 23 Dec 2025 16:17:44 GMT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPUmJCNTNSRDItcHdiS1h3anhWTEpWS3llNURVTUs4VV9uNUJiNnlMUUZvNDVNMHlVbXN3RWJMLWxycXR2OEl0cGdaUm5sMmNTWUdJd3BNZXBWWDR1X2JsSlZVcEs3czZQbmN1ckhUNklIbW5OelRZRHFpZzJ5RmhxR1BjU2dBWEZKS3prbFZwa1VvaDRTQmF2S0pWMFJIOC1LVm14RFU3aE12bmlvM29EdGxiaC1FZWFabV81TFN2aEhsQdIBxwFBVV95cUxOLUVDaUFjOGd3Uk5wQW4xVVBVdnJDbGFhZ24zMjN4bVZoTWRvQXppUXpGNFNPcnJ5aHNodmFYTU9fcWNGUFhWbWtFdkpfaE9xWDRuMkpaTkxjR0V0WVBTZzdlczM4Ukw0dnBYVjc2aW52UEdHejc2VWVSUl80SVg4aUhVY0FQaksxOFhzLWYxbHgwMHdrMU53cWIzTzhVTjFicDY2dndXS3VMRmR3elVuaUZZRHk3eDJFNGZYcEJBYkxjVXVFWWtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPekxMb0hCdkxua19sMm52MlRXaEtrYWs3N0VvRkh6Wm9QSmpVM2lub2w4bzN0NjBUanNaTTBxTFpLdmVlZjFMc0g4a0tpRm1xYmJHM2QzQS1yTW5yY0JLNmdhUlFQdGNRSnkwaUhMWlZVWVZqNG96blVodGx4TFEtZVl5QnBNZGlLcXBNUUdOZWcwRFVmUEJzaGlNZmxveHM?oc=5</t>
         </is>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>46013.70741898148</v>
+        <v>46014.67898148148</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Basketball Recap: Milan Comes Up Short - MaxPreps.com</t>
+          <t>South Carolina MBB heads into holidays with home win over SC State. What we learned - The State</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 07:51:07 GMT</t>
+          <t>Tue, 23 Dec 2025 16:59:38 GMT</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNUJzNU9JTE9kdm5rTTVFaW9UcGZUVTVNYU4zY0M4MWZLVThVUXUyZnVxVEhZMzQ4a1FqNGdOM3lDZk40QmRiV0pZUUh5Z0dsMWxaQ0dfdmJwWUIxak9heERiQWJWZHVVRWdBYzA0VE0xMEJ2NFZ6b28xZ0lDRjF4d3BpdC1YZ1FjSTF6NUFDMFljS1ZMVUlndTB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQamttWGVCSmlFVnBvQUNhRFdrdVh2REZHaWNuQjlFc3JOcnpsVVdrR1NESllzOGdwVkV6dF95d2Vjem9vU3M0aVoyNDZkUkRTRFlRajBVLUNnV2hZRXBNWlBESUVMMjVSZDRyS0hURHUzZmtSLTdCRG41Zm1wQnYwQUpELTZhZk5KRWNjQTg0dmhtWGhXVHdxT0dkMUdxUW1HUldHdWlCUXYyRWZhQzZZ0gGvAUFVX3lxTE5xMmNTYUE3MlZpbWExdzZ3Vm82Z0VlZndrOExGNDdVa3NNNXQyajBJeHR5ZjktZXU1b3otYVZlS2g4SHJlaWM3S0dNNllyZWJvYzBRelZJVlBjSHpWckJKbDVZWlB6Vm9JMEc2Y0RiMlVuOVllWThMTk5qazBBQ1ZLNXRIdG9JbXRrQWg5Z2l3Ry1CQ1FLdWtpTExNWVJCQXBLMmpnb1BXc0ZndEFMMTA?oc=5</t>
         </is>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>46013.32716435185</v>
+        <v>46014.7080787037</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Gennings Dunker credits George Barnett's belief in Iowa O-line journey - The Des Moines Register</t>
+          <t>Everything Lamont Paris said after South Carolina's win over SC State - On3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:06:40 GMT</t>
+          <t>Tue, 23 Dec 2025 13:47:11 GMT</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQLVpXckRpcUlHTGU0QmctN1JHcmluYVplUUFoRHdfOHd2cWJjSjR4RHR1eng4QUxhdDNiaUJreG1pb1pvN1BhejREWTNFRllIWUNwaFNJenZ5d1E1MlNrVXVBNEhQcWt2MXFseVZFT3BJaTVEdGFZbFpPUEtKZW9hRkhMbF96NUJmbWNPR3pCMXQ5a1BTUzcxWXhSNU9pVUJDM1owTUxLeWQwdmN6N2JySlhZTmozXzBRekhxUXpMaG9GSHNVU0NrdGFBNzNVenJkck4xMTRwMFg4cDNkVXBHYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQa3NfVzdJQXZieGlmV0ZwWmVjcUNRVV9wVk9kUmlCNFB6ZVh1NXpENFY2dmtINVlnRzRXOUVlNjhGYmwyWGdlbWttbEFFcGVZdnNRS2RseHEzY3FQSkVXamlpN0dTTExSVnhJc3NZR3FXVW1FcWpxLXhxZFFYVC1Ca1RJamZONzZLamEzTHA2VlQ3SEdZUDg3MXY3UkVfVEsxb0RDcnpXV0U2VmljX1Q2Q2xPUVo4eVhKcjlPVV9STDZlc2s?oc=5</t>
         </is>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>46013.50462962963</v>
+        <v>46014.57443287037</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Jackie Chan carries the Milan Cortina Olympic torch through the ruins of Pompeii - KFOR.com</t>
+          <t>Investors Hope for Bounce in Wonderla Holidays Limited After Selloff - Stock Price Divergence &amp; Explosive Trading Portfolio - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:28:07 GMT</t>
+          <t>Tue, 23 Dec 2025 07:34:54 GMT</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOMWxGQmsxRG9ra2xsQjFORThDQmI0Z2JXNEQ3NVFxUnNHdFJjSHBOZWZUX3doOVp2X1ZkYl92eFM1eFF0SWhHSnlkZFJhZnhTTzRiUk5vWUxTSHBJVVpTb21QWkxxYmdmelNkTlczLXItM3liVUR0SS1OWGNydXdjaTJLSjhDSGtVVF9XR0RsclkxSThpUEY4dFBMd3F2LXMxLVl0WGVYSWlxZHhvUjdiUHFGSmdRTHlyYW9yYnJpRzYtLXNDWDIyQ0FGemtDck1sSkxV0gHYAUFVX3lxTE9DTEhTbGRWbnVsd0VrNGpJS1ZwQU9QLTFTRUx3U184cEtNQVJxbVZQTWpldDdkWWdlN1VoZVZPd3ZiSEtFRDBOVWZjaDE3TzV5ZGdoU0x2Z0JMNG5hNWw3Q3QyOVdmb2RmaHNuZm9BTVlRZTNQVEstU1RkcU94YnZPYkF6QmlMN1pKNl9ObjU4TUNwX1pZN1hoQ0RrLTdJTi1FUTE2TGtzajU4YmVNb3BVeXp2MWppdW83aWhmNUVPMWpYcGp2M3NYTEhXLXE3aVUwMmNvRkkxMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNcHlKQlpVSjVFZDhaN2RRcnZMTExwUmRwU0gzVVh3bmlSRFRYMjR3WXpqalhWUVhueXNJNldIeTNFZUw3OVkwejdtbGcteVp3N1A2NG1weVZFRE9oaGRlLTNDSzJ2Mm8xVWQ0THJoQTZOcFAxbjh0ZjFDbGc4UjdoU1FfcFkyeW9xM1l6SWQ1RXV4LUIxak5BTzJHSVAwVmNQZ2xDNG5sQklfTHY2QlI5Rg?oc=5</t>
         </is>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>46013.72785879629</v>
+        <v>46014.31590277778</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Iowan Brittni Donaldson is a trailblazer in the NBA and WNBA - The Des Moines Register</t>
+          <t>Short Term Trend Reversal in Cineline India Limited Possible - Take Profit Strategies &amp; Free Explosive Trading Growth - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:49:14 GMT</t>
+          <t>Tue, 23 Dec 2025 20:08:32 GMT</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNbEJ5d3E4ZUxua3J1cWdpRnZkX3lqLU12S3UyUjFqa3JnZUZ3QXFhVnNwT3ZXVDZlM0wxc1FsODh6RUN1cXpwRkxyeUZQcUljTVViY0F6UVE4U3ktMzdLSUlpTTN0Z3IwbGxsa2tHaUFTMW02ai1SZDdHeTdudTAzV09yb05qam45ZUEzanJJWFJXMXR1Zk0tVTlkTnM4Q1VRU0Q4bGtVTS1BbTNHU3hv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPeXNQd3NQTEIta0pka2Q1SWtwVTJ0SEkyT254aGwxY2pRMnFveDNpZzF3cW9mRTVUT3ZIX0lGS3ozSnRObGF1cHFxelpVOVFHSFZUdTVXRjNGdEc2QTNOWUlIRGJYZUtldnhVN0RncEU1ZExrY25DVnVpLVdDQU1McHhBY2loQXA4UVpWbEpfSjdkMndNWVFKeXpsWQ?oc=5</t>
         </is>
       </c>
       <c r="F168" t="n">
         <v>1</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>46013.49252314815</v>
+        <v>46014.83925925926</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Logan Jones: Adversity helped shape Iowa's offensive line in 2025 - The Des Moines Register</t>
+          <t>South West Pinnacle Exploration - Blue Chip Stock Analysis &amp; Build Wealth Brick by Brick With Us - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:06:40 GMT</t>
+          <t>Tue, 23 Dec 2025 17:01:34 GMT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNWUZSbDROOG1RRTc1dV9iUnVtZHF6eFR2eVdaekIxTmdkZm1vSDVFNGFCa2Q5NUxYMEtzd0paMktoVDdqZGEyWFpiWW5kSkVUMGFDOWx1YTd6cVRNQjBaelJtMUptRUxyOUdVMjJuR3d2THoySmZiS2xKQ0YybjFyY0puUzhzZ29BaTlhQnpwdTQ5LTN2STd1aHFTM0dNNGpxT2FSb1pWMkpTVWt0ak1hQzAyMkVMYXh1eURzbXB0d3BhZHpuc1JwWDVIUzRBLTJZTkdZdUNtZldsbERSUUZpWDRDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOZFFoakJzcE13YnYxcHNTU1d3c2xxRUV4ZUQwLTEzMVE3amk2Zk1rV2pmdkVoQ2RJNTBDRVppelN0TTdfVXBtSUg4ak94bUxCWG1NdnRRZXMxRkJlTnFLd1ZDV09kSmhPZldtYWJEbE9GYm9FS2ltZUp1TzFQQWtFd05jTy1OcC0z?oc=5</t>
         </is>
       </c>
       <c r="F169" t="n">
         <v>1</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>46013.50462962963</v>
+        <v>46014.7094212963</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italian Championship game in Australia is canceled – 12/22/2025 – Sport - lnginnorthernbc.ca</t>
+          <t>'High stakes' Bridgerton season 4 is 'easiest to adapt yet' teases Netflix boss - Daily Express</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:32:33 GMT</t>
+          <t>Tue, 23 Dec 2025 09:17:00 GMT</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPMnRQODdabnM1ZTFWYUJpTzdmeGhlNC1uM000Q1JBNXg3NXVHdldLTlMwQ1RwekZjZmllTU9LM3hIYjRYN3pjdHJJMGo2UlV5eW5pLTBkckxRUjl4cVVRb3JJUXZqbXk3Tk04V0NoNEJZNU5YdFFyM1FkanBQWl9EX1l2aHFiTjEyV0RsaHJxcVU3bWF1TjlPaXVNUG5CbU9LZjFGRzZVZ01hdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPTk5DX2Y1WkRobEVxc2x5cDRaaUJmYXgxc3lWQ2VvaGFLTlpIRElTMHRNdjZlZW5hT1FSdUFzVy1UbU80d2pwT2E1cFhaUEVfb0UzX18tR0VMSUY3N0FSWVNEQkU1QjRld0piNTgwdGplV2Q1RllKZlhnZmtrY09FUWo2ZXDSAYoBQVVfeXFMUDg1ZXpnbHp5TmZGVS02cXdCLUVFbmhqMTlQWHVtMm9wbzZiOGxneEVqY211NEwxUC04MDkyNkhoczNTY2RuVzN0LVpLbDEzY1V1eXdUMEl2cGhOM1NEVWMtWFVJYnZBNkJxek5QemN0TGlGYTRycjhuSzlkRHoteFlPV2VLbWFfLU1n?oc=5</t>
         </is>
       </c>
       <c r="F170" t="n">
         <v>1</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>46013.7309375</v>
+        <v>46014.38680555556</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium’s police forces under pressure as staff shortages and public distrust deepen - belganewsagency.eu</t>
+          <t>Nancy Meyers to Begin Shooting New Movie in May with Kieran Culkin - SSBCrack News</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 06:00:00 GMT</t>
+          <t>Tue, 23 Dec 2025 18:46:04 GMT</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR24ycThyWHFHdFA2M1FOUDV1NFg5ZkJxcVZ5WVhuRG9Zc3R1OUxLbUdSTjVOSXhSUWxmWkN2MmxfQnB4VGRocnZuS2ltdVBUUjJhR19OcFltUVh0NnFTLVFsWlpfYThFbnlPM3IwU25uQlpsX0xCRTQ4NGFnRVU3b1hzVE1QcmQxOUw0TnQtbVhfb3FPcmoyXzdVcDQ0LTVqTEx5aTQtM2lXWHBuVW4xZDdBTU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNYWV5RGlSN2lZVmY4YWZLV0dKc0VCNmxUTXgzd2xpXzhPUzA1Qm9XQTFhdlo1QzFSNHVreGtoUFdITnpzR1h6M1dGV0lFcXc3Y2ozRlNsYWluMlNaN1VMQUpXb1pTVW9KUGV6RGxxcEgyeThnVFFEcUhZdGh1bFFhbEM0THRQT2MzYm9KOVBzellkdHZrQVc0Rw?oc=5</t>
         </is>
       </c>
       <c r="F171" t="n">
         <v>1</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>46014.25</v>
+        <v>46014.78199074074</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>EU slams China over 'unjustified' tariffs on European dairy imports - RFI</t>
+          <t>J.A. Finance Limited’s Price Action Aligns with Quant Signals - Day Trading Setups &amp; Market Monitoring and Alerts - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 06:24:54 GMT</t>
+          <t>Wed, 24 Dec 2025 02:54:33 GMT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPV3ptNG54M2ppQXRsTG5DbkJXMmJJT1RvVnVwTUoxNEtWZHRfTWNwR0Z1em0wbUpmWnpBNDdKMHJVcWlxLXBQdk1ZMTV4MEJQSmVXNjZQanpMVlNGWUcyQXAwQ1Faci1sanRub2J3b2VIZk9jT0luTnAxdVl6c1Zud25HN21YU19wc0NBVkxqd1ZEWkpWNWtOQnh2U2otTVN5akJURTdlMXYyQ2VBcGM0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZzZLVlJ4MVlvYXJOY1pDR2pYVHpJNENFOGo2VjlJSXNrUUhUSkdLYktyay1NT1VmdlBIMXMtekM2NG02RjUyb2tsZlZtc1FTZWl3OTAtbzBYUFpyNzVQZ2tIWkZQMlVMdVN2NTk4OURrRk1OT2ZWUGdDLUsyVWc1XzhDWWotYnY2OFBTXzI0Y1YtcFZnajc4TDlEMXRsU21ObUh0SFU4eURRbHBxdGk4NWVxRDhFcUlYWG1r?oc=5</t>
         </is>
       </c>
       <c r="F172" t="n">
         <v>1</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>46014.26729166666</v>
+        <v>46015.12121527778</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Europe Looks Frail When It Needs to Be Strong - Bloomberg.com</t>
+          <t>SPP Polymer Limited (SPPPOLY) vs yyy - Market Sentiment Surveys &amp; Small Budget Capital Investment - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 06:34:34 GMT</t>
+          <t>Tue, 23 Dec 2025 15:28:04 GMT</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOWUpEWEU2OVBzQTZoWmpBVlhXdlQyNjRXNWVoX2xwSDJCQnBxWDZqc1VWdTUtNWFzd0pvV2xUOGdpS0lST2Q3NGNOX1RXVi05blFhaUZLeVNBTERwaE14M0YtS21BUDcybDJ2S1o4OXBSdUNnNEVOUEtXQTVLV2s0cWZKODFmZmt2bzU0QlZfLVdHX1FXWnVUV25jZ2hHdUw1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOWl9WTF9FVGdkTTVaQ3FiVVB6cHpwVFlNZUZmQ0k0WDhwT0J3S2N1ZDVHWlptOHZPV2x3cHNxSHdGXzh6OEpvSnlJb2szdzFyOU95dUl6Z0paYVBhdm0yd2lObC1tcHI4aVZlOUhhTVNaVmFKMjBvaUp2ajIxdEd0ZkdlU1pfdw?oc=5</t>
         </is>
       </c>
       <c r="F173" t="n">
         <v>1</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>46014.27400462963</v>
+        <v>46014.64449074074</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spectacular Christmas light show in 800-year-old cathedral in Brussels - France 24</t>
+          <t>BREAKING NEWS: Nursing home explosion and collapse - NBC10 Philadelphia</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:34:12 GMT</t>
+          <t>Tue, 23 Dec 2025 21:13:02 GMT</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNNXN0Tk1ZRENNZTMyQzc4ZFlLRmpiTk4weThLSnlaNVZFNWFyNHhBelE0YVV0OThfaEdDeHVkUXlvMU01R0pzcnZrbWpwdGNwZHoxZDhYSzhJeTdrTHUxZk1JTnFMVXF0Um9yeXpwZHJ5eW1EZlY5eHh0eFVSczgxX2R4cnJnVE5DemVoWEZCc2hGYXNRS2hiVXVKUzJnejVfUU55S04yaDE1UGRXcFlfUGhEYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNTTlqY3lxcHl2VXBCd1lOTjg4ZDlGUVNNOUlXa2hlRU5zOVlieVV0YUpSb0szazM0TlpJZlJYUHJ2ZGg1eDFVdXB6bHFTUkh5YjBuWDM0OWp4X3pscHRvMllaLTh2SHdWRm45d0xEbUE4V3Z0aFBGS0JubkJycEZ1Q2xpdHJidFZKZDJCQmZ4eG1ydG5xaWZRQW1QYmhUVkQxUkVjMDR1S0JTaEHSAbMBQVVfeXFMUF8zeFR4TjZDWjl0QTV4cU85RHR2aVFPOXB6TTljVy1TWWIyb0Zpd3h6S3JiZVU3OHNMaFpDV0tDeGZHeVE5U0R6VlJZdEV1MlVUcHRVS2lVbDB0RnFqVGlCekpaWmZxRi1sVmxrYWNsT0o5ekM0R2tCbi11dThiY1RUWmFaN1daQnRKOHJHWnI5b253UXM3dE5yZjF6Tkt1NEJHWGpUdGRxamZuS2RzRmFOQVU?oc=5</t>
         </is>
       </c>
       <c r="F174" t="n">
         <v>1</v>
       </c>
       <c r="G174" s="2" t="n">
-        <v>46013.69041666666</v>
+        <v>46014.88405092592</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belgian Christmas markets disrupted by anti-Israel protests - The Jerusalem Post</t>
+          <t>Published on: 2025-12-24 05:03:58 - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 21:24:06 GMT</t>
+          <t>Wed, 24 Dec 2025 04:13:57 GMT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1JQ1BtSVZ5dHdKelJqVlc1LU4xNjZlNkFMcHBGMDc3MXRNck5NVTlmbnlpa3pERVkyckRxNWtzdzlTOXF1T0RxM05EWUQ5dFRpYUV3TENCZEJNTzg0b1Bab0pGbElqdDBDN2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPaEY5YkFuVzZOSW83TlVsZFVpMEJVcjhnSGxReGpnWlhUdTU1TDhkUzFsdG5XZEFILUt2NHVKU3RyX1NkcFVXUExwcV91VHptNllyc3REazhZWVc1UlpYTUFjN1dncFM2dERmdUF4RzJGX1VfcXRZSDFlSnp1MF9Tb3BpaHJ3TTBYQTRvV2d3aTNvS1luTld4NFV6bFpDbG9FUGRxTw?oc=5</t>
         </is>
       </c>
       <c r="F175" t="n">
         <v>1</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>46013.89173611111</v>
+        <v>46015.17635416667</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>A Huge Protest Shakes Europe’s Conscience Over Sudan - The Times of Israel</t>
+          <t>Iowa State's Milan Momcilovic's shooting mantra is 'Jellybean' | Hines - The Des Moines Register</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:26:00 GMT</t>
+          <t>Tue, 23 Dec 2025 11:50:00 GMT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPMGZYMFVHVE1YNkRXMWl1UVQ2ZmFYOEtnTkZxd1FfU0hSbUJGeWpRM05kY0FRd1E3NXR1SjJacFJVZDFQVlBaSTZBZ2MtdGxTdGJyaW1SZThSRW9hcHFCZXZwMzVXSWFudkt5WkNBYS1mWk02SE8xNmNCQm9xSjlFQ0dYTW10QkZ6MEFiRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQTnU0V3o5NmdqQk4yUDV1VHdmR05xM0pEMDdCV3JNTHlEaFkxQV8wZmhxY2R3YkV3YzNSbDFQblJKUDlJN2gwSVlKVEdVNVNkOXdHYXZzVlF2NHRiZkJURlRIRW5sNEh2QTFHMFlGWnktV3M4dmRQdnlzZzFIS3k4YWFpdUpHNjQ1T3VpTHlab3pIck9Id1lKallqR0YtSnZHRllKbGRFclhkMEVQZmRpNEx5SnE0al9WWTdUMDJwZGxYa2lDSW5zT2FES1ltZWIyOUhaV2JiUTFrQWl4S2tHWnZvQ19uemhqal9NUF9XRnFscXNaa1VnSFNVUU9FcDExbzZLRU5pV3JXTDcydW93?oc=5</t>
         </is>
       </c>
       <c r="F176" t="n">
         <v>1</v>
       </c>
       <c r="G176" s="2" t="n">
-        <v>46013.55972222222</v>
+        <v>46014.49305555555</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Exclusive: Former MEP Kaili doubles down on 'Belgiangate' - Euronews.com</t>
+          <t>Health-care manager who witnessed workplace stabbing sues hospital, WRHA for dismissal following PTSD diagnosis - CTV News</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:00:44 GMT</t>
+          <t>Wed, 24 Dec 2025 00:15:00 GMT</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQclAyU3JmazBZVWhlRmo4bmctaWdoRTVvWkYtMzFGNnJaakE4OV9jWU05QTBWOEwzZFV4SjVoUTFVZlNSNUFfNzhwbXh2bjl4YVItdWtjc290dFFySXlpNkhYQ3Iyemp0WVhpWEU0RVBlWUt2MzhSZ0UxMjNITmdPdm9DcG5WSE84dUo2ZngzRmViUnBNOHd4c2dWSjdfUncxX2p6ZGZ6MS00NkUzX3pTZ2xKb05xbVpxM3BiN2JhWDRxb2tMYk5uTE9pUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNQ3FraXNIQ1dHX2V5a1daRmZnWTN0ek02Wi1ESG1VV0RoV3hIQVV2RG4tOE5QaWtWSHlxc0FENkNfaDZiLVR1YWNxY1FkalBEazdJa3FxZENscHpUcUVRX1kteFpQSnlpdGxPS0xaR1Z0RjJILVJxbHJaUkgzejBkQjJqdkpPa1VTNXlkN1U3cENxY00zdE5zZi1aN1hrUzJpYmFiMEFaM0FFMi1VZnJFREpMNUFHQ0xuUE1Na1hmSnpkRzhpREpFOWtPNGg4dmRTUGUzcU5DSXlyRVlMVzBtSnpGTlMzdw?oc=5</t>
         </is>
       </c>
       <c r="F177" t="n">
         <v>1</v>
       </c>
       <c r="G177" s="2" t="n">
-        <v>46013.33384259259</v>
+        <v>46015.01041666666</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Eva Kaili renews attack on Belgian investigators as fresh Brussels fraud probe grips EU - EU Today</t>
+          <t>Kuwait shooting team secures 2 bronze medals at Arab Championships - Kuwait Times</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 21:54:41 GMT</t>
+          <t>Tue, 23 Dec 2025 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE95MmNjV2ZMci00MG1hQ0dORG9vMDRqZ1ZCRGJ1MngzSUFQR0tzLVkwQ0VvVmFlODU5cVNLSXktVnhJM2pqR250eDRWX0xfMVh6R3RvUnNRSmZfU19PYnAwUjM2bmtnRHo4TkpVM2lKRVU1Y2oyMi1vag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNaUZaTk1tM014S3FpQ21LSmZLeDctb1gxdnZVZ1pfVW5wUThQWHQ3ZVd4eDQzazFWTnNSVDh3aGJVa1FpMzRXNnJkR0pMVWhQUGdFSmNSaVZ1cjREX3VveXVFVTVHNXJfSmIzaXFCY2p3NklIRlpndnFna256aXBFRFYtM01NT3J5M0FmNWljTFZjWExOOXlRY0NrN19jVjBmck1pam5CSHhzNm16c3Vtb3g0UUYxalBpYzh1TFpWSVVvd9IBwgFBVV95cUxNaUZaTk1tM014S3FpQ21LSmZLeDctb1gxdnZVZ1pfVW5wUThQWHQ3ZVd4eDQzazFWTnNSVDh3aGJVa1FpMzRXNnJkR0pMVWhQUGdFSmNSaVZ1cjREX3VveXVFVTVHNXJfSmIzaXFCY2p3NklIRlpndnFna256aXBFRFYtM01NT3J5M0FmNWljTFZjWExOOXlRY0NrN19jVjBmck1pam5CSHhzNm16c3Vtb3g0UUYxalBpYzh1TFpWSVVvdw?oc=5</t>
         </is>
       </c>
       <c r="F178" t="n">
         <v>1</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>46013.91297453704</v>
+        <v>46014.79166666666</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Over €16,000 in fines issued for fly tipping in Brussels - The Brussels Times</t>
+          <t>Family of killed arabber protests after Baltimore officers cleared in shooting - The Baltimore Banner</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:16:09 GMT</t>
+          <t>Tue, 23 Dec 2025 17:52:00 GMT</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRTlxTWxSTno4ODUwUEctOG5Za0ZvVUVRT3NuOW53b2VtTzVhb0J4ZnpDUnl2Tl9IOWdLVmpIOVB1VUI5ZUt5TVNSWl81NjZuMnFDcV9CX1dGbXZxNWdORGcya2dDczE3SnZ2OXVURGMteTZlNkh5a3N0M0JQS2diU2NDMC1WbG1RQml2ODBnMUljZHdpWEduNWh4cU5CemZXYzdOZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNY05naEV6SDJFclpZZHFMYS1TaGRQRmtRUDItVC1ScExtVXd5NFVQZktKMm9aSjVPdkpMVEt4YjR6Rm1rUmNULVY5dVRSMkFJUTh5WEZWNXVONVRidXdzVmc3QzRnRzBpOEN5YV9ZRXdpUExZMXdsaXVDaDkwWlNrS2VvdUZ1WVZUM3dNX0RwMFo4YkRrczJLVC1qMUkwUG1RYURtWno1VmpCVXd0WGs5Wk0tcmNvSG1HVnBCWFhtRGU1UQ?oc=5</t>
         </is>
       </c>
       <c r="F179" t="n">
         <v>1</v>
       </c>
       <c r="G179" s="2" t="n">
-        <v>46013.46954861111</v>
+        <v>46014.74444444444</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Westmeath IFA chair joins farming protest in Brussels - Westmeath Independent</t>
+          <t>Technical Bounce Expected in Imagicaaworld Entertainment Limited Next Week - Federal Reserve Announcements &amp; Free Explosive Return Secrets - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:25:47 GMT</t>
+          <t>Tue, 23 Dec 2025 23:19:34 GMT</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPYkhyUFhOY0hLWDlEbUQ1TXg3X2hWWEtobE1qLVdaWlB2ZndxdjVhVU4teXhaejFXM0RVeWxXSFhURzZRWEc5bGRkVTg3Wl8zUkpfSzdjVjY3VThDdVFlQVRyeUdhTmJfUjg0NndPZG9PaGFqNGp3eVhSMU4tcWh2MzU0V3pYWFNNR29UX3ppUkNveFBKbDVZTF9XNEZSdkk4aHdJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOaU51d2FHYWdpdWZTNDNPTU5idXV2dFBiVHhQY0FpZnhSZlBzWi1JXzg1WXlibnVVTE40WFlxVnlCSHVhWUpFUVZuc191SWx6T2FqdUEwV3Q1ZU1BY19iUE4tQ0UwMUtwMUtVamp6YWtvelk1b3ZhOWp2UG0ycUFXTDg1MmVET0lGUTFsSjdsS3ZKRDRuYzB6cW80OHJCZlB3RjlKcHJxNXVxX0hEdXphQ0RhMEN4MjJiNHJNNnBiSWREUQ?oc=5</t>
         </is>
       </c>
       <c r="F180" t="n">
         <v>1</v>
       </c>
       <c r="G180" s="2" t="n">
-        <v>46013.68457175926</v>
+        <v>46014.9719212963</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>E-scooters to be banned in Brussels on New Year's Eve - The Brussels Times</t>
+          <t>Kathimerini explodes the 'bomb'/ Mitsotakis: Greece does not support Albania's membership talks, condition - Balkanweb.com</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:48:47 GMT</t>
+          <t>Tue, 23 Dec 2025 08:12:54 GMT</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOUmRBdzdGOG9CY3lfdzFySjdxZFprb3BDSERZY0c3c3MwVUh3S2lDWVNoc3lhRDc4WnJxbzBGZnQ2TUk0WnY5SGoxS05fck5ac3UyMkhPZ0ppQU5LODNPb0x3a3RHN1pSalJGT1dRMWxXbkpJV29HMEZQVjNYeGlNS2JCVUczZkpPNTU1ZnplaXRVVEZJWTI5M3JWVTRQTVR5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmEzd3ZTLW1ULU44Z3dkWG83d0Vwa3lHRVowT2tYWElBNUgxY1BHRVZZbGx3di04UXFEaGZ0Q1JfTUc5dWZDSHh4YlpEalNsV0V2REFqUkwzUkVjMG02SUhBVTNGckZXZzdfSDZobXhWNXR6bXV0aDltRlNTM0Znd29KZlAza3RYTUNuWENxVHVlbmUzRnRPVDBURVBRVGxjc2tTNWFrbHdqa0t1T2s2Z1NDSTctdmV3RHgzUGFSOE81NlRUSFJIcDNtdmpENEE?oc=5</t>
         </is>
       </c>
       <c r="F181" t="n">
         <v>1</v>
       </c>
       <c r="G181" s="2" t="n">
-        <v>46013.45054398148</v>
+        <v>46014.34229166667</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>US tariffs hit German car industry, threatening EU’s export-driven economy - RFI</t>
+          <t>Big 12 basketball power rankings: How high did Texas Tech climb after win vs. Duke? - Daytona Beach News-Journal</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:28:55 GMT</t>
+          <t>Tue, 23 Dec 2025 11:30:00 GMT</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQSnh2ZU5VQU9lWTduNGlDM214UEVWYzJnZGRZNXhUSEZweU9VWkQ4OTdmQ1NHeHVsUHpBbUtHSlZCV0NENTNZUm1PemMyMWRLQ0RORm44bmxENHNGQ3R0MnZHdG1uRVN3TWpuZE9JcUtKTEE0NUVab3hGX0w1MjFHMml6UzdTOC14SWhESXVtOUx1andpVWMyMGhZdDZGOUlYakNRTEFSSlRZbmJoem9ReFAwOVBJRXFfd1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNdzBEVE9wbUpIYU5taUlBTzQzeGRIZjFSQ09XUndsbnFmdV9tZzItek42UUJtODViUXR0aTBOWTVFWjdSNTVULTYxRXBDV01zRDFEVFZLUTJLTEZ6U29WaFBpYXZ6NGVjb2hkUDhITEtoSEtSX1hWeGpEaFVSRWJTOXZRQlBZUGJPWGUyUzFXbThzUnJtUDdNcWJQOGwyQWRrejQ4Q1JxNVFPeE9BX0FUZHpCRnZhSkhqaDR4ZkVWcWk1d3FyVko1VHJPSG82bUk1NDFxMHhyZnRrZ0RxZkxqQWNCeUZOaEk3Qzl0ODZkaVhqNU9yR2Rn?oc=5</t>
         </is>
       </c>
       <c r="F182" t="n">
         <v>1</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>46013.56174768518</v>
+        <v>46014.47916666666</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Belgian cannabis dealer linked to Dutch criminal network - The Brussels Times</t>
+          <t>Oregon Coach Dan Lanning Breaks Down Texas Tech’s Explosive Offensive Weapons - Sports Illustrated</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:41:58 GMT</t>
+          <t>Tue, 23 Dec 2025 13:48:39 GMT</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNR090Y3VqWlRnS2lNMGVvcExZbm85YzVZRl96MEFMSGNlMFRDb1lKRlV2cDN3X2xteHFEY2ZBWjVNS2ZvVFYwRjgyMi1ubGdZdThfbEs0TzJOUHhORExndlZxMDk1UXZTNURuLXptODZ6bmtLUk1uZ1hfUHpPbU5oNTlzNmhESHdNVC1NWjBlMmF3YXZmNlB3VGNVMU1YaUNJX0tqUEhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQa0lkTjAxOTVfVjVXSmtxbWhoRDEtV1lRdU9qdE1icHZURmF3WnQ1ODR6YVJKZUdYdEJHZFNXT0NHQ0piWTF2SWFTeHF5REM5NGF1VkNUZG54aGFtV25kcXFoVVllUTIzdkJPbHRINGxkZDExLTFPQUdtV083cTF6dy1BQlJzeENxZ0NqMjNSN2dqd2F4Z3E4cjFSRTNBNmV3ZWxjWHV6SHFDTTZvX0dqU1IxbndKQm40REZ4bnVjSVc3aV94QkkxMkN2NA?oc=5</t>
         </is>
       </c>
       <c r="F183" t="n">
         <v>1</v>
       </c>
       <c r="G183" s="2" t="n">
-        <v>46013.57081018519</v>
+        <v>46014.57545138889</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Swiss court to hear Indonesian islanders’ climate case against cement giant Holcim - RFI</t>
+          <t>Shooting last night in Gjirokastra, the perpetrator fired a pistol at a 35-year-old man, he is wanted - Balkanweb.com</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:18:27 GMT</t>
+          <t>Tue, 23 Dec 2025 07:30:00 GMT</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQlJXRHRjelhSUTVEeDF0MnBodVpoLVJGa1ZQbjZMUm9iTl9jell1TmtpQ1RNYUxSQ3VuTC11TFZ0VnNic2E2MHFYMUFQUVIyN0JWeWdpazYwdzAyU3JocmhjNEUwd0lwbGZRMVR4M2FMOVNEYUdzakpUeENGM2xoY1ZzaFNBRnJpc1FISWxpWEg0dmNiY1JyWUpaTEtJZEFJLVl6cGZBMV9IUGZDeERGeVp3TUc5OENYWnVfNFhlZzBNbmw1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPUXZJNUlzeFV2Z3pHMjZzTjJWdFpXREdKc1hiaElxbDlyQ2pRSkxuTWxINnU4OUVCbUVJSGIxaXJMYjdPQnhGeHN4Sl91TlpzTkdveVhSVk9BZTZsaG9Pc2hfN2I5NmhxSkF3dFR3VzN5TlJFMHlScmNELWZVeEtuY0Q1QTJjelRCd2ZlWjlMLTROcy1uODUtcm5XYkdtVE5xbXBPSmFWYmpaaDRRcnRZT211Qkwyakh0RV94dk1sNU84dw?oc=5</t>
         </is>
       </c>
       <c r="F184" t="n">
         <v>1</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>46013.47114583333</v>
+        <v>46014.3125</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>One person critically injured in Brussels apartment fire - The Brussels Times</t>
+          <t>Athletics, shooting top gold medal earners at SEAG - The Manila Times</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 11:16:09 GMT</t>
+          <t>Tue, 23 Dec 2025 16:09:00 GMT</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPTkFxOG5kZVhldDFnakZMYnFldHp0Z0psS0ZJeVdJLVRSNVdjZ3RMd2RGdXBMMnl4aWFQNk43VzgyZHI5ZmgxLUtPdW83RnA3eHZIbS1xQWszRkJWVm1YV2NZdXVSVHBkYWM2S19EcVRhMzdSSE90UElPSmx6M3FDcHNJOTFPNFJpS3k1SURjcmZ6VlpvSGdKd0l3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNUN5eHl0bmxaUXM4NlhfTVktZVZOSGl2NjBfUWlKN0VadkFVMXRRMWJkUGVxaXdPbjlMdnRZQUhSTHBnNktsdjd5em8td2NVWFNGSVJ6NUtSY3RnTVF3T21LdTY3ckViY2taX3NwOURISExXOThmY3RIZFM0UnhGLUxZQVVvT1N4N0M4ZVZoZEpJbFRVYXctVHNlckVxN1lLbXZ2UUduUDlRaDDSAasBQVVfeXFMTzVDeXh5dG5sWlFzODZYX01ZLWVWTkhpdjYwX1FpSjdFWnZBVTF0UTFiZFBlcWl3T245THZ0WUFIUkxwZzZLbHY3eXpvLXdjVVhTRklSejVLUmN0Z01Rd09tS3U2N3JFYmNrWl9zcDlESEhMVzk4ZmN0SGRTNFJ4Ri1MWUFVb09TeDdDOGVWaGRKSWxUVWF3LVRzZXJFcTdZS212dlFHblA5UWgw?oc=5</t>
         </is>
       </c>
       <c r="F185" t="n">
         <v>1</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>46013.46954861111</v>
+        <v>46014.67291666667</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>RTÉ tenders €1m contract to boost Brussels office - Gript</t>
+          <t>Divock Origi could offer Wilfried Nancy a Celtic option after Fabrizio Romano’s latest update - 67 Hail Hail</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:47:22 GMT</t>
+          <t>Tue, 23 Dec 2025 17:30:00 GMT</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE4xUWZUckgzSW5WVmY5Wk5STjVaU2diV0xXdXRzWnNaUWk2OE83TjAwUWh0MUtscVVJVnhBTDhWVEx5TVMxMDA0b1hiMEx5ZktaVlpWdG1rUWt5Wm82Z2lIMWNNU1lWdWstS1NYZjByYU92XzcweXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNelZtRUdVUHEzUDBOTmV2NkNCQWNONkUzX0dsSmE1dlRGa0VQSEp3eGxIUGVSSmFXTDdyeGFCN1RWeE5zamJBN2VFaDVrMk5IMU1JRnpRZWNyWjdXeEN1dmM0YWFLX0VONjdRMk16d3VPT2xvM054dnN5Y2xiWVM2dnFTQ2hTeXVnSWE3WTN3QlBQVUEzZ2hRWk9udi1EZmZfZEZxT1A2RjJwSFlrcC1WSGYzRF9sSEpIaUZaZ0RZUEliSGZvNUdF?oc=5</t>
         </is>
       </c>
       <c r="F186" t="n">
         <v>1</v>
       </c>
       <c r="G186" s="2" t="n">
-        <v>46013.65789351852</v>
+        <v>46014.72916666666</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>EU Commissioner pulls out of Brazil visit - Shannonside.ie</t>
+          <t>Park Na Rae’s Former Manager Exposes Even More Misdeeds In Explosive Interview - Koreaboo</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 17:23:13 GMT</t>
+          <t>Tue, 23 Dec 2025 07:37:28 GMT</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQZmhRTVo2WjlmbHlVeVJBaDhvY01ZVjhfWUJIVlpDQmg4QUstUGlZY1FzcmVXUXFSRGhoZGZvd1dIS2dlcFpBa3JKUlJnXzhRaVdwYVFpZV85dHF0cUFzRjlRZldZYmM2Q09jZWRub1dKeDk3OGdmNDVJRVBCbmMxZzV4NHdGNVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOLXFFejd1a2J6WkVEcVZYNWhVYzdkbEV5YWsyWktwYlZyRXktUzZMUHB2QzVUSkFPVHZFNlNPeTVRN2lfYVVUUzJveWZKQzl0ZG51X1NMaGlhTXVuRHlPazlQZjVnTUtiQVFMQl9RaGZEV3dRNDhDMjFkeklrTXZBLWJ4cFVwcGhOLXdvTm13S19GdlFpMElPcFNB?oc=5</t>
         </is>
       </c>
       <c r="F187" t="n">
         <v>1</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>46013.72445601852</v>
+        <v>46014.31768518518</v>
       </c>
     </row>
     <row r="188">
@@ -6620,24 +6620,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>The EU-Mercosur Deal Is an Opportunity Europe Can’t Afford to Miss - World Politics Review</t>
+          <t>Belgian Christmas markets disrupted by anti-Israel protests - The Jerusalem Post</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:58:15 GMT</t>
+          <t>Tue, 23 Dec 2025 10:36:00 GMT</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5yZ29faXd5SjVYVV83MWNUYktXX0ZWN0puWEZIenpVVGZ5eldya01QSERRMlg4VlFKRUV4eG5kNmlzYkJFTzhKdTg4VnM5UHA2Q3NCbnlkSXJoSFZwU1BZRm8wRmFpTHJQY2lMZXhJdWsxTG1h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1JQ1BtSVZ5dHdKelJqVlc1LU4xNjZlNkFMcHBGMDc3MXRNck5NVTlmbnlpa3pERVkyckRxNWtzdzlTOXF1T0RxM05EWUQ5dFRpYUV3TENCZEJNTzg0b1Bab0pGbElqdDBDN2c?oc=5</t>
         </is>
       </c>
       <c r="F188" t="n">
         <v>1</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>46013.58211805556</v>
+        <v>46014.44166666667</v>
       </c>
     </row>
     <row r="189">
@@ -6653,24 +6653,24 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>New app maps drink-driving checkpoints in Flanders, highlighting legal grey area - belganewsagency.eu</t>
+          <t>Death threats force far-right Wilders to suspend campaign - MSN</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 13:19:00 GMT</t>
+          <t>Wed, 24 Dec 2025 02:39:46 GMT</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNZzc2UktrbUozbHlvdGNVQmJPU3plTE5NY19FYTEyMHV3MjY4S0k3Q2E0Z2JHQTZ3aFU1WTFHSzVlMkczNS1yRERqVHBYaHV5aW82NzEtSnB2UlJzb3ExNW04cnAwV1RCa3JfTS1kM0RMLUhfY2dIY2d1NmJxMTEzMEM1NTZFdTB5Y3l5dzVROXEyYzZkQ2FDcnAtYk83dUhNWnkzejZfek1aSEpCYi1V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigANBVV95cUxPejRteVNuZW16ZDl3SkFETzZ6Y2YyaHF2MThZM2ZhSkptOWo3dVN5UUhYWnpKQlZSN29RMXFsSjc4MGg3eXdyVzAybFIyVVNyaWpiVS12d2hxVnMxeUFaRVRjdFFZWVpja3Yxb0xsVGZNb3o1MTVTd2tUeDRyc3JzNTlMVFdUNnNyNllsZEZBaE1JSHA3V1cyOFdqVU92NF9MZ0xEMXN4cmw2c2hWcnh1TUh5N2NLNkNqZ1NGT3dZQWhDQTlGeGN4d2gwNDM4akpoSEZVQmdwNkRZMjNIeDFYTlpKZkNjQVJWUEV0TENvQWI2bk1IZUF1clhZYVZLY0JsMDJNcjdRMzgzVm5veGRpbVBrRG5MaXZRTm9aRG9veGo1RnBDaXZxOHI5N3d1VXZseDRudzRXdUtPMXVhcURpbGlIWDNFX3hnd3RiRzVTNmpnLTlDQm9NWkMxeWhYMWljUURhNzYyZllTTnlRVkZmTHg0SGV3SUxwQ1pTcHh4ckQ?oc=5</t>
         </is>
       </c>
       <c r="F189" t="n">
         <v>1</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>46013.55486111111</v>
+        <v>46015.11094907407</v>
       </c>
     </row>
     <row r="190">
@@ -6686,24 +6686,24 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Rejoining the Customs Union would mean a Brexit forever war. Why would the EU let us? - Yahoo News UK</t>
+          <t>Westmeath IFA chairman joins Mercosur protest in Brussels - Westmeath Examiner</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:20:43 GMT</t>
+          <t>Tue, 23 Dec 2025 17:00:00 GMT</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPR3h2bGNwVEt0N1h5SnN6bVcxLVY5Uy1nbmhWbHU4ZThhUGk3d2p1UWptdFZQM1VjczVFSmVJR0Z1czUyanV0ZDFTbjVpM1Nfd19jaGhHa3FrdkM0NzVxWU5EdXFaZXVmWkZicldlTWFlS19KSFZvMmhiVjQ1emZnSkhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQY0U1UThQOTFDUG5WMmFQcU00aTZ1bkJaVGpCN0pMZEkwZDRmbXBhazE0M0tTcHY3N1pUUk84V25rMUotT3p5RG1Uem1rZ0EzcTJWbzZpbjdZNkxHaTB6Q2N6YmNrck5xZXFCMjBsWFFVM2JsUWZlY0IwMy15UVc2ZE0tQkxqcjdvc0xUMEVHVE5zekZNdndkR3pFWmR3QnFWTW9SWQ?oc=5</t>
         </is>
       </c>
       <c r="F190" t="n">
         <v>1</v>
       </c>
       <c r="G190" s="2" t="n">
-        <v>46013.51438657408</v>
+        <v>46014.70833333334</v>
       </c>
     </row>
     <row r="191">
@@ -6719,24 +6719,24 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Brazil's Lula Hopes EU-Mercosur Trade Deal Will Be Signed In January - Food Manufacturing</t>
+          <t>Pointed message in Taoiseach's rounded comments 23 December 2025 Free - Irish Farmers Journal</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:10:26 GMT</t>
+          <t>Tue, 23 Dec 2025 22:17:56 GMT</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZnRQeFl5N2l3TnA2NTdUTGhaMFU5VklEQzdRWnpHZC15SHZqb1JkMkVEM0YwS2gtQUlwcEdpQjRIOUFndnVVNFhCMngtc09TSGQzWXJEdVY5UFhTSGEwakZXNGY2SEFSSVQ5cTl4VTBCOGwzT2dteFVfdi1OQnhHMjN0QlBLUWNtdXd2RGoycS1maEdnaERQdlYxSGFVMjJ4S09IZFR4bnBBVlhlOV9BT2dOTmI0Nk9zWk9vWjRBbnU1c19GLVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNbTFVUXhUM2dQeGVEUWtvMV9fcXhFaUhyRTRwT3VYNzFPa2tRLTJwWFhqMVRpcm9RU3VDZUktRGkyVWE3VS1tUjRCZTdCVUg1Q3lkZFNCRmJVeU94YlA0R2VFdGNhU0J0WTJFbFZYNm9ZcUVfMUROZmxOQ0hNMEZkZGFnTk1MRHV3clY5WDY4ZG5GZ1lYSVFlWmJGTnpzcDBB?oc=5</t>
         </is>
       </c>
       <c r="F191" t="n">
         <v>1</v>
       </c>
       <c r="G191" s="2" t="n">
-        <v>46013.67391203704</v>
+        <v>46014.92912037037</v>
       </c>
     </row>
     <row r="192">
@@ -6752,24 +6752,24 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>EU to probe Czech aid for two nuclear units - France 24</t>
+          <t>EU-Mercosur agreement: No unified regional position - Central European Times</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:33:13 GMT</t>
+          <t>Tue, 23 Dec 2025 10:07:33 GMT</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdk01dEJDNlg2RzNoQUw4cFo4dXZaZ0VleU1OY1VadTlhNVpUNENzWEhMbVpDZ3RpbFB5dVpvbEZtM2pwLXRfczBENVRZOFc5UjZtR19BTnV3NG5Lak9lMzNQVzFTRmRIMFRfMlFCcUR4TkpOWXRCRFFMOHAyX0N0LUhucUZKRUdITXhJeU1rODZkbTE5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQSllZSGdGOGNkNVBxendNamFUNUgyeEZTdkVLODBUSFE0SHdxYjBoRGQ4Z21VZWpvRFhVSUVBWEFaeHB5aTdqMF9UWEpCZWtLUXdTNHFZR3hMai0tR1RuSmVfcjNNYWxMc2g1WExfRHFGbHNNMUV0RUdmOUpPQ0dtRHNxa0J3dXgyekdYZ0lwcw?oc=5</t>
         </is>
       </c>
       <c r="F192" t="n">
         <v>1</v>
       </c>
       <c r="G192" s="2" t="n">
-        <v>46013.52306712963</v>
+        <v>46014.42190972222</v>
       </c>
     </row>
     <row r="193">
@@ -6785,24 +6785,24 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cloudy Future for Bourbon Has Jim Beam Closing Kentucky Distillery for a Year - Food Manufacturing</t>
+          <t>Brussels demands more respect for emergency workers during New Year's Eve - The Brussels Times</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 21:21:32 GMT</t>
+          <t>Tue, 23 Dec 2025 16:42:14 GMT</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQZEdmN25jWmNiVU92ZXR4YTVyRVVqdzdSekJHNXRrQ25iSW1uTndJU2ljVFNUUVlfWENRQVh6N3lfQlZRWXJXS2NkWGJOelBzQzNLbHNueDBVMkdja3FPa3B2aXBCaHJYNTA0V05hVHdreDM2ZHhpcnBMN1VURzhjRi1tbWUzUTBubFk4MDMwampoMFNWN0hZaG1iRWoxdlRSWkpqMi1Pa0pMeWJoXzd2UWQtNTNEd0x2Y2I1RkJzVDFlWnpoT0VleHlacHlHamhldWtvYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZ2NLWVZMY0xibzUxejFGQnFmSmtRT2g5R25NME00NUtIQ1dXekQwUWhoRTY5aVpjc0lyY2RLYVRtRkRQZ05sMkt5WGFkSnItRndVdFBEQUFkS296VU0xUUhBenhSLVV6eU9LYlBGVUJzUVpSbW1tdm1lYlNvOVdOcFk0aEdjUG0zLVpKNU5nMWh4Tkk3Nk1kaEl5Wk9Hdnd3Uk5vQzV4N3dsWXkwQlBz?oc=5</t>
         </is>
       </c>
       <c r="F193" t="n">
         <v>1</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>46013.88995370371</v>
+        <v>46014.69599537037</v>
       </c>
     </row>
     <row r="194">
@@ -6818,24 +6818,24 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>India, New Zealand Finalize a Free Trade Agreement, Eyeing Growth as Global Uncertainties Persist - Food Manufacturing</t>
+          <t>Car bomb kills Russian Lieutenant General Fanil Sarvarov in Moscow - France 24</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 16:20:28 GMT</t>
+          <t>Tue, 23 Dec 2025 10:01:17 GMT</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQdVlpMHJsTWJwTFkxcHRqUVhJS2Jvb0g3cC1POFRTTXdXYjJKQXJBckxQTnNkT3o4TTU3S0ViOEM5OEZlbFZGVHR4UG1fVV9TX2tUYlppVHRQaDdBcjB1Wlg0WnpOOWIxTi1jckNseG54WXM4cGE1T01FOW95ZVkwazJLNWdsUDRBZ19oeFhJYUhmSnlEMHNMMnh1TDdQQ1h1ZV9VX1lPalJfb1I2X1RPdTZraGFTek5uNC05TlVCLXZVRFJ1SXZ2WnZfVnFMdUluOWZuRHdaOGNYaWc1SUNhWkMzUHBCN2ZPdFhJMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNWTJPQkwwOHY3VWl1N2p5eGVOcjBEV3h6alRYb0pUSEhvSl9ZRkJCX05TWnZBR21nLWVMRHFaeXdLZnVMaUpsdDVqRDF1bnY1bW0zMVA4d0h4ZFBBMGhFRHdnbG84MjNsYTRDVXVicE4yYTJJSmM0WWVnWU5kQTlqSFcxS1FocFZsV0FUYU10Uk5BeEhkV3d0eG13VlhyU1ROSk5JYllId3c3SnhpQkE?oc=5</t>
         </is>
       </c>
       <c r="F194" t="n">
         <v>1</v>
       </c>
       <c r="G194" s="2" t="n">
-        <v>46013.68087962963</v>
+        <v>46014.41755787037</v>
       </c>
     </row>
     <row r="195">
@@ -6851,24 +6851,24 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Pay scandal scars fade as IFA posts strong surplus - The Irish Independent</t>
+          <t>🇷🇺🇪🇺PEACE TALKS DANGLE - RUSSIAN GAS STILL POISONED FOR EUROPE A Russia–Ukraine peace deal might stop the shooting. It won’t resurrect Europe’s old gas habits. Yes, Nord Stream isn’t dead-dead. One pipeline is damaged, one is intact, and - x.com</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 05:30:00 GMT</t>
+          <t>Tue, 23 Dec 2025 19:30:00 GMT</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVjVQekJDNlllb01kdFE1UXl2bXphc3FZR3FhSTdlM3R2V01PdHZCV3N5TjFldUhJZWxQOHctVS1Ra290WWVtWEVUSXZrV2J6LV9KelJmM05IelZDYTE5UDR2T25oMWoyV3BXWVlWQjl3R1dER01kRWlPdkpfRHpCTWt6ZTdVZjNqTmlEZk9yYmRTQ2VyN0pURnZTdmZUMVEwbTRjbU5iTnJJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE50MmxhaWczVW1NVThXbzZsQURhZExPeXBmR0FzV19vMWcyYW1CWTJjRWs2dm9IUWZvS19OUFlfYnRwWVhUeU1NTW5OeFUzTEhoaEJOLWM2YkUwU3FiRUdBMWVR?oc=5</t>
         </is>
       </c>
       <c r="F195" t="n">
         <v>1</v>
       </c>
       <c r="G195" s="2" t="n">
-        <v>46014.22916666666</v>
+        <v>46014.8125</v>
       </c>
     </row>
     <row r="196">
@@ -6884,24 +6884,24 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>My mum charges me £100 for Christmas dinner - and I'm happy to pay every penny - Devon Live</t>
+          <t>Analysis: Italy targets radical Left and Hamas-linked groups - Brussels Signal</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:52:18 GMT</t>
+          <t>Tue, 23 Dec 2025 16:09:39 GMT</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUmRXZ1NKaDRvUm5GaVJSakJyME9vV0lnSnJvZ0Q4ampieGcya19ZekxYMlhHbkFReXU1NE5qUmM3cTJRTlVNYnk0V0xWbVozM09DcEYtbEkxX1o1WUpvdkxTdno2WXlzUmUwR1UxcjdTeUlHaWU1Mk1LVFR5cXlTUllQOGk3MmNpRmdfUzBrTdIBjwFBVV95cUxNUmRXZ1NKaDRvUm5GaVJSakJyME9vV0lnSnJvZ0Q4ampieGcya19ZekxYMlhHbkFReXU1NE5qUmM3cTJRTlVNYnk0V0xWbVozM09DcEYtbEkxX1o1WUpvdkxTdno2WXlzUmUwR1UxcjdTeUlHaWU1Mk1LVFR5cXlTUllQOGk3MmNpRmdfUzBrTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNNHF3Zm12TDBtRDN4VVZQbkpoT294TmNqdG1ZVnR1NENsV25TX3cyanlvTkloYkdON005Z2NWR0J4aHRRX3AzQW5JMzZScS04alBXdHo0ZnN3OUlRaGo1VjdXT2JnV0llOXh0aXY1Z0RvUDBoOGh4NXgzY1FEeFR6Zm9zVE96V1h2bWg4S1JIUUFDWk5jOGhJX0dn?oc=5</t>
         </is>
       </c>
       <c r="F196" t="n">
         <v>1</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>46013.66131944444</v>
+        <v>46014.67336805556</v>
       </c>
     </row>
     <row r="197">
@@ -6917,24 +6917,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Horizon police arrest 22-year-old for hit-and-run, DWI, and using false ID - KDBC</t>
+          <t>Belgian church sexton and former priest arrested over cold-case child murder - The Brussels Times</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 19:00:41 GMT</t>
+          <t>Tue, 23 Dec 2025 16:42:14 GMT</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNLVNpSVM0TGlGdVh5MlQtejdndzdRNlFocWZnYTB4enpacUlOUFRIX09KWHhsaXlyb0JzZVdOdG9DQUlmMjRXbUtySVAxQmtCT3NEbUdZTVJiVVdhLXRIZ0lYTVZuYnBWc3NNUGxrTmhSeE9ob2NZa01VODF6RWVMbUdscHNiOUsyWHR4Ym5XaGlWU0RaanpTRkF1Z0VPTzduUTNGTTJNNENvQ2VVeWozT2VQTHlrVm9rMUtueGhvTkh1QUl5bDB3TDloaG5JY2dYMElBbmdwMGRxa2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPb3pWSGx1NXlYV0diMWUxajh3OFA5MEtKb1JTMG0zQk5DM2J3YnZISENBU2FyeUxfQjZEODRFSmZvVzBfZEhMSWNHYy04MFlBRUNFVTBybzQ1VXl0NjA4cVVkUS13ZXdlbjJuSWlXNURwVjJNUzlFQ1N1V1FGcTZUQmtiUklMeVpFUVRIckxzVVoyemF1SG1UQjMzR1d5ZENiWDB4ZXJ1SG1TYjJ0MGUxR24tV1o?oc=5</t>
         </is>
       </c>
       <c r="F197" t="n">
         <v>1</v>
       </c>
       <c r="G197" s="2" t="n">
-        <v>46013.7921412037</v>
+        <v>46014.69599537037</v>
       </c>
     </row>
     <row r="198">
@@ -6950,24 +6950,24 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Swiss Mansion Where Ronald Reagan Held Cold War Peace Talks Heads to Auction - ԱՐՑԱԽ ԼՐԱՏՎԱԿԱՆ</t>
+          <t>Bulgaria joins the Euro next week amid domestic scepticism - Brussels Signal</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 19:41:16 GMT</t>
+          <t>Tue, 23 Dec 2025 13:25:39 GMT</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTFBKaDR1eEJKbzkxWHRzMTJudWJ3ZTN3OUlhbDJudlBlOG4xZWh3MHJoVWlKUHo4Z1ZtQVNQSHE4QTMxTXRKQlhoS1hNTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNOFJGejJEQ0dCNXh5MjVfMk1SVTNmclJ0MWRLRHVuNW1PVHZQRzIwdEF1eTNHQ3p4NGFKY1JEUmJjWklXVUdkWXJGSFZ1cGR0em4zd3NkaUtjU0RGQ1NBRWFPUUw4MUhkeE5JMUgzRjl2QjZUZjlxMXpJS1p4X1NuWjhRTEp6TVpMdjVGZmUxdlFfOWRrZG16aQ?oc=5</t>
         </is>
       </c>
       <c r="F198" t="n">
         <v>1</v>
       </c>
       <c r="G198" s="2" t="n">
-        <v>46013.82032407408</v>
+        <v>46014.55947916667</v>
       </c>
     </row>
     <row r="199">
@@ -6983,24 +6983,24 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>What happened overnight? Police blotter report for Monday, December 22 - Newzjunky</t>
+          <t>Suspect of violent robberies with screwdriver detained in Limburg - The Brussels Times</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 15:30:04 GMT</t>
+          <t>Tue, 23 Dec 2025 15:04:45 GMT</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQN2hsaHo5SjVnNjI1MEkwYlVLUU5Bd3RlZnZzTm1ITEx1dGYtaVRPSjRCcmFCbWhjNXdDZ1JSckRONW42UHI4UXhZbDQ4UlhacVphc0FKY242ODJJd2dialkzZ2oxVmt1NldvYzVvc3VpamhUeWhLN28wYnZiOVpBbjFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNSFFKN0R4aGVKVmhQcjVrNlQwT1pWV3dCX3o3TGR3N3pLbVM5SmJRWnRiY0pvOVNCU2J2cnJfMjJHdEhaa3R6cGNBNnEzSGN0Zm9qNXhDOTJrUl9kWENVVHQ4amEzWkRTX1ZmZ29vWTc3YmdKSW0zLWI0Y3NGVGVQOTVQdFNCSGZBOXR4R2FXWVdxOTQzdkNkS1ZYVEN0Zk9TeE5SOTRn?oc=5</t>
         </is>
       </c>
       <c r="F199" t="n">
         <v>1</v>
       </c>
       <c r="G199" s="2" t="n">
-        <v>46013.64587962963</v>
+        <v>46014.62829861111</v>
       </c>
     </row>
     <row r="200">
@@ -7016,24 +7016,24 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Drug-related violence rises in Belgium, increasing public safety concerns: Report - usmuslims.com</t>
+          <t>Analysis: Europeans start to rebel against the prospect of conscription - Brussels Signal</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 09:46:00 GMT</t>
+          <t>Tue, 23 Dec 2025 09:30:09 GMT</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQOVVqVk9vMFlCZ3ZyQm5PblcxREZ1MXJUSW5EQS1rSEt0Y09tRHhyMXlTazZiVGxUeHpaX3FqUmVDXzJ4eXQ5QjhqMkZQUy1NbnVCUndmTzFiNWZyZ1lHY09QTUppZE1aWEpFT3ZpODhFRnBBOURFa08wdVZWV2ZKRWV0ZUhvUGFTb1ZyTk5zcWlORktTa0R0YlAtWENmUllORHhUWWN6ZXFXZGdMUzVxYVNlWFBZanlN0gHIAUFVX3lxTFBCZ09PaUx6T2ZHQ18wT2pUN1d4YndsdkdEOW1PVTdONmR2VlFJZjk5Y214cWF6TUhsQVBpemlaTmZXckxWX1VVazhndEc5eWk0ZHZYNV9pcll1dXpRR3RnclFLZDRBZ3A0cU05VXoyUVBzWDY2NzkxaTNfekQ0aUtpenIwZDdsQWN6dnZLTEVoeFlMNEI3STJockxSalR3OFowQXFlMVQwNGNrRXZwc1BueGFXYXVCQU9jUlVLSTdjd2tUdkNpQVBJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNUGt0amdjdENXLUFLN3RVY3dKXzUxOTR0OWJWd2JiWm5nYmVVazMwQndpMVN6d2VxajJYSk9RRU4za1BrMXZER2NjMjR5RnlTZlpFQm5pQzhNcVFKd0lWaGxMUm9DM3BFZEM1WDU0LXJFdzdxTUdWeW9KbkQ0SGo5Z2ZzZ05zSl9NVU9FRUk3NF9Pd3hPLUwzNkpVdmpYMTROS1RtaGJSRGc?oc=5</t>
         </is>
       </c>
       <c r="F200" t="n">
         <v>1</v>
       </c>
       <c r="G200" s="2" t="n">
-        <v>46013.40694444445</v>
+        <v>46014.3959375</v>
       </c>
     </row>
     <row r="201">
@@ -7049,222 +7049,585 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Erasmus is back: The London-Brussels agreement - lnginnorthernbc.ca</t>
+          <t>Fierce anti-government protests in Albania after corruption charges - Brussels Signal</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 10:18:15 GMT</t>
+          <t>Tue, 23 Dec 2025 14:00:47 GMT</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPYWVlVlluaGNVbnRBSV9JSlAzZ0JHd29EOFU1RXJDc09JYlQxNFZFUXNFSC1vakMtcnBQQl9pSHNvZk43X0ZwcG5oQUk2UkJnZ04xb0NvaHVBMUdKREJ5OTZkNWk5S1BKWEw0VnNwdHBiMlFqdTZqVmdXZFMyMW1vb1c1eG5hUDFIeVpxOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPY0dBR1hUcHEwVUdtN3NmMVJwSEVYMnBtcTFRYk5nV0pCb0hzem1walpKR3QzcEZDT2hyT3RJV0VaeUtwRE5IU1pGSjI3TU5ZNzBJcDl1cElMY3FBallfT3hXWFY4aUpLbjlfanFfM3NQdk1QWnAzNUlOU1UtS1BUVGhlMTRpTzVyVDd5UWZIdk9NQm9FZVdCLVJrUVI0UHZLNkhMOQ?oc=5</t>
         </is>
       </c>
       <c r="F201" t="n">
         <v>1</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>46013.42934027778</v>
+        <v>46014.58387731481</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Village search Wertheim,</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR Wertheim) AND (incident OR protest OR police OR security OR evacuation OR closure)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Curt Cignetti Led Indiana to Impossible Success and Closure for Bob Knight - Sports Illustrated</t>
+          <t>Flemish Education Minister calls in police after students send threats over school holiday plans - The Brussels Times</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:00:05 GMT</t>
+          <t>Tue, 23 Dec 2025 16:42:13 GMT</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNbkEtQmFzRndxTTFnUHVJcUdFN1BBc2VOd1UwRUk4UVhRNkwxSEt4RWpyRUFzRW9UUDVramJfZWszay1FMkd1UThpQi00MzNnZWNzZFhzbzNCUlNjY284WDhfWjVxMUxEQVA4UVZHWlJtTlZBSDV0X1JnT2psQ1lpYnFmdGRXS1pXRjloTHdqWG9yQ2NxOU9CQmNwbE91Ul8zcDZ1OThSd21ydklkZlh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNMHo2VkplbXlsWDZVUkVHN2VIeDZubHZCVDkzNDJ0SldVSWlWUE1tLTVJQkJ6MWVRQlI3QlUzTGNWMnIxMGFCRXlqSHdLSGZ5ZEJKWi11ai05bi1STERhd2ZVWWRaZmM0UEFFWWpka1o4ZE8tTWtpMWNETHlUeTliZ0MwaDVSVUNPd01XUDEwMUtkeUhYVVZnQ3VKM205MThUdVlicEVSWlJFaUV3NlZfWDJjaVhYZzRVUTA5aExFbmc1Y3JNZ1ppWlRFSkp2V2M?oc=5</t>
         </is>
       </c>
       <c r="F202" t="n">
         <v>1</v>
       </c>
       <c r="G202" s="2" t="n">
-        <v>46013.50005787037</v>
+        <v>46014.69598379629</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Man dies after incident on Dartmoor by River Dart - Devon Live</t>
+          <t>Longford farmers deeply unhappy over controversial Mercosur trade deal - Ireland Live</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Tue, 23 Dec 2025 03:05:45 GMT</t>
+          <t>Tue, 23 Dec 2025 07:36:08 GMT</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNQ0NSei1heWU0M0JFVER6NDRhT1FhNzRlRHlMWEdTQjkyWk15M3hiQVJwell1T1F0LVM2LW1LOUZFS0VUd1ZaYkhhcGNLSnZ1WkMwbGN0YmEwNktxUUlFellEZHZGTzZvZVVaRlZ5WVNuTkEtQWhZdXVCd2hGaDhpQWEtMDZldFE1S1dj0gGQAUFVX3lxTE1CalJmMEhwN09sQzBRa1NkMmxzcHRvTjV6NjhNZ3B0bmhGRC0yLU5TZEFCRjBtRzJnMU1GaVVTNnZVRjVqYXdvSjBjc1NjQUhvRzdJdERwWGFNcEVoTGhmbGFBNS1nTWRsOExWckQ0c0RlanlmWTZ3djBJc3hMSHNZUEVoU3JxNHBCanY1cmFPdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNT1JCMzVWMXptaTNHaklpTFo4RUsxWHJkS0k4Wll0bnJnSUswWkFzNmxSdDFHTUJxeTdzX3hSYzEyRms4R3lPVHpxODFBQW94OGlYZzd2TTkwOWNTZ1dvT3Blb0JQWU5hQlVaMS01OUJFQzNvVHE2VXFBS21MMnpHSmpDODBxbE55bkEwVXNSZ29HZnp1T2VvWTRTd0E2N3cxaGZtZ3lncTVNNmtGaTB2SXJ3NTlYQTk0Q1I3ODdyX05TZEk2NThMU0t3?oc=5</t>
         </is>
       </c>
       <c r="F203" t="n">
         <v>1</v>
       </c>
       <c r="G203" s="2" t="n">
-        <v>46014.12899305556</v>
+        <v>46014.31675925926</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Car park at Castletown demesne reopens following standoff - RTE.ie</t>
+          <t>What happened overnight? Police blotter report for Tuesday, December 23 - Newzjunky</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 08:48:30 GMT</t>
+          <t>Tue, 23 Dec 2025 12:00:20 GMT</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOeU5aRElCMWZ3NnVoaU9oeE1YRjRrOUZYYUdvaUlDeFhqcGFCVi1MNTRPcXl0SmhQcWdiRDhXdjZaVlMyZGhxaWZlbFhmaDg1R2l3WHgzM05jam04YlIxSTE0VmJtZ21CZHNqWVZXSEkyOS1Wa0ZmcHhrYW1XUGlOWHRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNa0ptQlU0NUQ5Sjc3WXYzZWNyZGNRcUdpR2s0SFdRR214cmJ6UlNjbmlHMmtEdUliVnQwdm9PbWd4aW10cE1BaTduODgwNExPNC04V0VJV0lFV2JVLUxfQzhGV09WVkR2MHhIaWI1Y05tZG9DZUg3UkxMcTNxYmNFUlJ0TQ?oc=5</t>
         </is>
       </c>
       <c r="F204" t="n">
         <v>1</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>46013.36701388889</v>
+        <v>46014.50023148148</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>€239,040 Funding for Kildare playground recreational space upgrade - Ireland Live</t>
+          <t>IFA president from Laois demands farming future for son in front farmers from across Europe - Laois Live Leinster Express</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 14:40:04 GMT</t>
+          <t>Tue, 23 Dec 2025 12:26:57 GMT</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQaXJiUGNrU0JHTllMVS1aek0xOWVwd011SS16SlNfNndjSWw0WWtkOEZoQ3l6WUNOUE10MlJyWEZRZWtFNHlEY3RSbGg4OUhGRVZQLUs5Z2laeTRPZ2hWaUFONHl2bFdwRWR2T0VpZjJVTXdCRkxZTGROT2NqSzdQQTFfNzVFWVJfOUkzY29ubmxsMWVyd1MyVmlKYTg3WmpTcW14MWdLVzNOem1VcjJtWVNmUVUtNm95Z2tMQXY3X2M1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOd1lFa2hxc0dEajFESk53MDlJSmVOaWctZnZYazRKQzFsYzhVS0NfdkRSSGZKZTRKU2V5QlFScHJsZ29aZXBBZ0VBMGhnVzRvQ2VMZnI4aGllRThsbjI4aElKcTlMYzRBeDRoN2NUX01wWWgydHJoWVFURnNtMjRhcUIzQ3EydDdzU21VT0p2WkI1ams0Tjc1YXhSenh4R1Z3dkF0bmJqLXlWVW1RN2xPWHFMXy1XcHRzVmI0MXFhTWhqdFRMUHRZRGNaNjdlYXExakFQeW91QXdDOTI5YXB6SmVuT2lUdUE?oc=5</t>
         </is>
       </c>
       <c r="F205" t="n">
         <v>1</v>
       </c>
       <c r="G205" s="2" t="n">
-        <v>46013.61115740741</v>
+        <v>46014.51871527778</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Woman arrested on suspicion of murder in Irish toddler death probe - Kildare Now</t>
+          <t>Commission reports on partner countries’ compliance with visa-free travel requirements - EU Reporter</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Mon, 22 Dec 2025 12:35:00 GMT</t>
+          <t>Tue, 23 Dec 2025 08:40:21 GMT</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOS2hiUTRncTY1RXppdE9nYVo5eVI1Q25EN0FQMHc4cGM0WjZnNnBjbHNaNFlOQXVMNXduX1lrRHR1RnVZWUxBNmRjZ0VuTzBzS2RjT1UzQUVXY3V3ajg4VGNsY3ctRVg4Q090VFZsbFdDRnBrTVVBcGhMNW9JaEJBUERscV80OW43MjNhTllLdEZIMi1TWEdrY3hqZmxyNURreWFrTlFOQzFCWkF3ZmlhV0lrbDAwYThPdnlPZTFfcVUyXzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNamlQQVhrUVJyck10Q01HZ0xTcWJRNjR3ZHp2T1NqblJSc2VCR1RDQ3Z5SGVmYk1wYk9zWXpTUzV0X0JhVEFSMEJlVFhfcWlEUzRQb0lTcHFWRjlaSjQ5NW5QYzF6eEZOczlySlhYaXAtZzBUYm52WS1IOWp1WkRDYjBIT0ZfdzA5Y0JhV0t2d2t6ckxSellxT2N2ZDhwbTFaYm82YW1Gc2NydmRQYlNSa0FGY2NIb1ZHNHRpQjhlNmRyYXRPdV9ST211RXI5NWFlSjd0Wi1TQUZHWk05SHF4ZFUtYWZGWHM?oc=5</t>
         </is>
       </c>
       <c r="F206" t="n">
         <v>1</v>
       </c>
       <c r="G206" s="2" t="n">
-        <v>46013.52430555555</v>
+        <v>46014.36135416666</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Successful trial of Explosive Trace Detection equipment provided by the European Commission in Poland - EU Reporter</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 08:40:21 GMT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPRFpzTjQ4RF9fZk1GNi1USFZOVmJPQ1JVS2VMUUtzVEFLek1uc2VRRExSUktpUmswM3VlRDJ0QW5SRjJQWmZpZXNjYUlPYVFFV1ctQlJMVHpZNWRmWDhocjZCaWtTanlwZFNtaWdwV3JDbXEtczhqVjRGQ09GS2J1TUJKVV9zZTJheTVxQVlPUDVBQW5vUUhaUFZkb05rRWItOFNZYnFsOHZMVnRBUFF0SkNmTHRyazJ0U0xtR3IzOFVSX1RlM3VMTFNNOU9ScmxSVXJPZXBNSTNHemdtaXk4RXVqVXNEcWJnclMtdWQzbFRldw?oc=5</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>46014.36135416666</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Russia attacks Ukraine energy sector with drones and missiles strikes - France 24</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 15:52:06 GMT</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPYVlYMXdLbkM1aUdieUFwMzM1Rk5XbUlzUXlPMVoxS3FDY1ZKQ0czaXVHblZIZHoyb3lwUzNHU3FYQTBURDU3QUh3aHV4a0REbkJobEZzRWxiR3N1c3FWNHJXZUg1QmpZenRoa05ZcGJLNWEwZ01FWTVRYlVPWWNDWTFqVVJTRVZDVm8wWm9jeDhxSUo2WDdkd3phZTNHdFBfNnhaenI4NTIwLTBvS1JVbHln?oc=5</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>46014.66118055556</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Crisis in Brussels: political chaos and spending priorities spark harsh criticism - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 12:20:33 GMT</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZlUyWVRGX0tBeW4xX1phdmY5eTlydmRJQkd4MFhTemQzaTBUNFM0UGhRbnMzWTZjUENVVGNTdDh5QXJVRFcxU1J6RFhKRS04ekZkbWFJZmpWWkl4RlEtN0xWb1FRU3J5eEpBeTVPZzNlaW9qYTZ2MnlQU2NPdkFnMmZlMko0ZjNWRG9qWDg4azNRUGN6MkxtYmp5bmU5TVA5NWczcVJoV1BONGFSUDRrRl9YdF80dmZqR3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>46014.51427083334</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>US bans ex-EU commissioner, others over social media rules - The Business Standard</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 03:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbEdhcXdpYmd4cXREZ0V4M0hYNjRNeERQcnBrNGc5Uldmd2pYWjFtY1ZidkZkMktUYVJZSEZvUGhCdGtPc1V1OHFrclJaRGw2MktRSUNBTFdzaHRXX080SkQzeVBEczRlekR5aGJ6cUw4cTlSVEMtbWYtdXk0XzNGeV9qUXU0MWR4blRNQklJMEZBNERHN2ZtQVVRSdIBoAFBVV95cUxNNUo2cjl5MExFOHowVFU5RnVQM3EzcFd3eXZxU3FzZU03ckhjZ2gyeU9ROVI3c0ZoUURTZVM5Y1plbjVVVzZtQ1ZoVUk2Nll1VVlfVUJlX2kwVnc2WGtlTk9DVWtfLWpHQjdPc3BhcjRpMHowM1laMXpzVVdUU0FDN2k0enR4VEwxWDRvUnN4MzFLOVNnQ2dRY1lubG9JTW1Y?oc=5</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>46015.12847222222</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>EU moves entire thermal power plant to Ukraine in unprecedented operation - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 10:41:15 GMT</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOYnZtQ20tdDhHc044dng5V2xhZWhCM2xxOHhCTTlYZXpuT05haERQbXhXQzdJY3ZwT0VQMUtXQVhOUVFUalUwcUtTNV92QmE5Z1BIYTg4eVZHWTU5VENXU2FLdUdSaVhmdWpsNkU0OXRDb0NSc1hncjNZb3luUnN4SmowZjhuanFtU1AzRWJvMGVZVUxKVENmRWtJR0pEUi16cWgxQmxUT0h4cW9Ecjk5RE9DaS02QV93eHcxX3VxVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="2" t="n">
+        <v>46014.4453125</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Prince William brings his son to the same homeless shelter he first visited with Princess Diana - Cleveland 19 News</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 17:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOS0VqaUlPRlctNVZ6ZmlxZWh3SGZ1b2tUM3lOTGs2bzZ3bV90QWlpaWtIWjgwRFpzZV9OS1dGYkFoY2c1akhPUXk0VzFQWWZuNmotY3ZVNWdKc2tkeXVMX2VJTHZYaXR6MlV5aW1BM1dOVTg4TThKVUFDVFN4LW1hbHNxSlN6bS1HQXdNdkM0Z2JRT01EY09yWnI0YnBkNEoyMWVhSzc4ZlhzVlM2ZG5vMjltRHhYUk5GTXM2bGhaV3EtZEFEWkFjWUtFSWFaTlduM0pjMDd0VnVWNknSAdsBQVVfeXFMTktFamlJT0ZXLTVWemZpcWVod0hmdW9rVDN5TkxrNm82d21fdEFpaWlrSFo4MERac2VfTktXRmJBaGNnNWpIT1F5NFcxUFlmbjZqLWN2VTVnSnNrZHl1TF9lSUx2WGl0ejJVeWltQTNXTlU4OE04SlVBQ1RTeC1tYWxzcUpTem0tR0F3TXZDNGdiUU9NRGNPclpyNGJwZDRKMjFlYUs3OGZYc1ZTNmRubzI5bUR4WFJORk1zNmxoWldxLWRBRFpBY1lLRUlhWk5XbjNKYzA3dFZ1VjZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>46014.71111111111</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>France's parliament approves emergency bill to prevent US-style government shutdown - WKMG</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 11:23:48 GMT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQlBJbGtldHFoYXR2S1h5eE5RbWZaU3NQdTFBc2g5TUloVm9INkswcGhSWGFiT3g4V1ZfWGVZQlRhZnVCOENEY1otM3NKc3d5YUJDMGRPcUloLTJUS21NbF9tUVY0aGVlR1Zpak1JRmtyMjZKNGowMWdUZ3RzUEtHZWlSRDFNQUxzZHdSMnJLSnpIaGJucFI0V3JzSnh1YXFXZnFhU0hYU2VYNVNta0JvM3dWYmtJdUNaZ2owUVdnZXM5WTU3Zlg0?oc=5</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="2" t="n">
+        <v>46014.47486111111</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Germany deports criminals to Syria for first time in over ten years - Brussels Signal</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 15:19:44 GMT</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQWklnZDR5R1lBZUxKNkEyV3JkYi02blozZkNIcElELU1LTmxBamxhb1F3eWlzY3BRWVE0R1k0MHZfeDAtZk15ZHhBVm4tOEhLTEhoSGJKb3RaOFpRejFCU1R0eGtlcG1SWVc5emE0UHRCTFhWVDhuVVZ4WUltLWpZeFN2MXlUVVNxRXB0UGZTOU9DT0ZwdHZKZEhodUdqRHZqVUN5TA?oc=5</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="2" t="n">
+        <v>46014.63870370371</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Overturned vehicle on Highway 21 NB, left lane blocked - WTOC</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Mon, 22 Dec 2025 12:48:01 GMT</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOa1dHRWdJUGxibkUyV1U5S2pKSEZKUGlTbU5MbU1JNzAzZklINl93LTlBUEV1dmQtZDBkOERleXJnVHYtaFJnVVRNQTJYX3lPNW5iYTQ1dXdWX0gtRDVCQm9BTDVWaVJnYjJNUFJ4MExOMWF0SVhzYzNkeFM5NGxvVjNqdDNDQ0lDUmNLRXRyQncySlNNSVZvWGo5cnlLSFB2NEVGSdIBpAFBVV95cUxOa1dHRWdJUGxibkUyV1U5S2pKSEZKUGlTbU5MbU1JNzAzZklINl93LTlBUEV1dmQtZDBkOERleXJnVHYtaFJnVVRNQTJYX3lPNW5iYTQ1dXdWX0gtRDVCQm9BTDVWaVJnYjJNUFJ4MExOMWF0SVhzYzNkeFM5NGxvVjNqdDNDQ0lDUmNLRXRyQncySlNNSVZvWGo5cnlLSFB2NEVGSQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F207" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" s="2" t="n">
-        <v>46013.53334490741</v>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Driver rescued after lorry plunges down embankment in Powys collision - County Times</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 11:27:11 GMT</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNVWkxZGgzNlVSZUJFTml5TWItRjM1a2lKemlhN1lNdThWVE9udjdwVWlDTmo5Z3p6WnB4OWFaLXcyV3owaEtRSExtNjdmdThuN3Z6eklnOEU4R3YyVzRGdG00T2xGS1hNUUxCejUxWTZGNm9COHk5MDhNRXo0QUM2WDBzM013TW9TY3hieHNvbkJWRWVfcXhza3pn?oc=5</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>46014.47721064815</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Primary schools take part in Kildare Disability Week poster competition - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 20:37:36 GMT</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxONVZEZ01vUEZCWElfWXJxTlJWZVlrVlJDejRra2wzWGRzNXVpUmtOczBVOVpqd1BXWk5jWDIzSHZyTlJvdndIbmhmNTkyeGFpOFBSRm5rbnVTckhFbmlneGlaVjNqb18wU2V2eFZRak1Ed1pDVExPeUxmTkp3RVU3Ykk4aEtlVGEyOUJXektMNm1nNDlJZi1BZTNvX2NCeTI1WXVCN1pQc05wVnExSmxNSjRTUUlRalQxT2ZFa00welMyNE93QmRQZA?oc=5</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>46014.85944444445</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Woman arrested in child murder probe released without charge - Kildare Now</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 08:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPeXZKT1ozZW1oMzBHQ2hRdEdlcDdSTWlNa1BxcmJrMUpuVWpfeG1sSFJRdkU3VEFTSmY5MUozbnQzR19meXh5bjBLcld1dHFFUU5HaEV0cTRyTGEzQ3BuYm4wS1owVFJRbzBnaDVxOWVNbDA2UGRJdUlSaWRUOHloNnFLNE5sWHoxcER1Qk42aXktZFVmOE5GakUtWWtFSUxkd1N0OEx3M21RbVJmcnpvRUpCNUZ0U0hDeUR3?oc=5</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="2" t="n">
+        <v>46014.35763888889</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Two Kildare motorists speeding on National Slow Down Day - Ireland Live</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 14:34:37 GMT</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOURWUnFSTUY2T0QydHRBZkxFOUNOVHpnSGM0MEpxZ2xORWpRbUJDLXYtLTl3ZkEyaFA3U0pYTVdSQkRHUWhfZTZpN0x3Z3hWY1RJVk1YRHhwRDBVTkJKUm5uZ08ySzlVaXRUZzZMeW5JZ0FfMjNpZElaWWxWNGExd1NQbzNKdWhhNUJtY1VIWkJBblVYNXBBdHd3MHp1Z1dTanFiYmloZHFuNGVTUEVyMEZlOFQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="2" t="n">
+        <v>46014.60737268518</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>‘I want to bring anxiety to the surface': Shannon Cartier Lucy on her unsettling works - wallpaper.com</t>
+          <t>TikTok shopping habits go from budget to Burberry - Financial Times</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 09:00:00 GMT</t>
+          <t>Thu, 25 Dec 2025 05:00:09 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQQWRpR2hiTHFkdlBzaFRQTW1rZnZnZVM2VFR0N3ZvRDB5bS1mMnRmcmc5WktzeVU5WnNjWDJMeTNQNVZYM1ZzRXdzcFQzeURFdmVzNk5fTU0xVXFRQ0Y5Ni1WSXBGWHNiamVNSVJmZDZYTmsyamJQTzRibnlDQTViRTI2T0YxZlEx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE96RlFkeDlUNUJMVjhtcklDbklqQlpoaW5XdVZ2T01CS2hmaXlTeGFxeFdMcjRPYkgyYk5fN1ZTSmphZEpPYXdzRGRXd3R6Ykt4VWtmMWdWcXZyYmlFZldRc2FGS1lTTXpfOWVJekxIaWg?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46015.375</v>
+        <v>46016.2084375</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jun Aoki references translucent dress for colour-shifting Louis Vuitton flagship - Dezeen</t>
+          <t>Valentino Rossi once warned that his fans would never 'forget' the ending of the 2015 MotoGP season - motogpnews.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:30:00 GMT</t>
+          <t>Thu, 25 Dec 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOdTRYdUEyZWVlb3oyQ19PV0ZvRGxBN0ZPWUFwNnYxdk1mSWdWX0k0QzYwdVlVVTB1eVRqc1lkNTBUbEhUSnBPVW1BWmtaNGM0RmhkUHR3RjFpaXM3ZFFjekNYRWRwNEhRdGNxVEsyTnl3MmhqbldIYmgyeW4tNU9pNVlKcG5vdk9BTXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdkdXUzJCdWdueWdwaTh2MTZtNktQay1PX01wWktkOUdmM0cyLVhBaFNxajZZNHRZcnM2bTc1UExhdkg5SGxDTWhTU0lnZ3h2V09lOVJid29nSDlxZnF4U1pIdy1uajJXSTVPSVRwY1dtMS1kTjVnNXFCOEQzSVVjYVM3ck44cVltcFhiX25aQ3VneU5tVHRoa2drSEEtMlVsWVU5NDBzZmhzbTBDT25ZLWk0WFVGZERraG5zeTFPWXlhZ3FtR01SNVpEUDFBTmc2SkE?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46015.4375</v>
+        <v>46016.29166666666</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>This 70-year-old designer bag is officially the ultimate investment style for 2026, and years to come - Harper's BAZAAR</t>
+          <t>‘Percy Jackson’: Dior Goodjohn Breaks Down the “Epic” Battle in the Sea of Monsters - The Hollywood Reporter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 13:07:22 GMT</t>
+          <t>Wed, 24 Dec 2025 18:00:47 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQclU1bHFFQ3pQcFMwU1Zia0x0UFRINDYyTTZGQ3MxaExmQmhqYTZjU1ZRZkFPVDV6WXNOeDUxbU51bWZyX1NpQzVvWUZ0NVFncGttV1ZyRVAtcTNOOVFkT29oZjl4MHlNczhqVG9DeW14M0tnRFM3V2hlWXdKX0lDSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQWjdpYmZsYnl6ckhxR3ZsR0pVYWdodXE0Z1lDTl9RQ1F5REdpaXJwVHoxeEVLcDNFd0xHclZWR3N0ZUpPQlpPVWtLQURLOXl2WDZBNFJrcjFxVmkyNjlhQmxHUi1aZWM5bmg0MDdwZEVEUlZzSXdXVFJmWmJWeGFRZFNESkg3Yy1CV0NkdGs2NzZTcjNNQU53cFRQczk0MHNCWWVLYldBTE5IQmc?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46015.54678240741</v>
+        <v>46015.75054398148</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marc Marquez lacks “magic” of Valentino Rossi, claims former MotoGP winner - Crash.net</t>
+          <t>Henri Cartier-Bresson’s Iconic Book “Europeans” Reissued After 70 Years - DIYPhotography</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 09:00:00 GMT</t>
+          <t>Wed, 24 Dec 2025 19:26:39 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPajl6MFMtR01OdmhCa00xQWwwVERzZHhHQjExTk9IM2JTeW1Ma005a2ZPWmlGdkkzbXNXaThqQ0U2M0s3UmdWYjliWVMzWDFOMl9kTnZSWlE2NElPZERCLUlVb1dvRUpsQTJqSjdLT1BmUW5OTWJpcEtkNW5nYm0xemNINGtFNHhGOHhMbWVKZ1pNVXlJdWNUVEc1Q0ptbVRYZHZHdzhmUU80X0l1T0EydjFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNklWcnNOb29xSGZUOHdQRXozR0xFS3ZoLXlnRW9TNjl3MzJuV2Ryc3duSFFIOXZGTC1hWXFBTmlfekp2SS03TGsydU14LVhaamVIWGd0SmtXX2ZwWE9rd3g2SU5QNVBiZ3NNakFtb3luSjZQVEp2dmpFeEhhdWZQOVZvWWlhMUF6S29wR0x6Y0s3ZktxNGlKY09OeVd0U2pmREE?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46015.375</v>
+        <v>46015.81017361111</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Future Is Louis Vuitton's Latest Friend Of The House - L'OFFICIEL HOMME Singapore</t>
+          <t>Spirit airlines agents charged with theft after allegedly stealing passenger's Louis Vuitton purse at airport - Daily Mail</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:22:31 GMT</t>
+          <t>Wed, 24 Dec 2025 15:51:23 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPRDU4eDNPMm8xeHdIdGZOXzM1aEluOExCSURUeGtSaUZUZHZqVldwSDdiY3lFZzM4bWNFVGlJXzNJSHZaNVB3R29QeTRwcnJmOHE5ekdpWllmd1hkRnJtSEx5RnNTZFdfOXdJQVFFLXRfUy1PT21qOUtmdlA0UXZqRnBDSk1ZUlpINE5FTUFHT2Z4NVp0bmZ4alJXd2puZk9lOXNv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZTlSclVHVlhmTkNhQS1mdURHMUtOMzhITXdiVUFNUUpQa3B4SG1TTHBvWXlaSVF2amEwR2QxOGJIQnR3UTdqejdadi0taUpQeXFfTXRFNEpnX1g2RTcxUnRETlVrMl82TXBlaUpiQmhRVXczdHI3bE8wZG5OYnU0U2xfdWhMLVJndmUtd0JKN0FrNHE3MS11YUkzeW1HVk5ubmJRSlN4cEo3bl96M251LdIBtgFBVV95cUxPa21VNFU2TDk1SUk3VHJSM1B3R0NjelJtSVg3aERUbHJHU0NzaHB5bWlHTVJuUEVIU2ZPeVhTUVg1d0xvMGNyTHlEbWJqeFhPOTlIdE5zbGV3OE9WekxuM2M1YjR2YlZqR3czbXYyZVBGd29wbG5SeFV5VE4yZmtmTmlVLWY3OC0ta0hKd3BJWkJOSFlXdGNSTTNWMXNLR0hWQWRlU2pkOUNpSTgxZlBCWXpQOUZZQQ?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46015.43230324074</v>
+        <v>46015.66068287037</v>
       </c>
     </row>
     <row r="7">
@@ -647,57 +647,57 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Biggest Fashion News Stories of 2025 - fashionista.com</t>
+          <t>Biggest fashion moments of 2025: From Kendrick Lamar's jeans to Matthieu Blazy's Chanel debut - MSN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 13:45:00 GMT</t>
+          <t>Thu, 25 Dec 2025 01:14:54 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE05ZWFEaWtSaXB1QzUtU2E0cXAtNEZqeHlZcjh3NzdHS0lhUDdSdzFXZFhkc1FiZ0NYY0JYMGpxSG1jTjJYYS02bnh1dTBfMzMyc2FtUzhYdmVvLVUzNzZpZS02WW4xREdrMWFfOURfdmlwOXpxUk5FbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxQczF0YU9vVWZTOGJSdUxCWXBFcVFqcHV3TkNWTVY1eDVkMUVqdEJHamtxcTRoNWItbnNzLW9uN1ZnekFlYndWX1JlMlp6Z3NpTWEwQnltX2ZQVS1LOURmbW9TQzdBVTFwYWxlVUNoU3lyRWdGRDl0Vk55S041TXhCSFBJeXkyS2hPTzZWZ2RLTjYwSkZNS3BCMUJNZUJaTmZCTk55MTdhc09tUUo3T2ZzeHlVa0owYlAwOWpJWXVDN19MRjdxazBsNV9FcVZsbU9rQ0I1MDhCQ0lLa3RZdF9HTkVRY1BRSzlfT2R0VHNfbTJJeXRyNkN3TTZ0amxONVVlODZNNVFzN1Q3eWFGa3hVc095ekYtaGlFYUlYY1p1RUw?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46015.57291666666</v>
+        <v>46016.05201388889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The best red carpet moments of 2025 - Vogue Singapore</t>
+          <t>Driven by stronger fundamentals, Tier II/III boom, retail sector set for accelerated growth in 2026 - MSN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:52:53 GMT</t>
+          <t>Thu, 25 Dec 2025 07:33:29 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFA1M0tncHBwZEhiTk94WkFXYTFDdGxGZndoUTFZaDlZWmtOZEI0Z2wxM1ZLUTBTZlRyTVRrbXQza01BVi1EdlFqNDhwYW5MWmxTbmhZemFaNzd2QnNkTU1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPQVVCMWdYX0VaVVJwUVJ6TTZBZ0VSUkRFcl9NdGZvdV9uck8xdm9taXVXcmNVdmlmcGI4OXB6WG9WU292Vk9rbnJmT0ctSE9STlotVklRN09WMVZDYTBpWmhXUUNwb0NRRFB2STJuMUF0RUlRYkNzZ1MzVWVEaXoyYzJUT29FZlNpclZHRXEwQXp5T1hNZEkwMXF6X1lJdkJNcExSZElwR195alNOa1ptMHQ5Zlh4UzhtZWxGVlVZQldIYWp3WW5aQmJmVnBBQjRCaklHU1JPa0pfNFZ0YUtRemRjSk1tcWVZZ25HWVJGcU8tejR3OHFRd0FFRFotTG9ubHN6TVdQUmN2UQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46015.49505787037</v>
+        <v>46016.31491898148</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B&amp;M European Value Retail's (LON:BME) Returns Have Hit A Wall - Yahoo Finance UK</t>
+          <t>Retail (India) Limited’s Chart - Price Momentum Alerts &amp; Free Gain Edge With Data - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 14:01:09 GMT</t>
+          <t>Wed, 24 Dec 2025 17:22:22 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPZGhXbEl0WHFWRlZRZDJ6TVgxSTlkaTNBeDNFdkZOQlBvUTVsN2ltVnRvRV8xbjNLUEpjR2w4VEwwOGxENEgyLUJDMjZkODFhM1VJVzg3dzBmZTVSeGdjQXdITEU1bUN4VFdGbmhqZkw5WkNSVHdEUEtFVG9XTUpZMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPRFJPYkFIdDhxRHJTSTBFYk14SmxITzhLLUFwbjNyN19SU0xiZm1USGNlSXZJbTA5UGFGVXRaVmxZZjZIWFVUZi0xZDI2RU9icVRsLTdOZTFoUVpvSFpqSF9LSlBDMUlZcEFYam5pbXJVTGRZV091SG9TTE9iVHQ2ZWNwMHMtMlFRTTVlUjZodTNwVkYwdmNvd2pXODBQd0lUdTRtLTcxamt1SGpyVjlXOE5XWnJEVVZ6RXNHNnNCZmtldw?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46015.58413194444</v>
+        <v>46015.72386574074</v>
       </c>
     </row>
     <row r="10">
@@ -746,24 +746,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DHL Supply Chain signs multi-year contract with Siemens Mobility - Freightweek</t>
+          <t>Evri hires replacement delivery driver after parcel chaos on Oxfordshire estate - Oxford Mail</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:59:04 GMT</t>
+          <t>Wed, 24 Dec 2025 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQQVd4XzYybmprZ0phdnpCYlM3NENXM3Z6R0xRdmZUd0Jjak83bEdHT19lSkdDQjFYZmRhNGVRSkVueC15Y3ZETHc2M2prblYxSEQxUnNhNWpPeUdtTlctT2RTZXUwWmxlbjVWZ3QwaTA0U3VDX09vbm1VdllLX21wMmZDNm9NdFBySkxwQ0R4U0VEMnFzcmZQb3QwOVhyejZWbjdZZktlbHZFQTZtb2dCUm1UR0FCeHg3THRpNGJIQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPaE15WEhNT010TU5TMjNPdldWWWlIZVJNTmxCYXJucnFlTEl2RXBtSGFBbkNJOHhoUmN3TWg3OUltV0FuOVNSaVZkOVgxSFQxMTEtQ0FBTGh2MUJHQUpMSzVKcXhONl9PU0N6bTlJT1BqX0liSC1jU2hIaWRhWEUzUlY5Z0RQazBPWEs4V01LV3hSZjBIaHRobFpvOWxGR0U?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46015.45768518518</v>
+        <v>46015.66666666666</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Here's how to quickly tell if your Amazon order will arrive by Christmas - AOL.com</t>
+          <t>Streaming device deal: Save $20 on the Amazon Fire TV Stick 4K Max - Mashable</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 09:56:48 GMT</t>
+          <t>Wed, 24 Dec 2025 16:28:50 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOVFZNYXZDbmZpaWljejRYMGJ0MFBhck51SmNKWTVqSDE1X2RLSmtOazN1cVg4YTJ1VkppdFQ5TFp1ckl4TERTbTRaOFlOLW5TMk04YTBSSWZ6YS14X3dVUVdNQ3RCVmZmTG91ampocW84NzdtcUdQbDh4XzBMSDZXVVo1QTRuelFMeGNOajBQNlotWDE3ZWwwUWxxN2RoUy1SWk1Qc0V5dGVuVFdlT2UyajZ6Zklaa0VQbmpLTU1vYXRpNGRpWGpmR3h5cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBZNzZjamxGYzNYRlVfRktlSFItSjR2LVJVb2h3a2RfMWpXUGp4MExLZHQweWI1NEVlTHd6d0JrVVVFd1Z2Y0N1TDBZaE9Ma05lTkNWSVpJQTBpN0M4dUdUTjEzSklPRmMyeThTeHRNS0g2Qjh1QmRR?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46015.41444444445</v>
+        <v>46015.68668981481</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amazon delivery scam: As a tech journalist, I have this one warning for you | Technology News - Hindustan Times</t>
+          <t>Will there be mail on Christmas Eve? What about UPS, FedEx, banks? - The News-Press</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:03:51 GMT</t>
+          <t>Wed, 24 Dec 2025 17:55:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSHlGMmpqMWx2YjNheHFQR2FSR0tqZGh2UTRPWkVESG9Rd1FaUGtpQTRXdWFCSk5LOTAwaU1FZ0NFZnRybFhUdjJkZHhBaVczR2M1U2VhSHBqaXd3by12bmI5UTItaTNnREpBeUNwRDBCYzBhaEN1ZF9ReHNwQzhWWGYxSHpQdU1NTFNuVjJiRFctQXk3NEZrUkpQU1lJN3lkMkowanAtWmJHUmM4NDZnanJxNXZuaWhBRnB6RnNqY253d0tKNk5qajVnaENETWNhREHSAdcBQVVfeXFMUFZTQmVqT2JVelhBRFpRMjMyRHNkVTJ4UzhaX2JSRW5qeVZGNHhsYWRPUTVNblJlRzBfRnhCeDYwNzRoRWxTVnVFR25TczZMdHMtUWV0eWk4VlhUNHcxcUpfYXNyeHViX1FXN1NjLUFENE1tbkhFT3B1SE5VaU1tbG1EajJBSWIyb1pmZXdIMzZvOU1HSExfNk5WLVZqTnozZFV6UFJFd191cXIzR0tLYVNycUZiNGF4YWRFQVhBeXdhN0RfRGJUSHg1YkRPUDU3d0NabTFIX1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPMFFMRlNNS2JubXZ2aGh2ckRLZWFESC1LOWVqbkhMcnA4LWtrUVA0dDNWUno1NVFMLUZPWG9vaGFNRkkyMXpoVDR3aWtoampxWU9qNS1fckJSNUZwSmxTeDRhUmZMMW02SkxneGxjdnJFQk5GZTFuVUNVT2ZET3ZFZG5keWxWLUNMUDVVRHlxaFNGdXdjby1RZVVWcWU5WFhpSG80OWxZR0VfZWNSd1E?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46015.41934027777</v>
+        <v>46015.74652777778</v>
       </c>
     </row>
     <row r="13">
@@ -845,1278 +845,2367 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Stock hits 10% upper circuit as it expands operations by onboarding Amazon IXD Program - Trade Brains</t>
+          <t>Amazon delivery scam: As a tech journalist, I have this one warning for you - MSN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:03:00 GMT</t>
+          <t>Wed, 24 Dec 2025 23:01:39 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPWW5yTlZhS21faFdZVm5qWUJEZkFkS2tuLUFmUkRnejZ3eUU0b2NHbXdJYW5FNmZvQ0tCWUlCQmxFLUtES2FXNjdEdm1LY1IybFJvOUloa3JHUW01SWVWYUZkMTJ0NE53Nm1PbE1EeG1YbEpLM1VnR3NubDBibklHMzVnRmhaVjRnNGk2TWoyQndkMW5ybWxIdmFqR0xWdFBLaC03NmJHb3dEMnREaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOdklxVDhlYTlucXRsQ0hiLThhSnNkQWZXZFJyemg4Y3dYSXVibEZiSDNKQ2dLSGVZTnpacU9qSUNTQlhwMU5nTURLSjlRaDRESlJBc2hmWlhPTmtCNmd5NThlc3NYdVhWb2xxSlk0Y2hJZDRxaDVNclNqZEhfMVc0ZV9haTJjMTJYc19MbFEtUWl3ZXh5RnJHZkFqbDZwNnhfWWY4ZVVjMUs4aW82TFpyQ0tFYl85cm1LeVZjR083OE9iY3BmQzlfZC1LOUhuNjlqalB2SjFhOUM0eGNDZ3gwZ29xakhUV205cVc2SFo4dEh4YkYzMWlwNGNHdld3QTFQaGM4dVZFNnVHb2Va?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46015.41875</v>
+        <v>46015.95947916667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas Joins New York, Chicago, Boston, Phoenix, London, Tokyo and Frankfurt to Dominate the Business Travel Scene in 2025: Discover the Ultimate Corporate Hubs! - Travel And Tour World</t>
+          <t>Fast shipping is increasing emissions. Here’s why delivery has become more polluting - Florida Politics</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 09:34:56 GMT</t>
+          <t>Wed, 24 Dec 2025 16:32:23 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwJBVV95cUxPWHJSWkU1VWtpX1c4bTlRdTF0MFJmNkNoWEgtcVlzVmMzVGFBOU12NC1TWkdHSF90MTVINDAzTVFPaEZvdWpfcEk0VEpWSzY5U0JzRThXYW8yRkRWR2hfVEhjQkVkZlJwVVFhTUNic1BDWW1Zd0xDMWJ3RDlXbjRPRG1JbE1fQ2Rqa2FUUnR4c2NsRVliNDNWbjA4U0tOMFRHODRwX0RFNTNleEowMlBvN1VtU3VwYkM4LW0yN2E1VE9SM1hfZEl6YzVCa0xjdGpCamMwRno3dGZhUm1XdE1US2l0elZuUUVBZHJLQmprLXA2V1U4aDFwcFNmSzJFbXY4MDdkRVpHMmM2OVBaYjk1NkhybnU2TXgyOXd5OTFVY1VsVTJEeGo3eEVYWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQeG1yajhQWjIxajRlc2g3YlRjcXVEZjRSRTR6eWtabHBMZ0hvQU80ejVOYmNCT1BQYnZqR1BNSC1BakpBdXUyTUdOR1E4ZGxRUTVMS2M0WXd1QlQ5TkpySkdvSUtEMUp5ZklWWGRNRWJVWVdNa2Z3YWY5ZGVNS0tCaXZGZHYxUVB0QnF3N0YzOVFxRnZmSUVscW9pSGYyMUtBR1BabkpiYkdSNkFSVzNIYkh4b2ZFbS1GeXBaSHJYYXN5U3BZSWc?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46015.39925925926</v>
+        <v>46015.68915509259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Banaras Beads Limited Price Holds Above Key Fib Level - Weekly Market Snapshot &amp; Accelerated Financial Growth - Bollywood Helpline</t>
+          <t>Nihar Info launches Amazon Inter-State Xpress Delivery programme - BusinessLine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 13:17:04 GMT</t>
+          <t>Thu, 25 Dec 2025 06:42:56 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQQVNtN0ZNaF9qYWVTcnZMZmJFNjM3RUFYRXFwLUZ0b3pMa2NuRGV3cERzLWpUUVo1cnJuQnIyWjFyRFRQN1A3MXFXU0ZMczVuZi1KUDBWRTVkYWI0bzduUDZtY25MdHpwUHpTNmk0UXNPNmlSRW9SeG1lbEpPWHJTckVJWkpEVGdNdDVqaGtlSFBPeUZGcF92aDROOEFmVTJiZXh3QWxB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOTnJTYmJNdnNFcVNnOFJLX0lDR0V0STF1TnBYNTFYLWhKOGVSWFZwSjAybkZJb0ZKSWR0MW9ZUkVHREhxU3R5eWlUcEY0ak0wYnhheHVRbVNqSEhyVFQ5c2Z6TXNkSG4xeGxEcnlPbFNfWHRRdTBCcGZLNm5xdmlHTEU2MjNKUmEwMFFsbXJVY05qN0UzczV5c0VhLXJFVXVFR1d1MGpkMmNCbUtYRXBEcjJjUVFoVE9mUmpobHNrUnJKcFRNRFRzd211OG02SGphMnBnUFVR0gHcAUFVX3lxTFBNNDRTdmFYLWtvQzdxTzBveHJKSjVmeG5MZGs4Y3hDaXhvTm0yQ21hc21Ia29UMHEzYjBCa1RmeHRsTnlHekJyUnlhRTdqaHJScWI2enp2Qms2dVdCbHBNU2JFWXVxenhDaTZOamZFYlZPbWhqLXJEMlZKTW9SWjFHcWIxUFFkd2pqWVJZSGNpaHUzVTFHYVhKQ2JvOTFYc19mMFBHNDNyWEtGSEtCUjA5eFp5NExjVkt5QjlONU9Bd2I1b1QzczhSVVRnUnVpc1hhNm1SQ1dKdDBLVjY?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46015.55351851852</v>
+        <v>46016.27981481481</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Second victim killed in country road crash named as tributes left at scene - Manchester Evening News</t>
+          <t>OpenX integrates Amazon's machine learning to filter low-value impressions - PPC Land</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:28:00 GMT</t>
+          <t>Wed, 24 Dec 2025 15:41:42 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPOVBoQWNJeUtHdXpwUkJUb0RZT1Z4dmItUzFNbW5hdWlaRlZsMTBjUU9BbFItMTFUeUlnOGdnVTVSQWxaUU92M2dqZE12RWpHRjdTbmVtNGpNTGJwNGRSNmU4MHhjbzRsWXVCSXlscW5jOWVCOFhNTmtYUEcyQldWck1ZclU1a3ZrdEw2dzdhYllFYWR6M2diWmh6WUw4Zy1FWUYwUkM3TG5PaFB5TkJPYtIBtgFBVV95cUxQam55NHEwdURpYnpzN3Rla3ZJcC1kOUtuVEljU3dzNV9pNDZnVU83YmJOdFhFUWMxOHoySnhGSU4zM2xnbmR4QU45cE53WWZDbWlHcFJHbmZVN3lVdUxidnhTNVNYU3JPNGRwT2d1ODFQZFhYa0ZZdzdzY1ZXV1pLVnBKeV9VNTBNSkdORkUwMFlRc195S2E2XzJYc3B0UE9Vai0zbkt2MF9XR1dLY25DOERMQ3dlUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQVlM5aW9NYkNVd3l4Q0xybDFabVZwVXB0dzhWajgtMHZBalJ4VFJRVGJuZHFYbjRia1JkbDgxT21VNzBsNThMT25ON0kybFRZVDVCV3E5WjlxNFE3R1JKOFJsanFJeVlRRnJEUEF4NEdxZDBhNGp2WDQ0bVFMR3ZFSDRsYnp0WWZReUdHMDNNWFAxVmpDZFE?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46015.51944444444</v>
+        <v>46015.65395833334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The 25 Worst Columns of 2025, Part Four: An A-Bomb on Glastonbury, Mamdani derangement syndrome, and the least surprising Tory turn... - Conquest of the Useless | Mic Wright</t>
+          <t>Delivery disruption: Gig workers call nationwide strike against Swiggy, Zomato, Amazon &amp; others - NewsFirst Prime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 09:15:25 GMT</t>
+          <t>Thu, 25 Dec 2025 06:16:49 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNQlNiLVFYQ1l1NG9GLVNQNjN0S0h4ZWpDWTZzZnQyTFczQndwaExzWm8zOWtJRzU3LUpuUTJVa2xVOE9Sb3J2QXhtMGhfNWQ1RFYzSHRtWEhnVVNmSmNnc2lsRVN1dnZId1h4N0gyYnlQRHVaRy1GUVFhQ1NiVVlqNndR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQLS1NcVdWQXBtVElrNTJsZHFLRHNaUTFHZjRHMWljbW8zbGYwU0Z5YXRLSS1XUkZKbEtSbExmSU5DcjVBUGRYTWlMRldQSG9MZXF0c2VENzRCWmp2RG1UV1FPSE41V3BqQkVQbVZROU8yanI2aVF2QW9KRU5nOGNkWG92TU9lWVVqczlnbnlXSVoyMHNKbklxRF9fRm1UbkpkVmFjRWRhVXVlU3hfeWFmNUV2TTFoWlZuMmJUVUJkMDMtdWNSc3B5TGlUZFZ0dw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46015.38570601852</v>
+        <v>46016.26167824074</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Police make arrests during retail crime crackdown in Cheshire town - Chester Standard</t>
+          <t>Amazon claims AI speeds clean energy transition while IEA predicts renewable supply boom - MSN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:45:24 GMT</t>
+          <t>Wed, 24 Dec 2025 16:58:06 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxObjNCemh3WFpudmNKekZ5dGZtRXFqV3puUFdLVnFSRy1nY2ZrS1QyXzM2dGpxV0VwVXdST1VaWXhtVFh6OHc5WGdsQm9MMkl0ZVN0TzIwYVdha2hqSU1YYjNudDZwUVM4MER6UVI3T0ZQd0JMbWdiZmlhbjkxZGN2SmNoUnEyd1RqYnpxcFFIT01FMUJXQUhwVTFHVjdyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRG1kWGVUZ1F2bmRBOVVVQlg4X2xHWDJzdWpaNl8xT0tXenFiQXd2RlV0UE9vcURWZTBkRDV4WHN6V0d3ajg4aG5jRkZQVkpFNU5NWndqMTk1dzY0YjRZcHBIVW9jcDZlak13NnRyc3ItU0JrYUFwRnQ4RE9tc3JkeXRPQThEMTRJcU5rSDRscU9fbkMzcUxjaEkzNGFoc2hxclI5Z3M1R0xBdThOR3ZfVHJLMktZM2lhQjVIcVoxbGRjWHUwWDl4MzZ4UmVDa1lnRDBj?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46015.53152777778</v>
+        <v>46015.70701388889</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The latest rogues' gallery of criminals jailed in Nottinghamshire - Mansfield and Ashfield Chad</t>
+          <t>Amazon launches Christmas campaign with discounts greater than Black Friday and guaranteed delivery - Mix Vale</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:23:00 GMT</t>
+          <t>Thu, 25 Dec 2025 01:12:29 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQcnlEcnFlYzM1T2V6dHRkQ0RrLVZpNjNxVmZRQlZZVWlvYXlmVWJER3hXVUh3S21TZTEyYnBQVHJ2dzViM3ZWTk1vamxyVlNuQUplc0tia3hpbEwydGx1U1BBSk1IWWdTUms3angwNk1PWWpXa1lHdURfVGxIVHAtTXdBeVZDT2drX245WE5LWnhMREV1eERKY3JtbEtVMXRUQUhwQk8zem9KZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNSVdvaXdrTHpoSDVrOW1vOW1rSHlPNUpxaUdBXzdPa3VlTTcyLVptTllKamozSVhtaDg2UzFUeDY0dGNiNlk1b2VZcHNwaGtXR3FKb3UxRjJvTTBiNllDbTRUODlhWHJHVFFyUDgyQ2RnVllxTzVmZC15NDEtMnFnTklsM1JObENkU0J5bmFGdXhxN29WMl8zLVhiQjhnWmRhTjVqOGxuVWV1c2owbU5mM0t6V0JSeWNMMjdfZEdkdXByWUtURVV2MXNzeExtTEdCTk9wWWthdzPSAdgBQVVfeXFMTUlXb2l3a0x6aEg1azltbzlta0h5TzVKcWlHQV83T2t1ZU03Mi1abU5ZSmpqM0lYbWg4NlMxVHg2NHRjYjZZNW9lWXBzcGhrV0dxSm91MUYyb00wYjZZQ200VDg5YVhyR1RRclA4MkNkZ1ZZcU81ZmQteTQxLTJxZ05JbDNSTmxDZFNCeW5hRnV4cTdvVjJfMy1YYkI4Z1pkYU41ajhsblVldXNqMG1OZjNLeldCUnljTDI3X2RHZHVwcllLVEVVdjFzc3hMbUxHQk5PcFlrYXcz?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46015.51597222222</v>
+        <v>46016.05033564815</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Top 5 LPM Stories from 2025 - Loss Prevention Magazine</t>
+          <t>Parcels dumped in gardens across Beragh and Tyrone as Evri investigates - Photo 1 of 1 - Alpha Newspaper Group - tyronecon.co.uk</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 09:31:25 GMT</t>
+          <t>Wed, 24 Dec 2025 15:30:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5DcjdzUFdzYXdIcGlhMGx3NTRMSnQ4WkVBTU04RU5fTVV3QUMtMnZDYXBKS1lMcjNYMERrSkxxWmJlRElkMS1QbXkxT0phb3NfMnVrcE4zdEFBOGlubUtpU1lCTUxqaTREaWk0bGFmY09jZzll0gF0QVVfeXFMTkNyN3NQV3Nhd0hwaWEwbHc1NExKdDhaRUFNTThFTl9NVXdBQy0ydkNhcEpLWUxyM1gwRGtKTHFaYmVESWQxLVBteTFPSmFvc18ydWtwTjN0QUE4aW5tS2lTWUJNTGppNERpaTRsYWZjT2NnOWU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNWFhoNUZoRG03d3BKelRicmFyX0pnZkN2NkdVX3VNVFoyZTdURlVVdGxuZDBQN3RWVnpvYVlvMy14bGN1Y0JjQUtoWHktTm9zNDZDX3AxcGpZVTFHZk1QTUFidnRTQlJrYWU5Wk5Ib1RRNGVLNWxJZzAwLWp1ajN2bTd6TWQtSENMczB6ck9WcnJTSHJlQ3Nob05fYWYyd1F6WWR5bGxqTFVzaTJCTVdtekRkZzN6TE5senhVR19HVHRsMnQ5SzBpc2l3?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46015.39681712963</v>
+        <v>46015.64583333334</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Appeal after Midland bar assault leaves teen with eye injury - Birmingham Live</t>
+          <t>Fast delivery poses challenges, boosts emissions; green practices needed - India Today</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 13:23:00 GMT</t>
+          <t>Thu, 25 Dec 2025 07:20:41 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOamJXakxLM1VHRlNNZzFGTVpZTnZBNk53cWQ3V1R0RlRXSTc2cFVvMi0wOV9fMmhpOThKN0tZaHkwcU1PeTlZcFUzUXpPUE4wQnR4VkZxRnFsTVNGQ2R3YW5JdU9UMDd5bjkyVkotdWtlZnlzVjVNZzdURG5JLUNNMG11TVExSUFscHZpT3hNdGNLSzlpemZvONIBngFBVV95cUxNN0pDNnNJbkdDdHhFSUFCaVVjOU95WndZXzNKbW1ZbmJJVWZSMzhaZTBGMjNwUmotY0hkbURVTmREZ3lnejc0UkNBNHg3bVBoX1JWQU13ZkxURS1SeVhZdWx2UGYydDRXRWVNb1V0Z1lGS1FjcGJNSTRmZjlFSVQ0TlBpNE1GdldGNGNyallOZWRTWUhHamZ3bHhiUFNaUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPOFZjRUpab3B3dmxkU01QcUhuVk9hamZqVjk4c3JMZnpWaE5hSEF5RDVRLUNaaHZXMVBqSGFwME9aQ0swdklnblI5dEFGcnl5U3NzUUFNd0VCRmhKQmdkdnF0OE4tbHZJOEhVX1RLZGlkUDdwb01IUG42bXhVdWRaMVlUYTlXNDBTTjJhOWQ5ZE5jRzlWVFIyUU5SV1Q0cEtJcko4OG55UjllQ1dkY21uMVpmXzdtenRRdFM2VkkxNERkbnk1VzR4RXg2c9IB0AFBVV95cUxPUzI4X0hObnF2Sm95Y2xFSldIRC1RTHdKS192M2dtYWEtX2NaUVdmX1ByZUxRekZ0TVNVV2dKQ2RfSG9RV1ZjSHgta2dBNlNyMU0yNFVOUzB2OXdPTXJ5ekVjMDhJRTBtRkR6SFRMTlR0Q3ItTVFQekZESHpvRFBGOTRVSE9Ocnlnb3BzSEZVak9kd2cxdXJ6ZHlJeTVmaWFkc185NTAwUDVYX3BqRGVwakVUaFd0elZZWDAzVmdJN3ZMOFJRSXk0Z1hsVWJXeFdL?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46015.55763888889</v>
+        <v>46016.30603009259</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Police urge owners of this car to use extra security after arrest in Birmingham - Birmingham Live</t>
+          <t>NC Man Accused Of Shooting At Amazon Delivery Driver - thencbeat.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:57:00 GMT</t>
+          <t>Wed, 24 Dec 2025 21:49:20 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQM0xrbTdNcGhUZ3RZU3Z0NThncWtWUm1KSFRGUDJtbjBobS16c3JUeC1KQjZmXzBoNGNBRnp5VlFrTWd6VHR4dGkySUx6RERfOHIxRXZlbXI3cW5hTDh0YnBFM3Z3X3pKVHg4SllQbVlZY2VzNThzcDdxTXI2bmpSTXBLMHFoVkNfVGk2WGVJZHjSAZYBQVVfeXFMT3JkNWZJSzFaQTJiOVZMc1NabXVFOHpsNDhQQ0h1V01KVWlzZTZWTnFoRGJPNGd0bVRVVFk0V1FEVHg1WUFpckVtT3hqQnpGZ1VMWDVxWHF1MWRFMVVqNnZLcXdaX09QdWM2cjFWOGxmZTdJa0pRSzFEWXhydHdsM3FFcjRISGMtYWNnak1yemJVTHlVRmlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1fQm5KbGFaVHZRaTVVcDZWU25hZ21TSFZGOVlQRXhJSl9OMDBJVm9OZURHOXFiWjM0T1hBQy1pQXQ5Y1Y5bGYyeVI0bkJiMUlMUzlUc1ZZU0w2a2Fvay1ockhSVFR4Q29vNjZUVHFmWlBvTGFjTGpV?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46015.49791666667</v>
+        <v>46015.90925925926</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Multiple arrests made in statewide organized retail theft investigation - Lake County News,California</t>
+          <t>Horrible: Amazon Shares Statement After Flex Delivery Driver Allegedly Steals Woman's Cat - hotair.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:34:56 GMT</t>
+          <t>Wed, 24 Dec 2025 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQZzZUc3l5REFSSzBFN3BqbnhTWGhLMndVMjZfeG9qUHVWNzlhdDg1Wmp2VVlqVUFwTV9HamVuVTg4RmhoVjlsck9sZEdfM2xxaGdVcUdYekE5NjE0TjV0c194VlI4X3RmMkg1NHpSMU9MdVN5UjBOMGZfNGhqWlMxTjJxXzFtSEZKaTF4N0NYUnZPM09QWXlWS0NJZERJaGYyeFktWFFtUmVtMDRfd0lfUTlxRk8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOYkdWS2Q1ZHY3T3IxVWdUb2xBQTh1N2ZobVNxZUZRNXIwcHJMNUxVdXdqWFMtWjA2bzhvRzQzdUc4NFZYRGdrY0pzYVZoamF2SWxkbkpEVFE4Zkx4UTE1NTkxZGk3Q3F3aE5NcTRxRmd3ZXdDWHhyMngzVEJtd2t5VEV0aTJFVXFGOTZ6NjBuVzJfandyeF9XdjJzTjJkSEdkakJnQnBuTGlYNFRpc09wQUxPSkhMY3l5SkdfUUFUMU9abFlfZnl3bWlaekRENi1mdlE?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46015.44092592593</v>
+        <v>46015.66666666666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'Of course': Marcus Rashford confirms Man Utd return chances ahead of Barcelona transfer plan - FootballTransfers.com</t>
+          <t>Delivery companies may soon face new problems with holiday crunch hitting harder than expected - Red94</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:08:00 GMT</t>
+          <t>Thu, 25 Dec 2025 04:08:30 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNTWh2UXhOWV9Xa0RULUR2TlV1ZkY2SVlEcWUzV1JSQmRBeFp5X1dBR0N2ZHBieTZpekZJR09hekZmVEdvVWpmakk4SlhwOVFFc3B4MkdVSEtkb015aFRuNExMbU1zZkY0Ym1jdlpvLWRzUDRURFVJRDFIdWtjb0xkeTdDSHBNd3NWV3BGWHJZMjRqNjRkeFdLZVZmeGJsbElDUHhkVzBzZVYtTXpYRTNHejFUOFJRZ2JPWEc3U095ZW51bHhPcHg0cGU0OExfYUQ2dXo0NGNCdlI5OHJINE9WNGlPdGVjSzFSOVc3cDVval9KQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPN3VoeGZ6WmkwTmtsUVNRb1lNVFVJeXlRZ1VjYTRYdWdRTXRMcnZBaXpYeC1BWjNtMkFHMVNLNlUzQTJmY18zTDFab3Jlc2RQQmFabTMwYmd6cTU4YzN6b0RBOUNoLXhxR0VHRk93NHVwcXpYdU1oQ3dWSHdRcm9Cc0ZqRDhlbEZ4QXFpVHd1RFM1Q21FMk9zZ01fOGhHM1hQaUV1ZjN4dHRUY2Yt?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46015.46388888889</v>
+        <v>46016.17256944445</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bombshell at Camp Nou! From Las Palmas to Barça, Andreas Christensen is responsible - e-noticies.cat</t>
+          <t>Accuracy Shipping Limited Stock Fails to Break Resistance Traders React - Automated Trading Signals &amp; Free Explosive Return Secrets - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:00:00 GMT</t>
+          <t>Wed, 24 Dec 2025 21:24:32 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQXzlsSVE5c0l3b1E0MVZRRTRLWi1qZlI2RWRKQk9KMDdkZjcyRFVNbEFEM1ZiZDd2UVg0b0x0aUZFSlI1WU4yNWVDY2dscUtmRUlrM1Qxb3BvNTlKb2otM2hIUi1Fanl1Tk1hRDVseC1LT0k2MldhZGdBYUM5NDJscFlSaHU1clNjR0Vfc25MYmZURFExLTVKVE9NTzFJTFRX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQb2dhbWpXQ0x4Nllyd2Y4dVBRcUNHWTlUaUxBV0wxNURrWlI0bnRrZFh4Wl9mVkxpSEFETWQ5MnNodHJMbGFITHNxc19oZ0t2ZWdIdmt3ZVBSYXJ3YUpmYzhBLXBjeEdEZ3FGcVZaWUdLcnNKb3FZWHlyS05LQ1U4ZXhWTzBHUkIwV0EtTnM4Zk5PTXF2TGRTem5HSzk5SWFOZHV2OFhROGZhQQ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46015.5</v>
+        <v>46015.89203703704</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Local Town Searches Bicester and Kildare</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>(Kildare OR "Newbridge" OR "Bicester") AND ("protest" OR "boycott" OR "bomb" OR "shooting" OR "explosion" OR "stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mixed views on support for Israeli boycott among Kildare councillors - kildare-nationalist.ie</t>
+          <t>Child critically injured in stray dog attack in Al-Anbar - Shafaq News - شفق نيوز</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:32:55 GMT</t>
+          <t>Wed, 24 Dec 2025 23:08:04 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQX1pvNTdBbHQxSXY1V2hGREdTV2xsWFVOampnRU45ZGJVcS0td3JXcWRkWThwc2w2MDVxZmR2aG5oX1BYWHB5REkwYkpSeG1YUnFwTjJWUzZzMG9nN1hmWDNpYThtTV9ieGRtUHVwZnZZMFlheXNxdVh6SkhsbWJJR1JMbjFXMDVPdzZZS1lWa09XV1lLRWF0TFZPNnVfWXRsYTcyQjR4YUlYeXA4WG5kUGhSUktNVEw1dllhZTNtaFRNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNUlRud1lNUFJFTGZjOHcySVRqX0ROQ3dpcnBRLU5NTHZOTjdRMXZCT05uQTV6MkpXR21Fbkg1aVlwNTNNVmI2R2hYSjZhLXhtQlN4elVrdEo2ZG9wMlJtekFmLUMxUWRkekowZVNpMlc4NWtJQUo2eWhlYlNVVXJpRy1YWDBwYjB4V2I1dFFqYUwwcko50gGUAUFVX3lxTE1SVG53WU1QUkVMZmM4dzJJVGpfRE5Dd2lycFEtTk1Mdk5ON1ExdkJPTm5BNXoySldHbUVuSDVpWXA1M01WYjZHaFhKNmEteG1CU3h6VWt0SjZkb3AyUm16QWYtQzFRZGR6SjBlU2kyVzg1a0lBSjZ5aGViU1VVcmlHLVhYMHBiMHhXYjV0UWphTDBySjk?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46015.5228587963</v>
+        <v>46015.96393518519</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Police issue update after villagers evacuated in bomb scare - Oxford Mail</t>
+          <t>Published on: 2025-12-24 22:22:58 - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:47:34 GMT</t>
+          <t>Wed, 24 Dec 2025 22:52:57 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNQlFFMWctTHFUbUdxT2pqQWxFd3RWeHRrWFJmSDh3YVVTdlZid0F0elBaaFVid09laUdCcjFESEs2XzJxS0VtazIzTGk0bmpoRFFPTzBuWHh5U2Z3VklHellIZURjVDY5UHdBalFxZWFfZ25QdC1iYm9TRFdQTGlwclc5VHNGX1cyeDRIRFBYRTZFZXMxX3p5aUZ3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSTczc01NYmR2blFWU0xyRm5IZHVZRnI0VE02OUFONmx3OXhXMUdzTHRET256VUpaclMwR2N4elM4OHF1aXNWUzV4eHR6bE9KM3RTZFVoZmNyUmN0SG1sYTFiZDR6MTZSelpnU1JkMk1PRTRPVFpUUndRSXNhZGltdldYNXlzUEZ2UjNNTjhmLUVjM25ndUFleTZxRk8wVFFyN3pB?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46015.49136574074</v>
+        <v>46015.9534375</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Four men arrested after broad daylight stabbing in west London - london-now.co.uk</t>
+          <t>Greta Thunberg's arrest explained as government faces legal threat amid hunger strike update - The Mirror</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:15:40 GMT</t>
+          <t>Wed, 24 Dec 2025 15:20:45 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQWHlXa3JPWkFpVE1HOUY0b1hFeDlydnlNaDB1eVJtRWRGRGpMeVphRHZOQ2lPWnBveTJ3V3h2UUhiYTNDLVdqS3E5ZUpNU3U0YWpSRXZxdlB2eFBITjZZenZQNDRQUWl2YUppeWd0dmk0Wm5Ib0NKc3VHdHJmdGE4aVJjczJOMkl3Vko1bE51WE1Zdlo0dU0ydzAzZjBzYk9H?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOdjZTNkdQZWdkWkpUc21UN2VMZlc2X0RPRVpCZ003RW56d2kyczlxS2tpWGhMZXJXdUt1eXJRWEIyaTlQX0RpdlRUM1Z3aUFMRFVKck1nQVlzMXVJbkJ3QlZWSVlaSFpnOVhuSnEzd0VHVXc4V1lIQ0hFT0d6OU1XMmlkOG95aTRFZE5HYW9WM1JrNHlj?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46015.46921296296</v>
+        <v>46015.63940972222</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Two police officers killed in Moscow blast - Guardian Series</t>
+          <t>Officers out in force tackling Christmas retail crime - Cheshire's Silk 106.9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 09:47:15 GMT</t>
+          <t>Wed, 24 Dec 2025 14:40:52 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNmZtQThSMVo3Q0paaXB5eXN5VEd3azBGTC1SVk01YVZwTDIzdk4waV9Wb0lEaXVMejdKSUZHem9MSWw1VnRiMXpPRmlCWmV0QUltWTdBSkdLQ3dFV2VubXNwTHRnSlB6NXZrSHJRTTgyanRiTDRIMkd3empQOEdDTFR2bFpPaWdHcUp1cTFqeFhwZzJ2dUE1M3NCMlRMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOUHM4VVB4Y3FlWE1waU83ZXYwOXlFbUN1eWxXdWw1MkVwQjZ2cHZCZ3ZoaUw3akJ4bWxYN2pBOFBhVlEyMmN2d3ZTYmFlWlZwcVh5LTJCWHhZdUdrZUd1QVZpWVYySmxkaGVueWMyQ0hPZWJoWEFpeFpkVUx1TkZ0YXp1YTJhdEZaYUJtVmlWLVlqNHhpRnlLOUtQbw?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46015.4078125</v>
+        <v>46015.61171296296</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UK blitzed by 90 hours of 'non-stop' snow - as far south as Cornwall, London and Norfolk - Daily Express</t>
+          <t>13 arrested in retail crime probe. Goods traced to Modesto, other flea markets - Modesto Bee</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 09:17:00 GMT</t>
+          <t>Wed, 24 Dec 2025 20:38:50 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQMnFwMDZVTE43TTFVMnhCM0dkb09oX1Y4NHMzUFlGcU1TODh2QjlubV9hN2tEMVVTVjFmdFJBd2xfMkZWWi1nbDN2R21aaE9fZThVekpHbG81SnRvTzhPS1FhcTloMGhoUWFpVUEwZWNTNTRyWFgyWUJPVldWaldtddIBhgFBVV95cUxQSTgwSjJMQ241QmdNY25va2RaU2dpdTJOY0xmTFJlTTJXQWJpRmhSeU5IYzFUakVYLTR3dDdkMzRKYjBsY3ktZzdPY184SnBYd2NZSGJIMGtxMmVWanN3dlcwOGRYcGtiQS1jUUhnLXBlQzc3ZmpJQ3RVU21hUHhJSGxGLWtJQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1JNHdmc0FPZ1R1UG5WUExqVUtfZC1DekZab2x2TEJSYnhVN3BVSGQ0TnItTFNHc25JVUxTTkszWWhFSXdIMExtZWYwUE1wZm50cHRBb3pEMG12WVY0WkFPVFpWRER6S1BoQXpfU2Rn0gFuQVVfeXFMT0d1V2FUbEM2Q2VqaXhnZDBOTHZqY3NuVjdsTVlKQzA3RWZTQVlZUXlvcVA5SGNMVmhSQWYtdnlYcnoxUVhySWFIQ2NuRElLcTlDVUE5UjV1c0lpMnpIcTRYalRxRWlzejdmODJwQVE?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46015.38680555556</v>
+        <v>46015.86030092592</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Sopranos star accused of attempted murder after 'shooting woman in face' - Daily Express</t>
+          <t>EXCLUSIVE: Brazen shoplifting crew hits Nebraska Crossing; $3,000 in merchandise recovered - WOWT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:33:00 GMT</t>
+          <t>Thu, 25 Dec 2025 03:34:09 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNR0lmdDlIQnVJYTFkeHhKM1R2U2U1RDlHeTI2d3dOMHBDRXE1VEVDZFpqcmNYRkJjWnoxdXNKUk5uN1hramhmNjcxZ3ctMVRWRmVpN21uZEh5b2JDdHUzUUdmYnN2QUZfMWtydUhWNW5fV0pBSVBmNmZScERHUWs5YzdKcEN1SklvY0p2ZllTelk1WHZaMW5RQ002SdIBoAFBVV95cUxQZWRqTTBPc0sxTEpWcExtVUtBbnZFcjItdkVfY1czaXozRVlDRlRYbzNtbEVzWkhkelJvTlJXRnZ6a0F2VGZlR04yR19yN0d3OVJaUHdVcWtqb0NsRERKMG5HTzg2VmlxYlpTWHUzRWdMT2VwTHgyMDh2VFBRWEdxWHpxcEVzRlE2QXN1bzh1N0I2cl9mSHlmNlZ5TE00SVFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOZVVHZkdLd01OdFVrR2xWMVNnVUNtUng2c0Y1WEU4bnN4OS1lVHU4aFZSM3UyckpGbjNXUnhtNEYxQldGZzB3T1BzMVdhcmN6dXBFSERkYmtQUUZRM2lmczRGR2NuLUVEOTl1aFZidFIwUGZTVlpVYXZXMXJaNDI4T1k1UDVkb25OSVc5N29DN3BwUE1fR2VuN1BuMHBUYjZERUtTS2V6bmdzbU9zLVV5WVg4MHNVUjFEcFlKbW9ScnJLY0NqS1BHNmpmTdIBywFBVV95cUxOZVVHZkdLd01OdFVrR2xWMVNnVUNtUng2c0Y1WEU4bnN4OS1lVHU4aFZSM3UyckpGbjNXUnhtNEYxQldGZzB3T1BzMVdhcmN6dXBFSERkYmtQUUZRM2lmczRGR2NuLUVEOTl1aFZidFIwUGZTVlpVYXZXMXJaNDI4T1k1UDVkb25OSVc5N29DN3BwUE1fR2VuN1BuMHBUYjZERUtTS2V6bmdzbU9zLVV5WVg4MHNVUjFEcFlKbW9ScnJLY0NqS1BHNmpmTQ?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46015.48125</v>
+        <v>46016.14871527778</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3 Christmas wishes for the South Carolina men’s basketball team - The State</t>
+          <t>SCV News | CHP Makes Multiple Arrests Made in Statewide Organized Retail Theft Investigation - SCVNews.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:01:00 GMT</t>
+          <t>Wed, 24 Dec 2025 20:29:18 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOMHBDc0dCMkdkS1Qzel9JQTNXbGFBblRJNTNEbzRRWjBLMUxYOUNNMU5jd2I0UGV6blZfLUFFN0hjM2VzYmFxQmxoYlp6RDZIMEMtdnc4WjVXeWdNNVNwLUxHRG1KcTZpVWNKWV9Td3NuM3UwZ2VfSVRZb20zdXVUczI3WHMzb3hQVDl2aExwWk5ldk5vUkxVZS1fWmw4OFRSaHpRcy1oMUpvT2ZjaGlv0gGvAUFVX3lxTE1LNnNPX3hIdWxJa000NDgySkR2U3FTQzBnMHg1MGZNRDlYWG9TNUxwWFZ1WHRRa0xFUEtfVTVDd2JIWW80SkJzNVVjNzJLZG1yU1c1SzByMUw2dVJoMmo4UjVFNk0xZTByT1FNdXE0dGlGdTMxLVY3bmM1dU1CTjlmelVMdV9Jd3hrdHdkb1Zqa3JEVHprVWJ2bHlPUDgza3Y0M1hjMXR5UWRSc2hMNUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNcVNtX2x0SnB3UjNWNW5JQTVoOFhxY2g0c09DWGJlTHJvWElCWHgxU1BfYjNwT3dlcUk4WU5XUDhGV0hxeld5Z0VyTThnd2pacUdrYUtJUUJDaklFQ0NsUDRrbVhZVDlZajAwZ3AwMHR0OUJ3VmVBZTItMElMU3ZxU01sUzhmMFJpZmVLZC10WmhaRUFmN2dJV0NiVnBNQ0hwNU1FcA?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46015.50069444445</v>
+        <v>46015.85368055556</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>On this day: The Soviet invasion of Afghanistan started in 1979 - Philenews</t>
+          <t>Paterson Man Stole Nearly $6K in Power Tools from Local Lowe's, Authorities Charge - TAPinto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:35:29 GMT</t>
+          <t>Wed, 24 Dec 2025 15:07:45 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPSDQxTDFTV2NIeVczVFQtcjk2OGI1aVdvOVZhWHpKM0pMNXdsQzdmem1JWnhnXzVPZkNzTHhLQ2xnRjZUMVpzY0lzdDJQTjUwMjBxRTUwTmU4MFhZVGpLVHBmZUJVQ3RKbXlIN3JqSjBfQ0YzNHFtUHcyREhEZS1vMEhBRTZMSjN4R3pCX2p1UXRzclZKSGpMem4zVzBHbW5NcFItTmI3THN1TDBTVVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOR25TU3FiWTdOUFR4bTJCUmdhVU11d1JxTWdlaTF2Sk8ydFJEOXRDdjFMOTBSS0otYkwxdm9DQUp4b1FfTlg0U3pJOGlQVkdmNGg1YU5NbDhBcGJabG1CVndPQ0RrQUxtcFlmMk9zTDVLS1M2TUM5MEVkM3gzMVhMbUNDYWtQc1pTRURwc3pYR0psR0xsS3NvMzN2WVFTNVpuc0N5ZGNhYl92VDhVZEdCbVhpVUZHak0wTmNfNEZLanBUNmJQSlFZ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46015.44130787037</v>
+        <v>46015.63038194444</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Margaret Thatcher ignored French assassination threat flagged by MI5, documents reveal - Daily Express</t>
+          <t>Two Prolific Bognor Shoplifters Sentenced - sussex.news</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:07:00 GMT</t>
+          <t>Wed, 24 Dec 2025 15:41:27 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYW96dWY4b2lmSkJ6dGhjS0c5VkItLVdYazFJeGdPT3ZpNWpWUUNSaFpORnlkQk43QkVLdExoMURoX0MxMVFqakxZX0c4dU1nUHFwcjNKUWZuWWNxWGZ0blZBRDlJeDg2TFVQTU9kTkJOXzRSNlV4N2U0X2RoU05nbEdYeXBBWjVMS3FJOTdjVWQ4djg0MENKVDEzQ1I3elZya01iVXpmV3FOT2RnOWJaVVJB0gGyAUFVX3lxTE5hb3p1ZjhvaWZKQnp0aGNLRzlWQi0tV1hrMUl4Z09Pdmk1alZRQ1JoWk5GeWRCTjdCRUt0TGgxRGhfQzExUWpqTFlfRzh1TWdQcXByM0pRZm5ZY3FYZnRuVkFEOUl4ODZMVVBNT2ROQk5fNFI2VXg3ZTRfZGhTTmdsR1h5cEFaNUxLcUk5N2NVZDh2ODQwQ0pUMTNDUjd6VnJrTWJVemZXcU5PZGc5YlpVUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOcDUwbHE5clZWaE9ESjJ4V2MtdFJqRTNwdlRiUE80Rld6WlpNMDVGMzBvQ01wR3NNeHIzT3R2OXRHLW5oaE1kOTVQeXZIZEtESDdaV0ZBNXEyRG1jZ1JhWHo3MDloRDF2RTdDcFdUVjBQVkRsY3puLWtDLTVWRHExdHZQVQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46015.42152777778</v>
+        <v>46015.65378472222</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rescue efforts end after deadly explosion at Bucks Co. nursing home - NBC10 Philadelphia</t>
+          <t>Investigators sift through wreckage after fatal nursing home explosion in US - The Irish News</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:06:15 GMT</t>
+          <t>Wed, 24 Dec 2025 17:14:46 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPa0FsZWZrZEt4ZXVfRjliSUdtLURIZDBQUzJZeEpEY1pUVWlkNWZVV2xweHRfVHAySlZNMEdieGxfbi1SVlc3c2l0WUY5LW5ma0tZVUFWRlhld3RIdVYzU3puRFBiemlKTEFucVRyWWtwcHRtZVdNWHdwc1dRSy1pR3VqbC1MU0ZselVjVlpvRGVNOEI5LU91NUZiRG9yY3NhQTUyTi10ZWNPdUoySkNhc0tORlBucDhMYmZ1eDRoRWlRUdIBygFBVV95cUxNc2ZsOVBoUE1KQlN0V1pIVDZtRWtIbVptNDRrM3BFUWF4b1VrZHVQNVlUYzhpSUpoRjI1cE5kazlVZGlqU2s3MU5BbkJYMm9veXZFVGRmN1VzR3RBUUdnd21YLUF2X0FjMDVieWEyR0l5WWVsLVFGVEdqYUNQUWxCY0dyVjhyNDNoMlZDejdUVndsOUR1MUhNeXNUUXI2bnk2VVN5V2pSN25WbEx6c0hIZGJFNjIwcExwTjNxN3A4czA1ZThFMy0yUjNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSnNlUmVxWG95SThhaUsxSmRHMjJLNS0tRGRCVlhDRUV4SnYwYmlvY19FUHVMWU01QzdBSjhKdU5CQVdoN2dGdXFNRWpvZkdOYXVYc21jdjV1QXY1VnFtcV9NUTVMVHZ4bWxUS0sxbW5iWnZNbHZSQzBpTUhZeUpDY24walVjUzAycGg5Rk9KYlp6RmdCcVdVUzBIdjN0TDhRZ0JNVTQ4SFJpV2hUZDlFWmFoZlc5NHplbWlnZVkyazZNY1R3SFc0MmJqYkxndmZjMHpVT0d4R24?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46015.46267361111</v>
+        <v>46015.71858796296</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russian Hackers Claim Christmas Cyberattack on French Postal Service, Halting Deliveries - breitbart.com</t>
+          <t>How the war between two feared drug clans in Montenegro has reached Catalonia - Diari ARA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:41:04 GMT</t>
+          <t>Thu, 25 Dec 2025 07:00:55 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPNjZZYmpmd0VlU2lFRndnekJKdC1IeDZudEZOVXVxLU1XME9JSkszRkF2ckxNcS1DNmZBdmdPVHJDcGR0VkdRcEdfT21idDh4YmUzdlIwdy11UUZiWW5waXcwVm92eUtJTzNtTFV1YXc0ZGR3QmpvTjNKSFRDcTV4cHhXY2FrVjlUaWYzcEZncDdPOXExeVRfYU1VX1dvYXpobWdDejBtWFpCcVREcFRhMnFTZDB1TXVCbHhyaTdHcHJ3b3Ywa1VaUTFuaUIwNnpfUHfSAdIBQVVfeXFMTzY2WWJqZndFZVNpRUZ3Z3pCSnQtSHg2bnRGTlV1cS1NVzBPSUpLM0ZBdnJMTXEtQzZmQXZnT1RyQ3BkdFZHUXBHX09tYnQ4eGJlM3ZSMHctdVFGYllucGl3MFZvdnlLSU8zbUxVdWF3NGRkd0Jqb04zSkhUQ3E1eHB4V2Nha1Y5VGlmM3BGZ3A3TzlxMXlUX2FNVV9Xb2F6aG1nQ3owbVhaQnFURHBUYTJxU2QwdU11Qmx4cmk3R3Byd292MGtVWlExbmlCMDZ6X1B3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNaGFPZndqWU1sUkhMRWtleEFLeDJfdkh2VEdWRE9HWW5XM1pFQVNjMTZJMUZkQllEYkg3OGI4UENxRUQySHhPc1Y5WnFwTEU4ODNFSjgteUVTMllGMnZUUmNialJLaEhFUFRUWEdEVDYxYmlzbjhNSHdIX2FFSjFQeHFhWkRJaFlHbTdRcGY4VnUyVzVIUnNkUjZBNDI3emRXQTRRdWhYM0FHZk9lRTNXbm9lWmpHQ1FMUTdv0gHAAUFVX3lxTE9zbEZkRXFYSlByZGdhcnU1ZWVSdHh1SVFQUU9BX0pjUGVCQ1hHZHNLMkg3QW0wMXBELVJsNE5RcGV1bk1QUDBMYTU2Q2RLZUF1Ykl5MEVqcmZkVW1yaENvckxGcVE0NHI1SU1BbWZZejlqc3pzLVV2MXlBLUxESWhjaE03b1RWSEh4QTJpOENKNEtSQk9fOUVVWTVEdTRGdFZjN3NzZXI0Y2RTOVV2MFItejFCOVMwT0dHYmNxQlJEVQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46015.52851851852</v>
+        <v>46016.29230324074</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>How Kuuku Saah aims to serve community through real estate development - The Des Moines Register</t>
+          <t>Ecuador defender Pineida killed in shooting - AOL.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:02:58 GMT</t>
+          <t>Thu, 25 Dec 2025 00:28:28 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNSGQ2SVVTWWJFQjhjbVJXUmZyN1VocVNZbi1nS2xlUVprbWV5QXFnRkFPZU1YQVQzVmxpdUdzcWZxNkN1UGxtRWRyUEhvQ0VTQXgxc004T1RfOTlVWklGQUhFbWFVWEZxenJXWVYwZUtnM0FjWmJvdC1NSkUxX2lnODV3RWxITzByeTU4a2YwckZweTZzY0Y0UlUyZVo0b0ZFNU4zTDlESlB5OG5KU1JwUFJxWWVaRTRGRlRfWjNiSDdiWWN1ZDNuOWlqX09SRk5ORmxrd2hxSW5VNnRNRGhXYjR4dktHb0FnQXpCRFpjNXNYYnBD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNcjVqWk8wMTRQajVQbTJnUlAybnV4MTVubFBQN1ZFM3ZxZmx4SjdNNXpZbVhvQnlZdWNTUjBlTDZfSlE5QTE5UzV1N2N6QmpNRWlhTV83Vm9LS1lqTnBPbGJucEZZV1hXc2gzb0l0WFFpd1hfM09FbUFMMTNiZTl4eW41MmFFbTZUQ0xINg?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46015.50206018519</v>
+        <v>46016.01976851852</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Basketball Game Preview: Rising Sun Shiners vs. New Washington Mustangs - MaxPreps.com</t>
+          <t>Pattern Scan Adds Jio Financial Services Limited to Watchlist - Volume Spike Alerts &amp; 5 Stocks Every Investor Should Own - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:14:48 GMT</t>
+          <t>Wed, 24 Dec 2025 16:01:48 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNRzkyTndxTHpFZkd0OEYyR2JYc1lhamNudmtIVTJJd3MzZkpxdXVkWUtZQUVjaUZfMzR5N1U4NG9pMjl2aXNfOFo5aGh2Nm54bkUyZl82WkZ2N1BjZWVjcGVLVUNSRF80dmdpZmtubS1yaG1qbE03dVMwbnFMN2dlLXBxR0hfLTY2TmxrbDNvMHgtM3hoSEczUG8zOHRsT3JtRmoyaGdjdFFKNF9SY0tGclB0elF2ekRfMFZjRmM2ZndTa0Vi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQeENNTThYcVoySHJiX0p3Ti1kYlJsWjR0T0ttSEl5S0tWRUc1cFBvTGRLa0w2MlkxSXFtd3gyY2ltd2hXZ2JNZnh2UURlVnVQQkMycW9kNnZJVTIzVzViNDlLdXhldm9sTVo2VTVEcjVndndKWkFnOEVqcnlNSlViZVRkUHptZlQ1RWJicXJaLUVmXzA2Q0hzN3pHd2g?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46015.46861111111</v>
+        <v>46015.66791666667</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Watch: Milan publish behind the scenes video of Christmas photo shoot - SempreMilan</t>
+          <t>NCAA Under Massive Scrutiny as Drafted NBA Player James Nnaji Commits to Baylor in Explosive Move - Sportskeeda</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:00:00 GMT</t>
+          <t>Thu, 25 Dec 2025 06:46:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5VMlBaeEM0bTBKSDhKcnh6dmdwbkJrNG10STVtZ3hraGpCbUZKYV9oYXR2a1ZKeUk5dzdQUHpmSGRHeWh2REhObmE3X3l3Unp4ei13N1FQdUNuVGlUdjZMb2dra0JCb0tWNExwRDktMUXSAXZBVV95cUxNWV9PR3ZKUmphX3dXRmRaeE1WaTFwN3JjSDBqb3A3cDBkRXNVdGlaQ3RwQUVMRUJCdENWYTBfTTRQdEw2cDVQM1RjNmJ1TDRHbE5TZ1ZnTlFWUG9Eb3U1cGJhTDlEd3NQUXBfU2VOS3lNeDR1MXpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZVY5ME5TSWVKeFJPTC1MVmVuQmtubVBwZEhyNW1zVTB0TElGbkl1RTlvcldkU29GQ0VXd1VWTnVBWGtfdVRMX0NaYlN4VlhyMkNaa3JxdUZFblk0Z0dha0owNUxCQ1Y1NDkxODFYaDVxTmFwbEdhTGl5THlFTnpPN3BqYW84dl9keEw2bzF4am11NFZMcVBXNWNsamtjMEJPck9TTkN4aGp0UHhvSWxHNGk1Y3VfNkR6d2JnZlJHTlRaT2lkaWl3czVqUkQ?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46015.5</v>
+        <v>46016.28194444445</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tanker explosion on a highway in Italy (video) - mamul.am</t>
+          <t>Man charged with murder after fatal stabbing in north-west London - BBC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 08:54:36 GMT</t>
+          <t>Wed, 24 Dec 2025 16:49:15 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE5ITVpMMTk3bVdrZjM0NDVvR01pdlp0Qk5rMWVnMk5aQUd5bWU0Z1FnZy1wc2FsUUhCNHktTmtqdk5wY1NNbmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE83YlA2ZTBCOGFHR0FlQ2NkUDNDMFpmelZoallOVkJmdGVRZDhVZmFEcTZxMTlnaGxsZzVabGVSVmdXZmZZakxIU2pMUkhvSnFkYTh6MVpGZ19xcXpK0gFiQVVfeXFMUFVzSlh5YzVKRFd6eVo2T09EWU93WGx2bGZwaC1mNDVSMEZUM1RpYUtMeWtYRGQxZUpQZXNQZDFrVkQ4S0FxWVJqLWZTclNNR1BzaURsN0dCdFpIQll5MWxsS1E?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46015.37125</v>
+        <v>46015.70086805556</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NBA: The Spurs beat OKC again. The Heat, led by a lackluster Fontecchio, struggled. - Quotidiano Sportivo</t>
+          <t>New London police investigate reported shooting - NBC Connecticut</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:07:30 GMT</t>
+          <t>Wed, 24 Dec 2025 19:24:46 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUmhiTURlSmRjWGdKVTc3eFNfOTdTWEMtT1ZnOWNoeWIwX0pXQXJSY2YyMkVnWHYzZ3VSUUlicVZzVmVZcTVMQ1paeTJ2WTg0UVBiVWpQbXpXbFdPMjZrRlRUa3o4aF9sbkFwNmYxMGxPZVpRZFRfa3MwaXA1UnRCbFRmTEcySC1fdGs1UzVZSkZaTFVyS0VaU2tVY3BaYlFabXNUVHh5Mm1NbU9xVndUWjhqbzlERGRmdko0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPc2pIVUY4NGtzUS1lRkNrQ1hQR2tTSXUzSXNjY0Z3SjQyVC01enpnbWNEbGQ3UVJnMnIxVmRzRjViakhCajFTbTc5VkJ4TWtuc1BIQk1Kek5pdmxQN3J5VktTZXpEbFZqcGZTNUd3OFAzWW1hcS1OYzdzTUhfbnp5Si1pSW5IVTFleVlCRW11RDNqOGdGdzgwV2dlU0ZOTTllT0kwS1FhTXFxSW15RXfSAbYBQVVfeXFMUGZRMDZ4M2JtQ2RWQ00xa0t3alNxMVVWR0JhSnZtRW43eGx1ZE1BSnhUZENURmNJYUFjNnoya2pPZ0VEc1hLNXFQMzYzdmpZeFlkY255ay14ME5wUDFxNDB1djBSSjVsNmVwZUxHTkR4eUtpWkhDUmx1a2MtQXJoX3dxaUw2ZllwNlN0Q09vVkR6RzQzWUtsY1E3cmowTzVoNUFBYUhOdzR2eFNlWU5pb0VUejRiTkE?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46015.50520833334</v>
+        <v>46015.80886574074</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belgium moves to merge Brussels police zones to strengthen fight against crime - Anadolu Ajansı</t>
+          <t>The London borough with the most knife-crime in 2025 including triple stabbing - Yahoo News UK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:37:39 GMT</t>
+          <t>Thu, 25 Dec 2025 05:30:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQb1A3VUhXXzRHV25od183bHpvZGZvU3Q5Qkl6QllTTGo1MTFJMExwQlFrU3FtQW9feEQyS0lXd1owa1V1eFpxWnNxeWFtcXVrd3BSRjFHVjZocGJWbzQ5X19oWk54QnZDbF9mQ0REU3lUMzhOSUpYRmJQbE5oLVZjcU1nSVJGSjdiQUlwOFVoSEhNZDdXU21Wd3dzQWJFRFRYdlJuTU9IcUhUUlhCVzNRa2xQSDJ6TjJ0Nnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBiWWM0WXFZMEUwa1FvU0JfNDY2djk5WEcyNGJCbUtPU192WEd6WmNpMGlJajg0eGVDRzVKX3M1NXhiZnBaSmwwWWpTSHpDblhlVTlIM2l6NVBlMXYtWW5JTGxCd2VlaTMybWpnUlhTREdqSGtRbmh5dFk3RGI?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46015.48447916667</v>
+        <v>46016.22916666666</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thousands of farmers protest EU-Mercosur deal in Brussels - The Scottish Farmer</t>
+          <t>The underrated North London park perfect for a serene Boxing Day walk - My London</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:12:26 GMT</t>
+          <t>Thu, 25 Dec 2025 06:07:36 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNdTUzUFRZdHJWM1hOS0NQX1d6aHR3azk4ZTRMYUY0VEZld25FcklralhmZktkM0p5YUN1WUVueU5INUE3aTJWMGJIM0dqX2wzcGhHdlFTVWM4OVR2eHFTcjNpTEs4OXdQNGhESlJCUFBJV3FVQjJkUm5qb2czNW9oNTM2R0N4QTBycHB5blFYT2FyOUkxUHVIU2ZxSXZVeGIyYjZvU1p3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPRFJsY1Q5a3EwN3JSY2dLNm16ZU1zYjVBZlBqWVoxLUpsVEx1dVVTcXRIWFZMSGFNSXlieGE2eHk2MThnM2taREJ1SFFIUWpxZUN5cUZiSjNncVN5X0sxTGFYODQ4aEd2TVdmS0wtRFJZZGRLWV9PTmJQZ1c0eGNqTkZaUk9wY0RualBOY3hqeHVIbW9MdndyYUZR0gGfAUFVX3lxTFA0RjFfVEhDZXFoNEZwRUZ1TFBSTjdwVFhrbFdMd1JLeEZvMHk0S0pDdVUtcG1EenlnUU1LZTNfMmk4SWQtdEJ3NFkxalpydTBpekVXN2xHVF9naWFyVjFsajZtV2t5dlNGQmNNM2Z6NWJ4NTVDNEJpYWxOaW5oZ2xlRHdPYzJ3ZFNSd2xzYm93cHV1SkJOalFpMEtwbEtGUQ?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46015.42530092593</v>
+        <v>46016.25527777777</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fact Check: British man jailed for encouraging terrorism, not for calling COVID ‘fake’ - Reuters</t>
+          <t>New Hitchhikers Guide to the Galaxy experience opens in West London - how to get tickets - My London</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:58:46 GMT</t>
+          <t>Thu, 25 Dec 2025 06:31:16 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQbU1Oel9vV0tSN2ZCRlY5dl9uNHVtZGtfR2x4ZHpHcFhMeGFaY3dJYnVUdXVxQlV3TVlKeDJGM216bjVmUHR4TzMxd0FXaXV0MTBnSkZ6VmsxMUc4c2lmRGZoTzlsbUZ3Y0IxVTNhM3B5Q2NwQ3hRbmZ6YV9tZV9YaTU2MmJwelVlZGlkSjBKTlh6RjcyWlFRTGpPQjZINDI1b2syV3pWa3dVRFJrU29r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOLVpHZ2VDWWp6OERpbWVWRnZtdy1uNWl0cUFUbGFuLXhiZVdxYmpqTXpiZTZxSUdISU9KNFRoVnpJV3ZUUUFFTUttd1BOT2pxcWtCVlQ5VGdhbnVTM3RwSHlkVHVfWEF6RmFQNzFHUzh0TnRWRm9zaVIwOFotZVpVeE1Vb3QxdXk0WmVRc05wRHZqS24xWVB0SU5QWnFJSTZuQTQ4VjFB0gGrAUFVX3lxTFBCTk5SM2l4bzV5bzRsaGJzcUgtS2xZNEhTVG9xWF9sbE5nbXdOX2hKY1VmZEJ3Z0JUOHkxTGxxYW9veXVLdEdUMElmT2VjU1dZZmdqZHdBQjQxWkMwVDZFVjM4VDR4V3BjaFdtWlBuelRXa2FSVmxjUVY3Y2ZUZXNLXzNjLW1RYXlVZFVWYXhWcGR2cW5ma2NSMWNKbmRmdHJ2bDJzQkhWdWttOA?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46015.54081018519</v>
+        <v>46016.27171296296</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tomorrowland attendees sentenced after drug sales at festival - We Rave You</t>
+          <t>Two police officers are killed by car bomb in Moscow - days after Putin general ‘liquidated’ in blast - London Evening Standard</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:16:03 GMT</t>
+          <t>Wed, 24 Dec 2025 17:18:48 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOOGxGNzZ0aWtYdm5aYnpkLWlIX3NzWXBCYzRrYW5IMWxrSC1BNks4cVJsRXNjaExDRnktRXZqZkRmc1ZJcUpjQUliLUJ5bDdGdTV4NXV6RWtONWtfM0N2S1VxNTZ0RnlhS3pEQVJnc1JiMEg4aFBMVzFNdnVFOWxHUnI2c1dmS2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObjlpX1NmX0dSS0VsbVowcUZNTUtYd1FfeUpzNmpxWWdtRkNHWGRzNDg3NFlBRGV5SThSYm1qdGotN0Zxd0VYQmRkNllua091RkVHUUNxM2JrelJMOXR5SFRXZmVYM2ZzZmhDT21maUNNTGtFSERCLTFJdHdieFFxal85TFhDWDJIakFPMUNDOUpxNlhzNnZPNEh1eXpFeDFZZkp5WVNR?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46015.51114583333</v>
+        <v>46015.72138888889</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium's justice system under strain amid surge in drug-related violence: Report - Anadolu Ajansı</t>
+          <t>An explosion rocked Sumy - reports - news.cgtn.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:27:22 GMT</t>
+          <t>Thu, 25 Dec 2025 07:03:43 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNd29FeXZ1OTNlS3lxczJfNVoxVXpUZHhLelg5MmItT21TZjNSM2F2MVRVaUE5YTZlRkNTTzRrUld2enBHVDFiSWowVjdsU0dnalRuZGIxZFYyZVBJTUlBbkhsZW02VF9uY0tVYWlKQml1Z0l2Qlk0eFZnNFVBTFVsNXB6VEIzRnRVVEtxN1hrRl9xYk1BX2xrOVBfcnBoTTU3NkVvRTlVR04yeDNVMlFMLU1zc1BIcGZqcElF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8zdmd1T01vTy03d0VJQjBLRm15TVprMGd5T3VVamIxODZKREFkYUF4QVU1eGVkSWpWdkg1Z3lmZUk1NWNQQlV6M3hrZmFFNEtkZERrYkh3eHVVb2lBUVZmS2x1aFBFaXg3dW43bXFR?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46015.4356712963</v>
+        <v>46016.29424768518</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ukraine unveils 20-point peace proposal under discussion with US - Reuters</t>
+          <t>A-bomb survivors' groups denounce Japan's 'nuclear arms' remark - news.cgtn.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 10:40:02 GMT</t>
+          <t>Thu, 25 Dec 2025 05:01:19 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNRkMzVFdabjBLLXlURmlPQndKV2xsU1NWTDFjUFc2WWVmNXhaTWNyRXN0SUlfdXh3T05GUE5NZHdDNGkwd3Jad3lfSzJrbjJNRFFXWWszSnh6ZnQxclVjTmlkNkRIcWROUTNKaDJCaXlJcWVMQWExMHJBS1NRVk1qZkNLa1JKSHQ5UFE3U2tvZ2MzOElQUVUtalpRTXVBS1NCTGh6UVpRM28zdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQRW9Jc1hqRlYyb0pPOWowZDhaQzJRLUp4MWxBazhiMDUtbnhaYW1YdzRzQWZkMTQtN2tKTkxKQVpQUlhkRmdrUG5YeWN5RXlUUnNuaXBJNzJrcUdrVzRPNS1pQXNLaFJycWdtdzhJTHF2bENINmo2Q09YRFhRcU9hdWlsSVhtdlRWQ0RTQXZDRm44RXU0cTN2TXJfU2dfZm5qQTZfaEo0aE1KUjNyM1lxV0ROc0JCT1k3?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46015.44446759259</v>
+        <v>46016.20924768518</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>What happened overnight? Police blotter report for Wednesday, December 24 - Newzjunky</t>
+          <t>Hillingdon bin collection dates for Christmas and New Year plus how to recycle real trees - My London</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 12:00:23 GMT</t>
+          <t>Wed, 24 Dec 2025 20:32:04 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOdjlaVnBaSjM0bnJ4R0QwVUhwcHNyS01TYVduMzEyM3hqTkxybUxTRjl3d0YwdEZKMWlVTVh1cFh2TkVwemcza1l5YlhLU3dJNWRfSmVhLW9feFMwdnVQU281TmlXU3AyQlFtZlJhdVgzb3dHcTNpZzZVN2FudzhQLXNUV0xlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPaXNoZEFvSVpWdnZ5WDFlN1JhVjhWeG5FRWZMU2tCY1d1UE9vMWJRNG1Md3NlMkZYNDl1LWpSSHI1SmNvNFFQcXVEbElHekhyVXdwMWItN3d6VGxCMnV2LTMyNk82dFUwTEoxMHBGLUk5cTJhZ0RYTXo5NUY4YVM2M2VPM3RQM1lhSGxQclR5RjhLdFFIY1hUY3hyNWxWYkXSAaQBQVVfeXFMTW9VM1F0ZmpPV1NWdmZoRXJvaDNyMlcyVndUdnFpZEFBV04wb0duRzRteE5OOVVGcTZFc1ZyWVhCVWNfT05pYUVtUXdfUThWY2ZqZDJFSFZ2UUdOZktpM3RNYjlXeFpHOGh6YkRfOEFUdkJBNHJWTzRvYnpMb1UwdHprMHlEVEpuZUllNlFWX29RTmVYbFpOcEk1V05Vcm4tZHdoaEQ?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46015.5002662037</v>
+        <v>46015.85560185185</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>India must strengthen relations with all sides in Bangladesh - Prothom Alo English</t>
+          <t>Community marks one year since Doug Harless killed by London police - WKYT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 08:53:50 GMT</t>
+          <t>Wed, 24 Dec 2025 17:26:17 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5iakUtU0g0cWNXRU5ZcGpzTDE0WGczY1M0U1U0bmlkYzhvbVpEM19yZ0w0S2pucUFTdnJKcjNpVm4xeUxNOE9PRlNLbUQ4MnZpRzlYd1l2UHZ3b3PSAWhBVV95cUxNaUZIMlNDdXRNWldNVlBZRllEU1Y0aFpSOTZtZEJlZ3FLenZZZ3l0ODM1Q3RoNlNfdHcxQXRLVDlRRlI5WWZ1cS1zdmdqMFdiTzlPallZdEJWRFY5RFFBMlpWeG1jRGFXZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQZnBJcThfeGRubTk1aTUzeWFXYmh5WE00VHpJZ2RXMi1odWVUM1dydFJWd0ltekZlbDdvREpONWtiWE5uMnZ1bGFEdzl6SXg3UjRvT2hwc1JicXl6OXhXY0pRajZtN1hvRkZiaEVLUEtBclE1OFlmRVpvS0RUSmFuMjFOa3d0Y3A3a05aQUFjcGJ1d0FDZmpLbm4tdDF2QmlQcTJpZ2hyX29xUQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46015.3707175926</v>
+        <v>46015.72658564815</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EU 'strongly condemns' US visa restrictions on 5 Europeans, vows 'swift, decisive' action - usmuslims.com</t>
+          <t>One killed In Dhaka Crude Bomb Explosion As Bangladesh On Edge Before Tarique Rahman's Return - ETV Bharat</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 11:14:33 GMT</t>
+          <t>Wed, 24 Dec 2025 16:25:06 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNU9xUlFQaG5EZ3IzeFBCeGtFT3U0azU5bXRKQ1UwcGdveDJqSjZXd25WYmhhSUVhOVFoQ0NFdVBiRjV5cGpEUTNiNzloMFZzVkZ5LTQ5X3h4aDFXbUtGV3dVb0ozRjBNU2ZoaVJkcnQyU2pQNW51cmlUa3FTT2NXTHFvcVNIb1BrckxseE9KaVhUU25tR085Z2FnRjFJTHJO0gGwAUFVX3lxTE1NcGFLc0U4bTRNUDFsSkh3dXVISmMtNm14VGN0WG1jV013QUdFeTlYMUtOM1Jwa1dudEVlNDl5bnJJcFJKUWpCY3F4cmdSUnZzTHhRek9FTkI0OUJnRVgzTWo3Qk1MclNFNGZpNmR1eWlSWmtCMmRIZTNkSUlsRU1XTDEzcXJsR0k3ZXNDSC0ydm1ieXVtMmh4NkFMRVd3UUZMMjh5ZzVwX2FFMTMxMnp4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPcGNKRlNtVXdqN2dIZDZxc0lkOFFNSmFjd0dTUnRKamMzeUFWd1N4LWFWRlFZbUFRTUpPZ1B3NjJkcEJMNU5YbkxkSTcxV0k0MXFmT0tvQ0VOaG0xdzhWd0kzRmxmRi1CekFOMDIyeWVIeXpQbXJLZDVIUVZSZXE1Snc1QkdRdFRNNjItR0N4ckRlaDJTbFNtUzJRY0hicVRSd3dITE1UVdIBrAFBVV95cUxOU2hXUk0xaDVneElEUC1IV0FFd0lDeV80SFpGVnloZjZPZVZWM3RDVHUxMHJlMXJ6UzdDbFJXaE5LT1JNRzQ5dVZUYUJRNE1HT3Bxb0JZUXhiaEs0XzNVaGJfeE56VDUzVTh6M0YySXZIaXNrR0R6aEhSNlR5WHoteGhxdDJCOW9Ec3VyT3A2UzFOd1lNdmN1bXlxOUx2UkVvV3JtQkZnYUw1ZEhF?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46015.4684375</v>
+        <v>46015.68409722222</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Man slashed by masked attackers in Co Down - kildare-nationalist.ie</t>
+          <t>Pleasanton Man Shot, In Critical Condition: Police - Patch</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wed, 24 Dec 2025 13:32:59 GMT</t>
+          <t>Thu, 25 Dec 2025 02:55:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPUU9zX1JPWkdUMUtvTXg1NkQ3WkU4YVVUZzBXc1hicDdfeld5RUU1OGZQRW5xRVNhOXY3OGN1Njgzb1hBOXpubHQ2Y0RYeEd1bjE2Z1I2Wll1Z2VNM1BuSFRyc2hPLWpnSVFDZF90eWQ5M3Vwbzc0al9DUHF2MzJyc2NoaE9fVk1LMVZoNml0RWZ6bzMtNFRBN3drcDVmSzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPS2FzRUlvUHY1Vkl4dVlfNHFka0hjUmsxLWlQdnhfaHQ5Y0RQZHFYVjBUaVVPdlFRWEZtakQ1SEdPTEpsY21hU3pPV2JTOHlZc1pCRWlzbFhSRmxYMm9CdmpSeXJXNHUzNVZiUEZLV2lOdXc3VXF4TFRzQ2UxbHo4b0sxREtOY2drNGxJT3pqSlM4c1YwTWhvUFRDUWJvblZ6TXpwNGxNNzPSAaMBQVVfeXFMT2RwM0lsVFZMa054c256OTR5QlpueWVjSUdMRlNybXNDVm1Zei1RT1NpTUh6SnBMeXU1aFItcnhsOXZNczFrTHFDZlBEbG1zR3ZhWm1sdy1uYzd5d0xheGE5b21WYmVMYnVodUdmdEdFb01IYUVSaThOSVp2anZZM1hVU0NHS2gxSGtwOE9uQXpkYXROZ1Jqa2ZrS3ZMRzdXcWlSdw?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46015.56457175926</v>
+        <v>46016.12152777778</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>All Koreans want for Christmas is a better cake - The Korea Herald</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 04:23:57 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5GWGNPQ0pZSVR0QXNNQ3RWY3B1b2I0S0RSYnRfV1BvNTVTTW1aOXN0VmRMeU9vd1o0TjhnOUVUaXd6NVg0RUpfZGd3SE9nT3JkVkhkdktkQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46016.18329861111</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Man sentenced to 2 life sentences for 2023 Philly double murder - FOX 29 Philadelphia</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 18:26:01 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPeHVvdWNtVmNkeHoxRmdIay1jcWVPVXFGQXBBWklyQ1cweURkZE9Rb1FQYjhQdmNVMGc2OVF1VFJkeTRpUGw2VkdjeTRTNzBKVzRyR0tBeW52SjA4aDlnYzhKWElKXzVmS3V3eFhwdFNZeXBab3liVTJUS25DSkV1V2RzakhKdmZTSDdN0gGQAUFVX3lxTE1Wd3cyU1dpbUVjbElsNFpLMnJlbHdJNllsaFUxNGQxN2lyVGxFSUtjTTZOa09oQWg1RjdHX1I2ZFpwUUtPbFVUVXZsYVROYkc2akF5cmpxSlR4aU9XZGRORXhPaVZINjVWeHF5bkJiSlVHNFVWMW9sQmJCbXoxU3BEVS10a3hKSGVSaFBCUmY5eg?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46015.76806712963</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>12 killed, 59 wounded in Colo. theater shooting - Statesboro Herald</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 01:52:59 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPWUtuR014bnpUbVNGQVk4dWQ4X0ZpQ2Rna1Y2OWIxeGNRd2JuM2ZqLWxvUzF0cmdkU3FGZnd1TldybDNucmt5VU5FYXkwdTlaM2xqUnBQV2FFUE8zS0ZCdXctNFFaRjN4a0JZbEdYMmtMczRfbHUtRV9TcGtGYVNUUFZLTFZBQjhfZmUtQndn?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46016.07846064815</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Quant Models Detect Momentum Reversal in JSL Industries Limited - Straddle and Strangle Trades &amp; Free Explosive Trading Growth - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 07:09:53 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPTHA4bmRBaUhyMFFKODBBR0l2SEZuc0JsZUFqY203blpWVWxZcHFRT2RmVVNRMnU3dzI3NmxuZWZyZnRUUDhIZ2VXa2kzNTU3NjBZUDJGcG9NcVhXb3YyTk9lVGVfdEIxYzZyV09pNnZDYnNlSWFETFdEYU5LbTBScHhRUjU1STlEbHJLUmR0aVRDQkVpWUlibjNxa3cyU28?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46016.29853009259</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The Moscow-Kyiv conflict strains Paris-berlin ties - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQc3I5c2hSSHZMaWFUV3pHVER6QnNweU5wcnI5amN2S3VlWDNERzVwcERqM3I4WEZwRkxQcGRrcjctaFA2SERlWWk1a0ZBRjJxQ3lVcjFJcjlVX2Y2b0ZEZFNvczdaTDk0WV9jeFhVeWZsVFdsQnBVTFl5Mk9xN3dtSlhxVnB0T1JqRXBLZ3FDRERNRzlGazNQSWg1VF9FbkZoSG9odnh5VWV3YkhOc3VlYjRtRnjSAbQBQVVfeXFMUHNyOXNoUkh2TGlhVFd6R1REekJzcHlOcHJyOWpjdkt1ZVgzREc1cHBEajNyOFhGcEZMUHBka3I3LWhQNkhEZVlpNWtGQUYycUN5VXIxSXI5VV9mNm9GRGRTb3M3Wkw5NFlfY3hYVXlmbFRXbEJwVUxZeTJPcTd3bUpYcVZwdE9SakVwS2dxQ0RETUc5RmszUEloNVRfRW5GaEhvaHZ4eVVld2JITnN1ZWI0bUZ4?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46015.77083333334</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Polk has 'grown tremendously' throughout non-conference play - 247Sports</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 19:44:51 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSEpjN21FcC1CaVZrb2pzbzlCckdHRHZzN0xXSTk0c0VZR253a0JnZzFaY3dXWVhNSTl2OU80cjlBTGF0NV91ZHBEYkd2aUh6b25UeTg1Mnp4eUY1b1VUTzNkSmZKSnJjdzVSZTlJb05XNklRall6aTg5S0VzWHE0clRHNFNteFJWaUh5X24wRk5sSlh4dDV1aE83Y2xRZDZTVmktNWdnSnBIZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46015.8228125</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Deadly Double Shooting Lands Consecutive Life Sentences For Gunman - Patch</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 15:02:38 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOdmNqMlJCUkU1S3N5bEFaNGk5dHBkRE9QZ3huUHA1dnZMcTdPTjM3RmpkRXFVUUd3TVRtWi1oRWw4aWM4Y1haVlBnQ09nMlloeVgzUm9yT3FTN0NRVktZUUhNTzUyZzcySWE0MHBQMElWeEtianVaZlhJUVVmQ0VUMmpHbG5JeXpxUzlqQWNwY0lMbmNLbEZoanZRTzVUMkxhc3FvZ2lmMlc2TW9i0gHAAUFVX3lxTE9FMzM3bkZqTmZJU0k0eXVKNWgwRm9HTlhycURLZ00tbTl0S3FiTy0ybmpkX05neFRJUVhHUy1iUUhwS1daak0wSWx0b0tvemIzZ3lTSlNfN3hPQThnOTNYYjAzejNPSHVfeG1KN0tJbmNQWGJJWmdJcVpiNzBfVmNSaFhRNmM1WGFJT3hPM3AwZlRXcmRtbzNTVVloWGx6a0p0dTVkVjlfekZlbHhmSjlHVnEyZkRWZUJ5bnRrclV0MA?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46015.6268287037</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Indian men's hockey vice-captain Hardik Singh nominated for Khel Ratna, 24 Arjuna Awards nominees announced - ANI News</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 17:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOQ0tEclpUMV85ZEVCektKUThhQ0tKd1ByQWg0Z0M3dm5Ka3I4SXA5akk3Y3V1MWlfOGJHcUM0MFR3M0hndnFIaWtxS2ZCSFBVMzdvalFwNGl0X0ZUenRTUUl6VURTT2dRclM2eURLRXV2QzdSZnAybW1iMkZBbkJxck1qYmFuQ1VLSGxubU1OcUt6cjI2R0diZldvVF82cDNYcTNhb3NWWmhSYVV2ZHpkMjZuWFFRS2xZT3EtMXJIWEhsZWFzQ2EyVWhlZGFZWFd4TjN1QmMxX0JyZ2phME9OdnNpUmNUMVpKbGJZMndoeGJ6ai1rRG9UcTROSdIB-wFBVV95cUxOQ0tEclpUMV85ZEVCektKUThhQ0tKd1ByQWg0Z0M3dm5Ka3I4SXA5akk3Y3V1MWlfOGJHcUM0MFR3M0hndnFIaWtxS2ZCSFBVMzdvalFwNGl0X0ZUenRTUUl6VURTT2dRclM2eURLRXV2QzdSZnAybW1iMkZBbkJxck1qYmFuQ1VLSGxubU1OcUt6cjI2R0diZldvVF82cDNYcTNhb3NWWmhSYVV2ZHpkMjZuWFFRS2xZT3EtMXJIWEhsZWFzQ2EyVWhlZGFZWFd4TjN1QmMxX0JyZ2phME9OdnNpUmNUMVpKbGJZMndoeGJ6ai1rRG9UcTROSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46015.725</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IIFL Capital Services Limited Uptrend in Early Stages Indicators Say Yes - Support Zone Identification &amp; The Smart Money Is Buying These Picks - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 05:48:24 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQWU9yUzRtVWNpQlc1dWZrRnB6NFJ3SjFfUE1RSW1fV2J6dFE1MXhFVkxpRTFKUnpFMWowMVIxT1hNREZVcDJCYWRyV3FCVVV4YXZyVXIwZWFneGVWOGNhdktWQ2hPMzJ0c1E1LW15bTZiaTR2Q2k0c2lTM21SdTJzRmg3T1hGQlhYek5oaGxIbkRaQ0F6WGhVM1U1ZGpvSmhXaWt6Qk1XT2FtVTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46016.24194444445</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Film Room: Carter Breaks Off Explosive, Ojulari Gets His First Sack Back - Arizona Cardinals</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 16:05:15 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPU0NlSjJheDI4dHRpTTRDRWFKRGNIc0RLRW1zRlhPUEk2Vi1KNFUyaVp5Z3lINnM4WDhwak94UnNhNXZqd19tTzdVWHFhRTJLTVFpVndCZmg0M09qNFlIUTl1V2RjOG91UzdvTGdwM3k5VEt6eU1LRHJhdUMwZ2dPbHNySnZnTUNPT0w2R0g1RkxLWlVHZ2l6TjZyUWRKNkVFdjMzMEp5UURETk5tTVVJV1VnWUdpODg?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46015.6703125</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Intellectual Property Violation - Bollinger Bands Signals &amp; Accelerate Capital Gains - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 06:24:39 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9sRVZDcXVmMlpKQW13c0FoTVJiRWJZVUc5TXRmMWxScnF6YzJmdUVHVUpmYTB6MDhESnh1WlFvWXFVRlBjb0ktdGo3MG5qNW90aXpZRTY5WEh2NE1ITlVWOE1IUHUzVGdMNzY0akJTc3dlcGRkWTRGcFVUVlJOem8?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46016.26711805556</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Technical Bounce Expected in Resonance Specialties Limited Next Week - Morning Star Patterns &amp; Free Explosive Portfolio Gains - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 01:03:42 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQRzFvTmpDbDZXYzJULTlrcmVGMGc3VlpkVVlSVGVoaTFaZkNkbXRuOTBPUEFhQVRhMlJVanA2a1BBU1ZDd1ZBOUwxd0NGbk9MSGoyWmplVENDbkd2U0huSFh2WUE3VC1kYlByVURIWlBKUTg3U2RaUmZFTGpzWVBTUmc5cGVaeElsRnhHTDM0bnA3OEg0Ty1SdkFoWnYzOVo4VnZZajVtRmZ5eEJNbnlqTGlHT0Y5NGtnOGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46016.04423611111</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Mario Lopez reveals joint treatments after explosive sports destroyed his joints - paris-joaillerie.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 19:08:20 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQUnYzVjJsR2dVWWs5ZGFzX0gtbWNnNVB5WDVSZi1lc2VnSTFHRTRjWXRoZE5aaGg4bUxTcHBEYnBWR3ZsTGc3dDY2MGZpZk5FMzB6djFSNHE3TjlRejlvRDd4SGZXQ3lzQmpvUU1VMV93QXNvOXZueDZZT3pidXlPR2hxazhzUkYxZUE5aGI5TThFelZzekZmSmREak1SbW5sZ3MwbzctLVlsYXFLQWw5ZVpmR0lON2ZROEU5eDUweUtBQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46015.7974537037</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Explosion at Nigerian mosque kills at least seven - Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 23:44:41 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOQVo1NG45eTllZENBNzVJeG5ISkhWMlhJbzV2RkdNTXQ5M0hHVDF5TDBscG1nZ3l1RmFFWGJhekUxaWlQTHpMVjRtTENmV3A2Yy1rZzF5UDNzUXZyQUVzdnhSbl8zUF8yZEZ6TDlGNFhETnA5TjgtWnRoQnBmbkpvcGpPbF9UOGJUVDlEM1pra0IyUEktMGYyeEFZaWtvMlhjUUN3c0xTZElBSmxTVTNMdnp4X0lodTVlMS1HaTVMVTI?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46015.98936342593</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Netanyahu accuses Hamas of truce violation over Rafah explosion – Israel promises response - Українські Національні Новини</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 18:11:40 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPTlYtdEdKOTdOeGlCMlJTZGcwWFFFbDdyems2akdiaEl0c2RkalA3MGFoLXZsbEVWLVp5OEdNS1pFcDVoV0wxZzg5cENfZ2VOUVRVbnlfRWs0YTlLZlpjQ0VOa0FwOU5aMEJUQ2ZScmx0R1Ixb2F6d3Q2WXo5ZTlsaG5ZSGdudHlhVkJ1SWpteGY4QWhCWjQxLXZYclNpTlloQ24xUDZpbElUQ1hvdWFV0gGvAUFVX3lxTE9OVi10R0o5N054aUIyUlNkZzBYUUVsN3J6azZqR2JoSXRzZGRqUDcwYWgtdmxsRVYtWnk4R01LWkVwNWhXTDFnODlwQ19nZU5RVFVueV9FazRhOUtmWmNDRU5rQXA5TlowQlRDZlJybHRHUjFvYXp3dDZZejllOWxobllIZ250eWFWQnVJam14ZjhBaEJaNDEtdlhyU2lOWWhDbjFQNmlsSVRDWG91YVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46015.75810185185</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Centum Electronics Limited Included in Top Momentum Scan - Earnings Season Recap &amp; Double Digit Portfolio Growth - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 03:23:44 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQWHBOR1V0c0hndHZ4czZmaW84Q3N5cTVnMi1RQVRVV3dxRS1Kclo4N2lQZnJETXVmdnNFelhtWndmeXpyRWtMbHlPZWNfTWJrNERnc1Q5MzZVZU9yZTNtRjJNUGJvRlRKb3hxTnhEUmY4dExqYjZBNGdHd2pQRXo2c2JacVEweWU3aHZzNXh3Z1RqdVpNaUVQc0w0ZEhHVlYzWlZNcHlET0xZdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46016.14148148148</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Is Indbank Merchant Banking Services Limited (INDBANK) a Good Long Term Bet - Small Cap Stock Opportunities &amp; Explosive Capital Growth Plans - Bollywood Helpline</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 02:53:50 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQaUEzajVlYmtzYURieUdCOEM5Q3g4QlltbjJQbnBkUXhCZXVDWTRuM0RoRW9FM3A5WkdudHRseklwUnZyRmQ1MEs5S3VtV3RzMWhJUTI0T25XMnNJUDhQOWEtckJXeXQ5ZWdOa0dveFZSNmU2YjNYWFNNQURKQ0NoMzV4eWJfQ2RpRUJnNFh0VFJSWFVoQlBlN193d1pCazlsQkRFZEFUSmpVelBQTlBwU0JWT2djNnBqNVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46016.1207175926</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026 Olympics: Milan's short-term rental rush is over, hotel occupancy forecast at 85 percent. - Agenzia Nova</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 23:00:11 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPTVhIWXBkYTVfMTR4WkdtQjd6NUFsOFVQMUlFSFQxOFZ3MlV5NUNNOERvMmYySmVJMGVjeHg1LW5iaE1WWlRVa1dQMkZraEl4cFByQktSTkR1LWVuLV9rS0JoWGF1Yld0UE9Fd2dTX295eVU1Wk1kQ1JzOTBiN2tBN0F4TlFNTXcyTDBSbFBybEJqenpNanNON1l1dG13cnRwMktLal9NTzZjSTdyS3FqYzktTTRZWGoxekcxcEU4VUNaRF8zQVhKczhoLXNQbXFNSzlYR080NHBmSDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46015.95846064815</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Milan Momcilovic, No. 10 Iowa State jolt No. 1 Purdue - AOL.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 19:06:43 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE8tS3QxNHZFcHV6eGJaOEM4NDZpNkE2R0F2S28wOHhvajZuc3MxbERHMC1RNl90eUxDSWg4eHFoaVJKVXZuWXloaExWOF9nTHRiTmJDRE9IY05PU2xibFFSUGZkRWJreDh2YWo2NjdYSlNLa2ZoWF9DUkFucw?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46015.79633101852</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Liverpool have made their decision for Mohamed Salah - French Football Weekly</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 05:10:56 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQUDZXZVZqVHVNVnd5SVBGalBSemdxSVZSTzd5bUNIZ3dpOUF5SlEyLVRVUldlTEhIZHFnaHQ1RXdKQU8yNnZLdGRsbWttQ1JGLXAteE1oNlhlelFUcEZIS2VxUlEwN0R6ZEdidE96cTBsX3VxZGpmaWtNbzNRb1FsR0lJUlAwTldsZmt1dVlXWTQ2dm1xc0R4TEJDRzJWZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46016.21592592593</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Breathtaking view/ The moment a tanker explodes in the middle of the road in Italy - Indeksonline.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 00:33:56 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNajdNNk54cFJaSnpNMkVrZ3lRaTRhZnlmVTdmRTdkY1JUMk11VXZMVE5rMTNiYUZZM1docGtZbHpvUU9xVy1xdjEzTlJZVjNRZG9LUVFiVHB4VGVsNU8zLUFUeFhzZ1VoSDFWS0FKV3VzcEVEendqVVpWT2tEUlZ2SWQ0NVFmQVdTQllOMFItMXBNNXRDWDVXZnVuMzIzVldvT1NIbzllVk1SeGdBYjlneGV3Z0t5akk?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46016.02356481482</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>"He said some very, very, very mean things": Love Is Blind: Italy star Karen reflects on her explosive post-marriage clash with Nicola - Soap Central</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 17:21:46 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNOFVzT3V2b3N2VVpiYXFWaW90Z2ZJdEhyN1V4NEVHS2Q4V3BCUzhBZV9BNW5FX3dRQmJ1SWpNVTBTbmg3UDRaTl9ENG9LLUNxRE10ZHdhMnVGSUR4T01pM2J0X1R6XzRSdnF5aURsREFrcVB6aVlvWXZwbV9pR2ZqYkxCWGxnSW9jMXRlVHNodlcxTmM0d1pfcHJGSXVsZEdhbkJPQVEyWFFySTVjSXVrUmRKSWVZbFlsaXpNa01FaVdxcERBYU9CMW9LeTJNdDBlWmNnVEJIWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46015.72344907407</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Thousands of European farmers protest in Brussels demanding a robust CAP and fair competition - Floral Daily</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 14:38:07 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNaFQ5anFpWkI5c1AzNVlTeXdfRmM0NVZ5ZFQ3OHlGNmpaTjVHWkxpNjltVTBiZTFOVTlLNTROVzg3OEE3cEtWZk9DRkp1SFVWekg3cFo4c3ZiNm14QTNLOEpyR0pURjFWTF9OWm1QSWYtLUNQNVh2cGtCbjhhLTUtVDJ5N3RlNl9iTm5kUGU0NVBmUVFJY05tbWtGcWcyQ1I2WmlqRk9fWFVFNG9acTh1aFB0QmZjQUo1bktKMS1wbnB3cS1MQzVGUllCLVVwaFlLdHc1bw?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46015.60980324074</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Brussels police zones merger set to take effect in 2027 - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 15:01:35 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPMWs2OU1tMGVpakctXzlMWXdDZUg3VFdkVG9JeGQzNEVJaW1teDMycFdIajUyMko3OUVHcTJSRzc2UkFyc2tsX2plM25sQ25RR2ZnRDlPN3FHeVRFVHBuVmVkaHpYNldUYW4xRTNHNXpOd1J1Z25odXpSd09Mbm8wZ1BJQUx4LUV4N0M1NjF5OHVsTE1VMWJrZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46015.62609953704</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Farmers take their fury to the streets in Brussels - Irish Farmers Journal</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 22:05:34 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNel9yZ2wxWjZwNVlSWFB4RE1sbjNvdm1xcEhJQ2FjOXJhQ2xKMHNMNUJ0N1ZwUnJWNjNna0NPclh4dm5UTFZBY0JUYTBXSWI4NWpLM3JkaEN0a1h6X3RTZkhRZlkza0E4SjVzaGRLbWFFVWFnYjdZN0xtSGpyUEttWDA2QzVDMzBBbzdEOEZWSDBUV2JsajJuNTB3NV9adw?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46015.92053240741</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Brussels sprouts will taste 'amazing' if one ingredient is sprayed over them - The Mirror</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Thu, 25 Dec 2025 03:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTklFbUtwX0FmUWJtTmpWYzdraTRYLVBwSjNXalpCVmlOQUNSRVNHRlVNa3MxajlYY09hS2p3b29lNW1iLWRRV2RFMzlLZTVGX2ppMHBzREJiS0F4cUEyalhCWFl2ZzEtOGhTZVluUk9oMUxqMlp1Y1pSclRlcmk3QlpvOC1iZW1WbHfSAYoBQVVfeXFMT05JRW1LcF9BZlFibU5qVmM3a2k0WC1QcEozV2paQlZpTkFDUkVTR0ZVTWtzMWo5WGNPYUtqd29vZTVtYi1kUVdkRTM5S2U1Rl9qaTBwc0RCYktBeHFBMmpYQlhZdmcxLThoU2VZblJPaDFMajJadWNaUnJUZXJpN0JabzgtYmVtVmx3?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46016.13680555556</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Limerick IFA flag waved proudly at huge farmer protest in Brussels - Limerick Leader</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 16:03:01 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNMG94bkY2SWlZaU9UZnpfUWh6MmVIeHVPWk9sWVUyMHBUQm00ZEdOOEt2NzBKNnhLUjN5QVMzRDVYbnVJZHI0U2tGcDNkQUJ5V1c4bWxqT3F6RDNZVE1LSXlTVXRxN3lYMDl4Q25IbWhCdWdjcGJ6cmtuYnJPLVMtd0dWck1XcnRqUEl1YzhST2ZtSTdNZkhFMFpVS3VGMy1iRkkzbDN3eWU2cW1SMTFNWG85bGtNbmZwR2tRbnk4cw?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46015.66876157407</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Police identify students who threatened Flemish Education minister - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 15:01:35 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNQnA4eVgwVUZZVjI0QkFVZVBvbWhkQ3JOOVk5c1VGTmxVRkpBTGNwN0dCR1JtUkJWOTVMZVd1aVUyb2ZUbEFENEl5d1p4cjFuNXQ3aC1yLWpqX1FlcFJrMjN1N3E4bzczanpZR3E3aWxWdVNrWWVyRUtZNFpWMGRmc2xwMjFBX0VmMC1LTmQza3pUakc3U1FfSEplOVdZMEx3T1N5ZExkeGNzUktCTktwS1pn?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46015.62609953704</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Brussels Wants War, Hungary Wants Peace - ԱՐՑԱԽ ԼՐԱՏՎԱԿԱՆ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 15:34:03 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTFBjQVZYWENoOTlEY2E3UVhPSlJIWEYyYlZJaEkteGtEZFloSDRYTkh0cVlodHZmb0JZZ2ROYkFKNTgtZ2xhM2xPNk9Xcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46015.64864583333</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Police shoot knife-wielding man in Kraainem - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 20:13:47 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQLXpvWU1OZXh6UU1aUVlYZ3FIVklJV3hkcVhMOVBKdFdKX2RIRldDWlZ0R0JqZkdyQURDVFJGdk9rcDVRSjBKa0I3aHRJX3pIZVJ3WjRiTUZEUjczSU9MOUN5WWNiZ3F6Mm5Va0dob2c3X2UxT2lEbTFjelpGZU4weV9qQ2NTT3pCR1paT0JtN1FxR2d1?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46015.84290509259</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>14-year-old girl missing near Ghent - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 20:13:48 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQdnl4Y1Z3ZGhrbzlhd3p4QVRaV3dzSDA0VjdqekJacnFPSy13MVFwcEQya2hzbktMazNkcGx5TEFtMzBsQ1ZMWjBFMGtpV2hUYnQwLVBGUk9IcFFnbGZKWERrVnFTMkNibWRNM0FnbzJlZ0lrdnFIOFNkMkh0ZGExUFR3YVRrZnVFT1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46015.84291666667</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>How the Tobacco Industry’s Playbook of Doubt Fueled Climate Denial - 동아사이언스</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFBuamFVeXY4Y1VaV0JmZWFySHFQYzdQZnE2RDZVRmNkbFk5eTdGSnVLQm1CUTdxejlOSzJsM2VETlM2akM3MG1kVkNoQmNrdm9HZnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46015.95833333334</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EU warns of possible action after the US bars 5 Europeans accused of censorship - WPXI</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 17:42:19 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPT3MyTWFzN0xvdTJ6bXQ4TDh0SUdIeXhrVU5HT0ZxQVNXUnRwRnRxNk55ZHY3UFlXUUh1X2FVS2hGblhjazE4cDhzZDFCalN2Uml3aTA4S2JWeEY5MjMyRVRwRDVfX3V6QkRUb2VuekZuYnJ4ZGxHcjJFd2F1TnFjd1J6Ymdhc0HSAZsBQVVfeXFMTUp6Z2ZwQWpNVnJER3lFSlVqWVQyLXZJSkJMWDdiUEFIMFM1V2drTUxPZW9LXzBrMFZqOEVIMkJHVHBNSVBlYlYyU1VGTnRJWV9iWjFFcmMxMHBZQTBMaEhiRzNwbmsyTmJoSGMtcmQ1SXllWEhZeEhVMW1lRmM3TkkxQzNRTHRIME5OeEZfTlJ3a3pVbVNNbG1mREk?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46015.73771990741</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Inside the Bullring's giant beauty hall featuring Dior, Gucci and Armani - Birmingham Live</t>
+          <t>How Jorge Lorenzo reacted when Valentino Rossi set the same time for 15 straight laps - motogpnews.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:46:00 GMT</t>
+          <t>Fri, 26 Dec 2025 09:30:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOTi05TWJfVEJRLVROTUN0anJrSlM1bkU4d0RfS2tZbVRjOFZHXzJEX3dnQ3N1OVpyOFZoZ1UxQjZmdldkZ2U3T0dVNnY4RTNLOGVZMGJVenRielRmR1UtWFZVaXZXeUhCUVdwOUVCZWlCYjFlT2RoYS1VckQxUmRwSk9Ed25kQjM0NFh2a0llOXQzN0VoTlVsZzhLcnJjQXVjQzJoaDN2dmNEM1XSAbABQVVfeXFMTnkwSEstdmU3c2ZGMWZEaHd6WmpzUS05YTZ3dkt5c0hnLWtQaExfVnFXY1dVRVZlQjF4b1JveklWenNsU1JhUDljejk2WjFlelJHWVV5WXFHOEdkYS0xNEYydi1FXy03UEVibXN5YXppb3NjbV8tcWxJczRWaHM2Vl9UNWE2OEpLc21fRk5FVmEwUjZEVEhoOTlqVTNyUWI0d0lqMXVYbTEwUlRVV0ZGdS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPazlXaDM2TXNRMnpBNlJ2M2RWcWhTR1RERGxwMzV6V21uNENKd2pCRVd4N25YZmVZbVNIRGNnQ0x4dUdlckdZUVZWemtfdkFZVGM0ME00RW9SUFBOUHNRSEdRbkRPWjFTd2FCNUpoemlaR2ItMERwMHJ2NG84S1B3bE4wNGhGNmcyUDJENkpvV0FLN3hXRzBoNDdkR3ZJNHZmckFpNXlwX2lKeHhNdGJIYWdZQnBIU3lUdVd2dUZWeEtCUQ?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46017.24027777778</v>
+        <v>46017.39583333334</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kate Middleton Wears $4,000 Cartier Earrings on Christmas Morning in an Under-the-Radar Nod to Princess Diana - instyle.com</t>
+          <t>Dior Debuts a New Era of Dior Addict With A New Campaign of A-List Ambassadors - Hypebae</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 17:57:56 GMT</t>
+          <t>Fri, 26 Dec 2025 12:00:27 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNb0hzVWY0cERJOUl2WFdBb3pwSDRFRXU2U0hfYW45VkNWTHVvUXJuQXFVWDJqRTFZLTN0Q09Rd094M090cnppNHB4LW9RUUtmSUpOZXpkM1lSWElJSk80UmhHTEhjYWNiNEdDSmozaWZvVVk1WjdTWFNXbFgzNElJRkppaE10UllqcXh5eXF3aWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaHA3YVRjTFA1eXJHZkt4STAxNnlLSngwMS1Jb19yWTR4Q0lWbjJ6NDB6aXMtUHFOdWYxcmx2RTdHVXVxbmxDYk1mZFFXeldmQmUwaW80RzRQSFpxRm1qcDdvZ3NxcGs1eHNZQXB6dFVPUjBuUG54ZDRJUDUtcDhtdEdmT1dfMm11ZDNxUlVFNDlPU3VTNkxWNV9xaUlISDlUVEhEWUkzSzM4eDBVR2ZyOUxOMkVGMkZUZGFPbWlOOU9sY2xUX044Tm9LV2psZUNlQnlvZWpjNHBXSHpkZ2gyMnJyVzh4R3haNnZKdW41Y1haT0U?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46016.74856481481</v>
+        <v>46017.5003125</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Percy Jackson: Dior Goodjohn on Clarisse's Quest, Annabeth Alliance - Bleeding Cool News</t>
+          <t>Inside Tommy And Dee Hilfiger’s Lovingly Restored Country House - The Gloss Magazine</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 21:37:03 GMT</t>
+          <t>Fri, 26 Dec 2025 11:04:38 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQamotTWI2enJKWWNZQUtidmtBUUl0NWRoTGdyNHNFOW4yZk5YOHV3SVdwYWN5cFBOTVRfYThxZG5mX25YdDFyS3Nzd0RrWC1HbU9uRHVxRUo1WTEzV21GdjByTmFxa0d4SUFjRFJNd21QVW1MYzJ1R3ZHWTZVaHFXUk5VUGk3dlZ0T2doaXdzN054V2RHLTZIdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNX0tCcnJiNmFDWk9LWjBFSzZ0R2Ztc0Q0blItdkxqcWRLbEdDdzdXc0FfdXZxdTF5Q091LVFxaWkyRmhZM3Q0REE3cXh3TmozVDgxY0tiQXA1VjJHOHlxaGhvamJ1Z19MVnhkaEZUSHNsODNFNFNMR1J6ejY2YXE1bFFxRTAyQUVlTmZ3?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46016.90072916666</v>
+        <v>46017.46155092592</v>
       </c>
     </row>
     <row r="5">
@@ -581,222 +581,222 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Maison Louis Vuitton Sanlitun: A fusion of tradition and modernity in architectural elegance - China Daily</t>
+          <t>Taylor Swift Elevates $300 Jacket With $4K Louis Vuitton Bag - theFashionSpot</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 00:12:00 GMT</t>
+          <t>Fri, 26 Dec 2025 12:30:18 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1qZUpCMXduNGZsT0R1SzV6UUgyblZOQTA1YVlUUkV6QVQxQkVOdy1qZnQ0OUxuWmdwZjQwRGUxS004RkowY3F6SHJxSWJEc1dsT2hjbjJVdE9PSDVOUHdKcnFhYmh6X0lMdVNEWHBKSTNxd0dsSnR0UGFSdlZSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNbWxYT2UyRUt4TVpta1FxSlVLcm4xS1dQX3h4SlpPMUtSaGxlQl9acnMtWEIxZU03SlNyT19aMXFobTMtdzdoSFdteFNYMlluTnE5NWY2ZHgtczZDeDd0aUR2Um41SjVoSmtKNW12TVJrTkZVNmtUV09KZHM2UlB5Y2dUVWpHanh5YXd3dGNiT0xoeDVGUUp4cGIxSTjSAaIBQVVfeXFMTjlkVHY4UzNTVmlIRFRSQmxTUTliX3FxbXpORWV1ek1hdGhzcnNramdtNVFERk5uTlZXOXhHc2gtZ05aTkZFUUdSVGRJM3VfZ19iakltRE5Lakl0UmYzY0NseDJPek5GSW5id2JFbEQ3czRBcHBMc3JHSWYwSVZNRkdrbWhPVUU1VWxycWVueWJQM0JTZzlxSm9rblowMWZTcWtB?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46017.00833333333</v>
+        <v>46017.52104166667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Giorgio Armani: Milano, per amore - www.upscalelivingmag.com</t>
+          <t>New Strong Sell Stocks for Dec. 26 - sharewise.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 02:39:57 GMT</t>
+          <t>Fri, 26 Dec 2025 10:15:10 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOVTVjdENOLXl5cHhseGdLMTdPcDZGUGlMY3ZvYXB1eWgyZnZJWlpGU0FjLW1oWjhXTjB1c25CMGd6em1OVm9jdkxQemdFZ0dFRjFjWU5CQ3ltNXZTbi1fa2xTTTAtSTZDQ3RKOEtIMHFOU255enFDbGNPZHVmSWVDQ1daZHVRdHl2X0xhSWJzR3g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNaHVBUmt3a1IxUkRURU0yWHppbE9zVlRId1l1NzVOdWlQMWh3T0JOYTVIZlNRWFd5RllvNS1hang4UmlEU3FuekZiRHpMVENIam1FNEllM3phcG5zRE5HMWplWExndURENGR3MDRSLXUwTFU2ZU80ZGt3a3Z1N1BTaXR5cTM3bU9Ra1p6ekVvSDdkelYwVEFsaWhLeTY?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46017.11107638889</v>
+        <v>46017.42719907407</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cartier's Marlin Yuson on crafting the latest leather bags - Condé Nast Traveller Middle East</t>
+          <t>Sittingbourne pensioner overjoyed after wall hit by Amazon delivery driver fixed by Good Samaritan from Upchurch - Kent Online</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 21:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 14:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQaVJoMmc1ZVNMR3k3RFhEUEd2LVFicy1zaE00QXRqS2VvZm45UmtpSkgwOFNVYnloeVRTOXYwa1RNMW5KQUt2SDI2RTlDdG9JVGVLSHVOVlVFTXpnVUdETTZfbWtYUG1KOG1mWlFZaWdIN0NvUDhOcTNfNHo0ZmZJTlB5bkUwNzRDTHF1X0Q1ZTE4cVl4aXRnaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTG9KMEtEVThTWlpBa01ocndfbjRzc190ZmxXQTYyM0FZQ0FPVWFPU003cktheVhvaTdhYU5xLWRTWHVNN3pRUGNia1FEaWJReTZQUDF4SUQ5SE5aV196YW04VlEtWE14UGlPSzJERlIyRVBrSmtMWElFNkY0MExNdHpOdTZyUlhUbWROM2FvcHJ3WUZ0cktxOTJmZ3ZrY0tsbUczX1NjLUJGeWRTbjNveXBNQTJMeUE?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46016.875</v>
+        <v>46017.58333333334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jonathan Anderson Gets Downright Whimsical for Dior Menswear Fall 2026 - Esquire Singapore</t>
+          <t>Royal Mail on Boxing Day: Find out if there is post today - The Sun</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 04:03:56 GMT</t>
+          <t>Fri, 26 Dec 2025 09:42:41 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE11MEJDQjRFUTJ1aFhQckVCb21ScEV6eUhsem53REtCc05JNkluYjVoaWU1M3BtMEduNGxOUmZtamZVY1VhZHhaQ3FjTWs1SUNVQUNHLXlvNTRVNmhqOFUwRmtZdXIxZU1JeG9lV2hOV0xoQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOSVUyWW5JLWY1MkNaampHbkJFYVZyWmFCZjljY1Q5MVJVZW1ldllQUGpxWURFb1U0bWZCRTVPUFJRZXVBczYwcXE0b3RFMi1ZbjY4cldRSHJRZ3hxT1ExREQwcHhSNWtHbjRNMGtSaDNLNTJ3c1Z3U19YUXpVZ0liRA?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46017.16939814815</v>
+        <v>46017.40464120371</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Burberry Group (LON:BRBY) Stock Price Passes Above Two Hundred Day Moving Average - What's Next? - MarketBeat</t>
+          <t>Anker’s 140W Charger Is at Its Cheapest Price Ever With Same-Day Delivery for Amazon Prime Members - Gizmodo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:40:52 GMT</t>
+          <t>Fri, 26 Dec 2025 13:10:54 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOVnV6Wm9TVU5vSTJ0Smp5MXZXU3MzX0dTR2ZjcThMOEhoRHJFYTIyTUQ5WWZJSXlWSWJDZEZwSkhZZmM1czNCWVdCRUZablVnMzhQNEZ5bktlSmNDc0liOWg1b3kyYUc0WHlJbGVNQVNGUnIwV0JCOVUwWmkyNWg5aWNQQlJLcFFhSjBoTDFpWVgxRHFZZlRZa2t6ZjlKUXhMRnd6MkxQVC1MZ0dJQ3pRSzlsMkNrU01lWXpmTlRHT05UNTJsbWtDQnhpSGktenM3VUlDSTB4Vl9GNHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOVkp3RnEtdEYzcC05a2lYYjdBQ2ozTWhxem5NQVhiUF9ONThyclRyUGZ2OTE1VEUtbEluV1VLUmpYd2ZLcTk0ZmtBOHdfTjJzTndmaW5jVlBtR2hlWW5XaXZwbklNZXVnWHNYd0JXOXhxOWdXcE5RVWs5dUdkREZvWUNuU2pIendpT0NZY0M4VF9vSUhWY1E4SHg2WUNmclpENG5yZElQaG1zc004bEExams1WG8yWUxPOWtzVkZKbmlQUkNhNGNv?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46017.23671296296</v>
+        <v>46017.54923611111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paris Haute Couture Week Spring/Summer 2026 Official Schedule and Participating Brands - ouispeakfashion.com</t>
+          <t>Why are Swiggy, Zomato and Amazon gig workers going on strike on December 31? - India Today</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 04:59:00 GMT</t>
+          <t>Fri, 26 Dec 2025 08:44:48 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE42T1ZJTFVFVjF3Ymd5NDZpRVlaeGFtVm4yMGhFLTFRbkVaR1o2X0R2M1JMSjN1eTBTaWgyNEFIN1ZMWDJ4d3hTd0JRUFZrVGtORUVNemJPWGhZcVpjemhTdlgtVGVOOGdTbWt1SVE3NFI4RmRBUjYzVXlwRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOaUFlQzNwWUlISGd1NE1vNHRSeVBXTWxlSnlxaTUycmNHZkh4QVc2aVk0MEdFX0NvbDZzbWJwU1Zla3VoV0JiYkRoTHVnVWVndm0xZ05zN2k2VTUtRXRSOERPLTdfajBCd1dMYzgtOHc0N2UybEI0eVp1NHlVSWhtclJ3M3RlMlZyajc0X0tFdnVxWkdiN0I5UndDZkE0ZUlmWTFBcEV4Nl9PQW9pU2Ytb01MYlpMYkxPcmZsZmJmTUNwMV8waTY4QnAyclQ4Ujg50gHWAUFVX3lxTE1KVnhFR3otZmFvVWxaVjlHSW9WUURxWnBTWEh1elV0SV9FcXBOWXo4SVV2QkVOTDZuLTNNUzhiYnhDbkVnSHJWYTZhTnUzMFV2VVhfQUczNjFFZjhCWWlIa215cmZwSkhSR0x2aTN3VHBWMURwZDNYdXpjcEwyb05VeUVHVENCSVlPdkdJdXRoMEVneGxBNm9yWDF2dVpOUFUxRlJCS0VSVDloczA2QmY0dVNNYVJRRlN3QWlLZlhvZnl3MlRNQjhiU0I4M3c4MFVqR0tRRVE?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46017.20763888889</v>
+        <v>46017.36444444444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indian Retail Sector Eyes Margin-Led Growth In 2026, Driven By Tier II &amp; III Cities Demand - Free Press Journal</t>
+          <t>Walmart expands online footprint in New York to challenge Amazon - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 03:21:28 GMT</t>
+          <t>Fri, 26 Dec 2025 08:36:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNbGZVT1BGMUh1blZvZFktdlBfLURieDNaRmhFV0Vocm55WTk4UzYzdlktTkxZTEFLcEpYMDd4aGNMb2k4SFlwblltVm0zX2RWejN4V3lfeWQ2THJBU2N2ajBzRUxMb0NQSG93VUFoVmhBU25DN05YdnhCLXR3THBrdVlXSDZpYUVMZWZGOWh5VVhYVXN5WHUzN0JBMHljMEQwRHZLeDE2WFNlbmNnVUZoWFhVaEl1UU1OWXVLTzNqaHlUdGdDdFdKbjUwazHSAcwBQVVfeXFMTWxmVU9QRjFIdW5Wb2RZLXZQXy1EYngzWkZoRVdFaHJueVk5OFM2M3ZZLU5MWUxBS3BKWDA3eGhjTG9pOEhZcG5ZbVZtM19kVnozeFd5X3lkNkxyQVNjdmowc0VMTG9DUEhvd1VBaFZoQVNuQzdOWHZ4Qi10d0xwa3VZV0g2aWFFTGVmRjloeVVYWFVzeVh1MzdCQTB5YzBEMER2S3gxNlhTZW5jZ1VGaFhYVWhJdVFNTll1S08zamh5VHRnQ3RXSm41MGsx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPbWtSVEs2LUN1ZEhVdGZXRTRRR2xDdTdMLXZabXc2azVGQ1l6QUNmSUg4aEhsNVF1Z0hmbXBlWVFYbzFnbm16dlJSN1huTjdNWTZYc2ViMkVqeDVtNjlEeW80MkttckJWdmhVN254czFNOFlpWTlRQVlMX1RZWHFabGpocjF4TzFpZUEtSjVHRXE1X0o5Mks3OE1abG3SAZwBQVVfeXFMT21rUlRLNi1DdWRIVXRmV0U0UUdsQ3U3TC12Wm13Nms1RkNZekFDZklIOGhIbDVRdWdIZm1wZVlRWG8xZ25tenZSUjdYbk43TVk2WHNlYjJFang1bTY5RHlvNDJLbXJCVnZoVTdueHMxTThZaVk5UUFZTF9UWVhxWmxqaHIxeE8xaWVBLUo1R0VxNV9KOTJLNzhNWmxt?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46017.13990740741</v>
+        <v>46017.35833333333</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Royal Mail December 24: Christmas Delivery Delays Hit 92 Postcodes - Meyka</t>
+          <t>Two suspects arrested after Amazon van was stolen - Newark Advertiser</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 17:09:13 GMT</t>
+          <t>Fri, 26 Dec 2025 10:48:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOc3hpVDE0VmVPNTh2XzdHbG1yUWg0dWl5eFVMdndnNW5UcnRHb01NMW9vbUdfanhfTVM3WlZJcFd0RFp4cG1uZ2doaXNHT29ib0dBUGRkV29uZ3RmN0E5d3g3ejBBZGFIWTBMWWwtb0VvcnZndWFrcDBrM1JuNVc1ZDR2MzFzdWF5Q284QnhvTUdtQno1Z0RLRDhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPSGt6dlptNEJGME96ZjBWQzFLcFJNRXRRV0FlRzlUeGViRHpRTXNLSUdQVHE4b1NWWUdoRmJDZHg1bTY0UHVMbURNV0hGYTBGOTBSeklfS0ZhWXV6SFE1X0JBT2xMZUNzdEJFRzYyaXhTWWd2cC03ZTlGOXlSUnZFNTlhWWRBRWF4UTB2TmhNOUJLZFNIU29jZ2NkU3N0eVU?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46016.7147337963</v>
+        <v>46017.45</v>
       </c>
     </row>
     <row r="13">
@@ -845,24 +845,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Why Swiggy, Zomato, Amazon delivery partners are on strike on Christmas, New Year's Eve - MSN</t>
+          <t>Change in Amazon return policy in effect for holiday season: What to know - MSN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 20:27:30 GMT</t>
+          <t>Fri, 26 Dec 2025 12:22:28 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wJBVV95cUxPYVFSVTVxOUN6QmhVYVVaSWlhOF94NFdWZ2ltQlp6a0hGd1BfM09qVTQwSEJLYmh0dUFndXRtYndyR3JtS1lmREVJSGNBYXJGVDBBYzdoVXJya0dZM003WFhEV3psOGVldDhaSFNUQ2gwcFRjYjdxLWh2aUtJSzAyMEZOT1VyVks0Vm5kVDlUUmRQOHZkZzJPdDRYcFA3RmdjY3lTejhERDlPam15RERSUVoyUjZxQ3ZuZlZrMTZTUDBpNEh4N2ZKOWtwbXVDT0Y4WnJ0X1Rma3NNZ0dPeUVtaE9icTE5TVFTZlhiV0k1Q2d0SWxvaExmb2JCalYzNUtCbXBjRjRvRGpySE1QM1RMM0hZUEpSd3FUdGc4WElTV0lINGhfZlUxZEhDUjhJV3BVWnlVVERuV19GWFdKTXFPYVVtUWNnMElLN0FFNktJVGFWaHJQMFVCTTNLSUI1SWJPMWdv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AJBVV95cUxPcFJQNlBsUmJjc2U5TnFxVURONmQyd3hHdGVobFROY214a2dCNHFoMHYyZUVBMEU2MjZHbDFjNHJacVRHNnoxQkxram5jcG9UR3NtNnhDZ2lwMlluMTZFWm1Ya1JlYzlOeldjWWNEa29DNVBLTVU3MmEyRzlkajYwVllYUGN6WWlobHhvSGh6MHV1OFBvdHlwTFp2eVA3bWsyMFY2cXpYYjYzN1Vzc1VyNW04enJKYlFKaWVtWnUzbWNIMm91MDlwUVliNTloZ3pXek02bkc1Ym55b19oc2dMSWpteGNWTi1sZXJqcE5IZ1hqNm1IbWdPVExQTThKaDNNR00xNDJ0cC1jLVhCSFNDZE5jcmtIRC1YOUdkNmtYb3lFeFBCTU9HNzVOc3B0dWppaWVPN1dUTEpxOWNRLWFJeHRUdHJlQmtyUERqUFZ0eFlHTlZj?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46016.85243055555</v>
+        <v>46017.51560185185</v>
       </c>
     </row>
     <row r="14">
@@ -878,24 +878,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Discounts surpass Black Friday: Amazon starts Christmas campaign with guaranteed delivery until December 25th - Mix Vale</t>
+          <t>What goes on during an Amazon warehouse tour? Retail goliath lets tourists inside its vast UK hubs - MSN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 18:12:46 GMT</t>
+          <t>Fri, 26 Dec 2025 09:49:01 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOdWpzQkptU0xjUjBPVURmNlVGWlNfQ1ktSlMtM1dzdGFaWFFMRjFWRDdSNl9sUVRVdTNQTDNxZUg0OHQ3cE9zZm42VkVoeFFXMUN2TUtCSUFtYUZaNHFJU0MyUmhXTzVBRHVsOE1jejVLUVhJR0YyV0k3SHkzb1dRdW1hdnp2NVM1MDNES1FBelBDUS1WTTExQTIwUmE4VjBhVjRLNnpPZ3duZ0hRWXZLQjBMNUt5M2x6TEhnM05ORXVBTk5SSlBwS2lIWlVaSWJUUzNhblpyVUlzSGltbFNFd1Nfd1HSAeQBQVVfeXFMTnVqc0JKbVNMY1IwT1VEZjZVRlpTX0NZLUpTLTNXc3RhWlhRTEYxVkQ3UjZfbFFUVXUzUEwzcWVINDh0N3BPc2ZuNlZFaHhRVzFDdk1LQklBbWFGWjRxSVNDMlJoV081QUR1bDhNY3o1S1FYSUdGMldJN0h5M29XUXVtYXZ6djVTNTAzREtRQXpQQ1EtVk0xMUEyMFJhOFYwYVY0SzZ6T2d3bmdIUVl2S0IwTDVLeTNsekxIZzNOTkV1QU5OUkpQcEtpSFpVWkliVFMzYW5aclVJc0hpbWxTRXdTX3dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQQ0t5aFc0aU0yOGoxNmlRenVielFNSUFVZFJTTlJBdGZxNE55UUxQRG9zZ0VPelBuX013NzhFNWtZQzVlZk5ZaXpiSm1PY0pWU2VkNWFaUUhHRGIteVBWVE5IWkQ4TmFMOGs3d2ZkalNDa0pnZWNZOEpmaHRCYnJHbFdPZy1lQnZEOUFvVWhYcjN0eGxYSHZtWFNpVGM3NXp1Z2lUbGFsM2V3cUtrb296RWZiZnRrOEJ5R3RLZTBTaFh4RTR2SXc1UmpJaHZvZ2w5M2hZT1pkWjNPaDl4NktJMDhDb044eVU?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46016.75886574074</v>
+        <v>46017.40903935185</v>
       </c>
     </row>
     <row r="15">
@@ -911,24 +911,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amazon 2025 Deep Dive: The $6B USPS Standoff and the AWS AI Pivot - FinancialContent</t>
+          <t>Where will UPS stock be in 1 year? - MSN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 14:41:00 GMT</t>
+          <t>Fri, 26 Dec 2025 08:26:29 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNUXBpdWl1V011UEJTMlBKZzZFU2FwaUs1WXl2NWZLSkktd2dJRUY1ajNsczZVRUJ4NVdpMjVqRUNpRjhqV3RSTi1TMFFHSlAxaExTbTBQdVhZb0Q3RW13ZnNnTjZDNVdzbVVlMkk1R0l4eU5wSGgwTmRsS0pWYUY3c2hYX1pmbEZfYWdlVzlmS2JtNXF6RHhreDJzT1ozQ2UxYmlEMEtDczBHM1NWSDB5SkVGc2ZHZ3VOb1dYaHlvNXFvYVZyRUo1LVpsZ1pzQjg0S0tTOXRKcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxObC15dlZtSzZmdXlpMDdMSnQyOVFQcjJuSzdUQVZmdVlUOUF3ZmQwb3pDWDYyc20zRUtzS3hyaTJ1eXBHUXJpSWk1U1RfTEtNNnZkNWIzLUw3NnR4ZEhSRDQ3d09qMGVKSDNkR0ZzZGEycGpmdERvZ0IzWGMzZVdPNXJEWm9UOER2ZW5GUWJucWpyQ3FWVHpaLTVKc0FZTXBiZXU4NTExbWMtYXNpcWRQMWxDOA?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46016.61180555556</v>
+        <v>46017.35172453704</v>
       </c>
     </row>
     <row r="16">
@@ -944,24 +944,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Interested in FedEx? Mark your calendars for June 1, 2026. - MSN</t>
+          <t>Amazon Christmas party video full of Indian employees sparks racist comments - India Today</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:19:31 GMT</t>
+          <t>Fri, 26 Dec 2025 09:00:45 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPWUYtbDFzT0Z2MUYzWDBuOUtTN0FFWFVkU2QzcWVSYmtOczBFbkEwQl9ybXB4RllPX0RGYjdFZ09oVnEwRDBJX3FmSGNQT3NiaGhjVGlyTXhfMnFSbmFvSThFWFAtSkRxbmQ1RjA1a1NBTzNkcjRsYjk0MjFYUl9hcm9mTlRuQTJtTGE3Z0o5N3NJanFuRUFRTmViUlFRNk5kTXhsaWt5MXlCRDBtR1pMNGJVNlhGRUxWcGNOMUJOalFtLWpvVk9ZcUFoTVpSSkV6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxON1VTeXdaamtEVXJaUW1xQ3FYVV8xbE9LbkdTWC1GR1BXc0RCN2hUZEJCVGRlMXRUQkFTYXgxaVh0bmg0Mk1rb3psT3Nhc1djVWhnQ2pva3JwWEpNMndyQ0lsX3E1bmx6aURqVHRYazRjWEdzT0dJRzE4dUZsWURRcGdud21tSGpWUE91Z1VSUkVlN2JSUkNKd2RZY2FVeTVzSjVZY3ZRNmtqRWNJcFlzZ2FlSy1WckdaQ2IxSTZ4Yk0wbWI1bVAzNk5ESmVObUF5NTJENDV0bzhjV0XSAeABQVVfeXFMTWE1MlhUMWpqVVVDMW9uX3drOVppYXlkNTNNVEVPZUt4eWRIZEp5UEtyRE5vRjlFbVVSbGh3RTlvTnVSSDNBYnFnVkFZbkpEeUs0WGZ6QXlaMmVTQUxKQVYxU2xyLXlKellFS0djYnlXeTJkTVJQZDVyeElfcEJSdnFFcVpCMkhtZVJTZ1FiV1JxNXhwZDFlWkhhUnIxYXpxZDdxUm1qYlRwd2VpOGRRZmh2a21PQ2lTYlBhdGpiSHhwaWEzV2ZxTW5FZTFDTi1MRUVSYkJXT1pGWGVSZHZORW8?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46017.22188657407</v>
+        <v>46017.37552083333</v>
       </c>
     </row>
     <row r="17">
@@ -977,24 +977,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Swiggy, Eternal under pressure amid Amazon's quick commerce expansion says Macquarie — check downside - MSN</t>
+          <t>Trump just declared December 26th a national holiday. What’s open and closed? - Fortune</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:15:28 GMT</t>
+          <t>Fri, 26 Dec 2025 11:00:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxOVG4xRGl4VFh2WjFkU3daTTZEMnBOd1JYTjVLS21OUWRVajNYSE9LOWVlT0h3QzZjRjRBOGJVdTktZzBSd1F1SFdoVlRVWVNvUEtSOWIyM3l4TU9fZVoza0p6ZlByaVgxejBfVzRqT1d6cHN3WC10Wmdvd0RIby0xaDZuank3R0pid0VUSEh5VDF6eFJDQ2VkTXZGNFlpYWVqZFlGeEJHYWJOUUFCMmZ4c1dNbTFlbDFrcUZ0bS1wekNTZGcwVE9qbUhWbGZuZlVrN1pfQVZEeG1STThjVF8xNUtyZjQ0Y0pOaTIxZVdOTENHUjF6VkNN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPRTA3SUEtOGtTS0dhSHFOVWJ2aUNJNjU1RlJOQzNfeENZRE9JM1pLdnNFWDJaWjZKYm0td3NwWWdrYWJrdXBnanEycHNUQk1QQUE1c2MzR3lqbHZUbDRVYng4VjNKUGRNSmc3NzV3czQ2QVUyQWVvUjRFWk5YVkRNd2dHbjFURXdsX3JtSEdSeDlHZDhWNWd0Z2U5QnllOTZZNkFBQ0FRZWY5clJ4NFFHejZyYXk4TmxJcEJTR0Uwbw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46017.21907407408</v>
+        <v>46017.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -1010,783 +1010,783 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lucky Redditor scores $6,000 in free Samsung 9100 PRO SSDs after Amazon shipping blunder - Notebookcheck</t>
+          <t>FedEx: E-commerce Festivals Drive Strong Holiday Sales Outlook - Wazzup.PH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 18:48:00 GMT</t>
+          <t>Fri, 26 Dec 2025 12:17:15 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNenE2anhHbVF2a2VTUEJENWpZeGhkODR0OUFBRGJkUHNweXR1eDdxYWxob3VaNGE2elpWOG5XUmhJMGR1RlJWbmNXWXRCUDZnSTVVcE5ETFNWUXlkSDZOUWpnSHRWblpZZmpxb19NeHZ1ZFJrdlk5MVB1Q1c2bzZUS2ZEVnd6Vk1VUTJONGNBS29ORjUxems1amNjUGNpcFJZSHRtbl9XOXdhT21FeUQ0Z0h0ZlZNYkI5aGxJaEF3M09yOWRnLTZIcXpHQUo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOVmU2TmRfNkRRNFNnUC1FbmpBaFJIU2FXdFNMNHh0TGtaRnRxZW16ZWQ5MVVJYWQteHRtS000Mzl4eTZCN1NXOURHZ3hNMlZ5M0daZUN2TW5nM2Myc1h3THJNOGU4WlJ3SWZhUXpTY1RvcU00dUZ0dmFlZDZqZDg5T0ZjYVhqYXVTWk9WYg?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46016.78333333333</v>
+        <v>46017.51197916667</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Emerges as ASEAN's Premier Logistics Hub Amid Global Supply Chain Realignment - Nation Thailand</t>
+          <t>Five killed in mosque bombing in Syria's Homs - thenationalnews.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 23:31:00 GMT</t>
+          <t>Fri, 26 Dec 2025 11:16:55 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1FeHMtZElyaml4NGcwSE9jOGdBM0J0NmxsSmREMXFFdHppSW9IMUluUzdGYU1nQk04S3ByYVdmSG1lU2pHUlJObEVweUNILUQ4eEdnQUZ4a1RoV0NUYXlrRmpaUFA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPbFRZemhHT0ZURzhaZUEyZktRTDEzMDZqM3R6QnNicVVCUEhXODZNc0kybUluLWZYTEY5N0lDQVNMQWszYTE5X1Nfb0JhRkVxeFBmejI3WTZtV1lmeldXOW5XZFByakU3UFlpbXp1UVZnT0ZtSGZQaWdvVVdYbG5WR3pSSkE2Q3RBV0Q4X3FVcjIyaGlmTnFWUg?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46016.97986111111</v>
+        <v>46017.47008101852</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Where Will UPS Stock Be in 1 Year? - AOL.com</t>
+          <t>Momentum Traders Eye Electronics Mart India Limited for Quick Bounce - Price Gap Trading Strategies &amp; Master Stock Selection - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 14:31:04 GMT</t>
+          <t>Fri, 26 Dec 2025 11:12:04 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1UUG5rVmlBcFV2VzBNRkFkdWJfX2dPNWgyOGhickVZbWlJWVpqQWxBNUdKeDJpVGxMalJIcEcwM3JvWlFwS0Q5SVR5ZE1mSUJFVFREY3Vyb3FobzdBcEROWnZHVUhzZkVxcnFUNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQSnZuREYtdGc1X2NBa2JnN0lnb1RrQkV6SUozY2JIa1JYSml2SFM3SlZzYVJlU2hDb0pyblUwUm9TOG5FQUNHRVdLNTVxV2dKcjFTQ0g4SFR6aVU4NEprak5YN1ZmcGJtT0VoM2VHRVZrWXh2bENoMHE1N0gyNVl6ZEY2WEJtc2RqalNOMFdrbm9hbGdiV3pvdmZwQ3B2R2hReUxybWlMM1VITWZTejhIVQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46016.60490740741</v>
+        <v>46017.46671296296</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Is the post office open on Friday, Dec. 26? Does the mail run? - NJ.com</t>
+          <t>Will Tarmat Limited Reverse From Oversold Conditions - Chart Pattern Recognition &amp; Build Winning Strategies With Zero Cost - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 06:18:30 GMT</t>
+          <t>Fri, 26 Dec 2025 09:36:46 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOa2pEcDc1cVRhSTMzZ1BSOGZhVkdncEJfZm5MRUFra2xqSFRINTMxRU84am9JMkxJWWw3Q0w5TDc5YzhfaU50VzlkMUYybGVBM3ZoQkRmTF9rQ0pjc0k4MVl4UzJDSkJjY3RLcG51RklpMkVWTzF6ZUt3TV8tbFFnT1k4TG81Z9IBmgFBVV95cUxPVHdaanFuNzczb2NMUW9iV0M2bjBzUEFTbEZSQUctYk5NdFRHQ0w3UXZZN1ExRG1HYXZENWpJcWhxcFRHREpUSnBfckw0MzFmeUsxN2tjLXNvY3A2UTdVdU1SUnM5VU9rMDg5UC1PR1otN0J5aTdhcllFOHQ2dGJvWmstZXVubUk3S1hwSjFxN1JXaUxKbFNLSTlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNYml4N25wV3U0SnJITlVaREJZLVBhZC04SDVrd255cWtNcEZWMEtVYm90dHRnZlVqdTlyS1k3OWs0cmRKeU5zM095YWxIWjRYa3djamgxbGkzNWMwQTJIaWc5RzdqTWZqT0ZIOXhYbktzb0lIOUF6S3pWUzRzVzB0ZERJV2ZyS294bjBBY3l0X3A4VjNiTzVObTA2TQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46017.26284722222</v>
+        <v>46017.40053240741</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Delivery workers haul more NYC packages than Santa Claus - Gothamist</t>
+          <t>Crime is down, patrols are up - how local police teams have been transforming key areas of Grimsby - Grimsby Live</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 22:07:00 GMT</t>
+          <t>Fri, 26 Dec 2025 13:54:00 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNWjNPblZNVEJ6LVQta21YU1BWamE1NlhzdzhWY1BtVzkxZmJLTDFMNHFkQXlzY2ZGWlQ4ZDN4YjJ3dkZVaEs5aUJ0WHlIYmRlanVralJGaGRLRHJRZ2ZPYnMtLV9ldmpldWFnUmZEQkx0a1E3TjQwUDZ6M0k5b2xzNDMxaWM1LXRKOVpj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQQk1kX051aEg0clV4Q01KdjJiNHN2UWZ1dEdhNExKRmxHaUJmNmNnaEFVYkZBeVpGRFZzejVXYWY1Tm8ySHNYb2RpZlFwQjc4bEs4ZXNQWG9Ud2h5UC1XNDhNbkVjZjd3cWFxZU9hUTNVYXhSYk1nT29zbFZMNlo3VmNmVy1vZ0V3RUtFRHgtR0PSAZYBQVVfeXFMTkh5blFldWNzQy14QkhnUWVjTHZTb0szb0FnTWNYLTdzdjFxdzdfY2FPcHJFc0J2b0NqV2l0dWRuR1ByWEY3Skx4SzJYd0ppWTVVMGtMVUpQbmtJRExRNzRVZjRxN2huVURGSV8wamlTdGc5QkM3Tk8yaXdydFpJemNvTl9ud0IzQzdHYlBpakp6RThtR0p3?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46016.92152777778</v>
+        <v>46017.57916666667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FedEx H-1B hiring sparks outrage amid firing of American employees, Indian-origin CEO faces heat, 'They are now awful' - MSN</t>
+          <t>NSLC sees another sharp increase in thefts from stores - CBC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 19:51:53 GMT</t>
+          <t>Fri, 26 Dec 2025 10:00:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgNBVV95cUxOeHlPM3hoTW5jTzl2VURnSk9LZkNRTDlDYWFaZkZmdXo2Njhuc1ZrOXlwQzd0c2I0anMwMjhIN3R3dFAwQlBBMzVNcXVsdXRXU01NVllwdTJtNkswNFJSQWkzY0luS05zcFNIYkY4Y1I2aHo4eTRKMkFrbzVIckJlSjBHN2VnREkyc1VIeUVmRGtxLURBYjNNV2hkY3dqdlZpVkxQMmZURVUxVEV4ck92VXkzYTNuMFB4Rk9WeTBmek5IT0Zma0xGS1U0RnU4emhlaHl2b0oxd1k2dzVxczIyLXpqdk52ajR4OGtFdDBhdmtaSDg5Sktab0J4bVlqU01VeTlFOC13dUd3dnYzdFVHUVB2X2p1M1JGa3JQSjFuMDNVMGRMTUxsam5OWWZqTWZCdmdsNlFfRzJwQzdqbWloTjBNZU5sRHd4UEIyZzUyYU92OGZwdkM2Y0JqN1Y4SnNiMGJoU252aXlPQzZMSnk2cnd2OVd3WXlHcHNMR2xXLU5BUjFGZkpsemJWQmlTdXBkN0YxQm9UbXhlNDJxcFZRTmlyUGdLZWxWLUJFSS1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPUTVIUC0zMHFCemwwaUlveEcwRFU0clJPRVE3WW1MbS1QbGNVd3BhcGphX0Y2V1M3VFJsUUdIaHFPRUVKV0tiS2wxVUd6dHRLX3JWZXZhWVdVRy1nUktBSXRyRXY2N3U2UjZVX1JDbTBfZnJhMmpJUnE4Q05kczRWU3hhUFhWQWZOSFptZFNiemZIWnR0Z2ZUWXhwTQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46016.82769675926</v>
+        <v>46017.41666666666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Is Christmas Day a federal holiday? What stores are open? What to know - Cincinnati Enquirer</t>
+          <t>The best concerts in Madrid in February 2026: from Judeline to Nathy Peluso passing by Ángeles Toledano or Austra - Madrid Secreto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 14:47:00 GMT</t>
+          <t>Fri, 26 Dec 2025 09:03:54 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQQW1KODloTFVYakxhU3pURTRiU0hiTHdtZTFrNXhXODFGczRGOGl5bGhHeFdRRFpDMXVRWVViblVNd0RmN290TG9XeEJLRUxyRGJ2V1Z1Q2xUZHlaV1dLNjRSR1lGWnBlWEc0TXJSNUs0Q1RGNW41VkVnV1ROTjVOZkplRjdwOHM3VUI3MGl3endfekExcjBNUlJnUXlCY090Sl9OV01QMEVadUZBRGlRREE3Y2w2Z1M5Z3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE01X0Z5UXNfMlhlQldidnItejZRMDRHWG9JWHFvMGJfY193M0FZcEY0Tk1CTnRzY2swOTgtUGREZXJUTTdBY2VDM1U2c0p4YmVCZDdvMnBodkdJSnpyaHBscFExcHR0TkUwQjJ4Z0NMbWhnMlBHbElqTVgtTEhmQQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46016.61597222222</v>
+        <v>46017.37770833333</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches Belgium French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brussels unveils historic housing plan - financial-world.org</t>
+          <t>Bollinger Bands Expand on Infollion Research Services Limited — Volatility Ahead - Retail Investor Activity &amp; Explosive Capital Growth - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 01:00:50 GMT</t>
+          <t>Fri, 26 Dec 2025 13:10:17 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZi16RVR5RGVNaGMzZktjMkI3azFRUndhc2NwYVlRTHphbGY5QnJqX196UmVQbDhaX0ExSGNmR3dWZS0zTHJWVWNlRHVYOVJ2aDlaS0trMm9rRmUwdWRIeGNZaFlaSVlVaWVkQ1BUWFAybTlEOHBTMU5ScVh6Y0ttWkgyLVdIYmJENFhGX21EeWt4LTJrYjNqdzV2ejJuZ9IBnAFBVV95cUxQSDlUVWFFMlZFZk1SOU9DVTlURWhLdHpHRjhtcFNxYW1ZLUFIamtEUDFUbGtybTBYV04xQWJFWllYS0kzaXh1WEUwNnhHVzJfQlFUZG82cnBNWVJTZWl6bXBZRE53eEVKN0gxMlBNYVdNeUFCZXZFRzZyWEZ1SURyVUMxLWw1MUVDYmJkcTdZMHJWZFR2dlprMkNWS0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZFZJN3FpYWlraWxJd3JFd3VnT3dzZkt1ajlRb2I0TnFPZEhHMWxvVFd3eGlSUUNKdG4zTko1LWNWVjZRbUpoWFVmNVNtQkJWRUhZd09pdXNYUGdqSlgxeDNpb1ZaelkxTUFrbG1RdmZVYVNpMmdqb3FjOTFyOE1aY253ZGxmMHFuV01BQzdOeGNIaElzeXZzYWh4cDlSVlFZWnlyeGIwX01lZEk4NXRZdE9MVEZQWWl1Mkk1dzZmNzU?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46017.04224537037</v>
+        <v>46017.54880787037</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hinrunde Wrapped: Looking back on Bayern Munich’s first half - Bavarian Football Works</t>
+          <t>Cooper Flagg gets a Christmas Day lesson from Stephen Curry - Mundo Deportivo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 15:30:00 GMT</t>
+          <t>Fri, 26 Dec 2025 08:47:28 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOazJXb3ZtQ01lOHpqZTRWbFJlZHEwNGJ2ZHZBYXZKWU1DTjNsUWhrRFdiOEU5Mkd5ek1TVVM3NFVIQlFyQ0x5anMwMFZnaE9ROHVCQ0ZaRnFJTVNpT0pQTFQ2OXIwX2pzMGxnYk1WQUY2TDBOZEp5YjF5OUdZZXg1UVpWTFVwbEZYMV96TTVqclYxbEtudHJiOEtqQXZ1eUZweE9QR1VPZVRwUGgtc1RqdDA0TzFKaWpuc19UOHlidjhxVDJVbzdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNRUl0Y2R3dzJ6TUhFUFpZX21WSUdVVGRLb2ZhemhqMVFial9MbUZPMTB2VzBQVzhNdnM5TjR1elNTSnRXTTY5RXdCcUpneEdvS1VWUno0OFVfOUlUZ1oxOGlCQTVMcjcxd0U5SVNnc3FycDI2MXMzcjI0MXNaOTVmUUVJUWM4TjFNQWNyZURxMFZWdXU3RG1oOGl5WENqZEJqdVBBaTM1ZUVkYlktdzJieTFHNlFqR0lrSy1OMWp0SXRrWDDSAcMBQVVfeXFMTUVJdGNkd3cyek1IRVBaWV9tVklHVVRkS29mYXpoajFRYmpfTG1GTzEwdlcwUFc4TXZzOU40dXpTU0p0V002OUV3QnFKZ3hHb0tVVlJ6NDhVXzlJVGdaMThpQkE1THI3MXdFOUlTZ3NxcnAyNjFzM3IyNDFzWjk1ZlFFSVFjOE4xTUFjcmVEcTBWVnV1N0RtaDhpeVhDamRCanVQQWkzNWVFZGJZLXcyYnkxRzZRakdJa0stTjFqdEl0a1gw?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46016.64583333334</v>
+        <v>46017.3662962963</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Short Term Trend Reversal in Deep Polymers Limited Possible - Monthly Performance Summary &amp; Explosive Capital Growth - Bollywood Helpline</t>
+          <t>Real Madrid ready official Vini Jr announcement as Man Utd and Chelsea make €100m bids - FootballTransfers.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 00:16:57 GMT</t>
+          <t>Fri, 26 Dec 2025 09:13:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxONGxXVUY0OEZfeFFrcEN1SjVuMkMwOVRuN1poZnU3eEEzOENrTldmM2JtV2FWZFphVnJSMTZrZk9XSzl0WVJXODAzSGl6emF1WDhfX09JTnlTOHFyd1lMcEd2ZGctVXRUY3phQnlhYmUzT19fX2V6WWdFc0V5Z0dtd3ptUEt3VFhIbF9UVElNTGpmaThMSU1IRUV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNNmV6MTVsQ1pFaTNMeDFNMEtfNEZ0R05tZUdlX2xVODE0N1p5SDR4em10XzFua0d3OWh1UWtMdGwyUWJFMVJCQmI0YmQtbHZrV3hNanhHa19vbldWUVZtVVdfREFHVkcycmQ1dTdqUUNVVGJDSS1GakJmc0lSQndJcFhraFhPRmJseE1hQ3p0bXNRQ3JGc0ZxQVZlblpndWVVWE1ZNGw2eW9DT1dtbE5vSkdyM1E1VW1QalJNT29GNTJHdGtDRk56N1EyUzFiY3J1blNBX25mdnZ0SlFuZ0plVmN0cXFDQkdjNmVNWWhqbnpQY3l5RmJsU3NqdXQ1Rk5uWkJZR3U3clpBUms?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46017.01177083333</v>
+        <v>46017.38402777778</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piccadily Agro Industries Limited (530305) Hits 52 Week High - Breakout Stock Watch &amp; Explosive Growth Opportunities - Bollywood Helpline</t>
+          <t>How you view the companies who do not give information about subsidiaries in each quarters - High Beta Stocks &amp; Free Superior Stock Performance - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 04:29:26 GMT</t>
+          <t>Fri, 26 Dec 2025 11:16:05 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNZ05vWkVWOVhjbFBGejZxYkw0ZjAzQkpxV3ZzOTREYnA4TWp3bks1c1R6ZmRKMFFkWGNkMHg4b0ZGb2swM1NkX2QtbWtWYmpHaThfcUtGcklzS2pyX3JQSU83bU85emp5ZGUxTnFnT01MZkZoRmtnYnBDSTRGT2d2ZzUzM05jYXd6MVdSSjNoMmtNX1Z1VTJRZ1l1UEpzNU51cVgxbWV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTnIxdFMzdU1UeERrVEt1Q3ZXYUVBTHJEbC12ZHZURERpSlA1ZF9uRm5KcExJTURka2oyMDlxOFVKOEVEZVpIeVl6RGVsMUoxb0hXYnhneVpHQ3MyU2tSbmx3VjdCTTlEeEZ3Zml0ZHhHUUVQWXp6VHA3WGlTNTF2S3E1R2ZYS2FHTFc3ckpDOEExbVltdEFwcnhyXzVoLUswSTc5dVZoaGtUWllRdE9iNEV3QUlJTnRFZExpdUs3RGhVMVE?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46017.18710648148</v>
+        <v>46017.46950231482</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>Village Search Bicester and Kildare</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The impact of the Palestine solidarity movement - Red Flag (AU)</t>
+          <t>Boxing Day traffic chaos as shoppers queue at designer shopping outlet - Oxford Mail</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 01:26:12 GMT</t>
+          <t>Fri, 26 Dec 2025 11:32:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNM2tCeDFiY3N2cGNfUjduWXdkWjd3Vi1zMmlhMlpsY2ZCbnlPU3FmTjZFZklBaGdlMkVCNUhvbTc0VXRFa0gtMmZLYlVISDh0RHROdDZnM21PQ0VIbTMyNjdGRHRFd0dFVHZYLV84M19OT0tIVElQQTk0dWxNS3Z5UURJY0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNc2FUX2tqaTdHdjdBZVJGZGZfY0dqSHZkRzhNbFhWNndpdkZpVmp6N3lOU3V3d01zYnRLX2NkVmp3cjJmay1VeE80SzdNVjJzN1VJV2lhV3ZOZ0YzU1JrTlJJQWVXNWFHMUozQW45SnVoZTB6UWFyU2MtalUwVmlLWTZJeFl3aE9UaDNyYWdUSHFDYU1tZlZ5NGFsLUYwZEUyQmc?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46017.05986111111</v>
+        <v>46017.48055555556</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C.C. Citizens Police Academy Alumni Association responds to officer investigation - KRIS 6 News Corpus Christi</t>
+          <t>Man charged following fatal stabbing in Kilburn - Times Series</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 03:26:54 GMT</t>
+          <t>Fri, 26 Dec 2025 10:44:49 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPZFpLbFZFRld0eDZ2Qy1ScWlOTkJ5bGt5aGo2OWhKbE5Md2xoMlk3dDV5eDh4ZGo5UFFSbndNUDRicW9zRWdGR1ptU3FfU0t3NTQzdk4yQnpuZEFXVHk4OW1SYlg4Nkd3VVhUTFBKSUhkOXMzdTVnbzU1UkhHbE1QYmR1QlpNOTZTNFIwQ01PYm1DRC1HcDVzUUMxbmFPZDVNY3dITFJpQzBIUTN0SC13WmpWNzdxa0hMYkllSzBnQnZodGc3YmpqWUJnX1FHcDh1UlN2Q19GRnEtRVR5MGtnS2o1RnJFQ1hLaEw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbnlXaEFXWU5rSlN0c1RzbmNHcUdnYjBTNWw2d2QzQmVBZUVMRENfdEROczF3OE9pQU9GVnhLMFYwNkg5ZnF3XzJZSkMxd0VSN2liVjg1Yi1WUEdfWXJyTUd4blotcF9wUHB1YncyZUZ1X1RjdUlVbXYxTVU3NWF6dTFjZTFtU1RVbzZnWjRHOXVzRTRxX2pvMHlOQQ?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46017.14368055556</v>
+        <v>46017.44778935185</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$400K shipment of live lobsters hijacked on way to Costco in possible ring of thieves - New York Post</t>
+          <t>Kent woman in her 20s dies in London-bound M2 crash on Christmas Eve - london-now.co.uk</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 19:56:00 GMT</t>
+          <t>Fri, 26 Dec 2025 11:42:41 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxON3VOVFpIeTUxREdqeUhZX193ekxoOHpFQ01hbWVWT2VpcXo0TXVmQURRTU9QMmhUclFvdmczSFhWSy1nYXlkQkZxcmNVM1N3a2M0bloyNWVWQm4tQ05QblU1bDBTdTRRQ1VzUVpvNEdBdHU3QWxqUW0wSjJhb3UycHdIN1Q0b2dzdXk5c0hPY2lWc3pzc05wY3FvOERLY0FWMDU1bVBISk10SGg1a0R5UlBqU2R0S1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPeFVidEFqMWJnM2w1TzFDQUNERXg3ZHg0X1NadGp4dlZ6UXBGZENkeEdJeWNmejNxNVFyUnJMa1EtMlF4aEtacmNTMkVid0o3Y2o1LXNSREtLcDZlbnJGaXh3OEtTeXNqLW5rSDBqdTZWNUUyaHlKYmotVmNxQk1lUV9iY1Z3ZC0yd0NLRGZyNWUxRlQyRUJJZk1XSW1CSUZuU1Vz?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46016.83055555556</v>
+        <v>46017.48797453703</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fabrizio Romano Transfer News: Man Utd ONE TO WATCH, Barca PLAN, Glasner BOMB - FootballTransfers.com</t>
+          <t>The exact number of fines TfL issued fare evaders in 2025 - My London</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 07:59:00 GMT</t>
+          <t>Fri, 26 Dec 2025 12:08:43 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOQmRKbzBENlRjT2t2VkdwU3dhajZGRFYxMmY2TkFsUUthcUUtNWtTRTJsNkhESTJZaXJjMG5PNGRWbEc5MkJtRlFYcnk2VWsyUnUyTnNVQlV2bUJMWXdqR0FQS29KXzJ6YW9JTHNCN1F0bzU3UEJULW1VUzVXRGdUbk9OVjBWSGdGbTFNNFJfTTJZUE5MS0tqcTh2Vmd2ZmlGanpBR1pORzNQOEZiZXQycU43YUstZmhpT3V3eFdySzBHbURLZ3QtNmVxMjNLelJvRGNyVHllcDZVSS1sWmZlaTAwSV9tUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxORzFzWHZsZjZ3LUliN1pnRWhLYzZHSEtETlctRENnTjBhNjc2SWc0N1ZVbFczNUFkX3JDRHZ1SVk5cTU2RzJyT2dHT3dodEI5Xzk4WHdyX3dGRE5RcjdOLUpvdVFHdE1lMXNIdWNyR3M4TUx2RnRtMW8tTmhpTzh5SDhzcVJoZ9IBiwFBVV95cUxQZFhDZ0lqclFkX0pwOEZJeE03cm81WHVuY2hEYjVJalZoVTJXNmFYd3NEU3NOTGpfa0s4Qzh6RHZfTlBjWUF4djhwcGVGdGREbEk2YWFvUGJtVkZBVzluOTZLSnJZTmVSaXJucFozaUR6LU52NVZvRTJEX2NvSVItaXBIWWxiQmVDZjgw?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46017.33263888889</v>
+        <v>46017.50605324074</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Can KFin Technologies Limited (KFINTECH) Maintain Its Valuation - Emerging Market Stocks &amp; Capitalize on Stocks with Explosive Potential - Bollywood Helpline</t>
+          <t>5 top tips to get rid of Christmas clutter and maximise storage according to experts - My London</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 00:11:20 GMT</t>
+          <t>Fri, 26 Dec 2025 09:18:36 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNOU9mbEdGbFBGbTlja2RpVUV1V01kZ2gzeWFMVnlTeHhKb2hNNWlOZDRkbWYzRVU1OHZ6SGNQbnhBMzhyVGN2VDBDWXFuZnh6czM4UTJMbktoVDRGZWRtU1R4eTRXbEVCQjVNdjF1RXJZV1JGbTVDUC1ldkR1aGNTZGFrT1A3eElEeWszbjhlVmhLQl9kOTJfcmtrMHRtQVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE8yQkZoU2RHTjhia3JQRzVibHBwa1R4dkt6T0g5Q1pzTlo3Z1k4WE1EcWREd2NQX1Jrd0xTZGo4VlBxTUxzSC00a3U3TG9kYTBlbDkzVUtRTmV6TVJTSUtxVnpHeVBnS2J1dFpJOGg5bjJlaW56bHJRa9IBfkFVX3lxTE96TkJJalQyYTNFLWVLY2NiU3prU2VRc1M1X1pzdUtSYW1KV0tHVHlhNlJadWZlRkV5bVFPaG5vQzlLS25uUGt6bHVra2JPdjNWU05feEd6ZVVYdGlvMlo2cGRRa3JRaVBsZzByci1EQk81SHoxbGthUzdRNFVFUQ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46017.00787037037</v>
+        <v>46017.38791666667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Andreas Christensen and Marcus Rashford send Barcelona into Copa last 16 - IOL</t>
+          <t>Shizuoka factory reports "stabbing with a bladed weapon" — 14 injured, suspect apprehended by police - reports - news.cgtn.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 03:26:45 GMT</t>
+          <t>Fri, 26 Dec 2025 09:27:30 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPU0o1WHA1OVFZTTQ4LVlaZWdnT3BZY0pteWowcHZLcVg1Ni13b0I2aWFGMHhoZFZianNiZlBVQWxvR0NicDFMSFI2c3VmS3VST1pkQkVFTTdBUlpFMjVZZDFqZFZoU3cxbnNPZGJSM1I5VjdfLWw1ejJKOU9QN2VTbWVldTVEWGRGbzFvSTlJY0xSbFdsZEw0QXFqbE9jdlBZODh0YWVkOWhLR1J2bHctTEtjSHpYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBnSG5yTTZJekIwSXNCYUpHMjRKN1JRSmdfbFFsUDhvSkx4TWMzWnR2d0p0NE1zLUV4YXp1SkpUekVUdmlEckk4SV9PSmdBa2JReVdkSlV1ZmFEdnZmYkVoWGIyOWtVeGNmSkwwVExB?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46017.14357638889</v>
+        <v>46017.39409722222</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Football transfer watch: Liverpool beats Real Madrid in the race to sign the ‘new Vinicius’: Report - lokmattimes.com</t>
+          <t>Hundreds of northwest London arrests made as crime drops in 2025 - london-now.co.uk</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 17:04:24 GMT</t>
+          <t>Fri, 26 Dec 2025 10:17:11 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOLXplSUczRlM5VVVaSThvdi1XVW5ieUw1dXJxd2ZPMmdwVFdMaC10X1FENHpJTmNpaW1uOFZDSVpnSk4wNW15X2RYWWlKbGpRWFhtc2tmTTZIbDRIVDRSU1FnbUh0OTFsQVBrdFU1a3VNUkNmWTE2c3hvVFVCSkNoSF9kZmVLUTI5VmxjdUdXVWRDVHBqWkplUEJYTm9oOGM5VHc3dHhBSGFtdnpxSWxKQ2g4NUNrYVBsSnNoTVUyZ09mR0pDSnlEcS1CbW5hNlpSNGpFU0t3M0bSAdgBQVVfeXFMTi16ZUlHM0ZTOVVVWkk4b3YtV1VuYnlMNXVycXdmTzJncFRXTGgtdF9RRDR6SU5jaWltbjhWQ0laZ0pOMDVteV9kWFlpSmxqUVhYbXNrZk02SGw0SFQ0UlNRZ21IdDkxbEFQa3RVNWt1TVJDZlkxNnN4b1RVQkpDaEhfZGZlS1EyOVZsY3VHV1VkQ1RwalpKZVBCWE5vaDhjOVR3N3R4QUhhbXZ6cUlsSkNoODVDa2FQbEpzaE1VMmdPZkdKQ0p5RHEtQm1uYTZaUjRqRVNLdzNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPbVNzQ0s2dVJINTduQklxcFhyWE5wNmRPZVVhZlB3aVFUTmRhZC1NLXpkUzRiOEhSX3dJRDJmQnVxVm9GZ1M0cDV6R1E3M1Qyck85X1hGUmtHYnJ6dXN3OFFyZ1ZXRkE4azFiYUtIS3BpWnJ4ZzhzUEhSaDl4WjU5RWZmMzlocGo4UUpMb3JsRVFUNVI5aXBYT2pueGpBczdUdlg4YQ?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46016.71138888889</v>
+        <v>46017.42859953704</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Heatmap Data Shows High Activity in Remsons Industries Limited Sector - High Dividend Yield Stocks &amp; Explosive Capital Gains - Bollywood Helpline</t>
+          <t>Rutherford Co. 'has seen too much tragedy' with 3 juveniles charged in 3 deaths - The Tennessean</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 02:31:54 GMT</t>
+          <t>Fri, 26 Dec 2025 10:04:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUlJKV0dGbW5xdXdmR3NCcTJvSmlWdFNJQWg0RC1zcEpzbTBUMkJvNGp6dFprS0NKbll5WkhvLXdTMGVXWnlQbi0wbXlXWWJsQk92bTk5dTFmNWpUa1VpRmc0bWpsM1FRQzgyRzQ5RFBXR0J5NmxwNGJWOEpJb0NXdzQ1QkVCdDRYTHNfVHUtQlV3VjZwc3RSbi1hbGRmenR4cjJKZXJwbmNNZkpMMUJmdXhoLW5rU1VFTlIw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxORm5KazM1TV92eW5NWXBvOXdLOFU5NzlHMWFzUU1rd0N0WHd1MjdVampHb3ZYTDl4TGRlbkpWOHlVd2t6SlVSU3lzNEdGdjhmdzlLX2ttLWVrTUlBejVMUF9Ba011T216X3Z2SWd6MFBtd0ptSEpLcHNidEptTl9vZmczck5Lb3NROUJhSVo2RENfSmhFLU1EaUliTFNGNGc2OHA3LVFzeEhLbDFxUkxUVjVZT3lYQnhPd1BLTnlfdDlNc0MtSEFpSi01RmFfaFBXeXFCRzloVnF6Mm9wUEhudERjdThLUHJF?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46017.10548611111</v>
+        <v>46017.41944444444</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Would You Accumulate or Wait on The Ugar Sugar Works Limited (UGARSUGAR) - Stock Liquidity Analysis &amp; Outstanding Investment Returns - Bollywood Helpline</t>
+          <t>Mysterious Spray, Stabbing Attack Leaves 14 Injured At A Factory In Japan - ABP Live English</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 06:09:31 GMT</t>
+          <t>Fri, 26 Dec 2025 11:12:40 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPOTQxNDdCazJTU1g4Tzd4ekVGSWFCV2FLRmctMHZ1eFAtaGZOMVRsOS14Z05jMmxrSThmaWk1UTNPUFNtUjhQTkVJaDlRYnIzeUpnck5NQi1NdVF4bUVkWG5CcEswWDlxWnhvTi1pWF9YV1V2eVp5Wjl6OU9uLUJoM01NaDFzVFhVMzlMX1BXMEF0VENmbjJaNFpYM0NLUlV0SkRyVHdjNEFZQUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVDk5SlZwaVUyT2ZtSHRCNXFaUFRtMWZ4cm5RM3p1M3QtRHE5RUhEaFZVczlvemxTRW1vU3FITFo2SXJUTmQ1aTdXeWlubWdyTkFIWGNScEg0NHd0T2V2Zk5kS3NBTjBvSjFyT1FZWUNTZHFGQ0x0ZVRVOVVkUkJWRW83M19pZmVmSlgwSHRjSlVYdkxBQjBfbFlhOWhPam1JUm0yU0h30gGmAUFVX3lxTE9UOTlKVnBpVTJPZm1IdEI1cVpQVG0xZnhyblEzenUzdC1EcTlFSERoVlVzOW96bFNFbW9TcUhMWjZJclROZDVpN1d5aW5tZ3JOQUhYY1JwSDQ0d3RPZXZmTmRLc0FOMG9KMXJPUVlZQ1NkcUZDTHRlVFU5VWRSQlZFbzczX2lmZWZKWDBIdGNKVVh2TEFCMF9sWWE5aE9qbUlSbTJTSHc?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46017.2566087963</v>
+        <v>46017.46712962963</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>“Has been offered to” – Fabrizio Romano provides shock update on forgotten €44.5m Chelsea ace - chelsea.news</t>
+          <t>Man dies day before Christmas Eve after flat fire in Walthamstow - london-now.co.uk</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 06:45:00 GMT</t>
+          <t>Fri, 26 Dec 2025 14:13:53 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBVU2RjOHA1LTRHQjZVMUtfOWVId002bkJsWmFkTUtIYTJHWGd3Z3JoWURnVmZtam5CMkNSVDNtV1NRM3ZKX1ZDMm8xdXFIMzBvNmZSUm5jb1FyQzB0MHdXUGJkU3BzekFWTGhjS2hDckg3MGtTUjRN0gF8QVVfeXFMT1dDNlo0TnViczNCV0xXOEd6WlpUMlZucVBrdHdYOWIza3JnRHlsUWQwUHhpUmpqbXBwa05KSXlNS1dhVVZKeUN3ZnlwRE81aTJrblhTS0xlZzlKbnZtNkxxQjdRdHBVVVZSSW9xTzJxZ3ZsZUhoT2ZtN2NVRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOS3dackNDbWRNOU9CcHdnSktzNm5QVG9LdExBUmNSa2xJMlJKd0pJa0prTEs4N3dSR0w5T01hQU5ZcnlSdEhVR2ZSTzRITXgtOWFLbGRhUk5Td3RHLUhDZXV4RGpGeHdRV2F6WGZCbXF1ZURoX3ZCSXF4V2lSWVV1clRZd0lwQ0lfNV9LMTBJMjNyZUV4N3dzZkFpYTlaTHpqZVE?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46017.28125</v>
+        <v>46017.59297453704</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Flamengo fans cry foul after defeat against PSG, Cherki “bomb” gets people talking in Spain - French Football Weekly</t>
+          <t>Unclaimed Suitcase On Busy Udhampur Road Creates Panic - Kashmir Observer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 02:11:26 GMT</t>
+          <t>Fri, 26 Dec 2025 13:25:32 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPYXZxWExDZDNJc1gzTFE2X2VYNktXZzlpSmhfTW1vNWFWZ2JBdk5Da0F4WllNcDJNLS1oSnZyV0lEWmFNRUx4Y19OWDZjUjlORnpBVDVwMGlpZ25qQUdWOUtCNWlyWFBzeXRxMXhBM1hQMkQ0d0Rrb01mdXZEZUItXzl3ZURxLTgtRy1GaXJOem9NRnBXa041bEVOdHFNZFBFWXVyd29jak1RLTVWZDdQX3dzT3haeTd0VGpmMnhxVnpIWmNJbWV4S1JlUjcxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQm94Nmc4REtuN2g2WUNOU0lGZGZpRVRlRDVnR0hpa2U0UWxJWFhhNVB3MEJoa0R6WHdwdkYyTEdvYXdCRUxaMXF5MkRreHlVUmQ2SlNoNUZ1eVN5d0hESmE4aGdzUF9pVDkwN1FyRjM2cjJMb1BXMDJERnhoZHRHUE1nbUhQSjRESERIMzRuei1hdUhjNmN2MUpB?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46017.09127314815</v>
+        <v>46017.55939814815</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Local Town Searches Bicester and Kildare</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>(Kildare OR "Newbridge" OR "Bicester") AND ("protest" OR "boycott" OR "bomb" OR "shooting" OR "explosion" OR "stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Police hunt suspect following Bangor stabbing attack - kildare-nationalist.ie</t>
+          <t>Bomb threat sparks panic in Chandigarh District Court, premises evacuated - Tribune India</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 15:25:35 GMT</t>
+          <t>Fri, 26 Dec 2025 10:35:01 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQNFNaRk5qb2dMZDM1TkFIcEZrNnAzamtuQXBlN3JOVnJieFp4RG00cW9IVC1GQnFPeHFxRkVkYjZpOXFRZmNCWk9UaW10Wk9RbHM0UkpvdXVYci1lNXB1UG9sakpkN1hrU2owTE1HTGpGTEdsbXJfTWpESVZyWVdDTVlYSlEtekE0WXFhVV9SaUFJUnhhWjl4OVhubkUzTFJLUHAxTVhDd1JDVk9v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbTlTbW9LcG01X0lXakpETlgzTFF2M1Vudy1qblB0V05DUnV2SVV2MElyMnh5WnE2S1dWZHM1SGx6RlZuTVIycl9sQm9xczFITkh2SzZJTHdiQW1IS1JCaWlXWGtLUjB0QXpsSDFLZTdjdTRnUXc4aFY2RE9jQmRNcTFfM2RMTER2MVZ0N09Pai12bUhfYjFVb3RlSHl4TFJYY2lLV3NRM05WcmE1aHhkTVBjVzIyWnRqVXVWelhB0gG-AUFVX3lxTE9tOVNtb0twbTVfSVdqSkROWDNMUXYzVW53LWpuUHRXTkNSdXZJVXYwSXIyeHlacTZLV1ZkczVIbHpGVm5NUjJyX2xCb3FzMUhOSHZLNklMd2JBbUhLUkJpaVdYa0tSMHRBemxIMUtlN2N1NGdRdzhoVjZET2NCZE1xMV8zZExMRHYxVnQ3T09qLXZtSF9iMVVvdGVIeXhMUlhjaUtXc1EzTlZyYTVoeGRNUGNXMjJadGpVdVZ6WEE?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46016.6427662037</v>
+        <v>46017.4409837963</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Discover the ultimate shop-and-relax treat with voco The Club’s €50 Kildare Village gift card and stay package - MSN</t>
+          <t>UK snow maps show Britain 'disappear' under 763-mile blizzard - the 73 counties hit - Daily Express</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:51:33 GMT</t>
+          <t>Fri, 26 Dec 2025 09:57:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOY1cwd05RU2VQbmtzS3NmejlJN0Nhd1RUdjRmX3NjWXgyc0RqaXNnTUZhcVExRGNIQnJvamNxazJialBOWFpiUXp6d3ZMajJWaFFsY2FIOXlPRVlIOGlvN05zR2I3bnF0UVlNSFpnamJ4XzJac09LR3JFaWNVekcyU0IweVZVa1BUWVJQV2xrOFlYaFY2dWtoblBMY1ZOdlFTbkl6T2NKR1h4VlBYOHNYbGpmanN1VkVENHZ5LW9BWnM1WlFWZDVoZ0VHMldOSUtRTlNNcWJvWV9hak1FUVRQMFlHWEFNa1ZjaFNVMDFFckFtZDVHaS1fS2NB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE0tMHpTcFZmVlJTc2JJZFFGVXFTdVVCVnU2bmk3YU8yazNkaGF5RWsxX2o3SU9Ld00xZ1RsLTF6eUdjWkFvek1UT0txT2tRcXJVc3dJM1lCVkZiVGk2bnJxajNoa3ZNcW12Umg1Wm85X2pRTW1XaHpB0gF8QVVfeXFMTlNwUWV2R2pzY0dZWTNJMEVFMXZfX25rSDlQN205RzJXSWpiVzlnZXNOVjRWRmxLcTkzaVI1RWtJYWRjQjdpb00wMV9saERRc3FHOHpadzNJLWdrcFZ2V0QxeFREMFZNODNmRnlCc2RYZFF2Y2xLVU90UWdSbQ?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46017.24413194445</v>
+        <v>46017.41458333333</v>
       </c>
     </row>
     <row r="42">
@@ -1802,24 +1802,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New Covent Garden bar inspired by New York's cocktail scene set to open in 2026 - Wimbledon Guardian</t>
+          <t>Teenage girl was abducted and murdered 25 years ago - but the killer is still at large - Daily Express</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 09:01:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOZFF6RDJsSHlmNVk3SEl3dGpEeF9OZjFHYTNPSjRESGp4WDZGdE5ET0pRb1lhODUxVjFfNXdlX1RCd3djSU5YVEJFR3BvMGRFRkdSMDhJd2VIellkU01UdlA5Q0xhSzFCT2UzWGk1M3I1U0FtWUZXQk1OOERneGxJR1F5OGRhS1VIZXNnWm5qeF90cDhvaHcxZzh0ZWdDcHRwdk1ibW5oN05ocTZkZFhaVDcyN2xFTmREeGhEZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOZWs0MVVvNHBHUWthMkpKQnVaREdOa2p5NG9UUUVmNEVUcmI5NkpMMHFteWJtSEFOckdzbGFmWkkyNFlBa1hpamRhZkRVeUNXMVNxSkZUOEl6Q1NSYklUbXBlcnludFVtSnZIZHpJOWlyZ2FscUF4UmZCSXBJY0ZabNIBhgFBVV95cUxPMlNJdFctdkJqbFFWM1lFVWNWSldlNTB1MVRUaHVmQS1zVks4c1VnOEhPUlJ4TzE2QjQtNllyd0h1aGZrTzJUR0tab3dkNV9pQWpzNFVVSEpveVZRVmF3SGRxOW1qcElCclp3UGpkRWk1aEFJTHg1cXRFYjBEa25UMEJJaHBqZw?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46017.20833333334</v>
+        <v>46017.37569444445</v>
       </c>
     </row>
     <row r="43">
@@ -1835,1608 +1835,387 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>'I'm a bin man - don't throw away your wrapping paper this Christmas' - My London</t>
+          <t>Police Release Suspect Image as Bangor Stabbing Victim Fights for Life - UK News in Pictures</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 17:34:59 GMT</t>
+          <t>Fri, 26 Dec 2025 09:43:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9BMUZibTcyc0doZ29ySFk1RElZa3Q0cHdRZjR4X1MzZG1kTER6dVJ1V0RkbmhLVVUxMnphbF81T3RvdDNMdUpWTzJfb1VwOGFuQm9penZpTGZoUWg5V0YtMXpJRExmS1hiSExta3R6a01tZmh10gF6QVVfeXFMTjZ6Q1VBRy1ZLUl3UkF3ZzRxakNYby01NEtqbTFpQUdoVzZVMm93RTNsS3JSMkZ2TDJ0dFdpci02YkxlRXVtRG94ZEJuUG1STXVhLTBqVWctLXFzaWtBb2o2QS03cGc5LTN5bXZqQkxuUnZUc19IdHZZVHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQUWRkSzlDRFBKOHZGRnFyV1RtdlBrVTB0MDlXMmlkT29OM1BYLUlZY0x6Uzl5em5OVnpqUlUxc1d3b3FWZWd0ZzZYMUFrd1A2aWhLaTVLSlJYQTRUcTZfdE1MMXRSazRkSmZEazFkZ2lfYXczWkRCWDV1Ui1zVWI4ejZGeHdmbURMTlQyTFhsOE0zTFdfWVdzNmN2cXFfQkVoMW9sUTJwdmVUei1u?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46016.73262731481</v>
+        <v>46017.40486111111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Danielle Galligan selected for European Shooting Stars 2026 - MSN</t>
+          <t>Duluth man loses appeal in 2023 Lincoln Park murder case - Duluth News Tribune</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 03:24:52 GMT</t>
+          <t>Fri, 26 Dec 2025 13:00:57 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOTGFtOEpiTE56SlZpVUxhTVBHUmJaYm9BOUlPNEJxU0tsVFhYNUpyM2dWU3ZsSFJ1MkpZNEJaeGkyQ0NFUWhvVGoycHBJU2pSRVVUNXpBTHRMblJYeWFUUkNSQ2t1VTNQMXNGMTVtb1pTZm5HMmVBYzJ3a3BxX1RlNnNPNUtoNjFjREFNSHJHR1BHcHRIZzc3ODFQajRYdDdORHQ2QThPVEN6V2NxaWhkbTl4NUVVZDN2U1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQN1BfNmF0V0ZGRnhsTzBJVGlRUHp6TE5EQnBqeTRsU3dTcEFFTWJtSkNheXZPbjZWWkR2RnZtTEJkTFlKakxsWXdZUXlBNlh0cFJjRHAtdE9xY0xGbzVkb1N2YXZnWHNFc05oemZiNThfeXFuNGQyNnRmSTR2NzlzOXV4Rktpc2I2VUtYcjVWUnYzb3d4TEhnT0NSdzFJM2RXZzVR?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46017.14226851852</v>
+        <v>46017.54232638889</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Early Christmas morning shooting injures man on London Avenue in Gentilly - WDSU</t>
+          <t>KEI Industries Limited Volume Confirms Breakout — Analysts Bullish - Cash Flow Trends &amp; Free Explosive Return Secrets - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 15:02:00 GMT</t>
+          <t>Fri, 26 Dec 2025 12:23:25 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQRDRVY19iS1JnemI1Z01yc2szblc1S3JubVpVSTdaMmExdmdVai01a3VTTllIWGxMbFVhZTVpX00yVUpMY3UxY0pRVEVhQmx6MFlkcTJGX253RF9pdmctVHpIbWh5UkpCUGRiNHFiT2stM3ZWeFdSYl9paGJzMnNudW5vOVROTnJpZ25Qd0I1M1dXa3ppRUdhZ2FGcTl2dVoxUUJISUJBMHZrNEt0MktsWTln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPSTNUVWllQUdXM2RPb00wby1pQ0QyU1pGNUw0a3ZVTVVoYTl0MUlLMWdxVzRZbVpvdHRpR0oySnRpUjNBck1zQkRib19XZURSa1VJVUNuTE5PazI4SWp4dl83MTl2cHhVZEthWkNxWWlaMjdNODlJQjZ2UXR4b3UyLUNYTGZjWWtlYWdQU2FjeHZoTktSNmIxQXpsWXAtRExnMVF3SkZLem1mc0F3b1FoVVdkQ3JrRF94ZDI0NXVCdWtsZw?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46016.62638888889</v>
+        <v>46017.51626157408</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Michigan teen gets life in prison for Oxford High attack after wrenching statements: ‘I’ve done terrible things’ - nwitimes.com</t>
+          <t>Superhouse Limited Stock Poised for Technical Comeback - Protective Put Strategies &amp; Explosive Profit Growth - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 16:45:59 GMT</t>
+          <t>Fri, 26 Dec 2025 10:29:33 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOdzByTkdWdXdFa2h3eWxPSkFHMm84TmRKRTN3WGxBNFN5ZGY0RFFwM2VsMmxHS0VSM0FMa0poNFhKNENmbG9Pb0FkcTdPR25Vc3JKMkJ5TzZIbnVPazBEZ1doZ0FGLWUzYjdfcWRkckh0X052b2ZybW9CdVlxeWowaDlvSGJ6OWkzb0hJVTFwMWdQLURpWV92NGdsQnItbTRxTjNxVnNnNm1FTkd1emNJWTJ1eVIxcUxQN29XWmhQMUNIVS1Hb1FOeUpkaDk1QkxoU0hONWEtN0thTDM2aUxWS3pYMEM1NUNQMEZVSTdVTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNenV4bG5TanZnWXNrS21UVUNpYmF6QTB0RDdVamVnS1BOZHJxc0ZIUTdvLXJpRDUycDdPeHJVNm9nXzZkZUxlQ1J0S0VqWENlMDFCTzUzRVZXb0lFRnpfbFZ2SXFaTFAxUkJJT3l3UktHRy1WRy1XYWQwT0hQYmJQZWxuc042N19HZ2ZMeGw3ZzdpSWc?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46016.69859953703</v>
+        <v>46017.4371875</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Published on: 2025-12-25 21:18:12 - Bollywood Helpline</t>
+          <t>Can Spright Agro Limited Outperform Peers After Recent Pullback - Mean Reversion Trades &amp; Affordable Trading Portfolio - Bollywood Helpline</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 22:50:30 GMT</t>
+          <t>Fri, 26 Dec 2025 08:33:40 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOUXgwdUZERVRDcjNYVEtNX2VBNjhDNFZrTkJQUG1Mc296SGhmNXFYRXkyeW44VVQ4c2F0ZUhNZ19vV0hraTV3MVdURFVNNFRGbkU0c0JuWFFMdHZYVV82ajNiY2xXRk1UYzJhRXJpaTAwWkIzRVR2clpNYmpDcDBpanFKaXVya2Z2Q0d0UXEyaW1nc244WXYxaklESlMwTm50U0tYN0ZOa2VIRVplS1dLcGlsMnFCMlhucXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPT1pqeFJZQktaY0w0dnpFNUpOejg3TGRfaW5fSVY1OWxVbFFCY3hlMnRZMmp3d1VXZTFtOE5WLVAyTnRZUnhrcFBxOWpablI5anNWUWJYbXFuZzdnWU54VWxvLXpkR2hndEhiNGFQT29PcjI2SXZoZ2pqMWROeDRKemdrZ3hEWWozeTA2ZkFuVkM5dnZzNzgwVVNQNzVWdjNlWG1ySTR0azRTdw?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46016.95173611111</v>
+        <v>46017.35671296297</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>‘Build a Bangla, we dream of’ - The Hans India</t>
+          <t>Serie A | Milan vs Verona – Can Rossoneri find shooting boots? - Football Italia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 03:03:32 GMT</t>
+          <t>Fri, 26 Dec 2025 12:01:29 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOS0FkQllzM3NmSVVzSXY4RDUta0VFckZsc2swWWRONldtbjE2OUZmYl9paXNXRV93aS1SZjh1Z21zVHJRM1VaNVYtQWYzNzFreEZBRUtnZDVsdjZ6WkpraEwzOS11NVlBVFVEalRfZkNCNmdmNDJsT3BVMHB2SlJSZ0gtekw2eGdT0gGIAUFVX3lxTE5LQWRCWXMzc2ZJVXNJdjhENS1rRUVyRmxzazBZZE42V21uMTY5RmZiX2lpc1dFX3dpLVJmOHVnbXNUclEzVVo1Vi1BZjM3MWt4RkFFS2dkNWx2NnpaSmtoTDM5LXU1WUFUVURqVF9mQ0I2Z2Y0MmxPcFUwcHZKUlJnSC16TDZ4Z1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1NcTh6aGNFZFkyZldVZnI2WW1HRUc5c3I3UVVtZmRBS1VrTEllRUk3OFFZYkItdjdfVm9MRVJjQ0VKTWU5TkJnaWFNY3VEOW5PdnpfQWlNb2NhZVFpUlFfYVdYdm1NT295azdVcldwTDZTeVND0gF6QVVfeXFMTWZsZDlISUN6aEtJYWVhZDJhaWZZQlVMZUlRZ3g2ZUtNOFZjbDNjd21ua0c4MGFZeURxWnhFVlQzM1ZZd2FzeUNYSzcxaFI5MXVoNjNaVkxldy0tTi1TY0N3UlBWNUNQSXNKMnNGYV9MRWpZV0ZxNWFIMlE?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46017.1274537037</v>
+        <v>46017.50103009259</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hyderabad's RGIA gets bomb threat for Flynas flight; lands safely - irishsun.com</t>
+          <t>Liverpool facing decision on leaving Mohamed Salah at home after star's explosive attack - MSN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thu, 25 Dec 2025 15:31:00 GMT</t>
+          <t>Fri, 26 Dec 2025 11:44:27 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOek1CclNaWXVrem9xZUZ1ckdENkxVWVVfRzdYM1JIVWVEbG1kZWIzQlUxUjE1aXEyUzJubHVsSG16OHdLRlpTWlhobW9JUnFVcnBQVlV4dngzVHY2aGlQak9EbVFQck02NHE4TjY0YzRncS1NRkxFYkdqNTNCa0R1TGNWMnZkcEpMMGZNZ3dOUWlkeEx0WV9fenJsOG1QdHpMUjBjRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOS3pCekNRMk12TFltYndNUjlkd2NYQm1fNzV0SnhfTGZTTkQxbXNHRnBPY0pocFBSS2hvcFpwbF95clJNaHhGVDY2SnZmSXZPWERGTmpWWUQxbjQ2X3RveEJodjFLRzJLaWQ4RVZWamthb0JUbFd3ZGVaRXppYzZHdldNLWdMX3FUaWl6aXN6NldKbFZuNkdHTkpiLTd2SFFXaHBrMDFfd2kzR3Ixb3ZodHJiREFOcmZnS19zSUdFaTZwNFRGWHd1VnlzZk5DZHAyVFE?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46016.64652777778</v>
+        <v>46017.48920138889</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The 5 best fish and chips in London according to reviews you need to visit - Tottenham Independent</t>
+          <t>Forget about a backup striker: Allegri wastes no time, intensive tactical training for Fullkrug - Tribuna.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 10:51:50 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNY3E2VTc3dFBUM1JidDU5MjRDd2FUTWhDVEpsQ2wtNEI2XzA1czVXWnpXa2NydVY3Sktpa1hISFNCa21RRENNU05ZLURyaS1qemNqNFlQaFBRR3VPVEVsT0Z0cU1Gb19SUnp4elRMazA2R216Z3ZjMEU2WHg4WEo0UmZIVERVMUlPeUNJSmpKUWNHa0JMbmZhazVmVVZSdGdCTThqUHUzYmE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVFdwcUJBVHJzOXByMnNoeW83RVVmSTI2bFYxMTRDRWhQWi1LMlJ6dDNhOVdVUVZUR2hYRmprTWFRdnZkUGI3V2xCYzRTTkVjLW9oSlJWbVZPT3M2TXB2WXppdnNVZEFEaV9MLVRPbk9uWkNBMjRhTDhxelkyc2ZIek53VmFVUjdSOFR6a0J4SjBQSFlyb0NKOVV6MFBXdU1vME02NHN4bzFuZUdPVHU5ckstU0dtN2NnWEdmYWlJTU9HdHVXTFhuMFRZVERZUdIBzgFBVV95cUxQVFdwcUJBVHJzOXByMnNoeW83RVVmSTI2bFYxMTRDRWhQWi1LMlJ6dDNhOVdVUVZUR2hYRmprTWFRdnZkUGI3V2xCYzRTTkVjLW9oSlJWbVZPT3M2TXB2WXppdnNVZEFEaV9MLVRPbk9uWkNBMjRhTDhxelkyc2ZIek53VmFVUjdSOFR6a0J4SjBQSFlyb0NKOVV6MFBXdU1vME02NHN4bzFuZUdPVHU5ckstU0dtN2NnWEdmYWlJTU9HdHVXTFhuMFRZVERZUQ?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46017.20833333334</v>
+        <v>46017.45266203704</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bromley women living longer than those in neighbouring boroughs - london-now.co.uk</t>
+          <t>Cuomo says Milan lacked ‘now or never’ mentality in the summer: “It’s inexplicable” - SempreMilan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 09:40:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNeXBYSU5XVWNocTlrU1hpZzVrRWhlcjJUN29xTzZfbWY1VXJzMExZR0YtcEdhMmFfeGJtcUdZTXJIMjBja01Ld0d4VzZKdGlhclRUa2RMOFVDZjUzcm9CSkZDSm9jdWFqZEVGVnVSVjA2blNFN1hTSEwyUXQtcTJBR0kzZC1vRWQ0WU5xNEl6OXdvS2p1ZXpabXlrbmNUd0xJdTRV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBRUTVPZXpKMGdYdDVuT3UwQmFoMmpsMGt0eTdYaHpnMjI1MkRZNG1QcjBScG9obVFTcmVySkRRckQwNXg3bjZxY1U1VVNlbUV6NVhJY05HaHJWZldxQW9oSExnVnNfRHBPOVl1alRuS0ZwdS1jRUJmT1VhUzTSAYIBQVVfeXFMUGF0aE5uMjEyYTA3QzF5bllMSFdaOThLMzRyek4xYWZNZWhqb1NaSFJ1bl9fQlJUOWcxaHlFckxVc1ZPbEt1REgxZFFsV0FIVlJ2U2RPaWcwWWwtdUxpaGJQWnNVUkRDLW9lLWlnZkswNldqZDZKbFZUWjNTQ1NQVkVqZw?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46017.20833333334</v>
+        <v>46017.40277777778</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Businesses across Havering that we lost in 2025 - london-now.co.uk</t>
+          <t>Zelenskyy says a meeting with Trump over the war in Ukraine will happen 'in the near future' - Norwalk Hour</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 07:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 13:27:14 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQeGw4b0dmQUwyT09PMU1waUlNTzJnODRhM25NVGR2bF84MDdYWHZWN0VTVkpVanNZOWwwZ1RvekFhd0tfNlNoTjVucGZFRGl1am9WekhGU1ZxYllFQTFYWTkteFFQdWJ2eXdrck44YUZabzE0WHR4SWZSUnlRQVRfbmZXaUZweXRrUDJCMkJMcFllUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOQU9pZEo1QWZKS2JVTnh6LWZ6eDM0ZTJ3Z1I2SW16X2FheWJ1YmpPTmllcV9xT1lzQWZOblcxU05lSnM0MkxTQlZSMkh3X3pBMndDT0pWSHpwTFMweWhpM1J6SW5XZS1OUUR1RkpydXphN3BEb0xiU3VjUWxxcHJkVVRXZzZJRXlVRHZsV2Y1UWsyQTFQVnRMZzNvYWZ5a3R3d1l6Zw?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46017.29166666666</v>
+        <v>46017.56057870371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>All the biggest developments coming to Southwark in 2026 - london-now.co.uk</t>
+          <t>Irish police issue appeal following decapitation of stag in Co Dublin - MSN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 12:32:42 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOV3NjRFBjb1UxUEhqM3FXV2RGLUtielVGZEdqTi1SUnEzdnRXaDI1ZUVPTmZwOVVhUGlsbUNDMFFyd0huTnpzNk55TlhjRnFJX00tZ0FJLXRzb1lUejk0ZzctYkdPUS0zNmpFTzdWVWRiaUdZcGNFOVJNVVRvTWRUQkJDTnVlMkpwb05SblE1MFpWN3I2U05N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUzlyMXdQeUZseVpUcE5KU1JtaGxZQ0NpMXN3YmF6ZFBTZFhvOHhZMnNfRUMwSjVISWk1Z0F1V1lSQ0lUeEJHVWhMTzdta0FnVWVnNmFXMVdIUHJRMXg1aG1BVmxhSXgxTVI1eXhhTHhraHRFUXBzV1BBVWttemtMSHA0SHc5R3dIZmlNREJ6Ujd3SkQ4eTJHWWNVVGZoRGZIcjNDNW5rcF95RERWak5mNTlBeWNreTUwSzNJ?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46017.20833333334</v>
+        <v>46017.52270833333</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New 'fantastic' shared ownership homes launched in Epping - london-now.co.uk</t>
+          <t>Suitable funding source needed to progress project for Market Square in Kildare town - Ireland Live</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 07:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 09:40:52 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOb1p1R2dDLUVGQWJ1aTRpSC1XaG5SdkVDaXdLbGVtaWZSVFBzVkRJOXF6QW5PUjhrLVNSaVFIQ0djWkg2aXR2TDZ2TkJRRHhaMjJxakdVYWFUNDJqeC1VbkRzaWZtX28taU4zVUQ2c1NvaVRDa0pFbFIxdVRaODlhLTFOUFhvc1p6dmlFamZRak1ndDYxd1l3ejg2WmJpLWY0ek5MQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQaHdSQUxNRV9kX2tGbUJYeGdMOHg3X2pSVmN5UkYtU1JENEdYX3BfWmhteDBjUURNZXMtSVVhWk1HWWtLVExoaWgtbXk3NTJoRllsRTQzR1VDbFlic3V1QjI5V0NWZ2VaREIweU0yOV9TUEhEaW1rdXlIekJKcUF2NzFRenJmbXhmM0VTd1RUZ3N0VGVJVVBlSEVucmQ3eV9xYVllMUwzQ1pFU1hHTmhPc3FWdWZRZjlWOFZEYlVSX1oyeFVJMkpURURsRUhuSWNqMHpCem1fcC15RDQ?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46017.29166666666</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Vue Bromley to screen a packed Christmas weekend of classics and blockbusters - london-now.co.uk</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 05:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNS1FndnRnb2pITi1qblh5cEtUX0RhdE44S3ZES1EtRDE0Uk5IbE1tRjBIV29RdXVEWkpaNDlaNnRweWdSbV9iY1dZYzVYb1ZVemZpdkM0NnRyNllnazcyaXNkbU9EeHIxNXVMZmc0TENudVplSVpadGFOdElFYWdGQ3ZHbUhKa0plUGV4bGNjSWFjanpWSzFyNUVraXNoM3F6MEE?oc=5</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>46017.20833333334</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>UK snow maps show 13 counties to be hit as far south as London in Arctic blast - The Mirror</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 21:32:00 GMT</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5RdDNWUmc1eTg3eHI1MmlFaEdQVzNLU3BuYzlLZmhtbW1qNXk2RVVKME1oNFBYNWZDWXpkdGJXdHF6d0gzWUlpVHBBSDdiT3h6akFJYjF4bEJFMVJkaXZnUmVjREVWdUc1S0x1d1FpMkFXRjBqX2FiTGRlONIBe0FVX3lxTE5RdDNWUmc1eTg3eHI1MmlFaEdQVzNLU3BuYzlLZmhtbW1qNXk2RVVKME1oNFBYNWZDWXpkdGJXdHF6d0gzWUlpVHBBSDdiT3h6akFJYjF4bEJFMVJkaXZnUmVjREVWdUc1S0x1d1FpMkFXRjBqX2FiTGRlOA?oc=5</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>46016.89722222222</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>UK faces 739-mile snow storm 'lasting two days' with 13cm set to settle - Birmingham Live</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 06:25:00 GMT</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPLW42STFjN09zM1FxSm1EZzgzQUdrTFp5cV9tY0VvOXY3UFF2ZUFrR1hnbkJIbWVoeHBqNENGWERiVnM3YkZsLXRlNmxGZDRHQlhjNzJvWkloMms3dnhGSmczTmtPYm40RG90WHk0R0pxYXlQTkhPNl9kcDJ6QW9KajRHR0JIQzRrNko4WTBjaDg?oc=5</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>46017.26736111111</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>King Charles pays homage to Bondi heroes in Christmas speech - AFR</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 22:11:00 GMT</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPNndTSEd2RHZORzl2eGlBMEpPY1NHcUdpVU1RZGttSkZmX1ZXZ0VuMHZmTExDdXhKVHZjMkFBbmZLTjVMd2VCVXBoQjBCVnVEeHc2SW9vSzlXQlR5SlVhaEtkNkM4RDFIWlZWTDEycmtBTTN1MFFpSm1tWE5aMi1TR2FYbjdjVlBOSjFzU282ZEZyZVFla2NvUWJ5aFhhemdnckpmVjM3UnNhRGpBM0E?oc=5</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>46016.92430555556</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Call the Midwife icon gives huge marriage update after moving out of family home - The Mirror</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 21:15:00 GMT</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPYlhVTS0yQ3BMZ1hQS3pOZFNIa213VmdYZnlTOGxKVUZ2elZkMFdzQWEwM0F3cTI0ajFQV21BQWg5aGNVcHRUX2xXMVAwbmk2TG9YNmJObTZPbUJDV2kxSGo2cHRET2taelNZZVpwT1JlRnNVUnI3MXdfZmE3eEtpREUtMNIBgwFBVV95cUxPYlhVTS0yQ3BMZ1hQS3pOZFNIa213VmdYZnlTOGxKVUZ2elZkMFdzQWEwM0F3cTI0ajFQV21BQWg5aGNVcHRUX2xXMVAwbmk2TG9YNmJObTZPbUJDV2kxSGo2cHRET2taelNZZVpwT1JlRnNVUnI3MXdfZmE3eEtpREUtMA?oc=5</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>46016.88541666666</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Irrfan Khan’s health deteriorated while shooting Angrezi Medium, was in immense pain, reveals costume designer | Bollywood - Hindustan Times</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 03:18:09 GMT</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxQOGlRNDlIUlNGN0c1SUpfd1dxWnFLSmo5MzR5UDZqc2lPQkpPaGZGYXd6eTY5X1o2WEdhMEs5U1VXX0Fta2NaVmpyeTBpUzVtdlRpTE5FRFQwUU5IbkdMUXVfZGp1QnhpMEpfMHVvZGEzRWZ1aEgwOXU1NmRPR1VNOFRYZ1NnUV9MaFBlSkFnN3lmN3JEMjNETHdGYlI4Nl9oT1UyeDJZRjBQUnF1dndsb3l5WFZzVlNKQS10czR5SnRuQmNLbHdYT090a2RESk5hWTlWdFZwMC1HZ2V3bm5lc2lqdk56OXVxeFZBS2M2SWpJOWl2MzZkQ2dCaUpCcTM2dFpxSFBockNxT1BjSnJzYVJB0gGXAkFVX3lxTFA3MHhoaV9nbWFOR1lpRURxNUZFbHRqUWJNUWxTN0NSMjRZMnBiVVBKSW5KRWwzOENNdWFLOEdXci1FRWJZelk5ZjBybTgyV0hlcjB5VGNIWlAtODRqc0ZDeGlRQmFTRjB0YVcwc1VLYkdVanRfY2gxeUtfVW5UcnhaOTFXS1B5UnJUY21WQnFPWXZfMHMtdVF4NjFId1lpU0VWdGtkRVBzajBtdDc0YmtnN3hFUVJ6ZEhGZ01PeFdzZVBSZDd4SGVlc2xpT3RVUkJER2JLNk5OSWZrY2pST2VLWU01Y2RTbFNOd0x2ZGNkazRONF9pN2ZQSm1jdWtsR0tTczNITUd2UFhmNm1BUWhxUzFlSndYMA?oc=5</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>46017.13760416667</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Festive joy for parents as Christmas Day babies born at Ireland's maternity hospitals - Irish Mirror</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 14:42:26 GMT</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUlYwUV9TUGtfcjhKNFZxYi0tUlhSVVh3SWRiTWlkbU5EaUdhSlFLVnZuenRCVHN0N1RwTmxyWlRaQUdRNkhVS2dzblBUeUdmeTBsLVJ3Ym1aVVJkRnpkWGFuRVFHWU1rSXFsTk1uT2JJV3NSU2J3ekJZRVZUMkdGQWd4QWZGRkFEdktBVVB3UFhLUknSAZMBQVVfeXFMTVJWMFFfU1BrX3I4SjRWcWItLVJYUlVYd0lkYk1pZG1ORGlHYUpRS1Z2bnp0QlRzdDdUcE5sclpUWkFHUTZIVUtnc25QVHlHZnkwbC1Sd2JtWlVSZEZ6ZFhhbkVRR1lNa0lxbE5Nbk9iSVdzUlNid3pCWUVWVDJHRkFneEFmRkZBRHZLQVVQd1BYS1JJ?oc=5</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>46016.61280092593</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Bangladesh news highlights: Tarique Rahman meets Khaleda Zia after homecoming | World News - Hindustan Times</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 19:55:51 GMT</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdXFCNDYtTzRNWXNxbi1iNmdabkxZYTR3LXV6OXZtSXhsWTU0bXFNQS03UG1YQktpbzRHQktrZE5Lc1NBVVFJZEpGRWFjRFM3NU5XUUZrT3FBbVctY1hCZXJ5cmF6eWg0UXdfMDR1dVlHSENaZGM4bDVCWnNWV3dfdm5LWXJHMTBXVjktZ1cybk1MeU1tQXR4WVVDd2ZZYmlTaURDVWNwMTk5THhUaUU0NGxDVk1iYnVncnRTOS1JaThtbDd2SE8zdWpBUy1QQ2tNNE42YXdrX2swbHZxbTljNHdYR2hWMHZHZGFlWi1obXYwN3dn0gH6AUFVX3lxTE9ld1I0d0ZGQTZvSGllMktSUkVzZFg1eGQ5dm1GanNHVVhPSy1SQjEzeWZ1NGlNakJSczRFb2UtX05LUjNvQWRMMVhhdEFSRzNRb0FEVFFwTHNWaFhsRGR2N2IyY3VBZjNLVzI5VktOeG9lVEZCVlBkN0ZRdmpoNWJtR3RWTTFrSUlSdFRuVmNyYjZ6aS1PWlZ5QWVUUWVYelVoN1lKUm9iel93SG5wLU15STFQeFFrVUxscnZJX1ZybTc0eVJSUzBrNmFsT19ITkphQ21ma1pEem5XMVZ3cmowTjMyVFNLb0RzMmxYVEQwSGtBX0duZnNPd2c?oc=5</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>46016.83045138889</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Woman in her 80s dies on Christmas Day after 'serious assault' in UK market town - Daily Express</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 16:19:00 GMT</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQbURheXYzRUZTSzVMc1pGdFRMbFE1SFZpQWppNFVvWDlWSDNsNVlSOUxPWmRsTU84VEFxRmdTbHhvS1VpYlp1Qks0RG5WUVNDY1JLb0FMUmMtQ3F1SXdXRmxJZVFnamU5NzlOOUJheWUtRXE0UVR6Z0V1bUJuWThKdzBweDhpQXFTMWdkZjBnZ0NWbGPSAZgBQVVfeXFMTUg5QjFwbDlKTTR6Qm1xTi1DNVpVYWdWeTFuLWQ3U1RYSGdUOWFOU21HdndjZUppbVpXbVJyNXlrZFNIakJCZVAxSXlMS1ExcDQzckw1LVAyeUs2MzZ4NGNtUXJ1VWttbE5pdlhuYmFOZV8wOGVQR2NuTDFlUWd4VGxIREY3MFJWOHdpUHpRQ2JHSlhhSzExeVY?oc=5</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>46016.67986111111</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>All Koreans want for Christmas is a better cake - Nation Thailand</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 02:07:00 GMT</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE8tQXhhT1BYcEhIVDJ6dkc1N3NPa0dUaEF4Z1g2cGRGVjRSc3BYVDBQTzZIQnk4eTVIc3M0TE1IME1NQnV4LUd4OVFzU2M4eTZmTEZIZi1fUW1RNGJucDQxMjRhMnhaUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>46017.08819444444</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Lily Collins On Her Struggles Filming Emily In Paris As New Mom - News18</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 04:55:04 GMT</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOa3AwMlRQTFpJcjNsVWpTaDg4bzVOWHhGZTllMFI1RWZfWlF0akNlX0d3NEkxeWFaamQ2ZjlXNVZUdnVZVDc3MTM0aUItOUhqUVhkdUo3ZEdxVDFvN1BoUEo5R1RSMC1HN2dzTEdkQ1lUVkdzSmZnV3ZCV3lrYWVhNjdyU3ZqSE5vS0diME4xVlA5cUQxNC1FTjM2QWhjZ2gyN1dqQ2xYazlhb0hPYXc0b3FaT0Q2cU0tcDA00gHAAUFVX3lxTE00MmhNLVVnbGFIcXhUR19qOUthenl5aWhENlZwWWliVlNfc20yYktQNGVyeWZVWUk3NURIYkZmdjZwcExfOVZ6cEFRVTBaUXpkX3ZZUi0xby12MV9zM2VPWUtZdWlQMWVON0MtY1c1Ql8xV2dzMHFETms1bjQxWE1GaWk3djZWUjk4Z0hNNDR5WnJ3RWU1NEp2cHAzZi1QZThVdWVscFFjTHRYN3N5U0ZnZi1hMEgzSlgzRk5QS1hCWg?oc=5</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>46017.20490740741</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2025: Her Year – How Paris Olympics setback is fuelling boxer Preeti Pawar - The Indian Express</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 03:16:18 GMT</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQdDUtSUtrelB1S0c4OWxSSU85X1FWdUp6ZGJ2UXQ0ckhqbTY5REVuLU9PMnJGWjVCTUZFVGNGVl9YVW9aTjlndEJxRGNNcW9nNEI0ZTA5c3BkaVVHNVBEQzVOTHVqNVduN3FoaFk1bFdxWFp3dC1XbDBHZ19vcHNsUENGRnE2eXphQUUzTUJlcml2bzFKRGdhZWhDN3lHZ2xselE4d1ZEb09BLVNscEpGWmp5YzFnYllIbWww0gHCAUFVX3lxTE1YMjdINFdKVHM2Rm1hMlVjVHQ5TGJ4czhYekh1cXdLT2t4SWxJTTN3aURQbnNoWUhPUEdRY3otSDNGQWQ4a19ZU2k4WklBU1lEX3gwUThnRlFWVFQ3cGhhcFFMUlRUMkwxRUNNQTFtOXZCVmh3ZmxqMm5oMzZEV3E2X2laRk9teG1BcndaanZLOERsbXFjX3FkSzVwbGRkMGJxaWp3MHh5MVB1c0hhTW4wb3lydTEzc1BQMFZSYmVtaU1B?oc=5</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>46017.13631944444</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Zenith Drugs Ltd: Hidden Pharma Star Poised for Explosive Growth - Price Momentum Alerts &amp; Budget Friendly Portfolio Growth - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 04:07:01 GMT</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQWXBrdXJxVWFrcGtuUk1aMklLRWJTQkFKSkpyQkl2YUw4bEVibWJPWnVQRC1YQWlEak1weEEwOVM3cFItZER2SWdtZmJhQjN5NmJJaXlzd3ZwRDFpb3RnTENQb2xUYjhTekg4b2wwT3JHODJUcGxoQU5lUGxwMlE5WE5uODBmZHBXREV1NnBLTlRDLXZvSVZrV08zY3dUVFZn?oc=5</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>46017.17153935185</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>SoCal mother and 2-year-old daughter who were living in car surprised with fully furnished apartment - ABC7 Los Angeles</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 18:25:46 GMT</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxORHYzWG1UcnItR1FBRXBsMHV0NnhCaDRXQmlrNmxTQXFJSEdMNFpMdElmb0pyUDNLVm1XLXhHRXRyVTN6SWwzeGNYZWNfTkp2VVdNSGR0eDd6a1J0SGZwa3Z2ZGs3Rng5SVYzbm9xbVZva2l4WFZiVWVZQzFVdGJQS3BGem1od0xta0xVbmgzY1Bhc3BYSWJ0WTRQOWVCTm5VQTJfQjYtalE1QUFGZVFZaWFrbU1vanPSAbwBQVVfeXFMT3FjT3JCazVVS2ZILW51dGE0ZTRHYzdBbGpoZlhHSUYwSWZ4b19RUzBSZDFaQjBJUng5emlaSXlkbTYxWjIxNHZDWUZOaVdwMFNlWUxtM202eGZiZXlYb1dVTFdzUmoyd2prLThmVndmY25hVXlWOHRwR1QxOFlaZkxVb0JXX1FNbTA5ZnFPMW1SMkJMdkVzSGNYT3RqdElDajYxLWxXVkZhZVlDS1N6bEdxTGZLdTRrcll0UnY?oc=5</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>46016.76789351852</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Following the Bondi attacks, a US rabbi’s plea to the Australian government - SBS Australia</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 05:04:48 GMT</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUjNYRlVOUWFfQTFsLUhzY2RrRG1qbUFLSE55WkFrLTNFeTZReTRwU0lvOVc1bFl4TDdaZUhzMjM0R3JZUEdvQ3JibzNlTG1weXZyYUw4bUZ5NDdiUnd2UnQ3c0hhNndsdnBPWXY5MjZMT2prR0tsTHR6bC1CUFF5RjVfanZidFFGTzNEUGVBSE8zQTlkOGJVUmdZRmhIUDVyZHMwYmVfMXdSMjRPazVDN1dlUXBrMFlBcWRHOGgxZVA4YWk4SE00Q2FDSnoyamR6ZF81WTR6TzY?oc=5</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>46017.21166666667</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Mehuli Ghosh Interview: Arjuna Award Nomination, Asian Games 2026, Road to LA28 and more - Sports News Portal</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 04:48:04 GMT</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZXVDRlBXY1VtWHdvNUQwUWE4ZkM3ZnQxWjFnZm5IMGwwLXc2TFdldjllSWtEVV8yZ09DbXRkMkhYakxKcGtIR1d3bktPclNQeklLbllFOWNJY0JtTVRaWTh1NV9GNU1ITm9sSEdtbUY2OHpVNlRwb2pCZ2hWcmwxMV9XNTNEdW9FdUQ4OWY3SzZnSEV2ZFAxYjNSN2k4eXdMa00tZ2lKc3ZuRDjSAbMBQVVfeXFMTTR5OTJQTUJiM3Baa0lsUmlkc2tnNVJzQklhTzg0dHBGR2VOTjFDSXRFNlpJRFRFemQ2ZFM4ckNYZEJqX1kzME1TWXNDRDVMajd1QWV6QUsxUmxnQm5YYzBRWlhTRUtwNlNaaENsU3BuZHlqaDVnczBycFZjQXRpUWR0SVZ2SXFTMFJudmFpb2RkQmx6dkxTb0NjMWoyRlhvaU9KVHd0OUlRYVgybWdRc0RXeVU?oc=5</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>46017.2000462963</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Sentiment Tools Show Shift in Trader Mood on Mayank Cattle Food Limited - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 05:40:04 GMT</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNS2pkNHhqRVdHNENkWXRXNGdhZS1qMGlWcTNwbEE5MUlQb2RlLWZBdU1XMVh0eDlyMEtoSE1UVG80UGlDRjlKVXNJV3NERTlyRWtMNkR4cThPbUtMRExGT3B5N1liVDdPZjhwUVlmLVdHcUJqemlkRndGa0xQcUNIaEhXLWVqak5rRnNGUEd0UmwycmRtSW1OMlplZ2dKWkM4UkJISjN1dWl0Qm84MTFnelgwRzI?oc=5</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>46017.23615740741</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Used when: Market is flat or expected to stay in a range. - Dividend Aristocrats List &amp; Free Explosive Wealth Accumulation - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 23:32:47 GMT</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPcGJsZkVRTHlkWUxkMzBiMnJFc29rbkUwVnJuOC1NUmg5SlRQTi1XTkszZ1I5czRQcXRLRUFwZWdCTlk2cDBkWTlBTW9FdVdQSTZueUtwZzRlLWJmOFc3U3NYeVl1ODFDSlNuaVRzakx6SW0wSDhHQ0VLbjBJNnFIYXFvNHp0UmZYb2hYOFQ4MENGcmZFZkZNR25nb0pEZ3E3aGc?oc=5</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>46016.98109953704</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Earnings Chart Overlay Points to Bafna Pharmaceuticals Limited Upside - Earnings Beat Highlights &amp; Free Rapid Return Acceleration - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 01:14:23 GMT</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZ2VJRG40VUtCYVdSRkE0akxqTlBoVk5kZmhsZ21HNXJfUnBZendVNmdlWnBVY2NxLXlCMWgweUdYbEhObVl0OENlV0p1dEJNaVRZZUJFMmRpZDdUWWl5V201QUtxdjZVSllmVktFclZyVmowd2hoYWxaWVVZVFBkSkM1NDNJcTZKd3hXOVBKTVJNNXlmaFlMcG9xVDBtZnowMmVlTnYteWRMenhVRmNCOTZR?oc=5</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>46017.05165509259</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Is Sakuma Exports Limited Starting a New Uptrend - Retail Trading Trends &amp; Capitalize on Stocks with Explosive Potential - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 17:59:20 GMT</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOTFhmQ216UnppQV8zTlgyNkhRVm1Fd2ItdkZIYXUwZWd0ajUtV0NEb3VUdmlKU25PTkMzaEgyT2FwNkpnLWVlS0gtZkxBUWJrSWdlR0JBZ25mUW8yLXNNZzN2SS1uby1meU4wZkpKU2Nid0tqY2NEdldYNDA0TXMtT1JhbU9LMmFwZ2RNZzlFdl9STHdEaHc?oc=5</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>46016.74953703704</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Honeywell Automation India Limited (HONAUT) Announces Strategic Shift - Stock Liquidity Analysis &amp; High Yield Stock Picks - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 22:53:53 GMT</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeUg0NUpqQ0NxQlNCVmhsV0lDR2pVNzVXdGoyRE52aGg3UnVTdkNFeVRjQlAta2duUW1adi1pb2tJNXhrX1BGa0s1U0NXdl9qWmpJOEdURE90UVFvYzVGb19WdVFWRmV0SFVLMlJDWFhaWE1oMlkxd2tlR0lkYjRBdU5iOTItTWdPc0NYWDlVbUM3czRmVV9wNXQ1UVQyMm40TTB4YjFPTDBsMkZtTGxUSnhaWXBWekZRLTgw?oc=5</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>46016.95408564815</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Pacific Industries Limited (523483) Expands into New Market - Volume Profile Analysis &amp; Interactive Charts for Smarter Trading - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 16:58:49 GMT</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOMTg1YjRmdDg0alFIRG4tZ2JSeXhYbVlkellOWGxGVXZOMFF3UUFONE5aMlRRQzJjYVZkbXNNV1lleXdGeVdTM09DVGl4Q1dRenoxdElzbUdMbVdmcmJWVUU0TDlaRlJRcXZvcWlFaHhTMEd1bE9kbE4tYU05bG5iUEF3eTdRZXRoUHVrVm9QN3l4OUNZLVhaNjJUSTJKZVRQMGZTdHJ3WEdxbHgyVkE?oc=5</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>46016.70751157407</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Wyckoff Accumulation Phase Possible in Saboo Sodium Chloro Limited - Sector ETF Performance &amp; Rapid Portfolio Strategies - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 23:47:50 GMT</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQQU8zR1g2Ulo1NWYxT1RJUnVjSm9BQ1NveFRMOG5LQ3hjd1FGNk1RRWotR25PbE84aDl2MUhZQjd1MUFCbXM0UGZIZzMxejRvcENMSC1VNTdiYldIUkVxWU9vWVFCMU8zZ2dCdU9WTWlUV0RkWDIyN3NCSXowTEZlOEVqa2oxUy1vbWlGRkhnd3VWVkdrbWt0WXFYTlJVOURvOTg0?oc=5</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>46016.99155092592</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>The Best Celebrity Memoirs To Add To Your TBR List -- Ranked By How Juicy They Are! - Perez Hilton</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 16:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1RTWZSYkdyNXk4LXN2OGRFOUpfdHFwQVJybWQ2eF9wTFB2TU85a1Y5UXdwV1pVcm1oQ1B0OENzMjlkbFpiVXpSTUczdC1lSldteE9rdU5lZWRjVnROVU1lQ0RxZVpVbnBYa3ZIdjFvVzFBYVVhZDlSY2ZR0gF_QVVfeXFMTnpDNVBXUHRFLWd0UlFjTW1ocmRzdkFkbFd2djlFVzdFRGlfeXNTLWFaQ1RERlJLa1JGYUZjZkNabVVENEFvX3hyVmxKVmdaVTYweHdwV2lfR2lBaG9hNUlvYmIyQ0ttc1djWjdPakk3SlpIOTk2UW1adHI2M0MyNA?oc=5</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>46016.66666666666</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Nanterre vs Paris – Preview &amp; Prediction (Dec. 26, 2025) - basketballsphere.com</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 15:35:34 GMT</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNSHF3cno1S19mNV9rMS1DUHVaRy1sNUhkSGp6YTNtZHhPaXMwWXpyNWNOMGlKOUhnZU81LWU3M192M3FVR2twbFFtYlNYMHg3RWdJb0RJdFlQTEtGcmhTZGtxVENVV3owNE81VmFzcGEzNkx4Zmg2M0ozRmRhMlZQZHJkZVhTazE2?oc=5</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>46016.64969907407</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Can Diligent Industries Limited (531153) Maintain Its Valuation - Market Correction Analysis &amp; Budget Friendly Growth - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 04:14:18 GMT</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQNUpGak5DNmRsd1EwYktSaWdQSjZyNEVIb1BUWVFDTTBBTzFlUHp0ekJKNURNU0ZiZk5BMVNETFBjSlR2WnZSOHpkMHJZVEVtZmhZTmxKTUhRY2hSeDdTR05hZ1h6RUFEaURveTVqMVZGYTRFN3lSTVVaMlItSWVCSkpkN0lRNnZhdjNsc0FyZ0N4ZzlzN0ItaDZGR0VpUS1Yc3BzZXNfZFZJZWVjTkRDWnVCRQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>46017.17659722222</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Can Traders Expect Breakout From IntraSoft Technologies Limited This Week - Dividend Reinvestment Plans &amp; Explosive Growth Opportunities - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 18:44:15 GMT</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNLUZac1dDajROVjZiaklmaXV4YVZTZ0RicXEwTW80U25Eb3V0OGJJVDF6ZWFSQVdkbXdNY1pkbmFvSXFvX2VYZC1iRU5oel9FLU9JTjdVMDNVbWVDMnJrYTJCdEh3SW9kVzdyYUNOTE90UFk1OVktOHBwckJPaEpYcXhDZlhKanhIRGtJc0JraGQxREdnMnRiM2hRYVhGNi1MMVFQSUpEVXg3MlNV?oc=5</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>46016.78072916667</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Oriental Hotels Limited (ORIENTHOT) vs yyy - Candlestick Trading Patterns &amp; Explosive Capital Gains - Bollywood Helpline</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 14:53:44 GMT</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQSkM2NzBpWklnZVB2TF9CNXZfb3VxdTdTTWFBRUtnel9lTi12d0lvaUp5WVhTMDRMVlBoRldzOGh2VGgxLUhmM2l3dS1Ocl9STnlmX3MycXhlcjdGekpNZ2tSMzZpYTRfal8wbHRTTHJ0SjBNQ0Y4RDk0YXVidldncjk2M0Q3V1BmUjhlN2NB?oc=5</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>46016.62064814815</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Not Antoine Semenyo: Top three Liverpool targets to replace Mohamed Salah - LiverpoolWorld</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 19:29:00 GMT</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOdnZKNnUwejVEa1dzUHlWTlVFNkhvT1drTUVjSlB6dC1SNDNOYk9lelU1VUM0QXpETFlWc2stV1FCUWtiblVnYWhvRXdBa0tNWGVuSVZ6d2RvZVZLQ1JCbE5nak4tN3RCdnpnRlFmcUlGTFZ2MTVaWDVuYm5nMFpycTNudERYVXktbVRTek5RVVBWRm5FQk44dEg5OGI3eHl6V3QySTE1c0RDT0J6dzR6ZC1wMEVEdUU?oc=5</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>46016.81180555555</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>From ports to streets: The spread of organised crime violence in Europe - belganewsagency.eu</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 06:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPVXNTdFRMcWtqeGp1NFItNXphNmQxZHlfdG4waHZYZlJ1SEEtZFMzQUdNTjlBUnAzcnhfYkhrZFJyMUtHM3IxZ1hZT3FaLWxxYklqQmdGRWhRQ1dIRzhUV3dNUlEwZ2tWZldMaG5pVk5zTmhLR2dkelhGNDVHM0R0UEFnUGxNRkUyejA5c1RkTVJpM1NYY1AxSTEtU09rRlpULUFZ?oc=5</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>46017.25</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Man shot by police in the centre of Bruges, leaving him critically injured - The Brussels Times</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 20:30:02 GMT</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdmxGOW9IRkxJbUJielFaRHB0NWM2MkdRVzFsMjhYY1NyYzNWOVdwdlU1YXFBcy0tRllvVTRiZUFVbUlab1NhOHpJWFk5bTFnTENxVzBUcnpCWm9PcVNQOFVtbVFSRHJocUlCRXptY3lJV2Fla3F4b05aa0Y1bVltelBhNW9vRTBOY2dDTGZyWGQ1cGpEeFpiRmdwQUlKcWxmdmlTbC1oc2VPS1ZVb1k0bg?oc=5</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>46016.85418981482</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Zelenskyy says he's open to creating demilitarized zone in Ukraine's industrial heartland - bastillepost.com</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 00:25:55 GMT</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNRWNITnBlRVg5N2IzWGlQUE1USTVGYU55TzdxZVp6VmhqaDdvMEgxTEdia3R6S3lkblZaYTVMSkctMXNKYzRjM2FRRU9ORnc3bUtlajlELV92OXRERHEzOUdITmRiWjVSb3RTM0FzbWtxZkhQeVFJelIyNVJCV1cyczBJT3BDblpWQ01yMnpxM0cyU3YzYm1XTkppREh2akpqZjV5ckh5NkdSa0RJNTVNd0FJWjJvcXhNSE5yNHVYRi04NENwdFpmbmI0bWlZV0dBTE5mYW13?oc=5</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>46017.01799768519</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Monika Kryemadhi: Brussels' number one condition, Edi Rama's departure - Balkanweb.com</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 17:20:25 GMT</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPazNqYTJ1Y19EVFF2WDBZTmhNcGxMMmlFX0NLR0RkbWtKZVNzSWEwTmg5b1c4UVlEM0RLR1hCcTgxUTZELS11YWJ3UUdnNE5XZEFNUGNDQXI1SHdRdC1XTENpOFpJUXRTbnQ3ZEhxbThQdnZKRkI2d25oajhUR09MYzVaU1lMQ3VOUXlyU3p6b1R2NFhIZGllb3ZfOXRvQUZl?oc=5</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>46016.72251157407</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>The European laws curbing big tech... and irking Trump - Kuwait Times</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 17:09:00 GMT</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxObm5VY2FYOHVDYWdERlFRRUduUk01LVVjUWljVVJHaVNnMllMNWFwQlpKZ2NUZUpUbmc2QnUxenk2YWRCby15U3pJVk1GemFTTV9UbmZlSkNBOURjaTh3STB2ME5DanFTVGptNmJMcVBFc1FxOElLSXVjbEpDRDNZX1kyMzcxX25WVWhqbXpTTkNrY2o5Q2ZlS0NpT185QnBSdWx0X9IBpAFBVV95cUxObm5VY2FYOHVDYWdERlFRRUduUk01LVVjUWljVVJHaVNnMllMNWFwQlpKZ2NUZUpUbmc2QnUxenk2YWRCby15U3pJVk1GemFTTV9UbmZlSkNBOURjaTh3STB2ME5DanFTVGptNmJMcVBFc1FxOElLSXVjbEpDRDNZX1kyMzcxX25WVWhqbXpTTkNrY2o5Q2ZlS0NpT185QnBSdWx0Xw?oc=5</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>46016.71458333333</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>How the Art Nouveau soul of Brussels was saved - The Brussels Times</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 14:34:23 GMT</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPeFFrVVFBNTZseVpvc0VhSmQxRllRUHJsckNFRGpJZ3FYd01NaWY0Mm9Kd2VnbU43SmNvV2FvUVZYMEJ3QmQwLXdEdGR0VWVIUzR4ejZLalM0aTIycVFUQzhxYTJkUm9aOHBwUWVWNXBNLXViaG5iMVVLanRXQ1gxVnFhSFpWQ3QtT3NPcE1aRDhyU2l4YzU4?oc=5</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>46016.60721064815</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Local Town Searches  Maasmechelen Dutch Terms</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Two men killed in separate Christmas Eve crashes in Zwartsluis and Maasdijk - NL Times</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 15:25:00 GMT</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOaWY4cEhRaXBQNDhkTnlyMExXNXRScTNfZWtBelFTVGRvY2trMkJiay1ZcDRGejh5di1MdjR5WWhKdENvdmRYdzNsbmtHVVY3TGc3MGtuVlY0bTVobGduUVIyOVhYT1hvUjhCbmxzWWtRUHlWRGV6WWpXaWtqaXlHMjZUQXQzYUhrSTRuanRqYTdVY0hhY2c1QnV5Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>46016.64236111111</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Local Town Searches Wertheim German Terms</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Wurzburg vs Trier – Preview &amp; Prediction (Dec. 26, 2025) - basketballsphere.com</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Thu, 25 Dec 2025 15:37:24 GMT</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOVFd3SVlmbXRxeUpUdHVKc1FHdlZ3S3lzTEpSOU9Rc2preGs4MkdGQll2Nmk2ZFd6dGVVb1FNRzFlMmR3cmlyLWt1RFBFNDZ2XzRtQ2sxbWIycTFuU0JGbThpQ3diX1UxelNVTlByYXlEdlEtYThPYXFqbGJhUFNkTnBKcXV3a1Ri?oc=5</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>46016.65097222223</v>
+        <v>46017.40337962963</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>How Jorge Lorenzo reacted when Valentino Rossi set the same time for 15 straight laps - motogpnews.com</t>
+          <t>Luxury brands push into mass-market sports despite shift to exclusivity - Financial Times</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:30:00 GMT</t>
+          <t>Sat, 27 Dec 2025 05:00:06 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPazlXaDM2TXNRMnpBNlJ2M2RWcWhTR1RERGxwMzV6V21uNENKd2pCRVd4N25YZmVZbVNIRGNnQ0x4dUdlckdZUVZWemtfdkFZVGM0ME00RW9SUFBOUHNRSEdRbkRPWjFTd2FCNUpoemlaR2ItMERwMHJ2NG84S1B3bE4wNGhGNmcyUDJENkpvV0FLN3hXRzBoNDdkR3ZJNHZmckFpNXlwX2lKeHhNdGJIYWdZQnBIU3lUdVd2dUZWeEtCUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9RQmY1M3JVMEZrczA2Tk1scXRlMlJOdTRGMXcwRTRER2JkWnp3dmIzU1RISGFLMmZTNlhWRXJfVTcyZXVXeWhMR3FIb3lQOG8ySzB3RDlhZzNQMVpNWEY5M3VZa3FxdE5jUDRFbGR5cUc?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46017.39583333334</v>
+        <v>46018.20840277777</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dior Debuts a New Era of Dior Addict With A New Campaign of A-List Ambassadors - Hypebae</t>
+          <t>Dolce &amp; Gabbana Spring 1996 Ready-to-Wear Collection - Vogue</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 12:00:27 GMT</t>
+          <t>Fri, 26 Dec 2025 16:02:21 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaHA3YVRjTFA1eXJHZkt4STAxNnlLSngwMS1Jb19yWTR4Q0lWbjJ6NDB6aXMtUHFOdWYxcmx2RTdHVXVxbmxDYk1mZFFXeldmQmUwaW80RzRQSFpxRm1qcDdvZ3NxcGs1eHNZQXB6dFVPUjBuUG54ZDRJUDUtcDhtdEdmT1dfMm11ZDNxUlVFNDlPU3VTNkxWNV9xaUlISDlUVEhEWUkzSzM4eDBVR2ZyOUxOMkVGMkZUZGFPbWlOOU9sY2xUX044Tm9LV2psZUNlQnlvZWpjNHBXSHpkZ2gyMnJyVzh4R3haNnZKdW41Y1haT0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQQ2lJblZpWjR6NHF0d2ZYOFg3VTl0TUExQ2VqcEZjV0dYY3dQLTVuNEIwWVNuNTQtUUpEWHhBcXVNS3BvamRyUEtEVldhcmt3N0dRMXp6bkdRc2k4U3ZYVXhWSWFBR0ZuNGlkWDJYOHBSaHZiTjVVX0Y4YkNpTXZzNg?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46017.5003125</v>
+        <v>46017.66829861111</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Inside Tommy And Dee Hilfiger’s Lovingly Restored Country House - The Gloss Magazine</t>
+          <t>Jorge Lorenzo reveals the ‘secret’ he kept from Valentino Rossi during MotoGP title battle - motogpnews.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:04:38 GMT</t>
+          <t>Fri, 26 Dec 2025 20:00:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNX0tCcnJiNmFDWk9LWjBFSzZ0R2Ztc0Q0blItdkxqcWRLbEdDdzdXc0FfdXZxdTF5Q091LVFxaWkyRmhZM3Q0REE3cXh3TmozVDgxY0tiQXA1VjJHOHlxaGhvamJ1Z19MVnhkaEZUSHNsODNFNFNMR1J6ejY2YXE1bFFxRTAyQUVlTmZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNTjV4eEtfOVFBM2pFcm95eWhYdWMtVi05b3dNaHdtWXdsVGpjV1AtRUJqazQzb1ppUXJ0SjJvNVd3SWVURlQtd0ZFUkQydzRqZjdGYzYxRHcyREc4Zmx3V0EtcXpuWFhmdGZOWlFqbDBVSXM3bW9iY0JtMTF6SXdKb0Z1UzladmlmNWlxbXJMQnE4ejlPekU1NXk2TFdmaGMxRm03RGhkbHdQRGkyUmJQeE93Q2dtd0U5MHA1NTl4QThTOC01NkE?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46017.46155092592</v>
+        <v>46017.83333333334</v>
       </c>
     </row>
     <row r="5">
@@ -581,420 +581,420 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Swift Elevates $300 Jacket With $4K Louis Vuitton Bag - theFashionSpot</t>
+          <t>Shoppers race to buy Calvin Klein underwear for £8 each in Boxing Day sale - Liverpool Echo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 12:30:18 GMT</t>
+          <t>Fri, 26 Dec 2025 16:13:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNbWxYT2UyRUt4TVpta1FxSlVLcm4xS1dQX3h4SlpPMUtSaGxlQl9acnMtWEIxZU03SlNyT19aMXFobTMtdzdoSFdteFNYMlluTnE5NWY2ZHgtczZDeDd0aUR2Um41SjVoSmtKNW12TVJrTkZVNmtUV09KZHM2UlB5Y2dUVWpHanh5YXd3dGNiT0xoeDVGUUp4cGIxSTjSAaIBQVVfeXFMTjlkVHY4UzNTVmlIRFRSQmxTUTliX3FxbXpORWV1ek1hdGhzcnNramdtNVFERk5uTlZXOXhHc2gtZ05aTkZFUUdSVGRJM3VfZ19iakltRE5Lakl0UmYzY0NseDJPek5GSW5id2JFbEQ3czRBcHBMc3JHSWYwSVZNRkdrbWhPVUU1VWxycWVueWJQM0JTZzlxSm9rblowMWZTcWtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNazVsZzFnaHVZZFg2TWN1MnFTZGRHYm1rTF9xbnFGOE5GSHE1ZVh6d3RJVlZsQlQ2SkMwMVZkTlE4ZUdKaS1MaEpLU00xamh0aC1JWkRKSUN5dlhQcm5lZDlnWGExVk5jSGFZazN4NzhPeGszWW9yLUwybGRMcGN2YmVlVlBRRXhlb0xndWpvSzlKTWfSAZgBQVVfeXFMTlRMbjVsTFRHN28yMnI2OWRhT1NwUktmWXdnNTNneXp1UzVCbnNadXYwb3hmdHgzNHAwVzFOeU85Qlhadmd4WjVSNE1raDlsM2lQaXdjV1ZhYXB3NXZLbmlyV3Y5YlNjSTc2bUg4bThzaVE2dG5WaF83UTMybmNvQi0xOEZfb2pfemtZUDN4S29iUFR1MU1XbEM?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46017.52104166667</v>
+        <v>46017.67569444444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Strong Sell Stocks for Dec. 26 - sharewise.com</t>
+          <t>Dior Addict Launches Three New Lip Glow–Pairing Perfumes - V Magazine</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:15:10 GMT</t>
+          <t>Fri, 26 Dec 2025 17:05:00 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNaHVBUmt3a1IxUkRURU0yWHppbE9zVlRId1l1NzVOdWlQMWh3T0JOYTVIZlNRWFd5RllvNS1hang4UmlEU3FuekZiRHpMVENIam1FNEllM3phcG5zRE5HMWplWExndURENGR3MDRSLXUwTFU2ZU80ZGt3a3Z1N1BTaXR5cTM3bU9Ra1p6ekVvSDdkelYwVEFsaWhLeTY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNcFAwZDBOeU9MTGwzUXJDRTVTa0VMLXNwQndieUl3WnBFRnJJdUlBamRQbmhiSGxHXzhRNFdQUmJhcXY5Zms2M1g3b1NKRjREVG9RSGpaZlVJb242VTIzaW5QUEJZWmtNQkc1VzctUTFLUUg2Vk1vTGo2bFJ5ZVBwZ1RWSE5aVjFJa2pmR3BaX3Q?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46017.42719907407</v>
+        <v>46017.71180555555</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sittingbourne pensioner overjoyed after wall hit by Amazon delivery driver fixed by Good Samaritan from Upchurch - Kent Online</t>
+          <t>Willow Smith Doesn’t Really Care for Beauty Trends [Cosmo Exclusive] - Cosmopolitan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 14:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 17:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTG9KMEtEVThTWlpBa01ocndfbjRzc190ZmxXQTYyM0FZQ0FPVWFPU003cktheVhvaTdhYU5xLWRTWHVNN3pRUGNia1FEaWJReTZQUDF4SUQ5SE5aV196YW04VlEtWE14UGlPSzJERlIyRVBrSmtMWElFNkY0MExNdHpOdTZyUlhUbWROM2FvcHJ3WUZ0cktxOTJmZ3ZrY0tsbUczX1NjLUJGeWRTbjNveXBNQTJMeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQeG1XRWNsSHY0MFg0dWo0TlBhdU5WVkJHUFlyTmhMMTRtc0FMTmJicTBlNEtYc1lkU0FoOGEwS0U3YndNRTNZdUlYUnoxZ3pRTFBvTkRybFJpVW1QTEM2VUE1NWJ1cXNRU0tGRl9QakxIX05vaGdibHlNVXh3RTZBZ2cyamg1VzRQWlJOOFlYdzRnODB2QkVfNlN3?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46017.58333333334</v>
+        <v>46017.70833333334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Royal Mail on Boxing Day: Find out if there is post today - The Sun</t>
+          <t>Before and After: A Ralph Lauren Canopy Transforms a Basic Bed Frame in This Cozy Bedroom Makeover (It’s Very British) - Yahoo Life UK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:42:41 GMT</t>
+          <t>Fri, 26 Dec 2025 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOSVUyWW5JLWY1MkNaampHbkJFYVZyWmFCZjljY1Q5MVJVZW1ldllQUGpxWURFb1U0bWZCRTVPUFJRZXVBczYwcXE0b3RFMi1ZbjY4cldRSHJRZ3hxT1ExREQwcHhSNWtHbjRNMGtSaDNLNTJ3c1Z3U19YUXpVZ0liRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQV3ZKUnBZNnhJMjExZTBDaEhmMUJYVGlJTlBCdlN0cm5zSVY5SGRpay1ZX1ZhMGNsR0FHbWxSbTI1d2lBREl2R19hWkpLTmhPdGN0OUR5SFB6ZWw0Y1ZrNU5aR3h6aDk1RUQ2TV8yNFVmOTFJbllCVGM4SVVIdkdxdF9wb3M?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46017.40464120371</v>
+        <v>46017.79166666666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anker’s 140W Charger Is at Its Cheapest Price Ever With Same-Day Delivery for Amazon Prime Members - Gizmodo</t>
+          <t>Anya Taylor-Joy Always Layers Her Perfume in This Surprising Spot - Harper's BAZAAR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 13:10:54 GMT</t>
+          <t>Fri, 26 Dec 2025 18:01:47 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOVkp3RnEtdEYzcC05a2lYYjdBQ2ozTWhxem5NQVhiUF9ONThyclRyUGZ2OTE1VEUtbEluV1VLUmpYd2ZLcTk0ZmtBOHdfTjJzTndmaW5jVlBtR2hlWW5XaXZwbklNZXVnWHNYd0JXOXhxOWdXcE5RVWs5dUdkREZvWUNuU2pIendpT0NZY0M4VF9vSUhWY1E4SHg2WUNmclpENG5yZElQaG1zc004bEExams1WG8yWUxPOWtzVkZKbmlQUkNhNGNv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQYi1Yd3ItcnFvR0V1UmhYMDFmYXotQVJ2M1FLSXg2MFdZOElpTFdjdTFSeG5BVHRkQ0hDdUI3R0lONjdWOHhQMElQYXd5X0Zvc0NhWXdVOW5mY3pGVk11S0NqWmJMVTBfdk5yZE5YcDg1OVhNM2FhRE0yNXZ6VmJ5VkN3ZkM3SWpsazAzTWpOakc3MEhv?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46017.54923611111</v>
+        <v>46017.75123842592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Why are Swiggy, Zomato and Amazon gig workers going on strike on December 31? - India Today</t>
+          <t>A Michelin three-star chef returns to L.A. fine dining at Dior on Rodeo Drive - Los Angeles Times</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 08:44:48 GMT</t>
+          <t>Fri, 26 Dec 2025 18:44:42 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOaUFlQzNwWUlISGd1NE1vNHRSeVBXTWxlSnlxaTUycmNHZkh4QVc2aVk0MEdFX0NvbDZzbWJwU1Zla3VoV0JiYkRoTHVnVWVndm0xZ05zN2k2VTUtRXRSOERPLTdfajBCd1dMYzgtOHc0N2UybEI0eVp1NHlVSWhtclJ3M3RlMlZyajc0X0tFdnVxWkdiN0I5UndDZkE0ZUlmWTFBcEV4Nl9PQW9pU2Ytb01MYlpMYkxPcmZsZmJmTUNwMV8waTY4QnAyclQ4Ujg50gHWAUFVX3lxTE1KVnhFR3otZmFvVWxaVjlHSW9WUURxWnBTWEh1elV0SV9FcXBOWXo4SVV2QkVOTDZuLTNNUzhiYnhDbkVnSHJWYTZhTnUzMFV2VVhfQUczNjFFZjhCWWlIa215cmZwSkhSR0x2aTN3VHBWMURwZDNYdXpjcEwyb05VeUVHVENCSVlPdkdJdXRoMEVneGxBNm9yWDF2dVpOUFUxRlJCS0VSVDloczA2QmY0dVNNYVJRRlN3QWlLZlhvZnl3MlRNQjhiU0I4M3c4MFVqR0tRRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPS0xiWW5MRm01SXJaYnZvNHlSOTI3U1FuREZxNklSRTdlYjVVVzJqN0kzX0NhdUtoZDF4dHBFeld0dTZ4U21COHM0VVI0NlNtOWRMUmdBTE90QWJmdTF0aE1CR2VFNW0xbXcyeE1PMGhtVVRCajhwSzB6TEJkVEZ1bmpJeDVKbS16UjZUMzJvdWRSQkV2cE5mcVhfVjVJMUVxTThYZUlnUWdaRThKQTVnR0dGaTdMNnlqVjZ0Zk1STk9ZallWdTROV1VRTS1OR3lrLVAyQUQ2TDljSE1fZ1FIYUhFcDlqLXkxQjZF?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46017.36444444444</v>
+        <v>46017.78104166667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Walmart expands online footprint in New York to challenge Amazon - CHOSUNBIZ - Chosunbiz</t>
+          <t>December 26: CBP Seizes Fake Cartier, Rolex—Luxury Brand Impact - Meyka</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 08:36:00 GMT</t>
+          <t>Fri, 26 Dec 2025 16:16:18 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPbWtSVEs2LUN1ZEhVdGZXRTRRR2xDdTdMLXZabXc2azVGQ1l6QUNmSUg4aEhsNVF1Z0hmbXBlWVFYbzFnbm16dlJSN1huTjdNWTZYc2ViMkVqeDVtNjlEeW80MkttckJWdmhVN254czFNOFlpWTlRQVlMX1RZWHFabGpocjF4TzFpZUEtSjVHRXE1X0o5Mks3OE1abG3SAZwBQVVfeXFMT21rUlRLNi1DdWRIVXRmV0U0UUdsQ3U3TC12Wm13Nms1RkNZekFDZklIOGhIbDVRdWdIZm1wZVlRWG8xZ25tenZSUjdYbk43TVk2WHNlYjJFang1bTY5RHlvNDJLbXJCVnZoVTdueHMxTThZaVk5UUFZTF9UWVhxWmxqaHIxeE8xaWVBLUo1R0VxNV9KOTJLNzhNWmxt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOXzlQRF9QSElfVEd6SVZMQmI4WE1kM3NwNXMzNDdJR2xDWDBQZkp0RnFNNnY5OHhyWW0xN0VwWmstNU9hMzF6cXBDTktiN3ZPWlpDbWZ3SkxLV3FpX2VCZFFnVlFfd014MnBiN3VsWTJpLTFWb25jV0hScHpySEc1RGFiWDNTaUNQb1E5WWVMU19zaDQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46017.35833333333</v>
+        <v>46017.67798611111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Two suspects arrested after Amazon van was stolen - Newark Advertiser</t>
+          <t>Only for 3 days: a vintage clothing market with Ralph Lauren or Levi’s garments for 10 €. - Sevilla Secreta</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:48:00 GMT</t>
+          <t>Fri, 26 Dec 2025 15:17:33 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPSGt6dlptNEJGME96ZjBWQzFLcFJNRXRRV0FlRzlUeGViRHpRTXNLSUdQVHE4b1NWWUdoRmJDZHg1bTY0UHVMbURNV0hGYTBGOTBSeklfS0ZhWXV6SFE1X0JBT2xMZUNzdEJFRzYyaXhTWWd2cC03ZTlGOXlSUnZFNTlhWWRBRWF4UTB2TmhNOUJLZFNIU29jZ2NkU3N0eVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOa1poVGRTVkg1MXRzUEdFNlJFNi1POE8tRGhpdFJqdzhFczI2ZkZ4bmwzU3dtcGRQY2UzaDBTQzZTTjVSVHFROUJURFAtaTNyWkZVRWRnWUptWmpQejdjM2Zxdks4ZGhTQVBqRDE3bWZjTXBSWlE5S3pPZlNobnM5QkQ4ellvcGVj?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46017.45</v>
+        <v>46017.6371875</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Change in Amazon return policy in effect for holiday season: What to know - MSN</t>
+          <t>Luxury Calvin Klein perfume slashed from £87 to £44 in limited-time deal - InYourArea</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 12:22:28 GMT</t>
+          <t>Fri, 26 Dec 2025 17:01:19 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AJBVV95cUxPcFJQNlBsUmJjc2U5TnFxVURONmQyd3hHdGVobFROY214a2dCNHFoMHYyZUVBMEU2MjZHbDFjNHJacVRHNnoxQkxram5jcG9UR3NtNnhDZ2lwMlluMTZFWm1Ya1JlYzlOeldjWWNEa29DNVBLTVU3MmEyRzlkajYwVllYUGN6WWlobHhvSGh6MHV1OFBvdHlwTFp2eVA3bWsyMFY2cXpYYjYzN1Vzc1VyNW04enJKYlFKaWVtWnUzbWNIMm91MDlwUVliNTloZ3pXek02bkc1Ym55b19oc2dMSWpteGNWTi1sZXJqcE5IZ1hqNm1IbWdPVExQTThKaDNNR00xNDJ0cC1jLVhCSFNDZE5jcmtIRC1YOUdkNmtYb3lFeFBCTU9HNzVOc3B0dWppaWVPN1dUTEpxOWNRLWFJeHRUdHJlQmtyUERqUFZ0eFlHTlZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOeDllTFlyOEU2ZC0xYTBsUThIdDdJeG9mQkFPSkIzcFE4QnB4NV9sOWdkbEVxRktPSnVvc1IwSk1vVDU4dFg2NDU4Y04td3BjMEtUTDRlN0MxWm9NRml1cjlJVGJwUDZERkxDMFZFMXEzV29kUzdLc1l6dXhjWE5reE9CMGNtV1g4S1hNMzhzTlZHRng1eVQ4X25VaUNibW9hQ2tXNC0yTQ?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46017.51560185185</v>
+        <v>46017.70924768518</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What goes on during an Amazon warehouse tour? Retail goliath lets tourists inside its vast UK hubs - MSN</t>
+          <t>Burberry Group (OTCMKTS:BURBY) Stock Price Down 0.1% - What's Next? - MarketBeat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:49:01 GMT</t>
+          <t>Sat, 27 Dec 2025 05:17:10 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQQ0t5aFc0aU0yOGoxNmlRenVielFNSUFVZFJTTlJBdGZxNE55UUxQRG9zZ0VPelBuX013NzhFNWtZQzVlZk5ZaXpiSm1PY0pWU2VkNWFaUUhHRGIteVBWVE5IWkQ4TmFMOGs3d2ZkalNDa0pnZWNZOEpmaHRCYnJHbFdPZy1lQnZEOUFvVWhYcjN0eGxYSHZtWFNpVGM3NXp1Z2lUbGFsM2V3cUtrb296RWZiZnRrOEJ5R3RLZTBTaFh4RTR2SXc1UmpJaHZvZ2w5M2hZT1pkWjNPaDl4NktJMDhDb044eVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2MtTzkyaVR1aTcwWlFBWUowSU5FaHh3WkxmMlVVdGtoWXpnRm9Ea1ZrSnowNzJqQmRHS19NcWlVNVhSZHlscGFnVWNrUDVsZXllMUlOVEZhM1R3T3J3RFJhR2lNNlZuVkV6b1NuaXY2c3gxM1VsY1JqcnVfR2NsWG1Fcll1RnFIblhEVlBfaElTa1Rwd3BjeDRfS1gxTFAycEs2SU0xc1NNQmF2Y0d1V2dR?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46017.40903935185</v>
+        <v>46018.22025462963</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Where will UPS stock be in 1 year? - MSN</t>
+          <t>Beijing Flagship Architecture - Trend Hunter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 08:26:29 GMT</t>
+          <t>Fri, 26 Dec 2025 20:49:22 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxObC15dlZtSzZmdXlpMDdMSnQyOVFQcjJuSzdUQVZmdVlUOUF3ZmQwb3pDWDYyc20zRUtzS3hyaTJ1eXBHUXJpSWk1U1RfTEtNNnZkNWIzLUw3NnR4ZEhSRDQ3d09qMGVKSDNkR0ZzZGEycGpmdERvZ0IzWGMzZVdPNXJEWm9UOER2ZW5GUWJucWpyQ3FWVHpaLTVKc0FZTXBiZXU4NTExbWMtYXNpcWRQMWxDOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE52SzhSZThLRHgyTlQ2VGF2N0RKWE1KMWlZS2UwR2pVdVNjT3lZZDZuTWVELTdmWHp2U2x2YjhqSW52ekV5aEpkS29NM3J1RGdOSk1mandqUWJycFl0V2FybzluR29oR3Bt0gFuQVVfeXFMUEgwR0JRb00yM2lfSmRvR3pTV2luN3NEQ1dwX2UzeTZYNVh0LTRBMjdESUtyS2pQdjdlV0xtYTd6TEJJdXZJQUloMS1aSVRBVVJLbXpjVlFGSENFTXNxdU1XZm8ya3pxbkhkVF9XaHc?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46017.35172453704</v>
+        <v>46017.86761574074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Amazon Christmas party video full of Indian employees sparks racist comments - India Today</t>
+          <t>A study in effortless elegance with the Louis Vuitton Tambour - senatus.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:00:45 GMT</t>
+          <t>Fri, 26 Dec 2025 15:48:20 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxON1VTeXdaamtEVXJaUW1xQ3FYVV8xbE9LbkdTWC1GR1BXc0RCN2hUZEJCVGRlMXRUQkFTYXgxaVh0bmg0Mk1rb3psT3Nhc1djVWhnQ2pva3JwWEpNMndyQ0lsX3E1bmx6aURqVHRYazRjWEdzT0dJRzE4dUZsWURRcGdud21tSGpWUE91Z1VSUkVlN2JSUkNKd2RZY2FVeTVzSjVZY3ZRNmtqRWNJcFlzZ2FlSy1WckdaQ2IxSTZ4Yk0wbWI1bVAzNk5ESmVObUF5NTJENDV0bzhjV0XSAeABQVVfeXFMTWE1MlhUMWpqVVVDMW9uX3drOVppYXlkNTNNVEVPZUt4eWRIZEp5UEtyRE5vRjlFbVVSbGh3RTlvTnVSSDNBYnFnVkFZbkpEeUs0WGZ6QXlaMmVTQUxKQVYxU2xyLXlKellFS0djYnlXeTJkTVJQZDVyeElfcEJSdnFFcVpCMkhtZVJTZ1FiV1JxNXhwZDFlWkhhUnIxYXpxZDdxUm1qYlRwd2VpOGRRZmh2a21PQ2lTYlBhdGpiSHhwaWEzV2ZxTW5FZTFDTi1MRUVSYkJXT1pGWGVSZHZORW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9HSmVBaWdrcnVoeGppVGQ4SU1kS0tUN2tsajdPNU0wc3B3MVZ5YkJmTzFERDgtdWZ3aXpaSENuX3BIcmpwVUQxWVpqUmhoTUVGNXhQVlM2cHE0OWFtaW15ckpGazBqWGItMHVPeUlYaG5SSlZFdzRfU3l4d013S1k?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46017.37552083333</v>
+        <v>46017.65856481482</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trump just declared December 26th a national holiday. What’s open and closed? - Fortune</t>
+          <t>B&amp;M European Value Retail S.A. (LON:BME) Given Average Rating of “Moderate Buy” by Analysts - Defense World</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:00:00 GMT</t>
+          <t>Sat, 27 Dec 2025 06:45:44 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPRTA3SUEtOGtTS0dhSHFOVWJ2aUNJNjU1RlJOQzNfeENZRE9JM1pLdnNFWDJaWjZKYm0td3NwWWdrYWJrdXBnanEycHNUQk1QQUE1c2MzR3lqbHZUbDRVYng4VjNKUGRNSmc3NzV3czQ2QVUyQWVvUjRFWk5YVkRNd2dHbjFURXdsX3JtSEdSeDlHZDhWNWd0Z2U5QnllOTZZNkFBQ0FRZWY5clJ4NFFHejZyYXk4TmxJcEJTR0Uwbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQUjYyTEFndFQ4MkFWcHBKczNTTXk3UGthZkc3VVY2Wmtua2Q0aXVPY1V0ekFOU1hhYzRneWV4dTdWOEhFZllEX3Brd0J0blZMMS1TV0d0UkxJQnJkOUtrbDMzeGhKVEl6aExJLWZ6Nm9VdUtoSmdmTWk1TkUtN1V4NjJMQVl1al9scW9Lb01Pa2s2Rm52ZlRSN2REQTNOc3JVVkxpN0FCN3dWYll0ZnZGNGZXSGtlcDRWMXdEMkRLOU95T19yc0Y0OA?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46017.45833333334</v>
+        <v>46018.28175925926</v>
       </c>
     </row>
     <row r="18">
@@ -1010,1212 +1010,3291 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FedEx: E-commerce Festivals Drive Strong Holiday Sales Outlook - Wazzup.PH</t>
+          <t>Amazon reportedly lays off over 150 delivery drivers, union claims it's illegal - Mashable</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 12:17:15 GMT</t>
+          <t>Fri, 26 Dec 2025 23:00:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOVmU2TmRfNkRRNFNnUC1FbmpBaFJIU2FXdFNMNHh0TGtaRnRxZW16ZWQ5MVVJYWQteHRtS000Mzl4eTZCN1NXOURHZ3hNMlZ5M0daZUN2TW5nM2Myc1h3THJNOGU4WlJ3SWZhUXpTY1RvcU00dUZ0dmFlZDZqZDg5T0ZjYVhqYXVTWk9WYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5zdW82U1NvbC1WS3hCb21MbWNTa0ZfZnI0UW9kcXpVTjdLY1RFY3lCRmh2UzBWT3FCdTQ5OGtIQUh4RzVOWFZfcHlHOVpSbFllQWpZSGVwdmRmcHJyMkxEcW9EZHdCLUhDOE4wNXRHcUxwX1E?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46017.51197916667</v>
+        <v>46017.95833333334</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Five killed in mosque bombing in Syria's Homs - thenationalnews.com</t>
+          <t>Unusual Amazon misdelivery, Reddit user reports massive oversupply of PCIe 5.0 SSDs - igor´sLAB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:16:55 GMT</t>
+          <t>Sat, 27 Dec 2025 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPbFRZemhHT0ZURzhaZUEyZktRTDEzMDZqM3R6QnNicVVCUEhXODZNc0kybUluLWZYTEY5N0lDQVNMQWszYTE5X1Nfb0JhRkVxeFBmejI3WTZtV1lmeldXOW5XZFByakU3UFlpbXp1UVZnT0ZtSGZQaWdvVVdYbG5WR3pSSkE2Q3RBV0Q4X3FVcjIyaGlmTnFWUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPSEZYZ1MzMWZ6SjZOM1NmdWtDdVRlLURfMzl5dURiY1BwOXJEWHRRRVYxMFVNT0duOUZwNUh0XzVSdldyMDBMVURhQVRQVFhpZUh4aU9CQ2FVRGZuRWlzbXRORVhSemphLUhCSEt5bDItNlZScFBqRDZLcmhzTjE2VHI2Y0tUdUtTbTQyaXo1ek9BbjRKSUVLajE2LWhtNVFZaV92Ri1SaVlfazlNRkE1RS1scw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46017.47008101852</v>
+        <v>46018.20833333334</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Momentum Traders Eye Electronics Mart India Limited for Quick Bounce - Price Gap Trading Strategies &amp; Master Stock Selection - Bollywood Helpline</t>
+          <t>Man fired shotgun at Amazon delivery driver who mistakenly pulled into his driveway with her teenage son in the car: Police - MSN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:12:04 GMT</t>
+          <t>Sat, 27 Dec 2025 03:23:21 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQSnZuREYtdGc1X2NBa2JnN0lnb1RrQkV6SUozY2JIa1JYSml2SFM3SlZzYVJlU2hDb0pyblUwUm9TOG5FQUNHRVdLNTVxV2dKcjFTQ0g4SFR6aVU4NEprak5YN1ZmcGJtT0VoM2VHRVZrWXh2bENoMHE1N0gyNVl6ZEY2WEJtc2RqalNOMFdrbm9hbGdiV3pvdmZwQ3B2R2hReUxybWlMM1VITWZTejhIVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxNZzlvb2laUEZPX2wyWlNoZ0VLaWlreFQ5SHNPVS1Cb2dHRUNVckE4ZzZ0YlRlLUNVcktCWW5MMXdBN3JwaXRRWldIRVZtYzV4ZVgxYWJ6b05LOHpZZkd4WEZoSVc3Vk9FZF9jVU9tVWxIUW5CODNqRG1sMFl1dGdfbzFad3BwWDFaOGNGYnVzQjhKWV9DQmc0ZHZNYVE2Z083QTkwZVZTVXhjWkNfQlpweFZlc1l0VjRsMTdYeTlTallvejZzdEhQeElVQWp5dVg0TVFPTlU1eWNxSERhX1pvcUdKTGRzQndIWjFYdUp1aGx0Uy00SnhxaU1pVW5sUjFyenZZR1E5QVU2dk4zLUtmS1hQOG5Mcm51NFZkaA?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46017.46671296296</v>
+        <v>46018.14121527778</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Will Tarmat Limited Reverse From Oversold Conditions - Chart Pattern Recognition &amp; Build Winning Strategies With Zero Cost - Bollywood Helpline</t>
+          <t>DPD apology after delivery van hits man's car - AOL.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:36:46 GMT</t>
+          <t>Fri, 26 Dec 2025 21:13:41 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNYml4N25wV3U0SnJITlVaREJZLVBhZC04SDVrd255cWtNcEZWMEtVYm90dHRnZlVqdTlyS1k3OWs0cmRKeU5zM095YWxIWjRYa3djamgxbGkzNWMwQTJIaWc5RzdqTWZqT0ZIOXhYbktzb0lIOUF6S3pWUzRzVzB0ZERJV2ZyS294bjBBY3l0X3A4VjNiTzVObTA2TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPZzBPbk1kM25LV0FwWjhTaC1GZmtsS3RnM0FyQWNzT2dwV1NRd1FpNkNzOHVmVjNybTFGc3Rta1lxOThlM1dPTXZQb2hMaHJ3NXhiTVhzLVM2Mkc4TGdENzZpdlR3Z2sxYjhEd2U4UUxRRFhvQzZDS3d3OEl0M2h6X0c2WQ?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46017.40053240741</v>
+        <v>46017.88450231482</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Crime is down, patrols are up - how local police teams have been transforming key areas of Grimsby - Grimsby Live</t>
+          <t>Scrapyard worker injured in UPS plane crash dies on Christmas, raising deaths to 15 - Scripps News</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 13:54:00 GMT</t>
+          <t>Fri, 26 Dec 2025 17:24:21 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQQk1kX051aEg0clV4Q01KdjJiNHN2UWZ1dEdhNExKRmxHaUJmNmNnaEFVYkZBeVpGRFZzejVXYWY1Tm8ySHNYb2RpZlFwQjc4bEs4ZXNQWG9Ud2h5UC1XNDhNbkVjZjd3cWFxZU9hUTNVYXhSYk1nT29zbFZMNlo3VmNmVy1vZ0V3RUtFRHgtR0PSAZYBQVVfeXFMTkh5blFldWNzQy14QkhnUWVjTHZTb0szb0FnTWNYLTdzdjFxdzdfY2FPcHJFc0J2b0NqV2l0dWRuR1ByWEY3Skx4SzJYd0ppWTVVMGtMVUpQbmtJRExRNzRVZjRxN2huVURGSV8wamlTdGc5QkM3Tk8yaXdydFpJemNvTl9ud0IzQzdHYlBpakp6RThtR0p3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNTnNiU3Foc3lEM1pvSmt4QUxORlJsTmpfUDBRR2dKQjh2dE1NN2xKWHVRUGNQd2Z1bDRleUk3Qlg4UVRsQzNZZFNBUnB4WFpYTmE4aGF6THBnNlRBRmFyNXdTaXhvTzR0SjJvekVIeHplZV9ER3gxbk54TmZmTGNNakJLUFFhS2VKb2JtYVFwRU1za0RmYnNMLTU3bVNiV2w2cnl5UlIzRkNpQnhnRjBmQ05XS3paSUFKTmc?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46017.57916666667</v>
+        <v>46017.72524305555</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NSLC sees another sharp increase in thefts from stores - CBC</t>
+          <t>Inside Amazon’s Big Bets: Leading on Climate and Delivery - WCBE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:00:00 GMT</t>
+          <t>Fri, 26 Dec 2025 17:12:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPUTVIUC0zMHFCemwwaUlveEcwRFU0clJPRVE3WW1MbS1QbGNVd3BhcGphX0Y2V1M3VFJsUUdIaHFPRUVKV0tiS2wxVUd6dHRLX3JWZXZhWVdVRy1nUktBSXRyRXY2N3U2UjZVX1JDbTBfZnJhMmpJUnE4Q05kczRWU3hhUFhWQWZOSFptZFNiemZIWnR0Z2ZUWXhwTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQdmtxNF9xdHE1VFFuLTB5dFp1ajZmZExidUdLRzJDLWNyQngyQl9uMTFkRVpjUTFpZV9tR2VWYmlxWVhwTXlVOE9IUnZ5dUpmeXR4RnFobWVndmxIT05jc0ZwUGJqdXVuTWxGV1FnNmRfb1BCQjRSZUh0d2ZZdTgwQWxnMnVCcy1NMllsUWp5QS1LNnJ2bU93QzROREJCOTJ4QjRlLTBHczNxNmM3Q1ZUTjlaYjRoZlBJY3JiemQ5RVVHQmk2NXIzWkstMUU3Rnk4blBfckZZcw?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46017.41666666666</v>
+        <v>46017.71666666667</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The best concerts in Madrid in February 2026: from Judeline to Nathy Peluso passing by Ángeles Toledano or Austra - Madrid Secreto</t>
+          <t>Amazon Stock Today (AMZN): Price Action, AWS AI Shake‑Up, OpenAI Talks, Analyst Targets—and What Investors Are Watching on Dec. 26, 2025 - ts2.tech</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:03:54 GMT</t>
+          <t>Fri, 26 Dec 2025 18:09:29 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE01X0Z5UXNfMlhlQldidnItejZRMDRHWG9JWHFvMGJfY193M0FZcEY0Tk1CTnRzY2swOTgtUGREZXJUTTdBY2VDM1U2c0p4YmVCZDdvMnBodkdJSnpyaHBscFExcHR0TkUwQjJ4Z0NMbWhnMlBHbElqTVgtTEhmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNYmZYc05pbzlBb2hUVzdYWFVGY1phd1E3TE5tel9tQ1NFZVJvdGRraThkcnYzQ3lTakpSQ2ctMklPZzBLS3dQX29rZnNIN1ZPOEJLSVhLdzdZYS01NXhTXzJnaEV4ZzhCSjJGRmNEdlpYQjE5S2dKdEk0STF2cU01ck85UEJ4ajY2dW1FVG5GYmpsOFd1a1Rua0c4OVRGLTR5RzdPR3FnOTdoekVTdW5mZVZnQS1qVnR2LUVqbmhSLWI1RldMNThDLVNjUkZFWGNjOW51MDJRRTlMYkE2cW1DWUJqMA?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46017.37770833333</v>
+        <v>46017.75658564815</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bollinger Bands Expand on Infollion Research Services Limited — Volatility Ahead - Retail Investor Activity &amp; Explosive Capital Growth - Bollywood Helpline</t>
+          <t>How to cancel your Amazon Prime membership - Mashable</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 13:10:17 GMT</t>
+          <t>Sat, 27 Dec 2025 04:31:02 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZFZJN3FpYWlraWxJd3JFd3VnT3dzZkt1ajlRb2I0TnFPZEhHMWxvVFd3eGlSUUNKdG4zTko1LWNWVjZRbUpoWFVmNVNtQkJWRUhZd09pdXNYUGdqSlgxeDNpb1ZaelkxTUFrbG1RdmZVYVNpMmdqb3FjOTFyOE1aY253ZGxmMHFuV01BQzdOeGNIaElzeXZzYWh4cDlSVlFZWnlyeGIwX01lZEk4NXRZdE9MVEZQWWl1Mkk1dzZmNzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5ic1V0VkFGNTNfbXBMWXQ3Q1cyNXZXMHdaRmJDZTRKakF3VWJid1M4VkNMcEJ3dnFzb0lvSmlmWE9ZdTNfa01qRUJrVHpxT1lVTkVoYlg0cjJsRU5RNkFMU1drQjBiQQ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46017.54880787037</v>
+        <v>46018.18821759259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cooper Flagg gets a Christmas Day lesson from Stephen Curry - Mundo Deportivo</t>
+          <t>Delivery workers haul more NYC packages than Santa Claus - Gothamist</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 08:47:28 GMT</t>
+          <t>Fri, 26 Dec 2025 15:01:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNRUl0Y2R3dzJ6TUhFUFpZX21WSUdVVGRLb2ZhemhqMVFial9MbUZPMTB2VzBQVzhNdnM5TjR1elNTSnRXTTY5RXdCcUpneEdvS1VWUno0OFVfOUlUZ1oxOGlCQTVMcjcxd0U5SVNnc3FycDI2MXMzcjI0MXNaOTVmUUVJUWM4TjFNQWNyZURxMFZWdXU3RG1oOGl5WENqZEJqdVBBaTM1ZUVkYlktdzJieTFHNlFqR0lrSy1OMWp0SXRrWDDSAcMBQVVfeXFMTUVJdGNkd3cyek1IRVBaWV9tVklHVVRkS29mYXpoajFRYmpfTG1GTzEwdlcwUFc4TXZzOU40dXpTU0p0V002OUV3QnFKZ3hHb0tVVlJ6NDhVXzlJVGdaMThpQkE1THI3MXdFOUlTZ3NxcnAyNjFzM3IyNDFzWjk1ZlFFSVFjOE4xTUFjcmVEcTBWVnV1N0RtaDhpeVhDamRCanVQQWkzNWVFZGJZLXcyYnkxRzZRakdJa0stTjFqdEl0a1gw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNWjNPblZNVEJ6LVQta21YU1BWamE1NlhzdzhWY1BtVzkxZmJLTDFMNHFkQXlzY2ZGWlQ4ZDN4YjJ3dkZVaEs5aUJ0WHlIYmRlanVralJGaGRLRHJRZ2ZPYnMtLV9ldmpldWFnUmZEQkx0a1E3TjQwUDZ6M0k5b2xzNDMxaWM1LXRKOVpj?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46017.3662962963</v>
+        <v>46017.62569444445</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Real Madrid ready official Vini Jr announcement as Man Utd and Chelsea make €100m bids - FootballTransfers.com</t>
+          <t>Indian-origin CEO faces heat as surge in FedEx H-1B hiring sparks outrage, 'They are now awful' - MSN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:13:00 GMT</t>
+          <t>Sat, 27 Dec 2025 05:23:26 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNNmV6MTVsQ1pFaTNMeDFNMEtfNEZ0R05tZUdlX2xVODE0N1p5SDR4em10XzFua0d3OWh1UWtMdGwyUWJFMVJCQmI0YmQtbHZrV3hNanhHa19vbldWUVZtVVdfREFHVkcycmQ1dTdqUUNVVGJDSS1GakJmc0lSQndJcFhraFhPRmJseE1hQ3p0bXNRQ3JGc0ZxQVZlblpndWVVWE1ZNGw2eW9DT1dtbE5vSkdyM1E1VW1QalJNT29GNTJHdGtDRk56N1EyUzFiY3J1blNBX25mdnZ0SlFuZ0plVmN0cXFDQkdjNmVNWWhqbnpQY3l5RmJsU3NqdXQ1Rk5uWkJZR3U3clpBUms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwNBVV95cUxQUHIxRWU5amZucXRMc3ZZSTRLQmJ5WlpMSk1jUWxqQ0F4SDhwUkdqZ1BGdFhNbWgwekl1MTBKa3pxMkhWOF84WUs2ZzRkZkNOdEVpNkFvR0F6U0c4djZvQzN3LXZuNktsYlJuUjc4NmYtNVI5R3F2NW5Sd3lHRWxuRkFZb05QcEJYVW1tTEttV2Z3OTg5ZDRYWjRKSUdQUWwwX3JmbWVVNW9VT2pzanptVGthZEl2Mjc4SlRmXzdmTHhCZnRZaEh1U2tTU1ZJUUVMVktPS0pGVXdDRVM3aWNPTFk1MkhnLW1zd0lKanJ0V1c5RUZ4d1JlMGRHOUNFTE1oZWh6ejlyaXJPdDlSMDVybDlJUTl3SURfUGo0S3NhMVRNRzA0V1FVNHRfdXpaTkNjSGZlOGdXNl9mQVk0Ml91OUU0NUFUTmZIZlNyMEg1Y210Rkd6amRhYWRoUUctMUFoT1dPRzItaExMUVhyczBxZ2x1c3gxUWNMNl9RLTVkVzg3NUloVWJqNGpRVQ?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46017.38402777778</v>
+        <v>46018.22460648148</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How you view the companies who do not give information about subsidiaries in each quarters - High Beta Stocks &amp; Free Superior Stock Performance - Bollywood Helpline</t>
+          <t>Amazon says they’ve fired driver after video of her peeing and pooping outside of homes goes viral - AOL.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:16:05 GMT</t>
+          <t>Sat, 27 Dec 2025 04:26:48 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTnIxdFMzdU1UeERrVEt1Q3ZXYUVBTHJEbC12ZHZURERpSlA1ZF9uRm5KcExJTURka2oyMDlxOFVKOEVEZVpIeVl6RGVsMUoxb0hXYnhneVpHQ3MyU2tSbmx3VjdCTTlEeEZ3Zml0ZHhHUUVQWXp6VHA3WGlTNTF2S3E1R2ZYS2FHTFc3ckpDOEExbVltdEFwcnhyXzVoLUswSTc5dVZoaGtUWllRdE9iNEV3QUlJTnRFZExpdUs3RGhVMVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE85ZE8wNnhQWWJESTVRWWMxcGhBeW93bzlab3A0SEpGbUk5b2RyODRndC1LRmxIVFZRSG5NYWtoYVFoblk5SVpPdmFnMHJudVBCdzJZeUNrVk9nR0dWQmtFVW9SaTdoams0Xzg0SkpRMA?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46017.46950231482</v>
+        <v>46018.18527777777</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boxing Day traffic chaos as shoppers queue at designer shopping outlet - Oxford Mail</t>
+          <t>Nationwide, Santander, Royal Mail and Evri customers given £757 warning - Manchester Evening News</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:32:00 GMT</t>
+          <t>Fri, 26 Dec 2025 15:43:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNc2FUX2tqaTdHdjdBZVJGZGZfY0dqSHZkRzhNbFhWNndpdkZpVmp6N3lOU3V3d01zYnRLX2NkVmp3cjJmay1VeE80SzdNVjJzN1VJV2lhV3ZOZ0YzU1JrTlJJQWVXNWFHMUozQW45SnVoZTB6UWFyU2MtalUwVmlLWTZJeFl3aE9UaDNyYWdUSHFDYU1tZlZ5NGFsLUYwZEUyQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPU290Q0hGQzVzZkRfVm40Tk8zSWhhZGprcFBOb25qaTRFNnlHdzBIQ1pDQ0Q2Z21MMkpVdV9vcUJCX0htNlIzY09CTDZUTEQ5MTdkTUZNMV9PN2lLZ1o3alRsdkQ5NXNkQ2lHN3BJWnhZWXo2YlZtNEpGRktURGZUd2hJTV8yOEQ5Z3FraUNPS0tlY0VzbEU2dlVpUkxIZEREWG9Na3ZmRTbSAa4BQVVfeXFMUGM1UDh6WVRBeWhtdm5PUTc1bkhkby1IU29Kb056S05kWWtFaEZ4TGR0MWVDNWVKRW4yNHV2UXNGcFJ0MURDblk0Yk5jdFZlcFU2MkZGbFcxcUxyYmdOM3d0RFZjY2xNTzVSX1NHbkdsYjU4S0ktMnBWY3loOGlkQWpnT2UyTXREa0dvV1ROcDF5ejlJZV9qTDBRSFJuSDlnNWh0Z3h1VWpzZkxJY2NB?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46017.48055555556</v>
+        <v>46017.65486111111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Man charged following fatal stabbing in Kilburn - Times Series</t>
+          <t>Amazon MGM releases first teaser trailer for 'Madden' - kare11.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:44:49 GMT</t>
+          <t>Fri, 26 Dec 2025 16:56:46 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbnlXaEFXWU5rSlN0c1RzbmNHcUdnYjBTNWw2d2QzQmVBZUVMRENfdEROczF3OE9pQU9GVnhLMFYwNkg5ZnF3XzJZSkMxd0VSN2liVjg1Yi1WUEdfWXJyTUd4blotcF9wUHB1YncyZUZ1X1RjdUlVbXYxTVU3NWF6dTFjZTFtU1RVbzZnWjRHOXVzRTRxX2pvMHlOQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPSWVuLUNTNzg2LXZpdndfcGN0dmUwS3ZSYkVGSUhwaXdHX0kwY1luOW1BWHRBOHdFaklwazlMSzVjeWN2R1dfMlN6UDl6dG9JejN0NEFLcVdMaFZ2UW13aTlvVFF2WEVXUlhqUjhyVFlKRFpiOWw0cGUtUWF6RmxxRmdLX09VSUtJRzVEZmk0c2tVbGE4VWtsZVByQ3dvQWJGZ0Q3eDRWcTZ1WmhIQUZVRTZyaF9MTDZFbHFOampseDFpZ1ljUU9pNXcwQ1VocjluNXc?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46017.44778935185</v>
+        <v>46017.70608796296</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kent woman in her 20s dies in London-bound M2 crash on Christmas Eve - london-now.co.uk</t>
+          <t>Texas FedEx Driver Says Familys Dog Attacked Her: The Last Thing I Want to do is Call Animal Control - Patch</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:42:41 GMT</t>
+          <t>Fri, 26 Dec 2025 23:02:38 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPeFVidEFqMWJnM2w1TzFDQUNERXg3ZHg0X1NadGp4dlZ6UXBGZENkeEdJeWNmejNxNVFyUnJMa1EtMlF4aEtacmNTMkVid0o3Y2o1LXNSREtLcDZlbnJGaXh3OEtTeXNqLW5rSDBqdTZWNUUyaHlKYmotVmNxQk1lUV9iY1Z3ZC0yd0NLRGZyNWUxRlQyRUJJZk1XSW1CSUZuU1Vz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQY3ZhT0JpN0NkLWY2T2pzTVVRN1k2REE0ampFaHc4eS0zOWpNcjgyZTVZdnhiTWllUDRueHlGOUx6WXkyZFpZWUdOU21FdG5UWWdKRlVsRXUwX1pIWkNueXc5NFA5WXBwQnRQNmNnZUV0bDJJWi1PYi1ueGVwSl9XSmxob0c1ZDFfQlZ0aXl6bi1iZ1d2UVhRbm9sWm5QVW0zLVBLU0tFV3VTcEVObF9oSTRjRXpyNEHSAeABQVVfeXFMUEU4QUhMT19HUjlpdERzMFd0bGFZaTdhMTFoU3lHUTlvU2RTanJYSEI3RDk0Ml9xWXNRdXNhQW9vbS1yOXBCRFBzT21wTXRFMGg2empUT3FDZXlNclIydW0xTnZiT1h6MHhSVXdFZDlsa3JOdWxzMTlfNWtlYzRGUl9BX0JvR3hORkt5VjRSaG1aVnl1RFh5OGg4NWZTUERjSk9wa3hmZ2FLeUctMjl5RUJSU1BmX0wtTW1WMHBoNXVETVdaMll5a3VXclJMYnRzR1hyQnIxNDRORTRENVY3ZW8?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46017.48797453703</v>
+        <v>46017.96016203704</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The exact number of fines TfL issued fare evaders in 2025 - My London</t>
+          <t>USPS plans to expand, and Amazon doesn't like it - MSN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 12:08:43 GMT</t>
+          <t>Fri, 26 Dec 2025 22:52:15 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxORzFzWHZsZjZ3LUliN1pnRWhLYzZHSEtETlctRENnTjBhNjc2SWc0N1ZVbFczNUFkX3JDRHZ1SVk5cTU2RzJyT2dHT3dodEI5Xzk4WHdyX3dGRE5RcjdOLUpvdVFHdE1lMXNIdWNyR3M4TUx2RnRtMW8tTmhpTzh5SDhzcVJoZ9IBiwFBVV95cUxQZFhDZ0lqclFkX0pwOEZJeE03cm81WHVuY2hEYjVJalZoVTJXNmFYd3NEU3NOTGpfa0s4Qzh6RHZfTlBjWUF4djhwcGVGdGREbEk2YWFvUGJtVkZBVzluOTZLSnJZTmVSaXJucFozaUR6LU52NVZvRTJEX2NvSVItaXBIWWxiQmVDZjgw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUU5mVjBrcGVwVmI3RHhqMkVvSXc3N2luY3VNNWlqeVpwSlZpa205dXNEdnpKREpqbnIxMEpYWmI2YXJfeE5DUVlZOHdGM1Q2MzlWME4xY284S0NhX0RnV19rN29jc0M1bHQyMUdzNlpuY0pnZm8yUUp3OUtrTWN0N0RPeHl2S3F2OUNlWE5ldnZrYnRCeTA1M0FCMVd0U1dKYUQ2ZzNRZWJHVEVMS3pfNHI4cnk0bTFQdlp4Ml9ZTDJaOVViUkE?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46017.50605324074</v>
+        <v>46017.95295138889</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5 top tips to get rid of Christmas clutter and maximise storage according to experts - My London</t>
+          <t>PBM Polytex Limited (514087) to Launch New Product Line - Stochastic Oscillator Alerts &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:18:36 GMT</t>
+          <t>Sat, 27 Dec 2025 06:51:48 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE8yQkZoU2RHTjhia3JQRzVibHBwa1R4dkt6T0g5Q1pzTlo3Z1k4WE1EcWREd2NQX1Jrd0xTZGo4VlBxTUxzSC00a3U3TG9kYTBlbDkzVUtRTmV6TVJTSUtxVnpHeVBnS2J1dFpJOGg5bjJlaW56bHJRa9IBfkFVX3lxTE96TkJJalQyYTNFLWVLY2NiU3prU2VRc1M1X1pzdUtSYW1KV0tHVHlhNlJadWZlRkV5bVFPaG5vQzlLS25uUGt6bHVra2JPdjNWU05feEd6ZVVYdGlvMlo2cGRRa3JRaVBsZzByci1EQk81SHoxbGthUzdRNFVFUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNTWRpa2lSSGZhYkZGU2VsenB4YXhlQngybFdQR2dqYVUtZ3pWYmljM2ZNclVDMFJLVFZabmIxbHFZNUVya1lDSzJNU2dpOWZGYkRLWFJtcHFxa3pEZnRFU1hIVE9CN0plcEphQXFXcEhNdktkamM5dmFmczJLUy1oVU5xQTNYb3pkaG4yclp4ZmlYS0F5?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46017.38791666667</v>
+        <v>46018.28597222222</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shizuoka factory reports "stabbing with a bladed weapon" — 14 injured, suspect apprehended by police - reports - news.cgtn.com</t>
+          <t>Atal Realtech Limited’s Price Action Aligns with Quant Signals - Bollinger Bands Signals &amp; Free Unlock Hidden Market Opportunities - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:27:30 GMT</t>
+          <t>Sat, 27 Dec 2025 05:51:25 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBnSG5yTTZJekIwSXNCYUpHMjRKN1JRSmdfbFFsUDhvSkx4TWMzWnR2d0p0NE1zLUV4YXp1SkpUekVUdmlEckk4SV9PSmdBa2JReVdkSlV1ZmFEdnZmYkVoWGIyOWtVeGNmSkwwVExB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPLVFoOWJER1Z4bEI3ZWNvWTV4QktjNzRTTGIteURVUWM2ZTlNREh5YnBwSVB4VE9zMDZWX2pHZ2NKSnhKYTNZR2h2aHpOT24wWmhZTDFVRThWV0thaUd5dnNPSkY1VF9CUURYNXZSSDZlV21rV3M2RklkWnJ0UU1rS2ctZDJSeHF5WFZmZjlKRi1yV3h4ZlgtX3hPdHpBRGo0MDllTXI3emFnNlU1OWZjcEo1bw?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46017.39409722222</v>
+        <v>46018.24403935186</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hundreds of northwest London arrests made as crime drops in 2025 - london-now.co.uk</t>
+          <t>Tamilnadu Telecommunications Limited (TNTELE) to Launch New Product Line - Long-Term Investment Plans &amp; Interactive Charts for Smarter Trading - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:17:11 GMT</t>
+          <t>Sat, 27 Dec 2025 02:35:21 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPbVNzQ0s2dVJINTduQklxcFhyWE5wNmRPZVVhZlB3aVFUTmRhZC1NLXpkUzRiOEhSX3dJRDJmQnVxVm9GZ1M0cDV6R1E3M1Qyck85X1hGUmtHYnJ6dXN3OFFyZ1ZXRkE4azFiYUtIS3BpWnJ4ZzhzUEhSaDl4WjU5RWZmMzlocGo4UUpMb3JsRVFUNVI5aXBYT2pueGpBczdUdlg4YQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNMlZnZDVhM0xNMXVHLW5aVXJKUk1ESV9JaDd6WHlZeVZfUUdPNHptRzhFOUJTbi1kbktDZVNmMi1zUHpsT2VpUWJlZjRCVDZRd2lzRTQ0MGx2M1VBNUNodkdLN25sRmFiRm4tX0lZemhWeEVTOV9tVjhsZktOSEw0aERvdktHMkVEeWtzdlB4TzJfZndvQy0tZFk1M1lVaU9Ec0x2TDJDR2gwb0U?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46017.42859953704</v>
+        <v>46018.10788194444</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rutherford Co. 'has seen too much tragedy' with 3 juveniles charged in 3 deaths - The Tennessean</t>
+          <t>Published on: 2025-12-26 21:32:21 - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:04:00 GMT</t>
+          <t>Fri, 26 Dec 2025 16:03:06 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxORm5KazM1TV92eW5NWXBvOXdLOFU5NzlHMWFzUU1rd0N0WHd1MjdVampHb3ZYTDl4TGRlbkpWOHlVd2t6SlVSU3lzNEdGdjhmdzlLX2ttLWVrTUlBejVMUF9Ba011T216X3Z2SWd6MFBtd0ptSEpLcHNidEptTl9vZmczck5Lb3NROUJhSVo2RENfSmhFLU1EaUliTFNGNGc2OHA3LVFzeEhLbDFxUkxUVjVZT3lYQnhPd1BLTnlfdDlNc0MtSEFpSi01RmFfaFBXeXFCRzloVnF6Mm9wUEhudERjdThLUHJF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOWE1zYmJBMkZUbnNwWFNMdGpNQVVEeW1NS2VxYUZDVDFMb182NFF4T29ON1RfajJIazBTTVhvNWpJQ1hYRk1OZGNseHVtSkc0STNqb0gzcG1aTE16a2dMa3VPX1hVOE5kV096RUMzcU9lQkU1WUJQYmhXeHdFVW5teGdSV2s4OEFTT0RiT0RYRFg2OGJKZlctY2FEWTQybXJQVnc?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46017.41944444444</v>
+        <v>46017.66881944444</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mysterious Spray, Stabbing Attack Leaves 14 Injured At A Factory In Japan - ABP Live English</t>
+          <t>Cologne legend Overath believes El Mala can make the leap into the World Cup squad: ‘You're never too young! - Tribuna.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:12:40 GMT</t>
+          <t>Sat, 27 Dec 2025 06:57:54 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVDk5SlZwaVUyT2ZtSHRCNXFaUFRtMWZ4cm5RM3p1M3QtRHE5RUhEaFZVczlvemxTRW1vU3FITFo2SXJUTmQ1aTdXeWlubWdyTkFIWGNScEg0NHd0T2V2Zk5kS3NBTjBvSjFyT1FZWUNTZHFGQ0x0ZVRVOVVkUkJWRW83M19pZmVmSlgwSHRjSlVYdkxBQjBfbFlhOWhPam1JUm0yU0h30gGmAUFVX3lxTE9UOTlKVnBpVTJPZm1IdEI1cVpQVG0xZnhyblEzenUzdC1EcTlFSERoVlVzOW96bFNFbW9TcUhMWjZJclROZDVpN1d5aW5tZ3JOQUhYY1JwSDQ0d3RPZXZmTmRLc0FOMG9KMXJPUVlZQ1NkcUZDTHRlVFU5VWRSQlZFbzczX2lmZWZKWDBIdGNKVVh2TEFCMF9sWWE5aE9qbUlSbTJTSHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNbW5SazgtUG5oSHpna1M5NWFWX0lhYms2YnA5QUtoa1ZuQjljSVlielRSVnNRbnpJalVDSmVGNDV1VjUtdXZzdGduRmI2MTNiSlRObzlkdkZQbThHekVZU21uQXNla2lUR2JJU0dtWlZhMFMyNjNXLTV6dFZUREJuMVBPb2RmWVlJLThvZ2hJa3JlZksxdjRqdVFVWUhSaFUzY01XM3VuX01zN0x2LWV3NzJ0akNIYVdEWWNac2VJbldKeGNNbE1j0gHMAUFVX3lxTE1wc3VzYklZbkJWSzZyLUY4eUNPMlFuNHZxdUlaRDEteGMtSnk1WXNsRE8wOUN5RXVVVmd4S3FMZXYxbjh6OWtqYzBUUDFfTWhnSlEzX3BKSWZ4czE1NGd2QUlRZkNIMTdXWktyNW90QU9vOEktVjEwZDBNdTVJRmJ4NnNJSVpNNzJ1aEtqMGNnZ045ZVZ0YlVQczNpV0lrbVBoWmJOdmQyR3p3bjVoUGE1b0hBaS1EdUw4SHBkekROXzJzOVBuN25WSmxlbw?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46017.46712962963</v>
+        <v>46018.29020833333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Man dies day before Christmas Eve after flat fire in Walthamstow - london-now.co.uk</t>
+          <t>Burbank Police Join Statewide Retail-Theft "Blitz" - Outlook Newspapers</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 14:13:53 GMT</t>
+          <t>Sat, 27 Dec 2025 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOS3dackNDbWRNOU9CcHdnSktzNm5QVG9LdExBUmNSa2xJMlJKd0pJa0prTEs4N3dSR0w5T01hQU5ZcnlSdEhVR2ZSTzRITXgtOWFLbGRhUk5Td3RHLUhDZXV4RGpGeHdRV2F6WGZCbXF1ZURoX3ZCSXF4V2lSWVV1clRZd0lwQ0lfNV9LMTBJMjNyZUV4N3dzZkFpYTlaTHpqZVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPdC1MVDROT1dsaGNMWUJXUS1TZjNFRm92M2JST0Y1NVlvMy1NM2diWXRtOW5rSFVwTEE2emRGX3hBeGtHdXo1UllpYzNOSDRUa1pFek5iOXZ2aDJtLWw1OUJFVW1hN1p2M213R3hnWDhnMkFLTnlYbUZXQWZKUHhaV0NkNlYzYWpNYk9YbGlNcXY5aG9qODVvdlprYU5XQVlkM3lDd0JQTmgzR2xadXNwTFBSRnYyaFkxVmt1TmwxM1FGemRFM2JiZG56OWNvTTBTekItR1Y0S3BiQQ?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46017.59297453704</v>
+        <v>46018.33333333334</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unclaimed Suitcase On Busy Udhampur Road Creates Panic - Kashmir Observer</t>
+          <t>Experts warn of post-holiday gift card, shipping scams - WILX</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 13:25:32 GMT</t>
+          <t>Fri, 26 Dec 2025 23:20:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQm94Nmc4REtuN2g2WUNOU0lGZGZpRVRlRDVnR0hpa2U0UWxJWFhhNVB3MEJoa0R6WHdwdkYyTEdvYXdCRUxaMXF5MkRreHlVUmQ2SlNoNUZ1eVN5d0hESmE4aGdzUF9pVDkwN1FyRjM2cjJMb1BXMDJERnhoZHRHUE1nbUhQSjRESERIMzRuei1hdUhjNmN2MUpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPeHNBY2tGM09YN0Vlal9oYkRBOWRzZHl6dzE0ZXNwR0dCQkNnUmh4R21Rc0FIdkpMclMzcDVWY1BMTDUyVnpZUmdDX1AzVWtrRkFuNW1sWlBqTUQ2U01TaEZhOGdMcUhGdGE3M1hPeWNFb1IyMmNCb3BPM0p6SXcwb2kyYVZxQkp6MGt0ZGNZd1Y4RlFYdFF1VUdiOGdZanfSAZ8BQVVfeXFMT3hzQWNrRjNPWDdFZWpfaGJEQTlkc2R5encxNGVzcEdHQkJDZ1JoeEdtUXNBSHZKTHJTM3A1VmNQTEw1MlZ6WVJnQ19QM1Vra0ZBbjVtbFpQak1ENlNNU2hGYThnTHFIRnRhNzNYT3ljRW9SMjJjQm9wTzNKekl3MG9pMmFWcUJKejBrdGRjWXdWOEZRWHRRdVVHYjhnWWp3?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46017.55939814815</v>
+        <v>46017.97222222222</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bomb threat sparks panic in Chandigarh District Court, premises evacuated - Tribune India</t>
+          <t>Five arrested for stealing 1L - Times of India</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:35:01 GMT</t>
+          <t>Fri, 26 Dec 2025 23:42:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbTlTbW9LcG01X0lXakpETlgzTFF2M1Vudy1qblB0V05DUnV2SVV2MElyMnh5WnE2S1dWZHM1SGx6RlZuTVIycl9sQm9xczFITkh2SzZJTHdiQW1IS1JCaWlXWGtLUjB0QXpsSDFLZTdjdTRnUXc4aFY2RE9jQmRNcTFfM2RMTER2MVZ0N09Pai12bUhfYjFVb3RlSHl4TFJYY2lLV3NRM05WcmE1aHhkTVBjVzIyWnRqVXVWelhB0gG-AUFVX3lxTE9tOVNtb0twbTVfSVdqSkROWDNMUXYzVW53LWpuUHRXTkNSdXZJVXYwSXIyeHlacTZLV1ZkczVIbHpGVm5NUjJyX2xCb3FzMUhOSHZLNklMd2JBbUhLUkJpaVdYa0tSMHRBemxIMUtlN2N1NGdRdzhoVjZET2NCZE1xMV8zZExMRHYxVnQ3T09qLXZtSF9iMVVvdGVIeXhMUlhjaUtXc1EzTlZyYTVoeGRNUGNXMjJadGpVdVZ6WEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOdDA0aTVDME1WUzQ3dFZmUGJyNlBXUmlENGFVeHA3cjZoVnpXd3NMd0U0QTk0Zk1SeFNkbjZ3bGlRSnlsbkZ5aHVqMm1rcUw5OW53enQ3QXNRRGpiNkZCa1Q3U2ZxMlNkMXlIczdNVjlHdElobG9fU3FReG1oeHRTcERGMjNURTlZZ1RoNW1uczdndjd0NFVabGptYkdtWTRVeklaOVhLUdIBrAFBVV95cUxOMzFudUVwX3BsZ2NLaTNxalNDMFM3M2RxOEdVNE1GUWJKNnJwQ3I3TWdDRUFROVZiSjZWRlVDY1BScFUtWTV6VlBmWlJORDlzbWpDaU90TnpOYkRDQmYtQkdsWUFXMVVGUG1qZk9QSDJsYzZiYkJ1TjF2VHZrbUt6VDhVQ0Z4bW1VMzFCM3BGcTJrcW1POUpldGpCajhkN2FlRTdTSVRObWYteWd0?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46017.4409837963</v>
+        <v>46017.9875</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UK snow maps show Britain 'disappear' under 763-mile blizzard - the 73 counties hit - Daily Express</t>
+          <t>Prolific shoplifter finds jail, not Narnia, at the back of a wardrobe - Waikato Times</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:57:00 GMT</t>
+          <t>Fri, 26 Dec 2025 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE0tMHpTcFZmVlJTc2JJZFFGVXFTdVVCVnU2bmk3YU8yazNkaGF5RWsxX2o3SU9Ld00xZ1RsLTF6eUdjWkFvek1UT0txT2tRcXJVc3dJM1lCVkZiVGk2bnJxajNoa3ZNcW12Umg1Wm85X2pRTW1XaHpB0gF8QVVfeXFMTlNwUWV2R2pzY0dZWTNJMEVFMXZfX25rSDlQN205RzJXSWpiVzlnZXNOVjRWRmxLcTkzaVI1RWtJYWRjQjdpb00wMV9saERRc3FHOHpadzNJLWdrcFZ2V0QxeFREMFZNODNmRnlCc2RYZFF2Y2xLVU90UWdSbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPM0p4N0h6NVBrVmVpM0VjbHNHeFplOHFELVRzMmNjT05mbGVsbDlIRW5VWHphS3kxcktLLXItSVQ2M25uS1dwUkE1Z24xSFROVDFycU05RWVEUFVDLTRyTFdXOHU1OENWTTU4ZUlXcWxzTEcxUXhYazh0WWtvWnhBWl9CM3hCYVVKUnFROVVlVzh5U0s2c1dLRkx4MkVjT0d6UUZRbUY0QQ?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46017.41458333333</v>
+        <v>46017.625</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Teenage girl was abducted and murdered 25 years ago - but the killer is still at large - Daily Express</t>
+          <t>Michigan Leads The Charge: 14 AGs Launch Massive Blitz Against Gift Card Fraud - AOL.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:01:00 GMT</t>
+          <t>Sat, 27 Dec 2025 05:42:46 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOZWs0MVVvNHBHUWthMkpKQnVaREdOa2p5NG9UUUVmNEVUcmI5NkpMMHFteWJtSEFOckdzbGFmWkkyNFlBa1hpamRhZkRVeUNXMVNxSkZUOEl6Q1NSYklUbXBlcnludFVtSnZIZHpJOWlyZ2FscUF4UmZCSXBJY0ZabNIBhgFBVV95cUxPMlNJdFctdkJqbFFWM1lFVWNWSldlNTB1MVRUaHVmQS1zVks4c1VnOEhPUlJ4TzE2QjQtNllyd0h1aGZrTzJUR0tab3dkNV9pQWpzNFVVSEpveVZRVmF3SGRxOW1qcElCclp3UGpkRWk1aEFJTHg1cXRFYjBEa25UMEJJaHBqZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1mN3lsMVZWajZmUnJqSUlwamNlQVFHNXFPbTRhRlZtUVdicmdWUk96ekRCMDZwbGhNWVBVcnFlTXRHeHRVSFVLbkNvaG52OEM2TjNzTnJJTGt2VlJuUV9EMlBTSmZ5bklWcmc2WmhtdUd2bmc3cWhV?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46017.37569444445</v>
+        <v>46018.2380324074</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Police Release Suspect Image as Bangor Stabbing Victim Fights for Life - UK News in Pictures</t>
+          <t>Japan: Man arrested for stabbing 15 Yokohama Rubber factory employees in Shizuoka - lokmattimes.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:43:00 GMT</t>
+          <t>Sat, 27 Dec 2025 07:55:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQUWRkSzlDRFBKOHZGRnFyV1RtdlBrVTB0MDlXMmlkT29OM1BYLUlZY0x6Uzl5em5OVnpqUlUxc1d3b3FWZWd0ZzZYMUFrd1A2aWhLaTVLSlJYQTRUcTZfdE1MMXRSazRkSmZEazFkZ2lfYXczWkRCWDV1Ui1zVWI4ejZGeHdmbURMTlQyTFhsOE0zTFdfWVdzNmN2cXFfQkVoMW9sUTJwdmVUei1u?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQZmZ1dEgyd09aZFlEeUUwRGJQR3JKeEx3U29ic3NLYWNhbnV4RnM5cEpFNURNMG9zcW5LaVpXSnF3T2ZqN29KV2Q0WDZWd2xGNkxHLWRpQmlHdk4zRWdDOU0zMDl5UlM3U053a09Oa1BiSGRFNVpkRDVydEMxWEFnODhSUEljVjM1RFNWRDQ4UDRSYzh3NnNrc3RrQk1VeFlNTmFDMFRjN1FNdmcwOWZWM2lwSFczcTdYVzdIQV92OHbSAcYBQVVfeXFMTXhjbzNPVUJvdGFaWWpvTXd4amN3WTNOWDVqejVfMURORWd6MEpxckUzeWZFdmV6Yl9GUDdVbGlBYndFczdNQmttaGdsSFFEVi10NnZ6b1ZzRzh5dHVxR1BCUTU5Z0ZNLWVpUjFLeko2NzVCdjkzNXFlZE9jaWtzaFZTcllCN3VEYmNiM0ZONHZjOHVpeTdkV3p0ZTRfTF9mVHBDVTZKSC1lTnBlcmQ5NGctY1JKSk5zOXJTaHZwRDJoOVNWUTBn?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46017.40486111111</v>
+        <v>46018.32986111111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Duluth man loses appeal in 2023 Lincoln Park murder case - Duluth News Tribune</t>
+          <t>Is This the Dip to Buy in Ushanti Colour Chem Limited - Retail Investor Activity &amp; Budget Friendly Portfolio Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 13:00:57 GMT</t>
+          <t>Sat, 27 Dec 2025 02:25:54 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQN1BfNmF0V0ZGRnhsTzBJVGlRUHp6TE5EQnBqeTRsU3dTcEFFTWJtSkNheXZPbjZWWkR2RnZtTEJkTFlKakxsWXdZUXlBNlh0cFJjRHAtdE9xY0xGbzVkb1N2YXZnWHNFc05oemZiNThfeXFuNGQyNnRmSTR2NzlzOXV4Rktpc2I2VUtYcjVWUnYzb3d4TEhnT0NSdzFJM2RXZzVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPNlE1b3RrY2hPY3FXZTVPQ0M3LUJ0VXBnc1BXYW1IdW13OEZRZ0ZTSk5ZVFhCTjc0dzl5Rmctckp2ZWFhZW9BX3EteWhzSEw4ZHlPS0U5TkNMeFljUllYeVNXRXd2OWRSeEtRb2dJWnA2czJaRlQwZmpVSnB5YzJiMDcwY3dpV1hKdGVHeGsxckFWZw?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46017.54232638889</v>
+        <v>46018.10131944445</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KEI Industries Limited Volume Confirms Breakout — Analysts Bullish - Cash Flow Trends &amp; Free Explosive Return Secrets - Bollywood Helpline</t>
+          <t>PSG tempts Pedro, but scares his clause, Enrique ignites the challenge with Barça: I want to eliminate them - Balkanweb.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 12:23:25 GMT</t>
+          <t>Fri, 26 Dec 2025 15:53:50 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPSTNUVWllQUdXM2RPb00wby1pQ0QyU1pGNUw0a3ZVTVVoYTl0MUlLMWdxVzRZbVpvdHRpR0oySnRpUjNBck1zQkRib19XZURSa1VJVUNuTE5PazI4SWp4dl83MTl2cHhVZEthWkNxWWlaMjdNODlJQjZ2UXR4b3UyLUNYTGZjWWtlYWdQU2FjeHZoTktSNmIxQXpsWXAtRExnMVF3SkZLem1mc0F3b1FoVVdkQ3JrRF94ZDI0NXVCdWtsZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQM3h3dS11cWtFQWdiRFpKMmQ2aWppYmFYampQdmx0N2VXX0hnVkhVblFaQ1N4am5ISVBlcHRBZDBYLTVHUWxaQlV0UmxabWZTZUVuWnJoWk54NXdJbUJ2LU5SRlJuYWQwTVhwX2hiaXhiNlRfWmNmSUVIRG9QN3BVQ0ZGeVBRaE1uYXJmOFFJS1BKOVhjLTFheUdsR1JqV0ZJaEVZNTUwUGN3dDZPSjhGNHFiaVpER294MG1KMnRVcEJoNFpudldZTEs1dGxFeV9fcEd1TXdpdG5DZw?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46017.51626157408</v>
+        <v>46017.66238425926</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Superhouse Limited Stock Poised for Technical Comeback - Protective Put Strategies &amp; Explosive Profit Growth - Bollywood Helpline</t>
+          <t>US: Five injured after shooting Northwest DC, investigations underway - lokmattimes.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:29:33 GMT</t>
+          <t>Sat, 27 Dec 2025 07:27:57 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNenV4bG5TanZnWXNrS21UVUNpYmF6QTB0RDdVamVnS1BOZHJxc0ZIUTdvLXJpRDUycDdPeHJVNm9nXzZkZUxlQ1J0S0VqWENlMDFCTzUzRVZXb0lFRnpfbFZ2SXFaTFAxUkJJT3l3UktHRy1WRy1XYWQwT0hQYmJQZWxuc042N19HZ2ZMeGw3ZzdpSWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQaEJpdUpSMGlBMDBLZkw4UDF5RWY2ZjZaR2phT1RPcHVUdUxpWkFRcmIwTjJ1YVZEbTlZSGExamVHR3p0TE41bXpZTHlxR1JFUmZCZ21rQ3R4d2t6UzJIc3IzT2VzYUtxRG8ybGxNMFl3Q2VzQUtfMGVVZ2E5YzU2ZnFEQUp3ZW5OaGxxRE5NQzVBU2NxSXpKM21fd3puRXdWMEg3U1dzLUZ6ZV9PWjNN0gG0AUFVX3lxTE41TThPX3ByU1lvNGxuZ2xGQXJxUWlEc0RXWjNQY3VOblZ5a0FtdG02VG1zdjZYQV80dVhDVEh4RHVPdDRKZk9fMkJYMnctTEtBeFZ5TWRTMy1mV0JfQkhyVkM2SDNpZVdpN2xmZnRuem5oXy0wUnJJQUduNEdVRjNiUDdxS1hzcEhjZnUwU3ZVSmdyMmhwcEw3TnlyUzU2S2tYREg4MDhSdlFNZ3prRGdIYVFXMQ?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46017.4371875</v>
+        <v>46018.31107638889</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Can Spright Agro Limited Outperform Peers After Recent Pullback - Mean Reversion Trades &amp; Affordable Trading Portfolio - Bollywood Helpline</t>
+          <t>Soprano Asmik Grigorian to lead ‘Carmen’ and sing mezzo-soprano role this summer - KRON4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 08:33:40 GMT</t>
+          <t>Fri, 26 Dec 2025 19:19:06 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPT1pqeFJZQktaY0w0dnpFNUpOejg3TGRfaW5fSVY1OWxVbFFCY3hlMnRZMmp3d1VXZTFtOE5WLVAyTnRZUnhrcFBxOWpablI5anNWUWJYbXFuZzdnWU54VWxvLXpkR2hndEhiNGFQT29PcjI2SXZoZ2pqMWROeDRKemdrZ3hEWWozeTA2ZkFuVkM5dnZzNzgwVVNQNzVWdjNlWG1ySTR0azRTdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPTUQ0UGVRWVo3cUpIYUp2QzQ3aVNQTnZwTm9wN1BRSEExRjhUMzVCRnE3NWpobFowWEMtN2NqYnp5SmlmLU9SRWNHVnJyNlhzVlZyOXUweFBqTzlHeGlSWUdlYTk5UWp0aXNCRm90cVUtUm5mUFZJVzVlYk5ENnllWUhwZzdra0dZUzFBZjl6YnIyUjJnMVJ0WGxPbnlwWDBHOWhWOW1ISnJBX0dXZEt3RWNoTVlKZ0xXaUpUbk5YbVIwS2VwVmROc01LY1J0dHFPWDBqTHd2UdIB3AFBVV95cUxPckZYblhMRmJJU09jcTE0WUJySU9qaFFlWHRiVjB0bVVDM1Ewd21XQmtyLVRrMG1jd1lsalRhb0FCcy1lMkxQYkNBZE94OGxlWVl4Qnlld1FFQkE1Tmc0YS1Rckd5WDUwMm9SX0xaNVZYekFpOHFDcEJOVTQxcFNsUUJKVDNKM1JmbDZCVVZCSk4teUl4LUVvdURlYlVfd2N3ZmY2bml6N25CTi1LbWI0Z0hMNzZRRmFNMGZFeWlGUWhBUk5NTjNlaGlhOXhmR3BncFF1UzhTSFdCMW1r?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46017.35671296297</v>
+        <v>46017.80493055555</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serie A | Milan vs Verona – Can Rossoneri find shooting boots? - Football Italia</t>
+          <t>Flagging Deletion of non value additive posts - Fundamental Strength Indicators &amp; Get Peace of Mind with Portfolio Health Checks - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 12:01:29 GMT</t>
+          <t>Sat, 27 Dec 2025 02:27:19 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1NcTh6aGNFZFkyZldVZnI2WW1HRUc5c3I3UVVtZmRBS1VrTEllRUk3OFFZYkItdjdfVm9MRVJjQ0VKTWU5TkJnaWFNY3VEOW5PdnpfQWlNb2NhZVFpUlFfYVdYdm1NT295azdVcldwTDZTeVND0gF6QVVfeXFMTWZsZDlISUN6aEtJYWVhZDJhaWZZQlVMZUlRZ3g2ZUtNOFZjbDNjd21ua0c4MGFZeURxWnhFVlQzM1ZZd2FzeUNYSzcxaFI5MXVoNjNaVkxldy0tTi1TY0N3UlBWNUNQSXNKMnNGYV9MRWpZV0ZxNWFIMlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZzl5SUVkbzRWMUp6dTdPUEhPU3RiUW9JdnpwSzByZTFSNnR3OXluVXRuTDl4RkpTMGdOUWdDR1RPMHNFbzZOdnF2V25sTUNrLWJDWWVZT19GWS1KcW92UE40OThzdnJ0Q0dkZmVMNGZWQkdSUlpNVVNQTHhGcTZZdFpHVzA1Sm9X?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46017.50103009259</v>
+        <v>46018.10230324074</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Liverpool facing decision on leaving Mohamed Salah at home after star's explosive attack - MSN</t>
+          <t>Shweta Tripathi shoots for next in Bhopal: It came to me when I was craving something immersive - lokmattimes.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 11:44:27 GMT</t>
+          <t>Sat, 27 Dec 2025 04:28:28 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOS3pCekNRMk12TFltYndNUjlkd2NYQm1fNzV0SnhfTGZTTkQxbXNHRnBPY0pocFBSS2hvcFpwbF95clJNaHhGVDY2SnZmSXZPWERGTmpWWUQxbjQ2X3RveEJodjFLRzJLaWQ4RVZWamthb0JUbFd3ZGVaRXppYzZHdldNLWdMX3FUaWl6aXN6NldKbFZuNkdHTkpiLTd2SFFXaHBrMDFfd2kzR3Ixb3ZodHJiREFOcmZnS19zSUdFaTZwNFRGWHd1VnlzZk5DZHAyVFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPZWVrOWh0UkhaNkZFc04zRUZnUXVhdThRaTVZTmltOWdaaURmYVNUSUphYnE3WE9nMjJYMGNRVGxRSXBLMjFXRTExLWlrUThlMUNoaWRaSHhYS1UzSDhuUEV0YU9QZW5JRm4yZTVkd3cyNmFIcnNzWENJSVptZm9TbGhPd3BkdkpCdXBSLVNQTGgxMktrR3BNdlZxVTUxbTY2RWNHZnNIN1pDVno2SnBsNFNld0pXRFBTWDZUQ2NFZ0gwQXFZbTk5ZVVjRTJfMklvM0hR0gHYAUFVX3lxTE9KeFhoeVAtUEMyVzhlMXprTWVvb2NzUEFjd0ViZjhVQVNEcGVUMy1vTDJZRXFPd184R21ubTFfYU8yd0Q3d1k1REhoYlZOVFRZUWhFcVFPY2gxZzNSRE1ZcFIxWS10ZUwtS3Z5TnFrM2lmWko0aDNzYm14NmJTQVhWaWhrNlJOVG5rcFhDWU12SDRxR3NLd1EzM3BnMGpyc29yV2xDNTBLU0x5eWxCYW5FUEd2M0RBQXVHTVhZd2xmUTFFcVBSdFRTcmU0aTdpNjRDb3RPZEpKZw?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46017.48920138889</v>
+        <v>46018.18643518518</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Forget about a backup striker: Allegri wastes no time, intensive tactical training for Fullkrug - Tribuna.com</t>
+          <t>Price formed a lower high just below the resistance indicating weakening bullish momentum. - Debt-to-Equity Ratio Analysis &amp; Free High Profit Capital Plays - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 10:51:50 GMT</t>
+          <t>Sat, 27 Dec 2025 04:58:26 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVFdwcUJBVHJzOXByMnNoeW83RVVmSTI2bFYxMTRDRWhQWi1LMlJ6dDNhOVdVUVZUR2hYRmprTWFRdnZkUGI3V2xCYzRTTkVjLW9oSlJWbVZPT3M2TXB2WXppdnNVZEFEaV9MLVRPbk9uWkNBMjRhTDhxelkyc2ZIek53VmFVUjdSOFR6a0J4SjBQSFlyb0NKOVV6MFBXdU1vME02NHN4bzFuZUdPVHU5ckstU0dtN2NnWEdmYWlJTU9HdHVXTFhuMFRZVERZUdIBzgFBVV95cUxQVFdwcUJBVHJzOXByMnNoeW83RVVmSTI2bFYxMTRDRWhQWi1LMlJ6dDNhOVdVUVZUR2hYRmprTWFRdnZkUGI3V2xCYzRTTkVjLW9oSlJWbVZPT3M2TXB2WXppdnNVZEFEaV9MLVRPbk9uWkNBMjRhTDhxelkyc2ZIek53VmFVUjdSOFR6a0J4SjBQSFlyb0NKOVV6MFBXdU1vME02NHN4bzFuZUdPVHU5ckstU0dtN2NnWEdmYWlJTU9HdHVXTFhuMFRZVERZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNZHA1UXNfQXZuOUZJdmJNZ21UUlVaSk1RQzhPVFZJQUQ5bGJXU3R3cWNhSWE3SzNWbnJaNjB5X1lHUnF5NDdlWW1HejNJaU5iazR0dmo4ZGJINjlhNVNCXzBrUjN4TFA4SUdZTUtySUZsTnhqTG5nRXF6NEp0QVRwZzVWeDNwbUZRYkwwMVl4X2lPcmxnaWxsM3BvclN3RXRyM3FvMWlqSXhoSlc1NGlUTHRhRUdYcHhDcEhVMHB2TDhUV2FJN2I2RVV3M3RYOUozTVdCY3BRNA?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46017.45266203704</v>
+        <v>46018.20724537037</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cuomo says Milan lacked ‘now or never’ mentality in the summer: “It’s inexplicable” - SempreMilan</t>
+          <t>World News | Syria: 8 Killed, 18 Injured in Explosion at Mosque in Homs - LatestLY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 09:40:00 GMT</t>
+          <t>Fri, 26 Dec 2025 14:48:20 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBRUTVPZXpKMGdYdDVuT3UwQmFoMmpsMGt0eTdYaHpnMjI1MkRZNG1QcjBScG9obVFTcmVySkRRckQwNXg3bjZxY1U1VVNlbUV6NVhJY05HaHJWZldxQW9oSExnVnNfRHBPOVl1alRuS0ZwdS1jRUJmT1VhUzTSAYIBQVVfeXFMUGF0aE5uMjEyYTA3QzF5bllMSFdaOThLMzRyek4xYWZNZWhqb1NaSFJ1bl9fQlJUOWcxaHlFckxVc1ZPbEt1REgxZFFsV0FIVlJ2U2RPaWcwWWwtdUxpaGJQWnNVUkRDLW9lLWlnZkswNldqZDZKbFZUWjNTQ1NQVkVqZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPb0RETUF3T3dEZG9NTUZPT0hlMlFVUFM1eHVRaVlsaTBjcDctYUxBWWNkeUprVWdmUzVOVGZQVU8yRlRPUEVaYU1EMWdTcVRKQ3BWeGRNVWkyRDRGUHhzZmZjWW1pNnVjWnIwQ0lHaEFzRXhlSGFnN3laZlFFSTdzZFA1bW5ocVEwUi1DSnBFQ000NDF5NkpId2xxLUJ0ZkpwR1p3S3BqMnhMQTg0QWR1SzNfR2lEeGNYTDZPa29B0gG-AUFVX3lxTE9vRERNQXdPd0Rkb01NRk9PSGUyUVVQUzV4dVFpWWxpMGNwNy1hTEFZY2R5SmtVZ2ZTNU5UZlBVTzJGVE9QRVphTUQxZ1NxVEpDcFZ4ZE1VaTJENEZQeHNmZmNZbWk2dWNacjBDSUdoQXNFeGVIYWc3eVpmUUVJN3NkUDVtbmhxUTBSLUNKcEVDTTQ0MXk2Skh3bHEtQnRmSnBHWndLcGoyeExBODRBZHVLM19HaUR4Y1hMNk9rb0E?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46017.40277777778</v>
+        <v>46017.61689814815</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Zelenskyy says a meeting with Trump over the war in Ukraine will happen 'in the near future' - Norwalk Hour</t>
+          <t>Sports News - LatestLY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 13:27:14 GMT</t>
+          <t>Fri, 26 Dec 2025 16:38:21 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOQU9pZEo1QWZKS2JVTnh6LWZ6eDM0ZTJ3Z1I2SW16X2FheWJ1YmpPTmllcV9xT1lzQWZOblcxU05lSnM0MkxTQlZSMkh3X3pBMndDT0pWSHpwTFMweWhpM1J6SW5XZS1OUUR1RkpydXphN3BEb0xiU3VjUWxxcHJkVVRXZzZJRXlVRHZsV2Y1UWsyQTFQVnRMZzNvYWZ5a3R3d1l6Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPb2JNcVFINVNpZWxmTncyLXJNdTM0V0EtS1JmbDBKRUZDQ0JMS3g5R1FrZnZrdlhiaF85RXZXRmNGSjRPN1d0Z0poZ0xxZUU4dm5YRmduS1pFZjNITWZGRW44b2NRXzNwVjNPaHFodHFRNFhHQ3gzYlNoZWtCdHIyMHMxa1pHRjBwbGtfMmZ5ZDVNanpKdS1oWjhGZl9ReGM3TEZjTG1HZ1JqbXgxenhrN1BMXzEtdER3TzFLWEZzZTNKdUo0VEpfNGhZTmVTNlg2Tlk1dzlBX0tUT21hRno0bzhCNU5kNGhUZFN2SGRjS2tDV1ZXWC1TWEdB0gH6AUFVX3lxTE9vYk1xUUg1U2llbGZOdzItck11MzRXQS1LUmZsMEpFRkNDQkxLeDlHUWtmdmt2WGJoXzlFdldGY0ZKNE83V3RnSmhnTHFlRTh2blhGZ25LWkVmM0hNZkZFbjhvY1FfM3BWM09ocWh0cVE0WEdDeDNiU2hla0J0cjIwczFrWkdGMHBsa18yZnlkNU1qekp1LWhaOEZmX1F4YzdMRmNMbUdnUmpteDF6eGs3UExfMS10RHdPMUtYRnNlM0p1SjRUSl80aFlOZVM2WDZOWTV3OUFfS1RPbWFGejRvOEI1TmQ0aFRkU3ZIZGNLa0NXVldYLVNYR0E?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46017.56057870371</v>
+        <v>46017.69329861111</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irish police issue appeal following decapitation of stag in Co Dublin - MSN</t>
+          <t>India News | Chandigarh Sector 43 District Court Complex Receives Bomb Threat, No Suspicious Object Found - LatestLY</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fri, 26 Dec 2025 12:32:42 GMT</t>
+          <t>Fri, 26 Dec 2025 15:26:29 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUzlyMXdQeUZseVpUcE5KU1JtaGxZQ0NpMXN3YmF6ZFBTZFhvOHhZMnNfRUMwSjVISWk1Z0F1V1lSQ0lUeEJHVWhMTzdta0FnVWVnNmFXMVdIUHJRMXg1aG1BVmxhSXgxTVI1eXhhTHhraHRFUXBzV1BBVWttemtMSHA0SHc5R3dIZmlNREJ6Ujd3SkQ4eTJHWWNVVGZoRGZIcjNDNW5rcF95RERWak5mNTlBeWNreTUwSzNJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPblNxdUJxRmhjV29CbHBIVC12d1JlTFhmWTdJZFFHWWpEd3U5X0lzTm00YURLajJIME5CZkdSNGE2TGg4cnZ5c0wyMGxWcDlvX09acXlVakQtRnNXXzlwdzc2WllmUzVrZEZJVHdXX2pfS0xLTGtpZHpnTmtxVGtacXlsQUNIb01GNWlpVHd4QXZ5OWdRd3l1RkNXUEV0VE9pdWVIM2hETlBiU1p6aHVNNnNBZHdEWVp5UUJBS0NmdkFrNmg5WlZta29DZlM5YkxaWG9YX1ZKX1kwX1NoeThmSTJfQXJObjFkR2ZONdIB7AFBVV95cUxPblNxdUJxRmhjV29CbHBIVC12d1JlTFhmWTdJZFFHWWpEd3U5X0lzTm00YURLajJIME5CZkdSNGE2TGg4cnZ5c0wyMGxWcDlvX09acXlVakQtRnNXXzlwdzc2WllmUzVrZEZJVHdXX2pfS0xLTGtpZHpnTmtxVGtacXlsQUNIb01GNWlpVHd4QXZ5OWdRd3l1RkNXUEV0VE9pdWVIM2hETlBiU1p6aHVNNnNBZHdEWVp5UUJBS0NmdkFrNmg5WlZta29DZlM5YkxaWG9YX1ZKX1kwX1NoeThmSTJfQXJObjFkR2ZONQ?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46017.52270833333</v>
+        <v>46017.6433912037</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>"Lo de Vinicius y Mbappé nos pasó en el Barça con Stoichkov y Romario, nos desequilibró" - Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 18:12:22 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPUTVkUnMwbnRpZi1zQlRRYzZRbVQ2VUx0aV9URWlNYlRGMnEycnl1a3dOOUVQRFdlZU52ZXpnRGc4ZWlPbTFjQldnMi1sMHptcTdOVTZfWk1pR1QzSnNibFhtVVpKQ0V4d3BUaDRxa0ZhbzZmMUF0cXFLRnY4YmlmMXU3RTgwSUVzemZEd0J5SGtyZ1o3ckdwTFE2OE5DVm1QcGtBU2Q3WnRKWDFWS1V2X3lGUGFVVGo0ckR3WWJ6X2N4Nng1cHhGdkFQTTLSAdoBQVVfeXFMT0NHcnJvUk9TTXVMLTctZVI0bkJUd1llMHFwc3hNNmtsT08yOXprUm5hd1l1TEVPcnhKX0J5aUZQZVl6b2JrZFdweEFrNjFrSl9nVUdISnJFcC1qaVlpQ05kMHFJYnZ0eW15TkRUWEdPZ0JUaVA5bW9GNGZMOXEzT1RIRzViT0ZFYk0ya0FkQWJYTlBJM09mM2gzRnh2Z0NpVW5hUUJQMzBsLUJwa0F5eERnaW9fak5RSGMtZFFtSGtHNGpxaU9ScGNOcG9rNk9hVzNfb0k4cUVEa3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46017.75858796296</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Local Town Searches Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>(Kildare OR "Newbridge" OR "Bicester") AND ("protest" OR "boycott" OR "bomb" OR "shooting" OR "explosion" OR "stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Man fighting for life after Christmas Day shooting in Sheffield - Bicester Advertiser</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 19:41:09 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOekl1MWVJS2dGSTRuS0hQWGRxa1h2UGMwQUJUZlFVd0d2YWcyRkNnWEVfYjNMemZTajBZU3R4QTlqazhBRUFYMzBhbEdOa05ubXVMMmNsNXpwNFB0WUhMX1Bacl9zbHREWFNnaFBEY09zc2x1V1FxbEFhbS1PR28xQi1WcFVJNGZNUnVNZk5Xc2prTmp0UzU0Y2tpekxHMldSQXlQNDZjZVNCQ3hDY2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46017.82024305555</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>And you thought Boxing Day sales didn't matter any more! Thousands queue at designer outlets and hit the nation's High Streets despite Rachel Reeves' £1billion economic wrecking ball - Daily Mail</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 15:42:21 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwJBVV95cUxNVm5mbTBUT3Zob3ZXN2RrN29tbFdiSDFlRUJETFdwd1owdl92YWI4V1l0aHpSSEdOMldXcnk0MFF5Vm5JZ3Rnck5ObEtFWEtQMHJ6Nnh1ZlF2UEdEdGsyaUh0SktPa0NMM0NueG1WY1ZvVXhNangxUXl0Y1p2VFJNOTdtV0p5M2wyOHJhQXBxVk9aRnk4SlJmZnpIdExJZ1V5LWQ5a2piTjdJeTU4cWZFRDMzV18xNThEVGlYaEdqZXFtOTBrWC1qYTBtSGh6bVNwa3NXWUpQeUc5OGV4YXdfNkJndXBWRERaa21TZlFkeWFsYWNTNjdaQjN5Rm0weHBUVThtVU4zQTJsb3JDQ2h5cnc0SVQyclI5eXV3QzRIYWhKVVdnWVBOUTh3SmNBM2ZhMS10WWtfVdIBvAJBVV95cUxNc0Y0QmVleUhHRmlZYk1OdTB5YUNnWFhmVmlwV0ZxUk1YU0NpNG1QUnNLSlRjM2R0NmRtbllpNnJ1M0RHcEt5Vlp0N05OY1FtVEZrSEVLMUFXcVREVUhEZlV6TWtDUkdxMHdTUDE3d2JJVTZhNERqd2stR0lrYktseWY5cGJLcmFXVlVnQk5QUnZRMjhiVVVBcjUzeGJwbVA1Z1JNMUVxNll0NTM2T1pGeFFPV3NzNFJlTzR1TDBqQW9uTnpZNkxEcFpYZjRQSUZSYVZ6U2RTaDFlZjhMbGxtS2V3UGpMZllwNXEwdFRHMXg2ZnVMVEFHTXBvbnFjcXNwVnZfYl84SG9nTUN4LVU4U2I5R0VrblgzZFNhdTRfVTIxeDNveV9DMUVWdzNOSFVhbWhXTGR4M3hreGdJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46017.65440972222</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bromley biggest developments in 2026 from thousands of homes, new leisure centre and 19-storey tower - My London</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 07:04:36 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQU0xpQnVmTWp3SVYzWVJJaTJEYnNQRUNNWDdXLUZHQjZVZHBITzROMUIzUXpUNG5KaVBseWxoVkpXMkZZUlhCc3B4SFhqZ1RJZElwMFczempXTEJrV2VrVzFtRV9nNm03NUhGdTZFZnVETFdKS3YtSEp4cmROd00waHhRTUZpSGNNSHpNYjg4WEtVTU9EdXdocFAtR2JET2poTndz0gGoAUFVX3lxTE9SSzludUE3eDRKOUw0WERtbkZVS1dHOHpFOThJOHBfZmFuY3NlUUMzVXFkeVltV0JTMnRISVJ2NTZva2NXclA2dmhha3U0cUZQWURsbm4xSHpoOF9SS2VMWjljbl9LUnRzclM1bVIyelhWdEJjd0VmeEtnakZmVW5rcnpwamFhX2pyaWlHYjVRZFRVVHFUc09ydVA5U0l3UUc5SG90dnJiSg?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46018.29486111111</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>UK snow bomb horror as new weather maps show 'one inch per hour' to fall in days - The Mirror</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 20:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBsaHQzaHR4Ylh2MDVHVEVvSVM1UlYwbXViVTVsY2tDUTkwdXdBb1haT05IckN3RzZrMGVtc1lBS2RrTFJIeHIwT08wTFhtZVB6ZFJ4dXg5eWJnQ2NyT3loVmJDQXh4c0dPdUloMEFlZ1NkMDREcjBRbERn0gF_QVVfeXFMUFRFQ1Uta2pxR2QzSEpWM0pncnJVZzI1bE0tS1N4LUljT2dmWXZSWTlCNklRWm5hZmNBVzMxaEY5RnJtQ1kzemw3MUM3bkNFVXp1MWhaWHVQNENOU0w2U2Y2Y01tRU9ZYkZPMno1X2V1QmRjVUZyRjZMVzZFa3J2cw?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46017.85833333333</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ten stabbing victims in one year amid 400 knife crimes in Islington - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 14:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOSzE5WnYxSzlqbVlaUU9xaWhjTDI1SnA0X2dvOTRPVjJKbmF1SVZ5MTZkSHIzYm0xVVNweGRfd3paemYxdFYzZGhWTWFPTjIzVlZqcUdqWFhxbEJaVnF3S3BtMTZPOUlWQlZDZ2kzWG43b3psLXdfZVF1QzFYVElIT3h0VmFheWtQTmJDNGNpcUJUTWkyZkUyeUFGN0ZtM09EQ2JZZE5R?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46017.61736111111</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Snow bomb to dump one inch per hour across major Scottish cities in January - Daily Record</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5UY0dkUWpscU1HVG9tanVCOVJiY2FaMzFrNmpscFZCR1BLdFUtZnI3NEZ3RDlrVXU1aXFGczFQVEpDU2pkMFN1NXQ2Y2RlbDZWY0lnWlZtT3N5ZkFXRGo2MDdseG0tSkJlSmFWZlZpSElqTXVIMng3Rl8wMGfSAYIBQVVfeXFMT3hibnM5NndYRzFBOWVIUXFuSG5DSGJ5NDlKSEI3NExPZ0FTUjZNTEc0akdjcGdRTFpOeHhHTlo5ZWh5NGQ3anc4TGVfcUo0Zkg5eVRnRjVlQUZxWUx4NFZPaVNrVnlqTjdwQ2ZhN25pSkxKaXdhcms5cVJONVNNcW5lUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46017.95138888889</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Lady Panthers struggle, fall to London 66-28 - Record Herald</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 23:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPMkF0XzNQdjk2bjhqaGxQUnVQdW11bW82anlfUWxOVk51TGp6bHJiMXBXdXh0SWVjZnFnRUlYTWw2LWlmNURnZTZsZXF4WnpzaXNsWXFpRVlCdUZLOEhlS3gtdER0S2gzSHZScTNfTkFzZ1RGa3NjUDU5LUotdXpmUmlHYlNKZWswZEJoRA?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46017.9625</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>West Ham must not sign 'brilliant' Chelsea 'bomb squad' defender after Fabrizio Romano update - opinion - LondonWorld</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUk5SQmgxRjJ5dVBwVFZzX2xQQzY1d2xXR2Y5bDJwRHd0VDFrNHEtcHNrNlpsZkJFSHpBa1lwUkRFQmhYNXBoc1JpeW9fc2Z6NVc5dlBZRGxFWFcxSjVfdDd5ZUtuXy1UTG5PYVdsV3J1T0FkN2J2eHRyZUI0REtZSzZtS2otckVpb1NXcXpfT3FwbXYwMTRGeTZMMTFNN3FuOXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46017.83333333334</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brits share Christmas horrors from hiding presents too well to spending days alone with their pets - My London</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 17:20:19 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPMnhtT2RqdGRPZmhQYVo3NVNjWUEyRE11T0RwX1N4Z0FjYnB4LTFlVmp2SjQzdG9YcUR6Q2NwbjhqeHNmTmJsa3FxdVBqVG9rbHB0SEEydVJOWkllVW1meTg1NkljLUF0Uk1XNDFEdWJkT09kY3dvV3JCVFJucU44X210QW9VaGNHcDJ2TVVWTHg1YTgwOURhNFNpT3FMUGJqMm9seXk3TEPSAZQBQVVfeXFMUDFiaHNyY2lJbkdYVTZvSVZ3MWZGZXRfTlBpX29INGZDRTVwSTlWRi1KdnVoN25TTV92cVFwQkpMWTdwN2VCU2Z4NnNwSnFxSXFMdWduRDVYTk9DRFV6WmVwNU04WDFtZ2lKYk5TV1ltWTE3REJSUEFKYUNsT2dOTHlmc2xjczdPVVZpVkVSVjVMdUNjNg?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46017.72244212963</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1 killed, 4 injured in Christmas Day shooting in Southern California - news.cgtn.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 23:28:16 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9LOFZjODNxT0dnZnNxWVB6M2R3dnRERlZlQkVFcnpSMklFT2kwNW5DZjJzVGNCVU1HTHBNc1dGSW1QTDFsV0JWOVVPSHdILTZTLWpfNEVrZzZfR2I2UWc2OVBfWVljTW5INl9JWU9B?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46017.97796296296</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Suspect killed after shooting at sheriff's office in Idaho, U.S. - news.cgtn.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 07:25:32 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQU1RvVV9oOEU0NmdXNVNPYjBrVUkxQUFoRVZhLTI3UUxzejJDNjNjaGhISlhOcE03MzRHaktvS05XQk45UU9yNXk5M2hGOHJvTkRoSlZjZHg4QmNKbmhSc3JrT1dBS3c1ajY4N3JMRnFUR2ZWcUl2VkJucy04UGVaVkt5cTM0ZHVtYzY3eGprVEtMNzY0X3praURzZWZyYXVZQXFTZGNaNGluX256QkM1a1REUWd0SnF2SEtlcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46018.30939814815</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Local HS dance team performing in London parade - FOX 7 Austin</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 16:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1CckU3UmJ5ZkN6UU5ic3p4TTN3VldTaXAzTnh5ZTF1enpwd2dwRHlDSm1IcWNUbjRKRFFwQUZVTmlDUlRDU0FmaGdlbkhyNE5KSTNPTGZLTGMxN0t4WVhvcHNQUdIBaEFVX3lxTE1hX3lldlNGNEtPbTBUWTNFYUtUUzFVRWZ6Xzk2cGUwOVlRWjBzQjBiWmlFWkwtXzBuVnpsZTQteHR2ck51MWhJczZ0Y1E0TElwcERUVWQ5MWFYOEh4eHViOU9TMGNjcVdf?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46017.67291666667</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Turkey detains 115 ISIS suspects over alleged holiday attack plots - irishsun.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 19:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPTFhtTTdxZVVrTzc3M1dpZEo3OG1JcUtOeXY3LXRaVUp1NlV0SUtLOEh5T0NPSTZwZXdzSmg2SkZrek5rVHlYMG5hTk1FUVZNYl9rSVVrVjN3cWFjQjVuTFB5LWg1a0FKcDJKVU5mNjZ2NVNkcWRPYThfdVMzQlVuYk9HR3JYLVoyUG84QWZtdDlFYkJQbGZwM2Z1Qm5MdVRPSEtkazF2UlNldw?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46017.83263888889</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>The area of London with the most stalkings as offences rise in 2025 - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQdGQ3ZGlmV2RHWjRjeG5EcmtKTEpISEcxQWNZdWk5a0JEU1V4am1lRWZRNk5VOUtrTnBtSDI5N2dUSE5uY21OemZ6Vk5CZS1YeDFjRkxxdU0yM0gxbFJGYjg4NHF0WjVNd29QTDEwcXg1cU5VNllsWjdCOWEzNDhOVEd6c2tNdmlHcXZSa2hpZVY4b2Q1YVFmQ0dXdXF2QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46018.20833333334</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>London council starts issuing speeding fines to cyclists amid locals complaints - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPRUk1OHBTRnhOX0cxXzIySmVtYjZUdDFMUVpwaDVadndUeDd4ZmhmeFZJMkxXVjRyQ0hESndVbFduaW04czZKMDlKb09sUFdJQ2dwWWRWcmVCVVplaWJJSFotZTRtbmhELWdkNVpjNUhaaWhKQ0RCMzlVcm1zWXlJXzlNbjI4aHJWVTVHalQzQU5kT2VCd2tvalVMM2dscWU4X1pMRFR3?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46018.20833333334</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Call 999 if you see missing boy, 15, from south east London - News Shopper</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 15:23:35 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNeHRzQkszTDhNcTFlTmFaOVFUQ29pejNZQ1EtWjdZQnpCR0Z1cGsxV1pteVFMREhqcnFiY0p0bk9MMHc5S2JsQ0RHV1lEWXJ3WmhPUGRtb1NOU2lKYzZfQVdsaUVmWTFBMVZLc3kyN1BQblZZNGJmOHRaTzdITi14WmUwMGxVczY5LV9SUlpNeDlISy1H?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46017.64137731482</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Flight to Dublin Airport cancelled after plane's tyre bursts on Boxing Day - Belfast Live</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 18:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQSkN4b1U3aXFNeDF6QldBdzk5Y1NMRUdhanlmdWdoVWtNOFB5RkZwWUJYSjJyYy1WZWZ5bnRDb21UOUdEb1hZODNHX3RzLUNzYTZGRFpfRnd4NnJZWXp2R0VEQ3NnaGVZSUMzc3NSZTlVVDRPdGprUUdhdDBGMG9CVS1kYkFOWW9jWXhFQXZ0RHY3dUs2U2VvR2JtNNIBoAFBVV95cUxPbi1rbFJLcDFzdWpHcnNMYTJ6V2pBSmt0enFQVWV4UDZpaGhOQWZVWTNHN1JUalJjaHZvd0RXS0lXWkdmRFdqaVFjYzRZcGZoczZhbkN2WEFNNkpnckljU3Q1MlRRcDRGSHdmdERrdWN2d0VnaDFGVWI1QUE3YkJjempabzRlODBOcWFtaWVjRlphMng1THZEVjRKelp4ZmtJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46017.7875</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Sydenham woman-beater jailed for strangling victim and lifting her her off ground - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 17:21:31 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxObFRwbVoxeEZjWnhfNDA1Ync2bmplV2lYTGdhdnlQOWNUQmpuZ202V1FKM0NsZjVjcGJBSFNjLXZpT2x4dXc1aEp3WDFLYm9SZVppTzJhWXVIMi1JcnIzS3luemNnSDJmb05zZDZPVlZIdFlVNkg0QkVIY2t5YktaTzRILUV1LUNNZkZFVkRiNnZUc3VRTDdQVGNCTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46017.72327546297</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Basketball Game Preview: London Pirates vs. Cornerstone Christian Warriors - MaxPreps.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 00:49:04 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPRm8yZ21LSTVzbVViT01uNzh1eDVQX2lZVVlJT2FMSnpkZ0hQLUttM1NLWGZlTl9sUTdYZkNjOTNXZjM0MFpnN0w5ekJDZ1pETkpXdnlrcHEwR2xFV2pFcHFiMXJpUDhTVEFsWTdOSDFhWjd3YnVLb0dMV2xiel96R1V3RHk4TEpwYkdjQmt5T1dvT3k0bFB2OWx5Y3RwSjZaUGZfaDBhMlN4TjNhU1c0ZC0yLXdfRkFHa2JGanBpMWI5TEFveDVUNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46018.03407407407</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Suspect arrested after stabbing his pregnant wife to death in front of their other children, cops say - Newswav</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 01:04:48 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPOWpDdnFlbjZCOG9hZkY2Y0Y0cjlJNHZMVFZSR0FjcU1jemljbG9HSVhIcFU0eUh4ek9oN1dCZW9QMElPd0t0czZlMmRZc2NsUllGRGpxdTVQOHRoWmxMalVGYWNfTHlDdktPNUhIMmlUSW5xenRSU1R3SWc2V3Z4Y1MyQmh4a3REbGpsd01yeGU0WktTMnFqRzZSN29MUDhmQzdHY2VvYUZEOHdJUVZ3enNOekJ1cEk?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46018.045</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>French police arrest suspect after three women stabbed on Paris metro - France 24</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 18:43:15 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNUhDNXJUZmQzeUlhUmlLci1qcW84MnRIOXdlT0VlUGxsT3JCcGhfajQ2VmNCT1N6UWJoVWJlZUpOb2ZsX2p5UmN2d1ZsMFRDQ1NsZTd1c19IZTdGQTRXbmlYZlBpUmdnSlhZUEVLM2YxN2FETS0zQ3FOV2hHdHFWeDk4TmpHYi1pT3RFWDgtMXoxUTBBZHdILU9saGsyUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46017.78003472222</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Assailant stabs 3 in Paris metro spree - The Economic Times</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 19:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOZjdwMERqVHdwOWhMNl85VVdPZWJGLUpnTFN5WDFXaDhGVzVtS1BRWGNLS0txVDZLY2ZoSHF6UDhWQVYxaFN4T0tvU2Rsdl9PbDlNaGhRQU1nWG9SX296QmtWY3VWd18tWU9rY1NzWllBSWFpbVhGWk1lV0VnWEhOQ1N3dzZJRDFTREVhTlRRd3lROW8xWk9OenV4aGdMUG1JNmZBYmJfSERzaTVsSmxaQjB2aXdlZ3p3LTZleVNjNmkzZ1F10gHEAUFVX3lxTE5mN3AwRGpUd3A5aEw2XzlVV09lYkYtSmdMU3lYMVdoOEZXNW1LUFFYY0tLS3FUNktjZmhIcXpQOFZBVjFoU3hPS29TZGx2X09sOU1oaFFBTWdYb1Jfb3pCa1ZjdVZ3Xy1ZT2tjU3NaWUFJYWltWEZaTWVXRWdYSE5DU3d3NklEMVNERWFOVFF3eVE5bzFaT056dXhoZ0xQbUk2ZkFiYl9IRHNpNWxKbFpCMHZpd2VnenctNmV5U2M2aTNnUXU?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46017.79375</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>UN chief says those behind ‘unacceptable’ Homs attack must face justice - Arab News</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 00:53:38 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1lNEY1UzFyTE4tTTVjcjFTSkVXa1FCVG5pa2F6SzN2UXo3U202aG1HRnhWcmY3RGVqb2NoOHRjdng0OGRkcWFBRW1CN29SRzJyeWlr?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46018.03724537037</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Short Term Charts Align With Long Term Uptrend in Salora International Limited - Bullish Engulfing Patterns &amp; You’ll Thank Yourself in 6 Months - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 06:20:31 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNZWJDQ3lRY2V4a3JlcGMwM2taaWM4YzFCTk9LMDNLRGdjYTN2ZHk1QXkzNGdVRzhZTThuVHJnZzJZWXNiYmZydXltTWZ2X0pjQ3JXYndOVFZLMXJnVUZ6MkpmbWV3SmJIUjNoazhsMTFHRDkyNWgyTUJiRXNHcHpJZ3BYVE92X3pfc2ExbVVIaHBydG5YUWY4QTNzUjZ2RGNsRU5ZTHZMVmJGWm9wUjNNU1N5ZXRhZVVIc0lDWDZmbFN1azAtMGQ0?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46018.26424768518</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Aly Traoré is attracting interest from Paris Saint-Germain - Foot Africa</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 18:45:09 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQblJUMFY1Z2owMTRKOHVvbUc2WlZFWXU1TDAyUjVIN0xYSFNUdUJZRjVUN3hiOTFkV1FxU0V2aC1NZGF1X1hiS3psZVVmTWV0OU1UUGt6SjFqR196T1VZNVBfdnRwOWhrMTQ0bGtnaFVEUjVkdUlWc2JaM0ZQNEhvUTRiWU9WQS0tU3lMMXMwNjRQMUVoQk5qSHZTeFNSeERQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46017.78135416667</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Powerful Bomb Explosion Strikes Bank in Thessaloniki - Greek City Times</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:19:46 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNZmstbTc3YzRfS2cwRGgwM3ctWHlrWGVPOVhqZjNsSUF0VjdXWDNnTWJFZndFWmR1RzdhRFljUTduckstb1dhX0o2ZFc3N3lhVjlEbmtsVE4wcF9LTHAtR0xVaF9XbUYyOTZZdDdMQzRnTTQ0WTI5cHcxRWc5ZUpGcjNDNmZ0eDdlT29RNzJZb1hvM3l2Ync?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46017.93039351852</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Two people have died in an explosion at a Norwegian chemical plant in France ᐉ Новини от Fakti.bg - World - fakti.bg</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 02:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPZGNUTHlMVXA5cHBlQ0c5M2Etbkd5X3UwSEc1NlU5WU00RThSNHI0MFN4NDAzY0xGNnhjaXFKZGo3WHdhR1hzQnZsdFJWaEdXYVNTTlgySnNySGtvT0ttNktHYTRFWG16MGREeUdUSlNubWF4T3ZMbUV3NDc2SUZIYTIxQTFfdktRT2tDbXBvSjBkaUhJYzNGNjJ6Ym52TUJpMHFfcnBpaF9tYmhiT3VsT3VtVkM?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46018.09791666667</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Support Zone Holds Steady for Ceigall India Limited After Dip - AI-Driven Market Analysis &amp; Beat the Market with AI Reports - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 02:31:54 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQY09iRFZaVEFSVDdic3AyZDNhdTlOMFFGS2NBWi15NXVvM0xjWHdVcXM4d2MtRXRERF93NENBWnJoUDRRc25KM2EyUXcwLUxzRlRkRjIxZElPX2NZSjM0Sm5yLUtwQURMTjhDdGF0N0U2U1BUUVlydElIQ3c2RXRaNFMtRDBSWjhvM2IxaUJnLVQ2TzRiRl9EZWpBWWE2NlRFRU1aLTRVNXdQYnFsR1VlTw?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46018.10548611111</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Jattashankar Industries Limited (514318) Quarterly Results Are Out - High Yield Income Stocks &amp; High Profit Stock Alerts - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 02:26:53 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOSnlmTjN5Q2cyTTJ5NTM3ZUJVbEV5TnJjSmljYkplMXp4dGh4dkU1bnNtcTVCaWJpS0hkcjg5aGh4VGdVckNJY0VmZTcyZDdURmFlSnpwWHVQQjZrV1pJMllmTUVrUWR4TVd2Q05wQTh0Vmk4SlN5X0NEOUc5ZUFMTDEzdFZld0E0Si0wdVVuSzFQTFdYOGw3OEdjWGdtdWF5OWsw?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46018.10200231482</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Aban Offshore Limited Approaches Support With Recovery in Sight - Sector-Based Investing &amp; Explosive Profit Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 20:24:42 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOS0RTTWlZZnZaT3FSY0RtX2JmbGFDRkdmeGRzY2dtT3JIN2kydHR4aW5ZWElwVUR3TUJjUHhOa3N4VmFhaUxJRkltSW9qaVktWXZ4SWI2MVdPZVlLaEpSbVQzdHlrNHpaM3kxbmpFX2hKOHU3cDd3eGxlZEJyNDVlQXYxYkdEQWtOVk9mUDJ3R2c3ZmNKa1ZBa0paM1c2dHFZSFI3RVljblp4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46017.85048611111</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Premium Capital Market and Investment Limited Added to High Probability Setup List - Earnings Volatility Patterns &amp; Free Explosive Portfolio Gains - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 03:35:57 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxONktnRXJWNEZWMUptNjUtR2NxTDRMZy1DSFhpYmdSanNaTUVNdldmekpkeXJaZURqR0t1WUtqMEUyZ1hlM3FBYTZZUnFqLWpRZ2pJX0VlUzFJSTBYNUdrZDh1ZlNxZTduTFRNdC1OU24zN2d3Y1B1M29oUXJudmxaNzZFRTJ6bFRMdlJVQ1liZ1Jka1NMaUl6SmVSSE1mQmxvckQyYzlNdmtjU0J3ZjVjeElfVkt1eGU4UU9UZFZTMkRSb056QTIxOFJ4TDc?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46018.14996527778</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Spices Trading Limited After Rally - Contrarian Investment Ideas &amp; Capitalize on Stocks with Explosive Potential - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 02:20:46 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPU2sybnM4U1k5UU1rc292cXN6N2k3Z01fc3NKb3gxOFJ5Y3ZMZGVNX0V3bjV0SmlTQkQ3S1Q0RVpseHQ0c3NUZVgwN1RUd2V0RElaa19JOUtfRFd3U3I5alF6NFV1amZaR2xHNUNXd01CNW1rUl9QS21abmxHMTAzbUR1a1kyN0VqSElOZkJvRTVVWGdHUTFxWVo0QjRsRkFEc3ExbzBjSXp2OFhiWmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46018.09775462963</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Trapped Investors in Sudarshan Chemical Industries Limited Await Breakout Signal - Bollinger Bands Signals &amp; Free Explosive Wealth Accumulation - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:42:10 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOamZESFVoUjZwRkMxdi1TRldiM3NHOVRmUDIwWmZidURLcXBUNGpTTGpFTDZfT1dnbGIwZ3Jpc1poSEMybUpRdnR3V0J5RDhIbHlOT1VnR0txNHFDMG56R3lJOHpjdFVDVzNKck5selVQSzU3bWhLdWFnQlVRYk53d01OM2hja2s5Ykw5WFlyWXpYZzRTMmJQVm1MaWt0Q21pLWttNkQtVjNCMUlCWTV1aVlBdmRXdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46017.94594907408</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Can Dhanada Corporation Limited Regain Momentum After Breakdown - Take Profit Strategies &amp; Minimize Portfolio Damage with Warnings - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:24:02 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPSVk1U3R0UkpLUk9MV0VnOXlSWGZwRTlJaFczczNoOFIyeWRGLXBYdzJIMmJjQUZNQWRjMkx4b2NET3p5SlZSV1VPWVFkTUlJMWxSOUhrTy1EZjN3ejlfcnQyZTg5WW9hWVJPMWY1S2ZrZmkxY01feUpDaVcyeUtMc0w3Rlhhcnl0YmZBN0htODZ0X3NObXZDcXZUanhWUmRjc1M4TnBLcko1dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46017.93335648148</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Relief Rally in Atul Ltd Stock — Can It Hold - Price Channel Trading &amp; Secret Picks Wall Street Isn’t Talking About - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:14:07 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQNm1yVzgwRVRjckdsc1NRMmFTWUxOa1laLWRWMWZQUnRUX3pEbGFIWldNcWhZNWNmMGExNWZ2X203RXUySk9QdjEzV2o5WHFpd0gxdzVNSzR2MU5BazZ6NmQ5ZlcwbEZERk16MTRJVU9pc0hYcHlLRV9pRDJUSWhZbjBBMTBjMmFiUndCRjluemFENTVMdW1hT2ZROA?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46017.9264699074</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Trident Texofab Limited Could See a Relief Rally From Support - Mean Reversion Trades &amp; Explosive Growth Opportunities - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 21:16:25 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPakJXTzluazlPRWZTWTVBdjdKNlJEMTVtLVplZUwzNkhwMmNIX080U1JZWmlJUmVPYThBYWpmUjdDZzNhTnQ1SkRTSEhHUkZIQ3J6UlMtTXNuVHN4aVRMM1dXTTNJaklfUjd3UnpjTVFkTlkwSC1PVzNRYmlCUFhDM3g2OWhwRThpVHdvNmZ5SFVJMVpwdDRaVnpuMEhpa3hfcHZXRXJTYndsRHp4cWFaYQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46017.88640046296</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Goblin India Limited Recovers — But Is It Sustainable - Small Cap Stock Opportunities &amp; Achieve Explosive Results - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 03:27:46 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNakgzMmZrTTctTEdoUHV4UmJTYVFxb1VMdWVrbEE4LVI2dndsRURTc0s0cElQVjFYb1ZRNmkwVXNaeHRWQ01rdGZ3LWoyZjRvdDVlbnFfdEt2VU0yb2lwU0UwQzQ1QVJQWlVWOEF2b0ZfcDNwLXBVMF9lNDh5dXlMaEdZZEdIZUdvQTE4Z2l3clk3OTBSR1RYaUZFUHhiZWFBV2dDZ0doaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46018.1442824074</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Linde India Limited (LINDEINDIA) Announces Strategic Shift - High Beta Stocks &amp; Access Free Tools and Start Investing - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:30:55 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMDJXQUpYSVR1YXpyN21FUjZqdFZ1ejFDMzQzbjJ1UGZrSU9PTkdDVXBWVkhxZVNpbWpUYmM4T0VYcjJ0YmRDbmNEclU0VDJ4TGNTUDBsbko1RHdVenpOdkxGN1g4eVJDcDZ1QW1lbjFWYVRmcmpTejBqZFh2M1o3M0w4UkRtVFpCQXd0d2FLbTZqcWMtQ2dpcUtjaDd4Z0VveE5zTA?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46017.93813657408</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>V.I.P. Industries Limited (VIPIND)’s Trend in 2025 - Low Beta Stocks &amp; Small Budget Capital Gain - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:41:38 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSnVxckdNMnAtdkF1WS1RcW9mbVIyTVlJamFxaWNQdlo0dmhkZ2hjRDNfNF9FS2FlaGJEQlA3ZllKTlBVRWdOTS15WnN0VWxxTXE3UENQMlhWSVFSTEJwbnVPR1BLWVVBUmdqYnM5Yy1DOHBJMmUwTDh2bmpDRklDRzBBVkxKMzhGNXFKQV9TNlEzM3JBczdteGRndUVCMnVMcVFyZg?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46017.9455787037</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Dhanlaxmi Cotex Limited (512485) Signs Major Deal - Low Beta Stocks &amp; Free Explosive Return Secrets - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 18:10:38 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNV1RLNUNvYVRUZFo1WS1ZeUd6SXlKYmpjTDJXRVRzelhjVVhqWFNpN01FS3VhX29SZXdHZ2tRbG1jY0ZpakNVc3lWTFg2QXR1MUtYakZNVW9KOEFZbkVYckszR3BZekJ5NmtnT0NkZ2VkSDhqem1kWTUyZjIxbHFrQV9VYi1OenZtSnNMQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46017.75738425926</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cone’s pep talk sparks Abarrientos explosion - Daily Tribune</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 20:17:12 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQU2lUd2xnM3ZldkUyVlRiSER2dGEyanVPT1RvS2tXTEw3bERZVEVQUWdvQ255dGl0U1JzM3BxVjgzbmFvVE05eGN3YThIYUVmTFlVRmhvTjZtU3VNOHJ2UnMxREZIX01fXzM3RFJrdENsTUtVZnJZN3VNTklUYXJCQjdtOVhlejBSNEprVVdzdWjSAZABQVVfeXFMUFNpVHdsZzN2ZXZFMlZUYkhEdnRhMmp1T09Ub0trV0xMN2xEWVRFUFFnb0NueXRpdFNSczNwcVY4M25hb1RNOXhjd2E4SGFFZkxZVUZob042bVN1TThydlJzMURGSF9NX18zN0RSa3RDbE1LVWZyWTd1TU5JVGFyQkI3bTlYZXowUjRKa1VXc3Vo?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46017.84527777778</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dagupan Explosion Kills 2 - Daily Tribune</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 16:04:47 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBPQlkya0ZOdDUyQm9PSExzZEM5eWFKbjQ0V0tjRTlkaHdsWDg2V1NMMFhScWJ2ZllIUG1JVk1xUVZkb1lkRnV5UWhOcWtBcGJVMTFqSjdtbDdWWnNLSndyOHhQOUFobmJpWVVHdGdmemY3RHM0emJuX9IBeEFVX3lxTFBPQlkya0ZOdDUyQm9PSExzZEM5eWFKbjQ0V0tjRTlkaHdsWDg2V1NMMFhScWJ2ZllIUG1JVk1xUVZkb1lkRnV5UWhOcWtBcGJVMTFqSjdtbDdWWnNLSndyOHhQOUFobmJpWVVHdGdmemY3RHM0emJuXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46017.66998842593</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bullish Pattern Emerging on Emkay Taps and Cutting Tools Limited (EMKAYTOOLS) - Monthly Performance Summary &amp; Smart Beta Strategies That Actually Work - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 05:22:37 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNdHhjSEw3T0lNSjZTQzFXRmhkMWs2VDJjbjdqUUs2dFJHQ1hpZG96bjJWOVZNdXFiVFdTLUgtaENWRlVLSjFtQ1hqSEtrSnR5Q3E4dURoQzA5cVdrclJpVk83ekFVaXFKUnE2WXgyUzBxWjJpc1ctd2pKU3AzTmFFTFF5MXJHOC01UzRrNFJCcUtZd0JVSHRWOU05Q1liTVJOTThiZWlkS3ExLTN2TmlkS0h3?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46018.22403935185</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Who are Reuben and Chloe in Emmerdale as huge update floors Mack - Daily Express</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 18:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQZlJBR1ZuYjRjVVpLUTVlNU1tRnRvU0tUTnpnclFEenNPMDg3Rjd3N19heTY2dzhzRFlvbGRFUTdhdkNlX0JHcVVnNlZHMEpIZUlwRV9RZkd4RmMtLW50Ui1hTFZGMVJRY2ZBY2I0dW1paUk5V04xSWsxdl9RZkhjQmtLWHdZbzhVTnfSAY8BQVVfeXFMTjJpWG13bHVQNE9XRVROc2MwWUFWeTdRUERORk52OVNMZU9HMXFKMzlfRDFHRnZPcGYtM3hzT0VkdXZtRjVTNkJjTkkyZm9obGp3MzBzUWJsdV9jTkNqZW90Mm1fZjhZUjlWTXdWRkdXdVJYaUJiWTNFMlZreldqQkJRSW5BYmdLd1pHNkVRdzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46017.76597222222</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Olympiacos Climbs Euroleague Standings After Bologna Victory - Greek City Times</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 23:27:25 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQRG12MFhrWV9wTEZLYXdWQTB0REZ2SXpxcmZRTWtYbnNxc2F6V1hCMW5pMkFBSzk5d292aVJRNHktMXdBRFBSbFBZRk1tMUZfN3hGaUR0ckdWOVdrcHVUZFRHVmJfeEZ2N1hqdHBmcGRsT19UQVlDeE5pSTJJNllJejhSSzZob0xocjhSTXJpcGNHZlhodTh4aWxXWjRfenJR?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46017.97737268519</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tampa native Rashad Godfrey excited to return home for Iowa bowl game - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 19:48:03 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNeG4tS0d4SHNBZ0ZwVzJUS29DRUE4ZUQ1UjVFZzRObTljUjNvczNOQzhyUGpoSS04cV9JRmRqY3JIT3UtWkhCdkc1aUxnMzRSUzFpX3VvM09KRUFNdUlnUUNndlVocWpqR1NMS0FoME1YMVVaNnJHMmNXaWg4TnNPOUx1ZWNLR05ibG45bmFtZHNSWEk5REptRnNXYTF5RlBpRjFwT3A1TXNIc2lONlpEWktCV25sS2dOVUVCemZ1Y0MwRENUUGJSSWJleGk0anJ1OHY4S3pvY096d1VPOXYyaUlqV195eW81X29XbU1SUHNxY3ZzUHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46017.82503472222</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Analytic Reyer Venezia: A EuroLeague-caliber offense, but defense needs reassessment. - Backdoorpodcast.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 15:45:35 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOS2V2aHdXRUpGdGNocXRGZDZuQ0NLUnpnY3k5US1zSDNBY3AxVUNTckFhT0dmcUZYSTd2TEJBdElGRUI5OUNMR1VfWmgyN2ZocUhJRFhIaDltZ2M4aHVSV19QbGhwMnk3cmswZHFDQnJOYzhjak5lTlZHNEpfcEd5SzM3Z2xFbHdiaEJXcWhxWFBTM2VvaFZrNEtlXzF2V3Bp?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46017.65665509259</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Iowa's Max Llewellyn on trying to stop Vanderbilt's Diego Pavia - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 19:00:55 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOemItLXZMR0VMRWJUZDBrMmlMSzA1SWJscXNHZllfcHNxWm5qd3FlYXRaMGVvWllKRUN5cmlZTnA0ZU1mMnQzdjFVelNRbENWSnBaNTJwVDVXdzhPT29HemhkQ1I4UmdZM2s1bFMtNGpvU29ZWXZDMkNfSUFXQzZBOFNZTWo3cEt2dGlnWEg1dUhVZDFrMGN3M3dleHRYbkxCQlhnUzJjX3JCU0l4XzdKN2tPQWl2WGdGeUtGankybWhaUFQ2QW5jb2NINGJLNXJCNnVaTjVyV042NDhpcXVlSTdiUTdZMjU1Z0RF?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46017.79230324074</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Report: De Winter swap could sway Juventus to part ways with Gatti - SempreMilan</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 17:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1DU0hhVFV4c3hUcy1aaUppRWNNTTRwY21JcG11ZnpTUnBTTzdEZHpNQWRJdFd2b1ZBYzd1M1JXamttZzMzdTJuSURMeGRZbkVkN25zSndfWElRVFgxSnc4UDJXQ2tkX1k4b1hzTtIBckFVX3lxTE1rV0RVcHZFT0F6WXRQNWljclQyckF1ZVhENml5aGxBb25zNFk5V0M0ZFFRX3dJaTJtLTVtRFdXZ3ZJZndnSDM5Mk0xWEtONUZDa09HY09ja2dJSVlzMGFqLUYyeHZ6Yk04SXlQNlNTM0JhQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46017.73611111111</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Sella will play in Milan tomorrow. Urania will have Gentile back. Berdini remains a doubt. - Quotidiano Sportivo</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 07:44:23 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNSTBKbE5rczFwOHFrc0tMVUdwOEZISVNIcjJPRHNUX1pyMXByN3dZNlRWR2RhV3BQWnVnQWJ0VUxPNG1EM3Y0NzI0YWlZNHpaRGM4eE9pZmtmNW8tTTNQVXRkT1NQZFAzbnZyU2dVTTNJblpJTTc4TGlIZklHekdpbDVwLXVmRFhoM3gzRA?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46018.32248842593</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Derby Decider: Inter Milan vs AC Milan – Can the Nerazzurri Defend San Siro Fortress? - inews.zoombangla.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 16:14:03 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNVzIyLVhIRjNkem1NR011TnFlYWVEY1g3ZWxPZF8yN2lxeUlWNklLamU4YjlHLXpaRzdCOGlldUl3a0Z2ekctNXdIZUwxeHJTaEs3UzJPckh6eE1TemFxZjZtbzd0cEdDSGhnM3hVdXhkbU55Q1h2RzY2bmlFc0RlYmhTOElwbUdkZlhTbHdMR1V3TEhIeTZwQUNqZzRfRkdfWWZVNmNYUDFSYzYycUh2aA?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46017.67642361111</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ukraine: Russian bomb hits busy road in Kharkiv, killing two and injuring six - Lapresse.US</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 16:51:01 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPZlExaGlmN3p0aVN3WXlSY2dTamtxTXRROTJIQ1hIRFFuQlRkVWNUZ2ZLcGowWG9wRGwwSnZWYVpMUDJ5Z3MzTHBvSkozOC1SSEM2d2ZwZUdCZll1TFN1ZmNfb3pSRmhVZlBhZGZKMEJZQjBTalB6dGRlc09YS0M5eE13OHhQLUFwQWpobDZfNldLU0gxMm5uX3Fick9ZdnBNSkFNWWV2c010NEhxWXJDdXFacw?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46017.70209490741</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Phoenix Suns Hold Off Cold-Shooting New Orleans Pelicans, 115-108 - Bharatbarta</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 04:17:01 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBhMTVTQnFFTnBuM3M1clhjZXc4WVZuWEFEa3pMMU5HbUcyX0NTXzVRMWJhVFg2VHlwdlRoU0ZmbktKUkk0c2xLNHlSU0lwc2JmbUkzUk1uUkhPdWdRWXB4VkUtR0RnQWxIMjdURFJDZkbSAXZBVV95cUxOUlZlVEs0aF9MNWxfdDlZdzl5Vmp4SFJMakZjRlhnSlVTMFBDUTNVY2RJZHplQnp3bTRkT2lvLUFSMHR4RU9XMndMYjhoTkVBYWhzcVZtZHkwMEIxOERsUnRxRkxuQlRHOGRlWm94TjA5SEdkYlJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46018.1784837963</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Brussels steps up policing for New Year's Eve - belganewsagency.eu</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 06:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGdHT21UVk01dC1RMEpnYlM4MDVEbXdRX0l3aklhVlNJek5jNXFlSHNiazhQaDdlWW15S1VISlhGVWRRNFhSSzJvYXFSOFV3d3FBYWM1UGJ5bVJSd0gwbkVfZnpPVWRlWlJGcWtHLVk2Q2xNYUdfd2g4cTFSYkt2ZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46018.28402777778</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Brussels Airport cancels 2,395 flights amid year of labor strikes - Türkiye Today</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 02:48:45 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPX1dxUVRSWGNoaGc3bEk5bUxEamloenQ4YjZRMEtZQkY5NDFrU3MwUDJ6bW01RUI1ZU1XcUJoSVRCdzBpZGtHTDJzbFFZZXFUSklGSUtTS19TNzl4VndobkptVGJPQ2VHY2oxTnNlS0x5THJ0bl9tU3pIeVJBX0s2ZENjd2FlcC1NWkloVC02Nzg1dlBmdVZhd2ZYWURhb3AtME5YZ2lqYzRUNlU?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46018.1171875</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Arrest warrant issued for man who attacked police officers with a knife in Kraainem - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:50:21 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxONEt0cU1ianRkeXZqeVk2bG0tME1mSEZxaEl6NDJfdkdwS2ZvSFEwak5vQnFZUlM2THJyRlFlUkFjcWhxMUZneC1OQ0lxZFdlRFVadXVfYW0wZC1FcDdQZnFsaUJwRzNYN3FfWXBfcS0zSnpNdThIaW1DUUo1Zk9IMUFyMDRIdTZTRUpNNXRhNmpGRkk4SGxlSTREWWNmUHV4dm5KR0pIOTU0aktYNm1rWHEzczNjTXFKTncwRzZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46017.95163194444</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Drug users in Brussels risk seizure of phones and cars (VIDEO) - VRT</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 06:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxONmhmNWlDUXBoNklpZWNZNzN1RlF4TTduaWRWMUtLTGRMaDBVYnptVU1leG43ZnRLc3QzWWdxa2x1anpIYk1aaXFtbmNDZmNTbmVsN3VzS2o0VWlFeEN1cGVYemZYZW5ZS3NPZktUZlNxTUM1cnJndEFvcnZjdUNLNG1zejBHQmlqR1BWaXNXaG54LW9hZnhqRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46018.25138888889</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Zelensky to meet Pres. Trump in Florida to address security guarantees, reconstruction - WPEC</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 03:13:32 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwJBVV95cUxPcnBOd1ptYkVaNFNac1BGQ0dfTXcwZ1VxRjJhQjFsRlVTNkd6d1NIMGFEYnRvODE2ZHJjQTJHSDVUUG5HX01LV0t5eVNkdnpJT1hIOGpRTjVYcVQ5bWdkTERzSFdkNmlnUmNqRWxveFpPbjVrVTV5SFY0X0FIRUc4LXNzcldzandfVXFfLWVNekVYVGZCU1FkNVJodzBLWmxaakFYN2dWV2c1Z3FSR2RhajJvYS1WTzZOVERZb2hvT1ZOa016OGhGc1J1MWVGWUxDMUNPSmdzTENUVUhBSE1KSGFQV1drMzNQVDZZdFVSLWxud3V6d3lOVlRSN2dHX0ZlZkpDV2NlaWlXby0zRnlQcExJTDI2RDNPSGY3X0lXcTRja0RQa1hGeHh0dnk0eC1mcFRrRG84RVhYNEx6dTlr?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46018.13439814815</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Police targeted by fireworks in Ganshoren - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 22:50:21 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNempzU0c2UkduSVprOXVtczZ6V3VPalV1dFBBRzQxZDBsZUFBRml1d0ZxdG1pbGEwbXlNX3lqbVpvTXBmeHVhcjh0TEZ1b05oemltdlJPdzVhV0ZkaFhhSjVFMEJxV1d4T2h1dXRYeW9fbUMyV01pUHFJM3RXT2lrSGFWZUtuQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46017.95163194444</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Eurovision 2026 Divides the Pop Scene: Belgium and Italy Threaten Boycott - Inbox.lv</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 16:18:36 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPZ2FKWkVvRHNjOGdkclAxMVBTamJLR0d6eXlEWTdCWGRNdFpkQWRxczNDY015XzBPbktsRldqNlhZSmt3MWNlb2FNemVVYkZOSldKam5lUzFDRUwteDItS09rN01GY0RiNm5JUERtc2FmbmFoeG1sTXdnUEdCMFdMUUJlTGxKSVQ1TFd1VkR1V1BFak5Semtvbk9MZHVHVzlhY2Z5T0ZhdFdMT2o1VkFqcDdlMnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46017.67958333333</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Two men missing at sea after Christmas swim in England - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 15:33:45 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPWDZzQ192NTNjeEpTU19DTW9fdUdENDBVMDhEYkhqcy1fZ0hFSkNubjVFZ0RQWFhPRDlPeTdMNC0tcnkzT0JuVWNacTBoVUQwektWQlgwV2FvemJRVkR5VE1qUWtMeGhGWTJmTFFJV0c5QUhjRFBGQlRsX1F0RGN2U3Eyd0JUY3BPbzBaalJETXpIY3ljd2RB?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46017.6484375</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Suitable funding source needed to progress project for Market Square in Kildare town - Ireland Live</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Fri, 26 Dec 2025 09:40:52 GMT</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQaHdSQUxNRV9kX2tGbUJYeGdMOHg3X2pSVmN5UkYtU1JENEdYX3BfWmhteDBjUURNZXMtSVVhWk1HWWtLVExoaWgtbXk3NTJoRllsRTQzR1VDbFlic3V1QjI5V0NWZ2VaREIweU0yOV9TUEhEaW1rdXlIekJKcUF2NzFRenJmbXhmM0VTd1RUZ3N0VGVJVVBlSEVucmQ3eV9xYVllMUwzQ1pFU1hHTmhPc3FWdWZRZjlWOFZEYlVSX1oyeFVJMkpURURsRUhuSWNqMHpCem1fcC15RDQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>46017.40337962963</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 16:39:03 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPRERIc3lpdm0zckQ4OEktX25uNWFDYklKV3NxanZHdTU2QWlpQm5aWlNWcnNCREU5bGlvTXhxRHh6LW5LTlVGN1RTN2NwSU00ZEUySVJuR19qZW5BS1U5ZVcxMEo3T1hrV3UzYWFRR3RncVVRZGdqc3RkQVVfUTNOT1hCMExqVnV5ZXdocEk2c0ZveXJHcExOZmREUFN1ZDdSeEE2eVFEWDhYMXQ4X2FvQU1UVm1kRnQwWGxkTGFBS29ndUtXSDZ3bG1uMkhueXdJY2hfVnVwZzJxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46017.69378472222</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Christy Moore interrogation in UK questioned by Irish officials in 2004 - Kildare Now</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 00:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPYWx2YWd0ZlUzN09QSDlrZnNQR0JTYl80RVk5OW53dUQ0Mm9PV3B0WmxWcDE0RVl6V2VOY1JOeWRMaDJWVXNHak1Ia2YxVi0tYUlMWTZvMEhHWjdaNno1VXBPY3hUajhrZVc4c2FRS3hpM0JoaTVzN21CcWwtYzljY2xtRk5Gek9LZGNlU3l2YVg3TlJELW1LMkNLN01nWGF1VjVDQmRtXzZXNW1TX2FqNU5ESFVPRGdBWXVsT1VlT2pWcXZoMVFMSW1n?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46018.00069444445</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NEW 4pc Gucci Guilty Pour Homme (For Him) EDT and EDP Fragrance Spray Sample Set - www.noisemag.net</t>
+          <t>Massimo Rivola shares Aprilia ‘priority’ amid links with Valentino Rossi’s VR46 - motogpnews.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:11:39 GMT</t>
+          <t>Sun, 28 Dec 2025 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOWFExN0h3clZQTGhPRGtEV0hTT2k2dFRjY2NDR3k1SzNaRFlGVmtYSnpHV2I5SFpobHpkRFF4b0tGYURqQl9STElHZXR2bnNaMG5mMkxWVld4QmpES3dZTW5rd3RkS1dIZkcxVDZCNENYNlhCRnBXbTBnVnB1QzVlQ1FPWldXeVk2NVlyV2s4bU04UUhyNTNKQkNIcmxaTFhmdFI4b3duWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQb2t2YXI0ZTNvY01uTU5VbmJjV3ExTGxsYl80Ry1SYnN1ZGtRRE1wTW9XZ0NxQU5wanZ2VzRhNktyN2k0Mk04bTNfeWlXUE5UUkxOVjIyT19aUUhtU3Jta20xQWRJYlBxQnQ5ZWxZN0Z4RVpSSmNxLU1xUDNWMEtwWnBQSVZyb01kOGk0S3VvNzVuczhCekIxTG92dDFRRWhJUGhtY3BqOElpV29fbTBoeUx4V3BRbGpTaEpMcUxmOWI0LXBCNXVFVA?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46018.42475694444</v>
+        <v>46019.29166666666</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Watch Moments That Defined 2025, From Taylor Swift’s Cartier Demoiselle to Rihanna’s Royal Oak - British Vogue</t>
+          <t>Armani men’s fragrance: already a French favorite in 2026 - Paris Select Book</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 13:00:00 GMT</t>
+          <t>Sat, 27 Dec 2025 19:20:49 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9VZmJZSFhsR1Y4cGlEUUhON0I5LXFRSzMzVXBLZm1yeW42TlRRRXJrQ3lvbU1jT2ZLenZ0UlRDa1RJU3k2YUxNeVk4TUZEeExHOUtTSm90V19fazV5SW80cjhHbEwySUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQUZhUGxMczBJeXBKNlJWYnU5YVVKTmZZWW94a3gwbjBqMXlBWm93MWswUEVublRZUl80OXRZeE9SRkVWajgtNjZhYmtIQW0zcXR4NWIzZ2N2bnpIRGQ2ZDVrZ3pXTUpMWGFhM18zOS1pX2lWN1BSU1hBUzQ1TlViUzNZSWo3a2p5elBPSmN5THpOMmtCeHdGWW12YkFSd2ZZYWxIeg?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46018.54166666666</v>
+        <v>46018.80612268519</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Everything Meghan Markle Wore in 2025: Custom Balenciaga, Ralph Lauren Suits and More - WWD</t>
+          <t>'Divine' Gucci perfume with more than 1,300 five-star reviews has £40 off - Daily Express</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:03:08 GMT</t>
+          <t>Sun, 28 Dec 2025 08:01:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNdG1LWVVuYUxlMnE4WW10aXZ4WTh6eHFhOEZTWGxtbGtWS2ZFTlY3dWZmRkNtTTdhLVpVV3dlMjdLTnZkMzhwcTFCM0gtWHlEY3hXSmlKU0NSaDZnRFpKbUJtY2pqT1VEbFlqWTU4V0g5eS1JOHQ5cjhCTGpoUHVUX19IVEdfTUlwbTNwWlZIYVA3R3pHX0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQLS1MamdubDBuWjBfV044dXk1LUFmSWotX0J6X3JELW5uQWpFTlhzREI4NVh6Mm9rbUVyMk9RbmxoSThzYW92TEx1QUllM2RuRHU3TWhwNkxidFBUYVBfU0lqaHdtQjhJYi1vU004UThyc1ZSS3NZRGxtVkVYRUdWNS1kN25CMHhG0gGOAUFVX3lxTE1FOFJiWHNpN1ZXb2hEMWdkM3NaQklfTjR4M09XLS14c21aQUtPbW9QZzJkd2ZHamRpTEQ1TXU4RW5CUUR3TVJZOERZNndVejFxdGdtV1NsREl5RHZKRmpnVjJrQ2Z5dktPTk9rY1drT2l1ak1xaGlhMkRrSWhIQWhPYkZLd2JfUGhZV016QXc?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46018.50217592593</v>
+        <v>46019.33402777778</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cate Blanchett guest edits TODAY on BBC Radio 4; new campaigns for Armani Sì perfume and Uniqlo Heattech - Cate Blanchett Fan</t>
+          <t>Timothee Chalamet fans think he showered Kylie Jenner with $60k Cartier for Christmas - Daily Mail</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:00:49 GMT</t>
+          <t>Sat, 27 Dec 2025 23:18:28 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNZll4aklWY0xBQzJmVDJLQktuR0otcnBBQm5NbzZYaFAtZU5nM3JOT19GUlU3Mk45bEZZX2FoLXhmcmZmLWJqVlBjSFRhV0JzRnRsam9QTFQ0SDE0SE56YTZicTlaNklUNWs3V0xsQkxWX2d0dXE0UHh6Y2RZc2pJYklRYVdCXzF2Y2FQaHhNZFFrZVFxSEd3LWFfaUlqYlpOTW1teEx1ZjlDcEtoRUtkampkUUhNbXVVLUd5NTZNYURpSXZ5aHBzUXp1elk3b0xzMjlmTVk1VWRQWHpOOFBF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOOEE3MlRNbEtQQ2oyNHJSNWk3YTVSMUdqWFg2X0QtSlAybTRqLXhBRjhnVmxWZmNUdzdxQks2U1pFczlDSmo1bDA2dXpVaXFEN3NPN3BfY0R5NDhUMjIxbHptczY1c2pGTXlELWs1RXdWYUF2ZjVkZ1BZZC1VamsxcDg1X2Z4VldaakFYek1WTWlha21ZQ1dnVXJxSDNsd0lESmZ0aXBNMzBnVk1NU0I1Vk5PSkhSV01f0gG-AUFVX3lxTE13a0pvQWRnWHdTWXAzeEtNTFlrcXJCcVM5LUkyVGpsblFhb0hma01QWFFyQXlQTTRNYVpqYmlXcmk5QmZMemEtNHR5QU1PYWMwaUtTeFlXcF9zLVlaX29fbjBDT2pCckd2b05EdDJqTU9sMHhCNUNFcGczY2p1aTVtUmNPTDFNTURlVW92em1tMlVzbzVZeExYUUJIeUcxeVZZakpiVm5lX1lyTDIyYVh6M21vQkdtb0VXUTBycnc?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46018.4172337963</v>
+        <v>46018.97115740741</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inside a Bird Lover’s $130,500 Living Room, Where Gucci Herons Steal the Show - The Wall Street Journal</t>
+          <t>Dior Launches New Addict Lip Glow Oils and Matching Fruity-Floral Perfumes - L'OFFICIEL USA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 14:00:00 GMT</t>
+          <t>Sat, 27 Dec 2025 16:01:39 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivANBVV95cUxNeXZ4OXlUYVh1RlNraEd1N3M0WUtRSFU0UHp0T1VYbFBoUDZGX1o4eWFxTmVxNkJUaFFTS1JRcXl0cW5OdmpnS2Rqa056RG56eE9xb2NlNDdXNzBGb3FvVmdrc1RibXpTSV85Q1d5MjhmbGVUbjBtRTZ0N1VzTkFvS1ZURmJxdUNGOVRnUlFnbndYd095TkJQNTRoak9fRmdxWHNickNZaEM3Umk0QVZLRjdfV0JaUng1bXNFcHFMNVNWdzIzem4zLVFpQnNIRF9lcE8xU09nZWRBbVVnWnJDeGUwTzEyQ1NmUVNfTDBPRU42VjZvQ2ZkVTZpZ2Iyck13Tl8zNVNfLVVrY3FFbERkb1k0NkFiNTRZYldmLVI0ZlVidXBkN3NuZVJuWFdwdWJpalRZajBIaEJqRVBOWUR3MUg4YVUyUjAwYzNzRTBzTWJ1bFlMM0I4S0Z6R2tITl94WkF3ZjBKNVY5cV9pSXJRcWR5SUpLZklLZnF0Ml9YOHFsc3JQWUM0VGZkTDRqSmxnVkg5ekljOGRvOEU2MEc0QlFLNEZUQV9mNlJaRS1uYzBrLXl6a29qbFdFemY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPWlZfQ2hDZlc5QnpMdWl1Y3BlMUV6akpEaWJqVmFfRm0ybk5mcnVDTzQ3LVRNS2RFcVNMY1RmT2NBaGs2MlB6b2puZ0lHRk9VQ3E0b3NFbkhJNjZheGdSNlUtYUVGTVNRZk9udDRxSnFkZDg1U3hjdTJ2OElGNmNwMm9fekNTSUx2VlltYl9IaFAzVlMxeTBHRUlR?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46018.58333333334</v>
+        <v>46018.6678125</v>
       </c>
     </row>
     <row r="7">
@@ -647,123 +647,123 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Burney Co. Boosts Stake in Ralph Lauren Corporation $RL - MarketBeat</t>
+          <t>'Very comfortable' £42 Calvin Klein boxer three cut slashed to £26 in Amazon sale - Daily Star</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 09:33:06 GMT</t>
+          <t>Sun, 28 Dec 2025 07:26:18 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPVm9jOFZ1a3pVUmtITmlrRVF1UlR5YXNFRkYtd1UtcThXVC1ZVVlFRXZWdlNRdDEzMHlVd05la1ljdWwzbVZqQjdpQ1pGNVhubWlvTGtwLWtpZlBLWF9vTjhDTm9EbmY5Z2dCV1JBUkVKN2laZWg4Q1BjWUZVeEVvbVRocjVPU0xialdjdHpvMHFZTm95YjFrTmdsR0dGSFhiMHc5WnNESWNrcWlxNnV3YmtfdlI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOQmRiNVFOVUhObGdZbWl1MWZIbzJTNkYxVFRPdm5yRzdTYjBEZFRpVUtDS2Vkb3NXNHVfaExMaHl4ZUJQSTVNb1pMd3pMbE5jSHp6b0dad0pJc2M0T0JGT0dDaUl3TUhyWFl1UzNPZHRRMWd3R0ZPWklGU2RmRHVPZVpnN3V2clk?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46018.39798611111</v>
+        <v>46019.30993055556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wave of companies sign up to Generation Logistics campaign - Motor Transport</t>
+          <t>B&amp;M European Value Retail SA Unsponsored ADR (OTCMKTS:BMRRY) Short Interest Up 76.1% in December - MarketBeat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:05:13 GMT</t>
+          <t>Sun, 28 Dec 2025 07:57:50 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOMThnR2Q5TzdqbnZkZ1hwSXFwekZjbnN6X283dUpLNXdaVDVSMDFsWXl3NG5tY25OVy1YOHdyNHdJUlRjeWctNWtMQ3hlUk1Qemp5N2FhOWduVVR0YWZUS1k4SkdCUTlvaWdMdEdjVnhxczB2Z0xtbXN6c0xQcVhGTWYtemNfQVJqTGVsWk5ncEJuT05GWFNwZWVqN1hPS1hZWVc0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNRTR3Nm1wMVV0czZqZlJmeHlGSThIX2lpbVV3ZzQ4enhzTDdsalowNTV0RktkYWJVZkZ6ejZBVEVUaWdlUWptNkRKMU1hY2Roc0lUZnFFRlotRnIxcjFsYmZfbXY4OEFMTGRjSU1VejZUdXB5bW5OY3dBbDdfVEc0bTlrMENkN29zY2w4c3R5a1pDS285Q3lmMEdIUGF3VGNLZEg5UWJNUDdaVUJpWXdmaVRNRTlFRi1oSkZiUzFwNzFyRVliZzZpbEZZNk5ZNHRLRGgxc0V5X1lPZzN6?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46018.42028935185</v>
+        <v>46019.3318287037</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Evri and Home Office issue 'crucial' warning for millions of UK households - Birmingham Live</t>
+          <t>Driven by stronger fundamentals, Tier II/III boom, retail sector set for accelerated growth in 2026 - MSN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 08:26:00 GMT</t>
+          <t>Sat, 27 Dec 2025 15:24:06 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQYnFuWXZwX1laSkxvMmhvaGg0MjhsM3JpTUI3d1FlakVWd3pJX1AyRkZUTDNkUWp0dWdZSmliakFLQ2NiMnpGbjFIS2doUV9NMjdSeVg0eDFSTnlGak1WVURxZXI5UmN2NXBIQkNPZWhSYWJLVXV6VDNHRXQzZG54dU9zN25jYUZFTTZHRDQzMUlfU3RIaUQyd2x5NNIBmwFBVV95cUxQYnFuWXZwX1laSkxvMmhvaGg0MjhsM3JpTUI3d1FlakVWd3pJX1AyRkZUTDNkUWp0dWdZSmliakFLQ2NiMnpGbjFIS2doUV9NMjdSeVg0eDFSTnlGak1WVURxZXI5UmN2NXBIQkNPZWhSYWJLVXV6VDNHRXQzZG54dU9zN25jYUZFTTZHRDQzMUlfU3RIaUQyd2x5NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPQVVCMWdYX0VaVVJwUVJ6TTZBZ0VSUkRFcl9NdGZvdV9uck8xdm9taXVXcmNVdmlmcGI4OXB6WG9WU292Vk9rbnJmT0ctSE9STlotVklRN09WMVZDYTBpWmhXUUNwb0NRRFB2STJuMUF0RUlRYkNzZ1MzVWVEaXoyYzJUT29FZlNpclZHRXEwQXp5T1hNZEkwMXF6X1lJdkJNcExSZElwR195alNOa1ptMHQ5Zlh4UzhtZWxGVlVZQldIYWp3WW5aQmJmVnBBQjRCaklHU1JPa0pfNFZ0YUtRemRjSk1tcWVZZ25HWVJGcU8tejR3OHFRd0FFRFotTG9ubHN6TVdQUmN2UQ?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46018.35138888889</v>
+        <v>46018.64173611111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'My Package in There?:' Amazon Driver Says This 'Might' Be His Last Day. People Can’t Believe He Still Has a Job - Motor1.com</t>
+          <t>Contrasting B&amp;M European Value Retail (OTCMKTS:BMRRY) and Dogness (International) (NASDAQ:DOGZ) - Defense World</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 09:00:15 GMT</t>
+          <t>Sun, 28 Dec 2025 06:55:27 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB3Sk5yU1VvelVaa3RfSlZ1SGFkS1k2UWNGS2NJQ0tGNV92QVFMMEVub1FZMU9uUFMzZjRPU0dIU29nZ1JwRVFSNkRhYkNQdGFIMzN6U1BfYWpiWTg5OXVUVjYydkc2Z3BMWGFiaUhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNLW13azVXX1gwZmRUbTBEQU9MVGVHaENzOEZMenctX2JWenB0d25tdHRvQk03T1pYTXUzSE1kLUtMeWE5ZkdfN1A5RWhzaHR4dTZiSEY3NGhTblcxNWRXUm9md1JobGdxeFBvYzJCdkt4cGhibnRZM3NaeUR3MzdyTXFLZjFRSU1EQzVkN1RidTdJbU42YlgtdmRiU0N6MzZ3U05aaUVYa09uVGVLLUxWdTlZWm1lMlpyTUx2UGpQSjk4d21EVjN2NS1mZw?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46018.37517361111</v>
+        <v>46019.28850694445</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Woman claims Amazon delivery box came stuffed with hundreds of blank ballots - AOL.com</t>
+          <t>Kentucky scrapyard worker injured in UPS plane crash dies on Christmas, raising deaths to 15 - Daily Mail</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:39:13 GMT</t>
+          <t>Sun, 28 Dec 2025 03:55:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPWHlJdEh4OVBjSFFPWUhjRTZZcTFpbzVXV0c4Sk05UnlrVmNxTnhLa18tLVFHb0NvQjJCT0VKLXcwTnpKV1FBNHROai04QmxxQW5VUFhhR293VlJ1VzBUMC0zSU5wSVUzYmdxUkNIM20zaUpVOF9vZDM1VFRScE14RW9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPZTRnLV9ILUlsYnUzWEN6ZE1YS2xVSkZUTXF2RXQ0akwzZlZEZVNNUTM2Y2lTal9OR0tWZmRsbzdsVmFMVW9FSXFUQzBVbTJWMDg0RVhQRXNTTXAxVHlZaHBiUGt4NFh5V2J1VjJ0alcyUGdtWGhpR0FCQ3k1QjdCYk5GYUNxM0tvTzh3aURvXy1CUGtQX2NudmlDS0xRRi1r0gGmAUFVX3lxTE9iRkhXUDVhVml3QXhHQUpxbkd4WFlXeWhRWEVLbGw3MlQ1cW9Xd1VjUFo1SDl1bFhVbDAwdkFCbk4ydXkzNGVYZ3ZVNkI2Vm9qbXZ1RGVuekdwNmdLcS12VXQwTmNQRFVDVEFRSlprRU1Rd2Q2eTdTYlQ0d2Z2cURxNEhfTXVkVlVrbWJwOUM3UG10NVhCMVN6VWVVZWQ1cHF4aDZQOVE?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46018.5272337963</v>
+        <v>46019.16319444445</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Walmart Sees Online Sales Skyrocket in 2025 as it Takes on Amazon, but the Christmas Shopping Season Has Taxed Its Delivery System - | Cord Cutters News</t>
+          <t>Man chased Amazon driver and shouted racist abuse in 'red mist' pursuit - Ardrossan Herald</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 13:35:17 GMT</t>
+          <t>Sat, 27 Dec 2025 15:37:54 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPaVpJQWFETmdRLUxTMkRhSlJqR2x2Tm5pbUlDMDJ3RlY1ck9KbmdyckpEa2s1UnUtWTg2QzhZN2ZqRTFiNXdueThBMERzVkg3cUtMVUlzTm1uTjI1ME9CbkREQkw4aHJJd2U5XzhsQl9hR1M2cHR2eFBpR29pQkoxVHY5VnhzbUw1b1hXYUo5M20xNS1oQ2IxYlgzMlpubmt2a3hPTENMRzhoOUVFdUZtME5BSnFuT090emo0Z3RXUzlXbG9FamY5QURGQ2NnNnU4ME9BdzFFLW1mZzhUWFlRRzhDNUoweDBsbFp5NVd6WdIB9wFBVV95cUxPS0k0NEJseWppaWhBX1JVNjVpa1VYUG9rekdBV1FCdDllMElLWXVTV2JBQ2NlSzU4d1dHb2tiZVFKMVpsbk9GTWJhRWpIbEJLTklzSXZqWG9iNTNUSUtneWhJeDdrRXBpUllwbGFuMWNuR3h3cUZNcDZHTWxnMFQwTndjMkNLOURKTjlva3Z4MUhCWjkwR1BfczNydGJPak1PSnBIcDR6d08yMlQtZlB5clV0aHpubkFOMXFla3A2cG5GYTdJWUY4WmpMUG1BTHhZMzNyWUdMbUI2V1BVZ1VGaGpvMEN6ZElzVnFSUDNYejRNRXBWSWw4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPLVZxNXl2ZThvLWZtME9DYWU2ZlRScDFFQzM5bzBKeGJmRHM2Wm0zbGctakVOX0RubTFxaFZmWi1VSmpBa0xTaXp5S0plUV9YOEFlVVQ0Q3pLaWVWZjdnaFNBRkluYW9PdzR3Q0RKOUEyM0JpbklWTW1ycjJRSzNJRDlZUGZ5alhaRllYVnZPcVBjalBOd1V6LUpDb3o?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46018.56616898148</v>
+        <v>46018.65131944444</v>
       </c>
     </row>
     <row r="13">
@@ -845,24 +845,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amazon plans a new 'rush' pickup service as it doubles down on rapid delivery - AOL.com</t>
+          <t>‘My Package in There?:’ Amazon Driver Says This ‘Might’ Be His Last Day. People Can’t Believe He Still Has a Job - Motor1.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:25:10 GMT</t>
+          <t>Sat, 27 Dec 2025 21:20:20 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQRjNxRy1hbXVBRjA4SWFFeFZzOG1zejh3WlVRNDNBYlNBUlBDbUU5cDgxcFFHLWFsV2NVT2Qxb0tKbjBSUVRNQ19ZWEozR0U3aDhPMFZ5S0dtSGJWZlRlQkFscDR4ZTVadnlOMlVYblpJNHYybXVMQ2VFYXdYcGc2RmVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB3Sk5yU1VvelVaa3RfSlZ1SGFkS1k2UWNGS2NJQ0tGNV92QVFMMEVub1FZMU9uUFMzZjRPU0dIU29nZ1JwRVFSNkRhYkNQdGFIMzN6U1BfYWpiWTg5OXVUVjYydkc2Z3BMWGFiaUhn?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46018.47581018518</v>
+        <v>46018.88912037037</v>
       </c>
     </row>
     <row r="14">
@@ -878,24 +878,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'Grinch' UPS sued over holiday pay for workers - AOL.com</t>
+          <t>How to cancel your Amazon Prime membership - Mashable</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:30:37 GMT</t>
+          <t>Sat, 27 Dec 2025 23:00:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5HbC11LVhpYVpjcy1YY0dJUTdTLU5KZUhJS3FmQkNQMTVjWTFVWkhiUlNMdU9LMzdzRzEzSlFqSl9CQ0VDcnFnVW1HYVhRWDlhVks0cnNhVUN1clpZa2FHVmpkNjBjQzlLaTVIcmtTbjlIWl9DSFM3MUhJem8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5ic1V0VkFGNTNfbXBMWXQ3Q1cyNXZXMHdaRmJDZTRKakF3VWJid1M4VkNMcEJ3dnFzb0lvSmlmWE9ZdTNfa01qRUJrVHpxT1lVTkVoYlg0cjJsRU5RNkFMU1drQjBiQQ?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46018.47959490741</v>
+        <v>46018.95833333334</v>
       </c>
     </row>
     <row r="15">
@@ -911,1311 +911,3522 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Where Will UPS Stock Be in 1 Year? - AOL.com</t>
+          <t>Amazon Drone Delivery Now Live in Hazel Park, Nearby Cities - Metro Detroit News</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 09:46:38 GMT</t>
+          <t>Sat, 27 Dec 2025 21:01:36 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1UUG5rVmlBcFV2VzBNRkFkdWJfX2dPNWgyOGhickVZbWlJWVpqQWxBNUdKeDJpVGxMalJIcEcwM3JvWlFwS0Q5SVR5ZE1mSUJFVFREY3Vyb3FobzdBcEROWnZHVUhzZkVxcnFUNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSjBMZTZfZk9aYjRVdGRyQzladXJJRlNkeFdUWjFuelUwV1NPZV9fYzlkRjBQU3RDdFY1dTZZUWVrYzJ3MmdaZWFSSjlwZ1JCc284OXBTYmw0UF9DcFoxUGNnRy1weXlscC1EU0Nfbld4ZW83OW1OUk02dFFTZDhqZjNzb1UtS0pXdjNPNTlOdUd5b2N5OGc?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46018.40738425926</v>
+        <v>46018.87611111111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Specialities Limited Recovery Likely Here’s What Data Shows - Stock Buyback Updates &amp; Explosive Capital Gains - bollywoodhelpline.com</t>
+          <t>Platform Vs Partner: Gig Workers' Strike To Disrupt New Year's Eve Surge - NDTV</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:35:33 GMT</t>
+          <t>Sat, 27 Dec 2025 15:18:18 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPNm9xVlFCNDRsZm1hcWFoZ2RjVE9BbVBfZHhLU1RUdFlpV016M0xhc0pmb0ZXQkt0NXd1OElvNTlVSTcxQ0ZzZFZoUXNid19yQXJNSUJncTZYaTZNeVA3cHZKMzUwckM2VzFZMXUycFJNejBod2R0RmVtR25udjcyWWRLcXVrekhVX0RycEJZa1pfT0xaQmlsTkE2eEVMb3hGYUlPVmc4Mk4zdlVOaU1sRDZvQkJIVkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdHF2OHFXbjc3UW56ekNmcGYycEhRbFI2S256NmZhX01GbWRGeTVlZmkzQVpxTjhFc3B6c3ZiaGE3a3FjYUw5bkRYYms4U2xlNkVMOUtUQTVBaFNXbGdaVWM5bUlieFZ4MkJMeTlCcWo5dHNlSXBSVWIzN3ZRNXlnaF8xOS1LQkZnaHVrMHNxekE3ZlVTREF6ZFZ5VlMzcnotQ0pQSkI1MzNzNzVIWFpB0gG3AUFVX3lxTE44S2RYdnhYdFUxbE03SEJhRS1seXUzTng0cGs3ckpPOTViaVJXaU9HblZrZEpuVkVoMjhXUU42SFR4T3dxZWNpNVFiSzF3bjJiNDZDaG9VSlRMeHU5blFJTzM4YXZlNklFay1yUkw0Z2Y0YU5pamZqYzVRS05oanVEQ2lhSHlQZExpZnpSbHIxNzRXYWQtTUQ0SVdMUEZVNWZIc0xPR01wVFJUTDhmYXBnaGhZZUFRVQ?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46018.48302083334</v>
+        <v>46018.63770833334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, German language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bombe" OR "explosion" OR "unbeaufsichtigtes Paket"  OR "verdächtiges Paket" OR "Sprengstoffe" OR "Bombendrohung" OR "Schießen" OR "Stechen")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Neue Virus-Variante lässt Fallzahlen in die Höhe schießen: Experte warnt vor „großer Saison“ - Frankfurter Rundschau</t>
+          <t>Amazon Prime Is Cracking Down on Account Sharing. Here’s What It Means for You - AOL.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:35:00 GMT</t>
+          <t>Sat, 27 Dec 2025 23:39:17 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQdjlTZExkUWlNbC1EODAwdFpzVkRaVlM1Rjk3VTlCQ1E3cVNJV3prVmlVT01QSGJGYzVPWGNncUhUcDlEbU5kZFFzWGg1ZEtpYVBSQlFuZ1RIV3dLSklsaGhuWGwxUC1RZ18wZXczQllhdVVKdWJpeDkzdjl5UU5oVnQxQVB5OTFQSTFabUNla3JDN1Z6a0VacC1DcG1UMUJIVnN0eEc0eDJMQldiMUJMT2FWbkpZS1VyYzFjM0E0UkVPNzljd0pVOVVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE45c0kyeTFsWmtmTDF3TnQtUXY1RG9NMFpCdnJoVGszV1JCcFF3SjdteGVWOXVqVURNaVEyblV4Vm5nelhPa2hDYUJpWS1TTmpuWHNqUF9VaDBRSER2UTRfX2Q2emc0UzBGb2hKMEtyQ0I2bloybDZlNQ?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46018.52430555555</v>
+        <v>46018.98561342592</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Labour Is Building Farage’s State - tribunemag.co.uk</t>
+          <t>Brecon Posties are the best in Wales - it's official! - Brecon &amp; Radnor Express</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 09:55:09 GMT</t>
+          <t>Sun, 28 Dec 2025 07:04:05 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9zOGFEblVPRFdCb3BsMlJjQUdEcmFHMHozckhfWEFsdUV6ZU5xa0U4bGQwWGZPYWlmNjh2TXNQSjA1cnRKbnlWWnFLU2FlTW8tc2N3X3hmOVFrTnVjNi1lclNUb3ctdlhEV2tEMHlBUFJDUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPaW85ZU1jcXBDb1pFUXJVNmNocU9JUmo4ZkxMMTlxRUlyS2UwcWxuN3U1U1U3cFR6Tm9kc3YtT2VHLTI0NEpaTU5lQUdxeVRqdk82MHAxTmdNR3M1eG5keldlZE8zZmJEcFlvVjVuQ3dGNUtvUU14RG5GaEtZaXhsWHlfNFRRWktEdDZYZjM2VXdFU3cySWJfYg?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46018.41329861111</v>
+        <v>46019.29450231481</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland’s eye-watering shoplifting crimes revealed as number of shocking thefts soar - The Scottish Sun</t>
+          <t>Wigan mum believed to be UK's longest-serving Evri courier after almost 40 years - Wigan Today</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:16:00 GMT</t>
+          <t>Sat, 27 Dec 2025 15:45:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQZUJkMnBfeVBvUV9vclNFZ1hWcGpwZWVxblNJSGNWaVVCd2diZEZhRnc1VWozcUZVNXpBWk5sb3NhYjVaTDV1NThrRXBqQVpLUG9oRV8wR1FuVGljdlE1UTNpdFQyM2xmU3paOS04d05hV3lGNFdUOG02NmJVRXNLTjFqckdjdDRINENZYnpXYlZtQWZoYWE2b0h4d2lEWDQxa2Q2SHRBSGw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQX0ZmMlhyX3IzRWowdDZzVUc5NnVTZGxYaGN6d3NrUUhkMndIdmswS2tiQWV5NUVzTHRjTnEyaFdrREpPUlBSZzhJV05BSkJ4eFdyX2FOY0xqRy1qZHFlSklfWng4X3dzVHdVWVl2S041bDItTWdSLTNSWnZJOFBITHpLekdBY2drNTJxUS1jRldzOVVuOWZuQi05b1lBU0Fsc3N4Tl93YURyN05nUS1wVHczQXN6YlNwdXNTbkE2ZUgzVGlh?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46018.42777777778</v>
+        <v>46018.65625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Man accused of shooting Glasgow gangsters at Spanish bar to spend New Year's in jail - The Mirror</t>
+          <t>Mom can’t believe who opens the front door.🚪#Humankind - facebook.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:04:00 GMT</t>
+          <t>Sun, 28 Dec 2025 02:46:24 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPQ0l6RTR1Rnc1U0xSOWlLRFkxd1FlZXJWYVZGSlktbElJbTdNZzJReGJXRXJIOGVLNnJ6dVE3dE92WDNtSi1jTjZ1QUNvVXZ0bXc0S29qMjZ1bl9ISkUxS2FNdTVNeXJ1U2o1Z3lhWkh1d2hWelVaT2JnU016OUExSzByMjB0N2JaQ2RiZWZiNXJud9IBlwFBVV95cUxPS3Q0NUk0SmJsSzFhc2FsLXdlbmUzRktfMjBZMG13ZEV3VGFjWWNaUTVCWUtHNHBuZHo1OV9pQlJOcDluMnpqX1psU3N4RkllNnFoUTNNQld0SEtnWi1pTzgyTGdaT2tqTTlKTVIybjRsYlIzTDJERWdDUENjRGF3TW9CSVo2Uk5NVnFEdlhzOWhFNExCRmFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQSHlwVHJKaDFDMERqejNGSnlwbHR6Qmt0RC1PWGQxeWRtNXZrbmtHdGpUTWxfZGFzVzVueEJtbUI0QXF1SlFXLWQ0NHRBb0l6Ml9NSGx1UkVZRnNTaVlpazlndDRJdktQb0R6aW9YbW1QcVhfU1Y1VzZtOHhHU0J0c0dUcy1hbkd6?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46018.50277777778</v>
+        <v>46019.11555555555</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Man United make Premier League star 'top transfer priority' as Vinicius Jr claim emerges - Manchester Evening News</t>
+          <t>I tried Amazon’s winter fashion IRL to find 5 unexpected New Year’s Eve outfits for any kind of celebration - MSN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:43:27 GMT</t>
+          <t>Sat, 27 Dec 2025 23:36:42 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQcURCT2xSSmZBa2JNanBFSGNDNGItZDh1LVlLcnVXZTZ2VG9pUHhJejRqNkpBQVdTeURlX0o2aHN6WDhNcU1STTU4S1hQUlFUcDdvaVdadGh1ZzJmUk9XOFBzOHBZeEtBYWpuZ0VWWjN6VkIzM2pYV3Jyb1djWllHZFlfOHZTSkRzbmN1SUdiSW41WkFzOWpibndubzFDcGpyWC1BSEVfT3ByZW1w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwNBVV95cUxOVFNMYVNFMHpFWXdUMXAtcE5ocXFSUzMxTGRId0Jndng0amRtXzRMSVAtSnRRcFhrRUNUeEl6TE42TDlnTnJpUlZSVU5LREdhdWZxcXRtN2Jaa2VEUXBvc1lsc2dQblRhcFZDeWZhcjNmRVk5SjBKMjhHTFE1akJGajVNZXVuXzhGbU9HOHdWdFRCWElFY3lVSElOMzJkVzFaeVUtM0otZmdpZmR3d0JwVjlJMlhEQzBVREpiVDFkcWNjUEowMkZERVplYzI4U2thM2p1RV9hVVlFdkhjNmI0bE05QW1zUTF1WGE2czFLTlNVUkVWNFdOMUxLaTdOVWsyY29iZEx1eS12Z2tHdUpyNWtsYXhYYWdnYjQyWUJsRGFIMlNBb1JMd0VNZUdaUFJFenhPRjg1T1U0LWg4dVZEOVJJRmVmYUh3T2w0NTlxbEdKVzh0SDM0YUdCRDhlN0tKelFCVHY2ZkhCSUxZeVVJcElSZVdra1I0OEZBSnppU1ZRbzA1ZEl0TExyQ3c2RGtvLWFkdDdOY2d6bFp2Z29Ra0U2dF9DN0pHZ1JldHJDRTl0NDdDLUNWcGtLamU3d1VBXzVvR2N4cw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46018.44684027778</v>
+        <v>46018.98381944445</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scan Projects Limited (531797) Quarterly Results Are Out - Resistance Breakout Alerts &amp; Low Entry Investment Growth - bollywoodhelpline.com</t>
+          <t>Postman Pat given his marching orders as Royal Mail now seeking gender-neutral postpersons - MSN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:01:04 GMT</t>
+          <t>Sun, 28 Dec 2025 03:44:21 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPbHhoV1lnUjFZZjFyQ2h0ZW5pc0x2MkxDSFhuOEVEem52QndsSVRJbk8zWFBaSmZVWnE5RW5BV1hIajIwXzBwUF9yWUdDUUZ3NWRjd0lqY1dkYlRveFBYN1A0Nm5YcTVMV29lak1KUzhOc3h5ZGUxNV9qQUxZV3lybk03UVc2bjJ5MFFnMU82MUdyaXVwdVIybzB5c090ZXlCdFZ6dmRKMnFhQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQb2o4bHZ5YXN5VWRDcEpvOWUyZTljMmN3QVNnbEtSenN6R29IbG4xVGdNb1U3V0t5bW1IM0ctdU5seDRBbGJzM0ptUExLMG5LU2tZVWhiUWxIb0Y3YnZBcnZqSW82ZVBJRFFWWDBHYmM4Y0xMWk1XbFladF9STTdZSEMtQloybUVWVFZqNHI2cXdhcmhmX3Z5cDZrVDViRld5V0FyOVUyUEpQbV9vTWhPcjB3Wm9acXk2UnluRHNqMmVIOVpGeWkyaGc2aE9PWWEtYkdoMzJfWQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46018.45907407408</v>
+        <v>46019.15579861111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IGC Industries Limited Moves Into Overbought Range Analysts Cautious - Portfolio Allocation Tips &amp; Explosive Capital Gains - bollywoodhelpline.com</t>
+          <t>Amazon Web Services announces enhancements for Bedrock AgentCore - MSN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:30:53 GMT</t>
+          <t>Sat, 27 Dec 2025 18:15:05 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOQVpOUDBOdkVwVWZRZC1Ka2ZZU3JxZlZFSlNZZXJhdFB1VEF3bVJXSVZ4eEhJZmlBVjFPR21ibmdnU0Q4X0VDN0ZqNVFZMkhVa0p3NXU0Tk9ENW03ZDA5MGdfTElGLXRVdmc2TVNqaGhBVC15UVVWLXczSjl1VkJLeEFyc3BaWHRRb3gzT0pTUDVMMGx4ZlZYajFvR1BSbm8xcXhqVHJydWVidXZ2T3prRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxPV1p6a3Fwa3RCdndvckNXdUszMGhiMGFWZWZnNzBOWV8xd3pCbHJCN3RYT3hwVS1kSldDM0hLcXEzQXRMVFVfNmNybzVOTi14ZXViYllkbkpNcVk2VlZZZG5nX2c4Y3JYNGgxZ2JHdTVuMkUtdUZ0UFB3cWNleE45S01aUXpaVnk0c0Q5NDJreW8zLTQ0OEdlMlhmSVphNzZzaDFqWkNMMlZqRW9tQzFtYXBOUHZ5QmRiVXZ4bko3cm1vcXYwUHpmcjEzbmFfWVRxMlZKeWtmQk5OWjBpVzlFU3FpNzVFZVJSSGNKQXpqRE9WWllDNFktaThGenQtNHlVTFI5WXUxMjFDay1obFFnNTJrZDFXVjcxa1Z2SlI1dFZqZk9OMkhOVy1xS2FTcklLZWpxbTdGRGMwVDhfaUdVRnVZS2lQT2JhYUJFUERmQU4?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46018.52144675926</v>
+        <v>46018.76047453703</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bangladesh: Explosion at madrasa near Dhaka injures four, including two children - lokmattimes.com</t>
+          <t>Malcolm's best tech in 2025: iPhone Air, Powerbeats Pro 2, and a cheap UPS - AppleInsider</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 08:50:01 GMT</t>
+          <t>Sat, 27 Dec 2025 16:59:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOVnhnN2QxWnlxZ2hRcFdIT1VMdmFsWXh0OE5XRnkzdlRmTlJDdU5ueGlTd0NaLWZUeDhrdnp2QlNCbEkzckt1eGxyTnlTQi1vZVJQXzY4Y3cxV0hsbFZfbE5TYUVJOEJxRUFIWXVEVjAtUXNKNjVNbmdibDF4bFE2N0JCRFZtM0dfNWE4cHUta3VOMUdyc2c0ZWNpUTY4T1pfRUNhbXZOWmtRcmoyc0M0cllIWTAzMkpxX3BBUERR0gHDAUFVX3lxTFBnMDVvQmhvdHpzY3JLSk1VYmtqVWp1SDc1dWYwcGgwV2RJX3ZaSGlSNzlzUWlDZkdjYjhRVVR4S25kV0VXdjBUYUtEc2FXeUxiMG9lOUhzMC1tS3AtN1EzbEVRYTBQOFBnemdHWEp5dXRpbkpqVDBYdDhZM2tYdDFIQ3dHMDA3dUV0VzB0dFh6U3VfVzQyRnVQaGFSajJaOFM4QUhPZmxQSEtjZl9Yc1IyMk9zMFRGNFJwcjg1UFBaa0JiYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQ09uYUI4SlpYVGRkbnBBdjV3dTRJNFFKYWc2TVlTaFlFZ0p1bzlxUjQ0cWNfT3dhWlF2a2FKaE5VSzhHc3ptdU52M2RpUlFKUHlHaEtkR0hkRnVpS3JfTFZCY1hWbHZfMmIzMWRfN1hraXUxNWxOdjBmcTFhdXFFVW5JQnhRMVoxMi1WdXZmTFFBUElFQ1pybEE5QzUwckl6RW51REVzTF9MMXNvNVFxRkxTRQ?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46018.36806712963</v>
+        <v>46018.70763888889</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RSI + MACD Show Convergence for Krishna Ventures Limited - Market Depth Overview &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
+          <t>Unlucky Amazon shopper orders DDR5 memory but gets DDR4 hidden under the heatspreader — RAM sold as new was a switcharoo - MSN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:16:40 GMT</t>
+          <t>Sat, 27 Dec 2025 19:54:34 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQVERMbHBfNmQ2NHdTNUdzT2tDZTU3ZGE4VF9wMEl0eUttWVFHVlBhSk9taS1iamRGVWhnZy1OeWJfQkVnMm1WYjhoNGthYVFRblFFaWFnbEI1eEtjbVpoOEJmcUwwZHB0UFBrNDg5U1F3dkZzR19TYkNlNXRFZFB5Y3BsTWpvY0tiRWphOEx5RTdIUkc1a3ZYcElJLWxndllG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwNBVV95cUxQcE1pal91MEtQSHJYLU5XZENpSDA5UjRzVUdLV2xaNUZhb2RjQ1FFOU92UE5BZVFmT05SMV9QWjlWMFBGdldKNVNEcVQybjRibHlXR3RlREw5SW1tQWRpUlM3SVByMG0ycW9ZOVVlcmNoeWZEVFV2eXRIVGwzN3BjbkxmdXktZnhNUWFmU2JPbWNtRHNMb2dLSG5GMlk5bThOT3JPcmhKYVBLU0ZEWjJtTGVJVjNfLTlIbU9TbDNNSXI1dXdPdFYtQjdfeTU3RW1kSHZ1SE1qWjdjcV9nTFdZbjg3T2h1UjVSNGxidldTV3dNQ0M4cXhhRXhTRkFYQ0QzMWJUWWtvTXZVT01DSUx4QldVNDh4NXNPV2lBRkNMd1k3X3JUbElKWk90bTVfMXNubVVjdnV4Q0hadzViUXlEUlRfbk9QaFNtN0YtbVVQZkZoSVY5LU5DWk9LNjRJTEhuYy1NNGxpaWpVVmw5V2xYc3RaMWFURnZERzhhWkFtZEItU19pYVlPQXVLeDhFMGdueFpuQkF1bw?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46018.51157407407</v>
+        <v>46018.82956018519</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alembic Limited Stock Approaches Key Moving Average - Day Trading Setups &amp; Explosive Growth Opportunities - bollywoodhelpline.com</t>
+          <t>Costco will finally deliver all those giant bulk items with its new grocery service - Mashable</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:37:18 GMT</t>
+          <t>Sat, 27 Dec 2025 23:00:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPVGJGTUZYQ1FaNHp0RklGeS1qZ2lJcjFCVko4MzhUOERLMW82anZadHJya2NLVHNKcmY0eFdKRHg2eWNoTW1rNHFyUzRqdVhEb0x2eEl1V2lqMXZ3YzZPT3N0d1FXbFZNTDNKSFNpVVpxX2xFOWdoZEMyeUtUZTh3VG5yVHFkYUZ0V21uTUsyY3BjZFRNX3RnWjlKSWtPbW5RWUZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE82bkNEbG9FdWR1emRlVTRiRW5ic3VjNC1RbnVBUU4tamJ5ZTJpaHpzM3VHSE9uaUJSSkpIUXlpNi1fbDVwTHJfcEp1U0I0RlQzNExzMWk0bC1MZTZ6YTRWckVB?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46018.48423611111</v>
+        <v>46018.95833333334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Journalist: European side in negotiations over permanent transfer for £38.5m Chelsea ace - chelsea.news</t>
+          <t>Amazon Flex to pay $3.78M in Seattle gig worker settlement - AOL.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:15:00 GMT</t>
+          <t>Sun, 28 Dec 2025 05:43:12 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE52S2hqbkY0ZjhldDBzTG84Sk5mTVNub2JSWWcxUjRjaWtJTmdRSmVnVEpIVU4wbGVFN1JoODJkQmdkM0Fmb3F4ekVVTlNwZjBQRUtmZHFmVFlmOTdGdGFPYWc0d3YzX3dKMElaOTBPd0_SAXZBVV95cUxPdThLTXlHQWlaSWljX3JVajE2c3VHUHl2NlpyZWwzSWwtRzNvNjVhQlFOaGlqczRUOHRhNno3R3ZOWHZGVTRyWVN3MHlMVXVLTEFoQ2ZQTkpHQzJ2cG0zd1Y2ZmFURkVWSDR0VkRWaVJsbndEb3RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1fZU9QT1F4ZVdFYVZlRG82NUgtNnpQUFNGQ2J4Yk9OUWgtUHdjWTlKZnVxWXp5NTNzMV9iODNSQmhKYVgyMU9LdjJXNFYtSGV1aHVncDFwYnk1UHBldVNNdFRaSXhLNUxwVHI3Qk80M0F4Z0E?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46018.42708333334</v>
+        <v>46019.23833333333</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Recap as M25 closed near Brentwood with major delays after crash - london-now.co.uk</t>
+          <t>IS IT NAUGHTY OR NICE? - PressReader</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:10:43 GMT</t>
+          <t>Sun, 28 Dec 2025 03:16:39 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNeVlXQ1ZIMEZ0RUE1eml1TmJxSklkemdLRHFRSzU3M0xxYk5DNjNOWlF2OEM1YllRS3VwZ3h2VUtfbDAwekdrMkRpdFdEOGkzeXFCZFRaTFFxbnhldFpRZ09IUEhYQ1JkSlRDd09PYlJ4NDNjVDBGSUR1SmRXbnpWVWFVY0d3WWJ5N1F3WE9QbEZmdGV1QUg3ZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa3ZJZUg2SnMxcDgtQjA5c3AzN0lCY3hKWTJGU0JYS05kLWxwVEtoX0UtSnpvNk9kUGRlSHJCSkJ1YlB2NEpxZ2JxS0dWaV9ZWHFhdkpkMW94RHNtZ05XTk5rZExoZm9HR0YyRUlDdGJsQ3pocWttT2pERGYyTXBPeG1UNUw1M1U?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46018.50744212963</v>
+        <v>46019.1365625</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>What to know about UK snow bomb bringing 'one inch per hour' in just days - The Mirror</t>
+          <t>Could Amazon Help You Become a Millionaire? - AOL.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 13:53:27 GMT</t>
+          <t>Sat, 27 Dec 2025 18:43:47 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFB4WHN5dGVOMUxXbU4xdm5MNWIwdFFtQVIzXzgzLUVSVEE4SVpMSFFhemFEUG5xckltVUJZZEIxZmdrbkgzMzNpVmZyd2pldkpHdTRteDlYQVN1dE1JVXNJYjJDVkhDTXZzOW9xT01xQ1Z0aWd0c0FEYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVUthTG03T3R1Wk1Vd0FUdEdtY2tWTjlRYlNacUJ2NzNZSWZiY2xwTmZqTV8tckdJVlJ2MC1hQUpmR0xhLXplbUV1dWJ5NEd5eFpuMWpxcDBZN3lDdWtTWXVISW03MjdnTlJ3NURmdUNCazIwdkJBdzJjUlJKNUFzX1ZFemNUQQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46018.57878472222</v>
+        <v>46018.78040509259</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UK weather maps show country wide snow bomb to arrive in days - Manchester Evening News</t>
+          <t>Quick commerce platforms drum up sales, push deals ahead of New Year’s Eve to offset delivery strike &amp; rus - The Economic Times</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 13:11:00 GMT</t>
+          <t>Sun, 28 Dec 2025 00:30:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOY2J0d0FmODNIdTNWb2Q0Vkd5aXp2YlM4LTUzUE1jQlMtZ2pYa1o1TEIwa2hiN1BRcVlIZzB3S2tGT0t6S2FVZG90eGQtMkpTTUQyQnROYTI5ZGdVRUwwd0VPYjVDY1VueWI2VFZlYTg4QnVZaUNURUM3ZnluaVhMYkVmSzBCRFVQZnNtSWo4UTIxSmIx0gGaAUFVX3lxTFBNVlBnSFJJNFAzWnJiV092ZF95cUtWdTVLajloVWp5YlNFRjF1WG1WT2RUSnVVOC1wNS1KRHVxdEJIYjlXd2VVV2Vod0d0TDJiSi1Cd05GeHB5NmZHbnpqY0NDOWdHQUt2U3NFMGFHVUNMUG41OUdXbEVKOFdySnUwT0gyWGF1WEtiaE9yOXJGTUFzR1NWRE1BSlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOLXVFTmtxWjN1elhZSi1tUVZCbWNvZ2pVdDkzZERiQlFOSGhRdW1oeUt5SmxYUEtNYm52V24td3ZmU0drekVMSEdJMHZXc3F4M1RXanBMeENjYWZ0QUhOQnRUeWpleXM3VERxWTFBMmx3QW5GRHpvSlpLaDd1SWtyU0U5dF9SRzRnX3JqRFpjT0pkTC1Xa21IVk1BTy1FN2ZoQlYydl81cWVLQVM3Uzd2Yjd4YW9ONTB3eGhiMEtKRXNDMTZBeFN5Uk9aRUhfNl9GN1Z1UVJLV1dTWHNNT196MmVLbTlXMG9SRFRsc25aeXlBNXpvcktmNjJIR3JBUmZxZ2ZKVmZqa2zSAYgCQVVfeXFMTi11RU5rcVozdXpYWUotbVFWQm1jb2dqVXQ5M2REYkJRTkhoUXVtaHlLeUpsWFBLTWJudlduLXd2ZlNHa3pFTEhHSTB2V3NxeDNUV2pwTHhDY2FmdEFITkJ0VHlqZXlzN1REcVkxQTJsd0FuRkR6b0paS2g3dUlrclNFOXRfUkc0Z19yakRaY09KZEwtV2ttSFZNQU8tRTdmaEJWMnZfNXFlS0FTN1M3dmI3eGFvTjUwd3hoYjBLSkVzQzE2QXhTeVJPWkVIXzZfRjdWdVFSS1dXU1hzTU9fejJlS205VzBvUkRUbHNuWnl5QTV6b3JLZjYySEdyQVJmcWdmSlZmamts?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46018.54930555556</v>
+        <v>46019.02083333334</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>I was immersed in London's terror underbelly - new 9/11 is coming any day - The US Sun</t>
+          <t>Christmas Party Video At Canadian Amazon Warehouse Shows All Indian Staff, Fuels Hiring Debate - Vibes Of India</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 08:40:47 GMT</t>
+          <t>Sat, 27 Dec 2025 14:48:38 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQVTBvNm44SlhzRjRtb0tHZy1MQzV5ZzZ3UnRtMGNGVTd2amZuRlZ0eDAxaEZBMUFJWjYxSmhkWUNDUTdMcG14dElRRlZBMlhoTnFsZHRENDB2bFkyYl9Yc2twN3h4ZmxWampFSjZ4M3FiR2hoUjNRY3YxVDVsS2huY09uYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE53eVNMbzljMEpGWVVnVVo2RF90d1d0QkZsWHp4NFRyTnNaZ1k3TDBqTEFldWNCejVvMTdqX1BUd0ZYWkpIZHhKamF6X19EcHc?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46018.36165509259</v>
+        <v>46018.61710648148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Urgent search to find missing vulnerable man, 80, from Forest Hill - london-now.co.uk</t>
+          <t>Amazon halts drone delivery plans in Italy: ‘Conditions not met’ - Lapresse.US</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 09:56:18 GMT</t>
+          <t>Sat, 27 Dec 2025 20:03:17 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUmh4RWgtYzczNTBmV0k1S2Y4V3Vkcl9MT3ZncjFnU2NRcGp2TkpERkVQX0xGUGZjVmx2YWFjTTdKUUhYOW1YRjAzV3lLaThKYWpVbDc3eGRrMldGMkZQb3I3eWw3M1NRMlFTZmhsR0NRT1hLSkRGNl9HWndEd295allTN1VkdGh2OThuUWNpQWhuUDNyWUpPS3pyM29CcDVuVlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZ3lJdzVDRGYxa2JKSHA4S3AzLWtOQ3BpNmlWX1NwMWRSeTBaQm9JcTFhbE53SVVKM1hMWlFBaE16aklaeVFMX3oyMWFDdXRoZXRKQzFoWXlkd3FhcWt6ZFZiQlFnNEdyUFFKRVc2R3lWbE1DZHVqS0RKWnhrY0VqWkVRS3BVRkNFcHkzSFBTY3dfSVpQVGZzU2lUVGJCcjAybGJn?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46018.41409722222</v>
+        <v>46018.83561342592</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Firefighters tackle early-morning car fire on M25 near Dartford - london-now.co.uk</t>
+          <t>Why Swiggy, Zomato, Amazon And Quick Commerce Delivery Workers Have Called A Nationwide Strike On Dec 31 | Explained - The Daily Jagran</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:22:15 GMT</t>
+          <t>Sat, 27 Dec 2025 16:06:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPTVJUNmFPTXkxZUYxdUZMMFNjSG80WGQzRzBjRTcyRF8zVDJWMWd5WHR4aWlkeHBEM3p2dnBwZnlha2VsN1g2UVZsVlJBc1RueWwzaUhSaVQ0SmZEN3htVWEwTzBucmxRX2xMZlJGazVZek1XcHg2UU1DeFZFd1hMLVFZZzVuZkdrU3d1OWtYanM2aHNob1NV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQNHEzYjh1VUdXMDdfUkNDeXJGUElSVkJ5NHZoSkhjOWJWbzBUWnBleXA2Uk5pTC1MUWFEazFwUHM5TDV0YUlBRjNUWUdiMlF4bG04bEpHZk1RNDlITUt1U2lmQlgyRXFkNlFYQ3lBeG5lYWJYRTFnS1NJUE1WZk9YMWZUaTJaVHc4RXVOU01idlNmM2cxaXl0QjBRdTFLaXJhY0V5d01BOEpMSTlmOElmV09IX2dyeS1HR1ZUd2FmQi1uRDljQWxKWHdSSDNQN0hmYmdNcmk3S0I5WU9TblRySnk0NUZ0WHRRUmxoTlFVbw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46018.47378472222</v>
+        <v>46018.67083333333</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>All Southeastern trains to London Victoria cancelled until New Year’s Eve - News Shopper</t>
+          <t>What’s Open and What’s Closed in the U.S. on New Year’s Day 2026 - KnowInsiders</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 09:33:52 GMT</t>
+          <t>Sun, 28 Dec 2025 01:31:46 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNW1td1M1Q3puaTFNa3VSS2J5bHItRE1BNXlSYy1Ca05xb0ZMaTBwMXE5dVFmaEcyZjc5V3A2WmJLbTdoZ1lOTnhobG1WdUx5RnJ2R3Fza3RZY3lsd2luRTZlQ0xIU203a05wWUJocGVEQTJkLVg5RVFid0M2dGV2RzNfanVFenJ2QV8zNGhMZDZMU3lrRXlUUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZGlyVk9xNXBRNEhHSnR1MjRXTVl0ZlcxME9wNDNmbTVGYUV1cjB6U2M4MmtVVTUwOTFia2tYR3NqMnlJMUVOZTBINzhNNTZBN3JxRnJPZHZ3bFRlZEFsUTNiTV9rbmhtVXpwYlpQV1VCcW1zaFZzVmxabkI1VkZGc2NscEItcldnYmlUQzJ4enowdmd1ZWVZZXNZUQ?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46018.39851851852</v>
+        <v>46019.06372685185</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hospice to collect and recycle Christmas trees in 17 postcode areas - london-now.co.uk</t>
+          <t>The Amazing Amazon Upcoming Sales 2025 worth waiting for - TechnoSports Media Group</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:00:00 GMT</t>
+          <t>Sat, 27 Dec 2025 20:43:43 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPTHIzakItcDZjNDhCNzRjUEJMSkl0VlJmRzdOSjBwTXdhWEVETXBIbkhzQmFESmhwRm5jVFlaTGN6blVwOFVya1VEUzN3UlNkR0R0VHEweUd3Q2tTdjUwQTNhYkFsdUZkVUJmLWVPWmswRE9MTlhIYkg0QTg1U1ZUbS1GYWdWbnpMb1BLejFfZG42eTBNMTFXb19jQUkzemJNbjMwSGs4WlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQd0NseGl2NTkzdzNRZjI4YldoZzhBZ19saV9BV05MNGRJd1BNTHhiT19XSUlvX0Raa293YUhoTVV3U0JZUnE3enEwS0NwUjF5NjZMRDhXTlRQUFNiWDFseHlpdjlwSXprS0VvYWE1RlRXX1VtbDNDUXV4NXVJNnhPMA?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46018.5</v>
+        <v>46018.86369212963</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Watch as armed officers and police dog chase down stabbing suspects - Essex Live</t>
+          <t>Globe Multi Ventures Limited Could See a Relief Rally From Support - Stochastic Oscillator Alerts &amp; High Return Capital Gains - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:29:11 GMT</t>
+          <t>Sun, 28 Dec 2025 07:53:09 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOVkI3eEtXTkRGeDZVNEJYWFNEYlQ5UUE2YXRsRFpSeG5SbWdrM3dNLXVrMVZ4TC1KMHNBNEstRG5Gd1RFLXdsU1UzbkxKN2QxUDA3c1YtQ2xfZzdraV9qV0ZocGZnNWJUU0tRMjBESXZSNWtGUjBtMVVIN0ZLSExCaERMUmhDYXFuVmZZ0gGQAUFVX3lxTE5TM1N2MmdaX25DVUtuTTYweXJwRF9IZUE1ZkY4cFNhUzhZN1VkMy1QeUJZZVFHbUZwN1RlZVVwQ3dSdDNLZUFCMGYwVUZEZDBCRklDSEJRVkRTckFxWVM2TkpBU1FGakZSblB5aXdwcFJGc1dUMncyZVJfTWpnNUdhTDMzMkhla3hmQU1vaklySw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNb3JFMHgxWE5vcE5mRDFFQlJzR2F6SjE1VlV0R04yRkpBeUdBYTlmRFhfczB5eU1TdWp5dUI0V0pLZUloVHg2azAtNzEwakhGT09KRWxJSmZ4ZzBRRHRhUE9pTUZ1MEZPd2ZwTEpSY3F5NFJwQVVtejNhN0hTRU5Vb2E0RWVSbnRyeWZJWEs1N2VKWS0zOGVXeFdEdWVUMEtnMnJB?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46018.47859953704</v>
+        <v>46019.32857638889</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>'It's sickening': Essex town market trader stolen from by 78-year-old woman - london-now.co.uk</t>
+          <t>Quant Models Detect Momentum Reversal in SSPN Finance Limited - Retail Investor Activity &amp; Fast Growing Investment Ideas - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:17:02 GMT</t>
+          <t>Sun, 28 Dec 2025 05:15:51 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPckY2UFZ0WkVUTm9LV1FJT00xQ093SU1hWkdjQ2hXZXR5ZnRidFBMZkNKRDVDSVMxLVU2SDBfS3Rtb0N3Z2hxUHIwRW8tdGdIVFpxOG5LYk5MREVtaVFiZXZEZ2VVR2l3YTRFTDlJVXNOcjFiU2tWZXZ5SVVMeC1URFd2ZzFDYUpjdDV5SEhJRXR5QzlzUTAtbTRJMTlvZTVDTVBtaDEzWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxORmFkMm5lV3cybjRvOTVBMEVGX0tQckdwSm5mb1RWTFJuZUJ1Z1JUNEFHRmxudHN3WHRPQjNXSWgtVmRVSDk1bm5OMWVrWk5laEg4YVZpS1dsWkZNQVBSZ0o4LXg1VnJXa1FxclFXMi0tT29kUUZ2aXV2ZklLRU5rbGlEX043Zy16cF9SYWZkNzh0WDN5aEFYYlA2bUppc0lSUUpBYmE0RQ?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46018.42849537037</v>
+        <v>46019.21934027778</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inside Christmas Break with the Royals at Sandringham (Hint: It 'Isn't All That Relaxing') - Yahoo News New Zealand</t>
+          <t>DSJ Keep Learning Limited Charts Flash Early Recovery Signals - Swing Trading Ideas &amp; Free Explosive Return Secrets - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 13:00:00 GMT</t>
+          <t>Sat, 27 Dec 2025 16:01:22 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPVEYzd3kwejVrU3RINE1uSGg5U3hfTFNOMW9BSTBIaFJlTU4yY21fTlVWbmF5WmZKaXg2T2djY2xOVmRnLW5lYndTZUs4VnY2QUZ2YjFrMm9faUlhSlZkRU0wMF96cEl0cTE3ajJ5ZFRieEs3YkZsVTNZSFFOYVJhY29uMHByVmo2RlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOeHc5V2VOMDZiekpMM1BmN2tjcEE2cWh5Zm5rLVJaa1dLOFpkQ1pqMDM0S2RaMDVETzludHRiLXFSV0U0ZmpGX3Jzdm1rVUpFTkM5bkVOdTVDVkYzR256dHk2a1ZpdTVCZGN4WUN5YVdzY3FZRnJzN2VlaGktN0J3SzFnb3NFR3c1cTZEQWJjanQwdzFpUElYc1I3OGVsRDg1YUgyQnowNA?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46018.54166666666</v>
+        <v>46018.66761574074</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jane’s Addiction and Perry Farrell reach settlement in lawsuit over onstage fight - NME</t>
+          <t>Can CLC Industries Limited Overcome Bearish Sentiment - Volume Analysis Techniques &amp; Free Explosive Return Secrets - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 09:16:23 GMT</t>
+          <t>Sat, 27 Dec 2025 22:41:42 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQZ05fRER1WDVHbkRGcGxGZmoxTHdHOGh6c3BvbEhZZUFHemZMbHF6bzFWR1p3c3Z0QXJScEtpRHFteE5xbWRGZ05CczBGRWZjc1VUaWdEM0c2RmFjbnNGY3ppcVBOZnVwdGJZNUFCTTIyUXlmOHpzTl9RSGZUa2xjREktYm43SWNublMxVUZjNTlqZXdUa1VPUTE1TXQzV1JyNHRIYlUzYzZvcml1QVJMMS1oRGthbTkxMTdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNMW9RNEdEWDhrS2dMRnF3RmVMbm1LdGdaWUVKQjBULVJ5THh2WGUxa2o1dkdUQmJrUUZveUVpbHAyZkRmZ2pxWW1iRHdGS0k0SWppSUZZd21NcFRuVEt4OE04a0hPMjQtMTZwNWpEY01adURnRG5sUlFFQ3dPcTNCc1oyOGJiQTAzejgybmpyYzlHbDNrTnRJWnlZQWNmdw?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46018.38637731481</v>
+        <v>46018.945625</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Real Time Data Flags Unusual Activity in Premier Limited - Large Cap Stability Picks &amp; Explosive Profit Growth - bollywoodhelpline.com</t>
+          <t>Published on: 2025-12-28 08:16:11 - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:33:19 GMT</t>
+          <t>Sun, 28 Dec 2025 03:29:16 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZDdTSWkteXN3dEk3Ri1HZmg5amFrMm1QNlg0cTl0eGpUV3BUNU5rUlFicm1RRjAyTEFyRjdFN3JWakt3YktVQWtoMlVjQnJtUTRIc0l0b3RCX1FHa0dMekxYbFp0QU1neEc1dURIMXRzRmdSSmZGSTgtR2N4eTZWWUxMbjJJQ2NlWGRiOUkxTWxQejBGZXhkV00yOVZNQlJrUU04MUxsTkRGdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOclZwT05XTVJCMEtIY01sRXB1cFp1RFc4cnl3Ri1WYk1LQTlzbDRmLUw1TXFPaHZkMERvbUY1Y0hUMGllNS1XaTNoMElkUDdlQURGSWpQVHlGN3I5SHhqaGREeVNyM3Y2ajViLUpic01wZGpHcG1LZC1fOC1IZXAwMDQ5VkdqbmxmZGJZbDd2eUh4NFd1ZnJzbmotTEVVMTZIaDBPOFFoUktrY0VDT04teDR6dFhVbVVtb3VPYQ?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46018.43980324074</v>
+        <v>46019.14532407407</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Today in History: December 27, Charles Darwin sets out on world voyage - Boston Herald</t>
+          <t>Jindal Steel And Power Can the turnaround happen - Ex-Dividend Date Alerts &amp; Analyze Your Portfolio Risk in Seconds - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 09:04:50 GMT</t>
+          <t>Sat, 27 Dec 2025 20:56:42 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPenJhaU43eUlKWEZ0SFRzZ21tSDdSNWRueXhhenlDNDVCWFVTUVBrS1JBM1RIOW1FTnk2SXhXdWZMZk5SQmRYUXhTX0V0WU9WQkNiSTZEMlQxcjgzZ1RObjlyTE1id2s0OHpZNlNCTnVadlVPZVVvOHZ4VVlQWjFUX0pwVFNXSnR5eDFwUVZzSm95YWg0eUN6YlFBSS1jSWVWdEhobnF4X0FlSDZpWUxmV2g0TdIBswFBVV95cUxPenJhaU43eUlKWEZ0SFRzZ21tSDdSNWRueXhhenlDNDVCWFVTUVBrS1JBM1RIOW1FTnk2SXhXdWZMZk5SQmRYUXhTX0V0WU9WQkNiSTZEMlQxcjgzZ1RObjlyTE1id2s0OHpZNlNCTnVadlVPZVVvOHZ4VVlQWjFUX0pwVFNXSnR5eDFwUVZzSm95YWg0eUN6YlFBSS1jSWVWdEhobnF4X0FlSDZpWUxmV2g0TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPTzZJaV9fZU5aVEZtMnMzbGl0VVJfQk1nYlhSa3Z3UXZReVk4UEJxSHNmM0FqWXhKOXpxbXFzR19WVmpEel93U2tqdEZSLTBUd0psMnN0X0MzdnhXNjBMMngyVGFTcXdvLVBhS0RjNFpXRWhncUhQeDVkQjVKX0Q5SUh3QmJsQUxwMk1V?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46018.37835648148</v>
+        <v>46018.87270833334</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tarique Rahman completes process of voter registration and national identity card - Prothom Alo English</t>
+          <t>Chemicals Limited Price Holds Above Key Fib Level - IPO Market Watch &amp; Low Cost Capital Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:17:40 GMT</t>
+          <t>Sat, 27 Dec 2025 19:34:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBRVF9iZjd0OF9WTGlnNzFXbGcwczhpQTM5N2huV3JfU09VWU1kbWR5S0hiQTliMUJ3UGlDLWozSWk5VU1pdG9Kb0JMOG5YQUxhRWRIbmJZUzBfajRfR3cwX2VrNndHbDRf0gFoQVVfeXFMUFFUX2JmN3Q4X1ZMaWc3MVdsZzBzOGlBMzk3aG5Xcl9TT1VZTWRtZHlLSGJBOWIxQndQaUMtajNJaTlVTWl0b0pvQkw4blhBTGFFZEhuYllTMF9qNF9HdzBfZWs2d0dsNF8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPWllYNFo1UVNxN2RHZ093Sl9SVWZOMkVWQmM3dGd0SE9DakJBbWs2aXZNcE9JSHRMam1WMUp0eTFza25wdUhxM0ZySXl5OXlLOXJrZjUwSmRweHZwX0VCWHNOXzhURjBEbkZTRWFwcFZxZnF6bjU2a29mWGw5UGlJQm41V0F4c0RoS3RfVlBmMVZHZVdPWmtEa1hJWHN4cWZqaGtYeDdKOUFtNkx3RE85aXE2MjdyTWU2d2lzRy1n?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46018.51226851852</v>
+        <v>46018.81527777778</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Paris Metro Stabbings: Three Woman Injured in Stabbing Spree On Line 3 Metro in Paris - WION</t>
+          <t>Luis Diaz reveals reasons behind smooth transition at Bayern Munich - Bayern Strikes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:34:00 GMT</t>
+          <t>Sun, 28 Dec 2025 07:30:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPTUlQc3I4end5OV90VE95UEVXWWZ5bURhNXp6dHVYTFZzUEZUUlJfQUpqUV9OWHdIa3VSSFBOaE9RUkpGbWM4aXJ1ek1vTHlQVFdNdE5CX1pCc21jU3JpZm5FTjlqSjRkTU45WUcweTdXRFdhTzFkUmVHMlM2YjlWbU9JN0FCTGppTDBvMkpleXlWRjZOQVNraVZmdUU5YVBNYndteGR1QXlmZmd5cWE5OVNuRXE4blJWRjJNWG92QThnNDNXNDJQeNIBzgFBVV95cUxNTW1Rd1BRY1d0aWJXYlJlbHNsNDFueXJCQkRDbjB1TVdsMWVlZmc4R2piMTM5QUFTZ3ZxQ2xRakltX2o4dGM0NVZsbGN3UWtkbTFzYnhBN0FVbkxSVXoxSExQblZMMFM3NHhzRDlzMC1xa3BLSDM3Q0NvQklvamJrazA4Qlh1MmFNc0x1THJJcVZYdVhiRHFzWkhQWFpBQkFSVnV3R244WXV4TkpvUVZzdmtrNlRZb0dzS2s4dG8tS3JuWUJsRk83N2VkUnJvZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNMjlaOV95eWIyMGg5d0c0czBnaUxQMlBodEZQZnUwSDdfZk9iY2ttaGhJZHRJUWM4Y0pGUGVnWGFwUGMzczYwTDlWY1ZfbFlGTThvZ0RxQ1h6X2h1bEJ4aEx1MHhUa2l6bjFxbUliR2tyc0d0QWd0b0tyT1ZKalB1cXA1TFZyYkhscWZXbkZReTZuVlI5NDdveA?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46018.48194444444</v>
+        <v>46019.3125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Illegal African Migrant With Deportation Order Suspected in Paris Metro Mass Stabbing - breitbart.com</t>
+          <t>Miliband recruits Extinction Rebellion cheerleaders to gov roles - MSN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:55:10 GMT</t>
+          <t>Sat, 27 Dec 2025 16:11:49 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQT3lwMVNEUXFwX1pHVHNNZVVEejgySXVuVUxxd3JHMDNDR0h2X1dPd0xiaWNzbjcwWlE0clg0ZmlTdXUzZGxzdXMyaVRxOFZhWl94Um5ucXhNMFlwaUhSZ2wxZHU4S3ZDSzd3UFNEekZiSmptaGV1eWNqT25zcU1rWTl2U3lHdWg0Ukp4U1M1TzF0dVE1TUx5enN3Qnp2dTF6RzZ1Q1d1T3NGcm9RV0NublEzYWppZ2gtX1FvVVkyYWRrcnRJdG8yOWJR0gHPAUFVX3lxTFAzUkdqdXMtRzJ5Z2F0NTZZR0Z3NHl4d3UxQ2ZmREdpNDBsVGNmZTVaU19RdmxHM3NHdU44LTIwdklsX29VRm9HbFFuN0g5RldxVTdwV1k4bXpkcjl3Q1RnX1JnNGYyTkhWU3RTWXpSb3hHNVNNTGpNb1VhVFdFVkRQWFAtNjQ2WThaMnhQUkNnTUt6bERoZ3d1anFQc2R3Njc1cDZuZzlMRHhDc0RiZWtNY1hhWTFoQzIxOXhtQloweS1IS0FQTHdiZ0R1OG1QQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygJBVV95cUxPeEtoLW1YTVpFTlEwaXRyc2YxOXllZUNrV0dVdUVwUXljb0ZDVTc1am9aWDFDcDNTNnJzWTJOeVJTMTlvNHBsZ1p2TjJaLVkwdGlJQlBfUG9QbU8wQkNFLTZYeGFBMDJHbXNQNFhvYm84dkFpNEV4WG1XTGFwSmttLS1kclo4NFVsS25zM1hWUlg3YUowZU9ucG8wbHI3V1VtdGZKYnN5Y3puUVJDbXhmTy1yTnpUSDRTaDhheFlLQkpXUldMUVR1aUM5eWp0SUtMbTJpcmhVNGNocWxkeEhTa0ZQQThvLW16N0lGRk1jam00Ty1BY2hlNjRkbFNrZkh1bkc4bFZEdktvdFhRM3hLUjVUUlQ4dGFCWERWQkRfb3p0VHpIQTY4cVhNaUNwWXg2V2lsRVVjRTh5RkxCRy16YktJeHR6TXhGMEE?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46018.53831018518</v>
+        <v>46018.67487268519</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Modison Limited Stock Lags Behind Sector Benchmarks - Price Action Trading &amp; Explosive Capital Growth - bollywoodhelpline.com</t>
+          <t>Best Images of the Week: Powerful Moments from Around the World - Starts at 60</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:26:59 GMT</t>
+          <t>Sat, 27 Dec 2025 21:59:58 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNemJwRXFfY0xSOVAtQ1NtaHg3X1dZcXBmb21hWmtkNFIxSEg0NzJrcXEwdnJjZUE0TU9TMlhQMERZaTZTZWRDOXhnN1FnNTA5U3pmcU1BR1VodnNIZUYxalM2VkZJUWFreV90SEE3RnJnajVRM21TSWV1blEwaWJvYjZjZ0M3NTBJV3BIQVR5cFhKSkdqbDY2QWJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPcWthZTRZV0JtVXVRU0ZDQVMtczR0Ullrb0I0RXdpbS01YVR3WGxIZTdvMWZEam1RazZNalFJWDVrejZHQmxuQWxpeVRPUTZhQTF1N0RTNjBrdURaNXdDX3ZLdHRReEg0X0tRNEEwcENFVVY0cEh4ZGNmRUZWNTR4dFVjX0dZVTJrUzkwbS1EREtRcVZKNWc?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46018.51873842593</v>
+        <v>46018.91664351852</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AuSom Enterprise Limited Trading Near Value Zone — Recovery Ahead - Low Risk Investment Ideas &amp; Affordable Market Insights - bollywoodhelpline.com</t>
+          <t>Continuing our work to tackle shop theft - West Midlands Police</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:43:57 GMT</t>
+          <t>Sun, 28 Dec 2025 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQeHlxbnpVZnhNdWl5cVRPRXAzZUlfZW1sWFYtaGVwU2gzMDBOZjdIRkNuVEZLbEpMX0lwTldvYXJvOV96Rmk1eGZkQ2cyN1pubHVYQV9hWjU0bmY2ekxSUTBrbTV6cVhHWTFZWWNXLUs3aTctcVMxVlNwS0d0NGthb2diOTJacEY0amJCUFY0UkQwRExsYTE4bmtqUUNFY1hIQjBqU3JXbUxvb1Rv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOSXUzSkZxRVhTTXFEZEQzdXBQQjJ2QlF3Vi1XWkZSMXpXaGVNZW5RdjhENFpWMFRNX3lPSVJmeWJidFJrdE5rVTY0b1lWMVBHdDU1Mkl4Q19hcVVwMjA0dmp4cGVZaGxBWFJtWW1IWGNKZ2RKbXd5c1VkcXFVOEltZWpCMVUtb284am9JY19xRGJ2SjFJVzl2aWdHNUFwQzMtNzhTOEYyQmVxbXYtRjF5YUE0VlhjLXhDNGFR?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46018.4471875</v>
+        <v>46019.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Recovery Setup Building in Yogi Limited Experts Say - AI-Driven Market Analysis &amp; Explosive Growth Opportunities - bollywoodhelpline.com</t>
+          <t>Shoplifting couple target Aldi, M&amp;S and Boots in £1,100 crime spree - MSN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:14:27 GMT</t>
+          <t>Sat, 27 Dec 2025 22:18:35 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNV2RHWXJUR2ttOE5udzgtcHdPeTBHTVRObmM2dmREbFUzZHZzLV9Xekh3blFxc0JnMWxTejBvU21UaEo3V2kwbTZhR3dLaFlIWmNwZHQxZmd4UWtPOWs1OUp0cGNrOUtYU2dRWTR4ZkhpT0JGdDVhR3UxRy1CVDBIRW5oT3h2RGp6c1VmSnRrVldmaHNhS045d2J3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywJBVV95cUxPWl9iOVo5WEtiWGNzZXl5dnVOdTZaSlp0ZzNwZHF0bC1MV2lxT0J3aVpDdmtQbTVFMmpRQmo1MlU1cWFHcnFFanN5MEoyQ0tfQUhUQkZ4Q2tuX1VrY1lCem5sOVVNMGZQV0RqbWJnUnNvYkNlNk1XRE95VmE5NFpNVFpPMGIwVkVZT2lXdWpDeXV5R0t5TGYwb0NQTjF5bE1kVGN6TF83RkJSM05DTld6LVItYjMzN3lwTk10SlpmdkJQSjdKSlhNazBSZHk3NkN6SzBUaVRmaHlUR0JIWXFxSk5OTlJsTWQ0ZVMwalFSRk81Z01zSkIyUjJ3alBxX3VMb1VFeXo3bVY3Z0JMZ1AwVFhjbnJTR2FFNUYtMDRqWGk4UW83U1haU3plZVBHcktZaGt2V2dhMGNnUmNfY1o4SXJrV1Y2OVFIYnpz?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46018.46836805555</v>
+        <v>46018.92957175926</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Recovery Setup Building in Starlite Components Limited Experts Say - Risk-Reward Ratio Analysis &amp; Small Budget Big Profits - bollywoodhelpline.com</t>
+          <t>How bad is organized crime? In Florida, crooks steal gas stations - PressReader</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:13:05 GMT</t>
+          <t>Sun, 28 Dec 2025 05:19:36 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOQXpETzlONWR4T0tfX0lobF9VVGZ0cFhfcGV1MXdaTEwtYnd0S3U2Qk9QV0ZhRTcyVGllSGRPaDVDamtlTFJVbHhzbG5EbzZtLWktN1pseU9LNlRSeFBaVTFrVjUxV0hJeC16QmJEeWZaMEl5d3JmMGdkeEJQaW5rNldmckliUzIxcE1jaEJtRi1IZENhV0M2R3ljLXdzaWljSGNpaDUwTFNOdTgtYmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNN19ob1FRelVJZDAwZUY0Z0JKV3dnV0JwVFpRMmdmUXZOVFZGVjZVWTY2SWdlTm5VWWtKbUR3YWliQlN4QTNMank1NGlMWktOOUVZYkdYa3gwdXREaEpRSkNyMG1KTEF6Um0xRHpYajVXbDR3NWlJQWl0NGlXYWphN3pR?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46018.46741898148</v>
+        <v>46019.22194444444</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>T.V. Today Network Limited (TVTODAY)’s Trend in 2025 - Price Action Trading &amp; Free Trading Psychology Coaching - bollywoodhelpline.com</t>
+          <t>Five arrested for stealing 1L - Times of India</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 10:20:07 GMT</t>
+          <t>Sat, 27 Dec 2025 15:17:00 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOSjRNbGVYQmJRbGl5RVdQbFpFVm5wd2paY21CakgyVDFfMVFXNFlfakhjVEpta1N5RUxHRDQ2TjdmeDBCR0RaVTdXTmZSeFlFYUVmZHNMNktNTWt1eXZ4ODVlVmtXZmhoa2ROVHVpWUFRcUdKZUt3WXFDalk1c3RNOEJjWEFwcXRIWVpPTk9RSU1WaElVMFJxRWxtYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOdDA0aTVDME1WUzQ3dFZmUGJyNlBXUmlENGFVeHA3cjZoVnpXd3NMd0U0QTk0Zk1SeFNkbjZ3bGlRSnlsbkZ5aHVqMm1rcUw5OW53enQ3QXNRRGpiNkZCa1Q3U2ZxMlNkMXlIczdNVjlHdElobG9fU3FReG1oeHRTcERGMjNURTlZZ1RoNW1uczdndjd0NFVabGptYkdtWTRVeklaOVhLUdIBrAFBVV95cUxOMzFudUVwX3BsZ2NLaTNxalNDMFM3M2RxOEdVNE1GUWJKNnJwQ3I3TWdDRUFROVZiSjZWRlVDY1BScFUtWTV6VlBmWlJORDlzbWpDaU90TnpOYkRDQmYtQkdsWUFXMVVGUG1qZk9QSDJsYzZiYkJ1TjF2VHZrbUt6VDhVQ0Z4bW1VMzFCM3BGcTJrcW1POUpldGpCajhkN2FlRTdTSVRObWYteWd0?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46018.43063657408</v>
+        <v>46018.63680555556</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Olympiacos survives late Virtus surge to secure rare win in Bologna - TalkBasket.net</t>
+          <t>La Liga: Why Atletico Madrid players were forced to train barefoot - MSN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 08:40:21 GMT</t>
+          <t>Sun, 28 Dec 2025 01:31:43 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQeWZROFprb250RTVNUW10XzNsSVYwWURjOUV4eTlSTHA5Vkk3NDdQdm4wYzE2UzlVRzJ6bjR6ZGJLaGNQbDN5NjRxVEFhZWppTGwzOWdCRG9PelNyelhYZlBnT1l0TEw5MjJ5bFBhREpNd2dSUHM3TmFyWktOS1hwdkgwRE9KSlY4VFRGU3hUTFh2MVRMZTBzUUYxTEExMVZ6M2g40gGrAUFVX3lxTE5WcDA2SmhWX3Y2clpmZnM2U0pNdmNCMVNFM3VDUUlRaDBTaHRUMk05OE1xOEE2WldtNmhjcGMzdGN5a0w1N3Z3a3J6b0diMFZXOVpMTEhlaVdBZVJDWVl3QU1TVmd0S055UlUzTkE2SDVBZjY2N3pvWXQ4cUFwU2xDOE1MS3BCYk9LZHJSamdXaTVXTTU5c3BxSUN0Y090Ym5zUWdDV2pKQkQ1SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgNBVV95cUxNMmtlMlpDdlUxazRlZGJrMUppYW1BUDRyb21WM3BUUzM5dkFNVFoxWUpacVJZUnc1dXdiaDNLeGdkQ01UdkhYN0Q1dmpYbHpXR1hWNllYVTg1X3BGS0ljNVY2SzNuSnM1Rk1STDBNbmlidnRGbGN2aHE5eWFxM1djMjVlUmZ2UVRoVTZXTWJfb2R3MmpCTjg0VUVoaVRuaVhObkdoX1BtNnVOc25NVzh2cGlNV0pjY1hveV9mR21FdmlmS3hMaWI5dXVlME94dHliQjQzTEZISDNDQVFlUlplaGhfRjlEVkJIX0xORFY1NEZkRGRUeDQtOVE5d2NkX1BfcGpFNkRmaW9KQWI5c0tpZjREeklhYlFlU3FZWnZ3QXNBSGVveGhqZGk0NmtkV0FmUzhSY1VrR1B6aVdkUmt2S3NsbjV6YjVHbjJqendtMkhleXFNd0Nhbk04YlhhcGIwWXdOYU02bWFkenN1M3paQnhKZnhKLXQ1V1Fkd08zR1lyOGVubVdmLTFMQkM3dw?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46018.36135416666</v>
+        <v>46019.06369212963</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brussels Notebook: Politicians will remain on Santa’s ​naughty list in 2026 - Farming Life</t>
+          <t>Real Madrid are monitoring the €45m defender, who Arsenal also want - Gazeta Express</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 11:00:00 GMT</t>
+          <t>Sat, 27 Dec 2025 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOcjVVTE5iUVc0LU1CeTItd1hJb3h4WXJidVAxTE85cjZOR0FsckM3Y1VyTVVKNldUM1BCMjl4bjRMSFVPSUNOTXRVYjIwY3hWTDk4QXZmNzk5a0RzdUN0Ry1PeERmbF9GX3drRWZveE9nV0l6cXZXVFVCV0d1SUNiankyNlFRc2pBNGkwRlJRdWdJVEZPcWFpSExKR1VfbFlnSVJ1VEVpbnFtX3dkNjBLNm1HTmViQWpv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMjVIOEZJYjNWSC1YTkFJdGIya1l2ZllTV0xBcFZCSlFjTTNBaF9IQ3NOcWUtNmU5RlVoeFZqbVd1MnNpcUZTUVEtaS0tVEFvU1dkampZY0ZxRUlEeGRaS3l6azJXUEtXa2ZMNzRjb09ZTzVXUFU1OHZFQzdESFVkQ3cxOU5WSDJFOVFaMVlwY2hXTFE0REU3YWRYbGJyT3E5YVRUNUI2V2tydw?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46018.45833333334</v>
+        <v>46018.625</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium braces for New Year's Eve 2026 after past years chaos - The Brussels Times</t>
+          <t>Is This the Dip to Buy in SG Finserve Limited - Risk Management Strategies &amp; Build Winning Strategies With Zero Cost - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 12:35:24 GMT</t>
+          <t>Sun, 28 Dec 2025 04:41:39 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOQjY0eFhVX1RYMmIyd1dIRzUtanEzWDVadmRsZGNwd2J3QWJEc0RuZ3R2clpBcWdZT0Uxa0czWm1YWEl1VzBqcXYtc25vWGs0c2piamRDcFVyNGJsclB4cnQ4b294dTVEWVRHY1FRU1p3Q3JxTmxuV29IWk5VMXpSVWtWSGRqOEMzVGdmMnlBOTVlVjlseExSZWtYU291cGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNTVhkcW1IUm5JcTBpWmNKdkkzVGdVWU9QQTFjMHRncmk2TkJOMV9PZjZEbkM1SEpsd3Q0SmxBUUEwVXg0MVhudXhHQ3M1Z0hyVWdiV004dzFTQzN5eThVZ09heEtJaFM2VUN3RlUzb3BDWlJzbXBJeG9CdUNldW4xMnFjMlFHQ2w2SjZ6Qll0N0VrZw?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46018.52458333333</v>
+        <v>46019.19559027778</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Why France’s farmers are leaning into conspiracies - UnHerd</t>
+          <t>3 arrested in fatal stabbing near Pinkerton - cnhinews.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sat, 27 Dec 2025 13:05:48 GMT</t>
+          <t>Sat, 27 Dec 2025 16:45:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPWlZTWFp6SHhrUGh2Z0lOdzFjUHlZZndjTU5vTmVhVEFyVWpVdFdzUnBuRjZIRFJ5TUYyQ2dWYy1Bd0JJQlJad0duN3ROd2tqdWpZMnpIZDdpT2NUS2E0WUUyanBkYTN5dWstLU8wOVNEcWRiSW9LQ1JqR29FNE9zY2RqUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBqUXZiYmZaQnp0VzhXOFFiUVJBcEtscHd2emd2OWQ1M2NJcVMxa01EWVBRWFdXSjF2UWpiS2dJekVmcFhKOGRPQW5MR2s5dkJMOTdwMjBCb28xSzYtNnc3ekVsckZwUlN2VHEyTjhjS3RNWXFoYUMwRkZHUVhiWlk?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46018.54569444444</v>
+        <v>46018.69791666666</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Quant Strategy Flags Hybrid Financial Services Limited for Entry - Breakout Stock Watch &amp; High Yield Trading Signals - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 22:56:29 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPcEJMaFhWQ29BbjR5NjFnRXliQzE1R1BPYnpLUlJQdHpMd2VqLTFaZVNzOEhvVlh4aW9yWW0zNnRFdGhaZ091QUJMN1JxRFFueE1YR2hGeDZBNVY3SkxsN3Z6aHU0NUdSTUxabmZCdndCVmh5ZnJfUUlHLTNaUnR6ekxrVVJTV1NCSmwzb3FoM1kyWWFsbWN2TUlFNlVhTDVNSXlZSlVtMTBQODg?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46018.9558912037</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Salona Cotspin Limited Inches Toward Key Resistance — Will It Break - Dividend Stability Analysis &amp; Free Extraordinary Earning Power - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 04:58:52 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZGJ4aEo3NVlVU0dhazBQb3VValFCQ3JZZ3hWdXRXYVBCb1p3NEtabEplUGhoeE1hdU1uTW1yOE1MQk1SSDA0bDFPLUFJOGcxVW9KcFh5bVFnZ1EwbElZTmdVb0tlLUY3SFAyS3BWUDJSVWViekRuV0otUHVKM3VHZE9lQzZYWUFFaDNleEMzREhJbFlTN21DWXRPbkZDQlZOdVFjaUJTNUdnV0dCRnBzbUVGZWE3UDRJS2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46019.2075462963</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Is There Enough Volume to Lift Chemfab Alkalis Limited - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 00:38:25 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNS0pYck82NTcxSWRPX2w4M25QaXR6dUZyTDJ3TGkwNmFkM21TbWNnQVNydVRMRS1oOFNOc2sySHE0WnpvZC1GdzVxWk9nbzA3UmxobDJ4OEhHbXpOc0QwQURkMHROYlNHWVlqQVpSZ2NPd1hOdDBiWmE5VEdpMFdBTm1fdHNldmZNSjJhdjNlSFN0OUZ0?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46019.02667824074</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dugar Housing Developments Limited Price Holds Above Key Fib Level - Price-to-Book Ratio Updates &amp; Capital Efficiency Improvement - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 02:35:54 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQUlFwRXBKS1k4emhtUnlLUEh5a3dzWkpVaGRER0hiQjlqdkNuUVpSckFDZjN2TGhtdXdzVXlmaE02b29tNl9vSGJxSlpyRzJ0QmY3Y3pZYUNnSHUwVHgtM3o1NERLbTltS3Bsejg1SFR4MkZVZ2h1RU1CR015Z2NRX2xIQXJncHVqdVlfMDZ5SUJxSjh1dlktZzh4aEdDRFJqWEZSQkltRmtZTlVWZkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46019.10826388889</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>RSI Crosses Above 30 for Fervent Synergies Limited — Reversal in Sight - Energy Sector Updates &amp; Real-Life Case Studies You Can Follow - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 16:50:50 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRGEtU3dyVG85eXByS1k3S2IzRlZSMUphSm4xTDZJYzZrN3dfQVp1MHFQUTNEdEw5ejRIc0UtRWpmRmNoVlNDdW5aRE1PZnYyZTJzbFRRTjVNbVdxRXluNmpraFhOTzBNcFlhTXlZVjU3OGdPd3hkemlmYUhXY0UwLVdVWTFicGpYRzRjQmg1dmdyem1Tc2lnUHRCcDhBM0huVXlYZ1VuYndtSkg0NzhNWGN1VQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46018.70196759259</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Live Scanner Shows Breakout on Dolphin Medical Services Limited - Economic Indicators Overview &amp; Affordable Market Strategies - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 22:56:06 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQb3lZVzQyNTkzZkJEVmtWTDB2am1iT1ZOLWE0dnVIUW5DY2owVm5SQmhMeXUya3gyeFZjTm9JSGw4YzdSZTRBa2xxR0U5dUxQZ2ItQUVhWktBSTljcXRHSEJPNDQyeXB2QlRpMDl5dnFCZUJTdnFHaDIyZ2J0V01DdWplUkpxdFFudEI3NVBzbzE4M1RjUGpCbVlpbVF3OUU?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46018.955625</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bomb from Spain, Real Madrid asks Barça to pay compensation for Negreira case - Indeksonline.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 21:41:36 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOZmh4TlRqZ0dWQjc1ODJ2WlpXS2dVdW9jaW9xUmRJdkVBZG9FbkdBOWJYTm85MmlJMnRPOGxmRmdlM3UwaUE1eTlURlMxX1E3WUQ4WERfa0lFUC00anpaMGltaEVVQk9ybXdhalhya21GNEwwdUZzT2RON2h6T1NZZ3c5MUNyS2dUb0h2MFVvaXdvekttUktNenVkeXkzeTdURnRvaXFnRnBuS3Nm?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46018.90388888889</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Uravi Defence and Technology Limited Reaches Critical Trendline Support - Institutional Buying Trends &amp; Rapid Profit Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 00:21:23 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNcGhQci13RU5SSWVfVVFtaVM3VW9Tb1NudjRmTE5mbzJPaTg2M3lNZWZyQjQwT0trTGh4MkJLamU5amU4cWw2NzVqdlZxYjhtbkd2SzY5eDMyQU84enRaS0JERVZ2OTM0RGJHUjRsbExWcjdVU291bVRUX21Nc1pQX1B4TkR4azAtS3k5bWktcEtJcENsZFFKNTBrRDljQWlwYXU1RVJoTmZKTHRLUUgtM0RMUUR5Zmtpb3E2eDhjTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46019.01484953704</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tamil Nadu Newsprint and Papers Limited (TNPL)’s Trend in 2025 - Stock Watchlist Updates &amp; Free Explosive Portfolio Gains - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:37:01 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPZW1PS1JsckNOOG8zZlFBOWZNSHVpSGhzU2w4TVl5MVppX0tHQklzUnFoMmFzZFQtY25ua3hKLXpVaTJQUWhWaGc3cEVUZk43RV90OXVOV3NXVlhsVW9uM0JnSHpXTnY4WVdOOUpvd0lieGhOVU9Jb25tOUh2ejVoN1hSbjBHb1A4N2JWYjdZRi1uT1VabFRrZ1dVY0tCUUVsaGJPaVdmeGpiOHhGa0FLa0hKbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46018.73403935185</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bombshell! Cope reveal Real Madrid's plan: two signings already sealed for January - madrid-barcelona.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWTlvMTJ0cGpzOWhHODB2VFhPeHVnUWhuOUpFOUUzcWRmbDVJb2FDZ2N5bER0eDJTOHB4b1RCTDl0OGdCUldzeXJFNm10VlJvb05BbkwtaWpFVkd6T1I1LUdMWlRBdE5HVHl0anJxY0Jnc0w1a3FudTlNbl83V1p2bHZGb0pRWUp0NXVnM3ZXNnZFaHFnUWRrSk9HZDhfTDFsTEZqX1NYMEFNM28zanhGag?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46018.75</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Campazzo's Historic Night Despite Real Madrid Loss - footboom1.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 15:57:15 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNU3FiVFpuMzEtaTc3bUE2QTg4RWl6OWQ5TnY2NnlzM3BpXzV2ampPVERBVDk2M2ZpR2M5UlhRZVRfYjVWN0hrQU9GRFpkd0l2cWVXRFR3bFVEejVuX1BpR3MzR0MxS3Rnb3JHN1VmT092aVEyV0JfUmYwRHdEc0FKU2poMGhtMGhveUtzZ2VzSTBvUXpfdnUtUWJpWlBpWjZjTmYzVlF2VTN4UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46018.66475694445</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Carlos Sainz exposes shocking contrasts at Williams: can the team reclaim its former glory? - motorcyclesports.net</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 19:31:49 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPNENGQUpzU1RpMVMySlhOeTJlVDdfcmZpLUxMVk1hcGkzZUZCNTB2UlVuSHJDY0ZRX3Zqa1NqTEllcktiWjZ5NXMwWUdmUXBOUElWb0diV2ZheEhJbFdoVXppNlE4YmlmWkFXRkJ1STlrYUt2UTVtOWhXeTkyeWVkdENKelJjbUpKa0RLVUc4QWQzM0RuT1JLRWw5b2h5bnRTMHcxUmZHM042VzhIYlJPdjc2ZXNTYTU3QWNGQkdpSXZCTEpHXzB1V1BWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46018.81376157407</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, Spanish   language</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomba" OR "amenaza de bomba"  OR "explosión" OR "paquete sospechoso" OR "paquete desatendido" OR "explosivos" OR "explosiva" OR "tiroteo"  OR "puñalada")</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Online speculation ties Christian Pulisic to Hollywood star Sydney Sweeney - Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:30:45 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQZWZFT1I2UkpPel9nRlFKYWM2SnpJVUpXay16Qk50S2dJaDZSeFNIckZTRnkzUG50ekpCbkctVUpOSGQ5T2wtcFNQbWVwMFBYRGlzN0FaOFlOS2R1YVBjVWwyN1E5T0RzWkJRbUo1bzhJU3dJQzg0TW1OYUNfU2JGQkd5ODIybml2b0laM1ZtYVN5LTRNTjdTMzNidnJkUTl0cUNWZmNsYmlrY3pDVzVZUXdqZHl0amItbjZQN3A5TktzYUF6Z2l2N042VE5NSjBMWkpRQWgwdG96d9IB2gFBVV95cUxQZWZFT1I2UkpPel9nRlFKYWM2SnpJVUpXay16Qk50S2dJaDZSeFNIckZTRnkzUG50ekpCbkctVUpOSGQ5T2wtcFNQbWVwMFBYRGlzN0FaOFlOS2R1YVBjVWwyN1E5T0RzWkJRbUo1bzhJU3dJQzg0TW1OYUNfU2JGQkd5ODIybml2b0laM1ZtYVN5LTRNTjdTMzNidnJkUTl0cUNWZmNsYmlrY3pDVzVZUXdqZHl0amItbjZQN3A5TktzYUF6Z2l2N042VE5NSjBMWkpRQWgwdG96dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46018.7296875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Local Town Searches Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>(Kildare OR "Newbridge" OR "Bicester") AND ("protest" OR "boycott" OR "bomb" OR "shooting" OR "explosion" OR "stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>New image released in Bangor Christmas Eve stabbing investigation - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 18:34:44 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOb1BfUDFzSDFXdThLOTdyT2hjM1A1Qkh0UXczeEhlNUF1X29FeWRFdTlvTlBCZDZuUlhmbHVrRGFpc0wxdVRYSTRMTmRaTDJHTVU3alpPcHdTal95eU5VMTlKeHNDOFBEaHJaRWExTTAzUGZNOWNLWXRnUlN0LXpQWGN0SkFKRFM3YWVIMEFkaUZfLXljMUJPSGRmT1o4VENLZ3prZDZIWnZHNnFQWjVsMkFKb1hSZ2kwa0lmU2h3?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46018.77412037037</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bicester review of the year 2025 part 2: The biggest stories - Yahoo News UK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBNUkpZNGs1bDlTUmx0SzVjWkVaRURaUnVXdThoamU3MzFjQnNwVklsMDR6MmtEMDhIaHBvWE5uc0VLVDJoOHZfaFJKSWZSNnViSmdJV3hCYlFVaW5OMmFpcWJmcDFNR3RmV0t1d1pxZHFyM2htNmMw?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46018.70833333334</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Elliott takes over $1 billion stake in Lululemon, source says - MSN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:07:24 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQTms2b2ZibVBuMkRnM0Jnb2lfa1kwY3pfUjFDdlEyUUh6cDcxTWllWTJNOTdmWmhZNlRSMGFPZGxrYVoyVmM2am1WekduNmlOaUV1dXVnSGo3R0lJeGFLVUZHN1l5NU03QlNRZERUZk9pWXF4T2lNR0JSU3RUaDRFOW0zWTd3X2hGZmhELTYtdDFkazlTWmRHcHRUR1pYbnQ4V3VWMGFlYm4zTUhXZnpDSUN0QVNGdVFpa0h6ekdLa2sxVnlHRDQycVNEVV91Y2Rza1psYTJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46018.71347222223</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Man taken to hospital after Boxing Day stabbing in Edgware - Romford Recorder</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 15:22:52 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOZEtqS201RHUyNGJERmpwdUFXcDhRTG1BVkwtMVl3bmRkelNRVU1WUDZENU9aTWZuZER4N09aZ3BkZk1FYnN6TTUtaF8tMHh0Slh1TW41VW9EXy1nWXlPUjFJTENJa01xekJvcE9naTRpLU10czY5SEpfS1hPV2pGaUJaWGJuXzZPbHF5d2RTelpmRjJZTlVySFg1Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46018.64087962963</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>UK snow forecast maps show eight-inch blizzard to bury major cities within days - The Mirror</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 16:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQM2gtd0dvVWFLOW1LdmxFb2poNEN2Ymc1TmhNMlNvMXEwTjFCS21abmpWVncxTElURHRMbW9aRlZHTmloUXNGVTg5Y1E2ZnlzTzVQeHZoLXplNmR3NzNxNU9tSERZb1NKYTVUemsyWGViSE54NnA2d2x6X2JxSm5EYWtn0gGHAUFVX3lxTE5QWDlwOWJlOGFJRjBzMGpwWmtibUJWSktldzktTXR6WGtGOHE5MGJlX3V2X0Fhc2dGUzAtWkNfUHdoWXdBWmcwdTJuNXhZanpCUERaYjBRd0xmX3JvZV80ZGpKel9FMkJZMnp5ZlYzZTBIUXlJNEd2YUd6YjRxelRYallxTGdqZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46018.68819444445</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>The enchanting winter walk one hour from London where you can visit famous writer's house - My London</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 05:03:45 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPdXBrUmNRTXVTWW93MWlJVDVKUEZaeFJncW5UMWNMX3ZMRE53bzk3blp6T1ZIV3k4eXljRTI0SUJWb1BOQTlDVTF6eEtUV1U2ZEE0M25FeF9HVFkyMW9Md1U1aFI5RFhheW96cVlWa1YzcmFaZDdwVE5laDJRQVVtb3g4cG43dkUteHBUc3lIcEpqc03SAZgBQVVfeXFMUHB5RElJWnhKUDAtZTA2aWFCMzhkWXBIdEhfc0c0cmNiX2p4QUlIRHJKNnJoRHYwVmtzU1VwN0RRNk0wMGhSSmZKVFowR2tnLW45Ml9NQU51bFBrUnpTbGJudnkzaUpFSnZkTXdHMThiRWRCdXZUV3pkbWZ6RTZMaUhEQ2VYd2FKQmxZeGEtRG1wNlUxSVVkTUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46019.2109375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4 rescued from King's Cross hotel after early-morning fire - My London</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:44:12 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQjlqVS1xN2EyZTJ2Zm1vaW0tN1JvNGlqUjhrSFJyRkoyNUVsWkZkT2ZvODF4dGRyb1hoR0tBWS1oNjk5bWhsT1FaUnZ5QVRxaFZLZEZwTWFrSFZiLUktQWllSS02aXBuai1kRWxZWHFhbnlacGFPYVdUZ0pSNS03T1RpSlBUd9IBiwFBVV95cUxNdmdnUlp0dVRISmNDZDA0bjlBYmc5QXpkNW5SZktDQjJrY1V2ZEhnLWx5T2NBQzhUNHBGWU9jSGF1X3NZTVJ1R3NtWExHUGdrLXJmZnk2S1dMbU1LZXIwRV9EajhubXdGNnM0WV9Hb19fX0FPWDJVemFBRmhmZ3Nja2JmZ1dXVGlMUHU4?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46018.73902777778</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UK under-25s who need to be 'ready to fight' will be paid military gap years from March 2026 - My London</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 14:31:41 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNc05LTFczYm0xSEJDT2Z1UFF5QkhSTDhKNVg2Ul9VSlpma0I0d1JBWjVBcWtsNEZmWF84VXJPUWkxMUcyazZ6RXAwOEpyeWZHclBVSWpRX2JJVUxaUXpYV011dC1WR3d0X3hBY0Nya0FZYUhpeDhJYXBjZk44UEJHWdIBhgFBVV95cUxOdGZndFVrdHV3ZDUxUTZxcmlaX29JaXdPd21yRTFrbXBhZ3RVaHl4U2xPRGtWTnllb0ZjcHhjN0FHM1dIQV9JVEZRR0dPcS1xTGxDaWZJQlZzTFFVY013aW9ycktCZ0J6WDBNbE40Q1Y5NzVfWHZXM2Y1N0FONm10cEJpZmQtdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46018.60533564815</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>UK weather maps show 700-mile snow bomb to hit in days - Yorkshire Live</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNd1pSeFkwSnVnZmlqNkJjc3VYMHMydHpmWUc4TG45bHZBQjlVNW1YY3ZGM0NUa1N3cTZyaGhZWXhTWHJjS2xPcVhTVm1qMUJNdDhNODBZaE0xYU9zUmpnYWc5Qml2Zm11NXVtcUVVOE9zU21GWExZMFRQSWFFWTVLM3JWdjhZdi02bjJJ0gGQAUFVX3lxTFBfaGc4OFpOSlZ1ejBVSlpOZG81Y2wwMm4xSFl6V040SU5CaGt4XzRvcU94NVplYW5sMV9CLWVjZjhuNVViYm1jT2pLQWlhc2FoajF5UDlmQ0hrbmlsTFoyN3hfNHBTMEdMZWxmVmh5Q21PVGNWelpNbDQ3bzhlNEtrTWh4TXBfT19nbTdxdDBGXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46018.74097222222</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>State Papers: Government refused to pay bomb damage claim sought by Lord Longford and Viscount de Vesci - The Irish Independent</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 05:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPSXRlX1d6VlJlQTl6S0NkaGlXc3N1anhUb3k3c005a3c5amtXVzBqXzl5RUVYalptYVctM1lFUmVHMXYyMHVaTktGMkFSUG5aajZoNzZEdDMyWDkyTkU5V2ZVZjBpQlpPZ0trSVRxbjNWSk0tVHZPakl5Zy15SFRrZ3pvUXN6d01tbnNlTi1rZGFvU2hCVGdnOWFsOTJrLXA5akE3em5mSV9iTDBaY3dKRGpQaV9pVThmSUJXWC0wNU1GVEFUTnZWb0RuS1pVUE1WQVpBd2l4ampMNTlUQnVuWlY4bncwc3Jldm1TZHJQckR6djg5WmlMRFpGR19NSzA?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46019.22916666666</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Irrfan Khan’s health deteriorated while shooting Angrezi Medium - dailyasianage.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 07:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNc3RwVXlnQ3JBNnk5NXowQkVZcTU0MkNHZjZDWm0wUWlwYUpuNGx1M3EwYURoY2V6QVlzNW40bDhTUTZjSXpHWGF4ZXF2REQ4RWVYRWVsQTMwSjkxWFZlc19HMDFpOTZ0X0pNNlFyQXlNRkRLV3pDYzVXaUxheDlrbG45VmFvZEQtdmZSNzZVM3A4LTUxVzlEaFBKV0pCdXhBa3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46019.30416666667</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Paris metro stabbing suspect released from custody, sent to psychiatric hospital - Malay Mail</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 01:16:43 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOQWNmTmwzSC1EY0E2TS0zOG1ibmtiMVp0VGoxaFlVZC05M3J6TER5WHFIT3NjVTYyZTgxdV9ER3dnU3VqWll3cDMwazJHUDY4dDc0amZ5WXlZdmR0RXFneWo2MXB4R0dHaWhtRzc1bTdFVUR0X0Z4a2kzVU9YMm5hbGttVXl0d3pQbGZyOEZmOExRUXFFTC1kVXRzTlFRWFlYU2NZY1gtQzJhZDNWM2h5aUFfaXF0Y084NWxlQTUycEpjZTNTMW9jVDZ2MmRHczTSAdQBQVVfeXFMUEdMdmZLNzRlajloamFjUjR4QktYNFR2WThibFRseVNMVWVLWnNqbWpkZFZ2QW1ibjZIMGphNjhYdXdRbmNvT1lzTG5lUWZFeHByYU0tUUtRR0dtODVFbmVWc0JHR2N6T2UxcmdSSWFleVlpQkM3bzBUMk9TSGZpSGZRdUlwT0s4ZW5zZU4weTVabWdxM3JUZG05aDFFeEdmVkVfWThOajJZZHFOT3JDUkFnNDhVd01veTBGbmNwQjdqRmVqRm5Ka1dGdlhLR0tnLWVMTU8?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46019.05327546296</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Police in France arrested a man suspected of injuring three women with a sharp weapon in different metro stations in Paris. - facebook.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 22:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPY2VkbUxVeFA1bHFGUnRJa29qNHd3VHN2SnRJUGpqS0F5Rk80R2c0U0RuQ2g2TzlqSEVqcW5hWlhXTFFmOENFaHR2RkZHY3I3RHgxTHdQdzdJYU1PNVJkVHFESEVyQk1fZC1FWHZqWE1NTkwzY3V0N3V2ampoNERhM0tUaFVGX0tUSjV3ZVdYWFVBaWdhREViMDlsU3Q2bkE0TjdfZWhsbUgtQ1o1d0ZudzUwT3pRQUVVYmRXU0xIY3VSNHlQZ2I1NFdZbWM5MDV3LUwzMkJTbkpxWHVfT0JybA?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46018.93680555555</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Explosive Start: This Apocalyptic Netflix Thriller Astonishes Audiences from Its First Days - 3DVF</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 18:59:06 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNRDBfSjBxYnFUZ2Q2bGd5aExnS1hvbHF3d3I0aHJ1TDZkckdleWdOX2o5UXJCR3VmcHFzRmp1LVJpRVU1VFpETDQwbmQtVGJGR3cyWWlXUTNaNG1mc3BmNF9lMlh3MzlwSWdIb1JkM2FVell5ay1VUWNueUVNek9PbXJGUWpva0lNSU4yTkZfbkdfaEZvemhjWHd3ZlAzdGttTjgtbGRBczJpMkRLWHZnNw?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46018.79104166666</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GOLD for Tilottama Sen at 68th National Shooting Championship!! 🥇 She defeated the likes of Asian Games medallist Ashi Chouksey to top the podium in women's 50m Rifle 3P event. 🔫👏 - facebook.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 15:19:49 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNY0NyWkdiMllaYnhJUDRmaHk1MFhmeGJ5NENoZ2F1WGRsME5NeExIR08xZ1l6M0U1c2pROEY2dW5TZjVHVC1XQjZBeUc4YU9XZWRaVFhQZDBickYweHoyblg3cjN4NTNzTlNWTmRtRG9kczlvN3llOEQ3WHNfZHktMl8wTHVIMjVM?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46018.63876157408</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Musician who canceled show over Trump's name criticized - The Manila Times</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 16:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQVUZCd3pXamthODBtVWo4VW5qTE9HM3hLc0w3eXAtSTZ2b3dpVnF2LXF3bXFRVjNYWGF0ZTZ3YXVxX1RVcGdPY1NKX1BzSTkxR3owWDF6Y3hScVIzeVpGVEI2dktZbERoZEpoYVBXd25xVmNaQ29nSklzZ3ZYNENobTNEM1E0d2xXUzdEbmlLSzBYa0xzcmVZd0g4TjhUVDVTOFlnSGJJdWRicDVocHVhV1REdTZjbFlaUzVPUW0yRlhqd0HSAcMBQVVfeXFMUFVGQnd6V2prYTgwbVVqOFVuakxPRzN4S3NMN3lwLUk2dm93aVZxdi1xd21xUVYzWFhhdGU2d2F1cV9UVXBnT2NTSl9Qc0k5MUd6MFgxemN4UnFSM3laRlRCNnZLWWxEaGRKaGFQV3ducVZjWkNvZ0pJc2d2WDRDaG0zRDNRNHdsV1M3RG5pS0swWGtMc3JlWXdIOE44VFQ1UzhZZ0hiSXVkYnA1aHB1YVdURHU2Y2xZWlM1T1FtMkZYandB?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46018.66805555556</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Powerful explosions heard in Ukraine's capital - The Manila Times</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 16:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQRk5JaW5UbXg2ajZxV1o2eXNiMlBCWVhZMWh3bHNmZm05QzNIclNld0xlVTlSVkNnVmRzQ2U5bHdhYXV6RHA2ZEV4TVdheG5pZ1NmWW40eGhjV19MTWRYeVlpUGNpMUdQYm5FdVBoVGh3Q2NvbjQ4UzNYeHg1cHdxMTNmVUFCak4xeG9TTF8tSThZR3B6NmR4bmNTNUhfbmFXUWpycW9ScWNtR3hicWxoWjY0bEtBTDDSAbcBQVVfeXFMUEZOSWluVG14Nmo2cVdaNnlzYjJQQllYWTFod2xzZmZtOUMzSHJTZXdMZVU5UlZDZ1Zkc0NlOWx3YWF1ekRwNmRFeE1XYXhuaWdTZlluNHhoY1dfTE1kWHlZaVBjaTFHUGJuRXVQaFRod0Njb240OFMzWHh4NXB3cTEzZlVBQmpOMXhvU0xfLUk4WUdwejZkeG5jUzVIX25hV1FqcnFvUnFjbUd4YnFsaFo2NGxLQUww?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46018.67013888889</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Iran president says US, Israel and Europe waging total war against Tehran - Malay Mail</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 01:41:02 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR2ZFU3dnc2Y0cmJ4dWRhelBOWlIxdWpFY3VEMU5iSkxQM2J4X2g0U2MxTU1pV0NRMEhINmNnNjNRYUx1anJMaWp3eFhPLTNXZUxGdEpvendEc1U4bGczVk1BQzJQY0NDd3RodGdmUFUzcGxCdXEwaERDMWM1c3Q4NzdmdFhhbUNpaC1HVEV3TnhkQnk0Wmw1QTBkcGlXSl9pT1pVaTBZY1dSdVlIY0pYSERnTzVEZnFZM1lqenhaSmswQlVSRThDUDRZVdIBywFBVV95cUxQR2ZFU3dnc2Y0cmJ4dWRhelBOWlIxdWpFY3VEMU5iSkxQM2J4X2g0U2MxTU1pV0NRMEhINmNnNjNRYUx1anJMaWp3eFhPLTNXZUxGdEpvendEc1U4bGczVk1BQzJQY0NDd3RodGdmUFUzcGxCdXEwaERDMWM1c3Q4NzdmdFhhbUNpaC1HVEV3TnhkQnk0Wmw1QTBkcGlXSl9pT1pVaTBZY1dSdVlIY0pYSERnTzVEZnFZM1lqenhaSmswQlVSRThDUDRZVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46019.07016203704</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Florida: Death Penalty Sought for Man Charged in Woman’s ‘Brutal’ Dollar General Stabbing - breitbart.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 16:59:30 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOWGNIRm1Kd09GWjh1NExLZ3VZTjVuNV9mUHk0RldsVGNYbjg1WXFUbzIxWmpCcWZLV1BYNmpTVHlEVjhvM2JrNFZvQ01yVzFOQVZ2bENDMjU1cDhLOGs4YXE2SGE5V2R2NWtydExBc0Y1QUU5eGlkbmRFTjlLVFgzZ1BUcnNBMW8zWmhYWUREQjJsdkxTLTk1Q2U4NVdSdk9uNERDc1dLR29UXzVwaDhyVjlyS3FRUEw4SFRXVmpKRWZ2RDVn0gHEAUFVX3lxTE5YY0hGbUp3T0ZaOHU0TEtndVlONW41X2ZQeTRGV2xUY1huODVZcVRvMjFaakJxZktXUFg2alNUeURWOG8zYms0Vm9DTXJXMU5BVnZsQ0MyNTVwOEs4azhhcTZIYTlXZHY1a3J0TEFzRjVBRTl4aWRuZEVOOUtUWDNnUFRyc0ExbzNaaFhZRERCMmx2TFMtOTVDZTg1V1J2T240RENzV0tHb1RfNXBoOHJWOXJLcVFQTDhIVFdWakpFZnZENWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46018.70798611111</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>New Year's Eve terror threats force several major cities to cancel events - The Mirror</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 03:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPaFBWTWNmYUhaVUJwSGFLRnoyRmpweTJVVzBPVm5vYy1WNE04a3pnc2xOYVdTbWFTN2hONXIweGFBZWIyT01JazMtN1ZVX2o0U1ptRDhRSTkyeVA2SEYzOXB0blpEc0pVdXF4Ymg0cjJZSEF5S2FwanZUS1FyaHFJNW92blRhREcyUFHSAYoBQVVfeXFMT2hQVk1jZmFIWlVCcEhhS0Z6MkZqcHkyVVcwT1Zub2MtVjRNOGt6Z3NsTmFXU21hUzdoTjVyMHhhQWViMk9NSWszLTdWVV9qNFNabUQ4UUk5MnlQNkhGMzlwdG5aRHNKVXVxeGJoNHIyWUhBeUthcGp2VEtRcmhxSTVvdm5UYURHMlBR?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46019.15833333333</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Security Limited After Selloff - Market Depth Overview &amp; Free Explosive Earning Power - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 02:39:47 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQdzBvTE1IcjJ6dUFYMEdleHVQTWJ1MlNtWVBjc0pJZnVReDZydXRBMFptcG4tLVExdUZBZEhvN2RVamlCZ0hxMFpZdFRaM0RHc1g1ZDlaNU9ZRl9Mc2VpVFM3V3hIdmVHRmZWY2VNbVM4WU1NeHZQLWNPcnVvTktyMGhYbFBRbTJfMk9kTkZjbzF2SVp6N3A5OW1KRHFaVjZudVUyNDl2NmFteWxCMUN1WEEyN1NBa051OEFrU3UxLTNlZ2ZJSU93?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46019.11096064815</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Pigments Limited for Entry - Swing Trading Watchlist &amp; Explosive Profit Trading - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 01:02:35 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaHltSkpDR05fSnZuU3U5ZXNFNnp6LUwyX1FLTkJTZGF0OXVZV19nX1FrbVBncVVaMXo0Qld2a3I5eWdkalR3OVpjM2dSODFqaWlEQ3dDVVJjR2NpVFc1SXhtbmJWSVgySGpPVHUxU1M2cjNRRVN4SGtxRjdGMm84VHB1enU4QVlucDJscjdCY3hJLW5LM3pIMTJscGItSUJTODBsbWxPQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46019.04346064815</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Am I trading with the trend or against it - Growth Stock Opportunities &amp; Explosive Profit Potential - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 22:56:02 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPcFI0S0JZQnh6S1VFUVhrRWQ1QWVncDZ6MnVNVWlFeDNEb0NxSk9iQ2U0OFR1dnE5SjU4SktyTlg2R1ZyMGJteHRXdmRReHlEZEJ2Z3RtRGhxYXV5Q0lhQk9rOUhlWnBWNUdZMXRFMFNRc2FDOHZvQUpyX0FNM2hZZ0lnYUdCM2VSWU1HNVl5Q1d5T25VdGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46018.9555787037</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AI Champdany Industries Limited (532806) to Launch New Product Line - Technical Breakout Signals &amp; Achieve Explosive Results - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 19:24:59 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNd2Y2SHBGWFlWdFliN1lCYkxvOG9XY3BqalBPMGNXQ0hsdC1QQnVSLXR4WWtqZk5zTkZlUnA3NlItZllweGphN2F3RWtPTjlsS0JCOHNPd0l1UU5qMjJhLVBzalViTlRYWkhRQlNfU1I5Q051Wk5FT3BYLWtVQ2pVVGxMQl9LUW41dlI3TnRBd3d0WXRVTHJEUmlpNWNCV3JNbHotQTE5aUhZMWZqYWdFdGUyUTlnOVNL?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46018.8090162037</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Rolling with the punches - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 00:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOR041ZVI4NWU2QUwtd0dNZEJqdUxHaW9WUGd3Y0EzbWpYOUxMSGpWUHdMSnRYbTd1aFJjUUNhTEN4T2lrdEdwbXdiNTAxeGt1eng3ZGE0RU50a1lpdE5Va3JNUE1jU2V0a2xNU0dxLWJSdkRPSGFvRUY1WDQ5Z2cxSXN6NmPSAZIBQVVfeXFMT3gtQXNfaloxd3dwV2stQVpmcGJQTmdwbkd2S1lGQVVDYTNWZ3g3NmVHMURmMzFSbG1TV2k2WkRvYTlEMHY3QU1BYW8zcWFJaXlFZTlyYi0zSndsclIwcjl5a3FYWm5lMGRZM09CcnBkRnloV2VkdUJ1Ym56TUJucU15dnRyMHc5cTFjcjBZcnJ5aFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46019.02083333334</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Limited Breakout Confirmed by Volume Metrics - Price Action Trading &amp; Explosive Capital Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 21:11:09 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNSXl2WGxKczFveFFtRFB1TV9LVFNkMllnNUZNb3hHV2F2VVNrcUZRQ0x3XzNfZWlFbzFLdFdMbVNKTUZ0bjhCR1Njb2tScHpEVjBCQVExaXE4U0JLZDJWYUlqYlByeXByNU9rZmlfdEFmam9oVU51X1EwaTg0bVV1UXVaRXRLOVRPWmpjUkhGX2ZwUmJGUkVLU2FnMEthVHJYYUhXVFc4NTJodThqUEUtQ3BlMG9FY3Rv?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46018.88274305555</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Trend Reversal Possible in Kimia Biosciences Limited Charts Indicate - Price-to-Book Ratio Updates &amp; Free Explosive Wealth Accumulation - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:57:54 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPV2kyREktSHlLTlRFRTJXTzJMVXRFcWR5bnA0a2RLVGc0OUhxZUlHdDMxRmRRV3BlbE5JOWdwdC1jVHlZeXNOdlFGVEI4UW1aRnpoU3N4cFlkazVkbktiQl83RnNIcUxrZFpjRGpVX2lPMXJ2ako5TXg3MTZKTlRoWmlkZVNNSlZETzhXaFVQdXpKa2hzNHRMY0RXUTNXU1owVEJldjBn?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46018.74854166667</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Monte Carlo Fashions Limited Included in Top Momentum Scan - Stock Price Divergence &amp; Explosive Capital Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 21:11:09 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxORUxrTm1zajJieG9TdW9jYnVlakpxOTZ5TG4wTjM4MDBYc2g1QS1ONnZrN2N3RXJHZXRBUDBSXzVXYUJHeEtIVVZ6WVFzZXhDRE1Vd0xwbkJ5VFhENjhpeWZ5YTM1Uy05NE9NSHUwakhQdDBQSmtJSDk2aTNlZmphTW5FMFJ0LTNaYUxUMW8wdWt4NnpOOV9rRg?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46018.88274305555</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cosmic CRF Limited Breaks Below Key Support Level - Market Depth Overview &amp; Free Explosive Earning Power - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 00:46:18 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcU9XaDNPV21iUWtTbFgxdHJsQndRYUJ2Yk9qakpRcmc1RE5menRHYjdFTDI3OG4wZmVpaXFmS1B1eG5RWFRnTGdlb1ByOHMtZmVEVTBEY3IyYzFzX0xzbloxcE05cHJkSXl4YzFWWFZXSVhobTYxbEYxS1huSFB5UGQyRjhqMkstUzNtTVJlMDRLY2hiRjBB?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46019.03215277778</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Bullish Order Block Entry zone for long trades. - Bollinger Bands Signals &amp; Free Unmatched Market Gains - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 23:00:17 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPSmoxM3NhYWpIUzJUR0R3SXhRdXhmNlJiYW5rR1VsaDlsU21ENUFMM0JoZEt6b3Q3cFRDdHREZFFxSXV4NkhPWTVnWFFVRnJXcEI4VE1wendDMXFmV0V1UzM5RnRRTWctNWVxX3VQWHZJVzF3Q29YdDBEeGtTZmhOQkdPOWNFcjNIT3RrWGVfVlppQ3hDZ3I2M2Z6NlgwZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46018.95853009259</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Hawkins Cookers Limited Tests 50 Day MA After Sharp Decline - Sell Signals and Alerts &amp; Plan Your Exit as You Enter – Risk First - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 03:16:46 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQYUFBeHMteDJabkw1SVhJbXZnS215QlFxLThCYXRCMXBQTVdqamEwdFhPdDFhc2VXeWVEenNrYW9NNmxOVXRaR2RxcE1NVXVQa3hrYUJ0NFFzejlGUDVfVmR5NUtHTXNzZVE1R25TV1BsX2RUa3hfUXVZZ1NyLWJfWDZFNFk4czFGMzhmWk5LYktJQjFxTzhDdWZXMTVKaUw1S2t5Qw?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46019.13664351852</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Technical Analysis: Bharat Heavy Electricals Limited (500103) - Trading Volume Surges &amp; Explosive Capital Gains - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 22:31:35 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOMmh4WUZ6VFF0Y24wMDI0YWhoakJiSHhfWWs4OW5PdGhzVENjUmJOS2RRb3V3WDRmRGRmME9qdGNzc24wdjM0V1gxTVljOHd2NXlRSUpLOU5KdGpEZm9QOFBiM0ViTFhkeF8yVTlyc1JEeFBERmxFMTBkWDVhNGx6QXdhMk1IaVdqR3U3WG9GanpNekRZWWp5X2FsSHVabG1oOXBpWkVlWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46018.93859953704</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Technical Bounce Expected in Nagarjuna Fertilizers and Chemicals Limited Next Week - Mean Reversion Trades &amp; Explosive Profit Trading - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:21:03 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNMEVvamx6M0syM29Qc3pPdUlPbDhqUk5nTk1mU1cyQndCbklrNDc3em94RnhncWZ4QnZoUy1Kc1h5emxNLWVsYV9LQ01mazhSZVR4UXZEa29IZVFuTDVNTmh5NzY5RUJtdkkzUDVJQzEyS05jV3FxSU9IaVNkLTRDZXItaHlJUXl5WnNSQ3NoSWk5SFU4ZDgyWnhDYmNBUkx0UkRkUS1vSUhsUm9WTWhmYUJqaE1PMkl1?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46018.72295138889</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Panchmahal Steel Limited (513511) Hits 52 Week High - Double Top/Bottom Patterns &amp; Stay One Step Ahead of Risk Events - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 22:32:20 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPRFYtOUZnb2UzRDNHUXlMRzlZS0FvUWZCR2ZlcVFkMVVGMHM4Umx5bDZpLTFTbG9aOFVGa21adGRUVkt3S25TSml0VUdZbzhBQ0xpX0FqY0xhTk9Xb1E1NTdPbnhScDRBcV9wb09TdGlpOEljWWdrWkk4ZjM3NDFCZjgta29XT01iSGw4RUtwSnhUN0w3RFVXZ1o3RV96dUZ3S3JN?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46018.93912037037</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Over 1.2 tons of illegal fireworks seized in Milan ahead of New Year - Qazinform</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 14:47:16 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPUmcyREJVUWxVZEQwcF9WaWxIbFFxM3FzbEdBSmgzeHJyU2R0bXZXVFJ4V0IzWW9NY3U5dkRUMkN6cGZHakhPZTl3RXFyUTc5Rk4tcFVDTUFrNEFZMjhQeEVibjBnWDRxRkxjTl9VVXpCY0dHaThuN1hCWnFjeVdQX0M5ZkRjNVg0TDdhdmRJdXRRaGwzSzEwRXhDaEM5eXF0ZGtj0gGjAUFVX3lxTE1nc0huOG5ja3RRd3BKUk01QVljcnZCb3h3WjFXYWZMTXZpYkpTX29IeThiQklNaXM1TXRoT3lMdHZuMXhILWd4NFN6ME1uTVdoUndIUlZRTGtvbzdhX0EzR1IzUEh6RXhDU0xlUS1JZXFiMThaQXU3M2RfVDVPaUJkbHFHTVVzTTEtSEhOTVp0RV80WEt2cVJjMXBDWjlHZEE4b1k?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46018.61615740741</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Milan renewal for Maignan approaches confirmation: the details &amp; figures - Football Italia</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 18:28:25 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE84WTBOcXZmLWhfTVRRaUdZcUdMLTYyejFBc3Y5N2hmWTJSZWN4c0YwclFIMERnNG9DdGlnZHJORDh4Q2drSmE1eWVIQzB6TnNzTVRjUktvSjVXOG0ybTk4WC0zRlpxODdUVm1ZR3UxUDlDMXVV0gF0QVVfeXFMTzhZME5xdmYtaF9NVFFpR1lxR0wtNjJ6MUFzdjk3aGZZMlJlY3hzRjByUUgwRGc0b0N0aWdkck5EOHhDZ2tKYTV5ZUhDMHpOc3NNVGNSS29KNVc4bTJtOThYLTNGWnE4N1RWbVlHdTFQOUMxdVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46018.7697337963</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>WATCH: Longtime NFL assistant Tom Moore speaks to Hawkeyes in Tampa - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 03:36:59 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxONWNEYnE0bjJrc0JDdmc5V0o5eUt6M2hqbUN0UzNKYVJUMlExV1RrcGg3UkdRRVgtOXdNMG5MS3RKcHl1eWVVYjlyYUk1ckNoUUVwUnd4Znk0cjJPWnpTX3g0WUJ1YWRIM1lydmlpaUphWVVaRVZOMUxwX1pkSzctV2ZZdlRLWXNSY1Jya21pZU9KdlI4RjIyRExtWTdYTnlURmlmVGlZdUpVUWxIbzNjZUF6ODFtaFNXY05hNU0xcEw3a3RmMlFMenN3cXg3RWpxdHZQM1BmMWx6Y2YzN0NneVMya3duTzJYV0JJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46019.15068287037</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>What is ski mountaineering? Sport to make its Olympic debut in Milan - KREM</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 15:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxNd0hMaXFDNjJwdm1yUzZTUDVhMHZnM3NWNnlqNW9qeFhweWNsNzNma2pVVFQ0YkRudWNTWWlWbFpLZ3U0cVlGcVpCSVdpMF9jc1ZxUHB1WHNQSGVvMTlVaml5ZldkSGlmUkVxVE5QM1BCVW04d19FY0x0U0ZuMmZxOEw1V3BubE53aUNadF9vdC01UUQ1OGh4NUR5bTBhbzh2Z3BwclUydlVZUmRCY1doSC13eE5INU43UU9sb3VRc1U1Mldlc0EteGtJWkVoU2RTb0NlUmVDMTNEdjk4U3J1SlpXRGJMTWwxRHp2aTMyZGxSazZTVFZyYzk1UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46018.63819444444</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NBA Draft: Three Juniors On Their Way to Standout Seasons - Sports Illustrated</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 16:00:02 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOQXZRa2x1Qldhd2R4eXVXb29nanJpUDU3cnpDZUhYaWN1M3pjYWlidERyVHpvcUNXYW5Ca2pxZUhIVVI2cjdYMDU5V2U2aVMxZWx3NVA0dDhoMmRGNWdUTWVTYWV6X0ZjNmhwNG9CUVlibk1fOERjRFNMTTNIX1E4aEg3dmNkZzkydDloYlVaVGlGb2VqVFdpTERn?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46018.66668981482</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Consensus all-American Kaden Wetjen preps for final game as a Hawkeye - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 19:53:57 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPNElJbjVqY2JzSXVPTDlDTWdlT21Da3Z0ZDBiQVp4dHhsbzktcHpXTjgyZ3FQV0Qydl9lS0pGOGVNZEFYWmF2djF3c3g4Y0lPSXF2Zno5OUQ3clhyNUVpRWNzOXlQUTMyc1NPdHhjcmxWX2YwMEtaNXh3a3U1WGR5Rm9kYjhydV9WcWdDYXNzdk40cDB6YWFmbTQwdTV0a2FuOThJa01pQ3JraXlwbncwZC1MYmlwNTZSbkxOMUZ5aUQ2YjBrdWpxNXRaZndQSGg2QmtNc3YzdHNWc1pkRUxlbU4wTmF2NFh3eDNwQkFMUW40UEVPaFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46018.82913194445</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Šćepanović elected as Director of the Police Directorate for a full term - vijesti.me</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 20:08:49 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPdkg4T1NpSWhveU9jVjFUaE5oT1QyR1Awc0xOMDVwQ3dCdVFjU0tIQUd3VnpQMm5RYWYyS2pJSDBKYkdwRDR6a1U4Qmo4VEdFbE1oNTNTTl9GZWZlUkROSHJRNzEwSjVFZmhuTlAwMmVuQ1U1b2NjNU1WZmhIRjVrU1RfcjR2MVl4Zmg5cTREVWhITy1QTFNIVzJkNE9MZmltWEdpZ18xV1A4Vmtm0gGsAUFVX3lxTE92SDhPU2lJaG95T2NWMVRoTmhPVDJHUDBzTE4wNXBDd0J1UWNTS0hBR3dWelAyblFhZjJLaklIMEpiR3BENHprVThCajhUR0VsTWg1M1NOX0ZlZmVSRE5IclE3MTBKNUVmaG5OUDAyZW5DVTVvY2M1TVZmaEhGNWtTVF9yNHYxWXhmaDlxNERVaEhPLVBMU0hXMmQ0T0xmaW1YR2lnXzFXUDhWa2Y?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46018.83945601852</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Iowa's Nathan McNeil returns to native Florida, sizes up freshman year - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 19:56:23 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQaGZLRUI1elZqNVFGZkZjUG9YMzQtelFPNlFzaF9LaDJhR1Utd1JWekdCbWhLQW9kaklMUHI1TTJTVkJwNDZpV1huUGhMVFlrWEFoMjVXTlZzNmpoYVozaXJObUt5WmZscnRXLWdYdE1WWjRLNklGR0tRMVNUd1I4MldfdURwQjc3QXF1N2E4MTUyUkU1T25NUnNOQ0g2OEx1RS0xbFlkYlRfbnYtMGstdTRIdWMzTkVNeFdrNVRIcDQxR3p2VEVQSDdVdlZXQ3gxazl5a1NOUHhRWGE1NUZIQmpTWXExbzc3X2FaSUVZdmplMTJk?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46018.83082175926</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Iowa running back Kamari Moulton embraces the warmth of native Florida - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 19:53:51 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNY09qMWdhZ2xyVEdzMVQ3d3lQTDBfNjkwNmJpd3JXaGJObWhrZE95THFkVTh2WjBIZy1INGl3T3NGczh5Rlp4VGJMUlJrREV6ekJLWmdkdjBlSFYwQVo0ZUVpVUdKamEzN3puUzJTMWxQMmlOTUN1ZW1FWWlaUzcwakMxOUgtcGFOeE9xVFRGeFFPYW5oREpqUmM2cTJGYk1hbmpqOVI5R0pjRzU3Q1N5azQ5X0FsVl9sdkJxVXNjUm11OGpYV3VjcExBMTM2STZ1TjBvRDV1THdfcWlzT1dvMldRSXkyQVlIWGpPU3pBWFk5YWEwYTJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46018.8290625</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Logan Jones' reaction to Iowa offensive line winning Joe Moore Award - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 18:52:38 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOUnlrZkJFZXgtb2p3dm9LenY3RjhHbDNXbmhRZjRIU3pfNU5WUDFFOENlaWpJLWI4SlhFdEJLdWZYSE9NN1lRcVZMUFFmcGRFMENDQ2wtdURkY0c0V280ZUpPbmVFS2pBR2lIX08wV2NzOGthdEJxakRCTTZQR2thSHFTbDdvdzhrcUY3Y2Znbk9vRTBuOEpTbHJ5TXdXQTBJUm9GZ3BXMElmdFU0dzhpbE54bnhLMWI3WVRuUGVKcVlTV2I0dklnc1p2a3Ytd0h0SUp1amtGNVFmR040ZDIwYWR0c1pvakFkemZkT2pQVTllVU0?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46018.78655092593</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Iowa QB Mark Gronowski getting set for 68th and final college game - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 18:23:42 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNSU9uNnFlYWkwQkQ1cFR0Q05zcFU0cGFPazVkanNFYnUzYzFCMmFrMmpBdllNWGJnVWFXZlhIdEhQd1pnY1pZYnNZcXZ4M1VKMDUwRC1BdDRuYjNNSi1JQVJDT200eHlwVmFjVHR5VlV5Z0RudVkzbC1HalFzM3pKSHNzWGl4N2ZyMEVJMFFtaWxkVldFNzRnb2w0V2ltUmxLZENPcDk1Q2JpTFlXd2djU1BDdkdOcGkzOXN3YmgyZlBhemZOMmtYcElydUZFdDEyZDRvYmdvSzdMbmhTc2dyd2ppRU9BV3dKaGtvYUhfUm0?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46018.76645833333</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Momcilovic Shines as No. 4 Iowa State Dominates Long Beach State - CollegeNetWorth.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 22:04:42 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNQWVBdUhKUnBUR21NenJSREhlMHNKT09fWGp2X253NnU5eEE1UE91blhFMlZ2WlJOWWJ0N0VPOHdjZy1YWElMSmk4SXNpMTlZd1pDMDFudlBnME52QVBsQmh2MlhidEdjX0pROXV4QzltdW9KZVdIOUFMWEl3WVl5UTRWOE9iUFptN0ZkVkktTkdURjVyRE5xeHZGT1c?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46018.91993055555</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, Italian  language</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("Milan"  OR "Bologna") AND ("Bomba" OR "esplosione" OR "sparatoria"  OR "Accoltellamento" OR "esplosivi" OR "pacco incustodito" OR "pacco sospetto" OR "minaccia bomba")</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sydney Sweeney dating rumour explodes - Herald Sun</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 01:40:04 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNZ1ZUZHhkaGh0cW41ZTVMQ0pLZGVDeVhIUXd6ckxPOGlrdU0zVXZpTE1aTkZXNmx3NHlpeTJLaXBjMXI1NWw3TGhDSVZTbV90T01VQ0F4Y3o4U0Q1OVR0LTBHbXNpMEpYYUQxd01VNmd1VXBHdXlkWXdHcFVmbWxXVVhIaUlBTmJYSVVRNEMtOE5fN1lydE5wYVoyMnJySGFFa2FiU2R5UHdfbVVDVVFZbzZsZVZiSzVBZ3Y5cGxuX09xM1B2YWxTdUtzUkNTR3JCbUlWT2xQWVMwZS1fdjVPcjR2YU1aS2phNkVBS1pudWFCVFBFYUVlSlVSa1ZaV2ZzdE15UXNvZ21Dd9IBigJBVV95cUxNZ1ZUZHhkaGh0cW41ZTVMQ0pLZGVDeVhIUXd6ckxPOGlrdU0zVXZpTE1aTkZXNmx3NHlpeTJLaXBjMXI1NWw3TGhDSVZTbV90T01VQ0F4Y3o4U0Q1OVR0LTBHbXNpMEpYYUQxd01VNmd1VXBHdXlkWXdHcFVmbWxXVVhIaUlBTmJYSVVRNEMtOE5fN1lydE5wYVoyMnJySGFFa2FiU2R5UHdfbVVDVVFZbzZsZVZiSzVBZ3Y5cGxuX09xM1B2YWxTdUtzUkNTR3JCbUlWT2xQWVMwZS1fdjVPcjR2YU1aS2phNkVBS1pudWFCVFBFYUVlSlVSa1ZaV2ZzdE15UXNvZ21Ddw?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46019.06949074074</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Elon Musk Says Brussels Is “No Longer Belgian”, Cites Demographic Shift - Republic World</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Sat, 27 Dec 2025 11:05:10 GMT</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPajNyYUFUSzZ1dTZFc0g1WU1hVHhxUktwdktUVHpGRm90YjQ4cmxWMWxJUDlEajZxN2JpUE1uU3FLNHl6YjZROFI2Z2NIYUVpUmlXRmhBWURPdE5fb3RmWTZ5TE5RcmRLUVBvM3V4UW16aU5TcW1tejQ4QXdWUHBZbDVBSEdOdHdVeFFiaHpYM2d1c0RRU2xlYURnX09HMVJxWFNYQkV5RnJfOWV3c3hMaS01MNIBswFBVV95cUxPajNyYUFUSzZ1dTZFc0g1WU1hVHhxUktwdktUVHpGRm90YjQ4cmxWMWxJUDlEajZxN2JpUE1uU3FLNHl6YjZROFI2Z2NIYUVpUmlXRmhBWURPdE5fb3RmWTZ5TE5RcmRLUVBvM3V4UW16aU5TcW1tejQ4QXdWUHBZbDVBSEdOdHdVeFFiaHpYM2d1c0RRU2xlYURnX09HMVJxWFNYQkV5RnJfOWV3c3hMaS01MA?oc=5</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>46018.46192129629</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Fire in car park forces temporary evacuation of Sheraton Brussels Airport hotel - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 15:40:46 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNdTF3VW93V1VRanIwemVYV1VZazh4enZBSW1CWUVoMWZ6RHRLUUFSUlVybFNtUVZYOUc4RGF4NWhxTS1mb0tBckdPeUdMaGZaenBBekdNdmFCZDJYSlFkcGtidEJsemN4QUZQTER1ZlRsM0Z1YWlXSUw2OWdReU5aaG5jZlBSUThXaDhJdVhJOC1KcFdLNDV6bm9yUDVUNUNicEl2TUYwMElxN0ZyNEdrX1Y5YWlFV2gtOW9oeDdOeXlrRDNWZTh5YzE2Zk9aOU9BYVHSAdcBQVVfeXFMT3BGZDJ2Z1JaMGowYmk1cDg1b2xOLXBtYy14MkY0NmZIOExWQ3hMMVdUUGo5SGVTZHNTaENjd2Q3X0hCU3oycm5SN2RIZG9JdE8wdnFYZ09DV3pSR0piTFc5R18xdXFGU2FtV3JMZTRsc2t5Y2gtaURFU0JYUGlXTEN4TXc3TWFfTV9RRE9WWl9sVnhCdWdTOUMyNnhPVm9LUVZjeEZlbkgxcWpleFhuUFJtOE03RDVEZ1Q2dFZlSnMzbndUWlgtMDlpSVJKamllakFLZW54V1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46018.65331018518</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Antwerp Police Reports - West Bend News</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5PWVZydTBYUU55cFF5TGNLdlppaVFONXNpbENrVE0xMEM5bFJCc095NmNScllVQ0k4Ni1vYTRQdmZ5MkkxdjJudWVRXzdMZDdBQWhDRUw0YWgwQnhuMXVYUms5MnFMdlduRVhnc2E1QUpsZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46018.71180555555</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>US bans ex-EU commissioner, others over social media rules - The Business Standard</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 21:15:21 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbEdhcXdpYmd4cXREZ0V4M0hYNjRNeERQcnBrNGc5Uldmd2pYWjFtY1ZidkZkMktUYVJZSEZvUGhCdGtPc1V1OHFrclJaRGw2MktRSUNBTFdzaHRXX080SkQzeVBEczRlekR5aGJ6cUw4cTlSVEMtbWYtdXk0XzNGeV9qUXU0MWR4blRNQklJMEZBNERHN2ZtQVVRSdIBoAFBVV95cUxNNUo2cjl5MExFOHowVFU5RnVQM3EzcFd3eXZxU3FzZU03ckhjZ2gyeU9ROVI3c0ZoUURTZVM5Y1plbjVVVzZtQ1ZoVUk2Nll1VVlfVUJlX2kwVnc2WGtlTk9DVWtfLWpHQjdPc3BhcjRpMHowM1laMXpzVVdUU0FDN2k0enR4VEwxWDRvUnN4MzFLOVNnQ2dRY1lubG9JTW1Y?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46018.88565972223</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Wizz Air expands at London Luton with slots from TUI, 15th based aircraft and six new routes - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:06:40 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNZ25rWlAwMWpEcm4tbVpadkNLR1ZzV2JVanJnTWlWZG9LQzVsQ18taFlwVWIzbXNURGp1ejYyNVZzN1NXbHZyOTBRb3FSRldwTl9tWFRXY09ZS2daTnF5VENJa2lORWYtaGFrZE94MFgtRDFsejFUb3NnaF83MF9WbldCVUh1VXQ4UjFaQUxzUkZqWkp6SFZGOHNzdzhFeWtKRlRtRjlZWDNBRHdrZ2RRRmhsVmxmaWFZdW4xbUZtVmlNQk5YU2xpVnhYS21TaFlHcUZyMVVEc9IB1wFBVV95cUxNZ25rWlAwMWpEcm4tbVpadkNLR1ZzV2JVanJnTWlWZG9LQzVsQ18taFlwVWIzbXNURGp1ejYyNVZzN1NXbHZyOTBRb3FSRldwTl9tWFRXY09ZS2daTnF5VENJa2lORWYtaGFrZE94MFgtRDFsejFUb3NnaF83MF9WbldCVUh1VXQ4UjFaQUxzUkZqWkp6SFZGOHNzdzhFeWtKRlRtRjlZWDNBRHdrZ2RRRmhsVmxmaWFZdW4xbUZtVmlNQk5YU2xpVnhYS21TaFlHcUZyMVVEcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46018.71296296296</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mother accused of shooting son over disrespect during Christmas brunch - Shore News Network</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:40:40 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPaGZORTkxeXNpRldsXzZRRUp4MThxTDZsRjEzYmRWdUVVZFRJX2ptMWlFanJwWEtpcUJjWTFTdnJjZ2JQSmQ3RmdNeHNBNWRoeXZkUGFCdUI1SFJMVXBHcU1hZU5LWVdRMTBvQ0gwRWZncEVWZi1sTTh1VTZRZm5QZmRBVVpPMTlwNlFuZjQ3LWN5TnhubVFUOEl1WFlPTnFJQzl0eGFtQdIBrAFBVV95cUxOYndpT2VVd2NDQXlJOEJORWhGZTJuMjZhZ2w4eEt0RUFtQjkzTXNHMWw2RjNXNUNxUUZTaFpTb19wclNNYWQ3YmdwWTRTZjNtUkZmMEtVUU9PbFN4R05YWWJHV2dHQ2tkUXE5R1EwZHJ2bkQ2bmJ6STFrVHRIdzNsemFCQTBIT3l6VF94YjhHVVdYZTkxY1ZKUjJUYk5iTXA0aGhmY2l3b1B6MUJR?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46018.73657407407</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>A SWISS A220 and a small jet slide into snowbanks amid severe winds at Kittilä Airport, no injuries reported - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 16:56:34 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOcGZrUjNFT0NwdWVrYzdxNkFRUk01TF9GY29VYURNYjVPc3pWZ2M0V01mb09fMWVtZHRhU0sxd2hjUmE2M0gwMVJKUmJWa011REl3UWNBSk1QeXljbTV1WVVNMmFlcVFMc3VINWlVOURrTWh0ZDYzVkRQRW4yMGJJSzVlVElsNzV2blRxaGZDamVSUFF5OEhqY3BPb2ZOa1V2QzI0MmhQaVBCbF9IbXc4TEx6MXduTGY5NW5kQTV0NS1VV3BiRUZYWXBLYlJXdFVqT1NCeGxtYlFRd1JSSUJBb19SSUJuM2Y5RGlrc0JybzY3eGYwLURfQ3FXTdIB-wFBVV95cUxOcGZrUjNFT0NwdWVrYzdxNkFRUk01TF9GY29VYURNYjVPc3pWZ2M0V01mb09fMWVtZHRhU0sxd2hjUmE2M0gwMVJKUmJWa011REl3UWNBSk1QeXljbTV1WVVNMmFlcVFMc3VINWlVOURrTWh0ZDYzVkRQRW4yMGJJSzVlVElsNzV2blRxaGZDamVSUFF5OEhqY3BPb2ZOa1V2QzI0MmhQaVBCbF9IbXc4TEx6MXduTGY5NW5kQTV0NS1VV3BiRUZYWXBLYlJXdFVqT1NCeGxtYlFRd1JSSUJBb19SSUJuM2Y5RGlrc0JybzY3eGYwLURfQ3FXTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46018.70594907407</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Polish airports reopen after precautionary air defence alert triggered by Russian attacks on Ukraine - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 17:36:56 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNUVg0cjhiZlFKVjdEQ3lydk9oa0I5LTdULUR6TjZNUi0zb21JZldaVGx5SWdVbzkzRkVONVYzbGlyVlh5TkxoZ1dvdW83M1V0RjlwUG1iSEtCa3g2UHNXb2JqUnV4LUJVQ2YxSjZHSlRWazVYa1dISDhXMFZqdG5MQlZuSERaeWpRbHdRLWZOWld2X1ZwVVhmRjNyNVdwZFgzNnFERDRxMjctbU5FSlQ2NEI5eWFYUGgwRk4wdDFXdDl0Z2pRS1o4Z0Q0Zlp2R1B0eE8xc0djWlNxdXBkb241TmdCUkZzbDJBR0ZKN0hvTUNULTdKdjR6YtIB-AFBVV95cUxNUVg0cjhiZlFKVjdEQ3lydk9oa0I5LTdULUR6TjZNUi0zb21JZldaVGx5SWdVbzkzRkVONVYzbGlyVlh5TkxoZ1dvdW83M1V0RjlwUG1iSEtCa3g2UHNXb2JqUnV4LUJVQ2YxSjZHSlRWazVYa1dISDhXMFZqdG5MQlZuSERaeWpRbHdRLWZOWld2X1ZwVVhmRjNyNVdwZFgzNnFERDRxMjctbU5FSlQ2NEI5eWFYUGgwRk4wdDFXdDl0Z2pRS1o4Z0Q0Zlp2R1B0eE8xc0djWlNxdXBkb241TmdCUkZzbDJBR0ZKN0hvTUNULTdKdjR6Yg?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46018.73398148148</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tributes pour in for 'lovely, friendly and kind' mum-of-three who passed away on Christmas Eve - Belfast Live</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 15:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNbTk0UWlxVWJCUGtCTElFWkE0RFByUFd1OVJwZUl4LXpRTkJLTVN3dEZYbkZjbENQdUVSODdfbkx2RVV3VUJYYXBQYUFhWGZ5U2d3MlpEVXlUZWhsSkZ5LXZKSEc5Y2o2Wm9kTTkySGRJZE1Udlp4VEJQcHl0NmNyZGFHR3JxQUVXcGxUVVV5RVVpMkFaeWpoeTFXZ0xmODI20gGgAUFVX3lxTE1tOTRRaXFVYkJQa0JMSUVaQTREUHJQV3U5UnBlSXgtelFOQktNU3d0RlhuRmNsQ1B1RVI4N19uTHZFVXdVQlhhcFBhQWFYZnlTZ3cyWkRVeVRlaGxKRnktdkpIRzljajZab2RNOTJIZElkTVR2WnhUQlBweXQ2Y3JkYUdHcnFBRVdwbFRVVXlFVWkyQVp5amh5MVdnTGY4MjY?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46018.65555555555</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Recap: The Best Vintage-Inspired Watches of 2025 - Monochrome Watches</t>
+          <t>New Era and Polo Ralph Lauren Reveal a Triple Collaboration With MLB - hypebeast.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:30:09 GMT</t>
+          <t>Mon, 29 Dec 2025 06:16:42 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPS0ZhVW1Da1lWVXotTTBtYlRXYkRHay1yXzhXOGZDV2F1Q0pBQXlXaEtFNzNTNm9iSWpuOEVEeTV0YU9MMGhwOTVfN2RWTEhkSlY4RXNNSU1KMFZXWGluRk5zMmc4RExHWUEweEVuRGtzUktOYWNjbmlIRms2Q05QRE9Da3VSRlNiR0s3UDVwYUNQOHVCMS1MNHNnV05QN0pILTk3b0tUM1FVdlJQUDlEMFNNeU53R3dsclVteQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNWDVrZTNJV1MtX3BhRVltQV84UjBmUDVFLXh1QjVfRVRtallndVZmY08yWDdFWXpWTHhUWS1pRGNxSjZ2Z3lTY2ROQWxVNThmYV9GT0VTU2pWQkVjeGJta3RNa3E1dFNyeWZBRURYZ2N1LTh0T0pfc0l0SEExOE1HWjFGS0s4VkZ0ZVduVGJWa2NYQVRUMV9lLVFhTzdRdllFUndLZThxOFltcGs?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46019.43760416667</v>
+        <v>46020.26159722222</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Calvin Klein men's boxer 3-pack slashed to £26 in Amazon Boxing Day sale - Wales Online</t>
+          <t>'Comfortable' Calvin Klein boxers that 'look good' now £26 for three in Amazon sale - Birmingham Live</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:14:00 GMT</t>
+          <t>Sun, 28 Dec 2025 17:41:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxONlBtZ0hGN2xhRjdYRS1DbEZGbW8xZ1VZTDVBNDB2dUk1Z3IwQkNBZEFuLVd6eU1zVmpGb3VUZ1FTZVRiODEzc0Joc1U0QW1Udk5Bdm9RbmVxU2h0TnZPSm9uSE94VlFzWEpmVTh3bDBac0IwUTZsTXBCNVUzQ1VGeEpTREJBNGRKakHSAY8BQVVfeXFMTVd5MlFoN0ZlQ2VuaXRTN09UNnBYS1NVWUR6Z1doS2lkVlJ5X194SFBLX3NrbWViVnBMNDF2bDNQY1UyM1JsZWhmWnhJemdoXy1mQXRlaTk1Mk1YTXBDZ0ZDSjdQOEx6R3BvSmlidDlCc01rQ2czdmd1TTlIeUI2ZWJpTEhTQ216cjZrSnMtTG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQblF2Q2ZobzZrR3ZmWkdZSVZvWWMzZ1BCdURwRmR5MVk3Z1IweWVxV3Q3aGo2dFE3SmRoYkZZcldGZkhIeEFidWNWdGVWMkRVaWo3ZlJkOHBTSzVyZnZrWlNyQmVYNnE5UC14NWNONGxYSnJ4NVZEckd2V2FuM2N4N2E0ZTIyb29Qd2lPUnBEQmE0UWcyM0xSQWdmai3SAaIBQVVfeXFMTzlucUV5SEl3dWpBRHV4N2tDNC1KNVQ2QUxHNEVRODl3emZTV25IbkNGUUlSQy11dmlLaGp6c2U3ZHRsVXlkLThleFF4TDFQc3B1WjRPaUVZZGRpcGViSUNWLXFfb00wOVl1WHF5OG83Sk9wVFdTVjhEYWVweUoyX3pQUnNWOE1mMHhiaE9hdF9CQkR0S2h2WlF6Zm1kLUZhVFdB?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46019.42638888889</v>
+        <v>46019.73680555556</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Short Interest in Burberry Group PLC (OTCMKTS:BURBY) Drops By 41.1% - MarketBeat</t>
+          <t>Valentino Rossi's next move for Pedro Acosta could arrive at 'any moment' amid VR46 revelation - motogpnews.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 12:33:29 GMT</t>
+          <t>Sun, 28 Dec 2025 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOanVfRGlhWURvcmM2RmdHa3lXazE5UEthbkJvVzNTZ2o1YlpqT1BJVnB1dnFqN0UtLTB1STh3eXBzVFA2elozRE8zTWpzc3R2NFRPT3NJWGhRbXNXdWZaNF9RamFhbEpRbW5JZldVY1RIaTNCc1RrY3JTbW1aTFgwdDlhblRTOXlHRGNfaGpYSHJwLUpxa3g0UUFCcHQyLVhLbHJGRGx4TzhPaEFwQkFjeDAwdVk0M1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOd05tTUNhQWl2Q1VQSkNjOTRhckI3T0JveVM3SUJCUVhWbGZaX2ZtY3dKS0JZZ0JoQnhsUkMxMkdLY09GUlIyX3RDaktoYjZzWGhOeVl1VFA2TUlMaHREOVo1emMyX0dBc24tNFF3UzBkZzZyUWg1NzAwOEhzd0VpaW96WUJIRmxQX0stQy1TMGN1VEN3YlJiN0tvUV9KRDdzYm9zd0g2U2o4VlVvckpRd05xZ3l6elhBZWdPWjIwMmpldGt6WmpjcV9B?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46019.52325231482</v>
+        <v>46019.625</v>
       </c>
     </row>
     <row r="5">
@@ -581,156 +581,156 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5 Luxury Brands Making A Comeback In 2026 - BusinessToday Malaysia</t>
+          <t>The Best Royal Jewels of 2025: #6 (A Royal Tiara Takeover in London’s Galleries) - The Court Jeweller</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:18:36 GMT</t>
+          <t>Mon, 29 Dec 2025 06:00:50 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOZC0wRm5tOTlLaUxlclZiR19aMmtELU05M1JxMUh5MTdpWFZ3QlZzR3ZUTm5uX0owYVJnbk5JTHJKREhLYjd5ZmZRYjZxa0pPT1FHTExDT2o4THUtY3lyTzlySlNka2N6RmZIYXpxWEs3T0FtMC1sLW9mVmVlVW5tU0lKbmdFTkZZTEtDbEg4VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNc1lOdzhRcjBQODhBWWxqQ2VlUnllbGl0RXB4bTVZQ1BnbHNPVFJBeHRCY1Y1WkdSZEVIMG1tMnFKeUNHOUlGRzE4QjF3ZlUyNXJYWmo3R2g5cUZnNVJ2VzNub2U5RFAwNHd4Sml3cTM2aTRNbHQzRTI5ZDVqSUZISzd4am83RmZycFBwMmlqLXBmbEI0M0N1b1dySjlWdGZ2dkNJbXdROVNkeXZBbEJGajVIV1pvSS1PR3o4Y0pn?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46019.38791666667</v>
+        <v>46020.2505787037</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GiFi exits Switzerland; Maxi Bazar to close 18 stores — December 28 - Meyka</t>
+          <t>I thought he said 'I love you' - then came the brutal clarification - Metro.co.uk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 13:06:01 GMT</t>
+          <t>Sun, 28 Dec 2025 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNU0JzRGpucjluU0hXd0hGVGZrZGtYTnRJdjUxbUxwSVAzcVFLeWo5anM4WVY5R2NyMnlsblBpODgyMGxBdzhKSU1tRWo4OG9QZXdiSFpWRGRzMkpwU0VubWZHTlBtSmdFVUhKbUVZNWg2YmNYNC1oQmtlWjEzVUZBOC1iNFFqNlZGbXdtdGpaTlQ4NEF6Z3Y0OQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNSkpnVzJ5Q2xmWDRjNU5NWklyamZNcVZCOGhTNHRvZ3F2TkZTeS1SLWRtcUp3OVNBbGt4WWZjQl9wYjZxeFhVSlJCaU80UEpoako3NVNYNjljNnFmU1RLbWZWUDFWZlVlVUxkUnIxU1hudjZxM1BReWU1T19kWHVJY1pHSkFkeEJLRl9Nd3Jyb3d2MUxt0gGaAUFVX3lxTE9LX0xFREhTWmNzN3FTU1FqQmFkdERVYnlJT0lCeElER3hWNnFTVXNRbnRfS1FxMURCWklfN01ZYW5XMmJpZ1ZjaUR4RXQ3ZEctQ1VMZmsybzRoMlIxSGZpNHNZQzI5clpqdzFMQkMxeF8zNnVuUzRsaDV3aGhDU2QwMXVkcndXTjRPaXVBbG9LMUtfemVMRE9sZ1E?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46019.54584490741</v>
+        <v>46019.625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>London Marylebone</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("marylebone station" OR "london Marylebone") AND ("incident" OR "delay" OR "closed" OR "delays" OR "protest" OR "boycott" OR "bomb" OR "Bomb threat" OR "shooting" OR "explosion" OR "stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oxford to London train service cancelled due to passenger incident - This Is Oxfordshire</t>
+          <t>Why Fans Think Timothée Chalamet Gifted Kylie Jenner $60,000 Worth of Cartier Jewelry for Christmas - Marie Claire</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 13:50:55 GMT</t>
+          <t>Sun, 28 Dec 2025 19:44:41 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQLVdJMVpJaUJwRzcyTV8xUFRFaElDMzJTbDdyenpPWWJYYWtvXzdlYzduWjRNU2V2d0p0ZHl5UUhDRk9XSG15WDF5TjVMQUpNWWVsazhOM0YtZ1VrcHBTdUtGMnBtRVlHWGQyR3lmTURmZ2NLUXFuY3BORXYzQmlhbmhzUHRnSG1iTkdnemVoTWZsMXJkLUlXM1lKRnNxaThsT3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSW1YY0VtVzNEZzNrQW5GWXAzc3ZldVZ1OGNOdmZJa0NUcWZpZWVYRC1VT0hEM21NQ2xLdlNpSkdmSVduT2pMTFI3QU93YXQ0TldSNG5KNGpjX3kxZENhTmlwQmFpeS01VERERXR0b2ROUENCOGF4WTJpMUpGX0Vfd3BOSVN4eUl6MnB2a1VTM0ZtWHBwR0tRcDcwWWVhRUlwdS0xVA?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46019.57702546296</v>
+        <v>46019.82269675926</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amazon Announces Major Change to Delivery Schedule - AOL.com</t>
+          <t>Cost of the Holidays: Is it easier for Londoners? - Digital Journal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:00:28 GMT</t>
+          <t>Sun, 28 Dec 2025 22:08:23 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNU0lnRWU5UkhwRzRDSktDamhpcFhGazVrdEhUbVhwMFdKMGFKS1ZYU3U1VENmLWVqU0xsM194TFNwV3psdFl5X1FqRURqQ0RBYm9qUlRYamlrcEp2eGNvS21sSDhnRDJtaVRoenBobUxuZjFYNlJEMjFiUUdtaG9aZEpJTXVEQThnOEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQYTRLWG1wSFREc2tsOVJrYV9xM2ZlZFZ1LUhhd3ZZYlBQZVh1aC1PdGhCOU5TZmI2bEZVZzJZa0tDM0JxOG9wNGtkNUxTNEJMRU9rWXE4N1dmQXIza0J4NGZZVGtfeEM0Wi1PaldKeUwtbEdqaDNEdFN1OWhaSjBOY2lnbF9SbHN1R1ctZ1RMRjRwbkFH?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46019.37532407408</v>
+        <v>46019.92248842592</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amazon halts plans for drone delivery in Italy - Yahoo Finance</t>
+          <t>Louis Vuitton enters beauty scene, selling out $95 lipstick - Rolling Out</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:30:12 GMT</t>
+          <t>Sun, 28 Dec 2025 17:45:27 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNeTdJcFdiZ1QxSEVKbENrbGt0bEJ2TGV0UU04b3ZlRFhuMWY0OG40dFJlWldic0Y3N1VCTllrQkFyWkhMWG5YQnE3NUJGN3hkSzk0c05VRVVCa21aWVFPR3VFbWxpV3JzTkllX2lXdzRKMmpPUW82MlhRVURlSUtTcE5VeUhkdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFB4WGxfWkZQN05UeU5ZRUkzSW9MMkx2Zmc0a2tOd1hXYW8tM1VBcWlfMGlfWERvSDJpeDZweVNLNzRrSlprelhqNTFOdDVFa2hFcmZDYUJtZGVUcHFENm50bUhYeDlwQkZzMjNWRkVEUHBJME9jT2N5Vg?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46019.43763888889</v>
+        <v>46019.73989583334</v>
       </c>
     </row>
     <row r="10">
@@ -746,24 +746,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Evri delivery jobs: Parcel firm to recruit 2,500 UK workers amid expansion and BBC Panorama scrutiny - MSN</t>
+          <t>Here's how to quickly tell if your Amazon order will arrive by Christmas - AOL.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:30:03 GMT</t>
+          <t>Mon, 29 Dec 2025 06:04:06 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxNV3JaZVlNeGhLVUp6RnFCV0QwSVBUV1JFUjdGUXZIZVJSNzV4R1A3azh2SE9ES1FkOWgtQnhFb21zUGpnQW9NTENZTmtfZ05wT0c4TlFNakdCZ3VZNG1CUVdvUFlkNzh3Mjl5Ykd3aFpNcW9BMkVCbFBqY2FIVXRyNjMwcEFXYVJVcmNnQVY5bnJ0Y21RdXg5b3FDcm5UY2wyb2M2SkpTeXNoWXcxSV9tOFAxUF9lQ1JzUG9xLTZPSzJKaFZkdTdPSmhxU2Fqc0k1LWVMOThnamxfY2MwYXpCaXlnc3FIblFzS250ZGdRYS1DWExuM2M4ZHdmNG9fSUhTbnkxb1BHbzRoTnIwdW8tZkx0SmxMUFNxU3FmZzFFNllYbExkUzktYzFmSXl0ekZzaHk5NHBhME5SZHM2TTc5T1NaNkp1cV84NUhYbnFaai1xdWNBSlNpSmkyd1BwbV93YjFkRzFoRmFPRG9jRS1GeWJqSG1tZGdW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOVFZNYXZDbmZpaWljejRYMGJ0MFBhck51SmNKWTVqSDE1X2RLSmtOazN1cVg4YTJ1VkppdFQ5TFp1ckl4TERTbTRaOFlOLW5TMk04YTBSSWZ6YS14X3dVUVdNQ3RCVmZmTG91ampocW84NzdtcUdQbDh4XzBMSDZXVVo1QTRuelFMeGNOajBQNlotWDE3ZWwwUWxxN2RoUy1SWk1Qc0V5dGVuVFdlT2UyajZ6Zklaa0VQbmpLTU1vYXRpNGRpWGpmR3h5cw?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46019.43753472222</v>
+        <v>46020.25284722223</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kentucky scrapyard worker injured in UPS plane crash dies on Christmas, raising deaths to 15 - Daily Mail</t>
+          <t>Amazon halts plans for drone delivery in Italy - Trending Now Infrastructure</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 08:35:36 GMT</t>
+          <t>Sun, 28 Dec 2025 14:55:44 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPZTRnLV9ILUlsYnUzWEN6ZE1YS2xVSkZUTXF2RXQ0akwzZlZEZVNNUTM2Y2lTal9OR0tWZmRsbzdsVmFMVW9FSXFUQzBVbTJWMDg0RVhQRXNTTXAxVHlZaHBiUGt4NFh5V2J1VjJ0alcyUGdtWGhpR0FCQ3k1QjdCYk5GYUNxM0tvTzh3aURvXy1CUGtQX2NudmlDS0xRRi1r0gGmAUFVX3lxTE9iRkhXUDVhVml3QXhHQUpxbkd4WFlXeWhRWEVLbGw3MlQ1cW9Xd1VjUFo1SDl1bFhVbDAwdkFCbk4ydXkzNGVYZ3ZVNkI2Vm9qbXZ1RGVuekdwNmdLcS12VXQwTmNQRFVDVEFRSlprRU1Rd2Q2eTdTYlQ0d2Z2cURxNEhfTXVkVlVrbWJwOUM3UG10NVhCMVN6VWVVZWQ1cHF4aDZQOVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxOQ09RYWhSUjJXYmRGZkp1aXEtbnk5OWhaY0pNdXZzY1hwSjJGYzlNbTAwVXl2V1ZudjM2OVdOamJRMzMxeXdzRkFqRWJrbW16X0wtakVTc0ZXUXpPSDF0RDdEYXpCeFQ0UWZ5bktOZG5qUmo1V0x2U0N1bEVkeGg3LWdnX1B6OGhJZHA1VzN4bFZLdXJMUmltQk9NeHlrUHN0eXpPdTF2N0dfbWFCaEtqTFFIUzhvVlpVR1BqSzF4TjNSeEtVWm9ZTGtqX2VQaXNtdUthZjh6cnNobk5tU01fWjRCcDcwZ1RqeWhKeVJYNU9oUlREbnlZNUMtV0tISUx6a1ZrNnhJSC1CRHdxX1F3a3NPWjRrZGFHM0RDS2JB?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46019.35805555555</v>
+        <v>46019.62203703704</v>
       </c>
     </row>
     <row r="12">
@@ -812,24 +812,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Why Delivery Deadlines Create Dangerous Driving Conditions - Container News</t>
+          <t>‘My Package in There?:’ Amazon Driver Says This ‘Might’ Be His Last Day. People Can’t Believe He Still Has a Job - Motor1.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 12:01:11 GMT</t>
+          <t>Sun, 28 Dec 2025 19:03:26 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQazRZYmhCSko2LTdYSzBhWS1RdVAtUEw4WkdsUzJGd2RwRWhZalR5UkpVcVRSYzVtOXFaTjhESEZ2RjZhWkhCaXZSWDVqU0FQeVdhZ0lNUGwwZ3dhVkF0UDc3ZWFnbHo5bDBtLVhqS1RhTFVBYVpfSFFYLWxXVzhBM0FaMy1Qb2pHakEtQTBMZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB3Sk5yU1VvelVaa3RfSlZ1SGFkS1k2UWNGS2NJQ0tGNV92QVFMMEVub1FZMU9uUFMzZjRPU0dIU29nZ1JwRVFSNkRhYkNQdGFIMzN6U1BfYWpiWTg5OXVUVjYydkc2Z3BMWGFiaUhn?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46019.50082175926</v>
+        <v>46019.79405092593</v>
       </c>
     </row>
     <row r="13">
@@ -845,24 +845,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USPS Expands Last-Mile Delivery Services Amid Financial Struggles - Букви</t>
+          <t>Amazon says they’ve fired driver after video of her peeing and pooping outside of homes goes viral - AOL.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:25:52 GMT</t>
+          <t>Sun, 28 Dec 2025 21:39:12 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOblRQRFNxbVZyY1ZaN2FtMlRDMnlrVTNRWE1SM19LREprQzBGZTRvRjNMQThBcG5kQTVFRWsxOXNNRThpdURkVXgwUi1veWR1MmUzR1R0VjRjLTAycVlzN3htaWRoSWRyZ3ZOQVZHODNOTVJjV05qUlhBcm82ZHJEeEFWT0E5VW9HT2dqXzFFTkdzXzRKZDJOZzdVaHZQLWPSAZ8BQVVfeXFMTm5UUERTcW1WcmNWWjdhbTJUQzJ5a1UzUVhNUjNfS0RKa0MwRmU0b0YzTEE4QXBuZEE1RUVrMTlzTUU4aXVEZFV4MFItb3lkdTJlM0dUdFY0Yy0wMnFZczd4bWlkaElkcmd2TkFWRzgzTk1SY1dOalJYQXJvNmRyRHhBVk9BOVVvR09nal8xRU5Hc180SmQyTmc3VWh2UC1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE85ZE8wNnhQWWJESTVRWWMxcGhBeW93bzlab3A0SEpGbUk5b2RyODRndC1LRmxIVFZRSG5NYWtoYVFoblk5SVpPdmFnMHJudVBCdzJZeUNrVk9nR0dWQmtFVW9SaTdoams0Xzg0SkpRMA?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46019.43462962963</v>
+        <v>46019.90222222222</v>
       </c>
     </row>
     <row r="14">
@@ -878,57 +878,57 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Solar, trucks, Triangle research, Amazon delivery: NC’s 5 biggest layoffs of 2025 - Raleigh News &amp; Observer</t>
+          <t>Amazon Prime Adds Free Same-Day Grocery Delivery. Here's How it Works - AOL.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:00:00 GMT</t>
+          <t>Sun, 28 Dec 2025 15:17:04 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBIazRQMmlsdmttbHBmWmVDY05DeG1rY1JqU182YVZCS0N5TjhSeUwyMGR5VU5laUpzbDUtOUFCdW9kVnVyOWgyR3l5OEJVaDdyNGZMU0xZdHdHa2NJcUVfWGN2ZV91NjBPbVJYcnRkXzlld9IBckFVX3lxTE43WGwyXzd3V3ctV1ppSVVxWG0xSnRtaFlldzRTRC1VR3pZd183RUU5blN2MGF0VEV4enZ2RjlwejhGQlZ1eDVob0NUOUVlMWFqekFBcXNMWGVtV0xXUXdKNFRFTUFtNE45aWJrZnZJd3dudw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5Nc0ZIQURuNHZ1WGhHX281Uy1JTkZFbmFIZWp0YnF0Tm1lLVhRSU1XOVdxWHFDNlFXTmxUV0dVd1FmOU52SFVSSUgwMnNqWmlCUWltZkI3UDR6aEdnZEZLOEVtd2l5cE5RNWZhZUtwcw?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46019.41666666666</v>
+        <v>46019.63685185185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No deliveries on December 31st? Gig workers of Amazon, Zepto, Blinkit, and Swiggy are on strike - Times Bull</t>
+          <t>'Do us a favour and resign' - Tottenham boss Thomas Frank told to resign by former player in explosive social media rant - Goal.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 11:53:43 GMT</t>
+          <t>Sun, 28 Dec 2025 22:40:24 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOdExaWU1IZVpjQjBaS0VJX05xTW5DeFVJUXhyZ2xZYkp2YmtKRF9YU1RQQjdSVlNwY1F4em1Oel9hQkpXenFkV09Xd1k2aG1qNnQtQVZIVUhFUGxfV2UxWmwzeUtGSjNBYmpPZ3NtcGY3SzBEOWRnUG9RUThwYnVVc0ZNVWgtMDZJWGNhelJtVFBwVjVmMG9LV0ZYTFZYMXg5UEZhNTF3MmRZQ04tT1ZYX0VSc19mN1FUUWdHTmZnX2ZYdGgyd0tJS3cyQ29zRy1KRWNKMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNRXU0WDJ5NEJfOFdmaEdnTXRGcjltMHdtOG9sTFBiVXdVU284eEVVMGFxZEYzVjcwRG8xLUNOSDZsVTNsSUFWREpiX3kxMXM1UlZYeVVrU29XalRXVUc3dU5TVVFXMnFFTmxEYXZuWHlfVHZOSUNRLURBTFZBVGJOeUVSNThjUm5LV01HdUFuUzdlVF9ubVhjUFQ3YkZQc0VlOHBJai1mRTlNRzRhS0trOHN6dmFOUExWUGx2VzJuR0FUY2hCZFFJWkthWmczQm45dnZFZUlacE9MSFd3eHpybW5qVGN3NzJvRzRzaDBGcEc?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46019.49563657407</v>
+        <v>46019.94472222222</v>
       </c>
     </row>
     <row r="16">
@@ -944,24 +944,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1,000-pound U.S.-made WWII bomb found in Belgrade construction site - CBS News</t>
+          <t>Federal (505744) Hits 52 Week High - Earnings Beat Highlights &amp; Low Entry Investment Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 13:56:42 GMT</t>
+          <t>Mon, 29 Dec 2025 06:42:48 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE41OFFjU205bWNBaFlYTUVjRGd0eHpEM3AyTXZOcHl0TUlUaUJDbGxIWGZQSDJOSVkwTFdDdDgtbkM3YW9PUWlaNTFaazU2LTVENW9ocnJaU3dReVBqbExlaGNFMjFjcGdsc29GajJjSlBEM0Q2YnJB0gF8QVVfeXFMTjc4OWJFMzVYZjdJV2pCdlJZQTBaMWJrWTE0a1JyZWh0OVJVU1ZqNnN4U0VKWjRyTktWOTlYYUVLamFzX3RFN3hrekh2X0hDQklVM0w0NEVTT0VranQyQzBEaHFwNEN3RXBvUDZxU2plUFFnbURVX3VrSDUteg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBESnhNWUp5bDh2S29uT25YUTRsQlNXYVVQUnRWQjVyTGZRakJQRm1EZGpDVW9aOUwzVGVMNXNDNF9GdTU2UlItTGxIVWstZmVjQzZlRmphTEcxeUVzN3FhNFN2VU96ak9pNXVmZDNXLTVISXlBMkFVMw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46019.58104166666</v>
+        <v>46020.27972222222</v>
       </c>
     </row>
     <row r="17">
@@ -977,24 +977,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bayern Munich legend highlights strengths of Lennart Karl - Bayern Strikes</t>
+          <t>Row deepens over vanished river wave in Munich - thepress.net</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:30:00 GMT</t>
+          <t>Sun, 28 Dec 2025 16:14:10 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNb0hYY3pKd3NKRks1eWZURFVhLUNNWF9jcjZicTNvTGo4N3VwSzNFS3FUaHpvVXlqTnhiakQ0cllEQWVjaDc0eThJbUZrajc3djN1MVc1SjI0dE91UmduSWQtQkNYS3FrVnp4WmNidHZwd3pXUm8zd1g3YUd6OGE0Xy1QTURHMWN2WTlr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNQzZZZ3FmVnB0Mzd6RHlnak1Td2FiTFdFQVBHaERXYWQ0YWVueXhVOEFtV0hNLUhKbkQ4cjgzTE1iM2NjQkhLUG9lOVoxdWNiY2tQa0xQdUhsWTRyd3U4czZuLUZPVGh0RS1hdlRJQWI2N3Z1dlRIdDdWdEVjekR1WDZjSVpheVdxSDAzN3BYeU1PT0EwR0pEWGdDX19JTzI1OVc3LVE5WmJvMGVJZUppYTVheldTNzllSE9VYjVodnBIUkpDNEFvVWJSM1BONkc1?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46019.39583333334</v>
+        <v>46019.67650462963</v>
       </c>
     </row>
     <row r="18">
@@ -1010,651 +1010,2796 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Debate over surfing in German park gets gnarly after city removes wave-creating device - breitbart.com</t>
+          <t>The Eisbach wave in Munich was a popular tourist attraction before it was removed in October - IslanderNews.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 12:56:36 GMT</t>
+          <t>Sun, 28 Dec 2025 19:03:08 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQT3lnS2c5SDRnWS1xUnd1aXlUZ2xQUVYzS1BJUzYzUHo5MmEwYUNIUk9zOGUtVzZlU2NWSjBHbnRBeFI5Q0lObGlCem4tRnEwYnVJaW9aaGRRTVp4MFphSkk2YXBCS29QZWtuX1V4ck12SVJKYmVmeVI5bTBQOHpfNmF5WTFzaU1hX1FHc0YzaFRaMGtOUThlOHZpckNOWlB4SEl0SFFZeHBSZDA5VXZyNThwY1ZjNUtIbGfSAb8BQVVfeXFMUEczY1g2aFRaQ0FUaEZXWDBkZEdIM0tQRzZXbE43UkZnc2JpemppNHhfZFVXRUhscUdkb1pSRTBSSzByZFRFTHcxOHM3a1h3SWthTTNYOXRUVHl2SnFRbXpweUZtMGdVMzBmMVlTaklYd1FtRGZCMjVIbVVNcFBhekdxTlV1QW5KcUtFZWhtTVR4aDRKbDhRRFo5OTZ0ZkJ5MzFtUUlkdERBd2ktYlBFaHRDTjRHRWJjeUZqSll2UEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNdVBmZFBpN2Y1blBiRlQ5TGNOMEJZUUZPbWJ2b1JIUUhEUG1fOGhmQURlVTh6WjNGbGJDdU9jOTNyQXlVSnZVS19GWkhnMElBVXUyanh4b1k1MzcwTG5MSGxrdmFjUmIxeTZ0cTN4RWlRQVNiVmJCelFFekxmXzRxVG56VmcySFdqcFJhblhrck9zLU1mSjRBZFM5cDU0WEx5NWhvazMtNW9uQVNTNmhGM2NoUm1KcHNRR0hRbkxUcmZTV2YwX3AxM1lZclBkcWdWbWd2TTZPV2d2b0Nqa1lGbUhyTlhSOTNvN0ZVbGFDblhuNU9OelFkUkpBbkFPUVU1dkp5LVB3?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46019.53930555555</v>
+        <v>46019.79384259259</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russian submarine followed spy ship into British waters as it mapped gas pipeline - inkl</t>
+          <t>Traders Consider Averaging Down in Switching Technologies Gunther Limited - Price Action Analysis &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 11:08:33 GMT</t>
+          <t>Mon, 29 Dec 2025 05:28:39 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOVW9ZOXZiZ2YzLXFiNTl2VGVWYzdRQ3RSWnNMU0F1WlhSNTJMSDhvUjhkMVpMUWl5WDJXWHZQT2x6RlJSbzZvTlpYYTJIVmtfMFZseGFuR0RuLUd5d3I5bS05bk5oVTEwRm8xeVdrY05qU0NsRXdDQWliUURYU3MxNHlRMlJpX0VjUFZRSHNWamNycXhMYm0tbnhYS0owYWFkdGZiN082M1haTkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQYzNrUVplMVdEQ1FtOHgydms4TnNqX2xIUVE0M0wwRFRNcnJFTkJlY1ItVE1jRU5leTdBYW11YVN2eEdidS1oMmdhR1JwU2ZCRWlieW9pSm1FaUJvX1EweC1MdXBGNXpON1Z1bzZiYmFwclU3QVVMSXg3UGN1NnZoYlltRE5ES0JRS25wSFZLbWwzd3ZoVGhyWU9iRFFqcjF3dGMyNjZseFdkdmdx?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46019.46427083333</v>
+        <v>46020.22822916666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>City MP: “Funding boost for police will help to keep Portsmouth’s streets safe” - portsmouth.co.uk</t>
+          <t>Heatmap Data Shows High Activity in Radico Khaitan Limited Sector - Price-to-Book Ratio Updates &amp; Double Digit Portfolio Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:18:18 GMT</t>
+          <t>Mon, 29 Dec 2025 02:45:10 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxORlhJemFIZnpvbXliUTg1bzFkaDVPaDZYRkVMaVNhR1VVU2wtLTd1ZWxNdGJQV2MzZThiYUVGbEFsV1BkMUs5RzczMktWV3kteHFhNDJtcFNHWEJkM0xfXzNYRFBkU2ZMX1A1YndQby1pUWRKaFZwMFpya25DY082VTZVNUppQkpxMm5XUTdiNkw0MWZHOXJvajJoekhIeF9ydlFPUVZ0R1NIajAxQXdscTVuaXkwOFJySFBvZlM0am5JUWdI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNNXJycmlrV0lUeXpGeG5QZmgyVXF5ZUJEa3pyNzlFWEZuMThoQXZzM1hhX3BuaWc0R1pVOThCSF9oQWdYN1l4YU8wUnZaMmFkejRBTEFHNDNLdVp1MFduNFJ5Wmw0cG5JT1lKODRzTHNJZXlEbDFlYm1ueVdnNEJ1NzdyUkRsZEw1THRvT2hvcmtEZ05YLXV4b0FZbjFUYTFtZ2hnb1k3SnhLUUpr?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46019.38770833334</v>
+        <v>46020.11469907407</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>and if this section breaks through right away an upward trend can be connected. - Weekly Market Snapshot &amp; Best Stocks For Explosive Growth - bollywoodhelpline.com</t>
+          <t>Published on: 2025-12-28 21:57:42 - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 08:56:43 GMT</t>
+          <t>Sun, 28 Dec 2025 17:57:13 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNYUItaWZqWnJ3eXJCWGxveUdVM3E3N0NBcmRtMWtfcnZiQTZweDlCR3p2al9zZXUzVldranNqZ0VpM2tEVTZvb1lqTTNXYWlQOGJ3eVQ5azBZWHdHM1ZpX3ZYUi1oTENuMzRDX25GU1MzXzJBMEtUOHVYVlFweEg5b1lUMWtuNWxRaFpLODNsWWFLNk4wV0lOZUNCZGJCQmNZeXIzLTdURG96VlZzZ0ZxMWstWkpXVmlnWl9ackpncw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOS3JjdG03eDRuRkhwRTBfMFlHS1RFZXVPRmlUelFNVl9SY0N1Tzd1cTA0cVluLWRaXzNRb3lLMGdfRE5JLW9xQ3R1SS14SDZqTk40dkFhWHBZZUxtUWVJcTZYMFNRVjlNYTFjbE43Sk1nVnNKYW9xTGxsblJfaG5LYmcwTUFaYnJvU2hrc2hrQ3lRLXd3RjZuY00zcWUtSUIxWjRtNUJR?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46019.37271990741</v>
+        <v>46019.74806712963</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Peta Village Search</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("peta") AND ("Ingolstadt" OR "Kildare" OR "vallee" OR "bicester" OR "Wertheim" OR "Rosas" OR "Roca" OR "Fidenza" OR "Maasmechelen")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kiri Industries Limited Attempts Reversal From Key Support - Earnings Volatility Patterns &amp; Superior Wealth Growth - bollywoodhelpline.com</t>
+          <t>Brigitte Bardot remembered as ‘angel for animals’ by Peta founder - Bicester Advertiser</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 08:32:00 GMT</t>
+          <t>Sun, 28 Dec 2025 16:17:50 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNY21hdzJ3U1pYU1VwQ04wWTZ3eUt6ZDA0SFNXTDByYlFVeVN4dFhHYmVNT0JhU3VZTXBGOEY0Yi1sbl9TczVMZW1Zd0pOcVZxY2dHVC1abWtLOW03SnhGUE9WSzRMNG5ibEdOXy1JSUZLVE5PU1hIVEVaZml3RzhrMFBwdEVTb2JCUXhMVnFnSWNwcjhVVUtfWUNWWDJUalptbHNwR1NBWl8tYzN0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPRzRpWHR5aENLZXVodDVkNnZDcmpLM3l3TnZCNGlEVTF5b0UtZ1hqMjZ1SkRFV1NfU3ZKUHZLTWhZclpMSlhMRVNkX2JkZ2l0WFljNk55Vmp2ZFFuY2pyUlh4WUJHQVMzRDNDVzlCZWRrMXhENmE0azhFSk5BYjByMU9rMkJfWVZSRVVzZm5QZ3JRUEFyUDc4WGloTlBDX2hvUlYyNmlLWXNXT240ZVE4R2pR?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46019.35555555556</v>
+        <v>46019.67905092592</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bomb threat to British Airways London–Hyderabad flight; aircraft lands safely - MSN</t>
+          <t>Scandal-hit Wessex Water ex-boss was paid £170,000 bonus despite ban - GB News</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 08:34:54 GMT</t>
+          <t>Sun, 28 Dec 2025 15:02:48 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gJBVV95cUxQZEUtRmRJd3FuX1c1VGVoelpVVGU4eWpqdXJyZXNzMDgzbXZ3M1pDaVJSb0JqUXVMdUp2allIbVVqTXZpVjRmZF9id0FvOEhvQmVyS0ZlR0h1dksybFlPM2hhaFVQSE9LWW9jelVmNVdqUUxWVmRMNTVkcmFxTlBldnRYLUZXd1lYZllRM051Qk01dXBVTEo5QWpwQjFXZHNmZzFzUlZTS0F1WnNCUTdELU40enpVS2dUQTczQjB2em50dkJUa0Z4RzZsa2l3bVZzTG85MTZZaGxtNTRuMm5PMTlYam1QMzI2U2QyTld1cE5PVTNzVzBaY1l1a1BvS0tXeE5jSUczZlJGU2phYld3NHIyc0JCR2lLSEhFajg5MlZjN0M5Ni1pVTVSTnVzNVNHZE5VVUZDLTdZUEZTMGxWWWVqMEZBWFY3Y1dzRF9pcG1sNjlhV3o3UGpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQQng5RmU5czZodnpjNUotcXhPRmV0YU1WUTRvSzhKdEh3Y2RhaTRNR0VmVnZYSW9meWNRMDdmbEtXckJTT2lVQVQ5eTZCeXYxd3ZYUHVmcUVYOG43ZlpIMW1vZk5VNkxZMGJ1ejFPZU93YzV3RWIzbjlIbnBmbExLU1oyOHVpdw?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46019.35756944444</v>
+        <v>46019.62694444445</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Man stabbed while sat in his car in North London Boxing Day attack - My London</t>
+          <t>The Special Terrorism Policing Powers Triggered by the Bondi Beach Massacre Explained - Sydney Criminal Lawyers</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:15:55 GMT</t>
+          <t>Mon, 29 Dec 2025 06:18:27 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNUFlGUFJ0bFhDMjdubXQ5VTFVdVdneHRQOFlvUm9nbTlUUDVYaC12RTdjNVhUZ05Pdk96Q25vRUtjTjZwZ3lQTHpxVzE1bUZsMUlpNnNlRVFHU2tpSDB6bmdxdm9ubnZpQXRVUE5CQ2g3STRDZ01ZVmNwUG1kdU1KUUprcEQxYWJkdllR0gGQAUFVX3lxTE16MjI4TUtrWUJ2T1RxSVFZSXE4SzRNLVctX0xjRFN0YjhKSU15MzZDMTRPY3BTY1BaaGVwLWNDRXR2VlRpb3dYY095bVBtWWc4SldVS1A4aGo0d04yb1hfX2xENEtHMVBRcHFRVlBYQ3FESl9iODJqMnZPaEZZbzBVUzIydW1Wb0ZVanFXblRCYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOd1JuVGNzOUxzSWR5YmI0cjFHQ3loVlFEaThGNV96NjRRcl9iN214S3BOWWZzakFUWkgydl9BNUpTN2tSMFRINGlmbnVvMjFwTkpRd1I5aG54c2lpa2dIQXFQdS1NMUdIeUJ4bS10ZDIzejgtSmVrcnI4eXBsN1ZRUFVlY2tOZXZXd2M5UEp1NmpnaWpVdFhwLXBkakxydHoyZ3VPM3RDcXJnQnRQczhtTGZ0TmhJU2RreEFXTFFNSjVod0c1VzVHcUZZQjY?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46019.38605324074</v>
+        <v>46020.2628125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paris knife attack: 3 women stabbed on metro stations! Here's what we know so far - MSN</t>
+          <t>Pilot, flight attendant barred after testing positive for alcohol at Schiphol - NL Times</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 11:36:38 GMT</t>
+          <t>Mon, 29 Dec 2025 05:30:00 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxORWVNSTlLSkpnWE5yYjF2X2NqRGpYelF1NGxCNkN2Y2VvRmdUZ2pLVTdJUmR5MzJPRnYxY0JidXQ5SjdvQ1JSN04wb0RvLTFRdGljX1ZPZHdjSnduaGVqNjl2YVlBVFNtdEhvZUdWSWJRT0w3eEtIbkpvNkZBcVlyQjhIY0ItbXpVMDFqN01qdHhTNW9RT2kyMEtzbDdYN2ZiTGxZZzQzeEpBU25WWmVxb1hJNjlUNHpkcjVtMExDMFlZWUh5clE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNeVhGNmdmMzFreG5ZOG5TWlQ1emt3d0FNbmFMRVBHdzllQkFWSWhwMlVPVDVtcHNiTXZYQTNDTDhuekd3aUc2dWwzbzZVYVoyVUFKMFAxdjlUdTQzXzdpZFFzanUwNUFRSEt0OVV3eVBJbzJSQnpDUzZxS2piUEhIekNDdXlFTWJTTXFlMTJlaF9ZSmNadFB3NQ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46019.48377314815</v>
+        <v>46020.22916666666</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paris Metro Stabbings Suspect Moved To Psychiatric Hospital - NDTV</t>
+          <t>VoCoVo's Martin Smethurst talks 2026 trends and challenges including retail crime and AI solutions - Retail Technology Innovation Hub</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:04:00 GMT</t>
+          <t>Mon, 29 Dec 2025 06:03:08 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOYnpFbk5HbFFjeEJrLTZfTnhqQk5WMTlTZFRpS1lVZF9SYnBFTElDLV95X2pJT1JxNnA0UXliRFhibWpXQW15RjMxMDgxZTJBUVNEbkJVcGs5SnNxc1R1MWd1RTRiZ2xKSV9GT1FLVlEyQkNNR2xTOVlCNkcwb3dWUkVWYVZlMGNBekpfT0c1Sjk1M1U3Q2RCSTZTd0xGWFNFTW1aN0FCZ0JBUdIBqgFBVV95cUxOYnpFbk5HbFFjeEJrLTZfTnhqQk5WMTlTZFRpS1lVZF9SYnBFTElDLV95X2pJT1JxNnA0UXliRFhibWpXQW15RjMxMDgxZTJBUVNEbkJVcGs5SnNxc1R1MWd1RTRiZ2xKSV9GT1FLVlEyQkNNR2xTOVlCNkcwb3dWUkVWYVZlMGNBekpfT0c1Sjk1M1U3Q2RCSTZTd0xGWFNFTW1aN0FCZ0JBUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPX2RjRHBFaTEzQlJpdFNCcWF3dThGR0Z6VHBuVU1QMjJvaVhLUXM3Rm80UC1qRnJCekZVRnhSd1NBa2FYbDlDaW1ISnVhVjIzR3VQS2x0UjVtM0U4MmdiYUJsNnNUVDNkMEJScVI5TU50bnpsRlRWSTM2X0wwTEF1YzFGNmhGOTBrczAtdXVSekVrbHZRRHRnTGZldlU0cnVweFhPU08xZnJVTjVjc0lXNzlaRGxNMUk0dGlHWTVqcEN0TlhrTUNVQ01GWlhiNFZTRk9BaDU4ZWl6OEtSMGFYS3VhSQ?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46019.37777777778</v>
+        <v>46020.25217592593</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Major cities cancel or tighten security at New Year events amid terror concerns | World News - Hindustan Times</t>
+          <t>Appeal following shop theft in Sandwell - West Midlands Police</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:27:27 GMT</t>
+          <t>Sun, 28 Dec 2025 17:00:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNVnNhRHd0ck1XZHVTWU9RZUtZRFRZTnRtc2FiQ2JTQjBxZE5kcE5fMkpSLW1aZlZxbV9vVmd5REZxYlRuREUzWFc0dmpaaWNVdmZCMHA0bzNnWVZqMFhlOTJhMHdjOFVmeEZIUGptQndRUmJocWprZFVUWTJJeXdnTHFLZFBpYmdVMEl2Q3ZzZ1N0NUtUOXpZOVBCaEZ3bE5TZDBMVGZteUsyS1lVZlhZelVxcWRGUTR1a1NNMWtDODFGZm5jNWRFODJVeWNsM1NxYkV0cERVR29Ia2RyZTVr0gHfAUFVX3lxTE1Wc2FEd3RyTVdkdVNZT1FlS1lEVFlOdG1zYWJDYlNCMHFkTmRwTl8ySlItbVpmVnFtX29WZ3lERnFiVG5ERTNYVzR2alppY1V2ZkIwcDRvM2dZVmowWGU5MmEwd2M4VWZ4RkhQam1Cd1FSYmhxamtkVVRZMkl5d2dMcUtkUGliZ1UwSXZDdnNnU3Q1S1Q5elk5UEJoRndsTlNkMExUZm15SzJLWVVmWFl6VXFxZEZRNHVrU00xa0M4MUZmbmM1ZEU4MlV5Y2wzU3FiRXRwRFVHb0hrZHJlNWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQUDl1SGcxQlVhYngyRVNyd1pYU2I0cDk2WEpZV2V2eENjeUh6OUxVS1F0SGppRTFTbi0tb2NLbDR0TzhlcWZZM0E2Z2MyMWZzckVvLWVKamJpbTdSZnFVeDJxY283YzgtTG5Zck0wdEZ6M3Y1alNTd1N2c1p2cTM0ejI0ako5QXRhaVlwTmlxOHA2TnBjbGtmOWhKcnhrTEcyeHZZQW82ZUZNeFB3OUMzazdBb2R3eklPc2c?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46019.43572916667</v>
+        <v>46019.70833333334</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gujarat Petrosynthese Limited (506858) Stock Rallies - Risk Management Strategies &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
+          <t>Fear in the Aisles: Why Retail Crime needs to be tackled by the next Scottish Government - enlighten.scot</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 12:27:43 GMT</t>
+          <t>Mon, 29 Dec 2025 00:02:28 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNM19HU3dLQXhIZ0o1cDk0MnVaY0o0SnU1RG95UGltV2dtcV95Tm9OMjdpTFhjY2E3a2lqZDRzRENZeHNSTWowWmZLNldybW8yRUozamNodHJZaW9pVkpFdmMzcThLb2pjOGx4ZjlxT1RhNlpnZWZtRlNWdUN1aUhFX2F0WnhaeXo1d0p4b2hrdXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNRURfUi04UE03cjMzekZTTGIyMlVudldZY1JJc3FKa1h2NG5sRTQ4YzlzNVZHZ1cyX0lybV9CNFlzMUh0aFN5aFlVakUxY1pCVkZaamZxOHpmcHlFUWlaV1VpRDhaQ01PVG1JMzBGVWd6N1gzTTNDYjRreGlwNVVnNXdkbURYaHBROVpwQ2ZzOFhXd0ZLWWxZMGhKUlpCUGR2LWFVZXNQX1dHT3BLd1Y1eVd3TVZrZw?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46019.51924768519</v>
+        <v>46020.00171296296</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alleged baby abuse: Police receive three reports, one woman arrested - newswav.com</t>
+          <t>Police launch appeal after bike stolen from retailer - Halesowen News</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:04:38 GMT</t>
+          <t>Sun, 28 Dec 2025 17:09:25 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNLTJYa09fRENYQ1dueUR6dUQtZXpRMFlMZktCNGJWNnBwZXVPbWZIZ0FCUW9wZWlWalZBclBockFJaWpzaUxKQnNKNFQtdGVnNzlEd0Y4Y2pyUG1CVExOVTVMcXNGUGdCZ2ZMQUZiazBWSVVNVVFDZGJWVmZSeDNldGJla3hjb0k0eVVxTmZRa2Q4bmFrZHZidEU0ZElac3VsQS1URjhvNWFqR3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNMFZjVDhhblQ0STlrbXh5Mi1sNkFtVG1YZ2tzRTRKc250QU95SDdPYmt2cXE5OGZnZlRfMndIemJKTEI4SFFibzVpLXRidFdvT1N3OHhZLUViemt4MGRzVlk0VWJQVWoyQldScXpISlVJQXVHdVp1RVNDc3dNUGFoXzlXVXJjRkt4VUZaNWlETmh3SnpjamUtYW9QWQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46019.3782175926</v>
+        <v>46019.71487268519</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brigitte Bardot, French Screen Legend Turned Political Activist, Dies Aged 91 - breitbart.com</t>
+          <t>Have you seen this man? Police issue photo of man wanted in connection with Oldbury shop theft - Express &amp; Star</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:28:13 GMT</t>
+          <t>Sun, 28 Dec 2025 17:53:17 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQQzVOdHRfN28yelozTU5LcFBhdUxxaW5QalZBUVlmRHpuT25HMm5mTWNQUWNaZTZ2TUplMTFHajdyUmNvZWZlbDNvTFQ3aFdxTnhGNm4tUWdWTDM4eVN6X2FGYms5ZHJZaVJyZTdXeTI4Nk1Xcnc3d053NW96bjFSQVV3ejdLSEJHeGt5b2llbUNIcVp1NldCWFgxNHdVZl9tak03eVZRSEZBa1VBMzJYM1pQdWEwaUp4Q1FoMFdVbnl2WkJVcWfSAcsBQVVfeXFMUGwtd01XenpwemlGUXpMS2ZBVWMxZVVCcE9EajJZd3F0LVZHLXowTVQzcW1tMWQzSW9veFlhLThBV3BwSzBzT1dKaUJLdmlSeG9xQ21yZjA4RS1GbldSVDZyT2JvWGFXdkFrVzdQSmswODFxOF9TT0VPOTBDaWU0cTVGRXBkRGVTbzhrY3dNRHYxNzJzOWdjeDFpaURNMGlRSmd2TER6a1ZqTWY2QTBrT1ViTzJldmhjWUt3NF8wZVZSQUgtekpNQXVjV00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNLWp4a3lhSmNocUxUdElGanpJa3RDRUtPdjQxVTkwcnN6NlFKd2oybzU3RW9DUXZrS2l0OUhTNndIcUtUT0FBc2xZdmFQckZKZVo3Q1h1TTNFdFhZNGtZS0syMW9GdE1Na1ROeG5xY3l2SXNNUl8tdVZEa1p0TFl3bmtqUE1ibzVWOElZYUp6MEZPdHZncW9IT1diRnltMzBPLVg1ZkF4U2lDNExlRDV0VjBFMzI0MmFKT2UtOXRFLXFvSVlXalBHWEVuY0xxQlRBSlMtckhBbkRfZjY1ME5hVA?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46019.43626157408</v>
+        <v>46019.74533564815</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No. 3 Iowa State hosts Houston Christian following Momcilovic's 27-point game - FOX Sports</t>
+          <t>Police looking for woman over 2nd case of shop theft at Waterway Point in under a week - mustsharenews.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:43:24 GMT</t>
+          <t>Sun, 28 Dec 2025 17:31:09 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPcEFVMlFVd01sRDdheTZiSnZEUXRZVjJUUmdNaDFxc25CcTdmRndqLXdCVDFGQThMQWs5R3ljWDZtYThFejU4Y2ZxLWM3VTFsU2lONVQyYXhHYk1PbHZWc0p1Q2dGU2I1WnZRUndiZ3ZDbnhCUGFwSld0TW1DT0NfWWJ0VVdtNVg2eWZIY3Joc2k1MlZNREtvc214bnpCNXdIY0NLTWpOMjFtVmhQbXNJVzNPWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFA2TTBtdHBjTUUtb2h2NjZlNTRTZ0RlMHhZemFXd1A4THl6N1ItSnluYW5PTjdqVS1QSWpLT0g5Y2h4U1ExUHA2YlczdFprNWlEMG82N0hNYlNvdHNObjB5aHZaY9IBaEFVX3lxTFA1ckxZVHYxbGZsOUd3VjRnakdiY3RZSTlzTkdUV0tSN29zUDB1LXhEWVZuX3pYNkRNS1owMkRrVnVMNGQ4ZkhDWHFGclkxWkhsUzViRlNHUEd0Qmh2MHFBWEpEbkxDTUJC?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46019.40513888889</v>
+        <v>46019.72996527778</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>'Mo Salah exposed Arne Slot weakness – he needs to take leaf out of Jurgen Klopp's book' - The Mirror</t>
+          <t>Comeback and 10th consecutive league victory - realmadrid.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:00:00 GMT</t>
+          <t>Sun, 28 Dec 2025 15:27:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPbjlycFBVQWFpNVVpazFVYjdUODYzTWFpejd6THEwSzQ4ZWhSZ2tUZGpMWW10VVJuVE4tajAwOXhubE5Odnl3QnRvU0t0T3J5QTc2UWRFRFc4eVFNbGowcVlxLXNnZ0ZrblNDSWZPSVI3RmlCbHI2andIbVVwUjlhZGhOcGk3NWlud0pTLVJUODLSAZABQVVfeXFMT245cnBQVUFhaTVVaWsxVWI3VDg2M01haXo3ekxxMEs0OGVoUmdrVGRqTFltdFVSblROLWowMDl4bmxOTnZ5d0J0b1NLdE9yeUE3NlFkRURXOHlRTWxqMHFZcS1zZ2dGa25TQ0lmT0lSN0ZpQmxyNmp3SG1VcFI5YWRoTnBpNzVpbndKUy1SVDgy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPUFdUdFdVc195YlpxTjQwOGlfSmNzUDJKSUYzbF9ONGlnWC1WZzE2VFVNQTNWSHRlb0V2Y0xJcldDYjZlQkl3UC1mMV83SFFnRkw0QW5vY1ZUUXh6bjU1a0FwUHdTVi1MY0c5cUY0bV9xYUN2ZEhKWExlQ01WMWRZS2ZXd0ZhUFN4elp2ekttWjhSeUpqTzZRZA?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46019.41666666666</v>
+        <v>46019.64375</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Should Belgium continue to grant asylum to controversial individuals? - EU Reporter</t>
+          <t>Why isn't Kylian Mbappe playing tonight for Real Madrid vs Manchester City? - MSN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 10:27:22 GMT</t>
+          <t>Sun, 28 Dec 2025 20:54:45 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOOEVDbWtHLWg3dGxPbWMzeWlzLTJaa0FSSFItd0JVd3BIRnBiWnptZG9LZzNZb2VWNlpmd2pRUDFWZWNDSVJJS3NuaGVjd19RVEdkNE5zcjNhQmgtMW9TNVh3X0xGa2FHa1ZvQUdfbVVSQ0xkOHpzR2dZUENYWWszaXhBWXpUUnYtcTVHYzB2aFNSVVdwcEJ5WHcta2Q5ZkFNUmpGeDhJZTNDN1hBRmtJWDFLQVFlX0lpNDA4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgNBVV95cUxNc2RISW9hN0xrajRaeEJpZmVrQkxyYnFyTGxXUGtFeEM4MmNJT3Z4ZGdGZzhPdFlRU1JGel9nakM1cUhUUVNYVXRTcHNRODFzTHJfSGpBWTRjeHJqQUZnVGlSN0RDT3hjcWs2NkstRDQteUIzMUo5Q2h3dzhWdFNFNVRzZGlsN3VCaGpUQVlWRTQtXzA0RzVqWTFoZWRCbmFoZTZ1QlZLMENFenVlTWhPdExaVTdmaTFldTBNeS1mUXp2X1F3bVJ3VDdXQzFkZGIwNVRBeTJ4U1BuZUtuNktHcTVXRmNMZ2VHbmU3b1Z3YlFaRjdacWRQUXBpaHFVUHNmLU53eDYzUzhaZHZBVV84REd0NWJadmpsd2lXVVBxNTZyUlo1SDdxbUJBeEdEWFVVWVBtcWh6RElNMzd3SnhmWkszWkxZUkZoZG9QMXRUSGx5RzZONGhBeWtEVWF3UDBaUXJYRm5icUNscU1FTURweW5oX2Q4cnNxcjdtTkU4WVBnVm1SZXhJMkFiRVlLZXo1a1d4VzdxS3NYZw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46019.4356712963</v>
+        <v>46019.87135416667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Moscow airports grounded after drone strikes, hundreds of flights disrupted - Aviation24.be</t>
+          <t>Globale Tessile Limited Shows Support at Fibonacci Level - Stock Price Targets &amp; Affordable Portfolio Strategies - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 12:55:48 GMT</t>
+          <t>Mon, 29 Dec 2025 05:28:32 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQd20yNEE0cFFVaXd3aVQxZElzai1Kd3ktempremhoVEZ4NVlZdng0QXo2eDZGVW5zbExOcW05Y1ZrUDJpWWpaMHM5SXZWUkpPb1NiX1hOYmRrN0RFUzRYRWRZUm8tSDQ1R1VxUVJEQ2ZGczVZNzRsT0FReHZuX1BnZ1JFamFid3VTYllFTG1wSm4zcTZ2RllUanZMQURIaDZEbEM4c3hxaGJGb0R6VXFaaG55MDPSAbQBQVVfeXFMUHdtMjRBNHBRVWl3d2lUMWRJc2otSnd5LXpqa3poaFRGeDVZWXZ4NEF6Nng2RlVuc2xMTnFtOWNWa1AyaVlqWjBzOUl2VlJKT29TYl9YTmJkazdERVM0WEVkWVJvLUg0NUdVcVFSRENmRnM1WTc0bE9BUXh2bl9QZ2dSRWphYnd1U2JZRUxtcEpuM3E2dkZZVGp2TEFESGg2RGxDOHN4cWhiRm9EelVxWmhueTAz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOUGNyNVMyV1lrazZJVWZCWjljdzk4U0dtWnBtdUZ3SGE5QzlkaXh6NzRwNFBPZmFjOWV2RHc2R01CeDg1Zlo5VDNMUDNfUC11c3d0UXF0SVI0QjVOYXdYNG9PYmg2bHlLS2JpamR4VXlHVzV0TXdITGZWY05IeG91SC1uTEpBMTZTWmhOckZfckdwYjVVNkE?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46019.53875</v>
+        <v>46020.22814814815</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Dunbar Armored Robbery, the Antwerp Diamond Heist and More of History’s Most Daring Thefts - AOL.com</t>
+          <t>Learn to avoid retail traps and false breakouts. - Automated Trading Signals &amp; Best Stocks For Explosive Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 09:20:23 GMT</t>
+          <t>Mon, 29 Dec 2025 05:38:54 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQQTZQRzh4VGdEV2xKYmdaWWdPam9aWEVQdUhncUVOUXRmTXZXS05sUER4YVJ0WF9xd0l2OERpM0tCekdxRkxRWnZSdnJMNXB1em5MYk1tMWpzLUo4cmhEeHBwTGJhNGNJQzBUTFNYWDh6ZGg4ZUh6LW9adHY4alpqX080SDdreG1BcUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNRDNkNEliVGRLUkhpM194TlU2QVI3SlBGaWNkellSMWNmTzYycWFJZG9IWk5CSzJWajdYMld6RFB4VmZHc1RiX1JyeUFVUWpQRy1ycEw4NjVmN2hINl9VUmZMRFNES2lUSnotMUdDSzVHN2N5TGg4TEZNUE0yUXZ0bUxrb3pFblFvbnlpS2JiNFktVTM2Q1E?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46019.38915509259</v>
+        <v>46020.23534722222</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany-Terror-Netherlands /WRD/ - IRNA English</t>
+          <t>How to watch Iowa vs Penn State NCAAW game: Live stream, TV channel, and start time - Goal.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 11:45:41 GMT</t>
+          <t>Sun, 28 Dec 2025 16:31:02 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE5mTThyZ0dHQmtSUWRBRDg1d09JQnlEc1NmWHlRaV9DUEZZMlFCaTdHRUowd2pqRkpHMkowMUF2cERsOTlVTXfSAUZBVV95cUxOZk04cmdHR0JrUlFkQUQ4NXdPSUJ5RHNTZlh5UWlfQ1BGWTJRQmk3R0VKMHdqakZKRzJKMDFBdnBEbDk5VU13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOaE9fT19RM1ZKLTFncklITUc4ODd0QkdLZzkzYmNBcnFzWXJ2dnRWcWpkTkV0TFNBVEM0STkwcWpkaDA2bGlteEdSd3NtY3dMUUVqbmJ2QWVQcDJoSFpYdUZOZl91ZXdRdDQ2ZldDVzlOSXJyQUtMX21vZlE5RFRUZk1DQ0wyOURPTUpvak1fNnBTYndvM3NGTUZ3?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46019.49005787037</v>
+        <v>46019.68821759259</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Igarashi Motors India Limited (IGARASHI)’s Trend in 2025 - Trading Volume Trends &amp; Access Our Free Weekly Investment Letter - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 18:50:31 GMT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxORFBNX3hSazhyNF9HbjVxMFlaa2IxeHllU2EzeUk2NjltcGRTRXlOWjhrWVlHbkNFMmtaUGVGRG1jRjJjMGhZaGdWSE9XMWJhR0tZNk1wS2lZM042OWM5TmR0YXZsaFVMNzJjQW11d09SbVZwWWdJYVFGaHVlLUJRcUY0ZXFFRWhQQjBBUm5BMDJIS1JTbzU5aERGTlBHcThKZ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46019.78508101852</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Is Bulkcorp International Limited (BULKCORP) a Good Long Term Bet - Cup and Handle Formations &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 14:52:45 GMT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNYklRZzBSdm4xeHFicmdQT0NrU3IxWHRnNERTZVpxVUpaNjJHX1JocFVvVDhWSU5zTzdJelZ0VlNyYmM4bG9lSWE5SkRvaHNvQUd5X2ZvcEl5aFlKaklCdi1tdmF1WDI4RFpMS195Q3pRTHNtdDF3eDVCZUlvZUkxcU85V3RIeXBsN1E5UTNiNGtMR2NCZVFBLVEtZ2h4R1NGT05zeGlnOUZMSXNB?oc=5</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46019.61996527778</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Holdings Limited Crosses 200 Day MA — Signal or Noise - Price Action Trading &amp; Affordable Market Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:34:55 GMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZ25vRVVTQnBSZmI2UkxkOWo1aW9NdFl5ZUEwU2pQZlc4QW50WlhRRUZNdVlRZjZxNlF6a1dvak5ZZ0JWemM3b29wZEh6bTg1REtJVHFYN0FhbFRSa285aFJ6T3Fwb1MtTzJGTFdSRmIyZjVHa0pQUTlnTG1rTW50Q1NlSXNXWlpMR2Nmd0FaTDl2enN3eDh5ZHBoMlA0QUx0dk1CeDRkZDVzNUwwbkFsSTNDNkhYaVlMX2tyT1ByYUlMX0gwTk9hTmZqZ1VpcUJMTEFZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46019.73258101852</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>High Level City searches   Spain, English   language</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Marcus Rashford: Barcelona reach final decision on Man United transfer - The Peoples Person</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 23:35:36 GMT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZ2hhOGdsdEhPSm56aHgyS2h5andVSzRFMUMyZHpHcWdPeDcyNGVLWDJuUXctbEh4YUotX0tvaVdZWEVrNXdjVVJsTkRkUnhkOXZBaFVPX1V4UW52Y0lUY3pkZkNrZWFQYlU4X0VZTm93blE5bFYtb3RzSTZEaHlfeVZ1a2VzOE9IeTZmRVFFM2g4bXpiX1hFbGszaC1jTXUyZmJXOWgwRmZ0TTRpTURfenowRFM2TGZs?oc=5</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46019.98305555555</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>And you thought Boxing Day sales didn't matter! Thousands queue for bargains despite Rachel Reeves - MSN</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 05:56:31 GMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQN3o4Y2hOR284ZnVKekNzSElBbDNSQVlTS19sRmlRZkxtOGNCbmZCeDhpX0tLNE84MjAxUXVCODZkU0UxcFlYSlVFSGJMdV9QbnRDbEdsN2JCODhXdU5ieTJzenl5cG5IXzNiaFBiV1R2VFhob2RCdVVsVlhrZEUyOXlmSDc3UlF2Mi0waERrUVFJdWtaNl9oZFFFT1JZaE9QendVbndYVTcycDNJRWFsV28tMVB0SFdOdUxIYVRCSnFDU1Z0dy01U3pyUmxxUWprNDBjbnhXdWlrWUF0WnUw?oc=5</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46020.24758101852</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Village Search Bicester and Kildare</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Литва направила ноту протеста России в связи с активизацией атак на Киев перед переговорами в США - Semana.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:36:21 GMT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwJBVV95cUxOdC1qVmRHbXhWTEtzMVFNZHVtLVNDd2l5TE1tamFnTVk1NEYzd0J5S1pMbHRxZXhGWkNQeUIzR0hKWk8zS0VjWUdkMm1SRXB2OWZJblB2TFdNUmN6TFBfUVNrRzVjTlZ2cldlR2ZDemIxNWFjWXZmVVJRdG1KdS1hdGxhT1VVOE1GT2hLb2xBcWIzNEwtZks5NVFNb1BpWVh0M1F1RmFMb3UxVE5kZWNxeG5QaGh3TjdQY29SQW9KN25Nd1QyXzFKcElkUTVIamxCTlpNYVJaNWxMMzFLMmdGZjNHdlJTTjM5eVp5N3E5U0xNdVE5a0VNcHpSOVUzNEhOTlJmUDZoQ2t2N3kxZ2F0LXp2Q09JSzY2dEhRQ2pKVWlzYnNJcnJXTjlnMUZ2UWlrV0VCSVRGZXlRenM?oc=5</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46019.73357638889</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sonic boom like an 'explosion' across the East, police logs show - BBC</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 06:10:15 GMT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA4c291ZExreUtXM2t0M1B0ZDlFQW9ieDRCeEtfZFBCWTJrQTAxZUVQR0x5REZVa1NGU2puNC0xWG1qS2VWYjYza3EwNUFfbjc1UlRlcU9OeDhPdzJQ0gFiQVVfeXFMTnE3Z0Z4WjJjRDByMHNLck9LdldYeDhoVlNSZGx0ekpQUnlaazN6cE9BTy1DZGo4MmVOaW4xQlNfMHZBMnB2Uk12eWJyMGJMNTN5NE5nb1lkaWJ0VnM1OUljeEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46020.25711805555</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Boy, 15, Dies in Stabbing, Second Man Charged with Murder After 2-Week Manhunt - People.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 18:24:54 GMT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNUdrQ1ZwZllZNU4tVmF6YWpDNXVQY3pxdkIxcVpQQ3JkY0VXNGx3dmhEWDJWZ1NuUUd2YUNvV0FVaEo3S0lQenRPSWlHWTFudHRaclFuRXBRQlQyMWMxQ1hXZm5jeVJzb2FSVGlyMXo2TGM1aGV6a0pvUFhxZ3Iyag?oc=5</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46019.76729166666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Kilburn man charged after arrest alongside murder suspect in north west London - Kilburn Times</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 15:07:07 GMT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOVDR4QUJIOWg1UENnWk5XWTg5RkJ1YXg0ckZxN0c1R0dQOEhVQ3hlZEt2RS15Y2IzR2VkeTVNM0loVHQ2bVowNTV2MHhFa1pjUlJyMmEwMS1CRVFoSlhKS1FubUpvb1Z1QU43OTZKTWdXODN1OFF3Z1NyYmYyOGdIV2cxdGpFWkE0TmxUbE5tT2V4eU9QNG12V2wwc0V4YjNGa18w?oc=5</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46019.62994212963</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brigitte Bardot pictured in 1959 in London, in the heyday of her brief but explosive film career - IslanderNews.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 23:01:34 GMT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxNVk5ycXhoWTVnVnZ4d2E0WVBDaWVRVHpGejd2LTlydmI1cDZYMGNGdlNORS1pei1GSlIzS1pvX2xpMjZnSGtQbUMta1ZicDRzQ2c5c3NDOE5EaWNNaEF3Um1HNUszVkhzSWNGcUlUMl9hM01TeVRnNGV3VTZuVUtBMEZuRTZvSC0yenkwT3dLN0U2b2NqUHJVTUpnMWs3WVdRUmJ1MGV5Uml0b1BzbGl3MTBWM1RhMkdCa0EzUUJTbGxXLW90aThWWWNncTgxSDI0VzU3eWJ5amhnQmREWVpPa2JLd0oxX3BmVGE2d0xOVG9ORjFZanhYaENBdjBXWlN5Vkhjcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46019.9594212963</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Dublin Gas Explosion Report BROADCAST: 1987.MAR.26 - RTE.ie</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 15:27:54 GMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOR1RBR016TnN1NmxSNkdBNy13TXFwN1pVS0dUSTRRZGZ2Wkhwc0JJYlBHYjZHMGpmYzBBZG9ocENMQThTc1Z5Wkp3OE8ySHBQR1I5U0kwWkprNm90bmlZSVNfYVhFOGZrZVdXRWpXaURkWnZrMU1vczhnbDllYVdOOUlfdF9nVUp2ZHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46019.644375</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>England Joins Northern Ireland, Scotland, and Wales in an Explosive Surge of Tourism That’s Taking the United Kingdom by Storm and Setting New Milestones for Global Travel - Travel And Tour World</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 06:02:17 GMT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgJBVV95cUxQNUJ2WmRVM3dkYi1kcTRQXzdwcTVmT3BPOG44YmlZNXJBam5wd1phNGRWZHF4MlZONVZJZGE3eUhGejFJRGpjSUFhbHNnbk94anU2bmtrZFB2dnB0WXlXZHZaUkNrRnYwd1prdGZXVVA5bjBMVzdQWG11bzEtV2RZTElmVmpwaVdSTnF2Y1p4UUc2MlhyVkhWaDF5cnNlVWRpZ2lfVC1BUjNzRTR4TzZkbzRnRFNNUHVqQ2NHTnVnTlRTTkxSZ21PWmt3bDVCX2Yxc3VvNmlXSjM4UFJvd1RwelhuMmphUXpLeE9jWWY3Ump2VTUyNDRGMVhfQXNWeVdXMjJLdHJnWlJZNF9xUWM4OW9Mb19pUk1UWUdwUEZMN1VCNl8ycFNDaUVsWTBuOXp6S0MwSTZqbHdqeVVHSGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46020.25158564815</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Norfolk: Driver shot dead by police after 'fleeing two-car crash brandishing handgun' - GB News</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 06:50:24 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1XSnpTczRWd3VUQ0V1YUFYU1NPZGFUanZhdnJuQ1ZJUVFXbEJ6eDJtZThnRWhBS0FRRC1hNWliTHlHUlI4UE5ueUxXWTRMWFFiWEh4WWk1RkE1bi1TVmlZRFc3ODBibjViYWE4Z3FBWi1nalczbXJqX3dzOEljUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46020.285</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Man, 38, charged with GBH after Lidl supermarket stabbing - Colchester Gazette</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOa1hEQ0QtNFhucFZiNWU2dE8wUXNPZ0tqcjlXNTM3dWRhTlVaa3A5S0FuOGhnLWlEcWg5Z0h3cFI0UDEzbUZkdDFHOUhiU283VTd2MW1QSmpLMXZzdlRtWDl5Zzk2US1vOWJKNVE4RlpacmVwWU81cFdTbmpuaUxCOGE2TjFmcDdkNjl2dQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46020.20833333334</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UK faces monster 47cm snow bomb - with Birmingham in firing line - Birmingham Live</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 06:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOM1pmOEJORkNtaEtMVnNDd0FtVk5vbTRDbWQxQXAtcVdsSk5uOWJsTTN6S2FycVNQOVB6b1JrTnc1ZnllRERqRWdWLTl1Q3RBOVAxNExZa1NOeWp2UVlpNFpqajBDbS1ZSlVZd1hwYU16WnFvYUU3MUtlaW9Bb3RPMHNwZDhoZDhCd0o1Qm1DZWTSAZYBQVVfeXFMTVJCM2U5cEdBNndXZDd2Q0FFMmYxM0E0SXMtd291NlktUmdxWW5nNUpMeWw0SXhmbnFNaVctV0xiLTd5OTJycEV3M3RHYm0xSHg2Q2tYY1h3OHdOTUJBS3VqUld3eXhMRUlrbGpCbmNJbTZUaW5MSkZQQ3BDU2h4dlRyYVlXVV9PZHRiYXZCRDNEOEczRU9R?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46020.25347222222</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1 death notice published in Romford Recorder last week - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQcjc3QjMzQWtwS0FqYXFPNkhsUHpua21qR3NtRlBBNHB1ZXNzaWR5OVRrQmtZWVhyNWlDUEZGYjNIUmVJeDZTUFEzMjdzRUFjelpULUVxeWYwSXJNMmNnNVF3bThXcU9kcl9rZkhwZlVVRm0wNWpqM3JiU19tM0tJUkxIbU1PcTRoYVV6REpUY3I1Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46019.70833333334</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ten injured in UK train stabbing; counter-terror police join probe - MSN</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 02:35:47 GMT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNdGJXSWxLelo4VFItX3Nzc3d0NUV1eW5CVlRHZGtjQXpJNS1acVlQMWg1UThXVmp3OWVUYm9uNnZMaTJfWl91MWd5d09lRC1vNkhkTWtNREZpYndmUUxsWDlMRklyWmZsTDZhbk15R3Zjc3JTWHA2TFVxUk8zRU1GSVl6V3pCOXpKd0pOcURmX3FBZk9HeGhKUjJhOThJMl93NHdEWmt1S1JJTUtyUjVabGpGeHg5VE5FczlQMURRQVkzLWdjcGktWFNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46020.10818287037</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>'Angel Delight' drug mules given update after fearing execution in Bali - My London</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:19:38 GMT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMHNNTFBuMEljZzkxR0lzNXhORDNaVVZjRUtQTHh1ZkE4Zm9CS2hwYlRpQmVOcjhwaG5zSVQwZTdCNlF5VmUtX2pXbTRoS0ZlbVB5NzRZOGdZcVQ2R3BzSUUwb2lRTTZOb1V0c3pHRGNYdU5XNmVmcnh0UllOSVMxVkdiOThialhTYm9BatIBkgFBVV95cUxQYm9abXN3UXFsblJsSXQ5QjZObU9OSTFTdDdiVlBwZGtsVWplWDRDalNPa2lncFltbTlIbGh4VGc3M2h2a09XOWRIRHMwNnFPb29jWkhZQUh1a1UzbWg5V191X2JkZkJPbUtZam9qS1J1RFVsLTAwYk1EeDRBRlN5TTFaYWpOMVhMUGpkNEppQ3VQUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46019.7219675926</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TUESDAY, Dec. 30, 2025 - The Korea Times</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 03:30:04 GMT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQY29Za3kySlZEbThpWUJSWDZNZWk0TXVjN0d5Um1CdDd1OUpSbUYtUjliODdoTl9HT19KVm9XM21rbGhJWVN1ZlpMcHc3SGlJUTcwUmprZkViX0VYYm8zSjl6ZnJ6NVFhUFQwbGNRVEtKQU5YNjByR2hBWnBZVlVBcEdsZEhTNlHSAYwBQVVfeXFMT05wdUsxX2xEVGtHUGF5U2l2Nkk3dUpCRTFRNW82R294TnRFSjlQTlBFOWVFWTU1TGd2TFo4WnJqZklpN3NtRlloYi1JUkNZbmxjWXkwNnNDbGxRUkZObkVLUUtURHA2aDRzYnY1R3BhckZ4WEZfYUw3bHB3RVZuMngtWjVtTUR4Q1dFN0M?oc=5</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46020.14587962963</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fibonacci Support Holding Strong in Raasi Refractories Limited - Market Liquidity Analysis &amp; Explosive Growth Trading - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 01:13:53 GMT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNQXpoYV9laWVhYjRJZm1mYWk5VjgtNEJ4Q2NOcmxkNEdFSHJPd1B1eWROSmlqeHE3a2ZSVW12NjFNT21YcU9lcmJWLWQya2p4eDMxVUMyMmRpb0pxZTIzdFFGdzRBM0owREN2V1RaZHpoLXBFdmpIMkNMbkRwTXIycFNQSHVaM1RrUnFQQXZCZFJYdzV1ak5DdHl4T29Cd3NDaTJmNWlSeXA?oc=5</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46020.05130787037</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🧱 Building Blocks: How to Read and Use Volume Profile - Volatility Trading Techniques &amp; Free High Yield Investment Strategies - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 06:44:15 GMT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNaUNWX3pCMjJVbEd5cDljbmgtbVVjUjVFSWtoY2VfY2YwZzNkVzE2SWlKblNteUV3a216X2JlZFkxLU1BaENaSEg3eFhkWkVtTGFvUXRHel9Oc1c5WVdtNnFPUHJTX1I4NFVzTXp4dDR2V0FlWjFuNzNhNlBmQTVtSVR0QkxUV25vZnVfMC1hS3k2ZE9ZMzVlQTlraTh3bFgzWE1EclNpbFJ3b2tlYkhKNEMtcW0?oc=5</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46020.28072916667</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tinder Date Eye Gouging, Officer-Involved Fatal Shooting: 2025 Top Eastern Montco Crimes - Patch</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOUDJmeW1sejl2WTBlMTZ6NEZiUXI4LTAxczBWRDNrYWFhb1RIUXpFaVplLWJzRHpBSzZMa2xENVE4Qjd4OHY5YzlUdThEbTJMYzQ1WjJKTDc2TXpTZk1lQTNEUHJwdGVFcEw4VnUwcUZWLWZRcFAxVmFtVDBZaXczSkFiTm12aUxqdWhScEJFZTRLaFVEd1J4bF94LUdGaXlqajh3Tll2djNfMXdEaW42Q0l30gHWAUFVX3lxTE82OEoxOURkTXg3dkFMNnZJc3FBY25vY0h2YjJtUXhLT0JBWEltcVUzUnBtRGF3cFNwazBfWG9vTTNKTzJKMi12eVQ1WFc0NVI4MUZGbkQ4Rk85MHVwMkZnUk4xTlhWQkZ4QVhRUUplUHJPR3dlX2FlRUtkY2NsRndndE1IWUd2VVRJZzExVUhicU5IMUV1anpTMkN3cEtHVnlGdUNNSThTYkRTU09qaGRiMGtCQXl1NjdTci1BdXdDaUtfYVc3T1ptVXYyUVRMTE1ncDBiYkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46019.67430555556</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Trendlines Suggest Libord Securities Limited May Bottom Out Soon - Earnings Date Calendar &amp; Big Data Market Reports - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 18:00:53 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOOWNSaURJNEY1ZjR0TU04M2lBby1uMWF4ZkJNa0JFWTdWUWxqTnhZbjh2bUFBYXY0ZzBBUkVnUXd6eDFaQnVoQlhYenZQQ3otd3VpNjFvTlhBajFYWjI3a2I1a0ZlUnRIanFLQkU2TlFva3ZGWVNBWEdBQXNGb1R5THlXLWJWelg2cFV4OUZJcGVCVEZRYWx6Nm83bEZIbUd1aXc5UHNHM2ZSbk0?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46019.75061342592</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Report: Raheem Sterling’s transfer preference revealed with January window fast approaching - chelsea.news</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9lMVQ2THhhMTFQdEN4cXJIekRrQW55blJnQzFzV3Qwc3Fuc19rbUVJTmdqWlNRMGw4eHQtYW1iRE03ZHByN2dWVVQzMGk0WVF6UjgzNHdsUlRPNW5YNEFkN1JCMk85RndRam5pZlFYMmJMOUw5TkxZ0gF8QVVfeXFMTmd1OGYtVW9CbV9xWHhBcTlscVJHUEdfVW5QVnFmVENFWFRrMmstNmpmQzN6MXRhNXh4Slp1MUlQOFd3bkE2aXdPTTV0d0R0Z3Bicm4tdHRSbU1fWVBZaXZhNXZhR2pWeXJja045THduellldEJLOXFyZFpJRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46019.72916666666</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>How “Emily in Paris” season 5 pays tribute to assistant director who died during filming - MSN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 18:46:24 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNbTlPMVotT29CeGV6WmZYN3dVN3NrNTJncnJxVHVQS0IyVWczT3hHYi16U0s3bTVoTmdnMEhIZThjUEgxWVdvcEZ5Z3lZUVJhNHlCUklaVl96X3FZRzg3a3F1THJOU1F0WUZOZG9RVlBHdk1qWTZZS09icGg2QzJpQWlzVS1aeHA4WFBDNk90TE1RcFR3TjZZQ0ZFcEk3aVQyMTVOTGtLOWtPbk9ycTZSbDdROGdQMmxRYkxrQ3Z6b05jVFdRSnowcnZmdUZHZGRjN2J4MEYyNW1qRFQ0YU9ZZE93?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46019.78222222222</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Bardot: from defending sheep to flirting with the far right - Dunya News</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 06:41:10 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWkFYT3pyYXNfZnBUN1VKVWEybEhGV0cwVmJLa0JxcUR1akJyRWg2R3h4VERxSUtGMnNpYVZQUG8tbFdidFh1bDZTREsyZG9sSUx5RHcwOThBSURyWGZ2YVQxVlBxSVR5ZTdwSEQ4NWpmQ2p5R3QtcGpCT3dvZmZyN2hyZ1R5Rno3RmY5RDAwVlB4MGxSUmtvUkhkZ1c2dm1EMU5ZNlh0ZV91SFN1dE9XbHg5dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46020.27858796297</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Disney Changes Spider-Man Ride After Just 3 Years of Operation - Inside the Magic</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 15:40:28 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9GUW9FN25JZnFwQVhEc2JKaUFqRXJtaDNreHF6bmFMLUdUZEpsOTVXTExVems3enBNd3lkWTU3YUctM3ljYWN5NmFvTmlXendOOUUzNjQ1SFNUbzFVMzY1WUxHREIwektwMDBWYW1ZNVNGTDdUZXZrMTR3?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46019.65310185185</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Young gun O’Sullivan shooting for the stars at Melton - NT News</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 04:13:54 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQcXJHNFExMzl3bWYxSFVfWVRGS2tpek93RThTTjRnVVpFRnEwelprbEhmaDNiRktrTGZ5eWdvanVSbllvRm94bG16aGFFejFFTDFCdk9lTVZ0b2RmNFhISk0xTWdYWUpyRVRTOEJSbFItN2FVZVlBQk1jSG8xNTZaYUQwTGZZaklfeHlITW5Bb20zTlQ4OHFodkZjbExGZFVrcDNMS3NQbm9xT3MwakEwMHNZdkw1YjgwRlhqTTN2MFdZZVhZRmZ5X3ZZN2wtRC0zS2EwRjF0YV80NmdEblN2MFhYSW5DMy0yZlhmaEVjZzEtZ053OUxyazBrQ0ZZWGl3dGRJNQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46020.17631944444</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dupont sparks explosion as Toulouse demolish La Rochelle - RFI</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 22:20:15 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUVVWeHU1WkpjSUpUelZrcGhkLWllWF85X1FKc2NNUnVGMFZoeDI2eWdDWExYXzMtMFg5WGJDeVpJdzMtOUtkOFp3emt4aGhKQUxLeDQ1Vnh0VXVTck5CU0RnMEVJbVRORHZXd2ZBSE1QekpnWFlGNUhyU3Z1MlJVdFp6T1d5aFZvamlEaHZNbk1vRDVNU25CZU9R?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46019.93072916667</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Suriname Man Goes on Stabbing Spree, Kills At Least 9 Including Children - Shocking Details Emerge - Times Now</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:57:54 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNLVQweFRaWVdNOERicVNvLWxTQllldHkyd1NKT2xkNWpIUnNnVEx5XzRoSWNtVUphdWxoUGV4dnE0aGxVSk9JdHg4OGVyam5OTVhqMTJIbTNySF9RVTFqRWx1Y3NZY3hJUUMyVmlsbW0zMlIxalN6ZWZXa2gwUENTcE85ejRsSUhpSFpxVktpbDNrTTU4RDhhdWVmV3hmdGxDdnZyS0dMSWE3aWN4ZjV3NVlHRUVFNmZfVzUwUk9FYV9tTkg5SGFKdXVjQlR5WTlMdnd6WEx0YmJtTDFBc0RRQ3owNmJ4N2lKaGJXeVd5Mmx4dTE4eXFzVTQxNE5MTGtscEZRUlJYREMzWldiM1RPVDBOaW1QQdIBmwJBVV95cUxPSU4zZWJBV3p3eks4N0puTkZtNE96UzB6cE1CanJRWUxpS2ZFc0tsQkVhdE9pRkpDc1ItR1dMMlhxdjM4RUJyUl81LTdzbXBpRnYwQkFKQnc5bFhpOW9qclQtQTRmOWNSMmJBa2tvV1EwNGl4VWpqV3cxRDAtWEtmXzRzeVFnbmRicjM2bV8weFdaUVhmbFNPb3h1dHdWVDJxNEdfR0ZzZUNjTDBiWUZ2TEdYV2RROFVobFUzQmdNbzlfdWhOUkRhaTIxS212VW5vaFFyelJPRnlFRXY1UGpFZVk1ZzcyQURxY2ZVdmZQLVZXNE9yQTZwMTVwVGh3aTQtVHU5ZEFQUHI5cy1jVElYdTZkeFRGQy1oOWxF?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46019.706875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bahram Beyzaie renowned Iranian director and member of the Oscars, dies at 87 - آسیانیوز ایران</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 19:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOelQ0V0k4ZU5IVlRIQXhwTlNKR01lU29BRHFxaDQ1UGZ3N0M1Y3loQTYyQ1NSNTVseUVwTGg1OFN5ajFDOTh5WElFazhpd1BTM0QyXzk3c1FidUxmZHppYU95bEVkRU5qUDBnbV9pSWVSVHFSd0NQeEtJeUZTUWQ3eDNFS3k?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46019.83263888889</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Gujarat Petrosynthese Limited (506858) Stock Rallies - Risk Management Strategies &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 18:27:43 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNM19HU3dLQXhIZ0o1cDk0MnVaY0o0SnU1RG95UGltV2dtcV95Tm9OMjdpTFhjY2E3a2lqZDRzRENZeHNSTWowWmZLNldybW8yRUozamNodHJZaW9pVkpFdmMzcThLb2pjOGx4ZjlxT1RhNlpnZWZtRlNWdUN1aUhFX2F0WnhaeXo1d0p4b2hrdXo?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46019.76924768519</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Guinea junta strongman headed for victory in presidential vote - The Manila Times</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNajJSNlZkSjc3RFhoMVFnSXZEU0VKRXNTVVl6SUlMMmJVQm00M0V2V3NFT2REUmF2Mkg2Y3REUldWLW9mUE9WWFdjT05sR0xjYjNJQVd0Zmt1WnV1Ums5a1BBakd5SENEcVBfcmZhbkhQZ3Q4RVdLY0VvWEFVbnQxZHNna2dKY2ViRk91NTNkQTNTY0xxeEdhWkpZNFdNb2ZmLVBjTU4tbmd0b3JTeTNudHhtMFo0bWlmX0xpVGxHZjRGYWwyMXBNVzU5V2poQdIBzgFBVV95cUxNajJSNlZkSjc3RFhoMVFnSXZEU0VKRXNTVVl6SUlMMmJVQm00M0V2V3NFT2REUmF2Mkg2Y3REUldWLW9mUE9WWFdjT05sR0xjYjNJQVd0Zmt1WnV1Ums5a1BBakd5SENEcVBfcmZhbkhQZ3Q4RVdLY0VvWEFVbnQxZHNna2dKY2ViRk91NTNkQTNTY0xxeEdhWkpZNFdNb2ZmLVBjTU4tbmd0b3JTeTNudHhtMFo0bWlmX0xpVGxHZjRGYWwyMXBNVzU5V2poQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46019.66875</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Options Data Show Bullish Bias in H.P. Cotton Textile Mills Limited - Sell Signals and Alerts &amp; High Yield Market Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 23:59:30 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQcE1BOHRZV2VPZTd3Y29xekdrcFFYMmFEOVRpUlY3b3oyWG9EclZkN25iUHZhVy1tbEpici12TFFHcjQ0U1gtM2I1bTY1aGZLd1lDUXBFVnBISlE0ZkJYcWpGMHJHVUNoenJwVTJKaHo4V0RuNzlwWGZCWThFNjJ5UUwxVV9Vb0NsdFprRGZ5YmFlZUttR1RDdVRXRkpSd3E1aWNCMg?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46019.99965277778</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Bulgaria adopts euro amid fear, uncertainty - The Manila Times</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPdzhnTGhNUDZVRHRvRlFNckhSN2Q3MzI5N2FNRmlsRUdybXh6a181NjJIV2s5Z0VHMGxzUndvMXdqOWFKeE00dmJGcm9uT1VMYXFDQXlqVUxCWWhaaWxiLXhiVkhfVndEY05jbzJBWHE5RzdiYXhYQjdYX0U3b0d3b1dtX3Q4U1c4akRHdjFjREpOSHhIeUtsN21XeEgtWVpwWngtUjVYT0dhWG1XbWRoVUMtWdIBswFBVV95cUxPdzhnTGhNUDZVRHRvRlFNckhSN2Q3MzI5N2FNRmlsRUdybXh6a181NjJIV2s5Z0VHMGxzUndvMXdqOWFKeE00dmJGcm9uT1VMYXFDQXlqVUxCWWhaaWxiLXhiVkhfVndEY05jbzJBWHE5RzdiYXhYQjdYX0U3b0d3b1dtX3Q4U1c4akRHdjFjREpOSHhIeUtsN21XeEgtWVpwWngtUjVYT0dhWG1XbWRoVUMtWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46019.66805555556</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tech billionaire Durov’s claim of fathering “hundreds” is a genetic time bomb experts warn - MSN</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 22:56:02 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNVGVFR0E4YkxKYkxBVGVYM2F5bVBKWEk2dFg3SEFqRWlHTTAyOFlsMFVzbHRVODlaUTlpY1lkWk9RdjhibFU5eXVpaGJ4dll2NHNtMkFPQ3ozTmZ4ZjYtS0o3YU8tdkFQZ1JBZzNzakpJc3JXaS1uU1prQU14VmVSOTh4dEZidklWMk1CbUhyS2xLYlk4VzNiYU92STFLcl9SU3ZyaHFFWmZhTlkyS2FGdnhvcWdCOXpOeFVxLV9ocEl4UzJhUkQ5b2k0TWZhTHpWRWdn?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46019.9555787037</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SITI Networks Limited’s Beta Climbs After Market Volatility - Technical Analysis Insights &amp; Reinvest for Maximum Compounding Returns - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 22:03:41 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTGJ5MjY0UTNZRkE4WHYwbDAwNEwtdUFEU3BnQzRZY1prenVxcE5VX3VibEtjSG9vaXRPWHhGRDdzY2Z4Q3Y5amFoczFwNzNza3p6SzU3bzhJU28zM1p0dm9QejRwcDY1QS1oUDRzVU1Od2hPZmxwcFo4SWNpelZ2TkRqOURveTlhZjlDbkxSWktxUXN6ZFBGVVZsRmg4TWxTN0NOaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46019.91922453704</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Macron welcomes coalition of the willing in January in Paris ᐉ Новини от Fakti.bg - World - fakti.bg</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 02:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRTVoNVpZd3JMZ2tacjY3eXo3V0I2aEVCX1pPaWRKWkRaT01qZXMwcXRaUjRLVGlvemF1SkJ5Y3NESE5yVTRKd0M0REUxcy1sdHpTRVhmSjJpaUMzc1FNVXlxeUV4UFhUdlp4eVBtY0dLdGFxTWJzSGp3QWg1ZHFOS0NfRlNZQm5WYlBWRmlLNHRXeXUzeFo3RF9LeFBFRTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46020.08819444444</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Bomb at the foundations of the EU: The France - Germany axis split into two pieces, relations Macron - Merz extremely frozen - bankingnews.gr</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 15:05:32 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxOWl9LelJROFRBcTFTYnpGQXBlYkdYTG1EYjJ6UVotZ0dTT0FZc1l1U1k3dFpyalQ1NlhYdkQ3SkE0cEVReFJndkxPRERNRmR2Y0g4ZjJ3S280TWRJLThMVWZKbFE0dXpoUFBjLXlJQTRhV3BtdUJyVFhfQ1lhVlZDV0tud2pkd1JIZjgwZmVyekpEMkdoSnQtLTZYTF9zYTVvcTU5RTdEbVY3SFU0NEd2dWdCSGZ1blNMdXJrb0F1YVA4OFU3S2tGZGh0RHN0NEZPSC05QVk4aXJiUmtNc0VvT1lHWXZndE4tSFhFMkVVU1V5aVBqdE9qUWk4a1FNeW5rYnZUUWUzRmxPX3dEWmJyblUxT0xGUUxFZlpwTw?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46019.6288425926</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>After the Flood season 2 unveils explosive first-look trailer as Sophie Rundle drama returns - Radio Times</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 20:27:19 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQM1luXzZ6dkxiTDNzbW5uV1FBeENERVQ3RnppMXJZT0NvQWVxSEVVM3I4a0lNUFQ3UWFwWEpwRy1rUlpNd0liQlR3ZUI5Ym1wTjVmcno0aU0weGcyQVJCLVQwMXBCMUNIUWlLTkdiUVl2YzEtMTZ3VGpCWGhKVGVtWUVsUVF4aGNUT3dzTG1lVktuTlRl?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46019.85230324074</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Shriram Properties Limited (543419) Expands into New Market - Earnings Forecast Updates &amp; Target Triple-Digit Stock Opportunities - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 02:19:56 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQVWhRUjEzaG9ud1JlUks2QXl3SW1TeXNRMmFzWWprU0liNDV2M0Rkekp1ZmV5dHJZVVZBR2luS3M5OFBBYkJnazBySVZGcmJ4XzVsdTl1czVHNWxnSnNTZV8ydGE2cW0ya3NTWko1cTVQY3hJZUVsUGlNOF93eDM1R1pYTW43SHAyMDk4WVpXMkdraG5fbVQ3MmotR1VRR2Q5OWdqSGlKdmhtQWtCT2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46020.09717592593</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Lee Kang-in Misses Ligue 1 Team of the Year - 조선일보</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:50:30 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNMnc3THBmWG5Mb295eTlJT2lkVlNiSXRuTGNjbkt1QXlOYnhHOXN4U1pUeC1qLTBVcmVIRlFjaFY5ZlNWbGdfbEFHNkNtaHF2STkwelNXSF9hUXVXTGxrUGNoMW81YlU1c1JsMy1WcGlZN09xQkoyZDRSSkVHUGpEZ3poQkItdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46019.70173611111</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ukraine peace deal close - Trump - PM News Nigeria</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 06:25:42 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBrOHQ4NEx1QU5UeE5XTDdDX1AtWTZOdUtHcEoxOU5La21Cd2pEdk9iX3RKeWxkN29oclV0dl9lSGpkV29YVV9jTjY1Z19aMjlQV1MtSzZMLXVHNVRoWjB0M0J5NlF0clB5aWRyNGd2T1N2SmRRUXB3WTZ5UXkwNm8?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46020.26784722223</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>10 spectacles à voir absolument en janvier 2026 - Le Bonbon</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 19:08:54 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQcFctaDlBNU5IX1pZSzF1Y3FaZ09HOWF2dllaenR4RVV3RldBX0R6WE9jaDBKX0N0LXZmS0d3ZG1Fd0t0QVQ1TFE3aUVDbkhjR2RzOFpGVENLVVBMOTdGNVZBdHlGWllNXzVvRDNnSllyQ3lVRDZqd1RUcEwtM3psVW13OUFiLXBBMXJVU3Bodw?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46019.79784722222</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Vedant Fashions Limited (MANYAVAR) Expands into New Market - Day Trading Setups &amp; High Profit Trading Plans - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 04:51:44 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPY2ZSclpiLVhVdzZ2ZUJmSXEtMDFpcV9DYmc0eC1iY0pCMXl6NV8yNl9lOWVUUHRONlVOQ2dvaVBiQ2lEQzJDcjh0MFNBM1VkTEV5cXFFZDZaYVhNRnNWWUJFWDByaHdja3FpRGNfLWJzNG1DaGhTR24wbU9PQlljRU5fVDNsWUV3QUlzbkY5ZXVkZ2FxQWk1YmoyelpSRk41LXVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46020.20259259259</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Short Interest Drops in Vardhman Textiles Limited After Rally - Financial Sector Performance &amp; Explosive Capital Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 00:35:04 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMXRVZS1xVHFmMGFUcDg5N09LYW1hUmpTVzBVWWFIcXUxT2xrdnB0WVd5cW9DU0ZmNURxNk9iT0o3TVo0bk00UXJDOXN4LV9JNkFwdWc2NHhBcHVhenVUSHZVNXJPMzhsUlZmZFJwbDh5VGF0UUk2ZXd3c1BNMEVoM3phSXFObldYWENLSFBUSnBvV3RIYi1fQnVmNjc?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46020.02435185185</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Kapston Services Limited Stock Lags Behind Sector Benchmarks - Healthcare Stock Analysis &amp; Outstanding Profit Strategies - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:58:35 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQRHZlMm9BMnBDWEIzc2VDcDBVTGM3dEUxLWFXX1FOWjJvOGhheGRxR2l5RmwydkNtWkFaWmgtLTNRdlVYQkJpYWNPbEdPbEhqRkdjR05IWGQwVVoxRTl6QjJwLS00RkpweFM4ZVltaGlTMVUwZFItbDE0eG9mWmdqQ2Y1RHpaYVFOanJzamI1R0tUSnkwei1Fa2JWaV9QTThHMmlOMlJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46019.70734953704</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Is Rajesh Power Services Limited Forming a Bottom Pattern - Stock Liquidity Analysis &amp; Market Crushing Stock Picks - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 22:59:40 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPYVNjbU5YNXpMY0FBdGZWZDBRd2c4ZWd3aTFkeXIyWGVtSzFkM1VlSUlUTXhYX0RJb1Zod2U3SHppX3JnbXNnUlNOTjlOVUdSNVZoMnJyWGhNY1VYWXY3aGR1RlJSd1NEYzFzSzFFWldydXUzb0NQa1ZGMy1BVllmUTBOc3NUcWR2eW5NaWxsTHJpb1pwQlZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46019.95810185185</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Thomas Cook (India) Limited Recovers — But Is It Sustainable - Dividend Stock Watch &amp; Explosive Profit Potential - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:48:44 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOT216WWZwQkpyQk51R2R1QThkbWM4ejJHeGJsbXhSNnhVamVtWDV6YThZMmViR2h3Z2xsa2hjLTFJVkE1Ynp2SDVxVHE4US1LSGJjdGtrWHZwaUFYUlpBOU5wd2toUkNuZno3NW9qR29YdW9SbG5GOXNWSTVEYXk0RnJnQ3NmaU5wUHJ5Rjl1ZUMtNDZ5a0VpWW9TVlNsNUo0Y3VEeGYzSkg4WmE2LVo2ZmRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46019.74217592592</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Oklahoma man doing target practice in back yard charged in fatal shooting of neighbor - The Guardian</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWE1lajNQQ3Nqb29oVUUxN0l1cFU1WHlUR1c3cEhpZjNicG90UmMyR3ItcFdwamZydmo2b3ppZ1BtNkJiVldrSDE1ZGlaYjh0bGRPLWtXVFZ6X0pDdTBrSk1FZllIbDhFS3JoV0lHV1lNVl84aGZhYXByQ1J5UUVzc0NsYnNDUnJ1dDFXQjh0dU9KcVcwWTluZ256c0g4SXl3LUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46019.72430555556</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Baltimore Police investigate fatal shooting in Federal Hill - The Baltimore Banner</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 23:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZkdXVkNGQm1LS1VFLXRlSWt4S3pUTVB5MXZRWlhxbGRCelJtNURPaWEwZWZlckljbmt1ODRqQ1FXWUZtakhya2lfTXp0NEc4X2FQMlBKc3U1WTFobGM2UGRJSDFoeENWRUIxeEhzRmhHaU5nN3haVW03bG8yV1AwQjlLbTRkeVhUa1Mtb0I4VkEtM3FIWlJNS2dScUVFN3FqNWl2dVY3T0hpS3JvdThtbkI0SVE4bHVlV2JsWnRsZklQY01MQ3ZCNDFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46019.97291666667</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Player ratings: Milan 3-0 Verona – Pulisic and Nkunku get the job done - Football Italia</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 14:33:12 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOYlRJNUwtZnY1VTRCRVVuM1dKRzVQd0VCZ3dmOGZHUXBqdlYxVm95cFhWLThMNG5ueUhBNU9kY203djZtak5DSzJldllJTGFwckdzUWwtdVl3NlVmSkU1T3Nsc01rRXhnOVBXZjBhVm5td2VPWW51S0VfUUdjWDN3b3JsUHRDQdIBhgFBVV95cUxOYlRJNUwtZnY1VTRCRVVuM1dKRzVQd0VCZ3dmOGZHUXBqdlYxVm95cFhWLThMNG5ueUhBNU9kY203djZtak5DSzJldllJTGFwckdzUWwtdVl3NlVmSkU1T3Nsc01rRXhnOVBXZjBhVm5td2VPWW51S0VfUUdjWDN3b3JsUHRDQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46019.60638888889</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Pulisic ends 2025 with a goal for AC Milan. He’s hoping for more with US at home World Cup in 2026 - FOX 56 News</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:05:24 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPbFRDMUVIdmpqRlhtWUJ4bWdHYjBEYjFBUlpaWVloNE0yaVhibjd4OUJnbEpmYWJVUEp3VVVUQnROV0dtUUJuNjE1a2t3anZIOEZ0N0NzVk42WW5oUUVBRURINktLYUVzYWhxdlExQWNkX2pnWEt5eUlTS2QwRGlwbVR6UWt2ekV3Z08zejNBMllKNVJwMjhobVZqOHRwS21rS3Vhd0s3bEM3R09UX2NpeFFDWWtWemV2NVFoMmoyd0hkY0pxblh5dzR1bVQ1SkM1QjBNNWJjcHnSAd4BQVVfeXFMTU1TT2UwWHBpaGVpLVJCaXBmeHE5eC1Ic1V2RUZQRmZIVmxINkRzdDdnNnU5MmZFWl9iNEpta0xuSWtSYWF4UjlOb2RDckQ0bnVfQnp5ZEFzeVRjNTI2T3JMeDY5Vy1PMmlnVGdoTGZ2TnB2TzVDaFNEZHRhSXV6QkhnMUNLYnVlbnROX2JYQ0plWTR0bnhHVU5tazFjU0FPWW95ai1iSUhFX1RVVGNyekxiX0czUkNId0hRcTd4LTk0dE9KOWxRY1I1c3p6dXNUWUlOUDRXVW1vX1FpZGZR?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46019.67041666667</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ADC Spokesman Knocks Tinubu Over Europe Trip - The Whistler Newspaper</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 20:06:03 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE00LUxLWkpGOXZCeURLQXBoOEF6R2s3RUR4YXMxTlYxbGNQVVBFUTN5dzQ0ZFpUb05sQmdOcFZsMnF6YTBqekJ2SHR1aXlROVBUZXUzRUV4X1NVbGdSZWlwTDR2MnB0bnoxbnNSdjNfMW5CMjNiXzFJ0gF8QVVfeXFMTlZLLUp4N1dwdUdtUEhhc0syTk01VW91TnZyR1BNYVh3S3MxMU1MenpTN3NlQnNZTlA5enZBVmE1ZmNVRzdwT3hxRS1IVlYzSXNxWE5HS19OakdBdi1lUHRXM21NOGVGZmNxWVVwZF9ScFNfYjN2enhnd3hqbg?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46019.83753472222</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Pulisic angrily hits out at ‘made up stories’ about dating Sydney Sweeney - Football Italia</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:56:01 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNa1lQTEFHQWtFcEZCRS1OMXREa0JkMmZfekV0dWdvVjljZzdTR1ZzeVRhMDZCcnFCRUtSRkU4NFpEa2RkMlB6SDJlblM5Y0xWbXhZbU1RckZMZlZJbDNmOEJncUt3RjFrcWgtb3FKaUpZWUZiOXl2Y3VCdDE0dkxvdUlySdIBgwFBVV95cUxNa1lQTEFHQWtFcEZCRS1OMXREa0JkMmZfekV0dWdvVjljZzdTR1ZzeVRhMDZCcnFCRUtSRkU4NFpEa2RkMlB6SDJlblM5Y0xWbXhZbU1RckZMZlZJbDNmOEJncUt3RjFrcWgtb3FKaUpZWUZiOXl2Y3VCdDE0dkxvdUlySQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46019.70556712963</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ragin' Cajuns make it two in a row with holiday win over Norfolk State - The Advocate</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 22:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPXzg5WlFKdGN3a2lMNHVFZHREM2xTYXdtbGNxSnp2WVhwaEFucTEwMURocUFQV2pGZDEyQ0dBMFdsZnk0Tjg0cjJFSnF3YkJIdkVYeTk4bEVDWF9hRVQ2WHItYkZ0VnJmZHpXVC1qR0YwZS11a184UWZnbGFXTFphVDNFNFVRSW5lZ1ViTGotMWxuTlBfVk1jaWk4cmhiREtfZHphWXVRdkF4cnp1eDUtQno2M2RpeFltSlJKLVhVLUFqb3NJRnRTWi1NZDJqSjBjT0hONzg3NXFfYkRFMW95R2o1VFdoR3RxdUYwXw?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46019.94791666666</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Jay Idzes Demonstrates Resilience in 1-1 Serie A Draw Between Bologna and Sassuolo - Semana.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 20:02:44 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxPNVRTNV9tNXN0SDJtTTVhOWx5Smk5d0dhTXYxN2N0UC1mSU9Gbi16alE2WlRHUUNYMW1LOW9CTndtTWVFVWRmcmlHcjFzQmg5djMwcWdHcl9ReEV4OWZCRDdEWW40MzVkd3BBbzdaT1lCQW1fQkxFaUwzNkNTTWltQTFyRFJpek1MUFIzSHk1QV96T1g1MDIzRHNybFJJeldPOU5EemtmVHpXZ3R5OEZhUDlNNWVKRlpkX3VDVVVuaUFQa0puc0dqRng2UzFjeUNlX2VXSGJpOTVIbi1oQzRXd3UtRHZEbzc3MzVOcXU2N1p2Y1lFVDRjVmh0aGdBNE5DRGphMWVhempBbHA0b1hlbzIyVGZJNTh5Y3FzUlFWNHVqZnF5?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46019.83523148148</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mumbai Crime: Vile Parle Man Booked For Assaulting BMC Officer During Poll Duty - Free Press Journal</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 04:53:34 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPanFLYjVzY1Atd3JLazZwRVBHYWFNSDgzWXpBbHBPN21jZTY1Vkh4YVFxZUtBMnRmMTdSWHgyRW1TbjhCOVBfQWFSLTc0SmJ0Y3daUlZwYWlNQ1dvRTJzcG1zR1NSTm9xUHkzRWlpcnFZbElUd3FqSDlzUnk1VVlQM2R4aDA1c1VhWjNPMmV6UTg0SzRKMmRoVmNCS3NyUzlDcWFpNkt6RTVnTkMwX0JTR3g0UUJNdV9G0gG-AUFVX3lxTFA0SHAxMElPSzVyUlU1TlF2YlMwSUxYN2ZzdGhud0ZrR1dOYk1PZF9qQW53SS0yMUxoUlpXZkR1S0dYZnhRWkxWTUlYUHh6RENqT2NmUDFnVzRBa1Rtb1hGbU1SQ0hLcnhCZk9ta0FOeUg0UUFWZEV6TWlPcnVHYzBJUGwxQmxhbE14OG5CWXRqbGFDRUNOSFhHMThid21BTEQ2eWJZaS1rS2l6UFVYT3JwZDg0b0dGNFNWWnFCd0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46020.20386574074</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>What happened overnight? Police blotter report for Sunday, December 28 - Newzjunky</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 12:00:29 GMT</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNVVMxZXVrVldLZW4yM0gtSmMtaFF3ZHdDVGZaUmhGYjlJUTBsWTlpaWFTMmh6MnFhWWZRWW9oY1cteG5mQ2VORUFiWTNkcTQ0T3hxMnY1REo1NjlHal82ajBDTlY5dkUyd3I4eWg0Ynhkd1hmTjVXNWNNdVhUaHdYVVR3?oc=5</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>46019.50033564815</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dutch police deploy drones near Belgian border to curb illegal fireworks - belganewsagency.eu</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPNzhLYUN0U0Qxb0UxbWpFaEp3a1RDX3VIa1pEcEZVTC1tS2d6dzRDWHRyOTlyUk5ZT1M4MEZyQ3VKVHg3Q0xrY3pZOEgzaG5lMGZrYWVOc0t4em5LSnNGQ3YtQlRVUmpmcm80WXJpUG9xcXBBVFlwWmVGN0xNckZlZXlLZkRfYXg3bnphbzlQUUF0T3pUaUE4bXNJWjAwYm1MQVIydVJR?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46019.71666666667</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2025 in protests: How unrests and clashes shaped the year - AnewZ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNWXFVYkhjdjBNRGM2cGZ3U1FaZWxRaHg3aDY1MksxTDR4dWhZeWN0a0NTXzRjc0tKeWpQcm1MY0dCTldUeGp3SkVhVS1HRzFESEdNaVFWZ2tmSXNxVHpuckN1RlY1THNkUlQ0WllpQlQtckJqcGxuMWowUDlUVS1IWGhMdERXSTlVWkEtU0J5bzhublQwNTQyVzVQZGlUem55RFZJdFVBVWEydFpfLXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46019.71944444445</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>India clears three new airlines to boost competition after IndiGo disruptions - Aviation24.be</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 15:35:58 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRW5OSlZrUTZkS1ZIeUd0amhVa2h0NXVTTXlzU0lSV2JVNjdnbDBYN09fS2o4cGtqZmptd2JELWpnYjVVZjFmdklwWDJMWkFLUkVBTUZjS25nMTRQZm5jZURvX000T1JqVWdCSktuM243bXFYY0w5RHEtOGpPYmd3dTZUOG0wX3dLU0dGQWlGcEl4cklPQjUxUTNrZnlSZ1MxNVpBNFhlM09RRWw4ellQSzFmeFgxS285Wk5KRnFwVGpXZi1UZTNV0gHHAUFVX3lxTFBFbk5KVmtRNmRLVkh5R3RqaFVraHQ1dVNNeXNTSVJXYlU2N2dsMFg3T19Lajhwa2pmam13YkQtamdiNVVmMWZ2SXBYMkxaQUtSRUFNRmNLbmcxNFBmbmNlRG9fTTRPUmpVZ0JKS24zbjdtcVhjTDlEcS04ak9iZ3d1NlQ4bTBfd0tTR0ZBaUZwSXhySU9CNTFRM2tmeVJnUzE1WkE0WGUzT1FFbDh6WVBLMWZ4WDFLbzlaTkpGcXBUaldmLVRlM1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46019.64997685186</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US bans ex-EU commissioner, others over social media rules - The Business Standard</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 21:44:20 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbEdhcXdpYmd4cXREZ0V4M0hYNjRNeERQcnBrNGc5Uldmd2pYWjFtY1ZidkZkMktUYVJZSEZvUGhCdGtPc1V1OHFrclJaRGw2MktRSUNBTFdzaHRXX080SkQzeVBEczRlekR5aGJ6cUw4cTlSVEMtbWYtdXk0XzNGeV9qUXU0MWR4blRNQklJMEZBNERHN2ZtQVVRSdIBoAFBVV95cUxNNUo2cjl5MExFOHowVFU5RnVQM3EzcFd3eXZxU3FzZU03ckhjZ2gyeU9ROVI3c0ZoUURTZVM5Y1plbjVVVzZtQ1ZoVUk2Nll1VVlfVUJlX2kwVnc2WGtlTk9DVWtfLWpHQjdPc3BhcjRpMHowM1laMXpzVVdUU0FDN2k0enR4VEwxWDRvUnN4MzFLOVNnQ2dRY1lubG9JTW1Y?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46019.90578703704</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Brussels’ Drug Consumption Rooms: A Dangerous Surrender to Addiction - The European Times News</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 16:33:01 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMlR1TWVVRWpwbE8wODN5MlNqRndCVlpiZWM2OV9SYVFzcm5ibGh4eGUzaEF1M2YwYzJpa3NMNmxlbnpxaWFqc2JZa3JPWGFBU1dUR2duSmpHMzBRUFVIMHJqRlBhcjluVU1wZUFPdHBSSFNGZk56aEVCM3V3bVBJWkExSWhlVjViaHF5MHBuYUFseDhHWjllQzBrclJ5WHBPdERMUw?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46019.68959490741</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ice Storm Warning Issued - WWNY</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 22:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9xR1pqc1AtZ2NHMFV0M2xOemYzLWtjdzVZM3J3a2NKVnk4a3VzaVkzWEs5M3dtRDNGXzlIUENoSzRtWkVwWW90MWY0OHJKVmk2b3JfaUhYRmxRM1Zvazlmc19zMTI0eExfMXVqMHZGVnJJaFNsYzlNZ3ZFQ2ViN2_SAX9BVV95cUxPcUdaanNQLWdjRzBVdDNsTnpmMy1rY3c1WTNyd2tjSlZ5OGt1c2lZM1hLOTN3bUQzRl85SFBDaEs0bVpFcFlvdDFmNDhySlZpNm9yX2lIWEZsUTNWb2s5ZnNfczEyNHhMXzF1ajB2RlZySWhTbGM5TWd2RUNlYjdv?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46019.95763888889</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HRA: Committee supports amendments to the Law on Internal Affairs, despite announcements that it will await the EC's opinion - vijesti.me</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 15:23:35 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQYnA0SXpSdC1pMjB1TlNxOHpmZFBTOFh1WHljVTZ6Q0VrZEdYc2lWaklfU21id2RWaHVXQi1OcDRLVWRXNHhwYWIzc2RhR21PTUw5dWJNbXlPV3kyYXQtMGVwMGdsYnNEalBQdzB6Y2k1ZHZHSkpiYW9DLVFqVHVKTHpMckYzZVpfdUo2MXY4dVBMV2hmNU1mRU9rcDhIeHhRWnFJRFQ3VEZSNnVoQU1ZSU1YdjZ1VTg5ZTJpZHRoNHpQSHJSblZEMUx5UXMxMWx1dGZyVW1DM0ZGWTVRMXJ4OFd1aUpNTFVsQ3JfZ0FjcWTSAfABQVVfeXFMUGJwNEl6UnQtaTIwdU5TcTh6ZmRQUzhYdVh5Y1U2ekNFa2RHWHNpVmpJX1NtYndkVmh1V0ItTnA0S1VkVzR4cGFiM3NkYUdtT01MOXViTW15T1d5MmF0LTBlcDBnbGJzRGpQUHcwemNpNWR2R0pKYmFvQy1RalR1Skx6THJGM2VaX3VKNjF2OHVQTFdoZjVNZkVPa3A4SHh4UVpxSURUN1RGUjZ1aEFNWUlNWHY2dVU4OWUyaWR0aDR6UEhyUm5WRDFMeVFzMTFsdXRmclVtQzNGRlk1UTFyeDhXdWlKTUxVbENyX2dBY3Fk?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46019.64137731482</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Crosskeys earn win in festive derby over Newbridge - South Wales Argus</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 23:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPeWJ4SHIyZlpESmx1M25GT08wVFlVTzFyUEFRQXBjNUlBdkNTVVJxUlFnUEN1YmFPcHl2V05tLVZJQnhPRzEzXy1FalZyYVIyRk1vR2wyMUx5d2ZKMkpsSFowMDA5WWg2SEhZazRmVXpSQkZWXzRSQzNFd3FIU0RreUtCaUh0d2k4QW01YmZERERyRlFPUnRST21FZXQwUHItYVI1Sw?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46019.97916666666</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New Era and Polo Ralph Lauren Reveal a Triple Collaboration With MLB - hypebeast.com</t>
+          <t>Audio Amplifier Testing with an Oscilloscope: Roberto Armani on Square Waves and Bode Plots - Elektor Magazine</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:16:42 GMT</t>
+          <t>Mon, 29 Dec 2025 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNWDVrZTNJV1MtX3BhRVltQV84UjBmUDVFLXh1QjVfRVRtallndVZmY08yWDdFWXpWTHhUWS1pRGNxSjZ2Z3lTY2ROQWxVNThmYV9GT0VTU2pWQkVjeGJta3RNa3E1dFNyeWZBRURYZ2N1LTh0T0pfc0l0SEExOE1HWjFGS0s4VkZ0ZVduVGJWa2NYQVRUMV9lLVFhTzdRdllFUndLZThxOFltcGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9jQXI0ZlI2N2x4VFUycDJvdElaMG5mTHc4czZfQVEyYTB6bWplbnFYa0V2TENaLVp3WXV5MnpGY2FyOVJKTEwyQ2x5aVU1eVAwQS1Ydm1oeTdzLS1CeHJZaW1yc3pPOXdQbDduQg?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46020.26159722222</v>
+        <v>46020.5</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'Comfortable' Calvin Klein boxers that 'look good' now £26 for three in Amazon sale - Birmingham Live</t>
+          <t>Dior Beauty hits update on Addict franchise - Luxury Daily</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:41:00 GMT</t>
+          <t>Mon, 29 Dec 2025 13:25:50 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQblF2Q2ZobzZrR3ZmWkdZSVZvWWMzZ1BCdURwRmR5MVk3Z1IweWVxV3Q3aGo2dFE3SmRoYkZZcldGZkhIeEFidWNWdGVWMkRVaWo3ZlJkOHBTSzVyZnZrWlNyQmVYNnE5UC14NWNONGxYSnJ4NVZEckd2V2FuM2N4N2E0ZTIyb29Qd2lPUnBEQmE0UWcyM0xSQWdmai3SAaIBQVVfeXFMTzlucUV5SEl3dWpBRHV4N2tDNC1KNVQ2QUxHNEVRODl3emZTV25IbkNGUUlSQy11dmlLaGp6c2U3ZHRsVXlkLThleFF4TDFQc3B1WjRPaUVZZGRpcGViSUNWLXFfb00wOVl1WHF5OG83Sk9wVFdTVjhEYWVweUoyX3pQUnNWOE1mMHhiaE9hdF9CQkR0S2h2WlF6Zm1kLUZhVFdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9ZT0Y1aHBRYXROTFFFMzRiNjJKWTdibklXdC04cnlzaGphRUJIcTFndm1YbFpUWEtJREw0TFpLNENoR0U1U1dJRTh0Qnd1TmJla01KdzZMZWdCM3c4LWM1Rjh2V25DQVRWaXA5Q0JDWXZPYUdBcHFHUGJrd2Y?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46019.73680555556</v>
+        <v>46020.55960648148</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Valentino Rossi's next move for Pedro Acosta could arrive at 'any moment' amid VR46 revelation - motogpnews.com</t>
+          <t>How Après-Ski Style Became One of Fashion's Most Enduring Trends - W Magazine</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 15:00:00 GMT</t>
+          <t>Mon, 29 Dec 2025 13:00:25 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOd05tTUNhQWl2Q1VQSkNjOTRhckI3T0JveVM3SUJCUVhWbGZaX2ZtY3dKS0JZZ0JoQnhsUkMxMkdLY09GUlIyX3RDaktoYjZzWGhOeVl1VFA2TUlMaHREOVo1emMyX0dBc24tNFF3UzBkZzZyUWg1NzAwOEhzd0VpaW96WUJIRmxQX0stQy1TMGN1VEN3YlJiN0tvUV9KRDdzYm9zd0g2U2o4VlVvckpRd05xZ3l6elhBZWdPWjIwMmpldGt6WmpjcV9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5kUGpBblRmRzdncWdMVDdXOVVvNlhWX0JNeF9wNklrVURvU1VsT0tTaUdrWUd6cjY4UkZsdU96UmRoNTNfRGlEVUxBeWQwYm42b1lOWEFxYUFqZXVXdExueGlqZ0gwanNFNXozekx5ZmZrZVQzcEhYMEdB?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46019.625</v>
+        <v>46020.54195601852</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Best Royal Jewels of 2025: #6 (A Royal Tiara Takeover in London’s Galleries) - The Court Jeweller</t>
+          <t>The Fortunate Ones - V Magazine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:00:50 GMT</t>
+          <t>Mon, 29 Dec 2025 13:00:00 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNc1lOdzhRcjBQODhBWWxqQ2VlUnllbGl0RXB4bTVZQ1BnbHNPVFJBeHRCY1Y1WkdSZEVIMG1tMnFKeUNHOUlGRzE4QjF3ZlUyNXJYWmo3R2g5cUZnNVJ2VzNub2U5RFAwNHd4Sml3cTM2aTRNbHQzRTI5ZDVqSUZISzd4am83RmZycFBwMmlqLXBmbEI0M0N1b1dySjlWdGZ2dkNJbXdROVNkeXZBbEJGajVIV1pvSS1PR3o4Y0pn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1hMVhKX1dUaGVncV9PV3g4OURCZV83VkZsTi1VcE9xSDIyU1NWNEk2eE5mZndzQzVEWk92SGZocDlvY2ZFLWN6TlJ1c2wwQTBHSWs0MzZHa2VOamJuZlE?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46020.2505787037</v>
+        <v>46020.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -614,123 +614,123 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>I thought he said 'I love you' - then came the brutal clarification - Metro.co.uk</t>
+          <t>Kylie Jenner Flaunts $57K Cartier Jewelry for Christmas Celebrations - theFashionSpot</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 15:00:00 GMT</t>
+          <t>Mon, 29 Dec 2025 10:33:34 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNSkpnVzJ5Q2xmWDRjNU5NWklyamZNcVZCOGhTNHRvZ3F2TkZTeS1SLWRtcUp3OVNBbGt4WWZjQl9wYjZxeFhVSlJCaU80UEpoako3NVNYNjljNnFmU1RLbWZWUDFWZlVlVUxkUnIxU1hudjZxM1BReWU1T19kWHVJY1pHSkFkeEJLRl9Nd3Jyb3d2MUxt0gGaAUFVX3lxTE9LX0xFREhTWmNzN3FTU1FqQmFkdERVYnlJT0lCeElER3hWNnFTVXNRbnRfS1FxMURCWklfN01ZYW5XMmJpZ1ZjaUR4RXQ3ZEctQ1VMZmsybzRoMlIxSGZpNHNZQzI5clpqdzFMQkMxeF8zNnVuUzRsaDV3aGhDU2QwMXVkcndXTjRPaXVBbG9LMUtfemVMRE9sZ1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQUkxmTlpZQXpLT0M5X3ZlcG9sV3VYWG82OXpBaWFNLV92cjZZMWJkR1lZR184VngxcEJJYWd6WHlkWUhpNnRVWFBLZkNtSFVYenNHRC1KMWc4b0l4VFgwVjNkdGh0QjNybU1vNDhTZGh1NGJJUnBpMmtBUllYNGFTZ25La3FvNzJGNkxWSkI2TUR1ZGFSWGs3clc3c1pFZmlnSGlZQ3NSdG9FcC1qQUhOWldiWEfSAboBQVVfeXFMTzd2T1dhM0JOdVI5bWNNTjZ5RUVPS01jdlAyVnlXZnM5ZGdzVy1lci1TZGtncnBWTHlhUDNzR0JPd29RM0pIbUtsbkthM3lHbW5pQTRvZUN6b2hDX0t6NllnWjlIVnZrZlhVS1YwWTUxSDF3ZzB1LVd2cU9aUWltV1lVYUtlSmlybjQ5WTczcWpJSjU0cFpQel82bVdCQ0wyMzA5MkNGdGlQSmtGQ1RzaFN2YzJJd0N0VGR3?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46019.625</v>
+        <v>46020.43997685185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>London Marylebone</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("marylebone station" OR "london Marylebone") AND ("incident" OR "delay" OR "closed" OR "delays" OR "protest" OR "boycott" OR "bomb" OR "Bomb threat" OR "shooting" OR "explosion" OR "stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Why Fans Think Timothée Chalamet Gifted Kylie Jenner $60,000 Worth of Cartier Jewelry for Christmas - Marie Claire</t>
+          <t>One dead after incident on Oxford-bound train - Herald Series</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 19:44:41 GMT</t>
+          <t>Mon, 29 Dec 2025 10:23:29 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQSW1YY0VtVzNEZzNrQW5GWXAzc3ZldVZ1OGNOdmZJa0NUcWZpZWVYRC1VT0hEM21NQ2xLdlNpSkdmSVduT2pMTFI3QU93YXQ0TldSNG5KNGpjX3kxZENhTmlwQmFpeS01VERERXR0b2ROUENCOGF4WTJpMUpGX0Vfd3BOSVN4eUl6MnB2a1VTM0ZtWHBwR0tRcDcwWWVhRUlwdS0xVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQdkgwd1RwTFQ1U2Z4aml0RndTSUhPOU1kemxBaFU5UXJDZFdYanRSb2NGS1RFbk5OTjZLcVBMQlBXZUl2UjhKMURFelk3Qm8tMFFySFpCU3RkVWppVHQ1dkpKMFdvTEFmZ2Z2THlScGc4ZVV0alRyczNtRlA4MEJZMDVzS2FJclVya2RaSWY1UU54R2tPRFVBeC1n?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46019.82269675926</v>
+        <v>46020.43297453703</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cost of the Holidays: Is it easier for Londoners? - Digital Journal</t>
+          <t>Delivery start-ups finally get the K-shaped economy they need - Financial Times</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 22:08:23 GMT</t>
+          <t>Mon, 29 Dec 2025 13:11:13 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQYTRLWG1wSFREc2tsOVJrYV9xM2ZlZFZ1LUhhd3ZZYlBQZVh1aC1PdGhCOU5TZmI2bEZVZzJZa0tDM0JxOG9wNGtkNUxTNEJMRU9rWXE4N1dmQXIza0J4NGZZVGtfeEM0Wi1PaldKeUwtbEdqaDNEdFN1OWhaSjBOY2lnbF9SbHN1R1ctZ1RMRjRwbkFH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE91c3FzS2xxVnMyYThndTl0UzRLT2k1S3RxYnhFTGppY2NNLVRMX090WWhuWjFXY0V6X0NXU0dac1ptcWJ5YkRlV280RnFKNlJWZFBDd1dXS09ib0g0d2RLaTlkMDBROFlMcFZiNnRLVUI?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46019.92248842592</v>
+        <v>46020.54945601852</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brand search Google News and X - PROTEST</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Louis Vuitton enters beauty scene, selling out $95 lipstick - Rolling Out</t>
+          <t>Amazon shelves commercial drone delivery roll-out in Italy after review - Retail Insight Network</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:45:27 GMT</t>
+          <t>Mon, 29 Dec 2025 12:29:10 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFB4WGxfWkZQN05UeU5ZRUkzSW9MMkx2Zmc0a2tOd1hXYW8tM1VBcWlfMGlfWERvSDJpeDZweVNLNzRrSlprelhqNTFOdDVFa2hFcmZDYUJtZGVUcHFENm50bUhYeDlwQkZzMjNWRkVEUHBJME9jT2N5Vg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSHFhQWh6b0pmb3JYaHF2S0k1TmgzWUdvNndudGE1bEpjRmp1WnNDd2JnTnZTV1pUMjlldXNhVFktT29UdEpodmhVWFpURVRLdFlGclhYdjJRaWZwZ2dkd3IxYUQ4VlZPYkxEQTFYaGxrRlJDX1VQX0hadnpkazNxamk2SzR2eEdkWDZEQlFn?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46019.73989583334</v>
+        <v>46020.52025462963</v>
       </c>
     </row>
     <row r="10">
@@ -746,24 +746,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Here's how to quickly tell if your Amazon order will arrive by Christmas - AOL.com</t>
+          <t>Siemens Mobility signs contract with DHL Supply Chain - Logistics Manager</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:04:06 GMT</t>
+          <t>Mon, 29 Dec 2025 09:06:45 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOVFZNYXZDbmZpaWljejRYMGJ0MFBhck51SmNKWTVqSDE1X2RLSmtOazN1cVg4YTJ1VkppdFQ5TFp1ckl4TERTbTRaOFlOLW5TMk04YTBSSWZ6YS14X3dVUVdNQ3RCVmZmTG91ampocW84NzdtcUdQbDh4XzBMSDZXVVo1QTRuelFMeGNOajBQNlotWDE3ZWwwUWxxN2RoUy1SWk1Qc0V5dGVuVFdlT2UyajZ6Zklaa0VQbmpLTU1vYXRpNGRpWGpmR3h5cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNVi1yNHQ0YjZYZkVLdFBNcElsaXBva3h3TVJQTGlRT0puRXVWQjFoYVQwQXF3MmpXMFhrZ1BUWTdHcDhCaVhjZjA3WmFJNlJOUTlyUnFUNTZ6UmoxSUVoMUVkWmVDM2w0VV9UbTV5Znp6eG5tR08wU1YtanZOOEFnTWZtSTNmcDlzeDdod251TDY?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46020.25284722223</v>
+        <v>46020.3796875</v>
       </c>
     </row>
     <row r="11">
@@ -779,24 +779,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amazon halts plans for drone delivery in Italy - Trending Now Infrastructure</t>
+          <t>Here's how to quickly tell if your Amazon order will arrive by Christmas - AOL.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 14:55:44 GMT</t>
+          <t>Mon, 29 Dec 2025 10:27:54 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxOQ09RYWhSUjJXYmRGZkp1aXEtbnk5OWhaY0pNdXZzY1hwSjJGYzlNbTAwVXl2V1ZudjM2OVdOamJRMzMxeXdzRkFqRWJrbW16X0wtakVTc0ZXUXpPSDF0RDdEYXpCeFQ0UWZ5bktOZG5qUmo1V0x2U0N1bEVkeGg3LWdnX1B6OGhJZHA1VzN4bFZLdXJMUmltQk9NeHlrUHN0eXpPdTF2N0dfbWFCaEtqTFFIUzhvVlpVR1BqSzF4TjNSeEtVWm9ZTGtqX2VQaXNtdUthZjh6cnNobk5tU01fWjRCcDcwZ1RqeWhKeVJYNU9oUlREbnlZNUMtV0tISUx6a1ZrNnhJSC1CRHdxX1F3a3NPWjRrZGFHM0RDS2JB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOVFZNYXZDbmZpaWljejRYMGJ0MFBhck51SmNKWTVqSDE1X2RLSmtOazN1cVg4YTJ1VkppdFQ5TFp1ckl4TERTbTRaOFlOLW5TMk04YTBSSWZ6YS14X3dVUVdNQ3RCVmZmTG91ampocW84NzdtcUdQbDh4XzBMSDZXVVo1QTRuelFMeGNOajBQNlotWDE3ZWwwUWxxN2RoUy1SWk1Qc0V5dGVuVFdlT2UyajZ6Zklaa0VQbmpLTU1vYXRpNGRpWGpmR3h5cw?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46019.62203703704</v>
+        <v>46020.43604166667</v>
       </c>
     </row>
     <row r="12">
@@ -812,90 +812,90 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>‘My Package in There?:’ Amazon Driver Says This ‘Might’ Be His Last Day. People Can’t Believe He Still Has a Job - Motor1.com</t>
+          <t>Delivery workers linked to Zomato, Swiggy, Zepto, Blinkit, Amazon and Flipkart, have announced a nationwide strike on December 31, 2025. The strike follows a similar nationwide protest on Christmas Day, December 25, over the same set of demands. Worke - instagram.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 19:03:26 GMT</t>
+          <t>Mon, 29 Dec 2025 09:21:55 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB3Sk5yU1VvelVaa3RfSlZ1SGFkS1k2UWNGS2NJQ0tGNV92QVFMMEVub1FZMU9uUFMzZjRPU0dIU29nZ1JwRVFSNkRhYkNQdGFIMzN6U1BfYWpiWTg5OXVUVjYydkc2Z3BMWGFiaUhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFAzRDEzRlF2cm1LZmNxcWhIaTRDSUUxRzRMa013VnBKeVJRblYxX09Xa3BudVlLcnB6cERTRFl2WHV0YUFwQ2pWQmxfNTBqM3MtM0E?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46019.79405092593</v>
+        <v>46020.39021990741</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amazon says they’ve fired driver after video of her peeing and pooping outside of homes goes viral - AOL.com</t>
+          <t>Bayern Munich starlet Lennart Karl garners praise from legend Thomas Müller - Bavarian Football Works</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 21:39:12 GMT</t>
+          <t>Mon, 29 Dec 2025 09:30:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE85ZE8wNnhQWWJESTVRWWMxcGhBeW93bzlab3A0SEpGbUk5b2RyODRndC1LRmxIVFZRSG5NYWtoYVFoblk5SVpPdmFnMHJudVBCdzJZeUNrVk9nR0dWQmtFVW9SaTdoams0Xzg0SkpRMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxONzVoZV9SMGxfcTB0XzFXcklvR20xWlNidGVrVFFXbTdtX2lMZ0xTeGpFTjVhU2tHYkNCcFlCUHdIa1UwWlhpcVFyNldGQ1VZZzg3Y3BSSGhsbDN3bmhTVXNfQTI3S0VRU2FtQlg5azhLNjl6NS1mRm1kQW5GdFJJUkhjVW5BaERyQU0wclc2Nk1fUk83a3k3c1VQYnlmdTN1ZkpaVFVFWGVUeTh6anpjN1NWc3NIb1U3Uy11TkM3WUp2UEFEUTAwYnBXSzBqS3I3dEdweUYxQk0?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46019.90222222222</v>
+        <v>46020.39583333334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amazon Prime Adds Free Same-Day Grocery Delivery. Here's How it Works - AOL.com</t>
+          <t>The True Meaning of Support and Resistance - Price Momentum Alerts &amp; Market Analysis Tools You Can Trust - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 15:17:04 GMT</t>
+          <t>Mon, 29 Dec 2025 11:41:36 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5Nc0ZIQURuNHZ1WGhHX281Uy1JTkZFbmFIZWp0YnF0Tm1lLVhRSU1XOVdxWHFDNlFXTmxUV0dVd1FmOU52SFVSSUgwMnNqWmlCUWltZkI3UDR6aEdnZEZLOEVtd2l5cE5RNWZhZUtwcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNOTFieXVtUnJaaVlEYThhQ2ZIeS1WVm9VYk1BQTVtb212U0l3TWVYcUFrWUpfd3lYejcxcFdULURZSGc5Z3hNeVA1VExwcm4xMjltbkdmSW9McFg3MVU3bEJhSjZRSThZeGktWjladGlvVlo0QXE1ajVWcTNjdkRkNHBkNjJyMVJyMm9RQVFR?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46019.63685185185</v>
+        <v>46020.48722222223</v>
       </c>
     </row>
     <row r="15">
@@ -911,24 +911,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'Do us a favour and resign' - Tottenham boss Thomas Frank told to resign by former player in explosive social media rant - Goal.com</t>
+          <t>Manipulate price to create breakout traps. - Straddle and Strangle Trades &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 22:40:24 GMT</t>
+          <t>Mon, 29 Dec 2025 12:09:59 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNRXU0WDJ5NEJfOFdmaEdnTXRGcjltMHdtOG9sTFBiVXdVU284eEVVMGFxZEYzVjcwRG8xLUNOSDZsVTNsSUFWREpiX3kxMXM1UlZYeVVrU29XalRXVUc3dU5TVVFXMnFFTmxEYXZuWHlfVHZOSUNRLURBTFZBVGJOeUVSNThjUm5LV01HdUFuUzdlVF9ubVhjUFQ3YkZQc0VlOHBJai1mRTlNRzRhS0trOHN6dmFOUExWUGx2VzJuR0FUY2hCZFFJWkthWmczQm45dnZFZUlacE9MSFd3eHpybW5qVGN3NzJvRzRzaDBGcEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOXzJRX19IVHRvNzJKWW5WMGVnbXM1eHI1MldKRERsREo3bDh6U3pJWTB0X2YtSzNPU1pVMGc2MmxXNHNCcDc2ekJENndSTHNHb1FkN01qNWVfNW5PY0YxWUFsb25FT1Y3UjFrelJJOHpZb3FMdk9JSnItNWNkMjM0blJtYw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46019.94472222222</v>
+        <v>46020.50693287037</v>
       </c>
     </row>
     <row r="16">
@@ -944,24 +944,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Federal (505744) Hits 52 Week High - Earnings Beat Highlights &amp; Low Entry Investment Growth - bollywoodhelpline.com</t>
+          <t>Reversal Traders Monitor Benares Hotels Limited for Entry - Options Trading Strategies &amp; Explosive Growth Opportunities - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:42:48 GMT</t>
+          <t>Mon, 29 Dec 2025 11:57:22 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBESnhNWUp5bDh2S29uT25YUTRsQlNXYVVQUnRWQjVyTGZRakJQRm1EZGpDVW9aOUwzVGVMNXNDNF9GdTU2UlItTGxIVWstZmVjQzZlRmphTEcxeUVzN3FhNFN2VU96ak9pNXVmZDNXLTVISXlBMkFVMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNaXNubUJ0bEZERnhlMnhQd3BFTmFpbUQ1QVJURjYtbktoRWFCUy03QW9wZXo0Q1BYM0FZYXIzRkN1Nnc1UDRUZE9RRk5QRWVxTTdhcE1oTHVWcGZnTW5haUZPX3pzMUJkOHNrM1ZXYXAxWUNoMXB4SUcxc0lsa2phcmVBSG9lYlRPS0xHcGIydllhLWFxbDItZGsxVFNfX3h0MVE?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46020.27972222222</v>
+        <v>46020.4981712963</v>
       </c>
     </row>
     <row r="17">
@@ -977,24 +977,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Row deepens over vanished river wave in Munich - thepress.net</t>
+          <t>Will Autoline Industries Limited Hold Gains Into Close - Industrial Stocks Review &amp; Outperform With Our Smart Trading Calculator - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 16:14:10 GMT</t>
+          <t>Mon, 29 Dec 2025 11:11:15 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNQzZZZ3FmVnB0Mzd6RHlnak1Td2FiTFdFQVBHaERXYWQ0YWVueXhVOEFtV0hNLUhKbkQ4cjgzTE1iM2NjQkhLUG9lOVoxdWNiY2tQa0xQdUhsWTRyd3U4czZuLUZPVGh0RS1hdlRJQWI2N3Z1dlRIdDdWdEVjekR1WDZjSVpheVdxSDAzN3BYeU1PT0EwR0pEWGdDX19JTzI1OVc3LVE5WmJvMGVJZUppYTVheldTNzllSE9VYjVodnBIUkpDNEFvVWJSM1BONkc1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOSTV3ay1ITnI3LXVhVWRWeVFTV1lCcEpMdFFEMVl2UHphcjBQZHVWdU9CNWlIZEhhSFJSNE1wcXNYc0stMFE3dm9tTnMxTXFKM2RUcE1jSm4xczcyTkUtQ1RkOFp0azRKUUowYmp0TGhCUDVHdnFRQUJ2djY2RTM0ZHdSQk44U2ZrN0VrMnRwOF9OLWpx?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46019.67650462963</v>
+        <v>46020.46614583334</v>
       </c>
     </row>
     <row r="18">
@@ -1010,24 +1010,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The Eisbach wave in Munich was a popular tourist attraction before it was removed in October - IslanderNews.com</t>
+          <t>Are Bears Losing Grip on Mason Infratech Limited - Risk Adjusted Returns &amp; Free Explosive Return Secrets - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 19:03:08 GMT</t>
+          <t>Mon, 29 Dec 2025 09:14:55 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNdVBmZFBpN2Y1blBiRlQ5TGNOMEJZUUZPbWJ2b1JIUUhEUG1fOGhmQURlVTh6WjNGbGJDdU9jOTNyQXlVSnZVS19GWkhnMElBVXUyanh4b1k1MzcwTG5MSGxrdmFjUmIxeTZ0cTN4RWlRQVNiVmJCelFFekxmXzRxVG56VmcySFdqcFJhblhrck9zLU1mSjRBZFM5cDU0WEx5NWhvazMtNW9uQVNTNmhGM2NoUm1KcHNRR0hRbkxUcmZTV2YwX3AxM1lZclBkcWdWbWd2TTZPV2d2b0Nqa1lGbUhyTlhSOTNvN0ZVbGFDblhuNU9OelFkUkpBbkFPUVU1dkp5LVB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNX3JYUTQzOXdXTnFFY2RpdlJqcTc3Qkg2SG1sVHNHRU0yblFkd0FkN1hRTlpKbXpVOE9ET1AzUmY1bGVja1NPdjVhTWJHNnJTSVN5Ml9tNGtycU5lLTNDZ2pmMVFidk5ad1hYSHlmNlgxb0lwTXV4b2lsUGl5SDF2cnNGQXQwQTRGcGJR?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46019.79384259259</v>
+        <v>46020.38535879629</v>
       </c>
     </row>
     <row r="19">
@@ -1043,24 +1043,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Traders Consider Averaging Down in Switching Technologies Gunther Limited - Price Action Analysis &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
+          <t>International Exposure: Diversified revenue streams from 67 countries - Institutional Buying Trends &amp; Outstanding Profit Investment - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 05:28:39 GMT</t>
+          <t>Mon, 29 Dec 2025 10:22:05 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQYzNrUVplMVdEQ1FtOHgydms4TnNqX2xIUVE0M0wwRFRNcnJFTkJlY1ItVE1jRU5leTdBYW11YVN2eEdidS1oMmdhR1JwU2ZCRWlieW9pSm1FaUJvX1EweC1MdXBGNXpON1Z1bzZiYmFwclU3QVVMSXg3UGN1NnZoYlltRE5ES0JRS25wSFZLbWwzd3ZoVGhyWU9iRFFqcjF3dGMyNjZseFdkdmdx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZkpfYzZnWXZDMlRKT2haNGRLRXo0Z0w1WG5Sbm1hWTV2NDVWQ2N4VWhLUmYtbTJvSnJobFZYLUZJOXczbW1wd3NqdzAyVHhxYTdQR2FSRjgzdFNrdDh1X0k5aXF1ZzNYV0tWanZ0X1M3RG1adUN6VjVlSnNuUG1Yc3djdkNkM1B0Z1JQblBxVkR1VjY2UVM3bkVoVEZHUXlpVkdWZVFzNA?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46020.22822916666</v>
+        <v>46020.43200231482</v>
       </c>
     </row>
     <row r="20">
@@ -1076,387 +1076,387 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Heatmap Data Shows High Activity in Radico Khaitan Limited Sector - Price-to-Book Ratio Updates &amp; Double Digit Portfolio Growth - bollywoodhelpline.com</t>
+          <t>Aurangabad Distillery Limited (AURDIS) Signs Major Deal - Insider Trading Activity &amp; Invest With Confidence - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 02:45:10 GMT</t>
+          <t>Mon, 29 Dec 2025 12:17:24 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNNXJycmlrV0lUeXpGeG5QZmgyVXF5ZUJEa3pyNzlFWEZuMThoQXZzM1hhX3BuaWc0R1pVOThCSF9oQWdYN1l4YU8wUnZaMmFkejRBTEFHNDNLdVp1MFduNFJ5Wmw0cG5JT1lKODRzTHNJZXlEbDFlYm1ueVdnNEJ1NzdyUkRsZEw1THRvT2hvcmtEZ05YLXV4b0FZbjFUYTFtZ2hnb1k3SnhLUUpr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQQUlKXzBVSnZnQU56YWxnbUJHSjJLRGJBR2Y5YzNlT2g3Q1FHZThXRmdaZ0FuV3Q0SUM0eHp5LTFVUEhvUmJybzFxYW5DRW9vZkxKVThyVUlHWFo2LXd4NU1hOURkX0tieGFhdFNWaTVGcjJ5c1VRMmlDN3psMHFEWk1Sa2Q4LVNneDBoVS1vVXFmWWs1UDZ6SGlWTXJMT1k?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46020.11469907407</v>
+        <v>46020.51208333333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Published on: 2025-12-28 21:57:42 - bollywoodhelpline.com</t>
+          <t>‘Organised’ shoplifting gang operating in Fermanagh - The Fermanagh Herald</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:57:13 GMT</t>
+          <t>Mon, 29 Dec 2025 13:43:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOS3JjdG03eDRuRkhwRTBfMFlHS1RFZXVPRmlUelFNVl9SY0N1Tzd1cTA0cVluLWRaXzNRb3lLMGdfRE5JLW9xQ3R1SS14SDZqTk40dkFhWHBZZUxtUWVJcTZYMFNRVjlNYTFjbE43Sk1nVnNKYW9xTGxsblJfaG5LYmcwTUFaYnJvU2hrc2hrQ3lRLXd3RjZuY00zcWUtSUIxWjRtNUJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOYUhRUkxobGpnUGtVcWhaRVE0VmNQUnJvT1o3c3VWNXkwbEZoS0ZUbEY1bzJpT3RKRURlNGVlOTM4amhJdUpFa0x4SmdBM1plZ2FaNDF2RU9BTWZ3VVFUeXdqVnpxWkVTMldELWVwODA2MzBtOWNYaTFEQS1fOVk4Y2dvX3pRY0RkVE1UdFFLNA?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46019.74806712963</v>
+        <v>46020.57152777778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peta Village Search</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("peta") AND ("Ingolstadt" OR "Kildare" OR "vallee" OR "bicester" OR "Wertheim" OR "Rosas" OR "Roca" OR "Fidenza" OR "Maasmechelen")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brigitte Bardot remembered as ‘angel for animals’ by Peta founder - Bicester Advertiser</t>
+          <t>Worksop shop theft crackdown sees over 10 years of jailtime secured for offenders - Worksop Guardian</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 16:17:50 GMT</t>
+          <t>Mon, 29 Dec 2025 11:42:00 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPRzRpWHR5aENLZXVodDVkNnZDcmpLM3l3TnZCNGlEVTF5b0UtZ1hqMjZ1SkRFV1NfU3ZKUHZLTWhZclpMSlhMRVNkX2JkZ2l0WFljNk55Vmp2ZFFuY2pyUlh4WUJHQVMzRDNDVzlCZWRrMXhENmE0azhFSk5BYjByMU9rMkJfWVZSRVVzZm5QZ3JRUEFyUDc4WGloTlBDX2hvUlYyNmlLWXNXT240ZVE4R2pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPWGxVRWwyeDI3WW1adEg0UUNQb3hpN3Y0ZV9jWUJuU2xsQURKdlhISlVVcG9BbEJSRzNnSGo5Z3I0Z2VZazhNOGZVYzZNSzRScW1OUGFCQmxtZUFpd1JDanhPYWNtMzdKSGJzNWJmV0N6WHloM2hjSktHb3BidGlnRmpUcW5EcUVTNWpYNHFvZDllcW9Id3lsWmFmRG1GMFQ3dUZEVy1xbGZaMjZnMmNVTUY3bk1lakRJbzJ5NHJtRC00UjJLc0gyUkF3czB6aEk?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46019.67905092592</v>
+        <v>46020.4875</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scandal-hit Wessex Water ex-boss was paid £170,000 bonus despite ban - GB News</t>
+          <t>Prolific shoplifter Jason Christopher Evans jailed for series of thefts - The Purbeck Gazette</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 15:02:48 GMT</t>
+          <t>Mon, 29 Dec 2025 12:26:06 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQQng5RmU5czZodnpjNUotcXhPRmV0YU1WUTRvSzhKdEh3Y2RhaTRNR0VmVnZYSW9meWNRMDdmbEtXckJTT2lVQVQ5eTZCeXYxd3ZYUHVmcUVYOG43ZlpIMW1vZk5VNkxZMGJ1ejFPZU93YzV3RWIzbjlIbnBmbExLU1oyOHVpdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQd211Y21oLXdBUXkwX0x6TElGUE43MkcxTFhyOE1aRWJ6WW45UVZnX0VvT21Ta3pod3dkU3BWbjZYM2doUlk2VXVWSklZYmhaOXFQUHAxdWNuYXJSVzF5S09YMTJIam1IdUZuMTVHMEdzUGhabFo0MFBwYnBIcXhiNXhieWZqbmViRTFQSm9XWE10VlRkRnJKSXU5Tm95ZmR0ZkpQelp4Smg0Um8?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46019.62694444445</v>
+        <v>46020.518125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The Special Terrorism Policing Powers Triggered by the Bondi Beach Massacre Explained - Sydney Criminal Lawyers</t>
+          <t>Organized crime is a problem, and it's getting worse. | Opinion - The Palm Beach Post</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:18:27 GMT</t>
+          <t>Mon, 29 Dec 2025 11:03:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOd1JuVGNzOUxzSWR5YmI0cjFHQ3loVlFEaThGNV96NjRRcl9iN214S3BOWWZzakFUWkgydl9BNUpTN2tSMFRINGlmbnVvMjFwTkpRd1I5aG54c2lpa2dIQXFQdS1NMUdIeUJ4bS10ZDIzejgtSmVrcnI4eXBsN1ZRUFVlY2tOZXZXd2M5UEp1NmpnaWpVdFhwLXBkakxydHoyZ3VPM3RDcXJnQnRQczhtTGZ0TmhJU2RreEFXTFFNSjVod0c1VzVHcUZZQjY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOekkzRVhiUDBzbEdQYXVSMmNQb3JaU3lHS1FPdmV2N1MwanMySVM2d2dzclk0SklQS0tuSEhjYU42VkVTN3VncDJSTlYwZ29BQTNIaEdDUENKbk9oeTJ4RnNsazdmZlBRX1N1REF1Ny1WM0k1QUdRUURCQ01JQi1nUkY5RGtXMkFxQnlKenhFMnFNZUpyYVJnRFBGRkxubFZQM2xTaTJ3NlVGZG5XRTdTYkJfMzZNTjZmZjFBSXAydzlKeHNFblBLOHRZSHh5N19LYjQw?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46020.2628125</v>
+        <v>46020.46041666667</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pilot, flight attendant barred after testing positive for alcohol at Schiphol - NL Times</t>
+          <t>QUIZ: What happened in 2025 across Barcelona and Catalonia? - Catalan News</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 05:30:00 GMT</t>
+          <t>Mon, 29 Dec 2025 10:27:45 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNeVhGNmdmMzFreG5ZOG5TWlQ1emt3d0FNbmFMRVBHdzllQkFWSWhwMlVPVDVtcHNiTXZYQTNDTDhuekd3aUc2dWwzbzZVYVoyVUFKMFAxdjlUdTQzXzdpZFFzanUwNUFRSEt0OVV3eVBJbzJSQnpDUzZxS2piUEhIekNDdXlFTWJTTXFlMTJlaF9ZSmNadFB3NQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1xVmNCSF9WRzJLenVHZ1kyZ09yVkdqNUhHRjFjNy0zb3phT0NoLWZubzF2MmsybDdnTjlRUU1pSVp2YlF4YmhGZ3g2YTNiakFNMHdWaWUxQ2c3cktMY3ZtNy1NeFdENWVSYUJCeE9VUHJEaU53UTh5cVdRSVppeU0?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46020.22916666666</v>
+        <v>46020.4359375</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VoCoVo's Martin Smethurst talks 2026 trends and challenges including retail crime and AI solutions - Retail Technology Innovation Hub</t>
+          <t>Cristiano Ronaldo wants to keep playing until 1,000th goal - The Malaysian Reserve</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:03:08 GMT</t>
+          <t>Mon, 29 Dec 2025 11:26:34 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPX2RjRHBFaTEzQlJpdFNCcWF3dThGR0Z6VHBuVU1QMjJvaVhLUXM3Rm80UC1qRnJCekZVRnhSd1NBa2FYbDlDaW1ISnVhVjIzR3VQS2x0UjVtM0U4MmdiYUJsNnNUVDNkMEJScVI5TU50bnpsRlRWSTM2X0wwTEF1YzFGNmhGOTBrczAtdXVSekVrbHZRRHRnTGZldlU0cnVweFhPU08xZnJVTjVjc0lXNzlaRGxNMUk0dGlHWTVqcEN0TlhrTUNVQ01GWlhiNFZTRk9BaDU4ZWl6OEtSMGFYS3VhSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOLWd1elVfenFYLTFKYjcyNWQxRjN1S01LMVZ2Ynp0RUZUOWlvWkJYX29ZWjZFY0U5dXJiXy1tZzNfM3B4Z3NtWGNzeEZoMVZ0ZTdRN0tXblFyVUJFdGpFYzctcEtvazlHVzFHZGtfWE0yMEptOTJCRHhkNG5HN19VaHoyRGtjZ2tLNFl2TEdsOHJMZUNTc3FwalBGQmVjM0pQWmlhM2JCZ1Y?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46020.25217592593</v>
+        <v>46020.47678240741</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Appeal following shop theft in Sandwell - West Midlands Police</t>
+          <t>False bomb alarm at Adem Jashari Airport - Gazeta Express</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:00:00 GMT</t>
+          <t>Mon, 29 Dec 2025 08:35:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQUDl1SGcxQlVhYngyRVNyd1pYU2I0cDk2WEpZV2V2eENjeUh6OUxVS1F0SGppRTFTbi0tb2NLbDR0TzhlcWZZM0E2Z2MyMWZzckVvLWVKamJpbTdSZnFVeDJxY283YzgtTG5Zck0wdEZ6M3Y1alNTd1N2c1p2cTM0ejI0ako5QXRhaVlwTmlxOHA2TnBjbGtmOWhKcnhrTEcyeHZZQW82ZUZNeFB3OUMzazdBb2R3eklPc2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFAxaDhPTS1OR29IQkhoZ3UtNTBFZnRVY0hSbWphdlJ2bURqWUpHNTVfT1hTMFhOaTI0a0d2X2FJQWdHMkhCZUlUVlU4NDYyUG5OSVA5SHFmZjZOOEs2R3VUSHZqSXI3S0xRZVJxc0F1R01OOHVQWkU2aUpRQ3BWWGM?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46019.70833333334</v>
+        <v>46020.35763888889</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fear in the Aisles: Why Retail Crime needs to be tackled by the next Scottish Government - enlighten.scot</t>
+          <t>Is It Too Late to Sell Cupid Breweries and Distilleries Limited - Stock Split Announcements &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 00:02:28 GMT</t>
+          <t>Mon, 29 Dec 2025 12:17:17 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNRURfUi04UE03cjMzekZTTGIyMlVudldZY1JJc3FKa1h2NG5sRTQ4YzlzNVZHZ1cyX0lybV9CNFlzMUh0aFN5aFlVakUxY1pCVkZaamZxOHpmcHlFUWlaV1VpRDhaQ01PVG1JMzBGVWd6N1gzTTNDYjRreGlwNVVnNXdkbURYaHBROVpwQ2ZzOFhXd0ZLWWxZMGhKUlpCUGR2LWFVZXNQX1dHT3BLd1Y1eVd3TVZrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZFJRNXJrS0o2VUNGRDF0QUFPUGpERzJicVUtZ1cxNEdOZ1NKZWJUQlJyT0VvaWhwbmJHVF9xbUV2RGVrOUkwdFZaV2Q4QlhsUDk2R1lObHljcFhYd2k5YnpvRGZrSDlkRGlMOXVwZ0hvOHNNZEpVVlFkc244SDJnZ1FaSzRyUmVNWDV4eWprTWY4ekY4NExJbjVxSTMxeGFjbENfZ0dLZ3A0UQ?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46020.00171296296</v>
+        <v>46020.51200231481</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Police launch appeal after bike stolen from retailer - Halesowen News</t>
+          <t>AI Trend Models Suggest Bounce for PlatinumOne Business Services Limited - High Dividend Yield Stocks &amp; Outstanding Growth Strategies - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:09:25 GMT</t>
+          <t>Mon, 29 Dec 2025 09:04:35 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNMFZjVDhhblQ0STlrbXh5Mi1sNkFtVG1YZ2tzRTRKc250QU95SDdPYmt2cXE5OGZnZlRfMndIemJKTEI4SFFibzVpLXRidFdvT1N3OHhZLUViemt4MGRzVlk0VWJQVWoyQldScXpISlVJQXVHdVp1RVNDc3dNUGFoXzlXVXJjRkt4VUZaNWlETmh3SnpjamUtYW9QWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOVlZWSTZic1FQU2FHQnBONjNWeG1BTmNJNTJ3RWVCamlwVWdsVTAyaER5MnZyM0lBVnR5T0NDR19QYXVCcVQ3d2hKLUxJbmZGYzhFVVQ2LTZSTEdWMk8zN0pUWU5ZSnpESEtBdHpXa3VRc2pNV3Z2bS16NWJzdkZweWZNeGNocW9BLXJvbTJHSHlEVnBydlE1OU5KVU9FNnNsU21OOHpXNWV0a3M?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46019.71487268519</v>
+        <v>46020.37818287037</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Have you seen this man? Police issue photo of man wanted in connection with Oldbury shop theft - Express &amp; Star</t>
+          <t>Energy Limited (540649) Signs Major Deal - Earnings Per Share Trends &amp; Advanced Stock Screening Tools - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:53:17 GMT</t>
+          <t>Mon, 29 Dec 2025 12:43:50 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNLWp4a3lhSmNocUxUdElGanpJa3RDRUtPdjQxVTkwcnN6NlFKd2oybzU3RW9DUXZrS2l0OUhTNndIcUtUT0FBc2xZdmFQckZKZVo3Q1h1TTNFdFhZNGtZS0syMW9GdE1Na1ROeG5xY3l2SXNNUl8tdVZEa1p0TFl3bmtqUE1ibzVWOElZYUp6MEZPdHZncW9IT1diRnltMzBPLVg1ZkF4U2lDNExlRDV0VjBFMzI0MmFKT2UtOXRFLXFvSVlXalBHWEVuY0xxQlRBSlMtckhBbkRfZjY1ME5hVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOY0hrNzJRYUFGLWNVWEhQNFN5LVF0TXBrVy1IN0p2Q3NESUNnNXZCTWVnejd5YUFfWEd1MmJmdmlyX0VidDd2MnNJTDNpbFJPbkJDTUVuNFk3dkFCTUxfSzNVQWtsdzJwaTR1OU5QMG5hMGZmbElVWHFNZUwwSEhFVlZwT1BBWldFajhmWGJUR0VNbTg?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46019.74533564815</v>
+        <v>46020.53043981481</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Police looking for woman over 2nd case of shop theft at Waterway Point in under a week - mustsharenews.com</t>
+          <t>Mewar Hi (540150) Gets Regulatory Approval - Market Capitalization Trends &amp; Free Gain Edge With Data - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:31:09 GMT</t>
+          <t>Mon, 29 Dec 2025 10:26:04 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFA2TTBtdHBjTUUtb2h2NjZlNTRTZ0RlMHhZemFXd1A4THl6N1ItSnluYW5PTjdqVS1QSWpLT0g5Y2h4U1ExUHA2YlczdFprNWlEMG82N0hNYlNvdHNObjB5aHZaY9IBaEFVX3lxTFA1ckxZVHYxbGZsOUd3VjRnakdiY3RZSTlzTkdUV0tSN29zUDB1LXhEWVZuX3pYNkRNS1owMkRrVnVMNGQ4ZkhDWHFGclkxWkhsUzViRlNHUEd0Qmh2MHFBWEpEbkxDTUJC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOam8yRDBiTG9ib1hJSHZWc2o0a0FDVmFxYWZlWl9DMlloaGlFWDV0RXhjUXhfQjRsZl9xd2NmMW1GengzU0FlbzF0ZGd5SllwQ0ZfZ2NXOE9pMUJBNHhGT3h6REMtV0E1VmRHQ3M4M0FJOEp3a012MzI3WWtEODRoYjRsZUoyQnRZdWlWSWpQRzY0bmhGakRxUA?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46019.72996527778</v>
+        <v>46020.43476851852</v>
       </c>
     </row>
     <row r="32">
@@ -1472,24 +1472,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Comeback and 10th consecutive league victory - realmadrid.com</t>
+          <t>Can Honda India Power Products Limited Bounce Back From Weekly Low - Candlestick Trading Patterns &amp; Best Stocks For Explosive Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 15:27:00 GMT</t>
+          <t>Mon, 29 Dec 2025 12:59:05 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPUFdUdFdVc195YlpxTjQwOGlfSmNzUDJKSUYzbF9ONGlnWC1WZzE2VFVNQTNWSHRlb0V2Y0xJcldDYjZlQkl3UC1mMV83SFFnRkw0QW5vY1ZUUXh6bjU1a0FwUHdTVi1MY0c5cUY0bV9xYUN2ZEhKWExlQ01WMWRZS2ZXd0ZhUFN4elp2ekttWjhSeUpqTzZRZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQZ05fY0Z5dWdpMlV5VDRHUy1SVlotdnlIY1VRVk4wMG9ZT0hiS1JYS1JScDZ2MGhWelo1UXAzOHA5eVI4UG9lN29QLXhLZ05zTENOTWIwb3EyZ1dMb25OUnI0WW1BejA4V2VlUWcydUo0T1cxaHk5bVM4NzlpdlpDNGp5Qi14VTU0bUp4cmdFUlZuN2laZF90bGNLV1Nzc3JTdU1UVGhPT21YVlBuWXc?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46019.64375</v>
+        <v>46020.54103009259</v>
       </c>
     </row>
     <row r="33">
@@ -1505,24 +1505,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Why isn't Kylian Mbappe playing tonight for Real Madrid vs Manchester City? - MSN</t>
+          <t>Menon Pistons Limited Recovery Linked to Earnings Surprise - Large Cap Stability Picks &amp; Explosive Profit Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 20:54:45 GMT</t>
+          <t>Mon, 29 Dec 2025 10:42:55 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgNBVV95cUxNc2RISW9hN0xrajRaeEJpZmVrQkxyYnFyTGxXUGtFeEM4MmNJT3Z4ZGdGZzhPdFlRU1JGel9nakM1cUhUUVNYVXRTcHNRODFzTHJfSGpBWTRjeHJqQUZnVGlSN0RDT3hjcWs2NkstRDQteUIzMUo5Q2h3dzhWdFNFNVRzZGlsN3VCaGpUQVlWRTQtXzA0RzVqWTFoZWRCbmFoZTZ1QlZLMENFenVlTWhPdExaVTdmaTFldTBNeS1mUXp2X1F3bVJ3VDdXQzFkZGIwNVRBeTJ4U1BuZUtuNktHcTVXRmNMZ2VHbmU3b1Z3YlFaRjdacWRQUXBpaHFVUHNmLU53eDYzUzhaZHZBVV84REd0NWJadmpsd2lXVVBxNTZyUlo1SDdxbUJBeEdEWFVVWVBtcWh6RElNMzd3SnhmWkszWkxZUkZoZG9QMXRUSGx5RzZONGhBeWtEVWF3UDBaUXJYRm5icUNscU1FTURweW5oX2Q4cnNxcjdtTkU4WVBnVm1SZXhJMkFiRVlLZXo1a1d4VzdxS3NYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQa01GaDdHdHd6UGxBci1fMTh4Tm9CWlVHZzNEcU1rVFRPMlFvdUxEZ2lIalBRQmhDeWlkLUx1eHZNWDBwaUVqd2xUQTdVTkVEOWpaZVp5MHpSbWtKNDBnV0Z5WG1HX1MwUnpNcTJwXzhCbERuS29LMHhQa1poMFU4SHd6T0E0Z205cG9VLVhjUmZRYzlJWEY0cHRQQkJyc3U5X2hF?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46019.87135416667</v>
+        <v>46020.44646990741</v>
       </c>
     </row>
     <row r="34">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Globale Tessile Limited Shows Support at Fibonacci Level - Stock Price Targets &amp; Affordable Portfolio Strategies - bollywoodhelpline.com</t>
+          <t>Marcus Rashford: Atletico Madrid will exploit Barcelona’s decision - The Peoples Person</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 05:28:32 GMT</t>
+          <t>Mon, 29 Dec 2025 13:00:49 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOUGNyNVMyV1lrazZJVWZCWjljdzk4U0dtWnBtdUZ3SGE5QzlkaXh6NzRwNFBPZmFjOWV2RHc2R01CeDg1Zlo5VDNMUDNfUC11c3d0UXF0SVI0QjVOYXdYNG9PYmg2bHlLS2JpamR4VXlHVzV0TXdITGZWY05IeG91SC1uTEpBMTZTWmhOckZfckdwYjVVNkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdE1WNXJhNmxYQlNJMlJmcEpPNHZhRnFjX2F2RnhrQzNwSFZrNUZNOWlfNjUzZGtFd2dFcGZVYnUtZzRteHlDcG9Iamd0dDBZY1Y1bDZxZEk5YUdfbWY5Q1lCc1ZDT0F5amJ4OC01SEEwVUJQMzR6a2hkOU9Xdl9odldRUkxFQm1GWUNJREt1RnJraXZOT3J4MUNGTUJNSTdBbUFvNmdKa0Z3TFRhNG5ETXNR?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46020.22814814815</v>
+        <v>46020.5422337963</v>
       </c>
     </row>
     <row r="35">
@@ -1571,2235 +1571,1080 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Learn to avoid retail traps and false breakouts. - Automated Trading Signals &amp; Best Stocks For Explosive Growth - bollywoodhelpline.com</t>
+          <t>The Lancashire man on Britain's 'Most Wanted' list after double stabbing - Lancs Live</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 05:38:54 GMT</t>
+          <t>Mon, 29 Dec 2025 09:07:58 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNRDNkNEliVGRLUkhpM194TlU2QVI3SlBGaWNkellSMWNmTzYycWFJZG9IWk5CSzJWajdYMld6RFB4VmZHc1RiX1JyeUFVUWpQRy1ycEw4NjVmN2hINl9VUmZMRFNES2lUSnotMUdDSzVHN2N5TGg4TEZNUE0yUXZ0bUxrb3pFblFvbnlpS2JiNFktVTM2Q1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQdkZjWlVidmNub01TR25YTVZ1T05wWDgxZmNHejdhdTdyT0FEMEFPS3pDQVBZWTNTU2JGWW0wdTR1bVdGVVNSQkt3QkpGQUxOa2xobTN2RXlNMjRBSU1uZ2ZkdFZIcTlERXhzamdPbFI4VTJRWks5QnFVTGpsRnRIbVNJWkJ0Sm1XQUR1WmNac3pZUdIBlwFBVV95cUxOWUNJVjZ3ZTJPWHA3NDk1UE83M2NoakZkYjg3c0dsek9qOU9lRXBiNGVCa2FpQ21NaTRXSFF1aW5jYVhSbTFrU1NQRHNvNmVPbnNqMF9uYUVBeUMzMlRlV1lXREVTTGo5TkNXeFRLZklqSUhYVXp2SHl3RkNEOGljQ1FnaG9oemVrYVlKWjNndVJXYlpqcXhB?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46020.23534722222</v>
+        <v>46020.38053240741</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Village Search Bicester and Kildare</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>How to watch Iowa vs Penn State NCAAW game: Live stream, TV channel, and start time - Goal.com</t>
+          <t>Lululemon founder launches proxy fight for board changes, WSJ reports - Reuters</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 16:31:02 GMT</t>
+          <t>Mon, 29 Dec 2025 12:50:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOaE9fT19RM1ZKLTFncklITUc4ODd0QkdLZzkzYmNBcnFzWXJ2dnRWcWpkTkV0TFNBVEM0STkwcWpkaDA2bGlteEdSd3NtY3dMUUVqbmJ2QWVQcDJoSFpYdUZOZl91ZXdRdDQ2ZldDVzlOSXJyQUtMX21vZlE5RFRUZk1DQ0wyOURPTUpvak1fNnBTYndvM3NGTUZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOY3NHbEFJU1JxWk5xNElPdGxneW9PWV81MkdBbzJnRi1DVlJnUG55bHlab1lSNVhmSWtzaFBzZ2Vra1ltWEotM05CQmdwQTQ0cjJURUpjY3h5ZGlkTVg2Z0pzR0lNZ0twcDFwSnZrYlRqUmEtdW1wT2NFeUZVU3R6VkdveXVKVnd6V21meTQzZXBINkFtUmF5VDR1VS1FeE9Qam92dzBoNURqV2FnNFFZbDlDWXRtNWlfUVhNUkRLSWpsblVkbnJPaW5DMVVaa2I0YWh2MmdndmtDX0QtMmc?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46019.68821759259</v>
+        <v>46020.53472222222</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Igarashi Motors India Limited (IGARASHI)’s Trend in 2025 - Trading Volume Trends &amp; Access Our Free Weekly Investment Letter - bollywoodhelpline.com</t>
+          <t>LIVE updates as busy road closed by 'police incident' in Greenwich - News Shopper</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 18:50:31 GMT</t>
+          <t>Mon, 29 Dec 2025 13:23:22 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxORFBNX3hSazhyNF9HbjVxMFlaa2IxeHllU2EzeUk2NjltcGRTRXlOWjhrWVlHbkNFMmtaUGVGRG1jRjJjMGhZaGdWSE9XMWJhR0tZNk1wS2lZM042OWM5TmR0YXZsaFVMNzJjQW11d09SbVZwWWdJYVFGaHVlLUJRcUY0ZXFFRWhQQjBBUm5BMDJIS1JTbzU5aERGTlBHcThKZ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPTGx3VUVyMC1nYjIwNU5uUGJRRWtzMVVmdkRtV1djRGhlTERvZW8wVHpXS0xLNVY2eG9TSV9MQXB3cnluWjNIV3RYNEx1azNRekM2UWRLd0dyMWFvNWQ3ZzJ3MnJlMHNsakNpZnpCcVJubkhHV0U0czV3ekJCTTdFQ0RFRDZ2N0VFYkFLVVYyczhwZFBEM0xIR0R6c0VKV1E?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46019.78508101852</v>
+        <v>46020.55789351852</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Is Bulkcorp International Limited (BULKCORP) a Good Long Term Bet - Cup and Handle Formations &amp; Explosive Capital Growth Plans - bollywoodhelpline.com</t>
+          <t>Man shot dead by Norfolk Police in Thetford after two-car crash - BBC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 14:52:45 GMT</t>
+          <t>Mon, 29 Dec 2025 11:18:08 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNYklRZzBSdm4xeHFicmdQT0NrU3IxWHRnNERTZVpxVUpaNjJHX1JocFVvVDhWSU5zTzdJelZ0VlNyYmM4bG9lSWE5SkRvaHNvQUd5X2ZvcEl5aFlKaklCdi1tdmF1WDI4RFpMS195Q3pRTHNtdDF3eDVCZUlvZUkxcU85V3RIeXBsN1E5UTNiNGtMR2NCZVFBLVEtZ2h4R1NGT05zeGlnOUZMSXNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1HTzlEbmplTkdmVlZCNXJkSzFWWHY4dWF3YkFDYXEzSEVzenhCRjM0OG1FUGlJQXVJaE9vWjRfcGZpWEp6Vkc3QjVidldXZjdZRGlfSEIzZmI5Z9IBX0FVX3lxTE1UVFNJSUNybXV6aWRILThrbmE2eVRUcjRiRDgyX0Z3eHlZX3JzcFJnWEY5N01fcGJvQ0VNbktPNjZzMGFfWk9zYjBiTE9HSGJGblpIMElIUXJ6bVZwZDQ0?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46019.61996527778</v>
+        <v>46020.47092592593</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Holdings Limited Crosses 200 Day MA — Signal or Noise - Price Action Trading &amp; Affordable Market Growth - bollywoodhelpline.com</t>
+          <t>Limerick style icon almost nabbed by UK police with suspected IRA bomb threat - Limerick Leader</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:34:55 GMT</t>
+          <t>Mon, 29 Dec 2025 10:02:50 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZ25vRVVTQnBSZmI2UkxkOWo1aW9NdFl5ZUEwU2pQZlc4QW50WlhRRUZNdVlRZjZxNlF6a1dvak5ZZ0JWemM3b29wZEh6bTg1REtJVHFYN0FhbFRSa285aFJ6T3Fwb1MtTzJGTFdSRmIyZjVHa0pQUTlnTG1rTW50Q1NlSXNXWlpMR2Nmd0FaTDl2enN3eDh5ZHBoMlA0QUx0dk1CeDRkZDVzNUwwbkFsSTNDNkhYaVlMX2tyT1ByYUlMX0gwTk9hTmZqZ1VpcUJMTEFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTzlTb05PbnRLck8tNlpDMndENWNLbXhNYjBEdDQzcHltbm9QYXQ5UEZ3dVJVbE53aFk3aGRpdHFjcVNlUjgwVjNoVnA4dTZNVjNtT0Q5N1B0bnI0ZnlwNENjS0pwS0Q0MkRvXzU1ajBrUHJWYnpCa2RDcVFUaXFBSHNjd3FRY1VBbjFRUlhseVk2VVVZaEh4UDN3bHNmOFEwazJFdXJmbl9GeEtJa0xvZ1oxMUs2eHBUODl5SEUxV0tkNFNYRk9Bblpn?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46019.73258101852</v>
+        <v>46020.41863425926</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Marcus Rashford: Barcelona reach final decision on Man United transfer - The Peoples Person</t>
+          <t>Remembering Bardot: ‘sex symbol', ‘crazy cat lady’ and far-right supporter - RFI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 23:35:36 GMT</t>
+          <t>Mon, 29 Dec 2025 10:14:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZ2hhOGdsdEhPSm56aHgyS2h5andVSzRFMUMyZHpHcWdPeDcyNGVLWDJuUXctbEh4YUotX0tvaVdZWEVrNXdjVVJsTkRkUnhkOXZBaFVPX1V4UW52Y0lUY3pkZkNrZWFQYlU4X0VZTm93blE5bFYtb3RzSTZEaHlfeVZ1a2VzOE9IeTZmRVFFM2g4bXpiX1hFbGszaC1jTXUyZmJXOWgwRmZ0TTRpTURfenowRFM2TGZs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTnpHTTcySFd4Z2J4REJHVDNvZGJ6UHY2cUh5b3dyZUcxODhCNzd1NkVWeVFKTnRhN1B1U1BPTWhmb3hGV21MNDh4ckptV25PbFpmRXRmeHNydUlWU3ZqVkFKZWhVZmFuWWR2SmswY2NFZ1psVU5weGVrNkRGVUVIaTNMbkp6eXMya0NkeG5kVmJFX0kwQUxWa2ZIUmtMNjNuQkJnUg?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46019.98305555555</v>
+        <v>46020.42638888889</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>And you thought Boxing Day sales didn't matter! Thousands queue for bargains despite Rachel Reeves - MSN</t>
+          <t>Mysskin’s London plan for sequel! - IndiaGlitz</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 05:56:31 GMT</t>
+          <t>Mon, 29 Dec 2025 11:27:46 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQN3o4Y2hOR284ZnVKekNzSElBbDNSQVlTS19sRmlRZkxtOGNCbmZCeDhpX0tLNE84MjAxUXVCODZkU0UxcFlYSlVFSGJMdV9QbnRDbEdsN2JCODhXdU5ieTJzenl5cG5IXzNiaFBiV1R2VFhob2RCdVVsVlhrZEUyOXlmSDc3UlF2Mi0waERrUVFJdWtaNl9oZFFFT1JZaE9QendVbndYVTcycDNJRWFsV28tMVB0SFdOdUxIYVRCSnFDU1Z0dy01U3pyUmxxUWprNDBjbnhXdWlrWUF0WnUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxObk01eG53VE9Sek1VRmF5V0k4MklteGlYT21EamowU19nNEVfUk13MW10MTRGSVAycEkxWS10WEJmMUkya3RLYy1pVGU0bkJYRC1RY2VycGZuWXlMTkxSVVNqYTNrVGpPMzNlbUpFd2dqdFZucmQ2MnhyOThYaVdIckI4OFZyQnhZNjhMTThB?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46020.24758101852</v>
+        <v>46020.47761574074</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Литва направила ноту протеста России в связи с активизацией атак на Киев перед переговорами в США - Semana.com</t>
+          <t>Police send Durian Tunggal shooting audio to CyberSecurity Malaysia - Newswav</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:36:21 GMT</t>
+          <t>Mon, 29 Dec 2025 08:52:07 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwJBVV95cUxOdC1qVmRHbXhWTEtzMVFNZHVtLVNDd2l5TE1tamFnTVk1NEYzd0J5S1pMbHRxZXhGWkNQeUIzR0hKWk8zS0VjWUdkMm1SRXB2OWZJblB2TFdNUmN6TFBfUVNrRzVjTlZ2cldlR2ZDemIxNWFjWXZmVVJRdG1KdS1hdGxhT1VVOE1GT2hLb2xBcWIzNEwtZks5NVFNb1BpWVh0M1F1RmFMb3UxVE5kZWNxeG5QaGh3TjdQY29SQW9KN25Nd1QyXzFKcElkUTVIamxCTlpNYVJaNWxMMzFLMmdGZjNHdlJTTjM5eVp5N3E5U0xNdVE5a0VNcHpSOVUzNEhOTlJmUDZoQ2t2N3kxZ2F0LXp2Q09JSzY2dEhRQ2pKVWlzYnNJcnJXTjlnMUZ2UWlrV0VCSVRGZXlRenM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPRVhSOXJnTHdiQ0RfNWluUzIzdFB1c3FVNE01V3MwMWRJOWdVTHVia3ZyT29SSDNSR3AwcTRKd18teXFvZTFYN3NLZkloZ2ZxenoyRVYxN2VFd1N6Z0lwQjd3aWpmVTZGM1hVZ3dDakdjS2dRNkRQMkQxZk5OQ2JPY1NWWGtLXzd5U3pNa18xeTQ1ZFY5NERKUlVjWlQ1UHF4bWhGZTdWOGFpU3B2?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46019.73357638889</v>
+        <v>46020.36952546296</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sonic boom like an 'explosion' across the East, police logs show - BBC</t>
+          <t>New Year's Eve terror threat prompts major cities to cancel celebratory events - GB News</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:10:15 GMT</t>
+          <t>Mon, 29 Dec 2025 10:52:30 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA4c291ZExreUtXM2t0M1B0ZDlFQW9ieDRCeEtfZFBCWTJrQTAxZUVQR0x5REZVa1NGU2puNC0xWG1qS2VWYjYza3EwNUFfbjc1UlRlcU9OeDhPdzJQ0gFiQVVfeXFMTnE3Z0Z4WjJjRDByMHNLck9LdldYeDhoVlNSZGx0ekpQUnlaazN6cE9BTy1DZGo4MmVOaW4xQlNfMHZBMnB2Uk12eWJyMGJMNTN5NE5nb1lkaWJ0VnM1OUljeEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOYjJFbWdOV3hrQ1pSZ3Vjd0dIT1AwTjkzSTdUQ1lqeTFKbU5ZWnJnZkFJNFFtTEZOekRKWkV0X1NCWGcteHZmQkpZUGd6UGFRckJFbHNpYTlNRWV0YjFobTFBSjQxQmNlUjdXeXVpQ1R4cW95WVdvR3VFSFdyMWtiQnMyYUVNd1FMSWo4MVVkUHZIS2JKSEIwUmpkMzlRTVYwTkN3?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46020.25711805555</v>
+        <v>46020.453125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boy, 15, Dies in Stabbing, Second Man Charged with Murder After 2-Week Manhunt - People.com</t>
+          <t>Paris train station partially evacuated after soda-maker exploded - The Local France</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 18:24:54 GMT</t>
+          <t>Mon, 29 Dec 2025 13:23:56 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNUdrQ1ZwZllZNU4tVmF6YWpDNXVQY3pxdkIxcVpQQ3JkY0VXNGx3dmhEWDJWZ1NuUUd2YUNvV0FVaEo3S0lQenRPSWlHWTFudHRaclFuRXBRQlQyMWMxQ1hXZm5jeVJzb2FSVGlyMXo2TGM1aGV6a0pvUFhxZ3Iyag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNZDljZnI4R3dzT2V1Wk1xeGlWRV9Bc3p2M3pnVEN2VkxmWml4U1JCM284WUw2VHNLU2ZXdXZmRkppNW1FVGFHeEJ6SXg5TjBUeWJ1eFhMTXBjNGVTSDZyVVU3cDl6NjE5Ym1Nd2FqWWJWWGk0Q3NBTnlENVAwTDlDNFlZSjVZQ3hDYm5nVU5fTURFYm1DSzZFM2ZQaWQ2NlU?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46019.76729166666</v>
+        <v>46020.55828703703</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kilburn man charged after arrest alongside murder suspect in north west London - Kilburn Times</t>
+          <t>All the Filming Locations of ‘Emily in Paris’ Season 5 That You Can Visit - Prestige Hong Kong</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 15:07:07 GMT</t>
+          <t>Mon, 29 Dec 2025 09:46:03 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOVDR4QUJIOWg1UENnWk5XWTg5RkJ1YXg0ckZxN0c1R0dQOEhVQ3hlZEt2RS15Y2IzR2VkeTVNM0loVHQ2bVowNTV2MHhFa1pjUlJyMmEwMS1CRVFoSlhKS1FubUpvb1Z1QU43OTZKTWdXODN1OFF3Z1NyYmYyOGdIV2cxdGpFWkE0TmxUbE5tT2V4eU9QNG12V2wwc0V4YjNGa18w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOVXZjQjRnOGRiVUlVdFlOYm8xV3RTSmFDeUlycWZNZlFMMjk5QnJSaGJKQWlsZmZLMjhnd3VreUVmTFV0T3FuT3J6QmJlSS1sQkYzSlByS0Nna1ktMURFOUFJekZaX3BwdjFqdy1xRnpHdUhGQzJweWl4U0Z5TDdEZFIycnduVV9VSnNCRVozd9IBlAFBVV95cUxQV2RqcGJ0elNzRVE3WDJUNmFjQVBCM1RZckpoLUJ2ZnJ0RGRPOFU4TlByUHo3NzZhS3kyaHBTOWc4UHBud24zSU9YNzdqQnUyZ0hpQ3ZaWGhlSjVrZ3lUTS1mV0ZCRGhGVWZ2dllmbkFXOFd6aVlObjhSMVpXZllncWgxTTVZeC1zcXNGVm9QeFBvS0Nl?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46019.62994212963</v>
+        <v>46020.40697916667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brigitte Bardot pictured in 1959 in London, in the heyday of her brief but explosive film career - IslanderNews.com</t>
+          <t>Paris metro stabbings suspect moved to psychiatric hospital - Diamond Fields Advertiser</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 23:01:34 GMT</t>
+          <t>Mon, 29 Dec 2025 11:12:35 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxNVk5ycXhoWTVnVnZ4d2E0WVBDaWVRVHpGejd2LTlydmI1cDZYMGNGdlNORS1pei1GSlIzS1pvX2xpMjZnSGtQbUMta1ZicDRzQ2c5c3NDOE5EaWNNaEF3Um1HNUszVkhzSWNGcUlUMl9hM01TeVRnNGV3VTZuVUtBMEZuRTZvSC0yenkwT3dLN0U2b2NqUHJVTUpnMWs3WVdRUmJ1MGV5Uml0b1BzbGl3MTBWM1RhMkdCa0EzUUJTbGxXLW90aThWWWNncTgxSDI0VzU3eWJ5amhnQmREWVpPa2JLd0oxX3BmVGE2d0xOVG9ORjFZanhYaENBdjBXWlN5Vkhjcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQZGN6QjdRcTZMUEtwT2Y3T29iOTY4SElGUkd0UUFhZzhTZEkxb1JuaWlob25rTy1JVFB3Zm9vdUtaenM1UGs5VkFMQVpKU1B4Tk80a0RudUp0MHlCVTVOTndEYy1qb2FHVmxmdVJnT1NId0tLajVFNUYwcFhESDJHcnF5V3g5bDI2RW9HemllVFJReEJRUTZibGJkbUkwNTZudnc?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46019.9594212963</v>
+        <v>46020.46707175926</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dublin Gas Explosion Report BROADCAST: 1987.MAR.26 - RTE.ie</t>
+          <t>Alkem looks to offer explosive move in the near term. - Candlestick Pattern Analysis &amp; Free Real-Time Stock Market Data - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 15:27:54 GMT</t>
+          <t>Mon, 29 Dec 2025 11:55:18 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOR1RBR016TnN1NmxSNkdBNy13TXFwN1pVS0dUSTRRZGZ2Wkhwc0JJYlBHYjZHMGpmYzBBZG9ocENMQThTc1Z5Wkp3OE8ySHBQR1I5U0kwWkprNm90bmlZSVNfYVhFOGZrZVdXRWpXaURkWnZrMU1vczhnbDllYVdOOUlfdF9nVUp2ZHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQ3hXcmdKVWI1NWxBUFRELWxPbVpRM3Q3QkdwYkpoMU1xV0F2S3EtY0NuUWJRSG0wV1doSGtoVm9xaTV3QkhtdDIyRFMxMEh3QlJ5dTJZY3ZXY3ZzZkVNX1A2d0pnZzVCOXBMNjRfT3F4SDU4UGV0RHhQOGRGdHpiVUpTUDRNcE9mQk0ybWZreFg5UQ?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46019.644375</v>
+        <v>46020.49673611111</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Joins Northern Ireland, Scotland, and Wales in an Explosive Surge of Tourism That’s Taking the United Kingdom by Storm and Setting New Milestones for Global Travel - Travel And Tour World</t>
+          <t>Vardhman Special Steels Ltd (VSSL) - Candlestick Pattern Analysis &amp; Free High Profit Capital Plays - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:02:17 GMT</t>
+          <t>Mon, 29 Dec 2025 13:38:52 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgJBVV95cUxQNUJ2WmRVM3dkYi1kcTRQXzdwcTVmT3BPOG44YmlZNXJBam5wd1phNGRWZHF4MlZONVZJZGE3eUhGejFJRGpjSUFhbHNnbk94anU2bmtrZFB2dnB0WXlXZHZaUkNrRnYwd1prdGZXVVA5bjBMVzdQWG11bzEtV2RZTElmVmpwaVdSTnF2Y1p4UUc2MlhyVkhWaDF5cnNlVWRpZ2lfVC1BUjNzRTR4TzZkbzRnRFNNUHVqQ2NHTnVnTlRTTkxSZ21PWmt3bDVCX2Yxc3VvNmlXSjM4UFJvd1RwelhuMmphUXpLeE9jWWY3Ump2VTUyNDRGMVhfQXNWeVdXMjJLdHJnWlJZNF9xUWM4OW9Mb19pUk1UWUdwUEZMN1VCNl8ycFNDaUVsWTBuOXp6S0MwSTZqbHdqeVVHSGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBaYzNvcmN6QXN1cGxkR0g0N0cxRXhOa1BCcmQzcDA2X1pkUlJ1Zk1XV21jdVVEUnR4QXBXSlczaGt5QnpPVTNzbkNJRDNJZEY5QWhROTVXV2FBWXlfX3hydDdHbHo2cEs1RGd0SG1CT2ZsclFRaVZEag?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46020.25158564815</v>
+        <v>46020.56865740741</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norfolk: Driver shot dead by police after 'fleeing two-car crash brandishing handgun' - GB News</t>
+          <t>2025 in Review: Discover Our Top Gaming Picks of the Year! - Sortir à Paris</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:50:24 GMT</t>
+          <t>Mon, 29 Dec 2025 11:28:45 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1XSnpTczRWd3VUQ0V1YUFYU1NPZGFUanZhdnJuQ1ZJUVFXbEJ6eDJtZThnRWhBS0FRRC1hNWliTHlHUlI4UE5ueUxXWTRMWFFiWEh4WWk1RkE1bi1TVmlZRFc3ODBibjViYWE4Z3FBWi1nalczbXJqX3dzOEljUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQOXdpSjVaWUZsc1MtOV83WDl2SlhoVy00Nmk5bHV5WXlUVHlxVTk0Q0FGZXI3STBUY1U0cUxBUm5MQnUwUFdJR2JuLVk5eU9NYlVVb1dvclZHZmNJa3VZUGtzTHpIek5Qenp5OHpJZURYV3dHTjFaaTB4cWYyWFNhdTVlSjByNGtJRXNkVFNYTGQyU0JLa01penVXSVljbFpTZ3hadlFIZWpyMzNRSGJyWWZoeUpEd0Vaa1dHakhDTEJQWmdXOWdDVXJxLXRkdWh3WlhWV1Naa0Z1NU5FNEZrSQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46020.285</v>
+        <v>46020.47829861111</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Man, 38, charged with GBH after Lidl supermarket stabbing - Colchester Gazette</t>
+          <t>Suvidhaa Infoserve Limited Bounces Off Moving Average Support - Capital Gains Strategies &amp; Free Explosive Return Secrets - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 05:00:00 GMT</t>
+          <t>Mon, 29 Dec 2025 09:19:56 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOa1hEQ0QtNFhucFZiNWU2dE8wUXNPZ0tqcjlXNTM3dWRhTlVaa3A5S0FuOGhnLWlEcWg5Z0h3cFI0UDEzbUZkdDFHOUhiU283VTd2MW1QSmpLMXZzdlRtWDl5Zzk2US1vOWJKNVE4RlpacmVwWU81cFdTbmpuaUxCOGE2TjFmcDdkNjl2dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZDlZemhlRTEzOEwzclR1eUtTMk4zWTExWjc1YjNHa2dqdmJROE9ZTE52SkJ2Mm5YX01NNEdzYmoxRDVwRWtKZjREX3c2TW4yd2xvaERmdGFEa2JITHRrRy1kMkxzRWNPMlV5aHU0Zm10ZDF0enJiaW9TX1FaWS1za1Q2SmQwUU0ya2M1WG5KSlM5eWJVZ1JTQmQxenF0aE5DUFdDaWU0aWJqVGJIbXE5Mg?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46020.20833333334</v>
+        <v>46020.38884259259</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UK faces monster 47cm snow bomb - with Birmingham in firing line - Birmingham Live</t>
+          <t>Site of Mariupol-theater massacre reopens under Russian occupation - TVP World</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:05:00 GMT</t>
+          <t>Mon, 29 Dec 2025 10:51:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOM1pmOEJORkNtaEtMVnNDd0FtVk5vbTRDbWQxQXAtcVdsSk5uOWJsTTN6S2FycVNQOVB6b1JrTnc1ZnllRERqRWdWLTl1Q3RBOVAxNExZa1NOeWp2UVlpNFpqajBDbS1ZSlVZd1hwYU16WnFvYUU3MUtlaW9Bb3RPMHNwZDhoZDhCd0o1Qm1DZWTSAZYBQVVfeXFMTVJCM2U5cEdBNndXZDd2Q0FFMmYxM0E0SXMtd291NlktUmdxWW5nNUpMeWw0SXhmbnFNaVctV0xiLTd5OTJycEV3M3RHYm0xSHg2Q2tYY1h3OHdOTUJBS3VqUld3eXhMRUlrbGpCbmNJbTZUaW5MSkZQQ3BDU2h4dlRyYVlXVV9PZHRiYXZCRDNEOEczRU9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQd0xTVHBuZGFZcmRlTTlZUUhhY19USXNpOUpOZHJZdzlGWkNEUlBfdV9ab3htWjdJX2RKQnk2eF8zZFdHN3JYRTJkWUl6VDJLZjNRQXdxcWhhZlc1eld6bGJTWmVmczBHRFdBRDc1TVNqOUpPZjVUNmNRX0Y4dWM5alVVR3FUbWdDTDNtU2VqR0prVDg5ZzlDZ1IxcExqUEc2TmtMMnZjemFPaGo2bDJxVzJDNnhiSkk?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46020.25347222222</v>
+        <v>46020.45208333333</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  English language</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1 death notice published in Romford Recorder last week - london-now.co.uk</t>
+          <t>Analysts Apply Wyckoff Model to Vision Corporation Limited Stock - Short-Term Trading Alerts &amp; Set Your Capital Stop-Loss Limits Effectively - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:00:00 GMT</t>
+          <t>Mon, 29 Dec 2025 09:57:09 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQcjc3QjMzQWtwS0FqYXFPNkhsUHpua21qR3NtRlBBNHB1ZXNzaWR5OVRrQmtZWVhyNWlDUEZGYjNIUmVJeDZTUFEzMjdzRUFjelpULUVxeWYwSXJNMmNnNVF3bThXcU9kcl9rZkhwZlVVRm0wNWpqM3JiU19tM0tJUkxIbU1PcTRoYVV6REpUY3I1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPdjJwemZiaUVUZ2l3dEVKdWRXazBwSkpCWDBwYzV1NjRGeWF1ZnlBYTNXNm5Fc0VlNGdTVGtnRDZxMURzQ1NTNmVPT3hSNWoxLXBMalZ6SlFycEQxWTFOMjhsQzJpWTJ5bWxJUV9lZ3hNaGVONVNfVmowYUFuWHR5Q2p1cl9WS2kxazdzWExueUhzRUpKV0JKWEZhOWNZbVgx?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46019.70833333334</v>
+        <v>46020.4146875</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ten injured in UK train stabbing; counter-terror police join probe - MSN</t>
+          <t>Investors Hope for Bounce in Ambo Agritec Limited After Selloff - Earnings Volatility Patterns &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 02:35:47 GMT</t>
+          <t>Mon, 29 Dec 2025 08:31:44 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNdGJXSWxLelo4VFItX3Nzc3d0NUV1eW5CVlRHZGtjQXpJNS1acVlQMWg1UThXVmp3OWVUYm9uNnZMaTJfWl91MWd5d09lRC1vNkhkTWtNREZpYndmUUxsWDlMRklyWmZsTDZhbk15R3Zjc3JTWHA2TFVxUk8zRU1GSVl6V3pCOXpKd0pOcURmX3FBZk9HeGhKUjJhOThJMl93NHdEWmt1S1JJTUtyUjVabGpGeHg5VE5FczlQMURRQVkzLWdjcGktWFNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNNm53R0Q3ZnZxQWJ0NmppRGF1ZXUtV0ZyVTQzTlluVEo5Q3haODEyNmQxSkdhbGE4elNrelBoLVFISHNLQUVIOGdZRS1ZZVQ0LTctMEUxQjU2aFVDT3FpbGxIel9GdnFGZm9XRDd1UFpLM1BtRWJWb2NNY3RmVXJKbkQwZ01ON05Bb1dwMmItR29nclIyZV9TWWc1alRCd3M?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46020.10818287037</v>
+        <v>46020.35537037037</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>'Angel Delight' drug mules given update after fearing execution in Bali - My London</t>
+          <t>Trapped Investors in Hilton Metal Forging Limited Await Breakout Signal - Stock Watchlist Updates &amp; Free Explosive Portfolio Gains - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:19:38 GMT</t>
+          <t>Mon, 29 Dec 2025 08:34:42 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOMHNNTFBuMEljZzkxR0lzNXhORDNaVVZjRUtQTHh1ZkE4Zm9CS2hwYlRpQmVOcjhwaG5zSVQwZTdCNlF5VmUtX2pXbTRoS0ZlbVB5NzRZOGdZcVQ2R3BzSUUwb2lRTTZOb1V0c3pHRGNYdU5XNmVmcnh0UllOSVMxVkdiOThialhTYm9BatIBkgFBVV95cUxQYm9abXN3UXFsblJsSXQ5QjZObU9OSTFTdDdiVlBwZGtsVWplWDRDalNPa2lncFltbTlIbGh4VGc3M2h2a09XOWRIRHMwNnFPb29jWkhZQUh1a1UzbWg5V191X2JkZkJPbUtZam9qS1J1RFVsLTAwYk1EeDRBRlN5TTFaYWpOMVhMUGpkNEppQ3VQUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMVRwWkl3dVVjVlJLaWFxWmpDekZiRF9nNVVQeWZPcnVOZFlvQnhHc3hoQlF6eHNPdVNkNVNrbnRmdUdSTm5uQlZWYncxVGpPaVU5SmV4cTgxZG9QVEZRU2hvSC1RVmZIbWVZNzBZZ0laNjdCaUxEemFaZ0hsZTNmeGRVQ1VyWm8tNGd3Umk0Y0k1VzdxbXNHMC1ZV3ZEQnRPYVRGeGhVUGdPM2h5a2stUjVwT24?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46019.7219675926</v>
+        <v>46020.35743055555</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TUESDAY, Dec. 30, 2025 - The Korea Times</t>
+          <t>Steel Co. (Gujarat) Limited Matches Institutional Buying Filter - Fundamental Stock Analysis &amp; Explosive Profit Potential - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 03:30:04 GMT</t>
+          <t>Mon, 29 Dec 2025 08:34:38 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQY29Za3kySlZEbThpWUJSWDZNZWk0TXVjN0d5Um1CdDd1OUpSbUYtUjliODdoTl9HT19KVm9XM21rbGhJWVN1ZlpMcHc3SGlJUTcwUmprZkViX0VYYm8zSjl6ZnJ6NVFhUFQwbGNRVEtKQU5YNjByR2hBWnBZVlVBcEdsZEhTNlHSAYwBQVVfeXFMT05wdUsxX2xEVGtHUGF5U2l2Nkk3dUpCRTFRNW82R294TnRFSjlQTlBFOWVFWTU1TGd2TFo4WnJqZklpN3NtRlloYi1JUkNZbmxjWXkwNnNDbGxRUkZObkVLUUtURHA2aDRzYnY1R3BhckZ4WEZfYUw3bHB3RVZuMngtWjVtTUR4Q1dFN0M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQYW13VUFUZ2JSV1RoOThESlRqMnBvRGJmcEZOOW85WXdyZlB6QVE2WURVSnFNX0VhRUZCWEtmNGFEUGwwb0c5WFllT1NqeXRpOVhhMHZXZ0V3NnZHTU9KQTg0NEtOOG1FY3NYeE9LNDZTZ3JXUnBOdmI1d0Qzb1Zsby1PNmpsLWdNTFI2Q0FLU2xQNDJOQVljTUxjejFuSmpsdmZVelhIUm9FbTdQVFlxWHpXUzl4dmNKRC1nUTJqczlyNUxfS2c?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46020.14587962963</v>
+        <v>46020.35738425926</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches  France  French language</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fibonacci Support Holding Strong in Raasi Refractories Limited - Market Liquidity Analysis &amp; Explosive Growth Trading - bollywoodhelpline.com</t>
+          <t>Morris Engineering Company Limited Possible - Stock Valuation Metrics &amp; Outstanding Growth Opportunities - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 01:13:53 GMT</t>
+          <t>Mon, 29 Dec 2025 08:39:45 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNQXpoYV9laWVhYjRJZm1mYWk5VjgtNEJ4Q2NOcmxkNEdFSHJPd1B1eWROSmlqeHE3a2ZSVW12NjFNT21YcU9lcmJWLWQya2p4eDMxVUMyMmRpb0pxZTIzdFFGdzRBM0owREN2V1RaZHpoLXBFdmpIMkNMbkRwTXIycFNQSHVaM1RrUnFQQXZCZFJYdzV1ak5DdHl4T29Cd3NDaTJmNWlSeXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPcUQyRVQyUndOVEQ2ZF9YWDhZbnJkRWtWWDduSG04WFFyUlJzYXo2MFZNb1N0YUl4WHBNZ1BaNm5sTXgtNDRNQ0NvZC1oVk1NRGxYX2xhQVhFMnZKTGRPUUVlcFp5dTIzYWVHQnpPeUNTblVXRkNtRHN0LWE3SS03bE5oS2RMV3BEdjhGRVBhUEc4elVfRF84YkRHemkyaXJRc20tTmE2UFVoNGFvd0hyejlVMjY5dw?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46020.05130787037</v>
+        <v>46020.3609375</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>🧱 Building Blocks: How to Read and Use Volume Profile - Volatility Trading Techniques &amp; Free High Yield Investment Strategies - bollywoodhelpline.com</t>
+          <t>Houston Christian visits No. 3 Iowa State following Momcilovic's 27-point performance - FOX Sports</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:44:15 GMT</t>
+          <t>Mon, 29 Dec 2025 09:43:40 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNaUNWX3pCMjJVbEd5cDljbmgtbVVjUjVFSWtoY2VfY2YwZzNkVzE2SWlKblNteUV3a216X2JlZFkxLU1BaENaSEg3eFhkWkVtTGFvUXRHel9Oc1c5WVdtNnFPUHJTX1I4NFVzTXp4dDR2V0FlWjFuNzNhNlBmQTVtSVR0QkxUV25vZnVfMC1hS3k2ZE9ZMzVlQTlraTh3bFgzWE1EclNpbFJ3b2tlYkhKNEMtcW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZklKeXFnVWw3T3l4YVE5bkxLYlF1bFd6MThYV1puZkp0NW1oVzlFRGtDZjg3V2dhTUM0NjZaOFBaNWljbTYxWlpUd0ZIb0duREVoMnFMOE9jZU5YdXZwcXFJMTU0SjdCVUJjRDUyU1BWV0JBY1ZQRU5Xem4tRkpkOFROZTQxcDN3M1FlX2VLSW13ano2YkpXZzZWekNRV1pRT2R2NkVtMGlYTllMM01fY2REMTdIZ2ZZNWZTUFlR?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46020.28072916667</v>
+        <v>46020.40532407408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tinder Date Eye Gouging, Officer-Involved Fatal Shooting: 2025 Top Eastern Montco Crimes - Patch</t>
+          <t>Christian Pulisic denies dating Sydney Sweeney and asks media to stop - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 16:11:00 GMT</t>
+          <t>Mon, 29 Dec 2025 11:36:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOUDJmeW1sejl2WTBlMTZ6NEZiUXI4LTAxczBWRDNrYWFhb1RIUXpFaVplLWJzRHpBSzZMa2xENVE4Qjd4OHY5YzlUdThEbTJMYzQ1WjJKTDc2TXpTZk1lQTNEUHJwdGVFcEw4VnUwcUZWLWZRcFAxVmFtVDBZaXczSkFiTm12aUxqdWhScEJFZTRLaFVEd1J4bF94LUdGaXlqajh3Tll2djNfMXdEaW42Q0l30gHWAUFVX3lxTE82OEoxOURkTXg3dkFMNnZJc3FBY25vY0h2YjJtUXhLT0JBWEltcVUzUnBtRGF3cFNwazBfWG9vTTNKTzJKMi12eVQ1WFc0NVI4MUZGbkQ4Rk85MHVwMkZnUk4xTlhWQkZ4QVhRUUplUHJPR3dlX2FlRUtkY2NsRndndE1IWUd2VVRJZzExVUhicU5IMUV1anpTMkN3cEtHVnlGdUNNSThTYkRTU09qaGRiMGtCQXl1NjdTci1BdXdDaUtfYVc3T1ptVXYyUVRMTE1ncDBiYkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBPcG9tOVlRbUpzUHZuX0tncTA0ejhoUkhJUGxfN0dBZ1hEanNoOHA4dzBzQl9qUDVmNUo3V1R1MUxUQlZlenNQbVc3eEw5MUcyeV9SRVZNaGR4UGxac3VqQUlVc3d1WFhuYTVwSnd6bXhMalVCM0lRdDJtdWoyQmvSAZMBQVVfeXFMTVdkQ2ZfS2FMcDBaZ0xFWXB5TGZ5YjhUNHpleDZXOUdjSkJXcUhUTUQwRjBzVGlabWNqRVBTNGUwQkZUMFhqM2g4SWV4S0hVUWRBUVpwa3B2dGVQYlBYTVhfNXRnRzZxbEdEU3RmRjBIdGtkQ1Z5cUVQMUlmdVlmV3UxbDFfbkIxaDZGSkRRb3d4ZjVZ?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46019.67430555556</v>
+        <v>46020.48333333333</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Italy, English   language</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Trendlines Suggest Libord Securities Limited May Bottom Out Soon - Earnings Date Calendar &amp; Big Data Market Reports - bollywoodhelpline.com</t>
+          <t>Doncic and LeBron calm the storm at the Lakers - MARCA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 18:00:53 GMT</t>
+          <t>Mon, 29 Dec 2025 10:35:48 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOOWNSaURJNEY1ZjR0TU04M2lBby1uMWF4ZkJNa0JFWTdWUWxqTnhZbjh2bUFBYXY0ZzBBUkVnUXd6eDFaQnVoQlhYenZQQ3otd3VpNjFvTlhBajFYWjI3a2I1a0ZlUnRIanFLQkU2TlFva3ZGWVNBWEdBQXNGb1R5THlXLWJWelg2cFV4OUZJcGVCVEZRYWx6Nm83bEZIbUd1aXc5UHNHM2ZSbk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPcjc2b2Vha1kwRUJFV244cHhCN0xxZGZYSXoyT2wwYmpFRkJaa1cyVTQ2dGc4eGFRSkRXUVlRM2FfaC1zb1g4YTJFb3pxRXRhNU5naC1uQ2NJZFRqR21nQXVsaDE5VzYxSXJhZEx0MUI1VXp0bXN3SjBWeXJYUXYycFlGWW9jRzNONDd5QzZNTGE1amNsdnk5WUpiV3NIZGM00gGgAUFVX3lxTE9yNzZvZWFrWTBFQkVXbjhweEI3THFkZlhJejJPbDBiakVGQlprVzJVNDZ0Zzh4YVFKRFdRWVEzYV9oLXNvWDhhMkVvenFFdGE1TmdoLW5DY0lkVGpHbWdBdWxoMTlXNjFJcmFkTHQxQjVVenRtc3dKMFZ5clhRdjJwWUZZb2NHM040N3lDNk1MYTVqY2x2eTlZSmJXc0hkYzQ?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46019.75061342592</v>
+        <v>46020.44152777778</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Report: Raheem Sterling’s transfer preference revealed with January window fast approaching - chelsea.news</t>
+          <t>Independent fashion shops see Christmas sales fall despite busy city centres - belganewsagency.eu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 17:30:00 GMT</t>
+          <t>Mon, 29 Dec 2025 09:09:00 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9lMVQ2THhhMTFQdEN4cXJIekRrQW55blJnQzFzV3Qwc3Fuc19rbUVJTmdqWlNRMGw4eHQtYW1iRE03ZHByN2dWVVQzMGk0WVF6UjgzNHdsUlRPNW5YNEFkN1JCMk85RndRam5pZlFYMmJMOUw5TkxZ0gF8QVVfeXFMTmd1OGYtVW9CbV9xWHhBcTlscVJHUEdfVW5QVnFmVENFWFRrMmstNmpmQzN6MXRhNXh4Slp1MUlQOFd3bkE2aXdPTTV0d0R0Z3Bicm4tdHRSbU1fWVBZaXZhNXZhR2pWeXJja045THduellldEJLOXFyZFpJRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQbk9iZElhQzBEZ2hiN0xPdFlPaHJ5ZW95NXRld0JRdVoxeVdncUxJMkx6UGJxUndoeGJxWmtOWGJ1LTlhSkI0YnZVWVlCdjZSQzI5b0ZEdFdlZTRKYzk5LTJJRmdueEM0ZFhja2h4bzc2SEtYNUw2RnVxemtIVDRVNUpTdElCODV5UmphWHFGU2gySGpDV0lqV2daTV9LcEpUaGNjY25WOFRUMFk?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46019.72916666666</v>
+        <v>46020.38125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>How “Emily in Paris” season 5 pays tribute to assistant director who died during filming - MSN</t>
+          <t>Brussels sanctions, fertiliser wars and European farmers paying the price - Brussels Signal</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 18:46:24 GMT</t>
+          <t>Mon, 29 Dec 2025 10:55:50 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNbTlPMVotT29CeGV6WmZYN3dVN3NrNTJncnJxVHVQS0IyVWczT3hHYi16U0s3bTVoTmdnMEhIZThjUEgxWVdvcEZ5Z3lZUVJhNHlCUklaVl96X3FZRzg3a3F1THJOU1F0WUZOZG9RVlBHdk1qWTZZS09icGg2QzJpQWlzVS1aeHA4WFBDNk90TE1RcFR3TjZZQ0ZFcEk3aVQyMTVOTGtLOWtPbk9ycTZSbDdROGdQMmxRYkxrQ3Z6b05jVFdRSnowcnZmdUZHZGRjN2J4MEYyNW1qRFQ0YU9ZZE93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPVkczd0xBQU91bUFQbkVGT3l0VjVmODJrWVoxU3ZlZjFXVzZpTHJ4NzUwLWtnc25zdnNjNDBsOFI3Q2tUeVdxWnRWRzgwMUhTRklZMkwxMzYwT2I1WjFHVzM3c2MxZXJhWWlidWtMel9pcU1wNDJTeWV0OEhGWXgwNjQxRTRINFR2SzNOdTNLX2RqTF9ydlI1OVV1NmVyVUs2MnFSM0ptR185RGc?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46019.78222222222</v>
+        <v>46020.45543981482</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bardot: from defending sheep to flirting with the far right - Dunya News</t>
+          <t>Activist daubs red paint on the front of the British Embassy - VRT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 06:41:10 GMT</t>
+          <t>Mon, 29 Dec 2025 08:55:14 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWkFYT3pyYXNfZnBUN1VKVWEybEhGV0cwVmJLa0JxcUR1akJyRWg2R3h4VERxSUtGMnNpYVZQUG8tbFdidFh1bDZTREsyZG9sSUx5RHcwOThBSURyWGZ2YVQxVlBxSVR5ZTdwSEQ4NWpmQ2p5R3QtcGpCT3dvZmZyN2hyZ1R5Rno3RmY5RDAwVlB4MGxSUmtvUkhkZ1c2dm1EMU5ZNlh0ZV91SFN1dE9XbHg5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZ01JZUN6dFFEOG56NkJjd2dBNVNpWUt6cVZMS2tPanBsN04wSjJHRVpMZGw3TzdTOG1vTGVGNFU3TmhaVjI2SnFBWVBzcExJR2xQTThqM1gwYUJrY0xrNUdPdmlYcWNiRTJNSGcyNTVCMm93QWVCN19icVUwd1cxVk1JSXIxRmowQTBRMnVZZ2E0dGw3V1VnSlNFU2FYb0kyQ1FJ?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46020.27858796297</v>
+        <v>46020.37168981481</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Disney Changes Spider-Man Ride After Just 3 Years of Operation - Inside the Magic</t>
+          <t>Hoti returns from Brussels: No compromise with Serbia! Only mutual recognition. At the dialogue table until an agreement is reached - Balkanweb.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 15:40:28 GMT</t>
+          <t>Mon, 29 Dec 2025 09:53:27 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9GUW9FN25JZnFwQVhEc2JKaUFqRXJtaDNreHF6bmFMLUdUZEpsOTVXTExVems3enBNd3lkWTU3YUctM3ljYWN5NmFvTmlXendOOUUzNjQ1SFNUbzFVMzY1WUxHREIwektwMDBWYW1ZNVNGTDdUZXZrMTR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOQzZoLTI2QmVwY3FyZmNFTUtzUTd0Nk9rRGVsVW5kb3VBM3pibG0zS2Q4eVdYYnVwem42d1JHRTdQdzA3Tmo3WFlQdTdldUNUdW8tdzY2VjI2dGpwQ2Z2REFLb1EzYjdfNlREZzlSOWhQMUJsSGNNdmliT1dYd1JHZVM3MnFVSWxzOUwzUGsweGE5Mk9XbnR0Nzdab3VOTk9Ja1QwaThzU2RSbXRtc3BIUmU3VlNqTXN5R2JRdVB1eW16VWFsb2VxX1pOZ21pUW9LUFJ3NFh3dWpINEFDV1NRYkZ4d1U0b25fZWQzYlFtd1lsUnB1?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46019.65310185185</v>
+        <v>46020.41211805555</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Belgium Dutch language</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Young gun O’Sullivan shooting for the stars at Melton - NT News</t>
+          <t>What happened overnight? Police blotter report for Monday, December 29 - Newzjunky</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mon, 29 Dec 2025 04:13:54 GMT</t>
+          <t>Mon, 29 Dec 2025 12:24:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQcXJHNFExMzl3bWYxSFVfWVRGS2tpek93RThTTjRnVVpFRnEwelprbEhmaDNiRktrTGZ5eWdvanVSbllvRm94bG16aGFFejFFTDFCdk9lTVZ0b2RmNFhISk0xTWdYWUpyRVRTOEJSbFItN2FVZVlBQk1jSG8xNTZaYUQwTGZZaklfeHlITW5Bb20zTlQ4OHFodkZjbExGZFVrcDNMS3NQbm9xT3MwakEwMHNZdkw1YjgwRlhqTTN2MFdZZVhZRmZ5X3ZZN2wtRC0zS2EwRjF0YV80NmdEblN2MFhYSW5DMy0yZlhmaEVjZzEtZ053OUxyazBrQ0ZZWGl3dGRJNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQS3Boek0wZXdsaUFnTUV2dmwxWllNcnRiWjdzMTl5RzM5dzdtb0ZJcExKRmtvQWxkZEZFWXEtN0R4MWtFMVV6Yy1PX1EzUHBaVk45TlhkTFd2RExnYTRXYUtlNnJsbi03eXJpeUZOenBTWGZNZnNIQ0FxRE54OFltazVja2U?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46020.17631944444</v>
+        <v>46020.51666666667</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dupont sparks explosion as Toulouse demolish La Rochelle - RFI</t>
+          <t>Police name man found dead in Co Down - kildare-nationalist.ie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 22:20:15 GMT</t>
+          <t>Mon, 29 Dec 2025 13:01:27 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUVVWeHU1WkpjSUpUelZrcGhkLWllWF85X1FKc2NNUnVGMFZoeDI2eWdDWExYXzMtMFg5WGJDeVpJdzMtOUtkOFp3emt4aGhKQUxLeDQ1Vnh0VXVTck5CU0RnMEVJbVRORHZXd2ZBSE1QekpnWFlGNUhyU3Z1MlJVdFp6T1d5aFZvamlEaHZNbk1vRDVNU25CZU9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOd3JpNGN6QkFpR1FkV3NLeHp5N0JwakxwdjJOZjR6RW4yZC1ISkFjMXY3dE1hZElFaklMOEV0a2s4YnUyNVhOZVY1V0NsdE1PSUVWek5RUlQwc3NWVkJJWmpNUVlFX2VIT2FaN1E0eE02U1J5ZkJ0NDBqNExNcXBEYldvYTdYbXFTM1g0SHJmVGhxc0o0WURtSg?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46019.93072916667</v>
+        <v>46020.54267361111</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Suriname Man Goes on Stabbing Spree, Kills At Least 9 Including Children - Shocking Details Emerge - Times Now</t>
+          <t>Applications remain open for fund aimed at supporting historic buildings across Kildare - Ireland Live</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 16:57:54 GMT</t>
+          <t>Mon, 29 Dec 2025 13:33:40 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNLVQweFRaWVdNOERicVNvLWxTQllldHkyd1NKT2xkNWpIUnNnVEx5XzRoSWNtVUphdWxoUGV4dnE0aGxVSk9JdHg4OGVyam5OTVhqMTJIbTNySF9RVTFqRWx1Y3NZY3hJUUMyVmlsbW0zMlIxalN6ZWZXa2gwUENTcE85ejRsSUhpSFpxVktpbDNrTTU4RDhhdWVmV3hmdGxDdnZyS0dMSWE3aWN4ZjV3NVlHRUVFNmZfVzUwUk9FYV9tTkg5SGFKdXVjQlR5WTlMdnd6WEx0YmJtTDFBc0RRQ3owNmJ4N2lKaGJXeVd5Mmx4dTE4eXFzVTQxNE5MTGtscEZRUlJYREMzWldiM1RPVDBOaW1QQdIBmwJBVV95cUxPSU4zZWJBV3p3eks4N0puTkZtNE96UzB6cE1CanJRWUxpS2ZFc0tsQkVhdE9pRkpDc1ItR1dMMlhxdjM4RUJyUl81LTdzbXBpRnYwQkFKQnc5bFhpOW9qclQtQTRmOWNSMmJBa2tvV1EwNGl4VWpqV3cxRDAtWEtmXzRzeVFnbmRicjM2bV8weFdaUVhmbFNPb3h1dHdWVDJxNEdfR0ZzZUNjTDBiWUZ2TEdYV2RROFVobFUzQmdNbzlfdWhOUkRhaTIxS212VW5vaFFyelJPRnlFRXY1UGpFZVk1ZzcyQURxY2ZVdmZQLVZXNE9yQTZwMTVwVGh3aTQtVHU5ZEFQUHI5cy1jVElYdTZkeFRGQy1oOWxF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTEZiQS1TSXpxSUd1YWFHVmlHOUViT3hzSG1VYVMzUWhjUHZPd1JDUEtTSmFlcjliWjBKUkNqblV5RU5HV2lCRXc0ZFZjNFk0ZFprd3BuaGRXSXEzb3VnNktLRkZsRzFuN2dTeTR4SlpIaTF3S0hib1dwTFJYVU1SX1UzVS1KUnBjQ0U4clk0eUJrRUREb2ppTjJnUGFZMWhKdThRZFdDVkEzVjA1VXF5ek4zZ0I3SUc2V0VyX2J6Vk5wa2JIWi1COHRrWnRXUlhqOXF3blV5Z2VGa1F5?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46019.706875</v>
+        <v>46020.56504629629</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bahram Beyzaie renowned Iranian director and member of the Oscars, dies at 87 - آسیانیوز ایران</t>
+          <t>John Major reprimanded John Bruton for ‘stormy’ speech in 1995 - kildare-nationalist.ie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sun, 28 Dec 2025 19:59:00 GMT</t>
+          <t>Mon, 29 Dec 2025 13:45:42 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOelQ0V0k4ZU5IVlRIQXhwTlNKR01lU29BRHFxaDQ1UGZ3N0M1Y3loQTYyQ1NSNTVseUVwTGg1OFN5ajFDOTh5WElFazhpd1BTM0QyXzk3c1FidUxmZHppYU95bEVkRU5qUDBnbV9pSWVSVHFSd0NQeEtJeUZTUWQ3eDNFS3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNc3o1bi1IdW5yTHd6WVdnNmY5SkpOaV9naVloVWV0RlZVZkJydjhIaUNCcmYxMlFuR3BacDVZTHk3T05JN0JFZTFLWXNjel9BbUtON1B5aTVrMWRmVnFjZVVOcGFyTjVsNURwTHpBRmZ0NmE0ZEhIUlZwN3pGU2RZYTlpWjVTQnRtUkc2MFZtQWlYd1lpVGtORVBrTUJjbVlQWkc3bG1qQkQydnVULS1DOWI0SEN2dEU?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46019.83263888889</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Gujarat Petrosynthese Limited (506858) Stock Rallies - Risk Management Strategies &amp; Free Explosive Trading Growth - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 18:27:43 GMT</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNM19HU3dLQXhIZ0o1cDk0MnVaY0o0SnU1RG95UGltV2dtcV95Tm9OMjdpTFhjY2E3a2lqZDRzRENZeHNSTWowWmZLNldybW8yRUozamNodHJZaW9pVkpFdmMzcThLb2pjOGx4ZjlxT1RhNlpnZWZtRlNWdUN1aUhFX2F0WnhaeXo1d0p4b2hrdXo?oc=5</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>46019.76924768519</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Guinea junta strongman headed for victory in presidential vote - The Manila Times</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 16:03:00 GMT</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNajJSNlZkSjc3RFhoMVFnSXZEU0VKRXNTVVl6SUlMMmJVQm00M0V2V3NFT2REUmF2Mkg2Y3REUldWLW9mUE9WWFdjT05sR0xjYjNJQVd0Zmt1WnV1Ums5a1BBakd5SENEcVBfcmZhbkhQZ3Q4RVdLY0VvWEFVbnQxZHNna2dKY2ViRk91NTNkQTNTY0xxeEdhWkpZNFdNb2ZmLVBjTU4tbmd0b3JTeTNudHhtMFo0bWlmX0xpVGxHZjRGYWwyMXBNVzU5V2poQdIBzgFBVV95cUxNajJSNlZkSjc3RFhoMVFnSXZEU0VKRXNTVVl6SUlMMmJVQm00M0V2V3NFT2REUmF2Mkg2Y3REUldWLW9mUE9WWFdjT05sR0xjYjNJQVd0Zmt1WnV1Ums5a1BBakd5SENEcVBfcmZhbkhQZ3Q4RVdLY0VvWEFVbnQxZHNna2dKY2ViRk91NTNkQTNTY0xxeEdhWkpZNFdNb2ZmLVBjTU4tbmd0b3JTeTNudHhtMFo0bWlmX0xpVGxHZjRGYWwyMXBNVzU5V2poQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>46019.66875</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Options Data Show Bullish Bias in H.P. Cotton Textile Mills Limited - Sell Signals and Alerts &amp; High Yield Market Growth - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 23:59:30 GMT</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQcE1BOHRZV2VPZTd3Y29xekdrcFFYMmFEOVRpUlY3b3oyWG9EclZkN25iUHZhVy1tbEpici12TFFHcjQ0U1gtM2I1bTY1aGZLd1lDUXBFVnBISlE0ZkJYcWpGMHJHVUNoenJwVTJKaHo4V0RuNzlwWGZCWThFNjJ5UUwxVV9Vb0NsdFprRGZ5YmFlZUttR1RDdVRXRkpSd3E1aWNCMg?oc=5</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>46019.99965277778</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Bulgaria adopts euro amid fear, uncertainty - The Manila Times</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 16:02:00 GMT</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPdzhnTGhNUDZVRHRvRlFNckhSN2Q3MzI5N2FNRmlsRUdybXh6a181NjJIV2s5Z0VHMGxzUndvMXdqOWFKeE00dmJGcm9uT1VMYXFDQXlqVUxCWWhaaWxiLXhiVkhfVndEY05jbzJBWHE5RzdiYXhYQjdYX0U3b0d3b1dtX3Q4U1c4akRHdjFjREpOSHhIeUtsN21XeEgtWVpwWngtUjVYT0dhWG1XbWRoVUMtWdIBswFBVV95cUxPdzhnTGhNUDZVRHRvRlFNckhSN2Q3MzI5N2FNRmlsRUdybXh6a181NjJIV2s5Z0VHMGxzUndvMXdqOWFKeE00dmJGcm9uT1VMYXFDQXlqVUxCWWhaaWxiLXhiVkhfVndEY05jbzJBWHE5RzdiYXhYQjdYX0U3b0d3b1dtX3Q4U1c4akRHdjFjREpOSHhIeUtsN21XeEgtWVpwWngtUjVYT0dhWG1XbWRoVUMtWQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>46019.66805555556</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Tech billionaire Durov’s claim of fathering “hundreds” is a genetic time bomb experts warn - MSN</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 22:56:02 GMT</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNVGVFR0E4YkxKYkxBVGVYM2F5bVBKWEk2dFg3SEFqRWlHTTAyOFlsMFVzbHRVODlaUTlpY1lkWk9RdjhibFU5eXVpaGJ4dll2NHNtMkFPQ3ozTmZ4ZjYtS0o3YU8tdkFQZ1JBZzNzakpJc3JXaS1uU1prQU14VmVSOTh4dEZidklWMk1CbUhyS2xLYlk4VzNiYU92STFLcl9SU3ZyaHFFWmZhTlkyS2FGdnhvcWdCOXpOeFVxLV9ocEl4UzJhUkQ5b2k0TWZhTHpWRWdn?oc=5</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>46019.9555787037</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>SITI Networks Limited’s Beta Climbs After Market Volatility - Technical Analysis Insights &amp; Reinvest for Maximum Compounding Returns - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 22:03:41 GMT</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTGJ5MjY0UTNZRkE4WHYwbDAwNEwtdUFEU3BnQzRZY1prenVxcE5VX3VibEtjSG9vaXRPWHhGRDdzY2Z4Q3Y5amFoczFwNzNza3p6SzU3bzhJU28zM1p0dm9QejRwcDY1QS1oUDRzVU1Od2hPZmxwcFo4SWNpelZ2TkRqOURveTlhZjlDbkxSWktxUXN6ZFBGVVZsRmg4TWxTN0NOaw?oc=5</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>46019.91922453704</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Macron welcomes coalition of the willing in January in Paris ᐉ Новини от Fakti.bg - World - fakti.bg</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Mon, 29 Dec 2025 02:07:00 GMT</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRTVoNVpZd3JMZ2tacjY3eXo3V0I2aEVCX1pPaWRKWkRaT01qZXMwcXRaUjRLVGlvemF1SkJ5Y3NESE5yVTRKd0M0REUxcy1sdHpTRVhmSjJpaUMzc1FNVXlxeUV4UFhUdlp4eVBtY0dLdGFxTWJzSGp3QWg1ZHFOS0NfRlNZQm5WYlBWRmlLNHRXeXUzeFo3RF9LeFBFRTg?oc=5</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>46020.08819444444</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  English language</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Bomb at the foundations of the EU: The France - Germany axis split into two pieces, relations Macron - Merz extremely frozen - bankingnews.gr</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 15:05:32 GMT</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxOWl9LelJROFRBcTFTYnpGQXBlYkdYTG1EYjJ6UVotZ0dTT0FZc1l1U1k3dFpyalQ1NlhYdkQ3SkE0cEVReFJndkxPRERNRmR2Y0g4ZjJ3S280TWRJLThMVWZKbFE0dXpoUFBjLXlJQTRhV3BtdUJyVFhfQ1lhVlZDV0tud2pkd1JIZjgwZmVyekpEMkdoSnQtLTZYTF9zYTVvcTU5RTdEbVY3SFU0NEd2dWdCSGZ1blNMdXJrb0F1YVA4OFU3S2tGZGh0RHN0NEZPSC05QVk4aXJiUmtNc0VvT1lHWXZndE4tSFhFMkVVU1V5aVBqdE9qUWk4a1FNeW5rYnZUUWUzRmxPX3dEWmJyblUxT0xGUUxFZlpwTw?oc=5</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>46019.6288425926</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>After the Flood season 2 unveils explosive first-look trailer as Sophie Rundle drama returns - Radio Times</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 20:27:19 GMT</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQM1luXzZ6dkxiTDNzbW5uV1FBeENERVQ3RnppMXJZT0NvQWVxSEVVM3I4a0lNUFQ3UWFwWEpwRy1rUlpNd0liQlR3ZUI5Ym1wTjVmcno0aU0weGcyQVJCLVQwMXBCMUNIUWlLTkdiUVl2YzEtMTZ3VGpCWGhKVGVtWUVsUVF4aGNUT3dzTG1lVktuTlRl?oc=5</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>46019.85230324074</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Shriram Properties Limited (543419) Expands into New Market - Earnings Forecast Updates &amp; Target Triple-Digit Stock Opportunities - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Mon, 29 Dec 2025 02:19:56 GMT</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQVWhRUjEzaG9ud1JlUks2QXl3SW1TeXNRMmFzWWprU0liNDV2M0Rkekp1ZmV5dHJZVVZBR2luS3M5OFBBYkJnazBySVZGcmJ4XzVsdTl1czVHNWxnSnNTZV8ydGE2cW0ya3NTWko1cTVQY3hJZUVsUGlNOF93eDM1R1pYTW43SHAyMDk4WVpXMkdraG5fbVQ3MmotR1VRR2Q5OWdqSGlKdmhtQWtCT2c?oc=5</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>46020.09717592593</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Lee Kang-in Misses Ligue 1 Team of the Year - 조선일보</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 16:50:30 GMT</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNMnc3THBmWG5Mb295eTlJT2lkVlNiSXRuTGNjbkt1QXlOYnhHOXN4U1pUeC1qLTBVcmVIRlFjaFY5ZlNWbGdfbEFHNkNtaHF2STkwelNXSF9hUXVXTGxrUGNoMW81YlU1c1JsMy1WcGlZN09xQkoyZDRSSkVHUGpEZ3poQkItdw?oc=5</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>46019.70173611111</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ukraine peace deal close - Trump - PM News Nigeria</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Mon, 29 Dec 2025 06:25:42 GMT</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBrOHQ4NEx1QU5UeE5XTDdDX1AtWTZOdUtHcEoxOU5La21Cd2pEdk9iX3RKeWxkN29oclV0dl9lSGpkV29YVV9jTjY1Z19aMjlQV1MtSzZMLXVHNVRoWjB0M0J5NlF0clB5aWRyNGd2T1N2SmRRUXB3WTZ5UXkwNm8?oc=5</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>46020.26784722223</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>10 spectacles à voir absolument en janvier 2026 - Le Bonbon</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 19:08:54 GMT</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQcFctaDlBNU5IX1pZSzF1Y3FaZ09HOWF2dllaenR4RVV3RldBX0R6WE9jaDBKX0N0LXZmS0d3ZG1Fd0t0QVQ1TFE3aUVDbkhjR2RzOFpGVENLVVBMOTdGNVZBdHlGWllNXzVvRDNnSllyQ3lVRDZqd1RUcEwtM3psVW13OUFiLXBBMXJVU3Bodw?oc=5</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>46019.79784722222</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Vedant Fashions Limited (MANYAVAR) Expands into New Market - Day Trading Setups &amp; High Profit Trading Plans - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Mon, 29 Dec 2025 04:51:44 GMT</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPY2ZSclpiLVhVdzZ2ZUJmSXEtMDFpcV9DYmc0eC1iY0pCMXl6NV8yNl9lOWVUUHRONlVOQ2dvaVBiQ2lEQzJDcjh0MFNBM1VkTEV5cXFFZDZaYVhNRnNWWUJFWDByaHdja3FpRGNfLWJzNG1DaGhTR24wbU9PQlljRU5fVDNsWUV3QUlzbkY5ZXVkZ2FxQWk1YmoyelpSRk41LXVn?oc=5</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>46020.20259259259</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Short Interest Drops in Vardhman Textiles Limited After Rally - Financial Sector Performance &amp; Explosive Capital Growth - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Mon, 29 Dec 2025 00:35:04 GMT</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMXRVZS1xVHFmMGFUcDg5N09LYW1hUmpTVzBVWWFIcXUxT2xrdnB0WVd5cW9DU0ZmNURxNk9iT0o3TVo0bk00UXJDOXN4LV9JNkFwdWc2NHhBcHVhenVUSHZVNXJPMzhsUlZmZFJwbDh5VGF0UUk2ZXd3c1BNMEVoM3phSXFObldYWENLSFBUSnBvV3RIYi1fQnVmNjc?oc=5</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>46020.02435185185</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Kapston Services Limited Stock Lags Behind Sector Benchmarks - Healthcare Stock Analysis &amp; Outstanding Profit Strategies - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 16:58:35 GMT</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQRHZlMm9BMnBDWEIzc2VDcDBVTGM3dEUxLWFXX1FOWjJvOGhheGRxR2l5RmwydkNtWkFaWmgtLTNRdlVYQkJpYWNPbEdPbEhqRkdjR05IWGQwVVoxRTl6QjJwLS00RkpweFM4ZVltaGlTMVUwZFItbDE0eG9mWmdqQ2Y1RHpaYVFOanJzamI1R0tUSnkwei1Fa2JWaV9QTThHMmlOMlJ3?oc=5</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>46019.70734953704</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Is Rajesh Power Services Limited Forming a Bottom Pattern - Stock Liquidity Analysis &amp; Market Crushing Stock Picks - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 22:59:40 GMT</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPYVNjbU5YNXpMY0FBdGZWZDBRd2c4ZWd3aTFkeXIyWGVtSzFkM1VlSUlUTXhYX0RJb1Zod2U3SHppX3JnbXNnUlNOTjlOVUdSNVZoMnJyWGhNY1VYWXY3aGR1RlJSd1NEYzFzSzFFWldydXUzb0NQa1ZGMy1BVllmUTBOc3NUcWR2eW5NaWxsTHJpb1pwQlZJ?oc=5</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>46019.95810185185</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>High Level City searches  France  French language</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Thomas Cook (India) Limited Recovers — But Is It Sustainable - Dividend Stock Watch &amp; Explosive Profit Potential - bollywoodhelpline.com</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 17:48:44 GMT</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOT216WWZwQkpyQk51R2R1QThkbWM4ejJHeGJsbXhSNnhVamVtWDV6YThZMmViR2h3Z2xsa2hjLTFJVkE1Ynp2SDVxVHE4US1LSGJjdGtrWHZwaUFYUlpBOU5wd2toUkNuZno3NW9qR29YdW9SbG5GOXNWSTVEYXk0RnJnQ3NmaU5wUHJ5Rjl1ZUMtNDZ5a0VpWW9TVlNsNUo0Y3VEeGYzSkg4WmE2LVo2ZmRR?oc=5</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>46019.74217592592</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Oklahoma man doing target practice in back yard charged in fatal shooting of neighbor - The Guardian</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 17:23:00 GMT</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWE1lajNQQ3Nqb29oVUUxN0l1cFU1WHlUR1c3cEhpZjNicG90UmMyR3ItcFdwamZydmo2b3ppZ1BtNkJiVldrSDE1ZGlaYjh0bGRPLWtXVFZ6X0pDdTBrSk1FZllIbDhFS3JoV0lHV1lNVl84aGZhYXByQ1J5UUVzc0NsYnNDUnJ1dDFXQjh0dU9KcVcwWTluZ256c0g4SXl3LUE?oc=5</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>46019.72430555556</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Baltimore Police investigate fatal shooting in Federal Hill - The Baltimore Banner</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 23:21:00 GMT</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZkdXVkNGQm1LS1VFLXRlSWt4S3pUTVB5MXZRWlhxbGRCelJtNURPaWEwZWZlckljbmt1ODRqQ1FXWUZtakhya2lfTXp0NEc4X2FQMlBKc3U1WTFobGM2UGRJSDFoeENWRUIxeEhzRmhHaU5nN3haVW03bG8yV1AwQjlLbTRkeVhUa1Mtb0I4VkEtM3FIWlJNS2dScUVFN3FqNWl2dVY3T0hpS3JvdThtbkI0SVE4bHVlV2JsWnRsZklQY01MQ3ZCNDFn?oc=5</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>46019.97291666667</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Player ratings: Milan 3-0 Verona – Pulisic and Nkunku get the job done - Football Italia</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 14:33:12 GMT</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOYlRJNUwtZnY1VTRCRVVuM1dKRzVQd0VCZ3dmOGZHUXBqdlYxVm95cFhWLThMNG5ueUhBNU9kY203djZtak5DSzJldllJTGFwckdzUWwtdVl3NlVmSkU1T3Nsc01rRXhnOVBXZjBhVm5td2VPWW51S0VfUUdjWDN3b3JsUHRDQdIBhgFBVV95cUxOYlRJNUwtZnY1VTRCRVVuM1dKRzVQd0VCZ3dmOGZHUXBqdlYxVm95cFhWLThMNG5ueUhBNU9kY203djZtak5DSzJldllJTGFwckdzUWwtdVl3NlVmSkU1T3Nsc01rRXhnOVBXZjBhVm5td2VPWW51S0VfUUdjWDN3b3JsUHRDQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>46019.60638888889</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Pulisic ends 2025 with a goal for AC Milan. He’s hoping for more with US at home World Cup in 2026 - FOX 56 News</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 16:05:24 GMT</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPbFRDMUVIdmpqRlhtWUJ4bWdHYjBEYjFBUlpaWVloNE0yaVhibjd4OUJnbEpmYWJVUEp3VVVUQnROV0dtUUJuNjE1a2t3anZIOEZ0N0NzVk42WW5oUUVBRURINktLYUVzYWhxdlExQWNkX2pnWEt5eUlTS2QwRGlwbVR6UWt2ekV3Z08zejNBMllKNVJwMjhobVZqOHRwS21rS3Vhd0s3bEM3R09UX2NpeFFDWWtWemV2NVFoMmoyd0hkY0pxblh5dzR1bVQ1SkM1QjBNNWJjcHnSAd4BQVVfeXFMTU1TT2UwWHBpaGVpLVJCaXBmeHE5eC1Ic1V2RUZQRmZIVmxINkRzdDdnNnU5MmZFWl9iNEpta0xuSWtSYWF4UjlOb2RDckQ0bnVfQnp5ZEFzeVRjNTI2T3JMeDY5Vy1PMmlnVGdoTGZ2TnB2TzVDaFNEZHRhSXV6QkhnMUNLYnVlbnROX2JYQ0plWTR0bnhHVU5tazFjU0FPWW95ai1iSUhFX1RVVGNyekxiX0czUkNId0hRcTd4LTk0dE9KOWxRY1I1c3p6dXNUWUlOUDRXVW1vX1FpZGZR?oc=5</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>46019.67041666667</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ADC Spokesman Knocks Tinubu Over Europe Trip - The Whistler Newspaper</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 20:06:03 GMT</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE00LUxLWkpGOXZCeURLQXBoOEF6R2s3RUR4YXMxTlYxbGNQVVBFUTN5dzQ0ZFpUb05sQmdOcFZsMnF6YTBqekJ2SHR1aXlROVBUZXUzRUV4X1NVbGdSZWlwTDR2MnB0bnoxbnNSdjNfMW5CMjNiXzFJ0gF8QVVfeXFMTlZLLUp4N1dwdUdtUEhhc0syTk01VW91TnZyR1BNYVh3S3MxMU1MenpTN3NlQnNZTlA5enZBVmE1ZmNVRzdwT3hxRS1IVlYzSXNxWE5HS19OakdBdi1lUHRXM21NOGVGZmNxWVVwZF9ScFNfYjN2enhnd3hqbg?oc=5</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>46019.83753472222</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Pulisic angrily hits out at ‘made up stories’ about dating Sydney Sweeney - Football Italia</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 16:56:01 GMT</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNa1lQTEFHQWtFcEZCRS1OMXREa0JkMmZfekV0dWdvVjljZzdTR1ZzeVRhMDZCcnFCRUtSRkU4NFpEa2RkMlB6SDJlblM5Y0xWbXhZbU1RckZMZlZJbDNmOEJncUt3RjFrcWgtb3FKaUpZWUZiOXl2Y3VCdDE0dkxvdUlySdIBgwFBVV95cUxNa1lQTEFHQWtFcEZCRS1OMXREa0JkMmZfekV0dWdvVjljZzdTR1ZzeVRhMDZCcnFCRUtSRkU4NFpEa2RkMlB6SDJlblM5Y0xWbXhZbU1RckZMZlZJbDNmOEJncUt3RjFrcWgtb3FKaUpZWUZiOXl2Y3VCdDE0dkxvdUlySQ?oc=5</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>46019.70556712963</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ragin' Cajuns make it two in a row with holiday win over Norfolk State - The Advocate</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 22:45:00 GMT</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPXzg5WlFKdGN3a2lMNHVFZHREM2xTYXdtbGNxSnp2WVhwaEFucTEwMURocUFQV2pGZDEyQ0dBMFdsZnk0Tjg0cjJFSnF3YkJIdkVYeTk4bEVDWF9hRVQ2WHItYkZ0VnJmZHpXVC1qR0YwZS11a184UWZnbGFXTFphVDNFNFVRSW5lZ1ViTGotMWxuTlBfVk1jaWk4cmhiREtfZHphWXVRdkF4cnp1eDUtQno2M2RpeFltSlJKLVhVLUFqb3NJRnRTWi1NZDJqSjBjT0hONzg3NXFfYkRFMW95R2o1VFdoR3RxdUYwXw?oc=5</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>46019.94791666666</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Jay Idzes Demonstrates Resilience in 1-1 Serie A Draw Between Bologna and Sassuolo - Semana.com</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 20:02:44 GMT</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxPNVRTNV9tNXN0SDJtTTVhOWx5Smk5d0dhTXYxN2N0UC1mSU9Gbi16alE2WlRHUUNYMW1LOW9CTndtTWVFVWRmcmlHcjFzQmg5djMwcWdHcl9ReEV4OWZCRDdEWW40MzVkd3BBbzdaT1lCQW1fQkxFaUwzNkNTTWltQTFyRFJpek1MUFIzSHk1QV96T1g1MDIzRHNybFJJeldPOU5EemtmVHpXZ3R5OEZhUDlNNWVKRlpkX3VDVVVuaUFQa0puc0dqRng2UzFjeUNlX2VXSGJpOTVIbi1oQzRXd3UtRHZEbzc3MzVOcXU2N1p2Y1lFVDRjVmh0aGdBNE5DRGphMWVhempBbHA0b1hlbzIyVGZJNTh5Y3FzUlFWNHVqZnF5?oc=5</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>46019.83523148148</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>High Level City searches   Italy, English   language</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Mumbai Crime: Vile Parle Man Booked For Assaulting BMC Officer During Poll Duty - Free Press Journal</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Mon, 29 Dec 2025 04:53:34 GMT</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPanFLYjVzY1Atd3JLazZwRVBHYWFNSDgzWXpBbHBPN21jZTY1Vkh4YVFxZUtBMnRmMTdSWHgyRW1TbjhCOVBfQWFSLTc0SmJ0Y3daUlZwYWlNQ1dvRTJzcG1zR1NSTm9xUHkzRWlpcnFZbElUd3FqSDlzUnk1VVlQM2R4aDA1c1VhWjNPMmV6UTg0SzRKMmRoVmNCS3NyUzlDcWFpNkt6RTVnTkMwX0JTR3g0UUJNdV9G0gG-AUFVX3lxTFA0SHAxMElPSzVyUlU1TlF2YlMwSUxYN2ZzdGhud0ZrR1dOYk1PZF9qQW53SS0yMUxoUlpXZkR1S0dYZnhRWkxWTUlYUHh6RENqT2NmUDFnVzRBa1Rtb1hGbU1SQ0hLcnhCZk9ta0FOeUg0UUFWZEV6TWlPcnVHYzBJUGwxQmxhbE14OG5CWXRqbGFDRUNOSFhHMThid21BTEQ2eWJZaS1rS2l6UFVYT3JwZDg0b0dGNFNWWnFCd0E?oc=5</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>46020.20386574074</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Dutch police deploy drones near Belgian border to curb illegal fireworks - belganewsagency.eu</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 17:12:00 GMT</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPNzhLYUN0U0Qxb0UxbWpFaEp3a1RDX3VIa1pEcEZVTC1tS2d6dzRDWHRyOTlyUk5ZT1M4MEZyQ3VKVHg3Q0xrY3pZOEgzaG5lMGZrYWVOc0t4em5LSnNGQ3YtQlRVUmpmcm80WXJpUG9xcXBBVFlwWmVGN0xNckZlZXlLZkRfYXg3bnphbzlQUUF0T3pUaUE4bXNJWjAwYm1MQVIydVJR?oc=5</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>46019.71666666667</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2025 in protests: How unrests and clashes shaped the year - AnewZ</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 17:16:00 GMT</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNWXFVYkhjdjBNRGM2cGZ3U1FaZWxRaHg3aDY1MksxTDR4dWhZeWN0a0NTXzRjc0tKeWpQcm1MY0dCTldUeGp3SkVhVS1HRzFESEdNaVFWZ2tmSXNxVHpuckN1RlY1THNkUlQ0WllpQlQtckJqcGxuMWowUDlUVS1IWGhMdERXSTlVWkEtU0J5bzhublQwNTQyVzVQZGlUem55RFZJdFVBVWEydFpfLXc?oc=5</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>46019.71944444445</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>India clears three new airlines to boost competition after IndiGo disruptions - Aviation24.be</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 15:35:58 GMT</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRW5OSlZrUTZkS1ZIeUd0amhVa2h0NXVTTXlzU0lSV2JVNjdnbDBYN09fS2o4cGtqZmptd2JELWpnYjVVZjFmdklwWDJMWkFLUkVBTUZjS25nMTRQZm5jZURvX000T1JqVWdCSktuM243bXFYY0w5RHEtOGpPYmd3dTZUOG0wX3dLU0dGQWlGcEl4cklPQjUxUTNrZnlSZ1MxNVpBNFhlM09RRWw4ellQSzFmeFgxS285Wk5KRnFwVGpXZi1UZTNV0gHHAUFVX3lxTFBFbk5KVmtRNmRLVkh5R3RqaFVraHQ1dVNNeXNTSVJXYlU2N2dsMFg3T19Lajhwa2pmam13YkQtamdiNVVmMWZ2SXBYMkxaQUtSRUFNRmNLbmcxNFBmbmNlRG9fTTRPUmpVZ0JKS24zbjdtcVhjTDlEcS04ak9iZ3d1NlQ4bTBfd0tTR0ZBaUZwSXhySU9CNTFRM2tmeVJnUzE1WkE0WGUzT1FFbDh6WVBLMWZ4WDFLbzlaTkpGcXBUaldmLVRlM1U?oc=5</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>46019.64997685186</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>US bans ex-EU commissioner, others over social media rules - The Business Standard</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 21:44:20 GMT</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbEdhcXdpYmd4cXREZ0V4M0hYNjRNeERQcnBrNGc5Uldmd2pYWjFtY1ZidkZkMktUYVJZSEZvUGhCdGtPc1V1OHFrclJaRGw2MktRSUNBTFdzaHRXX080SkQzeVBEczRlekR5aGJ6cUw4cTlSVEMtbWYtdXk0XzNGeV9qUXU0MWR4blRNQklJMEZBNERHN2ZtQVVRSdIBoAFBVV95cUxNNUo2cjl5MExFOHowVFU5RnVQM3EzcFd3eXZxU3FzZU03ckhjZ2gyeU9ROVI3c0ZoUURTZVM5Y1plbjVVVzZtQ1ZoVUk2Nll1VVlfVUJlX2kwVnc2WGtlTk9DVWtfLWpHQjdPc3BhcjRpMHowM1laMXpzVVdUU0FDN2k0enR4VEwxWDRvUnN4MzFLOVNnQ2dRY1lubG9JTW1Y?oc=5</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>46019.90578703704</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Brussels’ Drug Consumption Rooms: A Dangerous Surrender to Addiction - The European Times News</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 16:33:01 GMT</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNMlR1TWVVRWpwbE8wODN5MlNqRndCVlpiZWM2OV9SYVFzcm5ibGh4eGUzaEF1M2YwYzJpa3NMNmxlbnpxaWFqc2JZa3JPWGFBU1dUR2duSmpHMzBRUFVIMHJqRlBhcjluVU1wZUFPdHBSSFNGZk56aEVCM3V3bVBJWkExSWhlVjViaHF5MHBuYUFseDhHWjllQzBrclJ5WHBPdERMUw?oc=5</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>46019.68959490741</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ice Storm Warning Issued - WWNY</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 22:59:00 GMT</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9xR1pqc1AtZ2NHMFV0M2xOemYzLWtjdzVZM3J3a2NKVnk4a3VzaVkzWEs5M3dtRDNGXzlIUENoSzRtWkVwWW90MWY0OHJKVmk2b3JfaUhYRmxRM1Zvazlmc19zMTI0eExfMXVqMHZGVnJJaFNsYzlNZ3ZFQ2ViN2_SAX9BVV95cUxPcUdaanNQLWdjRzBVdDNsTnpmMy1rY3c1WTNyd2tjSlZ5OGt1c2lZM1hLOTN3bUQzRl85SFBDaEs0bVpFcFlvdDFmNDhySlZpNm9yX2lIWEZsUTNWb2s5ZnNfczEyNHhMXzF1ajB2RlZySWhTbGM5TWd2RUNlYjdv?oc=5</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>46019.95763888889</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>High Level City searches   Belgium Dutch language</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>HRA: Committee supports amendments to the Law on Internal Affairs, despite announcements that it will await the EC's opinion - vijesti.me</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 15:23:35 GMT</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQYnA0SXpSdC1pMjB1TlNxOHpmZFBTOFh1WHljVTZ6Q0VrZEdYc2lWaklfU21id2RWaHVXQi1OcDRLVWRXNHhwYWIzc2RhR21PTUw5dWJNbXlPV3kyYXQtMGVwMGdsYnNEalBQdzB6Y2k1ZHZHSkpiYW9DLVFqVHVKTHpMckYzZVpfdUo2MXY4dVBMV2hmNU1mRU9rcDhIeHhRWnFJRFQ3VEZSNnVoQU1ZSU1YdjZ1VTg5ZTJpZHRoNHpQSHJSblZEMUx5UXMxMWx1dGZyVW1DM0ZGWTVRMXJ4OFd1aUpNTFVsQ3JfZ0FjcWTSAfABQVVfeXFMUGJwNEl6UnQtaTIwdU5TcTh6ZmRQUzhYdVh5Y1U2ekNFa2RHWHNpVmpJX1NtYndkVmh1V0ItTnA0S1VkVzR4cGFiM3NkYUdtT01MOXViTW15T1d5MmF0LTBlcDBnbGJzRGpQUHcwemNpNWR2R0pKYmFvQy1RalR1Skx6THJGM2VaX3VKNjF2OHVQTFdoZjVNZkVPa3A4SHh4UVpxSURUN1RGUjZ1aEFNWUlNWHY2dVU4OWUyaWR0aDR6UEhyUm5WRDFMeVFzMTFsdXRmclVtQzNGRlk1UTFyeDhXdWlKTUxVbENyX2dBY3Fk?oc=5</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>46019.64137731482</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Crosskeys earn win in festive derby over Newbridge - South Wales Argus</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Sun, 28 Dec 2025 23:30:00 GMT</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPeWJ4SHIyZlpESmx1M25GT08wVFlVTzFyUEFRQXBjNUlBdkNTVVJxUlFnUEN1YmFPcHl2V05tLVZJQnhPRzEzXy1FalZyYVIyRk1vR2wyMUx5d2ZKMkpsSFowMDA5WWg2SEhZazRmVXpSQkZWXzRSQzNFd3FIU0RreUtCaUh0d2k4QW01YmZERERyRlFPUnRST21FZXQwUHItYVI1Sw?oc=5</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>46019.97916666666</v>
+        <v>46020.57340277778</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>130 YEARS OF THE LOUIS VUITTON MONOGRAM - Wonderland Magazine</t>
+          <t>Giorgio Armani, remembered by Stella Jean - The Observer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:03:19 GMT</t>
+          <t>Wed, 31 Dec 2025 05:13:48 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPQnBibndCYkpsTVU2endUMlY4VXVlSGthRVhwTDRhM1ZlMWo3WlhyMG5aM0lNYXpBbmxVVkpJX2JLN2RxdXJELWZSb3hGMzlMWnNpWm9nVXhJc0lWdWo3VnRBWlVVR2J5bTF6MzYycGVyVUp3N0dzS2c4dzFNMEpQc3loQlotcVEtVkF3SEttaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQdF9jcDBEa09rNl9JTEtTUDhKbnFFS1lobUFwVjA4NHhWTXd2dlMwaXA1dm9abGo3ZXJhQXhZUjVfSlhJZ1pVRUZndUhYeGFmdDBGa1RHYUk3NGhwWjk0ZEV1R2RZdlZZOU5hVS16SW4xX2FCUW9Pa1JkdjNNQ3NDZkRScExBNW5BSjF2Q0tSazZTdkdDd2MtUm15eVhlTjNxTFE?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46021.4189699074</v>
+        <v>46022.21791666667</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maison Louis Vuitton Sanlitun: Beijing's new cultural retail space - Dao Insights</t>
+          <t>Louis Vuitton’s monogram turns 130 - see its most iconic celebrity moments - HELLO! Magazine</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 08:29:42 GMT</t>
+          <t>Wed, 31 Dec 2025 07:30:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5rSTJ0dW85S01pZG9TejF6U3VRS0ROcTZrMXpiUmwyNUV5OUVsMjlfVm5YUmcxVldZQUl1czRrVkh4d05TWmVBSU5zbVNqWTVEc01DVkpWUVp2Sk54d0dOT2JSQjFnRDNwYms0cG5NcXlVZzRha2p2S05wUmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNa1lQbUZvMTA0Q0tfeFlGbUtOSUNFN3dkQmlweDQ0Vk9hYm1WMFEwYk92TGY4eVpFbmNEVVo2dDJFcXMxSGtVWEEzVzRXaURPaDhLM1lsb1VwU0txOHRwOE1Nc29WRlBseU93dFNxOERNSGpZYWF3Wlc1MjA0a1Vlc2FRWERTYlk2ZVRrNGFIb1dfM2pWTGF1MnBDakxIQndPSlRzVXRZTzlqNUJJeWtObUE3Umt3UU1kaHdPT9IBywFBVV95cUxObWhYZncwQWh6dnlhbTZZVklqT0oxcGZXR2FOOHZzMjltM3dpSTN3a2JHQWhobG82bkhLLVZ4VHVKd0VIWGkxOHRhVTM0QzUwbUdPV3RYT0MyUmpTOXdxb0d6Um1mdFVDbEI0bHJieFdvRXlzRnNQdzNQNDFEQ19rX3VjaWZhQmEyRXgzalZRa3RNUUQxSTczd0dycUFGY2t6UGQ2WnpCTUN6MUcwOENGNTNsak5KNlB0ZGQ5bEtoRWVGdTFPLWpodWszdw?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46021.35395833333</v>
+        <v>46022.3125</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>This Treasured Motif Is Celebrating a Big Birthday - Harper's BAZAAR</t>
+          <t>Fresnillo, Burberry Shine in Best Year for UK Stocks Since 2009 - Bloomberg.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:33:51 GMT</t>
+          <t>Wed, 31 Dec 2025 06:15:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPS2RreUNZZ3RfT2xzX2dXYjVySFFacm9MWnUtbmlPd09ta0oxLU9ZblgtaTBHdG5odHBIYkQyMkRUZnJZSHM2UDMyOUhPb3VUbmNZb0hrWEx2MjV3VHZFNUpFSmpSQTRKdnJRcTZOemc0WGZKUThlVHB2M2w3Z0JXVWR4WHF5ZHZTdVprMUlobndUU2ZuMFRZUW1ENjBRRy1nT1FMeFRVcElDaVlSZXROV0RQSnBYUDFFZGs0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORUFobDVyY240dzVqTldVczRWVWk3ck1BYUVhM0k3QUU1bERBOWc2SUdRaDR3U2lKbzlMVGE1eVdQN2hSTXhXNmctQ3RaTFRDcUNnVjYxUzNyUjFMWFdHNGg4WUdUeEVOQ0x6bS0yRUYtRk5ydXpDZlY3OGN3NGJGUDF3MmdCSlNYTkdtOXVpOEVlTDVMSnAtZlVwdktUUTVtOUs1MUlNTTJJSUJ1dG5qd3BqSQ?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46021.39850694445</v>
+        <v>46022.26041666666</v>
       </c>
     </row>
     <row r="5">
@@ -581,24 +581,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alexander Calder’s art will take center stage at Fondation Louis Vuitton - Hube magazine</t>
+          <t>louis vuitton sanlitun opens in beijing with a fluid glass facade by jun aoki - Designboom</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 12:33:40 GMT</t>
+          <t>Wed, 31 Dec 2025 06:45:55 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQSGpkTDZvb0k1c3RwZW5NSlB6dEczUlFsejVYcWVNeE5FclpjaldiVDBLVzlfVmNLR2hiRHVlWDAxUHM5a2FWanZvZ09NdE9pMDVwUGJJcXYxZ0ZKYUQtb19mUFVQZEVUb1lCTVRkSksyb0xpVjFkSHVudTFjd1RaTTdTdVRwTW9oTUpaYkYtMlVYVms4U0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPZGRxUl91blBBTzBzR1J1Y2M4M0ptN3o1RmFWM0VLRzVJQ0hFU2duekxPQXRKQ09ZQzdMR1JVdllUQXVUcDRMNy10QV9VWkhoXy1qWDcyckY5S3BHWXdtMHhHelpNTDJlVHhnR3JfdkdON3hkSk1KakFWS2RDWXFDVGo3QjNyX2F5b0RqNUc3bXJnVEFEeFE2Z09fcmU2NVpyWlE2NFQtRkg1aEZNVUZwWS0yY1ROYWs?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46021.52337962963</v>
+        <v>46022.28188657408</v>
       </c>
     </row>
     <row r="6">
@@ -614,24 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Calvin Klein taps Trent Alexander-Arnold to front its latest Holiday Campaign - daman.co.id</t>
+          <t>What Ralph Lauren CEO Patrice Louvet Gets Right About Culture - Forbes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:15:24 GMT</t>
+          <t>Tue, 30 Dec 2025 22:45:22 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQZk9sRmNlNmhKVzdjbFJPS21NNVBrR0hnZGp0MTJ5aTZoZWRVT0hQZ092ZnVDT3VYd1BFQXJXRnFSbmtVbTA4bnFJemJVTjZpMHFqZEJQYWk0NkIyX1cySFp2NzRXYkxOZDRlX3BDQkdNTHZGQlotZk9TcWFGUlYxVXFWWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOSEFIUjdzbUtBRWFYX1BlX2Zpd2dyMk9WV0puQkgxV2d1SFNyRTdadTlYR1VUeEIzRVRMdURIaHpBTGs5TGUtWUdwWjFNN3Rvd0dLT0xVM3FoQk1kbHJQSGd3dGxsM01kejVCTXE0emNhNGpRYklPbjJYZi04RmtpWmlwZHUxemhieFVnQmZQYUt3M29FNHg4N2V3dUN1ZEtEOVZmQ3BsUXZtRXpxSUE4b202aVVPWnM?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46021.42736111111</v>
+        <v>46021.9481712963</v>
       </c>
     </row>
     <row r="7">
@@ -647,24 +647,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Polo Ralph Lauren Sleeveless Polo Shirt, White - Botswana Unplugged</t>
+          <t>From a One-Off Speedboat to a Cartier Tank Cintrée: 2 Drops on the Vault - Robb Report</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:06:52 GMT</t>
+          <t>Tue, 30 Dec 2025 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQRDJVVC1GdGVCNGtzSXZ0Uko2bDNBaTlLMEQ5VjFMMkoyRWs2QW03aGxMbjJUY3kzYmtaMmp3RnF1RkRqMEdoOEk2Z281R1M3WjI2OFFWMEVKbzNfRDVhTG1SQjBwYjJFYlZ1RU9ZWHNFMFNrVUE2M3k2NXdDNkg1blJDZzFuMUJ6Q1RNaGJWTkNySnQyQTY0MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNRzRzc1NNWXBrTERRWURPTG1HT19ZY3NUTlhVSHlwX1g2ak1GaHdVQUNjNHVQZDlvbUtjMmMxbU1xT1JrV3MybWhGbXE2SWxyTEpqbTJKSVVJazl4cWxQa1B0ZW4wUnF1MzM3R0R6WnEzZWlraUxRZFpRM1lKbVZ1UHo3eTU4U1pWWWVHbDJRX2Rkdw?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46021.46310185185</v>
+        <v>46021.66666666666</v>
       </c>
     </row>
     <row r="8">
@@ -680,24 +680,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LVMH v. Morgan Stanley: A Battle Over Bias, Brands &amp; Market Power - The Fashion Law</t>
+          <t>The “secret” Jorge Lorenzo kept from Valentino Rossi in 2015 MotoGP title battle - Crash.net</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:00:37 GMT</t>
+          <t>Tue, 30 Dec 2025 18:48:20 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPRkVsTVhGQUQ3TWFCZlZ0MVVhQm1PdFRzTGRiT1ZVVDV6ZWROOU84a3E1Nl8yb2p6MTJQbjJzbzBqQmVhbE1KQ2thYXVhWW5salR2aWE1cERmMk1ZUV9WN0F3SnU5YlRFNzJQWlZtQ3Jmc2NRX0ZLNzJxUkFZLUpRelByTXFERmJneXJIWFAxNzNMWUgxZUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQMnVXWG5ZUDhROEtqUGF5bnZBem5lQ1ZXbUJpUzMxZVRxSEFHVF9vdTBYSzVGMmNhTnNFcm12MTAyd2FCZU9tSmh2Qk5SVzF3YzBOMHlrZGUtREJDRU12MTV5WHNwZ0MxQzdET3hiQUt0dE0xSG1leTdWMG1kckJBSGhDclVOaDFVX2o0RUlBVG45NU12SE94SFFnd0dNMVVQd2h3SS1BamJZTDhZRk1n?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46021.54209490741</v>
+        <v>46021.78356481482</v>
       </c>
     </row>
     <row r="9">
@@ -713,24 +713,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Queen of Christmas Mariah Carey wraps up in two fur-look coats as she enjoys a shopping spree at the Gucci store in Aspen - Daily Mail</t>
+          <t>Melissa and Joe Gorga’s daughter Antonia shows off $10K+ Christmas haul with Cartier jewelry - Page Six</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:01:50 GMT</t>
+          <t>Tue, 30 Dec 2025 18:51:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNVGNWTVhINGhLSWlDR2s2T2tGbDF3MkIwU292RnB1aHdHb0l2dzM1d3EtY2lkeHZlYVBZZ0tLZFI5N1FwQldpaXZISW1Fb1FpNllGZmZPUXRETlRiQlNhMEV2azZMTDlQTUwxMFJvVW5tQ3hfb2pmZFpDb0ZCNVhzM2VOUTlybzlDVWF6NTNRbDJORjlGejBuMTVpZS1IdjhVcFk0YVFab9IBrAFBVV95cUxPcV96bVZRcktyRVNNOVIxbTNQZ0J3cWpvUnduMGN4QjhIb0pYR2JsOWREaS1MZEZWQXRCVkJiSXFubjl5UjBxRHE2eGFnb1RrZjJuNzhtek9xaE9fWmdFd2FxWkVQVmdSVV9vM25UZFpFWEIwbXhNX2tlVnBMM2drMGdLUDNFWTg5T1daRU1lVEJFbVVUNDdtZjRKUDF3TVdCV1VSQ3p2TnJUSmpG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOY1BWVzBoTHZaQzNRQU94MVQ3RTloLXVQS25ZbmNaZ25sVG9UdHZyM09BTllJb1FCM0MxRFdMTlJTaXk3cWFhYlpTcWd1bnlFSjBPMnJsZll3aDl5LWF6WkhlazBJS1ozcjJYNmVDOE9QV2V6c3FYeUlkSmJfdFlDbURXZ0V2eWVEN2dTMHBvY3gxTWJIdUtJdlcwbXFoZWhQV1lEdzU3WVRZbkwtSS1TVjlFV05GNXZhUHNoVUwxSmZwcGRmQXYyZjloLTI5Z3lJTGdZX3QzY3JQOHNz?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46021.41793981481</v>
+        <v>46021.78541666667</v>
       </c>
     </row>
     <row r="10">
@@ -746,189 +746,189 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>An Autopsy of 2025’s Fashion Top Moments - CR Fashion Book</t>
+          <t>Mariah Carey wins winter dressing in looks from Louis Vuitton, Gucci and more in Aspen - Page Six</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:20:40 GMT</t>
+          <t>Tue, 30 Dec 2025 21:09:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5XRFlNaDNray0yRUEybm1xWVc2c3dOUnRxbUdxTE9DbHMxWGtqc053NW1CdThFNC1tRVUyYnVXVEhXc3QtNkZrZWxPNTFtWnBjN0pFR01EWVBqemR3bGxqYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOaFhaUTBXcnpiMzdTUWkyVVVGV1dwejFlODlyT0RWa3FJOXNSTTVqWlVNdXU4MHl2bWhZTlRuLWZNeVB2dUVET2I1V3pDR25HOXA3UEdyREREbUpfZ2ZHMVNac3YwMW5EUmctRjMwM1B6ODVYNEw1ejFGQmMtdy0yVV9aYnJhdzU3bEIxMXU3U0E0NlZLelAtSm41R1gtaGRrOFFPV3lyaHY?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46021.55601851852</v>
+        <v>46021.88125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Value Retail</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B&amp;M European Value Retail: Discount King Tests New Highs as UK Shoppers Trade Down - AD HOC NEWS</t>
+          <t>Do You Know Bobby Garnett, the Black Godfather of Vintage Fashion Who Inspired Ralph Lauren? - The Root</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 12:21:19 GMT</t>
+          <t>Tue, 30 Dec 2025 16:55:08 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQX05ieWlYNUt4bmRSV3M2VmNnWEZ6N0NiUnJ3d0Q5LWwzRFpPSHlSMm5rUFB5cnVwZnR6MHFNVkx5NTJaRGdMcWhWbEo0cjBmMDBYY081Q3hQaXBDajhRUlI0REkxNXVFcy0xbjg2MFByeDg1LWFoTldKR29WZUFaZzZTTm8tN0N1Q213cUNYTjNGQ2hsMnZzd1dLRzdwaDJFbDVtUEpYQWVPZ21oQjdQYnRUNFQ1YWJienJxdE1pODdjZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQSi1feUYwODJLekFEamFhVUFtUGV2YkNDNHhrMFAxbW1pNUx6aXBfblFocEx4eExfRVFaVWlGME12ZnZlUm5CSlhJNG1kaUlGNS1jYWZmZ2xjdmk4R0VLbXhOOGJzRmxQVzVwVUp4WXhuWWFwVXhYN2FObEZHdEF4TUFCcGdCUjhNMFZHTFFWWXFVNjQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46021.51480324074</v>
+        <v>46021.7049537037</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amazon Prime Air Drone Delivery Operations Slashed in Italy – What Now? - DroneXL.co</t>
+          <t>B&amp;M European Value Retail (OTCMKTS:BMRRY) Trading 5.3% Higher - Here's What Happened - MarketBeat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:44:19 GMT</t>
+          <t>Tue, 30 Dec 2025 16:57:01 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBWd28wUk1ITXRtbkdzakRGeVpKaldyR29GcFNSb1dlN3AzQ1pVUVVDMnR3enhxZl9SRWZ6SjJTdklLb0VFaldOVEFrMGZVdFdqWTQxUGdGM2FwdDNhX1JzSUNveTAzS3NlX0xRejNxaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSzVORjB6TDdKZk5sYmJUbVpRcElZR3VZYlVKbXNCZHRzaW5aa25UbnJZdnN0MF9zOEJtMGs0c2pkQlNyWFNFRGhZRy01d2pWX3dPUTZMaElMRHRFOHVZNmV2ekFTajlnRVJDbnNkTERDcUh3UDVrejZPUWdEcXFjYTUxTkNXUmVPNzFlSDRLZkQ3bXcyRkVUTDRvU3NNYWxfZElwV3g0d0lzbzQxdklMM1YzUDRZRlQwTVZXMEVEcmxOeWZSeHEyZg?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46021.40577546296</v>
+        <v>46021.70626157407</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amazon Driver Banned After Taking Family's Cat During Delivery: Watch Video - AOL.com</t>
+          <t>Small value retail digital payments on a rise: RBI report - The Hindu</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:02:02 GMT</t>
+          <t>Tue, 30 Dec 2025 15:17:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNEFOck1DZjNtcEFvMkhnMldGWWluVW9rTHo3TUttVmRZU2xpNVVyMENRdGlxRk5JY1F6S3hUYkd2TkVacE9selZBcFJNZ3Q2ankwVDBFb2VNajZpbThGLXZrTzdpUTVlNjliS0ptbTFTTXZnQzMxNmI0dWJSZXJ0dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOVFF1Zy1TS3Fwc3RpbVV1V2VKcm01OXpZQ3hNcmEyV09JWUhNLUNqWUM5Q0JjcHdQYnJha3VrTWVTcC1USUs0a0dKTGxuWFVsRGJkUUxqNHRjNzFyWXRET25kaktBWGxlanZOVzBRUzNFdTRJcV9Wa05aTTNKWXdLNkxhaFhaT0hVUW1tRVE4VWZpUTM2ODdhc0x6UmUtejhYQ2d4dlJ2MmtQeWxJUkI00gG2AUFVX3lxTE9QVTlIX3ZzcmFQX0NqMGZkVkhid0lkRFJzdDlnQU12cUpWSlhiNW9ia2NEUWFROFZwUVBjaXFEX1ZldWtBVTFPcVRqY2JiamY1a2E2bkZiM0g2d3hTTGlwbHNDcVBYY0pZMGxWN0F0Z2ZrLVhYN2dWSzlSaUVyTDlrWHcyV1h3WTBnV253X2JBYTFjTHcyVFFkSWJ2Q3JPRmNFcW1KMGVoMGFHLTZIM1RqLW5SREpn?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46021.45974537037</v>
+        <v>46021.63680555556</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amazon backs Flowers Foods at SCOTUS on delivery driver legal status - FreightWaves</t>
+          <t>IoT Platform Surges on Strategic Partnership to Expand Industrial Applications - The Globe and Mail</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 12:00:00 GMT</t>
+          <t>Wed, 31 Dec 2025 08:11:09 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQTHktQnBOUlFKZE1ZV3U0d2VaMU9iY3Y3WDhSUFhJN2xJTWd5SFNra3RQLWs2NDBXUFlyLUQ1MWJJeUNpU1VLZ3pSMVNWeU5VaW9fX1NHT3NYZVBERWVORTZSTjUweTdHbXlXdjhyQUFDV0ZXQlVRQUNXVzFtTXFXMFpKdmJqYTFFVWRtb050SXZrQ2J5Skc1Y0NGaTUzcEVzeVdudg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOOXY2LUtjWlNqTDl1eFhCbU5FMzFENG10eF9wQkhXY0dOcjBGSU54VnVSQUdKZlNSM2ZsNmZzSVh2VERzYjVJZEdNay05SndOSGRrM2V6RHNwSlBoZE0xWk4wTFJsQnVSTUVoaFFNbnp6WXlLTmtyZDZtN3BmbTU3cXN5ZVhKMVExeGw3eVQxdkhJYkN6bWRQRzNlRmZpd0hOQ0oweHFxRGs5ZGtfcjhJdHJnYjRKNmdGaks3SXNVUUt6NHY0UlR2TUpvOV9jbzduREJnMk1MZFZwWHZLM19udzhWNE5rMExQQ1N3QzdCQ2NiTkl5M3JSTg?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46021.5</v>
+        <v>46022.34107638889</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Value Retail</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("valueretail" OR "Value retail" OR "Bicester Collection")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amazon to pay $1.5 billion to millions of customers over 'deceptive' Prime sign-ups - Mashable</t>
+          <t>Why did DAIC stock surge over 55% today? - MSN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:45:00 GMT</t>
+          <t>Tue, 30 Dec 2025 17:30:26 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9DNlJadzRjcEdRSWVuSFk2aFNnMXBmZzgxV2RyaUMzREdFUDdndThmNXhoVHRmbW5JanZFQnNnd1NSbUNrOXMtYWo3TmtFSVE1VkFxNUtNM3lObmV3cWNv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPZFRaLVV6OUFqZ2pUZWd0SUI2YU5ocjdKR2tlWlBqM2ZDVndSVWlPcTl4OXd0UWxPbE04RjRsSVgteXREZ3FweWhRZU5JMEt6WWVaRDNhTUxsOXN5Rk9tX19pWjBPSVM3WTZIejRmbkpscThGVlVuOXlFQmZhSkJrMlJTNzZNWlVPanhMR1R1TkhWTkZ5UW9NMHBTaW52WFFjV3VOSTF4NHhzNDdsWFpmbFYyTm4?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46021.44791666666</v>
+        <v>46021.7294675926</v>
       </c>
     </row>
     <row r="16">
@@ -944,24 +944,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DHL Confirms ‘More Than Just a Handful’ Tesla Semi Trucks Order for 2026 - eletric-vehicles.com</t>
+          <t>Amazon's driver monitoring app is an invasive nightmare - Mashable</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 14:02:30 GMT</t>
+          <t>Wed, 31 Dec 2025 05:38:42 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPSzFzNTZHSHZjY0dIVS1HNkxoQ203M1lPTjR0UVY0SzNfdG1XVExyWjlFYWpDTFdLanBnR1JVeENUZTkybnFiYno3bXBLUFg5Q2FtRFROZGxRYVptZG9uTzUzVjFkR1lCSGVPSXR3QWFTVVhaZ18xUkpiNzBSS3dlNE5JZ3U5RTRlejNJWGF2TEt6N1pVY2V3LXNqMlNrenFNT1VqV1dEc2oxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1fcWxSd1dlUnd1RGtBNlVNbVUxNEtSUHNCTThKWThRYUVCQUd3RGxQcHo1Y21wdzVlQWVFbEtueDhEN2VOQTByb2VEcm9PeDVEY2piLWVZSXA3VFhxWXp2TlRSX2Z2YTlyYWdmRzl0OWdRLWt0NTBGdUNXTmJudw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46021.58506944445</v>
+        <v>46022.23520833333</v>
       </c>
     </row>
     <row r="17">
@@ -977,24 +977,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Is the post office open on New Year’s Eve 2025? - NJ.com</t>
+          <t>eBay UK Confirms DHL Removed Temporarily From Simple Delivery, Sellers Left Without Bulky Item Option - Value Added Resource</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:00:00 GMT</t>
+          <t>Wed, 31 Dec 2025 00:29:56 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPcUw5cEZOa0VNZWlHLURwSTdIU0ZzQXdNS0tZV3ZoM0EwTDk1ODdLelRnYzh3UlJGSFc4TURiRzVabnRqd3VxdGktZmhIcG5UOVhFSmFPQ1BpS0FkQTl4Vm9feXBjQ2dOOFV2cTdlTG1ORzNhaGxNT1I2T08zcWhMYWFCQ0xUQXFvMEdHQXVfc9IBowFBVV95cUxPSkJ6MGhRc3NURmpQQU9WYzI1MXFTM3VvbnNPdlNIcm1jUm9wMEZCZ2c5bkZGQ01LcTMzWGQtUHgwUUpZREdidy15NWhtc0JsRDlBRUVnNFZOX1lBOUlOVmE1aWd3cjMwRDI2TlhBZmVEUVlLSGFLdXpXemtFdXJtaUs4YkV2YTJNTkt6cm1Vb2JWVkR6aHNVMkZCYUE5b19OLTFN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQb3RJOVJJcXZjY1hJeUU2RnlxQ01kUnBBNmstcWZpd2FmWDU4NEhDSzVTdmpRenQ2eVZ4emdFZnpGU0xUV283alowVWI5T19vMEdxSmNyam9QZDhIem9vcnFqMEdZdVM3X29Pd0NuTTBBbVJKN19NOGdVdWd5TWVMQlgwUGdweTA?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46021.54166666666</v>
+        <v>46022.02078703704</v>
       </c>
     </row>
     <row r="18">
@@ -1010,24 +1010,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Meth-inspired voices to stolen UPS truck to prison: Shreveport man agrees to guilty plea - The Shreveport-Bossier City Advocate</t>
+          <t>New York Files Lawsuit Against UPS Alleging Unpaid Wages for Seasonal Delivery Workers - Law Commentary</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:00:00 GMT</t>
+          <t>Wed, 31 Dec 2025 05:06:25 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPLUZXS3V1Vk1Jd1lJYVYwLU90Qi1xc0NfS0tDNGxXOW9HTHhCT3Z2OVExUWVrZlUxczNpNUJUeHpzMWhxQmwtcGJxdlNNVlpDcGF0NVJtdVEybWZWREdsdXU0dTBfb0YxcVlFa01EejA3aE84d2c0S0hVQmZuNUxMQWtiLWZvZ2N5blhKdzc2ajd3ci1kSkotakswOThBZmtOTXlxUjdwMU44dXhyNFY5V0JrSE81SmlVTjFMRkphVmxrdm4xU2tka3dLel9jSktwd3BualZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQTnJRMFpxQ3Vxd3huYzBXS2ozR2hWTzJoTFFPUnp5Mk10VnAwMkJuY0pDdXZ1U3F1RU12T1oyUGZKeXUyWThrNmsxVW5ZZU93ZjFiTUVlTlpSYzM3SFFLSlgyakJEald3NkVPaHU3SUx2UWJIMGV5REczYVExS2ZlNnpBYlgza0ZqbmlvMW9wSF9DZzhtdUhFY2h3blp6cXQ5WkxLOGJQc3J0Rk1iUlRWQnRISzU4Y2RFYmpKNnlyMzViUlk?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46021.45833333334</v>
+        <v>46022.21278935186</v>
       </c>
     </row>
     <row r="19">
@@ -1043,24 +1043,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Why Gig Workers from Zomato, Swiggy, Blinkit, Zepto, Amazon, and Flipkart Are Striking on New Year’s Eve - Gizbot</t>
+          <t>Amazon plans for 75 percent of operations to be run by robots, report reveals - Mashable</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:01:36 GMT</t>
+          <t>Wed, 31 Dec 2025 03:37:34 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQUFVIcHFSeE4tSkwteUlMcHhxczcyUk1tMG51Z1FIZXJVWXNIMmxGOTFyWUdva1pEM1ZvMU5NdXk3NGRiVl80SkdFZ3Zkd1RGTkl0Q1FocUpHMEQtYlIxcWxpZllKNE1acl9aYzVUb3pKT1RDcHhYSkRndl9TSVk4dlR3b0Z4YUtVUGdRWkh0STdtVXBRQzdzbWlma0FrUTBvV3hOaHR5QWFjNUpGV1pqYVVJV09scnIyVUZnM3k5TzA4d1JUMHZvSU1pV04zWWw4S1daZXFvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9lN2N5UlVmSnZIcGM5NEhZY1N6MHgtVFZ1V2YtQ0JvUDVHZG1HYlhzT2g4eEVfeHJSNl81M2hYNlJDcVdJWVFJWlM1ck0tWTdzR2NFd29xaE5jMUxIbnpYbEpLOGh2eW5h?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46021.37611111111</v>
+        <v>46022.15108796296</v>
       </c>
     </row>
     <row r="20">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USPS plans to expand, and Amazon doesn't like it - MSN</t>
+          <t>Man accused of violently beating 77-year-old neighbor over Amazon package delivery mix-up - Cleveland 19 News</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:18:37 GMT</t>
+          <t>Tue, 30 Dec 2025 18:00:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUU5mVjBrcGVwVmI3RHhqMkVvSXc3N2luY3VNNWlqeVpwSlZpa205dXNEdnpKREpqbnIxMEpYWmI2YXJfeE5DUVlZOHdGM1Q2MzlWME4xY284S0NhX0RnV19rN29jc0M1bHQyMUdzNlpuY0pnZm8yUUp3OUtrTWN0N0RPeHl2S3F2OUNlWE5ldnZrYnRCeTA1M0FCMVd0U1dKYUQ2ZzNRZWJHVEVMS3pfNHI4cnk0bTFQdlp4Ml9ZTDJaOVViUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNekJ4YmE0T0JRQl9pOThocnJXelpMc1pUM3I5UXp4NzhmdlZBVFZGbHk4X0ZwU1NIVWJlTmx4VzJZRmduWXpqWWVabWpNeGFzTnNJU1VOX013cHhZc242dmlqVDliWm5hanZkRHJrT1pwbmw2S04zOTQtUjhRNEp2bkhIaUc4Sms3MGowRVZReElleEpFcEJ3SkxLTy1CZzEweUlOYkl5R0hRRWRJNGtrREVlNDlDQ1NRWWtDVzFUYTFjOVR10gHYAUFVX3lxTE1TVzBhMUZ0NklTcnhRSzQ0M2JNZWlxaTRYejhaSFlYS2tXb3pGZ2Y4WVhUNWpkdmphR1FRN0JpUkwzeVU0ZVk5bmZqU3lVc2VFWnR1NlQ0OXI0RUp4WjUxVDctN01ndTlYX0JPUFlpQzZESnZnNmlkVlBxRkYyZm9GZmczLXZPUFd2WE94OUFCa2dwamJjdmNXcXhKRldsSXNibTVFNThLel9SMXFVQ0Z4OHhmTTJLemE3N01UMm00ZkY1Z2N4aFR2SnJVQVA0S2d6dWc2RXBEZQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46021.42959490741</v>
+        <v>46021.75</v>
       </c>
     </row>
     <row r="21">
@@ -1109,1278 +1109,3225 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amazon Drone Delivery Dallas Launch: Residents Spark Outcry Over Noise Pollution - hypefresh.com</t>
+          <t>Are banks, post offices, UPS and FedEx open on New Year's Eve 2025? - USA Today</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:44:56 GMT</t>
+          <t>Tue, 30 Dec 2025 20:02:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVzBUeGhmWFJQM3ZsQWp4SkYxeG5pOUZ4QWRRRVBuZ2QxQ0IxOUxvS1MyN2swVkpNd1dwSy13M2pUZTlqN1ZYTzhsNWJyWmRJTHUtUHM1TnY2d1ZHYmJXVlZQT1ZXTzNzcWRlOXI0eUdZOWh0Q2gxcGduaFAydTREbjFlSU1PeDhnaWp6MnBLeXlXc1RUNmVKVElzck9oTk10cmFwdG4waGhqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQVW5wd3pJUkhCSFo5M1JYMGhOa3lUaWlWY1NJVjZfRzZ1RnFlNFQyU05SWDVEbVhYWE1wY25lQkpqbHFjTjdPN2RvZzZFLXRvVXhoUTJTbkZrci1MTC1NaEx2LWdhZV9KRDJ1Q1plRG9sLU10d1RqRHdqMDVMdG9XYVpJdkswWEotY1ItamFMeHhncmE4cTU0Z2xQZ1lsVE9td1F5cjM4aDlNSlRRTHYw?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46021.48953703704</v>
+        <v>46021.83472222222</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austrian international for FCB? ++ Frankfurt sign new striker - bluewin E-Mail</t>
+          <t>$20M suit: Amazon’s high-pressure delivery practices to blame in Isle of Wight wreck - The Virginian-Pilot</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:11:11 GMT</t>
+          <t>Wed, 31 Dec 2025 04:52:30 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTjFaUHhvZ2ZRWmw0MGFmd0pCQm1XaTgyNmFmM3VQOS1YdS1Xb0pNREV1dkNRZ0dRVXZvNENsSU5kcGVodGdvRVNfNXhZZ180b09QZUVZUE4wV3JISUM4TVJ2TVp2eDFNSF9ZSjNoX3hISmhIak5MN241aDlzODJFa2pDRWpMQzAyVHg5UnZ1STdMdW85dWFJZlpidk14dkEtazdGdFpOdWRlUjl1UUlsMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNVEo5OTRfdDVuOTFXRXlTTjFuNkw3TkZSUnlsMXlmOU9UMVZ0RExmbURJd1p2M3kzaFIzeWRwTEd5WkJuWVFPZzF4T0Z6ZVFTRHVjMWtmeWZpRVdFZDJYWTVzQUg1bVFLU3NCSEZaQVY3ZjQ4cGNlbjZGZDlSeXFwNXdyTGl2ajBzWFZJSGVxNWprNXVkdXpCLU9XVk44T1VEZTc2Wkp2X1BJX3BSdmR6dE8yTXp5R3l5N0FMbUZR?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46021.3827662037</v>
+        <v>46022.203125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Troopers drive 600 miles to deliver Christmas gifts to 2-year-old cancer patient - Atlanta News First</t>
+          <t>Swiggy, Zomato, Amazon delivery staff go on nationwide strike before New Year. What are their demands? | India News - Hindustan Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 08:40:00 GMT</t>
+          <t>Wed, 31 Dec 2025 07:25:01 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNX25ubFBfaWRmclYxY29peXZCQmJ5QmlZWWJ4djdwY1hmSTZ0WGxlUFJOY1JzYUJwX0dMcGhnLWlKcl9VUW1NNVlTRngzNHQ3cS0xWThPZU5paEV3Tm01VG9pRXpRbC16WFZ3ODN1T0lXTzRwdkwxNUNHMGdiODl5VC1rV0VUMk5vcXEwLWNJa2NHU0NzQXJnbXp3cjFWVlYzaFN4Si04empCVTA4dE1qclBqOUZLUVFYZ0g4ZFFyT0NnVDBCSGFrZmZlMHJuSW_SAc8BQVVfeXFMTV9ubmxQX2lkZnJWMWNvaXl2QkJieUJpWVlieHY3cGNYZkk2dFhsZVBSTmNSc2FCcF9HTHBoZy1pSnJfVVFtTTVZU0Z4MzR0N3EtMVk4T2VOaWhFd05tNVRvaUV6UWwtelhWdzgzdU9JV080cHZMMTVDRzBnYjg5eVQta1dFVDJOb3FxMC1jSWtjR1NDc0FyZ216d3IxVlZWM2hTeEotOHpqQlUwOHRNanJQajlGS1FRWGdIOGRRck9DZ1QwQkhha2ZmZTBybklv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQT3hWV3pLUEl6UDRET282b2p0LWlIRWdDVTlCVk5ST3B5NmdvSVB6NF95eXJHWno1STBtYXQtM2JweXZKaE55X05UOGdzSm1oQ1RQQVB6LWRWa2pqOURNcE4zaEVvYW95QkRpMy11RThhelZKMDVZTUl2cGtzUXNqVElLOHk3TDFLcTY3cHpRZS1PYVRjMUZhamV5UDRXY2tiQU9HdzJVeS1hcllYeVJuSE1xSG1faXhETDNrN011dHFSVVBkNFctSnVVOVlYWml4bWJOb05RMlZleUt0d3NpdXBkUGlCSUUxUUtvVHlSRGhMR1HSAfgBQVVfeXFMTXdWd21fVVVRVW9GWFZKX2VxQURwd0RzaDF1OWk3ZHRoSVlfVUloT282dXJPYUp4NkdwN3VsWkthRjFwUG9RUU9NRV9aMG05Z0tEYlZGNHJHbHJkSkw4U0NHNC1YcDJCZEpTSThfc3ZURVAzNjBvd1JodlBZalBOQmpJWlRPSnRrTHZFRmFQRG5MUnIyNUJKQUR6blZBUlFCRFN4QmJqSGFxQjhKR3I5SXlIeHl4OE1sZkVTVzhKSm41QkJPRDIyczFyUmtIT0FBRjI1OWhwWXVMYkRUYTNUQTVSYjlXZGtud3h4NVUwOVcteDJkSlFZY3Y?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46021.36111111111</v>
+        <v>46022.30903935185</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Another day, another threat? Hyderabad airport rocked by bomb scares; international flights affected - MSN</t>
+          <t>What Caught My Eye: Amazon drone delivery - News 9</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:53:31 GMT</t>
+          <t>Tue, 30 Dec 2025 15:53:07 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AJBVV95cUxQRkdSVW0zVjNjU3BCQmpENWVIdnZFSWFnd0pvYnQzNnZ0TDlsUE8zS1dJMHhaNE1UUk1KSkZLU1JMLXVXSWhVSWtMbFZpZzlZaUpKcy1tNk1yZUVBQUlLMFhGNEtzVG1YaS1reWFBM3dfOV9TeVVvRjRTbzRIX013X0FaSTVXa3lVU19ZQm9zQ0tCVjh0OXpZVVZYdnZERDhMOVZXTGJYYmRkelc4NmFKOGR4anVERWlNekR4SnhYQlhuX0ZQMDMzdmVxNzBlclZyOXl4VWt1bHpScTFlZ2ItZWwxNkFJNFE5aTB3d1NJdnFkeUdPV18xVU44NXRjWmdYMVVDRmVpRTFuS0N1MUJVMGNBRW1RM2pzUFRXNFdCNDdIanA3b1BKSUN3WDNrUVJKRUFmVUpUNDk4M3BzMGlWNWpYd1Ric0F3NTY0RkxuNW1LaEREWlU2U08wODh0NUlCTEtLV1ZYelYyNkRqaFNweXlDWWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE53OVNaRlIxSkNkZFpXend0WHZ5cXhLa3BSeUNPUUg5eUFTbGdmd2lmM1NESlpSR3NybmJxQnMzTnFmTUE5MGFnTVJ5dFVZa1hGRmV6b3RTbVBrY3BGTXpuNWE1OGJMQVhrQzg0a1VyTF9qVlpLdWl3anh3R1VfZw?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46021.49549768519</v>
+        <v>46021.66188657407</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PETA Twitter search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alabama Barker hits out at haters calling dad and Kourtney Kardashian's Christmas present 'inappropriate' - LADbible</t>
+          <t>UPS warns of shipping delays as plane crash halts package sorting at major hub - AOL.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:57:12 GMT</t>
+          <t>Wed, 31 Dec 2025 03:44:17 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOLVhDVjdBa1JVd1VzRUlMdk9JMTRxdzc5bmx0UjU3cU9xQTY1R3lodlc3VEtmMTJISDlIQ1hhOS1GTDlsTFg1UEZTSkRBU21GeXh6VllpU3pmVG5YYVduOVVEazdXS253dTAySm5ZN1l3ZXFmYUN6bEwxY2RneGZ2RTFkci1UZDJEODQwdkRIY3FsMy0tUzV6NzE2NVVOa2ljOUR4TmtUOFpfNk96UkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNUlFTejlFNldtYnpIUWlydlBkY0RHVlVweHVxajVSZDhZZmNQVm1QSnVlVWFtX0RZZFRNdDhZQ0laZHBXWkNzdk1wclRRS2lyZU16Y1podUlMcGxPMml5N1IwbDJnV3BodXVkZGk1Nm9YV1lhMFVTN1R3enoxS2ZhMQ?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46021.49805555555</v>
+        <v>46022.15575231481</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Novara Media Contributors Share Their Top Stories of 2025 - Novara Media</t>
+          <t>The Terrifying Reason a N.C. Amazon Driver and Her Son Were Shot At While Delivering Packages - The Root</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:55:21 GMT</t>
+          <t>Tue, 30 Dec 2025 19:26:28 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQUTE1cTFpaVBsX0V1NnlpbDhLUTJFTjBBZFA3RmFucWlIM2ZtSTVISHNuWDR6ZVhERlVDWmVhekFFSXJTVUFNOU1sMlcxblpVOVR1ZW5PVWEwd1VQX2VtamRabzUtZ0dBREdxMU1KLWU5VDUtazRDS2ZDUWdFR05iS2NpZnlwU0RrN3V0UXRfOHpQSWVVaEhlTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOU0xmTDBYWDJTTHlMcktBTUxJS1BhQmtXZXg0YkVQZFhSamNBMkFsa1hmeVBPTEc1TkFsRTBiNVNJSDlMcWFxSlN1TE1OUXNSei1EeEVmOUkya2ZBSWJNRTROMXZEZXFhdERLN0g5YTdYblJsVEJNZXhabUpsakZuc1M5VEJUbm9tQXA1QURlUk1zdw?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46021.45510416666</v>
+        <v>46021.8100462963</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches Belgium French language</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Armagh, Banbridge and Craigavon police urge public and business owners to help them stop shoplifting gang - NorthernIrelandWorld</t>
+          <t>Passengers stranded as Eurostar suspends all Europe trains over power problem - thestar.ng</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:35:00 GMT</t>
+          <t>Tue, 30 Dec 2025 14:30:30 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQWXhuX003bHVHX0hvemtTTUJvVnA2LWpxR2YwRnJmaDZfRVRuTHJ6eDdoOW1ZaTR1VE1LNDMyeGhLdmc0U1JBYUgxYlRuNnBxVWRhZDVkanVMaFpTSnNDMnFuaGR4cU1ManV3WW1HbURlcnRKLWVxeVdLUm9yeTdrSW84b0Q4ZHVCVVE4dFRxME1fNlAtdTZTbjBpajUtM3NqUmE0RVVkaDJwTDdtbGV3dUNmZVpPM1pmT3VFejR4R0c3aW9tOF9yeEp3eE1HSmVIQ3VxV2JYelMwSHBlakZmYkR5Y2xIYUo3enFF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOb2RfSnJ3UlVERHYyem5xakJnbVpJOFhQYmtVRlZfS2VBVGd4TEt0cHNRZW5zcndoVUZnT2xaenBzb1JRTTFvcW85d2NyVmlyX0J4NVlrWVV5Y3VaNHdZUGw1a3ZnY3RLdXZiZ3hrcUhhRVFZdnh6MmpQWkFkZ3p3T2o5TGl3T28yLUt0dHNmTDQ3d08yaDg5UXduaktMMnVhS3NwM2dwRjbSAagBQVVfeXFMTm9kX0pyd1JVRER2MnpucWpCZ21aSThYUGJrVUZWX0tlQVRneExLdHBzUWVuc3J3aFVGZ09sWnpwc29SUU0xb3FvOXdjclZpcl9CeDVZa1lVeWN1WjR3WVBsNWt2Z2N0S3V2Ymd4a3FIYUVRWXZ4ejJqUFpBZGd6d09qOUxpd09vMi1LdHRzZkw0N3dPMmg4OVF3bmpLTDJ1YUtzcDNncEY2?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46021.39930555555</v>
+        <v>46021.60451388889</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prolific shoplifter jailed for 32 weeks - Bournemouth One</t>
+          <t>Can Sharda Ispat Limited (513548) Maintain Its Valuation - Real-Time Stock Alerts &amp; Free Explosive Portfolio Gains - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:11:19 GMT</t>
+          <t>Wed, 31 Dec 2025 02:50:45 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1CbFg2dHUwazBobzBvdkJVR1k2ZHNBZXlUdnNEUWVUVkdDTzdycGJONmNNMkFoYkxvdXJJd2JFVTBZMDB3YnhZbHN3dzFrNmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNX291MTFXMUhnRTNKRC1SX0JfZU8tMFBHZlBzV2tua1FRQUJ3M0d5bEJGdGZZTFk5LU9VRHFYbGtXcVUtVTFLa3lvSmN1RUY0bUdUSHQwckRIWWt6aHNrZWNaQjdjbllYMFRydHJxQjZ5eW1heVhZenZFX2ZrY3hjRzM3RUFQaHJ1N0ZPQmZoaGc2b0xtVVVZ?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46021.54952546296</v>
+        <v>46022.11857638889</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>PETA Twitter search</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>peta (gucci OR dior OR armani OR lv OR valentino OR vuitton OR polo OR ralph OR klein OR hilfiger OR prada OR balenciaga OR goose OR burberry OR lvmh)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mobile shop theft in Siliguri, police begin investigation - be.siliguritimes.com</t>
+          <t>A Largely Unknown 1970s Photo Project Captured Over 80,000 Images of American Pollution - PetaPixel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:45:17 GMT</t>
+          <t>Tue, 30 Dec 2025 18:32:31 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOazRDUHpWYVhTcmFfdGM4NHp0OWZlRGM2NTF1Z2VOWFpiY1FQazFXR3VET3JRYWc1SkRWTzBzMGl1UHhQUmxnVl8tbHVsUTAxS0s5Z2ZLWmhiSnpGdEhYUGV2ZlJROHBMZ2NReUlweUxyWk5ldkhWdlhiaWJMUk9mbjctTm1aN3VnWGR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZEl4bHVYTzcyRlhvUC1ZVU80TklJbzIza0dGd3MzZXBKNjRhZ01DOFFQc3M5a1BxcUVSS0gtZ0VGYlBsbkc4OWtuSkhnTkljcC1uc1dsNGJ3dEFmbEhmaXdXdFhLdkZreENjOS1iMFQ4QTBvUlBYZ0YtcVhsOGZTNUt1V2xrSmhfSVdQcW5aQmlqYjBVb0czYXRyMUdYMDd2Wnd2NEVGQnFxR05fQ2R4WmFHNWFVYmsta2NDdw?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46021.44811342593</v>
+        <v>46021.77258101852</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Industries Limited Uptrend in Early Stages Indicators Say Yes - Ex-Dividend Date Alerts &amp; Small Budget Wealth Building - bollywoodhelpline.com</t>
+          <t>French ban on 'forever chemicals' in cosmetics, clothing to enter force - Courthouse News</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:02:50 GMT</t>
+          <t>Tue, 30 Dec 2025 16:14:31 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPVWhHYlFTZmJqRnE5ajctcUhLWmktUGE4SWo1Y0RCY1ZiVE5ZOFBCUlV2ZTFrX3dJLUwxeFFnRDl6R3gwVDdWQWlfMUpldzYzb3F5dEtaemIxTmFkeHZpZy1CZFNPV3pwUUY2dlFfZmdQeDhveXRaQ1RUcWRqWm5wS2t3MFFNeXNCeEdyZkg5ejFjX0VRWTBnakU0MWZaeElSaUtVVDVyV2dtZkktOTh1UW42TU1fSUFQNEY3cU13aVVSUnkxWlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNX040MkZmWXBuTWJKWlAtU2NLUlpBbm40bWc1TnF4dlduWkprZUhmXzlUMUQ0UDdHblVPZmZpWXdCQnZfSHUyYmpsMHVscjFfdnpQaml2WTEzbERFSW8xenppb3RqWUd0MHZYN1Zsc0o4SHVNZlZoNDBKRGxhcFI5aFNMV0JhaXdPZUp1SHpkM0hRRENpMFFzbUwzOGxScXE2NnN5T3pnNENoQU00?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46021.46030092592</v>
+        <v>46021.67674768518</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Former Patriots guard Branch joins Indonesian club| The New Times - The New Times</t>
+          <t>APD Retail Crime Initiatives Show Measurable Results Through Enforcement, Partnerships, and Visibility - Anchorage Police Department</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 12:37:33 GMT</t>
+          <t>Wed, 31 Dec 2025 00:14:52 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQQlZJa3lsbE5IOC1fZThQQ2NDLTFfQ3RWTmw5UXotdkN4VV9JblBubm9ETWtSUFNaWHc0X1dPTEk0Y1QxcmhoaTNlNmVLOXRiVXczOFFrZlhpVUdoWVRYMFlBcEJsandZZUZPb2N5aFVKMmJmaldIN3pkcndRd1p2cWFKaWZvWWo1SmQ3N2x1aXFZaWpLT25OVXBnaExtVWVUY3RQOGxfUW9kUDlrMnpKdUp30gGyAUFVX3lxTFBCVklreWxsTkg4LV9lOFBDY0MtMV9DdFZObDlRei12Q3hVX0luUG5ub0RNa1JQU1pYdzRfV09MSTRjVDFyaGhpM2U2ZUs5dGJVdzM4UWtmWGlVR2hZVFgwWUFwQmxqd1llRk9vY3loVUoyYmZqV0g3emRyd1F3WnZxYUppZm9ZajVKZDc3bHVpcVlpaktPbk5VcGdoTG1VZVRjdFA4bF9Rb2RQOWsyekp1Snc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPdER3YXJTZEI2c211SlA3SEQwOVpBMW5TOHd4MGdkSVBmak1YWnV2dndSeFJZXzBjYTNyU3VhY1Bja0JLUDdkSWhWNXFUekM1TU5tZUtFNHBRSFQtMGYtNVk4bUhqMjdFUzdIUkRWTGpESWZpa0g1SnRaLW9tRWRScC1hdVRDTXByUHhsekhEdnQ1Y0RhYkV6bjVjZXBYYVdOb01oVDhuRE0yamtPcFdJNjVQOFRUV21RTEFaWmxPeG1HSmhhV2pHeHdlTWF1aURNVHBV?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46021.52607638889</v>
+        <v>46022.01032407407</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wembanyama, the NBA’s alien: redefines the alley-oop - Mundo Deportivo</t>
+          <t>KRF partners with AG, legislature to combat organized retail crime - Messenger-Inquirer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 12:10:00 GMT</t>
+          <t>Wed, 31 Dec 2025 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOS1NqMVd6cWMyUjRvM0k4YThGdFVmd3pzai1aZzZoeHpWVFJBYkNZbzNPSVdhYjJPX042d09mQkZRQXFiMkNDU3piMmtCVjVhOERUTlR5Tmt5VTZKZTd6cFJxSUFFeUVCM2tDdHZWcmsxNTJENFVzSlUzVG5pZU1XUzhYMjQwQlhKWnZmMFBadFcyMHp3cWx0SlZhbmJyN1pSQlFTOXF3NDBacGpqcF9IUmNaRjFyTEdReHfSAboBQVVfeXFMTktTajFXenFjMlI0bzNJOGE4RnRVZnd6c2otWmc2aHh6VlRSQWJDWW8zT0lXYWIyT19ONndPZkJGUUFxYjJDQ1N6YjJrQlY1YThEVE5UeU5reVU2SmU3enBScUlBRXlFQjNrQ3R2VnJrMTUyRDRVc0pVM1RuaWVNV1M4WDI0MEJYSlp2ZjBQWnRXMjB6d3FsdEpWYW5icjdaUkJRUzlxdzQwWnBqanBfSFJjWkYxckxHUXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxPenNvOHZXVlV3ZDNzdHRCTk5QdjJYZFYxaHphWWhTSVBqUnIxU3pCVE1WSkltb3MyYkxHTjduaFZ5MHBWdXF2NFhKRmw5alRCQS1jWGQ0Yy1zcEVWcVI2VUhXdzJTNTk0SmRFQzdIVkZvTE1RS2ZJU1VNeUZEN1pNX2U1ZmVaS0phQl9SaHZ5OGRPUEU4UTIzcjhwZWZCcWVtNHpnZ3lZdHA2MXVMcktuQjZ1N1BLemxtQlVaMF8xYlB4dEtmYlpzUEtaSVVmZjliU3JrVFFSSnBuUlZwNml5R3RUR2E4VVRJTGRNS0l5OXppNmtjTWd0cHRUZ3gxT1lYTHFLX1Z3bk42YUlSbnlrYw?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46021.50694444445</v>
+        <v>46022.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Manchester United’s staggering valuation proves they still rule English football - lentedesportiva.com</t>
+          <t>Seminar to focus on retail crime - Niagara Falls Review</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 08:35:00 GMT</t>
+          <t>Wed, 31 Dec 2025 00:19:57 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOQ3NfZG9kYndDak45cGlWa2RXOTQ4cGk1OUVRVXNSOERuUzVWYVRHOG1YWEZOYWcxOFRHQjU1RldfMEVRdTRlelRoak9TX20xMjFXNlUyZU1TMG84WnFUV2hlMjJwS1FsNG0yZEh0V0pFYTV2T3huTWFsRXR2bldzRG5MMmtCWktON3VIdmJMSzBIYTZXMWo5cHM0akpMWkN4RnpPRXgweVFrRlA3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNaVRZSHp6dU9rVVBDbzJ1eEw4b2NuVndLa1g2a3ZYTTBRSjNYM0JLcHZPTkF2dVp2RDk3TlpaV01RMXE0dWh3dW1hTkxmM2J2Y21RSnEybGVPMjRrTVdMd0YwRnp2X0p1dVdYVjJvWUJ4Z0w0LW0xRHNXbDAtNnJ2Y0lkQmVIS0trVWlZVWVnZ3ZtTUxtZS1hQU8teEdYb0RNWi1yX3ZxZElhbEtzdkFwdVRKZEZoU3hlVGExSkI0RmctUERCVUpz?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46021.35763888889</v>
+        <v>46022.01385416667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Girona could steal Barcelona’s star keeper from Premier League giants - lentedesportiva.com</t>
+          <t>Worksop shoplifter sentenced after crime spree - Nottinghamshire Police</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 08:42:11 GMT</t>
+          <t>Tue, 30 Dec 2025 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdVFUdTFQaWFZSmE0d21WQkVmbUpJVHNjMmVWWU1BVG81M3BCc0VWUFM2X3p6a0Z0SnRWcUppdjdxVld4RFROYlJ1eUdqZmRERHp0bFlaZ1NWam1OWkUzNzc1ZThVLXVRcVJlaGR3OUFMaXF2dTJFOFpFN2Z5RVZiNVV1V3F2eElTby1oM0k4TmNSd1VRd2g5cFhMUkdPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQb0NxV1VDZkVzZFI5U2pMaEZhOTBtUXZPUmVCUkNTbVdxalk3M1RiQk9jWVNIMFY1ZnQzUTg0eC1PQ2hKQi1jWk5lOTVBSTNvaGMwQ1NEVGkzMUt3Zl9PaFg1bTVTZnJnaUJuTk1NM1BHY0xNbnU4ekhnTEtsS1FLRjBxMDhSdG5Wd1VjeTFnX3dMaWZpM0tVdHJibkhpT1BXMm9pRmpJcW1aM201VDBpbl9OOGFiZHY2enpKVTJwMDk2MURVa3RsZllR?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46021.36262731482</v>
+        <v>46021.625</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fifa boss says pricey World Cup tickets are saving global football and fans are furious - lentedesportiva.com</t>
+          <t>How Kentucky's AG says he's working to combat drugs, violent crime - The Courier-Journal</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 08:51:53 GMT</t>
+          <t>Tue, 30 Dec 2025 15:06:00 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOU2xqZHROR1RFQzN3UnFFZXpraFcwMk4ySFBfVUJwc1cxWWNnN21pbjJXRVpWUFFyY1B6bTRQQUhsVXQ3bVBlOVhmcUI3T3Z3MTVmQ09rZXdObllXNkpTVGhuck5SaGIzMG9nOVJlN003Ni14OFlsTC13V2VEdVk0cFhiVURqXzgyRFBUcEE4bGdfc3dOSGZSTGtvbUptVUhvMTkzbkZwN1lsT3hqTkJfUng5Unp1TkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQdGJ0aEMtWUllUDFoNWQyNV9pWFFrZk5RaUY2RE5hcVFmaHhKUklLNzdKZnJyRHZDbEhVZWFqNHBhZTd4ZmU4bi1rYmhOZDQxeHZvZEh0RlhXTlB5OWM3MnlzVmZsWlZlaE5wR3dPVlNXdEozZlA3cHZGaWZZVGJuNzJoSXlCaGVXbXB4cjFYRHA1Mm5PNGNsbkZLQ2dyMm5idm9xdmNZYVVSSHNncUdTa2FuVDd2UHhlZ1RWOHZ6aU1yb05GMzZiaG1QdXpXa0RhUk5jM3NIelRtMXF0X2g5Vl8xYllYMHFNSmhz?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46021.36936342593</v>
+        <v>46021.62916666667</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Village Search Bicester and Kildare</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fire service statement after roads closed outside Bicester Village - Oxford Mail</t>
+          <t>Madrid strengthen their lead in Murcia - realmadrid.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:14:00 GMT</t>
+          <t>Tue, 30 Dec 2025 19:01:00 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPc3lqV3c2U2xwYU9vMjdiZHY3XzROd3NZZnJWWkI0dkxXTy0tald2RFBPVDhQeDE5cHExdmJ6QlI5ZzJER2F5MTNuUDFyejBNbTR2VUZfRUM5ZldUZXpUckRSdENLRDlSekctbGUtaUktUGdtZmZsZWRrU1ZDaWhPd2dIdGJHbEVsb21pZ3hJdFBOWEFxcWdsQ2o0eU9KRVZTbUQ3NWZ2SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONG0ySV9OMnNGZEtlLUgyMHBQYlQtaWZpdHAtQmd4M283NGdDZjZVT0pZVmZjQVFRWUN3ZUctczhWMG9oaGdoTEwxNzJrdUV2QkZKZjR5M19UdUJjM3F1VkdJMFVNV1lBRVJaMHA0Q0RudW9rUVZIWXROeUVoTlQ3cUpnc1JHaTRxcHhDM2h0NXVCeVo2NU1zTzg0LW1hcmZ5TE5QeUJWSkhOMDVmN2M2OHJRVGZYQQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46021.42638888889</v>
+        <v>46021.79236111111</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boy, 16, continues to fight for life after shooting in busy street - thestar.co.uk</t>
+          <t>Barcelona monitoring Algerian talent Ibrahim Maza at AFCON 2025 - footballtoday.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 08:55:00 GMT</t>
+          <t>Wed, 31 Dec 2025 05:37:52 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQS3lydkNOa1RfbjlXNHlTZ08wNmpsRTl4TWZfN0hKdW8wV2RFeHpMZW5QaXdLQXIzakx2WGREQ2s0TUd0cUNyc3lRTHY4alhlbjRleC14alNkdk85UGlZLU9peGZPd2duYTBuX09fTEtVZV9MUlJMc01VcEVBXzlsaDVNRzBDbUlOdDhwQTNycWpwbHc3RW1CdUVocXFSa242Ul9uUHV5NFFkVUk5dkRIQjFzVi0zVy00Z1hV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNTHhZWXRFMnpaUW95dkNRVTFRaWt3VmdfUF9TbmRWei0tSld5UUpZZTlwYUl1M3ZGMndjX1ItbDVsby1xT1VNY1VlSjFJbncyRUE3clR3WWE0RXdWVU9FTU9mOUVDdW5EMGlRaHpUMmd1b3RlYTZZUGdhLXVXbU9yXzY2cjM1NEY3d2ZveDJzd0FsSUlTLUJMWEpVamk5TW1TSzZJ?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46021.37152777778</v>
+        <v>46022.23462962963</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Police fired twice during fatal shooting, says Watchdog | News - Hits Radio (Norfolk) - hellorayo.co.uk</t>
+          <t>Barcelona in 'advanced talks' to sign Egyptian attacking gem in sublime transfer coup - TEAMtalk</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:13:26 GMT</t>
+          <t>Tue, 30 Dec 2025 21:04:53 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5md0dEczZuNUNFaFh2ZjRGbmpXUlhiQWxBN3RUbXotTkhjRGdPRHhVTWhmd2Nsbll3Z25DRk1UQ0doSG5ucmlRc2pjZmk4UjJETjFycnhSLU41ZzdVYktSYWxrMWNpTkFfQ2RJMzRhMU50TkJWN0Vweg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOVXFNcFFKTWprLVFhODJEYWxHX3VpbkZkVVlpUm13WnFoSS1rTXgwZUdnUlRsTWU0S1FnTGsxS0xsVWltVkE3M0xYZlJxOHp0Y2tPMW9rUnhMV1JINHFPZEk5VmRYUDBJUk50MUhFV2NSeFJoS000MG5SVWpfa2JxalB2OHVzc2hQVkZoX1NFQUcxSTUzRDhaNkxtbWFnUlEt?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46021.46766203704</v>
+        <v>46021.8783912037</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chatham youth arrested for shooting in downtown London - CTV News</t>
+          <t>2025 was one of three hottest years on record, scientists say - PBS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:56:51 GMT</t>
+          <t>Tue, 30 Dec 2025 16:32:24 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNNXBkMU5ud2s5dGY4NXN5TF8yRm5rU3RyamRqWDNpSUlJTkdoUUgyS2ZfZno2dkNldUdiQVpyX0NNUzNnQ0F2UHdGcTFkN1lEUks2bnNxX2xHYUd2dlVoMmxQV1FMdlZ4NGtYMGlOWllscnVUOEloc0pKT3RUalhkRV9uUk5oa1RkNjdvRlNTNF9hNW9KSWo3Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSkdzTks5WmtZUDIxc2VQY2cyZnFqWkpkU2gwSWlBOU9KQUZkV0xkbTlCRUVfeE9lZU5KY05BZzVqUy1QMEE1dExzZnBIRlBCUnJqNURmR09wbjVid09PN0Q5UHp3M1NiQkNwSEhHT3ZjNF9fTEFLZ3FpYjc5NzdHbWpTbnVucE5vVjdaRXVTRno4MmNaSjFFNFpPTlEyallWRzBz0gGjAUFVX3lxTFBKR3NOSzlaa1lQMjFzZVBjZzJmcWpaSmRTaDBJaUE5T0pBRmRXTGRtOUJFRV94T2VlTkpjTkFnNWpTLVAwQTV0THNmcEhGUEJScmo1RGZHT3BuNWJ3T083RDlQenczU2JCQ3BISEdPdmM0X19MQUtncWliNzk3N0dtalNudW5wTm9WN1pFdVNGejgyY1pKMUU0Wk9OUTJqWVZHMHM?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46021.4978125</v>
+        <v>46021.68916666666</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Everything we know so far after 'gunman' was shot dead by police on A11 - Norwich Evening News</t>
+          <t>Echoes of Figo: Joan Garcia braced for toxic reception in explosive Barca-Espanyol clash - BeSoccer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:59:00 GMT</t>
+          <t>Tue, 30 Dec 2025 17:05:44 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObEYxOERaVDMyQmZSVW1QZVJTLVgtYUU1NDNtQzdSR1pMZHlyUjUyczNTMlBrWC1UZEgyajRRZVcxTGNMQUtEU0JnOVNVTzhSZTJ1MkNsVjY2MDVoSk5PSDhzelQzai12Z0VNUXlSY0pGX1dvR3RVMVJBMnkzYW01U193dllOZzFILVJISW82U3lDbDk1YWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZV9WcXpKX2h1OFY0ZWdpTTFFc2NORDNpcEJNUERiNjVWaEswRl9yZXQxQlN3WjJ4dGlTb0N6T20tU09WLUhRWm1iVFk5WFBpT1FZcWhvaGtaYndxUUlSR3J1WlZJLXgzeU1XQ0V5MEZMaVdIZXRvS3B5NXlPZEZuUDdXV3NzS24ya3ZGV3RJTnZIRXhEZFZnLWhtTG5nWVNvdGo2dC1JMHZ1R1BBQUowT1BBNHFyOW5PUi1kRDNmS1NId9IBxwFBVV95cUxOV2dfOWpVRzRNd0VlQlpNbm1qZ0dNaENFUGFLTEtzUXd6OUxwRlpzMExVb2gyVVlKTHd4MzRzc1ZEdHZCWkxockU2bkYwSkloYzE5dk5SbXJTZlFBUjVPRm9IQjJvZWtLZm00bXdPWHRfcHJoekRLVlpsV2trSU84MXUzY2NXOXJzbjhUOTZ0aDFjcmJ2MXlES1NfZGZZVjVLLUVlWmdtVnI1OGhSenNVVWhGTU1WazBRWTdqY2ZQOERYZ1FaRWpv?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46021.41597222222</v>
+        <v>46021.71231481482</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LIVE as Oxford Street blocked in 'emergency services' incident - london-now.co.uk</t>
+          <t>Basketball: Monaco Dominates Barcelona in EuroLeague - nice-premium.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:06:18 GMT</t>
+          <t>Tue, 30 Dec 2025 21:44:56 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPNHVMYkc0WV85SHhkQUNiSnZTX2VieUcxQXZyenZOOUlCQ2dNMjdUTU45bTVRN2dwLWRsZ0hPT3pXdzdhamE0MVZjbi1GaWdhdUE1OGpZZmtoOFgwWmJwZHk3Qnlfai13dlIxRFZRb2F3Qk5GVVlpd3BnUlI2Ny1jZld4ZG5ubWF3MVppczZzRksxZTRwVmNuWU9JcTdrd3RFNWliWmlmLUpwaVJU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPRjA4ZzhOQUdsNVl4YVNwS0swS3pIZV9PZnBEZWFxWTRhVW50ZFgxdUFfMUs3MzlKLVVIWmVOZlRVNEFLaXFVODRFeTdINjFEUS1adnNuZ2Y1SHc4ekpLelFRbUt4Tl9mWjFSVXRSdThMTTZuelJOVlNzQ1dubks5cklSSzZtNGlh?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46021.42104166667</v>
+        <v>46021.9062037037</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rail chaos as power problem shuts Eurostar - Bangkok Post</t>
+          <t>Scandal at the Palau: Xavi Pascual sent off against Monaco - Diari ARA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:45:00 GMT</t>
+          <t>Tue, 30 Dec 2025 21:44:45 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOeEt0bEd5ak5TTlVvYmpqb243QzZkVzdZTzRWdHVMQjh0ODEwTXllUjZScW00ZjVubVBuRU10QzBET1p0M1M3NG9HNUJDMHJDT1QzbjhicjFWb056X3RWUTRtcWdSYm1aZWZOVlkxSGFQYm5XRXdqMUFmOUo5dlE0QUVRZmlOOVpuWU5n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPMDAwcks4QUg5NDhlbTNzZ204NHZKRFRZM3BRWm5LQUlubFNsY2tmY09KVm5aYktjaVM3TlkwVk9FYVFCZ0hrU20yb1ZaMjNtYkhrZlozZmdOcVowZjc1N3oydWp3VGg1d0VidFQ4d2E3Wlc1am12Wk94bjFZaGhjTmNwalllS0ZHMWNweDJldm9wMG5tQ2ZTWU9LMkhKLUNq0gGgAUFVX3lxTE8wMDBySzhBSDk0OGVtM3NnbTg0dkpEVFkzcFFabktBSW5sU2xja2ZjT0pWblpiS2NpUzdOWTBWT0VhUUJnSGtTbTJvVloyM21iSGtmWjNmZ05xWjBmNzU3ejJ1andUaDV3RWJ0VDh3YTdaVzVqbXZaT3huMVloaGNOY3BqWWVLRkcxY3B4MmV2b3Awbm1DZlNZT0sySEotQ2o?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46021.57291666666</v>
+        <v>46021.90607638889</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eurostar suspends all trains to and from London - Al Arabiya English</t>
+          <t>Industries Limited Uptrend in Early Stages Indicators Say Yes - Ex-Dividend Date Alerts &amp; Small Budget Wealth Building - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:16:00 GMT</t>
+          <t>Tue, 30 Dec 2025 23:02:50 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNSFJPTWFPblRqNUgtQUFORDlLeHpwQV9HdmVGOEM4V0VQVGxnSGV0akh1UWhSOWFkUzVXNGxua2Y0cTl6WWxBYnRIQ0w2WV91dUh5dE1CaWx3UE5faUpzdXRzU3JNaDZxX1pPWDRONlNTdlhWYTY2d0l0YUpmT0N6djlPb3hHbU5tSDJKNnFqSFlzZU9TQlVtNEJ4YnVJYTAtMXfSAacBQVVfeXFMTTRCcVFmSVhIWUlpRHVDN3o4RFF1RTItLUkwSklnZWJLYnVnZ1NCWHlvb3YzbUl4enhMY19VaXl3Q2g3bm5YSlkxVFBjTWROWVRncktIam5xMkcxalNfRFQxZVBSWWRrcTRacFRKS2gwR1dNMU5VbFh1VWxZdEFXZXFHMVBWWHB3TU5KLWtBZUtyUnNCUEhBZzM2MjVKOG5CZHdxd3gzaGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPVWhHYlFTZmJqRnE5ajctcUhLWmktUGE4SWo1Y0RCY1ZiVE5ZOFBCUlV2ZTFrX3dJLUwxeFFnRDl6R3gwVDdWQWlfMUpldzYzb3F5dEtaemIxTmFkeHZpZy1CZFNPV3pwUUY2dlFfZmdQeDhveXRaQ1RUcWRqWm5wS2t3MFFNeXNCeEdyZkg5ejFjX0VRWTBnakU0MWZaeElSaUtVVDVyV2dtZkktOTh1UW42TU1fSUFQNEY3cU13aVVSUnkxWlE?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46021.55277777778</v>
+        <v>46021.96030092592</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>George and Amal Clooney granted French citizenship along with children - RFI</t>
+          <t>An impressive Santi Aldama looks on as Ja Morant and Joel Embiid rediscover their star power - Mundo Deportivo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:52:13 GMT</t>
+          <t>Wed, 31 Dec 2025 07:13:46 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPRkpRZk5YSHQ0UjJIT0xiaklPdXhOQ0JkUVZWU2JrS083MkVicWhINERGVkFaNDlSU3pXWi0zeUluLVRmdFNNczRkWFNuNURJNkVzUENLSXNlVTJKdXRHbThYZlVsVS11QzQ0SXBxT0R4VHRzcTM0Z0I2bE5zWldNWmNrMElYUlF4Z0F4OGluYkl5a2otWFNJbXQ5cGlCbER0eXg5eHlPaVpuai1P?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOMTdRMnI0R3lxQkNwdmoxMEFEOUgxM0FxSnlXWm42X19jM0lIM00xam45dXZYdFJJRHV0cDFzdlZxazVXX3ZVTzZsZnN4M0p0RFVsVEFoc29Ed2NrbWtRQ3A5NWwtOC13TW9HRFFwTWxDSVlpZkFBZXNUUi0wMmdxTldJSlRUYWdqck5jd05zb2F4azJZaVFrYWhXb3YwNG5zZWR6RDlrY3JOMm1VbFl6dTJ1eThKelhMR09tZDRMTm1fSzM5eGFCYTNlZVdqVFZvNXE1WWZIQ2dPbWFaaEo1UDcxSnnSAfIBQVVfeXFMUGZYSkNRUEtqbWRYRWZHX0Nzdi1sQVZfdkJOSHNzU3BYWWk5eTJPVGxUTzRLUjBrZUhZOHdzcU5xdnYyVjdLczB6Q3U5R1BNcjRyUHlyb2JySDI5REN6OXhYd1ZzTWg5Mno5VlBvdGEtaUpibEJBLTZ3S1JwN3lmZFpaaURTeTNNQ2xLclBxUUlmSDVKWUcxeTB0S295QnRVRU1nV0piRE1LZnBHcmY0ajdPbEdzZll3b211ZDh0SWdFa0taT0xVVWRsTXBfZmgyU1JxX1FLSUw1Q2tHclNpY3ZxUEU3aFREanY0ekNiNGlzNWc?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46021.45292824074</v>
+        <v>46022.30122685185</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shooting of Nayanthara-starrer 'Mookuthi Amman 2' wrapped! - lokmattimes.com</t>
+          <t>Miami Heat set franchise record in explosive win over Denver - BasketNews.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:50:24 GMT</t>
+          <t>Tue, 30 Dec 2025 14:40:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNUzd2UUJMb2l2MEpPZ2VqbFE2MXZBVk9Gc0tkemkxd0Q3a0xCYjROcGRPVHUwQnR2NlhSdTJ0RzRqNHFHQ3ptUVo3NDZ4OXpTWllnbEQxd0RFUklyZWhxZW1Tb2FiMHFZOEl2X3pzRHloa240ZndEUUxfRWltcUxYYXRsYWhJLVFpWTFWZ1JsVkZHcDBDbGVvWEdYd3RRcWvSAaQBQVVfeXFMTzhfcXc3NFRTWEtfV2s0dnltR0oydDdRLU04cHpHU2F6VXFJeHlUc0pjWTdza2hrNlNZenloZWF5c2w2MkdZMTZSQW5ZSE1QN2FyaGlHSlM4UFdOMFNRNmdLTTk3b2dHYjdKeHdfWEZoSHBvSTZ6aWZubXVrWEhXbWZscngxNlAyTlNGNF9KZGM0OE1CeE1tY3pURXUxblVZTmIxRnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPQnRPVkNmUXE0Sy13a29EQnE1TkhrV1VYQnl4OTNfbi1xQlBtX2Y3M19CQkZ0S09ZWkthb0plMlFiZkJfYWtWYjJaX1ZwRDJUM0ZIaDNtOThtNjNQX1o0Wk03M213RmdPQ3lUWmxxd2VMZk5JbUhCczctS25OSFB0UjJta0d1Zlh3aWh1d1RtTQ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46021.57666666667</v>
+        <v>46021.61111111111</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Secret plan to build a Downing Street bunker and make the building bomb-proof revealed - Daily Express</t>
+          <t>Texas A&amp;M basketball vs Prairie View A&amp;M: Live updates, TV/streaming info for final nonconference matchup - MSN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:53:00 GMT</t>
+          <t>Tue, 30 Dec 2025 15:36:37 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPVXB5RGhkR3Z3N2JhVHR6VzFjSkZ3eXpxY0VQM1JBOWoxMFZ3Sm56cFZ3UmhfeUNTU2ZuM1k1SWFZZUp4c0hrQnpJcTdITWpxUVVfSHotOU83X0U5MjBSTE85ZzJxcEhUbkNEeG5YbHNPN3RvTmRCWnVHcTA1cHJNcnpvakNGTjRLSkJIdkE3SjluYl9s0gGaAUFVX3lxTE04TFJ6M0stWjBlRnZrWXRmRG1RbW5saWZQWWhpNUtEbERtYzY5ekNNdTZMN29EcU95V0xGblJsdnV1SVJtQS1sY0E1ZGE4eGRfU25JSTdtVlFkWjR0RzF0RTF3S2dtckIwa3hiQzJabVdacWxBeVQtcDRYclNLZ2NOUjZJV09nenpZQjNDbk9kN0h0RklLNjZIZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxPU092U2REcFVGanlCNm16M2xkbGxmX3lWU19PTkEtYlBqc3k3RWMyYUFLNm9DNHdIT29XMDlHY2lCVVY3amRwTllTVlMyRDhNY1BGT211VElXeDB2aUc3QWZlUVZGV3R2MFFNX3BwWk1jTXpJdTYyenp0RjJYNlhRVERPaTlEUC1pZ2VyNGRqbTd2dTJ6NWVuR0RkMkIxUkZpdzRGN2dyNGVqWFpIMzEwLTl2Uk9qQm8wN2xjaFh2Y094RDd5VTVvUnNPQ0t1VkpWd19CemhqVzRkcEhVV3dBdzdUNV9kRTJfT0E?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46021.45347222222</v>
+        <v>46021.65042824074</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ashton Turner’s explosive knock leads Perth Scorchers to dominating win over Sydney Thunder in BBL|15 - Cricket Times</t>
+          <t>Rúben Neves's valuable gesture brings his January move to Real Madrid closer - madrid-barcelona.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 12:29:58 GMT</t>
+          <t>Wed, 31 Dec 2025 05:30:00 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPMnFhRFJpTDhWTE5CWkZxeHU3cHJPald6Y2RJVUF4N3d6SEVNSFFpVVFsR1R0eDBaMlpuUUdPeW5hVnpySGNrRXE5dlM3YTUwRGhsUlE1LVRZV2lDOGV2STUwQ3BIbmJld2xUMkwwcThsSDdJbURKTWRmYUN2Tm5kVGVwUFI0Q3U4Rk9RYlhNUXZZc0FaYnNBajRjekxvWERzNklNZWlkSU5XRWs2OFNhYVJ4Vi1fSWY2SEF4SU91QUtfbGxsY1ItU21pUVJadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUTFqeHRQQ3l3azA1cHBHcWNrNDRtUHVWRlRCUkowaGY1aGVJeWJRTkM5bDZZYzAtWFJUWGlQc2RGRmFrWVRwSzRxZngybTlkcFBYeEd2NmZ5d3YwWDlhWWhkYm9jc0cxWEhBUk5vRkZ6M3FLOURnaHhXNWh3RVVnWDYzeHlLUmRKVjhVMjd1X3cxSG1GZFNiY1pjNk5LeHlLT2hweEp5MW0yQkpCS0E3RjNkTWtGc0F2bjNZX1M1OW9iTEE?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46021.52081018518</v>
+        <v>46022.22916666666</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Life Back Then: When “Free Cures” and “Non-Explosive Lamps” Were Cutting-Edge - The Sun Times News</t>
+          <t>Trade bomb between Real Madrid and PSG! - Fichajes.net</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 12:34:09 GMT</t>
+          <t>Tue, 30 Dec 2025 14:45:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNQmtDQWtnWURsMEdWbDdRd2xqTFZsNzlpUGFnM0Q3X0p2TlktbjFtTW5vVy1aNGJxVW1XMEFSVElCSGJCRl9rWldUalItQmVKS2t4b2gzRTlzcjYyY1BsR1paRmxWdTRTdEdGS1RCdmwtaGRzTXAydGlEMGR3dzBNYTVyUUtScDJqWEJWNGc1Y2pobXFENGgzNXdZN09HaW1UdGNF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOdUVBeHBKWEhyRXRiNk90SG85QVNkSHFrUlV1OF9ZV1VFek5fQWdtQTVIVkJ0VXZEZUlJbnk5YU1rR0tMTGFHamdHX2RxYWxVTXhwaHMzcmwzcGtJaXJUX1BYd0Z0SjNOZkNQaDkxeWZVRFJOTUw5S0VaeWdXMTNUUmhZdko4c2szTlhhSEtR?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46021.52371527778</v>
+        <v>46021.61458333334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City searches   Italy, English   language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Roma Misfit Dovbyk Linked to Milan, Como, and Napoli - The Cult of Calcio</t>
+          <t>Warning in La Liga: Lamine Yamal at the forefront of targeting and a study reveals the spread of racism in stadiums and platforms - عالم تسعة</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:00:00 GMT</t>
+          <t>Tue, 30 Dec 2025 16:43:55 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQNE9pdWt3YlFaMWZCSVl3RV9SZ3psVmFMUjBkbFdHUWNVTjRwalEyODlRc3lJLXBQNzlmcHZLUUl6WFhySXFINjJlbnJTdVZZR1Q4cWZTSGFVZlNSY1Q2MDRITGZGNmdZVmJlOGdIRG83bXVqZndPQ2xzNDBLUTlMa1dB0gGHAUFVX3lxTE9sZXV2SF95Nkl5enBkME5rTEJIbTlaX2xMc2NtcGFVZXAxWWptam4wZmN5RFBEOXU0LTVwWFNwZTB5S1RWU3JDdGZuYkNBcFl1TGpDa1dCal9RUEdPRElaUWppVFhLT3R3VmNBN0FIQTlzMUEyY0hsNTFFYjAxV19VY3RJRkFPZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNUUlxZXBkend1SjZQQjlQUmZHNHFPb2tVQ3NEdG1oNEJTT3pqQ3FBV2FDb016NGZiemp0VHNIRUVFZ3FPRzJCenVJczRaWEJaVXZONTRweFZvOXlXTWoyMVBGLU1XM0xUSmpQdU9GYmlUUkpLZUVZRE15X0RLSUd3T2U0OEYwS0YyeWNvUlBQX3ExVnlxM0gtRzZqbXdOeVdfUDZYVF95VkZSSkxjelZwbHY2dXVoR2xYZk9fWGFxX1pFVEJUNm9RY01UTU9IMXJIU2U2NXVKYmlsMUFIanBuYTRrQ1RZbVByWGpnUHFUZEo1bnphZVE?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46021.45833333334</v>
+        <v>46021.69716435186</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nine injured in tram crash on Antwerp’s Left Bank - belganewsagency.eu</t>
+          <t>Published on: 2025-12-31 01:01:21 - bollywoodhelpline.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:18:00 GMT</t>
+          <t>Tue, 30 Dec 2025 19:33:03 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVXJLZnhJcndyQzdWN19fM0pGRWpQeVQwQTd5bDNnNXYzRXVUbGs5RmhhSmI0SWRzcXd3SHpGZmRab0M4ZHhQMVExbFFmNEdFNVVEdHZkSklla3FGeW5KUUNwR1BUVTE4QUN1MHZ5Q1ByQk9HMzc2TXg2WEJDZFN5bEtnLUs1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxONHQyVFVSZEZUV1R2MU1RNFVXQUc1SzdjbjlPS1JUUlVVNklVdzdEX3pMektobW93cDlsdHBLNFRtZWhHZmxDeUpiUGRLMURPNnk2LUZ2YUVMd1VUS2N5eUk1WWtlOGVGUW9zdnZ2ZVBMV0pDNE9NX2k1NFFMWTl0V0RYa3FlRzJjTTJGTGtTOS10M0xPZlY5c19YVkF2S0dnejZZ?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46021.3875</v>
+        <v>46021.81461805556</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Village Search Bicester and Kildare</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France to deploy 10,000 security forces in Paris to deter New Year’s Eve riots - Brussels Signal</t>
+          <t>Looking back at shops which opened in Bicester Village in 2025 - Oxford Mail</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:56:52 GMT</t>
+          <t>Tue, 30 Dec 2025 14:35:08 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPbXpDYnBqakZ0MFFhV1d0d0JVd09ncU04Wk9VNWFiRElwNnh5dTJkWG1nMkY3MXBCWGo4cnhMM3V3NmdDRHhhZ3YxdlhkcTh4eGhGNUdJWjB3ZGcwcWdWci03VWk4czc2QjlpT2M1eVdPMDNJWFNobnZQeWxTTVp1MHhKSjVfZlZqRlFMVVNBX1p3Qm1OMVpfclNMOUk1NUZOT1VEYlNDUm1uVG90MGxqaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQY0lUbkpWM2J4QXJ4X3BQb2ZkRVpfSTZIMzNFSHN2ZXZlc01zVnNXNnFzTmtLRTJzNVd6anlDZm1GMlc5bHMyU19zdG9XM2YzUkFmU3pfSVE0REV3TzZwcWttMk5WN1VOelFLUTNwXzgxTXZGd0pna2VmRDNRSGJZOVNieDd3WF9ZMzZYMXZWRlY?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46021.58115740741</v>
+        <v>46021.60773148148</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Village Search Bicester and Kildare</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>‘Cry of the people left out’: Polish farmers swamp roads with tractors over EU-Mercosur trade deal - TVP World</t>
+          <t>Residents of Kildare village afraid to leave their driveways due to dangerous driving in the area - The Irish Independent</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:29:00 GMT</t>
+          <t>Wed, 31 Dec 2025 06:40:00 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQNVo2R0tDeko0ZEp5eVRVcVhqNm1TMnRWM2FqMkFURDZSYUdmMmFCNUJBRkhHajBPN1dDbHZaX3hydHQ5eTBwbm1RbktTZzVET1NCRE9DOE5tblo2OGRNazJfNG9lMlRpQ2xSQ1RyMFlnNUNnRGUtOFExbzdWei1naWltS21tR3l4YzlUZzF3XzBfSnpULXAyTEJlOFRCdGx1VTVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQNlJ5ek8yM2NYUlJrbnZ4blRLZDNudFlFMU1aWG81YVhPc1ZSMl9sWGM1ME1YTzVuaEFXdWxDUnhyWTFOVWZ4d3E3dk1MemJfU2NJX2F4OHdTMWg3dkZ3dE1jUUxZMGd6N0hkbHB0eE9yT3dRUlVwb0NGRndxR0l0QXNBeWNkbWFUOG5Wc2JQNHNxVjVrdkcxSG9DVDAweXQ5UDYteTVsdDk5eVZqUTctZjRVNkpnMFNxemNDS0s1TW5mQkNNSE5ZSW4wNVhieWh4VTVPV01PdzRKSUV2VUp3b0VwcExZYzhjOFg1ZWZnR3ZQRnRyQVE?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46021.39513888889</v>
+        <v>46022.27777777778</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>Village Search Bicester and Kildare</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>( "Bicester Village" OR "BicesterVillage"  OR "#BicesterVillage"  OR "Kildare Village" OR "KildareVillage" OR "#KildareVillage" )</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jan De Nul advances critical infrastructure works for Antwerp’s Oosterweel Link - Project Cargo Journal</t>
+          <t>Lululemon founder puts forward board nominees - thestar.com.my</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:00:18 GMT</t>
+          <t>Tue, 30 Dec 2025 22:33:32 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMmVnTnBjUDZDU2xJTkY4UF84d1ZkSTBmV1VFcERvZFRET2N1ZXVELWFSM1RyUW1pUkJMcFRNMWdXNWRzUHQ2d3loWmV4OTM1dHZKNEFfb1VtR3VzT1BQdGRDdWtob3VZc3JjYmdvMHRxR0wyX3ZqSHkwZFZfRWw5MXpYNjJ1V1F6bmhvWWpIdTZtVko2cGdDNVY0b3g4ektSVXQ0Q0tTcTdDRUQ5eGFocFZOSkRiVC1ROFBYRVVSMDRZRkxpQmJEQ3V4MkNLeGUtSUpFVTYzYlVOU25sVU9md0x2Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOVF9Cbk5pTlEyeXJOSUVCX1F1OXNTWGlka3FXaEtJMkkzcjJyTjFGenJLZlJTcHBFU0Jael9teG0xVmthMW5lbmJjWVpuLTc1QUFFWjVwQjBvem9uUzRqOFg1VHBxNDVvcl9Gd0hITEU5Z0JTVHJMby1ER0VKaHJoQ2o1WktkN0d1cEpUUFNTUXZ1aVNubUNKOGZtRm5Sd0otNVAwZUtUTXNxZw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46021.416875</v>
+        <v>46021.9399537037</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Level City searches   Belgium Dutch language</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Europe has 5-10 years left: Dominic Green on mass immigration &amp; civil unrest - Brussels Signal</t>
+          <t>Mystery surrounds 30 minutes between car crash and man being shot by police on A11 - Eastern Daily Press</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 11:16:02 GMT</t>
+          <t>Tue, 30 Dec 2025 16:50:00 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPYUpFa1RvZEtaa1hsYTRkZ3J1dXdORFVGYVhiZzBYVlBKSjRTYjFWNm5KN3BpMGZsZ0xBd0dZVmxDRFN3TV9UMnUtdUdVVEJJTnkzbXN3YktBN29SdE50Z3hiQ3VjYzlGNGh4c1ZldkwxT2RKYVJSNzZSd3E0ZDdYM3VxcXVza2tGYl9jaU1wQ3oxaDJUUlNDREhaSTBIRm5NMHNtQncya2VrWGhx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNNzVQYmE0SUkxYjFZbnE1bFFIOXVzU1kyQ1EyYUdndmNLUkpIelBIZWpYMWZqQ0gyR1F5blVDSEttS1JwaFk2VGRjQ3pFSGFKanU4eWMzdkQ4eUlNYkFEeUxNS2laanBfVlNieUFfRTVDVTNtUmpuLWVPMGk1VHY0UGQ4dHQ?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46021.46946759259</v>
+        <v>46021.70138888889</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Appeal to find missing Newbridge man - Gwent Police</t>
+          <t>Moment comedian's bag is stolen from under her London restaurant seat as thief pulls 'dance move' - London Evening Standard</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 09:18:00 GMT</t>
+          <t>Tue, 30 Dec 2025 21:29:46 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPOExJWTBkTl9mUmJPQTJTMkRlYzJ0MnJnX29fU1ViS25IbWEwUHdBbXc2Z21PbjRHcGtBZHBfNWNXTVNVakFiU2dYdlVmWVVEOVgwVnRqUkk3RTRQTThnTE0wMnJORUhzbVVrNm9ISlQ1QmVwcXZjeWlxekw3cXE2cDdSQy1HSzZId0NpNDZMdlpNTDFsbXRCZDRjSDRrMC1uTWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYTdjd1lvOGtnalNjOVZLdW9rUTNvMTFOXzhpMmJhY2lqR1Nlcm9DbFRYOUlDZHU3aTdHUmZmekJKOFM5LUVtYVllMkxiQ2s1b2lvLWJETWFFZloxQ3Zvd3ZLbW91RnBHMzVqMWF3aDdYNktoOXNaQ1FUTG5HaVpSTC1pZ3YyTDhrSzFmVTRPSUFNYThOZ1VoY3FJUVdRbDRhczVHbF9BNU43MHVicS1yZ2thdzJqeWRqSDhSUA?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46021.3875</v>
+        <v>46021.8956712963</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Woman dies in hospital after road crash in Co Fermanagh - kildare-nationalist.ie</t>
+          <t>Woman in her 40s 'unexpectedly' found dead in Croydon - Sutton Guardian</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 12:05:45 GMT</t>
+          <t>Tue, 30 Dec 2025 18:03:18 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQMkhuUThvRHJOT0JqRV83M2d3QVFOSjRDbTRDWDhSQ3U5X3ozNk9OSWxLakZObVhNRG45RXpXMnNsU05GQ3Z6TXZmV05ZQkJjV2V0QWpJY20wX2dCWnR3czhVQ1Q0SXBmWTFlRUJUTEZ2Tm9NZWdTVWFEd0tMMkM3T2JyQnNCZ3N3OTFNSzlfeGphSG9TZEp2V21zMGgwZ01oekIzREdpbmtKUTY4OXUwdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQRmxTUXFFVWMtVU5LMHNDb0lqa1pTV1JaY2cxcXNyVi1zOHpVbzlkaWVKLVBuQTl0YW5vRm5YOVFNUHpubXlDWml4LWdUYnVEczhQUGllaER1WVNWUndTUk5hNGlud211QTRyUUFyYmJQSkhIb3hXSEZMUVlyM0JIeHUzYlRFcXBsc0VJbUlZcU9LRWZDNUhR?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46021.50399305556</v>
+        <v>46021.75229166666</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AIB rolls out new cash machines in Kildare - Ireland Live</t>
+          <t>FA to charge West Ham after explosive incident vs Brighton – Exclusive - West Ham Zone</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 10:36:26 GMT</t>
+          <t>Tue, 30 Dec 2025 20:23:47 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQMHZfTmZVTkNBbDlUUDh3YjRBV09KeHBNY0hkYXVJaWxacFZaeXJycDJ6bTF0VExDQUhfQW5mVmp3aW04X0ozMEh5eTBSOUwya1BMdXFQMEx2MmpSejdFdk85TlNWRHRKczY4TjJ4UXl1ZGhESUU0T3NYT3NzNURneG85SEMwdUtXM2pGQ0lyVGprLTJuUnhhaGVYcFNVZ2RPRHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNYjhjREktQ19vLXpwS1QzWDBuT0RZR1ozVWE0dGN6TDZmaGx4aWR2cklSR1JmYl9GTFQ0bFNfYlNxeEpUN1hFbkhPSXNuTmZOX3daWHpHbDV5NWhoOU01eWNMSm9xX0tkTmlhMENVbWRNcEx5WnZyNUdGdERuWGJ0MUJkNldURldEcGlXZS1teXpJenZmZzNZZGxuOFBRby1DS3FOVTFaY2RPLXkz?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46021.44196759259</v>
+        <v>46021.84984953704</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ireland / Kildare Protest Groups - Social Media</t>
+          <t>High Level City searches   UK &amp; Ireland</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Police seize ‘significant quantity’ of drugs following chase - kildare-nationalist.ie</t>
+          <t>10 London council homes found being illegally sublet on Airbnb - My London</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tue, 30 Dec 2025 13:32:43 GMT</t>
+          <t>Tue, 30 Dec 2025 16:56:45 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNTE81WnZiUHFVemQtM1ppZmRaazVJaExsUXd2MHdESDduTUx1aHlmWDRneHdFODgtdlA3dlZOSjkzZWxnRzRXTUFrWGxYcXd2azVHOHB2NkxWbVVjSzN6RUI1d1hCSG1YQTJtY2NvZENHbk5GTm5fMlpuY24xM1A0bzdHTWQtTHl0RmpHNGVZVmhjOVBDMzloY1hDNGR0SFp2aG9XYk5zbjZCemYwUVVXVTJzM1c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOZXRRWFY5OFlCYjZDS2lVZnJJUVA0R21FUVo2eG5LMENKdndjY2RVZmdhcU5DSjNPVi1WajBldEVnREhkYTJSRGJSc1NsbFU3eXZneTUzUl82RGZnODF5MDhVMmtvdHFOM0tOaERiTVBVeFRjMWVobkMyck9nT3hkSGZsUjgtYWdKTDllTWdhb9IBlAFBVV95cUxNRVRhYXhtbHgtUGZ4bjdUWURfcmhBYk9WZW9wanZnb3Z2N2FDUVJKaXo1bjU5OWVHSE40djZUTzg2WnVralhTTGVKaGN1Z21ka2lUMkpEdkk0dVBacnl2NEdROTVmQkxjSVNpRHlGYmItYXdNeVM1WndPTG4yOVpwZFpRWTkwaHZ3ajhaLUZYcnd6SmY2?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46021.56438657407</v>
+        <v>46021.70607638889</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Michigan's high court mulls hurdle holding up Oxford shooting suit - The Detroit News</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 19:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNVU83OWhqWkFnM05lZENmV2RVOTdES1hUTFByRl9iSzZZQ1VsZ0dvYjVSMkR2OUNwYy1pV2lUZGZqSHI4cjAzaXFGRVBtanFpZnhGSkxvYm14NTc4WnJmUUVOTGxYMzFWaWgzTkR3SkMxbEhma0FNRVBmQS1obE5oZmhkZ01QLXpHTUJJRDlLS0UxMW1sZDJHSkFpeXg3aFh6UDNVNEp0VGhEM0lKMUxiWlByLXMwUUd4NzYycW03VS1NOFR1cEhUTEF1U1ROeHZYYzg1cHJoWGZCMC1TTl9wa0QwZWk5cXhRU016aHA4UHhzQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46021.81875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Interactive tracker shows how safe you'll be if nuclear bomb hits as Putin debuts missile - The Mirror</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 21:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1XWFZDU3hsaEM5UTNFQUNpd2VlU3Y4TnltdGlEa1BjbEphUXhpcjR1M21iR0k0YjBoWjFnZy1IU25BS2tXWkxGWU9aU3MtMHU3NlpFcFRKYW1Cdnk3X3A0emQwRUdrRlU2Qnk5bmxoWnhMbExCNHgtcWJrcEt0VzDSAYQBQVVfeXFMTkpGMldnM2k4c0dKeXlmdHJEQkQ5T2dOTFVDNGdydjd2NW5jbWZPaXdjaGhyU0R3ZG5mekhWZ3l2TXZHRGR2eVIxWjc3RFNDZXNVWmZTNlRieHMyaGp4VVRKbEt3ZmhxZTdncG9IMS1fbG1Gb3dqQ00zeHB5MFExQUdXY1JQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46021.88263888889</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Police raid home of suspects in fatal stabbing of boy, 15 - MSN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 01:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxObC1lRDdEQWNrTDQ3cUdRaW0zcms1WHFpeGdYLWl2SDB2UXZNLUFCOTBGSGFuTXNoWUJITDdJVnN6VVFYWkpUaUNOcldmRGdfWmtCVEF4akx3TUkzdVZ1eVk3dDFnTndIaE5aTHpsQ0ZQdEotM1B2WC1PNGR2OFcxUW5TSkstc2hUQlJXemo0ZXRIbFgwMnhJNFFMQkRra2FrV0luT1RmaFBVb09aQ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46022.07847222222</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025 Year in Review - Oxford Leader</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 05:20:38 GMT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1aZ25WdHpPTkIyaDlCYmpoR1RCS25LclRRVUZtQ2xTWnJzUTNhRXVTY3ZlX0xoQ3RWQllZVTZuMEtWcVczT1JicWo5NlNGcHNsclpHYTF0ZG1EZFVpZWRMOUJZLWFZbmt4S21N?oc=5</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46022.22266203703</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Transport for London - My London</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:47:18 GMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1hdFhJUDBZNktZQ1hmWmVpell3Z1hJRElPWWdwQTZCVWVUaXZ1dnJadVFtcWFWb1ZBeklBdVFTbWNWNmdNM2tHZHZzbXRzeVlfdEt1QjNRS3hHU3AyRkhsNXI5VjdXc0k?oc=5</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46021.74118055555</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Unclaimed Bag Causes Bomb Scare at Jammu Bus Stand - Kashmir Observer</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:20:38 GMT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPVmswUW8wSm85amhXVldmckJjZzdhbjJ3YUJ6WVFmbkZEUk5aWDZGcTZrbk1DMERGQkhyZklETHZjNXZaOGUyc2lUczd4TlpnaGU5Qm5NdHVTbEExWi02NGFZTkt2UzhZNFoybk1BZjE1enpjZ2ZnbC1ZRE4xMVZ1MDJjeHYxS005ZENFUkl5R21Db3FQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46021.72266203703</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>October, November and December 2025's biggest Oxford Mail stories - Oxford Mail</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcHlmaTBua2twMnZGSk9ieVhjR2w4MjVyeU55VVFZU2toc19ra2dOU1A2ZlAyT2ZDdV9wZEJGUHA4YlVYWGZQX3pScDljMnNYd2U2a0ZXeGFxMTBCN0E0WTNVSXMyYW5aTHNxT04yQXdJSW51SElpZ3hRVmNDTUpJSzhGZGgyU2x6SUFNeGVTYUtLS1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46022.20833333334</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Brackley back up Boxing Day win by beating Boston - Guardian Series</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:27:25 GMT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPb25ZRG9fYnZHMmEtUjBFSkUzUHBseWpJbWRXS0RXaWZleUZuRWNONEZHT3JPWml2OXdpa1VxalMyLVpSQVgtYlhYR3o2ejlmRkVYajVlNTBubURWSVVPRVYzOUFyRnZGUXdGLVpHejVWRVdpTEYzMEZHejV2eDZjcnZKWXFTRmhXb0g2NDExQWNPNEN2dHF6S3pWazhrOVRoeUc3WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46021.93570601852</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Stockbroker diagnosed with incurable blood cancer made MBE - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQTGZlMzNpcldzeDJ3Z1NmXzBrbXZzMDNlOUtKZXdaYlVvTEc1QWhiaWZYSHlIa3RRaGc4M0Q4c09FX3MtdkRhZzEwRGJnOTNnYkV3LTk2QXFQVTkxNXRoN0JRVTFWMHpjOGloU29QVm9iQ3JRTnVXT0pfV1phNGhnMDFBaHlRN0ZRc3lhOVRRTFdfZHVBVUJhNHk2bWYyS1YwNGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46022.25</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>York beat 10-man Altrincham after late drama - Guardian Series</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:08:38 GMT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNHhINFFqc3ZwZTRQYXpUUlpERjZLYkdKYkw3dWRvVFpKV3NOS0dublE5YTh1XzB5OUh6WjlydU9ySmQ5VkJvVVVaSWt1cGNGekpwNEhHdHlsOVNnSVowaW5tVkxXbHFjOUo2MllITk5xOUViRzJvR09KZ0RPN1k5SnJnZ3kwdDlhS0hDcV85M090OVNRT1ozWWtWRXZ6Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46021.92266203704</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Luke Armstrong gives Carlisle victory over Morecambe - Guardian Series</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:08:41 GMT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNV09aNjQ1bFRzVGhnT2tXUVNwVkViWmtzNGFRWTVFYllMRi1udTVaWGxDS2UwZm82b3dLZk5SYkFfbDBxdi1JdnBwTnY3dkhBcWtvb1FLc0hmRDBpMm9IaUNZOU9naXkwMlYweTQtdHhRMXRkUWVBSjRqRE45Y25qc29JYUxvbnBQT0Y2ME1sczhIZ1hYMlk1QVVuWllTcmJhRDFzaFJFZnlOQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46021.92269675926</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>The south east London New Year’s Eve travel changes to trains, Overground and DLR - london-now.co.uk</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQZEUxeTl0X0tjYkhVSFlITjFWWWJKU3U0LVJ6el9RYmRlNHZMeEx1c0NaaUpNUTF1Snl6a2pZZlJsYzdSWGZvSHZGZjZIRU5ETkxrLXZQUHZZV2ZZeEMwc0hBQWZfWlloU1lRR3ZoWDl1NEgzUk5zN2dyVWJWeXJ3U2txejBNN0o1bmRJUWJBTi1qVktxMmVpT1VEallOaXgwbEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46021.63541666666</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Global New Year Celebrations Curtailed Amid Security Fears as London Presses On - Kursiv Media</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:22:18 GMT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPU0VHcFJHamZlT0VwTnFTaHpVSkRnOG1jX2p5UDdBbVZDb1A1WW96SjRFUXE0YWlLdXRaeHVLaWJRYk12U1Rpb0NhRy1IcmNuV2p4NGhsWmlpRUpOTGJfTDJLekktNXF2NVo0dlF1aUdsRDFIUWhxbk9yeHRNN2JMVVdkWUxwZEtDaUZOSDFZQ3dieGNHU3RSWkRFeVROX1lNT2xjMndoWW5jdnBGN0NjRmgtamZZNGctSnfSAb8BQVVfeXFMT3VjZHRMdDh5LTQ1QVJ6UWowb29Ga3BZV09EN3JodloxaGxCSjhicDA4TDBjTHJqYUs2cEFLbUZvRGp4V3dDQm9LTmJUUXpnVXNCLVRWd0VwSkxoWjRSRkNWbG9uOGhNa0xrYmg1Q0VwRFdjRTNibzJxQUp4c3RySlNQd3RuLWd2Umc2NjBqSVZFS0lXRzN0Z0wxb1lXdjcwSF9SVU9kYU0yM1RpOEV0UXBicXBMNVJ4eFNyUWllT00?oc=5</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46021.64048611111</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2 investment trusts from the London Stock Exchange to consider in 2026 - MSN</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 14:29:17 GMT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNX2RfbzlydWRKT3hMU0YyT01lZGdidmdnTndoSjdVVmdhdlh2OXRpOWRSa2RwdXJZUmREQkd4OWN3ZFhrMEFUSGJnNjRyLTdscDlOYXUzNjhNNkxnRDZiOUdDaDlQNXg5VlF3MnFBM21ST3VvU1VOSlFJMG0xTDE4Ykt6WGhXV2YzRTB1YnJEaVVtRmFUbGVGcnRkeHg2eXUtRjFSOU5WVHN6YVhWWXptRlhpWW1zQm1kMWdzNUs5SzlaejQ1N0dqU0UxWnhSbGt0Smx1LTY3amktNDJTSnhj?oc=5</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46021.60366898148</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Inside Putin's secret £100m palace where he is 'trying to become immortal' - Daily Express</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOcEpBcUZ1bmlnTkNfUG9CSGlqYXJ1X3E1UTBqRE9BSnU3b3FmbWExWDFUWnVXQzlhc2pxZ2xabnRoRHJ6N090aGpMQnpHZEFsRU9vZkFrSi1hb1YxQWNESjlETHNnUWd3cnhfM0Z0STlvUGZDRzdoSHdUc1hjTFdUX29RONIBiAFBVV95cUxPNkwxQTk2Q0VKbmVwM2pGM2xka0p2c0RYZ084WjJGalJzcWRjUHJPWUJNNzl6em9iSGNkbE0tSW1mN0Q1OUpRa0FiREJxa1BTVWdvMVhzT1pEYkVsNUtkRWFoQUpFRkxxRHYzUjVoSjZLXzRmWnJHRlIyNXM4QjlJQXZhcDlJekdO?oc=5</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46021.70902777778</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>High Level City searches   UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Lerone Murphy Recalls Near-Death Shooting Incident That Changed His Life - TotalProSports</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 04:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPYnNhbGhrMC12NnA5RmRreXBRN2M0Nl9CMlM5OGl4MlQ4SEt6aEFPbDA2bjNWS2JBS21wSnBDZ3lna0MxSlBFbXhuZk16c3Q3dXhYYzl6bVVHM3dzcTBKWHJLYy1NbGVpS0U4TFRDdUNQdGhDbmQyNXlFY3QwcHV5TkY1WkVZMzZSM1lIcC1uRE1VeWdVRlBic0lFT2h6VjlUbUE4aXJqRW9BY0pf?oc=5</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46022.18402777778</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>18-year-old Paris man arrested after stabbing - WAND-TV</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 03:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNRWJXUDZSUG9fbFJoUzNRQmctaUktczNtbWE5VUVVekN0eld3c1VrZFJ2bUVTTU54WHpZVXR4NmllT1FHeWFpYVh4ZmFORnp5RUFPYkltbFAwOU8yR2diWHIwLXQxaDIzcWc4aW5WTmhoMU1fWDhXSFJQWDlFZm1HQUUwNDVXN3JraUNxVGdRbzdDWWhpb2hZVlFjU1VxVVFwZ3hDMk1qdWY1cGxScjRFQkJfc09UZy14ekVDNlk4MlphWHRIazdkdA?oc=5</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46022.14166666667</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New Year's Eve events cancelled around world as chilling warning issued - full list - The Mirror</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:46:01 GMT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQSnpwMmpMN0MyOUVidEZQbEVKWnJKSk9RYkYxVTQwZjVqRlAwRnh3TV9YV1RtOFV5SW04VDNFWXVxLWl1Y3lLUmNGVzdVQTlYcWlmZWlhY0FMRlNsREZJN2hVTHN5anZKRUdQWEk3ejBSNzh5X1pXUTdIaldwQ1NBd19FUjZJUGvSAYwBQVVfeXFMTUdKQTVRMjF2LU01LS1MZGJHZGV0NDQzak5RR01XaEdISmVsYy13NHJKQ0Q2TTR3Y2dzdW9PRXNJNlZDb1B5d2todGtldjg2SzdUb1A0Y2oxVUpBaEhoZkJaM2RfNnlLQ1RWV0xBZWdHYm9SdXJuRjhOeHRveFRGbENxUGJHbS1Sb1FMRDY?oc=5</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46021.78195601852</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>South Carolina cruises past UAlbany in non-conference finale - Southeastern Conference</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 02:39:49 GMT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOTDh5aGpuQVhoN2VfT3JwYUw4eGFodE43Mnl2ODhveVZGdWk3SVRYUmFwbUZLRmFFeVB0aEUzUHU1cEJZNXhFc3ZPanh0LUp1SnUtRGtKN09DRzQ1QzNTY3R2dzVLSG5BLTNmOVh5cjRDcmhtTjRJdEwxbkJVM1RjSFhtS1Z0dEJJOTZzUGV5X3BLUjJwcVdEbWQ5NzZkNXRn?oc=5</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46022.11098379629</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Paris launches winter emergency plan as homeless man dies from cold - RFI</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:00:42 GMT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOU1pGaWpxdnVmY2NQRWZjZlJUQmw5aWxSQ2pfR3VCbmRaNXhJX2xrLUk5RldDYzVodHh0TkI4ZXQ2OVhILWJYLWo2Q3ZIaDlLMmJvQWliN1VSNXlURDlDTG90aDJNdFM1b1prd05CcFhMX2hESzV4YmJlT1JqUzB6Z2c1YzlELWZQV1pSTUczZkdjZldObEJEU1lONUdjOGZFZWxEM19Rdmg?oc=5</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46021.70881944444</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>India’s in-form shooters, boxers await inclusion in Olympic scheme | Hindustan Times - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:56:13 GMT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOZUtXNFhCRWI1X0tQOV92NE5XaEQyWjNLbU1mdkoxM1FvYVJNT1lqVEs4ak5hbTJGMXdTRW8tdkw3TjlXTTJYZUd1QnNpR0dPbjJFNTM3V2VtZmRZVTNsa2QtQUdiM042V3JVcWx5a1ZxaEx1VWx2d3Z1M0g4QzVFMmFucWdielZRTjJ0X25zWXZnV3JLd1ZmaHpaOTJ6bTAzVUVJS3ZzZlJJUWtxN0lvQmFLREwxTjJvZm9CcGlfOG9XOW1paWpkVExB0gHPAUFVX3lxTE5ubEdBZ0k3SWllNTF0WkpVMjctNE5oNkdZREVqUjhaTTNiemMwa09DRlNRWkQzWXRXNlFmbnd6NHpsVmlMSmFuRktiellrWHdJZnlJbi05S215RERucE9iMlcxdWFCWDlXZDNjcjBjVnlKcHhOOHJKZ2NFM0MxaXljNmhHNXZGZTVSam1JQklqTUlvM3hUWEpHcWhTLVZEVV9YUWtDNXdZQks4UWlOTkZTMmNyM2JoS1ROVUtoaTFENmVTXzZJWS1xVU9zT3RaVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46021.95570601852</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>National Shooting Championships: ​Delhi’s Addya Katyal wins Junior Women’s Trap title - lokmattimes.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 14:25:45 GMT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRHVSYVdFT3hDWnBlMTBySUJLZTlmSUZIdDBPQ05aanQwdkpIaUtLNWZEZ1NFTG5wSGNtckhhMzJjN1NPamRVelVxS000MjgzRTBMOWh0QlR5RWtSX3lBRVBlMnFaUkxwanh4TjhzZVFjVDBGcFVsSjBpZFdPeFZuczY1eG1HLUNpeFhlZXhNNUh1b1Z4NlJGOXNwNmhBS3d2LVhUQmFNQlY0NEswSkZuWmhXTGlfYzFMNm43RlhVTjLSAcYBQVVfeXFMT2VxSzVydWs5cFhxQTJINjdRWFFPbnluWExaMHJTYjU5Q1VneENkVThqTXRXQVpVTnB2RjR4eFV0d3BjTjJIMmFPRFo4UnY3cnFxYmJRR24xcUktbnZtWGNacERKTHlOOGlMUG54WnhmRUUwX2ZaUkYzMkZlWDhMRVoyVmJSTjlPNDRWaFN1ZzdMUDZPU2Zadm85N2VCc3FXTl9BWFhzYWM5SWhGcW9JTk01NGItQUZlOVBaTFkteDBYUUFwdGx3?oc=5</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46021.60121527778</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Jordan B. Peterson delivers a talk at the Folies Bergère in Paris - Sortir à Paris</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:05:03 GMT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbllyRTVUdnBKZzNXbXpCeWVNMTd1YTZvRDRTQVNaMEJmd1ZlS0lWblBFcGlIeUlTR2VyY2JRUTJWS21jY3VtTGROVkdaSHlRQVdJeGx2OHctX29LSF9KdTVTUVhweWVCYTU5WmJ2VkZTSWRhZWdaWDZtYk5QTFhVNzJXb19KdngxTjRBdWNvOTctVDJJeW5PVHYxamt2UE9qbVc3aFIyZjlEakk4ay14ZUU4N0tfSzFmMHlYQV9UUmJIbXVzcnUzTG9IUGJuTExmWmgtT1laLTlOQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46021.75350694444</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Paris Autry Game Report: @ Southern School of Energy and Sustainability - MaxPreps.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:17:46 GMT</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOb18td010VEZ0TFl3di00ZEcxTXk3cjE4emNXZ3dsWmstYU03ZU5hTXRRbnoxbWtWOVBsMWZVb2o1M3ljLWQ3aDBwSGx5YVlCSGFmc19tZF9KSU1IZjJGejBTbXZMRVBmNk10WXRITXVvSjd1SWJiWFhOMGhjTWFwdHE3M3hPX0p2UEctUkpGQ3huRmUzMTF0TmlEVTBQVzQ0YjFtZExLQ0UyVXJ5UmppU3FpWHhiS2Q4bWJ0TUdpTF9UNmV4LTRHQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46021.63733796297</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  English language</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Cockeysville Shooting: Heavy Barricade Situation As Police Surrounds Apartment Complex – Urnserenity - androididee.nl</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:50:48 GMT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE5zSTFFNXU3empWUWZlMTFDM1pGMHd6NDdDQk5HNWY1N1RIM24weHQ5Q1VFUUk1RkRuMEo4cHRxZzlEeWtNdnlHaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46021.70194444444</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Hind Rectifiers Limited Stocks Attracting Dip Buyers - Healthcare Stock Analysis &amp; Explosive Profit Growth - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 03:37:50 GMT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNbHNDdGhmODFxaVAyZzh1RUNpSTNFNXpXbTNQejJqTElHa2x4czhTTHFkRWpXSUp1X00yd0N4dGZOTDhuWXZqdW9YTkpFVzBaZUgxUWlabUp0cG5tTTdNUmNMQVVyUVFFRU5YbUEzWUhwck9CWE5udHA1T1NSZjNZNW1mRjBQYnBoR0xvMDRNeTYwTFd6V3h2cXp1Sl9OSmIyTWs3cg?oc=5</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46022.15127314815</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fibonacci Retracement Aligns with Support in Thomas Scott (India) Limited - Volatility Index Analysis &amp; Explosive Capital Gains - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:02:13 GMT</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbzNXOEUzeHQzcTY1RURud2xid2FjZERsa0VDeEpMUFljRFVSQUlYUVpRWWd5bmdja0JJcUZxSm1PV0JhbnB3ZHg4U2IxOE5kcFkxelhhZHNfVnpnYkp4U1NJYkFId3V6d1pZaXA0VzhyR19qOFpLWm40eEZPNENzUDZQelE4LXBYd28yOVVlLUFHM0FEeGNmTkdUZEJ6UHJlLUtITXRIa1d0TUxD?oc=5</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46021.75153935186</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>High Level City searches  France  French language</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Is Bannari Amman Spinning Mills Ltd (532674) a Good Long Term Bet - Technical Breakout Signals &amp; Superior Trading Portfolio - bollywoodhelpline.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:29:18 GMT</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQN0xud3pkZGpyVk5DRkJzWHUzZWtlQ1BwczJyb3RoTjc3ZGVrNEswMDFid1g5UEpSNzhETU8xTng0bnJoVVkyTXBOZjRiSXRRblVtVkhGdjgxcThhcGs3b2YweFh5UlQ3SEFha1BXVE5zNzJJdF9fcEhtUUhfSHF4dndyMDVFdWlWOTNDbkM2ZnJYT2tQU050V2ZYZE85VE10V3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46021.72868055556</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>UL walk-on shooter playing key role in Cajuns' recent turnaround - The Advocate</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 20:00:58 GMT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQcnBYMXh2c0NIWEEzbi1BdGRmTHZianBXQ0Z2MndSWnY5T1A2dEdubFdvQW9YRnN2TWY3NXdrempyNlFSamptbXFDSDNVOVRSMHhueENsSVItTHhBVGZ1cHU0UmpFTlQxWXVSU25JWW9jczVwcmxMNzFvdGkwaU5vVDROYjdWMjFwVmwwZlRPVmFGVFl6Qm1YQktwLXBOSHZLUFhfRFhicng4cmc2VUwxR3N2Sy1HbmVGbkprc1pQWHM4NjQ3aHd5SnJ6eHFib2Ywak5TYjBlZTRKMTY5Nkx2SndNWHBpUWRxUWRPNVVmd01WYWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46021.83400462963</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Changing women’s hockey landscape continued in 2025, Canada’s Olympic prep altered - larongeNOW</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 19:38:01 GMT</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQjlsODJDSmZQdnZ1OEptdk5sbVlyWXVwcFFpeWNSWmhuWGJLMk95c3FoeGFVSEZmazFSTWl3NF9QTTAtUTJBdmt2V0FTdXdHbUE5TG9wTG5ZODQ3VW9CZVUzTzg1c1QtdFl3VUczdW9ma0xMeU9Hak8tWXFwenVzVm1VVzNFRTV0ZUItNENwdHl3YWFfNDhjUVJMMlAwUlBGeFhhZDhucnRFbk8zVHRmQV9keVo?oc=5</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46021.81806712963</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Iowa's Kirk Ferentz on the biggest challenge of facing QB Diego Pavia - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:23:36 GMT</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRUw3cTNWTHk2MXZLeE95YV8wVS1IRG9DeHp3UEJkSDZpZHBlVWg1bXE1eGxFa2pzT0R1VzBQMWpMM0FDdEJqaTVpeHNESTBkaUFVR0xPbC1LZWFSZ3hXakh1LUZPMnh1MEZmRUhGM3FmSE5JZzVsakFJcDc2ODRNaGlLSzB4cE1BVGZaNV9ZeDVjRTFwbGZmWDBtZkl1Mmo2VTFtM25reVMteFJQVC1pOXZGZGF0Xy1mdTdvMjBXWXM1ejlOV0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46021.76638888889</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>250 kilos of illegal fireworks were seized between Busto Arsizio and Castellanza: a 29-year-old man was charged. - lamilano.it</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 20:54:24 GMT</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPYjJkRldDYjNILU8yRS1iaEpWSHFkcmtBdUFZcnQ1TU1iWHIxUXZUMFhLeFp2azlXanZUMmhRdkUyandyY3BsV3FkSUFxYklzWVdaamlSWU8xNzI0R3gwalNpZnFjMlVkSFpseWI1UHZVUWR1Y2loNk1EV0k0a0l0SjNGelNuUWxFQ3gySEwzQzVKcUJTdWRpbjIwRlp5bDUwanRTZWNHTzllZ05xUGxhWTlaZE4yeENRZmVwa3g2T3U4NmZFenRoVHlscU1qNmpSR1ZnRDVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46021.87111111111</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Vanderbilt's Clark Lea emphasizes the offensive-line battle vs. Iowa - The Des Moines Register</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:25:50 GMT</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxQYnVnSi1aYnpTNU9Qb1JoRzRlSkc0emN4NW5PQ3FMZEdTbVFNRjRwUjdBSzdTd3lsbFBHTVh4YWl5bVQwVVpZeElTZm5IRlZMaEp2b1RCOXZ4U0syUWY3MjVVWE1vMlZ4OTVxZkpaNFRhd0dkNVhFLTFfSHktWEhnV2tUOGNyWW1QTGJ1TzlRaHF5d3ZwWHRrNzhZVEhpM0ltbDVBcXBhcmpON1Byanl2OXpkRDVHdGZpMjcxNFVpOFV0LXFsbmdpdWhjenBFQ0FGQWxyTTJZQnRfZ3kxTTM0ZDU4T2xYZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46021.76793981482</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>How to silence an inconvenient witness: The Kavački clan feared the statements of the person detained after the murder in Herceg Novi - vijesti.me</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:15:21 GMT</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOX2phVFdyV0ZRa1NiTWM3ZENlaGljM3kxOENzNVJTeC1VenRpRGVZd1Fqem9mOERIc1lLaU5vTDl3ZGtqVnVhOU5ydnBGVTZUR3ZCSWdXTnVoVEo5TEdzWjkxZTkzV0NpWlZZb3lIeGpWMlRrQ2VPZ0QtWWJoTWZhajQ3YUpqMUxXeUlnOXZmMEExZ3MxUGkxb2d2c0xOSk5FNUV3Q29qalNPTk40OTJQbFNVcjNfT1dlRVAtZkp5UF9xV1A3ZHBwTzluTlR2MHJaVGFWSFZMLWpiSWotOGVtaU41OWFidFc5Tll5Sll3QlVILU9raTdLeEU4a0dKMDNRNW42Zm5XYVXSAYgCQVVfeXFMTl9qYVRXcldGUWtTYk1jN2RDZWhpYzN5MThDczVSU3gtVXp0aURlWXdRanpvZjhESHNZS2lOb0w5d2RralZ1YTlOcnZwRlU2VEd2QklnV051aFRKOUxHc1o5MWU5M1dDaVpWWW95SHhqVjJUa0NlT2dELVliaE1mYWo0N2FKajFMV3lJZzl2ZjBBMWdzMVBpMW9ndnNMTkpORTVFd0NvampTT05ONDkyUGxTVXIzX09XZUVQLWZKeVBfcVdQN2RwcE85bk5UdjByWlRhVkhWTC1qYklqLThlbWlONTlhYnRXOU5ZeUpZd0JVSC1Pa2k3S3hFOGtHSjAzUTVuNmZuV2FV?oc=5</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46021.76065972223</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, English   language</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>("Milan" OR "Bologna") AND ("Bomb" OR "Bomb Threat" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive")</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Biathlon Team Names 3 to Thrilling 2026 Olympic Roster - Total Apex Sports</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:05:10 GMT</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE16a1dBTzRtS0hKN012ZnY4c3JqbXFHd0VIVGhSTG9lR3R3TUYydmpsYjVqRkdhYWt5VUhoWTdNNjVVQ3dSTV95QkZYZm5jOHhGSUJYLW92MHotbG9WSmkxbVMxMGRodlVKUEFjY3Z3ZFVYQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46021.62858796296</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>High Level City searches   Italy, Italian  language</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>("Milan"  OR "Bologna") AND ("Bomba" OR "esplosione" OR "sparatoria"  OR "Accoltellamento" OR "esplosivi" OR "pacco incustodito" OR "pacco sospetto" OR "minaccia bomba")</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Stock exchanges, 2025 record for Milan with banks and defence. The Ftse Mib ends the year at the top since January 2001 - Il Sole 24 ORE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 06:19:51 GMT</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPYV9SaGoxWmJwUTJYMUZJRGI4S1g5YlB2M2Z6Mk8yVG9RLXk2NkVvTjRCdzhFdzZFckY2czZrcUtlOFlkYll3Nktqd2tEaF8xeUZ6bFotMllaNGZpVmRYNGJoQWVSTFZYcWhlaEppaE1TWVhXbWxXYVk4UVVxQVNEeHRKYVZsU3o4U0dQektWWEZzaUpSby1J?oc=5</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46022.26378472222</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2025: Belgium's year in headlines - belganewsagency.eu</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 06:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5FdUVkUXBUV3VJQm1MRUpvcXRmVG1tbEkwZHdEYWxpVEpfM05hNl91SjV0a1c3V1ZuSFc4RTJqMGFGZ19SQzhIaDVUbEppSXR1RWpHRl9aQ2Z2R0RleXVoNjV5Ry1Qck1fUDllNi0tSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46022.27916666667</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dutch police arrest Syrian man suspected of being IS member and of planning attack - Global Banking | Finance</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 23:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE41ZktHOGxMS1FtNXE3aTQ4ZXU4ODNLYXg0OW91TWhoSnBaMGU5NTkxWXVpeFpoNl9MaFltS0xOUjdBSEZoLXpNbEtaVUVpNW1IRkZJTzB3RWJ4RGlTd0d1QVdFcUtQUkZLSWgxZkhsa3VHZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46021.99722222222</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Brussels activates regional crisis centre for New Year's Eve - belganewsagency.eu</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 08:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZjRQYWtfTHBwYlNORkh2aWxFWUw4WDRLX25heTNJSFRBcFctNWZpQ2RmV0ZYdjJWbndRaWc4aW1RZVQ1LWh1N1UzZV9PUWdXMW5NeGNwUmdraU5SX2lOMUxvcTd1RWkxQXNlVDk0WGdESVhuMUNUNnZ3UEM1LWJlMmc0YUFzTEtJSk1Gd3hpN3o3VnY3?oc=5</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46022.34444444445</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Polish farmers stage nationwide protest against EU’s planned Mercosur free trade deal - Notes From Poland</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 14:39:52 GMT</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxONUpNMTM5YW5yNlV5VnhSQ1p0MGlpckF6eVB5V0JWNmZ2QjIzT0I0XzJlR3pTeHV4QXFuUXQ2SzhsSExvR1pwR05RVUpINGlYRFN3V0dXV2h1Wld5T29kNlczOVZ3Wl9PcFhVaXdtS3hxSkNaTUFlYmhVOC1GVlBCN0hueG5xSjBGNjVJdDZJLUpsbVVoajB0MVVFMWRMb1I5cXpwdi04d3QyaVFWY19xRlViTF9sY2c5bzYyV3U4NE16dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46021.61101851852</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Disorder in Molenbeek after Morocco-Zambia football match - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 00:53:32 GMT</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOQXBEQ1hEYzk1RlB2RS1xYVpOV1BFTXBlR0JJQmlVc0NkendlbmdRcXFudmlieU5DWTcxTklJX25ncHZMenpWdV9uX0xZdlgwc21iQW1wLWZsVHhtck40RnpSaTN1VDh6M2ttUkYwemo3VWdCampGYnhVaExSZVd5NF9vR3lYNGJ3cWhZY3BIakIxemxGeTVTeVZyOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46022.03717592593</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>France’s president to skip Bardot’s funeral as Le Pen confirms attendance - South China Morning Post</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 20:12:44 GMT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPejBURGpROURJbmUyU1BXcHl3eGxwWGdVRmh1SktwU0JJYW9CM1FySENwWkREVXluejQ3ZzluUjZnVEpFZmpJQ3JZQ2tXQzlwTWpvU3Y4NHN4MURRdWp6cUZvaHgxenROUk54aEhFLVpWMU9MRFNjbzd4d2U5cm45a2JiVkZfVXo1c3Rob0dtSk5hRDlOcHoxUTJEcGpDZ2VlQkVpektvSTF2SEdnYUVSS1FrTjdaT0w2cGpjU3RoQndfalFLMTNvc0o0eHZQUdIBzgFBVV95cUxQT1VNUUZtSUNwQXNRUFhpamwxYVFhbkc2MjZScER2Q09uN0RxcUZCM21CVkxnT0JDYXpPRlpob1BSV0J2cnlFRXloODhxUXNKQ0R2TngzZU9lX1IyVGE1NGV4SFZJWkI0djVLcEF2RzQ2UF93RE51VklrZ3hVYk1aUWlMdlprQmRXeUQwZFhLZGh6bDFfRFVLWWNjdU9FQUpPR1J6d0ZSQjRNYW9heG5ITDlmVnM4U3hMU1FHVUMzYVAwSHZ4UnFob2xCdkpPdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46021.84217592593</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Anger over minister's stance on contracts - Irish Farmers Journal</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:37:07 GMT</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZGgtUU5RZkJzempPMzZEMFJaM2l0S245VU9tSkRnRHd4eWxfc0E1ZFZzaVpqOXlUai1CZVp6dGMtRlFkc19td0lWbm5Cb250ZkVnRXYxX0YzYTlYcE41T0dDMFUxYTRMdnFRRVJuaFhwMTdiY0oyZzFsN0h2U3hoWVRJc1pHRFo2TElCTDBZSlI?oc=5</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46021.94244212963</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Person hospitalized with hand injury in Toledo shooting - WTVG</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 00:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxObjdDUnpqWDdqY1ZESG1UdXhLRHE0NGtNeDZSNTRUZFVtWTI4MGIyRnk5Wm9RcGIyNVB0amZmRGFXTVVRNVA5NW1wUWxNUWxRSlBzOHFJVWtPdHFRLUV3ajZLYThoc0JrZGRBVlpfXzhFeE5VeFJzUzBFbnBYZWtrTlZKVkt1LUlabkdmdHgzcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46022.01180555556</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Gerald Lee Wolf Obituary December 30, 2025 - Dooley Funeral Home</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:14:06 GMT</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1EcG4yYXNfWTFEZmxQVDZURmx4Z3lCbUpzNzBUTnp5OTBNanlXcGExbWMwSW1GdHpMYTJuWEl1Y0c0ajBPMUFZTWFkRTducDRSOEpOX2EwZzQtMzZ3NlJLNks4aHJvWms?oc=5</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46021.718125</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>What will joining the Eurozone mean for the Bulgarian economy? - MSN</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 06:24:20 GMT</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNU21yLXdrMTB5V2E1RTB0LWVwMTN2MEl1dVpCN2RuNjZVc09XdDd4aVBEbEtvVUx6cTNweEdqaDRYZmZCUm02N3JGb2J3VzVEZnluOWJkYzRTbDg5aFhJXy0wRnJ5SDBjdVVrR2tmT05YN2l5TEJuRmdYUnpIWk44cXpYX2EwT0c2ZHd2WEI0d2JTR1dtblNDenNSWWxINm5lTDJsdmc3eFhGcVQ0eEU0WmNTZjJPd00?oc=5</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46022.26689814815</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Luxembourg station to undergo €138m transformation - Luxembourg Times</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQUXNQTU1RRkpNc2dyOXAxNndnYzlCV3BpY0hEYUM2Y1QzV1FoOTdiVkRHUHFlOC1XbGtETGV0TW12Z0VOSVVyWndkSDFhdnlNM1VmdU14b3I1UW5udnNSX2dTbHhwRDhrYUZpNWU3TTVDQjdWNUNGdmJsSG1PR2xLMHFOUkdzaHktUVFZRzlMT1phYUtZM1RmWjNZTE10aXo1?oc=5</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46021.64583333334</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Man arrested for taking his 87-year-old mother hostage - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 00:53:31 GMT</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPdTMwLUJFdmFvY1AxVllWVFY3c2hXYWF0ZnNQSzNEUnhqNEZMUzN4aG1TZ3lIcjRoVWszU3d6U1p5YnFndWtOQlNhTDBhUVZrckxERWtJZlRuT1lLRGFRVUlEZUZFXzBDd0tqZTVPOERHRTFUUTJuLTJSV0JBaklJVjcwUHdua1lBVnBNcVBuaEhBdEdtQzNoNTlBMWNneVVHYjZfWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46022.03716435185</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Young man found dead in Namur was leader of French far-right group - The Brussels Times</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:38:46 GMT</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQXgySFhwS3FGN21OVm1sMWR3MGNtcjVkazBob0hKRkpubGdqZXlhZ3JRTzJncng0TFVQZXVvbXBDd0czSkNUTmFtbTRkTjR1ZU9YM3ZGd1AtcklhMjVhZ2d6LTVHTnZZQnFqWmVQSnZ4UC1RcGtPNTB1cHZTa0paNWlnZnVWNWJxYW1nLUFYYXJJU0VWMFpjbUtrZGNYQmptMTRnUFpfbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46021.94358796296</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>High Level City searches   Belgium Dutch language</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>("Brussels" OR "Maastricht" OR "Antwerp") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR riot)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>🚨 EUROPE’S SECURITY ORDER IS COLLAPSING UNDER GEOPOLITICAL PRESSURE A truth bomb that should shake Brussels, Berlin, and beyond: Europe’s entire post-WWII security framework is unraveling… and fast. Here’s the uncomfortable reality no - x.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE5OejNtUVZENzZhWVNQdDJ6aU5QTlI4NzVYSzltSVg0cTZLZEhQVVdFQmhQTENNeXY3ZGhxdmw2cm5ZeXJrVk9jeXJ1RUlnX2RZa2Y0dzdDNDlTUGhMTHluUG9n?oc=5</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46021.625</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Local Town Searches Wertheim German Terms</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Indo Sport podcast: A Closer Lookback | The Stabbing of Monica Seles - The Irish Independent</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 14:29:40 GMT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPamV1YmpwcFFDdlcyMXMtY0pybTJtUFpkcWwxTXJFYTlQZXhtQlA0dUZrenkxbUE5RThkOER0dWRIYWhSQ01VXzBIbnVvcjE1QzVCSS1WaG1FcXNLa1U4VTFsNmNuVXRieVJNaDQ5MVNiSTVNbkZvQnR4dXd2YXNhRVBRM25QcjVvaW5GNk1wNGNHSWwwcVV1X043M0tieE1uMVp0M0ZaaUZ1V0hpU0R4dEExS1UwNWZiS3JQeFlEdGJjMGNJSnJ1LUtsU1J4SHo5?oc=5</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46021.60393518519</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Local Town Searches Wertheim German Terms</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "Wurzburg" OR "Aschaffenburg") AND (bomb OR explosion OR shooting OR stabbing OR police OR evacuation OR "suspicious package" OR "unattended package" OR protest OR boycott)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Germany bank heist nets €30M in cash, valuables - The Express Tribune</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 02:12:46 GMT</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNNzRsS0I3X0ZQODlycE1uek02OUlUNjZRRmZNSkdvTmoyeGNSaVpTQmlRc3JjMGduZ1FxOGxOeGl3YzRNdklaRDBWSnUzU2RBam1saVdpTDhwdE9uel8taXhFdUtkWU5Jek01aDZxQVA2WHo2S01wMC1VYlM0eFRSaTdDWnRVSTBBaFHSAZIBQVVfeXFMTXVzYWFEMDAyUS1nbnVFOHVXNE4tM2VoM0d0SDJHdlJTczJrSTlQalVBclNGeE1NN2NiRnFwUDF1VXFtOThCZ0tFX2ozRzJ6R1ZCT2FGN2xyLVVaMXlLNXFWZ0pna3Z2RzFaa0FlZ2NoNFpsdExhREtKd1FJQkdhaEhGYWtIUFctcHZIYmRPUVFSWEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46022.09219907408</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>Ireland / Kildare Protest Groups - Social Media</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Trimble warned that review of Assembly must include decommissioning - kildare-nationalist.ie</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Tue, 30 Dec 2025 08:36:26 GMT</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNM216Y2JyRXI3RV9MQ1k2ZE9uRThpbGxQVFU4TWpkLVdLTTVmVXVpSERIalVGTmNQS0JiQ1lRem40djAwYzlSXzF3NVFHRVRLeC1LQWxXU3JIdVVYSll4andhOENOMmpHeE84LWxSUFpkSFZnM0lhWDNWMEZmVlNfd0lscUx3QlBVRXM4c05VRDB2WHZ3bFp3ZUZpTnZJd3lFc3lJY2Z5X1BvOTR5UHVMbFR6QXphZ3Rkc2dnV0tVSWk?oc=5</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>46021.35863425926</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Offaly: Appeal for information on getaway car in murder investigation - BBC</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:10:05 GMT</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE53NDI0ODdPOVl4RUdxWWJWV0czU05UNG9nc0NGR0I4V2R6U3JUT3RQeGlEMGdOdUZOcTRTTzVLNEVESUlWb0d0aXJHQ1l1S0Vfel9manlnUFIzQWN60gFiQVVfeXFMTUducDVWMEYzMzM3MEV6NVNmTDBXZzNGaGNXQTJfR21BNmwxdHF6RFVCTTFFZmdEY0FVbUUyb1dUbW5STzA0VDAxZ3BhUzIwNlI4S1BBcFF4ZlFxcU5rYVpic1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46021.75700231481</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Man, 40s, killed in horrific crash in Kildare as gardai confirm busy road closed - The Irish Sun</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:04:10 GMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNdnVMMmRaOTJ4NndoNW1mQk82SXBxMWFRME16SjN0NUlUYWZYNEJqM1Bya3NJRjI3M2lZbGdYX1ZnUVFhRjVCLVdIMEZablBnTTZqWDA3SDQ1VUdhdHpsMWpBOHYxNFB5dUR3angyREtsdlpJQWZpT2ZwdzNXS0ZKU29YUWRpd3JaZlVz?oc=5</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46021.91956018518</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Man may require facial reconstructive surgery following assault in Omagh - kildare-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:34:52 GMT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNHBCVkJ0ZHdTbWhxOVR1bDhtVW0wbGJSMGZmT1NfeFRsM2VCNDd4cVhKVHBHQUZyNWlOUnFKVC0tbm01TjhUWVVMaWJ1SFJGODhzS0pyci1sQVlzV2VteW8zdDZCSFh1NTBwZ0Z3VWNBSE84VDl5TzNJelNfMFNvaS10U0F0V2dudjU4VFhkbGtWY1BBZE1ybEJyS3N6T3BBRlFoVzJRWnBDdkU2QzlsZDhqYXJ4dGdBeF9VVnhoSTE?oc=5</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46021.64921296296</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Protesters make feelings known at Abbeyleix hunt - laois-nationalist.ie</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:12:47 GMT</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQVmQ4NVBvcVBnSTFFb2dvbTFWUGUtUzZGQ0tJRUp1dVAxWUlEaXhESnVtUnBGdEZlUkJsRTB6b2VYcEFyTTBMc2h6TG1JM2NnaWhBdzJ3NnR4Sy1lX00tTUZNYkhxcjdQaFhkRWw0bTY2T0xZZmtjMWptSHcwd0l1MVFBam9RWTRjeXJPczVGU2RMdjFmLXNucm1pWmkzWWd1ellqVA?oc=5</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46021.75887731482</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Wales breaking news plus weather and traffic updates (Tuesday, December 30) - Wales Online</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:52:30 GMT</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQMjZGMXRpeTlPbHVuM2xiZVEzSnh4QXlXVUpMbmZScmRKRDNURlVySFlwQlZleWs1NGU1MEVFRGtXTHV6QXNycFZaVGpiMS14TW03aEctbElZNFVIcVE1ZFVPTnR4MTRRSGpPWlNSVng4RFJrVjhDWElqYTEyTGc0NFJVSjlKTnFtQU0zUHREYUHSAZYBQVVfeXFMT3hsRWpVZTJTbVR5amptWXhJWDh3eDdwVDhJc254VzZZMTdqMHJ5Qy1lTUNrUXpVSklTZjJxRTR5dTlua1ZIQTdYeHZpVzFPenJLeFAzLVpyT1Jrb1g2SzREaHJacnlRZjVWRDJReGVVaHZjM1NndmNLdWhzU0JCUEpVYkVwX3FsVnFGT2hPdng5Nnc5cXd3?oc=5</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46021.703125</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Five injured after alleged crowbar attack at community hospital - Irish Mirror</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:37:09 GMT</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNM3dLOTk1MC1FNEJkUlBCcy1NVExWekJmbTFwRGx2NWQ3c1VVamozVFJsSlJUWnB0dDZ1a1MzMDhURVVMZ254ZXJoaEFidzNva0U4TWtsbUdKd0p4cjQyd0xub3o2YUNxb202Zm1Gd2hkYV9RNlVlaHhTUXFsSG9TcVVESkVCemxLSm1nSmFIa9IBlAFBVV95cUxNOVVkSXlCNXpoMkptUVlOT2lZeWozWlE3TFVaRjFnYVJ6V3JGTlFidWlDUnBXMEl0YkhYOW1rUUNnaDNaY29fcXRnbkU2MkItVzJ4WUZtRHpOTGd0c3gwQWdzU1dKbWVXMVZwdFQtbmZLSUZiX0NLVk9sWV8zUzhueG9HMy0wM3lIOWxmcWl6RUZfazcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46021.65079861111</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Ireland / Kildare Protest Groups - Social Media</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>("Kildare" OR "Newbridge" OR "Celbridge") AND (protest OR demonstration OR activist OR police OR disruption)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Thousands caught speeding including motorist detected at 207km/hr - Leinster Leader</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:38:12 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNN0ZXbzJLakk3R3h0c3pHTEZuRi0weFBoZGRmNGtVbUlkaU00bHVNbC1yTUsxY1dXdkVUSGx2aktpaG9FX01wdTJnUk1tMHZQLXlCbmdjN1JtTFF4UmFhLVVyYU9adVd0ZXUwZlotWTdTR2xrUlVxem1MVTZDQzg1QmFMT1J0UVI4UFhfa0JfQmFQNmdMOUZ5bjY4THR6aUtRNG9keWV3YTN0dGxHaEJZczlCUTRlMTQyQkNzZGlUTTVxSFN1c3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46021.65152777778</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Local Town Searches Ingolstadt German Terms</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>("Ingolstadt") AND (protest OR strike OR boycott OR police OR evacuation OR bomb OR "bomb threat" OR explosion OR stabbing OR shooting OR "suspicious package" OR "unattended package")</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MP News: National Games 2025, A Year Of Silver Lining - Free Press Journal</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 02:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQWkFaUFRIVG9SQXdZclh0bDRLRVFfTk81eFVRUDNVVDNZVGE3ZWdCeThoZTdoNmgwdmU4V2VRdzFwSzZBVW5tallsUVNHQjNzTUFYLWJ4TnE4ZHRvY29qYUZPQ3Y5UGJaUVVOSUQxTlZLVUE3OWxqMnZzWXRlOENzQ2otcFZWTFB3U2ZYUnd4aEg1SjZ40gGaAUFVX3lxTE5qT0ROUTlxVkd5MTNSUE5DZVVRSVFIMlhxWWZUMW8wM19HZk52d1oyb1JjUDF2NlFxZXlhU0RfNGUtWlZ2cmF1Wk04X1E3bjhrckxfVEhfQ3AwNzhPTnEwOEd1NGJRQ3ZyT2xmY0ZwSUxOejRaeHBrYjJyRGN5SEFybHJCXzZYcnBWVWwzUTY1eWI1LUgtN2c4V2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46022.08333333334</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_deduped.xlsx
+++ b/data/latest_deduped.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Louis Vuitton Flagship in Beijing Designed by Jun Aoki - parametric-architecture.com</t>
+          <t>Gucci car, anyone? Autocar's 'alternative' predictions for 2026 - Autocar</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 11:29:38 GMT</t>
+          <t>Thu, 01 Jan 2026 05:12:58 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE4wWEtISl9hS3BhbXc0VEhMM2pjX00zLV9oMVRRUVFJM2lEeXBFT1h3RkdTM20wLU5iNWJoY0VqMjBDdDRUVXV0VDk3blhnMzZIbzdTZlprTUpMOFdEM0lWbElJR1A1aDYtaG5HNXhHMjd3akZJbFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOU0JwVzVwR0lFQTRpVEJWdFdZUjhMNTlRWHMya21LVEZzSWxGS2FDQ3NKaVZwbHhfZENhZlA0clFlZmdfclRhb3pjeWJ1VlVyNWVpVFdMRGdBU0lWOTJadnZoTzYyNzRmcXZmYi1EY3Z0MXJIbjFTZHpkUlpUalZ3eDhJOTJBVkczX05UMmdGNGhpbTROT210RmhvaE9ldGc?oc=5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46022.47891203704</v>
+        <v>46023.21733796296</v>
       </c>
     </row>
     <row r="3">
@@ -515,24 +515,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>This Louis Vuitton Bag Is Cosigned By Kendall Jenner &amp; Serena van der Woodsen - Bustle</t>
+          <t>How Marc Marquez’s route to seven MotoGP world championships compares with Valentino Rossi - motogpnews.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 13:01:25 GMT</t>
+          <t>Wed, 31 Dec 2025 17:00:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBNOFJha0pvSmF0SWRyZ1hjT0VHOVV5WUVQN0FRU29IanQxcVQ1ejBzREctRmM0eHNMOEY3UnVvX3oyWEctSUhjdXQ0YldmYlV3aE5sX2d6RXI1MlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbV9oR3pGelNzMlMwNGM1UjNDaFNQTnkwc2Myd0ZYZHZETUxpb1JzT21CUlBPSEdDN3RVQm1Hem9DU09PTGN5NW5LYlNsM0tYdV81OTZwMkF4aFl1TnZNajVMejV0c2s0QkxHckVZbUZBNXJRdzRCaWxxUklvbVhBWExJN3VQeWJNdDdXT0twc0x3bWh4U3prb2N2NTRmTUhxX0ZyRHNPcnpsTmN2a3NMbGpzdUV3SkNGM1hzWXM1c29sR0ZITUhB?oc=5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46022.54265046296</v>
+        <v>46022.70833333334</v>
       </c>
     </row>
     <row r="4">
@@ -548,24 +548,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Polo Ralph Lauren And New Era Team Up For Limited-Edition MLB Caps - maxim.com</t>
+          <t>Long Before It Was a Trend, James Brolin’s ’70s Living Room Was Already Doing the Ralph Lauren Look - Homes and Gardens</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:05:00 GMT</t>
+          <t>Thu, 01 Jan 2026 07:00:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTEswbEloaUh1bWo3NzJJYm01R1NCUzk3MmF6SXY1M1NsS3Z6TnBwcG5BekU5MFFEaF8xMGlqQWVuX1BXdkNzUkxOLXBHVGEySXBHY1hneUozamRtZ0xVUVdZLXNlbEpzZW5HS1ZjWXV2cUYtLWsxNHluYzNpRy16SHJwemp2SDlLdXVSM29BeV9VOTdwVlpGY1dVYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQnhTejhKQWIwcmJMVDdmdzV0blVKMGsyZHYyUmY2RWVtN0cycmRkY3FQc2NGd3pLR3hxT0hoOWtUWG1ZdmlUZS00N1BfcU1MVlFJRExFbnQyczN6a2c3WFJfVDltQWVtNkxaNS1XN1lsZmowZVllbDFOUWNSMFFBVVNNbUIwb2lXSmpLLU5OTGlJVV9jNFl1R2RubzM3Q3FfU3VneXBvWQ?oc=5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46022.42013888889</v>
+        <v>46023.29166666666</v>
       </c>
     </row>
     <row r="5">
@@ -581,1641 +581,3390 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Louis Vuitton marks 130 years of the Monogram with a year-long celebration - Harper's Bazaar Australia</t>
+          <t>New Year, New Looks for Lady Dior Bag - L'Officiel Singapore</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:00:48 GMT</t>
+          <t>Thu, 01 Jan 2026 05:57:10 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZGRfdUIzRHFQampDTDF6Y2hCQUwzaVQ3WW5xb3dLV3dSMDhjb2ZqWU1nMGhod3ZkMUh4elhBejJVYUxSNGVmaE5lUjc5SDZlejVXem1wT3JoQ1U4RTRkaGU4bjhaUHdIUjU1MnZhbzJVczNUYUhnS1dzY0lXb3RQNWpOUi1lVlJzTGtSVUNySWxjWEd6NmwzSTViOTZBaFdpeEFGZk9XYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOE5oQ1FBaFpyTjVYeFNPU3ptN0dNY3l0VHhTN0FoNXVpTTdzTjFPanNtdFIxYUtIeVctcl9rVWFUS0hlQ3VrV01mNktuT0dva0hhOVJtY1pUZTI2VXlDd0cycGIxZFJfWW5TZHJyVXVzOExBZWMyVTAyNWRCeXBCNmRWb040UQ?oc=5</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46022.41722222222</v>
+        <v>46023.24803240741</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sacked Royal Mail workers fairly dismissed, tribunal rules - Kent Online</t>
+          <t>Why the Louis Vuitton Monogram is still the most powerful symbol in fashion - Her World Singapore</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 12:05:00 GMT</t>
+          <t>Thu, 01 Jan 2026 01:02:45 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWGJRNzNDWnVrd1Y4ai1KRE5oU19Hak9YTHFhUHVkREE4THo1YmxrZEZ2YmdXUjAySGJybVcwZWVub3J1Rm1UdW9WWW5JcmdpdHB1MjlWaks3ODgxVnNlem9TQXk2SlhRVE1nTDRtcnpHb1VtLVN5QndoeHBUMS14bVlOR0JERkhGU3QyTHRYRWlDNk4zel8wcEVNS1kyTExXN3lTUl9DcV85dC1QRkhV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOcGhkTGJQcXRLSURlWFM0ZGFkWmh2NzRYZzRhR0FIOFFCWU45ckJ1d0xDRVdPaVhuaE5zaGlQSGp0RWlwNFJOcXlyUTIxVEVDRE1oOGFJLVhEYlRnb2lPWTZxemFoWHdlV05wM2txODRZYzVKRGVKX3ZkX0gzZWJIRTZTVnRnMDM2WkpScks5QU5OaXZlV3dV?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46022.50347222222</v>
+        <v>46023.04357638889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amazon abandons drone delivery plans in Italy - Maaal</t>
+          <t>Ralph Lauren (RL) Registers a Bigger Fall Than the Market: Important Facts to Note - Yahoo Finance</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:59:15 GMT</t>
+          <t>Wed, 31 Dec 2025 23:15:06 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBIMGdCeU9kbFpPeVRXOXpGWmt0TWlEQWFHR0pDT19lMWZRSkY2eEc2eVd5c1dhQWxBZ19iTGd0ajdOV3dQd0xJT3VvVVhsQk14cGN1N3dSVzVOM09zdkVRNHJBWURjVGlEa01qZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOVTBVSHZzQ0c5c0ExRmZsSjhLdHVGOHhLaE8xdFdxbEFPb0ZwZk5OVzlDakJPejZmOWV2TzBELVlIcGtzYnVRVXE5VDhRMFlfbVVuc1J0TUF1Mkt0MjQxNWxlbHhYMWJqel9ESTdNMHI1cERGQ3NyV3JSWVQzcDRzLTN2bDI?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46022.4578125</v>
+        <v>46022.96881944445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>‘Withdraw 10-Minute Delivery’: Swiggy, Zomato, Amazon Delivery Staff Go on Nationwide Strike; 5 Key Demands Ex - Times Now</t>
+          <t>The Luxury Alpine Looks Shaping Winter Style This Season - a+ Singapore</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 08:31:11 GMT</t>
+          <t>Thu, 01 Jan 2026 01:00:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxOeC02QkhpNjhYNDF4REdsanQxUTgxU1F4QVJHV2RtS1Zld2c2dU1lX1k0d3dXRHVvRm0xUVhKdXlGYmFsZ01DcGF1dE1nYXU1Y3lUY3JtdFh2QjZBWlJpSlhvZVFmZ3pVY3lIUWJuYTUtU2JFenBlOWtZc3lObGphZkduNFZMZ1h5WFliLWFJU2NsWG8zTmNWcUg4MjdjcUFibHlwdWlLNGdKeEJwNE94dmpsRlF1R21tbzczUUg5MnlnZnJ0aDVwcjNyLVU1UVgydk9ydU1wMF9XZTRPZExucTJaN1h6cWtXXzAwcmlEYWY1aUNsNHZrU0JYTjUzTkxacWdhS1pBXzRMWlU1TUFkelF30gGXAkFVX3lxTFA2Tjh6VVFrNGtTUE92SzdCMWFTZjQxQ3pRNjlOUk9IYjNCUWFyLUJVZXJMTHdFRENJOXdfckZnZUdUQ0pxdmk3eDdLWWZYX3hOSUJ2LUZmdFpabWRfcWZDVlhSaWFIMVhPZnNLeHRQX3NjVnhiX01JN0lRMUl0alhrVVprdWFXd01ZLVlhS0h1OHV5bmlDdXd0dUNrZDBfUU43d0UtMDN0T0ljUWhnUTNySEJCTTk4YWJWQlpKbWlTcTBZSVkxVnlxNlphQ2ZWSXp1VG9TeFhTREZaMEFzekZ6YlR2Zk5GX2h0RXJGUGo2cGpyamhURGlFbUk2bWFLX0oyRkw4Q2hhcFlCR0cyQWJlWjltYzB0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBLSWxCR0hHWllPQkpGQ2tMNzNBbW1ZV2NoRVVoelNGQ1pjN3p3d005dzNIV3YyNE9vTXU2OXhCZHNlbnpFdU5aa0VDc3gzRlR5OHJ6Z3p4TDlzbmFsd285cU9OeDlvNEc0YnUxRzd4MkxVbVpDa1JzLXdzYw?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46022.35498842593</v>
+        <v>46023.04166666666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amazon delivery driver strikes up chat with customer’s cat with hilarious moment captured on Ring doorbell - What's The Jam</t>
+          <t>Inside Katy Perry's love affair with scent and Dolce &amp; Gabbana's latest perfume - NZ Herald</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 11:26:25 GMT</t>
+          <t>Thu, 01 Jan 2026 06:38:28 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOUkFtSGl2RExaSUFLRGwwRUNySzZJcHlHYjE4LS1SaGdpdml0MmF5YzFaQUNONmx4VGx2RXAwcm1CaFN3VTZwSDBoODdyM3hHVXBFRTNsV0NqTlhNWGs5bS1KLWZUMHJHdTllN1dsdUpxYTlONjUzMmQ4b29rS1NBMW1RYzZtTnE0T1ZwTHVZY1V3QS1DNTI0RVR2d1d1MV9WTl9nS3J4enZlS3F3ZjhDdDZDRktCUTJuQkVremZBdzRsVHVjbmZsMWdXZXhlSk5yUWJHSTM0R083MU5mZE5BcNIB4AFBVV95cUxOUkFtSGl2RExaSUFLRGwwRUNySzZJcHlHYjE4LS1SaGdpdml0MmF5YzFaQUNONmx4VGx2RXAwcm1CaFN3VTZwSDBoODdyM3hHVXBFRTNsV0NqTlhNWGs5bS1KLWZUMHJHdTllN1dsdUpxYTlONjUzMmQ4b29rS1NBMW1RYzZtTnE0T1ZwTHVZY1V3QS1DNTI0RVR2d1d1MV9WTl9nS3J4enZlS3F3ZjhDdDZDRktCUTJuQkVremZBdzRsVHVjbmZsMWdXZXhlSk5yUWJHSTM0R083MU5mZE5BcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNNnp5bUJxZC10dmNTVnJadnBpbXg2ell1Sm5maGZrdGNHdjRRQlRtLW5xMnUxRWlseERDZXRfY3pTN21nWVpyN3JyM0lOM3gzTHdsNzdHbVpadkpDamtvcl9HZjhkMF9jSU55ZmFnalJMUm95RExnQ2xoRFo4MkdJdFZtUF9JUzVndjJRb29IeTJldV9LTk92VVNmNHo4RmQzN2pPV0VoNzZPc0otNnRQb0pOOFR4S3JvVnBTUlBEVWhQNW1QRHdrS1ZzN0xtQ2U0dFBENUtXcw?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46022.47667824074</v>
+        <v>46023.27671296296</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Level City searches   Germany, English Terms</t>
+          <t>Brand search Google News and X - PROTEST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "louis Vuitton" OR "Valentino" OR "Burberry" OR "dolce &amp; gabbana" OR "Polo Ralph Lauren" OR "Cartier" OR "Calvin Klein"  OR "Hilfiger" OR "Tommy H" OR "Timberland" OR "Prada" OR "Nike" OR "Balenciaga" OR "Canada Goose" ) AND ("protest")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany news: Fireworks back on sale, reignite ban debate - DW</t>
+          <t>Louis Vuitton Climbs Ladders and Jumps Snakes - AugustMan Singapore</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 08:48:44 GMT</t>
+          <t>Thu, 01 Jan 2026 06:22:30 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcGtCbWpKdWRXck0yMFRTbS11andPNHMtN21VeTYzeXUxVllrNVJPYlNRbFlOajdqS2hMMWNrZlFJbDNfRV8wUlF6bGVJWUd5dHZNOU5EeGY2OHBFdEpvbzd1YzFYSThYMTNyVlEyaVFuem55Mkxyd2RiWldEQkpvTGl6b1RFUXctQ0VRQlcwcWhmYi1KMXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPNThVTlhKSXdOWmVKOE11LXplMnBNbnI1cm5BUE1lNDk5M2dwUVJTNzJ1a25jMkdsamdZbGFCVmVoWkNUMF8taXVIbHdLc0pRNUxnM0JJNmt3Uk1UWWVid3JoRV95c01sQkgyR1ZKdVd5U0M0NjlVblVtRUlOMGY4VVpYSGdVLW1xYWhF0gGQAUFVX3lxTFBxSmRhSDFPUXdBZmdaem1ZeFJOdnlyaGtBNm1hMVZrQ3NLZ0tyd1JoOG9EZkdEWnFlWTVpLVpFSE9aeGptZE9VSjhGSG8wVW56cDViY21EdmFhYkltV0RXWjBQVFBEeDd4OHFtQzgySGFxVngyMEtQNzhPVFB5WWhJcE1MV00tWEdDd1o4M01YOA?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46022.36717592592</v>
+        <v>46023.265625</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XR and JSO Broad search</t>
+          <t>Cotswold Designer Outlet</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>"Extinction Rebellion"</t>
+          <t>("Cotswold Designer Outlet")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Activists plan new protest against Reform’s bid to scrap council’s net zero targets - Lynn News</t>
+          <t>The Cotswold hot tub cottage that makes for a dreamy January retreat - Birmingham Live</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 14:16:00 GMT</t>
+          <t>Thu, 01 Jan 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNWmFYSFhDV0x6ZVNxRWI1czkyOEMzWnVvZjlJVzJxWXRQNkdOdTVvS2x3Qko1elhiZS1vaDRybWd5c3NhdnRXWUN6Sm53RzMtTjlxczVuQXBIRElPdVNROGNWNnlHNlpkbW80YU9vdnFMWGtHeVQyTVVlcDUzX3dFN0ZjRi1VbnFFT1k5amt2V3IwV0N5VGQ5SERPejJpSGNRUXBJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOd2hid0k1TDZLblJnaUVLR3R5Zkg3TkUtQjg4a1ZPaldlUDFPU0xmWU44VmkxVHdYQ1RkSHJKNjlBd0swc3ExQ3R4ZU55WmF2czlBcnpoaEtzc1BqUWRsN19xNVFXa0pyaUFSZVM3YzZHSnUzSGhQSUI4MFFBZktKelI3c2NULXZPVHBnU1dRZjJTRl9oM0VaY2gxekI0RGPSAaQBQVVfeXFMTS0tU2w4QTFuYWtqaXRzNlJwUmhpaUZ2NEFHX2F5b190cGtmUWM4WHdVRlR4aXFJS2Y4SjhYTmJSTVNxUHR0dHR1ejRySzF2TDhkeHFQc1BnRkhaZ2M5RDREVTNORGFFZnRJZHJ3ZHhzU1BaQzRnbXpXSUJkbGdTN2FUeE1fXzhkSU1HZEI5WThTVXN0cFRTdFphTVRDcjhTWGF5ZGM?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46022.59444444445</v>
+        <v>46023.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prolific Worthing shoplifter sentenced over latest offences - Sussex Police</t>
+          <t>Explained: How Amazon Trained Consumers to Expect Everything Instantly, Rewiring Patience - Storyboard18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:48:00 GMT</t>
+          <t>Thu, 01 Jan 2026 06:26:29 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNU29zQ1VNN1I0REUwMUNBN0FOT09vQ2lNdm9ieDlrcDVWa2JsUGx6SFI1Y0g5MHFUQ2hBMTZwMnJIWDFJcXdmeXg1T1JDZS1reVNld3VSa1U5REhydGV3bHY3SmJ4VHh6OHBlcXpoeU1WQjlOSDBydmJrLTQ3VDQ5T3lWNjNaYkdNRERRX2Z2N3pnV1pxRkppdm9NR2U4TFBUZjF1U003ajR6aXg0RlM4RXRac3JsRUJhdm8zWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPOXRwbGZlNEl4T0RnNmZ6RTJOVHNSTWQwM0xLVWN6SXRwQkxydFJKOVV6djVBWFBiUkNJQUVvSFlxUGNGZ2hBLXBlZTVJVXhtNnA2clRsZk11Q0tZblBFOHBEd050V0ZBZ3drRmhrelZ1OGo1WkFuTU10YjMyR0tnMEtyUVlfclBDc2MxT0tKVTFsaU1Bd080c3FPTzJwcFRvcFlQd0YxREVPMGJhZjBvTHMwT1VXVGZ2Z1g3cGEtOTF0Z2JQWm5LMVl3clhORl83Ql82clB30gHbAUFVX3lxTE9XUktPaW9lRWswVTFQWDZFZTB5X05WVEM4OFpPRHVmVHRzc3NrLVNUa0tBZ1BDTlhoYkpHbHdIckl2UkZncFdSeVZab3BGLTF4YjZaV0JHRDd4MS1fQll5NFZSXzVhbnJ1SmtmUldqS3liZk1aSnhvRVo5blgtdHlkQ2RGYzdkQ3VxY1Y0RzFya0o5ZlU5Y3EtU0ZtdnZiclRQM1l0YU81N1RLdWU5OUFxT3BjbE56cVpWRmJRcFBieFJtRVhLQV85dng5a3F0Z0FKdGJQb0hxZHZlNA?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46022.45</v>
+        <v>46023.2683912037</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A 61-year-old woman has been banned from Broadmead following repeat shoplifting - BristolWorld</t>
+          <t>Here's how to quickly tell if your Amazon order will arrive by Christmas - AOL.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 12:59:00 GMT</t>
+          <t>Thu, 01 Jan 2026 02:46:56 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNci1wZTJOaXhfS01lVDZwbDhpOTQ4UXVScVRiU1AxUWJRenhaY1VUaVdoZnp3MGhONXp4Xy00Rjg3enRNLVVCN0VIOUhFNEdzRF9ST2ZKM19ZTTNrOTlqaEFTZG1aWFJ5dHI3ak5LYzR5SngzRE01VDNObmtXaVMxdWpTWmNOM21KQ0ZqTkRDVDVOUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOVFZNYXZDbmZpaWljejRYMGJ0MFBhck51SmNKWTVqSDE1X2RLSmtOazN1cVg4YTJ1VkppdFQ5TFp1ckl4TERTbTRaOFlOLW5TMk04YTBSSWZ6YS14X3dVUVdNQ3RCVmZmTG91ampocW84NzdtcUdQbDh4XzBMSDZXVVo1QTRuelFMeGNOajBQNlotWDE3ZWwwUWxxN2RoUy1SWk1Qc0V5dGVuVFdlT2UyajZ6Zklaa0VQbmpLTU1vYXRpNGRpWGpmR3h5cw?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46022.54097222222</v>
+        <v>46023.11592592593</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>On patrol with Carlisle’s volunteer helping shops fight crime - in-Cumbria</t>
+          <t>Winklevoss-Backed Cypherpunk Ups ZEC Stake to 1.7% of Supply After $29M Purchase - NFTgators</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:36:31 GMT</t>
+          <t>Wed, 31 Dec 2025 16:50:55 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQRlRiUFFSeUNndVB0OFlnVWZLN1VLanRLMU5zWEF4andnUll5NFpRRHZybk1lbTA4V003N2hzeHhpR2d0bHo2YVNWU0ttMlpvdnljMVVkb0NrU3FwTHkxZHBpX2VzNXZuNmJiTkY2V2Fxdi1uXzRNa0M4RnM1YlE4Sms3MTl2MmR5S2NOalhmLWRsNGotRWFiTXdpdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQY3JOQUR4VXZTQm9NcS1maG1QdzVYNWpoUVd3NzlscVFWa0hLRWdoVHBtUDl1N2hWZW82OG43WEhQNHh4bEJXMXlQRS1TdnNmZEpFVTFmMmQzUk5IaFRTaEZROWQ4b0xrd0tYOWx0WGk1TmJVeGZkb1IyeGhDSmxxOWhTZzEyd0taTGJkTEFWU09YaEdEUWprRV95dVVYV0FoUTFDT1pBZWU?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46022.44202546297</v>
+        <v>46022.70202546296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shoplifting UK</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State AGs Launch Holiday Warning Blitz as Gift Card Scams Surge Nationwide - MyChesCo</t>
+          <t>Amazon Has Big Changes Planned For 2026 - Here's What To Look For - bgr.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:00:00 GMT</t>
+          <t>Wed, 31 Dec 2025 21:17:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY283LXphREpYUlBCM2dTZzRjT3U1Rl81aFFQOEVMdng1cmdibjJLbnpSalBndmJ5UmZfbW5qN2UtT05SVG5PX0ZReExySWNRN3g3V00wejJzOVNaN3RSOHpGdzNUemRJVHBCYkRjelZxQWNyclhVLThZMHhtdVB2aWFpX3JxTEx6cjJ5ZEItcE9MeFhNcjFVeFA0WFBTZG1GT3diREZkRXViT0R4SVEwZHRqR3Faa2NiNkdfNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFAxdS1iaFZBRnltbHN6X0JLLUl1OXhoUXZnMDRmc21GbkxMTC13OXR0LWlQZ1hDRFdUaEFycURpMTI3V3RZbHVUR2EyM2ZqWm5QQ2V2cUNKb2tfclNHcGp6c080UGpjNFhrTHNFRA?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46022.375</v>
+        <v>46022.88680555556</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jose Mourinho once made Cristiano Ronaldo CRY during furious dressing room rant after superstar committed ultimate football sin while playing for Real Madrid, Luka Modric reveals - Daily Mail</t>
+          <t>Amazon Expands Oklahoma Footprint With Last-Mile Delivery Station - Business Facilities</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 13:51:08 GMT</t>
+          <t>Wed, 31 Dec 2025 16:21:08 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNSGlJZUZpSFg5NXZESDdiY2NXTUE3ZGJaM3RPbU9yT2RCMDd1R3R2LWZPaEcweWRYNFVrSU5WOEZIR1drNHVreGJvc3l6X1VlNTRxdXJnaGpKbjl1Zi03d3Z0Z3VVaTJwaUVqb1VsY2JuZTJFbVp3WlZYa2dmZnBFZmNXZTJUdW5ZRFFWT1FFc3hwaHk2cEFlNG9Cdy0zZWo4SlHSAacBQVVfeXFMUGZ4c3FPTldoS0NJa19WdExSWHRVTFRRY3NmWFVHYU5PbWdxNXpIUFpUc281SzhfMWdVdy1idVd4ajJDajFPdHkxdW9DVHlfQ2pqWktTQzJpMExCM1NmVG1Oa3N0VnhWTWhLeXE4MXM4UmF4Y0RLZHBqNl9ENWVyTFFwM1VsNjh3Y0NCT2V0bjFUai1fMlp2djRqNkRWVW9FZGI1TVc4VW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOelJldHJrdGQtdGgyV0xYRFpfRUdsTDdwSDBpVGpMZWdoVGNqZm5ieGlhRWJjd09wRm5PNVZqSWRsbGpkOUxTa1lKZGI5ZDJEcURiVWdMbXlSeVU3T0d2TlJnR1dhREVwS3ZnN1JlT05WWDBRb3NnWmFJQUpaY0x2c0JmTy1GOXFiWGJ3QWpFaDFLZW83dGZzcTBQR28?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46022.57717592592</v>
+        <v>46022.68134259259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🚨🇧🇷 ROBERTO CARLOS – WORLD CUP WINNER, CHAMPIONS LEAGUE LEGEND – IN HOSPITAL AFTER 3+ HOUR HEART SURGERY Roberto Carlos, 52. One of the greatest left-backs in football history. World Cup 2002. 3 Champions League titles with - x.com</t>
+          <t>Arriving Today By 10 Pm Amazon Out For Delivery Still Out For Delivery Still- - shababeek.org</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 11:45:00 GMT</t>
+          <t>Thu, 01 Jan 2026 00:14:44 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9RVFJPelVBWU5jOHcyYm1wTUJZbFkzcDNDZWdFQW5fM1NZWmJyUkFnZ1Y1MmJ1ajhfS2JXWWNJeDhrRGxyUEhDZWk3RGJqMVBteDZaVEVLRENueDkzYVNlbU53?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNdnhxR3RzVnN2MzdLTERBYnl6SnVkd0Q0N1pmTEtDdWRZRGZXZ2xLVVZrU1Z0a2pyMDJNOTF0ZTV0M2U5TDg1c3RUMGRWd3lFLWhTbU5YVjFtMkMtUXhWdzZLSFR4UUd2TVFrVVl6Zk5KbUM0amVLdk1zSXpObmEtRG9UbW5jT2d6ZUd6cVRyOXFRNkkxdk5NaWFSSldfZHFsVnZHRDVXNHFEVnJTWThfVy1Jcw?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46022.48958333334</v>
+        <v>46023.01023148148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monaco dismantles Barcelona at Palau Blaugrana - TalkBasket.net</t>
+          <t>Man accused of violently beating 77-year-old neighbor over Amazon package delivery mix-up - WTOC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:08:33 GMT</t>
+          <t>Wed, 31 Dec 2025 15:44:59 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOQVFkaG05ZUlyUHBEdEp3MHVFMHB3dVpOUkxlbGkxUnVXQ1pLYVRVdmstOVlhMXBEejVjM19zenlBbGtJQ1lWVmtGaUUtM1dOdDhvY0QwYVdkbnJVUFNnVkh4OU1QWURfREU0WnVid2dBRURaOGhQdUhQTEhaR3g5NXBXNUd2WjjSAY8BQVVfeXFMTnNxbmwtMjdwdkdVNFVKbTdqb01ucVRxN18xMXZUTkpTTHAxRDJFdkFEYWtRTWRXTGNvZFFCbEo4LUpXOUNOMTFoS3NBbGpDNTN1aUdNeUhYdktvamozeTRpZnhrU3R3OWpSeEdUWlJQaVNweEJPdkhmb1RTNDJ3SkItak9IM3BhQXh3Nk9kM3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPRkZ5cEJuSjgyUkNISWlKR0xwZEh1TXhwRmNYeXV2T21ZYnQ2dmNjeV9ldnNfZHU2M0JzUnoxRE9tN3c0eU90SHh4ejBPejFQYjBVX0VEb19KLUtBVkI4bGNCSjl0amdYdFZTcUtVUGpLTURhUTZtbUp0QzJHWm9Bc1dvYnJDVldtNGlMMlZ2eXpFX2xzNnNobFB0TXRHdnRBTVdTbktlZ1pCR0oxQlB3T3l1WWlGaTMtUS130gHPAUFVX3lxTE9mdGM3U19uT3ZEdnlocExWVUVhSVYtUEdnVlBHRjV6THN3eXN6elk5bHFkWlFVQkw3dlh3cFJtSXFfcjh0Mmx3RmdUNlpVd3FqMUlLdl9qbVhnalphSU9oR3BwTVBaX0M3cVBJVGt4eWU5VDZBay1CVjZ0bVBweVZycng5eWlPelVONnZwS1ZyRjdvZXpBdWJkNDRCSU13M1VoUlRhSzVleDNuWmw3UlE4OF9lVmNvOUpNcjhUZi0wZGtEQmZncWpfd1hHNEVvVQ?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46022.3809375</v>
+        <v>46022.65623842592</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Level City searches   Spain, English   language</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bombshell at Real Madrid! Vinícius Júnior to Chelsea: His agents are already negotiating the 2026 mega transfer - madrid-barcelona.com</t>
+          <t>Are banks, post offices, UPS and FedEx open New Year's Day 2026? What to know - USA Today</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:00:00 GMT</t>
+          <t>Wed, 31 Dec 2025 20:01:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxORnZjSzBMU2NaNzF4UlJIZmZlM0UxcXYtS0hScHBaUmJZSFphTEJFQ3EtODgyVW9SQTNsQkJMZjhOOFVGX1drd1FfOWpxNHlJNEJkTUlNM0RyWDl2MmJ0Zi1ZRFhBWldoTG1tVzJ1cFJoRWt2X2tST2RmQTFMSThnVC1CVi1BN0VNZHNBVTAwY0hNRm9GdXNiWWRNZGVGUS03MnZtb0hyYVNwLU9FcTBkVzJCX3E3ZnNKRU13UHJ3V2NUdW1vVUZsOC0weldhTm8zT2hGS1JNeGk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxORjlMSEJIRVRrbzhPLXFwWjBOSDd1dlIwdndrTmJadnVieXdPVV9Ec0IxMkJTZmRPTHJid1hMZ1RpQTFtZm1MeFBwdHdNSENFa0t4UzRYQURtek9LcGZjeUcwZDl6T185eEdJNDdoNlB2ZzZZaGVYV1BncDYyUUVUQm9IeC03VXV3cHJTdmxnd3VocGFHbnZZX3YxMm1ITDJGWXBSZGlDQ05zVHljWVUw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46022.375</v>
+        <v>46022.83402777778</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'Guns' found and four more arrests after Oxford 'shooting' - Oxford Mail</t>
+          <t>'Grinch' UPS sued over holiday pay for workers - AOL.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 13:30:00 GMT</t>
+          <t>Thu, 01 Jan 2026 01:48:38 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOaXoyTThIa0F5MVg1Y3JVeDdfSEh1bDByVW1VY0pSanV1enc4YVppUjk1akdKYnpLcGptVi0xcG9wNDJJcTJrS3FCeE80ekVGdW84TFZlQTcyU3ZDQjZ4MGs1UmM4dlhSYWN6UjlhSlRfX3hfeU5hQU4yLTVqR3F2T2tSdU5vcXN1WDU1eXJJTy14NEdZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5HbC11LVhpYVpjcy1YY0dJUTdTLU5KZUhJS3FmQkNQMTVjWTFVWkhiUlNMdU9LMzdzRzEzSlFqSl9CQ0VDcnFnVW1HYVhRWDlhVks0cnNhVUN1clpZa2FHVmpkNjBjQzlLaTVIcmtTbjlIWl9DSFM3MUhJem8?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46022.5625</v>
+        <v>46023.07543981481</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Islington stabbing: Boy killed by single stab wound, court hears - BBC</t>
+          <t>Texas Woman Orders Christmas Gifts for 5-year-old. Then She Checks Her Ring Camera After Amazon Delivery - Patch</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 12:51:14 GMT</t>
+          <t>Wed, 31 Dec 2025 18:00:38 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9iVmRlSW5yU2VJMV9fS3NsdWVkRnNueDItUlQ1c1BlTXVDREhYN2ZWRXZyY0tZZUZQX0RIZHJLYXJfd292dEVya1BOdmdHTncycU43a0lCWURyZ9IBX0FVX3lxTE5lVnQ0ZU8tWWFTTTJoLWI3YmRJWFYxTlYxUXNnbGhHYVVJZmNNSEo0NHlyRWVreUR0eDlmenVqYzlLRkVPMkpYeDc4R1BvX1R6YmN4eEFGZjBOUUFMWDNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOR3M1ckdUdHpXd2g3aFQ2M3IydmNyTTRncmYwMjh6Y0hiY0p5NmkyZk4zTXB5SlBQOWJnRUpoc1JXOFFka0tqRUR5UzNCbEhheEZpWDRWODdsblNnU0Q3bXJxdzN2SkduODFaMVl1N29ZSldibEFwUXVTRE5abElhOXg5UWYtSXlpUXFzRy01OTBwa1NJRWJjZWFTQzVkUWdZNUxrRzFMOGZ2QURqempDVHRUU082SWPSAecBQVVfeXFMTlFHZXNKSmRSOGlua0ltV0ZPWncyU09WV2QyNmp6c3ZlbTRxMFl6OGlKcUc5eEM2djE0eG40enRwX1pScEdxc1BYQ0I5NGN4VlRlTHZtS3lMdG04WjFGaTVTUFFMeV9tNkxWSDNCUlNmUkZOMTBlOVJ4azl0UUtvNFpuQjhNeWNjZ0dUaTRUZ2QzRHhvWER6UEQ3MTFyRXc1UElfbDNtRXZ2M1YzbGZERk1RU25jT2RZZ2FpTXAwS3dRUWRXYXdDVVI2ZXdRRFV0VVV0bUo4U0ZHTGlBczBKcmdpYUZZdzlF?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46022.5355787037</v>
+        <v>46022.75043981482</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Two men in hospital after being ‘stabbed by group' in south east London - london-now.co.uk</t>
+          <t>Amazon’s $25 Thanksgiving Meal for Five Might Be the Ultimate Holiday Hack - AOL.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 14:18:42 GMT</t>
+          <t>Wed, 31 Dec 2025 20:51:57 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOMWwtMXY1SDNrbHhwaFN5RDNGRFVkaW5zb3RRbG5ETmtNVWpybHMyN2tQeElvaGkwQnZuQVQ0RXVxWHZRUFVnNUlHaFVLNlRob1RURlJLUzgyekFxcGg2S3hDdV83dndHQ2RXdmJhU1RfalhFZVE5dk1tQXVSbjRtWGVWQ213SEQ1M1ZTTEFyTEFROFk0c3BtaG5oQkhuNmtmSHRidw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxON0pWdWUyTFVwa2JBczZvZWFOeDBlRnVMR0twbEhsZWNmZkRibmNXdXNHWTNCNjRLTW9aWlpORHAwTUlybzRyZlB6azkxM05GVzJxSHlmWldGT1R5SWFzT0RkTVJKYjBDYWpkNkZobG4wYmt3dEZGSHFSWXVnZW5PS3ZR?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46022.59631944444</v>
+        <v>46022.86940972223</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>One of London's most popular New Year's Eve fireworks viewing spots is turned into no-go zone for 'public safety' after fatal stabbing - Daily Mail</t>
+          <t>Derbyshire fox stuck in delivery van engine among RSPCA’s wackiest animal rescues of 2025 - Derbyshire Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:55:57 GMT</t>
+          <t>Thu, 01 Jan 2026 01:00:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQa05Kd1ItekRlbXJKMXl4NG96cEw5cndPYjNxbF9jZ0w2U2NwdzExTWZCeWxyUzRRU2ZmWk01enV3c3MwYzNDcmFCRS1adm5nM29IZFRDTjQxTGhkOVYyVjFaeEFNSGE0bXNSNEZ6ckRma1czR1JxaHJ6RjEybkR5QmRSc1JtakwydjNEMTEwNkQ2eEpwUU9UdkIwVHlXc0JpdGhlYzVfWnFIS0NiMHFmTjQ3VdIBuAFBVV95cUxOSUNLelE5RzZsZDdhQ1BEZmh4N3BNUGJtSGVGbFlaMzdMWFU1NE84cHN6ZGZtaWR2NDhJbnNEMDdLRkRIdWZhVEYzS3BXdGdVN3d0VElMUFpMSlVRMjJFSk9VdzFtTzdrQ1pLWkFWODQyc2xTbTZSYWhYMzRrdEZ0a1NWeGdrdWZadmdNLWpQVWJuNUEzMy0zalUwOXcwRWNsaDR5QThoR0Y2R3QzcHM4M1pBX2Q0SUN2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQTFB0bjZCMEpCazhDRHVvWnJpNTJvbmY4M3NwbjRaWkw4Y2VDMzJoeUZ2TjN3TnVKa2VsdWMyNk52SzJfZlRudzhKTDRvTEVwOU10Z0RuX3RQcW5DdGhDOUFnWDJORnNVU1ROV1ZEaXM0Sk80OHNmcDJIbzZvYThXcGdtWDRaZTdSUzhWQkdnQzVZeWhQOFo2YXpqaFBpNVBBSWZqMUtzOWtYQV9tWG9SYVRoWnJkX1AxRDRzTG84UkQ1RHh2YjRqbFVIVkRWS1Fja1hLMzQ2Yw?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46022.41385416667</v>
+        <v>46023.04166666666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A Proof-of-Concept for a Drama Series Needs Talent + More Streaming Gigs - Backstage</t>
+          <t>NSTC to lead 57 start-ups to CES in the US - Taipei Times</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:31:25 GMT</t>
+          <t>Wed, 31 Dec 2025 16:00:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxON3Rrc1lLcjFlWkRpVWh5dUUtNFJwckV3a0dYczdlR2NoM2hqQlRyMGU0SzFpbDlfSHFSVzZYbzhfTFBlNThPWmhwdWdvSmU1QzZDUjhpSnY5b1l4RmNsN2RiTVAzMy1EMVJINDY4ZGdQTE9YQjV2MVVWVFFHZzh3blFxa1lKVE9fU0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE4ybWFLSzhnZWh6bG15a2cwajJWaG50aWxSdURieWxLV014d1dGcUdxUXh2V25KNjU0ZnV2d2hXR2pwV1AzdUFmVWtzUWttR2NNTVV1THNYX2VuelFTalByb2p6M2FLeXduOUZ5eG03UlVlVFhkelE?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46022.43848379629</v>
+        <v>46022.66666666666</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Man, 22, appears in court accused of murdering schoolboy, 15, weeks before Christmas in stabbing - Daily Mail</t>
+          <t>Amazon Expands Space Coast Footprint With $6.1 Million Land Buy - TalkOfTitusville.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 13:47:10 GMT</t>
+          <t>Wed, 31 Dec 2025 20:33:17 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQYXZLSE42aEFRZ2d5QURBTENWNE1SUktpbVlnc0NHUnhsU21kSldlbi12TVprQ21Kek42YmF5OWQwdWVlQTlUZXd4UV9rYkZFcWxQZ3k2c0lVTGdnSGRPeFlHUHlfRmUzTU1tTURQOEs2UXY0MmZ3bk1DaWNwQ3VqOWstWXNLSTVXN3JDZ19tcVdLY294dkVDVWJRSnlBQWVvVXfSAacBQVVfeXFMTjdabjB0UTJMM2gydjI1QnZCcU9ySnF5ZEkyMUxnR21rOWdJOExoa0RWZXJGSGtVeVJrV1lrOGczM05oakEwZjJzMW5sYTlFczA4SnRFd3hoMWNvVkJVMlhESXBsNFItWllRanFFcUtiend2TDB3bXd5amR6TzJNd1dGUnBJMldXWmRERTcwR0IzYkFFenU4UTlvcDdlYlJnWFk1WXUtR0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZmxBNHRfQmtrbFA1WkZCNzRYcFNLSGd2d1lycWh6ZXF6eE1YSFNnY3NsRkk5M0l4OXlCZk1aT1A2TDhxWGJ3czVqNkFfeTU5UVJCNVM4ZU9OeVZtTDljR2VtNDFpTk4tRXZsMXVUNklIemRURXJlcW05WE92Sjd4b3FUV0hlci1RdHNwRG9Mc3pncG8zQlJwTmcyRUZWQTdfWlRZLS1B?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46022.5744212963</v>
+        <v>46022.85644675926</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gordon Ramsay 'takes explosive swipe at Adam Peaty's mum' in wedding speech - London Evening Standard</t>
+          <t>Amazon buys 45 acres in Brevard County - The Business Journals</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:32:24 GMT</t>
+          <t>Wed, 31 Dec 2025 18:34:00 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNR1lQMmpxSjZ1SVpLSldCOEFna0hrbldTQkQ0QU5DMzhVWExzOFJVX2lfNHhxM2pDTG16Nk5vWGVoUVJWTkktbHM2bm9QWnJreFFoVGVSRldnQ0ZLMV9EbkRaWkRETm9GV2toZC15bk1DU2pxV1FqQ3owUkRnakZFdWZ0ZC1VVGU5dnQzNmVpaGo3dmVpZndJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZ29vdUNHdzc4LUxrVkNiRWlfeUgwd2hKTlpMeXdGYm1RNzRrU0pTUk1ZUWFrOHFqNDVhNHVUbkFHQ1pSMm4zTGJyNWZtelVYcEttWXJVZlp0NmVCZmFsWmc5eGs1WHc3WkJIMlgwS3dITGNieXJvS0E2MnpXS2dta1B6NGltMFYyUlpaRWN0MGYyX0JSMjFoLVpvMjlMbmRuQzQw?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46022.3975</v>
+        <v>46022.77361111111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bomb Threat At Delhi Hospital Turns Out To Be Mock Drill - ETV Bharat</t>
+          <t>Are You Using Same-Day Delivery Offers That Lower Price Tags Before Coupons? - inkl</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:43:07 GMT</t>
+          <t>Wed, 31 Dec 2025 17:50:48 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQRm05eGtob0RrcDBvdWE4dE55NWZEb0tHTWVmMjlIaG5obWhWc3dkNl9aLWYzUzVyWGVuQzhjWXlJVGktVmV4X3FaYnZFYkpOOFdxNGo4WFZfOHYxdE9LR1lDUTJTOHZxUUhMWnBtcWhDenUtMmpRVHFPSlJERWJzR3cyRUpSQ1I0S0g3T01VY25QOXctaDhuVXQ0Z05sYzlUS2dqSmVmYkxiUk3SAbABQVVfeXFMT0hReG53SzRRMzFIT29OanJhZ2pJSzRyamY2cS1zbWx4bzQyUThWSGxMMENMZW5SOTVBNjBGbnFVMTJKMUpvUXduUW1YOXVKMnhKT2MyS1IxZU1uRU9xUjhzcjJFLW12OE5BUnJyeWplbnJJUU5nNkxwODRTZl9KRUhaOVVCLXV3MlhjM0NkdlFkbm5BbUZMOGdRRmpIVVcxTzdFUEttd295NUdPZnBPWFg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNU1lvOUFXb0RhV2lyTVQ4T1VSSlB3V3ZwSm5JUnRQbDJ5eXdZY1U0aE1veF9HaFZ2VlpGNjNxOFB3RlhCd0NzY2RuZDUwQmFOMkNYUlhLSkFoaGxtWG1uNjFPX2lnOEl5U3ZNUXpoemU0RTNCZHdFUnFQSG0yS2ltaWlvWVV6VlhqaXRrODFmci1UWjZfaE84alV4aW9PZDlyVVBn?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46022.44660879629</v>
+        <v>46022.74361111111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Heavy police presence in Sydney for New Year's celebrations after Bondi attack - BBC</t>
+          <t>Nationwide Strike: Delivery Employees Demand Pay Hikes; Zomato, Swiggy Announces New Incentives, All Details - Goodreturns</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 11:49:13 GMT</t>
+          <t>Wed, 31 Dec 2025 15:52:40 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE12MGEtUWFhYjBrLWxJZEVNS3ZYMktuYmRYYlJZY1VNd2xFV3NPSlpHb0ZXTWtneEZ1WU9fZVM4M2ptN09GYlF5cVNxMFNXUGdaUjZnQmF3LXRBRnh40gFiQVVfeXFMTnZDT2tRMFI5T0pudnY4LXN3OTNHVEtqZ2MxampXMFZfTEJ0M2VHbmRycVVyNWdmbEsxX0tzcUZhekhYU0hQbVZsYURnUnNrUEhvTTVHVXJjNXNpTlVHZGJaaHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNSUhmdW10OFhUbXRsQ09KZWJETlJWOTJrOGtPTDhZcElPRjY0QS1MUkRRTlNpOXE4OGZJSWxyR2ZfaXBTYkxndHN4UWJQQ1JHMHVGRUhGSVFhT29rTkJjdXAzZVBIMjUzSTlwMTFDQy1xNE03X1JFREFvQnJQYTZZOXNKT0ZmZEhRS0V4SlctMEd5LUpIQWtaZW92eXNVXzc5MnlMZDJRUGZtOGlvSE5sYmxpTzcwWEw2YzJZNzBNaWxfRkczMFQ4ZDhCQWNGT2kwZkd2QmVzdU1tY0ttcGc?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46022.49251157408</v>
+        <v>46022.66157407407</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Snow and ice to hit London as Met Office issues yellow weather warning - Times Series</t>
+          <t>Read New Year’s Eve Par Gig Workers Ki Strike, Food Aur Grocery Delivery Ho Sakti Hai Prabhavit - Gallinews</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:17:01 GMT</t>
+          <t>Wed, 31 Dec 2025 14:48:13 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNRXp4Rjg0OVBEWUx4dHFvYkVqdW14SVF1djdEMmlBVDR2V2FKRHhxQlVjZnhMTVJTSnpCUW5uMktnUi12T3BiMXp4WGdCRnhRSzRoT1I0cWZlSXVTZGxqc1M1bVp4WVhzZVhJN01mT2VTT01zTFdtU0V2MTBIVEgzUlpKa3VVQVNuWGVGQTJBM3ZYQk5ULTM5ZXVxWTBrc2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNSlg3ZVMyaGRwR01fYW5xT0d3X3BEZEhnTkloaUVyNEhfeEQwNzNleDFwdDVVLXE3UVJfbDdna2lqUFFaUjZUdTFkbjlkMEFTTG90Tkl0N0ZrV2JHRkIteUh0MGsyRy00LTBWOFd2aVY2cnBpTy1jcjItU2V3ZzhnNnlkamdweWxybklLd2pfQ2tsRVdUV21iZTByU0hmSFhKaTQ4WWt1RjhNSDA2b2Q4MA?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46022.4284837963</v>
+        <v>46022.61681712963</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches Belgium French language</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("brussels" OR "Maastricht" OR "Antwerp" ) AND ("Bombe" OR "alerte à la bombe" OR "explosif" OR "colis sans surveillance" OR  "explosion" OR "colis suspect" OR "tournage" OR "poignarder")</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Article: When Dick and Liz Came to Dublin - Film Ireland</t>
+          <t>New Year celebrations marred by fires, violence and fatal firework incidents across Europe - belganewsagency.eu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:59:27 GMT</t>
+          <t>Thu, 01 Jan 2026 07:23:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FRll0Wl9RMzVBanRwTlBKdGQ2azcydWl6S1lrenlwNG5EZ2pJRGVjSm5NT1FUWkhSc1p5TDdOOUtSMG1PSVNMbE9EYnpRcVVSS1N2NnhrZzhEUnktRHc1WjU3SE5BcWpYaExxSkVPZ2pWX0dIUG1ERA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWVM0WG5QeGl4eXNlT1RQNklKLU9ralpIU2QwN1c1Vjd5cnZUV0habm93UEJLNkcwRVU4N1FMWDRnbEJMNjlJeFY1WC1PcXhQWU0xRTEtZVprb0ZiOW5LT19WUm5TdWJlVDAtcUliMGJCX0NiazZuMS1Xd0JBTE1LcGZ6NFhQMkZhT1RPV0FIcVh3N0hDRXR1SkFOaktnNVlBOUYwbDJHMUJibG1jUkRBZVRXcExFSDZFNmw2ZA?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46022.41628472223</v>
+        <v>46023.30763888889</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fireworks displays in New Zealand and Australia kick off 2026 celebrations - Guardian Series</t>
+          <t>Germany news: Police face risk of violence on New Year's Eve - DW</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 14:08:48 GMT</t>
+          <t>Thu, 01 Jan 2026 02:00:12 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNSXZvY3Q2bDhIQ3hGQm9aaGk4bVhkd0c5RktDcEhaWGNod0p6TWhmMmJBb0ZLZlJIbDZsUTU4Q3hNMmZXTDFqenNmVG9KczNTMmpPTDZvSjVkdHd1UDNJRmkxVllrOWhseDBMcjdjaWtiRnZVc2JDMDBvQzJqSENfSERYVFhkNzhFVXROamx4cHpwZnpKYzJzOGFaMWZHQ2UzcVQzWkRsVkctQ2hYcXdaaGVEbi05TWpKcWUwdjJZWU1GazA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQODYtMWs2Y0Y4QmNudngybkREZk5pN25HS1ZnbFpGSUFaeWtta1VSNkkzQ2dMeXFrS0F6UVY3YldsRFBvR1lfZy15clNMT18tZjB1SmJuSEZZRGxvQUN4LWJUcUwwUUFYdXRmNmhWMmZDRUotam44NWNiNGJtaXlNdEpiQjBqX2diQTVjWFBnbGZEejl0NmgyVkx3?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46022.58944444444</v>
+        <v>46023.08347222222</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Channel Tunnel power malfunction fixed, but rail delays linger - News4JAX</t>
+          <t>Hot Mulligan Announce 2026 Europe UK And Ireland Headline Tour - That Eric Alper</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:07:04 GMT</t>
+          <t>Wed, 31 Dec 2025 22:10:51 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQbHZ4ZjltZlVoUllEeEdJeWZhQk8zRlE3YnJBZXViQ3FUZmdOQ2ZicjJQTkp1WnpOWDdqQ3RkNURRMWJaNmtPeHJ6ZHB6WlJjbVFTSHdmMjBtMGZUY2NwSThmczlXNkxFdnRvbkp2RVM3SjNHSU5aeVlPRWVBbTgyTWRIVmRBVHlQWVdEZWd0Q1JPdF9BMGlwTEZtT3FaaXF0NTBSd0ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPWUhyWFJodUxjVGZqTk94N0ZEODZfczRobHlya2htb0p3aURZWVVHR0MtTHF0cUQ1SS1ueWxaTk5jODdVOGYzaDN3Z05PNFBaSXpDdHJFMExLRC1RREt0QnRvN2doSXRKaE1jc2xjZzhUU2V6ME9QOWp6Y0RWLXpOSmxPRHlHNVh3V1J1NmltUld3OTltOWpMMG51SmZVUnJ4ZE12VHA5SQ?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46022.3799074074</v>
+        <v>46022.92420138889</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, English Terms</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>‘Roads, rates and rubbish’: Worst councils of 2025 revealed - Sky News Australia</t>
+          <t>Russia releases footage of Kyiv drone ‘attack’| Gulf Times - Gulf Times</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 08:52:56 GMT</t>
+          <t>Wed, 31 Dec 2025 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPTFBjdzVmNS15dEJpS0x6Qnd0TmZ1bXJ1TVEzWGV4eGtJWk8wUzh6NkR3aGZoNndsUGdPM19sc0haRmN3TGRGT1JGVmxMZ3FpbDFpNk1udnRBZWZBeDVNZHpqYXliWkxVTm0zZGNpRDBlelJYZktqLUhvNlhvY2xxQUVJWUxRNHNSdXRUbE1ZTnB4Um0zYVR1RGliYkVnUU0xeEhGLXkzcFJwTWlGOHBLaGVSUEN1anhkNWRIUzBfdWdJdkpsWE5FUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQaTdtLXQyM2RxaGdTTkpTN2x3cFFucGRsN2N1RWVGdVBSLUR5a1FFeGFybkp6cmoyZXVRZERkYjYtTHFQVUZ5c1I1STZjcmVDREl6UC11UVlONHh4aHE3ODE0czhvSVVBaDJYWUp4UHUzTHVxQzNrTHgxYm12LXhKeG8yMW5RcEtwX1pHZnBha0pzMUY2ZV9SZ3BZdHNpYXBYMERlRVd2SXlOOTRxS25YSHozd9IBswFBVV95cUxQaTdtLXQyM2RxaGdTTkpTN2x3cFFucGRsN2N1RWVGdVBSLUR5a1FFeGFybkp6cmoyZXVRZERkYjYtTHFQVUZ5c1I1STZjcmVDREl6UC11UVlONHh4aHE3ODE0czhvSVVBaDJYWUp4UHUzTHVxQzNrTHgxYm12LXhKeG8yMW5RcEtwX1pHZnBha0pzMUY2ZV9SZ3BZdHNpYXBYMERlRVd2SXlOOTRxS25YSHozdw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46022.3700925926</v>
+        <v>46022.875</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City searches   UK &amp; Ireland</t>
+          <t>High Level City searches   Germany, German language</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>( "Frankfurt" OR  "Cologne"  OR "Munich"  ) AND ("Bombe" OR "explosion" OR "unbeaufsichtigtes Paket"  OR "verdächtiges Paket" OR "Sprengstoffe" OR "Bombendrohung" OR "Schießen" OR "Stechen")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Where was Project Hail Mary shot? Revisiting key filming locations of the upcoming Ryan Gosling sci-fi film - Soap Central</t>
+          <t>Silvester live: Zwei Böller-Tote in Bielefeld, verheerende Explosion in Schweizer Ski-Ort - Frankfurter Rundschau</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 08:30:04 GMT</t>
+          <t>Thu, 01 Jan 2026 07:28:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQU1BRZEhNTzgwekpXVXBsUXdLV0EwVDhHY2Y2ODUzNDBLeGgwaHlOZWJJZU5Ha1VrSEVydGYwYjF4T3NoQkNiWkl5bkwyc0RvVUNJcmo1NUFDcDBfNEJ4THZEZE5mc1RQNE82R1RCRWtvUUEzWnIxaGdVcm9lUUFtVjdTd0VpX0V4UUZEam0wZ0JmZkFvLVdFcDhvRUo4UkZHeEtOOTJXNE1oM2g2M0lSazRxVUw1OUp3QmEyRGg5STVVV3YtM1ZDVU1nT1dEdDA4TGtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNOFQyZnNLbFJqb0F4NlJ3S18tR3B5WG9BVzhWWnFVT2U4N2ZpdGhFZGlESjRSTG1QZ3NZSFdnLVNZRE1tQjhVeTctdmp5dE1qclIwUmYtV3NERmRBckxaSXZPQ2FSZU5VN0ZrSDhlVVdneEZRNlhBb3lzc0NGcFpvTnF0bFYyU2R0OGlid1lrbE56RHVPb2xRc2lrMVZjRVJlaWU3MGhYcUFoRjhJWVJaS1RLdVJPZW5XZXdHRjdGMA?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46022.35421296296</v>
+        <v>46023.31111111111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Team GB's 2025 Wrapped: Everything that happened from July to December - Team GB</t>
+          <t>‘I Really Love My Husband’ Soundtrack Album Released - Film Music Reporter</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:02:09 GMT</t>
+          <t>Wed, 31 Dec 2025 21:07:03 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPTU9BWkY1R3FPZnEzRHEwMXpIdWM0dXdFZXZLYVBFMW9pbFpMZ1NmSFRMZ3YzNGljQk42cWl0ZktkUGZNZnhDX0xvdk9uUXVyV2FGeDVIQ1gxbG5zMUJJT2xEdFhQQmQ2NlVBUHJDclBldkdnMjBjTy1YZ0x6OTUyWnlnaFlwMlpZbldfNXNOQkJ2VjdNZjFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPMHdPeDlaVXJYeDc3b05lTEUzT2gxb2hFNDhxSlFseDJuUE5zYTNhY0RJX1hfdGk0M2tDT0JyRVNCZmxIajNleDdhUGplZ2VIMXRvbUZta0hzd2ZFTzVtVzg4R3hkWGExLVh4REJsN2d6akgyUE8tQ1ZrekYyRmM1d1lHWTBpMlBKSDdNT1BmbUpnTTZEZm80?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46022.41815972222</v>
+        <v>46022.87989583334</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>XR and JSO Broad search</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"Extinction Rebellion"</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Can Traders Expect Breakout From Arrow Greentech Limited This Week - High Frequency Trading Trends &amp; Free Explosive Wealth Accumulation - bollywoodhelpline.com</t>
+          <t>Why a red-robed group in white face paint walk a Cape Cod bridge around Labor Day - AOL.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:34:25 GMT</t>
+          <t>Thu, 01 Jan 2026 06:26:52 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNM2dJVXdtczE0MEFKcHM3eVFqN1VMWjdoZk50RVg5STF4SWFKc2xUM1ZsR0FsbDU2NkJHa2ZTYXUxNWNmWmR3OG5mR3RydUJnUFF4aFJpT0hEYWxsYUVNZjFhWWZyLXBZSjdLb3FaQ05IN1FsM1NERGo2ZjNvVFp4Z2RqWmZraHAya1dtMmE1UGRNVjZfNFNGaHU3STdXNldaVWNFcjBtSjBFeHhleGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5mOW83Y3Q3WTlRQlNWb2d0ZTJMRzFINTlKR0UtZldlcWl0bHRVTWdrc2dpLXY3Wi00QmFTZldPSkJOXzBwdDR0cTB4NjVyb2VOOTlPR1laemhORE0xUGNRalM0ZjJXUUV5UVU3YzNPRGJkQnk5?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46022.39890046296</v>
+        <v>46023.26865740741</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nando De Colo delivers late dagger as ASVEL shocks Paris Basketball - TalkBasket.net</t>
+          <t>Prolific shoplifter who stole from stores across West Sussex town jailed - The Argus</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 08:54:16 GMT</t>
+          <t>Wed, 31 Dec 2025 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZTBwcFM3SGVyVEotSjVvRHRpVHBYVTJ4OXl6NzhleFZncFFyTEpITnZHUF9zM1RneXVxMlJ5cDVKYUxTSHlJWnJBZEhCUVIzOEYzdWVxMnVOUHlSc0pzMDN1QlBFQXNwUmRQcW9KU0V2YkdJSFgxQjk0OUY1TDR4Wm84NG5scjBiSURqTk50MnJpcjNVSDVFVDJqZmxpOTU4UThV0gGrAUFVX3lxTE9WUHlCd1lrc1AxLUdRRlpmUlFLUUxSTmsxR2VjRGJMNEVPcmdMNDB6ZVFVNkJpZWtLWFRvZWQ3UjVyVUZLbk00OXA3ZzV6RXBGdUZ2R01EZllIOEptdnFBUVk4NC1vY1dxY21LOG4wNVUzX0ZGQ2NoZlNfMDlCeGZsbzVab280UlRSTGFwLUdaU3I4MFlZTklDMU9lUGhZWlZjd2d0NHg4aGVSdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNSUlnWU1sZ0gzUUdFbkU5a3Z1X1Q3R2p2X0lnTElnLUFGb3FGRVhZdFA2TXdjSEg0MERsbWQ0MjFXeHNmbzhtbW5ycFhmdjdsVE9VenkzOExEZWgwREZEd3E4TXd4YjZ0LXBjbkV0QW5hbE9RWDR1eU54Tkw1Qzc0MGdwWHd0V3h0RUF2eWNCT24tT1U?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46022.37101851852</v>
+        <v>46022.625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>Shoplifting UK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>"shoplifting gang" OR "shoplifting trend" OR "pickpocket gang" OR "theft from person" OR "retail crime" OR "shop theft"</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Karnataka’s Tilottama Sen crowned National Champion in 50m Rifle three positions at National Shooting Championships | DD News On Air - News On AIR</t>
+          <t>Security measure spotted at Bunnings - News.com.au</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 10:40:50 GMT</t>
+          <t>Wed, 31 Dec 2025 21:08:26 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNREdzN2FIdE11aTBkdFRIVU5hRWNCd2xXSUVWbzJFQkt2aWk3Q0lxb1R1MG9EaG1sTGRPRzhvcWF2ZkxuMFAxTTNKV2ZpXzhWeDY3RmdTR1JyUzZyLVd2dzhpSy0wS21IWGdZTGNZWGZPby1QUy1kNy04YkxXN1lRNWFNOTRId0drMzJlVHhVR2xWWW9wWk9tMEgtLVpNVVNZRjYxbHd1UjFmemM4VWxma2s0SlZSbk1zVktRa1J2Zkd6ckg3T3Vfa2xzRXBoeXpQb3JILWRxcEhldEVf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPbk5sMEVCazVRRXBxeVppZ3hTTnhRUFZ3UGtGVVJCb2JpdVJwR09RNXVzNnJibzlRT3dMM3o3eDNZdlVVUUVST1BpWElVdHA5bTFxOWZ4YTlIcV9qc05lUXpBMUFDdFdoWHpzUlhwT0JUQktmb0YyY011dHNNalJIOEhPSHU0NXRpSTY0WjNISDhuZlM1X0g0VllQNHFlWFF0aTliTkxSLWJnT2l4NzRrRENTczl2anB4Q0ZmaWF1OUpQWFF0OFlNTlFIRDNiNF9aVEp5QWhjTlVXX2lZYTZka21NejhWSE9qY0lOdnlLNFdzR3dfLXpJMW91Z9IB-wFBVV95cUxPbk5sMEVCazVRRXBxeVppZ3hTTnhRUFZ3UGtGVVJCb2JpdVJwR09RNXVzNnJibzlRT3dMM3o3eDNZdlVVUUVST1BpWElVdHA5bTFxOWZ4YTlIcV9qc05lUXpBMUFDdFdoWHpzUlhwT0JUQktmb0YyY011dHNNalJIOEhPSHU0NXRpSTY0WjNISDhuZlM1X0g0VllQNHFlWFF0aTliTkxSLWJnT2l4NzRrRENTczl2anB4Q0ZmaWF1OUpQWFF0OFlNTlFIRDNiNF9aVEp5QWhjTlVXX2lZYTZka21NejhWSE9qY0lOdnlLNFdzR3dfLXpJMW91Zw?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46022.44502314815</v>
+        <v>46022.88085648148</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>In the fifth season, "Emily in Paris" makes Italians suffer - lnginnorthernbc.ca</t>
+          <t>Haaland 3rd, Alvarez 7th, Mbeumo 16th - The top goalscorers of 2025 - Transfermarkt</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:11:56 GMT</t>
+          <t>Wed, 31 Dec 2025 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPOFUtTHVsaUhvR0dDYjlGa0lXNFo2eERVYWwza05FZWJLNV94ZjdFMUZ0THpqd3RwMUMzenlYaEFCSFIwWWpfQmVhQ1hmN0QtUmdwMWN4Sm9kLVN2MHB0Ymd4VEVsTkdncmY4LVVGcElMVkRPWlJ2dzJuVUhzZnlSTG5XM0R1ZlY0WFk0QmFLWi1hV3BEZl9IVFl3cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNRnQ3U0p3YUtmakdjb2ZCRlIxYnpzNVpkYnRiUG5tN1RXMTU5b2p1b3VPbVFGODhVMnNsRjZERE5Zd0lZNzVfOC0tVnZnYlhsRFlTWVVpNW4tNElnUzZheWVpVVg1Vm1nSUcwNGxBa3RBRUd6djdobnRqWHBGMTNzZWVPaDlVcHlQdm9uTTBOeWZtcWt2VjAyazhQYlcyUnNqOGxZNk1KZGd1TnJvQnlFRm5n?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46022.38328703704</v>
+        <v>46022.625</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City searches  France  English language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Paris") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing"  OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maduro accuses US of sharing fake news about Venezuela - lnginnorthernbc.ca</t>
+          <t>Barcelona dominates Spain, Mbappé makes history in La Liga - Gazeta Express</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:28:55 GMT</t>
+          <t>Wed, 31 Dec 2025 19:13:00 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOVEpjb2lzdTZKcklKTm5sZnhyb1V4Q2V0SHRHN3BTUzd3VnlVVFdzTGJ0ekZTQ3lFVi1wRmhEc2NvWktIR2t2YWdDUmRwQWlaZmNVSTlmZFY3TUZCV3Nib1pLLVhzS3ZLcHRSeVItMlJkTmZEcFNmN2ZLS1BqN2NRdldZWlhmNS1lYXQxdV9PTnMxWGxjV2ZpMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOQ1hjTHdLMHhiYm02cUFIbEJOZ1UxM2lRaFFWTEU2QmRKSm1OeGlBNmh3VndfZmRna2Uza29mbEZHMVYwdjhHNWNld0tBUzFOLTVSOHdxVW5yaXltX2pXcko1R2NZcXJpazNvcEVEWWhuY3JxTTljaHVTelVEWmQ1NThCNXN3cGNtRWpjX3I0MnhReml3TmxB?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46022.39508101852</v>
+        <v>46022.80069444444</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Affordable Housing the opportunity - Dividend Reinvestment Plans &amp; Explosive Growth Opportunities - bollywoodhelpline.com</t>
+          <t>Real Madrid star Kylian Mbappé sidelined with knee injury - Click2Houston</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 11:12:10 GMT</t>
+          <t>Wed, 31 Dec 2025 15:47:58 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPN3VRR0FhSVVSMndmODdjQ3QyOGp1TVZBUXoxMGhHMzJzMVFhOHBrQ1p5eHJ4U3Z3MUJpSEpxMjRaOXBQV0NCbk55eU1jU0hfYzFzNmFJTEFHbk8zaVFSZXVoVHE3QVZwQ1JkUjlFZHhaMV81WEFyQko2SzU4TGdxWE96cjMyZFp6ZmoteA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOSnNJSS1Jb3l2N0I1TEktclh6R2txVzNXbHZHekJLMWNjeS1QVU9pN2M5dmRpdXM1YTRsc2pQSEVOaWRJYVhYV20xYmd3Y21lVVlnWmQtWVFfcUpURF9VTzQ3OWV3V0gxMUhONlhpRmpFVGxXaGVCcXJpbEJTdDdMTnQ3ZWUzQU9pZm41YjFJSWI1V2ZPM1JwNmlZRnRDSTYwdEltQlpHN1pEdw?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46022.46678240741</v>
+        <v>46022.65831018519</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gian Life Care Limited Crosses 200 Day MA — Signal or Noise - Chart Pattern Recognition &amp; Free Discover Fast Growing Stocks - bollywoodhelpline.com</t>
+          <t>Harry Kane tops BBC poll as Britain names best player of 2025 - CHOSUNBIZ - Chosunbiz</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 11:57:35 GMT</t>
+          <t>Thu, 01 Jan 2026 00:07:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUVdtcmVqSGUzS1RyRnhGTVZsaXlZN3lSQzZHYnpJRHVpZDFTbGZUYTEtbE1pb0c1aUZuRGlURHd1aFljRjJlVmc4NjdJUWV4YmNZUVBnVy1Oa0tnOTl5M0V3OFI0TUdrMkJIZlhmZnNJdlltSzNRRnpaX3ZJMXEzN2dBLVdRck14ZW45OHpaMEdMRzdTZTlCclFVRXlaRlk4bjJZNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9rWmJySV9wT1oydVlmQlBMU0k2emxDT1RmUlBJaDNNSGRkTml2WEUyb1FEUmp3UWtVYmNqYUdzcGZwMVUyVW11a2NJUndHajZHaFQxTzB6bHBVbWNCdkV5U3pacE9JZ2YyNEkwWHJLQkIyQjNETzBqSWp4M205TUHSAZMBQVVfeXFMUGZoR0REMzZHT1lsNGtMUVNLQUlYT19mY1ZYUGlnOFFWWk5hVkdrQ0JxbGF5eVg2N1pzVDAtVkoyX1Fwa0hiRzB3ejZBZ05uT01hTnhwZDQ2UXNaQWtrVDc0OVR2X2NDclo4OVVaN2FfOGU2VHpmNlIxTHlkOXlSTjFlSEduUk14TDI2dWYtTmR2WGlJ?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46022.49832175926</v>
+        <v>46023.00486111111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spain, English   language</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Paris" ) AND ("Bombe" OR "alerte à la bombe" OR "explosion" OR "explosifs" OR "explosif" OR "explosive"  OR "colis sans surveillance"  OR "colis suspect" OR "tournage" OR "poignarder")</t>
+          <t>("Madrid" OR  "Barcelona")  AND ("Bomb" OR "explosion" OR "shooting" OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat")</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New system prevents hearing loss caused by chemotherapy - lnginnorthernbc.ca</t>
+          <t>Barcelona assess Yeremay Hernandez as long-term attacking option – Report - Sempre Barca</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 31 Dec 2025 09:17:54 GMT</t>
+          <t>Thu, 01 Jan 2026 06:46:18 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPakxRVlZCOUgzZEc4N2FwQmk1RzA5Z0o3dXZYaUQzSXB2d21GRUtjeG80WWJsSG9MZE9NWlY2MFgzWTN1NG5LVUtOaEprZm9hanhzLTh0US00RUJ0c1FzLXlKNExFbGRjQTdKMDlGc2NlM1RLZmpNVVdYdl9lNENjRVRVN2kwUV8xWUZFTlRYM3BLa2VuUHRidFdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVVFFVENRd2xucFQ3YVR1VUthT3ZmbHg2eFlpanRpU240RFZLaHpmc2w2NG4zeDdDckJhMDRoM0dqVUpHaHRFcE1vempRcmhHSnljZklrY2xVaGU0Y1k0aVhBcFVyNlpZZXJFSS02OC1iWm5FZjBjWGxqOWxWNkJNdEhydjltakxzcW1BeEFmMlBHZldpSGctWDNfWjTSAaIBQVVfeXFMUGI3b2Jld0FzeXdFRWZLcUMxaU16Yk9OQW1EUmRHX3FsNlhTTEZwcDdKbmJZeG5feTh1Y0l2TFNJSjgwbnptcG0zYTlYcGpsVklCYVlYdVAyb25oTnhPckZJU3phMGZDTXBRa2lRa09wN1NpQTFBSWZTLTliU0NvNV84ZXVTeVgwRjRsby1KTlVBV1NCNWtjMFhyNTdVV3hjY3pB?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46022.38743055556</v>
+        <v>46023.28215277778</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City searches  France  French language</t>
+          <t>High Level City searches   Spa